--- a/table/resources/sample/PointsAwardRanking.xlsx
+++ b/table/resources/sample/PointsAwardRanking.xlsx
@@ -125,12 +125,57 @@
         </r>
       </text>
     </comment>
+    <comment ref="G1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+该资源是需要下载的，配置资源名称</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+空值：表示默认读取数据
+有日期：表示对应月份读取数据</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="42">
   <si>
     <t>序列ID</t>
   </si>
@@ -150,6 +195,12 @@
     <t>奖励价值</t>
   </si>
   <si>
+    <t>图片资源</t>
+  </si>
+  <si>
+    <t>开始日期</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -162,6 +213,9 @@
     <t>long</t>
   </si>
   <si>
+    <t>string</t>
+  </si>
+  <si>
     <t>id</t>
   </si>
   <si>
@@ -171,61 +225,82 @@
     <t>ranking</t>
   </si>
   <si>
-    <t>awardtype</t>
-  </si>
-  <si>
-    <t>getitem</t>
+    <t>awardType</t>
+  </si>
+  <si>
+    <t>getItem</t>
   </si>
   <si>
     <t>price</t>
   </si>
   <si>
+    <t>time</t>
+  </si>
+  <si>
     <t>1</t>
   </si>
   <si>
+    <t>其它道具名称1_1</t>
+  </si>
+  <si>
+    <t>icon.png</t>
+  </si>
+  <si>
+    <t>其它道具名称2_1</t>
+  </si>
+  <si>
+    <t>其它道具名称3_1</t>
+  </si>
+  <si>
+    <t>其它道具名称4_1</t>
+  </si>
+  <si>
+    <t>其它道具名称5_1</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>1990000_10000000</t>
+  </si>
+  <si>
+    <t>1990000_9000000</t>
+  </si>
+  <si>
+    <t>1990000_8000000</t>
+  </si>
+  <si>
+    <t>1990000_7000000</t>
+  </si>
+  <si>
+    <t>1990000_6000000</t>
+  </si>
+  <si>
+    <t>11_20</t>
+  </si>
+  <si>
+    <t>1990000_5000000</t>
+  </si>
+  <si>
+    <t>21_30</t>
+  </si>
+  <si>
+    <t>1990000_4000000</t>
+  </si>
+  <si>
+    <t>31_40</t>
+  </si>
+  <si>
+    <t>1990000_3000000</t>
+  </si>
+  <si>
+    <t>41_50</t>
+  </si>
+  <si>
+    <t>1990000_2000000</t>
+  </si>
+  <si>
     <t>Name_1</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>1990000_10000000</t>
-  </si>
-  <si>
-    <t>1990000_9000000</t>
-  </si>
-  <si>
-    <t>1990000_8000000</t>
-  </si>
-  <si>
-    <t>1990000_7000000</t>
-  </si>
-  <si>
-    <t>1990000_6000000</t>
-  </si>
-  <si>
-    <t>11_20</t>
-  </si>
-  <si>
-    <t>1990000_5000000</t>
-  </si>
-  <si>
-    <t>21_30</t>
-  </si>
-  <si>
-    <t>1990000_4000000</t>
-  </si>
-  <si>
-    <t>31_40</t>
-  </si>
-  <si>
-    <t>1990000_3000000</t>
-  </si>
-  <si>
-    <t>41_50</t>
-  </si>
-  <si>
-    <t>1990000_2000000</t>
   </si>
 </sst>
 </file>
@@ -432,7 +507,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -453,19 +528,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.15"/>
+        <fgColor theme="9" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -782,7 +863,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -806,16 +887,16 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -824,89 +905,89 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -952,19 +1033,22 @@
     <xf numFmtId="49" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
@@ -1309,7 +1393,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K49"/>
+  <dimension ref="A1:L88"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="10.375" style="4" customWidth="1"/>
@@ -1318,11 +1402,13 @@
     <col min="4" max="4" width="11.625" style="5" customWidth="1"/>
     <col min="5" max="5" width="21.125" style="4" customWidth="1"/>
     <col min="6" max="6" width="14.5" style="6" customWidth="1"/>
-    <col min="7" max="9" width="14.5" style="7" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="4"/>
+    <col min="7" max="7" width="16.5" style="6" customWidth="1"/>
+    <col min="8" max="8" width="14.5" style="6" customWidth="1"/>
+    <col min="9" max="10" width="14.5" style="7" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:8">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -1341,56 +1427,74 @@
       <c r="F1" s="11" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="8" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="8" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+        <v>18</v>
+      </c>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="8"/>
       <c r="B4" s="8"/>
       <c r="C4" s="9"/>
       <c r="D4" s="9"/>
       <c r="E4" s="8"/>
       <c r="F4" s="11"/>
-    </row>
-    <row r="5" s="2" customFormat="1" spans="1:9">
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+    </row>
+    <row r="5" s="2" customFormat="1" spans="1:10">
       <c r="A5" s="13">
         <v>1</v>
       </c>
@@ -1401,19 +1505,22 @@
         <v>1</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F5" s="13">
         <v>99999999</v>
       </c>
-      <c r="G5" s="15"/>
+      <c r="G5" s="13" t="s">
+        <v>22</v>
+      </c>
       <c r="H5" s="15"/>
-      <c r="I5" s="15"/>
-    </row>
-    <row r="6" s="2" customFormat="1" spans="1:9">
+      <c r="I5" s="20"/>
+      <c r="J5" s="20"/>
+    </row>
+    <row r="6" s="2" customFormat="1" spans="1:10">
       <c r="A6" s="13">
         <v>2</v>
       </c>
@@ -1424,19 +1531,22 @@
         <v>2</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F6" s="13">
         <v>88888888</v>
       </c>
-      <c r="G6" s="15"/>
+      <c r="G6" s="13" t="s">
+        <v>22</v>
+      </c>
       <c r="H6" s="15"/>
-      <c r="I6" s="15"/>
-    </row>
-    <row r="7" s="2" customFormat="1" spans="1:9">
+      <c r="I6" s="20"/>
+      <c r="J6" s="20"/>
+    </row>
+    <row r="7" s="2" customFormat="1" spans="1:10">
       <c r="A7" s="13">
         <v>3</v>
       </c>
@@ -1447,19 +1557,22 @@
         <v>3</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F7" s="13">
         <v>77777777</v>
       </c>
-      <c r="G7" s="15"/>
+      <c r="G7" s="13" t="s">
+        <v>22</v>
+      </c>
       <c r="H7" s="15"/>
-      <c r="I7" s="15"/>
-    </row>
-    <row r="8" s="2" customFormat="1" spans="1:9">
+      <c r="I7" s="20"/>
+      <c r="J7" s="20"/>
+    </row>
+    <row r="8" s="2" customFormat="1" spans="1:10">
       <c r="A8" s="13">
         <v>4</v>
       </c>
@@ -1470,19 +1583,22 @@
         <v>4</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F8" s="13">
         <v>66666666</v>
       </c>
-      <c r="G8" s="15"/>
+      <c r="G8" s="13" t="s">
+        <v>22</v>
+      </c>
       <c r="H8" s="15"/>
-      <c r="I8" s="15"/>
-    </row>
-    <row r="9" s="3" customFormat="1" spans="1:11">
+      <c r="I8" s="20"/>
+      <c r="J8" s="20"/>
+    </row>
+    <row r="9" s="3" customFormat="1" spans="1:12">
       <c r="A9" s="13">
         <v>5</v>
       </c>
@@ -1493,20 +1609,23 @@
         <v>5</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F9" s="13">
         <v>55555555</v>
       </c>
-      <c r="G9" s="15"/>
+      <c r="G9" s="13" t="s">
+        <v>22</v>
+      </c>
       <c r="H9" s="15"/>
       <c r="I9" s="20"/>
-      <c r="K9" s="2"/>
-    </row>
-    <row r="10" s="3" customFormat="1" spans="1:11">
+      <c r="J9" s="21"/>
+      <c r="L9" s="2"/>
+    </row>
+    <row r="10" s="3" customFormat="1" spans="1:12">
       <c r="A10" s="13">
         <v>6</v>
       </c>
@@ -1517,18 +1636,19 @@
         <v>6</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="F10" s="13"/>
-      <c r="G10" s="15"/>
+      <c r="G10" s="13"/>
       <c r="H10" s="15"/>
       <c r="I10" s="20"/>
-      <c r="K10" s="2"/>
-    </row>
-    <row r="11" s="3" customFormat="1" spans="1:11">
+      <c r="J10" s="21"/>
+      <c r="L10" s="2"/>
+    </row>
+    <row r="11" s="3" customFormat="1" spans="1:12">
       <c r="A11" s="13">
         <v>7</v>
       </c>
@@ -1539,18 +1659,19 @@
         <v>7</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F11" s="13"/>
-      <c r="G11" s="15"/>
+      <c r="G11" s="13"/>
       <c r="H11" s="15"/>
       <c r="I11" s="20"/>
-      <c r="K11" s="2"/>
-    </row>
-    <row r="12" s="3" customFormat="1" spans="1:11">
+      <c r="J11" s="21"/>
+      <c r="L11" s="2"/>
+    </row>
+    <row r="12" s="3" customFormat="1" spans="1:12">
       <c r="A12" s="13">
         <v>8</v>
       </c>
@@ -1561,18 +1682,19 @@
         <v>8</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="F12" s="13"/>
-      <c r="G12" s="15"/>
+      <c r="G12" s="13"/>
       <c r="H12" s="15"/>
       <c r="I12" s="20"/>
-      <c r="K12" s="2"/>
-    </row>
-    <row r="13" spans="1:11">
+      <c r="J12" s="21"/>
+      <c r="L12" s="2"/>
+    </row>
+    <row r="13" spans="1:12">
       <c r="A13" s="13">
         <v>9</v>
       </c>
@@ -1583,17 +1705,18 @@
         <v>9</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="F13" s="13"/>
-      <c r="G13" s="15"/>
+      <c r="G13" s="13"/>
       <c r="H13" s="15"/>
-      <c r="K13" s="2"/>
-    </row>
-    <row r="14" spans="1:11">
+      <c r="I13" s="20"/>
+      <c r="L13" s="2"/>
+    </row>
+    <row r="14" spans="1:12">
       <c r="A14" s="13">
         <v>10</v>
       </c>
@@ -1604,17 +1727,18 @@
         <v>10</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F14" s="13"/>
-      <c r="G14" s="15"/>
+      <c r="G14" s="13"/>
       <c r="H14" s="15"/>
-      <c r="K14" s="2"/>
-    </row>
-    <row r="15" customFormat="1" spans="1:11">
+      <c r="I14" s="20"/>
+      <c r="L14" s="2"/>
+    </row>
+    <row r="15" customFormat="1" spans="1:12">
       <c r="A15" s="13">
         <v>11</v>
       </c>
@@ -1622,21 +1746,22 @@
         <v>1</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="F15" s="13"/>
-      <c r="G15" s="15"/>
+      <c r="G15" s="13"/>
       <c r="H15" s="15"/>
-      <c r="I15" s="7"/>
-      <c r="K15" s="2"/>
-    </row>
-    <row r="16" s="3" customFormat="1" spans="1:11">
+      <c r="I15" s="20"/>
+      <c r="J15" s="7"/>
+      <c r="L15" s="2"/>
+    </row>
+    <row r="16" s="3" customFormat="1" spans="1:12">
       <c r="A16" s="13">
         <v>12</v>
       </c>
@@ -1644,21 +1769,22 @@
         <v>1</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F16" s="13"/>
-      <c r="G16" s="15"/>
+      <c r="G16" s="13"/>
       <c r="H16" s="15"/>
       <c r="I16" s="20"/>
-      <c r="K16" s="2"/>
-    </row>
-    <row r="17" s="3" customFormat="1" spans="1:11">
+      <c r="J16" s="21"/>
+      <c r="L16" s="2"/>
+    </row>
+    <row r="17" s="3" customFormat="1" spans="1:12">
       <c r="A17" s="13">
         <v>13</v>
       </c>
@@ -1666,21 +1792,22 @@
         <v>1</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="F17" s="13"/>
-      <c r="G17" s="15"/>
+      <c r="G17" s="13"/>
       <c r="H17" s="15"/>
       <c r="I17" s="20"/>
-      <c r="K17" s="2"/>
-    </row>
-    <row r="18" s="3" customFormat="1" spans="1:11">
+      <c r="J17" s="21"/>
+      <c r="L17" s="2"/>
+    </row>
+    <row r="18" s="3" customFormat="1" spans="1:12">
       <c r="A18" s="13">
         <v>14</v>
       </c>
@@ -1688,609 +1815,1666 @@
         <v>1</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="F18" s="13"/>
-      <c r="G18" s="15"/>
+      <c r="G18" s="13"/>
       <c r="H18" s="15"/>
       <c r="I18" s="20"/>
-      <c r="K18" s="2"/>
-    </row>
-    <row r="19" s="3" customFormat="1" spans="1:11">
-      <c r="A19" s="16">
-        <v>101</v>
-      </c>
-      <c r="B19" s="16">
+      <c r="J18" s="21"/>
+      <c r="L18" s="2"/>
+    </row>
+    <row r="19" s="3" customFormat="1" spans="1:12">
+      <c r="A19" s="13">
+        <v>31</v>
+      </c>
+      <c r="B19" s="13">
         <v>2</v>
       </c>
-      <c r="C19" s="17">
+      <c r="C19" s="14">
         <v>1</v>
       </c>
-      <c r="D19" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="E19" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="F19" s="16">
+      <c r="D19" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="E19" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="F19" s="13">
         <v>99999999</v>
       </c>
-      <c r="G19" s="15"/>
+      <c r="G19" s="13"/>
       <c r="H19" s="15"/>
       <c r="I19" s="20"/>
-      <c r="K19" s="2"/>
-    </row>
-    <row r="20" s="3" customFormat="1" spans="1:11">
-      <c r="A20" s="16">
-        <v>102</v>
-      </c>
-      <c r="B20" s="16">
+      <c r="J19" s="21"/>
+      <c r="L19" s="2"/>
+    </row>
+    <row r="20" s="3" customFormat="1" spans="1:12">
+      <c r="A20" s="13">
+        <v>32</v>
+      </c>
+      <c r="B20" s="13">
         <v>2</v>
       </c>
-      <c r="C20" s="17">
+      <c r="C20" s="14">
         <v>2</v>
       </c>
-      <c r="D20" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="E20" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="F20" s="16">
+      <c r="D20" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="F20" s="13">
         <v>88888888</v>
       </c>
-      <c r="G20" s="15"/>
+      <c r="G20" s="13"/>
       <c r="H20" s="15"/>
-      <c r="I20" s="15"/>
-      <c r="K20" s="2"/>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21" s="16">
-        <v>103</v>
-      </c>
-      <c r="B21" s="16">
+      <c r="I20" s="20"/>
+      <c r="J20" s="20"/>
+      <c r="L20" s="2"/>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" s="13">
+        <v>33</v>
+      </c>
+      <c r="B21" s="13">
         <v>2</v>
       </c>
-      <c r="C21" s="17">
+      <c r="C21" s="14">
         <v>3</v>
       </c>
-      <c r="D21" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="E21" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="F21" s="16">
+      <c r="D21" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="E21" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="F21" s="13">
         <v>77777777</v>
       </c>
-    </row>
-    <row r="22" s="3" customFormat="1" spans="1:9">
-      <c r="A22" s="16">
-        <v>104</v>
-      </c>
-      <c r="B22" s="16">
+      <c r="G21" s="13"/>
+      <c r="H21" s="16"/>
+    </row>
+    <row r="22" s="3" customFormat="1" spans="1:10">
+      <c r="A22" s="13">
+        <v>34</v>
+      </c>
+      <c r="B22" s="13">
         <v>2</v>
       </c>
-      <c r="C22" s="17">
+      <c r="C22" s="14">
         <v>4</v>
       </c>
-      <c r="D22" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="E22" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="F22" s="16">
+      <c r="D22" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="F22" s="13">
         <v>66666666</v>
       </c>
-      <c r="G22" s="15"/>
+      <c r="G22" s="13"/>
       <c r="H22" s="15"/>
       <c r="I22" s="20"/>
-    </row>
-    <row r="23" s="3" customFormat="1" spans="1:9">
-      <c r="A23" s="16">
-        <v>105</v>
-      </c>
-      <c r="B23" s="16">
+      <c r="J22" s="21"/>
+    </row>
+    <row r="23" s="3" customFormat="1" spans="1:10">
+      <c r="A23" s="13">
+        <v>35</v>
+      </c>
+      <c r="B23" s="13">
         <v>2</v>
       </c>
-      <c r="C23" s="17">
+      <c r="C23" s="14">
         <v>5</v>
       </c>
-      <c r="D23" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="E23" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="F23" s="16">
+      <c r="D23" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="F23" s="13">
         <v>55555555</v>
       </c>
-      <c r="G23" s="15"/>
+      <c r="G23" s="13"/>
       <c r="H23" s="15"/>
       <c r="I23" s="20"/>
-    </row>
-    <row r="24" s="3" customFormat="1" spans="1:9">
-      <c r="A24" s="16">
-        <v>106</v>
-      </c>
-      <c r="B24" s="16">
+      <c r="J23" s="21"/>
+    </row>
+    <row r="24" s="3" customFormat="1" spans="1:10">
+      <c r="A24" s="13">
+        <v>36</v>
+      </c>
+      <c r="B24" s="13">
         <v>2</v>
       </c>
-      <c r="C24" s="17">
+      <c r="C24" s="14">
         <v>6</v>
       </c>
-      <c r="D24" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="E24" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="F24" s="16"/>
-      <c r="G24" s="15"/>
+      <c r="D24" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="E24" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="F24" s="13"/>
+      <c r="G24" s="13"/>
       <c r="H24" s="15"/>
       <c r="I24" s="20"/>
-    </row>
-    <row r="25" s="3" customFormat="1" spans="1:9">
-      <c r="A25" s="16">
-        <v>107</v>
-      </c>
-      <c r="B25" s="16">
+      <c r="J24" s="21"/>
+    </row>
+    <row r="25" s="3" customFormat="1" spans="1:10">
+      <c r="A25" s="13">
+        <v>37</v>
+      </c>
+      <c r="B25" s="13">
         <v>2</v>
       </c>
-      <c r="C25" s="17">
+      <c r="C25" s="14">
         <v>7</v>
       </c>
-      <c r="D25" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="E25" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="F25" s="16"/>
-      <c r="G25" s="15"/>
+      <c r="D25" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F25" s="13"/>
+      <c r="G25" s="13"/>
       <c r="H25" s="15"/>
       <c r="I25" s="20"/>
-    </row>
-    <row r="26" s="3" customFormat="1" spans="1:9">
-      <c r="A26" s="16">
+      <c r="J25" s="21"/>
+    </row>
+    <row r="26" s="3" customFormat="1" spans="1:10">
+      <c r="A26" s="13">
+        <v>38</v>
+      </c>
+      <c r="B26" s="13">
+        <v>2</v>
+      </c>
+      <c r="C26" s="14">
+        <v>8</v>
+      </c>
+      <c r="D26" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="E26" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F26" s="13"/>
+      <c r="G26" s="13"/>
+      <c r="H26" s="15"/>
+      <c r="I26" s="20"/>
+      <c r="J26" s="20"/>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" s="13">
+        <v>39</v>
+      </c>
+      <c r="B27" s="13">
+        <v>2</v>
+      </c>
+      <c r="C27" s="14">
+        <v>9</v>
+      </c>
+      <c r="D27" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="F27" s="13"/>
+      <c r="G27" s="13"/>
+      <c r="H27" s="15"/>
+      <c r="I27" s="20"/>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" s="13">
+        <v>40</v>
+      </c>
+      <c r="B28" s="13">
+        <v>2</v>
+      </c>
+      <c r="C28" s="14">
+        <v>10</v>
+      </c>
+      <c r="D28" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="F28" s="13"/>
+      <c r="G28" s="13"/>
+      <c r="H28" s="15"/>
+      <c r="I28" s="20"/>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" s="13">
+        <v>41</v>
+      </c>
+      <c r="B29" s="13">
+        <v>2</v>
+      </c>
+      <c r="C29" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="D29" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="F29" s="13"/>
+      <c r="G29" s="13"/>
+      <c r="H29" s="15"/>
+      <c r="I29" s="20"/>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" s="13">
+        <v>42</v>
+      </c>
+      <c r="B30" s="13">
+        <v>2</v>
+      </c>
+      <c r="C30" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="D30" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="F30" s="13"/>
+      <c r="G30" s="13"/>
+      <c r="H30" s="15"/>
+      <c r="I30" s="20"/>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" s="13">
+        <v>43</v>
+      </c>
+      <c r="B31" s="13">
+        <v>2</v>
+      </c>
+      <c r="C31" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="D31" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="F31" s="13"/>
+      <c r="G31" s="13"/>
+      <c r="H31" s="15"/>
+      <c r="I31" s="20"/>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" s="13">
+        <v>44</v>
+      </c>
+      <c r="B32" s="13">
+        <v>2</v>
+      </c>
+      <c r="C32" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="D32" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="E32" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="F32" s="13"/>
+      <c r="G32" s="13"/>
+      <c r="H32" s="15"/>
+      <c r="I32" s="20"/>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" s="13">
+        <v>61</v>
+      </c>
+      <c r="B33" s="13">
+        <v>3</v>
+      </c>
+      <c r="C33" s="14">
+        <v>1</v>
+      </c>
+      <c r="D33" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="F33" s="13">
+        <v>99999999</v>
+      </c>
+      <c r="G33" s="13"/>
+      <c r="H33" s="15"/>
+      <c r="I33" s="20"/>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" s="13">
+        <v>62</v>
+      </c>
+      <c r="B34" s="13">
+        <v>3</v>
+      </c>
+      <c r="C34" s="14">
+        <v>2</v>
+      </c>
+      <c r="D34" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="E34" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="F34" s="13">
+        <v>88888888</v>
+      </c>
+      <c r="G34" s="13"/>
+      <c r="H34" s="15"/>
+      <c r="I34" s="20"/>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" s="13">
+        <v>63</v>
+      </c>
+      <c r="B35" s="13">
+        <v>3</v>
+      </c>
+      <c r="C35" s="14">
+        <v>3</v>
+      </c>
+      <c r="D35" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="E35" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="F35" s="13">
+        <v>77777777</v>
+      </c>
+      <c r="G35" s="13"/>
+      <c r="H35" s="15"/>
+      <c r="I35" s="20"/>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" s="13">
+        <v>64</v>
+      </c>
+      <c r="B36" s="13">
+        <v>3</v>
+      </c>
+      <c r="C36" s="14">
+        <v>4</v>
+      </c>
+      <c r="D36" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="E36" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="F36" s="13">
+        <v>66666666</v>
+      </c>
+      <c r="G36" s="13"/>
+      <c r="H36" s="15"/>
+      <c r="I36" s="20"/>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" s="13">
+        <v>65</v>
+      </c>
+      <c r="B37" s="13">
+        <v>3</v>
+      </c>
+      <c r="C37" s="14">
+        <v>5</v>
+      </c>
+      <c r="D37" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="E37" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="F37" s="13">
+        <v>55555555</v>
+      </c>
+      <c r="G37" s="13"/>
+      <c r="H37" s="15"/>
+      <c r="I37" s="20"/>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" s="13">
+        <v>66</v>
+      </c>
+      <c r="B38" s="13">
+        <v>3</v>
+      </c>
+      <c r="C38" s="14">
+        <v>6</v>
+      </c>
+      <c r="D38" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="E38" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="F38" s="13"/>
+      <c r="G38" s="13"/>
+      <c r="H38" s="15"/>
+      <c r="I38" s="20"/>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" s="13">
+        <v>67</v>
+      </c>
+      <c r="B39" s="13">
+        <v>3</v>
+      </c>
+      <c r="C39" s="14">
+        <v>7</v>
+      </c>
+      <c r="D39" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="E39" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F39" s="13"/>
+      <c r="G39" s="13"/>
+      <c r="H39" s="15"/>
+      <c r="I39" s="20"/>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" s="13">
+        <v>68</v>
+      </c>
+      <c r="B40" s="13">
+        <v>3</v>
+      </c>
+      <c r="C40" s="14">
+        <v>8</v>
+      </c>
+      <c r="D40" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="E40" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F40" s="13"/>
+      <c r="G40" s="13"/>
+      <c r="H40" s="15"/>
+      <c r="I40" s="20"/>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41" s="13">
+        <v>69</v>
+      </c>
+      <c r="B41" s="13">
+        <v>3</v>
+      </c>
+      <c r="C41" s="14">
+        <v>9</v>
+      </c>
+      <c r="D41" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="E41" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="F41" s="13"/>
+      <c r="G41" s="13"/>
+      <c r="H41" s="15"/>
+      <c r="I41" s="20"/>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42" s="13">
+        <v>70</v>
+      </c>
+      <c r="B42" s="13">
+        <v>3</v>
+      </c>
+      <c r="C42" s="14">
+        <v>10</v>
+      </c>
+      <c r="D42" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="E42" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="F42" s="13"/>
+      <c r="G42" s="13"/>
+      <c r="H42" s="15"/>
+      <c r="I42" s="20"/>
+    </row>
+    <row r="43" spans="1:9">
+      <c r="A43" s="13">
+        <v>71</v>
+      </c>
+      <c r="B43" s="13">
+        <v>3</v>
+      </c>
+      <c r="C43" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="D43" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="E43" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="F43" s="13"/>
+      <c r="G43" s="13"/>
+      <c r="H43" s="15"/>
+      <c r="I43" s="20"/>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" s="13">
+        <v>72</v>
+      </c>
+      <c r="B44" s="13">
+        <v>3</v>
+      </c>
+      <c r="C44" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="D44" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="E44" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="F44" s="13"/>
+      <c r="G44" s="13"/>
+      <c r="H44" s="16"/>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45" s="13">
+        <v>73</v>
+      </c>
+      <c r="B45" s="13">
+        <v>3</v>
+      </c>
+      <c r="C45" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="D45" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="E45" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="F45" s="13"/>
+      <c r="G45" s="13"/>
+      <c r="H45" s="16"/>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" s="13">
+        <v>74</v>
+      </c>
+      <c r="B46" s="13">
+        <v>3</v>
+      </c>
+      <c r="C46" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="D46" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="E46" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="F46" s="13"/>
+      <c r="G46" s="13"/>
+      <c r="H46" s="16"/>
+    </row>
+    <row r="47" s="2" customFormat="1" spans="1:10">
+      <c r="A47" s="17">
+        <v>101</v>
+      </c>
+      <c r="B47" s="17">
+        <v>1</v>
+      </c>
+      <c r="C47" s="18">
+        <v>1</v>
+      </c>
+      <c r="D47" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="E47" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="F47" s="17">
+        <v>99999999</v>
+      </c>
+      <c r="G47" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H47" s="19">
+        <v>45931</v>
+      </c>
+      <c r="I47" s="20"/>
+      <c r="J47" s="20"/>
+    </row>
+    <row r="48" s="2" customFormat="1" spans="1:10">
+      <c r="A48" s="17">
+        <v>102</v>
+      </c>
+      <c r="B48" s="17">
+        <v>1</v>
+      </c>
+      <c r="C48" s="18">
+        <v>2</v>
+      </c>
+      <c r="D48" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="E48" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="F48" s="17">
+        <v>88888888</v>
+      </c>
+      <c r="G48" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H48" s="19">
+        <v>45931</v>
+      </c>
+      <c r="I48" s="20"/>
+      <c r="J48" s="20"/>
+    </row>
+    <row r="49" s="2" customFormat="1" spans="1:10">
+      <c r="A49" s="17">
+        <v>103</v>
+      </c>
+      <c r="B49" s="17">
+        <v>1</v>
+      </c>
+      <c r="C49" s="18">
+        <v>3</v>
+      </c>
+      <c r="D49" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="E49" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="F49" s="17">
+        <v>77777777</v>
+      </c>
+      <c r="G49" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H49" s="19">
+        <v>45931</v>
+      </c>
+      <c r="I49" s="20"/>
+      <c r="J49" s="20"/>
+    </row>
+    <row r="50" s="2" customFormat="1" spans="1:10">
+      <c r="A50" s="17">
+        <v>104</v>
+      </c>
+      <c r="B50" s="17">
+        <v>1</v>
+      </c>
+      <c r="C50" s="18">
+        <v>4</v>
+      </c>
+      <c r="D50" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="E50" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="F50" s="17">
+        <v>66666666</v>
+      </c>
+      <c r="G50" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H50" s="19">
+        <v>45931</v>
+      </c>
+      <c r="I50" s="20"/>
+      <c r="J50" s="20"/>
+    </row>
+    <row r="51" s="3" customFormat="1" spans="1:12">
+      <c r="A51" s="17">
+        <v>105</v>
+      </c>
+      <c r="B51" s="17">
+        <v>1</v>
+      </c>
+      <c r="C51" s="18">
+        <v>5</v>
+      </c>
+      <c r="D51" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="E51" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="F51" s="17">
+        <v>55555555</v>
+      </c>
+      <c r="G51" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H51" s="19">
+        <v>45931</v>
+      </c>
+      <c r="I51" s="20"/>
+      <c r="J51" s="21"/>
+      <c r="L51" s="2"/>
+    </row>
+    <row r="52" s="3" customFormat="1" spans="1:12">
+      <c r="A52" s="17">
+        <v>106</v>
+      </c>
+      <c r="B52" s="17">
+        <v>1</v>
+      </c>
+      <c r="C52" s="18">
+        <v>6</v>
+      </c>
+      <c r="D52" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="E52" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="F52" s="17"/>
+      <c r="G52" s="17"/>
+      <c r="H52" s="19">
+        <v>45931</v>
+      </c>
+      <c r="I52" s="20"/>
+      <c r="J52" s="21"/>
+      <c r="L52" s="2"/>
+    </row>
+    <row r="53" s="3" customFormat="1" spans="1:12">
+      <c r="A53" s="17">
+        <v>107</v>
+      </c>
+      <c r="B53" s="17">
+        <v>1</v>
+      </c>
+      <c r="C53" s="18">
+        <v>7</v>
+      </c>
+      <c r="D53" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="E53" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="F53" s="17"/>
+      <c r="G53" s="17"/>
+      <c r="H53" s="19">
+        <v>45931</v>
+      </c>
+      <c r="I53" s="20"/>
+      <c r="J53" s="21"/>
+      <c r="L53" s="2"/>
+    </row>
+    <row r="54" s="3" customFormat="1" spans="1:12">
+      <c r="A54" s="17">
         <v>108</v>
       </c>
-      <c r="B26" s="16">
+      <c r="B54" s="17">
+        <v>1</v>
+      </c>
+      <c r="C54" s="18">
+        <v>8</v>
+      </c>
+      <c r="D54" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="E54" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="F54" s="17"/>
+      <c r="G54" s="17"/>
+      <c r="H54" s="19">
+        <v>45931</v>
+      </c>
+      <c r="I54" s="20"/>
+      <c r="J54" s="21"/>
+      <c r="L54" s="2"/>
+    </row>
+    <row r="55" spans="1:12">
+      <c r="A55" s="17">
+        <v>109</v>
+      </c>
+      <c r="B55" s="17">
+        <v>1</v>
+      </c>
+      <c r="C55" s="18">
+        <v>9</v>
+      </c>
+      <c r="D55" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="E55" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="F55" s="17"/>
+      <c r="G55" s="17"/>
+      <c r="H55" s="19">
+        <v>45931</v>
+      </c>
+      <c r="I55" s="20"/>
+      <c r="L55" s="2"/>
+    </row>
+    <row r="56" spans="1:12">
+      <c r="A56" s="17">
+        <v>110</v>
+      </c>
+      <c r="B56" s="17">
+        <v>1</v>
+      </c>
+      <c r="C56" s="18">
+        <v>10</v>
+      </c>
+      <c r="D56" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="E56" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="F56" s="17"/>
+      <c r="G56" s="17"/>
+      <c r="H56" s="19">
+        <v>45931</v>
+      </c>
+      <c r="I56" s="20"/>
+      <c r="L56" s="2"/>
+    </row>
+    <row r="57" customFormat="1" spans="1:12">
+      <c r="A57" s="17">
+        <v>111</v>
+      </c>
+      <c r="B57" s="17">
+        <v>1</v>
+      </c>
+      <c r="C57" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="D57" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="E57" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="F57" s="17"/>
+      <c r="G57" s="17"/>
+      <c r="H57" s="19">
+        <v>45931</v>
+      </c>
+      <c r="I57" s="20"/>
+      <c r="J57" s="7"/>
+      <c r="L57" s="2"/>
+    </row>
+    <row r="58" s="3" customFormat="1" spans="1:12">
+      <c r="A58" s="17">
+        <v>112</v>
+      </c>
+      <c r="B58" s="17">
+        <v>1</v>
+      </c>
+      <c r="C58" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="D58" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="E58" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="F58" s="17"/>
+      <c r="G58" s="17"/>
+      <c r="H58" s="19">
+        <v>45931</v>
+      </c>
+      <c r="I58" s="20"/>
+      <c r="J58" s="21"/>
+      <c r="L58" s="2"/>
+    </row>
+    <row r="59" s="3" customFormat="1" spans="1:12">
+      <c r="A59" s="17">
+        <v>113</v>
+      </c>
+      <c r="B59" s="17">
+        <v>1</v>
+      </c>
+      <c r="C59" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="D59" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="E59" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="F59" s="17"/>
+      <c r="G59" s="17"/>
+      <c r="H59" s="19">
+        <v>45931</v>
+      </c>
+      <c r="I59" s="20"/>
+      <c r="J59" s="21"/>
+      <c r="L59" s="2"/>
+    </row>
+    <row r="60" s="3" customFormat="1" spans="1:12">
+      <c r="A60" s="17">
+        <v>114</v>
+      </c>
+      <c r="B60" s="17">
+        <v>1</v>
+      </c>
+      <c r="C60" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D60" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="E60" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="F60" s="17"/>
+      <c r="G60" s="17"/>
+      <c r="H60" s="19">
+        <v>45931</v>
+      </c>
+      <c r="I60" s="20"/>
+      <c r="J60" s="21"/>
+      <c r="L60" s="2"/>
+    </row>
+    <row r="61" s="3" customFormat="1" spans="1:12">
+      <c r="A61" s="17">
+        <v>131</v>
+      </c>
+      <c r="B61" s="17">
         <v>2</v>
       </c>
-      <c r="C26" s="17">
+      <c r="C61" s="18">
+        <v>1</v>
+      </c>
+      <c r="D61" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="E61" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="F61" s="17">
+        <v>99999999</v>
+      </c>
+      <c r="G61" s="17"/>
+      <c r="H61" s="19">
+        <v>45931</v>
+      </c>
+      <c r="I61" s="20"/>
+      <c r="J61" s="21"/>
+      <c r="L61" s="2"/>
+    </row>
+    <row r="62" s="3" customFormat="1" spans="1:12">
+      <c r="A62" s="17">
+        <v>132</v>
+      </c>
+      <c r="B62" s="17">
+        <v>2</v>
+      </c>
+      <c r="C62" s="18">
+        <v>2</v>
+      </c>
+      <c r="D62" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="E62" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="F62" s="17">
+        <v>88888888</v>
+      </c>
+      <c r="G62" s="17"/>
+      <c r="H62" s="19">
+        <v>45931</v>
+      </c>
+      <c r="I62" s="20"/>
+      <c r="J62" s="20"/>
+      <c r="L62" s="2"/>
+    </row>
+    <row r="63" spans="1:8">
+      <c r="A63" s="17">
+        <v>133</v>
+      </c>
+      <c r="B63" s="17">
+        <v>2</v>
+      </c>
+      <c r="C63" s="18">
+        <v>3</v>
+      </c>
+      <c r="D63" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="E63" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="F63" s="17">
+        <v>77777777</v>
+      </c>
+      <c r="G63" s="17"/>
+      <c r="H63" s="19">
+        <v>45931</v>
+      </c>
+    </row>
+    <row r="64" s="3" customFormat="1" spans="1:10">
+      <c r="A64" s="17">
+        <v>134</v>
+      </c>
+      <c r="B64" s="17">
+        <v>2</v>
+      </c>
+      <c r="C64" s="18">
+        <v>4</v>
+      </c>
+      <c r="D64" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="E64" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="F64" s="17">
+        <v>66666666</v>
+      </c>
+      <c r="G64" s="17"/>
+      <c r="H64" s="19">
+        <v>45931</v>
+      </c>
+      <c r="I64" s="20"/>
+      <c r="J64" s="21"/>
+    </row>
+    <row r="65" s="3" customFormat="1" spans="1:10">
+      <c r="A65" s="17">
+        <v>135</v>
+      </c>
+      <c r="B65" s="17">
+        <v>2</v>
+      </c>
+      <c r="C65" s="18">
+        <v>5</v>
+      </c>
+      <c r="D65" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="E65" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="F65" s="17">
+        <v>55555555</v>
+      </c>
+      <c r="G65" s="17"/>
+      <c r="H65" s="19">
+        <v>45931</v>
+      </c>
+      <c r="I65" s="20"/>
+      <c r="J65" s="21"/>
+    </row>
+    <row r="66" s="3" customFormat="1" spans="1:10">
+      <c r="A66" s="17">
+        <v>136</v>
+      </c>
+      <c r="B66" s="17">
+        <v>2</v>
+      </c>
+      <c r="C66" s="18">
+        <v>6</v>
+      </c>
+      <c r="D66" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="E66" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="F66" s="17"/>
+      <c r="G66" s="17"/>
+      <c r="H66" s="19">
+        <v>45931</v>
+      </c>
+      <c r="I66" s="20"/>
+      <c r="J66" s="21"/>
+    </row>
+    <row r="67" s="3" customFormat="1" spans="1:10">
+      <c r="A67" s="17">
+        <v>137</v>
+      </c>
+      <c r="B67" s="17">
+        <v>2</v>
+      </c>
+      <c r="C67" s="18">
+        <v>7</v>
+      </c>
+      <c r="D67" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="E67" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="F67" s="17"/>
+      <c r="G67" s="17"/>
+      <c r="H67" s="19">
+        <v>45931</v>
+      </c>
+      <c r="I67" s="20"/>
+      <c r="J67" s="21"/>
+    </row>
+    <row r="68" s="3" customFormat="1" spans="1:10">
+      <c r="A68" s="17">
+        <v>138</v>
+      </c>
+      <c r="B68" s="17">
+        <v>2</v>
+      </c>
+      <c r="C68" s="18">
         <v>8</v>
       </c>
-      <c r="D26" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="E26" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="F26" s="16"/>
-      <c r="G26" s="15"/>
-      <c r="H26" s="15"/>
-      <c r="I26" s="15"/>
-    </row>
-    <row r="27" spans="1:8">
-      <c r="A27" s="16">
-        <v>109</v>
-      </c>
-      <c r="B27" s="16">
+      <c r="D68" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="E68" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="F68" s="17"/>
+      <c r="G68" s="17"/>
+      <c r="H68" s="19">
+        <v>45931</v>
+      </c>
+      <c r="I68" s="20"/>
+      <c r="J68" s="20"/>
+    </row>
+    <row r="69" spans="1:9">
+      <c r="A69" s="17">
+        <v>139</v>
+      </c>
+      <c r="B69" s="17">
         <v>2</v>
       </c>
-      <c r="C27" s="17">
+      <c r="C69" s="18">
         <v>9</v>
       </c>
-      <c r="D27" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="E27" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="F27" s="16"/>
-      <c r="G27" s="15"/>
-      <c r="H27" s="15"/>
-    </row>
-    <row r="28" spans="1:8">
-      <c r="A28" s="16">
-        <v>110</v>
-      </c>
-      <c r="B28" s="16">
+      <c r="D69" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="E69" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="F69" s="17"/>
+      <c r="G69" s="17"/>
+      <c r="H69" s="19">
+        <v>45931</v>
+      </c>
+      <c r="I69" s="20"/>
+    </row>
+    <row r="70" spans="1:9">
+      <c r="A70" s="17">
+        <v>140</v>
+      </c>
+      <c r="B70" s="17">
         <v>2</v>
       </c>
-      <c r="C28" s="17">
+      <c r="C70" s="18">
         <v>10</v>
       </c>
-      <c r="D28" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="E28" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="F28" s="16"/>
-      <c r="G28" s="15"/>
-      <c r="H28" s="15"/>
-    </row>
-    <row r="29" spans="1:8">
-      <c r="A29" s="16">
-        <v>111</v>
-      </c>
-      <c r="B29" s="16">
+      <c r="D70" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="E70" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="F70" s="17"/>
+      <c r="G70" s="17"/>
+      <c r="H70" s="19">
+        <v>45931</v>
+      </c>
+      <c r="I70" s="20"/>
+    </row>
+    <row r="71" spans="1:9">
+      <c r="A71" s="17">
+        <v>141</v>
+      </c>
+      <c r="B71" s="17">
         <v>2</v>
       </c>
-      <c r="C29" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="D29" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="E29" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="F29" s="16"/>
-      <c r="G29" s="15"/>
-      <c r="H29" s="15"/>
-    </row>
-    <row r="30" spans="1:8">
-      <c r="A30" s="16">
-        <v>112</v>
-      </c>
-      <c r="B30" s="16">
+      <c r="C71" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="D71" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="E71" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="F71" s="17"/>
+      <c r="G71" s="17"/>
+      <c r="H71" s="19">
+        <v>45931</v>
+      </c>
+      <c r="I71" s="20"/>
+    </row>
+    <row r="72" spans="1:9">
+      <c r="A72" s="17">
+        <v>142</v>
+      </c>
+      <c r="B72" s="17">
         <v>2</v>
       </c>
-      <c r="C30" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="D30" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="E30" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="F30" s="16"/>
-      <c r="G30" s="15"/>
-      <c r="H30" s="15"/>
-    </row>
-    <row r="31" spans="1:8">
-      <c r="A31" s="16">
-        <v>113</v>
-      </c>
-      <c r="B31" s="16">
+      <c r="C72" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="D72" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="E72" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="F72" s="17"/>
+      <c r="G72" s="17"/>
+      <c r="H72" s="19">
+        <v>45931</v>
+      </c>
+      <c r="I72" s="20"/>
+    </row>
+    <row r="73" spans="1:9">
+      <c r="A73" s="17">
+        <v>143</v>
+      </c>
+      <c r="B73" s="17">
         <v>2</v>
       </c>
-      <c r="C31" s="17" t="s">
+      <c r="C73" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="D73" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="E73" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="F73" s="17"/>
+      <c r="G73" s="17"/>
+      <c r="H73" s="19">
+        <v>45931</v>
+      </c>
+      <c r="I73" s="20"/>
+    </row>
+    <row r="74" spans="1:9">
+      <c r="A74" s="17">
+        <v>144</v>
+      </c>
+      <c r="B74" s="17">
+        <v>2</v>
+      </c>
+      <c r="C74" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D74" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="E74" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="F74" s="17"/>
+      <c r="G74" s="17"/>
+      <c r="H74" s="19">
+        <v>45931</v>
+      </c>
+      <c r="I74" s="20"/>
+    </row>
+    <row r="75" spans="1:9">
+      <c r="A75" s="17">
+        <v>161</v>
+      </c>
+      <c r="B75" s="17">
+        <v>3</v>
+      </c>
+      <c r="C75" s="18">
+        <v>1</v>
+      </c>
+      <c r="D75" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="E75" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="F75" s="17">
+        <v>99999999</v>
+      </c>
+      <c r="G75" s="17"/>
+      <c r="H75" s="19">
+        <v>45931</v>
+      </c>
+      <c r="I75" s="20"/>
+    </row>
+    <row r="76" spans="1:9">
+      <c r="A76" s="17">
+        <v>162</v>
+      </c>
+      <c r="B76" s="17">
+        <v>3</v>
+      </c>
+      <c r="C76" s="18">
+        <v>2</v>
+      </c>
+      <c r="D76" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="E76" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="F76" s="17">
+        <v>88888888</v>
+      </c>
+      <c r="G76" s="17"/>
+      <c r="H76" s="19">
+        <v>45931</v>
+      </c>
+      <c r="I76" s="20"/>
+    </row>
+    <row r="77" spans="1:9">
+      <c r="A77" s="17">
+        <v>163</v>
+      </c>
+      <c r="B77" s="17">
+        <v>3</v>
+      </c>
+      <c r="C77" s="18">
+        <v>3</v>
+      </c>
+      <c r="D77" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="E77" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="F77" s="17">
+        <v>77777777</v>
+      </c>
+      <c r="G77" s="17"/>
+      <c r="H77" s="19">
+        <v>45931</v>
+      </c>
+      <c r="I77" s="20"/>
+    </row>
+    <row r="78" spans="1:9">
+      <c r="A78" s="17">
+        <v>164</v>
+      </c>
+      <c r="B78" s="17">
+        <v>3</v>
+      </c>
+      <c r="C78" s="18">
+        <v>4</v>
+      </c>
+      <c r="D78" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="E78" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="F78" s="17">
+        <v>66666666</v>
+      </c>
+      <c r="G78" s="17"/>
+      <c r="H78" s="19">
+        <v>45931</v>
+      </c>
+      <c r="I78" s="20"/>
+    </row>
+    <row r="79" spans="1:9">
+      <c r="A79" s="17">
+        <v>165</v>
+      </c>
+      <c r="B79" s="17">
+        <v>3</v>
+      </c>
+      <c r="C79" s="18">
+        <v>5</v>
+      </c>
+      <c r="D79" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="E79" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="F79" s="17">
+        <v>55555555</v>
+      </c>
+      <c r="G79" s="17"/>
+      <c r="H79" s="19">
+        <v>45931</v>
+      </c>
+      <c r="I79" s="20"/>
+    </row>
+    <row r="80" spans="1:9">
+      <c r="A80" s="17">
+        <v>166</v>
+      </c>
+      <c r="B80" s="17">
+        <v>3</v>
+      </c>
+      <c r="C80" s="18">
+        <v>6</v>
+      </c>
+      <c r="D80" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="E80" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="D31" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="E31" s="16" t="s">
+      <c r="F80" s="17"/>
+      <c r="G80" s="17"/>
+      <c r="H80" s="19">
+        <v>45931</v>
+      </c>
+      <c r="I80" s="20"/>
+    </row>
+    <row r="81" spans="1:9">
+      <c r="A81" s="17">
+        <v>167</v>
+      </c>
+      <c r="B81" s="17">
+        <v>3</v>
+      </c>
+      <c r="C81" s="18">
+        <v>7</v>
+      </c>
+      <c r="D81" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="E81" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="F31" s="16"/>
-      <c r="G31" s="15"/>
-      <c r="H31" s="15"/>
-    </row>
-    <row r="32" spans="1:8">
-      <c r="A32" s="16">
-        <v>114</v>
-      </c>
-      <c r="B32" s="16">
-        <v>2</v>
-      </c>
-      <c r="C32" s="17" t="s">
+      <c r="F81" s="17"/>
+      <c r="G81" s="17"/>
+      <c r="H81" s="19">
+        <v>45931</v>
+      </c>
+      <c r="I81" s="20"/>
+    </row>
+    <row r="82" spans="1:9">
+      <c r="A82" s="17">
+        <v>168</v>
+      </c>
+      <c r="B82" s="17">
+        <v>3</v>
+      </c>
+      <c r="C82" s="18">
+        <v>8</v>
+      </c>
+      <c r="D82" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="E82" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="D32" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="E32" s="16" t="s">
+      <c r="F82" s="17"/>
+      <c r="G82" s="17"/>
+      <c r="H82" s="19">
+        <v>45931</v>
+      </c>
+      <c r="I82" s="20"/>
+    </row>
+    <row r="83" spans="1:9">
+      <c r="A83" s="17">
+        <v>169</v>
+      </c>
+      <c r="B83" s="17">
+        <v>3</v>
+      </c>
+      <c r="C83" s="18">
+        <v>9</v>
+      </c>
+      <c r="D83" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="E83" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="F32" s="16"/>
-      <c r="G32" s="15"/>
-      <c r="H32" s="15"/>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33" s="18">
-        <v>201</v>
-      </c>
-      <c r="B33" s="18">
+      <c r="F83" s="17"/>
+      <c r="G83" s="17"/>
+      <c r="H83" s="19">
+        <v>45931</v>
+      </c>
+      <c r="I83" s="20"/>
+    </row>
+    <row r="84" spans="1:9">
+      <c r="A84" s="17">
+        <v>170</v>
+      </c>
+      <c r="B84" s="17">
         <v>3</v>
       </c>
-      <c r="C33" s="19">
-        <v>1</v>
-      </c>
-      <c r="D33" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="E33" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="F33" s="18">
-        <v>99999999</v>
-      </c>
-      <c r="G33" s="15"/>
-      <c r="H33" s="15"/>
-    </row>
-    <row r="34" spans="1:8">
-      <c r="A34" s="18">
-        <v>202</v>
-      </c>
-      <c r="B34" s="18">
+      <c r="C84" s="18">
+        <v>10</v>
+      </c>
+      <c r="D84" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="E84" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="F84" s="17"/>
+      <c r="G84" s="17"/>
+      <c r="H84" s="19">
+        <v>45931</v>
+      </c>
+      <c r="I84" s="20"/>
+    </row>
+    <row r="85" spans="1:9">
+      <c r="A85" s="17">
+        <v>171</v>
+      </c>
+      <c r="B85" s="17">
         <v>3</v>
       </c>
-      <c r="C34" s="19">
-        <v>2</v>
-      </c>
-      <c r="D34" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="E34" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="F34" s="18">
-        <v>88888888</v>
-      </c>
-      <c r="G34" s="15"/>
-      <c r="H34" s="15"/>
-    </row>
-    <row r="35" spans="1:8">
-      <c r="A35" s="18">
-        <v>203</v>
-      </c>
-      <c r="B35" s="18">
+      <c r="C85" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="D85" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="E85" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="F85" s="17"/>
+      <c r="G85" s="17"/>
+      <c r="H85" s="19">
+        <v>45931</v>
+      </c>
+      <c r="I85" s="20"/>
+    </row>
+    <row r="86" spans="1:8">
+      <c r="A86" s="17">
+        <v>172</v>
+      </c>
+      <c r="B86" s="17">
         <v>3</v>
       </c>
-      <c r="C35" s="19">
+      <c r="C86" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="D86" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="E86" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="F86" s="17"/>
+      <c r="G86" s="17"/>
+      <c r="H86" s="19">
+        <v>45931</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8">
+      <c r="A87" s="17">
+        <v>173</v>
+      </c>
+      <c r="B87" s="17">
         <v>3</v>
       </c>
-      <c r="D35" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="E35" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="F35" s="18">
-        <v>77777777</v>
-      </c>
-      <c r="G35" s="15"/>
-      <c r="H35" s="15"/>
-    </row>
-    <row r="36" spans="1:8">
-      <c r="A36" s="18">
-        <v>204</v>
-      </c>
-      <c r="B36" s="18">
+      <c r="C87" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="D87" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="E87" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="F87" s="17"/>
+      <c r="G87" s="17"/>
+      <c r="H87" s="19">
+        <v>45931</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8">
+      <c r="A88" s="17">
+        <v>174</v>
+      </c>
+      <c r="B88" s="17">
         <v>3</v>
       </c>
-      <c r="C36" s="19">
-        <v>4</v>
-      </c>
-      <c r="D36" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="E36" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="F36" s="18">
-        <v>66666666</v>
-      </c>
-      <c r="G36" s="15"/>
-      <c r="H36" s="15"/>
-    </row>
-    <row r="37" spans="1:8">
-      <c r="A37" s="18">
-        <v>205</v>
-      </c>
-      <c r="B37" s="18">
-        <v>3</v>
-      </c>
-      <c r="C37" s="19">
-        <v>5</v>
-      </c>
-      <c r="D37" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="E37" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="F37" s="18">
-        <v>55555555</v>
-      </c>
-      <c r="G37" s="15"/>
-      <c r="H37" s="15"/>
-    </row>
-    <row r="38" spans="1:8">
-      <c r="A38" s="18">
-        <v>206</v>
-      </c>
-      <c r="B38" s="18">
-        <v>3</v>
-      </c>
-      <c r="C38" s="19">
-        <v>6</v>
-      </c>
-      <c r="D38" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="E38" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="F38" s="18"/>
-      <c r="G38" s="15"/>
-      <c r="H38" s="15"/>
-    </row>
-    <row r="39" spans="1:8">
-      <c r="A39" s="18">
-        <v>207</v>
-      </c>
-      <c r="B39" s="18">
-        <v>3</v>
-      </c>
-      <c r="C39" s="19">
-        <v>7</v>
-      </c>
-      <c r="D39" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="E39" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="F39" s="18"/>
-      <c r="G39" s="15"/>
-      <c r="H39" s="15"/>
-    </row>
-    <row r="40" spans="1:8">
-      <c r="A40" s="18">
-        <v>208</v>
-      </c>
-      <c r="B40" s="18">
-        <v>3</v>
-      </c>
-      <c r="C40" s="19">
-        <v>8</v>
-      </c>
-      <c r="D40" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="E40" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="F40" s="18"/>
-      <c r="G40" s="15"/>
-      <c r="H40" s="15"/>
-    </row>
-    <row r="41" spans="1:8">
-      <c r="A41" s="18">
-        <v>209</v>
-      </c>
-      <c r="B41" s="18">
-        <v>3</v>
-      </c>
-      <c r="C41" s="19">
-        <v>9</v>
-      </c>
-      <c r="D41" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="E41" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="F41" s="18"/>
-      <c r="G41" s="15"/>
-      <c r="H41" s="15"/>
-    </row>
-    <row r="42" spans="1:8">
-      <c r="A42" s="18">
-        <v>210</v>
-      </c>
-      <c r="B42" s="18">
-        <v>3</v>
-      </c>
-      <c r="C42" s="19">
-        <v>10</v>
-      </c>
-      <c r="D42" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="E42" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="F42" s="18"/>
-      <c r="G42" s="15"/>
-      <c r="H42" s="15"/>
-    </row>
-    <row r="43" spans="1:8">
-      <c r="A43" s="18">
-        <v>211</v>
-      </c>
-      <c r="B43" s="18">
-        <v>3</v>
-      </c>
-      <c r="C43" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="D43" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="E43" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="F43" s="18"/>
-      <c r="G43" s="15"/>
-      <c r="H43" s="15"/>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44" s="18">
-        <v>212</v>
-      </c>
-      <c r="B44" s="18">
-        <v>3</v>
-      </c>
-      <c r="C44" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="D44" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="E44" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="F44" s="18"/>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45" s="18">
-        <v>213</v>
-      </c>
-      <c r="B45" s="18">
-        <v>3</v>
-      </c>
-      <c r="C45" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="D45" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="E45" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="F45" s="18"/>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46" s="18">
-        <v>214</v>
-      </c>
-      <c r="B46" s="18">
-        <v>3</v>
-      </c>
-      <c r="C46" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="D46" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="E46" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="F46" s="18"/>
-    </row>
-    <row r="47" spans="5:5">
-      <c r="E47" s="2"/>
-    </row>
-    <row r="48" spans="5:5">
-      <c r="E48" s="2"/>
-    </row>
-    <row r="49" spans="5:5">
-      <c r="E49" s="2"/>
+      <c r="C88" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D88" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="E88" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="F88" s="17"/>
+      <c r="G88" s="17"/>
+      <c r="H88" s="19">
+        <v>45931</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/table/resources/sample/PointsAwardRanking.xlsx
+++ b/table/resources/sample/PointsAwardRanking.xlsx
@@ -175,7 +175,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="43">
   <si>
     <t>序列ID</t>
   </si>
@@ -189,7 +189,7 @@
     <t>奖励类型</t>
   </si>
   <si>
-    <t>排名奖励</t>
+    <t>排名道具奖励</t>
   </si>
   <si>
     <t>奖励价值</t>
@@ -301,6 +301,9 @@
   </si>
   <si>
     <t>Name_1</t>
+  </si>
+  <si>
+    <t>2025/10/01 00:00:00</t>
   </si>
 </sst>
 </file>
@@ -507,7 +510,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="38">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -529,18 +532,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -863,7 +854,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -887,16 +878,16 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -905,89 +896,89 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1009,6 +1000,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -1022,6 +1016,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1036,16 +1033,7 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+    <xf numFmtId="49" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
@@ -1403,1044 +1391,1044 @@
     <col min="5" max="5" width="21.125" style="4" customWidth="1"/>
     <col min="6" max="6" width="14.5" style="6" customWidth="1"/>
     <col min="7" max="7" width="16.5" style="6" customWidth="1"/>
-    <col min="8" max="8" width="14.5" style="6" customWidth="1"/>
-    <col min="9" max="10" width="14.5" style="7" customWidth="1"/>
+    <col min="8" max="8" width="21.25" style="7" customWidth="1"/>
+    <col min="9" max="10" width="14.5" style="8" customWidth="1"/>
     <col min="11" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="10" t="s">
+      <c r="B1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="13" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="G2" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="11" t="s">
+      <c r="H2" s="13" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="11"/>
-      <c r="H3" s="11" t="s">
+      <c r="G3" s="12"/>
+      <c r="H3" s="13" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="11"/>
+      <c r="A4" s="9"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="13"/>
     </row>
     <row r="5" s="2" customFormat="1" spans="1:10">
-      <c r="A5" s="13">
-        <v>1</v>
-      </c>
-      <c r="B5" s="13">
-        <v>1</v>
-      </c>
-      <c r="C5" s="14">
-        <v>1</v>
-      </c>
-      <c r="D5" s="14" t="s">
+      <c r="A5" s="15">
+        <v>1</v>
+      </c>
+      <c r="B5" s="15">
+        <v>1</v>
+      </c>
+      <c r="C5" s="16">
+        <v>1</v>
+      </c>
+      <c r="D5" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="15">
         <v>99999999</v>
       </c>
-      <c r="G5" s="13" t="s">
+      <c r="G5" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="H5" s="15"/>
-      <c r="I5" s="20"/>
-      <c r="J5" s="20"/>
+      <c r="H5" s="16"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="19"/>
     </row>
     <row r="6" s="2" customFormat="1" spans="1:10">
-      <c r="A6" s="13">
-        <v>2</v>
-      </c>
-      <c r="B6" s="13">
-        <v>1</v>
-      </c>
-      <c r="C6" s="14">
-        <v>2</v>
-      </c>
-      <c r="D6" s="14" t="s">
+      <c r="A6" s="15">
+        <v>2</v>
+      </c>
+      <c r="B6" s="15">
+        <v>1</v>
+      </c>
+      <c r="C6" s="16">
+        <v>2</v>
+      </c>
+      <c r="D6" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="E6" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="15">
         <v>88888888</v>
       </c>
-      <c r="G6" s="13" t="s">
+      <c r="G6" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="H6" s="15"/>
-      <c r="I6" s="20"/>
-      <c r="J6" s="20"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="19"/>
+      <c r="J6" s="19"/>
     </row>
     <row r="7" s="2" customFormat="1" spans="1:10">
-      <c r="A7" s="13">
-        <v>3</v>
-      </c>
-      <c r="B7" s="13">
-        <v>1</v>
-      </c>
-      <c r="C7" s="14">
-        <v>3</v>
-      </c>
-      <c r="D7" s="14" t="s">
+      <c r="A7" s="15">
+        <v>3</v>
+      </c>
+      <c r="B7" s="15">
+        <v>1</v>
+      </c>
+      <c r="C7" s="16">
+        <v>3</v>
+      </c>
+      <c r="D7" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="F7" s="13">
+      <c r="F7" s="15">
         <v>77777777</v>
       </c>
-      <c r="G7" s="13" t="s">
+      <c r="G7" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="H7" s="15"/>
-      <c r="I7" s="20"/>
-      <c r="J7" s="20"/>
+      <c r="H7" s="16"/>
+      <c r="I7" s="19"/>
+      <c r="J7" s="19"/>
     </row>
     <row r="8" s="2" customFormat="1" spans="1:10">
-      <c r="A8" s="13">
+      <c r="A8" s="15">
         <v>4</v>
       </c>
-      <c r="B8" s="13">
-        <v>1</v>
-      </c>
-      <c r="C8" s="14">
+      <c r="B8" s="15">
+        <v>1</v>
+      </c>
+      <c r="C8" s="16">
         <v>4</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="D8" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="13" t="s">
+      <c r="E8" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="15">
         <v>66666666</v>
       </c>
-      <c r="G8" s="13" t="s">
+      <c r="G8" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="H8" s="15"/>
-      <c r="I8" s="20"/>
-      <c r="J8" s="20"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="19"/>
+      <c r="J8" s="19"/>
     </row>
     <row r="9" s="3" customFormat="1" spans="1:12">
-      <c r="A9" s="13">
+      <c r="A9" s="15">
         <v>5</v>
       </c>
-      <c r="B9" s="13">
-        <v>1</v>
-      </c>
-      <c r="C9" s="14">
+      <c r="B9" s="15">
+        <v>1</v>
+      </c>
+      <c r="C9" s="16">
         <v>5</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="D9" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="13" t="s">
+      <c r="E9" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="15">
         <v>55555555</v>
       </c>
-      <c r="G9" s="13" t="s">
+      <c r="G9" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="H9" s="15"/>
-      <c r="I9" s="20"/>
-      <c r="J9" s="21"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="20"/>
       <c r="L9" s="2"/>
     </row>
     <row r="10" s="3" customFormat="1" spans="1:12">
-      <c r="A10" s="13">
+      <c r="A10" s="15">
         <v>6</v>
       </c>
-      <c r="B10" s="13">
-        <v>1</v>
-      </c>
-      <c r="C10" s="14">
+      <c r="B10" s="15">
+        <v>1</v>
+      </c>
+      <c r="C10" s="16">
         <v>6</v>
       </c>
-      <c r="D10" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="E10" s="13" t="s">
+      <c r="D10" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="15"/>
-      <c r="I10" s="20"/>
-      <c r="J10" s="21"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="20"/>
       <c r="L10" s="2"/>
     </row>
     <row r="11" s="3" customFormat="1" spans="1:12">
-      <c r="A11" s="13">
+      <c r="A11" s="15">
         <v>7</v>
       </c>
-      <c r="B11" s="13">
-        <v>1</v>
-      </c>
-      <c r="C11" s="14">
+      <c r="B11" s="15">
+        <v>1</v>
+      </c>
+      <c r="C11" s="16">
         <v>7</v>
       </c>
-      <c r="D11" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="E11" s="13" t="s">
+      <c r="D11" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="15"/>
-      <c r="I11" s="20"/>
-      <c r="J11" s="21"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="15"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="20"/>
       <c r="L11" s="2"/>
     </row>
     <row r="12" s="3" customFormat="1" spans="1:12">
-      <c r="A12" s="13">
+      <c r="A12" s="15">
         <v>8</v>
       </c>
-      <c r="B12" s="13">
-        <v>1</v>
-      </c>
-      <c r="C12" s="14">
+      <c r="B12" s="15">
+        <v>1</v>
+      </c>
+      <c r="C12" s="16">
         <v>8</v>
       </c>
-      <c r="D12" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="E12" s="13" t="s">
+      <c r="D12" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
-      <c r="H12" s="15"/>
-      <c r="I12" s="20"/>
-      <c r="J12" s="21"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="20"/>
       <c r="L12" s="2"/>
     </row>
     <row r="13" spans="1:12">
-      <c r="A13" s="13">
+      <c r="A13" s="15">
         <v>9</v>
       </c>
-      <c r="B13" s="13">
-        <v>1</v>
-      </c>
-      <c r="C13" s="14">
+      <c r="B13" s="15">
+        <v>1</v>
+      </c>
+      <c r="C13" s="16">
         <v>9</v>
       </c>
-      <c r="D13" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="E13" s="13" t="s">
+      <c r="D13" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="15"/>
-      <c r="I13" s="20"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="16"/>
+      <c r="I13" s="19"/>
       <c r="L13" s="2"/>
     </row>
     <row r="14" spans="1:12">
-      <c r="A14" s="13">
+      <c r="A14" s="15">
         <v>10</v>
       </c>
-      <c r="B14" s="13">
-        <v>1</v>
-      </c>
-      <c r="C14" s="14">
+      <c r="B14" s="15">
+        <v>1</v>
+      </c>
+      <c r="C14" s="16">
         <v>10</v>
       </c>
-      <c r="D14" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="E14" s="13" t="s">
+      <c r="D14" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E14" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="15"/>
-      <c r="I14" s="20"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="19"/>
       <c r="L14" s="2"/>
     </row>
     <row r="15" customFormat="1" spans="1:12">
-      <c r="A15" s="13">
+      <c r="A15" s="15">
         <v>11</v>
       </c>
-      <c r="B15" s="13">
-        <v>1</v>
-      </c>
-      <c r="C15" s="14" t="s">
+      <c r="B15" s="15">
+        <v>1</v>
+      </c>
+      <c r="C15" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="D15" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="E15" s="13" t="s">
+      <c r="D15" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="15"/>
-      <c r="I15" s="20"/>
-      <c r="J15" s="7"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="16"/>
+      <c r="I15" s="19"/>
+      <c r="J15" s="8"/>
       <c r="L15" s="2"/>
     </row>
     <row r="16" s="3" customFormat="1" spans="1:12">
-      <c r="A16" s="13">
+      <c r="A16" s="15">
         <v>12</v>
       </c>
-      <c r="B16" s="13">
-        <v>1</v>
-      </c>
-      <c r="C16" s="14" t="s">
+      <c r="B16" s="15">
+        <v>1</v>
+      </c>
+      <c r="C16" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="D16" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="E16" s="13" t="s">
+      <c r="D16" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="F16" s="13"/>
-      <c r="G16" s="13"/>
-      <c r="H16" s="15"/>
-      <c r="I16" s="20"/>
-      <c r="J16" s="21"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="15"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="19"/>
+      <c r="J16" s="20"/>
       <c r="L16" s="2"/>
     </row>
     <row r="17" s="3" customFormat="1" spans="1:12">
-      <c r="A17" s="13">
+      <c r="A17" s="15">
         <v>13</v>
       </c>
-      <c r="B17" s="13">
-        <v>1</v>
-      </c>
-      <c r="C17" s="14" t="s">
+      <c r="B17" s="15">
+        <v>1</v>
+      </c>
+      <c r="C17" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="D17" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="E17" s="13" t="s">
+      <c r="D17" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="15"/>
-      <c r="I17" s="20"/>
-      <c r="J17" s="21"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="16"/>
+      <c r="I17" s="19"/>
+      <c r="J17" s="20"/>
       <c r="L17" s="2"/>
     </row>
     <row r="18" s="3" customFormat="1" spans="1:12">
-      <c r="A18" s="13">
+      <c r="A18" s="15">
         <v>14</v>
       </c>
-      <c r="B18" s="13">
-        <v>1</v>
-      </c>
-      <c r="C18" s="14" t="s">
+      <c r="B18" s="15">
+        <v>1</v>
+      </c>
+      <c r="C18" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="D18" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="E18" s="13" t="s">
+      <c r="D18" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E18" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="15"/>
-      <c r="I18" s="20"/>
-      <c r="J18" s="21"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="15"/>
+      <c r="H18" s="16"/>
+      <c r="I18" s="19"/>
+      <c r="J18" s="20"/>
       <c r="L18" s="2"/>
     </row>
     <row r="19" s="3" customFormat="1" spans="1:12">
-      <c r="A19" s="13">
+      <c r="A19" s="15">
         <v>31</v>
       </c>
-      <c r="B19" s="13">
-        <v>2</v>
-      </c>
-      <c r="C19" s="14">
-        <v>1</v>
-      </c>
-      <c r="D19" s="14" t="s">
+      <c r="B19" s="15">
+        <v>2</v>
+      </c>
+      <c r="C19" s="16">
+        <v>1</v>
+      </c>
+      <c r="D19" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="E19" s="13" t="s">
+      <c r="E19" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="F19" s="13">
+      <c r="F19" s="15">
         <v>99999999</v>
       </c>
-      <c r="G19" s="13"/>
-      <c r="H19" s="15"/>
-      <c r="I19" s="20"/>
-      <c r="J19" s="21"/>
+      <c r="G19" s="15"/>
+      <c r="H19" s="16"/>
+      <c r="I19" s="19"/>
+      <c r="J19" s="20"/>
       <c r="L19" s="2"/>
     </row>
     <row r="20" s="3" customFormat="1" spans="1:12">
-      <c r="A20" s="13">
+      <c r="A20" s="15">
         <v>32</v>
       </c>
-      <c r="B20" s="13">
-        <v>2</v>
-      </c>
-      <c r="C20" s="14">
-        <v>2</v>
-      </c>
-      <c r="D20" s="14" t="s">
+      <c r="B20" s="15">
+        <v>2</v>
+      </c>
+      <c r="C20" s="16">
+        <v>2</v>
+      </c>
+      <c r="D20" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="E20" s="13" t="s">
+      <c r="E20" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="F20" s="13">
+      <c r="F20" s="15">
         <v>88888888</v>
       </c>
-      <c r="G20" s="13"/>
-      <c r="H20" s="15"/>
-      <c r="I20" s="20"/>
-      <c r="J20" s="20"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="16"/>
+      <c r="I20" s="19"/>
+      <c r="J20" s="19"/>
       <c r="L20" s="2"/>
     </row>
     <row r="21" spans="1:8">
-      <c r="A21" s="13">
+      <c r="A21" s="15">
         <v>33</v>
       </c>
-      <c r="B21" s="13">
-        <v>2</v>
-      </c>
-      <c r="C21" s="14">
-        <v>3</v>
-      </c>
-      <c r="D21" s="14" t="s">
+      <c r="B21" s="15">
+        <v>2</v>
+      </c>
+      <c r="C21" s="16">
+        <v>3</v>
+      </c>
+      <c r="D21" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="E21" s="13" t="s">
+      <c r="E21" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="F21" s="13">
+      <c r="F21" s="15">
         <v>77777777</v>
       </c>
-      <c r="G21" s="13"/>
+      <c r="G21" s="15"/>
       <c r="H21" s="16"/>
     </row>
     <row r="22" s="3" customFormat="1" spans="1:10">
-      <c r="A22" s="13">
+      <c r="A22" s="15">
         <v>34</v>
       </c>
-      <c r="B22" s="13">
-        <v>2</v>
-      </c>
-      <c r="C22" s="14">
+      <c r="B22" s="15">
+        <v>2</v>
+      </c>
+      <c r="C22" s="16">
         <v>4</v>
       </c>
-      <c r="D22" s="14" t="s">
+      <c r="D22" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="E22" s="13" t="s">
+      <c r="E22" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="F22" s="13">
+      <c r="F22" s="15">
         <v>66666666</v>
       </c>
-      <c r="G22" s="13"/>
-      <c r="H22" s="15"/>
-      <c r="I22" s="20"/>
-      <c r="J22" s="21"/>
+      <c r="G22" s="15"/>
+      <c r="H22" s="16"/>
+      <c r="I22" s="19"/>
+      <c r="J22" s="20"/>
     </row>
     <row r="23" s="3" customFormat="1" spans="1:10">
-      <c r="A23" s="13">
+      <c r="A23" s="15">
         <v>35</v>
       </c>
-      <c r="B23" s="13">
-        <v>2</v>
-      </c>
-      <c r="C23" s="14">
+      <c r="B23" s="15">
+        <v>2</v>
+      </c>
+      <c r="C23" s="16">
         <v>5</v>
       </c>
-      <c r="D23" s="14" t="s">
+      <c r="D23" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="E23" s="13" t="s">
+      <c r="E23" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="F23" s="13">
+      <c r="F23" s="15">
         <v>55555555</v>
       </c>
-      <c r="G23" s="13"/>
-      <c r="H23" s="15"/>
-      <c r="I23" s="20"/>
-      <c r="J23" s="21"/>
+      <c r="G23" s="15"/>
+      <c r="H23" s="16"/>
+      <c r="I23" s="19"/>
+      <c r="J23" s="20"/>
     </row>
     <row r="24" s="3" customFormat="1" spans="1:10">
-      <c r="A24" s="13">
+      <c r="A24" s="15">
         <v>36</v>
       </c>
-      <c r="B24" s="13">
-        <v>2</v>
-      </c>
-      <c r="C24" s="14">
+      <c r="B24" s="15">
+        <v>2</v>
+      </c>
+      <c r="C24" s="16">
         <v>6</v>
       </c>
-      <c r="D24" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="E24" s="13" t="s">
+      <c r="D24" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E24" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
-      <c r="H24" s="15"/>
-      <c r="I24" s="20"/>
-      <c r="J24" s="21"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="15"/>
+      <c r="H24" s="16"/>
+      <c r="I24" s="19"/>
+      <c r="J24" s="20"/>
     </row>
     <row r="25" s="3" customFormat="1" spans="1:10">
-      <c r="A25" s="13">
+      <c r="A25" s="15">
         <v>37</v>
       </c>
-      <c r="B25" s="13">
-        <v>2</v>
-      </c>
-      <c r="C25" s="14">
+      <c r="B25" s="15">
+        <v>2</v>
+      </c>
+      <c r="C25" s="16">
         <v>7</v>
       </c>
-      <c r="D25" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="E25" s="13" t="s">
+      <c r="D25" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E25" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="F25" s="13"/>
-      <c r="G25" s="13"/>
-      <c r="H25" s="15"/>
-      <c r="I25" s="20"/>
-      <c r="J25" s="21"/>
+      <c r="F25" s="15"/>
+      <c r="G25" s="15"/>
+      <c r="H25" s="16"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="20"/>
     </row>
     <row r="26" s="3" customFormat="1" spans="1:10">
-      <c r="A26" s="13">
+      <c r="A26" s="15">
         <v>38</v>
       </c>
-      <c r="B26" s="13">
-        <v>2</v>
-      </c>
-      <c r="C26" s="14">
+      <c r="B26" s="15">
+        <v>2</v>
+      </c>
+      <c r="C26" s="16">
         <v>8</v>
       </c>
-      <c r="D26" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="E26" s="13" t="s">
+      <c r="D26" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E26" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
-      <c r="H26" s="15"/>
-      <c r="I26" s="20"/>
-      <c r="J26" s="20"/>
+      <c r="F26" s="15"/>
+      <c r="G26" s="15"/>
+      <c r="H26" s="16"/>
+      <c r="I26" s="19"/>
+      <c r="J26" s="19"/>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="13">
+      <c r="A27" s="15">
         <v>39</v>
       </c>
-      <c r="B27" s="13">
-        <v>2</v>
-      </c>
-      <c r="C27" s="14">
+      <c r="B27" s="15">
+        <v>2</v>
+      </c>
+      <c r="C27" s="16">
         <v>9</v>
       </c>
-      <c r="D27" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="E27" s="13" t="s">
+      <c r="D27" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E27" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="F27" s="13"/>
-      <c r="G27" s="13"/>
-      <c r="H27" s="15"/>
-      <c r="I27" s="20"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="15"/>
+      <c r="H27" s="16"/>
+      <c r="I27" s="19"/>
     </row>
     <row r="28" spans="1:9">
-      <c r="A28" s="13">
+      <c r="A28" s="15">
         <v>40</v>
       </c>
-      <c r="B28" s="13">
-        <v>2</v>
-      </c>
-      <c r="C28" s="14">
+      <c r="B28" s="15">
+        <v>2</v>
+      </c>
+      <c r="C28" s="16">
         <v>10</v>
       </c>
-      <c r="D28" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="E28" s="13" t="s">
+      <c r="D28" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E28" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="F28" s="13"/>
-      <c r="G28" s="13"/>
-      <c r="H28" s="15"/>
-      <c r="I28" s="20"/>
+      <c r="F28" s="15"/>
+      <c r="G28" s="15"/>
+      <c r="H28" s="16"/>
+      <c r="I28" s="19"/>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29" s="13">
+      <c r="A29" s="15">
         <v>41</v>
       </c>
-      <c r="B29" s="13">
-        <v>2</v>
-      </c>
-      <c r="C29" s="14" t="s">
+      <c r="B29" s="15">
+        <v>2</v>
+      </c>
+      <c r="C29" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="D29" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="E29" s="13" t="s">
+      <c r="D29" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E29" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="F29" s="13"/>
-      <c r="G29" s="13"/>
-      <c r="H29" s="15"/>
-      <c r="I29" s="20"/>
+      <c r="F29" s="15"/>
+      <c r="G29" s="15"/>
+      <c r="H29" s="16"/>
+      <c r="I29" s="19"/>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" s="13">
-        <v>42</v>
-      </c>
-      <c r="B30" s="13">
-        <v>2</v>
-      </c>
-      <c r="C30" s="14" t="s">
+      <c r="A30" s="15">
+        <v>42</v>
+      </c>
+      <c r="B30" s="15">
+        <v>2</v>
+      </c>
+      <c r="C30" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="D30" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="E30" s="13" t="s">
+      <c r="D30" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E30" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="F30" s="13"/>
-      <c r="G30" s="13"/>
-      <c r="H30" s="15"/>
-      <c r="I30" s="20"/>
+      <c r="F30" s="15"/>
+      <c r="G30" s="15"/>
+      <c r="H30" s="16"/>
+      <c r="I30" s="19"/>
     </row>
     <row r="31" spans="1:9">
-      <c r="A31" s="13">
+      <c r="A31" s="15">
         <v>43</v>
       </c>
-      <c r="B31" s="13">
-        <v>2</v>
-      </c>
-      <c r="C31" s="14" t="s">
+      <c r="B31" s="15">
+        <v>2</v>
+      </c>
+      <c r="C31" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="D31" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="E31" s="13" t="s">
+      <c r="D31" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E31" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="F31" s="13"/>
-      <c r="G31" s="13"/>
-      <c r="H31" s="15"/>
-      <c r="I31" s="20"/>
+      <c r="F31" s="15"/>
+      <c r="G31" s="15"/>
+      <c r="H31" s="16"/>
+      <c r="I31" s="19"/>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" s="13">
+      <c r="A32" s="15">
         <v>44</v>
       </c>
-      <c r="B32" s="13">
-        <v>2</v>
-      </c>
-      <c r="C32" s="14" t="s">
+      <c r="B32" s="15">
+        <v>2</v>
+      </c>
+      <c r="C32" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="D32" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="E32" s="13" t="s">
+      <c r="D32" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E32" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="F32" s="13"/>
-      <c r="G32" s="13"/>
-      <c r="H32" s="15"/>
-      <c r="I32" s="20"/>
+      <c r="F32" s="15"/>
+      <c r="G32" s="15"/>
+      <c r="H32" s="16"/>
+      <c r="I32" s="19"/>
     </row>
     <row r="33" spans="1:9">
-      <c r="A33" s="13">
+      <c r="A33" s="15">
         <v>61</v>
       </c>
-      <c r="B33" s="13">
-        <v>3</v>
-      </c>
-      <c r="C33" s="14">
-        <v>1</v>
-      </c>
-      <c r="D33" s="14" t="s">
+      <c r="B33" s="15">
+        <v>3</v>
+      </c>
+      <c r="C33" s="16">
+        <v>1</v>
+      </c>
+      <c r="D33" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="13" t="s">
+      <c r="E33" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="F33" s="13">
+      <c r="F33" s="15">
         <v>99999999</v>
       </c>
-      <c r="G33" s="13"/>
-      <c r="H33" s="15"/>
-      <c r="I33" s="20"/>
+      <c r="G33" s="15"/>
+      <c r="H33" s="16"/>
+      <c r="I33" s="19"/>
     </row>
     <row r="34" spans="1:9">
-      <c r="A34" s="13">
+      <c r="A34" s="15">
         <v>62</v>
       </c>
-      <c r="B34" s="13">
-        <v>3</v>
-      </c>
-      <c r="C34" s="14">
-        <v>2</v>
-      </c>
-      <c r="D34" s="14" t="s">
+      <c r="B34" s="15">
+        <v>3</v>
+      </c>
+      <c r="C34" s="16">
+        <v>2</v>
+      </c>
+      <c r="D34" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="E34" s="13" t="s">
+      <c r="E34" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="F34" s="13">
+      <c r="F34" s="15">
         <v>88888888</v>
       </c>
-      <c r="G34" s="13"/>
-      <c r="H34" s="15"/>
-      <c r="I34" s="20"/>
+      <c r="G34" s="15"/>
+      <c r="H34" s="16"/>
+      <c r="I34" s="19"/>
     </row>
     <row r="35" spans="1:9">
-      <c r="A35" s="13">
+      <c r="A35" s="15">
         <v>63</v>
       </c>
-      <c r="B35" s="13">
-        <v>3</v>
-      </c>
-      <c r="C35" s="14">
-        <v>3</v>
-      </c>
-      <c r="D35" s="14" t="s">
+      <c r="B35" s="15">
+        <v>3</v>
+      </c>
+      <c r="C35" s="16">
+        <v>3</v>
+      </c>
+      <c r="D35" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="E35" s="13" t="s">
+      <c r="E35" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="F35" s="13">
+      <c r="F35" s="15">
         <v>77777777</v>
       </c>
-      <c r="G35" s="13"/>
-      <c r="H35" s="15"/>
-      <c r="I35" s="20"/>
+      <c r="G35" s="15"/>
+      <c r="H35" s="16"/>
+      <c r="I35" s="19"/>
     </row>
     <row r="36" spans="1:9">
-      <c r="A36" s="13">
+      <c r="A36" s="15">
         <v>64</v>
       </c>
-      <c r="B36" s="13">
-        <v>3</v>
-      </c>
-      <c r="C36" s="14">
+      <c r="B36" s="15">
+        <v>3</v>
+      </c>
+      <c r="C36" s="16">
         <v>4</v>
       </c>
-      <c r="D36" s="14" t="s">
+      <c r="D36" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="E36" s="13" t="s">
+      <c r="E36" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="F36" s="13">
+      <c r="F36" s="15">
         <v>66666666</v>
       </c>
-      <c r="G36" s="13"/>
-      <c r="H36" s="15"/>
-      <c r="I36" s="20"/>
+      <c r="G36" s="15"/>
+      <c r="H36" s="16"/>
+      <c r="I36" s="19"/>
     </row>
     <row r="37" spans="1:9">
-      <c r="A37" s="13">
+      <c r="A37" s="15">
         <v>65</v>
       </c>
-      <c r="B37" s="13">
-        <v>3</v>
-      </c>
-      <c r="C37" s="14">
+      <c r="B37" s="15">
+        <v>3</v>
+      </c>
+      <c r="C37" s="16">
         <v>5</v>
       </c>
-      <c r="D37" s="14" t="s">
+      <c r="D37" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="E37" s="13" t="s">
+      <c r="E37" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="F37" s="13">
+      <c r="F37" s="15">
         <v>55555555</v>
       </c>
-      <c r="G37" s="13"/>
-      <c r="H37" s="15"/>
-      <c r="I37" s="20"/>
+      <c r="G37" s="15"/>
+      <c r="H37" s="16"/>
+      <c r="I37" s="19"/>
     </row>
     <row r="38" spans="1:9">
-      <c r="A38" s="13">
+      <c r="A38" s="15">
         <v>66</v>
       </c>
-      <c r="B38" s="13">
-        <v>3</v>
-      </c>
-      <c r="C38" s="14">
+      <c r="B38" s="15">
+        <v>3</v>
+      </c>
+      <c r="C38" s="16">
         <v>6</v>
       </c>
-      <c r="D38" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="E38" s="13" t="s">
+      <c r="D38" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E38" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="F38" s="13"/>
-      <c r="G38" s="13"/>
-      <c r="H38" s="15"/>
-      <c r="I38" s="20"/>
+      <c r="F38" s="15"/>
+      <c r="G38" s="15"/>
+      <c r="H38" s="16"/>
+      <c r="I38" s="19"/>
     </row>
     <row r="39" spans="1:9">
-      <c r="A39" s="13">
+      <c r="A39" s="15">
         <v>67</v>
       </c>
-      <c r="B39" s="13">
-        <v>3</v>
-      </c>
-      <c r="C39" s="14">
+      <c r="B39" s="15">
+        <v>3</v>
+      </c>
+      <c r="C39" s="16">
         <v>7</v>
       </c>
-      <c r="D39" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="E39" s="13" t="s">
+      <c r="D39" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E39" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="F39" s="13"/>
-      <c r="G39" s="13"/>
-      <c r="H39" s="15"/>
-      <c r="I39" s="20"/>
+      <c r="F39" s="15"/>
+      <c r="G39" s="15"/>
+      <c r="H39" s="16"/>
+      <c r="I39" s="19"/>
     </row>
     <row r="40" spans="1:9">
-      <c r="A40" s="13">
+      <c r="A40" s="15">
         <v>68</v>
       </c>
-      <c r="B40" s="13">
-        <v>3</v>
-      </c>
-      <c r="C40" s="14">
+      <c r="B40" s="15">
+        <v>3</v>
+      </c>
+      <c r="C40" s="16">
         <v>8</v>
       </c>
-      <c r="D40" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="E40" s="13" t="s">
+      <c r="D40" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E40" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="F40" s="13"/>
-      <c r="G40" s="13"/>
-      <c r="H40" s="15"/>
-      <c r="I40" s="20"/>
+      <c r="F40" s="15"/>
+      <c r="G40" s="15"/>
+      <c r="H40" s="16"/>
+      <c r="I40" s="19"/>
     </row>
     <row r="41" spans="1:9">
-      <c r="A41" s="13">
+      <c r="A41" s="15">
         <v>69</v>
       </c>
-      <c r="B41" s="13">
-        <v>3</v>
-      </c>
-      <c r="C41" s="14">
+      <c r="B41" s="15">
+        <v>3</v>
+      </c>
+      <c r="C41" s="16">
         <v>9</v>
       </c>
-      <c r="D41" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="E41" s="13" t="s">
+      <c r="D41" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E41" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="F41" s="13"/>
-      <c r="G41" s="13"/>
-      <c r="H41" s="15"/>
-      <c r="I41" s="20"/>
+      <c r="F41" s="15"/>
+      <c r="G41" s="15"/>
+      <c r="H41" s="16"/>
+      <c r="I41" s="19"/>
     </row>
     <row r="42" spans="1:9">
-      <c r="A42" s="13">
+      <c r="A42" s="15">
         <v>70</v>
       </c>
-      <c r="B42" s="13">
-        <v>3</v>
-      </c>
-      <c r="C42" s="14">
+      <c r="B42" s="15">
+        <v>3</v>
+      </c>
+      <c r="C42" s="16">
         <v>10</v>
       </c>
-      <c r="D42" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="E42" s="13" t="s">
+      <c r="D42" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E42" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="F42" s="13"/>
-      <c r="G42" s="13"/>
-      <c r="H42" s="15"/>
-      <c r="I42" s="20"/>
+      <c r="F42" s="15"/>
+      <c r="G42" s="15"/>
+      <c r="H42" s="16"/>
+      <c r="I42" s="19"/>
     </row>
     <row r="43" spans="1:9">
-      <c r="A43" s="13">
+      <c r="A43" s="15">
         <v>71</v>
       </c>
-      <c r="B43" s="13">
-        <v>3</v>
-      </c>
-      <c r="C43" s="14" t="s">
+      <c r="B43" s="15">
+        <v>3</v>
+      </c>
+      <c r="C43" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="D43" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="E43" s="13" t="s">
+      <c r="D43" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E43" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="F43" s="13"/>
-      <c r="G43" s="13"/>
-      <c r="H43" s="15"/>
-      <c r="I43" s="20"/>
+      <c r="F43" s="15"/>
+      <c r="G43" s="15"/>
+      <c r="H43" s="16"/>
+      <c r="I43" s="19"/>
     </row>
     <row r="44" spans="1:8">
-      <c r="A44" s="13">
+      <c r="A44" s="15">
         <v>72</v>
       </c>
-      <c r="B44" s="13">
-        <v>3</v>
-      </c>
-      <c r="C44" s="14" t="s">
+      <c r="B44" s="15">
+        <v>3</v>
+      </c>
+      <c r="C44" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="D44" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="E44" s="13" t="s">
+      <c r="D44" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E44" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="F44" s="13"/>
-      <c r="G44" s="13"/>
+      <c r="F44" s="15"/>
+      <c r="G44" s="15"/>
       <c r="H44" s="16"/>
     </row>
     <row r="45" spans="1:8">
-      <c r="A45" s="13">
+      <c r="A45" s="15">
         <v>73</v>
       </c>
-      <c r="B45" s="13">
-        <v>3</v>
-      </c>
-      <c r="C45" s="14" t="s">
+      <c r="B45" s="15">
+        <v>3</v>
+      </c>
+      <c r="C45" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="D45" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="E45" s="13" t="s">
+      <c r="D45" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E45" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="F45" s="13"/>
-      <c r="G45" s="13"/>
+      <c r="F45" s="15"/>
+      <c r="G45" s="15"/>
       <c r="H45" s="16"/>
     </row>
     <row r="46" spans="1:8">
-      <c r="A46" s="13">
+      <c r="A46" s="15">
         <v>74</v>
       </c>
-      <c r="B46" s="13">
-        <v>3</v>
-      </c>
-      <c r="C46" s="14" t="s">
+      <c r="B46" s="15">
+        <v>3</v>
+      </c>
+      <c r="C46" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="E46" s="13" t="s">
+      <c r="D46" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E46" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="F46" s="13"/>
-      <c r="G46" s="13"/>
+      <c r="F46" s="15"/>
+      <c r="G46" s="15"/>
       <c r="H46" s="16"/>
     </row>
     <row r="47" s="2" customFormat="1" spans="1:10">
@@ -2465,11 +2453,11 @@
       <c r="G47" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="H47" s="19">
-        <v>45931</v>
-      </c>
-      <c r="I47" s="20"/>
-      <c r="J47" s="20"/>
+      <c r="H47" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="I47" s="19"/>
+      <c r="J47" s="19"/>
     </row>
     <row r="48" s="2" customFormat="1" spans="1:10">
       <c r="A48" s="17">
@@ -2493,11 +2481,11 @@
       <c r="G48" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="H48" s="19">
-        <v>45931</v>
-      </c>
-      <c r="I48" s="20"/>
-      <c r="J48" s="20"/>
+      <c r="H48" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="I48" s="19"/>
+      <c r="J48" s="19"/>
     </row>
     <row r="49" s="2" customFormat="1" spans="1:10">
       <c r="A49" s="17">
@@ -2521,11 +2509,11 @@
       <c r="G49" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="H49" s="19">
-        <v>45931</v>
-      </c>
-      <c r="I49" s="20"/>
-      <c r="J49" s="20"/>
+      <c r="H49" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="I49" s="19"/>
+      <c r="J49" s="19"/>
     </row>
     <row r="50" s="2" customFormat="1" spans="1:10">
       <c r="A50" s="17">
@@ -2549,11 +2537,11 @@
       <c r="G50" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="H50" s="19">
-        <v>45931</v>
-      </c>
-      <c r="I50" s="20"/>
-      <c r="J50" s="20"/>
+      <c r="H50" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="I50" s="19"/>
+      <c r="J50" s="19"/>
     </row>
     <row r="51" s="3" customFormat="1" spans="1:12">
       <c r="A51" s="17">
@@ -2577,11 +2565,11 @@
       <c r="G51" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="H51" s="19">
-        <v>45931</v>
-      </c>
-      <c r="I51" s="20"/>
-      <c r="J51" s="21"/>
+      <c r="H51" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="I51" s="19"/>
+      <c r="J51" s="20"/>
       <c r="L51" s="2"/>
     </row>
     <row r="52" s="3" customFormat="1" spans="1:12">
@@ -2602,11 +2590,11 @@
       </c>
       <c r="F52" s="17"/>
       <c r="G52" s="17"/>
-      <c r="H52" s="19">
-        <v>45931</v>
-      </c>
-      <c r="I52" s="20"/>
-      <c r="J52" s="21"/>
+      <c r="H52" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="I52" s="19"/>
+      <c r="J52" s="20"/>
       <c r="L52" s="2"/>
     </row>
     <row r="53" s="3" customFormat="1" spans="1:12">
@@ -2627,11 +2615,11 @@
       </c>
       <c r="F53" s="17"/>
       <c r="G53" s="17"/>
-      <c r="H53" s="19">
-        <v>45931</v>
-      </c>
-      <c r="I53" s="20"/>
-      <c r="J53" s="21"/>
+      <c r="H53" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="I53" s="19"/>
+      <c r="J53" s="20"/>
       <c r="L53" s="2"/>
     </row>
     <row r="54" s="3" customFormat="1" spans="1:12">
@@ -2652,11 +2640,11 @@
       </c>
       <c r="F54" s="17"/>
       <c r="G54" s="17"/>
-      <c r="H54" s="19">
-        <v>45931</v>
-      </c>
-      <c r="I54" s="20"/>
-      <c r="J54" s="21"/>
+      <c r="H54" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="I54" s="19"/>
+      <c r="J54" s="20"/>
       <c r="L54" s="2"/>
     </row>
     <row r="55" spans="1:12">
@@ -2677,10 +2665,10 @@
       </c>
       <c r="F55" s="17"/>
       <c r="G55" s="17"/>
-      <c r="H55" s="19">
-        <v>45931</v>
-      </c>
-      <c r="I55" s="20"/>
+      <c r="H55" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="I55" s="19"/>
       <c r="L55" s="2"/>
     </row>
     <row r="56" spans="1:12">
@@ -2701,10 +2689,10 @@
       </c>
       <c r="F56" s="17"/>
       <c r="G56" s="17"/>
-      <c r="H56" s="19">
-        <v>45931</v>
-      </c>
-      <c r="I56" s="20"/>
+      <c r="H56" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="I56" s="19"/>
       <c r="L56" s="2"/>
     </row>
     <row r="57" customFormat="1" spans="1:12">
@@ -2725,11 +2713,11 @@
       </c>
       <c r="F57" s="17"/>
       <c r="G57" s="17"/>
-      <c r="H57" s="19">
-        <v>45931</v>
-      </c>
-      <c r="I57" s="20"/>
-      <c r="J57" s="7"/>
+      <c r="H57" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="I57" s="19"/>
+      <c r="J57" s="8"/>
       <c r="L57" s="2"/>
     </row>
     <row r="58" s="3" customFormat="1" spans="1:12">
@@ -2750,11 +2738,11 @@
       </c>
       <c r="F58" s="17"/>
       <c r="G58" s="17"/>
-      <c r="H58" s="19">
-        <v>45931</v>
-      </c>
-      <c r="I58" s="20"/>
-      <c r="J58" s="21"/>
+      <c r="H58" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="I58" s="19"/>
+      <c r="J58" s="20"/>
       <c r="L58" s="2"/>
     </row>
     <row r="59" s="3" customFormat="1" spans="1:12">
@@ -2775,11 +2763,11 @@
       </c>
       <c r="F59" s="17"/>
       <c r="G59" s="17"/>
-      <c r="H59" s="19">
-        <v>45931</v>
-      </c>
-      <c r="I59" s="20"/>
-      <c r="J59" s="21"/>
+      <c r="H59" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="I59" s="19"/>
+      <c r="J59" s="20"/>
       <c r="L59" s="2"/>
     </row>
     <row r="60" s="3" customFormat="1" spans="1:12">
@@ -2800,11 +2788,11 @@
       </c>
       <c r="F60" s="17"/>
       <c r="G60" s="17"/>
-      <c r="H60" s="19">
-        <v>45931</v>
-      </c>
-      <c r="I60" s="20"/>
-      <c r="J60" s="21"/>
+      <c r="H60" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="I60" s="19"/>
+      <c r="J60" s="20"/>
       <c r="L60" s="2"/>
     </row>
     <row r="61" s="3" customFormat="1" spans="1:12">
@@ -2827,11 +2815,11 @@
         <v>99999999</v>
       </c>
       <c r="G61" s="17"/>
-      <c r="H61" s="19">
-        <v>45931</v>
-      </c>
-      <c r="I61" s="20"/>
-      <c r="J61" s="21"/>
+      <c r="H61" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="I61" s="19"/>
+      <c r="J61" s="20"/>
       <c r="L61" s="2"/>
     </row>
     <row r="62" s="3" customFormat="1" spans="1:12">
@@ -2854,11 +2842,11 @@
         <v>88888888</v>
       </c>
       <c r="G62" s="17"/>
-      <c r="H62" s="19">
-        <v>45931</v>
-      </c>
-      <c r="I62" s="20"/>
-      <c r="J62" s="20"/>
+      <c r="H62" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="I62" s="19"/>
+      <c r="J62" s="19"/>
       <c r="L62" s="2"/>
     </row>
     <row r="63" spans="1:8">
@@ -2881,8 +2869,8 @@
         <v>77777777</v>
       </c>
       <c r="G63" s="17"/>
-      <c r="H63" s="19">
-        <v>45931</v>
+      <c r="H63" s="18" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="64" s="3" customFormat="1" spans="1:10">
@@ -2905,11 +2893,11 @@
         <v>66666666</v>
       </c>
       <c r="G64" s="17"/>
-      <c r="H64" s="19">
-        <v>45931</v>
-      </c>
-      <c r="I64" s="20"/>
-      <c r="J64" s="21"/>
+      <c r="H64" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="I64" s="19"/>
+      <c r="J64" s="20"/>
     </row>
     <row r="65" s="3" customFormat="1" spans="1:10">
       <c r="A65" s="17">
@@ -2931,11 +2919,11 @@
         <v>55555555</v>
       </c>
       <c r="G65" s="17"/>
-      <c r="H65" s="19">
-        <v>45931</v>
-      </c>
-      <c r="I65" s="20"/>
-      <c r="J65" s="21"/>
+      <c r="H65" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="I65" s="19"/>
+      <c r="J65" s="20"/>
     </row>
     <row r="66" s="3" customFormat="1" spans="1:10">
       <c r="A66" s="17">
@@ -2955,11 +2943,11 @@
       </c>
       <c r="F66" s="17"/>
       <c r="G66" s="17"/>
-      <c r="H66" s="19">
-        <v>45931</v>
-      </c>
-      <c r="I66" s="20"/>
-      <c r="J66" s="21"/>
+      <c r="H66" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="I66" s="19"/>
+      <c r="J66" s="20"/>
     </row>
     <row r="67" s="3" customFormat="1" spans="1:10">
       <c r="A67" s="17">
@@ -2979,11 +2967,11 @@
       </c>
       <c r="F67" s="17"/>
       <c r="G67" s="17"/>
-      <c r="H67" s="19">
-        <v>45931</v>
-      </c>
-      <c r="I67" s="20"/>
-      <c r="J67" s="21"/>
+      <c r="H67" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="I67" s="19"/>
+      <c r="J67" s="20"/>
     </row>
     <row r="68" s="3" customFormat="1" spans="1:10">
       <c r="A68" s="17">
@@ -3003,11 +2991,11 @@
       </c>
       <c r="F68" s="17"/>
       <c r="G68" s="17"/>
-      <c r="H68" s="19">
-        <v>45931</v>
-      </c>
-      <c r="I68" s="20"/>
-      <c r="J68" s="20"/>
+      <c r="H68" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="I68" s="19"/>
+      <c r="J68" s="19"/>
     </row>
     <row r="69" spans="1:9">
       <c r="A69" s="17">
@@ -3027,10 +3015,10 @@
       </c>
       <c r="F69" s="17"/>
       <c r="G69" s="17"/>
-      <c r="H69" s="19">
-        <v>45931</v>
-      </c>
-      <c r="I69" s="20"/>
+      <c r="H69" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="I69" s="19"/>
     </row>
     <row r="70" spans="1:9">
       <c r="A70" s="17">
@@ -3050,10 +3038,10 @@
       </c>
       <c r="F70" s="17"/>
       <c r="G70" s="17"/>
-      <c r="H70" s="19">
-        <v>45931</v>
-      </c>
-      <c r="I70" s="20"/>
+      <c r="H70" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="I70" s="19"/>
     </row>
     <row r="71" spans="1:9">
       <c r="A71" s="17">
@@ -3073,10 +3061,10 @@
       </c>
       <c r="F71" s="17"/>
       <c r="G71" s="17"/>
-      <c r="H71" s="19">
-        <v>45931</v>
-      </c>
-      <c r="I71" s="20"/>
+      <c r="H71" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="I71" s="19"/>
     </row>
     <row r="72" spans="1:9">
       <c r="A72" s="17">
@@ -3096,10 +3084,10 @@
       </c>
       <c r="F72" s="17"/>
       <c r="G72" s="17"/>
-      <c r="H72" s="19">
-        <v>45931</v>
-      </c>
-      <c r="I72" s="20"/>
+      <c r="H72" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="I72" s="19"/>
     </row>
     <row r="73" spans="1:9">
       <c r="A73" s="17">
@@ -3119,10 +3107,10 @@
       </c>
       <c r="F73" s="17"/>
       <c r="G73" s="17"/>
-      <c r="H73" s="19">
-        <v>45931</v>
-      </c>
-      <c r="I73" s="20"/>
+      <c r="H73" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="I73" s="19"/>
     </row>
     <row r="74" spans="1:9">
       <c r="A74" s="17">
@@ -3142,10 +3130,10 @@
       </c>
       <c r="F74" s="17"/>
       <c r="G74" s="17"/>
-      <c r="H74" s="19">
-        <v>45931</v>
-      </c>
-      <c r="I74" s="20"/>
+      <c r="H74" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="I74" s="19"/>
     </row>
     <row r="75" spans="1:9">
       <c r="A75" s="17">
@@ -3167,10 +3155,10 @@
         <v>99999999</v>
       </c>
       <c r="G75" s="17"/>
-      <c r="H75" s="19">
-        <v>45931</v>
-      </c>
-      <c r="I75" s="20"/>
+      <c r="H75" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="I75" s="19"/>
     </row>
     <row r="76" spans="1:9">
       <c r="A76" s="17">
@@ -3192,10 +3180,10 @@
         <v>88888888</v>
       </c>
       <c r="G76" s="17"/>
-      <c r="H76" s="19">
-        <v>45931</v>
-      </c>
-      <c r="I76" s="20"/>
+      <c r="H76" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="I76" s="19"/>
     </row>
     <row r="77" spans="1:9">
       <c r="A77" s="17">
@@ -3217,10 +3205,10 @@
         <v>77777777</v>
       </c>
       <c r="G77" s="17"/>
-      <c r="H77" s="19">
-        <v>45931</v>
-      </c>
-      <c r="I77" s="20"/>
+      <c r="H77" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="I77" s="19"/>
     </row>
     <row r="78" spans="1:9">
       <c r="A78" s="17">
@@ -3242,10 +3230,10 @@
         <v>66666666</v>
       </c>
       <c r="G78" s="17"/>
-      <c r="H78" s="19">
-        <v>45931</v>
-      </c>
-      <c r="I78" s="20"/>
+      <c r="H78" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="I78" s="19"/>
     </row>
     <row r="79" spans="1:9">
       <c r="A79" s="17">
@@ -3267,10 +3255,10 @@
         <v>55555555</v>
       </c>
       <c r="G79" s="17"/>
-      <c r="H79" s="19">
-        <v>45931</v>
-      </c>
-      <c r="I79" s="20"/>
+      <c r="H79" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="I79" s="19"/>
     </row>
     <row r="80" spans="1:9">
       <c r="A80" s="17">
@@ -3290,10 +3278,10 @@
       </c>
       <c r="F80" s="17"/>
       <c r="G80" s="17"/>
-      <c r="H80" s="19">
-        <v>45931</v>
-      </c>
-      <c r="I80" s="20"/>
+      <c r="H80" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="I80" s="19"/>
     </row>
     <row r="81" spans="1:9">
       <c r="A81" s="17">
@@ -3313,10 +3301,10 @@
       </c>
       <c r="F81" s="17"/>
       <c r="G81" s="17"/>
-      <c r="H81" s="19">
-        <v>45931</v>
-      </c>
-      <c r="I81" s="20"/>
+      <c r="H81" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="I81" s="19"/>
     </row>
     <row r="82" spans="1:9">
       <c r="A82" s="17">
@@ -3336,10 +3324,10 @@
       </c>
       <c r="F82" s="17"/>
       <c r="G82" s="17"/>
-      <c r="H82" s="19">
-        <v>45931</v>
-      </c>
-      <c r="I82" s="20"/>
+      <c r="H82" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="I82" s="19"/>
     </row>
     <row r="83" spans="1:9">
       <c r="A83" s="17">
@@ -3359,10 +3347,10 @@
       </c>
       <c r="F83" s="17"/>
       <c r="G83" s="17"/>
-      <c r="H83" s="19">
-        <v>45931</v>
-      </c>
-      <c r="I83" s="20"/>
+      <c r="H83" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="I83" s="19"/>
     </row>
     <row r="84" spans="1:9">
       <c r="A84" s="17">
@@ -3382,10 +3370,10 @@
       </c>
       <c r="F84" s="17"/>
       <c r="G84" s="17"/>
-      <c r="H84" s="19">
-        <v>45931</v>
-      </c>
-      <c r="I84" s="20"/>
+      <c r="H84" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="I84" s="19"/>
     </row>
     <row r="85" spans="1:9">
       <c r="A85" s="17">
@@ -3405,10 +3393,10 @@
       </c>
       <c r="F85" s="17"/>
       <c r="G85" s="17"/>
-      <c r="H85" s="19">
-        <v>45931</v>
-      </c>
-      <c r="I85" s="20"/>
+      <c r="H85" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="I85" s="19"/>
     </row>
     <row r="86" spans="1:8">
       <c r="A86" s="17">
@@ -3428,8 +3416,8 @@
       </c>
       <c r="F86" s="17"/>
       <c r="G86" s="17"/>
-      <c r="H86" s="19">
-        <v>45931</v>
+      <c r="H86" s="18" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="87" spans="1:8">
@@ -3450,8 +3438,8 @@
       </c>
       <c r="F87" s="17"/>
       <c r="G87" s="17"/>
-      <c r="H87" s="19">
-        <v>45931</v>
+      <c r="H87" s="18" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="88" spans="1:8">
@@ -3472,8 +3460,8 @@
       </c>
       <c r="F88" s="17"/>
       <c r="G88" s="17"/>
-      <c r="H88" s="19">
-        <v>45931</v>
+      <c r="H88" s="18" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/table/resources/sample/PointsAwardRanking.xlsx
+++ b/table/resources/sample/PointsAwardRanking.xlsx
@@ -175,7 +175,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="55">
   <si>
     <t>序列ID</t>
   </si>
@@ -234,6 +234,9 @@
     <t>price</t>
   </si>
   <si>
+    <t>picRes</t>
+  </si>
+  <si>
     <t>time</t>
   </si>
   <si>
@@ -243,18 +246,27 @@
     <t>其它道具名称1_1</t>
   </si>
   <si>
-    <t>icon.png</t>
+    <t>wdcc_ccb_1.png</t>
   </si>
   <si>
     <t>其它道具名称2_1</t>
   </si>
   <si>
+    <t>wdcc_ccb_2.png</t>
+  </si>
+  <si>
     <t>其它道具名称3_1</t>
   </si>
   <si>
+    <t>wdcc_ccb_3.png</t>
+  </si>
+  <si>
     <t>其它道具名称4_1</t>
   </si>
   <si>
+    <t>itemicon_1010101.png</t>
+  </si>
+  <si>
     <t>其它道具名称5_1</t>
   </si>
   <si>
@@ -300,10 +312,34 @@
     <t>1990000_2000000</t>
   </si>
   <si>
-    <t>Name_1</t>
-  </si>
-  <si>
-    <t>2025/10/01 00:00:00</t>
+    <t>其它道具名称6_1</t>
+  </si>
+  <si>
+    <t>其它道具名称7_1</t>
+  </si>
+  <si>
+    <t>其它道具名称8_1</t>
+  </si>
+  <si>
+    <t>其它道具名称9_1</t>
+  </si>
+  <si>
+    <t>其它道具名称10_1</t>
+  </si>
+  <si>
+    <t>其它道具名称11_1</t>
+  </si>
+  <si>
+    <t>其它道具名称12_1</t>
+  </si>
+  <si>
+    <t>其它道具名称13_1</t>
+  </si>
+  <si>
+    <t>其它道具名称14_1</t>
+  </si>
+  <si>
+    <t>其它道具名称15_1</t>
   </si>
 </sst>
 </file>
@@ -1467,9 +1503,11 @@
       <c r="F3" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="12"/>
+      <c r="G3" s="12" t="s">
+        <v>19</v>
+      </c>
       <c r="H3" s="13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1493,16 +1531,16 @@
         <v>1</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F5" s="15">
-        <v>99999999</v>
+        <v>33333333</v>
       </c>
       <c r="G5" s="15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H5" s="16"/>
       <c r="I5" s="19"/>
@@ -1519,16 +1557,16 @@
         <v>2</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F6" s="15">
-        <v>88888888</v>
+        <v>22222222</v>
       </c>
       <c r="G6" s="15" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H6" s="16"/>
       <c r="I6" s="19"/>
@@ -1545,16 +1583,16 @@
         <v>3</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F7" s="15">
-        <v>77777777</v>
+        <v>11111111</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="H7" s="16"/>
       <c r="I7" s="19"/>
@@ -1571,16 +1609,16 @@
         <v>4</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F8" s="15">
-        <v>66666666</v>
+        <v>5000000</v>
       </c>
       <c r="G8" s="15" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="H8" s="16"/>
       <c r="I8" s="19"/>
@@ -1597,16 +1635,16 @@
         <v>5</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F9" s="15">
-        <v>55555555</v>
+        <v>3000000</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="H9" s="16"/>
       <c r="I9" s="19"/>
@@ -1624,10 +1662,10 @@
         <v>6</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F10" s="15"/>
       <c r="G10" s="15"/>
@@ -1647,10 +1685,10 @@
         <v>7</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F11" s="15"/>
       <c r="G11" s="15"/>
@@ -1670,10 +1708,10 @@
         <v>8</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F12" s="15"/>
       <c r="G12" s="15"/>
@@ -1693,10 +1731,10 @@
         <v>9</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F13" s="15"/>
       <c r="G13" s="15"/>
@@ -1715,10 +1753,10 @@
         <v>10</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F14" s="15"/>
       <c r="G14" s="15"/>
@@ -1734,13 +1772,13 @@
         <v>1</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F15" s="15"/>
       <c r="G15" s="15"/>
@@ -1757,13 +1795,13 @@
         <v>1</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F16" s="15"/>
       <c r="G16" s="15"/>
@@ -1780,13 +1818,13 @@
         <v>1</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F17" s="15"/>
       <c r="G17" s="15"/>
@@ -1803,13 +1841,13 @@
         <v>1</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F18" s="15"/>
       <c r="G18" s="15"/>
@@ -1829,15 +1867,17 @@
         <v>1</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F19" s="15">
-        <v>99999999</v>
-      </c>
-      <c r="G19" s="15"/>
+        <v>33333333</v>
+      </c>
+      <c r="G19" s="15" t="s">
+        <v>23</v>
+      </c>
       <c r="H19" s="16"/>
       <c r="I19" s="19"/>
       <c r="J19" s="20"/>
@@ -1854,15 +1894,17 @@
         <v>2</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F20" s="15">
-        <v>88888888</v>
-      </c>
-      <c r="G20" s="15"/>
+        <v>22222222</v>
+      </c>
+      <c r="G20" s="15" t="s">
+        <v>25</v>
+      </c>
       <c r="H20" s="16"/>
       <c r="I20" s="19"/>
       <c r="J20" s="19"/>
@@ -1879,15 +1921,17 @@
         <v>3</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="F21" s="15">
-        <v>77777777</v>
-      </c>
-      <c r="G21" s="15"/>
+        <v>11111111</v>
+      </c>
+      <c r="G21" s="15" t="s">
+        <v>27</v>
+      </c>
       <c r="H21" s="16"/>
     </row>
     <row r="22" s="3" customFormat="1" spans="1:10">
@@ -1901,15 +1945,17 @@
         <v>4</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="F22" s="15">
-        <v>66666666</v>
-      </c>
-      <c r="G22" s="15"/>
+        <v>5000000</v>
+      </c>
+      <c r="G22" s="15" t="s">
+        <v>29</v>
+      </c>
       <c r="H22" s="16"/>
       <c r="I22" s="19"/>
       <c r="J22" s="20"/>
@@ -1925,15 +1971,17 @@
         <v>5</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E23" s="15" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="F23" s="15">
-        <v>55555555</v>
-      </c>
-      <c r="G23" s="15"/>
+        <v>3000000</v>
+      </c>
+      <c r="G23" s="15" t="s">
+        <v>29</v>
+      </c>
       <c r="H23" s="16"/>
       <c r="I23" s="19"/>
       <c r="J23" s="20"/>
@@ -1949,10 +1997,10 @@
         <v>6</v>
       </c>
       <c r="D24" s="16" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F24" s="15"/>
       <c r="G24" s="15"/>
@@ -1971,10 +2019,10 @@
         <v>7</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E25" s="15" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F25" s="15"/>
       <c r="G25" s="15"/>
@@ -1993,10 +2041,10 @@
         <v>8</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F26" s="15"/>
       <c r="G26" s="15"/>
@@ -2015,10 +2063,10 @@
         <v>9</v>
       </c>
       <c r="D27" s="16" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F27" s="15"/>
       <c r="G27" s="15"/>
@@ -2036,10 +2084,10 @@
         <v>10</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F28" s="15"/>
       <c r="G28" s="15"/>
@@ -2054,13 +2102,13 @@
         <v>2</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F29" s="15"/>
       <c r="G29" s="15"/>
@@ -2075,13 +2123,13 @@
         <v>2</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E30" s="15" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F30" s="15"/>
       <c r="G30" s="15"/>
@@ -2096,13 +2144,13 @@
         <v>2</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E31" s="15" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F31" s="15"/>
       <c r="G31" s="15"/>
@@ -2117,13 +2165,13 @@
         <v>2</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D32" s="16" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E32" s="15" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F32" s="15"/>
       <c r="G32" s="15"/>
@@ -2141,15 +2189,17 @@
         <v>1</v>
       </c>
       <c r="D33" s="16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E33" s="15" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="F33" s="15">
         <v>99999999</v>
       </c>
-      <c r="G33" s="15"/>
+      <c r="G33" s="15" t="s">
+        <v>23</v>
+      </c>
       <c r="H33" s="16"/>
       <c r="I33" s="19"/>
     </row>
@@ -2164,15 +2214,17 @@
         <v>2</v>
       </c>
       <c r="D34" s="16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E34" s="15" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="F34" s="15">
         <v>88888888</v>
       </c>
-      <c r="G34" s="15"/>
+      <c r="G34" s="15" t="s">
+        <v>25</v>
+      </c>
       <c r="H34" s="16"/>
       <c r="I34" s="19"/>
     </row>
@@ -2187,15 +2239,17 @@
         <v>3</v>
       </c>
       <c r="D35" s="16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E35" s="15" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="F35" s="15">
         <v>77777777</v>
       </c>
-      <c r="G35" s="15"/>
+      <c r="G35" s="15" t="s">
+        <v>27</v>
+      </c>
       <c r="H35" s="16"/>
       <c r="I35" s="19"/>
     </row>
@@ -2210,15 +2264,17 @@
         <v>4</v>
       </c>
       <c r="D36" s="16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E36" s="15" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="F36" s="15">
         <v>66666666</v>
       </c>
-      <c r="G36" s="15"/>
+      <c r="G36" s="15" t="s">
+        <v>29</v>
+      </c>
       <c r="H36" s="16"/>
       <c r="I36" s="19"/>
     </row>
@@ -2233,15 +2289,17 @@
         <v>5</v>
       </c>
       <c r="D37" s="16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E37" s="15" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="F37" s="15">
         <v>55555555</v>
       </c>
-      <c r="G37" s="15"/>
+      <c r="G37" s="15" t="s">
+        <v>29</v>
+      </c>
       <c r="H37" s="16"/>
       <c r="I37" s="19"/>
     </row>
@@ -2256,10 +2314,10 @@
         <v>6</v>
       </c>
       <c r="D38" s="16" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E38" s="15" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F38" s="15"/>
       <c r="G38" s="15"/>
@@ -2277,10 +2335,10 @@
         <v>7</v>
       </c>
       <c r="D39" s="16" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E39" s="15" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F39" s="15"/>
       <c r="G39" s="15"/>
@@ -2298,10 +2356,10 @@
         <v>8</v>
       </c>
       <c r="D40" s="16" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E40" s="15" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F40" s="15"/>
       <c r="G40" s="15"/>
@@ -2319,10 +2377,10 @@
         <v>9</v>
       </c>
       <c r="D41" s="16" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E41" s="15" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F41" s="15"/>
       <c r="G41" s="15"/>
@@ -2340,10 +2398,10 @@
         <v>10</v>
       </c>
       <c r="D42" s="16" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E42" s="15" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F42" s="15"/>
       <c r="G42" s="15"/>
@@ -2358,13 +2416,13 @@
         <v>3</v>
       </c>
       <c r="C43" s="16" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D43" s="16" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E43" s="15" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F43" s="15"/>
       <c r="G43" s="15"/>
@@ -2379,13 +2437,13 @@
         <v>3</v>
       </c>
       <c r="C44" s="16" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D44" s="16" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E44" s="15" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F44" s="15"/>
       <c r="G44" s="15"/>
@@ -2399,13 +2457,13 @@
         <v>3</v>
       </c>
       <c r="C45" s="16" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D45" s="16" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E45" s="15" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F45" s="15"/>
       <c r="G45" s="15"/>
@@ -2419,13 +2477,13 @@
         <v>3</v>
       </c>
       <c r="C46" s="16" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D46" s="16" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E46" s="15" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F46" s="15"/>
       <c r="G46" s="15"/>
@@ -2442,20 +2500,18 @@
         <v>1</v>
       </c>
       <c r="D47" s="18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E47" s="17" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="F47" s="17">
-        <v>99999999</v>
+        <v>33333333</v>
       </c>
       <c r="G47" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="H47" s="18" t="s">
-        <v>42</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="H47" s="18"/>
       <c r="I47" s="19"/>
       <c r="J47" s="19"/>
     </row>
@@ -2470,20 +2526,18 @@
         <v>2</v>
       </c>
       <c r="D48" s="18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E48" s="17" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="F48" s="17">
-        <v>88888888</v>
+        <v>22222222</v>
       </c>
       <c r="G48" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="H48" s="18" t="s">
-        <v>42</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="H48" s="18"/>
       <c r="I48" s="19"/>
       <c r="J48" s="19"/>
     </row>
@@ -2498,20 +2552,18 @@
         <v>3</v>
       </c>
       <c r="D49" s="18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E49" s="17" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="F49" s="17">
-        <v>77777777</v>
+        <v>11111111</v>
       </c>
       <c r="G49" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="H49" s="18" t="s">
-        <v>42</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="H49" s="18"/>
       <c r="I49" s="19"/>
       <c r="J49" s="19"/>
     </row>
@@ -2526,20 +2578,18 @@
         <v>4</v>
       </c>
       <c r="D50" s="18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E50" s="17" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="F50" s="17">
-        <v>66666666</v>
+        <v>5000000</v>
       </c>
       <c r="G50" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="H50" s="18" t="s">
-        <v>42</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="H50" s="18"/>
       <c r="I50" s="19"/>
       <c r="J50" s="19"/>
     </row>
@@ -2554,20 +2604,18 @@
         <v>5</v>
       </c>
       <c r="D51" s="18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E51" s="17" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="F51" s="17">
-        <v>55555555</v>
+        <v>3000000</v>
       </c>
       <c r="G51" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="H51" s="18" t="s">
-        <v>42</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="H51" s="18"/>
       <c r="I51" s="19"/>
       <c r="J51" s="20"/>
       <c r="L51" s="2"/>
@@ -2583,16 +2631,14 @@
         <v>6</v>
       </c>
       <c r="D52" s="18" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E52" s="17" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F52" s="17"/>
       <c r="G52" s="17"/>
-      <c r="H52" s="18" t="s">
-        <v>42</v>
-      </c>
+      <c r="H52" s="18"/>
       <c r="I52" s="19"/>
       <c r="J52" s="20"/>
       <c r="L52" s="2"/>
@@ -2608,16 +2654,14 @@
         <v>7</v>
       </c>
       <c r="D53" s="18" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E53" s="17" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F53" s="17"/>
       <c r="G53" s="17"/>
-      <c r="H53" s="18" t="s">
-        <v>42</v>
-      </c>
+      <c r="H53" s="18"/>
       <c r="I53" s="19"/>
       <c r="J53" s="20"/>
       <c r="L53" s="2"/>
@@ -2633,16 +2677,14 @@
         <v>8</v>
       </c>
       <c r="D54" s="18" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E54" s="17" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F54" s="17"/>
       <c r="G54" s="17"/>
-      <c r="H54" s="18" t="s">
-        <v>42</v>
-      </c>
+      <c r="H54" s="18"/>
       <c r="I54" s="19"/>
       <c r="J54" s="20"/>
       <c r="L54" s="2"/>
@@ -2658,16 +2700,14 @@
         <v>9</v>
       </c>
       <c r="D55" s="18" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E55" s="17" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F55" s="17"/>
       <c r="G55" s="17"/>
-      <c r="H55" s="18" t="s">
-        <v>42</v>
-      </c>
+      <c r="H55" s="18"/>
       <c r="I55" s="19"/>
       <c r="L55" s="2"/>
     </row>
@@ -2682,16 +2722,14 @@
         <v>10</v>
       </c>
       <c r="D56" s="18" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E56" s="17" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F56" s="17"/>
       <c r="G56" s="17"/>
-      <c r="H56" s="18" t="s">
-        <v>42</v>
-      </c>
+      <c r="H56" s="18"/>
       <c r="I56" s="19"/>
       <c r="L56" s="2"/>
     </row>
@@ -2703,19 +2741,17 @@
         <v>1</v>
       </c>
       <c r="C57" s="18" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D57" s="18" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E57" s="17" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F57" s="17"/>
       <c r="G57" s="17"/>
-      <c r="H57" s="18" t="s">
-        <v>42</v>
-      </c>
+      <c r="H57" s="18"/>
       <c r="I57" s="19"/>
       <c r="J57" s="8"/>
       <c r="L57" s="2"/>
@@ -2728,19 +2764,17 @@
         <v>1</v>
       </c>
       <c r="C58" s="18" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D58" s="18" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E58" s="17" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F58" s="17"/>
       <c r="G58" s="17"/>
-      <c r="H58" s="18" t="s">
-        <v>42</v>
-      </c>
+      <c r="H58" s="18"/>
       <c r="I58" s="19"/>
       <c r="J58" s="20"/>
       <c r="L58" s="2"/>
@@ -2753,19 +2787,17 @@
         <v>1</v>
       </c>
       <c r="C59" s="18" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D59" s="18" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E59" s="17" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F59" s="17"/>
       <c r="G59" s="17"/>
-      <c r="H59" s="18" t="s">
-        <v>42</v>
-      </c>
+      <c r="H59" s="18"/>
       <c r="I59" s="19"/>
       <c r="J59" s="20"/>
       <c r="L59" s="2"/>
@@ -2778,19 +2810,17 @@
         <v>1</v>
       </c>
       <c r="C60" s="18" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D60" s="18" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E60" s="17" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F60" s="17"/>
       <c r="G60" s="17"/>
-      <c r="H60" s="18" t="s">
-        <v>42</v>
-      </c>
+      <c r="H60" s="18"/>
       <c r="I60" s="19"/>
       <c r="J60" s="20"/>
       <c r="L60" s="2"/>
@@ -2806,18 +2836,18 @@
         <v>1</v>
       </c>
       <c r="D61" s="18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E61" s="17" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F61" s="17">
-        <v>99999999</v>
-      </c>
-      <c r="G61" s="17"/>
-      <c r="H61" s="18" t="s">
-        <v>42</v>
-      </c>
+        <v>33333333</v>
+      </c>
+      <c r="G61" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="H61" s="18"/>
       <c r="I61" s="19"/>
       <c r="J61" s="20"/>
       <c r="L61" s="2"/>
@@ -2833,18 +2863,18 @@
         <v>2</v>
       </c>
       <c r="D62" s="18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E62" s="17" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F62" s="17">
-        <v>88888888</v>
-      </c>
-      <c r="G62" s="17"/>
-      <c r="H62" s="18" t="s">
-        <v>42</v>
-      </c>
+        <v>22222222</v>
+      </c>
+      <c r="G62" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="H62" s="18"/>
       <c r="I62" s="19"/>
       <c r="J62" s="19"/>
       <c r="L62" s="2"/>
@@ -2860,18 +2890,18 @@
         <v>3</v>
       </c>
       <c r="D63" s="18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E63" s="17" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="F63" s="17">
-        <v>77777777</v>
-      </c>
-      <c r="G63" s="17"/>
-      <c r="H63" s="18" t="s">
-        <v>42</v>
-      </c>
+        <v>11111111</v>
+      </c>
+      <c r="G63" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="H63" s="18"/>
     </row>
     <row r="64" s="3" customFormat="1" spans="1:10">
       <c r="A64" s="17">
@@ -2884,18 +2914,18 @@
         <v>4</v>
       </c>
       <c r="D64" s="18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E64" s="17" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="F64" s="17">
-        <v>66666666</v>
-      </c>
-      <c r="G64" s="17"/>
-      <c r="H64" s="18" t="s">
-        <v>42</v>
-      </c>
+        <v>5000000</v>
+      </c>
+      <c r="G64" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="H64" s="18"/>
       <c r="I64" s="19"/>
       <c r="J64" s="20"/>
     </row>
@@ -2910,18 +2940,18 @@
         <v>5</v>
       </c>
       <c r="D65" s="18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E65" s="17" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="F65" s="17">
-        <v>55555555</v>
-      </c>
-      <c r="G65" s="17"/>
-      <c r="H65" s="18" t="s">
-        <v>42</v>
-      </c>
+        <v>3000000</v>
+      </c>
+      <c r="G65" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="H65" s="18"/>
       <c r="I65" s="19"/>
       <c r="J65" s="20"/>
     </row>
@@ -2936,16 +2966,14 @@
         <v>6</v>
       </c>
       <c r="D66" s="18" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E66" s="17" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F66" s="17"/>
       <c r="G66" s="17"/>
-      <c r="H66" s="18" t="s">
-        <v>42</v>
-      </c>
+      <c r="H66" s="18"/>
       <c r="I66" s="19"/>
       <c r="J66" s="20"/>
     </row>
@@ -2960,16 +2988,14 @@
         <v>7</v>
       </c>
       <c r="D67" s="18" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E67" s="17" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F67" s="17"/>
       <c r="G67" s="17"/>
-      <c r="H67" s="18" t="s">
-        <v>42</v>
-      </c>
+      <c r="H67" s="18"/>
       <c r="I67" s="19"/>
       <c r="J67" s="20"/>
     </row>
@@ -2984,16 +3010,14 @@
         <v>8</v>
       </c>
       <c r="D68" s="18" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E68" s="17" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F68" s="17"/>
       <c r="G68" s="17"/>
-      <c r="H68" s="18" t="s">
-        <v>42</v>
-      </c>
+      <c r="H68" s="18"/>
       <c r="I68" s="19"/>
       <c r="J68" s="19"/>
     </row>
@@ -3008,16 +3032,14 @@
         <v>9</v>
       </c>
       <c r="D69" s="18" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E69" s="17" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F69" s="17"/>
       <c r="G69" s="17"/>
-      <c r="H69" s="18" t="s">
-        <v>42</v>
-      </c>
+      <c r="H69" s="18"/>
       <c r="I69" s="19"/>
     </row>
     <row r="70" spans="1:9">
@@ -3031,16 +3053,14 @@
         <v>10</v>
       </c>
       <c r="D70" s="18" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E70" s="17" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F70" s="17"/>
       <c r="G70" s="17"/>
-      <c r="H70" s="18" t="s">
-        <v>42</v>
-      </c>
+      <c r="H70" s="18"/>
       <c r="I70" s="19"/>
     </row>
     <row r="71" spans="1:9">
@@ -3051,19 +3071,17 @@
         <v>2</v>
       </c>
       <c r="C71" s="18" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D71" s="18" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E71" s="17" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F71" s="17"/>
       <c r="G71" s="17"/>
-      <c r="H71" s="18" t="s">
-        <v>42</v>
-      </c>
+      <c r="H71" s="18"/>
       <c r="I71" s="19"/>
     </row>
     <row r="72" spans="1:9">
@@ -3074,19 +3092,17 @@
         <v>2</v>
       </c>
       <c r="C72" s="18" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D72" s="18" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E72" s="17" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F72" s="17"/>
       <c r="G72" s="17"/>
-      <c r="H72" s="18" t="s">
-        <v>42</v>
-      </c>
+      <c r="H72" s="18"/>
       <c r="I72" s="19"/>
     </row>
     <row r="73" spans="1:9">
@@ -3097,19 +3113,17 @@
         <v>2</v>
       </c>
       <c r="C73" s="18" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D73" s="18" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E73" s="17" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F73" s="17"/>
       <c r="G73" s="17"/>
-      <c r="H73" s="18" t="s">
-        <v>42</v>
-      </c>
+      <c r="H73" s="18"/>
       <c r="I73" s="19"/>
     </row>
     <row r="74" spans="1:9">
@@ -3120,19 +3134,17 @@
         <v>2</v>
       </c>
       <c r="C74" s="18" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D74" s="18" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E74" s="17" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F74" s="17"/>
       <c r="G74" s="17"/>
-      <c r="H74" s="18" t="s">
-        <v>42</v>
-      </c>
+      <c r="H74" s="18"/>
       <c r="I74" s="19"/>
     </row>
     <row r="75" spans="1:9">
@@ -3146,18 +3158,18 @@
         <v>1</v>
       </c>
       <c r="D75" s="18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E75" s="17" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="F75" s="17">
         <v>99999999</v>
       </c>
-      <c r="G75" s="17"/>
-      <c r="H75" s="18" t="s">
-        <v>42</v>
-      </c>
+      <c r="G75" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="H75" s="18"/>
       <c r="I75" s="19"/>
     </row>
     <row r="76" spans="1:9">
@@ -3171,18 +3183,18 @@
         <v>2</v>
       </c>
       <c r="D76" s="18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E76" s="17" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="F76" s="17">
         <v>88888888</v>
       </c>
-      <c r="G76" s="17"/>
-      <c r="H76" s="18" t="s">
-        <v>42</v>
-      </c>
+      <c r="G76" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="H76" s="18"/>
       <c r="I76" s="19"/>
     </row>
     <row r="77" spans="1:9">
@@ -3196,18 +3208,18 @@
         <v>3</v>
       </c>
       <c r="D77" s="18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E77" s="17" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="F77" s="17">
         <v>77777777</v>
       </c>
-      <c r="G77" s="17"/>
-      <c r="H77" s="18" t="s">
-        <v>42</v>
-      </c>
+      <c r="G77" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="H77" s="18"/>
       <c r="I77" s="19"/>
     </row>
     <row r="78" spans="1:9">
@@ -3221,18 +3233,18 @@
         <v>4</v>
       </c>
       <c r="D78" s="18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E78" s="17" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="F78" s="17">
         <v>66666666</v>
       </c>
-      <c r="G78" s="17"/>
-      <c r="H78" s="18" t="s">
-        <v>42</v>
-      </c>
+      <c r="G78" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="H78" s="18"/>
       <c r="I78" s="19"/>
     </row>
     <row r="79" spans="1:9">
@@ -3246,18 +3258,18 @@
         <v>5</v>
       </c>
       <c r="D79" s="18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E79" s="17" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="F79" s="17">
         <v>55555555</v>
       </c>
-      <c r="G79" s="17"/>
-      <c r="H79" s="18" t="s">
-        <v>42</v>
-      </c>
+      <c r="G79" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="H79" s="18"/>
       <c r="I79" s="19"/>
     </row>
     <row r="80" spans="1:9">
@@ -3271,16 +3283,14 @@
         <v>6</v>
       </c>
       <c r="D80" s="18" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E80" s="17" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F80" s="17"/>
       <c r="G80" s="17"/>
-      <c r="H80" s="18" t="s">
-        <v>42</v>
-      </c>
+      <c r="H80" s="18"/>
       <c r="I80" s="19"/>
     </row>
     <row r="81" spans="1:9">
@@ -3294,16 +3304,14 @@
         <v>7</v>
       </c>
       <c r="D81" s="18" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E81" s="17" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F81" s="17"/>
       <c r="G81" s="17"/>
-      <c r="H81" s="18" t="s">
-        <v>42</v>
-      </c>
+      <c r="H81" s="18"/>
       <c r="I81" s="19"/>
     </row>
     <row r="82" spans="1:9">
@@ -3317,16 +3325,14 @@
         <v>8</v>
       </c>
       <c r="D82" s="18" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E82" s="17" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F82" s="17"/>
       <c r="G82" s="17"/>
-      <c r="H82" s="18" t="s">
-        <v>42</v>
-      </c>
+      <c r="H82" s="18"/>
       <c r="I82" s="19"/>
     </row>
     <row r="83" spans="1:9">
@@ -3340,16 +3346,14 @@
         <v>9</v>
       </c>
       <c r="D83" s="18" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E83" s="17" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F83" s="17"/>
       <c r="G83" s="17"/>
-      <c r="H83" s="18" t="s">
-        <v>42</v>
-      </c>
+      <c r="H83" s="18"/>
       <c r="I83" s="19"/>
     </row>
     <row r="84" spans="1:9">
@@ -3363,16 +3367,14 @@
         <v>10</v>
       </c>
       <c r="D84" s="18" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E84" s="17" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F84" s="17"/>
       <c r="G84" s="17"/>
-      <c r="H84" s="18" t="s">
-        <v>42</v>
-      </c>
+      <c r="H84" s="18"/>
       <c r="I84" s="19"/>
     </row>
     <row r="85" spans="1:9">
@@ -3383,19 +3385,17 @@
         <v>3</v>
       </c>
       <c r="C85" s="18" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D85" s="18" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E85" s="17" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F85" s="17"/>
       <c r="G85" s="17"/>
-      <c r="H85" s="18" t="s">
-        <v>42</v>
-      </c>
+      <c r="H85" s="18"/>
       <c r="I85" s="19"/>
     </row>
     <row r="86" spans="1:8">
@@ -3406,19 +3406,17 @@
         <v>3</v>
       </c>
       <c r="C86" s="18" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D86" s="18" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E86" s="17" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F86" s="17"/>
       <c r="G86" s="17"/>
-      <c r="H86" s="18" t="s">
-        <v>42</v>
-      </c>
+      <c r="H86" s="18"/>
     </row>
     <row r="87" spans="1:8">
       <c r="A87" s="17">
@@ -3428,19 +3426,17 @@
         <v>3</v>
       </c>
       <c r="C87" s="18" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D87" s="18" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E87" s="17" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F87" s="17"/>
       <c r="G87" s="17"/>
-      <c r="H87" s="18" t="s">
-        <v>42</v>
-      </c>
+      <c r="H87" s="18"/>
     </row>
     <row r="88" spans="1:8">
       <c r="A88" s="17">
@@ -3450,19 +3446,17 @@
         <v>3</v>
       </c>
       <c r="C88" s="18" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D88" s="18" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E88" s="17" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F88" s="17"/>
       <c r="G88" s="17"/>
-      <c r="H88" s="18" t="s">
-        <v>42</v>
-      </c>
+      <c r="H88" s="18"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/table/resources/sample/PointsAwardRanking.xlsx
+++ b/table/resources/sample/PointsAwardRanking.xlsx
@@ -175,7 +175,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="94">
   <si>
     <t>序列ID</t>
   </si>
@@ -240,6 +240,144 @@
     <t>time</t>
   </si>
   <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>1990000_870000</t>
+  </si>
+  <si>
+    <t>1990000_660000</t>
+  </si>
+  <si>
+    <t>1990000_480000</t>
+  </si>
+  <si>
+    <t>1990000_360000</t>
+  </si>
+  <si>
+    <t>1990000_330000</t>
+  </si>
+  <si>
+    <t>1990000_300000</t>
+  </si>
+  <si>
+    <t>1990000_270000</t>
+  </si>
+  <si>
+    <t>1990000_240000</t>
+  </si>
+  <si>
+    <t>1990000_210000</t>
+  </si>
+  <si>
+    <t>1990000_180000</t>
+  </si>
+  <si>
+    <t>11_20</t>
+  </si>
+  <si>
+    <t>1990000_72000</t>
+  </si>
+  <si>
+    <t>21_30</t>
+  </si>
+  <si>
+    <t>1990000_60000</t>
+  </si>
+  <si>
+    <t>31_40</t>
+  </si>
+  <si>
+    <t>1990000_48000</t>
+  </si>
+  <si>
+    <t>41_50</t>
+  </si>
+  <si>
+    <t>1990000_30000</t>
+  </si>
+  <si>
+    <t>1990000_1450000</t>
+  </si>
+  <si>
+    <t>1990000_1100000</t>
+  </si>
+  <si>
+    <t>1990000_800000</t>
+  </si>
+  <si>
+    <t>1990000_600000</t>
+  </si>
+  <si>
+    <t>1990000_550000</t>
+  </si>
+  <si>
+    <t>1990000_500000</t>
+  </si>
+  <si>
+    <t>1990000_450000</t>
+  </si>
+  <si>
+    <t>1990000_400000</t>
+  </si>
+  <si>
+    <t>1990000_350000</t>
+  </si>
+  <si>
+    <t>1990000_120000</t>
+  </si>
+  <si>
+    <t>1990000_100000</t>
+  </si>
+  <si>
+    <t>1990000_80000</t>
+  </si>
+  <si>
+    <t>1990000_50000</t>
+  </si>
+  <si>
+    <t>1990000_116000000</t>
+  </si>
+  <si>
+    <t>1990000_88000000</t>
+  </si>
+  <si>
+    <t>1990000_64000000</t>
+  </si>
+  <si>
+    <t>1990000_48000000</t>
+  </si>
+  <si>
+    <t>1990000_44000000</t>
+  </si>
+  <si>
+    <t>1990000_40000000</t>
+  </si>
+  <si>
+    <t>1990000_36000000</t>
+  </si>
+  <si>
+    <t>1990000_32000000</t>
+  </si>
+  <si>
+    <t>1990000_28000000</t>
+  </si>
+  <si>
+    <t>1990000_24000000</t>
+  </si>
+  <si>
+    <t>1990000_9600000</t>
+  </si>
+  <si>
+    <t>1990000_8000000</t>
+  </si>
+  <si>
+    <t>1990000_6400000</t>
+  </si>
+  <si>
+    <t>1990000_4000000</t>
+  </si>
+  <si>
     <t>1</t>
   </si>
   <si>
@@ -270,43 +408,22 @@
     <t>其它道具名称5_1</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
     <t>1990000_10000000</t>
   </si>
   <si>
     <t>1990000_9000000</t>
   </si>
   <si>
-    <t>1990000_8000000</t>
-  </si>
-  <si>
     <t>1990000_7000000</t>
   </si>
   <si>
     <t>1990000_6000000</t>
   </si>
   <si>
-    <t>11_20</t>
-  </si>
-  <si>
     <t>1990000_5000000</t>
   </si>
   <si>
-    <t>21_30</t>
-  </si>
-  <si>
-    <t>1990000_4000000</t>
-  </si>
-  <si>
-    <t>31_40</t>
-  </si>
-  <si>
     <t>1990000_3000000</t>
-  </si>
-  <si>
-    <t>41_50</t>
   </si>
   <si>
     <t>1990000_2000000</t>
@@ -1536,12 +1653,8 @@
       <c r="E5" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="15">
-        <v>33333333</v>
-      </c>
-      <c r="G5" s="15" t="s">
-        <v>23</v>
-      </c>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15"/>
       <c r="H5" s="16"/>
       <c r="I5" s="19"/>
       <c r="J5" s="19"/>
@@ -1560,14 +1673,10 @@
         <v>21</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="F6" s="15">
-        <v>22222222</v>
-      </c>
-      <c r="G6" s="15" t="s">
-        <v>25</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
       <c r="H6" s="16"/>
       <c r="I6" s="19"/>
       <c r="J6" s="19"/>
@@ -1586,14 +1695,10 @@
         <v>21</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" s="15">
-        <v>11111111</v>
-      </c>
-      <c r="G7" s="15" t="s">
-        <v>27</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="F7" s="15"/>
+      <c r="G7" s="15"/>
       <c r="H7" s="16"/>
       <c r="I7" s="19"/>
       <c r="J7" s="19"/>
@@ -1612,14 +1717,10 @@
         <v>21</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="F8" s="15">
-        <v>5000000</v>
-      </c>
-      <c r="G8" s="15" t="s">
-        <v>29</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="F8" s="15"/>
+      <c r="G8" s="15"/>
       <c r="H8" s="16"/>
       <c r="I8" s="19"/>
       <c r="J8" s="19"/>
@@ -1638,14 +1739,10 @@
         <v>21</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="F9" s="15">
-        <v>3000000</v>
-      </c>
-      <c r="G9" s="15" t="s">
-        <v>29</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="F9" s="15"/>
+      <c r="G9" s="15"/>
       <c r="H9" s="16"/>
       <c r="I9" s="19"/>
       <c r="J9" s="20"/>
@@ -1662,10 +1759,10 @@
         <v>6</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F10" s="15"/>
       <c r="G10" s="15"/>
@@ -1685,10 +1782,10 @@
         <v>7</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F11" s="15"/>
       <c r="G11" s="15"/>
@@ -1708,10 +1805,10 @@
         <v>8</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F12" s="15"/>
       <c r="G12" s="15"/>
@@ -1731,10 +1828,10 @@
         <v>9</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F13" s="15"/>
       <c r="G13" s="15"/>
@@ -1753,10 +1850,10 @@
         <v>10</v>
       </c>
       <c r="D14" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="E14" s="15" t="s">
         <v>31</v>
-      </c>
-      <c r="E14" s="15" t="s">
-        <v>36</v>
       </c>
       <c r="F14" s="15"/>
       <c r="G14" s="15"/>
@@ -1772,13 +1869,13 @@
         <v>1</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F15" s="15"/>
       <c r="G15" s="15"/>
@@ -1795,13 +1892,13 @@
         <v>1</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F16" s="15"/>
       <c r="G16" s="15"/>
@@ -1818,13 +1915,13 @@
         <v>1</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F17" s="15"/>
       <c r="G17" s="15"/>
@@ -1841,13 +1938,13 @@
         <v>1</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F18" s="15"/>
       <c r="G18" s="15"/>
@@ -1870,14 +1967,10 @@
         <v>21</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="F19" s="15">
-        <v>33333333</v>
-      </c>
-      <c r="G19" s="15" t="s">
-        <v>23</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="F19" s="15"/>
+      <c r="G19" s="15"/>
       <c r="H19" s="16"/>
       <c r="I19" s="19"/>
       <c r="J19" s="20"/>
@@ -1897,14 +1990,10 @@
         <v>21</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="F20" s="15">
-        <v>22222222</v>
-      </c>
-      <c r="G20" s="15" t="s">
-        <v>25</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="F20" s="15"/>
+      <c r="G20" s="15"/>
       <c r="H20" s="16"/>
       <c r="I20" s="19"/>
       <c r="J20" s="19"/>
@@ -1924,14 +2013,10 @@
         <v>21</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="F21" s="15">
-        <v>11111111</v>
-      </c>
-      <c r="G21" s="15" t="s">
-        <v>27</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="F21" s="15"/>
+      <c r="G21" s="15"/>
       <c r="H21" s="16"/>
     </row>
     <row r="22" s="3" customFormat="1" spans="1:10">
@@ -1948,14 +2033,10 @@
         <v>21</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="F22" s="15">
-        <v>5000000</v>
-      </c>
-      <c r="G22" s="15" t="s">
-        <v>29</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="F22" s="15"/>
+      <c r="G22" s="15"/>
       <c r="H22" s="16"/>
       <c r="I22" s="19"/>
       <c r="J22" s="20"/>
@@ -1974,14 +2055,10 @@
         <v>21</v>
       </c>
       <c r="E23" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="F23" s="15">
-        <v>3000000</v>
-      </c>
-      <c r="G23" s="15" t="s">
-        <v>29</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="F23" s="15"/>
+      <c r="G23" s="15"/>
       <c r="H23" s="16"/>
       <c r="I23" s="19"/>
       <c r="J23" s="20"/>
@@ -1997,10 +2074,10 @@
         <v>6</v>
       </c>
       <c r="D24" s="16" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="F24" s="15"/>
       <c r="G24" s="15"/>
@@ -2019,10 +2096,10 @@
         <v>7</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E25" s="15" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="F25" s="15"/>
       <c r="G25" s="15"/>
@@ -2041,10 +2118,10 @@
         <v>8</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="F26" s="15"/>
       <c r="G26" s="15"/>
@@ -2063,10 +2140,10 @@
         <v>9</v>
       </c>
       <c r="D27" s="16" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="F27" s="15"/>
       <c r="G27" s="15"/>
@@ -2084,10 +2161,10 @@
         <v>10</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="F28" s="15"/>
       <c r="G28" s="15"/>
@@ -2102,13 +2179,13 @@
         <v>2</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="F29" s="15"/>
       <c r="G29" s="15"/>
@@ -2123,13 +2200,13 @@
         <v>2</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E30" s="15" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F30" s="15"/>
       <c r="G30" s="15"/>
@@ -2144,13 +2221,13 @@
         <v>2</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E31" s="15" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="F31" s="15"/>
       <c r="G31" s="15"/>
@@ -2165,13 +2242,13 @@
         <v>2</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D32" s="16" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E32" s="15" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="F32" s="15"/>
       <c r="G32" s="15"/>
@@ -2192,14 +2269,10 @@
         <v>21</v>
       </c>
       <c r="E33" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="F33" s="15">
-        <v>99999999</v>
-      </c>
-      <c r="G33" s="15" t="s">
-        <v>23</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="F33" s="15"/>
+      <c r="G33" s="15"/>
       <c r="H33" s="16"/>
       <c r="I33" s="19"/>
     </row>
@@ -2217,14 +2290,10 @@
         <v>21</v>
       </c>
       <c r="E34" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="F34" s="15">
-        <v>88888888</v>
-      </c>
-      <c r="G34" s="15" t="s">
-        <v>25</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="F34" s="15"/>
+      <c r="G34" s="15"/>
       <c r="H34" s="16"/>
       <c r="I34" s="19"/>
     </row>
@@ -2242,14 +2311,10 @@
         <v>21</v>
       </c>
       <c r="E35" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="F35" s="15">
-        <v>77777777</v>
-      </c>
-      <c r="G35" s="15" t="s">
-        <v>27</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="F35" s="15"/>
+      <c r="G35" s="15"/>
       <c r="H35" s="16"/>
       <c r="I35" s="19"/>
     </row>
@@ -2267,14 +2332,10 @@
         <v>21</v>
       </c>
       <c r="E36" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="F36" s="15">
-        <v>66666666</v>
-      </c>
-      <c r="G36" s="15" t="s">
-        <v>29</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="F36" s="15"/>
+      <c r="G36" s="15"/>
       <c r="H36" s="16"/>
       <c r="I36" s="19"/>
     </row>
@@ -2292,14 +2353,10 @@
         <v>21</v>
       </c>
       <c r="E37" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="F37" s="15">
-        <v>55555555</v>
-      </c>
-      <c r="G37" s="15" t="s">
-        <v>29</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="F37" s="15"/>
+      <c r="G37" s="15"/>
       <c r="H37" s="16"/>
       <c r="I37" s="19"/>
     </row>
@@ -2314,10 +2371,10 @@
         <v>6</v>
       </c>
       <c r="D38" s="16" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E38" s="15" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="F38" s="15"/>
       <c r="G38" s="15"/>
@@ -2335,10 +2392,10 @@
         <v>7</v>
       </c>
       <c r="D39" s="16" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E39" s="15" t="s">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="F39" s="15"/>
       <c r="G39" s="15"/>
@@ -2356,10 +2413,10 @@
         <v>8</v>
       </c>
       <c r="D40" s="16" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E40" s="15" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="F40" s="15"/>
       <c r="G40" s="15"/>
@@ -2377,10 +2434,10 @@
         <v>9</v>
       </c>
       <c r="D41" s="16" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E41" s="15" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="F41" s="15"/>
       <c r="G41" s="15"/>
@@ -2398,10 +2455,10 @@
         <v>10</v>
       </c>
       <c r="D42" s="16" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E42" s="15" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="F42" s="15"/>
       <c r="G42" s="15"/>
@@ -2416,13 +2473,13 @@
         <v>3</v>
       </c>
       <c r="C43" s="16" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D43" s="16" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E43" s="15" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="F43" s="15"/>
       <c r="G43" s="15"/>
@@ -2437,13 +2494,13 @@
         <v>3</v>
       </c>
       <c r="C44" s="16" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D44" s="16" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E44" s="15" t="s">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="F44" s="15"/>
       <c r="G44" s="15"/>
@@ -2457,13 +2514,13 @@
         <v>3</v>
       </c>
       <c r="C45" s="16" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D45" s="16" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E45" s="15" t="s">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="F45" s="15"/>
       <c r="G45" s="15"/>
@@ -2477,13 +2534,13 @@
         <v>3</v>
       </c>
       <c r="C46" s="16" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D46" s="16" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E46" s="15" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="F46" s="15"/>
       <c r="G46" s="15"/>
@@ -2500,16 +2557,16 @@
         <v>1</v>
       </c>
       <c r="D47" s="18" t="s">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="E47" s="17" t="s">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="F47" s="17">
         <v>33333333</v>
       </c>
       <c r="G47" s="17" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="H47" s="18"/>
       <c r="I47" s="19"/>
@@ -2526,16 +2583,16 @@
         <v>2</v>
       </c>
       <c r="D48" s="18" t="s">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="E48" s="17" t="s">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="F48" s="17">
         <v>22222222</v>
       </c>
       <c r="G48" s="17" t="s">
-        <v>25</v>
+        <v>71</v>
       </c>
       <c r="H48" s="18"/>
       <c r="I48" s="19"/>
@@ -2552,16 +2609,16 @@
         <v>3</v>
       </c>
       <c r="D49" s="18" t="s">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="E49" s="17" t="s">
-        <v>26</v>
+        <v>72</v>
       </c>
       <c r="F49" s="17">
         <v>11111111</v>
       </c>
       <c r="G49" s="17" t="s">
-        <v>27</v>
+        <v>73</v>
       </c>
       <c r="H49" s="18"/>
       <c r="I49" s="19"/>
@@ -2578,16 +2635,16 @@
         <v>4</v>
       </c>
       <c r="D50" s="18" t="s">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="E50" s="17" t="s">
-        <v>28</v>
+        <v>74</v>
       </c>
       <c r="F50" s="17">
         <v>5000000</v>
       </c>
       <c r="G50" s="17" t="s">
-        <v>29</v>
+        <v>75</v>
       </c>
       <c r="H50" s="18"/>
       <c r="I50" s="19"/>
@@ -2604,16 +2661,16 @@
         <v>5</v>
       </c>
       <c r="D51" s="18" t="s">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="E51" s="17" t="s">
-        <v>30</v>
+        <v>76</v>
       </c>
       <c r="F51" s="17">
         <v>3000000</v>
       </c>
       <c r="G51" s="17" t="s">
-        <v>29</v>
+        <v>75</v>
       </c>
       <c r="H51" s="18"/>
       <c r="I51" s="19"/>
@@ -2631,10 +2688,10 @@
         <v>6</v>
       </c>
       <c r="D52" s="18" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E52" s="17" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
       <c r="F52" s="17"/>
       <c r="G52" s="17"/>
@@ -2654,10 +2711,10 @@
         <v>7</v>
       </c>
       <c r="D53" s="18" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E53" s="17" t="s">
-        <v>33</v>
+        <v>78</v>
       </c>
       <c r="F53" s="17"/>
       <c r="G53" s="17"/>
@@ -2677,10 +2734,10 @@
         <v>8</v>
       </c>
       <c r="D54" s="18" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E54" s="17" t="s">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="F54" s="17"/>
       <c r="G54" s="17"/>
@@ -2700,10 +2757,10 @@
         <v>9</v>
       </c>
       <c r="D55" s="18" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E55" s="17" t="s">
-        <v>35</v>
+        <v>79</v>
       </c>
       <c r="F55" s="17"/>
       <c r="G55" s="17"/>
@@ -2722,10 +2779,10 @@
         <v>10</v>
       </c>
       <c r="D56" s="18" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E56" s="17" t="s">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="F56" s="17"/>
       <c r="G56" s="17"/>
@@ -2741,13 +2798,13 @@
         <v>1</v>
       </c>
       <c r="C57" s="18" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D57" s="18" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E57" s="17" t="s">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="F57" s="17"/>
       <c r="G57" s="17"/>
@@ -2764,13 +2821,13 @@
         <v>1</v>
       </c>
       <c r="C58" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D58" s="18" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E58" s="17" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="F58" s="17"/>
       <c r="G58" s="17"/>
@@ -2787,13 +2844,13 @@
         <v>1</v>
       </c>
       <c r="C59" s="18" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D59" s="18" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E59" s="17" t="s">
-        <v>42</v>
+        <v>82</v>
       </c>
       <c r="F59" s="17"/>
       <c r="G59" s="17"/>
@@ -2810,13 +2867,13 @@
         <v>1</v>
       </c>
       <c r="C60" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D60" s="18" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E60" s="17" t="s">
-        <v>44</v>
+        <v>83</v>
       </c>
       <c r="F60" s="17"/>
       <c r="G60" s="17"/>
@@ -2836,16 +2893,16 @@
         <v>1</v>
       </c>
       <c r="D61" s="18" t="s">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="E61" s="17" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="F61" s="17">
         <v>33333333</v>
       </c>
       <c r="G61" s="17" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="H61" s="18"/>
       <c r="I61" s="19"/>
@@ -2863,16 +2920,16 @@
         <v>2</v>
       </c>
       <c r="D62" s="18" t="s">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="E62" s="17" t="s">
-        <v>46</v>
+        <v>85</v>
       </c>
       <c r="F62" s="17">
         <v>22222222</v>
       </c>
       <c r="G62" s="17" t="s">
-        <v>25</v>
+        <v>71</v>
       </c>
       <c r="H62" s="18"/>
       <c r="I62" s="19"/>
@@ -2890,16 +2947,16 @@
         <v>3</v>
       </c>
       <c r="D63" s="18" t="s">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="E63" s="17" t="s">
-        <v>47</v>
+        <v>86</v>
       </c>
       <c r="F63" s="17">
         <v>11111111</v>
       </c>
       <c r="G63" s="17" t="s">
-        <v>27</v>
+        <v>73</v>
       </c>
       <c r="H63" s="18"/>
     </row>
@@ -2914,16 +2971,16 @@
         <v>4</v>
       </c>
       <c r="D64" s="18" t="s">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="E64" s="17" t="s">
-        <v>48</v>
+        <v>87</v>
       </c>
       <c r="F64" s="17">
         <v>5000000</v>
       </c>
       <c r="G64" s="17" t="s">
-        <v>29</v>
+        <v>75</v>
       </c>
       <c r="H64" s="18"/>
       <c r="I64" s="19"/>
@@ -2940,16 +2997,16 @@
         <v>5</v>
       </c>
       <c r="D65" s="18" t="s">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="E65" s="17" t="s">
-        <v>49</v>
+        <v>88</v>
       </c>
       <c r="F65" s="17">
         <v>3000000</v>
       </c>
       <c r="G65" s="17" t="s">
-        <v>29</v>
+        <v>75</v>
       </c>
       <c r="H65" s="18"/>
       <c r="I65" s="19"/>
@@ -2966,10 +3023,10 @@
         <v>6</v>
       </c>
       <c r="D66" s="18" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E66" s="17" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
       <c r="F66" s="17"/>
       <c r="G66" s="17"/>
@@ -2988,10 +3045,10 @@
         <v>7</v>
       </c>
       <c r="D67" s="18" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E67" s="17" t="s">
-        <v>33</v>
+        <v>78</v>
       </c>
       <c r="F67" s="17"/>
       <c r="G67" s="17"/>
@@ -3010,10 +3067,10 @@
         <v>8</v>
       </c>
       <c r="D68" s="18" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E68" s="17" t="s">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="F68" s="17"/>
       <c r="G68" s="17"/>
@@ -3032,10 +3089,10 @@
         <v>9</v>
       </c>
       <c r="D69" s="18" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E69" s="17" t="s">
-        <v>35</v>
+        <v>79</v>
       </c>
       <c r="F69" s="17"/>
       <c r="G69" s="17"/>
@@ -3053,10 +3110,10 @@
         <v>10</v>
       </c>
       <c r="D70" s="18" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E70" s="17" t="s">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="F70" s="17"/>
       <c r="G70" s="17"/>
@@ -3071,13 +3128,13 @@
         <v>2</v>
       </c>
       <c r="C71" s="18" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D71" s="18" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E71" s="17" t="s">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="F71" s="17"/>
       <c r="G71" s="17"/>
@@ -3092,13 +3149,13 @@
         <v>2</v>
       </c>
       <c r="C72" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D72" s="18" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E72" s="17" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="F72" s="17"/>
       <c r="G72" s="17"/>
@@ -3113,13 +3170,13 @@
         <v>2</v>
       </c>
       <c r="C73" s="18" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D73" s="18" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E73" s="17" t="s">
-        <v>42</v>
+        <v>82</v>
       </c>
       <c r="F73" s="17"/>
       <c r="G73" s="17"/>
@@ -3134,13 +3191,13 @@
         <v>2</v>
       </c>
       <c r="C74" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D74" s="18" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E74" s="17" t="s">
-        <v>44</v>
+        <v>83</v>
       </c>
       <c r="F74" s="17"/>
       <c r="G74" s="17"/>
@@ -3158,16 +3215,16 @@
         <v>1</v>
       </c>
       <c r="D75" s="18" t="s">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="E75" s="17" t="s">
-        <v>50</v>
+        <v>89</v>
       </c>
       <c r="F75" s="17">
         <v>99999999</v>
       </c>
       <c r="G75" s="17" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="H75" s="18"/>
       <c r="I75" s="19"/>
@@ -3183,16 +3240,16 @@
         <v>2</v>
       </c>
       <c r="D76" s="18" t="s">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="E76" s="17" t="s">
-        <v>51</v>
+        <v>90</v>
       </c>
       <c r="F76" s="17">
         <v>88888888</v>
       </c>
       <c r="G76" s="17" t="s">
-        <v>25</v>
+        <v>71</v>
       </c>
       <c r="H76" s="18"/>
       <c r="I76" s="19"/>
@@ -3208,16 +3265,16 @@
         <v>3</v>
       </c>
       <c r="D77" s="18" t="s">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="E77" s="17" t="s">
-        <v>52</v>
+        <v>91</v>
       </c>
       <c r="F77" s="17">
         <v>77777777</v>
       </c>
       <c r="G77" s="17" t="s">
-        <v>27</v>
+        <v>73</v>
       </c>
       <c r="H77" s="18"/>
       <c r="I77" s="19"/>
@@ -3233,16 +3290,16 @@
         <v>4</v>
       </c>
       <c r="D78" s="18" t="s">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="E78" s="17" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="F78" s="17">
         <v>66666666</v>
       </c>
       <c r="G78" s="17" t="s">
-        <v>29</v>
+        <v>75</v>
       </c>
       <c r="H78" s="18"/>
       <c r="I78" s="19"/>
@@ -3258,16 +3315,16 @@
         <v>5</v>
       </c>
       <c r="D79" s="18" t="s">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="E79" s="17" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="F79" s="17">
         <v>55555555</v>
       </c>
       <c r="G79" s="17" t="s">
-        <v>29</v>
+        <v>75</v>
       </c>
       <c r="H79" s="18"/>
       <c r="I79" s="19"/>
@@ -3283,10 +3340,10 @@
         <v>6</v>
       </c>
       <c r="D80" s="18" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E80" s="17" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
       <c r="F80" s="17"/>
       <c r="G80" s="17"/>
@@ -3304,10 +3361,10 @@
         <v>7</v>
       </c>
       <c r="D81" s="18" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E81" s="17" t="s">
-        <v>33</v>
+        <v>78</v>
       </c>
       <c r="F81" s="17"/>
       <c r="G81" s="17"/>
@@ -3325,10 +3382,10 @@
         <v>8</v>
       </c>
       <c r="D82" s="18" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E82" s="17" t="s">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="F82" s="17"/>
       <c r="G82" s="17"/>
@@ -3346,10 +3403,10 @@
         <v>9</v>
       </c>
       <c r="D83" s="18" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E83" s="17" t="s">
-        <v>35</v>
+        <v>79</v>
       </c>
       <c r="F83" s="17"/>
       <c r="G83" s="17"/>
@@ -3367,10 +3424,10 @@
         <v>10</v>
       </c>
       <c r="D84" s="18" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E84" s="17" t="s">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="F84" s="17"/>
       <c r="G84" s="17"/>
@@ -3385,13 +3442,13 @@
         <v>3</v>
       </c>
       <c r="C85" s="18" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D85" s="18" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E85" s="17" t="s">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="F85" s="17"/>
       <c r="G85" s="17"/>
@@ -3406,13 +3463,13 @@
         <v>3</v>
       </c>
       <c r="C86" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D86" s="18" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E86" s="17" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="F86" s="17"/>
       <c r="G86" s="17"/>
@@ -3426,13 +3483,13 @@
         <v>3</v>
       </c>
       <c r="C87" s="18" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D87" s="18" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E87" s="17" t="s">
-        <v>42</v>
+        <v>82</v>
       </c>
       <c r="F87" s="17"/>
       <c r="G87" s="17"/>
@@ -3446,13 +3503,13 @@
         <v>3</v>
       </c>
       <c r="C88" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D88" s="18" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E88" s="17" t="s">
-        <v>44</v>
+        <v>83</v>
       </c>
       <c r="F88" s="17"/>
       <c r="G88" s="17"/>

--- a/table/resources/sample/PointsAwardRanking.xlsx
+++ b/table/resources/sample/PointsAwardRanking.xlsx
@@ -143,7 +143,8 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-该资源是需要下载的，配置资源名称</t>
+该资源是需要下载的，配置资源名称
+资源尺寸大小：308 * 184 </t>
         </r>
       </text>
     </comment>
@@ -175,7 +176,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="75">
   <si>
     <t>序列ID</t>
   </si>
@@ -246,12 +247,21 @@
     <t>1990000_870000</t>
   </si>
   <si>
+    <t>jfdj_box_1.png</t>
+  </si>
+  <si>
     <t>1990000_660000</t>
   </si>
   <si>
+    <t>jfdj_box_2.png</t>
+  </si>
+  <si>
     <t>1990000_480000</t>
   </si>
   <si>
+    <t>jfdj_box_3.png</t>
+  </si>
+  <si>
     <t>1990000_360000</t>
   </si>
   <si>
@@ -378,85 +388,19 @@
     <t>1990000_4000000</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>其它道具名称1_1</t>
-  </si>
-  <si>
     <t>wdcc_ccb_1.png</t>
   </si>
   <si>
-    <t>其它道具名称2_1</t>
+    <t>2026/08/01 00:00:00</t>
   </si>
   <si>
     <t>wdcc_ccb_2.png</t>
   </si>
   <si>
-    <t>其它道具名称3_1</t>
-  </si>
-  <si>
     <t>wdcc_ccb_3.png</t>
   </si>
   <si>
-    <t>其它道具名称4_1</t>
-  </si>
-  <si>
     <t>itemicon_1010101.png</t>
-  </si>
-  <si>
-    <t>其它道具名称5_1</t>
-  </si>
-  <si>
-    <t>1990000_10000000</t>
-  </si>
-  <si>
-    <t>1990000_9000000</t>
-  </si>
-  <si>
-    <t>1990000_7000000</t>
-  </si>
-  <si>
-    <t>1990000_6000000</t>
-  </si>
-  <si>
-    <t>1990000_5000000</t>
-  </si>
-  <si>
-    <t>1990000_3000000</t>
-  </si>
-  <si>
-    <t>1990000_2000000</t>
-  </si>
-  <si>
-    <t>其它道具名称6_1</t>
-  </si>
-  <si>
-    <t>其它道具名称7_1</t>
-  </si>
-  <si>
-    <t>其它道具名称8_1</t>
-  </si>
-  <si>
-    <t>其它道具名称9_1</t>
-  </si>
-  <si>
-    <t>其它道具名称10_1</t>
-  </si>
-  <si>
-    <t>其它道具名称11_1</t>
-  </si>
-  <si>
-    <t>其它道具名称12_1</t>
-  </si>
-  <si>
-    <t>其它道具名称13_1</t>
-  </si>
-  <si>
-    <t>其它道具名称14_1</t>
-  </si>
-  <si>
-    <t>其它道具名称15_1</t>
   </si>
 </sst>
 </file>
@@ -1537,13 +1481,13 @@
   <dimension ref="A1:L88"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="10.375" style="4" customWidth="1"/>
-    <col min="2" max="2" width="13.5" style="4" customWidth="1"/>
-    <col min="3" max="3" width="13" style="5" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="5" customWidth="1"/>
-    <col min="5" max="5" width="21.125" style="4" customWidth="1"/>
-    <col min="6" max="6" width="14.5" style="6" customWidth="1"/>
-    <col min="7" max="7" width="16.5" style="6" customWidth="1"/>
+    <col min="1" max="1" width="7" style="4" customWidth="1"/>
+    <col min="2" max="2" width="8.875" style="4" customWidth="1"/>
+    <col min="3" max="3" width="11.375" style="5" customWidth="1"/>
+    <col min="4" max="4" width="11.5" style="5" customWidth="1"/>
+    <col min="5" max="5" width="21.375" style="4" customWidth="1"/>
+    <col min="6" max="6" width="10.375" style="6" customWidth="1"/>
+    <col min="7" max="7" width="23.625" style="6" customWidth="1"/>
     <col min="8" max="8" width="21.25" style="7" customWidth="1"/>
     <col min="9" max="10" width="14.5" style="8" customWidth="1"/>
     <col min="11" max="16384" width="9" style="4"/>
@@ -1654,7 +1598,9 @@
         <v>22</v>
       </c>
       <c r="F5" s="15"/>
-      <c r="G5" s="15"/>
+      <c r="G5" s="15" t="s">
+        <v>23</v>
+      </c>
       <c r="H5" s="16"/>
       <c r="I5" s="19"/>
       <c r="J5" s="19"/>
@@ -1673,10 +1619,12 @@
         <v>21</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
+      <c r="G6" s="15" t="s">
+        <v>25</v>
+      </c>
       <c r="H6" s="16"/>
       <c r="I6" s="19"/>
       <c r="J6" s="19"/>
@@ -1695,10 +1643,12 @@
         <v>21</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
+      <c r="G7" s="15" t="s">
+        <v>27</v>
+      </c>
       <c r="H7" s="16"/>
       <c r="I7" s="19"/>
       <c r="J7" s="19"/>
@@ -1717,7 +1667,7 @@
         <v>21</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F8" s="15"/>
       <c r="G8" s="15"/>
@@ -1739,7 +1689,7 @@
         <v>21</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F9" s="15"/>
       <c r="G9" s="15"/>
@@ -1762,7 +1712,7 @@
         <v>21</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F10" s="15"/>
       <c r="G10" s="15"/>
@@ -1785,7 +1735,7 @@
         <v>21</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F11" s="15"/>
       <c r="G11" s="15"/>
@@ -1808,7 +1758,7 @@
         <v>21</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F12" s="15"/>
       <c r="G12" s="15"/>
@@ -1831,7 +1781,7 @@
         <v>21</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F13" s="15"/>
       <c r="G13" s="15"/>
@@ -1853,7 +1803,7 @@
         <v>21</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F14" s="15"/>
       <c r="G14" s="15"/>
@@ -1869,13 +1819,13 @@
         <v>1</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D15" s="16" t="s">
         <v>21</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F15" s="15"/>
       <c r="G15" s="15"/>
@@ -1892,13 +1842,13 @@
         <v>1</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D16" s="16" t="s">
         <v>21</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F16" s="15"/>
       <c r="G16" s="15"/>
@@ -1915,13 +1865,13 @@
         <v>1</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D17" s="16" t="s">
         <v>21</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F17" s="15"/>
       <c r="G17" s="15"/>
@@ -1938,13 +1888,13 @@
         <v>1</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D18" s="16" t="s">
         <v>21</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F18" s="15"/>
       <c r="G18" s="15"/>
@@ -1967,10 +1917,12 @@
         <v>21</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F19" s="15"/>
-      <c r="G19" s="15"/>
+      <c r="G19" s="15" t="s">
+        <v>23</v>
+      </c>
       <c r="H19" s="16"/>
       <c r="I19" s="19"/>
       <c r="J19" s="20"/>
@@ -1990,10 +1942,12 @@
         <v>21</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F20" s="15"/>
-      <c r="G20" s="15"/>
+      <c r="G20" s="15" t="s">
+        <v>25</v>
+      </c>
       <c r="H20" s="16"/>
       <c r="I20" s="19"/>
       <c r="J20" s="19"/>
@@ -2013,10 +1967,12 @@
         <v>21</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F21" s="15"/>
-      <c r="G21" s="15"/>
+      <c r="G21" s="15" t="s">
+        <v>27</v>
+      </c>
       <c r="H21" s="16"/>
     </row>
     <row r="22" s="3" customFormat="1" spans="1:10">
@@ -2033,7 +1989,7 @@
         <v>21</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F22" s="15"/>
       <c r="G22" s="15"/>
@@ -2055,7 +2011,7 @@
         <v>21</v>
       </c>
       <c r="E23" s="15" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F23" s="15"/>
       <c r="G23" s="15"/>
@@ -2077,7 +2033,7 @@
         <v>21</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F24" s="15"/>
       <c r="G24" s="15"/>
@@ -2099,7 +2055,7 @@
         <v>21</v>
       </c>
       <c r="E25" s="15" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F25" s="15"/>
       <c r="G25" s="15"/>
@@ -2121,7 +2077,7 @@
         <v>21</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F26" s="15"/>
       <c r="G26" s="15"/>
@@ -2143,7 +2099,7 @@
         <v>21</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F27" s="15"/>
       <c r="G27" s="15"/>
@@ -2164,7 +2120,7 @@
         <v>21</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F28" s="15"/>
       <c r="G28" s="15"/>
@@ -2179,13 +2135,13 @@
         <v>2</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D29" s="16" t="s">
         <v>21</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F29" s="15"/>
       <c r="G29" s="15"/>
@@ -2200,13 +2156,13 @@
         <v>2</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D30" s="16" t="s">
         <v>21</v>
       </c>
       <c r="E30" s="15" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F30" s="15"/>
       <c r="G30" s="15"/>
@@ -2221,13 +2177,13 @@
         <v>2</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D31" s="16" t="s">
         <v>21</v>
       </c>
       <c r="E31" s="15" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F31" s="15"/>
       <c r="G31" s="15"/>
@@ -2242,13 +2198,13 @@
         <v>2</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D32" s="16" t="s">
         <v>21</v>
       </c>
       <c r="E32" s="15" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F32" s="15"/>
       <c r="G32" s="15"/>
@@ -2269,10 +2225,12 @@
         <v>21</v>
       </c>
       <c r="E33" s="15" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F33" s="15"/>
-      <c r="G33" s="15"/>
+      <c r="G33" s="15" t="s">
+        <v>23</v>
+      </c>
       <c r="H33" s="16"/>
       <c r="I33" s="19"/>
     </row>
@@ -2290,10 +2248,12 @@
         <v>21</v>
       </c>
       <c r="E34" s="15" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F34" s="15"/>
-      <c r="G34" s="15"/>
+      <c r="G34" s="15" t="s">
+        <v>25</v>
+      </c>
       <c r="H34" s="16"/>
       <c r="I34" s="19"/>
     </row>
@@ -2311,10 +2271,12 @@
         <v>21</v>
       </c>
       <c r="E35" s="15" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F35" s="15"/>
-      <c r="G35" s="15"/>
+      <c r="G35" s="15" t="s">
+        <v>27</v>
+      </c>
       <c r="H35" s="16"/>
       <c r="I35" s="19"/>
     </row>
@@ -2332,7 +2294,7 @@
         <v>21</v>
       </c>
       <c r="E36" s="15" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F36" s="15"/>
       <c r="G36" s="15"/>
@@ -2353,7 +2315,7 @@
         <v>21</v>
       </c>
       <c r="E37" s="15" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F37" s="15"/>
       <c r="G37" s="15"/>
@@ -2374,7 +2336,7 @@
         <v>21</v>
       </c>
       <c r="E38" s="15" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F38" s="15"/>
       <c r="G38" s="15"/>
@@ -2395,7 +2357,7 @@
         <v>21</v>
       </c>
       <c r="E39" s="15" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F39" s="15"/>
       <c r="G39" s="15"/>
@@ -2416,7 +2378,7 @@
         <v>21</v>
       </c>
       <c r="E40" s="15" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F40" s="15"/>
       <c r="G40" s="15"/>
@@ -2437,7 +2399,7 @@
         <v>21</v>
       </c>
       <c r="E41" s="15" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F41" s="15"/>
       <c r="G41" s="15"/>
@@ -2458,7 +2420,7 @@
         <v>21</v>
       </c>
       <c r="E42" s="15" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F42" s="15"/>
       <c r="G42" s="15"/>
@@ -2473,13 +2435,13 @@
         <v>3</v>
       </c>
       <c r="C43" s="16" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D43" s="16" t="s">
         <v>21</v>
       </c>
       <c r="E43" s="15" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F43" s="15"/>
       <c r="G43" s="15"/>
@@ -2494,13 +2456,13 @@
         <v>3</v>
       </c>
       <c r="C44" s="16" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D44" s="16" t="s">
         <v>21</v>
       </c>
       <c r="E44" s="15" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F44" s="15"/>
       <c r="G44" s="15"/>
@@ -2514,13 +2476,13 @@
         <v>3</v>
       </c>
       <c r="C45" s="16" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D45" s="16" t="s">
         <v>21</v>
       </c>
       <c r="E45" s="15" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F45" s="15"/>
       <c r="G45" s="15"/>
@@ -2534,13 +2496,13 @@
         <v>3</v>
       </c>
       <c r="C46" s="16" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D46" s="16" t="s">
         <v>21</v>
       </c>
       <c r="E46" s="15" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F46" s="15"/>
       <c r="G46" s="15"/>
@@ -2557,18 +2519,20 @@
         <v>1</v>
       </c>
       <c r="D47" s="18" t="s">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="E47" s="17" t="s">
-        <v>68</v>
+        <v>22</v>
       </c>
       <c r="F47" s="17">
         <v>33333333</v>
       </c>
       <c r="G47" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="H47" s="18"/>
+        <v>70</v>
+      </c>
+      <c r="H47" s="18" t="s">
+        <v>71</v>
+      </c>
       <c r="I47" s="19"/>
       <c r="J47" s="19"/>
     </row>
@@ -2583,18 +2547,20 @@
         <v>2</v>
       </c>
       <c r="D48" s="18" t="s">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="E48" s="17" t="s">
-        <v>70</v>
+        <v>24</v>
       </c>
       <c r="F48" s="17">
         <v>22222222</v>
       </c>
       <c r="G48" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="H48" s="18"/>
+        <v>72</v>
+      </c>
+      <c r="H48" s="18" t="s">
+        <v>71</v>
+      </c>
       <c r="I48" s="19"/>
       <c r="J48" s="19"/>
     </row>
@@ -2609,10 +2575,10 @@
         <v>3</v>
       </c>
       <c r="D49" s="18" t="s">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="E49" s="17" t="s">
-        <v>72</v>
+        <v>26</v>
       </c>
       <c r="F49" s="17">
         <v>11111111</v>
@@ -2620,7 +2586,9 @@
       <c r="G49" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="H49" s="18"/>
+      <c r="H49" s="18" t="s">
+        <v>71</v>
+      </c>
       <c r="I49" s="19"/>
       <c r="J49" s="19"/>
     </row>
@@ -2635,18 +2603,20 @@
         <v>4</v>
       </c>
       <c r="D50" s="18" t="s">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="E50" s="17" t="s">
-        <v>74</v>
+        <v>28</v>
       </c>
       <c r="F50" s="17">
         <v>5000000</v>
       </c>
       <c r="G50" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="H50" s="18"/>
+        <v>74</v>
+      </c>
+      <c r="H50" s="18" t="s">
+        <v>71</v>
+      </c>
       <c r="I50" s="19"/>
       <c r="J50" s="19"/>
     </row>
@@ -2661,18 +2631,20 @@
         <v>5</v>
       </c>
       <c r="D51" s="18" t="s">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="E51" s="17" t="s">
-        <v>76</v>
+        <v>29</v>
       </c>
       <c r="F51" s="17">
         <v>3000000</v>
       </c>
       <c r="G51" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="H51" s="18"/>
+        <v>74</v>
+      </c>
+      <c r="H51" s="18" t="s">
+        <v>71</v>
+      </c>
       <c r="I51" s="19"/>
       <c r="J51" s="20"/>
       <c r="L51" s="2"/>
@@ -2691,11 +2663,13 @@
         <v>21</v>
       </c>
       <c r="E52" s="17" t="s">
-        <v>77</v>
+        <v>30</v>
       </c>
       <c r="F52" s="17"/>
       <c r="G52" s="17"/>
-      <c r="H52" s="18"/>
+      <c r="H52" s="18" t="s">
+        <v>71</v>
+      </c>
       <c r="I52" s="19"/>
       <c r="J52" s="20"/>
       <c r="L52" s="2"/>
@@ -2714,11 +2688,13 @@
         <v>21</v>
       </c>
       <c r="E53" s="17" t="s">
-        <v>78</v>
+        <v>31</v>
       </c>
       <c r="F53" s="17"/>
       <c r="G53" s="17"/>
-      <c r="H53" s="18"/>
+      <c r="H53" s="18" t="s">
+        <v>71</v>
+      </c>
       <c r="I53" s="19"/>
       <c r="J53" s="20"/>
       <c r="L53" s="2"/>
@@ -2737,11 +2713,13 @@
         <v>21</v>
       </c>
       <c r="E54" s="17" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="F54" s="17"/>
       <c r="G54" s="17"/>
-      <c r="H54" s="18"/>
+      <c r="H54" s="18" t="s">
+        <v>71</v>
+      </c>
       <c r="I54" s="19"/>
       <c r="J54" s="20"/>
       <c r="L54" s="2"/>
@@ -2760,11 +2738,13 @@
         <v>21</v>
       </c>
       <c r="E55" s="17" t="s">
-        <v>79</v>
+        <v>33</v>
       </c>
       <c r="F55" s="17"/>
       <c r="G55" s="17"/>
-      <c r="H55" s="18"/>
+      <c r="H55" s="18" t="s">
+        <v>71</v>
+      </c>
       <c r="I55" s="19"/>
       <c r="L55" s="2"/>
     </row>
@@ -2782,11 +2762,13 @@
         <v>21</v>
       </c>
       <c r="E56" s="17" t="s">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="F56" s="17"/>
       <c r="G56" s="17"/>
-      <c r="H56" s="18"/>
+      <c r="H56" s="18" t="s">
+        <v>71</v>
+      </c>
       <c r="I56" s="19"/>
       <c r="L56" s="2"/>
     </row>
@@ -2798,17 +2780,19 @@
         <v>1</v>
       </c>
       <c r="C57" s="18" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D57" s="18" t="s">
         <v>21</v>
       </c>
       <c r="E57" s="17" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="F57" s="17"/>
       <c r="G57" s="17"/>
-      <c r="H57" s="18"/>
+      <c r="H57" s="18" t="s">
+        <v>71</v>
+      </c>
       <c r="I57" s="19"/>
       <c r="J57" s="8"/>
       <c r="L57" s="2"/>
@@ -2821,17 +2805,19 @@
         <v>1</v>
       </c>
       <c r="C58" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D58" s="18" t="s">
         <v>21</v>
       </c>
       <c r="E58" s="17" t="s">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="F58" s="17"/>
       <c r="G58" s="17"/>
-      <c r="H58" s="18"/>
+      <c r="H58" s="18" t="s">
+        <v>71</v>
+      </c>
       <c r="I58" s="19"/>
       <c r="J58" s="20"/>
       <c r="L58" s="2"/>
@@ -2844,17 +2830,19 @@
         <v>1</v>
       </c>
       <c r="C59" s="18" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D59" s="18" t="s">
         <v>21</v>
       </c>
       <c r="E59" s="17" t="s">
-        <v>82</v>
+        <v>40</v>
       </c>
       <c r="F59" s="17"/>
       <c r="G59" s="17"/>
-      <c r="H59" s="18"/>
+      <c r="H59" s="18" t="s">
+        <v>71</v>
+      </c>
       <c r="I59" s="19"/>
       <c r="J59" s="20"/>
       <c r="L59" s="2"/>
@@ -2867,17 +2855,19 @@
         <v>1</v>
       </c>
       <c r="C60" s="18" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D60" s="18" t="s">
         <v>21</v>
       </c>
       <c r="E60" s="17" t="s">
-        <v>83</v>
+        <v>42</v>
       </c>
       <c r="F60" s="17"/>
       <c r="G60" s="17"/>
-      <c r="H60" s="18"/>
+      <c r="H60" s="18" t="s">
+        <v>71</v>
+      </c>
       <c r="I60" s="19"/>
       <c r="J60" s="20"/>
       <c r="L60" s="2"/>
@@ -2893,18 +2883,20 @@
         <v>1</v>
       </c>
       <c r="D61" s="18" t="s">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="E61" s="17" t="s">
-        <v>84</v>
+        <v>43</v>
       </c>
       <c r="F61" s="17">
         <v>33333333</v>
       </c>
       <c r="G61" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="H61" s="18"/>
+        <v>70</v>
+      </c>
+      <c r="H61" s="18" t="s">
+        <v>71</v>
+      </c>
       <c r="I61" s="19"/>
       <c r="J61" s="20"/>
       <c r="L61" s="2"/>
@@ -2920,18 +2912,20 @@
         <v>2</v>
       </c>
       <c r="D62" s="18" t="s">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="E62" s="17" t="s">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="F62" s="17">
         <v>22222222</v>
       </c>
       <c r="G62" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="H62" s="18"/>
+        <v>72</v>
+      </c>
+      <c r="H62" s="18" t="s">
+        <v>71</v>
+      </c>
       <c r="I62" s="19"/>
       <c r="J62" s="19"/>
       <c r="L62" s="2"/>
@@ -2947,10 +2941,10 @@
         <v>3</v>
       </c>
       <c r="D63" s="18" t="s">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="E63" s="17" t="s">
-        <v>86</v>
+        <v>45</v>
       </c>
       <c r="F63" s="17">
         <v>11111111</v>
@@ -2958,7 +2952,9 @@
       <c r="G63" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="H63" s="18"/>
+      <c r="H63" s="18" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="64" s="3" customFormat="1" spans="1:10">
       <c r="A64" s="17">
@@ -2971,18 +2967,20 @@
         <v>4</v>
       </c>
       <c r="D64" s="18" t="s">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="E64" s="17" t="s">
-        <v>87</v>
+        <v>46</v>
       </c>
       <c r="F64" s="17">
         <v>5000000</v>
       </c>
       <c r="G64" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="H64" s="18"/>
+        <v>74</v>
+      </c>
+      <c r="H64" s="18" t="s">
+        <v>71</v>
+      </c>
       <c r="I64" s="19"/>
       <c r="J64" s="20"/>
     </row>
@@ -2997,18 +2995,20 @@
         <v>5</v>
       </c>
       <c r="D65" s="18" t="s">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="E65" s="17" t="s">
-        <v>88</v>
+        <v>47</v>
       </c>
       <c r="F65" s="17">
         <v>3000000</v>
       </c>
       <c r="G65" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="H65" s="18"/>
+        <v>74</v>
+      </c>
+      <c r="H65" s="18" t="s">
+        <v>71</v>
+      </c>
       <c r="I65" s="19"/>
       <c r="J65" s="20"/>
     </row>
@@ -3026,11 +3026,13 @@
         <v>21</v>
       </c>
       <c r="E66" s="17" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="F66" s="17"/>
       <c r="G66" s="17"/>
-      <c r="H66" s="18"/>
+      <c r="H66" s="18" t="s">
+        <v>71</v>
+      </c>
       <c r="I66" s="19"/>
       <c r="J66" s="20"/>
     </row>
@@ -3048,11 +3050,13 @@
         <v>21</v>
       </c>
       <c r="E67" s="17" t="s">
-        <v>78</v>
+        <v>49</v>
       </c>
       <c r="F67" s="17"/>
       <c r="G67" s="17"/>
-      <c r="H67" s="18"/>
+      <c r="H67" s="18" t="s">
+        <v>71</v>
+      </c>
       <c r="I67" s="19"/>
       <c r="J67" s="20"/>
     </row>
@@ -3070,11 +3074,13 @@
         <v>21</v>
       </c>
       <c r="E68" s="17" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="F68" s="17"/>
       <c r="G68" s="17"/>
-      <c r="H68" s="18"/>
+      <c r="H68" s="18" t="s">
+        <v>71</v>
+      </c>
       <c r="I68" s="19"/>
       <c r="J68" s="19"/>
     </row>
@@ -3092,11 +3098,13 @@
         <v>21</v>
       </c>
       <c r="E69" s="17" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="F69" s="17"/>
       <c r="G69" s="17"/>
-      <c r="H69" s="18"/>
+      <c r="H69" s="18" t="s">
+        <v>71</v>
+      </c>
       <c r="I69" s="19"/>
     </row>
     <row r="70" spans="1:9">
@@ -3113,11 +3121,13 @@
         <v>21</v>
       </c>
       <c r="E70" s="17" t="s">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="F70" s="17"/>
       <c r="G70" s="17"/>
-      <c r="H70" s="18"/>
+      <c r="H70" s="18" t="s">
+        <v>71</v>
+      </c>
       <c r="I70" s="19"/>
     </row>
     <row r="71" spans="1:9">
@@ -3128,17 +3138,19 @@
         <v>2</v>
       </c>
       <c r="C71" s="18" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D71" s="18" t="s">
         <v>21</v>
       </c>
       <c r="E71" s="17" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="F71" s="17"/>
       <c r="G71" s="17"/>
-      <c r="H71" s="18"/>
+      <c r="H71" s="18" t="s">
+        <v>71</v>
+      </c>
       <c r="I71" s="19"/>
     </row>
     <row r="72" spans="1:9">
@@ -3149,17 +3161,19 @@
         <v>2</v>
       </c>
       <c r="C72" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D72" s="18" t="s">
         <v>21</v>
       </c>
       <c r="E72" s="17" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="F72" s="17"/>
       <c r="G72" s="17"/>
-      <c r="H72" s="18"/>
+      <c r="H72" s="18" t="s">
+        <v>71</v>
+      </c>
       <c r="I72" s="19"/>
     </row>
     <row r="73" spans="1:9">
@@ -3170,17 +3184,19 @@
         <v>2</v>
       </c>
       <c r="C73" s="18" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D73" s="18" t="s">
         <v>21</v>
       </c>
       <c r="E73" s="17" t="s">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="F73" s="17"/>
       <c r="G73" s="17"/>
-      <c r="H73" s="18"/>
+      <c r="H73" s="18" t="s">
+        <v>71</v>
+      </c>
       <c r="I73" s="19"/>
     </row>
     <row r="74" spans="1:9">
@@ -3191,17 +3207,19 @@
         <v>2</v>
       </c>
       <c r="C74" s="18" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D74" s="18" t="s">
         <v>21</v>
       </c>
       <c r="E74" s="17" t="s">
-        <v>83</v>
+        <v>55</v>
       </c>
       <c r="F74" s="17"/>
       <c r="G74" s="17"/>
-      <c r="H74" s="18"/>
+      <c r="H74" s="18" t="s">
+        <v>71</v>
+      </c>
       <c r="I74" s="19"/>
     </row>
     <row r="75" spans="1:9">
@@ -3215,18 +3233,20 @@
         <v>1</v>
       </c>
       <c r="D75" s="18" t="s">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="E75" s="17" t="s">
-        <v>89</v>
+        <v>56</v>
       </c>
       <c r="F75" s="17">
         <v>99999999</v>
       </c>
       <c r="G75" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="H75" s="18"/>
+        <v>70</v>
+      </c>
+      <c r="H75" s="18" t="s">
+        <v>71</v>
+      </c>
       <c r="I75" s="19"/>
     </row>
     <row r="76" spans="1:9">
@@ -3240,18 +3260,20 @@
         <v>2</v>
       </c>
       <c r="D76" s="18" t="s">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="E76" s="17" t="s">
-        <v>90</v>
+        <v>57</v>
       </c>
       <c r="F76" s="17">
         <v>88888888</v>
       </c>
       <c r="G76" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="H76" s="18"/>
+        <v>72</v>
+      </c>
+      <c r="H76" s="18" t="s">
+        <v>71</v>
+      </c>
       <c r="I76" s="19"/>
     </row>
     <row r="77" spans="1:9">
@@ -3265,10 +3287,10 @@
         <v>3</v>
       </c>
       <c r="D77" s="18" t="s">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="E77" s="17" t="s">
-        <v>91</v>
+        <v>58</v>
       </c>
       <c r="F77" s="17">
         <v>77777777</v>
@@ -3276,7 +3298,9 @@
       <c r="G77" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="H77" s="18"/>
+      <c r="H77" s="18" t="s">
+        <v>71</v>
+      </c>
       <c r="I77" s="19"/>
     </row>
     <row r="78" spans="1:9">
@@ -3290,18 +3314,20 @@
         <v>4</v>
       </c>
       <c r="D78" s="18" t="s">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="E78" s="17" t="s">
-        <v>92</v>
+        <v>59</v>
       </c>
       <c r="F78" s="17">
         <v>66666666</v>
       </c>
       <c r="G78" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="H78" s="18"/>
+        <v>74</v>
+      </c>
+      <c r="H78" s="18" t="s">
+        <v>71</v>
+      </c>
       <c r="I78" s="19"/>
     </row>
     <row r="79" spans="1:9">
@@ -3315,18 +3341,20 @@
         <v>5</v>
       </c>
       <c r="D79" s="18" t="s">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="E79" s="17" t="s">
-        <v>93</v>
+        <v>60</v>
       </c>
       <c r="F79" s="17">
         <v>55555555</v>
       </c>
       <c r="G79" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="H79" s="18"/>
+        <v>74</v>
+      </c>
+      <c r="H79" s="18" t="s">
+        <v>71</v>
+      </c>
       <c r="I79" s="19"/>
     </row>
     <row r="80" spans="1:9">
@@ -3343,11 +3371,13 @@
         <v>21</v>
       </c>
       <c r="E80" s="17" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="F80" s="17"/>
       <c r="G80" s="17"/>
-      <c r="H80" s="18"/>
+      <c r="H80" s="18" t="s">
+        <v>71</v>
+      </c>
       <c r="I80" s="19"/>
     </row>
     <row r="81" spans="1:9">
@@ -3364,11 +3394,13 @@
         <v>21</v>
       </c>
       <c r="E81" s="17" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="F81" s="17"/>
       <c r="G81" s="17"/>
-      <c r="H81" s="18"/>
+      <c r="H81" s="18" t="s">
+        <v>71</v>
+      </c>
       <c r="I81" s="19"/>
     </row>
     <row r="82" spans="1:9">
@@ -3385,11 +3417,13 @@
         <v>21</v>
       </c>
       <c r="E82" s="17" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F82" s="17"/>
       <c r="G82" s="17"/>
-      <c r="H82" s="18"/>
+      <c r="H82" s="18" t="s">
+        <v>71</v>
+      </c>
       <c r="I82" s="19"/>
     </row>
     <row r="83" spans="1:9">
@@ -3406,11 +3440,13 @@
         <v>21</v>
       </c>
       <c r="E83" s="17" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="F83" s="17"/>
       <c r="G83" s="17"/>
-      <c r="H83" s="18"/>
+      <c r="H83" s="18" t="s">
+        <v>71</v>
+      </c>
       <c r="I83" s="19"/>
     </row>
     <row r="84" spans="1:9">
@@ -3427,11 +3463,13 @@
         <v>21</v>
       </c>
       <c r="E84" s="17" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="F84" s="17"/>
       <c r="G84" s="17"/>
-      <c r="H84" s="18"/>
+      <c r="H84" s="18" t="s">
+        <v>71</v>
+      </c>
       <c r="I84" s="19"/>
     </row>
     <row r="85" spans="1:9">
@@ -3442,17 +3480,19 @@
         <v>3</v>
       </c>
       <c r="C85" s="18" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D85" s="18" t="s">
         <v>21</v>
       </c>
       <c r="E85" s="17" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="F85" s="17"/>
       <c r="G85" s="17"/>
-      <c r="H85" s="18"/>
+      <c r="H85" s="18" t="s">
+        <v>71</v>
+      </c>
       <c r="I85" s="19"/>
     </row>
     <row r="86" spans="1:8">
@@ -3463,17 +3503,19 @@
         <v>3</v>
       </c>
       <c r="C86" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D86" s="18" t="s">
         <v>21</v>
       </c>
       <c r="E86" s="17" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F86" s="17"/>
       <c r="G86" s="17"/>
-      <c r="H86" s="18"/>
+      <c r="H86" s="18" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="87" spans="1:8">
       <c r="A87" s="17">
@@ -3483,17 +3525,19 @@
         <v>3</v>
       </c>
       <c r="C87" s="18" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D87" s="18" t="s">
         <v>21</v>
       </c>
       <c r="E87" s="17" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="F87" s="17"/>
       <c r="G87" s="17"/>
-      <c r="H87" s="18"/>
+      <c r="H87" s="18" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="88" spans="1:8">
       <c r="A88" s="17">
@@ -3503,17 +3547,19 @@
         <v>3</v>
       </c>
       <c r="C88" s="18" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D88" s="18" t="s">
         <v>21</v>
       </c>
       <c r="E88" s="17" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="F88" s="17"/>
       <c r="G88" s="17"/>
-      <c r="H88" s="18"/>
+      <c r="H88" s="18" t="s">
+        <v>71</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/table/resources/sample/PointsAwardRanking.xlsx
+++ b/table/resources/sample/PointsAwardRanking.xlsx
@@ -244,148 +244,148 @@
     <t>2</t>
   </si>
   <si>
-    <t>1990000_870000</t>
+    <t>1990000_6090000</t>
   </si>
   <si>
     <t>jfdj_box_1.png</t>
   </si>
   <si>
-    <t>1990000_660000</t>
+    <t>1990000_4620000</t>
   </si>
   <si>
     <t>jfdj_box_2.png</t>
   </si>
   <si>
-    <t>1990000_480000</t>
+    <t>1990000_3360000</t>
   </si>
   <si>
     <t>jfdj_box_3.png</t>
   </si>
   <si>
-    <t>1990000_360000</t>
-  </si>
-  <si>
-    <t>1990000_330000</t>
-  </si>
-  <si>
-    <t>1990000_300000</t>
-  </si>
-  <si>
-    <t>1990000_270000</t>
-  </si>
-  <si>
-    <t>1990000_240000</t>
+    <t>1990000_2520000</t>
+  </si>
+  <si>
+    <t>1990000_2310000</t>
+  </si>
+  <si>
+    <t>1990000_2100000</t>
+  </si>
+  <si>
+    <t>1990000_1890000</t>
+  </si>
+  <si>
+    <t>1990000_1680000</t>
+  </si>
+  <si>
+    <t>1990000_1470000</t>
+  </si>
+  <si>
+    <t>1990000_1260000</t>
+  </si>
+  <si>
+    <t>11_20</t>
+  </si>
+  <si>
+    <t>1990000_504000</t>
+  </si>
+  <si>
+    <t>21_30</t>
+  </si>
+  <si>
+    <t>1990000_420000</t>
+  </si>
+  <si>
+    <t>31_40</t>
+  </si>
+  <si>
+    <t>1990000_336000</t>
+  </si>
+  <si>
+    <t>41_50</t>
   </si>
   <si>
     <t>1990000_210000</t>
   </si>
   <si>
-    <t>1990000_180000</t>
-  </si>
-  <si>
-    <t>11_20</t>
-  </si>
-  <si>
-    <t>1990000_72000</t>
-  </si>
-  <si>
-    <t>21_30</t>
-  </si>
-  <si>
-    <t>1990000_60000</t>
-  </si>
-  <si>
-    <t>31_40</t>
-  </si>
-  <si>
-    <t>1990000_48000</t>
-  </si>
-  <si>
-    <t>41_50</t>
-  </si>
-  <si>
-    <t>1990000_30000</t>
-  </si>
-  <si>
-    <t>1990000_1450000</t>
-  </si>
-  <si>
-    <t>1990000_1100000</t>
-  </si>
-  <si>
-    <t>1990000_800000</t>
-  </si>
-  <si>
-    <t>1990000_600000</t>
-  </si>
-  <si>
-    <t>1990000_550000</t>
-  </si>
-  <si>
-    <t>1990000_500000</t>
-  </si>
-  <si>
-    <t>1990000_450000</t>
-  </si>
-  <si>
-    <t>1990000_400000</t>
+    <t>1990000_10150000</t>
+  </si>
+  <si>
+    <t>1990000_7700000</t>
+  </si>
+  <si>
+    <t>1990000_5600000</t>
+  </si>
+  <si>
+    <t>1990000_4200000</t>
+  </si>
+  <si>
+    <t>1990000_3850000</t>
+  </si>
+  <si>
+    <t>1990000_3500000</t>
+  </si>
+  <si>
+    <t>1990000_3150000</t>
+  </si>
+  <si>
+    <t>1990000_2800000</t>
+  </si>
+  <si>
+    <t>1990000_2450000</t>
+  </si>
+  <si>
+    <t>1990000_840000</t>
+  </si>
+  <si>
+    <t>1990000_700000</t>
+  </si>
+  <si>
+    <t>1990000_560000</t>
   </si>
   <si>
     <t>1990000_350000</t>
   </si>
   <si>
-    <t>1990000_120000</t>
-  </si>
-  <si>
-    <t>1990000_100000</t>
-  </si>
-  <si>
-    <t>1990000_80000</t>
-  </si>
-  <si>
-    <t>1990000_50000</t>
-  </si>
-  <si>
-    <t>1990000_116000000</t>
-  </si>
-  <si>
-    <t>1990000_88000000</t>
-  </si>
-  <si>
-    <t>1990000_64000000</t>
-  </si>
-  <si>
-    <t>1990000_48000000</t>
-  </si>
-  <si>
-    <t>1990000_44000000</t>
-  </si>
-  <si>
-    <t>1990000_40000000</t>
-  </si>
-  <si>
-    <t>1990000_36000000</t>
-  </si>
-  <si>
-    <t>1990000_32000000</t>
+    <t>1990000_812000000</t>
+  </si>
+  <si>
+    <t>1990000_616000000</t>
+  </si>
+  <si>
+    <t>1990000_448000000</t>
+  </si>
+  <si>
+    <t>1990000_336000000</t>
+  </si>
+  <si>
+    <t>1990000_308000000</t>
+  </si>
+  <si>
+    <t>1990000_280000000</t>
+  </si>
+  <si>
+    <t>1990000_252000000</t>
+  </si>
+  <si>
+    <t>1990000_224000000</t>
+  </si>
+  <si>
+    <t>1990000_196000000</t>
+  </si>
+  <si>
+    <t>1990000_168000000</t>
+  </si>
+  <si>
+    <t>1990000_67200000</t>
+  </si>
+  <si>
+    <t>1990000_56000000</t>
+  </si>
+  <si>
+    <t>1990000_44800000</t>
   </si>
   <si>
     <t>1990000_28000000</t>
-  </si>
-  <si>
-    <t>1990000_24000000</t>
-  </si>
-  <si>
-    <t>1990000_9600000</t>
-  </si>
-  <si>
-    <t>1990000_8000000</t>
-  </si>
-  <si>
-    <t>1990000_6400000</t>
-  </si>
-  <si>
-    <t>1990000_4000000</t>
   </si>
   <si>
     <t>wdcc_ccb_1.png</t>
@@ -1127,16 +1127,16 @@
     <xf numFmtId="49" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1493,7 +1493,7 @@
     <col min="11" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:12">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -1519,7 +1519,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:12">
       <c r="A2" s="9" t="s">
         <v>8</v>
       </c>
@@ -1545,7 +1545,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:12">
       <c r="A3" s="9" t="s">
         <v>13</v>
       </c>
@@ -1571,7 +1571,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:12">
       <c r="A4" s="9"/>
       <c r="B4" s="9"/>
       <c r="C4" s="10"/>
@@ -1581,7 +1581,7 @@
       <c r="G4" s="12"/>
       <c r="H4" s="13"/>
     </row>
-    <row r="5" s="2" customFormat="1" spans="1:10">
+    <row r="5" s="2" customFormat="1" spans="1:12">
       <c r="A5" s="15">
         <v>1</v>
       </c>
@@ -1602,10 +1602,10 @@
         <v>23</v>
       </c>
       <c r="H5" s="16"/>
-      <c r="I5" s="19"/>
-      <c r="J5" s="19"/>
-    </row>
-    <row r="6" s="2" customFormat="1" spans="1:10">
+      <c r="I5" s="17"/>
+      <c r="J5" s="17"/>
+    </row>
+    <row r="6" s="2" customFormat="1" spans="1:12">
       <c r="A6" s="15">
         <v>2</v>
       </c>
@@ -1626,10 +1626,10 @@
         <v>25</v>
       </c>
       <c r="H6" s="16"/>
-      <c r="I6" s="19"/>
-      <c r="J6" s="19"/>
-    </row>
-    <row r="7" s="2" customFormat="1" spans="1:10">
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
+    </row>
+    <row r="7" s="2" customFormat="1" spans="1:12">
       <c r="A7" s="15">
         <v>3</v>
       </c>
@@ -1650,10 +1650,10 @@
         <v>27</v>
       </c>
       <c r="H7" s="16"/>
-      <c r="I7" s="19"/>
-      <c r="J7" s="19"/>
-    </row>
-    <row r="8" s="2" customFormat="1" spans="1:10">
+      <c r="I7" s="17"/>
+      <c r="J7" s="17"/>
+    </row>
+    <row r="8" s="2" customFormat="1" spans="1:12">
       <c r="A8" s="15">
         <v>4</v>
       </c>
@@ -1672,8 +1672,8 @@
       <c r="F8" s="15"/>
       <c r="G8" s="15"/>
       <c r="H8" s="16"/>
-      <c r="I8" s="19"/>
-      <c r="J8" s="19"/>
+      <c r="I8" s="17"/>
+      <c r="J8" s="17"/>
     </row>
     <row r="9" s="3" customFormat="1" spans="1:12">
       <c r="A9" s="15">
@@ -1694,8 +1694,8 @@
       <c r="F9" s="15"/>
       <c r="G9" s="15"/>
       <c r="H9" s="16"/>
-      <c r="I9" s="19"/>
-      <c r="J9" s="20"/>
+      <c r="I9" s="17"/>
+      <c r="J9" s="18"/>
       <c r="L9" s="2"/>
     </row>
     <row r="10" s="3" customFormat="1" spans="1:12">
@@ -1717,8 +1717,8 @@
       <c r="F10" s="15"/>
       <c r="G10" s="15"/>
       <c r="H10" s="16"/>
-      <c r="I10" s="19"/>
-      <c r="J10" s="20"/>
+      <c r="I10" s="17"/>
+      <c r="J10" s="18"/>
       <c r="L10" s="2"/>
     </row>
     <row r="11" s="3" customFormat="1" spans="1:12">
@@ -1740,8 +1740,8 @@
       <c r="F11" s="15"/>
       <c r="G11" s="15"/>
       <c r="H11" s="16"/>
-      <c r="I11" s="19"/>
-      <c r="J11" s="20"/>
+      <c r="I11" s="17"/>
+      <c r="J11" s="18"/>
       <c r="L11" s="2"/>
     </row>
     <row r="12" s="3" customFormat="1" spans="1:12">
@@ -1763,8 +1763,8 @@
       <c r="F12" s="15"/>
       <c r="G12" s="15"/>
       <c r="H12" s="16"/>
-      <c r="I12" s="19"/>
-      <c r="J12" s="20"/>
+      <c r="I12" s="17"/>
+      <c r="J12" s="18"/>
       <c r="L12" s="2"/>
     </row>
     <row r="13" spans="1:12">
@@ -1786,7 +1786,7 @@
       <c r="F13" s="15"/>
       <c r="G13" s="15"/>
       <c r="H13" s="16"/>
-      <c r="I13" s="19"/>
+      <c r="I13" s="17"/>
       <c r="L13" s="2"/>
     </row>
     <row r="14" spans="1:12">
@@ -1808,7 +1808,7 @@
       <c r="F14" s="15"/>
       <c r="G14" s="15"/>
       <c r="H14" s="16"/>
-      <c r="I14" s="19"/>
+      <c r="I14" s="17"/>
       <c r="L14" s="2"/>
     </row>
     <row r="15" customFormat="1" spans="1:12">
@@ -1830,7 +1830,7 @@
       <c r="F15" s="15"/>
       <c r="G15" s="15"/>
       <c r="H15" s="16"/>
-      <c r="I15" s="19"/>
+      <c r="I15" s="17"/>
       <c r="J15" s="8"/>
       <c r="L15" s="2"/>
     </row>
@@ -1853,8 +1853,8 @@
       <c r="F16" s="15"/>
       <c r="G16" s="15"/>
       <c r="H16" s="16"/>
-      <c r="I16" s="19"/>
-      <c r="J16" s="20"/>
+      <c r="I16" s="17"/>
+      <c r="J16" s="18"/>
       <c r="L16" s="2"/>
     </row>
     <row r="17" s="3" customFormat="1" spans="1:12">
@@ -1876,8 +1876,8 @@
       <c r="F17" s="15"/>
       <c r="G17" s="15"/>
       <c r="H17" s="16"/>
-      <c r="I17" s="19"/>
-      <c r="J17" s="20"/>
+      <c r="I17" s="17"/>
+      <c r="J17" s="18"/>
       <c r="L17" s="2"/>
     </row>
     <row r="18" s="3" customFormat="1" spans="1:12">
@@ -1899,8 +1899,8 @@
       <c r="F18" s="15"/>
       <c r="G18" s="15"/>
       <c r="H18" s="16"/>
-      <c r="I18" s="19"/>
-      <c r="J18" s="20"/>
+      <c r="I18" s="17"/>
+      <c r="J18" s="18"/>
       <c r="L18" s="2"/>
     </row>
     <row r="19" s="3" customFormat="1" spans="1:12">
@@ -1924,8 +1924,8 @@
         <v>23</v>
       </c>
       <c r="H19" s="16"/>
-      <c r="I19" s="19"/>
-      <c r="J19" s="20"/>
+      <c r="I19" s="17"/>
+      <c r="J19" s="18"/>
       <c r="L19" s="2"/>
     </row>
     <row r="20" s="3" customFormat="1" spans="1:12">
@@ -1949,11 +1949,11 @@
         <v>25</v>
       </c>
       <c r="H20" s="16"/>
-      <c r="I20" s="19"/>
-      <c r="J20" s="19"/>
+      <c r="I20" s="17"/>
+      <c r="J20" s="17"/>
       <c r="L20" s="2"/>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:12">
       <c r="A21" s="15">
         <v>33</v>
       </c>
@@ -1975,7 +1975,7 @@
       </c>
       <c r="H21" s="16"/>
     </row>
-    <row r="22" s="3" customFormat="1" spans="1:10">
+    <row r="22" s="3" customFormat="1" spans="1:12">
       <c r="A22" s="15">
         <v>34</v>
       </c>
@@ -1994,10 +1994,10 @@
       <c r="F22" s="15"/>
       <c r="G22" s="15"/>
       <c r="H22" s="16"/>
-      <c r="I22" s="19"/>
-      <c r="J22" s="20"/>
-    </row>
-    <row r="23" s="3" customFormat="1" spans="1:10">
+      <c r="I22" s="17"/>
+      <c r="J22" s="18"/>
+    </row>
+    <row r="23" s="3" customFormat="1" spans="1:12">
       <c r="A23" s="15">
         <v>35</v>
       </c>
@@ -2016,10 +2016,10 @@
       <c r="F23" s="15"/>
       <c r="G23" s="15"/>
       <c r="H23" s="16"/>
-      <c r="I23" s="19"/>
-      <c r="J23" s="20"/>
-    </row>
-    <row r="24" s="3" customFormat="1" spans="1:10">
+      <c r="I23" s="17"/>
+      <c r="J23" s="18"/>
+    </row>
+    <row r="24" s="3" customFormat="1" spans="1:12">
       <c r="A24" s="15">
         <v>36</v>
       </c>
@@ -2038,10 +2038,10 @@
       <c r="F24" s="15"/>
       <c r="G24" s="15"/>
       <c r="H24" s="16"/>
-      <c r="I24" s="19"/>
-      <c r="J24" s="20"/>
-    </row>
-    <row r="25" s="3" customFormat="1" spans="1:10">
+      <c r="I24" s="17"/>
+      <c r="J24" s="18"/>
+    </row>
+    <row r="25" s="3" customFormat="1" spans="1:12">
       <c r="A25" s="15">
         <v>37</v>
       </c>
@@ -2060,10 +2060,10 @@
       <c r="F25" s="15"/>
       <c r="G25" s="15"/>
       <c r="H25" s="16"/>
-      <c r="I25" s="19"/>
-      <c r="J25" s="20"/>
-    </row>
-    <row r="26" s="3" customFormat="1" spans="1:10">
+      <c r="I25" s="17"/>
+      <c r="J25" s="18"/>
+    </row>
+    <row r="26" s="3" customFormat="1" spans="1:12">
       <c r="A26" s="15">
         <v>38</v>
       </c>
@@ -2082,10 +2082,10 @@
       <c r="F26" s="15"/>
       <c r="G26" s="15"/>
       <c r="H26" s="16"/>
-      <c r="I26" s="19"/>
-      <c r="J26" s="19"/>
-    </row>
-    <row r="27" spans="1:9">
+      <c r="I26" s="17"/>
+      <c r="J26" s="17"/>
+    </row>
+    <row r="27" spans="1:12">
       <c r="A27" s="15">
         <v>39</v>
       </c>
@@ -2104,9 +2104,9 @@
       <c r="F27" s="15"/>
       <c r="G27" s="15"/>
       <c r="H27" s="16"/>
-      <c r="I27" s="19"/>
-    </row>
-    <row r="28" spans="1:9">
+      <c r="I27" s="17"/>
+    </row>
+    <row r="28" spans="1:12">
       <c r="A28" s="15">
         <v>40</v>
       </c>
@@ -2125,9 +2125,9 @@
       <c r="F28" s="15"/>
       <c r="G28" s="15"/>
       <c r="H28" s="16"/>
-      <c r="I28" s="19"/>
-    </row>
-    <row r="29" spans="1:9">
+      <c r="I28" s="17"/>
+    </row>
+    <row r="29" spans="1:12">
       <c r="A29" s="15">
         <v>41</v>
       </c>
@@ -2146,9 +2146,9 @@
       <c r="F29" s="15"/>
       <c r="G29" s="15"/>
       <c r="H29" s="16"/>
-      <c r="I29" s="19"/>
-    </row>
-    <row r="30" spans="1:9">
+      <c r="I29" s="17"/>
+    </row>
+    <row r="30" spans="1:12">
       <c r="A30" s="15">
         <v>42</v>
       </c>
@@ -2167,9 +2167,9 @@
       <c r="F30" s="15"/>
       <c r="G30" s="15"/>
       <c r="H30" s="16"/>
-      <c r="I30" s="19"/>
-    </row>
-    <row r="31" spans="1:9">
+      <c r="I30" s="17"/>
+    </row>
+    <row r="31" spans="1:12">
       <c r="A31" s="15">
         <v>43</v>
       </c>
@@ -2188,9 +2188,9 @@
       <c r="F31" s="15"/>
       <c r="G31" s="15"/>
       <c r="H31" s="16"/>
-      <c r="I31" s="19"/>
-    </row>
-    <row r="32" spans="1:9">
+      <c r="I31" s="17"/>
+    </row>
+    <row r="32" spans="1:12">
       <c r="A32" s="15">
         <v>44</v>
       </c>
@@ -2209,9 +2209,9 @@
       <c r="F32" s="15"/>
       <c r="G32" s="15"/>
       <c r="H32" s="16"/>
-      <c r="I32" s="19"/>
-    </row>
-    <row r="33" spans="1:9">
+      <c r="I32" s="17"/>
+    </row>
+    <row r="33" spans="1:10">
       <c r="A33" s="15">
         <v>61</v>
       </c>
@@ -2232,9 +2232,9 @@
         <v>23</v>
       </c>
       <c r="H33" s="16"/>
-      <c r="I33" s="19"/>
-    </row>
-    <row r="34" spans="1:9">
+      <c r="I33" s="17"/>
+    </row>
+    <row r="34" spans="1:10">
       <c r="A34" s="15">
         <v>62</v>
       </c>
@@ -2255,9 +2255,9 @@
         <v>25</v>
       </c>
       <c r="H34" s="16"/>
-      <c r="I34" s="19"/>
-    </row>
-    <row r="35" spans="1:9">
+      <c r="I34" s="17"/>
+    </row>
+    <row r="35" spans="1:10">
       <c r="A35" s="15">
         <v>63</v>
       </c>
@@ -2278,9 +2278,9 @@
         <v>27</v>
       </c>
       <c r="H35" s="16"/>
-      <c r="I35" s="19"/>
-    </row>
-    <row r="36" spans="1:9">
+      <c r="I35" s="17"/>
+    </row>
+    <row r="36" spans="1:10">
       <c r="A36" s="15">
         <v>64</v>
       </c>
@@ -2299,9 +2299,9 @@
       <c r="F36" s="15"/>
       <c r="G36" s="15"/>
       <c r="H36" s="16"/>
-      <c r="I36" s="19"/>
-    </row>
-    <row r="37" spans="1:9">
+      <c r="I36" s="17"/>
+    </row>
+    <row r="37" spans="1:10">
       <c r="A37" s="15">
         <v>65</v>
       </c>
@@ -2320,9 +2320,9 @@
       <c r="F37" s="15"/>
       <c r="G37" s="15"/>
       <c r="H37" s="16"/>
-      <c r="I37" s="19"/>
-    </row>
-    <row r="38" spans="1:9">
+      <c r="I37" s="17"/>
+    </row>
+    <row r="38" spans="1:10">
       <c r="A38" s="15">
         <v>66</v>
       </c>
@@ -2341,9 +2341,9 @@
       <c r="F38" s="15"/>
       <c r="G38" s="15"/>
       <c r="H38" s="16"/>
-      <c r="I38" s="19"/>
-    </row>
-    <row r="39" spans="1:9">
+      <c r="I38" s="17"/>
+    </row>
+    <row r="39" spans="1:10">
       <c r="A39" s="15">
         <v>67</v>
       </c>
@@ -2362,9 +2362,9 @@
       <c r="F39" s="15"/>
       <c r="G39" s="15"/>
       <c r="H39" s="16"/>
-      <c r="I39" s="19"/>
-    </row>
-    <row r="40" spans="1:9">
+      <c r="I39" s="17"/>
+    </row>
+    <row r="40" spans="1:10">
       <c r="A40" s="15">
         <v>68</v>
       </c>
@@ -2383,9 +2383,9 @@
       <c r="F40" s="15"/>
       <c r="G40" s="15"/>
       <c r="H40" s="16"/>
-      <c r="I40" s="19"/>
-    </row>
-    <row r="41" spans="1:9">
+      <c r="I40" s="17"/>
+    </row>
+    <row r="41" spans="1:10">
       <c r="A41" s="15">
         <v>69</v>
       </c>
@@ -2404,9 +2404,9 @@
       <c r="F41" s="15"/>
       <c r="G41" s="15"/>
       <c r="H41" s="16"/>
-      <c r="I41" s="19"/>
-    </row>
-    <row r="42" spans="1:9">
+      <c r="I41" s="17"/>
+    </row>
+    <row r="42" spans="1:10">
       <c r="A42" s="15">
         <v>70</v>
       </c>
@@ -2425,9 +2425,9 @@
       <c r="F42" s="15"/>
       <c r="G42" s="15"/>
       <c r="H42" s="16"/>
-      <c r="I42" s="19"/>
-    </row>
-    <row r="43" spans="1:9">
+      <c r="I42" s="17"/>
+    </row>
+    <row r="43" spans="1:10">
       <c r="A43" s="15">
         <v>71</v>
       </c>
@@ -2446,9 +2446,9 @@
       <c r="F43" s="15"/>
       <c r="G43" s="15"/>
       <c r="H43" s="16"/>
-      <c r="I43" s="19"/>
-    </row>
-    <row r="44" spans="1:8">
+      <c r="I43" s="17"/>
+    </row>
+    <row r="44" spans="1:10">
       <c r="A44" s="15">
         <v>72</v>
       </c>
@@ -2468,7 +2468,7 @@
       <c r="G44" s="15"/>
       <c r="H44" s="16"/>
     </row>
-    <row r="45" spans="1:8">
+    <row r="45" spans="1:10">
       <c r="A45" s="15">
         <v>73</v>
       </c>
@@ -2488,7 +2488,7 @@
       <c r="G45" s="15"/>
       <c r="H45" s="16"/>
     </row>
-    <row r="46" spans="1:8">
+    <row r="46" spans="1:10">
       <c r="A46" s="15">
         <v>74</v>
       </c>
@@ -2509,1055 +2509,1055 @@
       <c r="H46" s="16"/>
     </row>
     <row r="47" s="2" customFormat="1" spans="1:10">
-      <c r="A47" s="17">
+      <c r="A47" s="19">
         <v>101</v>
       </c>
-      <c r="B47" s="17">
+      <c r="B47" s="19">
         <v>1</v>
       </c>
-      <c r="C47" s="18">
+      <c r="C47" s="20">
         <v>1</v>
       </c>
-      <c r="D47" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E47" s="17" t="s">
+      <c r="D47" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="E47" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="F47" s="17">
+      <c r="F47" s="19">
         <v>33333333</v>
       </c>
-      <c r="G47" s="17" t="s">
+      <c r="G47" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="H47" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="I47" s="19"/>
-      <c r="J47" s="19"/>
+      <c r="H47" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I47" s="17"/>
+      <c r="J47" s="17"/>
     </row>
     <row r="48" s="2" customFormat="1" spans="1:10">
-      <c r="A48" s="17">
+      <c r="A48" s="19">
         <v>102</v>
       </c>
-      <c r="B48" s="17">
+      <c r="B48" s="19">
         <v>1</v>
       </c>
-      <c r="C48" s="18">
+      <c r="C48" s="20">
         <v>2</v>
       </c>
-      <c r="D48" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E48" s="17" t="s">
+      <c r="D48" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="E48" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="F48" s="17">
+      <c r="F48" s="19">
         <v>22222222</v>
       </c>
-      <c r="G48" s="17" t="s">
+      <c r="G48" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="H48" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="I48" s="19"/>
-      <c r="J48" s="19"/>
-    </row>
-    <row r="49" s="2" customFormat="1" spans="1:10">
-      <c r="A49" s="17">
+      <c r="H48" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I48" s="17"/>
+      <c r="J48" s="17"/>
+    </row>
+    <row r="49" s="2" customFormat="1" spans="1:12">
+      <c r="A49" s="19">
         <v>103</v>
       </c>
-      <c r="B49" s="17">
+      <c r="B49" s="19">
         <v>1</v>
       </c>
-      <c r="C49" s="18">
+      <c r="C49" s="20">
         <v>3</v>
       </c>
-      <c r="D49" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E49" s="17" t="s">
+      <c r="D49" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="E49" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="F49" s="17">
+      <c r="F49" s="19">
         <v>11111111</v>
       </c>
-      <c r="G49" s="17" t="s">
+      <c r="G49" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="H49" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="I49" s="19"/>
-      <c r="J49" s="19"/>
-    </row>
-    <row r="50" s="2" customFormat="1" spans="1:10">
-      <c r="A50" s="17">
+      <c r="H49" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I49" s="17"/>
+      <c r="J49" s="17"/>
+    </row>
+    <row r="50" s="2" customFormat="1" spans="1:12">
+      <c r="A50" s="19">
         <v>104</v>
       </c>
-      <c r="B50" s="17">
+      <c r="B50" s="19">
         <v>1</v>
       </c>
-      <c r="C50" s="18">
+      <c r="C50" s="20">
         <v>4</v>
       </c>
-      <c r="D50" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E50" s="17" t="s">
+      <c r="D50" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="E50" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="F50" s="17">
+      <c r="F50" s="19">
         <v>5000000</v>
       </c>
-      <c r="G50" s="17" t="s">
+      <c r="G50" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="H50" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="I50" s="19"/>
-      <c r="J50" s="19"/>
+      <c r="H50" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I50" s="17"/>
+      <c r="J50" s="17"/>
     </row>
     <row r="51" s="3" customFormat="1" spans="1:12">
-      <c r="A51" s="17">
+      <c r="A51" s="19">
         <v>105</v>
       </c>
-      <c r="B51" s="17">
+      <c r="B51" s="19">
         <v>1</v>
       </c>
-      <c r="C51" s="18">
+      <c r="C51" s="20">
         <v>5</v>
       </c>
-      <c r="D51" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E51" s="17" t="s">
+      <c r="D51" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="E51" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="F51" s="17">
+      <c r="F51" s="19">
         <v>3000000</v>
       </c>
-      <c r="G51" s="17" t="s">
+      <c r="G51" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="H51" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="I51" s="19"/>
-      <c r="J51" s="20"/>
+      <c r="H51" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I51" s="17"/>
+      <c r="J51" s="18"/>
       <c r="L51" s="2"/>
     </row>
     <row r="52" s="3" customFormat="1" spans="1:12">
-      <c r="A52" s="17">
+      <c r="A52" s="19">
         <v>106</v>
       </c>
-      <c r="B52" s="17">
+      <c r="B52" s="19">
         <v>1</v>
       </c>
-      <c r="C52" s="18">
+      <c r="C52" s="20">
         <v>6</v>
       </c>
-      <c r="D52" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E52" s="17" t="s">
+      <c r="D52" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="E52" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="F52" s="17"/>
-      <c r="G52" s="17"/>
-      <c r="H52" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="I52" s="19"/>
-      <c r="J52" s="20"/>
+      <c r="F52" s="19"/>
+      <c r="G52" s="19"/>
+      <c r="H52" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I52" s="17"/>
+      <c r="J52" s="18"/>
       <c r="L52" s="2"/>
     </row>
     <row r="53" s="3" customFormat="1" spans="1:12">
-      <c r="A53" s="17">
+      <c r="A53" s="19">
         <v>107</v>
       </c>
-      <c r="B53" s="17">
+      <c r="B53" s="19">
         <v>1</v>
       </c>
-      <c r="C53" s="18">
+      <c r="C53" s="20">
         <v>7</v>
       </c>
-      <c r="D53" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E53" s="17" t="s">
+      <c r="D53" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="E53" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="F53" s="17"/>
-      <c r="G53" s="17"/>
-      <c r="H53" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="I53" s="19"/>
-      <c r="J53" s="20"/>
+      <c r="F53" s="19"/>
+      <c r="G53" s="19"/>
+      <c r="H53" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I53" s="17"/>
+      <c r="J53" s="18"/>
       <c r="L53" s="2"/>
     </row>
     <row r="54" s="3" customFormat="1" spans="1:12">
-      <c r="A54" s="17">
+      <c r="A54" s="19">
         <v>108</v>
       </c>
-      <c r="B54" s="17">
+      <c r="B54" s="19">
         <v>1</v>
       </c>
-      <c r="C54" s="18">
+      <c r="C54" s="20">
         <v>8</v>
       </c>
-      <c r="D54" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E54" s="17" t="s">
+      <c r="D54" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="E54" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="F54" s="17"/>
-      <c r="G54" s="17"/>
-      <c r="H54" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="I54" s="19"/>
-      <c r="J54" s="20"/>
+      <c r="F54" s="19"/>
+      <c r="G54" s="19"/>
+      <c r="H54" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I54" s="17"/>
+      <c r="J54" s="18"/>
       <c r="L54" s="2"/>
     </row>
     <row r="55" spans="1:12">
-      <c r="A55" s="17">
+      <c r="A55" s="19">
         <v>109</v>
       </c>
-      <c r="B55" s="17">
+      <c r="B55" s="19">
         <v>1</v>
       </c>
-      <c r="C55" s="18">
+      <c r="C55" s="20">
         <v>9</v>
       </c>
-      <c r="D55" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E55" s="17" t="s">
+      <c r="D55" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="E55" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="F55" s="17"/>
-      <c r="G55" s="17"/>
-      <c r="H55" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="I55" s="19"/>
+      <c r="F55" s="19"/>
+      <c r="G55" s="19"/>
+      <c r="H55" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I55" s="17"/>
       <c r="L55" s="2"/>
     </row>
     <row r="56" spans="1:12">
-      <c r="A56" s="17">
+      <c r="A56" s="19">
         <v>110</v>
       </c>
-      <c r="B56" s="17">
+      <c r="B56" s="19">
         <v>1</v>
       </c>
-      <c r="C56" s="18">
+      <c r="C56" s="20">
         <v>10</v>
       </c>
-      <c r="D56" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E56" s="17" t="s">
+      <c r="D56" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="E56" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="F56" s="17"/>
-      <c r="G56" s="17"/>
-      <c r="H56" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="I56" s="19"/>
+      <c r="F56" s="19"/>
+      <c r="G56" s="19"/>
+      <c r="H56" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I56" s="17"/>
       <c r="L56" s="2"/>
     </row>
     <row r="57" customFormat="1" spans="1:12">
-      <c r="A57" s="17">
+      <c r="A57" s="19">
         <v>111</v>
       </c>
-      <c r="B57" s="17">
+      <c r="B57" s="19">
         <v>1</v>
       </c>
-      <c r="C57" s="18" t="s">
+      <c r="C57" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="D57" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E57" s="17" t="s">
+      <c r="D57" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="E57" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="F57" s="17"/>
-      <c r="G57" s="17"/>
-      <c r="H57" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="I57" s="19"/>
+      <c r="F57" s="19"/>
+      <c r="G57" s="19"/>
+      <c r="H57" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I57" s="17"/>
       <c r="J57" s="8"/>
       <c r="L57" s="2"/>
     </row>
     <row r="58" s="3" customFormat="1" spans="1:12">
-      <c r="A58" s="17">
+      <c r="A58" s="19">
         <v>112</v>
       </c>
-      <c r="B58" s="17">
+      <c r="B58" s="19">
         <v>1</v>
       </c>
-      <c r="C58" s="18" t="s">
+      <c r="C58" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="D58" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E58" s="17" t="s">
+      <c r="D58" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="E58" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="F58" s="17"/>
-      <c r="G58" s="17"/>
-      <c r="H58" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="I58" s="19"/>
-      <c r="J58" s="20"/>
+      <c r="F58" s="19"/>
+      <c r="G58" s="19"/>
+      <c r="H58" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I58" s="17"/>
+      <c r="J58" s="18"/>
       <c r="L58" s="2"/>
     </row>
     <row r="59" s="3" customFormat="1" spans="1:12">
-      <c r="A59" s="17">
+      <c r="A59" s="19">
         <v>113</v>
       </c>
-      <c r="B59" s="17">
+      <c r="B59" s="19">
         <v>1</v>
       </c>
-      <c r="C59" s="18" t="s">
+      <c r="C59" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="D59" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E59" s="17" t="s">
+      <c r="D59" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="E59" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="F59" s="17"/>
-      <c r="G59" s="17"/>
-      <c r="H59" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="I59" s="19"/>
-      <c r="J59" s="20"/>
+      <c r="F59" s="19"/>
+      <c r="G59" s="19"/>
+      <c r="H59" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I59" s="17"/>
+      <c r="J59" s="18"/>
       <c r="L59" s="2"/>
     </row>
     <row r="60" s="3" customFormat="1" spans="1:12">
-      <c r="A60" s="17">
+      <c r="A60" s="19">
         <v>114</v>
       </c>
-      <c r="B60" s="17">
+      <c r="B60" s="19">
         <v>1</v>
       </c>
-      <c r="C60" s="18" t="s">
+      <c r="C60" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E60" s="17" t="s">
+      <c r="D60" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="E60" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="F60" s="17"/>
-      <c r="G60" s="17"/>
-      <c r="H60" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="I60" s="19"/>
-      <c r="J60" s="20"/>
+      <c r="F60" s="19"/>
+      <c r="G60" s="19"/>
+      <c r="H60" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I60" s="17"/>
+      <c r="J60" s="18"/>
       <c r="L60" s="2"/>
     </row>
     <row r="61" s="3" customFormat="1" spans="1:12">
-      <c r="A61" s="17">
+      <c r="A61" s="19">
         <v>131</v>
       </c>
-      <c r="B61" s="17">
+      <c r="B61" s="19">
         <v>2</v>
       </c>
-      <c r="C61" s="18">
+      <c r="C61" s="20">
         <v>1</v>
       </c>
-      <c r="D61" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E61" s="17" t="s">
+      <c r="D61" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="E61" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="F61" s="17">
+      <c r="F61" s="19">
         <v>33333333</v>
       </c>
-      <c r="G61" s="17" t="s">
+      <c r="G61" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="H61" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="I61" s="19"/>
-      <c r="J61" s="20"/>
+      <c r="H61" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I61" s="17"/>
+      <c r="J61" s="18"/>
       <c r="L61" s="2"/>
     </row>
     <row r="62" s="3" customFormat="1" spans="1:12">
-      <c r="A62" s="17">
+      <c r="A62" s="19">
         <v>132</v>
       </c>
-      <c r="B62" s="17">
+      <c r="B62" s="19">
         <v>2</v>
       </c>
-      <c r="C62" s="18">
+      <c r="C62" s="20">
         <v>2</v>
       </c>
-      <c r="D62" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E62" s="17" t="s">
+      <c r="D62" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="E62" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="F62" s="17">
+      <c r="F62" s="19">
         <v>22222222</v>
       </c>
-      <c r="G62" s="17" t="s">
+      <c r="G62" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="H62" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="I62" s="19"/>
-      <c r="J62" s="19"/>
+      <c r="H62" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I62" s="17"/>
+      <c r="J62" s="17"/>
       <c r="L62" s="2"/>
     </row>
-    <row r="63" spans="1:8">
-      <c r="A63" s="17">
+    <row r="63" spans="1:12">
+      <c r="A63" s="19">
         <v>133</v>
       </c>
-      <c r="B63" s="17">
+      <c r="B63" s="19">
         <v>2</v>
       </c>
-      <c r="C63" s="18">
+      <c r="C63" s="20">
         <v>3</v>
       </c>
-      <c r="D63" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E63" s="17" t="s">
+      <c r="D63" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="E63" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="F63" s="17">
+      <c r="F63" s="19">
         <v>11111111</v>
       </c>
-      <c r="G63" s="17" t="s">
+      <c r="G63" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="H63" s="18" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="64" s="3" customFormat="1" spans="1:10">
-      <c r="A64" s="17">
+      <c r="H63" s="20" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="64" s="3" customFormat="1" spans="1:12">
+      <c r="A64" s="19">
         <v>134</v>
       </c>
-      <c r="B64" s="17">
+      <c r="B64" s="19">
         <v>2</v>
       </c>
-      <c r="C64" s="18">
+      <c r="C64" s="20">
         <v>4</v>
       </c>
-      <c r="D64" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E64" s="17" t="s">
+      <c r="D64" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="E64" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="F64" s="17">
+      <c r="F64" s="19">
         <v>5000000</v>
       </c>
-      <c r="G64" s="17" t="s">
+      <c r="G64" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="H64" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="I64" s="19"/>
-      <c r="J64" s="20"/>
+      <c r="H64" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I64" s="17"/>
+      <c r="J64" s="18"/>
     </row>
     <row r="65" s="3" customFormat="1" spans="1:10">
-      <c r="A65" s="17">
+      <c r="A65" s="19">
         <v>135</v>
       </c>
-      <c r="B65" s="17">
+      <c r="B65" s="19">
         <v>2</v>
       </c>
-      <c r="C65" s="18">
+      <c r="C65" s="20">
         <v>5</v>
       </c>
-      <c r="D65" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E65" s="17" t="s">
+      <c r="D65" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="E65" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="F65" s="17">
+      <c r="F65" s="19">
         <v>3000000</v>
       </c>
-      <c r="G65" s="17" t="s">
+      <c r="G65" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="H65" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="I65" s="19"/>
-      <c r="J65" s="20"/>
+      <c r="H65" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I65" s="17"/>
+      <c r="J65" s="18"/>
     </row>
     <row r="66" s="3" customFormat="1" spans="1:10">
-      <c r="A66" s="17">
+      <c r="A66" s="19">
         <v>136</v>
       </c>
-      <c r="B66" s="17">
+      <c r="B66" s="19">
         <v>2</v>
       </c>
-      <c r="C66" s="18">
+      <c r="C66" s="20">
         <v>6</v>
       </c>
-      <c r="D66" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E66" s="17" t="s">
+      <c r="D66" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="E66" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="F66" s="17"/>
-      <c r="G66" s="17"/>
-      <c r="H66" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="I66" s="19"/>
-      <c r="J66" s="20"/>
+      <c r="F66" s="19"/>
+      <c r="G66" s="19"/>
+      <c r="H66" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I66" s="17"/>
+      <c r="J66" s="18"/>
     </row>
     <row r="67" s="3" customFormat="1" spans="1:10">
-      <c r="A67" s="17">
+      <c r="A67" s="19">
         <v>137</v>
       </c>
-      <c r="B67" s="17">
+      <c r="B67" s="19">
         <v>2</v>
       </c>
-      <c r="C67" s="18">
+      <c r="C67" s="20">
         <v>7</v>
       </c>
-      <c r="D67" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E67" s="17" t="s">
+      <c r="D67" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="E67" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="F67" s="17"/>
-      <c r="G67" s="17"/>
-      <c r="H67" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="I67" s="19"/>
-      <c r="J67" s="20"/>
+      <c r="F67" s="19"/>
+      <c r="G67" s="19"/>
+      <c r="H67" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I67" s="17"/>
+      <c r="J67" s="18"/>
     </row>
     <row r="68" s="3" customFormat="1" spans="1:10">
-      <c r="A68" s="17">
+      <c r="A68" s="19">
         <v>138</v>
       </c>
-      <c r="B68" s="17">
+      <c r="B68" s="19">
         <v>2</v>
       </c>
-      <c r="C68" s="18">
+      <c r="C68" s="20">
         <v>8</v>
       </c>
-      <c r="D68" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E68" s="17" t="s">
+      <c r="D68" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="E68" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="F68" s="17"/>
-      <c r="G68" s="17"/>
-      <c r="H68" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="I68" s="19"/>
-      <c r="J68" s="19"/>
-    </row>
-    <row r="69" spans="1:9">
-      <c r="A69" s="17">
+      <c r="F68" s="19"/>
+      <c r="G68" s="19"/>
+      <c r="H68" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I68" s="17"/>
+      <c r="J68" s="17"/>
+    </row>
+    <row r="69" spans="1:10">
+      <c r="A69" s="19">
         <v>139</v>
       </c>
-      <c r="B69" s="17">
+      <c r="B69" s="19">
         <v>2</v>
       </c>
-      <c r="C69" s="18">
+      <c r="C69" s="20">
         <v>9</v>
       </c>
-      <c r="D69" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E69" s="17" t="s">
+      <c r="D69" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="E69" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="F69" s="17"/>
-      <c r="G69" s="17"/>
-      <c r="H69" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="I69" s="19"/>
-    </row>
-    <row r="70" spans="1:9">
-      <c r="A70" s="17">
+      <c r="F69" s="19"/>
+      <c r="G69" s="19"/>
+      <c r="H69" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I69" s="17"/>
+    </row>
+    <row r="70" spans="1:10">
+      <c r="A70" s="19">
         <v>140</v>
       </c>
-      <c r="B70" s="17">
+      <c r="B70" s="19">
         <v>2</v>
       </c>
-      <c r="C70" s="18">
+      <c r="C70" s="20">
         <v>10</v>
       </c>
-      <c r="D70" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E70" s="17" t="s">
+      <c r="D70" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="E70" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="F70" s="17"/>
-      <c r="G70" s="17"/>
-      <c r="H70" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="I70" s="19"/>
-    </row>
-    <row r="71" spans="1:9">
-      <c r="A71" s="17">
+      <c r="F70" s="19"/>
+      <c r="G70" s="19"/>
+      <c r="H70" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I70" s="17"/>
+    </row>
+    <row r="71" spans="1:10">
+      <c r="A71" s="19">
         <v>141</v>
       </c>
-      <c r="B71" s="17">
+      <c r="B71" s="19">
         <v>2</v>
       </c>
-      <c r="C71" s="18" t="s">
+      <c r="C71" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="D71" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E71" s="17" t="s">
+      <c r="D71" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="E71" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="F71" s="17"/>
-      <c r="G71" s="17"/>
-      <c r="H71" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="I71" s="19"/>
-    </row>
-    <row r="72" spans="1:9">
-      <c r="A72" s="17">
+      <c r="F71" s="19"/>
+      <c r="G71" s="19"/>
+      <c r="H71" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I71" s="17"/>
+    </row>
+    <row r="72" spans="1:10">
+      <c r="A72" s="19">
         <v>142</v>
       </c>
-      <c r="B72" s="17">
+      <c r="B72" s="19">
         <v>2</v>
       </c>
-      <c r="C72" s="18" t="s">
+      <c r="C72" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="D72" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E72" s="17" t="s">
+      <c r="D72" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="E72" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="F72" s="17"/>
-      <c r="G72" s="17"/>
-      <c r="H72" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="I72" s="19"/>
-    </row>
-    <row r="73" spans="1:9">
-      <c r="A73" s="17">
+      <c r="F72" s="19"/>
+      <c r="G72" s="19"/>
+      <c r="H72" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I72" s="17"/>
+    </row>
+    <row r="73" spans="1:10">
+      <c r="A73" s="19">
         <v>143</v>
       </c>
-      <c r="B73" s="17">
+      <c r="B73" s="19">
         <v>2</v>
       </c>
-      <c r="C73" s="18" t="s">
+      <c r="C73" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="D73" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E73" s="17" t="s">
+      <c r="D73" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="E73" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="F73" s="17"/>
-      <c r="G73" s="17"/>
-      <c r="H73" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="I73" s="19"/>
-    </row>
-    <row r="74" spans="1:9">
-      <c r="A74" s="17">
+      <c r="F73" s="19"/>
+      <c r="G73" s="19"/>
+      <c r="H73" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I73" s="17"/>
+    </row>
+    <row r="74" spans="1:10">
+      <c r="A74" s="19">
         <v>144</v>
       </c>
-      <c r="B74" s="17">
+      <c r="B74" s="19">
         <v>2</v>
       </c>
-      <c r="C74" s="18" t="s">
+      <c r="C74" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="D74" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E74" s="17" t="s">
+      <c r="D74" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="E74" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="F74" s="17"/>
-      <c r="G74" s="17"/>
-      <c r="H74" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="I74" s="19"/>
-    </row>
-    <row r="75" spans="1:9">
-      <c r="A75" s="17">
+      <c r="F74" s="19"/>
+      <c r="G74" s="19"/>
+      <c r="H74" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I74" s="17"/>
+    </row>
+    <row r="75" spans="1:10">
+      <c r="A75" s="19">
         <v>161</v>
       </c>
-      <c r="B75" s="17">
+      <c r="B75" s="19">
         <v>3</v>
       </c>
-      <c r="C75" s="18">
+      <c r="C75" s="20">
         <v>1</v>
       </c>
-      <c r="D75" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E75" s="17" t="s">
+      <c r="D75" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="E75" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="F75" s="17">
+      <c r="F75" s="19">
         <v>99999999</v>
       </c>
-      <c r="G75" s="17" t="s">
+      <c r="G75" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="H75" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="I75" s="19"/>
-    </row>
-    <row r="76" spans="1:9">
-      <c r="A76" s="17">
+      <c r="H75" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I75" s="17"/>
+    </row>
+    <row r="76" spans="1:10">
+      <c r="A76" s="19">
         <v>162</v>
       </c>
-      <c r="B76" s="17">
+      <c r="B76" s="19">
         <v>3</v>
       </c>
-      <c r="C76" s="18">
+      <c r="C76" s="20">
         <v>2</v>
       </c>
-      <c r="D76" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E76" s="17" t="s">
+      <c r="D76" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="E76" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="F76" s="17">
+      <c r="F76" s="19">
         <v>88888888</v>
       </c>
-      <c r="G76" s="17" t="s">
+      <c r="G76" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="H76" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="I76" s="19"/>
-    </row>
-    <row r="77" spans="1:9">
-      <c r="A77" s="17">
+      <c r="H76" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I76" s="17"/>
+    </row>
+    <row r="77" spans="1:10">
+      <c r="A77" s="19">
         <v>163</v>
       </c>
-      <c r="B77" s="17">
+      <c r="B77" s="19">
         <v>3</v>
       </c>
-      <c r="C77" s="18">
+      <c r="C77" s="20">
         <v>3</v>
       </c>
-      <c r="D77" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E77" s="17" t="s">
+      <c r="D77" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="E77" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="F77" s="17">
+      <c r="F77" s="19">
         <v>77777777</v>
       </c>
-      <c r="G77" s="17" t="s">
+      <c r="G77" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="H77" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="I77" s="19"/>
-    </row>
-    <row r="78" spans="1:9">
-      <c r="A78" s="17">
+      <c r="H77" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I77" s="17"/>
+    </row>
+    <row r="78" spans="1:10">
+      <c r="A78" s="19">
         <v>164</v>
       </c>
-      <c r="B78" s="17">
+      <c r="B78" s="19">
         <v>3</v>
       </c>
-      <c r="C78" s="18">
+      <c r="C78" s="20">
         <v>4</v>
       </c>
-      <c r="D78" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E78" s="17" t="s">
+      <c r="D78" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="E78" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="F78" s="17">
+      <c r="F78" s="19">
         <v>66666666</v>
       </c>
-      <c r="G78" s="17" t="s">
+      <c r="G78" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="H78" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="I78" s="19"/>
-    </row>
-    <row r="79" spans="1:9">
-      <c r="A79" s="17">
+      <c r="H78" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I78" s="17"/>
+    </row>
+    <row r="79" spans="1:10">
+      <c r="A79" s="19">
         <v>165</v>
       </c>
-      <c r="B79" s="17">
+      <c r="B79" s="19">
         <v>3</v>
       </c>
-      <c r="C79" s="18">
+      <c r="C79" s="20">
         <v>5</v>
       </c>
-      <c r="D79" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E79" s="17" t="s">
+      <c r="D79" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="E79" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="F79" s="17">
+      <c r="F79" s="19">
         <v>55555555</v>
       </c>
-      <c r="G79" s="17" t="s">
+      <c r="G79" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="H79" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="I79" s="19"/>
-    </row>
-    <row r="80" spans="1:9">
-      <c r="A80" s="17">
+      <c r="H79" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I79" s="17"/>
+    </row>
+    <row r="80" spans="1:10">
+      <c r="A80" s="19">
         <v>166</v>
       </c>
-      <c r="B80" s="17">
+      <c r="B80" s="19">
         <v>3</v>
       </c>
-      <c r="C80" s="18">
+      <c r="C80" s="20">
         <v>6</v>
       </c>
-      <c r="D80" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E80" s="17" t="s">
+      <c r="D80" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="E80" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="F80" s="17"/>
-      <c r="G80" s="17"/>
-      <c r="H80" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="I80" s="19"/>
+      <c r="F80" s="19"/>
+      <c r="G80" s="19"/>
+      <c r="H80" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I80" s="17"/>
     </row>
     <row r="81" spans="1:9">
-      <c r="A81" s="17">
+      <c r="A81" s="19">
         <v>167</v>
       </c>
-      <c r="B81" s="17">
+      <c r="B81" s="19">
         <v>3</v>
       </c>
-      <c r="C81" s="18">
+      <c r="C81" s="20">
         <v>7</v>
       </c>
-      <c r="D81" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E81" s="17" t="s">
+      <c r="D81" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="E81" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="F81" s="17"/>
-      <c r="G81" s="17"/>
-      <c r="H81" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="I81" s="19"/>
+      <c r="F81" s="19"/>
+      <c r="G81" s="19"/>
+      <c r="H81" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I81" s="17"/>
     </row>
     <row r="82" spans="1:9">
-      <c r="A82" s="17">
+      <c r="A82" s="19">
         <v>168</v>
       </c>
-      <c r="B82" s="17">
+      <c r="B82" s="19">
         <v>3</v>
       </c>
-      <c r="C82" s="18">
+      <c r="C82" s="20">
         <v>8</v>
       </c>
-      <c r="D82" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E82" s="17" t="s">
+      <c r="D82" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="E82" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="F82" s="17"/>
-      <c r="G82" s="17"/>
-      <c r="H82" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="I82" s="19"/>
+      <c r="F82" s="19"/>
+      <c r="G82" s="19"/>
+      <c r="H82" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I82" s="17"/>
     </row>
     <row r="83" spans="1:9">
-      <c r="A83" s="17">
+      <c r="A83" s="19">
         <v>169</v>
       </c>
-      <c r="B83" s="17">
+      <c r="B83" s="19">
         <v>3</v>
       </c>
-      <c r="C83" s="18">
+      <c r="C83" s="20">
         <v>9</v>
       </c>
-      <c r="D83" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E83" s="17" t="s">
+      <c r="D83" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="E83" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="F83" s="17"/>
-      <c r="G83" s="17"/>
-      <c r="H83" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="I83" s="19"/>
+      <c r="F83" s="19"/>
+      <c r="G83" s="19"/>
+      <c r="H83" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I83" s="17"/>
     </row>
     <row r="84" spans="1:9">
-      <c r="A84" s="17">
+      <c r="A84" s="19">
         <v>170</v>
       </c>
-      <c r="B84" s="17">
+      <c r="B84" s="19">
         <v>3</v>
       </c>
-      <c r="C84" s="18">
+      <c r="C84" s="20">
         <v>10</v>
       </c>
-      <c r="D84" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E84" s="17" t="s">
+      <c r="D84" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="E84" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="F84" s="17"/>
-      <c r="G84" s="17"/>
-      <c r="H84" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="I84" s="19"/>
+      <c r="F84" s="19"/>
+      <c r="G84" s="19"/>
+      <c r="H84" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I84" s="17"/>
     </row>
     <row r="85" spans="1:9">
-      <c r="A85" s="17">
+      <c r="A85" s="19">
         <v>171</v>
       </c>
-      <c r="B85" s="17">
+      <c r="B85" s="19">
         <v>3</v>
       </c>
-      <c r="C85" s="18" t="s">
+      <c r="C85" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="D85" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E85" s="17" t="s">
+      <c r="D85" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="E85" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="F85" s="17"/>
-      <c r="G85" s="17"/>
-      <c r="H85" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="I85" s="19"/>
-    </row>
-    <row r="86" spans="1:8">
-      <c r="A86" s="17">
+      <c r="F85" s="19"/>
+      <c r="G85" s="19"/>
+      <c r="H85" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I85" s="17"/>
+    </row>
+    <row r="86" spans="1:9">
+      <c r="A86" s="19">
         <v>172</v>
       </c>
-      <c r="B86" s="17">
+      <c r="B86" s="19">
         <v>3</v>
       </c>
-      <c r="C86" s="18" t="s">
+      <c r="C86" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="D86" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E86" s="17" t="s">
+      <c r="D86" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="E86" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="F86" s="17"/>
-      <c r="G86" s="17"/>
-      <c r="H86" s="18" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8">
-      <c r="A87" s="17">
+      <c r="F86" s="19"/>
+      <c r="G86" s="19"/>
+      <c r="H86" s="20" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9">
+      <c r="A87" s="19">
         <v>173</v>
       </c>
-      <c r="B87" s="17">
+      <c r="B87" s="19">
         <v>3</v>
       </c>
-      <c r="C87" s="18" t="s">
+      <c r="C87" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="D87" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E87" s="17" t="s">
+      <c r="D87" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="E87" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="F87" s="17"/>
-      <c r="G87" s="17"/>
-      <c r="H87" s="18" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8">
-      <c r="A88" s="17">
+      <c r="F87" s="19"/>
+      <c r="G87" s="19"/>
+      <c r="H87" s="20" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9">
+      <c r="A88" s="19">
         <v>174</v>
       </c>
-      <c r="B88" s="17">
+      <c r="B88" s="19">
         <v>3</v>
       </c>
-      <c r="C88" s="18" t="s">
+      <c r="C88" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="D88" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E88" s="17" t="s">
+      <c r="D88" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="E88" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="F88" s="17"/>
-      <c r="G88" s="17"/>
-      <c r="H88" s="18" t="s">
+      <c r="F88" s="19"/>
+      <c r="G88" s="19"/>
+      <c r="H88" s="20" t="s">
         <v>71</v>
       </c>
     </row>

--- a/table/resources/sample/PointsAwardRanking.xlsx
+++ b/table/resources/sample/PointsAwardRanking.xlsx
@@ -176,7 +176,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="72">
   <si>
     <t>序列ID</t>
   </si>
@@ -244,148 +244,139 @@
     <t>2</t>
   </si>
   <si>
+    <t>1990000_3045000</t>
+  </si>
+  <si>
+    <t>jfdj_box_1.png</t>
+  </si>
+  <si>
+    <t>1990000_2310000</t>
+  </si>
+  <si>
+    <t>jfdj_box_2.png</t>
+  </si>
+  <si>
+    <t>1990000_1680000</t>
+  </si>
+  <si>
+    <t>jfdj_box_3.png</t>
+  </si>
+  <si>
+    <t>1990000_1260000</t>
+  </si>
+  <si>
+    <t>1990000_1155000</t>
+  </si>
+  <si>
+    <t>1990000_1050000</t>
+  </si>
+  <si>
+    <t>1990000_945000</t>
+  </si>
+  <si>
+    <t>1990000_840000</t>
+  </si>
+  <si>
+    <t>1990000_735000</t>
+  </si>
+  <si>
+    <t>1990000_630000</t>
+  </si>
+  <si>
+    <t>11_20</t>
+  </si>
+  <si>
+    <t>1990000_252000</t>
+  </si>
+  <si>
+    <t>21_30</t>
+  </si>
+  <si>
+    <t>1990000_210000</t>
+  </si>
+  <si>
+    <t>31_40</t>
+  </si>
+  <si>
+    <t>1990000_168000</t>
+  </si>
+  <si>
+    <t>41_50</t>
+  </si>
+  <si>
+    <t>1990000_105000</t>
+  </si>
+  <si>
     <t>1990000_6090000</t>
   </si>
   <si>
-    <t>jfdj_box_1.png</t>
-  </si>
-  <si>
     <t>1990000_4620000</t>
   </si>
   <si>
-    <t>jfdj_box_2.png</t>
-  </si>
-  <si>
     <t>1990000_3360000</t>
   </si>
   <si>
-    <t>jfdj_box_3.png</t>
-  </si>
-  <si>
     <t>1990000_2520000</t>
   </si>
   <si>
-    <t>1990000_2310000</t>
-  </si>
-  <si>
     <t>1990000_2100000</t>
   </si>
   <si>
     <t>1990000_1890000</t>
   </si>
   <si>
-    <t>1990000_1680000</t>
-  </si>
-  <si>
     <t>1990000_1470000</t>
   </si>
   <si>
-    <t>1990000_1260000</t>
-  </si>
-  <si>
-    <t>11_20</t>
-  </si>
-  <si>
     <t>1990000_504000</t>
   </si>
   <si>
-    <t>21_30</t>
-  </si>
-  <si>
     <t>1990000_420000</t>
   </si>
   <si>
-    <t>31_40</t>
-  </si>
-  <si>
     <t>1990000_336000</t>
   </si>
   <si>
-    <t>41_50</t>
-  </si>
-  <si>
-    <t>1990000_210000</t>
-  </si>
-  <si>
-    <t>1990000_10150000</t>
-  </si>
-  <si>
-    <t>1990000_7700000</t>
-  </si>
-  <si>
-    <t>1990000_5600000</t>
-  </si>
-  <si>
-    <t>1990000_4200000</t>
-  </si>
-  <si>
-    <t>1990000_3850000</t>
-  </si>
-  <si>
-    <t>1990000_3500000</t>
-  </si>
-  <si>
-    <t>1990000_3150000</t>
-  </si>
-  <si>
-    <t>1990000_2800000</t>
-  </si>
-  <si>
-    <t>1990000_2450000</t>
-  </si>
-  <si>
-    <t>1990000_840000</t>
-  </si>
-  <si>
-    <t>1990000_700000</t>
-  </si>
-  <si>
-    <t>1990000_560000</t>
-  </si>
-  <si>
-    <t>1990000_350000</t>
-  </si>
-  <si>
-    <t>1990000_812000000</t>
-  </si>
-  <si>
-    <t>1990000_616000000</t>
-  </si>
-  <si>
-    <t>1990000_448000000</t>
-  </si>
-  <si>
-    <t>1990000_336000000</t>
-  </si>
-  <si>
-    <t>1990000_308000000</t>
-  </si>
-  <si>
-    <t>1990000_280000000</t>
+    <t>1990000_456750000</t>
+  </si>
+  <si>
+    <t>1990000_346500000</t>
   </si>
   <si>
     <t>1990000_252000000</t>
   </si>
   <si>
-    <t>1990000_224000000</t>
-  </si>
-  <si>
-    <t>1990000_196000000</t>
-  </si>
-  <si>
-    <t>1990000_168000000</t>
-  </si>
-  <si>
-    <t>1990000_67200000</t>
-  </si>
-  <si>
-    <t>1990000_56000000</t>
-  </si>
-  <si>
-    <t>1990000_44800000</t>
-  </si>
-  <si>
-    <t>1990000_28000000</t>
+    <t>1990000_189000000</t>
+  </si>
+  <si>
+    <t>1990000_173250000</t>
+  </si>
+  <si>
+    <t>1990000_157500000</t>
+  </si>
+  <si>
+    <t>1990000_141750000</t>
+  </si>
+  <si>
+    <t>1990000_126000000</t>
+  </si>
+  <si>
+    <t>1990000_110250000</t>
+  </si>
+  <si>
+    <t>1990000_94500000</t>
+  </si>
+  <si>
+    <t>1990000_37800000</t>
+  </si>
+  <si>
+    <t>1990000_31500000</t>
+  </si>
+  <si>
+    <t>1990000_25200000</t>
+  </si>
+  <si>
+    <t>1990000_15750000</t>
   </si>
   <si>
     <t>wdcc_ccb_1.png</t>
@@ -2011,7 +2002,7 @@
         <v>21</v>
       </c>
       <c r="E23" s="15" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="F23" s="15"/>
       <c r="G23" s="15"/>
@@ -2033,7 +2024,7 @@
         <v>21</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F24" s="15"/>
       <c r="G24" s="15"/>
@@ -2055,7 +2046,7 @@
         <v>21</v>
       </c>
       <c r="E25" s="15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F25" s="15"/>
       <c r="G25" s="15"/>
@@ -2077,7 +2068,7 @@
         <v>21</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="F26" s="15"/>
       <c r="G26" s="15"/>
@@ -2099,7 +2090,7 @@
         <v>21</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F27" s="15"/>
       <c r="G27" s="15"/>
@@ -2120,7 +2111,7 @@
         <v>21</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F28" s="15"/>
       <c r="G28" s="15"/>
@@ -2141,7 +2132,7 @@
         <v>21</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F29" s="15"/>
       <c r="G29" s="15"/>
@@ -2162,7 +2153,7 @@
         <v>21</v>
       </c>
       <c r="E30" s="15" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F30" s="15"/>
       <c r="G30" s="15"/>
@@ -2183,7 +2174,7 @@
         <v>21</v>
       </c>
       <c r="E31" s="15" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F31" s="15"/>
       <c r="G31" s="15"/>
@@ -2204,7 +2195,7 @@
         <v>21</v>
       </c>
       <c r="E32" s="15" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F32" s="15"/>
       <c r="G32" s="15"/>
@@ -2225,7 +2216,7 @@
         <v>21</v>
       </c>
       <c r="E33" s="15" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F33" s="15"/>
       <c r="G33" s="15" t="s">
@@ -2248,7 +2239,7 @@
         <v>21</v>
       </c>
       <c r="E34" s="15" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F34" s="15"/>
       <c r="G34" s="15" t="s">
@@ -2271,7 +2262,7 @@
         <v>21</v>
       </c>
       <c r="E35" s="15" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F35" s="15"/>
       <c r="G35" s="15" t="s">
@@ -2294,7 +2285,7 @@
         <v>21</v>
       </c>
       <c r="E36" s="15" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F36" s="15"/>
       <c r="G36" s="15"/>
@@ -2315,7 +2306,7 @@
         <v>21</v>
       </c>
       <c r="E37" s="15" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F37" s="15"/>
       <c r="G37" s="15"/>
@@ -2336,7 +2327,7 @@
         <v>21</v>
       </c>
       <c r="E38" s="15" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F38" s="15"/>
       <c r="G38" s="15"/>
@@ -2357,7 +2348,7 @@
         <v>21</v>
       </c>
       <c r="E39" s="15" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F39" s="15"/>
       <c r="G39" s="15"/>
@@ -2378,7 +2369,7 @@
         <v>21</v>
       </c>
       <c r="E40" s="15" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F40" s="15"/>
       <c r="G40" s="15"/>
@@ -2399,7 +2390,7 @@
         <v>21</v>
       </c>
       <c r="E41" s="15" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F41" s="15"/>
       <c r="G41" s="15"/>
@@ -2420,7 +2411,7 @@
         <v>21</v>
       </c>
       <c r="E42" s="15" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F42" s="15"/>
       <c r="G42" s="15"/>
@@ -2441,7 +2432,7 @@
         <v>21</v>
       </c>
       <c r="E43" s="15" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F43" s="15"/>
       <c r="G43" s="15"/>
@@ -2462,7 +2453,7 @@
         <v>21</v>
       </c>
       <c r="E44" s="15" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F44" s="15"/>
       <c r="G44" s="15"/>
@@ -2482,7 +2473,7 @@
         <v>21</v>
       </c>
       <c r="E45" s="15" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F45" s="15"/>
       <c r="G45" s="15"/>
@@ -2502,7 +2493,7 @@
         <v>21</v>
       </c>
       <c r="E46" s="15" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="F46" s="15"/>
       <c r="G46" s="15"/>
@@ -2528,10 +2519,10 @@
         <v>33333333</v>
       </c>
       <c r="G47" s="19" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="H47" s="20" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I47" s="17"/>
       <c r="J47" s="17"/>
@@ -2556,10 +2547,10 @@
         <v>22222222</v>
       </c>
       <c r="G48" s="19" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="H48" s="20" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I48" s="17"/>
       <c r="J48" s="17"/>
@@ -2584,10 +2575,10 @@
         <v>11111111</v>
       </c>
       <c r="G49" s="19" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H49" s="20" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I49" s="17"/>
       <c r="J49" s="17"/>
@@ -2612,10 +2603,10 @@
         <v>5000000</v>
       </c>
       <c r="G50" s="19" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="H50" s="20" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I50" s="17"/>
       <c r="J50" s="17"/>
@@ -2640,10 +2631,10 @@
         <v>3000000</v>
       </c>
       <c r="G51" s="19" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="H51" s="20" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I51" s="17"/>
       <c r="J51" s="18"/>
@@ -2668,7 +2659,7 @@
       <c r="F52" s="19"/>
       <c r="G52" s="19"/>
       <c r="H52" s="20" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I52" s="17"/>
       <c r="J52" s="18"/>
@@ -2693,7 +2684,7 @@
       <c r="F53" s="19"/>
       <c r="G53" s="19"/>
       <c r="H53" s="20" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I53" s="17"/>
       <c r="J53" s="18"/>
@@ -2718,7 +2709,7 @@
       <c r="F54" s="19"/>
       <c r="G54" s="19"/>
       <c r="H54" s="20" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I54" s="17"/>
       <c r="J54" s="18"/>
@@ -2743,7 +2734,7 @@
       <c r="F55" s="19"/>
       <c r="G55" s="19"/>
       <c r="H55" s="20" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I55" s="17"/>
       <c r="L55" s="2"/>
@@ -2767,7 +2758,7 @@
       <c r="F56" s="19"/>
       <c r="G56" s="19"/>
       <c r="H56" s="20" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I56" s="17"/>
       <c r="L56" s="2"/>
@@ -2791,7 +2782,7 @@
       <c r="F57" s="19"/>
       <c r="G57" s="19"/>
       <c r="H57" s="20" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I57" s="17"/>
       <c r="J57" s="8"/>
@@ -2816,7 +2807,7 @@
       <c r="F58" s="19"/>
       <c r="G58" s="19"/>
       <c r="H58" s="20" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I58" s="17"/>
       <c r="J58" s="18"/>
@@ -2841,7 +2832,7 @@
       <c r="F59" s="19"/>
       <c r="G59" s="19"/>
       <c r="H59" s="20" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I59" s="17"/>
       <c r="J59" s="18"/>
@@ -2866,7 +2857,7 @@
       <c r="F60" s="19"/>
       <c r="G60" s="19"/>
       <c r="H60" s="20" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I60" s="17"/>
       <c r="J60" s="18"/>
@@ -2892,10 +2883,10 @@
         <v>33333333</v>
       </c>
       <c r="G61" s="19" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="H61" s="20" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I61" s="17"/>
       <c r="J61" s="18"/>
@@ -2921,10 +2912,10 @@
         <v>22222222</v>
       </c>
       <c r="G62" s="19" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="H62" s="20" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I62" s="17"/>
       <c r="J62" s="17"/>
@@ -2950,10 +2941,10 @@
         <v>11111111</v>
       </c>
       <c r="G63" s="19" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H63" s="20" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="64" s="3" customFormat="1" spans="1:12">
@@ -2976,10 +2967,10 @@
         <v>5000000</v>
       </c>
       <c r="G64" s="19" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="H64" s="20" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I64" s="17"/>
       <c r="J64" s="18"/>
@@ -2998,16 +2989,16 @@
         <v>21</v>
       </c>
       <c r="E65" s="15" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="F65" s="19">
         <v>3000000</v>
       </c>
       <c r="G65" s="19" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="H65" s="20" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I65" s="17"/>
       <c r="J65" s="18"/>
@@ -3026,12 +3017,12 @@
         <v>21</v>
       </c>
       <c r="E66" s="15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F66" s="19"/>
       <c r="G66" s="19"/>
       <c r="H66" s="20" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I66" s="17"/>
       <c r="J66" s="18"/>
@@ -3050,12 +3041,12 @@
         <v>21</v>
       </c>
       <c r="E67" s="15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F67" s="19"/>
       <c r="G67" s="19"/>
       <c r="H67" s="20" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I67" s="17"/>
       <c r="J67" s="18"/>
@@ -3074,12 +3065,12 @@
         <v>21</v>
       </c>
       <c r="E68" s="15" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="F68" s="19"/>
       <c r="G68" s="19"/>
       <c r="H68" s="20" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I68" s="17"/>
       <c r="J68" s="17"/>
@@ -3098,12 +3089,12 @@
         <v>21</v>
       </c>
       <c r="E69" s="15" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F69" s="19"/>
       <c r="G69" s="19"/>
       <c r="H69" s="20" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I69" s="17"/>
     </row>
@@ -3121,12 +3112,12 @@
         <v>21</v>
       </c>
       <c r="E70" s="15" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F70" s="19"/>
       <c r="G70" s="19"/>
       <c r="H70" s="20" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I70" s="17"/>
     </row>
@@ -3144,12 +3135,12 @@
         <v>21</v>
       </c>
       <c r="E71" s="15" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F71" s="19"/>
       <c r="G71" s="19"/>
       <c r="H71" s="20" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I71" s="17"/>
     </row>
@@ -3167,12 +3158,12 @@
         <v>21</v>
       </c>
       <c r="E72" s="15" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F72" s="19"/>
       <c r="G72" s="19"/>
       <c r="H72" s="20" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I72" s="17"/>
     </row>
@@ -3190,12 +3181,12 @@
         <v>21</v>
       </c>
       <c r="E73" s="15" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F73" s="19"/>
       <c r="G73" s="19"/>
       <c r="H73" s="20" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I73" s="17"/>
     </row>
@@ -3213,12 +3204,12 @@
         <v>21</v>
       </c>
       <c r="E74" s="15" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F74" s="19"/>
       <c r="G74" s="19"/>
       <c r="H74" s="20" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I74" s="17"/>
     </row>
@@ -3236,16 +3227,16 @@
         <v>21</v>
       </c>
       <c r="E75" s="15" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F75" s="19">
         <v>99999999</v>
       </c>
       <c r="G75" s="19" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="H75" s="20" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I75" s="17"/>
     </row>
@@ -3263,16 +3254,16 @@
         <v>21</v>
       </c>
       <c r="E76" s="15" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F76" s="19">
         <v>88888888</v>
       </c>
       <c r="G76" s="19" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="H76" s="20" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I76" s="17"/>
     </row>
@@ -3290,16 +3281,16 @@
         <v>21</v>
       </c>
       <c r="E77" s="15" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F77" s="19">
         <v>77777777</v>
       </c>
       <c r="G77" s="19" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H77" s="20" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I77" s="17"/>
     </row>
@@ -3317,16 +3308,16 @@
         <v>21</v>
       </c>
       <c r="E78" s="15" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F78" s="19">
         <v>66666666</v>
       </c>
       <c r="G78" s="19" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="H78" s="20" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I78" s="17"/>
     </row>
@@ -3344,16 +3335,16 @@
         <v>21</v>
       </c>
       <c r="E79" s="15" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F79" s="19">
         <v>55555555</v>
       </c>
       <c r="G79" s="19" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="H79" s="20" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I79" s="17"/>
     </row>
@@ -3371,12 +3362,12 @@
         <v>21</v>
       </c>
       <c r="E80" s="15" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F80" s="19"/>
       <c r="G80" s="19"/>
       <c r="H80" s="20" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I80" s="17"/>
     </row>
@@ -3394,12 +3385,12 @@
         <v>21</v>
       </c>
       <c r="E81" s="15" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F81" s="19"/>
       <c r="G81" s="19"/>
       <c r="H81" s="20" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I81" s="17"/>
     </row>
@@ -3417,12 +3408,12 @@
         <v>21</v>
       </c>
       <c r="E82" s="15" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F82" s="19"/>
       <c r="G82" s="19"/>
       <c r="H82" s="20" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I82" s="17"/>
     </row>
@@ -3440,12 +3431,12 @@
         <v>21</v>
       </c>
       <c r="E83" s="15" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F83" s="19"/>
       <c r="G83" s="19"/>
       <c r="H83" s="20" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I83" s="17"/>
     </row>
@@ -3463,12 +3454,12 @@
         <v>21</v>
       </c>
       <c r="E84" s="15" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F84" s="19"/>
       <c r="G84" s="19"/>
       <c r="H84" s="20" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I84" s="17"/>
     </row>
@@ -3486,12 +3477,12 @@
         <v>21</v>
       </c>
       <c r="E85" s="15" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F85" s="19"/>
       <c r="G85" s="19"/>
       <c r="H85" s="20" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I85" s="17"/>
     </row>
@@ -3509,12 +3500,12 @@
         <v>21</v>
       </c>
       <c r="E86" s="15" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F86" s="19"/>
       <c r="G86" s="19"/>
       <c r="H86" s="20" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="87" spans="1:9">
@@ -3531,12 +3522,12 @@
         <v>21</v>
       </c>
       <c r="E87" s="15" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F87" s="19"/>
       <c r="G87" s="19"/>
       <c r="H87" s="20" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="88" spans="1:9">
@@ -3553,12 +3544,12 @@
         <v>21</v>
       </c>
       <c r="E88" s="15" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="F88" s="19"/>
       <c r="G88" s="19"/>
       <c r="H88" s="20" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/table/resources/sample/PointsAwardRanking.xlsx
+++ b/table/resources/sample/PointsAwardRanking.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="PointsAwardRanking" sheetId="1" r:id="rId1"/>
@@ -171,12 +171,34 @@
         </r>
       </text>
     </comment>
+    <comment ref="I1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+活动开启后，会出现机器人占用此榜单位置</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="75">
   <si>
     <t>序列ID</t>
   </si>
@@ -202,6 +224,9 @@
     <t>开始日期</t>
   </si>
   <si>
+    <t>是否使用机器人占榜</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -241,6 +266,9 @@
     <t>time</t>
   </si>
   <si>
+    <t>robotUse</t>
+  </si>
+  <si>
     <t>2</t>
   </si>
   <si>
@@ -248,6 +276,9 @@
   </si>
   <si>
     <t>jfdj_box_1.png</t>
+  </si>
+  <si>
+    <t>1</t>
   </si>
   <si>
     <t>1990000_2310000</t>
@@ -1469,7 +1500,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L88"/>
+  <dimension ref="A1:M88"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="7" style="4" customWidth="1"/>
@@ -1480,11 +1511,12 @@
     <col min="6" max="6" width="10.375" style="6" customWidth="1"/>
     <col min="7" max="7" width="23.625" style="6" customWidth="1"/>
     <col min="8" max="8" width="21.25" style="7" customWidth="1"/>
-    <col min="9" max="10" width="14.5" style="8" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="4"/>
+    <col min="9" max="9" width="17.6416666666667" style="7" customWidth="1"/>
+    <col min="10" max="11" width="14.5" style="8" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -1509,60 +1541,69 @@
       <c r="H1" s="13" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="I1" s="13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="10" t="s">
-        <v>8</v>
-      </c>
       <c r="E2" s="14" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H2" s="13" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
+        <v>13</v>
+      </c>
+      <c r="I2" s="12" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
+        <v>21</v>
+      </c>
+      <c r="I3" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="9"/>
       <c r="B4" s="9"/>
       <c r="C4" s="10"/>
@@ -1571,8 +1612,9 @@
       <c r="F4" s="12"/>
       <c r="G4" s="12"/>
       <c r="H4" s="13"/>
-    </row>
-    <row r="5" s="2" customFormat="1" spans="1:12">
+      <c r="I4" s="13"/>
+    </row>
+    <row r="5" s="2" customFormat="1" spans="1:13">
       <c r="A5" s="15">
         <v>1</v>
       </c>
@@ -1583,20 +1625,23 @@
         <v>1</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F5" s="15"/>
       <c r="G5" s="15" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H5" s="16"/>
-      <c r="I5" s="17"/>
+      <c r="I5" s="16" t="s">
+        <v>26</v>
+      </c>
       <c r="J5" s="17"/>
-    </row>
-    <row r="6" s="2" customFormat="1" spans="1:12">
+      <c r="K5" s="17"/>
+    </row>
+    <row r="6" s="2" customFormat="1" spans="1:13">
       <c r="A6" s="15">
         <v>2</v>
       </c>
@@ -1607,20 +1652,23 @@
         <v>2</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F6" s="15"/>
       <c r="G6" s="15" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H6" s="16"/>
-      <c r="I6" s="17"/>
+      <c r="I6" s="16" t="s">
+        <v>26</v>
+      </c>
       <c r="J6" s="17"/>
-    </row>
-    <row r="7" s="2" customFormat="1" spans="1:12">
+      <c r="K6" s="17"/>
+    </row>
+    <row r="7" s="2" customFormat="1" spans="1:13">
       <c r="A7" s="15">
         <v>3</v>
       </c>
@@ -1631,20 +1679,23 @@
         <v>3</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F7" s="15"/>
       <c r="G7" s="15" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="H7" s="16"/>
-      <c r="I7" s="17"/>
+      <c r="I7" s="16" t="s">
+        <v>26</v>
+      </c>
       <c r="J7" s="17"/>
-    </row>
-    <row r="8" s="2" customFormat="1" spans="1:12">
+      <c r="K7" s="17"/>
+    </row>
+    <row r="8" s="2" customFormat="1" spans="1:13">
       <c r="A8" s="15">
         <v>4</v>
       </c>
@@ -1655,18 +1706,21 @@
         <v>4</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F8" s="15"/>
       <c r="G8" s="15"/>
       <c r="H8" s="16"/>
-      <c r="I8" s="17"/>
+      <c r="I8" s="16" t="s">
+        <v>26</v>
+      </c>
       <c r="J8" s="17"/>
-    </row>
-    <row r="9" s="3" customFormat="1" spans="1:12">
+      <c r="K8" s="17"/>
+    </row>
+    <row r="9" s="3" customFormat="1" spans="1:13">
       <c r="A9" s="15">
         <v>5</v>
       </c>
@@ -1677,19 +1731,20 @@
         <v>5</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F9" s="15"/>
       <c r="G9" s="15"/>
       <c r="H9" s="16"/>
-      <c r="I9" s="17"/>
-      <c r="J9" s="18"/>
-      <c r="L9" s="2"/>
-    </row>
-    <row r="10" s="3" customFormat="1" spans="1:12">
+      <c r="I9" s="16"/>
+      <c r="J9" s="17"/>
+      <c r="K9" s="18"/>
+      <c r="M9" s="2"/>
+    </row>
+    <row r="10" s="3" customFormat="1" spans="1:13">
       <c r="A10" s="15">
         <v>6</v>
       </c>
@@ -1700,19 +1755,20 @@
         <v>6</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F10" s="15"/>
       <c r="G10" s="15"/>
       <c r="H10" s="16"/>
-      <c r="I10" s="17"/>
-      <c r="J10" s="18"/>
-      <c r="L10" s="2"/>
-    </row>
-    <row r="11" s="3" customFormat="1" spans="1:12">
+      <c r="I10" s="16"/>
+      <c r="J10" s="17"/>
+      <c r="K10" s="18"/>
+      <c r="M10" s="2"/>
+    </row>
+    <row r="11" s="3" customFormat="1" spans="1:13">
       <c r="A11" s="15">
         <v>7</v>
       </c>
@@ -1723,19 +1779,20 @@
         <v>7</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F11" s="15"/>
       <c r="G11" s="15"/>
       <c r="H11" s="16"/>
-      <c r="I11" s="17"/>
-      <c r="J11" s="18"/>
-      <c r="L11" s="2"/>
-    </row>
-    <row r="12" s="3" customFormat="1" spans="1:12">
+      <c r="I11" s="16"/>
+      <c r="J11" s="17"/>
+      <c r="K11" s="18"/>
+      <c r="M11" s="2"/>
+    </row>
+    <row r="12" s="3" customFormat="1" spans="1:13">
       <c r="A12" s="15">
         <v>8</v>
       </c>
@@ -1746,19 +1803,20 @@
         <v>8</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F12" s="15"/>
       <c r="G12" s="15"/>
       <c r="H12" s="16"/>
-      <c r="I12" s="17"/>
-      <c r="J12" s="18"/>
-      <c r="L12" s="2"/>
-    </row>
-    <row r="13" spans="1:12">
+      <c r="I12" s="16"/>
+      <c r="J12" s="17"/>
+      <c r="K12" s="18"/>
+      <c r="M12" s="2"/>
+    </row>
+    <row r="13" spans="1:13">
       <c r="A13" s="15">
         <v>9</v>
       </c>
@@ -1769,18 +1827,19 @@
         <v>9</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F13" s="15"/>
       <c r="G13" s="15"/>
       <c r="H13" s="16"/>
-      <c r="I13" s="17"/>
-      <c r="L13" s="2"/>
-    </row>
-    <row r="14" spans="1:12">
+      <c r="I13" s="16"/>
+      <c r="J13" s="17"/>
+      <c r="M13" s="2"/>
+    </row>
+    <row r="14" spans="1:13">
       <c r="A14" s="15">
         <v>10</v>
       </c>
@@ -1791,18 +1850,19 @@
         <v>10</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F14" s="15"/>
       <c r="G14" s="15"/>
       <c r="H14" s="16"/>
-      <c r="I14" s="17"/>
-      <c r="L14" s="2"/>
-    </row>
-    <row r="15" customFormat="1" spans="1:12">
+      <c r="I14" s="16"/>
+      <c r="J14" s="17"/>
+      <c r="M14" s="2"/>
+    </row>
+    <row r="15" customFormat="1" spans="1:13">
       <c r="A15" s="15">
         <v>11</v>
       </c>
@@ -1810,22 +1870,23 @@
         <v>1</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F15" s="15"/>
       <c r="G15" s="15"/>
       <c r="H15" s="16"/>
-      <c r="I15" s="17"/>
-      <c r="J15" s="8"/>
-      <c r="L15" s="2"/>
-    </row>
-    <row r="16" s="3" customFormat="1" spans="1:12">
+      <c r="I15" s="16"/>
+      <c r="J15" s="17"/>
+      <c r="K15" s="8"/>
+      <c r="M15" s="2"/>
+    </row>
+    <row r="16" s="3" customFormat="1" spans="1:13">
       <c r="A16" s="15">
         <v>12</v>
       </c>
@@ -1833,22 +1894,23 @@
         <v>1</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F16" s="15"/>
       <c r="G16" s="15"/>
       <c r="H16" s="16"/>
-      <c r="I16" s="17"/>
-      <c r="J16" s="18"/>
-      <c r="L16" s="2"/>
-    </row>
-    <row r="17" s="3" customFormat="1" spans="1:12">
+      <c r="I16" s="16"/>
+      <c r="J16" s="17"/>
+      <c r="K16" s="18"/>
+      <c r="M16" s="2"/>
+    </row>
+    <row r="17" s="3" customFormat="1" spans="1:13">
       <c r="A17" s="15">
         <v>13</v>
       </c>
@@ -1856,22 +1918,23 @@
         <v>1</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F17" s="15"/>
       <c r="G17" s="15"/>
       <c r="H17" s="16"/>
-      <c r="I17" s="17"/>
-      <c r="J17" s="18"/>
-      <c r="L17" s="2"/>
-    </row>
-    <row r="18" s="3" customFormat="1" spans="1:12">
+      <c r="I17" s="16"/>
+      <c r="J17" s="17"/>
+      <c r="K17" s="18"/>
+      <c r="M17" s="2"/>
+    </row>
+    <row r="18" s="3" customFormat="1" spans="1:13">
       <c r="A18" s="15">
         <v>14</v>
       </c>
@@ -1879,22 +1942,23 @@
         <v>1</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F18" s="15"/>
       <c r="G18" s="15"/>
       <c r="H18" s="16"/>
-      <c r="I18" s="17"/>
-      <c r="J18" s="18"/>
-      <c r="L18" s="2"/>
-    </row>
-    <row r="19" s="3" customFormat="1" spans="1:12">
+      <c r="I18" s="16"/>
+      <c r="J18" s="17"/>
+      <c r="K18" s="18"/>
+      <c r="M18" s="2"/>
+    </row>
+    <row r="19" s="3" customFormat="1" spans="1:13">
       <c r="A19" s="15">
         <v>31</v>
       </c>
@@ -1905,21 +1969,24 @@
         <v>1</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F19" s="15"/>
       <c r="G19" s="15" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H19" s="16"/>
-      <c r="I19" s="17"/>
-      <c r="J19" s="18"/>
-      <c r="L19" s="2"/>
-    </row>
-    <row r="20" s="3" customFormat="1" spans="1:12">
+      <c r="I19" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="J19" s="17"/>
+      <c r="K19" s="18"/>
+      <c r="M19" s="2"/>
+    </row>
+    <row r="20" s="3" customFormat="1" spans="1:13">
       <c r="A20" s="15">
         <v>32</v>
       </c>
@@ -1930,21 +1997,24 @@
         <v>2</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F20" s="15"/>
       <c r="G20" s="15" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H20" s="16"/>
-      <c r="I20" s="17"/>
+      <c r="I20" s="16" t="s">
+        <v>26</v>
+      </c>
       <c r="J20" s="17"/>
-      <c r="L20" s="2"/>
-    </row>
-    <row r="21" spans="1:12">
+      <c r="K20" s="17"/>
+      <c r="M20" s="2"/>
+    </row>
+    <row r="21" spans="1:13">
       <c r="A21" s="15">
         <v>33</v>
       </c>
@@ -1955,18 +2025,21 @@
         <v>3</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F21" s="15"/>
       <c r="G21" s="15" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="H21" s="16"/>
-    </row>
-    <row r="22" s="3" customFormat="1" spans="1:12">
+      <c r="I21" s="16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="22" s="3" customFormat="1" spans="1:13">
       <c r="A22" s="15">
         <v>34</v>
       </c>
@@ -1977,18 +2050,21 @@
         <v>4</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F22" s="15"/>
       <c r="G22" s="15"/>
       <c r="H22" s="16"/>
-      <c r="I22" s="17"/>
-      <c r="J22" s="18"/>
-    </row>
-    <row r="23" s="3" customFormat="1" spans="1:12">
+      <c r="I22" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="J22" s="17"/>
+      <c r="K22" s="18"/>
+    </row>
+    <row r="23" s="3" customFormat="1" spans="1:13">
       <c r="A23" s="15">
         <v>35</v>
       </c>
@@ -1999,18 +2075,19 @@
         <v>5</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E23" s="15" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F23" s="15"/>
       <c r="G23" s="15"/>
       <c r="H23" s="16"/>
-      <c r="I23" s="17"/>
-      <c r="J23" s="18"/>
-    </row>
-    <row r="24" s="3" customFormat="1" spans="1:12">
+      <c r="I23" s="16"/>
+      <c r="J23" s="17"/>
+      <c r="K23" s="18"/>
+    </row>
+    <row r="24" s="3" customFormat="1" spans="1:13">
       <c r="A24" s="15">
         <v>36</v>
       </c>
@@ -2021,18 +2098,19 @@
         <v>6</v>
       </c>
       <c r="D24" s="16" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F24" s="15"/>
       <c r="G24" s="15"/>
       <c r="H24" s="16"/>
-      <c r="I24" s="17"/>
-      <c r="J24" s="18"/>
-    </row>
-    <row r="25" s="3" customFormat="1" spans="1:12">
+      <c r="I24" s="16"/>
+      <c r="J24" s="17"/>
+      <c r="K24" s="18"/>
+    </row>
+    <row r="25" s="3" customFormat="1" spans="1:13">
       <c r="A25" s="15">
         <v>37</v>
       </c>
@@ -2043,18 +2121,19 @@
         <v>7</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E25" s="15" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F25" s="15"/>
       <c r="G25" s="15"/>
       <c r="H25" s="16"/>
-      <c r="I25" s="17"/>
-      <c r="J25" s="18"/>
-    </row>
-    <row r="26" s="3" customFormat="1" spans="1:12">
+      <c r="I25" s="16"/>
+      <c r="J25" s="17"/>
+      <c r="K25" s="18"/>
+    </row>
+    <row r="26" s="3" customFormat="1" spans="1:13">
       <c r="A26" s="15">
         <v>38</v>
       </c>
@@ -2065,18 +2144,19 @@
         <v>8</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F26" s="15"/>
       <c r="G26" s="15"/>
       <c r="H26" s="16"/>
-      <c r="I26" s="17"/>
+      <c r="I26" s="16"/>
       <c r="J26" s="17"/>
-    </row>
-    <row r="27" spans="1:12">
+      <c r="K26" s="17"/>
+    </row>
+    <row r="27" spans="1:13">
       <c r="A27" s="15">
         <v>39</v>
       </c>
@@ -2087,17 +2167,18 @@
         <v>9</v>
       </c>
       <c r="D27" s="16" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F27" s="15"/>
       <c r="G27" s="15"/>
       <c r="H27" s="16"/>
-      <c r="I27" s="17"/>
-    </row>
-    <row r="28" spans="1:12">
+      <c r="I27" s="16"/>
+      <c r="J27" s="17"/>
+    </row>
+    <row r="28" spans="1:13">
       <c r="A28" s="15">
         <v>40</v>
       </c>
@@ -2108,17 +2189,18 @@
         <v>10</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F28" s="15"/>
       <c r="G28" s="15"/>
       <c r="H28" s="16"/>
-      <c r="I28" s="17"/>
-    </row>
-    <row r="29" spans="1:12">
+      <c r="I28" s="16"/>
+      <c r="J28" s="17"/>
+    </row>
+    <row r="29" spans="1:13">
       <c r="A29" s="15">
         <v>41</v>
       </c>
@@ -2126,20 +2208,21 @@
         <v>2</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F29" s="15"/>
       <c r="G29" s="15"/>
       <c r="H29" s="16"/>
-      <c r="I29" s="17"/>
-    </row>
-    <row r="30" spans="1:12">
+      <c r="I29" s="16"/>
+      <c r="J29" s="17"/>
+    </row>
+    <row r="30" spans="1:13">
       <c r="A30" s="15">
         <v>42</v>
       </c>
@@ -2147,20 +2230,21 @@
         <v>2</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E30" s="15" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F30" s="15"/>
       <c r="G30" s="15"/>
       <c r="H30" s="16"/>
-      <c r="I30" s="17"/>
-    </row>
-    <row r="31" spans="1:12">
+      <c r="I30" s="16"/>
+      <c r="J30" s="17"/>
+    </row>
+    <row r="31" spans="1:13">
       <c r="A31" s="15">
         <v>43</v>
       </c>
@@ -2168,20 +2252,21 @@
         <v>2</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E31" s="15" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F31" s="15"/>
       <c r="G31" s="15"/>
       <c r="H31" s="16"/>
-      <c r="I31" s="17"/>
-    </row>
-    <row r="32" spans="1:12">
+      <c r="I31" s="16"/>
+      <c r="J31" s="17"/>
+    </row>
+    <row r="32" spans="1:13">
       <c r="A32" s="15">
         <v>44</v>
       </c>
@@ -2189,20 +2274,21 @@
         <v>2</v>
       </c>
       <c r="C32" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="D32" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E32" s="15" t="s">
         <v>41</v>
-      </c>
-      <c r="D32" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="E32" s="15" t="s">
-        <v>38</v>
       </c>
       <c r="F32" s="15"/>
       <c r="G32" s="15"/>
       <c r="H32" s="16"/>
-      <c r="I32" s="17"/>
-    </row>
-    <row r="33" spans="1:10">
+      <c r="I32" s="16"/>
+      <c r="J32" s="17"/>
+    </row>
+    <row r="33" spans="1:11">
       <c r="A33" s="15">
         <v>61</v>
       </c>
@@ -2213,19 +2299,22 @@
         <v>1</v>
       </c>
       <c r="D33" s="16" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E33" s="15" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F33" s="15"/>
       <c r="G33" s="15" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H33" s="16"/>
-      <c r="I33" s="17"/>
-    </row>
-    <row r="34" spans="1:10">
+      <c r="I33" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="J33" s="17"/>
+    </row>
+    <row r="34" spans="1:11">
       <c r="A34" s="15">
         <v>62</v>
       </c>
@@ -2236,19 +2325,22 @@
         <v>2</v>
       </c>
       <c r="D34" s="16" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E34" s="15" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F34" s="15"/>
       <c r="G34" s="15" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H34" s="16"/>
-      <c r="I34" s="17"/>
-    </row>
-    <row r="35" spans="1:10">
+      <c r="I34" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="J34" s="17"/>
+    </row>
+    <row r="35" spans="1:11">
       <c r="A35" s="15">
         <v>63</v>
       </c>
@@ -2259,19 +2351,22 @@
         <v>3</v>
       </c>
       <c r="D35" s="16" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E35" s="15" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F35" s="15"/>
       <c r="G35" s="15" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="H35" s="16"/>
-      <c r="I35" s="17"/>
-    </row>
-    <row r="36" spans="1:10">
+      <c r="I35" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="J35" s="17"/>
+    </row>
+    <row r="36" spans="1:11">
       <c r="A36" s="15">
         <v>64</v>
       </c>
@@ -2282,17 +2377,20 @@
         <v>4</v>
       </c>
       <c r="D36" s="16" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E36" s="15" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F36" s="15"/>
       <c r="G36" s="15"/>
       <c r="H36" s="16"/>
-      <c r="I36" s="17"/>
-    </row>
-    <row r="37" spans="1:10">
+      <c r="I36" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="J36" s="17"/>
+    </row>
+    <row r="37" spans="1:11">
       <c r="A37" s="15">
         <v>65</v>
       </c>
@@ -2303,17 +2401,18 @@
         <v>5</v>
       </c>
       <c r="D37" s="16" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E37" s="15" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F37" s="15"/>
       <c r="G37" s="15"/>
       <c r="H37" s="16"/>
-      <c r="I37" s="17"/>
-    </row>
-    <row r="38" spans="1:10">
+      <c r="I37" s="16"/>
+      <c r="J37" s="17"/>
+    </row>
+    <row r="38" spans="1:11">
       <c r="A38" s="15">
         <v>66</v>
       </c>
@@ -2324,17 +2423,18 @@
         <v>6</v>
       </c>
       <c r="D38" s="16" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E38" s="15" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F38" s="15"/>
       <c r="G38" s="15"/>
       <c r="H38" s="16"/>
-      <c r="I38" s="17"/>
-    </row>
-    <row r="39" spans="1:10">
+      <c r="I38" s="16"/>
+      <c r="J38" s="17"/>
+    </row>
+    <row r="39" spans="1:11">
       <c r="A39" s="15">
         <v>67</v>
       </c>
@@ -2345,17 +2445,18 @@
         <v>7</v>
       </c>
       <c r="D39" s="16" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E39" s="15" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F39" s="15"/>
       <c r="G39" s="15"/>
       <c r="H39" s="16"/>
-      <c r="I39" s="17"/>
-    </row>
-    <row r="40" spans="1:10">
+      <c r="I39" s="16"/>
+      <c r="J39" s="17"/>
+    </row>
+    <row r="40" spans="1:11">
       <c r="A40" s="15">
         <v>68</v>
       </c>
@@ -2366,17 +2467,18 @@
         <v>8</v>
       </c>
       <c r="D40" s="16" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E40" s="15" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F40" s="15"/>
       <c r="G40" s="15"/>
       <c r="H40" s="16"/>
-      <c r="I40" s="17"/>
-    </row>
-    <row r="41" spans="1:10">
+      <c r="I40" s="16"/>
+      <c r="J40" s="17"/>
+    </row>
+    <row r="41" spans="1:11">
       <c r="A41" s="15">
         <v>69</v>
       </c>
@@ -2387,17 +2489,18 @@
         <v>9</v>
       </c>
       <c r="D41" s="16" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E41" s="15" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F41" s="15"/>
       <c r="G41" s="15"/>
       <c r="H41" s="16"/>
-      <c r="I41" s="17"/>
-    </row>
-    <row r="42" spans="1:10">
+      <c r="I41" s="16"/>
+      <c r="J41" s="17"/>
+    </row>
+    <row r="42" spans="1:11">
       <c r="A42" s="15">
         <v>70</v>
       </c>
@@ -2408,17 +2511,18 @@
         <v>10</v>
       </c>
       <c r="D42" s="16" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E42" s="15" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F42" s="15"/>
       <c r="G42" s="15"/>
       <c r="H42" s="16"/>
-      <c r="I42" s="17"/>
-    </row>
-    <row r="43" spans="1:10">
+      <c r="I42" s="16"/>
+      <c r="J42" s="17"/>
+    </row>
+    <row r="43" spans="1:11">
       <c r="A43" s="15">
         <v>71</v>
       </c>
@@ -2426,20 +2530,21 @@
         <v>3</v>
       </c>
       <c r="C43" s="16" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D43" s="16" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E43" s="15" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F43" s="15"/>
       <c r="G43" s="15"/>
       <c r="H43" s="16"/>
-      <c r="I43" s="17"/>
-    </row>
-    <row r="44" spans="1:10">
+      <c r="I43" s="16"/>
+      <c r="J43" s="17"/>
+    </row>
+    <row r="44" spans="1:11">
       <c r="A44" s="15">
         <v>72</v>
       </c>
@@ -2447,19 +2552,20 @@
         <v>3</v>
       </c>
       <c r="C44" s="16" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D44" s="16" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E44" s="15" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F44" s="15"/>
       <c r="G44" s="15"/>
       <c r="H44" s="16"/>
-    </row>
-    <row r="45" spans="1:10">
+      <c r="I44" s="16"/>
+    </row>
+    <row r="45" spans="1:11">
       <c r="A45" s="15">
         <v>73</v>
       </c>
@@ -2467,19 +2573,20 @@
         <v>3</v>
       </c>
       <c r="C45" s="16" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D45" s="16" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E45" s="15" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F45" s="15"/>
       <c r="G45" s="15"/>
       <c r="H45" s="16"/>
-    </row>
-    <row r="46" spans="1:10">
+      <c r="I45" s="16"/>
+    </row>
+    <row r="46" spans="1:11">
       <c r="A46" s="15">
         <v>74</v>
       </c>
@@ -2487,19 +2594,20 @@
         <v>3</v>
       </c>
       <c r="C46" s="16" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D46" s="16" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E46" s="15" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F46" s="15"/>
       <c r="G46" s="15"/>
       <c r="H46" s="16"/>
-    </row>
-    <row r="47" s="2" customFormat="1" spans="1:10">
+      <c r="I46" s="16"/>
+    </row>
+    <row r="47" s="2" customFormat="1" spans="1:11">
       <c r="A47" s="19">
         <v>101</v>
       </c>
@@ -2510,24 +2618,27 @@
         <v>1</v>
       </c>
       <c r="D47" s="20" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E47" s="15" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F47" s="19">
         <v>33333333</v>
       </c>
       <c r="G47" s="19" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="H47" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="I47" s="17"/>
+        <v>71</v>
+      </c>
+      <c r="I47" s="20" t="s">
+        <v>26</v>
+      </c>
       <c r="J47" s="17"/>
-    </row>
-    <row r="48" s="2" customFormat="1" spans="1:10">
+      <c r="K47" s="17"/>
+    </row>
+    <row r="48" s="2" customFormat="1" spans="1:11">
       <c r="A48" s="19">
         <v>102</v>
       </c>
@@ -2538,24 +2649,27 @@
         <v>2</v>
       </c>
       <c r="D48" s="20" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E48" s="15" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F48" s="19">
         <v>22222222</v>
       </c>
       <c r="G48" s="19" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="H48" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="I48" s="17"/>
+        <v>71</v>
+      </c>
+      <c r="I48" s="20" t="s">
+        <v>26</v>
+      </c>
       <c r="J48" s="17"/>
-    </row>
-    <row r="49" s="2" customFormat="1" spans="1:12">
+      <c r="K48" s="17"/>
+    </row>
+    <row r="49" s="2" customFormat="1" spans="1:13">
       <c r="A49" s="19">
         <v>103</v>
       </c>
@@ -2566,24 +2680,27 @@
         <v>3</v>
       </c>
       <c r="D49" s="20" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E49" s="15" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F49" s="19">
         <v>11111111</v>
       </c>
       <c r="G49" s="19" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H49" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="I49" s="17"/>
+        <v>71</v>
+      </c>
+      <c r="I49" s="20" t="s">
+        <v>26</v>
+      </c>
       <c r="J49" s="17"/>
-    </row>
-    <row r="50" s="2" customFormat="1" spans="1:12">
+      <c r="K49" s="17"/>
+    </row>
+    <row r="50" s="2" customFormat="1" spans="1:13">
       <c r="A50" s="19">
         <v>104</v>
       </c>
@@ -2594,24 +2711,27 @@
         <v>4</v>
       </c>
       <c r="D50" s="20" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E50" s="15" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F50" s="19">
         <v>5000000</v>
       </c>
       <c r="G50" s="19" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H50" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="I50" s="17"/>
+        <v>71</v>
+      </c>
+      <c r="I50" s="20" t="s">
+        <v>26</v>
+      </c>
       <c r="J50" s="17"/>
-    </row>
-    <row r="51" s="3" customFormat="1" spans="1:12">
+      <c r="K50" s="17"/>
+    </row>
+    <row r="51" s="3" customFormat="1" spans="1:13">
       <c r="A51" s="19">
         <v>105</v>
       </c>
@@ -2622,25 +2742,28 @@
         <v>5</v>
       </c>
       <c r="D51" s="20" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E51" s="15" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F51" s="19">
         <v>3000000</v>
       </c>
       <c r="G51" s="19" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H51" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="I51" s="17"/>
-      <c r="J51" s="18"/>
-      <c r="L51" s="2"/>
-    </row>
-    <row r="52" s="3" customFormat="1" spans="1:12">
+        <v>71</v>
+      </c>
+      <c r="I51" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J51" s="17"/>
+      <c r="K51" s="18"/>
+      <c r="M51" s="2"/>
+    </row>
+    <row r="52" s="3" customFormat="1" spans="1:13">
       <c r="A52" s="19">
         <v>106</v>
       </c>
@@ -2651,21 +2774,22 @@
         <v>6</v>
       </c>
       <c r="D52" s="20" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E52" s="15" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F52" s="19"/>
       <c r="G52" s="19"/>
       <c r="H52" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="I52" s="17"/>
-      <c r="J52" s="18"/>
-      <c r="L52" s="2"/>
-    </row>
-    <row r="53" s="3" customFormat="1" spans="1:12">
+        <v>71</v>
+      </c>
+      <c r="I52" s="20"/>
+      <c r="J52" s="17"/>
+      <c r="K52" s="18"/>
+      <c r="M52" s="2"/>
+    </row>
+    <row r="53" s="3" customFormat="1" spans="1:13">
       <c r="A53" s="19">
         <v>107</v>
       </c>
@@ -2676,21 +2800,22 @@
         <v>7</v>
       </c>
       <c r="D53" s="20" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E53" s="15" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F53" s="19"/>
       <c r="G53" s="19"/>
       <c r="H53" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="I53" s="17"/>
-      <c r="J53" s="18"/>
-      <c r="L53" s="2"/>
-    </row>
-    <row r="54" s="3" customFormat="1" spans="1:12">
+        <v>71</v>
+      </c>
+      <c r="I53" s="20"/>
+      <c r="J53" s="17"/>
+      <c r="K53" s="18"/>
+      <c r="M53" s="2"/>
+    </row>
+    <row r="54" s="3" customFormat="1" spans="1:13">
       <c r="A54" s="19">
         <v>108</v>
       </c>
@@ -2701,21 +2826,22 @@
         <v>8</v>
       </c>
       <c r="D54" s="20" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E54" s="15" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F54" s="19"/>
       <c r="G54" s="19"/>
       <c r="H54" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="I54" s="17"/>
-      <c r="J54" s="18"/>
-      <c r="L54" s="2"/>
-    </row>
-    <row r="55" spans="1:12">
+        <v>71</v>
+      </c>
+      <c r="I54" s="20"/>
+      <c r="J54" s="17"/>
+      <c r="K54" s="18"/>
+      <c r="M54" s="2"/>
+    </row>
+    <row r="55" spans="1:13">
       <c r="A55" s="19">
         <v>109</v>
       </c>
@@ -2726,20 +2852,21 @@
         <v>9</v>
       </c>
       <c r="D55" s="20" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E55" s="15" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F55" s="19"/>
       <c r="G55" s="19"/>
       <c r="H55" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="I55" s="17"/>
-      <c r="L55" s="2"/>
-    </row>
-    <row r="56" spans="1:12">
+        <v>71</v>
+      </c>
+      <c r="I55" s="20"/>
+      <c r="J55" s="17"/>
+      <c r="M55" s="2"/>
+    </row>
+    <row r="56" spans="1:13">
       <c r="A56" s="19">
         <v>110</v>
       </c>
@@ -2750,20 +2877,21 @@
         <v>10</v>
       </c>
       <c r="D56" s="20" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E56" s="15" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F56" s="19"/>
       <c r="G56" s="19"/>
       <c r="H56" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="I56" s="17"/>
-      <c r="L56" s="2"/>
-    </row>
-    <row r="57" customFormat="1" spans="1:12">
+        <v>71</v>
+      </c>
+      <c r="I56" s="20"/>
+      <c r="J56" s="17"/>
+      <c r="M56" s="2"/>
+    </row>
+    <row r="57" customFormat="1" spans="1:13">
       <c r="A57" s="19">
         <v>111</v>
       </c>
@@ -2771,24 +2899,25 @@
         <v>1</v>
       </c>
       <c r="C57" s="20" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D57" s="20" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E57" s="15" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F57" s="19"/>
       <c r="G57" s="19"/>
       <c r="H57" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="I57" s="17"/>
-      <c r="J57" s="8"/>
-      <c r="L57" s="2"/>
-    </row>
-    <row r="58" s="3" customFormat="1" spans="1:12">
+        <v>71</v>
+      </c>
+      <c r="I57" s="20"/>
+      <c r="J57" s="17"/>
+      <c r="K57" s="8"/>
+      <c r="M57" s="2"/>
+    </row>
+    <row r="58" s="3" customFormat="1" spans="1:13">
       <c r="A58" s="19">
         <v>112</v>
       </c>
@@ -2796,24 +2925,25 @@
         <v>1</v>
       </c>
       <c r="C58" s="20" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D58" s="20" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E58" s="15" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F58" s="19"/>
       <c r="G58" s="19"/>
       <c r="H58" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="I58" s="17"/>
-      <c r="J58" s="18"/>
-      <c r="L58" s="2"/>
-    </row>
-    <row r="59" s="3" customFormat="1" spans="1:12">
+        <v>71</v>
+      </c>
+      <c r="I58" s="20"/>
+      <c r="J58" s="17"/>
+      <c r="K58" s="18"/>
+      <c r="M58" s="2"/>
+    </row>
+    <row r="59" s="3" customFormat="1" spans="1:13">
       <c r="A59" s="19">
         <v>113</v>
       </c>
@@ -2821,24 +2951,25 @@
         <v>1</v>
       </c>
       <c r="C59" s="20" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D59" s="20" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E59" s="15" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F59" s="19"/>
       <c r="G59" s="19"/>
       <c r="H59" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="I59" s="17"/>
-      <c r="J59" s="18"/>
-      <c r="L59" s="2"/>
-    </row>
-    <row r="60" s="3" customFormat="1" spans="1:12">
+        <v>71</v>
+      </c>
+      <c r="I59" s="20"/>
+      <c r="J59" s="17"/>
+      <c r="K59" s="18"/>
+      <c r="M59" s="2"/>
+    </row>
+    <row r="60" s="3" customFormat="1" spans="1:13">
       <c r="A60" s="19">
         <v>114</v>
       </c>
@@ -2846,24 +2977,25 @@
         <v>1</v>
       </c>
       <c r="C60" s="20" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D60" s="20" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E60" s="15" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F60" s="19"/>
       <c r="G60" s="19"/>
       <c r="H60" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="I60" s="17"/>
-      <c r="J60" s="18"/>
-      <c r="L60" s="2"/>
-    </row>
-    <row r="61" s="3" customFormat="1" spans="1:12">
+        <v>71</v>
+      </c>
+      <c r="I60" s="20"/>
+      <c r="J60" s="17"/>
+      <c r="K60" s="18"/>
+      <c r="M60" s="2"/>
+    </row>
+    <row r="61" s="3" customFormat="1" spans="1:13">
       <c r="A61" s="19">
         <v>131</v>
       </c>
@@ -2874,25 +3006,28 @@
         <v>1</v>
       </c>
       <c r="D61" s="20" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E61" s="15" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F61" s="19">
         <v>33333333</v>
       </c>
       <c r="G61" s="19" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="H61" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="I61" s="17"/>
-      <c r="J61" s="18"/>
-      <c r="L61" s="2"/>
-    </row>
-    <row r="62" s="3" customFormat="1" spans="1:12">
+        <v>71</v>
+      </c>
+      <c r="I61" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J61" s="17"/>
+      <c r="K61" s="18"/>
+      <c r="M61" s="2"/>
+    </row>
+    <row r="62" s="3" customFormat="1" spans="1:13">
       <c r="A62" s="19">
         <v>132</v>
       </c>
@@ -2903,25 +3038,28 @@
         <v>2</v>
       </c>
       <c r="D62" s="20" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E62" s="15" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F62" s="19">
         <v>22222222</v>
       </c>
       <c r="G62" s="19" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="H62" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="I62" s="17"/>
+        <v>71</v>
+      </c>
+      <c r="I62" s="20" t="s">
+        <v>26</v>
+      </c>
       <c r="J62" s="17"/>
-      <c r="L62" s="2"/>
-    </row>
-    <row r="63" spans="1:12">
+      <c r="K62" s="17"/>
+      <c r="M62" s="2"/>
+    </row>
+    <row r="63" spans="1:13">
       <c r="A63" s="19">
         <v>133</v>
       </c>
@@ -2932,22 +3070,25 @@
         <v>3</v>
       </c>
       <c r="D63" s="20" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E63" s="15" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F63" s="19">
         <v>11111111</v>
       </c>
       <c r="G63" s="19" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H63" s="20" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="64" s="3" customFormat="1" spans="1:12">
+        <v>71</v>
+      </c>
+      <c r="I63" s="20" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="64" s="3" customFormat="1" spans="1:13">
       <c r="A64" s="19">
         <v>134</v>
       </c>
@@ -2958,24 +3099,27 @@
         <v>4</v>
       </c>
       <c r="D64" s="20" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E64" s="15" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F64" s="19">
         <v>5000000</v>
       </c>
       <c r="G64" s="19" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H64" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="I64" s="17"/>
-      <c r="J64" s="18"/>
-    </row>
-    <row r="65" s="3" customFormat="1" spans="1:10">
+        <v>71</v>
+      </c>
+      <c r="I64" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J64" s="17"/>
+      <c r="K64" s="18"/>
+    </row>
+    <row r="65" s="3" customFormat="1" spans="1:11">
       <c r="A65" s="19">
         <v>135</v>
       </c>
@@ -2986,24 +3130,27 @@
         <v>5</v>
       </c>
       <c r="D65" s="20" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E65" s="15" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F65" s="19">
         <v>3000000</v>
       </c>
       <c r="G65" s="19" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H65" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="I65" s="17"/>
-      <c r="J65" s="18"/>
-    </row>
-    <row r="66" s="3" customFormat="1" spans="1:10">
+        <v>71</v>
+      </c>
+      <c r="I65" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J65" s="17"/>
+      <c r="K65" s="18"/>
+    </row>
+    <row r="66" s="3" customFormat="1" spans="1:11">
       <c r="A66" s="19">
         <v>136</v>
       </c>
@@ -3014,20 +3161,21 @@
         <v>6</v>
       </c>
       <c r="D66" s="20" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E66" s="15" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F66" s="19"/>
       <c r="G66" s="19"/>
       <c r="H66" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="I66" s="17"/>
-      <c r="J66" s="18"/>
-    </row>
-    <row r="67" s="3" customFormat="1" spans="1:10">
+        <v>71</v>
+      </c>
+      <c r="I66" s="20"/>
+      <c r="J66" s="17"/>
+      <c r="K66" s="18"/>
+    </row>
+    <row r="67" s="3" customFormat="1" spans="1:11">
       <c r="A67" s="19">
         <v>137</v>
       </c>
@@ -3038,20 +3186,21 @@
         <v>7</v>
       </c>
       <c r="D67" s="20" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E67" s="15" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F67" s="19"/>
       <c r="G67" s="19"/>
       <c r="H67" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="I67" s="17"/>
-      <c r="J67" s="18"/>
-    </row>
-    <row r="68" s="3" customFormat="1" spans="1:10">
+        <v>71</v>
+      </c>
+      <c r="I67" s="20"/>
+      <c r="J67" s="17"/>
+      <c r="K67" s="18"/>
+    </row>
+    <row r="68" s="3" customFormat="1" spans="1:11">
       <c r="A68" s="19">
         <v>138</v>
       </c>
@@ -3062,20 +3211,21 @@
         <v>8</v>
       </c>
       <c r="D68" s="20" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E68" s="15" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F68" s="19"/>
       <c r="G68" s="19"/>
       <c r="H68" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="I68" s="17"/>
+        <v>71</v>
+      </c>
+      <c r="I68" s="20"/>
       <c r="J68" s="17"/>
-    </row>
-    <row r="69" spans="1:10">
+      <c r="K68" s="17"/>
+    </row>
+    <row r="69" spans="1:11">
       <c r="A69" s="19">
         <v>139</v>
       </c>
@@ -3086,19 +3236,20 @@
         <v>9</v>
       </c>
       <c r="D69" s="20" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E69" s="15" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F69" s="19"/>
       <c r="G69" s="19"/>
       <c r="H69" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="I69" s="17"/>
-    </row>
-    <row r="70" spans="1:10">
+        <v>71</v>
+      </c>
+      <c r="I69" s="20"/>
+      <c r="J69" s="17"/>
+    </row>
+    <row r="70" spans="1:11">
       <c r="A70" s="19">
         <v>140</v>
       </c>
@@ -3109,19 +3260,20 @@
         <v>10</v>
       </c>
       <c r="D70" s="20" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E70" s="15" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F70" s="19"/>
       <c r="G70" s="19"/>
       <c r="H70" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="I70" s="17"/>
-    </row>
-    <row r="71" spans="1:10">
+        <v>71</v>
+      </c>
+      <c r="I70" s="20"/>
+      <c r="J70" s="17"/>
+    </row>
+    <row r="71" spans="1:11">
       <c r="A71" s="19">
         <v>141</v>
       </c>
@@ -3129,22 +3281,23 @@
         <v>2</v>
       </c>
       <c r="C71" s="20" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D71" s="20" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E71" s="15" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F71" s="19"/>
       <c r="G71" s="19"/>
       <c r="H71" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="I71" s="17"/>
-    </row>
-    <row r="72" spans="1:10">
+        <v>71</v>
+      </c>
+      <c r="I71" s="20"/>
+      <c r="J71" s="17"/>
+    </row>
+    <row r="72" spans="1:11">
       <c r="A72" s="19">
         <v>142</v>
       </c>
@@ -3152,22 +3305,23 @@
         <v>2</v>
       </c>
       <c r="C72" s="20" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D72" s="20" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E72" s="15" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F72" s="19"/>
       <c r="G72" s="19"/>
       <c r="H72" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="I72" s="17"/>
-    </row>
-    <row r="73" spans="1:10">
+        <v>71</v>
+      </c>
+      <c r="I72" s="20"/>
+      <c r="J72" s="17"/>
+    </row>
+    <row r="73" spans="1:11">
       <c r="A73" s="19">
         <v>143</v>
       </c>
@@ -3175,22 +3329,23 @@
         <v>2</v>
       </c>
       <c r="C73" s="20" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D73" s="20" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E73" s="15" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F73" s="19"/>
       <c r="G73" s="19"/>
       <c r="H73" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="I73" s="17"/>
-    </row>
-    <row r="74" spans="1:10">
+        <v>71</v>
+      </c>
+      <c r="I73" s="20"/>
+      <c r="J73" s="17"/>
+    </row>
+    <row r="74" spans="1:11">
       <c r="A74" s="19">
         <v>144</v>
       </c>
@@ -3198,22 +3353,23 @@
         <v>2</v>
       </c>
       <c r="C74" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="D74" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="E74" s="15" t="s">
         <v>41</v>
-      </c>
-      <c r="D74" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="E74" s="15" t="s">
-        <v>38</v>
       </c>
       <c r="F74" s="19"/>
       <c r="G74" s="19"/>
       <c r="H74" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="I74" s="17"/>
-    </row>
-    <row r="75" spans="1:10">
+        <v>71</v>
+      </c>
+      <c r="I74" s="20"/>
+      <c r="J74" s="17"/>
+    </row>
+    <row r="75" spans="1:11">
       <c r="A75" s="19">
         <v>161</v>
       </c>
@@ -3224,23 +3380,26 @@
         <v>1</v>
       </c>
       <c r="D75" s="20" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E75" s="15" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F75" s="19">
         <v>99999999</v>
       </c>
       <c r="G75" s="19" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="H75" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="I75" s="17"/>
-    </row>
-    <row r="76" spans="1:10">
+        <v>71</v>
+      </c>
+      <c r="I75" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J75" s="17"/>
+    </row>
+    <row r="76" spans="1:11">
       <c r="A76" s="19">
         <v>162</v>
       </c>
@@ -3251,23 +3410,26 @@
         <v>2</v>
       </c>
       <c r="D76" s="20" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E76" s="15" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F76" s="19">
         <v>88888888</v>
       </c>
       <c r="G76" s="19" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="H76" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="I76" s="17"/>
-    </row>
-    <row r="77" spans="1:10">
+        <v>71</v>
+      </c>
+      <c r="I76" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J76" s="17"/>
+    </row>
+    <row r="77" spans="1:11">
       <c r="A77" s="19">
         <v>163</v>
       </c>
@@ -3278,23 +3440,26 @@
         <v>3</v>
       </c>
       <c r="D77" s="20" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E77" s="15" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F77" s="19">
         <v>77777777</v>
       </c>
       <c r="G77" s="19" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H77" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="I77" s="17"/>
-    </row>
-    <row r="78" spans="1:10">
+        <v>71</v>
+      </c>
+      <c r="I77" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J77" s="17"/>
+    </row>
+    <row r="78" spans="1:11">
       <c r="A78" s="19">
         <v>164</v>
       </c>
@@ -3305,23 +3470,26 @@
         <v>4</v>
       </c>
       <c r="D78" s="20" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E78" s="15" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F78" s="19">
         <v>66666666</v>
       </c>
       <c r="G78" s="19" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H78" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="I78" s="17"/>
-    </row>
-    <row r="79" spans="1:10">
+        <v>71</v>
+      </c>
+      <c r="I78" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J78" s="17"/>
+    </row>
+    <row r="79" spans="1:11">
       <c r="A79" s="19">
         <v>165</v>
       </c>
@@ -3332,23 +3500,26 @@
         <v>5</v>
       </c>
       <c r="D79" s="20" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E79" s="15" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F79" s="19">
         <v>55555555</v>
       </c>
       <c r="G79" s="19" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H79" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="I79" s="17"/>
-    </row>
-    <row r="80" spans="1:10">
+        <v>71</v>
+      </c>
+      <c r="I79" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J79" s="17"/>
+    </row>
+    <row r="80" spans="1:11">
       <c r="A80" s="19">
         <v>166</v>
       </c>
@@ -3359,19 +3530,20 @@
         <v>6</v>
       </c>
       <c r="D80" s="20" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E80" s="15" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F80" s="19"/>
       <c r="G80" s="19"/>
       <c r="H80" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="I80" s="17"/>
-    </row>
-    <row r="81" spans="1:9">
+        <v>71</v>
+      </c>
+      <c r="I80" s="20"/>
+      <c r="J80" s="17"/>
+    </row>
+    <row r="81" spans="1:10">
       <c r="A81" s="19">
         <v>167</v>
       </c>
@@ -3382,19 +3554,20 @@
         <v>7</v>
       </c>
       <c r="D81" s="20" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E81" s="15" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F81" s="19"/>
       <c r="G81" s="19"/>
       <c r="H81" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="I81" s="17"/>
-    </row>
-    <row r="82" spans="1:9">
+        <v>71</v>
+      </c>
+      <c r="I81" s="20"/>
+      <c r="J81" s="17"/>
+    </row>
+    <row r="82" spans="1:10">
       <c r="A82" s="19">
         <v>168</v>
       </c>
@@ -3405,19 +3578,20 @@
         <v>8</v>
       </c>
       <c r="D82" s="20" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E82" s="15" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F82" s="19"/>
       <c r="G82" s="19"/>
       <c r="H82" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="I82" s="17"/>
-    </row>
-    <row r="83" spans="1:9">
+        <v>71</v>
+      </c>
+      <c r="I82" s="20"/>
+      <c r="J82" s="17"/>
+    </row>
+    <row r="83" spans="1:10">
       <c r="A83" s="19">
         <v>169</v>
       </c>
@@ -3428,19 +3602,20 @@
         <v>9</v>
       </c>
       <c r="D83" s="20" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E83" s="15" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F83" s="19"/>
       <c r="G83" s="19"/>
       <c r="H83" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="I83" s="17"/>
-    </row>
-    <row r="84" spans="1:9">
+        <v>71</v>
+      </c>
+      <c r="I83" s="20"/>
+      <c r="J83" s="17"/>
+    </row>
+    <row r="84" spans="1:10">
       <c r="A84" s="19">
         <v>170</v>
       </c>
@@ -3451,19 +3626,20 @@
         <v>10</v>
       </c>
       <c r="D84" s="20" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E84" s="15" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F84" s="19"/>
       <c r="G84" s="19"/>
       <c r="H84" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="I84" s="17"/>
-    </row>
-    <row r="85" spans="1:9">
+        <v>71</v>
+      </c>
+      <c r="I84" s="20"/>
+      <c r="J84" s="17"/>
+    </row>
+    <row r="85" spans="1:10">
       <c r="A85" s="19">
         <v>171</v>
       </c>
@@ -3471,22 +3647,23 @@
         <v>3</v>
       </c>
       <c r="C85" s="20" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D85" s="20" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E85" s="15" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F85" s="19"/>
       <c r="G85" s="19"/>
       <c r="H85" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="I85" s="17"/>
-    </row>
-    <row r="86" spans="1:9">
+        <v>71</v>
+      </c>
+      <c r="I85" s="20"/>
+      <c r="J85" s="17"/>
+    </row>
+    <row r="86" spans="1:10">
       <c r="A86" s="19">
         <v>172</v>
       </c>
@@ -3494,21 +3671,22 @@
         <v>3</v>
       </c>
       <c r="C86" s="20" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D86" s="20" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E86" s="15" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F86" s="19"/>
       <c r="G86" s="19"/>
       <c r="H86" s="20" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9">
+        <v>71</v>
+      </c>
+      <c r="I86" s="20"/>
+    </row>
+    <row r="87" spans="1:10">
       <c r="A87" s="19">
         <v>173</v>
       </c>
@@ -3516,21 +3694,22 @@
         <v>3</v>
       </c>
       <c r="C87" s="20" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D87" s="20" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E87" s="15" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F87" s="19"/>
       <c r="G87" s="19"/>
       <c r="H87" s="20" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="88" spans="1:9">
+        <v>71</v>
+      </c>
+      <c r="I87" s="20"/>
+    </row>
+    <row r="88" spans="1:10">
       <c r="A88" s="19">
         <v>174</v>
       </c>
@@ -3538,19 +3717,20 @@
         <v>3</v>
       </c>
       <c r="C88" s="20" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D88" s="20" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E88" s="15" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F88" s="19"/>
       <c r="G88" s="19"/>
       <c r="H88" s="20" t="s">
-        <v>68</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="I88" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/table/resources/sample/PointsAwardRanking.xlsx
+++ b/table/resources/sample/PointsAwardRanking.xlsx
@@ -629,7 +629,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -645,6 +645,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -973,7 +979,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -997,16 +1003,16 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1015,89 +1021,89 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1138,6 +1144,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1146,7 +1155,10 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
@@ -1155,10 +1167,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1541,7 +1553,7 @@
       <c r="H1" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="14" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1552,13 +1564,13 @@
       <c r="B2" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="15" t="s">
         <v>10</v>
       </c>
       <c r="D2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="E2" s="15" t="s">
         <v>11</v>
       </c>
       <c r="F2" s="12" t="s">
@@ -1570,7 +1582,7 @@
       <c r="H2" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="12" t="s">
+      <c r="I2" s="16" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1587,7 +1599,7 @@
       <c r="D3" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="15" t="s">
         <v>18</v>
       </c>
       <c r="F3" s="12" t="s">
@@ -1599,7 +1611,7 @@
       <c r="H3" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I3" s="13" t="s">
+      <c r="I3" s="14" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1612,2125 +1624,2125 @@
       <c r="F4" s="12"/>
       <c r="G4" s="12"/>
       <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
+      <c r="I4" s="14"/>
     </row>
     <row r="5" s="2" customFormat="1" spans="1:13">
-      <c r="A5" s="15">
+      <c r="A5" s="17">
         <v>1</v>
       </c>
-      <c r="B5" s="15">
+      <c r="B5" s="17">
         <v>1</v>
       </c>
-      <c r="C5" s="16">
+      <c r="C5" s="18">
         <v>1</v>
       </c>
-      <c r="D5" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="15" t="s">
+      <c r="D5" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15" t="s">
+      <c r="F5" s="17"/>
+      <c r="G5" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="H5" s="16"/>
-      <c r="I5" s="16" t="s">
+      <c r="H5" s="18"/>
+      <c r="I5" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="J5" s="17"/>
-      <c r="K5" s="17"/>
+      <c r="J5" s="19"/>
+      <c r="K5" s="19"/>
     </row>
     <row r="6" s="2" customFormat="1" spans="1:13">
-      <c r="A6" s="15">
+      <c r="A6" s="17">
         <v>2</v>
       </c>
-      <c r="B6" s="15">
+      <c r="B6" s="17">
         <v>1</v>
       </c>
-      <c r="C6" s="16">
+      <c r="C6" s="18">
         <v>2</v>
       </c>
-      <c r="D6" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" s="15" t="s">
+      <c r="D6" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15" t="s">
+      <c r="F6" s="17"/>
+      <c r="G6" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="H6" s="16"/>
-      <c r="I6" s="16" t="s">
+      <c r="H6" s="18"/>
+      <c r="I6" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="J6" s="17"/>
-      <c r="K6" s="17"/>
+      <c r="J6" s="19"/>
+      <c r="K6" s="19"/>
     </row>
     <row r="7" s="2" customFormat="1" spans="1:13">
-      <c r="A7" s="15">
+      <c r="A7" s="17">
         <v>3</v>
       </c>
-      <c r="B7" s="15">
+      <c r="B7" s="17">
         <v>1</v>
       </c>
-      <c r="C7" s="16">
+      <c r="C7" s="18">
         <v>3</v>
       </c>
-      <c r="D7" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" s="15" t="s">
+      <c r="D7" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15" t="s">
+      <c r="F7" s="17"/>
+      <c r="G7" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="H7" s="16"/>
-      <c r="I7" s="16" t="s">
+      <c r="H7" s="18"/>
+      <c r="I7" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="J7" s="17"/>
-      <c r="K7" s="17"/>
+      <c r="J7" s="19"/>
+      <c r="K7" s="19"/>
     </row>
     <row r="8" s="2" customFormat="1" spans="1:13">
-      <c r="A8" s="15">
+      <c r="A8" s="17">
         <v>4</v>
       </c>
-      <c r="B8" s="15">
+      <c r="B8" s="17">
         <v>1</v>
       </c>
-      <c r="C8" s="16">
+      <c r="C8" s="18">
         <v>4</v>
       </c>
-      <c r="D8" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8" s="15" t="s">
+      <c r="D8" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="16"/>
-      <c r="I8" s="16" t="s">
+      <c r="F8" s="17"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="J8" s="17"/>
-      <c r="K8" s="17"/>
+      <c r="J8" s="19"/>
+      <c r="K8" s="19"/>
     </row>
     <row r="9" s="3" customFormat="1" spans="1:13">
-      <c r="A9" s="15">
+      <c r="A9" s="17">
         <v>5</v>
       </c>
-      <c r="B9" s="15">
+      <c r="B9" s="17">
         <v>1</v>
       </c>
-      <c r="C9" s="16">
+      <c r="C9" s="18">
         <v>5</v>
       </c>
-      <c r="D9" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E9" s="15" t="s">
+      <c r="D9" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="16"/>
-      <c r="I9" s="16"/>
-      <c r="J9" s="17"/>
-      <c r="K9" s="18"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="18"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="20"/>
       <c r="M9" s="2"/>
     </row>
     <row r="10" s="3" customFormat="1" spans="1:13">
-      <c r="A10" s="15">
+      <c r="A10" s="17">
         <v>6</v>
       </c>
-      <c r="B10" s="15">
+      <c r="B10" s="17">
         <v>1</v>
       </c>
-      <c r="C10" s="16">
+      <c r="C10" s="18">
         <v>6</v>
       </c>
-      <c r="D10" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E10" s="15" t="s">
+      <c r="D10" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="16"/>
-      <c r="I10" s="16"/>
-      <c r="J10" s="17"/>
-      <c r="K10" s="18"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="18"/>
+      <c r="I10" s="18"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="20"/>
       <c r="M10" s="2"/>
     </row>
     <row r="11" s="3" customFormat="1" spans="1:13">
-      <c r="A11" s="15">
+      <c r="A11" s="17">
         <v>7</v>
       </c>
-      <c r="B11" s="15">
+      <c r="B11" s="17">
         <v>1</v>
       </c>
-      <c r="C11" s="16">
+      <c r="C11" s="18">
         <v>7</v>
       </c>
-      <c r="D11" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E11" s="15" t="s">
+      <c r="D11" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="16"/>
-      <c r="I11" s="16"/>
-      <c r="J11" s="17"/>
-      <c r="K11" s="18"/>
+      <c r="F11" s="17"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="18"/>
+      <c r="I11" s="18"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="20"/>
       <c r="M11" s="2"/>
     </row>
     <row r="12" s="3" customFormat="1" spans="1:13">
-      <c r="A12" s="15">
+      <c r="A12" s="17">
         <v>8</v>
       </c>
-      <c r="B12" s="15">
+      <c r="B12" s="17">
         <v>1</v>
       </c>
-      <c r="C12" s="16">
+      <c r="C12" s="18">
         <v>8</v>
       </c>
-      <c r="D12" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E12" s="15" t="s">
+      <c r="D12" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="F12" s="15"/>
-      <c r="G12" s="15"/>
-      <c r="H12" s="16"/>
-      <c r="I12" s="16"/>
-      <c r="J12" s="17"/>
-      <c r="K12" s="18"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="18"/>
+      <c r="I12" s="18"/>
+      <c r="J12" s="19"/>
+      <c r="K12" s="20"/>
       <c r="M12" s="2"/>
     </row>
     <row r="13" spans="1:13">
-      <c r="A13" s="15">
+      <c r="A13" s="17">
         <v>9</v>
       </c>
-      <c r="B13" s="15">
+      <c r="B13" s="17">
         <v>1</v>
       </c>
-      <c r="C13" s="16">
+      <c r="C13" s="18">
         <v>9</v>
       </c>
-      <c r="D13" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E13" s="15" t="s">
+      <c r="D13" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="16"/>
-      <c r="I13" s="16"/>
-      <c r="J13" s="17"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="18"/>
+      <c r="I13" s="18"/>
+      <c r="J13" s="19"/>
       <c r="M13" s="2"/>
     </row>
     <row r="14" spans="1:13">
-      <c r="A14" s="15">
+      <c r="A14" s="17">
         <v>10</v>
       </c>
-      <c r="B14" s="15">
+      <c r="B14" s="17">
         <v>1</v>
       </c>
-      <c r="C14" s="16">
+      <c r="C14" s="18">
         <v>10</v>
       </c>
-      <c r="D14" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E14" s="15" t="s">
+      <c r="D14" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E14" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="F14" s="15"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="16"/>
-      <c r="I14" s="16"/>
-      <c r="J14" s="17"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="18"/>
+      <c r="I14" s="18"/>
+      <c r="J14" s="19"/>
       <c r="M14" s="2"/>
     </row>
     <row r="15" customFormat="1" spans="1:13">
-      <c r="A15" s="15">
+      <c r="A15" s="17">
         <v>11</v>
       </c>
-      <c r="B15" s="15">
+      <c r="B15" s="17">
         <v>1</v>
       </c>
-      <c r="C15" s="16" t="s">
+      <c r="C15" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="D15" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E15" s="15" t="s">
+      <c r="D15" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="F15" s="15"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="16"/>
-      <c r="I15" s="16"/>
-      <c r="J15" s="17"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="18"/>
+      <c r="I15" s="18"/>
+      <c r="J15" s="19"/>
       <c r="K15" s="8"/>
       <c r="M15" s="2"/>
     </row>
     <row r="16" s="3" customFormat="1" spans="1:13">
-      <c r="A16" s="15">
+      <c r="A16" s="17">
         <v>12</v>
       </c>
-      <c r="B16" s="15">
+      <c r="B16" s="17">
         <v>1</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="C16" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="D16" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E16" s="15" t="s">
+      <c r="D16" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E16" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="F16" s="15"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="16"/>
-      <c r="I16" s="16"/>
-      <c r="J16" s="17"/>
-      <c r="K16" s="18"/>
+      <c r="F16" s="17"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="18"/>
+      <c r="I16" s="18"/>
+      <c r="J16" s="19"/>
+      <c r="K16" s="20"/>
       <c r="M16" s="2"/>
     </row>
     <row r="17" s="3" customFormat="1" spans="1:13">
-      <c r="A17" s="15">
+      <c r="A17" s="17">
         <v>13</v>
       </c>
-      <c r="B17" s="15">
+      <c r="B17" s="17">
         <v>1</v>
       </c>
-      <c r="C17" s="16" t="s">
+      <c r="C17" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="D17" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E17" s="15" t="s">
+      <c r="D17" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="F17" s="15"/>
-      <c r="G17" s="15"/>
-      <c r="H17" s="16"/>
-      <c r="I17" s="16"/>
-      <c r="J17" s="17"/>
-      <c r="K17" s="18"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="18"/>
+      <c r="I17" s="18"/>
+      <c r="J17" s="19"/>
+      <c r="K17" s="20"/>
       <c r="M17" s="2"/>
     </row>
     <row r="18" s="3" customFormat="1" spans="1:13">
-      <c r="A18" s="15">
+      <c r="A18" s="17">
         <v>14</v>
       </c>
-      <c r="B18" s="15">
+      <c r="B18" s="17">
         <v>1</v>
       </c>
-      <c r="C18" s="16" t="s">
+      <c r="C18" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="D18" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E18" s="15" t="s">
+      <c r="D18" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="F18" s="15"/>
-      <c r="G18" s="15"/>
-      <c r="H18" s="16"/>
-      <c r="I18" s="16"/>
-      <c r="J18" s="17"/>
-      <c r="K18" s="18"/>
+      <c r="F18" s="17"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="18"/>
+      <c r="I18" s="18"/>
+      <c r="J18" s="19"/>
+      <c r="K18" s="20"/>
       <c r="M18" s="2"/>
     </row>
     <row r="19" s="3" customFormat="1" spans="1:13">
-      <c r="A19" s="15">
+      <c r="A19" s="17">
         <v>31</v>
       </c>
-      <c r="B19" s="15">
+      <c r="B19" s="17">
         <v>2</v>
       </c>
-      <c r="C19" s="16">
+      <c r="C19" s="18">
         <v>1</v>
       </c>
-      <c r="D19" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E19" s="15" t="s">
+      <c r="D19" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="F19" s="15"/>
-      <c r="G19" s="15" t="s">
+      <c r="F19" s="17"/>
+      <c r="G19" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="H19" s="16"/>
-      <c r="I19" s="16" t="s">
+      <c r="H19" s="18"/>
+      <c r="I19" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="J19" s="17"/>
-      <c r="K19" s="18"/>
+      <c r="J19" s="19"/>
+      <c r="K19" s="20"/>
       <c r="M19" s="2"/>
     </row>
     <row r="20" s="3" customFormat="1" spans="1:13">
-      <c r="A20" s="15">
+      <c r="A20" s="17">
         <v>32</v>
       </c>
-      <c r="B20" s="15">
+      <c r="B20" s="17">
         <v>2</v>
       </c>
-      <c r="C20" s="16">
+      <c r="C20" s="18">
         <v>2</v>
       </c>
-      <c r="D20" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E20" s="15" t="s">
+      <c r="D20" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E20" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="F20" s="15"/>
-      <c r="G20" s="15" t="s">
+      <c r="F20" s="17"/>
+      <c r="G20" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="H20" s="16"/>
-      <c r="I20" s="16" t="s">
+      <c r="H20" s="18"/>
+      <c r="I20" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="J20" s="17"/>
-      <c r="K20" s="17"/>
+      <c r="J20" s="19"/>
+      <c r="K20" s="19"/>
       <c r="M20" s="2"/>
     </row>
     <row r="21" spans="1:13">
-      <c r="A21" s="15">
+      <c r="A21" s="17">
         <v>33</v>
       </c>
-      <c r="B21" s="15">
+      <c r="B21" s="17">
         <v>2</v>
       </c>
-      <c r="C21" s="16">
+      <c r="C21" s="18">
         <v>3</v>
       </c>
-      <c r="D21" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E21" s="15" t="s">
+      <c r="D21" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E21" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="F21" s="15"/>
-      <c r="G21" s="15" t="s">
+      <c r="F21" s="17"/>
+      <c r="G21" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="H21" s="16"/>
-      <c r="I21" s="16" t="s">
+      <c r="H21" s="18"/>
+      <c r="I21" s="18" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="22" s="3" customFormat="1" spans="1:13">
-      <c r="A22" s="15">
+      <c r="A22" s="17">
         <v>34</v>
       </c>
-      <c r="B22" s="15">
+      <c r="B22" s="17">
         <v>2</v>
       </c>
-      <c r="C22" s="16">
+      <c r="C22" s="18">
         <v>4</v>
       </c>
-      <c r="D22" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E22" s="15" t="s">
+      <c r="D22" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E22" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15"/>
-      <c r="H22" s="16"/>
-      <c r="I22" s="16" t="s">
+      <c r="F22" s="17"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="18"/>
+      <c r="I22" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="J22" s="17"/>
-      <c r="K22" s="18"/>
+      <c r="J22" s="19"/>
+      <c r="K22" s="20"/>
     </row>
     <row r="23" s="3" customFormat="1" spans="1:13">
-      <c r="A23" s="15">
+      <c r="A23" s="17">
         <v>35</v>
       </c>
-      <c r="B23" s="15">
+      <c r="B23" s="17">
         <v>2</v>
       </c>
-      <c r="C23" s="16">
+      <c r="C23" s="18">
         <v>5</v>
       </c>
-      <c r="D23" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E23" s="15" t="s">
+      <c r="D23" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E23" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="F23" s="15"/>
-      <c r="G23" s="15"/>
-      <c r="H23" s="16"/>
-      <c r="I23" s="16"/>
-      <c r="J23" s="17"/>
-      <c r="K23" s="18"/>
+      <c r="F23" s="17"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="18"/>
+      <c r="I23" s="18"/>
+      <c r="J23" s="19"/>
+      <c r="K23" s="20"/>
     </row>
     <row r="24" s="3" customFormat="1" spans="1:13">
-      <c r="A24" s="15">
+      <c r="A24" s="17">
         <v>36</v>
       </c>
-      <c r="B24" s="15">
+      <c r="B24" s="17">
         <v>2</v>
       </c>
-      <c r="C24" s="16">
+      <c r="C24" s="18">
         <v>6</v>
       </c>
-      <c r="D24" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E24" s="15" t="s">
+      <c r="D24" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E24" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="F24" s="15"/>
-      <c r="G24" s="15"/>
-      <c r="H24" s="16"/>
-      <c r="I24" s="16"/>
-      <c r="J24" s="17"/>
-      <c r="K24" s="18"/>
+      <c r="F24" s="17"/>
+      <c r="G24" s="17"/>
+      <c r="H24" s="18"/>
+      <c r="I24" s="18"/>
+      <c r="J24" s="19"/>
+      <c r="K24" s="20"/>
     </row>
     <row r="25" s="3" customFormat="1" spans="1:13">
-      <c r="A25" s="15">
+      <c r="A25" s="17">
         <v>37</v>
       </c>
-      <c r="B25" s="15">
+      <c r="B25" s="17">
         <v>2</v>
       </c>
-      <c r="C25" s="16">
+      <c r="C25" s="18">
         <v>7</v>
       </c>
-      <c r="D25" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E25" s="15" t="s">
+      <c r="D25" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E25" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="F25" s="15"/>
-      <c r="G25" s="15"/>
-      <c r="H25" s="16"/>
-      <c r="I25" s="16"/>
-      <c r="J25" s="17"/>
-      <c r="K25" s="18"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="18"/>
+      <c r="I25" s="18"/>
+      <c r="J25" s="19"/>
+      <c r="K25" s="20"/>
     </row>
     <row r="26" s="3" customFormat="1" spans="1:13">
-      <c r="A26" s="15">
+      <c r="A26" s="17">
         <v>38</v>
       </c>
-      <c r="B26" s="15">
+      <c r="B26" s="17">
         <v>2</v>
       </c>
-      <c r="C26" s="16">
+      <c r="C26" s="18">
         <v>8</v>
       </c>
-      <c r="D26" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E26" s="15" t="s">
+      <c r="D26" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E26" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="F26" s="15"/>
-      <c r="G26" s="15"/>
-      <c r="H26" s="16"/>
-      <c r="I26" s="16"/>
-      <c r="J26" s="17"/>
-      <c r="K26" s="17"/>
+      <c r="F26" s="17"/>
+      <c r="G26" s="17"/>
+      <c r="H26" s="18"/>
+      <c r="I26" s="18"/>
+      <c r="J26" s="19"/>
+      <c r="K26" s="19"/>
     </row>
     <row r="27" spans="1:13">
-      <c r="A27" s="15">
+      <c r="A27" s="17">
         <v>39</v>
       </c>
-      <c r="B27" s="15">
+      <c r="B27" s="17">
         <v>2</v>
       </c>
-      <c r="C27" s="16">
+      <c r="C27" s="18">
         <v>9</v>
       </c>
-      <c r="D27" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E27" s="15" t="s">
+      <c r="D27" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E27" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="F27" s="15"/>
-      <c r="G27" s="15"/>
-      <c r="H27" s="16"/>
-      <c r="I27" s="16"/>
-      <c r="J27" s="17"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="18"/>
+      <c r="I27" s="18"/>
+      <c r="J27" s="19"/>
     </row>
     <row r="28" spans="1:13">
-      <c r="A28" s="15">
+      <c r="A28" s="17">
         <v>40</v>
       </c>
-      <c r="B28" s="15">
+      <c r="B28" s="17">
         <v>2</v>
       </c>
-      <c r="C28" s="16">
+      <c r="C28" s="18">
         <v>10</v>
       </c>
-      <c r="D28" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E28" s="15" t="s">
+      <c r="D28" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E28" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="F28" s="15"/>
-      <c r="G28" s="15"/>
-      <c r="H28" s="16"/>
-      <c r="I28" s="16"/>
-      <c r="J28" s="17"/>
+      <c r="F28" s="17"/>
+      <c r="G28" s="17"/>
+      <c r="H28" s="18"/>
+      <c r="I28" s="18"/>
+      <c r="J28" s="19"/>
     </row>
     <row r="29" spans="1:13">
-      <c r="A29" s="15">
+      <c r="A29" s="17">
         <v>41</v>
       </c>
-      <c r="B29" s="15">
+      <c r="B29" s="17">
         <v>2</v>
       </c>
-      <c r="C29" s="16" t="s">
+      <c r="C29" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="D29" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E29" s="15" t="s">
+      <c r="D29" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E29" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="F29" s="15"/>
-      <c r="G29" s="15"/>
-      <c r="H29" s="16"/>
-      <c r="I29" s="16"/>
-      <c r="J29" s="17"/>
+      <c r="F29" s="17"/>
+      <c r="G29" s="17"/>
+      <c r="H29" s="18"/>
+      <c r="I29" s="18"/>
+      <c r="J29" s="19"/>
     </row>
     <row r="30" spans="1:13">
-      <c r="A30" s="15">
+      <c r="A30" s="17">
         <v>42</v>
       </c>
-      <c r="B30" s="15">
+      <c r="B30" s="17">
         <v>2</v>
       </c>
-      <c r="C30" s="16" t="s">
+      <c r="C30" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="D30" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E30" s="15" t="s">
+      <c r="D30" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E30" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="F30" s="15"/>
-      <c r="G30" s="15"/>
-      <c r="H30" s="16"/>
-      <c r="I30" s="16"/>
-      <c r="J30" s="17"/>
+      <c r="F30" s="17"/>
+      <c r="G30" s="17"/>
+      <c r="H30" s="18"/>
+      <c r="I30" s="18"/>
+      <c r="J30" s="19"/>
     </row>
     <row r="31" spans="1:13">
-      <c r="A31" s="15">
+      <c r="A31" s="17">
         <v>43</v>
       </c>
-      <c r="B31" s="15">
+      <c r="B31" s="17">
         <v>2</v>
       </c>
-      <c r="C31" s="16" t="s">
+      <c r="C31" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="D31" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E31" s="15" t="s">
+      <c r="D31" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E31" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="F31" s="15"/>
-      <c r="G31" s="15"/>
-      <c r="H31" s="16"/>
-      <c r="I31" s="16"/>
-      <c r="J31" s="17"/>
+      <c r="F31" s="17"/>
+      <c r="G31" s="17"/>
+      <c r="H31" s="18"/>
+      <c r="I31" s="18"/>
+      <c r="J31" s="19"/>
     </row>
     <row r="32" spans="1:13">
-      <c r="A32" s="15">
+      <c r="A32" s="17">
         <v>44</v>
       </c>
-      <c r="B32" s="15">
+      <c r="B32" s="17">
         <v>2</v>
       </c>
-      <c r="C32" s="16" t="s">
+      <c r="C32" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="D32" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E32" s="15" t="s">
+      <c r="D32" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E32" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="F32" s="15"/>
-      <c r="G32" s="15"/>
-      <c r="H32" s="16"/>
-      <c r="I32" s="16"/>
-      <c r="J32" s="17"/>
+      <c r="F32" s="17"/>
+      <c r="G32" s="17"/>
+      <c r="H32" s="18"/>
+      <c r="I32" s="18"/>
+      <c r="J32" s="19"/>
     </row>
     <row r="33" spans="1:11">
-      <c r="A33" s="15">
+      <c r="A33" s="17">
         <v>61</v>
       </c>
-      <c r="B33" s="15">
+      <c r="B33" s="17">
         <v>3</v>
       </c>
-      <c r="C33" s="16">
+      <c r="C33" s="18">
         <v>1</v>
       </c>
-      <c r="D33" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E33" s="15" t="s">
+      <c r="D33" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E33" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="F33" s="15"/>
-      <c r="G33" s="15" t="s">
+      <c r="F33" s="17"/>
+      <c r="G33" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="H33" s="16"/>
-      <c r="I33" s="16" t="s">
+      <c r="H33" s="18"/>
+      <c r="I33" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="J33" s="17"/>
+      <c r="J33" s="19"/>
     </row>
     <row r="34" spans="1:11">
-      <c r="A34" s="15">
+      <c r="A34" s="17">
         <v>62</v>
       </c>
-      <c r="B34" s="15">
+      <c r="B34" s="17">
         <v>3</v>
       </c>
-      <c r="C34" s="16">
+      <c r="C34" s="18">
         <v>2</v>
       </c>
-      <c r="D34" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E34" s="15" t="s">
+      <c r="D34" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E34" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="F34" s="15"/>
-      <c r="G34" s="15" t="s">
+      <c r="F34" s="17"/>
+      <c r="G34" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="H34" s="16"/>
-      <c r="I34" s="16" t="s">
+      <c r="H34" s="18"/>
+      <c r="I34" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="J34" s="17"/>
+      <c r="J34" s="19"/>
     </row>
     <row r="35" spans="1:11">
-      <c r="A35" s="15">
+      <c r="A35" s="17">
         <v>63</v>
       </c>
-      <c r="B35" s="15">
+      <c r="B35" s="17">
         <v>3</v>
       </c>
-      <c r="C35" s="16">
+      <c r="C35" s="18">
         <v>3</v>
       </c>
-      <c r="D35" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E35" s="15" t="s">
+      <c r="D35" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E35" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="F35" s="15"/>
-      <c r="G35" s="15" t="s">
+      <c r="F35" s="17"/>
+      <c r="G35" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="H35" s="16"/>
-      <c r="I35" s="16" t="s">
+      <c r="H35" s="18"/>
+      <c r="I35" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="J35" s="17"/>
+      <c r="J35" s="19"/>
     </row>
     <row r="36" spans="1:11">
-      <c r="A36" s="15">
+      <c r="A36" s="17">
         <v>64</v>
       </c>
-      <c r="B36" s="15">
+      <c r="B36" s="17">
         <v>3</v>
       </c>
-      <c r="C36" s="16">
+      <c r="C36" s="18">
         <v>4</v>
       </c>
-      <c r="D36" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E36" s="15" t="s">
+      <c r="D36" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E36" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="F36" s="15"/>
-      <c r="G36" s="15"/>
-      <c r="H36" s="16"/>
-      <c r="I36" s="16" t="s">
+      <c r="F36" s="17"/>
+      <c r="G36" s="17"/>
+      <c r="H36" s="18"/>
+      <c r="I36" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="J36" s="17"/>
+      <c r="J36" s="19"/>
     </row>
     <row r="37" spans="1:11">
-      <c r="A37" s="15">
+      <c r="A37" s="17">
         <v>65</v>
       </c>
-      <c r="B37" s="15">
+      <c r="B37" s="17">
         <v>3</v>
       </c>
-      <c r="C37" s="16">
+      <c r="C37" s="18">
         <v>5</v>
       </c>
-      <c r="D37" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E37" s="15" t="s">
+      <c r="D37" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E37" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="F37" s="15"/>
-      <c r="G37" s="15"/>
-      <c r="H37" s="16"/>
-      <c r="I37" s="16"/>
-      <c r="J37" s="17"/>
+      <c r="F37" s="17"/>
+      <c r="G37" s="17"/>
+      <c r="H37" s="18"/>
+      <c r="I37" s="18"/>
+      <c r="J37" s="19"/>
     </row>
     <row r="38" spans="1:11">
-      <c r="A38" s="15">
+      <c r="A38" s="17">
         <v>66</v>
       </c>
-      <c r="B38" s="15">
+      <c r="B38" s="17">
         <v>3</v>
       </c>
-      <c r="C38" s="16">
+      <c r="C38" s="18">
         <v>6</v>
       </c>
-      <c r="D38" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E38" s="15" t="s">
+      <c r="D38" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E38" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="F38" s="15"/>
-      <c r="G38" s="15"/>
-      <c r="H38" s="16"/>
-      <c r="I38" s="16"/>
-      <c r="J38" s="17"/>
+      <c r="F38" s="17"/>
+      <c r="G38" s="17"/>
+      <c r="H38" s="18"/>
+      <c r="I38" s="18"/>
+      <c r="J38" s="19"/>
     </row>
     <row r="39" spans="1:11">
-      <c r="A39" s="15">
+      <c r="A39" s="17">
         <v>67</v>
       </c>
-      <c r="B39" s="15">
+      <c r="B39" s="17">
         <v>3</v>
       </c>
-      <c r="C39" s="16">
+      <c r="C39" s="18">
         <v>7</v>
       </c>
-      <c r="D39" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E39" s="15" t="s">
+      <c r="D39" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E39" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="F39" s="15"/>
-      <c r="G39" s="15"/>
-      <c r="H39" s="16"/>
-      <c r="I39" s="16"/>
-      <c r="J39" s="17"/>
+      <c r="F39" s="17"/>
+      <c r="G39" s="17"/>
+      <c r="H39" s="18"/>
+      <c r="I39" s="18"/>
+      <c r="J39" s="19"/>
     </row>
     <row r="40" spans="1:11">
-      <c r="A40" s="15">
+      <c r="A40" s="17">
         <v>68</v>
       </c>
-      <c r="B40" s="15">
+      <c r="B40" s="17">
         <v>3</v>
       </c>
-      <c r="C40" s="16">
+      <c r="C40" s="18">
         <v>8</v>
       </c>
-      <c r="D40" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E40" s="15" t="s">
+      <c r="D40" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E40" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="F40" s="15"/>
-      <c r="G40" s="15"/>
-      <c r="H40" s="16"/>
-      <c r="I40" s="16"/>
-      <c r="J40" s="17"/>
+      <c r="F40" s="17"/>
+      <c r="G40" s="17"/>
+      <c r="H40" s="18"/>
+      <c r="I40" s="18"/>
+      <c r="J40" s="19"/>
     </row>
     <row r="41" spans="1:11">
-      <c r="A41" s="15">
+      <c r="A41" s="17">
         <v>69</v>
       </c>
-      <c r="B41" s="15">
+      <c r="B41" s="17">
         <v>3</v>
       </c>
-      <c r="C41" s="16">
+      <c r="C41" s="18">
         <v>9</v>
       </c>
-      <c r="D41" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E41" s="15" t="s">
+      <c r="D41" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E41" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="F41" s="15"/>
-      <c r="G41" s="15"/>
-      <c r="H41" s="16"/>
-      <c r="I41" s="16"/>
-      <c r="J41" s="17"/>
+      <c r="F41" s="17"/>
+      <c r="G41" s="17"/>
+      <c r="H41" s="18"/>
+      <c r="I41" s="18"/>
+      <c r="J41" s="19"/>
     </row>
     <row r="42" spans="1:11">
-      <c r="A42" s="15">
+      <c r="A42" s="17">
         <v>70</v>
       </c>
-      <c r="B42" s="15">
+      <c r="B42" s="17">
         <v>3</v>
       </c>
-      <c r="C42" s="16">
+      <c r="C42" s="18">
         <v>10</v>
       </c>
-      <c r="D42" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E42" s="15" t="s">
+      <c r="D42" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E42" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="F42" s="15"/>
-      <c r="G42" s="15"/>
-      <c r="H42" s="16"/>
-      <c r="I42" s="16"/>
-      <c r="J42" s="17"/>
+      <c r="F42" s="17"/>
+      <c r="G42" s="17"/>
+      <c r="H42" s="18"/>
+      <c r="I42" s="18"/>
+      <c r="J42" s="19"/>
     </row>
     <row r="43" spans="1:11">
-      <c r="A43" s="15">
-        <v>71</v>
-      </c>
-      <c r="B43" s="15">
+      <c r="A43" s="17">
+        <v>71</v>
+      </c>
+      <c r="B43" s="17">
         <v>3</v>
       </c>
-      <c r="C43" s="16" t="s">
+      <c r="C43" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="D43" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E43" s="15" t="s">
+      <c r="D43" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E43" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="F43" s="15"/>
-      <c r="G43" s="15"/>
-      <c r="H43" s="16"/>
-      <c r="I43" s="16"/>
-      <c r="J43" s="17"/>
+      <c r="F43" s="17"/>
+      <c r="G43" s="17"/>
+      <c r="H43" s="18"/>
+      <c r="I43" s="18"/>
+      <c r="J43" s="19"/>
     </row>
     <row r="44" spans="1:11">
-      <c r="A44" s="15">
+      <c r="A44" s="17">
         <v>72</v>
       </c>
-      <c r="B44" s="15">
+      <c r="B44" s="17">
         <v>3</v>
       </c>
-      <c r="C44" s="16" t="s">
+      <c r="C44" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="D44" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E44" s="15" t="s">
+      <c r="D44" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E44" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="F44" s="15"/>
-      <c r="G44" s="15"/>
-      <c r="H44" s="16"/>
-      <c r="I44" s="16"/>
+      <c r="F44" s="17"/>
+      <c r="G44" s="17"/>
+      <c r="H44" s="18"/>
+      <c r="I44" s="18"/>
     </row>
     <row r="45" spans="1:11">
-      <c r="A45" s="15">
+      <c r="A45" s="17">
         <v>73</v>
       </c>
-      <c r="B45" s="15">
+      <c r="B45" s="17">
         <v>3</v>
       </c>
-      <c r="C45" s="16" t="s">
+      <c r="C45" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="D45" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E45" s="15" t="s">
+      <c r="D45" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E45" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="F45" s="15"/>
-      <c r="G45" s="15"/>
-      <c r="H45" s="16"/>
-      <c r="I45" s="16"/>
+      <c r="F45" s="17"/>
+      <c r="G45" s="17"/>
+      <c r="H45" s="18"/>
+      <c r="I45" s="18"/>
     </row>
     <row r="46" spans="1:11">
-      <c r="A46" s="15">
+      <c r="A46" s="17">
         <v>74</v>
       </c>
-      <c r="B46" s="15">
+      <c r="B46" s="17">
         <v>3</v>
       </c>
-      <c r="C46" s="16" t="s">
+      <c r="C46" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="D46" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E46" s="15" t="s">
+      <c r="D46" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E46" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="F46" s="15"/>
-      <c r="G46" s="15"/>
-      <c r="H46" s="16"/>
-      <c r="I46" s="16"/>
+      <c r="F46" s="17"/>
+      <c r="G46" s="17"/>
+      <c r="H46" s="18"/>
+      <c r="I46" s="18"/>
     </row>
     <row r="47" s="2" customFormat="1" spans="1:11">
-      <c r="A47" s="19">
+      <c r="A47" s="21">
         <v>101</v>
       </c>
-      <c r="B47" s="19">
+      <c r="B47" s="21">
         <v>1</v>
       </c>
-      <c r="C47" s="20">
+      <c r="C47" s="22">
         <v>1</v>
       </c>
-      <c r="D47" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="E47" s="15" t="s">
+      <c r="D47" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="E47" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="F47" s="19">
+      <c r="F47" s="21">
         <v>33333333</v>
       </c>
-      <c r="G47" s="19" t="s">
+      <c r="G47" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="H47" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="I47" s="20" t="s">
+      <c r="H47" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="I47" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="J47" s="17"/>
-      <c r="K47" s="17"/>
+      <c r="J47" s="19"/>
+      <c r="K47" s="19"/>
     </row>
     <row r="48" s="2" customFormat="1" spans="1:11">
-      <c r="A48" s="19">
+      <c r="A48" s="21">
         <v>102</v>
       </c>
-      <c r="B48" s="19">
+      <c r="B48" s="21">
         <v>1</v>
       </c>
-      <c r="C48" s="20">
+      <c r="C48" s="22">
         <v>2</v>
       </c>
-      <c r="D48" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="E48" s="15" t="s">
+      <c r="D48" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="E48" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="F48" s="19">
+      <c r="F48" s="21">
         <v>22222222</v>
       </c>
-      <c r="G48" s="19" t="s">
+      <c r="G48" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="H48" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="I48" s="20" t="s">
+      <c r="H48" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="I48" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="J48" s="17"/>
-      <c r="K48" s="17"/>
+      <c r="J48" s="19"/>
+      <c r="K48" s="19"/>
     </row>
     <row r="49" s="2" customFormat="1" spans="1:13">
-      <c r="A49" s="19">
+      <c r="A49" s="21">
         <v>103</v>
       </c>
-      <c r="B49" s="19">
+      <c r="B49" s="21">
         <v>1</v>
       </c>
-      <c r="C49" s="20">
+      <c r="C49" s="22">
         <v>3</v>
       </c>
-      <c r="D49" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="E49" s="15" t="s">
+      <c r="D49" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="E49" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="F49" s="19">
+      <c r="F49" s="21">
         <v>11111111</v>
       </c>
-      <c r="G49" s="19" t="s">
+      <c r="G49" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="H49" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="I49" s="20" t="s">
+      <c r="H49" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="I49" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="J49" s="17"/>
-      <c r="K49" s="17"/>
+      <c r="J49" s="19"/>
+      <c r="K49" s="19"/>
     </row>
     <row r="50" s="2" customFormat="1" spans="1:13">
-      <c r="A50" s="19">
+      <c r="A50" s="21">
         <v>104</v>
       </c>
-      <c r="B50" s="19">
+      <c r="B50" s="21">
         <v>1</v>
       </c>
-      <c r="C50" s="20">
+      <c r="C50" s="22">
         <v>4</v>
       </c>
-      <c r="D50" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="E50" s="15" t="s">
+      <c r="D50" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="E50" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="F50" s="19">
+      <c r="F50" s="21">
         <v>5000000</v>
       </c>
-      <c r="G50" s="19" t="s">
+      <c r="G50" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="H50" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="I50" s="20" t="s">
+      <c r="H50" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="I50" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="J50" s="17"/>
-      <c r="K50" s="17"/>
+      <c r="J50" s="19"/>
+      <c r="K50" s="19"/>
     </row>
     <row r="51" s="3" customFormat="1" spans="1:13">
-      <c r="A51" s="19">
+      <c r="A51" s="21">
         <v>105</v>
       </c>
-      <c r="B51" s="19">
+      <c r="B51" s="21">
         <v>1</v>
       </c>
-      <c r="C51" s="20">
+      <c r="C51" s="22">
         <v>5</v>
       </c>
-      <c r="D51" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="E51" s="15" t="s">
+      <c r="D51" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="E51" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="F51" s="19">
+      <c r="F51" s="21">
         <v>3000000</v>
       </c>
-      <c r="G51" s="19" t="s">
+      <c r="G51" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="H51" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="I51" s="20" t="s">
+      <c r="H51" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="I51" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="J51" s="17"/>
-      <c r="K51" s="18"/>
+      <c r="J51" s="19"/>
+      <c r="K51" s="20"/>
       <c r="M51" s="2"/>
     </row>
     <row r="52" s="3" customFormat="1" spans="1:13">
-      <c r="A52" s="19">
+      <c r="A52" s="21">
         <v>106</v>
       </c>
-      <c r="B52" s="19">
+      <c r="B52" s="21">
         <v>1</v>
       </c>
-      <c r="C52" s="20">
+      <c r="C52" s="22">
         <v>6</v>
       </c>
-      <c r="D52" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="E52" s="15" t="s">
+      <c r="D52" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="E52" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="F52" s="19"/>
-      <c r="G52" s="19"/>
-      <c r="H52" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="I52" s="20"/>
-      <c r="J52" s="17"/>
-      <c r="K52" s="18"/>
+      <c r="F52" s="21"/>
+      <c r="G52" s="21"/>
+      <c r="H52" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="I52" s="22"/>
+      <c r="J52" s="19"/>
+      <c r="K52" s="20"/>
       <c r="M52" s="2"/>
     </row>
     <row r="53" s="3" customFormat="1" spans="1:13">
-      <c r="A53" s="19">
+      <c r="A53" s="21">
         <v>107</v>
       </c>
-      <c r="B53" s="19">
+      <c r="B53" s="21">
         <v>1</v>
       </c>
-      <c r="C53" s="20">
+      <c r="C53" s="22">
         <v>7</v>
       </c>
-      <c r="D53" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="E53" s="15" t="s">
+      <c r="D53" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="E53" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="F53" s="19"/>
-      <c r="G53" s="19"/>
-      <c r="H53" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="I53" s="20"/>
-      <c r="J53" s="17"/>
-      <c r="K53" s="18"/>
+      <c r="F53" s="21"/>
+      <c r="G53" s="21"/>
+      <c r="H53" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="I53" s="22"/>
+      <c r="J53" s="19"/>
+      <c r="K53" s="20"/>
       <c r="M53" s="2"/>
     </row>
     <row r="54" s="3" customFormat="1" spans="1:13">
-      <c r="A54" s="19">
+      <c r="A54" s="21">
         <v>108</v>
       </c>
-      <c r="B54" s="19">
+      <c r="B54" s="21">
         <v>1</v>
       </c>
-      <c r="C54" s="20">
+      <c r="C54" s="22">
         <v>8</v>
       </c>
-      <c r="D54" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="E54" s="15" t="s">
+      <c r="D54" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="E54" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="F54" s="19"/>
-      <c r="G54" s="19"/>
-      <c r="H54" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="I54" s="20"/>
-      <c r="J54" s="17"/>
-      <c r="K54" s="18"/>
+      <c r="F54" s="21"/>
+      <c r="G54" s="21"/>
+      <c r="H54" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="I54" s="22"/>
+      <c r="J54" s="19"/>
+      <c r="K54" s="20"/>
       <c r="M54" s="2"/>
     </row>
     <row r="55" spans="1:13">
-      <c r="A55" s="19">
+      <c r="A55" s="21">
         <v>109</v>
       </c>
-      <c r="B55" s="19">
+      <c r="B55" s="21">
         <v>1</v>
       </c>
-      <c r="C55" s="20">
+      <c r="C55" s="22">
         <v>9</v>
       </c>
-      <c r="D55" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="E55" s="15" t="s">
+      <c r="D55" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="E55" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="F55" s="19"/>
-      <c r="G55" s="19"/>
-      <c r="H55" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="I55" s="20"/>
-      <c r="J55" s="17"/>
+      <c r="F55" s="21"/>
+      <c r="G55" s="21"/>
+      <c r="H55" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="I55" s="22"/>
+      <c r="J55" s="19"/>
       <c r="M55" s="2"/>
     </row>
     <row r="56" spans="1:13">
-      <c r="A56" s="19">
+      <c r="A56" s="21">
         <v>110</v>
       </c>
-      <c r="B56" s="19">
+      <c r="B56" s="21">
         <v>1</v>
       </c>
-      <c r="C56" s="20">
+      <c r="C56" s="22">
         <v>10</v>
       </c>
-      <c r="D56" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="E56" s="15" t="s">
+      <c r="D56" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="E56" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="F56" s="19"/>
-      <c r="G56" s="19"/>
-      <c r="H56" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="I56" s="20"/>
-      <c r="J56" s="17"/>
+      <c r="F56" s="21"/>
+      <c r="G56" s="21"/>
+      <c r="H56" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="I56" s="22"/>
+      <c r="J56" s="19"/>
       <c r="M56" s="2"/>
     </row>
     <row r="57" customFormat="1" spans="1:13">
-      <c r="A57" s="19">
+      <c r="A57" s="21">
         <v>111</v>
       </c>
-      <c r="B57" s="19">
+      <c r="B57" s="21">
         <v>1</v>
       </c>
-      <c r="C57" s="20" t="s">
+      <c r="C57" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="D57" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="E57" s="15" t="s">
+      <c r="D57" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="E57" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="F57" s="19"/>
-      <c r="G57" s="19"/>
-      <c r="H57" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="I57" s="20"/>
-      <c r="J57" s="17"/>
+      <c r="F57" s="21"/>
+      <c r="G57" s="21"/>
+      <c r="H57" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="I57" s="22"/>
+      <c r="J57" s="19"/>
       <c r="K57" s="8"/>
       <c r="M57" s="2"/>
     </row>
     <row r="58" s="3" customFormat="1" spans="1:13">
-      <c r="A58" s="19">
+      <c r="A58" s="21">
         <v>112</v>
       </c>
-      <c r="B58" s="19">
+      <c r="B58" s="21">
         <v>1</v>
       </c>
-      <c r="C58" s="20" t="s">
+      <c r="C58" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="D58" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="E58" s="15" t="s">
+      <c r="D58" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="E58" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="F58" s="19"/>
-      <c r="G58" s="19"/>
-      <c r="H58" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="I58" s="20"/>
-      <c r="J58" s="17"/>
-      <c r="K58" s="18"/>
+      <c r="F58" s="21"/>
+      <c r="G58" s="21"/>
+      <c r="H58" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="I58" s="22"/>
+      <c r="J58" s="19"/>
+      <c r="K58" s="20"/>
       <c r="M58" s="2"/>
     </row>
     <row r="59" s="3" customFormat="1" spans="1:13">
-      <c r="A59" s="19">
+      <c r="A59" s="21">
         <v>113</v>
       </c>
-      <c r="B59" s="19">
+      <c r="B59" s="21">
         <v>1</v>
       </c>
-      <c r="C59" s="20" t="s">
+      <c r="C59" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="D59" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="E59" s="15" t="s">
+      <c r="D59" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="E59" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="F59" s="19"/>
-      <c r="G59" s="19"/>
-      <c r="H59" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="I59" s="20"/>
-      <c r="J59" s="17"/>
-      <c r="K59" s="18"/>
+      <c r="F59" s="21"/>
+      <c r="G59" s="21"/>
+      <c r="H59" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="I59" s="22"/>
+      <c r="J59" s="19"/>
+      <c r="K59" s="20"/>
       <c r="M59" s="2"/>
     </row>
     <row r="60" s="3" customFormat="1" spans="1:13">
-      <c r="A60" s="19">
+      <c r="A60" s="21">
         <v>114</v>
       </c>
-      <c r="B60" s="19">
+      <c r="B60" s="21">
         <v>1</v>
       </c>
-      <c r="C60" s="20" t="s">
+      <c r="C60" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="D60" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="E60" s="15" t="s">
+      <c r="D60" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="E60" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="F60" s="19"/>
-      <c r="G60" s="19"/>
-      <c r="H60" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="I60" s="20"/>
-      <c r="J60" s="17"/>
-      <c r="K60" s="18"/>
+      <c r="F60" s="21"/>
+      <c r="G60" s="21"/>
+      <c r="H60" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="I60" s="22"/>
+      <c r="J60" s="19"/>
+      <c r="K60" s="20"/>
       <c r="M60" s="2"/>
     </row>
     <row r="61" s="3" customFormat="1" spans="1:13">
-      <c r="A61" s="19">
+      <c r="A61" s="21">
         <v>131</v>
       </c>
-      <c r="B61" s="19">
+      <c r="B61" s="21">
         <v>2</v>
       </c>
-      <c r="C61" s="20">
+      <c r="C61" s="22">
         <v>1</v>
       </c>
-      <c r="D61" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="E61" s="15" t="s">
+      <c r="D61" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="E61" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="F61" s="19">
+      <c r="F61" s="21">
         <v>33333333</v>
       </c>
-      <c r="G61" s="19" t="s">
+      <c r="G61" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="H61" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="I61" s="20" t="s">
+      <c r="H61" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="I61" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="J61" s="17"/>
-      <c r="K61" s="18"/>
+      <c r="J61" s="19"/>
+      <c r="K61" s="20"/>
       <c r="M61" s="2"/>
     </row>
     <row r="62" s="3" customFormat="1" spans="1:13">
-      <c r="A62" s="19">
+      <c r="A62" s="21">
         <v>132</v>
       </c>
-      <c r="B62" s="19">
+      <c r="B62" s="21">
         <v>2</v>
       </c>
-      <c r="C62" s="20">
+      <c r="C62" s="22">
         <v>2</v>
       </c>
-      <c r="D62" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="E62" s="15" t="s">
+      <c r="D62" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="E62" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="F62" s="19">
+      <c r="F62" s="21">
         <v>22222222</v>
       </c>
-      <c r="G62" s="19" t="s">
+      <c r="G62" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="H62" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="I62" s="20" t="s">
+      <c r="H62" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="I62" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="J62" s="17"/>
-      <c r="K62" s="17"/>
+      <c r="J62" s="19"/>
+      <c r="K62" s="19"/>
       <c r="M62" s="2"/>
     </row>
     <row r="63" spans="1:13">
-      <c r="A63" s="19">
+      <c r="A63" s="21">
         <v>133</v>
       </c>
-      <c r="B63" s="19">
+      <c r="B63" s="21">
         <v>2</v>
       </c>
-      <c r="C63" s="20">
+      <c r="C63" s="22">
         <v>3</v>
       </c>
-      <c r="D63" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="E63" s="15" t="s">
+      <c r="D63" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="E63" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="F63" s="19">
+      <c r="F63" s="21">
         <v>11111111</v>
       </c>
-      <c r="G63" s="19" t="s">
+      <c r="G63" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="H63" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="I63" s="20" t="s">
+      <c r="H63" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="I63" s="22" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="64" s="3" customFormat="1" spans="1:13">
-      <c r="A64" s="19">
+      <c r="A64" s="21">
         <v>134</v>
       </c>
-      <c r="B64" s="19">
+      <c r="B64" s="21">
         <v>2</v>
       </c>
-      <c r="C64" s="20">
+      <c r="C64" s="22">
         <v>4</v>
       </c>
-      <c r="D64" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="E64" s="15" t="s">
+      <c r="D64" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="E64" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="F64" s="19">
+      <c r="F64" s="21">
         <v>5000000</v>
       </c>
-      <c r="G64" s="19" t="s">
+      <c r="G64" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="H64" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="I64" s="20" t="s">
+      <c r="H64" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="I64" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="J64" s="17"/>
-      <c r="K64" s="18"/>
+      <c r="J64" s="19"/>
+      <c r="K64" s="20"/>
     </row>
     <row r="65" s="3" customFormat="1" spans="1:11">
-      <c r="A65" s="19">
+      <c r="A65" s="21">
         <v>135</v>
       </c>
-      <c r="B65" s="19">
+      <c r="B65" s="21">
         <v>2</v>
       </c>
-      <c r="C65" s="20">
+      <c r="C65" s="22">
         <v>5</v>
       </c>
-      <c r="D65" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="E65" s="15" t="s">
+      <c r="D65" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="E65" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="F65" s="19">
+      <c r="F65" s="21">
         <v>3000000</v>
       </c>
-      <c r="G65" s="19" t="s">
+      <c r="G65" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="H65" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="I65" s="20" t="s">
+      <c r="H65" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="I65" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="J65" s="17"/>
-      <c r="K65" s="18"/>
+      <c r="J65" s="19"/>
+      <c r="K65" s="20"/>
     </row>
     <row r="66" s="3" customFormat="1" spans="1:11">
-      <c r="A66" s="19">
+      <c r="A66" s="21">
         <v>136</v>
       </c>
-      <c r="B66" s="19">
+      <c r="B66" s="21">
         <v>2</v>
       </c>
-      <c r="C66" s="20">
+      <c r="C66" s="22">
         <v>6</v>
       </c>
-      <c r="D66" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="E66" s="15" t="s">
+      <c r="D66" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="E66" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="F66" s="19"/>
-      <c r="G66" s="19"/>
-      <c r="H66" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="I66" s="20"/>
-      <c r="J66" s="17"/>
-      <c r="K66" s="18"/>
+      <c r="F66" s="21"/>
+      <c r="G66" s="21"/>
+      <c r="H66" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="I66" s="22"/>
+      <c r="J66" s="19"/>
+      <c r="K66" s="20"/>
     </row>
     <row r="67" s="3" customFormat="1" spans="1:11">
-      <c r="A67" s="19">
+      <c r="A67" s="21">
         <v>137</v>
       </c>
-      <c r="B67" s="19">
+      <c r="B67" s="21">
         <v>2</v>
       </c>
-      <c r="C67" s="20">
+      <c r="C67" s="22">
         <v>7</v>
       </c>
-      <c r="D67" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="E67" s="15" t="s">
+      <c r="D67" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="E67" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="F67" s="19"/>
-      <c r="G67" s="19"/>
-      <c r="H67" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="I67" s="20"/>
-      <c r="J67" s="17"/>
-      <c r="K67" s="18"/>
+      <c r="F67" s="21"/>
+      <c r="G67" s="21"/>
+      <c r="H67" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="I67" s="22"/>
+      <c r="J67" s="19"/>
+      <c r="K67" s="20"/>
     </row>
     <row r="68" s="3" customFormat="1" spans="1:11">
-      <c r="A68" s="19">
+      <c r="A68" s="21">
         <v>138</v>
       </c>
-      <c r="B68" s="19">
+      <c r="B68" s="21">
         <v>2</v>
       </c>
-      <c r="C68" s="20">
+      <c r="C68" s="22">
         <v>8</v>
       </c>
-      <c r="D68" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="E68" s="15" t="s">
+      <c r="D68" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="E68" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="F68" s="19"/>
-      <c r="G68" s="19"/>
-      <c r="H68" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="I68" s="20"/>
-      <c r="J68" s="17"/>
-      <c r="K68" s="17"/>
+      <c r="F68" s="21"/>
+      <c r="G68" s="21"/>
+      <c r="H68" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="I68" s="22"/>
+      <c r="J68" s="19"/>
+      <c r="K68" s="19"/>
     </row>
     <row r="69" spans="1:11">
-      <c r="A69" s="19">
+      <c r="A69" s="21">
         <v>139</v>
       </c>
-      <c r="B69" s="19">
+      <c r="B69" s="21">
         <v>2</v>
       </c>
-      <c r="C69" s="20">
+      <c r="C69" s="22">
         <v>9</v>
       </c>
-      <c r="D69" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="E69" s="15" t="s">
+      <c r="D69" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="E69" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="F69" s="19"/>
-      <c r="G69" s="19"/>
-      <c r="H69" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="I69" s="20"/>
-      <c r="J69" s="17"/>
+      <c r="F69" s="21"/>
+      <c r="G69" s="21"/>
+      <c r="H69" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="I69" s="22"/>
+      <c r="J69" s="19"/>
     </row>
     <row r="70" spans="1:11">
-      <c r="A70" s="19">
+      <c r="A70" s="21">
         <v>140</v>
       </c>
-      <c r="B70" s="19">
+      <c r="B70" s="21">
         <v>2</v>
       </c>
-      <c r="C70" s="20">
+      <c r="C70" s="22">
         <v>10</v>
       </c>
-      <c r="D70" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="E70" s="15" t="s">
+      <c r="D70" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="E70" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="F70" s="19"/>
-      <c r="G70" s="19"/>
-      <c r="H70" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="I70" s="20"/>
-      <c r="J70" s="17"/>
+      <c r="F70" s="21"/>
+      <c r="G70" s="21"/>
+      <c r="H70" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="I70" s="22"/>
+      <c r="J70" s="19"/>
     </row>
     <row r="71" spans="1:11">
-      <c r="A71" s="19">
+      <c r="A71" s="21">
         <v>141</v>
       </c>
-      <c r="B71" s="19">
+      <c r="B71" s="21">
         <v>2</v>
       </c>
-      <c r="C71" s="20" t="s">
+      <c r="C71" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="D71" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="E71" s="15" t="s">
+      <c r="D71" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="E71" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="F71" s="19"/>
-      <c r="G71" s="19"/>
-      <c r="H71" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="I71" s="20"/>
-      <c r="J71" s="17"/>
+      <c r="F71" s="21"/>
+      <c r="G71" s="21"/>
+      <c r="H71" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="I71" s="22"/>
+      <c r="J71" s="19"/>
     </row>
     <row r="72" spans="1:11">
-      <c r="A72" s="19">
+      <c r="A72" s="21">
         <v>142</v>
       </c>
-      <c r="B72" s="19">
+      <c r="B72" s="21">
         <v>2</v>
       </c>
-      <c r="C72" s="20" t="s">
+      <c r="C72" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="D72" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="E72" s="15" t="s">
+      <c r="D72" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="E72" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="F72" s="19"/>
-      <c r="G72" s="19"/>
-      <c r="H72" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="I72" s="20"/>
-      <c r="J72" s="17"/>
+      <c r="F72" s="21"/>
+      <c r="G72" s="21"/>
+      <c r="H72" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="I72" s="22"/>
+      <c r="J72" s="19"/>
     </row>
     <row r="73" spans="1:11">
-      <c r="A73" s="19">
+      <c r="A73" s="21">
         <v>143</v>
       </c>
-      <c r="B73" s="19">
+      <c r="B73" s="21">
         <v>2</v>
       </c>
-      <c r="C73" s="20" t="s">
+      <c r="C73" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="D73" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="E73" s="15" t="s">
+      <c r="D73" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="E73" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="F73" s="19"/>
-      <c r="G73" s="19"/>
-      <c r="H73" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="I73" s="20"/>
-      <c r="J73" s="17"/>
+      <c r="F73" s="21"/>
+      <c r="G73" s="21"/>
+      <c r="H73" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="I73" s="22"/>
+      <c r="J73" s="19"/>
     </row>
     <row r="74" spans="1:11">
-      <c r="A74" s="19">
+      <c r="A74" s="21">
         <v>144</v>
       </c>
-      <c r="B74" s="19">
+      <c r="B74" s="21">
         <v>2</v>
       </c>
-      <c r="C74" s="20" t="s">
+      <c r="C74" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="D74" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="E74" s="15" t="s">
+      <c r="D74" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="E74" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="F74" s="19"/>
-      <c r="G74" s="19"/>
-      <c r="H74" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="I74" s="20"/>
-      <c r="J74" s="17"/>
+      <c r="F74" s="21"/>
+      <c r="G74" s="21"/>
+      <c r="H74" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="I74" s="22"/>
+      <c r="J74" s="19"/>
     </row>
     <row r="75" spans="1:11">
-      <c r="A75" s="19">
+      <c r="A75" s="21">
         <v>161</v>
       </c>
-      <c r="B75" s="19">
+      <c r="B75" s="21">
         <v>3</v>
       </c>
-      <c r="C75" s="20">
+      <c r="C75" s="22">
         <v>1</v>
       </c>
-      <c r="D75" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="E75" s="15" t="s">
+      <c r="D75" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="E75" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="F75" s="19">
+      <c r="F75" s="21">
         <v>99999999</v>
       </c>
-      <c r="G75" s="19" t="s">
+      <c r="G75" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="H75" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="I75" s="20" t="s">
+      <c r="H75" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="I75" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="J75" s="17"/>
+      <c r="J75" s="19"/>
     </row>
     <row r="76" spans="1:11">
-      <c r="A76" s="19">
+      <c r="A76" s="21">
         <v>162</v>
       </c>
-      <c r="B76" s="19">
+      <c r="B76" s="21">
         <v>3</v>
       </c>
-      <c r="C76" s="20">
+      <c r="C76" s="22">
         <v>2</v>
       </c>
-      <c r="D76" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="E76" s="15" t="s">
+      <c r="D76" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="E76" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="F76" s="19">
+      <c r="F76" s="21">
         <v>88888888</v>
       </c>
-      <c r="G76" s="19" t="s">
+      <c r="G76" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="H76" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="I76" s="20" t="s">
+      <c r="H76" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="I76" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="J76" s="17"/>
+      <c r="J76" s="19"/>
     </row>
     <row r="77" spans="1:11">
-      <c r="A77" s="19">
+      <c r="A77" s="21">
         <v>163</v>
       </c>
-      <c r="B77" s="19">
+      <c r="B77" s="21">
         <v>3</v>
       </c>
-      <c r="C77" s="20">
+      <c r="C77" s="22">
         <v>3</v>
       </c>
-      <c r="D77" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="E77" s="15" t="s">
+      <c r="D77" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="E77" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="F77" s="19">
+      <c r="F77" s="21">
         <v>77777777</v>
       </c>
-      <c r="G77" s="19" t="s">
+      <c r="G77" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="H77" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="I77" s="20" t="s">
+      <c r="H77" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="I77" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="J77" s="17"/>
+      <c r="J77" s="19"/>
     </row>
     <row r="78" spans="1:11">
-      <c r="A78" s="19">
+      <c r="A78" s="21">
         <v>164</v>
       </c>
-      <c r="B78" s="19">
+      <c r="B78" s="21">
         <v>3</v>
       </c>
-      <c r="C78" s="20">
+      <c r="C78" s="22">
         <v>4</v>
       </c>
-      <c r="D78" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="E78" s="15" t="s">
+      <c r="D78" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="E78" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="F78" s="19">
+      <c r="F78" s="21">
         <v>66666666</v>
       </c>
-      <c r="G78" s="19" t="s">
+      <c r="G78" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="H78" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="I78" s="20" t="s">
+      <c r="H78" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="I78" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="J78" s="17"/>
+      <c r="J78" s="19"/>
     </row>
     <row r="79" spans="1:11">
-      <c r="A79" s="19">
+      <c r="A79" s="21">
         <v>165</v>
       </c>
-      <c r="B79" s="19">
+      <c r="B79" s="21">
         <v>3</v>
       </c>
-      <c r="C79" s="20">
+      <c r="C79" s="22">
         <v>5</v>
       </c>
-      <c r="D79" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="E79" s="15" t="s">
+      <c r="D79" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="E79" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="F79" s="19">
+      <c r="F79" s="21">
         <v>55555555</v>
       </c>
-      <c r="G79" s="19" t="s">
+      <c r="G79" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="H79" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="I79" s="20" t="s">
+      <c r="H79" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="I79" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="J79" s="17"/>
+      <c r="J79" s="19"/>
     </row>
     <row r="80" spans="1:11">
-      <c r="A80" s="19">
+      <c r="A80" s="21">
         <v>166</v>
       </c>
-      <c r="B80" s="19">
+      <c r="B80" s="21">
         <v>3</v>
       </c>
-      <c r="C80" s="20">
+      <c r="C80" s="22">
         <v>6</v>
       </c>
-      <c r="D80" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="E80" s="15" t="s">
+      <c r="D80" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="E80" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="F80" s="19"/>
-      <c r="G80" s="19"/>
-      <c r="H80" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="I80" s="20"/>
-      <c r="J80" s="17"/>
+      <c r="F80" s="21"/>
+      <c r="G80" s="21"/>
+      <c r="H80" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="I80" s="22"/>
+      <c r="J80" s="19"/>
     </row>
     <row r="81" spans="1:10">
-      <c r="A81" s="19">
+      <c r="A81" s="21">
         <v>167</v>
       </c>
-      <c r="B81" s="19">
+      <c r="B81" s="21">
         <v>3</v>
       </c>
-      <c r="C81" s="20">
+      <c r="C81" s="22">
         <v>7</v>
       </c>
-      <c r="D81" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="E81" s="15" t="s">
+      <c r="D81" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="E81" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="F81" s="19"/>
-      <c r="G81" s="19"/>
-      <c r="H81" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="I81" s="20"/>
-      <c r="J81" s="17"/>
+      <c r="F81" s="21"/>
+      <c r="G81" s="21"/>
+      <c r="H81" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="I81" s="22"/>
+      <c r="J81" s="19"/>
     </row>
     <row r="82" spans="1:10">
-      <c r="A82" s="19">
+      <c r="A82" s="21">
         <v>168</v>
       </c>
-      <c r="B82" s="19">
+      <c r="B82" s="21">
         <v>3</v>
       </c>
-      <c r="C82" s="20">
+      <c r="C82" s="22">
         <v>8</v>
       </c>
-      <c r="D82" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="E82" s="15" t="s">
+      <c r="D82" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="E82" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="F82" s="19"/>
-      <c r="G82" s="19"/>
-      <c r="H82" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="I82" s="20"/>
-      <c r="J82" s="17"/>
+      <c r="F82" s="21"/>
+      <c r="G82" s="21"/>
+      <c r="H82" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="I82" s="22"/>
+      <c r="J82" s="19"/>
     </row>
     <row r="83" spans="1:10">
-      <c r="A83" s="19">
+      <c r="A83" s="21">
         <v>169</v>
       </c>
-      <c r="B83" s="19">
+      <c r="B83" s="21">
         <v>3</v>
       </c>
-      <c r="C83" s="20">
+      <c r="C83" s="22">
         <v>9</v>
       </c>
-      <c r="D83" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="E83" s="15" t="s">
+      <c r="D83" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="E83" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="F83" s="19"/>
-      <c r="G83" s="19"/>
-      <c r="H83" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="I83" s="20"/>
-      <c r="J83" s="17"/>
+      <c r="F83" s="21"/>
+      <c r="G83" s="21"/>
+      <c r="H83" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="I83" s="22"/>
+      <c r="J83" s="19"/>
     </row>
     <row r="84" spans="1:10">
-      <c r="A84" s="19">
+      <c r="A84" s="21">
         <v>170</v>
       </c>
-      <c r="B84" s="19">
+      <c r="B84" s="21">
         <v>3</v>
       </c>
-      <c r="C84" s="20">
+      <c r="C84" s="22">
         <v>10</v>
       </c>
-      <c r="D84" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="E84" s="15" t="s">
+      <c r="D84" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="E84" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="F84" s="19"/>
-      <c r="G84" s="19"/>
-      <c r="H84" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="I84" s="20"/>
-      <c r="J84" s="17"/>
+      <c r="F84" s="21"/>
+      <c r="G84" s="21"/>
+      <c r="H84" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="I84" s="22"/>
+      <c r="J84" s="19"/>
     </row>
     <row r="85" spans="1:10">
-      <c r="A85" s="19">
+      <c r="A85" s="21">
         <v>171</v>
       </c>
-      <c r="B85" s="19">
+      <c r="B85" s="21">
         <v>3</v>
       </c>
-      <c r="C85" s="20" t="s">
+      <c r="C85" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="D85" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="E85" s="15" t="s">
+      <c r="D85" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="E85" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="F85" s="19"/>
-      <c r="G85" s="19"/>
-      <c r="H85" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="I85" s="20"/>
-      <c r="J85" s="17"/>
+      <c r="F85" s="21"/>
+      <c r="G85" s="21"/>
+      <c r="H85" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="I85" s="22"/>
+      <c r="J85" s="19"/>
     </row>
     <row r="86" spans="1:10">
-      <c r="A86" s="19">
+      <c r="A86" s="21">
         <v>172</v>
       </c>
-      <c r="B86" s="19">
+      <c r="B86" s="21">
         <v>3</v>
       </c>
-      <c r="C86" s="20" t="s">
+      <c r="C86" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="D86" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="E86" s="15" t="s">
+      <c r="D86" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="E86" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="F86" s="19"/>
-      <c r="G86" s="19"/>
-      <c r="H86" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="I86" s="20"/>
+      <c r="F86" s="21"/>
+      <c r="G86" s="21"/>
+      <c r="H86" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="I86" s="22"/>
     </row>
     <row r="87" spans="1:10">
-      <c r="A87" s="19">
+      <c r="A87" s="21">
         <v>173</v>
       </c>
-      <c r="B87" s="19">
+      <c r="B87" s="21">
         <v>3</v>
       </c>
-      <c r="C87" s="20" t="s">
+      <c r="C87" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="D87" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="E87" s="15" t="s">
+      <c r="D87" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="E87" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="F87" s="19"/>
-      <c r="G87" s="19"/>
-      <c r="H87" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="I87" s="20"/>
+      <c r="F87" s="21"/>
+      <c r="G87" s="21"/>
+      <c r="H87" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="I87" s="22"/>
     </row>
     <row r="88" spans="1:10">
-      <c r="A88" s="19">
+      <c r="A88" s="21">
         <v>174</v>
       </c>
-      <c r="B88" s="19">
+      <c r="B88" s="21">
         <v>3</v>
       </c>
-      <c r="C88" s="20" t="s">
+      <c r="C88" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="D88" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="E88" s="15" t="s">
+      <c r="D88" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="E88" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="F88" s="19"/>
-      <c r="G88" s="19"/>
-      <c r="H88" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="I88" s="20"/>
+      <c r="F88" s="21"/>
+      <c r="G88" s="21"/>
+      <c r="H88" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="I88" s="22"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/table/resources/sample/PointsAwardRanking.xlsx
+++ b/table/resources/sample/PointsAwardRanking.xlsx
@@ -629,7 +629,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -645,12 +645,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -979,7 +973,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1003,16 +997,16 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1021,89 +1015,89 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1144,9 +1138,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1155,22 +1146,19 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1553,7 +1541,7 @@
       <c r="H1" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="13" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1564,13 +1552,13 @@
       <c r="B2" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="14" t="s">
         <v>10</v>
       </c>
       <c r="D2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="E2" s="14" t="s">
         <v>11</v>
       </c>
       <c r="F2" s="12" t="s">
@@ -1582,7 +1570,7 @@
       <c r="H2" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="16" t="s">
+      <c r="I2" s="12" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1599,7 +1587,7 @@
       <c r="D3" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="E3" s="14" t="s">
         <v>18</v>
       </c>
       <c r="F3" s="12" t="s">
@@ -1611,7 +1599,7 @@
       <c r="H3" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I3" s="14" t="s">
+      <c r="I3" s="13" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1624,2125 +1612,2125 @@
       <c r="F4" s="12"/>
       <c r="G4" s="12"/>
       <c r="H4" s="13"/>
-      <c r="I4" s="14"/>
+      <c r="I4" s="13"/>
     </row>
     <row r="5" s="2" customFormat="1" spans="1:13">
-      <c r="A5" s="17">
+      <c r="A5" s="15">
         <v>1</v>
       </c>
-      <c r="B5" s="17">
+      <c r="B5" s="15">
         <v>1</v>
       </c>
-      <c r="C5" s="18">
+      <c r="C5" s="16">
         <v>1</v>
       </c>
-      <c r="D5" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="17" t="s">
+      <c r="D5" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="17"/>
-      <c r="G5" s="17" t="s">
+      <c r="F5" s="15"/>
+      <c r="G5" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="H5" s="18"/>
-      <c r="I5" s="18" t="s">
+      <c r="H5" s="16"/>
+      <c r="I5" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="J5" s="19"/>
-      <c r="K5" s="19"/>
+      <c r="J5" s="17"/>
+      <c r="K5" s="17"/>
     </row>
     <row r="6" s="2" customFormat="1" spans="1:13">
-      <c r="A6" s="17">
+      <c r="A6" s="15">
         <v>2</v>
       </c>
-      <c r="B6" s="17">
+      <c r="B6" s="15">
         <v>1</v>
       </c>
-      <c r="C6" s="18">
+      <c r="C6" s="16">
         <v>2</v>
       </c>
-      <c r="D6" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" s="17" t="s">
+      <c r="D6" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="17"/>
-      <c r="G6" s="17" t="s">
+      <c r="F6" s="15"/>
+      <c r="G6" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="H6" s="18"/>
-      <c r="I6" s="18" t="s">
+      <c r="H6" s="16"/>
+      <c r="I6" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="J6" s="19"/>
-      <c r="K6" s="19"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="17"/>
     </row>
     <row r="7" s="2" customFormat="1" spans="1:13">
-      <c r="A7" s="17">
+      <c r="A7" s="15">
         <v>3</v>
       </c>
-      <c r="B7" s="17">
+      <c r="B7" s="15">
         <v>1</v>
       </c>
-      <c r="C7" s="18">
+      <c r="C7" s="16">
         <v>3</v>
       </c>
-      <c r="D7" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" s="17" t="s">
+      <c r="D7" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="F7" s="17"/>
-      <c r="G7" s="17" t="s">
+      <c r="F7" s="15"/>
+      <c r="G7" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="H7" s="18"/>
-      <c r="I7" s="18" t="s">
+      <c r="H7" s="16"/>
+      <c r="I7" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="J7" s="19"/>
-      <c r="K7" s="19"/>
+      <c r="J7" s="17"/>
+      <c r="K7" s="17"/>
     </row>
     <row r="8" s="2" customFormat="1" spans="1:13">
-      <c r="A8" s="17">
+      <c r="A8" s="15">
         <v>4</v>
       </c>
-      <c r="B8" s="17">
+      <c r="B8" s="15">
         <v>1</v>
       </c>
-      <c r="C8" s="18">
+      <c r="C8" s="16">
         <v>4</v>
       </c>
-      <c r="D8" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8" s="17" t="s">
+      <c r="D8" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="F8" s="17"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="18"/>
-      <c r="I8" s="18" t="s">
+      <c r="F8" s="15"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="J8" s="19"/>
-      <c r="K8" s="19"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="17"/>
     </row>
     <row r="9" s="3" customFormat="1" spans="1:13">
-      <c r="A9" s="17">
+      <c r="A9" s="15">
         <v>5</v>
       </c>
-      <c r="B9" s="17">
+      <c r="B9" s="15">
         <v>1</v>
       </c>
-      <c r="C9" s="18">
+      <c r="C9" s="16">
         <v>5</v>
       </c>
-      <c r="D9" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E9" s="17" t="s">
+      <c r="D9" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="F9" s="17"/>
-      <c r="G9" s="17"/>
-      <c r="H9" s="18"/>
-      <c r="I9" s="18"/>
-      <c r="J9" s="19"/>
-      <c r="K9" s="20"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="15"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="17"/>
+      <c r="K9" s="18"/>
       <c r="M9" s="2"/>
     </row>
     <row r="10" s="3" customFormat="1" spans="1:13">
-      <c r="A10" s="17">
+      <c r="A10" s="15">
         <v>6</v>
       </c>
-      <c r="B10" s="17">
+      <c r="B10" s="15">
         <v>1</v>
       </c>
-      <c r="C10" s="18">
+      <c r="C10" s="16">
         <v>6</v>
       </c>
-      <c r="D10" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E10" s="17" t="s">
+      <c r="D10" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="18"/>
-      <c r="I10" s="18"/>
-      <c r="J10" s="19"/>
-      <c r="K10" s="20"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="16"/>
+      <c r="J10" s="17"/>
+      <c r="K10" s="18"/>
       <c r="M10" s="2"/>
     </row>
     <row r="11" s="3" customFormat="1" spans="1:13">
-      <c r="A11" s="17">
+      <c r="A11" s="15">
         <v>7</v>
       </c>
-      <c r="B11" s="17">
+      <c r="B11" s="15">
         <v>1</v>
       </c>
-      <c r="C11" s="18">
+      <c r="C11" s="16">
         <v>7</v>
       </c>
-      <c r="D11" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E11" s="17" t="s">
+      <c r="D11" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="F11" s="17"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="18"/>
-      <c r="I11" s="18"/>
-      <c r="J11" s="19"/>
-      <c r="K11" s="20"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="15"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="16"/>
+      <c r="J11" s="17"/>
+      <c r="K11" s="18"/>
       <c r="M11" s="2"/>
     </row>
     <row r="12" s="3" customFormat="1" spans="1:13">
-      <c r="A12" s="17">
+      <c r="A12" s="15">
         <v>8</v>
       </c>
-      <c r="B12" s="17">
+      <c r="B12" s="15">
         <v>1</v>
       </c>
-      <c r="C12" s="18">
+      <c r="C12" s="16">
         <v>8</v>
       </c>
-      <c r="D12" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E12" s="17" t="s">
+      <c r="D12" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="F12" s="17"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="18"/>
-      <c r="I12" s="18"/>
-      <c r="J12" s="19"/>
-      <c r="K12" s="20"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="17"/>
+      <c r="K12" s="18"/>
       <c r="M12" s="2"/>
     </row>
     <row r="13" spans="1:13">
-      <c r="A13" s="17">
+      <c r="A13" s="15">
         <v>9</v>
       </c>
-      <c r="B13" s="17">
+      <c r="B13" s="15">
         <v>1</v>
       </c>
-      <c r="C13" s="18">
+      <c r="C13" s="16">
         <v>9</v>
       </c>
-      <c r="D13" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E13" s="17" t="s">
+      <c r="D13" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="F13" s="17"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="18"/>
-      <c r="I13" s="18"/>
-      <c r="J13" s="19"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="16"/>
+      <c r="I13" s="16"/>
+      <c r="J13" s="17"/>
       <c r="M13" s="2"/>
     </row>
     <row r="14" spans="1:13">
-      <c r="A14" s="17">
+      <c r="A14" s="15">
         <v>10</v>
       </c>
-      <c r="B14" s="17">
+      <c r="B14" s="15">
         <v>1</v>
       </c>
-      <c r="C14" s="18">
+      <c r="C14" s="16">
         <v>10</v>
       </c>
-      <c r="D14" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E14" s="17" t="s">
+      <c r="D14" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E14" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="18"/>
-      <c r="I14" s="18"/>
-      <c r="J14" s="19"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="16"/>
+      <c r="J14" s="17"/>
       <c r="M14" s="2"/>
     </row>
     <row r="15" customFormat="1" spans="1:13">
-      <c r="A15" s="17">
+      <c r="A15" s="15">
         <v>11</v>
       </c>
-      <c r="B15" s="17">
+      <c r="B15" s="15">
         <v>1</v>
       </c>
-      <c r="C15" s="18" t="s">
+      <c r="C15" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="D15" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E15" s="17" t="s">
+      <c r="D15" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="F15" s="17"/>
-      <c r="G15" s="17"/>
-      <c r="H15" s="18"/>
-      <c r="I15" s="18"/>
-      <c r="J15" s="19"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="16"/>
+      <c r="I15" s="16"/>
+      <c r="J15" s="17"/>
       <c r="K15" s="8"/>
       <c r="M15" s="2"/>
     </row>
     <row r="16" s="3" customFormat="1" spans="1:13">
-      <c r="A16" s="17">
+      <c r="A16" s="15">
         <v>12</v>
       </c>
-      <c r="B16" s="17">
+      <c r="B16" s="15">
         <v>1</v>
       </c>
-      <c r="C16" s="18" t="s">
+      <c r="C16" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="D16" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E16" s="17" t="s">
+      <c r="D16" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E16" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="F16" s="17"/>
-      <c r="G16" s="17"/>
-      <c r="H16" s="18"/>
-      <c r="I16" s="18"/>
-      <c r="J16" s="19"/>
-      <c r="K16" s="20"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="15"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="16"/>
+      <c r="J16" s="17"/>
+      <c r="K16" s="18"/>
       <c r="M16" s="2"/>
     </row>
     <row r="17" s="3" customFormat="1" spans="1:13">
-      <c r="A17" s="17">
+      <c r="A17" s="15">
         <v>13</v>
       </c>
-      <c r="B17" s="17">
+      <c r="B17" s="15">
         <v>1</v>
       </c>
-      <c r="C17" s="18" t="s">
+      <c r="C17" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="D17" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E17" s="17" t="s">
+      <c r="D17" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="F17" s="17"/>
-      <c r="G17" s="17"/>
-      <c r="H17" s="18"/>
-      <c r="I17" s="18"/>
-      <c r="J17" s="19"/>
-      <c r="K17" s="20"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="16"/>
+      <c r="I17" s="16"/>
+      <c r="J17" s="17"/>
+      <c r="K17" s="18"/>
       <c r="M17" s="2"/>
     </row>
     <row r="18" s="3" customFormat="1" spans="1:13">
-      <c r="A18" s="17">
+      <c r="A18" s="15">
         <v>14</v>
       </c>
-      <c r="B18" s="17">
+      <c r="B18" s="15">
         <v>1</v>
       </c>
-      <c r="C18" s="18" t="s">
+      <c r="C18" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="D18" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E18" s="17" t="s">
+      <c r="D18" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="F18" s="17"/>
-      <c r="G18" s="17"/>
-      <c r="H18" s="18"/>
-      <c r="I18" s="18"/>
-      <c r="J18" s="19"/>
-      <c r="K18" s="20"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="15"/>
+      <c r="H18" s="16"/>
+      <c r="I18" s="16"/>
+      <c r="J18" s="17"/>
+      <c r="K18" s="18"/>
       <c r="M18" s="2"/>
     </row>
     <row r="19" s="3" customFormat="1" spans="1:13">
-      <c r="A19" s="17">
+      <c r="A19" s="15">
         <v>31</v>
       </c>
-      <c r="B19" s="17">
+      <c r="B19" s="15">
         <v>2</v>
       </c>
-      <c r="C19" s="18">
+      <c r="C19" s="16">
         <v>1</v>
       </c>
-      <c r="D19" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E19" s="17" t="s">
+      <c r="D19" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="F19" s="17"/>
-      <c r="G19" s="17" t="s">
+      <c r="F19" s="15"/>
+      <c r="G19" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="H19" s="18"/>
-      <c r="I19" s="18" t="s">
+      <c r="H19" s="16"/>
+      <c r="I19" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="J19" s="19"/>
-      <c r="K19" s="20"/>
+      <c r="J19" s="17"/>
+      <c r="K19" s="18"/>
       <c r="M19" s="2"/>
     </row>
     <row r="20" s="3" customFormat="1" spans="1:13">
-      <c r="A20" s="17">
+      <c r="A20" s="15">
         <v>32</v>
       </c>
-      <c r="B20" s="17">
+      <c r="B20" s="15">
         <v>2</v>
       </c>
-      <c r="C20" s="18">
+      <c r="C20" s="16">
         <v>2</v>
       </c>
-      <c r="D20" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E20" s="17" t="s">
+      <c r="D20" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E20" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="F20" s="17"/>
-      <c r="G20" s="17" t="s">
+      <c r="F20" s="15"/>
+      <c r="G20" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="H20" s="18"/>
-      <c r="I20" s="18" t="s">
+      <c r="H20" s="16"/>
+      <c r="I20" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="J20" s="19"/>
-      <c r="K20" s="19"/>
+      <c r="J20" s="17"/>
+      <c r="K20" s="17"/>
       <c r="M20" s="2"/>
     </row>
     <row r="21" spans="1:13">
-      <c r="A21" s="17">
+      <c r="A21" s="15">
         <v>33</v>
       </c>
-      <c r="B21" s="17">
+      <c r="B21" s="15">
         <v>2</v>
       </c>
-      <c r="C21" s="18">
+      <c r="C21" s="16">
         <v>3</v>
       </c>
-      <c r="D21" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E21" s="17" t="s">
+      <c r="D21" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E21" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="F21" s="17"/>
-      <c r="G21" s="17" t="s">
+      <c r="F21" s="15"/>
+      <c r="G21" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="H21" s="18"/>
-      <c r="I21" s="18" t="s">
+      <c r="H21" s="16"/>
+      <c r="I21" s="16" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="22" s="3" customFormat="1" spans="1:13">
-      <c r="A22" s="17">
+      <c r="A22" s="15">
         <v>34</v>
       </c>
-      <c r="B22" s="17">
+      <c r="B22" s="15">
         <v>2</v>
       </c>
-      <c r="C22" s="18">
+      <c r="C22" s="16">
         <v>4</v>
       </c>
-      <c r="D22" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E22" s="17" t="s">
+      <c r="D22" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E22" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="F22" s="17"/>
-      <c r="G22" s="17"/>
-      <c r="H22" s="18"/>
-      <c r="I22" s="18" t="s">
+      <c r="F22" s="15"/>
+      <c r="G22" s="15"/>
+      <c r="H22" s="16"/>
+      <c r="I22" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="J22" s="19"/>
-      <c r="K22" s="20"/>
+      <c r="J22" s="17"/>
+      <c r="K22" s="18"/>
     </row>
     <row r="23" s="3" customFormat="1" spans="1:13">
-      <c r="A23" s="17">
+      <c r="A23" s="15">
         <v>35</v>
       </c>
-      <c r="B23" s="17">
+      <c r="B23" s="15">
         <v>2</v>
       </c>
-      <c r="C23" s="18">
+      <c r="C23" s="16">
         <v>5</v>
       </c>
-      <c r="D23" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E23" s="17" t="s">
+      <c r="D23" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E23" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="F23" s="17"/>
-      <c r="G23" s="17"/>
-      <c r="H23" s="18"/>
-      <c r="I23" s="18"/>
-      <c r="J23" s="19"/>
-      <c r="K23" s="20"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="15"/>
+      <c r="H23" s="16"/>
+      <c r="I23" s="16"/>
+      <c r="J23" s="17"/>
+      <c r="K23" s="18"/>
     </row>
     <row r="24" s="3" customFormat="1" spans="1:13">
-      <c r="A24" s="17">
+      <c r="A24" s="15">
         <v>36</v>
       </c>
-      <c r="B24" s="17">
+      <c r="B24" s="15">
         <v>2</v>
       </c>
-      <c r="C24" s="18">
+      <c r="C24" s="16">
         <v>6</v>
       </c>
-      <c r="D24" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E24" s="17" t="s">
+      <c r="D24" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E24" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="F24" s="17"/>
-      <c r="G24" s="17"/>
-      <c r="H24" s="18"/>
-      <c r="I24" s="18"/>
-      <c r="J24" s="19"/>
-      <c r="K24" s="20"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="15"/>
+      <c r="H24" s="16"/>
+      <c r="I24" s="16"/>
+      <c r="J24" s="17"/>
+      <c r="K24" s="18"/>
     </row>
     <row r="25" s="3" customFormat="1" spans="1:13">
-      <c r="A25" s="17">
+      <c r="A25" s="15">
         <v>37</v>
       </c>
-      <c r="B25" s="17">
+      <c r="B25" s="15">
         <v>2</v>
       </c>
-      <c r="C25" s="18">
+      <c r="C25" s="16">
         <v>7</v>
       </c>
-      <c r="D25" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E25" s="17" t="s">
+      <c r="D25" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E25" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="F25" s="17"/>
-      <c r="G25" s="17"/>
-      <c r="H25" s="18"/>
-      <c r="I25" s="18"/>
-      <c r="J25" s="19"/>
-      <c r="K25" s="20"/>
+      <c r="F25" s="15"/>
+      <c r="G25" s="15"/>
+      <c r="H25" s="16"/>
+      <c r="I25" s="16"/>
+      <c r="J25" s="17"/>
+      <c r="K25" s="18"/>
     </row>
     <row r="26" s="3" customFormat="1" spans="1:13">
-      <c r="A26" s="17">
+      <c r="A26" s="15">
         <v>38</v>
       </c>
-      <c r="B26" s="17">
+      <c r="B26" s="15">
         <v>2</v>
       </c>
-      <c r="C26" s="18">
+      <c r="C26" s="16">
         <v>8</v>
       </c>
-      <c r="D26" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E26" s="17" t="s">
+      <c r="D26" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E26" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="F26" s="17"/>
-      <c r="G26" s="17"/>
-      <c r="H26" s="18"/>
-      <c r="I26" s="18"/>
-      <c r="J26" s="19"/>
-      <c r="K26" s="19"/>
+      <c r="F26" s="15"/>
+      <c r="G26" s="15"/>
+      <c r="H26" s="16"/>
+      <c r="I26" s="16"/>
+      <c r="J26" s="17"/>
+      <c r="K26" s="17"/>
     </row>
     <row r="27" spans="1:13">
-      <c r="A27" s="17">
+      <c r="A27" s="15">
         <v>39</v>
       </c>
-      <c r="B27" s="17">
+      <c r="B27" s="15">
         <v>2</v>
       </c>
-      <c r="C27" s="18">
+      <c r="C27" s="16">
         <v>9</v>
       </c>
-      <c r="D27" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E27" s="17" t="s">
+      <c r="D27" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E27" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="F27" s="17"/>
-      <c r="G27" s="17"/>
-      <c r="H27" s="18"/>
-      <c r="I27" s="18"/>
-      <c r="J27" s="19"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="15"/>
+      <c r="H27" s="16"/>
+      <c r="I27" s="16"/>
+      <c r="J27" s="17"/>
     </row>
     <row r="28" spans="1:13">
-      <c r="A28" s="17">
+      <c r="A28" s="15">
         <v>40</v>
       </c>
-      <c r="B28" s="17">
+      <c r="B28" s="15">
         <v>2</v>
       </c>
-      <c r="C28" s="18">
+      <c r="C28" s="16">
         <v>10</v>
       </c>
-      <c r="D28" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E28" s="17" t="s">
+      <c r="D28" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E28" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="F28" s="17"/>
-      <c r="G28" s="17"/>
-      <c r="H28" s="18"/>
-      <c r="I28" s="18"/>
-      <c r="J28" s="19"/>
+      <c r="F28" s="15"/>
+      <c r="G28" s="15"/>
+      <c r="H28" s="16"/>
+      <c r="I28" s="16"/>
+      <c r="J28" s="17"/>
     </row>
     <row r="29" spans="1:13">
-      <c r="A29" s="17">
+      <c r="A29" s="15">
         <v>41</v>
       </c>
-      <c r="B29" s="17">
+      <c r="B29" s="15">
         <v>2</v>
       </c>
-      <c r="C29" s="18" t="s">
+      <c r="C29" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="D29" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E29" s="17" t="s">
+      <c r="D29" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E29" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="F29" s="17"/>
-      <c r="G29" s="17"/>
-      <c r="H29" s="18"/>
-      <c r="I29" s="18"/>
-      <c r="J29" s="19"/>
+      <c r="F29" s="15"/>
+      <c r="G29" s="15"/>
+      <c r="H29" s="16"/>
+      <c r="I29" s="16"/>
+      <c r="J29" s="17"/>
     </row>
     <row r="30" spans="1:13">
-      <c r="A30" s="17">
+      <c r="A30" s="15">
         <v>42</v>
       </c>
-      <c r="B30" s="17">
+      <c r="B30" s="15">
         <v>2</v>
       </c>
-      <c r="C30" s="18" t="s">
+      <c r="C30" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="D30" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E30" s="17" t="s">
+      <c r="D30" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E30" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="F30" s="17"/>
-      <c r="G30" s="17"/>
-      <c r="H30" s="18"/>
-      <c r="I30" s="18"/>
-      <c r="J30" s="19"/>
+      <c r="F30" s="15"/>
+      <c r="G30" s="15"/>
+      <c r="H30" s="16"/>
+      <c r="I30" s="16"/>
+      <c r="J30" s="17"/>
     </row>
     <row r="31" spans="1:13">
-      <c r="A31" s="17">
+      <c r="A31" s="15">
         <v>43</v>
       </c>
-      <c r="B31" s="17">
+      <c r="B31" s="15">
         <v>2</v>
       </c>
-      <c r="C31" s="18" t="s">
+      <c r="C31" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="D31" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E31" s="17" t="s">
+      <c r="D31" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E31" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="F31" s="17"/>
-      <c r="G31" s="17"/>
-      <c r="H31" s="18"/>
-      <c r="I31" s="18"/>
-      <c r="J31" s="19"/>
+      <c r="F31" s="15"/>
+      <c r="G31" s="15"/>
+      <c r="H31" s="16"/>
+      <c r="I31" s="16"/>
+      <c r="J31" s="17"/>
     </row>
     <row r="32" spans="1:13">
-      <c r="A32" s="17">
+      <c r="A32" s="15">
         <v>44</v>
       </c>
-      <c r="B32" s="17">
+      <c r="B32" s="15">
         <v>2</v>
       </c>
-      <c r="C32" s="18" t="s">
+      <c r="C32" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="D32" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E32" s="17" t="s">
+      <c r="D32" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E32" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="F32" s="17"/>
-      <c r="G32" s="17"/>
-      <c r="H32" s="18"/>
-      <c r="I32" s="18"/>
-      <c r="J32" s="19"/>
+      <c r="F32" s="15"/>
+      <c r="G32" s="15"/>
+      <c r="H32" s="16"/>
+      <c r="I32" s="16"/>
+      <c r="J32" s="17"/>
     </row>
     <row r="33" spans="1:11">
-      <c r="A33" s="17">
+      <c r="A33" s="15">
         <v>61</v>
       </c>
-      <c r="B33" s="17">
+      <c r="B33" s="15">
         <v>3</v>
       </c>
-      <c r="C33" s="18">
+      <c r="C33" s="16">
         <v>1</v>
       </c>
-      <c r="D33" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E33" s="17" t="s">
+      <c r="D33" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E33" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="F33" s="17"/>
-      <c r="G33" s="17" t="s">
+      <c r="F33" s="15"/>
+      <c r="G33" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="H33" s="18"/>
-      <c r="I33" s="18" t="s">
+      <c r="H33" s="16"/>
+      <c r="I33" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="J33" s="19"/>
+      <c r="J33" s="17"/>
     </row>
     <row r="34" spans="1:11">
-      <c r="A34" s="17">
+      <c r="A34" s="15">
         <v>62</v>
       </c>
-      <c r="B34" s="17">
+      <c r="B34" s="15">
         <v>3</v>
       </c>
-      <c r="C34" s="18">
+      <c r="C34" s="16">
         <v>2</v>
       </c>
-      <c r="D34" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E34" s="17" t="s">
+      <c r="D34" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E34" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="F34" s="17"/>
-      <c r="G34" s="17" t="s">
+      <c r="F34" s="15"/>
+      <c r="G34" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="H34" s="18"/>
-      <c r="I34" s="18" t="s">
+      <c r="H34" s="16"/>
+      <c r="I34" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="J34" s="19"/>
+      <c r="J34" s="17"/>
     </row>
     <row r="35" spans="1:11">
-      <c r="A35" s="17">
+      <c r="A35" s="15">
         <v>63</v>
       </c>
-      <c r="B35" s="17">
+      <c r="B35" s="15">
         <v>3</v>
       </c>
-      <c r="C35" s="18">
+      <c r="C35" s="16">
         <v>3</v>
       </c>
-      <c r="D35" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E35" s="17" t="s">
+      <c r="D35" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E35" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="F35" s="17"/>
-      <c r="G35" s="17" t="s">
+      <c r="F35" s="15"/>
+      <c r="G35" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="H35" s="18"/>
-      <c r="I35" s="18" t="s">
+      <c r="H35" s="16"/>
+      <c r="I35" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="J35" s="19"/>
+      <c r="J35" s="17"/>
     </row>
     <row r="36" spans="1:11">
-      <c r="A36" s="17">
+      <c r="A36" s="15">
         <v>64</v>
       </c>
-      <c r="B36" s="17">
+      <c r="B36" s="15">
         <v>3</v>
       </c>
-      <c r="C36" s="18">
+      <c r="C36" s="16">
         <v>4</v>
       </c>
-      <c r="D36" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E36" s="17" t="s">
+      <c r="D36" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E36" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="F36" s="17"/>
-      <c r="G36" s="17"/>
-      <c r="H36" s="18"/>
-      <c r="I36" s="18" t="s">
+      <c r="F36" s="15"/>
+      <c r="G36" s="15"/>
+      <c r="H36" s="16"/>
+      <c r="I36" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="J36" s="19"/>
+      <c r="J36" s="17"/>
     </row>
     <row r="37" spans="1:11">
-      <c r="A37" s="17">
+      <c r="A37" s="15">
         <v>65</v>
       </c>
-      <c r="B37" s="17">
+      <c r="B37" s="15">
         <v>3</v>
       </c>
-      <c r="C37" s="18">
+      <c r="C37" s="16">
         <v>5</v>
       </c>
-      <c r="D37" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E37" s="17" t="s">
+      <c r="D37" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E37" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="F37" s="17"/>
-      <c r="G37" s="17"/>
-      <c r="H37" s="18"/>
-      <c r="I37" s="18"/>
-      <c r="J37" s="19"/>
+      <c r="F37" s="15"/>
+      <c r="G37" s="15"/>
+      <c r="H37" s="16"/>
+      <c r="I37" s="16"/>
+      <c r="J37" s="17"/>
     </row>
     <row r="38" spans="1:11">
-      <c r="A38" s="17">
+      <c r="A38" s="15">
         <v>66</v>
       </c>
-      <c r="B38" s="17">
+      <c r="B38" s="15">
         <v>3</v>
       </c>
-      <c r="C38" s="18">
+      <c r="C38" s="16">
         <v>6</v>
       </c>
-      <c r="D38" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E38" s="17" t="s">
+      <c r="D38" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E38" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="F38" s="17"/>
-      <c r="G38" s="17"/>
-      <c r="H38" s="18"/>
-      <c r="I38" s="18"/>
-      <c r="J38" s="19"/>
+      <c r="F38" s="15"/>
+      <c r="G38" s="15"/>
+      <c r="H38" s="16"/>
+      <c r="I38" s="16"/>
+      <c r="J38" s="17"/>
     </row>
     <row r="39" spans="1:11">
-      <c r="A39" s="17">
+      <c r="A39" s="15">
         <v>67</v>
       </c>
-      <c r="B39" s="17">
+      <c r="B39" s="15">
         <v>3</v>
       </c>
-      <c r="C39" s="18">
+      <c r="C39" s="16">
         <v>7</v>
       </c>
-      <c r="D39" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E39" s="17" t="s">
+      <c r="D39" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E39" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="F39" s="17"/>
-      <c r="G39" s="17"/>
-      <c r="H39" s="18"/>
-      <c r="I39" s="18"/>
-      <c r="J39" s="19"/>
+      <c r="F39" s="15"/>
+      <c r="G39" s="15"/>
+      <c r="H39" s="16"/>
+      <c r="I39" s="16"/>
+      <c r="J39" s="17"/>
     </row>
     <row r="40" spans="1:11">
-      <c r="A40" s="17">
+      <c r="A40" s="15">
         <v>68</v>
       </c>
-      <c r="B40" s="17">
+      <c r="B40" s="15">
         <v>3</v>
       </c>
-      <c r="C40" s="18">
+      <c r="C40" s="16">
         <v>8</v>
       </c>
-      <c r="D40" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E40" s="17" t="s">
+      <c r="D40" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E40" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="F40" s="17"/>
-      <c r="G40" s="17"/>
-      <c r="H40" s="18"/>
-      <c r="I40" s="18"/>
-      <c r="J40" s="19"/>
+      <c r="F40" s="15"/>
+      <c r="G40" s="15"/>
+      <c r="H40" s="16"/>
+      <c r="I40" s="16"/>
+      <c r="J40" s="17"/>
     </row>
     <row r="41" spans="1:11">
-      <c r="A41" s="17">
+      <c r="A41" s="15">
         <v>69</v>
       </c>
-      <c r="B41" s="17">
+      <c r="B41" s="15">
         <v>3</v>
       </c>
-      <c r="C41" s="18">
+      <c r="C41" s="16">
         <v>9</v>
       </c>
-      <c r="D41" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E41" s="17" t="s">
+      <c r="D41" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E41" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="F41" s="17"/>
-      <c r="G41" s="17"/>
-      <c r="H41" s="18"/>
-      <c r="I41" s="18"/>
-      <c r="J41" s="19"/>
+      <c r="F41" s="15"/>
+      <c r="G41" s="15"/>
+      <c r="H41" s="16"/>
+      <c r="I41" s="16"/>
+      <c r="J41" s="17"/>
     </row>
     <row r="42" spans="1:11">
-      <c r="A42" s="17">
+      <c r="A42" s="15">
         <v>70</v>
       </c>
-      <c r="B42" s="17">
+      <c r="B42" s="15">
         <v>3</v>
       </c>
-      <c r="C42" s="18">
+      <c r="C42" s="16">
         <v>10</v>
       </c>
-      <c r="D42" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E42" s="17" t="s">
+      <c r="D42" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E42" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="F42" s="17"/>
-      <c r="G42" s="17"/>
-      <c r="H42" s="18"/>
-      <c r="I42" s="18"/>
-      <c r="J42" s="19"/>
+      <c r="F42" s="15"/>
+      <c r="G42" s="15"/>
+      <c r="H42" s="16"/>
+      <c r="I42" s="16"/>
+      <c r="J42" s="17"/>
     </row>
     <row r="43" spans="1:11">
-      <c r="A43" s="17">
-        <v>71</v>
-      </c>
-      <c r="B43" s="17">
+      <c r="A43" s="15">
+        <v>71</v>
+      </c>
+      <c r="B43" s="15">
         <v>3</v>
       </c>
-      <c r="C43" s="18" t="s">
+      <c r="C43" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="D43" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E43" s="17" t="s">
+      <c r="D43" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E43" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="F43" s="17"/>
-      <c r="G43" s="17"/>
-      <c r="H43" s="18"/>
-      <c r="I43" s="18"/>
-      <c r="J43" s="19"/>
+      <c r="F43" s="15"/>
+      <c r="G43" s="15"/>
+      <c r="H43" s="16"/>
+      <c r="I43" s="16"/>
+      <c r="J43" s="17"/>
     </row>
     <row r="44" spans="1:11">
-      <c r="A44" s="17">
+      <c r="A44" s="15">
         <v>72</v>
       </c>
-      <c r="B44" s="17">
+      <c r="B44" s="15">
         <v>3</v>
       </c>
-      <c r="C44" s="18" t="s">
+      <c r="C44" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="D44" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E44" s="17" t="s">
+      <c r="D44" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E44" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="F44" s="17"/>
-      <c r="G44" s="17"/>
-      <c r="H44" s="18"/>
-      <c r="I44" s="18"/>
+      <c r="F44" s="15"/>
+      <c r="G44" s="15"/>
+      <c r="H44" s="16"/>
+      <c r="I44" s="16"/>
     </row>
     <row r="45" spans="1:11">
-      <c r="A45" s="17">
+      <c r="A45" s="15">
         <v>73</v>
       </c>
-      <c r="B45" s="17">
+      <c r="B45" s="15">
         <v>3</v>
       </c>
-      <c r="C45" s="18" t="s">
+      <c r="C45" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="D45" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E45" s="17" t="s">
+      <c r="D45" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E45" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="F45" s="17"/>
-      <c r="G45" s="17"/>
-      <c r="H45" s="18"/>
-      <c r="I45" s="18"/>
+      <c r="F45" s="15"/>
+      <c r="G45" s="15"/>
+      <c r="H45" s="16"/>
+      <c r="I45" s="16"/>
     </row>
     <row r="46" spans="1:11">
-      <c r="A46" s="17">
+      <c r="A46" s="15">
         <v>74</v>
       </c>
-      <c r="B46" s="17">
+      <c r="B46" s="15">
         <v>3</v>
       </c>
-      <c r="C46" s="18" t="s">
+      <c r="C46" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="D46" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E46" s="17" t="s">
+      <c r="D46" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E46" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="F46" s="17"/>
-      <c r="G46" s="17"/>
-      <c r="H46" s="18"/>
-      <c r="I46" s="18"/>
+      <c r="F46" s="15"/>
+      <c r="G46" s="15"/>
+      <c r="H46" s="16"/>
+      <c r="I46" s="16"/>
     </row>
     <row r="47" s="2" customFormat="1" spans="1:11">
-      <c r="A47" s="21">
+      <c r="A47" s="19">
         <v>101</v>
       </c>
-      <c r="B47" s="21">
+      <c r="B47" s="19">
         <v>1</v>
       </c>
-      <c r="C47" s="22">
+      <c r="C47" s="20">
         <v>1</v>
       </c>
-      <c r="D47" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="E47" s="17" t="s">
+      <c r="D47" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="E47" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="F47" s="21">
+      <c r="F47" s="19">
         <v>33333333</v>
       </c>
-      <c r="G47" s="21" t="s">
+      <c r="G47" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="H47" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="I47" s="22" t="s">
+      <c r="H47" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I47" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="J47" s="19"/>
-      <c r="K47" s="19"/>
+      <c r="J47" s="17"/>
+      <c r="K47" s="17"/>
     </row>
     <row r="48" s="2" customFormat="1" spans="1:11">
-      <c r="A48" s="21">
+      <c r="A48" s="19">
         <v>102</v>
       </c>
-      <c r="B48" s="21">
+      <c r="B48" s="19">
         <v>1</v>
       </c>
-      <c r="C48" s="22">
+      <c r="C48" s="20">
         <v>2</v>
       </c>
-      <c r="D48" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="E48" s="17" t="s">
+      <c r="D48" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="E48" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="F48" s="21">
+      <c r="F48" s="19">
         <v>22222222</v>
       </c>
-      <c r="G48" s="21" t="s">
+      <c r="G48" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="H48" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="I48" s="22" t="s">
+      <c r="H48" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I48" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="J48" s="19"/>
-      <c r="K48" s="19"/>
+      <c r="J48" s="17"/>
+      <c r="K48" s="17"/>
     </row>
     <row r="49" s="2" customFormat="1" spans="1:13">
-      <c r="A49" s="21">
+      <c r="A49" s="19">
         <v>103</v>
       </c>
-      <c r="B49" s="21">
+      <c r="B49" s="19">
         <v>1</v>
       </c>
-      <c r="C49" s="22">
+      <c r="C49" s="20">
         <v>3</v>
       </c>
-      <c r="D49" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="E49" s="17" t="s">
+      <c r="D49" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="E49" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="F49" s="21">
+      <c r="F49" s="19">
         <v>11111111</v>
       </c>
-      <c r="G49" s="21" t="s">
+      <c r="G49" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="H49" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="I49" s="22" t="s">
+      <c r="H49" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I49" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="J49" s="19"/>
-      <c r="K49" s="19"/>
+      <c r="J49" s="17"/>
+      <c r="K49" s="17"/>
     </row>
     <row r="50" s="2" customFormat="1" spans="1:13">
-      <c r="A50" s="21">
+      <c r="A50" s="19">
         <v>104</v>
       </c>
-      <c r="B50" s="21">
+      <c r="B50" s="19">
         <v>1</v>
       </c>
-      <c r="C50" s="22">
+      <c r="C50" s="20">
         <v>4</v>
       </c>
-      <c r="D50" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="E50" s="17" t="s">
+      <c r="D50" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="E50" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="F50" s="21">
+      <c r="F50" s="19">
         <v>5000000</v>
       </c>
-      <c r="G50" s="21" t="s">
+      <c r="G50" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="H50" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="I50" s="22" t="s">
+      <c r="H50" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I50" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="J50" s="19"/>
-      <c r="K50" s="19"/>
+      <c r="J50" s="17"/>
+      <c r="K50" s="17"/>
     </row>
     <row r="51" s="3" customFormat="1" spans="1:13">
-      <c r="A51" s="21">
+      <c r="A51" s="19">
         <v>105</v>
       </c>
-      <c r="B51" s="21">
+      <c r="B51" s="19">
         <v>1</v>
       </c>
-      <c r="C51" s="22">
+      <c r="C51" s="20">
         <v>5</v>
       </c>
-      <c r="D51" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="E51" s="17" t="s">
+      <c r="D51" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="E51" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="F51" s="21">
+      <c r="F51" s="19">
         <v>3000000</v>
       </c>
-      <c r="G51" s="21" t="s">
+      <c r="G51" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="H51" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="I51" s="22" t="s">
+      <c r="H51" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I51" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="J51" s="19"/>
-      <c r="K51" s="20"/>
+      <c r="J51" s="17"/>
+      <c r="K51" s="18"/>
       <c r="M51" s="2"/>
     </row>
     <row r="52" s="3" customFormat="1" spans="1:13">
-      <c r="A52" s="21">
+      <c r="A52" s="19">
         <v>106</v>
       </c>
-      <c r="B52" s="21">
+      <c r="B52" s="19">
         <v>1</v>
       </c>
-      <c r="C52" s="22">
+      <c r="C52" s="20">
         <v>6</v>
       </c>
-      <c r="D52" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="E52" s="17" t="s">
+      <c r="D52" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="E52" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="F52" s="21"/>
-      <c r="G52" s="21"/>
-      <c r="H52" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="I52" s="22"/>
-      <c r="J52" s="19"/>
-      <c r="K52" s="20"/>
+      <c r="F52" s="19"/>
+      <c r="G52" s="19"/>
+      <c r="H52" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I52" s="20"/>
+      <c r="J52" s="17"/>
+      <c r="K52" s="18"/>
       <c r="M52" s="2"/>
     </row>
     <row r="53" s="3" customFormat="1" spans="1:13">
-      <c r="A53" s="21">
+      <c r="A53" s="19">
         <v>107</v>
       </c>
-      <c r="B53" s="21">
+      <c r="B53" s="19">
         <v>1</v>
       </c>
-      <c r="C53" s="22">
+      <c r="C53" s="20">
         <v>7</v>
       </c>
-      <c r="D53" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="E53" s="17" t="s">
+      <c r="D53" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="E53" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="F53" s="21"/>
-      <c r="G53" s="21"/>
-      <c r="H53" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="I53" s="22"/>
-      <c r="J53" s="19"/>
-      <c r="K53" s="20"/>
+      <c r="F53" s="19"/>
+      <c r="G53" s="19"/>
+      <c r="H53" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I53" s="20"/>
+      <c r="J53" s="17"/>
+      <c r="K53" s="18"/>
       <c r="M53" s="2"/>
     </row>
     <row r="54" s="3" customFormat="1" spans="1:13">
-      <c r="A54" s="21">
+      <c r="A54" s="19">
         <v>108</v>
       </c>
-      <c r="B54" s="21">
+      <c r="B54" s="19">
         <v>1</v>
       </c>
-      <c r="C54" s="22">
+      <c r="C54" s="20">
         <v>8</v>
       </c>
-      <c r="D54" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="E54" s="17" t="s">
+      <c r="D54" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="E54" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="F54" s="21"/>
-      <c r="G54" s="21"/>
-      <c r="H54" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="I54" s="22"/>
-      <c r="J54" s="19"/>
-      <c r="K54" s="20"/>
+      <c r="F54" s="19"/>
+      <c r="G54" s="19"/>
+      <c r="H54" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I54" s="20"/>
+      <c r="J54" s="17"/>
+      <c r="K54" s="18"/>
       <c r="M54" s="2"/>
     </row>
     <row r="55" spans="1:13">
-      <c r="A55" s="21">
+      <c r="A55" s="19">
         <v>109</v>
       </c>
-      <c r="B55" s="21">
+      <c r="B55" s="19">
         <v>1</v>
       </c>
-      <c r="C55" s="22">
+      <c r="C55" s="20">
         <v>9</v>
       </c>
-      <c r="D55" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="E55" s="17" t="s">
+      <c r="D55" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="E55" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="F55" s="21"/>
-      <c r="G55" s="21"/>
-      <c r="H55" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="I55" s="22"/>
-      <c r="J55" s="19"/>
+      <c r="F55" s="19"/>
+      <c r="G55" s="19"/>
+      <c r="H55" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I55" s="20"/>
+      <c r="J55" s="17"/>
       <c r="M55" s="2"/>
     </row>
     <row r="56" spans="1:13">
-      <c r="A56" s="21">
+      <c r="A56" s="19">
         <v>110</v>
       </c>
-      <c r="B56" s="21">
+      <c r="B56" s="19">
         <v>1</v>
       </c>
-      <c r="C56" s="22">
+      <c r="C56" s="20">
         <v>10</v>
       </c>
-      <c r="D56" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="E56" s="17" t="s">
+      <c r="D56" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="E56" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="F56" s="21"/>
-      <c r="G56" s="21"/>
-      <c r="H56" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="I56" s="22"/>
-      <c r="J56" s="19"/>
+      <c r="F56" s="19"/>
+      <c r="G56" s="19"/>
+      <c r="H56" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I56" s="20"/>
+      <c r="J56" s="17"/>
       <c r="M56" s="2"/>
     </row>
     <row r="57" customFormat="1" spans="1:13">
-      <c r="A57" s="21">
+      <c r="A57" s="19">
         <v>111</v>
       </c>
-      <c r="B57" s="21">
+      <c r="B57" s="19">
         <v>1</v>
       </c>
-      <c r="C57" s="22" t="s">
+      <c r="C57" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="D57" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="E57" s="17" t="s">
+      <c r="D57" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="E57" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="F57" s="21"/>
-      <c r="G57" s="21"/>
-      <c r="H57" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="I57" s="22"/>
-      <c r="J57" s="19"/>
+      <c r="F57" s="19"/>
+      <c r="G57" s="19"/>
+      <c r="H57" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I57" s="20"/>
+      <c r="J57" s="17"/>
       <c r="K57" s="8"/>
       <c r="M57" s="2"/>
     </row>
     <row r="58" s="3" customFormat="1" spans="1:13">
-      <c r="A58" s="21">
+      <c r="A58" s="19">
         <v>112</v>
       </c>
-      <c r="B58" s="21">
+      <c r="B58" s="19">
         <v>1</v>
       </c>
-      <c r="C58" s="22" t="s">
+      <c r="C58" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="D58" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="E58" s="17" t="s">
+      <c r="D58" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="E58" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="F58" s="21"/>
-      <c r="G58" s="21"/>
-      <c r="H58" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="I58" s="22"/>
-      <c r="J58" s="19"/>
-      <c r="K58" s="20"/>
+      <c r="F58" s="19"/>
+      <c r="G58" s="19"/>
+      <c r="H58" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I58" s="20"/>
+      <c r="J58" s="17"/>
+      <c r="K58" s="18"/>
       <c r="M58" s="2"/>
     </row>
     <row r="59" s="3" customFormat="1" spans="1:13">
-      <c r="A59" s="21">
+      <c r="A59" s="19">
         <v>113</v>
       </c>
-      <c r="B59" s="21">
+      <c r="B59" s="19">
         <v>1</v>
       </c>
-      <c r="C59" s="22" t="s">
+      <c r="C59" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="D59" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="E59" s="17" t="s">
+      <c r="D59" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="E59" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="F59" s="21"/>
-      <c r="G59" s="21"/>
-      <c r="H59" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="I59" s="22"/>
-      <c r="J59" s="19"/>
-      <c r="K59" s="20"/>
+      <c r="F59" s="19"/>
+      <c r="G59" s="19"/>
+      <c r="H59" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I59" s="20"/>
+      <c r="J59" s="17"/>
+      <c r="K59" s="18"/>
       <c r="M59" s="2"/>
     </row>
     <row r="60" s="3" customFormat="1" spans="1:13">
-      <c r="A60" s="21">
+      <c r="A60" s="19">
         <v>114</v>
       </c>
-      <c r="B60" s="21">
+      <c r="B60" s="19">
         <v>1</v>
       </c>
-      <c r="C60" s="22" t="s">
+      <c r="C60" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="D60" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="E60" s="17" t="s">
+      <c r="D60" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="E60" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="F60" s="21"/>
-      <c r="G60" s="21"/>
-      <c r="H60" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="I60" s="22"/>
-      <c r="J60" s="19"/>
-      <c r="K60" s="20"/>
+      <c r="F60" s="19"/>
+      <c r="G60" s="19"/>
+      <c r="H60" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I60" s="20"/>
+      <c r="J60" s="17"/>
+      <c r="K60" s="18"/>
       <c r="M60" s="2"/>
     </row>
     <row r="61" s="3" customFormat="1" spans="1:13">
-      <c r="A61" s="21">
+      <c r="A61" s="19">
         <v>131</v>
       </c>
-      <c r="B61" s="21">
+      <c r="B61" s="19">
         <v>2</v>
       </c>
-      <c r="C61" s="22">
+      <c r="C61" s="20">
         <v>1</v>
       </c>
-      <c r="D61" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="E61" s="17" t="s">
+      <c r="D61" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="E61" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="F61" s="21">
+      <c r="F61" s="19">
         <v>33333333</v>
       </c>
-      <c r="G61" s="21" t="s">
+      <c r="G61" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="H61" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="I61" s="22" t="s">
+      <c r="H61" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I61" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="J61" s="19"/>
-      <c r="K61" s="20"/>
+      <c r="J61" s="17"/>
+      <c r="K61" s="18"/>
       <c r="M61" s="2"/>
     </row>
     <row r="62" s="3" customFormat="1" spans="1:13">
-      <c r="A62" s="21">
+      <c r="A62" s="19">
         <v>132</v>
       </c>
-      <c r="B62" s="21">
+      <c r="B62" s="19">
         <v>2</v>
       </c>
-      <c r="C62" s="22">
+      <c r="C62" s="20">
         <v>2</v>
       </c>
-      <c r="D62" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="E62" s="17" t="s">
+      <c r="D62" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="E62" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="F62" s="21">
+      <c r="F62" s="19">
         <v>22222222</v>
       </c>
-      <c r="G62" s="21" t="s">
+      <c r="G62" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="H62" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="I62" s="22" t="s">
+      <c r="H62" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I62" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="J62" s="19"/>
-      <c r="K62" s="19"/>
+      <c r="J62" s="17"/>
+      <c r="K62" s="17"/>
       <c r="M62" s="2"/>
     </row>
     <row r="63" spans="1:13">
-      <c r="A63" s="21">
+      <c r="A63" s="19">
         <v>133</v>
       </c>
-      <c r="B63" s="21">
+      <c r="B63" s="19">
         <v>2</v>
       </c>
-      <c r="C63" s="22">
+      <c r="C63" s="20">
         <v>3</v>
       </c>
-      <c r="D63" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="E63" s="17" t="s">
+      <c r="D63" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="E63" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="F63" s="21">
+      <c r="F63" s="19">
         <v>11111111</v>
       </c>
-      <c r="G63" s="21" t="s">
+      <c r="G63" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="H63" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="I63" s="22" t="s">
+      <c r="H63" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I63" s="20" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="64" s="3" customFormat="1" spans="1:13">
-      <c r="A64" s="21">
+      <c r="A64" s="19">
         <v>134</v>
       </c>
-      <c r="B64" s="21">
+      <c r="B64" s="19">
         <v>2</v>
       </c>
-      <c r="C64" s="22">
+      <c r="C64" s="20">
         <v>4</v>
       </c>
-      <c r="D64" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="E64" s="17" t="s">
+      <c r="D64" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="E64" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="F64" s="21">
+      <c r="F64" s="19">
         <v>5000000</v>
       </c>
-      <c r="G64" s="21" t="s">
+      <c r="G64" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="H64" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="I64" s="22" t="s">
+      <c r="H64" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I64" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="J64" s="19"/>
-      <c r="K64" s="20"/>
+      <c r="J64" s="17"/>
+      <c r="K64" s="18"/>
     </row>
     <row r="65" s="3" customFormat="1" spans="1:11">
-      <c r="A65" s="21">
+      <c r="A65" s="19">
         <v>135</v>
       </c>
-      <c r="B65" s="21">
+      <c r="B65" s="19">
         <v>2</v>
       </c>
-      <c r="C65" s="22">
+      <c r="C65" s="20">
         <v>5</v>
       </c>
-      <c r="D65" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="E65" s="17" t="s">
+      <c r="D65" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="E65" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="F65" s="21">
+      <c r="F65" s="19">
         <v>3000000</v>
       </c>
-      <c r="G65" s="21" t="s">
+      <c r="G65" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="H65" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="I65" s="22" t="s">
+      <c r="H65" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I65" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="J65" s="19"/>
-      <c r="K65" s="20"/>
+      <c r="J65" s="17"/>
+      <c r="K65" s="18"/>
     </row>
     <row r="66" s="3" customFormat="1" spans="1:11">
-      <c r="A66" s="21">
+      <c r="A66" s="19">
         <v>136</v>
       </c>
-      <c r="B66" s="21">
+      <c r="B66" s="19">
         <v>2</v>
       </c>
-      <c r="C66" s="22">
+      <c r="C66" s="20">
         <v>6</v>
       </c>
-      <c r="D66" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="E66" s="17" t="s">
+      <c r="D66" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="E66" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="F66" s="21"/>
-      <c r="G66" s="21"/>
-      <c r="H66" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="I66" s="22"/>
-      <c r="J66" s="19"/>
-      <c r="K66" s="20"/>
+      <c r="F66" s="19"/>
+      <c r="G66" s="19"/>
+      <c r="H66" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I66" s="20"/>
+      <c r="J66" s="17"/>
+      <c r="K66" s="18"/>
     </row>
     <row r="67" s="3" customFormat="1" spans="1:11">
-      <c r="A67" s="21">
+      <c r="A67" s="19">
         <v>137</v>
       </c>
-      <c r="B67" s="21">
+      <c r="B67" s="19">
         <v>2</v>
       </c>
-      <c r="C67" s="22">
+      <c r="C67" s="20">
         <v>7</v>
       </c>
-      <c r="D67" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="E67" s="17" t="s">
+      <c r="D67" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="E67" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="F67" s="21"/>
-      <c r="G67" s="21"/>
-      <c r="H67" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="I67" s="22"/>
-      <c r="J67" s="19"/>
-      <c r="K67" s="20"/>
+      <c r="F67" s="19"/>
+      <c r="G67" s="19"/>
+      <c r="H67" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I67" s="20"/>
+      <c r="J67" s="17"/>
+      <c r="K67" s="18"/>
     </row>
     <row r="68" s="3" customFormat="1" spans="1:11">
-      <c r="A68" s="21">
+      <c r="A68" s="19">
         <v>138</v>
       </c>
-      <c r="B68" s="21">
+      <c r="B68" s="19">
         <v>2</v>
       </c>
-      <c r="C68" s="22">
+      <c r="C68" s="20">
         <v>8</v>
       </c>
-      <c r="D68" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="E68" s="17" t="s">
+      <c r="D68" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="E68" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="F68" s="21"/>
-      <c r="G68" s="21"/>
-      <c r="H68" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="I68" s="22"/>
-      <c r="J68" s="19"/>
-      <c r="K68" s="19"/>
+      <c r="F68" s="19"/>
+      <c r="G68" s="19"/>
+      <c r="H68" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I68" s="20"/>
+      <c r="J68" s="17"/>
+      <c r="K68" s="17"/>
     </row>
     <row r="69" spans="1:11">
-      <c r="A69" s="21">
+      <c r="A69" s="19">
         <v>139</v>
       </c>
-      <c r="B69" s="21">
+      <c r="B69" s="19">
         <v>2</v>
       </c>
-      <c r="C69" s="22">
+      <c r="C69" s="20">
         <v>9</v>
       </c>
-      <c r="D69" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="E69" s="17" t="s">
+      <c r="D69" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="E69" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="F69" s="21"/>
-      <c r="G69" s="21"/>
-      <c r="H69" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="I69" s="22"/>
-      <c r="J69" s="19"/>
+      <c r="F69" s="19"/>
+      <c r="G69" s="19"/>
+      <c r="H69" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I69" s="20"/>
+      <c r="J69" s="17"/>
     </row>
     <row r="70" spans="1:11">
-      <c r="A70" s="21">
+      <c r="A70" s="19">
         <v>140</v>
       </c>
-      <c r="B70" s="21">
+      <c r="B70" s="19">
         <v>2</v>
       </c>
-      <c r="C70" s="22">
+      <c r="C70" s="20">
         <v>10</v>
       </c>
-      <c r="D70" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="E70" s="17" t="s">
+      <c r="D70" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="E70" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="F70" s="21"/>
-      <c r="G70" s="21"/>
-      <c r="H70" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="I70" s="22"/>
-      <c r="J70" s="19"/>
+      <c r="F70" s="19"/>
+      <c r="G70" s="19"/>
+      <c r="H70" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I70" s="20"/>
+      <c r="J70" s="17"/>
     </row>
     <row r="71" spans="1:11">
-      <c r="A71" s="21">
+      <c r="A71" s="19">
         <v>141</v>
       </c>
-      <c r="B71" s="21">
+      <c r="B71" s="19">
         <v>2</v>
       </c>
-      <c r="C71" s="22" t="s">
+      <c r="C71" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="D71" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="E71" s="17" t="s">
+      <c r="D71" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="E71" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="F71" s="21"/>
-      <c r="G71" s="21"/>
-      <c r="H71" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="I71" s="22"/>
-      <c r="J71" s="19"/>
+      <c r="F71" s="19"/>
+      <c r="G71" s="19"/>
+      <c r="H71" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I71" s="20"/>
+      <c r="J71" s="17"/>
     </row>
     <row r="72" spans="1:11">
-      <c r="A72" s="21">
+      <c r="A72" s="19">
         <v>142</v>
       </c>
-      <c r="B72" s="21">
+      <c r="B72" s="19">
         <v>2</v>
       </c>
-      <c r="C72" s="22" t="s">
+      <c r="C72" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="D72" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="E72" s="17" t="s">
+      <c r="D72" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="E72" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="F72" s="21"/>
-      <c r="G72" s="21"/>
-      <c r="H72" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="I72" s="22"/>
-      <c r="J72" s="19"/>
+      <c r="F72" s="19"/>
+      <c r="G72" s="19"/>
+      <c r="H72" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I72" s="20"/>
+      <c r="J72" s="17"/>
     </row>
     <row r="73" spans="1:11">
-      <c r="A73" s="21">
+      <c r="A73" s="19">
         <v>143</v>
       </c>
-      <c r="B73" s="21">
+      <c r="B73" s="19">
         <v>2</v>
       </c>
-      <c r="C73" s="22" t="s">
+      <c r="C73" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="D73" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="E73" s="17" t="s">
+      <c r="D73" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="E73" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="F73" s="21"/>
-      <c r="G73" s="21"/>
-      <c r="H73" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="I73" s="22"/>
-      <c r="J73" s="19"/>
+      <c r="F73" s="19"/>
+      <c r="G73" s="19"/>
+      <c r="H73" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I73" s="20"/>
+      <c r="J73" s="17"/>
     </row>
     <row r="74" spans="1:11">
-      <c r="A74" s="21">
+      <c r="A74" s="19">
         <v>144</v>
       </c>
-      <c r="B74" s="21">
+      <c r="B74" s="19">
         <v>2</v>
       </c>
-      <c r="C74" s="22" t="s">
+      <c r="C74" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="D74" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="E74" s="17" t="s">
+      <c r="D74" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="E74" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="F74" s="21"/>
-      <c r="G74" s="21"/>
-      <c r="H74" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="I74" s="22"/>
-      <c r="J74" s="19"/>
+      <c r="F74" s="19"/>
+      <c r="G74" s="19"/>
+      <c r="H74" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I74" s="20"/>
+      <c r="J74" s="17"/>
     </row>
     <row r="75" spans="1:11">
-      <c r="A75" s="21">
+      <c r="A75" s="19">
         <v>161</v>
       </c>
-      <c r="B75" s="21">
+      <c r="B75" s="19">
         <v>3</v>
       </c>
-      <c r="C75" s="22">
+      <c r="C75" s="20">
         <v>1</v>
       </c>
-      <c r="D75" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="E75" s="17" t="s">
+      <c r="D75" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="E75" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="F75" s="21">
+      <c r="F75" s="19">
         <v>99999999</v>
       </c>
-      <c r="G75" s="21" t="s">
+      <c r="G75" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="H75" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="I75" s="22" t="s">
+      <c r="H75" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I75" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="J75" s="19"/>
+      <c r="J75" s="17"/>
     </row>
     <row r="76" spans="1:11">
-      <c r="A76" s="21">
+      <c r="A76" s="19">
         <v>162</v>
       </c>
-      <c r="B76" s="21">
+      <c r="B76" s="19">
         <v>3</v>
       </c>
-      <c r="C76" s="22">
+      <c r="C76" s="20">
         <v>2</v>
       </c>
-      <c r="D76" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="E76" s="17" t="s">
+      <c r="D76" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="E76" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="F76" s="21">
+      <c r="F76" s="19">
         <v>88888888</v>
       </c>
-      <c r="G76" s="21" t="s">
+      <c r="G76" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="H76" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="I76" s="22" t="s">
+      <c r="H76" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I76" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="J76" s="19"/>
+      <c r="J76" s="17"/>
     </row>
     <row r="77" spans="1:11">
-      <c r="A77" s="21">
+      <c r="A77" s="19">
         <v>163</v>
       </c>
-      <c r="B77" s="21">
+      <c r="B77" s="19">
         <v>3</v>
       </c>
-      <c r="C77" s="22">
+      <c r="C77" s="20">
         <v>3</v>
       </c>
-      <c r="D77" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="E77" s="17" t="s">
+      <c r="D77" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="E77" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="F77" s="21">
+      <c r="F77" s="19">
         <v>77777777</v>
       </c>
-      <c r="G77" s="21" t="s">
+      <c r="G77" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="H77" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="I77" s="22" t="s">
+      <c r="H77" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I77" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="J77" s="19"/>
+      <c r="J77" s="17"/>
     </row>
     <row r="78" spans="1:11">
-      <c r="A78" s="21">
+      <c r="A78" s="19">
         <v>164</v>
       </c>
-      <c r="B78" s="21">
+      <c r="B78" s="19">
         <v>3</v>
       </c>
-      <c r="C78" s="22">
+      <c r="C78" s="20">
         <v>4</v>
       </c>
-      <c r="D78" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="E78" s="17" t="s">
+      <c r="D78" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="E78" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="F78" s="21">
+      <c r="F78" s="19">
         <v>66666666</v>
       </c>
-      <c r="G78" s="21" t="s">
+      <c r="G78" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="H78" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="I78" s="22" t="s">
+      <c r="H78" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I78" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="J78" s="19"/>
+      <c r="J78" s="17"/>
     </row>
     <row r="79" spans="1:11">
-      <c r="A79" s="21">
+      <c r="A79" s="19">
         <v>165</v>
       </c>
-      <c r="B79" s="21">
+      <c r="B79" s="19">
         <v>3</v>
       </c>
-      <c r="C79" s="22">
+      <c r="C79" s="20">
         <v>5</v>
       </c>
-      <c r="D79" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="E79" s="17" t="s">
+      <c r="D79" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="E79" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="F79" s="21">
+      <c r="F79" s="19">
         <v>55555555</v>
       </c>
-      <c r="G79" s="21" t="s">
+      <c r="G79" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="H79" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="I79" s="22" t="s">
+      <c r="H79" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I79" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="J79" s="19"/>
+      <c r="J79" s="17"/>
     </row>
     <row r="80" spans="1:11">
-      <c r="A80" s="21">
+      <c r="A80" s="19">
         <v>166</v>
       </c>
-      <c r="B80" s="21">
+      <c r="B80" s="19">
         <v>3</v>
       </c>
-      <c r="C80" s="22">
+      <c r="C80" s="20">
         <v>6</v>
       </c>
-      <c r="D80" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="E80" s="17" t="s">
+      <c r="D80" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="E80" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="F80" s="21"/>
-      <c r="G80" s="21"/>
-      <c r="H80" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="I80" s="22"/>
-      <c r="J80" s="19"/>
+      <c r="F80" s="19"/>
+      <c r="G80" s="19"/>
+      <c r="H80" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I80" s="20"/>
+      <c r="J80" s="17"/>
     </row>
     <row r="81" spans="1:10">
-      <c r="A81" s="21">
+      <c r="A81" s="19">
         <v>167</v>
       </c>
-      <c r="B81" s="21">
+      <c r="B81" s="19">
         <v>3</v>
       </c>
-      <c r="C81" s="22">
+      <c r="C81" s="20">
         <v>7</v>
       </c>
-      <c r="D81" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="E81" s="17" t="s">
+      <c r="D81" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="E81" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="F81" s="21"/>
-      <c r="G81" s="21"/>
-      <c r="H81" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="I81" s="22"/>
-      <c r="J81" s="19"/>
+      <c r="F81" s="19"/>
+      <c r="G81" s="19"/>
+      <c r="H81" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I81" s="20"/>
+      <c r="J81" s="17"/>
     </row>
     <row r="82" spans="1:10">
-      <c r="A82" s="21">
+      <c r="A82" s="19">
         <v>168</v>
       </c>
-      <c r="B82" s="21">
+      <c r="B82" s="19">
         <v>3</v>
       </c>
-      <c r="C82" s="22">
+      <c r="C82" s="20">
         <v>8</v>
       </c>
-      <c r="D82" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="E82" s="17" t="s">
+      <c r="D82" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="E82" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="F82" s="21"/>
-      <c r="G82" s="21"/>
-      <c r="H82" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="I82" s="22"/>
-      <c r="J82" s="19"/>
+      <c r="F82" s="19"/>
+      <c r="G82" s="19"/>
+      <c r="H82" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I82" s="20"/>
+      <c r="J82" s="17"/>
     </row>
     <row r="83" spans="1:10">
-      <c r="A83" s="21">
+      <c r="A83" s="19">
         <v>169</v>
       </c>
-      <c r="B83" s="21">
+      <c r="B83" s="19">
         <v>3</v>
       </c>
-      <c r="C83" s="22">
+      <c r="C83" s="20">
         <v>9</v>
       </c>
-      <c r="D83" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="E83" s="17" t="s">
+      <c r="D83" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="E83" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="F83" s="21"/>
-      <c r="G83" s="21"/>
-      <c r="H83" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="I83" s="22"/>
-      <c r="J83" s="19"/>
+      <c r="F83" s="19"/>
+      <c r="G83" s="19"/>
+      <c r="H83" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I83" s="20"/>
+      <c r="J83" s="17"/>
     </row>
     <row r="84" spans="1:10">
-      <c r="A84" s="21">
+      <c r="A84" s="19">
         <v>170</v>
       </c>
-      <c r="B84" s="21">
+      <c r="B84" s="19">
         <v>3</v>
       </c>
-      <c r="C84" s="22">
+      <c r="C84" s="20">
         <v>10</v>
       </c>
-      <c r="D84" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="E84" s="17" t="s">
+      <c r="D84" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="E84" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="F84" s="21"/>
-      <c r="G84" s="21"/>
-      <c r="H84" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="I84" s="22"/>
-      <c r="J84" s="19"/>
+      <c r="F84" s="19"/>
+      <c r="G84" s="19"/>
+      <c r="H84" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I84" s="20"/>
+      <c r="J84" s="17"/>
     </row>
     <row r="85" spans="1:10">
-      <c r="A85" s="21">
+      <c r="A85" s="19">
         <v>171</v>
       </c>
-      <c r="B85" s="21">
+      <c r="B85" s="19">
         <v>3</v>
       </c>
-      <c r="C85" s="22" t="s">
+      <c r="C85" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="D85" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="E85" s="17" t="s">
+      <c r="D85" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="E85" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="F85" s="21"/>
-      <c r="G85" s="21"/>
-      <c r="H85" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="I85" s="22"/>
-      <c r="J85" s="19"/>
+      <c r="F85" s="19"/>
+      <c r="G85" s="19"/>
+      <c r="H85" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I85" s="20"/>
+      <c r="J85" s="17"/>
     </row>
     <row r="86" spans="1:10">
-      <c r="A86" s="21">
+      <c r="A86" s="19">
         <v>172</v>
       </c>
-      <c r="B86" s="21">
+      <c r="B86" s="19">
         <v>3</v>
       </c>
-      <c r="C86" s="22" t="s">
+      <c r="C86" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="D86" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="E86" s="17" t="s">
+      <c r="D86" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="E86" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="F86" s="21"/>
-      <c r="G86" s="21"/>
-      <c r="H86" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="I86" s="22"/>
+      <c r="F86" s="19"/>
+      <c r="G86" s="19"/>
+      <c r="H86" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I86" s="20"/>
     </row>
     <row r="87" spans="1:10">
-      <c r="A87" s="21">
+      <c r="A87" s="19">
         <v>173</v>
       </c>
-      <c r="B87" s="21">
+      <c r="B87" s="19">
         <v>3</v>
       </c>
-      <c r="C87" s="22" t="s">
+      <c r="C87" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="D87" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="E87" s="17" t="s">
+      <c r="D87" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="E87" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="F87" s="21"/>
-      <c r="G87" s="21"/>
-      <c r="H87" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="I87" s="22"/>
+      <c r="F87" s="19"/>
+      <c r="G87" s="19"/>
+      <c r="H87" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I87" s="20"/>
     </row>
     <row r="88" spans="1:10">
-      <c r="A88" s="21">
+      <c r="A88" s="19">
         <v>174</v>
       </c>
-      <c r="B88" s="21">
+      <c r="B88" s="19">
         <v>3</v>
       </c>
-      <c r="C88" s="22" t="s">
+      <c r="C88" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="D88" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="E88" s="17" t="s">
+      <c r="D88" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="E88" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="F88" s="21"/>
-      <c r="G88" s="21"/>
-      <c r="H88" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="I88" s="22"/>
+      <c r="F88" s="19"/>
+      <c r="G88" s="19"/>
+      <c r="H88" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I88" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/table/resources/sample/PointsAwardRanking.xlsx
+++ b/table/resources/sample/PointsAwardRanking.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="PointsAwardRanking" sheetId="1" r:id="rId1"/>
@@ -176,7 +176,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="107">
   <si>
     <t>序列ID</t>
   </si>
@@ -469,19 +469,7 @@
     <t>1990000_15750000</t>
   </si>
   <si>
-    <t>wdcc_ccb_1.png</t>
-  </si>
-  <si>
-    <t>2026/08/01 00:00:00</t>
-  </si>
-  <si>
-    <t>wdcc_ccb_2.png</t>
-  </si>
-  <si>
-    <t>wdcc_ccb_3.png</t>
-  </si>
-  <si>
-    <t>itemicon_1010101.png</t>
+    <t>2036/08/01 00:00:00</t>
   </si>
   <si>
     <t>名次</t>
@@ -1183,7 +1171,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1251,6 +1239,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3921,14 +3912,12 @@
       <c r="G86" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H86" s="21">
-        <v>33333333</v>
-      </c>
+      <c r="H86" s="21"/>
       <c r="I86" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="J86" s="22" t="s">
         <v>97</v>
-      </c>
-      <c r="J86" s="22" t="s">
-        <v>98</v>
       </c>
       <c r="K86" s="18"/>
       <c r="L86" s="18"/>
@@ -3951,14 +3940,12 @@
       <c r="G87" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="H87" s="21">
-        <v>22222222</v>
-      </c>
+      <c r="H87" s="21"/>
       <c r="I87" s="21" t="s">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="J87" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K87" s="18"/>
       <c r="L87" s="18"/>
@@ -3981,14 +3968,12 @@
       <c r="G88" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="H88" s="21">
-        <v>11111111</v>
-      </c>
+      <c r="H88" s="21"/>
       <c r="I88" s="21" t="s">
-        <v>100</v>
+        <v>27</v>
       </c>
       <c r="J88" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K88" s="18"/>
       <c r="L88" s="18"/>
@@ -4011,14 +3996,10 @@
       <c r="G89" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="H89" s="21">
-        <v>5000000</v>
-      </c>
-      <c r="I89" s="21" t="s">
-        <v>101</v>
-      </c>
+      <c r="H89" s="21"/>
+      <c r="I89" s="21"/>
       <c r="J89" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K89" s="18"/>
       <c r="L89" s="18"/>
@@ -4041,14 +4022,10 @@
       <c r="G90" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="H90" s="21">
-        <v>3000000</v>
-      </c>
-      <c r="I90" s="21" t="s">
-        <v>101</v>
-      </c>
+      <c r="H90" s="21"/>
+      <c r="I90" s="21"/>
       <c r="J90" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K90" s="18"/>
       <c r="L90" s="19"/>
@@ -4075,7 +4052,7 @@
       <c r="H91" s="21"/>
       <c r="I91" s="21"/>
       <c r="J91" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K91" s="18"/>
       <c r="L91" s="19"/>
@@ -4102,7 +4079,7 @@
       <c r="H92" s="21"/>
       <c r="I92" s="21"/>
       <c r="J92" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K92" s="18"/>
       <c r="L92" s="19"/>
@@ -4129,7 +4106,7 @@
       <c r="H93" s="21"/>
       <c r="I93" s="21"/>
       <c r="J93" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K93" s="18"/>
       <c r="L93" s="19"/>
@@ -4156,7 +4133,7 @@
       <c r="H94" s="21"/>
       <c r="I94" s="21"/>
       <c r="J94" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K94" s="18"/>
       <c r="N94" s="3"/>
@@ -4182,7 +4159,7 @@
       <c r="H95" s="21"/>
       <c r="I95" s="21"/>
       <c r="J95" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K95" s="18"/>
       <c r="N95" s="3"/>
@@ -4208,7 +4185,7 @@
       <c r="H96" s="21"/>
       <c r="I96" s="21"/>
       <c r="J96" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K96" s="18"/>
       <c r="L96" s="9"/>
@@ -4235,7 +4212,7 @@
       <c r="H97" s="21"/>
       <c r="I97" s="21"/>
       <c r="J97" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K97" s="18"/>
       <c r="L97" s="19"/>
@@ -4262,7 +4239,7 @@
       <c r="H98" s="21"/>
       <c r="I98" s="21"/>
       <c r="J98" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K98" s="18"/>
       <c r="L98" s="19"/>
@@ -4289,7 +4266,7 @@
       <c r="H99" s="21"/>
       <c r="I99" s="21"/>
       <c r="J99" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K99" s="18"/>
       <c r="L99" s="19"/>
@@ -4316,7 +4293,7 @@
       <c r="H100" s="21"/>
       <c r="I100" s="21"/>
       <c r="J100" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K100" s="18"/>
       <c r="L100" s="19"/>
@@ -4343,7 +4320,7 @@
       <c r="H101" s="21"/>
       <c r="I101" s="21"/>
       <c r="J101" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K101" s="18"/>
       <c r="L101" s="19"/>
@@ -4370,7 +4347,7 @@
       <c r="H102" s="21"/>
       <c r="I102" s="21"/>
       <c r="J102" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K102" s="18"/>
       <c r="L102" s="19"/>
@@ -4397,7 +4374,7 @@
       <c r="H103" s="21"/>
       <c r="I103" s="21"/>
       <c r="J103" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K103" s="18"/>
       <c r="L103" s="19"/>
@@ -4424,7 +4401,7 @@
       <c r="H104" s="21"/>
       <c r="I104" s="21"/>
       <c r="J104" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K104" s="18"/>
       <c r="L104" s="19"/>
@@ -4451,7 +4428,7 @@
       <c r="H105" s="21"/>
       <c r="I105" s="21"/>
       <c r="J105" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K105" s="18"/>
       <c r="L105" s="19"/>
@@ -4478,7 +4455,7 @@
       <c r="H106" s="21"/>
       <c r="I106" s="21"/>
       <c r="J106" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K106" s="18"/>
       <c r="L106" s="19"/>
@@ -4505,7 +4482,7 @@
       <c r="H107" s="21"/>
       <c r="I107" s="21"/>
       <c r="J107" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K107" s="18"/>
       <c r="L107" s="19"/>
@@ -4532,7 +4509,7 @@
       <c r="H108" s="21"/>
       <c r="I108" s="21"/>
       <c r="J108" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K108" s="18"/>
       <c r="L108" s="19"/>
@@ -4559,7 +4536,7 @@
       <c r="H109" s="21"/>
       <c r="I109" s="21"/>
       <c r="J109" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K109" s="18"/>
       <c r="L109" s="19"/>
@@ -4586,7 +4563,7 @@
       <c r="H110" s="21"/>
       <c r="I110" s="21"/>
       <c r="J110" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K110" s="18"/>
       <c r="L110" s="19"/>
@@ -4613,7 +4590,7 @@
       <c r="H111" s="21"/>
       <c r="I111" s="21"/>
       <c r="J111" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K111" s="18"/>
       <c r="L111" s="19"/>
@@ -4640,7 +4617,7 @@
       <c r="H112" s="21"/>
       <c r="I112" s="21"/>
       <c r="J112" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K112" s="18"/>
       <c r="L112" s="19"/>
@@ -4664,14 +4641,12 @@
       <c r="G113" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="H113" s="21">
-        <v>33333333</v>
-      </c>
+      <c r="H113" s="21"/>
       <c r="I113" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="J113" s="22" t="s">
         <v>97</v>
-      </c>
-      <c r="J113" s="22" t="s">
-        <v>98</v>
       </c>
       <c r="K113" s="18"/>
       <c r="L113" s="19"/>
@@ -4695,14 +4670,12 @@
       <c r="G114" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H114" s="21">
-        <v>22222222</v>
-      </c>
+      <c r="H114" s="21"/>
       <c r="I114" s="21" t="s">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="J114" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K114" s="18"/>
       <c r="L114" s="18"/>
@@ -4726,14 +4699,12 @@
       <c r="G115" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="H115" s="21">
-        <v>11111111</v>
-      </c>
+      <c r="H115" s="21"/>
       <c r="I115" s="21" t="s">
-        <v>100</v>
+        <v>27</v>
       </c>
       <c r="J115" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="116" s="4" customFormat="1" spans="1:14">
@@ -4754,14 +4725,10 @@
       <c r="G116" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="H116" s="21">
-        <v>5000000</v>
-      </c>
-      <c r="I116" s="21" t="s">
-        <v>101</v>
-      </c>
+      <c r="H116" s="21"/>
+      <c r="I116" s="21"/>
       <c r="J116" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K116" s="18"/>
       <c r="L116" s="19"/>
@@ -4784,14 +4751,10 @@
       <c r="G117" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="H117" s="21">
-        <v>3000000</v>
-      </c>
-      <c r="I117" s="21" t="s">
-        <v>101</v>
-      </c>
+      <c r="H117" s="21"/>
+      <c r="I117" s="21"/>
       <c r="J117" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K117" s="18"/>
       <c r="L117" s="19"/>
@@ -4817,7 +4780,7 @@
       <c r="H118" s="21"/>
       <c r="I118" s="21"/>
       <c r="J118" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K118" s="18"/>
       <c r="L118" s="19"/>
@@ -4843,7 +4806,7 @@
       <c r="H119" s="21"/>
       <c r="I119" s="21"/>
       <c r="J119" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K119" s="18"/>
       <c r="L119" s="19"/>
@@ -4869,7 +4832,7 @@
       <c r="H120" s="21"/>
       <c r="I120" s="21"/>
       <c r="J120" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K120" s="18"/>
       <c r="L120" s="18"/>
@@ -4895,7 +4858,7 @@
       <c r="H121" s="21"/>
       <c r="I121" s="21"/>
       <c r="J121" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K121" s="18"/>
     </row>
@@ -4920,7 +4883,7 @@
       <c r="H122" s="21"/>
       <c r="I122" s="21"/>
       <c r="J122" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K122" s="18"/>
     </row>
@@ -4945,7 +4908,7 @@
       <c r="H123" s="21"/>
       <c r="I123" s="21"/>
       <c r="J123" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K123" s="18"/>
     </row>
@@ -4970,7 +4933,7 @@
       <c r="H124" s="21"/>
       <c r="I124" s="21"/>
       <c r="J124" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K124" s="18"/>
     </row>
@@ -4995,7 +4958,7 @@
       <c r="H125" s="21"/>
       <c r="I125" s="21"/>
       <c r="J125" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K125" s="18"/>
     </row>
@@ -5020,7 +4983,7 @@
       <c r="H126" s="21"/>
       <c r="I126" s="21"/>
       <c r="J126" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K126" s="18"/>
     </row>
@@ -5045,7 +5008,7 @@
       <c r="H127" s="21"/>
       <c r="I127" s="21"/>
       <c r="J127" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K127" s="18"/>
     </row>
@@ -5070,7 +5033,7 @@
       <c r="H128" s="21"/>
       <c r="I128" s="21"/>
       <c r="J128" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K128" s="18"/>
     </row>
@@ -5095,7 +5058,7 @@
       <c r="H129" s="21"/>
       <c r="I129" s="21"/>
       <c r="J129" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K129" s="18"/>
     </row>
@@ -5120,7 +5083,7 @@
       <c r="H130" s="21"/>
       <c r="I130" s="21"/>
       <c r="J130" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K130" s="18"/>
     </row>
@@ -5145,7 +5108,7 @@
       <c r="H131" s="21"/>
       <c r="I131" s="21"/>
       <c r="J131" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K131" s="18"/>
     </row>
@@ -5170,7 +5133,7 @@
       <c r="H132" s="21"/>
       <c r="I132" s="21"/>
       <c r="J132" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K132" s="18"/>
     </row>
@@ -5195,7 +5158,7 @@
       <c r="H133" s="21"/>
       <c r="I133" s="21"/>
       <c r="J133" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K133" s="18"/>
     </row>
@@ -5220,7 +5183,7 @@
       <c r="H134" s="21"/>
       <c r="I134" s="21"/>
       <c r="J134" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K134" s="18"/>
     </row>
@@ -5245,7 +5208,7 @@
       <c r="H135" s="21"/>
       <c r="I135" s="21"/>
       <c r="J135" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K135" s="18"/>
     </row>
@@ -5270,7 +5233,7 @@
       <c r="H136" s="21"/>
       <c r="I136" s="21"/>
       <c r="J136" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K136" s="18"/>
     </row>
@@ -5295,7 +5258,7 @@
       <c r="H137" s="21"/>
       <c r="I137" s="21"/>
       <c r="J137" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K137" s="18"/>
     </row>
@@ -5320,7 +5283,7 @@
       <c r="H138" s="21"/>
       <c r="I138" s="21"/>
       <c r="J138" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K138" s="18"/>
     </row>
@@ -5345,7 +5308,7 @@
       <c r="H139" s="21"/>
       <c r="I139" s="21"/>
       <c r="J139" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K139" s="18"/>
     </row>
@@ -5367,14 +5330,12 @@
       <c r="G140" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="H140" s="21">
-        <v>99999999</v>
-      </c>
+      <c r="H140" s="21"/>
       <c r="I140" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="J140" s="22" t="s">
         <v>97</v>
-      </c>
-      <c r="J140" s="22" t="s">
-        <v>98</v>
       </c>
       <c r="K140" s="18"/>
     </row>
@@ -5396,14 +5357,12 @@
       <c r="G141" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="H141" s="21">
-        <v>88888888</v>
-      </c>
+      <c r="H141" s="21"/>
       <c r="I141" s="21" t="s">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="J141" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K141" s="18"/>
     </row>
@@ -5425,14 +5384,12 @@
       <c r="G142" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="H142" s="21">
-        <v>77777777</v>
-      </c>
+      <c r="H142" s="21"/>
       <c r="I142" s="21" t="s">
-        <v>100</v>
+        <v>27</v>
       </c>
       <c r="J142" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K142" s="18"/>
     </row>
@@ -5454,14 +5411,10 @@
       <c r="G143" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="H143" s="21">
-        <v>66666666</v>
-      </c>
-      <c r="I143" s="21" t="s">
-        <v>101</v>
-      </c>
+      <c r="H143" s="21"/>
+      <c r="I143" s="21"/>
       <c r="J143" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K143" s="18"/>
     </row>
@@ -5483,14 +5436,10 @@
       <c r="G144" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="H144" s="21">
-        <v>55555555</v>
-      </c>
-      <c r="I144" s="21" t="s">
-        <v>101</v>
-      </c>
+      <c r="H144" s="21"/>
+      <c r="I144" s="21"/>
       <c r="J144" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K144" s="18"/>
     </row>
@@ -5515,7 +5464,7 @@
       <c r="H145" s="21"/>
       <c r="I145" s="21"/>
       <c r="J145" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K145" s="18"/>
     </row>
@@ -5540,7 +5489,7 @@
       <c r="H146" s="21"/>
       <c r="I146" s="21"/>
       <c r="J146" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K146" s="18"/>
     </row>
@@ -5565,7 +5514,7 @@
       <c r="H147" s="21"/>
       <c r="I147" s="21"/>
       <c r="J147" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K147" s="18"/>
     </row>
@@ -5590,7 +5539,7 @@
       <c r="H148" s="21"/>
       <c r="I148" s="21"/>
       <c r="J148" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K148" s="18"/>
     </row>
@@ -5615,7 +5564,7 @@
       <c r="H149" s="21"/>
       <c r="I149" s="21"/>
       <c r="J149" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K149" s="18"/>
     </row>
@@ -5640,7 +5589,7 @@
       <c r="H150" s="21"/>
       <c r="I150" s="21"/>
       <c r="J150" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K150" s="18"/>
     </row>
@@ -5665,7 +5614,7 @@
       <c r="H151" s="21"/>
       <c r="I151" s="21"/>
       <c r="J151" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="152" spans="1:11">
@@ -5689,7 +5638,7 @@
       <c r="H152" s="21"/>
       <c r="I152" s="21"/>
       <c r="J152" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="153" spans="1:11">
@@ -5713,7 +5662,7 @@
       <c r="H153" s="21"/>
       <c r="I153" s="21"/>
       <c r="J153" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="154" spans="1:11">
@@ -5726,6 +5675,8 @@
       <c r="C154" s="22" t="s">
         <v>47</v>
       </c>
+      <c r="D154" s="23"/>
+      <c r="E154" s="23"/>
       <c r="F154" s="22" t="s">
         <v>21</v>
       </c>
@@ -5735,7 +5686,7 @@
       <c r="H154" s="21"/>
       <c r="I154" s="21"/>
       <c r="J154" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="155" spans="1:11">
@@ -5748,6 +5699,8 @@
       <c r="C155" s="22" t="s">
         <v>49</v>
       </c>
+      <c r="D155" s="23"/>
+      <c r="E155" s="23"/>
       <c r="F155" s="22" t="s">
         <v>21</v>
       </c>
@@ -5757,7 +5710,7 @@
       <c r="H155" s="21"/>
       <c r="I155" s="21"/>
       <c r="J155" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="156" spans="1:11">
@@ -5770,6 +5723,8 @@
       <c r="C156" s="22" t="s">
         <v>51</v>
       </c>
+      <c r="D156" s="23"/>
+      <c r="E156" s="23"/>
       <c r="F156" s="22" t="s">
         <v>21</v>
       </c>
@@ -5779,7 +5734,7 @@
       <c r="H156" s="21"/>
       <c r="I156" s="21"/>
       <c r="J156" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="157" spans="1:11">
@@ -5792,6 +5747,8 @@
       <c r="C157" s="22" t="s">
         <v>53</v>
       </c>
+      <c r="D157" s="23"/>
+      <c r="E157" s="23"/>
       <c r="F157" s="22" t="s">
         <v>21</v>
       </c>
@@ -5801,7 +5758,7 @@
       <c r="H157" s="21"/>
       <c r="I157" s="21"/>
       <c r="J157" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="158" spans="1:11">
@@ -5814,6 +5771,8 @@
       <c r="C158" s="22" t="s">
         <v>55</v>
       </c>
+      <c r="D158" s="23"/>
+      <c r="E158" s="23"/>
       <c r="F158" s="22" t="s">
         <v>21</v>
       </c>
@@ -5823,7 +5782,7 @@
       <c r="H158" s="21"/>
       <c r="I158" s="21"/>
       <c r="J158" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="159" spans="1:11">
@@ -5836,6 +5795,8 @@
       <c r="C159" s="22" t="s">
         <v>57</v>
       </c>
+      <c r="D159" s="23"/>
+      <c r="E159" s="23"/>
       <c r="F159" s="22" t="s">
         <v>21</v>
       </c>
@@ -5845,7 +5806,7 @@
       <c r="H159" s="21"/>
       <c r="I159" s="21"/>
       <c r="J159" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="160" spans="1:11">
@@ -5858,6 +5819,8 @@
       <c r="C160" s="22" t="s">
         <v>59</v>
       </c>
+      <c r="D160" s="23"/>
+      <c r="E160" s="23"/>
       <c r="F160" s="22" t="s">
         <v>21</v>
       </c>
@@ -5867,7 +5830,7 @@
       <c r="H160" s="21"/>
       <c r="I160" s="21"/>
       <c r="J160" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="161" spans="1:10">
@@ -5880,6 +5843,8 @@
       <c r="C161" s="22" t="s">
         <v>61</v>
       </c>
+      <c r="D161" s="23"/>
+      <c r="E161" s="23"/>
       <c r="F161" s="22" t="s">
         <v>21</v>
       </c>
@@ -5889,7 +5854,7 @@
       <c r="H161" s="21"/>
       <c r="I161" s="21"/>
       <c r="J161" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="162" spans="1:10">
@@ -5902,6 +5867,8 @@
       <c r="C162" s="22" t="s">
         <v>63</v>
       </c>
+      <c r="D162" s="23"/>
+      <c r="E162" s="23"/>
       <c r="F162" s="22" t="s">
         <v>21</v>
       </c>
@@ -5911,7 +5878,7 @@
       <c r="H162" s="21"/>
       <c r="I162" s="21"/>
       <c r="J162" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="163" spans="1:10">
@@ -5924,6 +5891,8 @@
       <c r="C163" s="22" t="s">
         <v>65</v>
       </c>
+      <c r="D163" s="23"/>
+      <c r="E163" s="23"/>
       <c r="F163" s="22" t="s">
         <v>21</v>
       </c>
@@ -5933,7 +5902,7 @@
       <c r="H163" s="21"/>
       <c r="I163" s="21"/>
       <c r="J163" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="164" spans="1:10">
@@ -5946,6 +5915,8 @@
       <c r="C164" s="22" t="s">
         <v>67</v>
       </c>
+      <c r="D164" s="23"/>
+      <c r="E164" s="23"/>
       <c r="F164" s="22" t="s">
         <v>21</v>
       </c>
@@ -5955,7 +5926,7 @@
       <c r="H164" s="21"/>
       <c r="I164" s="21"/>
       <c r="J164" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="165" spans="1:10">
@@ -5968,6 +5939,8 @@
       <c r="C165" s="22" t="s">
         <v>69</v>
       </c>
+      <c r="D165" s="23"/>
+      <c r="E165" s="23"/>
       <c r="F165" s="22" t="s">
         <v>21</v>
       </c>
@@ -5977,7 +5950,7 @@
       <c r="H165" s="21"/>
       <c r="I165" s="21"/>
       <c r="J165" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="166" spans="1:10">
@@ -5990,6 +5963,8 @@
       <c r="C166" s="22" t="s">
         <v>71</v>
       </c>
+      <c r="D166" s="23"/>
+      <c r="E166" s="23"/>
       <c r="F166" s="22" t="s">
         <v>21</v>
       </c>
@@ -5999,7 +5974,7 @@
       <c r="H166" s="21"/>
       <c r="I166" s="21"/>
       <c r="J166" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -6036,34 +6011,34 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="R1" s="1">
         <v>50</v>
@@ -6106,30 +6081,30 @@
       </c>
       <c r="K2" s="1">
         <f ca="1" t="shared" ref="K2:O2" si="4">RAND()</f>
-        <v>0.0259208143240577</v>
+        <v>0.816183286213281</v>
       </c>
       <c r="L2" s="1">
         <f ca="1" t="shared" ref="L2:P2" si="5">J2+$R$1*K2/MAX(1,($A2*($A2-1)))++$R$1/$A2</f>
-        <v>1101.2960407162</v>
+        <v>1140.80916431066</v>
       </c>
       <c r="M2" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>0.616528769787779</v>
+        <v>0.224176597207967</v>
       </c>
       <c r="N2" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>1182.12247920559</v>
+        <v>1202.01799417106</v>
       </c>
       <c r="O2" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>0.235092717854201</v>
+        <v>0.392322832471508</v>
       </c>
       <c r="P2" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>1243.8771150983</v>
+        <v>1271.63413579464</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="R2" s="1">
         <v>1</v>
@@ -6172,30 +6147,30 @@
       </c>
       <c r="K3" s="1">
         <f ca="1" t="shared" ref="K3:O3" si="6">RAND()</f>
-        <v>0.642058514706658</v>
+        <v>0.439008271570802</v>
       </c>
       <c r="L3" s="1">
         <f ca="1" t="shared" ref="L3:P3" si="7">J3+$R$1*K3/MAX(1,($A3*($A3-1)))++$R$1/$A3</f>
-        <v>341.051462867666</v>
+        <v>335.97520678927</v>
       </c>
       <c r="M3" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>0.545843418453009</v>
+        <v>0.534055166913635</v>
       </c>
       <c r="N3" s="1">
         <f ca="1" t="shared" si="7"/>
-        <v>379.697548328992</v>
+        <v>374.326585962111</v>
       </c>
       <c r="O3" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>0.811542046855817</v>
+        <v>0.849880224124062</v>
       </c>
       <c r="P3" s="1">
         <f ca="1" t="shared" si="7"/>
-        <v>424.986099500387</v>
+        <v>420.573591565212</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="R3" s="1">
         <v>30</v>
@@ -6238,30 +6213,30 @@
       </c>
       <c r="K4" s="1">
         <f ca="1" t="shared" ref="K4:O4" si="8">RAND()</f>
-        <v>0.733399523674593</v>
+        <v>0.248106901434934</v>
       </c>
       <c r="L4" s="1">
         <f ca="1" t="shared" ref="L4:P4" si="9">J4+$R$1*K4/MAX(1,($A4*($A4-1)))++$R$1/$A4</f>
-        <v>322.778329363955</v>
+        <v>318.734224178624</v>
       </c>
       <c r="M4" s="1">
         <f ca="1" t="shared" si="8"/>
-        <v>0.197439253783861</v>
+        <v>0.0215654732939499</v>
       </c>
       <c r="N4" s="1">
         <f ca="1" t="shared" si="9"/>
-        <v>341.090323145487</v>
+        <v>335.580603122741</v>
       </c>
       <c r="O4" s="1">
         <f ca="1" t="shared" si="8"/>
-        <v>0.832324778558032</v>
+        <v>0.694202077048308</v>
       </c>
       <c r="P4" s="1">
         <f ca="1" t="shared" si="9"/>
-        <v>364.693029633471</v>
+        <v>358.032287098143</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="R4" s="1">
         <f>24*60/R3</f>
@@ -6305,30 +6280,30 @@
       </c>
       <c r="K5" s="1">
         <f ca="1" t="shared" ref="K5:O5" si="10">RAND()</f>
-        <v>0.281974666187661</v>
+        <v>0.113481989811328</v>
       </c>
       <c r="L5" s="1">
         <f ca="1" t="shared" ref="L5:P5" si="11">J5+$R$1*K5/MAX(1,($A5*($A5-1)))++$R$1/$A5</f>
-        <v>163.674894442449</v>
+        <v>162.972841624214</v>
       </c>
       <c r="M5" s="1">
         <f ca="1" t="shared" si="10"/>
-        <v>0.543647312379003</v>
+        <v>0.660395992139216</v>
       </c>
       <c r="N5" s="1">
         <f ca="1" t="shared" si="11"/>
-        <v>178.440091577361</v>
+        <v>178.224491591461</v>
       </c>
       <c r="O5" s="1">
         <f ca="1" t="shared" si="10"/>
-        <v>0.656658814252148</v>
+        <v>0.98717294959106</v>
       </c>
       <c r="P5" s="1">
         <f ca="1" t="shared" si="11"/>
-        <v>193.676169970078</v>
+        <v>194.837712214757</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="R5" s="1">
         <v>6500</v>
@@ -6371,30 +6346,30 @@
       </c>
       <c r="K6" s="1">
         <f ca="1" t="shared" ref="K6:O6" si="12">RAND()</f>
-        <v>0.162884797559768</v>
+        <v>0.795876842518287</v>
       </c>
       <c r="L6" s="1">
         <f ca="1" t="shared" ref="L6:P6" si="13">J6+$R$1*K6/MAX(1,($A6*($A6-1)))++$R$1/$A6</f>
-        <v>160.407211993899</v>
+        <v>161.989692106296</v>
       </c>
       <c r="M6" s="1">
         <f ca="1" t="shared" si="12"/>
-        <v>0.284581693997958</v>
+        <v>0.697130138072451</v>
       </c>
       <c r="N6" s="1">
         <f ca="1" t="shared" si="13"/>
-        <v>171.118666228894</v>
+        <v>173.732517451477</v>
       </c>
       <c r="O6" s="1">
         <f ca="1" t="shared" si="12"/>
-        <v>0.98191942442169</v>
+        <v>0.819606043124285</v>
       </c>
       <c r="P6" s="1">
         <f ca="1" t="shared" si="13"/>
-        <v>183.573464789949</v>
+        <v>185.781532559288</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="R6" s="1">
         <f>R5/R4</f>
@@ -7806,27 +7781,27 @@
       </c>
       <c r="K31" s="1">
         <f ca="1" t="shared" ref="K31:O31" si="39">RAND()</f>
-        <v>0.0967208005162257</v>
+        <v>0.949075059305236</v>
       </c>
       <c r="L31" s="1">
         <f ca="1" t="shared" ref="L31:P31" si="40">J31+$R$1*K31/MAX(1,($A31*($A31-1)))++$R$1/$A31</f>
-        <v>22.3618805057768</v>
+        <v>22.4108663827187</v>
       </c>
       <c r="M31" s="1">
         <f ca="1" t="shared" si="39"/>
-        <v>0.448708758551681</v>
+        <v>0.0542003799881181</v>
       </c>
       <c r="N31" s="1">
         <f ca="1" t="shared" si="40"/>
-        <v>24.0543350321303</v>
+        <v>24.0806480137525</v>
       </c>
       <c r="O31" s="1">
         <f ca="1" t="shared" si="39"/>
-        <v>0.277728470404801</v>
+        <v>0.783768319687715</v>
       </c>
       <c r="P31" s="1">
         <f ca="1" t="shared" si="40"/>
-        <v>25.7369631051421</v>
+        <v>25.7923588367231</v>
       </c>
     </row>
     <row r="32" ht="16.5" spans="1:16">
@@ -8094,27 +8069,27 @@
       </c>
       <c r="K36" s="1">
         <f ca="1" t="shared" ref="K36:O36" si="45">RAND()</f>
-        <v>0.311153057333273</v>
+        <v>0.901376199713249</v>
       </c>
       <c r="L36" s="1">
         <f ca="1" t="shared" ref="L36:P36" si="46">J36+$R$1*K36/MAX(1,($A36*($A36-1)))++$R$1/$A36</f>
-        <v>19.088703909972</v>
+        <v>19.1135032016686</v>
       </c>
       <c r="M36" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.0888939408753595</v>
+        <v>0.830665005243266</v>
       </c>
       <c r="N36" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>20.521010378076</v>
+        <v>20.5769765212166</v>
       </c>
       <c r="O36" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.117025872305315</v>
+        <v>0.432229608780747</v>
       </c>
       <c r="P36" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>21.9544988601056</v>
+        <v>22.02370885772</v>
       </c>
     </row>
     <row r="37" ht="16.5" spans="1:16">
@@ -8154,27 +8129,27 @@
       </c>
       <c r="K37" s="1">
         <f ca="1" t="shared" ref="K37:O37" si="47">RAND()</f>
-        <v>0.29536002553011</v>
+        <v>0.0225498032988156</v>
       </c>
       <c r="L37" s="1">
         <f ca="1" t="shared" ref="L37:P37" si="48">J37+$R$1*K37/MAX(1,($A37*($A37-1)))++$R$1/$A37</f>
-        <v>18.5434666676798</v>
+        <v>18.5326408652102</v>
       </c>
       <c r="M37" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.31099270299798</v>
+        <v>0.205981672207753</v>
       </c>
       <c r="N37" s="1">
         <f ca="1" t="shared" si="48"/>
-        <v>19.9446965368464</v>
+        <v>19.9297036299804</v>
       </c>
       <c r="O37" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.436192380041265</v>
+        <v>0.0797426207330985</v>
       </c>
       <c r="P37" s="1">
         <f ca="1" t="shared" si="48"/>
-        <v>21.3508946471655</v>
+        <v>21.3217569085809</v>
       </c>
     </row>
     <row r="38" ht="16.5" spans="1:16">
@@ -8214,27 +8189,27 @@
       </c>
       <c r="K38" s="1">
         <f ca="1" t="shared" ref="K38:O38" si="49">RAND()</f>
-        <v>0.272156454142164</v>
+        <v>0.453949731680878</v>
       </c>
       <c r="L38" s="1">
         <f ca="1" t="shared" ref="L38:P38" si="50">J38+$R$1*K38/MAX(1,($A38*($A38-1)))++$R$1/$A38</f>
-        <v>18.0282341011315</v>
+        <v>18.0350581731112</v>
       </c>
       <c r="M38" s="1">
         <f ca="1" t="shared" si="49"/>
-        <v>0.0339165234993521</v>
+        <v>0.77971454652506</v>
       </c>
       <c r="N38" s="1">
         <f ca="1" t="shared" si="50"/>
-        <v>19.3808585952568</v>
+        <v>19.4156780885213</v>
       </c>
       <c r="O38" s="1">
         <f ca="1" t="shared" si="49"/>
-        <v>0.989297118732469</v>
+        <v>0.0150306605572645</v>
       </c>
       <c r="P38" s="1">
         <f ca="1" t="shared" si="50"/>
-        <v>20.7693457243384</v>
+        <v>20.7675936538575</v>
       </c>
     </row>
     <row r="39" ht="16.5" spans="1:16">
@@ -8274,27 +8249,27 @@
       </c>
       <c r="K39" s="1">
         <f ca="1" t="shared" ref="K39:O39" si="51">RAND()</f>
-        <v>0.251789636035714</v>
+        <v>0.203753320168378</v>
       </c>
       <c r="L39" s="1">
         <f ca="1" t="shared" ref="L39:P39" si="52">J39+$R$1*K39/MAX(1,($A39*($A39-1)))++$R$1/$A39</f>
-        <v>17.540959802135</v>
+        <v>17.5392515405465</v>
       </c>
       <c r="M39" s="1">
         <f ca="1" t="shared" si="51"/>
-        <v>0.356041334280435</v>
+        <v>0.403609233573458</v>
       </c>
       <c r="N39" s="1">
         <f ca="1" t="shared" si="52"/>
-        <v>18.8694107741933</v>
+        <v>18.8693941164204</v>
       </c>
       <c r="O39" s="1">
         <f ca="1" t="shared" si="51"/>
-        <v>0.447860070300623</v>
+        <v>0.892908018769496</v>
       </c>
       <c r="P39" s="1">
         <f ca="1" t="shared" si="52"/>
-        <v>20.2011269929096</v>
+        <v>20.2169370758361</v>
       </c>
     </row>
     <row r="40" ht="16.5" spans="1:16">
@@ -8334,27 +8309,27 @@
       </c>
       <c r="K40" s="1">
         <f ca="1" t="shared" ref="K40:O40" si="53">RAND()</f>
-        <v>0.0995314381813581</v>
+        <v>0.341556422898264</v>
       </c>
       <c r="L40" s="1">
         <f ca="1" t="shared" ref="L40:P40" si="54">J40+$R$1*K40/MAX(1,($A40*($A40-1)))++$R$1/$A40</f>
-        <v>17.0748829769967</v>
+        <v>17.083048462311</v>
       </c>
       <c r="M40" s="1">
         <f ca="1" t="shared" si="53"/>
-        <v>0.342596253256693</v>
+        <v>0.0976756490240525</v>
       </c>
       <c r="N40" s="1">
         <f ca="1" t="shared" si="54"/>
-        <v>18.3684928370931</v>
+        <v>18.3683951441269</v>
       </c>
       <c r="O40" s="1">
         <f ca="1" t="shared" si="53"/>
-        <v>0.854492457796838</v>
+        <v>0.153097371006048</v>
       </c>
       <c r="P40" s="1">
         <f ca="1" t="shared" si="54"/>
-        <v>19.6793731494344</v>
+        <v>19.6556116546197</v>
       </c>
     </row>
     <row r="41" ht="16.5" spans="1:16">
@@ -8394,27 +8369,27 @@
       </c>
       <c r="K41" s="1">
         <f ca="1" t="shared" ref="K41:O41" si="55">RAND()</f>
-        <v>0.349504771847821</v>
+        <v>0.747372638900624</v>
       </c>
       <c r="L41" s="1">
         <f ca="1" t="shared" ref="L41:P41" si="56">J41+$R$1*K41/MAX(1,($A41*($A41-1)))++$R$1/$A41</f>
-        <v>16.6458174606361</v>
+        <v>16.6585696358622</v>
       </c>
       <c r="M41" s="1">
         <f ca="1" t="shared" si="55"/>
-        <v>0.592535980618994</v>
+        <v>0.443272978515616</v>
       </c>
       <c r="N41" s="1">
         <f ca="1" t="shared" si="56"/>
-        <v>17.9148089984765</v>
+        <v>17.9227771031223</v>
       </c>
       <c r="O41" s="1">
         <f ca="1" t="shared" si="55"/>
-        <v>0.119392905479516</v>
+        <v>0.531959370886758</v>
       </c>
       <c r="P41" s="1">
         <f ca="1" t="shared" si="56"/>
-        <v>19.1686356941649</v>
+        <v>19.1898270829584</v>
       </c>
     </row>
     <row r="42" ht="16.5" spans="1:16">
@@ -8454,27 +8429,27 @@
       </c>
       <c r="K42" s="1">
         <f ca="1" t="shared" ref="K42:O42" si="57">RAND()</f>
-        <v>0.99678651018773</v>
+        <v>0.388149333156535</v>
       </c>
       <c r="L42" s="1">
         <f ca="1" t="shared" ref="L42:P42" si="58">J42+$R$1*K42/MAX(1,($A42*($A42-1)))++$R$1/$A42</f>
-        <v>16.2499020277496</v>
+        <v>16.2313460162548</v>
       </c>
       <c r="M42" s="1">
         <f ca="1" t="shared" si="57"/>
-        <v>0.581346274772516</v>
+        <v>0.740554041428543</v>
       </c>
       <c r="N42" s="1">
         <f ca="1" t="shared" si="58"/>
-        <v>17.4871381946634</v>
+        <v>17.4734360784934</v>
       </c>
       <c r="O42" s="1">
         <f ca="1" t="shared" si="57"/>
-        <v>0.974452457449112</v>
+        <v>0.102471034649306</v>
       </c>
       <c r="P42" s="1">
         <f ca="1" t="shared" si="58"/>
-        <v>18.736359306171</v>
+        <v>18.6960723905254</v>
       </c>
     </row>
     <row r="43" ht="16.5" spans="1:16">
@@ -8514,27 +8489,27 @@
       </c>
       <c r="K43" s="1">
         <f ca="1" t="shared" ref="K43:O43" si="59">RAND()</f>
-        <v>0.722922380038765</v>
+        <v>0.0704419139434409</v>
       </c>
       <c r="L43" s="1">
         <f ca="1" t="shared" ref="L43:P43" si="60">J43+$R$1*K43/MAX(1,($A43*($A43-1)))++$R$1/$A43</f>
-        <v>15.8456133095249</v>
+        <v>15.8266678836801</v>
       </c>
       <c r="M43" s="1">
         <f ca="1" t="shared" si="59"/>
-        <v>0.230081126590797</v>
+        <v>0.803343488300972</v>
       </c>
       <c r="N43" s="1">
         <f ca="1" t="shared" si="60"/>
-        <v>17.0427701366617</v>
+        <v>17.0404699594147</v>
       </c>
       <c r="O43" s="1">
         <f ca="1" t="shared" si="59"/>
-        <v>0.0918041872616333</v>
+        <v>0.552877881174804</v>
       </c>
       <c r="P43" s="1">
         <f ca="1" t="shared" si="60"/>
-        <v>18.2359119539457</v>
+        <v>18.2469995146173</v>
       </c>
     </row>
     <row r="44" ht="16.5" spans="1:16">
@@ -8574,27 +8549,27 @@
       </c>
       <c r="K44" s="1">
         <f ca="1" t="shared" ref="K44:O44" si="61">RAND()</f>
-        <v>0.954954721612753</v>
+        <v>0.0573570945425994</v>
       </c>
       <c r="L44" s="1">
         <f ca="1" t="shared" ref="L44:P44" si="62">J44+$R$1*K44/MAX(1,($A44*($A44-1)))++$R$1/$A44</f>
-        <v>15.4749433754599</v>
+        <v>15.4500929428168</v>
       </c>
       <c r="M44" s="1">
         <f ca="1" t="shared" si="61"/>
-        <v>0.283306525924844</v>
+        <v>0.10200067550006</v>
       </c>
       <c r="N44" s="1">
         <f ca="1" t="shared" si="62"/>
-        <v>16.6455775539185</v>
+        <v>16.6157075794586</v>
       </c>
       <c r="O44" s="1">
         <f ca="1" t="shared" si="61"/>
-        <v>0.919771391185308</v>
+        <v>0.671670320002679</v>
       </c>
       <c r="P44" s="1">
         <f ca="1" t="shared" si="62"/>
-        <v>17.8338325758229</v>
+        <v>17.7970938009426</v>
       </c>
     </row>
     <row r="45" ht="16.5" spans="1:16">
@@ -8634,27 +8609,27 @@
       </c>
       <c r="K45" s="1">
         <f ca="1" t="shared" ref="K45:O45" si="63">RAND()</f>
-        <v>0.947485353364613</v>
+        <v>0.863024300709164</v>
       </c>
       <c r="L45" s="1">
         <f ca="1" t="shared" ref="L45:P45" si="64">J45+$R$1*K45/MAX(1,($A45*($A45-1)))++$R$1/$A45</f>
-        <v>15.1148912619811</v>
+        <v>15.1126592045642</v>
       </c>
       <c r="M45" s="1">
         <f ca="1" t="shared" si="63"/>
-        <v>0.0903219565601399</v>
+        <v>0.284319774663767</v>
       </c>
       <c r="N45" s="1">
         <f ca="1" t="shared" si="64"/>
-        <v>16.2536418422285</v>
+        <v>16.2565365770447</v>
       </c>
       <c r="O45" s="1">
         <f ca="1" t="shared" si="63"/>
-        <v>0.970490533394766</v>
+        <v>0.0596387256844793</v>
       </c>
       <c r="P45" s="1">
         <f ca="1" t="shared" si="64"/>
-        <v>17.4156526914197</v>
+        <v>17.3944762896685</v>
       </c>
     </row>
     <row r="46" ht="16.5" spans="1:16">
@@ -8694,27 +8669,27 @@
       </c>
       <c r="K46" s="1">
         <f ca="1" t="shared" ref="K46:O46" si="65">RAND()</f>
-        <v>0.86894854826434</v>
+        <v>0.985853375371285</v>
       </c>
       <c r="L46" s="1">
         <f ca="1" t="shared" ref="L46:P46" si="66">J46+$R$1*K46/MAX(1,($A46*($A46-1)))++$R$1/$A46</f>
-        <v>14.7694178926329</v>
+        <v>14.7723700347316</v>
       </c>
       <c r="M46" s="1">
         <f ca="1" t="shared" si="65"/>
-        <v>0.939554941644274</v>
+        <v>0.251335398585788</v>
       </c>
       <c r="N46" s="1">
         <f ca="1" t="shared" si="66"/>
-        <v>15.9042551386341</v>
+        <v>15.8898279993423</v>
       </c>
       <c r="O46" s="1">
         <f ca="1" t="shared" si="65"/>
-        <v>0.116322616219509</v>
+        <v>0.00627655796000703</v>
       </c>
       <c r="P46" s="1">
         <f ca="1" t="shared" si="66"/>
-        <v>17.0183036895487</v>
+        <v>17.0010976093918</v>
       </c>
     </row>
     <row r="47" ht="16.5" spans="1:16">
@@ -8754,27 +8729,27 @@
       </c>
       <c r="K47" s="1">
         <f ca="1" t="shared" ref="K47:O47" si="67">RAND()</f>
-        <v>0.197668293583851</v>
+        <v>0.0638825235358458</v>
       </c>
       <c r="L47" s="1">
         <f ca="1" t="shared" ref="L47:P47" si="68">J47+$R$1*K47/MAX(1,($A47*($A47-1)))++$R$1/$A47</f>
-        <v>14.4250644515358</v>
+        <v>14.4218329111965</v>
       </c>
       <c r="M47" s="1">
         <f ca="1" t="shared" si="67"/>
-        <v>0.340857838308714</v>
+        <v>0.263710393349165</v>
       </c>
       <c r="N47" s="1">
         <f ca="1" t="shared" si="68"/>
-        <v>15.5202542543935</v>
+        <v>15.5151592492001</v>
       </c>
       <c r="O47" s="1">
         <f ca="1" t="shared" si="67"/>
-        <v>0.978509659483502</v>
+        <v>0.159870507737641</v>
       </c>
       <c r="P47" s="1">
         <f ca="1" t="shared" si="68"/>
-        <v>16.630846275154</v>
+        <v>16.6059773774063</v>
       </c>
     </row>
     <row r="48" ht="16.5" spans="1:16">
@@ -8814,27 +8789,27 @@
       </c>
       <c r="K48" s="1">
         <f ca="1" t="shared" ref="K48:O48" si="69">RAND()</f>
-        <v>0.0912851377057509</v>
+        <v>0.917284534919631</v>
       </c>
       <c r="L48" s="1">
         <f ca="1" t="shared" ref="L48:P48" si="70">J48+$R$1*K48/MAX(1,($A48*($A48-1)))++$R$1/$A48</f>
-        <v>14.1094191752476</v>
+        <v>14.1285218440084</v>
       </c>
       <c r="M48" s="1">
         <f ca="1" t="shared" si="69"/>
-        <v>0.653056223431998</v>
+        <v>0.528647329160902</v>
       </c>
       <c r="N48" s="1">
         <f ca="1" t="shared" si="70"/>
-        <v>15.1883520203778</v>
+        <v>15.2045775176707</v>
       </c>
       <c r="O48" s="1">
         <f ca="1" t="shared" si="69"/>
-        <v>0.449332412948018</v>
+        <v>0.970285229320827</v>
       </c>
       <c r="P48" s="1">
         <f ca="1" t="shared" si="70"/>
-        <v>16.2625733990307</v>
+        <v>16.2908468337975</v>
       </c>
     </row>
     <row r="49" ht="16.5" spans="1:16">
@@ -8874,27 +8849,27 @@
       </c>
       <c r="K49" s="1">
         <f ca="1" t="shared" ref="K49:O49" si="71">RAND()</f>
-        <v>0.292643916167011</v>
+        <v>0.222334643267628</v>
       </c>
       <c r="L49" s="1">
         <f ca="1" t="shared" ref="L49:P49" si="72">J49+$R$1*K49/MAX(1,($A49*($A49-1)))++$R$1/$A49</f>
-        <v>13.8141100158725</v>
+        <v>13.8125517429802</v>
       </c>
       <c r="M49" s="1">
         <f ca="1" t="shared" si="71"/>
-        <v>0.352652237806029</v>
+        <v>0.957547264286712</v>
       </c>
       <c r="N49" s="1">
         <f ca="1" t="shared" si="72"/>
-        <v>14.863592556604</v>
+        <v>14.8754406451142</v>
       </c>
       <c r="O49" s="1">
         <f ca="1" t="shared" si="71"/>
-        <v>0.0642356659017287</v>
+        <v>0.370630625976557</v>
       </c>
       <c r="P49" s="1">
         <f ca="1" t="shared" si="72"/>
-        <v>15.9066828860788</v>
+        <v>15.9253216430304</v>
       </c>
     </row>
     <row r="50" ht="16.5" spans="1:16">
@@ -8934,27 +8909,27 @@
       </c>
       <c r="K50" s="1">
         <f ca="1" t="shared" ref="K50:O50" si="73">RAND()</f>
-        <v>0.462891257286927</v>
+        <v>0.358524759852181</v>
       </c>
       <c r="L50" s="1">
         <f ca="1" t="shared" ref="L50:P50" si="74">J50+$R$1*K50/MAX(1,($A50*($A50-1)))++$R$1/$A50</f>
-        <v>13.5302485386328</v>
+        <v>13.5280298630921</v>
       </c>
       <c r="M50" s="1">
         <f ca="1" t="shared" si="73"/>
-        <v>0.584558934852071</v>
+        <v>0.187529376043008</v>
       </c>
       <c r="N50" s="1">
         <f ca="1" t="shared" si="74"/>
-        <v>14.563083550003</v>
+        <v>14.5524246202359</v>
       </c>
       <c r="O50" s="1">
         <f ca="1" t="shared" si="73"/>
-        <v>0.93634825546527</v>
+        <v>0.882426679749641</v>
       </c>
       <c r="P50" s="1">
         <f ca="1" t="shared" si="74"/>
-        <v>15.6033970758419</v>
+        <v>15.5915918540741</v>
       </c>
     </row>
     <row r="51" ht="16.5" spans="1:16">
@@ -8994,27 +8969,27 @@
       </c>
       <c r="K51" s="1">
         <f ca="1" t="shared" ref="K51:O51" si="75">RAND()</f>
-        <v>0.508518477789458</v>
+        <v>0.609682005254878</v>
       </c>
       <c r="L51" s="1">
         <f ca="1" t="shared" ref="L51:P51" si="76">J51+$R$1*K51/MAX(1,($A51*($A51-1)))++$R$1/$A51</f>
-        <v>13.2552758873018</v>
+        <v>13.2573404490869</v>
       </c>
       <c r="M51" s="1">
         <f ca="1" t="shared" si="75"/>
-        <v>0.649880051636582</v>
+        <v>0.183344110382654</v>
       </c>
       <c r="N51" s="1">
         <f ca="1" t="shared" si="76"/>
-        <v>14.2685387454985</v>
+        <v>14.2610821656253</v>
       </c>
       <c r="O51" s="1">
         <f ca="1" t="shared" si="75"/>
-        <v>0.591106114221508</v>
+        <v>0.526782935281393</v>
       </c>
       <c r="P51" s="1">
         <f ca="1" t="shared" si="76"/>
-        <v>15.2806021355846</v>
+        <v>15.2718328377739</v>
       </c>
     </row>
     <row r="52" ht="16.5" spans="1:16">
@@ -9054,27 +9029,27 @@
       </c>
       <c r="K52" s="1">
         <f ca="1" t="shared" ref="K52:O52" si="77">RAND()</f>
-        <v>0.45599822262234</v>
+        <v>0.976043246877303</v>
       </c>
       <c r="L52" s="1">
         <f ca="1" t="shared" ref="L52:P52" si="78">J52+$R$1*K52/MAX(1,($A52*($A52-1)))++$R$1/$A52</f>
-        <v>12.9893332984828</v>
+        <v>12.9995302597427</v>
       </c>
       <c r="M52" s="1">
         <f ca="1" t="shared" si="77"/>
-        <v>0.29857410657279</v>
+        <v>0.778143790862758</v>
       </c>
       <c r="N52" s="1">
         <f ca="1" t="shared" si="78"/>
-        <v>13.9755798495921</v>
+        <v>13.9951801379949</v>
       </c>
       <c r="O52" s="1">
         <f ca="1" t="shared" si="77"/>
-        <v>0.329089972449196</v>
+        <v>0.277154781091727</v>
       </c>
       <c r="P52" s="1">
         <f ca="1" t="shared" si="78"/>
-        <v>14.9624247510126</v>
+        <v>14.98100670233</v>
       </c>
     </row>
     <row r="53" ht="16.5" spans="1:16">
@@ -9114,27 +9089,27 @@
       </c>
       <c r="K53" s="1">
         <f ca="1" t="shared" ref="K53:O53" si="79">RAND()</f>
-        <v>0.138150228296106</v>
+        <v>0.955895957190924</v>
       </c>
       <c r="L53" s="1">
         <f ca="1" t="shared" ref="L53:P53" si="80">J53+$R$1*K53/MAX(1,($A53*($A53-1)))++$R$1/$A53</f>
-        <v>12.7288489862047</v>
+        <v>12.74426651503</v>
       </c>
       <c r="M53" s="1">
         <f ca="1" t="shared" si="79"/>
-        <v>0.563233938239164</v>
+        <v>0.973384399024627</v>
       </c>
       <c r="N53" s="1">
         <f ca="1" t="shared" si="80"/>
-        <v>13.701006488811</v>
+        <v>13.724156869461</v>
       </c>
       <c r="O53" s="1">
         <f ca="1" t="shared" si="79"/>
-        <v>0.869757202540743</v>
+        <v>0.335297555088612</v>
       </c>
       <c r="P53" s="1">
         <f ca="1" t="shared" si="80"/>
-        <v>14.6789430876523</v>
+        <v>14.6920169289461</v>
       </c>
     </row>
     <row r="54" ht="16.5" spans="1:16">
@@ -9288,27 +9263,27 @@
       </c>
       <c r="K56" s="1">
         <f ca="1" t="shared" ref="K56:O56" si="83">RAND()</f>
-        <v>0.250745951446983</v>
+        <v>0.238528396258783</v>
       </c>
       <c r="L56" s="1">
         <f ca="1" t="shared" ref="L56:P56" si="84">J56+$R$1*K56/MAX(1,($A56*($A56-1)))++$R$1/$A56</f>
-        <v>12.0244233325159</v>
+        <v>12.0242176497687</v>
       </c>
       <c r="M56" s="1">
         <f ca="1" t="shared" si="83"/>
-        <v>0.223556750853385</v>
+        <v>0.309452156591731</v>
       </c>
       <c r="N56" s="1">
         <f ca="1" t="shared" si="84"/>
-        <v>12.937277823271</v>
+        <v>12.9385181911254</v>
       </c>
       <c r="O56" s="1">
         <f ca="1" t="shared" si="83"/>
-        <v>0.596105019148938</v>
+        <v>0.710845230387937</v>
       </c>
       <c r="P56" s="1">
         <f ca="1" t="shared" si="84"/>
-        <v>13.8564041703948</v>
+        <v>13.859576191637</v>
       </c>
     </row>
     <row r="57" ht="16.5" spans="1:16">
@@ -9348,27 +9323,27 @@
       </c>
       <c r="K57" s="1">
         <f ca="1" t="shared" ref="K57:O57" si="85">RAND()</f>
-        <v>0.962047566684816</v>
+        <v>0.576767502105547</v>
       </c>
       <c r="L57" s="1">
         <f ca="1" t="shared" ref="L57:P57" si="86">J57+$R$1*K57/MAX(1,($A57*($A57-1)))++$R$1/$A57</f>
-        <v>11.8175657072514</v>
+        <v>11.8113111607485</v>
       </c>
       <c r="M57" s="1">
         <f ca="1" t="shared" si="85"/>
-        <v>0.637920487431689</v>
+        <v>0.188817814245969</v>
       </c>
       <c r="N57" s="1">
         <f ca="1" t="shared" si="86"/>
-        <v>12.7207787021772</v>
+        <v>12.7072335278628</v>
       </c>
       <c r="O57" s="1">
         <f ca="1" t="shared" si="85"/>
-        <v>0.490869545945595</v>
+        <v>0.674658131529615</v>
       </c>
       <c r="P57" s="1">
         <f ca="1" t="shared" si="86"/>
-        <v>13.6216045064945</v>
+        <v>13.6110429131149</v>
       </c>
     </row>
     <row r="58" ht="16.5" spans="1:16">
@@ -9408,27 +9383,27 @@
       </c>
       <c r="K58" s="1">
         <f ca="1" t="shared" ref="K58:O58" si="87">RAND()</f>
-        <v>0.954701629868488</v>
+        <v>0.299030887163281</v>
       </c>
       <c r="L58" s="1">
         <f ca="1" t="shared" ref="L58:P58" si="88">J58+$R$1*K58/MAX(1,($A58*($A58-1)))++$R$1/$A58</f>
-        <v>11.6064332962072</v>
+        <v>11.5961627645232</v>
       </c>
       <c r="M58" s="1">
         <f ca="1" t="shared" si="87"/>
-        <v>0.00104380673915427</v>
+        <v>0.115320494040202</v>
       </c>
       <c r="N58" s="1">
         <f ca="1" t="shared" si="88"/>
-        <v>12.4836426290195</v>
+        <v>12.4751621456955</v>
       </c>
       <c r="O58" s="1">
         <f ca="1" t="shared" si="87"/>
-        <v>0.230674039046092</v>
+        <v>0.0141786351823994</v>
       </c>
       <c r="P58" s="1">
         <f ca="1" t="shared" si="88"/>
-        <v>13.3644489266236</v>
+        <v>13.3525772245674</v>
       </c>
     </row>
     <row r="59" ht="16.5" spans="1:16">
@@ -9468,27 +9443,27 @@
       </c>
       <c r="K59" s="1">
         <f ca="1" t="shared" ref="K59:O59" si="89">RAND()</f>
-        <v>0.489704951255368</v>
+        <v>0.176199690308285</v>
       </c>
       <c r="L59" s="1">
         <f ca="1" t="shared" ref="L59:P59" si="90">J59+$R$1*K59/MAX(1,($A59*($A59-1)))++$R$1/$A59</f>
-        <v>11.3957910609688</v>
+        <v>11.3910496020918</v>
       </c>
       <c r="M59" s="1">
         <f ca="1" t="shared" si="89"/>
-        <v>0.433388545263016</v>
+        <v>0.874591502756476</v>
       </c>
       <c r="N59" s="1">
         <f ca="1" t="shared" si="90"/>
-        <v>12.2644146021857</v>
+        <v>12.2663459043113</v>
       </c>
       <c r="O59" s="1">
         <f ca="1" t="shared" si="89"/>
-        <v>0.709852136754094</v>
+        <v>0.587819849369956</v>
       </c>
       <c r="P59" s="1">
         <f ca="1" t="shared" si="90"/>
-        <v>13.1372193834433</v>
+        <v>13.1373050671875</v>
       </c>
     </row>
     <row r="60" ht="16.5" spans="1:16">
@@ -9528,27 +9503,27 @@
       </c>
       <c r="K60" s="1">
         <f ca="1" t="shared" ref="K60:O60" si="91">RAND()</f>
-        <v>0.357662246792222</v>
+        <v>0.363385008828885</v>
       </c>
       <c r="L60" s="1">
         <f ca="1" t="shared" ref="L60:P60" si="92">J60+$R$1*K60/MAX(1,($A60*($A60-1)))++$R$1/$A60</f>
-        <v>11.1975111374458</v>
+        <v>11.1975947546585</v>
       </c>
       <c r="M60" s="1">
         <f ca="1" t="shared" si="91"/>
-        <v>0.580649172100631</v>
+        <v>0.163219420572725</v>
       </c>
       <c r="N60" s="1">
         <f ca="1" t="shared" si="92"/>
-        <v>12.0534528261089</v>
+        <v>12.0474372359644</v>
       </c>
       <c r="O60" s="1">
         <f ca="1" t="shared" si="91"/>
-        <v>0.877194210126674</v>
+        <v>0.879152714737619</v>
       </c>
       <c r="P60" s="1">
         <f ca="1" t="shared" si="92"/>
-        <v>12.913727434673</v>
+        <v>12.9077404609021</v>
       </c>
     </row>
     <row r="61" ht="16.5" spans="1:16">
@@ -9588,27 +9563,27 @@
       </c>
       <c r="K61" s="1">
         <f ca="1" t="shared" ref="K61:O61" si="93">RAND()</f>
-        <v>0.320828526655423</v>
+        <v>0.982371338371249</v>
       </c>
       <c r="L61" s="1">
         <f ca="1" t="shared" ref="L61:P61" si="94">J61+$R$1*K61/MAX(1,($A61*($A61-1)))++$R$1/$A61</f>
-        <v>11.0073563351223</v>
+        <v>11.0167001601465</v>
       </c>
       <c r="M61" s="1">
         <f ca="1" t="shared" si="93"/>
-        <v>0.954598846465882</v>
+        <v>0.0206072356353579</v>
       </c>
       <c r="N61" s="1">
         <f ca="1" t="shared" si="94"/>
-        <v>11.8541727030102</v>
+        <v>11.85032455613</v>
       </c>
       <c r="O61" s="1">
         <f ca="1" t="shared" si="93"/>
-        <v>0.036162413558319</v>
+        <v>0.598507004948683</v>
       </c>
       <c r="P61" s="1">
         <f ca="1" t="shared" si="94"/>
-        <v>12.6880168048966</v>
+        <v>12.6921113782338</v>
       </c>
     </row>
     <row r="62" ht="16.5" spans="1:16">
@@ -9648,27 +9623,27 @@
       </c>
       <c r="K62" s="1">
         <f ca="1" t="shared" ref="K62:O62" si="95">RAND()</f>
-        <v>0.292914699823084</v>
+        <v>0.107720843854193</v>
       </c>
       <c r="L62" s="1">
         <f ca="1" t="shared" ref="L62:P62" si="96">J62+$R$1*K62/MAX(1,($A62*($A62-1)))++$R$1/$A62</f>
-        <v>10.823673698085</v>
+        <v>10.8211437273751</v>
       </c>
       <c r="M62" s="1">
         <f ca="1" t="shared" si="95"/>
-        <v>0.813383894259287</v>
+        <v>0.236239281134709</v>
       </c>
       <c r="N62" s="1">
         <f ca="1" t="shared" si="96"/>
-        <v>11.6544576310667</v>
+        <v>11.6440431711064</v>
       </c>
       <c r="O62" s="1">
         <f ca="1" t="shared" si="95"/>
-        <v>0.00589061449918038</v>
+        <v>0.728344249564206</v>
       </c>
       <c r="P62" s="1">
         <f ca="1" t="shared" si="96"/>
-        <v>12.4742102350899</v>
+        <v>12.4736653603081</v>
       </c>
     </row>
     <row r="63" ht="16.5" spans="1:16">
@@ -9708,27 +9683,27 @@
       </c>
       <c r="K63" s="1">
         <f ca="1" t="shared" ref="K63:O63" si="97">RAND()</f>
-        <v>0.34418245948752</v>
+        <v>0.630225026736764</v>
       </c>
       <c r="L63" s="1">
         <f ca="1" t="shared" ref="L63:P63" si="98">J63+$R$1*K63/MAX(1,($A63*($A63-1)))++$R$1/$A63</f>
-        <v>10.6470674571587</v>
+        <v>10.6508490881377</v>
       </c>
       <c r="M63" s="1">
         <f ca="1" t="shared" si="97"/>
-        <v>0.506912520152858</v>
+        <v>0.829719330858715</v>
       </c>
       <c r="N63" s="1">
         <f ca="1" t="shared" si="98"/>
-        <v>11.4602207162829</v>
+        <v>11.4682700205922</v>
       </c>
       <c r="O63" s="1">
         <f ca="1" t="shared" si="97"/>
-        <v>0.812096815633903</v>
+        <v>0.551673421651819</v>
       </c>
       <c r="P63" s="1">
         <f ca="1" t="shared" si="98"/>
-        <v>12.2774086699534</v>
+        <v>12.2820150420313</v>
       </c>
     </row>
     <row r="64" ht="16.5" spans="1:16">
@@ -9768,27 +9743,27 @@
       </c>
       <c r="K64" s="1">
         <f ca="1" t="shared" ref="K64:O64" si="99">RAND()</f>
-        <v>0.221902101084516</v>
+        <v>0.316160166155489</v>
       </c>
       <c r="L64" s="1">
         <f ca="1" t="shared" ref="L64:P64" si="100">J64+$R$1*K64/MAX(1,($A64*($A64-1)))++$R$1/$A64</f>
-        <v>10.4739106771772</v>
+        <v>10.4751172576313</v>
       </c>
       <c r="M64" s="1">
         <f ca="1" t="shared" si="99"/>
-        <v>0.115340715178015</v>
+        <v>0.872622382589964</v>
       </c>
       <c r="N64" s="1">
         <f ca="1" t="shared" si="100"/>
-        <v>11.2690379264755</v>
+        <v>11.2799383326772</v>
       </c>
       <c r="O64" s="1">
         <f ca="1" t="shared" si="99"/>
-        <v>0.539840104719847</v>
+        <v>0.839854450767654</v>
       </c>
       <c r="P64" s="1">
         <f ca="1" t="shared" si="100"/>
-        <v>12.069599115732</v>
+        <v>12.0843399513507</v>
       </c>
     </row>
     <row r="65" ht="16.5" spans="1:16">
@@ -9828,27 +9803,27 @@
       </c>
       <c r="K65" s="1">
         <f ca="1" t="shared" ref="K65:O65" si="101">RAND()</f>
-        <v>0.664277473241323</v>
+        <v>0.536074587596445</v>
       </c>
       <c r="L65" s="1">
         <f ca="1" t="shared" ref="L65:P65" si="102">J65+$R$1*K65/MAX(1,($A65*($A65-1)))++$R$1/$A65</f>
-        <v>10.3132970916821</v>
+        <v>10.3117072741517</v>
       </c>
       <c r="M65" s="1">
         <f ca="1" t="shared" si="101"/>
-        <v>0.137117689924259</v>
+        <v>0.811016406939302</v>
       </c>
       <c r="N65" s="1">
         <f ca="1" t="shared" si="102"/>
-        <v>11.0962474598607</v>
+        <v>11.1030145212616</v>
       </c>
       <c r="O65" s="1">
         <f ca="1" t="shared" si="101"/>
-        <v>0.54058717372212</v>
+        <v>0.306478819907076</v>
       </c>
       <c r="P65" s="1">
         <f ca="1" t="shared" si="102"/>
-        <v>11.8842011698523</v>
+        <v>11.8880651018656</v>
       </c>
     </row>
     <row r="66" ht="16.5" spans="1:16">
@@ -9888,27 +9863,27 @@
       </c>
       <c r="K66" s="1">
         <f ca="1" t="shared" ref="K66:O66" si="106">RAND()</f>
-        <v>0.422352666634542</v>
+        <v>0.879230280011452</v>
       </c>
       <c r="L66" s="1">
         <f ca="1" t="shared" ref="L66:P66" si="107">J66+$R$1*K66/MAX(1,($A66*($A66-1)))++$R$1/$A66</f>
-        <v>10.1493071233971</v>
+        <v>10.1547984408655</v>
       </c>
       <c r="M66" s="1">
         <f ca="1" t="shared" si="106"/>
-        <v>0.12984397532311</v>
+        <v>0.0757285120322477</v>
       </c>
       <c r="N66" s="1">
         <f ca="1" t="shared" si="107"/>
-        <v>10.9200985173312</v>
+        <v>10.9249394085582</v>
       </c>
       <c r="O66" s="1">
         <f ca="1" t="shared" si="106"/>
-        <v>0.784110312170466</v>
+        <v>0.291629548201985</v>
       </c>
       <c r="P66" s="1">
         <f ca="1" t="shared" si="107"/>
-        <v>11.6987536893525</v>
+        <v>11.697675340628</v>
       </c>
     </row>
     <row r="67" ht="16.5" spans="1:16">
@@ -9948,27 +9923,27 @@
       </c>
       <c r="K67" s="1">
         <f ca="1" t="shared" ref="K67:O67" si="108">RAND()</f>
-        <v>0.116063482558666</v>
+        <v>0.0621229473248055</v>
       </c>
       <c r="L67" s="1">
         <f ca="1" t="shared" ref="L67:P67" si="109">J67+$R$1*K67/MAX(1,($A67*($A67-1)))++$R$1/$A67</f>
-        <v>9.98969770958693</v>
+        <v>9.9890690320201</v>
       </c>
       <c r="M67" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.0276004189768104</v>
+        <v>0.151786549342834</v>
       </c>
       <c r="N67" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>10.7475951503675</v>
+        <v>10.7484138635975</v>
       </c>
       <c r="O67" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.465378016613301</v>
+        <v>0.163349017963036</v>
       </c>
       <c r="P67" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>11.5105948941509</v>
+        <v>11.5078934558815</v>
       </c>
     </row>
     <row r="68" ht="16.5" spans="1:16">
@@ -10008,27 +9983,27 @@
       </c>
       <c r="K68" s="1">
         <f ca="1" t="shared" ref="K68:O68" si="110">RAND()</f>
-        <v>0.793003984059914</v>
+        <v>0.0832016202171213</v>
       </c>
       <c r="L68" s="1">
         <f ca="1" t="shared" ref="L68:P68" si="111">J68+$R$1*K68/MAX(1,($A68*($A68-1)))++$R$1/$A68</f>
-        <v>9.84614432365513</v>
+        <v>9.83811851673696</v>
       </c>
       <c r="M68" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.208661737534123</v>
+        <v>0.257709859327856</v>
       </c>
       <c r="N68" s="1">
         <f ca="1" t="shared" si="111"/>
-        <v>10.5947723396833</v>
+        <v>10.5873011248252</v>
       </c>
       <c r="O68" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.721242081299206</v>
+        <v>0.396013975588541</v>
       </c>
       <c r="P68" s="1">
         <f ca="1" t="shared" si="111"/>
-        <v>11.349196153357</v>
+        <v>11.3380475515054</v>
       </c>
     </row>
     <row r="69" ht="16.5" spans="1:16">
@@ -10068,27 +10043,27 @@
       </c>
       <c r="K69" s="1">
         <f ca="1" t="shared" ref="K69:O69" si="112">RAND()</f>
-        <v>0.80717506717012</v>
+        <v>0.235391599021674</v>
       </c>
       <c r="L69" s="1">
         <f ca="1" t="shared" ref="L69:P69" si="113">J69+$R$1*K69/MAX(1,($A69*($A69-1)))++$R$1/$A69</f>
-        <v>9.69937637255454</v>
+        <v>9.69310131254413</v>
       </c>
       <c r="M69" s="1">
         <f ca="1" t="shared" si="112"/>
-        <v>0.848772732615186</v>
+        <v>0.187009232662606</v>
       </c>
       <c r="N69" s="1">
         <f ca="1" t="shared" si="113"/>
-        <v>10.4439853797167</v>
+        <v>10.4304477703214</v>
       </c>
       <c r="O69" s="1">
         <f ca="1" t="shared" si="112"/>
-        <v>0.337533111330811</v>
+        <v>0.435395476167456</v>
       </c>
       <c r="P69" s="1">
         <f ca="1" t="shared" si="113"/>
-        <v>11.1829837676813</v>
+        <v>11.1705201526323</v>
       </c>
     </row>
     <row r="70" ht="16.5" spans="1:16">
@@ -10128,27 +10103,27 @@
       </c>
       <c r="K70" s="1">
         <f ca="1" t="shared" ref="K70:O70" si="114">RAND()</f>
-        <v>0.711114505187117</v>
+        <v>0.537174930079317</v>
       </c>
       <c r="L70" s="1">
         <f ca="1" t="shared" ref="L70:P70" si="115">J70+$R$1*K70/MAX(1,($A70*($A70-1)))++$R$1/$A70</f>
-        <v>9.55574503948409</v>
+        <v>9.55389146344927</v>
       </c>
       <c r="M70" s="1">
         <f ca="1" t="shared" si="114"/>
-        <v>0.86293008520673</v>
+        <v>0.383153057817261</v>
       </c>
       <c r="N70" s="1">
         <f ca="1" t="shared" si="115"/>
-        <v>10.2895784802898</v>
+        <v>10.2826121908344</v>
       </c>
       <c r="O70" s="1">
         <f ca="1" t="shared" si="114"/>
-        <v>0.39636066566757</v>
+        <v>0.0494511995502229</v>
       </c>
       <c r="P70" s="1">
         <f ca="1" t="shared" si="115"/>
-        <v>11.0184399537091</v>
+        <v>11.007776845561</v>
       </c>
     </row>
     <row r="71" ht="16.5" spans="1:16">
@@ -10188,27 +10163,27 @@
       </c>
       <c r="K71" s="1">
         <f ca="1" t="shared" ref="K71:O71" si="116">RAND()</f>
-        <v>0.510480766377873</v>
+        <v>0.451528294435207</v>
       </c>
       <c r="L71" s="1">
         <f ca="1" t="shared" ref="L71:P71" si="117">J71+$R$1*K71/MAX(1,($A71*($A71-1)))++$R$1/$A71</f>
-        <v>9.41522236818196</v>
+        <v>9.41461209414529</v>
       </c>
       <c r="M71" s="1">
         <f ca="1" t="shared" si="116"/>
-        <v>0.862697263335984</v>
+        <v>0.0941078967374904</v>
       </c>
       <c r="N71" s="1">
         <f ca="1" t="shared" si="117"/>
-        <v>10.1384386959598</v>
+        <v>10.1298720102606</v>
       </c>
       <c r="O71" s="1">
         <f ca="1" t="shared" si="116"/>
-        <v>0.986463050341222</v>
+        <v>0.32933752950083</v>
       </c>
       <c r="P71" s="1">
         <f ca="1" t="shared" si="117"/>
-        <v>10.8629362430648</v>
+        <v>10.847567015742</v>
       </c>
     </row>
     <row r="72" ht="16.5" spans="1:16">
@@ -10248,27 +10223,27 @@
       </c>
       <c r="K72" s="1">
         <f ca="1" t="shared" ref="K72:O72" si="118">RAND()</f>
-        <v>0.829420391893495</v>
+        <v>0.254373136504336</v>
       </c>
       <c r="L72" s="1">
         <f ca="1" t="shared" ref="L72:P72" si="119">J72+$R$1*K72/MAX(1,($A72*($A72-1)))++$R$1/$A72</f>
-        <v>9.2839981930774</v>
+        <v>9.27821300942157</v>
       </c>
       <c r="M72" s="1">
         <f ca="1" t="shared" si="118"/>
-        <v>0.345993731583923</v>
+        <v>0.654524023152058</v>
       </c>
       <c r="N72" s="1">
         <f ca="1" t="shared" si="119"/>
-        <v>9.99170436743941</v>
+        <v>9.98902311025811</v>
       </c>
       <c r="O72" s="1">
         <f ca="1" t="shared" si="118"/>
-        <v>0.405272883621372</v>
+        <v>0.55723419657592</v>
       </c>
       <c r="P72" s="1">
         <f ca="1" t="shared" si="119"/>
-        <v>10.7000069115402</v>
+        <v>10.6988544402035</v>
       </c>
     </row>
     <row r="73" ht="16.5" spans="1:16">
@@ -10308,27 +10283,27 @@
       </c>
       <c r="K73" s="1">
         <f ca="1" t="shared" ref="K73:O73" si="120">RAND()</f>
-        <v>0.310725889539223</v>
+        <v>0.3082357185735</v>
       </c>
       <c r="L73" s="1">
         <f ca="1" t="shared" ref="L73:P73" si="121">J73+$R$1*K73/MAX(1,($A73*($A73-1)))++$R$1/$A73</f>
-        <v>9.14818785103227</v>
+        <v>9.14816349489997</v>
       </c>
       <c r="M73" s="1">
         <f ca="1" t="shared" si="120"/>
-        <v>0.990286944852194</v>
+        <v>0.120953986586239</v>
       </c>
       <c r="N73" s="1">
         <f ca="1" t="shared" si="121"/>
-        <v>9.85231820064937</v>
+        <v>9.84379097911932</v>
       </c>
       <c r="O73" s="1">
         <f ca="1" t="shared" si="120"/>
-        <v>0.607969753897316</v>
+        <v>0.880377745747247</v>
       </c>
       <c r="P73" s="1">
         <f ca="1" t="shared" si="121"/>
-        <v>10.5527091411218</v>
+        <v>10.5468463170081</v>
       </c>
     </row>
     <row r="74" ht="16.5" spans="1:16">
@@ -10368,27 +10343,27 @@
       </c>
       <c r="K74" s="1">
         <f ca="1" t="shared" ref="K74:O74" si="122">RAND()</f>
-        <v>0.473592346170097</v>
+        <v>0.645538643745291</v>
       </c>
       <c r="L74" s="1">
         <f ca="1" t="shared" ref="L74:P74" si="123">J74+$R$1*K74/MAX(1,($A74*($A74-1)))++$R$1/$A74</f>
-        <v>9.02277009461729</v>
+        <v>9.02440580901584</v>
       </c>
       <c r="M74" s="1">
         <f ca="1" t="shared" si="122"/>
-        <v>0.485499004476773</v>
+        <v>0.73577912987757</v>
       </c>
       <c r="N74" s="1">
         <f ca="1" t="shared" si="123"/>
-        <v>9.7123201231987</v>
+        <v>9.71633673681148</v>
       </c>
       <c r="O74" s="1">
         <f ca="1" t="shared" si="122"/>
-        <v>0.206941219710501</v>
+        <v>0.298553000673609</v>
       </c>
       <c r="P74" s="1">
         <f ca="1" t="shared" si="123"/>
-        <v>10.399220248957</v>
+        <v>10.404108359725</v>
       </c>
     </row>
     <row r="75" ht="16.5" spans="1:16">
@@ -10542,27 +10517,27 @@
       </c>
       <c r="K77" s="1">
         <f ca="1" t="shared" ref="K77:O77" si="127">RAND()</f>
-        <v>0.609462606608179</v>
+        <v>0.908666444176373</v>
       </c>
       <c r="L77" s="1">
         <f ca="1" t="shared" ref="L77:P77" si="128">J77+$R$1*K77/MAX(1,($A77*($A77-1)))++$R$1/$A77</f>
-        <v>8.66324090005797</v>
+        <v>8.66586549512435</v>
       </c>
       <c r="M77" s="1">
         <f ca="1" t="shared" si="127"/>
-        <v>0.270461364211288</v>
+        <v>0.525592987613641</v>
       </c>
       <c r="N77" s="1">
         <f ca="1" t="shared" si="128"/>
-        <v>9.32350810500719</v>
+        <v>9.32837069677009</v>
       </c>
       <c r="O77" s="1">
         <f ca="1" t="shared" si="127"/>
-        <v>0.483830270242076</v>
+        <v>0.882750612430578</v>
       </c>
       <c r="P77" s="1">
         <f ca="1" t="shared" si="128"/>
-        <v>9.98564696702686</v>
+        <v>9.99400886003702</v>
       </c>
     </row>
     <row r="78" ht="16.5" spans="1:16">
@@ -10602,27 +10577,27 @@
       </c>
       <c r="K78" s="1">
         <f ca="1" t="shared" ref="K78:O78" si="129">RAND()</f>
-        <v>0.65595379700631</v>
+        <v>0.480501511784591</v>
       </c>
       <c r="L78" s="1">
         <f ca="1" t="shared" ref="L78:P78" si="130">J78+$R$1*K78/MAX(1,($A78*($A78-1)))++$R$1/$A78</f>
-        <v>8.54969201808789</v>
+        <v>8.54819293841237</v>
       </c>
       <c r="M78" s="1">
         <f ca="1" t="shared" si="129"/>
-        <v>0.110659019333865</v>
+        <v>0.839714498195246</v>
       </c>
       <c r="N78" s="1">
         <f ca="1" t="shared" si="130"/>
-        <v>9.19998814778144</v>
+        <v>9.20471818190345</v>
       </c>
       <c r="O78" s="1">
         <f ca="1" t="shared" si="129"/>
-        <v>0.6154491607344</v>
+        <v>0.814921332720053</v>
       </c>
       <c r="P78" s="1">
         <f ca="1" t="shared" si="130"/>
-        <v>9.85459724860795</v>
+        <v>9.86103159041951</v>
       </c>
     </row>
     <row r="79" ht="16.5" spans="1:16">
@@ -10662,27 +10637,27 @@
       </c>
       <c r="K79" s="1">
         <f ca="1" t="shared" ref="K79:O79" si="131">RAND()</f>
-        <v>0.520200098862502</v>
+        <v>0.336690869957127</v>
       </c>
       <c r="L79" s="1">
         <f ca="1" t="shared" ref="L79:P79" si="132">J79+$R$1*K79/MAX(1,($A79*($A79-1)))++$R$1/$A79</f>
-        <v>8.43756410338714</v>
+        <v>8.43603638752878</v>
       </c>
       <c r="M79" s="1">
         <f ca="1" t="shared" si="131"/>
-        <v>0.644903391085741</v>
+        <v>0.100366274804318</v>
       </c>
       <c r="N79" s="1">
         <f ca="1" t="shared" si="132"/>
-        <v>9.08395857051239</v>
+        <v>9.07789757862771</v>
       </c>
       <c r="O79" s="1">
         <f ca="1" t="shared" si="131"/>
-        <v>0.972413028235047</v>
+        <v>0.971244534126548</v>
       </c>
       <c r="P79" s="1">
         <f ca="1" t="shared" si="132"/>
-        <v>9.73307955809343</v>
+        <v>9.72700883848558</v>
       </c>
     </row>
     <row r="80" ht="16.5" spans="1:16">
@@ -10722,27 +10697,27 @@
       </c>
       <c r="K80" s="1">
         <f ca="1" t="shared" ref="K80:O80" si="133">RAND()</f>
-        <v>0.144062079330552</v>
+        <v>0.863557987828934</v>
       </c>
       <c r="L80" s="1">
         <f ca="1" t="shared" ref="L80:P80" si="134">J80+$R$1*K80/MAX(1,($A80*($A80-1)))++$R$1/$A80</f>
-        <v>8.32638804024124</v>
+        <v>8.33222620892428</v>
       </c>
       <c r="M80" s="1">
         <f ca="1" t="shared" si="133"/>
-        <v>0.732216321102323</v>
+        <v>0.889971532346015</v>
       </c>
       <c r="N80" s="1">
         <f ca="1" t="shared" si="134"/>
-        <v>8.96524081791977</v>
+        <v>8.97235905160804</v>
       </c>
       <c r="O80" s="1">
         <f ca="1" t="shared" si="133"/>
-        <v>0.35173430895447</v>
+        <v>0.0949073880809694</v>
       </c>
       <c r="P80" s="1">
         <f ca="1" t="shared" si="134"/>
-        <v>9.60100626995608</v>
+        <v>9.60604054615592</v>
       </c>
     </row>
     <row r="81" ht="16.5" spans="1:16">
@@ -10782,27 +10757,27 @@
       </c>
       <c r="K81" s="1">
         <f ca="1" t="shared" ref="K81:O81" si="135">RAND()</f>
-        <v>0.694101005915298</v>
+        <v>0.957160990690132</v>
       </c>
       <c r="L81" s="1">
         <f ca="1" t="shared" ref="L81:P81" si="136">J81+$R$1*K81/MAX(1,($A81*($A81-1)))++$R$1/$A81</f>
-        <v>8.22542801428731</v>
+        <v>8.22750918505293</v>
       </c>
       <c r="M81" s="1">
         <f ca="1" t="shared" si="135"/>
-        <v>0.366974324941202</v>
+        <v>0.290078294064353</v>
       </c>
       <c r="N81" s="1">
         <f ca="1" t="shared" si="136"/>
-        <v>8.8533312921745</v>
+        <v>8.85480410826546</v>
       </c>
       <c r="O81" s="1">
         <f ca="1" t="shared" si="135"/>
-        <v>0.52071070683963</v>
+        <v>0.354544735672425</v>
       </c>
       <c r="P81" s="1">
         <f ca="1" t="shared" si="136"/>
-        <v>9.48245083890582</v>
+        <v>9.48260905079452</v>
       </c>
     </row>
     <row r="82" ht="16.5" spans="1:16">
@@ -10842,27 +10817,27 @@
       </c>
       <c r="K82" s="1">
         <f ca="1" t="shared" ref="K82:O82" si="137">RAND()</f>
-        <v>0.150160322266386</v>
+        <v>0.942481516259535</v>
       </c>
       <c r="L82" s="1">
         <f ca="1" t="shared" ref="L82:P82" si="138">J82+$R$1*K82/MAX(1,($A82*($A82-1)))++$R$1/$A82</f>
-        <v>8.11844259507922</v>
+        <v>8.12455618453904</v>
       </c>
       <c r="M82" s="1">
         <f ca="1" t="shared" si="137"/>
-        <v>0.365240467508827</v>
+        <v>0.149150466413088</v>
       </c>
       <c r="N82" s="1">
         <f ca="1" t="shared" si="138"/>
-        <v>8.73854475918036</v>
+        <v>8.74299098752062</v>
       </c>
       <c r="O82" s="1">
         <f ca="1" t="shared" si="137"/>
-        <v>0.0608171508912438</v>
+        <v>0.53402533378029</v>
       </c>
       <c r="P82" s="1">
         <f ca="1" t="shared" si="138"/>
-        <v>9.35629797793724</v>
+        <v>9.36439550398497</v>
       </c>
     </row>
     <row r="83" ht="16.5" spans="1:16">
@@ -10902,27 +10877,27 @@
       </c>
       <c r="K83" s="1">
         <f ca="1" t="shared" ref="K83:O83" si="139">RAND()</f>
-        <v>0.413594471221387</v>
+        <v>0.36043049098472</v>
       </c>
       <c r="L83" s="1">
         <f ca="1" t="shared" ref="L83:P83" si="140">J83+$R$1*K83/MAX(1,($A83*($A83-1)))++$R$1/$A83</f>
-        <v>8.02027698337264</v>
+        <v>8.01987677274153</v>
       </c>
       <c r="M83" s="1">
         <f ca="1" t="shared" si="139"/>
-        <v>0.867458832949618</v>
+        <v>0.899537795894995</v>
       </c>
       <c r="N83" s="1">
         <f ca="1" t="shared" si="140"/>
-        <v>8.63656318356046</v>
+        <v>8.6364044586486</v>
       </c>
       <c r="O83" s="1">
         <f ca="1" t="shared" si="139"/>
-        <v>0.617973992491609</v>
+        <v>0.830967139246133</v>
       </c>
       <c r="P83" s="1">
         <f ca="1" t="shared" si="140"/>
-        <v>9.25097129852953</v>
+        <v>9.25241595472844</v>
       </c>
     </row>
     <row r="84" ht="16.5" spans="1:16">
@@ -10962,27 +10937,27 @@
       </c>
       <c r="K84" s="1">
         <f ca="1" t="shared" ref="K84:O84" si="141">RAND()</f>
-        <v>0.121038354914054</v>
+        <v>0.477031962793678</v>
       </c>
       <c r="L84" s="1">
         <f ca="1" t="shared" ref="L84:P84" si="142">J84+$R$1*K84/MAX(1,($A84*($A84-1)))++$R$1/$A84</f>
-        <v>7.92037201259855</v>
+        <v>7.92298730504551</v>
       </c>
       <c r="M84" s="1">
         <f ca="1" t="shared" si="141"/>
-        <v>0.929994245963429</v>
+        <v>0.509556887167194</v>
       </c>
       <c r="N84" s="1">
         <f ca="1" t="shared" si="142"/>
-        <v>8.52961381575725</v>
+        <v>8.52914038238291</v>
       </c>
       <c r="O84" s="1">
         <f ca="1" t="shared" si="141"/>
-        <v>0.610087232100242</v>
+        <v>0.632329190614911</v>
       </c>
       <c r="P84" s="1">
         <f ca="1" t="shared" si="142"/>
-        <v>9.13650543515264</v>
+        <v>9.13619540141475</v>
       </c>
     </row>
     <row r="85" ht="16.5" spans="1:16">
@@ -11022,27 +10997,27 @@
       </c>
       <c r="K85" s="1">
         <f ca="1" t="shared" ref="K85:O85" si="143">RAND()</f>
-        <v>0.452532052232778</v>
+        <v>0.00517069878615417</v>
       </c>
       <c r="L85" s="1">
         <f ca="1" t="shared" ref="L85:P85" si="144">J85+$R$1*K85/MAX(1,($A85*($A85-1)))++$R$1/$A85</f>
-        <v>7.82739911110322</v>
+        <v>7.82419083977901</v>
       </c>
       <c r="M85" s="1">
         <f ca="1" t="shared" si="143"/>
-        <v>0.949455270817597</v>
+        <v>0.184384392808018</v>
       </c>
       <c r="N85" s="1">
         <f ca="1" t="shared" si="144"/>
-        <v>8.4294462659427</v>
+        <v>8.42075125567695</v>
       </c>
       <c r="O85" s="1">
         <f ca="1" t="shared" si="143"/>
-        <v>0.105116187030152</v>
+        <v>0.226429562055273</v>
       </c>
       <c r="P85" s="1">
         <f ca="1" t="shared" si="144"/>
-        <v>9.02543820646931</v>
+        <v>9.01761320032737</v>
       </c>
     </row>
     <row r="86" ht="16.5" spans="1:16">
@@ -11082,27 +11057,27 @@
       </c>
       <c r="K86" s="1">
         <f ca="1" t="shared" ref="K86:O86" si="145">RAND()</f>
-        <v>0.951542069967869</v>
+        <v>0.672364482630485</v>
       </c>
       <c r="L86" s="1">
         <f ca="1" t="shared" ref="L86:P86" si="146">J86+$R$1*K86/MAX(1,($A86*($A86-1)))++$R$1/$A86</f>
-        <v>7.73775589684851</v>
+        <v>7.7358008717271</v>
       </c>
       <c r="M86" s="1">
         <f ca="1" t="shared" si="145"/>
-        <v>0.509286867680148</v>
+        <v>0.814084581937174</v>
       </c>
       <c r="N86" s="1">
         <f ca="1" t="shared" si="146"/>
-        <v>8.32955762561378</v>
+        <v>8.32973703826728</v>
       </c>
       <c r="O86" s="1">
         <f ca="1" t="shared" si="145"/>
-        <v>0.333409154044211</v>
+        <v>0.64932794447973</v>
       </c>
       <c r="P86" s="1">
         <f ca="1" t="shared" si="146"/>
-        <v>8.92012771772894</v>
+        <v>8.92251944684206</v>
       </c>
     </row>
     <row r="87" ht="16.5" spans="1:16">
@@ -11256,27 +11231,27 @@
       </c>
       <c r="K89" s="1">
         <f ca="1" t="shared" ref="K89:O89" si="149">RAND()</f>
-        <v>0.999690439092608</v>
+        <v>0.992515759561432</v>
       </c>
       <c r="L89" s="1">
         <f ca="1" t="shared" ref="L89:P89" si="150">J89+$R$1*K89/MAX(1,($A89*($A89-1)))++$R$1/$A89</f>
-        <v>7.47126234612783</v>
+        <v>7.47121548954781</v>
       </c>
       <c r="M89" s="1">
         <f ca="1" t="shared" si="149"/>
-        <v>0.410626201004421</v>
+        <v>0.511438568582007</v>
       </c>
       <c r="N89" s="1">
         <f ca="1" t="shared" si="150"/>
-        <v>8.04212589237263</v>
+        <v>8.04273742377314</v>
       </c>
       <c r="O89" s="1">
         <f ca="1" t="shared" si="149"/>
-        <v>0.274384719253801</v>
+        <v>0.336631886970153</v>
       </c>
       <c r="P89" s="1">
         <f ca="1" t="shared" si="150"/>
-        <v>8.61209966927476</v>
+        <v>8.61311772606527</v>
       </c>
     </row>
     <row r="90" ht="16.5" spans="1:16">
@@ -11316,27 +11291,27 @@
       </c>
       <c r="K90" s="1">
         <f ca="1" t="shared" ref="K90:O90" si="151">RAND()</f>
-        <v>0.99035656624007</v>
+        <v>0.252040224032516</v>
       </c>
       <c r="L90" s="1">
         <f ca="1" t="shared" ref="L90:P90" si="152">J90+$R$1*K90/MAX(1,($A90*($A90-1)))++$R$1/$A90</f>
-        <v>7.38630207205209</v>
+        <v>7.38158861225762</v>
       </c>
       <c r="M90" s="1">
         <f ca="1" t="shared" si="151"/>
-        <v>0.911885629987566</v>
+        <v>0.111339157713189</v>
       </c>
       <c r="N90" s="1">
         <f ca="1" t="shared" si="152"/>
-        <v>7.95392136233547</v>
+        <v>7.944097161528</v>
       </c>
       <c r="O90" s="1">
         <f ca="1" t="shared" si="151"/>
-        <v>0.31637724951607</v>
+        <v>0.112132179207351</v>
       </c>
       <c r="P90" s="1">
         <f ca="1" t="shared" si="152"/>
-        <v>8.51773888818784</v>
+        <v>8.50661077349945</v>
       </c>
     </row>
     <row r="91" ht="16.5" spans="1:16">
@@ -11376,27 +11351,27 @@
       </c>
       <c r="K91" s="1">
         <f ca="1" t="shared" ref="K91:O91" si="153">RAND()</f>
-        <v>0.951087001070644</v>
+        <v>0.391749662452552</v>
       </c>
       <c r="L91" s="1">
         <f ca="1" t="shared" ref="L91:P91" si="154">J91+$R$1*K91/MAX(1,($A91*($A91-1)))++$R$1/$A91</f>
-        <v>7.30306546192928</v>
+        <v>7.29957396793041</v>
       </c>
       <c r="M91" s="1">
         <f ca="1" t="shared" si="153"/>
-        <v>0.595716379622113</v>
+        <v>0.0461749782474896</v>
       </c>
       <c r="N91" s="1">
         <f ca="1" t="shared" si="154"/>
-        <v>7.86233959663354</v>
+        <v>7.85541775680836</v>
       </c>
       <c r="O91" s="1">
         <f ca="1" t="shared" si="153"/>
-        <v>0.481953573499023</v>
+        <v>0.909215152794394</v>
       </c>
       <c r="P91" s="1">
         <f ca="1" t="shared" si="154"/>
-        <v>8.42090360146187</v>
+        <v>8.41664881269347</v>
       </c>
     </row>
     <row r="92" ht="16.5" spans="1:16">
@@ -11436,27 +11411,27 @@
       </c>
       <c r="K92" s="1">
         <f ca="1" t="shared" ref="K92:O92" si="155">RAND()</f>
-        <v>0.207825961888096</v>
+        <v>0.435227951559306</v>
       </c>
       <c r="L92" s="1">
         <f ca="1" t="shared" ref="L92:P92" si="156">J92+$R$1*K92/MAX(1,($A92*($A92-1)))++$R$1/$A92</f>
-        <v>7.21738599488332</v>
+        <v>7.21877428541856</v>
       </c>
       <c r="M92" s="1">
         <f ca="1" t="shared" si="155"/>
-        <v>0.874879870443335</v>
+        <v>0.982030489703067</v>
       </c>
       <c r="N92" s="1">
         <f ca="1" t="shared" si="156"/>
-        <v>7.77217769128408</v>
+        <v>7.77422013700405</v>
       </c>
       <c r="O92" s="1">
         <f ca="1" t="shared" si="155"/>
-        <v>0.645407831435425</v>
+        <v>0.0275580913552955</v>
       </c>
       <c r="P92" s="1">
         <f ca="1" t="shared" si="156"/>
-        <v>8.32556845948576</v>
+        <v>8.32383892877056</v>
       </c>
     </row>
     <row r="93" ht="16.5" spans="1:16">
@@ -11496,27 +11471,27 @@
       </c>
       <c r="K93" s="1">
         <f ca="1" t="shared" ref="K93:O93" si="157">RAND()</f>
-        <v>0.978844558017969</v>
+        <v>0.17548769559197</v>
       </c>
       <c r="L93" s="1">
         <f ca="1" t="shared" ref="L93:P93" si="158">J93+$R$1*K93/MAX(1,($A93*($A93-1)))++$R$1/$A93</f>
-        <v>7.14273079645257</v>
+        <v>7.13793291743664</v>
       </c>
       <c r="M93" s="1">
         <f ca="1" t="shared" si="157"/>
-        <v>0.665080316996187</v>
+        <v>0.0323797095398477</v>
       </c>
       <c r="N93" s="1">
         <f ca="1" t="shared" si="158"/>
-        <v>7.69018110890477</v>
+        <v>7.68160455927575</v>
       </c>
       <c r="O93" s="1">
         <f ca="1" t="shared" si="157"/>
-        <v>0.391456053543648</v>
+        <v>0.635758358648453</v>
       </c>
       <c r="P93" s="1">
         <f ca="1" t="shared" si="158"/>
-        <v>8.23599725829287</v>
+        <v>8.22887975253094</v>
       </c>
     </row>
     <row r="94" ht="16.5" spans="1:16">
@@ -11556,27 +11531,27 @@
       </c>
       <c r="K94" s="1">
         <f ca="1" t="shared" ref="K94:O94" si="159">RAND()</f>
-        <v>0.952203965750061</v>
+        <v>0.117687989812941</v>
       </c>
       <c r="L94" s="1">
         <f ca="1" t="shared" ref="L94:P94" si="160">J94+$R$1*K94/MAX(1,($A94*($A94-1)))++$R$1/$A94</f>
-        <v>7.06493807834122</v>
+        <v>7.06006129026305</v>
       </c>
       <c r="M94" s="1">
         <f ca="1" t="shared" si="159"/>
-        <v>0.616071238290789</v>
+        <v>0.369314653966818</v>
       </c>
       <c r="N94" s="1">
         <f ca="1" t="shared" si="160"/>
-        <v>7.60617271624615</v>
+        <v>7.59985391914317</v>
       </c>
       <c r="O94" s="1">
         <f ca="1" t="shared" si="159"/>
-        <v>0.973458206867605</v>
+        <v>0.530536664251997</v>
       </c>
       <c r="P94" s="1">
         <f ca="1" t="shared" si="160"/>
-        <v>8.14949587079773</v>
+        <v>8.14058870563366</v>
       </c>
     </row>
     <row r="95" ht="16.5" spans="1:16">
@@ -11616,27 +11591,27 @@
       </c>
       <c r="K95" s="1">
         <f ca="1" t="shared" ref="K95:O95" si="161">RAND()</f>
-        <v>0.214934503918403</v>
+        <v>0.844648361894326</v>
       </c>
       <c r="L95" s="1">
         <f ca="1" t="shared" ref="L95:P95" si="162">J95+$R$1*K95/MAX(1,($A95*($A95-1)))++$R$1/$A95</f>
-        <v>6.98475711795881</v>
+        <v>6.98835877580585</v>
       </c>
       <c r="M95" s="1">
         <f ca="1" t="shared" si="161"/>
-        <v>0.61848523668268</v>
+        <v>0.248311841534792</v>
       </c>
       <c r="N95" s="1">
         <f ca="1" t="shared" si="162"/>
-        <v>7.52020944715512</v>
+        <v>7.52169389272151</v>
       </c>
       <c r="O95" s="1">
         <f ca="1" t="shared" si="161"/>
-        <v>0.822783671039529</v>
+        <v>0.278681015960751</v>
       </c>
       <c r="P95" s="1">
         <f ca="1" t="shared" si="162"/>
-        <v>8.05683026430817</v>
+        <v>8.05520270658539</v>
       </c>
     </row>
     <row r="96" ht="16.5" spans="1:16">
@@ -11676,27 +11651,27 @@
       </c>
       <c r="K96" s="1">
         <f ca="1" t="shared" ref="K96:O96" si="163">RAND()</f>
-        <v>0.555194704212947</v>
+        <v>0.535535182922426</v>
       </c>
       <c r="L96" s="1">
         <f ca="1" t="shared" ref="L96:P96" si="164">J96+$R$1*K96/MAX(1,($A96*($A96-1)))++$R$1/$A96</f>
-        <v>6.91240310584666</v>
+        <v>6.91229303013955</v>
       </c>
       <c r="M96" s="1">
         <f ca="1" t="shared" si="163"/>
-        <v>0.837822215646088</v>
+        <v>0.685700945423441</v>
       </c>
       <c r="N96" s="1">
         <f ca="1" t="shared" si="164"/>
-        <v>7.44340994915934</v>
+        <v>7.44244813061784</v>
       </c>
       <c r="O96" s="1">
         <f ca="1" t="shared" si="163"/>
-        <v>0.576394803967761</v>
+        <v>0.883468314147892</v>
       </c>
       <c r="P96" s="1">
         <f ca="1" t="shared" si="164"/>
-        <v>7.97295303316812</v>
+        <v>7.97371055118978</v>
       </c>
     </row>
     <row r="97" ht="16.5" spans="1:16">
@@ -11736,27 +11711,27 @@
       </c>
       <c r="K97" s="1">
         <f ca="1" t="shared" ref="K97:O97" si="165">RAND()</f>
-        <v>0.214680857356646</v>
+        <v>0.982894403782189</v>
       </c>
       <c r="L97" s="1">
         <f ca="1" t="shared" ref="L97:P97" si="166">J97+$R$1*K97/MAX(1,($A97*($A97-1)))++$R$1/$A97</f>
-        <v>6.83779978540217</v>
+        <v>6.84201148247687</v>
       </c>
       <c r="M97" s="1">
         <f ca="1" t="shared" si="165"/>
-        <v>0.697312309469668</v>
+        <v>0.0219822370655671</v>
       </c>
       <c r="N97" s="1">
         <f ca="1" t="shared" si="166"/>
-        <v>7.3624561028883</v>
+        <v>7.36296533246079</v>
       </c>
       <c r="O97" s="1">
         <f ca="1" t="shared" si="165"/>
-        <v>0.509987229539316</v>
+        <v>0.177352024136529</v>
       </c>
       <c r="P97" s="1">
         <f ca="1" t="shared" si="166"/>
-        <v>7.88608541883972</v>
+        <v>7.88477099048785</v>
       </c>
     </row>
     <row r="98" ht="16.5" spans="1:16">
@@ -11796,27 +11771,27 @@
       </c>
       <c r="K98" s="1">
         <f ca="1" t="shared" ref="K98:O98" si="167">RAND()</f>
-        <v>0.14002666594476</v>
+        <v>0.339603445482476</v>
       </c>
       <c r="L98" s="1">
         <f ca="1" t="shared" ref="L98:P98" si="168">J98+$R$1*K98/MAX(1,($A98*($A98-1)))++$R$1/$A98</f>
-        <v>6.76621577891938</v>
+        <v>6.76728738963425</v>
       </c>
       <c r="M98" s="1">
         <f ca="1" t="shared" si="167"/>
-        <v>0.86015783624368</v>
+        <v>0.366214816348723</v>
       </c>
       <c r="N98" s="1">
         <f ca="1" t="shared" si="168"/>
-        <v>7.28629824152807</v>
+        <v>7.28471766678389</v>
       </c>
       <c r="O98" s="1">
         <f ca="1" t="shared" si="167"/>
-        <v>0.24121113456431</v>
+        <v>0.317865201925549</v>
       </c>
       <c r="P98" s="1">
         <f ca="1" t="shared" si="168"/>
-        <v>7.80305732193274</v>
+        <v>7.80188833474955</v>
       </c>
     </row>
     <row r="99" ht="16.5" spans="1:16">
@@ -11856,27 +11831,27 @@
       </c>
       <c r="K99" s="1">
         <f ca="1" t="shared" ref="K99:O99" si="169">RAND()</f>
-        <v>0.900004067501697</v>
+        <v>0.749522523163122</v>
       </c>
       <c r="L99" s="1">
         <f ca="1" t="shared" ref="L99:P99" si="170">J99+$R$1*K99/MAX(1,($A99*($A99-1)))++$R$1/$A99</f>
-        <v>6.70050496564013</v>
+        <v>6.69971345741197</v>
       </c>
       <c r="M99" s="1">
         <f ca="1" t="shared" si="169"/>
-        <v>0.605050483647492</v>
+        <v>0.340573613094492</v>
       </c>
       <c r="N99" s="1">
         <f ca="1" t="shared" si="170"/>
-        <v>7.21389151352382</v>
+        <v>7.21170890035903</v>
       </c>
       <c r="O99" s="1">
         <f ca="1" t="shared" si="169"/>
-        <v>0.0498744894551026</v>
+        <v>0.678411648269607</v>
       </c>
       <c r="P99" s="1">
         <f ca="1" t="shared" si="170"/>
-        <v>7.72435792678626</v>
+        <v>7.72548131592956</v>
       </c>
     </row>
     <row r="100" ht="16.5" spans="1:16">
@@ -11916,27 +11891,27 @@
       </c>
       <c r="K100" s="1">
         <f ca="1" t="shared" ref="K100:O100" si="171">RAND()</f>
-        <v>0.546421722243013</v>
+        <v>0.12099284205504</v>
       </c>
       <c r="L100" s="1">
         <f ca="1" t="shared" ref="L100:P100" si="172">J100+$R$1*K100/MAX(1,($A100*($A100-1)))++$R$1/$A100</f>
-        <v>6.63031551083407</v>
+        <v>6.62812303051977</v>
       </c>
       <c r="M100" s="1">
         <f ca="1" t="shared" si="171"/>
-        <v>0.780177401782107</v>
+        <v>0.0308410036039357</v>
       </c>
       <c r="N100" s="1">
         <f ca="1" t="shared" si="172"/>
-        <v>7.13938671987232</v>
+        <v>7.13333247704422</v>
       </c>
       <c r="O100" s="1">
         <f ca="1" t="shared" si="171"/>
-        <v>0.859575981240703</v>
+        <v>0.919116666297905</v>
       </c>
       <c r="P100" s="1">
         <f ca="1" t="shared" si="172"/>
-        <v>7.64886711557032</v>
+        <v>7.64311972022242</v>
       </c>
     </row>
     <row r="101" ht="16.5" spans="1:16">
@@ -11976,27 +11951,27 @@
       </c>
       <c r="K101" s="1">
         <f ca="1" t="shared" ref="K101:O101" si="173">RAND()</f>
-        <v>0.209018321639142</v>
+        <v>0.600452107815753</v>
       </c>
       <c r="L101" s="1">
         <f ca="1" t="shared" ref="L101:P101" si="174">J101+$R$1*K101/MAX(1,($A101*($A101-1)))++$R$1/$A101</f>
-        <v>6.56166170869515</v>
+        <v>6.56363864700917</v>
       </c>
       <c r="M101" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.609475433002806</v>
+        <v>0.407420601875879</v>
       </c>
       <c r="N101" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>7.06473986744769</v>
+        <v>7.06569632681662</v>
       </c>
       <c r="O101" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.282776555708112</v>
+        <v>0.957656777936848</v>
       </c>
       <c r="P101" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>7.56616803187045</v>
+        <v>7.57053297721024</v>
       </c>
     </row>
     <row r="102" ht="16.5" spans="1:16">
@@ -12150,27 +12125,27 @@
       </c>
       <c r="K104" s="1">
         <f ca="1" t="shared" ref="K104:O104" si="177">RAND()</f>
-        <v>0.379248664745552</v>
+        <v>0.68444488522771</v>
       </c>
       <c r="L104" s="1">
         <f ca="1" t="shared" ref="L104:P104" si="178">J104+$R$1*K104/MAX(1,($A104*($A104-1)))++$R$1/$A104</f>
-        <v>6.36959474902316</v>
+        <v>6.37104723436716</v>
       </c>
       <c r="M104" s="1">
         <f ca="1" t="shared" si="177"/>
-        <v>0.447308455312509</v>
+        <v>0.152213849745762</v>
       </c>
       <c r="N104" s="1">
         <f ca="1" t="shared" si="178"/>
-        <v>6.85716046601969</v>
+        <v>6.85720854147617</v>
       </c>
       <c r="O104" s="1">
         <f ca="1" t="shared" si="177"/>
-        <v>0.492044212279471</v>
+        <v>0.593618003463857</v>
       </c>
       <c r="P104" s="1">
         <f ca="1" t="shared" si="178"/>
-        <v>7.34493908876993</v>
+        <v>7.34547057271291</v>
       </c>
     </row>
     <row r="105" ht="16.5" spans="1:16">
@@ -12210,27 +12185,27 @@
       </c>
       <c r="K105" s="1">
         <f ca="1" t="shared" ref="K105:O105" si="179">RAND()</f>
-        <v>0.712280991910336</v>
+        <v>0.28875264694334</v>
       </c>
       <c r="L105" s="1">
         <f ca="1" t="shared" ref="L105:P105" si="180">J105+$R$1*K105/MAX(1,($A105*($A105-1)))++$R$1/$A105</f>
-        <v>6.30933663644469</v>
+        <v>6.30735974909888</v>
       </c>
       <c r="M105" s="1">
         <f ca="1" t="shared" si="179"/>
-        <v>0.208961669202934</v>
+        <v>0.348531426105049</v>
       </c>
       <c r="N105" s="1">
         <f ca="1" t="shared" si="180"/>
-        <v>6.79108122974754</v>
+        <v>6.78975580691303</v>
       </c>
       <c r="O105" s="1">
         <f ca="1" t="shared" si="179"/>
-        <v>0.321808007063908</v>
+        <v>0.559986884364687</v>
       </c>
       <c r="P105" s="1">
         <f ca="1" t="shared" si="180"/>
-        <v>7.27335255166252</v>
+        <v>7.27313886742631</v>
       </c>
     </row>
     <row r="106" ht="16.5" spans="1:16">
@@ -12270,27 +12245,27 @@
       </c>
       <c r="K106" s="1">
         <f ca="1" t="shared" ref="K106:O106" si="181">RAND()</f>
-        <v>0.110387146208951</v>
+        <v>0.452252573532014</v>
       </c>
       <c r="L106" s="1">
         <f ca="1" t="shared" ref="L106:P106" si="182">J106+$R$1*K106/MAX(1,($A106*($A106-1)))++$R$1/$A106</f>
-        <v>6.24592668107239</v>
+        <v>6.24749199896306</v>
       </c>
       <c r="M106" s="1">
         <f ca="1" t="shared" si="181"/>
-        <v>0.794557896587722</v>
+        <v>0.676263267020408</v>
       </c>
       <c r="N106" s="1">
         <f ca="1" t="shared" si="182"/>
-        <v>6.72575524286995</v>
+        <v>6.72677891868385</v>
       </c>
       <c r="O106" s="1">
         <f ca="1" t="shared" si="181"/>
-        <v>0.757742811932833</v>
+        <v>0.223736401958934</v>
       </c>
       <c r="P106" s="1">
         <f ca="1" t="shared" si="182"/>
-        <v>7.20541523743008</v>
+        <v>7.20399382894923</v>
       </c>
     </row>
     <row r="107" ht="16.5" spans="1:16">
@@ -12330,27 +12305,27 @@
       </c>
       <c r="K107" s="1">
         <f ca="1" t="shared" ref="K107:O107" si="183">RAND()</f>
-        <v>0.767779976481766</v>
+        <v>0.932591054036461</v>
       </c>
       <c r="L107" s="1">
         <f ca="1" t="shared" ref="L107:P107" si="184">J107+$R$1*K107/MAX(1,($A107*($A107-1)))++$R$1/$A107</f>
-        <v>6.18943297383864</v>
+        <v>6.19017336502262</v>
       </c>
       <c r="M107" s="1">
         <f ca="1" t="shared" si="183"/>
-        <v>0.529320342285459</v>
+        <v>0.144677044802197</v>
       </c>
       <c r="N107" s="1">
         <f ca="1" t="shared" si="184"/>
-        <v>6.66350898615798</v>
+        <v>6.66252142003072</v>
       </c>
       <c r="O107" s="1">
         <f ca="1" t="shared" si="183"/>
-        <v>0.0981825102895508</v>
+        <v>0.30802908226998</v>
       </c>
       <c r="P107" s="1">
         <f ca="1" t="shared" si="184"/>
-        <v>7.13564817084033</v>
+        <v>7.13560331168512</v>
       </c>
     </row>
     <row r="108" ht="16.5" spans="1:16">
@@ -12390,27 +12365,27 @@
       </c>
       <c r="K108" s="1">
         <f ca="1" t="shared" ref="K108:O108" si="185">RAND()</f>
-        <v>0.879910427825525</v>
+        <v>0.868731002370915</v>
       </c>
       <c r="L108" s="1">
         <f ca="1" t="shared" ref="L108:P108" si="186">J108+$R$1*K108/MAX(1,($A108*($A108-1)))++$R$1/$A108</f>
-        <v>6.13154606959895</v>
+        <v>6.13149678629154</v>
       </c>
       <c r="M108" s="1">
         <f ca="1" t="shared" si="185"/>
-        <v>0.984143983720996</v>
+        <v>0.426743766490888</v>
       </c>
       <c r="N108" s="1">
         <f ca="1" t="shared" si="186"/>
-        <v>6.60317428324611</v>
+        <v>6.6006677603988</v>
       </c>
       <c r="O108" s="1">
         <f ca="1" t="shared" si="185"/>
-        <v>0.240198700292095</v>
+        <v>0.619690643929398</v>
       </c>
       <c r="P108" s="1">
         <f ca="1" t="shared" si="186"/>
-        <v>7.0715228932809</v>
+        <v>7.0706893202821</v>
       </c>
     </row>
     <row r="109" ht="16.5" spans="1:16">
@@ -12450,27 +12425,27 @@
       </c>
       <c r="K109" s="1">
         <f ca="1" t="shared" ref="K109:O109" si="187">RAND()</f>
-        <v>0.199391710333226</v>
+        <v>0.779666818186753</v>
       </c>
       <c r="L109" s="1">
         <f ca="1" t="shared" ref="L109:P109" si="188">J109+$R$1*K109/MAX(1,($A109*($A109-1)))++$R$1/$A109</f>
-        <v>6.07130231788825</v>
+        <v>6.07381302707765</v>
       </c>
       <c r="M109" s="1">
         <f ca="1" t="shared" si="187"/>
-        <v>0.949882389641663</v>
+        <v>0.559277991316197</v>
       </c>
       <c r="N109" s="1">
         <f ca="1" t="shared" si="188"/>
-        <v>6.53837519080986</v>
+        <v>6.53919584981613</v>
       </c>
       <c r="O109" s="1">
         <f ca="1" t="shared" si="187"/>
-        <v>0.858938554073766</v>
+        <v>0.341484115083428</v>
       </c>
       <c r="P109" s="1">
         <f ca="1" t="shared" si="188"/>
-        <v>7.00505457188495</v>
+        <v>7.00363633144941</v>
       </c>
     </row>
     <row r="110" ht="16.5" spans="1:16">
@@ -12510,27 +12485,27 @@
       </c>
       <c r="K110" s="1">
         <f ca="1" t="shared" ref="K110:O110" si="189">RAND()</f>
-        <v>0.00885750462309942</v>
+        <v>0.849864230307227</v>
       </c>
       <c r="L110" s="1">
         <f ca="1" t="shared" ref="L110:P110" si="190">J110+$R$1*K110/MAX(1,($A110*($A110-1)))++$R$1/$A110</f>
-        <v>6.01430877295542</v>
+        <v>6.01788083685996</v>
       </c>
       <c r="M110" s="1">
         <f ca="1" t="shared" si="189"/>
-        <v>0.250269239617228</v>
+        <v>0.640077401100398</v>
       </c>
       <c r="N110" s="1">
         <f ca="1" t="shared" si="190"/>
-        <v>6.47408735450323</v>
+        <v>6.479315076586</v>
       </c>
       <c r="O110" s="1">
         <f ca="1" t="shared" si="189"/>
-        <v>0.97863553728878</v>
+        <v>0.711022188121851</v>
       </c>
       <c r="P110" s="1">
         <f ca="1" t="shared" si="190"/>
-        <v>6.93695957476015</v>
+        <v>6.94105064483321</v>
       </c>
     </row>
     <row r="111" ht="16.5" spans="1:16">
@@ -12570,27 +12545,27 @@
       </c>
       <c r="K111" s="1">
         <f ca="1" t="shared" ref="K111:O111" si="191">RAND()</f>
-        <v>0.665300597703811</v>
+        <v>0.441168093766404</v>
       </c>
       <c r="L111" s="1">
         <f ca="1" t="shared" ref="L111:P111" si="192">J111+$R$1*K111/MAX(1,($A111*($A111-1)))++$R$1/$A111</f>
-        <v>5.96190700833071</v>
+        <v>5.9609723440107</v>
       </c>
       <c r="M111" s="1">
         <f ca="1" t="shared" si="191"/>
-        <v>0.642223274274544</v>
+        <v>0.717702971146798</v>
       </c>
       <c r="N111" s="1">
         <f ca="1" t="shared" si="192"/>
-        <v>6.4191306249874</v>
+        <v>6.41851072170522</v>
       </c>
       <c r="O111" s="1">
         <f ca="1" t="shared" si="191"/>
-        <v>0.378680838020478</v>
+        <v>0.372499474168782</v>
       </c>
       <c r="P111" s="1">
         <f ca="1" t="shared" si="192"/>
-        <v>6.87525523231859</v>
+        <v>6.87460955187273</v>
       </c>
     </row>
     <row r="112" ht="16.5" spans="1:16">
@@ -12630,27 +12605,27 @@
       </c>
       <c r="K112" s="1">
         <f ca="1" t="shared" ref="K112:O112" si="193">RAND()</f>
-        <v>0.349360904766976</v>
+        <v>0.65663031653283</v>
       </c>
       <c r="L112" s="1">
         <f ca="1" t="shared" ref="L112:P112" si="194">J112+$R$1*K112/MAX(1,($A112*($A112-1)))++$R$1/$A112</f>
-        <v>5.90642653933156</v>
+        <v>5.90768480883101</v>
       </c>
       <c r="M112" s="1">
         <f ca="1" t="shared" si="193"/>
-        <v>0.581799834716415</v>
+        <v>0.39960383421644</v>
       </c>
       <c r="N112" s="1">
         <f ca="1" t="shared" si="194"/>
-        <v>6.35925946248765</v>
+        <v>6.35977163861895</v>
       </c>
       <c r="O112" s="1">
         <f ca="1" t="shared" si="193"/>
-        <v>0.68691738227944</v>
+        <v>0.389440592055012</v>
       </c>
       <c r="P112" s="1">
         <f ca="1" t="shared" si="194"/>
-        <v>6.81252284243146</v>
+        <v>6.81181684988863</v>
       </c>
     </row>
     <row r="113" ht="16.5" spans="1:16">
@@ -12690,27 +12665,27 @@
       </c>
       <c r="K113" s="1">
         <f ca="1" t="shared" ref="K113:O113" si="195">RAND()</f>
-        <v>0.586846208963064</v>
+        <v>0.786603088060525</v>
       </c>
       <c r="L113" s="1">
         <f ca="1" t="shared" ref="L113:P113" si="196">J113+$R$1*K113/MAX(1,($A113*($A113-1)))++$R$1/$A113</f>
-        <v>5.85419420129087</v>
+        <v>5.8549975992924</v>
       </c>
       <c r="M113" s="1">
         <f ca="1" t="shared" si="195"/>
-        <v>0.599237953354005</v>
+        <v>0.264135112059419</v>
       </c>
       <c r="N113" s="1">
         <f ca="1" t="shared" si="196"/>
-        <v>6.30303283527315</v>
+        <v>6.3024884901871</v>
       </c>
       <c r="O113" s="1">
         <f ca="1" t="shared" si="195"/>
-        <v>0.531734047838465</v>
+        <v>0.739998520235792</v>
       </c>
       <c r="P113" s="1">
         <f ca="1" t="shared" si="196"/>
-        <v>6.75159997671394</v>
+        <v>6.75189324614043</v>
       </c>
     </row>
     <row r="114" ht="16.5" spans="1:16">
@@ -12750,27 +12725,27 @@
       </c>
       <c r="K114" s="1">
         <f ca="1" t="shared" ref="K114:O114" si="197">RAND()</f>
-        <v>0.742690668749125</v>
+        <v>0.459958193707205</v>
       </c>
       <c r="L114" s="1">
         <f ca="1" t="shared" ref="L114:P114" si="198">J114+$R$1*K114/MAX(1,($A114*($A114-1)))++$R$1/$A114</f>
-        <v>5.80255487780005</v>
+        <v>5.80143788793342</v>
       </c>
       <c r="M114" s="1">
         <f ca="1" t="shared" si="197"/>
-        <v>0.855311968959515</v>
+        <v>0.731791116316434</v>
       </c>
       <c r="N114" s="1">
         <f ca="1" t="shared" si="198"/>
-        <v>6.24841183090119</v>
+        <v>6.24680684777981</v>
       </c>
       <c r="O114" s="1">
         <f ca="1" t="shared" si="197"/>
-        <v>0.0131012946181568</v>
+        <v>0.569592947935174</v>
       </c>
       <c r="P114" s="1">
         <f ca="1" t="shared" si="198"/>
-        <v>6.69094146623075</v>
+        <v>6.69153501208107</v>
       </c>
     </row>
     <row r="115" ht="16.5" spans="1:16">
@@ -12810,27 +12785,27 @@
       </c>
       <c r="K115" s="1">
         <f ca="1" t="shared" ref="K115:O115" si="199">RAND()</f>
-        <v>0.367598932070455</v>
+        <v>0.969106002294464</v>
       </c>
       <c r="L115" s="1">
         <f ca="1" t="shared" ref="L115:P115" si="200">J115+$R$1*K115/MAX(1,($A115*($A115-1)))++$R$1/$A115</f>
-        <v>5.74975779743856</v>
+        <v>5.75209247788502</v>
       </c>
       <c r="M115" s="1">
         <f ca="1" t="shared" si="199"/>
-        <v>0.892894212520041</v>
+        <v>0.70422188127564</v>
       </c>
       <c r="N115" s="1">
         <f ca="1" t="shared" si="200"/>
-        <v>6.19181995476087</v>
+        <v>6.19342232527391</v>
       </c>
       <c r="O115" s="1">
         <f ca="1" t="shared" si="199"/>
-        <v>0.221586245797323</v>
+        <v>0.174526808200813</v>
       </c>
       <c r="P115" s="1">
         <f ca="1" t="shared" si="200"/>
-        <v>6.63127650749258</v>
+        <v>6.63269622221616</v>
       </c>
     </row>
     <row r="116" ht="16.5" spans="1:16">
@@ -12870,27 +12845,27 @@
       </c>
       <c r="K116" s="1">
         <f ca="1" t="shared" ref="K116:O116" si="201">RAND()</f>
-        <v>0.4188249948734</v>
+        <v>0.974647187700575</v>
       </c>
       <c r="L116" s="1">
         <f ca="1" t="shared" ref="L116:P116" si="202">J116+$R$1*K116/MAX(1,($A116*($A116-1)))++$R$1/$A116</f>
-        <v>5.69953785276458</v>
+        <v>5.70165769331693</v>
       </c>
       <c r="M116" s="1">
         <f ca="1" t="shared" si="201"/>
-        <v>0.334098940590187</v>
+        <v>0.477045198149884</v>
       </c>
       <c r="N116" s="1">
         <f ca="1" t="shared" si="202"/>
-        <v>6.13559467557385</v>
+        <v>6.13825969636098</v>
       </c>
       <c r="O116" s="1">
         <f ca="1" t="shared" si="201"/>
-        <v>0.75599060737138</v>
+        <v>0.905453979474853</v>
       </c>
       <c r="P116" s="1">
         <f ca="1" t="shared" si="202"/>
-        <v>6.57326054364163</v>
+        <v>6.57649560017286</v>
       </c>
     </row>
     <row r="117" ht="16.5" spans="1:16">
@@ -12930,27 +12905,27 @@
       </c>
       <c r="K117" s="1">
         <f ca="1" t="shared" ref="K117:O117" si="203">RAND()</f>
-        <v>0.873967375646127</v>
+        <v>0.510587273704762</v>
       </c>
       <c r="L117" s="1">
         <f ca="1" t="shared" ref="L117:P117" si="204">J117+$R$1*K117/MAX(1,($A117*($A117-1)))++$R$1/$A117</f>
-        <v>5.65170152689523</v>
+        <v>5.65033953251014</v>
       </c>
       <c r="M117" s="1">
         <f ca="1" t="shared" si="203"/>
-        <v>0.608096119691846</v>
+        <v>0.32142127547192</v>
       </c>
       <c r="N117" s="1">
         <f ca="1" t="shared" si="204"/>
-        <v>6.08501523049227</v>
+        <v>6.08257874268807</v>
       </c>
       <c r="O117" s="1">
         <f ca="1" t="shared" si="203"/>
-        <v>0.961793268348814</v>
+        <v>0.0896040566111227</v>
       </c>
       <c r="P117" s="1">
         <f ca="1" t="shared" si="204"/>
-        <v>6.51965463554605</v>
+        <v>6.51394907273534</v>
       </c>
     </row>
     <row r="118" ht="16.5" spans="1:16">
@@ -12990,27 +12965,27 @@
       </c>
       <c r="K118" s="1">
         <f ca="1" t="shared" ref="K118:O118" si="205">RAND()</f>
-        <v>0.215159913859936</v>
+        <v>0.664306312023906</v>
       </c>
       <c r="L118" s="1">
         <f ca="1" t="shared" ref="L118:P118" si="206">J118+$R$1*K118/MAX(1,($A118*($A118-1)))++$R$1/$A118</f>
-        <v>5.60055688149816</v>
+        <v>5.60221156171539</v>
       </c>
       <c r="M118" s="1">
         <f ca="1" t="shared" si="205"/>
-        <v>0.453497367751454</v>
+        <v>0.63743543805456</v>
       </c>
       <c r="N118" s="1">
         <f ca="1" t="shared" si="206"/>
-        <v>6.02957801827885</v>
+        <v>6.03191033653875</v>
       </c>
       <c r="O118" s="1">
         <f ca="1" t="shared" si="205"/>
-        <v>0.831494383991431</v>
+        <v>0.0924699522445693</v>
       </c>
       <c r="P118" s="1">
         <f ca="1" t="shared" si="206"/>
-        <v>6.4599917170115</v>
+        <v>6.45960142831684</v>
       </c>
     </row>
     <row r="119" ht="16.5" spans="1:16">
@@ -13050,27 +13025,27 @@
       </c>
       <c r="K119" s="1">
         <f ca="1" t="shared" ref="K119:O119" si="207">RAND()</f>
-        <v>0.0236062097827208</v>
+        <v>0.228016421651428</v>
       </c>
       <c r="L119" s="1">
         <f ca="1" t="shared" ref="L119:P119" si="208">J119+$R$1*K119/MAX(1,($A119*($A119-1)))++$R$1/$A119</f>
-        <v>5.55201943433935</v>
+        <v>5.5527597291817</v>
       </c>
       <c r="M119" s="1">
         <f ca="1" t="shared" si="207"/>
-        <v>0.603771055526294</v>
+        <v>0.447453422882474</v>
       </c>
       <c r="N119" s="1">
         <f ca="1" t="shared" si="208"/>
-        <v>5.97793487348004</v>
+        <v>5.97810904622821</v>
       </c>
       <c r="O119" s="1">
         <f ca="1" t="shared" si="207"/>
-        <v>0.824174210487703</v>
+        <v>0.901207041903617</v>
       </c>
       <c r="P119" s="1">
         <f ca="1" t="shared" si="208"/>
-        <v>6.40464852772634</v>
+        <v>6.40510168363913</v>
       </c>
     </row>
     <row r="120" ht="16.5" spans="1:16">
@@ -13224,27 +13199,27 @@
       </c>
       <c r="K122" s="1">
         <f ca="1" t="shared" ref="K122:O122" si="211">RAND()</f>
-        <v>0.11609359452046</v>
+        <v>0.930191726553585</v>
       </c>
       <c r="L122" s="1">
         <f ca="1" t="shared" ref="L122:P122" si="212">J122+$R$1*K122/MAX(1,($A122*($A122-1)))++$R$1/$A122</f>
-        <v>5.41362291182686</v>
+        <v>5.41642628005012</v>
       </c>
       <c r="M122" s="1">
         <f ca="1" t="shared" si="211"/>
-        <v>0.471762075912724</v>
+        <v>0.157439060729432</v>
       </c>
       <c r="N122" s="1">
         <f ca="1" t="shared" si="212"/>
-        <v>5.82847057737752</v>
+        <v>5.83019156607191</v>
       </c>
       <c r="O122" s="1">
         <f ca="1" t="shared" si="211"/>
-        <v>0.0661612653303922</v>
+        <v>0.273202295861578</v>
       </c>
       <c r="P122" s="1">
         <f ca="1" t="shared" si="212"/>
-        <v>6.24192154592205</v>
+        <v>6.2443554858235</v>
       </c>
     </row>
     <row r="123" ht="16.5" spans="1:16">
@@ -13284,27 +13259,27 @@
       </c>
       <c r="K123" s="1">
         <f ca="1" t="shared" ref="K123:O123" si="213">RAND()</f>
-        <v>0.791539763147667</v>
+        <v>0.545763563420471</v>
       </c>
       <c r="L123" s="1">
         <f ca="1" t="shared" ref="L123:P123" si="214">J123+$R$1*K123/MAX(1,($A123*($A123-1)))++$R$1/$A123</f>
-        <v>5.37119475600578</v>
+        <v>5.37036229360324</v>
       </c>
       <c r="M123" s="1">
         <f ca="1" t="shared" si="213"/>
-        <v>0.77797211886292</v>
+        <v>0.520749704770044</v>
       </c>
       <c r="N123" s="1">
         <f ca="1" t="shared" si="214"/>
-        <v>5.78366587143345</v>
+        <v>5.78196217744272</v>
       </c>
       <c r="O123" s="1">
         <f ca="1" t="shared" si="213"/>
-        <v>0.0974363216102665</v>
+        <v>0.159463857837399</v>
       </c>
       <c r="P123" s="1">
         <f ca="1" t="shared" si="214"/>
-        <v>6.19383196112864</v>
+        <v>6.19233835905036</v>
       </c>
     </row>
     <row r="124" ht="16.5" spans="1:16">
@@ -13344,27 +13319,27 @@
       </c>
       <c r="K124" s="1">
         <f ca="1" t="shared" ref="K124:O124" si="215">RAND()</f>
-        <v>0.303199667199125</v>
+        <v>0.374330849180655</v>
       </c>
       <c r="L124" s="1">
         <f ca="1" t="shared" ref="L124:P124" si="216">J124+$R$1*K124/MAX(1,($A124*($A124-1)))++$R$1/$A124</f>
-        <v>5.32554711337865</v>
+        <v>5.32578412251493</v>
       </c>
       <c r="M124" s="1">
         <f ca="1" t="shared" si="215"/>
-        <v>0.0122211600887334</v>
+        <v>0.523893591619577</v>
       </c>
       <c r="N124" s="1">
         <f ca="1" t="shared" si="216"/>
-        <v>5.73209189933123</v>
+        <v>5.73403380128216</v>
       </c>
       <c r="O124" s="1">
         <f ca="1" t="shared" si="215"/>
-        <v>0.159011636489625</v>
+        <v>0.140068805257194</v>
       </c>
       <c r="P124" s="1">
         <f ca="1" t="shared" si="216"/>
-        <v>6.13912579122943</v>
+        <v>6.1410045756566</v>
       </c>
     </row>
     <row r="125" ht="16.5" spans="1:16">
@@ -13404,27 +13379,27 @@
       </c>
       <c r="K125" s="1">
         <f ca="1" t="shared" ref="K125:O125" si="217">RAND()</f>
-        <v>0.406873285080035</v>
+        <v>0.360566232252989</v>
       </c>
       <c r="L125" s="1">
         <f ca="1" t="shared" ref="L125:P125" si="218">J125+$R$1*K125/MAX(1,($A125*($A125-1)))++$R$1/$A125</f>
-        <v>5.28260842278088</v>
+        <v>5.28245661628721</v>
       </c>
       <c r="M125" s="1">
         <f ca="1" t="shared" si="217"/>
-        <v>0.549289244976262</v>
+        <v>0.438297765767388</v>
       </c>
       <c r="N125" s="1">
         <f ca="1" t="shared" si="218"/>
-        <v>5.6876349414177</v>
+        <v>5.68711927615401</v>
       </c>
       <c r="O125" s="1">
         <f ca="1" t="shared" si="217"/>
-        <v>0.918841175525932</v>
+        <v>0.972601073707403</v>
       </c>
       <c r="P125" s="1">
         <f ca="1" t="shared" si="218"/>
-        <v>6.09387294684495</v>
+        <v>6.09353352042921</v>
       </c>
     </row>
     <row r="126" ht="16.5" spans="1:16">
@@ -13464,27 +13439,27 @@
       </c>
       <c r="K126" s="1">
         <f ca="1" t="shared" ref="K126:O126" si="219">RAND()</f>
-        <v>0.482023559703589</v>
+        <v>0.548075337312242</v>
       </c>
       <c r="L126" s="1">
         <f ca="1" t="shared" ref="L126:P126" si="220">J126+$R$1*K126/MAX(1,($A126*($A126-1)))++$R$1/$A126</f>
-        <v>5.24026459212808</v>
+        <v>5.24047766237842</v>
       </c>
       <c r="M126" s="1">
         <f ca="1" t="shared" si="219"/>
-        <v>0.553296707180553</v>
+        <v>0.604445972071556</v>
       </c>
       <c r="N126" s="1">
         <f ca="1" t="shared" si="220"/>
-        <v>5.64204942021576</v>
+        <v>5.64242748809478</v>
       </c>
       <c r="O126" s="1">
         <f ca="1" t="shared" si="219"/>
-        <v>0.623179507872836</v>
+        <v>0.850713143486417</v>
       </c>
       <c r="P126" s="1">
         <f ca="1" t="shared" si="220"/>
-        <v>6.04405967669276</v>
+        <v>6.04517172404151</v>
       </c>
     </row>
     <row r="127" ht="16.5" spans="1:16">
@@ -13524,27 +13499,27 @@
       </c>
       <c r="K127" s="1">
         <f ca="1" t="shared" ref="K127:O127" si="221">RAND()</f>
-        <v>0.328850124847131</v>
+        <v>0.680679585888173</v>
       </c>
       <c r="L127" s="1">
         <f ca="1" t="shared" ref="L127:P127" si="222">J127+$R$1*K127/MAX(1,($A127*($A127-1)))++$R$1/$A127</f>
-        <v>5.19786936547571</v>
+        <v>5.19898628439964</v>
       </c>
       <c r="M127" s="1">
         <f ca="1" t="shared" si="221"/>
-        <v>0.629931194895083</v>
+        <v>0.0108745869511837</v>
       </c>
       <c r="N127" s="1">
         <f ca="1" t="shared" si="222"/>
-        <v>5.5966945438722</v>
+        <v>5.5958462037233</v>
       </c>
       <c r="O127" s="1">
         <f ca="1" t="shared" si="221"/>
-        <v>0.00778379714357924</v>
+        <v>0.821331568791543</v>
       </c>
       <c r="P127" s="1">
         <f ca="1" t="shared" si="222"/>
-        <v>5.99354465116472</v>
+        <v>5.99527900235438</v>
       </c>
     </row>
     <row r="128" ht="16.5" spans="1:16">
@@ -13584,27 +13559,27 @@
       </c>
       <c r="K128" s="1">
         <f ca="1" t="shared" ref="K128:O128" si="223">RAND()</f>
-        <v>0.598802642285196</v>
+        <v>0.758871571479732</v>
       </c>
       <c r="L128" s="1">
         <f ca="1" t="shared" ref="L128:P128" si="224">J128+$R$1*K128/MAX(1,($A128*($A128-1)))++$R$1/$A128</f>
-        <v>5.15747657368543</v>
+        <v>5.15797672657005</v>
       </c>
       <c r="M128" s="1">
         <f ca="1" t="shared" si="223"/>
-        <v>0.0697312146947697</v>
+        <v>0.717651928461352</v>
       </c>
       <c r="N128" s="1">
         <f ca="1" t="shared" si="224"/>
-        <v>5.55139524389758</v>
+        <v>5.55391989595032</v>
       </c>
       <c r="O128" s="1">
         <f ca="1" t="shared" si="223"/>
-        <v>0.886539311130365</v>
+        <v>0.125285143404439</v>
       </c>
       <c r="P128" s="1">
         <f ca="1" t="shared" si="224"/>
-        <v>5.9478661203853</v>
+        <v>5.94801215049164</v>
       </c>
     </row>
     <row r="129" ht="16.5" spans="1:16">
@@ -13644,27 +13619,27 @@
       </c>
       <c r="K129" s="1">
         <f ca="1" t="shared" ref="K129:O129" si="225">RAND()</f>
-        <v>0.70304897673046</v>
+        <v>0.633593007894304</v>
       </c>
       <c r="L129" s="1">
         <f ca="1" t="shared" ref="L129:P129" si="226">J129+$R$1*K129/MAX(1,($A129*($A129-1)))++$R$1/$A129</f>
-        <v>5.11719687800422</v>
+        <v>5.11698324621031</v>
       </c>
       <c r="M129" s="1">
         <f ca="1" t="shared" si="225"/>
-        <v>0.0480712020117291</v>
+        <v>0.59623065502605</v>
       </c>
       <c r="N129" s="1">
         <f ca="1" t="shared" si="226"/>
-        <v>5.50796973480174</v>
+        <v>5.50944212494747</v>
       </c>
       <c r="O129" s="1">
         <f ca="1" t="shared" si="225"/>
-        <v>0.237225615784711</v>
+        <v>0.567221293347914</v>
       </c>
       <c r="P129" s="1">
         <f ca="1" t="shared" si="226"/>
-        <v>5.8993243903621</v>
+        <v>5.90181177705545</v>
       </c>
     </row>
     <row r="130" ht="16.5" spans="1:16">
@@ -13704,27 +13679,27 @@
       </c>
       <c r="K130" s="1">
         <f ca="1" t="shared" ref="K130:O130" si="230">RAND()</f>
-        <v>0.0499125936022906</v>
+        <v>0.600372005408779</v>
       </c>
       <c r="L130" s="1">
         <f ca="1" t="shared" ref="L130:P130" si="231">J130+$R$1*K130/MAX(1,($A130*($A130-1)))++$R$1/$A130</f>
-        <v>5.07524803958819</v>
+        <v>5.07691488615979</v>
       </c>
       <c r="M130" s="1">
         <f ca="1" t="shared" si="230"/>
-        <v>0.747979045583004</v>
+        <v>0.328176452378097</v>
       </c>
       <c r="N130" s="1">
         <f ca="1" t="shared" si="231"/>
-        <v>5.46510989474075</v>
+        <v>5.46550553675444</v>
       </c>
       <c r="O130" s="1">
         <f ca="1" t="shared" si="230"/>
-        <v>0.951345828388679</v>
+        <v>0.776862113874067</v>
       </c>
       <c r="P130" s="1">
         <f ca="1" t="shared" si="231"/>
-        <v>5.85558756500598</v>
+        <v>5.85545485274849</v>
       </c>
     </row>
     <row r="131" ht="16.5" spans="1:16">
@@ -13764,27 +13739,27 @@
       </c>
       <c r="K131" s="1">
         <f ca="1" t="shared" ref="K131:O131" si="232">RAND()</f>
-        <v>0.915746825856607</v>
+        <v>0.977817149135306</v>
       </c>
       <c r="L131" s="1">
         <f ca="1" t="shared" ref="L131:P131" si="233">J131+$R$1*K131/MAX(1,($A131*($A131-1)))++$R$1/$A131</f>
-        <v>5.03850848785288</v>
+        <v>5.03869355142854</v>
       </c>
       <c r="M131" s="1">
         <f ca="1" t="shared" si="232"/>
-        <v>0.582351871082393</v>
+        <v>0.429033354348831</v>
       </c>
       <c r="N131" s="1">
         <f ca="1" t="shared" si="233"/>
-        <v>5.42486016307972</v>
+        <v>5.42458810525785</v>
       </c>
       <c r="O131" s="1">
         <f ca="1" t="shared" si="232"/>
-        <v>0.918616427007583</v>
+        <v>0.995295218637135</v>
       </c>
       <c r="P131" s="1">
         <f ca="1" t="shared" si="233"/>
-        <v>5.81221441599269</v>
+        <v>5.81217097710829</v>
       </c>
     </row>
     <row r="132" ht="16.5" spans="1:16">
@@ -13824,27 +13799,27 @@
       </c>
       <c r="K132" s="1">
         <f ca="1" t="shared" ref="K132:O132" si="234">RAND()</f>
-        <v>0.966296777688442</v>
+        <v>0.259404787989981</v>
       </c>
       <c r="L132" s="1">
         <f ca="1" t="shared" ref="L132:P132" si="235">J132+$R$1*K132/MAX(1,($A132*($A132-1)))++$R$1/$A132</f>
-        <v>4.99990104749762</v>
+        <v>4.99782561593656</v>
       </c>
       <c r="M132" s="1">
         <f ca="1" t="shared" si="234"/>
-        <v>0.68649208419386</v>
+        <v>0.682105406813657</v>
       </c>
       <c r="N132" s="1">
         <f ca="1" t="shared" si="235"/>
-        <v>5.38359597434493</v>
+        <v>5.38150766351969</v>
       </c>
       <c r="O132" s="1">
         <f ca="1" t="shared" si="234"/>
-        <v>0.785511336221281</v>
+        <v>0.669949291563362</v>
       </c>
       <c r="P132" s="1">
         <f ca="1" t="shared" si="235"/>
-        <v>5.76758162125104</v>
+        <v>5.76515402080555</v>
       </c>
     </row>
     <row r="133" ht="16.5" spans="1:16">
@@ -13884,27 +13859,27 @@
       </c>
       <c r="K133" s="1">
         <f ca="1" t="shared" ref="K133:O133" si="236">RAND()</f>
-        <v>0.636244921835134</v>
+        <v>0.125960562508985</v>
       </c>
       <c r="L133" s="1">
         <f ca="1" t="shared" ref="L133:P133" si="237">J133+$R$1*K133/MAX(1,($A133*($A133-1)))++$R$1/$A133</f>
-        <v>4.96078025943163</v>
+        <v>4.95930476683585</v>
       </c>
       <c r="M133" s="1">
         <f ca="1" t="shared" si="236"/>
-        <v>0.350464378608861</v>
+        <v>0.456412741020075</v>
       </c>
       <c r="N133" s="1">
         <f ca="1" t="shared" si="237"/>
-        <v>5.34058150965893</v>
+        <v>5.33941236786818</v>
       </c>
       <c r="O133" s="1">
         <f ca="1" t="shared" si="236"/>
-        <v>0.842769997485998</v>
+        <v>0.0130279520629923</v>
       </c>
       <c r="P133" s="1">
         <f ca="1" t="shared" si="237"/>
-        <v>5.72180626676478</v>
+        <v>5.71823791711657</v>
       </c>
     </row>
     <row r="134" ht="16.5" spans="1:16">
@@ -13944,27 +13919,27 @@
       </c>
       <c r="K134" s="1">
         <f ca="1" t="shared" ref="K134:O134" si="238">RAND()</f>
-        <v>0.866501008002905</v>
+        <v>0.476555922771988</v>
       </c>
       <c r="L134" s="1">
         <f ca="1" t="shared" ref="L134:P134" si="239">J134+$R$1*K134/MAX(1,($A134*($A134-1)))++$R$1/$A134</f>
-        <v>4.92386221521988</v>
+        <v>4.92275164024486</v>
       </c>
       <c r="M134" s="1">
         <f ca="1" t="shared" si="238"/>
-        <v>0.633620568641428</v>
+        <v>0.670244912802232</v>
       </c>
       <c r="N134" s="1">
         <f ca="1" t="shared" si="239"/>
-        <v>5.30160663470222</v>
+        <v>5.30060036692748</v>
       </c>
       <c r="O134" s="1">
         <f ca="1" t="shared" si="238"/>
-        <v>0.282442527742521</v>
+        <v>0.42954024231167</v>
       </c>
       <c r="P134" s="1">
         <f ca="1" t="shared" si="239"/>
-        <v>5.6783508888824</v>
+        <v>5.67776355968867</v>
       </c>
     </row>
     <row r="135" ht="16.5" spans="1:16">
@@ -14004,27 +13979,27 @@
       </c>
       <c r="K135" s="1">
         <f ca="1" t="shared" ref="K135:O135" si="240">RAND()</f>
-        <v>0.903253106817275</v>
+        <v>0.663912879473421</v>
       </c>
       <c r="L135" s="1">
         <f ca="1" t="shared" ref="L135:P135" si="241">J135+$R$1*K135/MAX(1,($A135*($A135-1)))++$R$1/$A135</f>
-        <v>4.88694661964655</v>
+        <v>4.88627514554896</v>
       </c>
       <c r="M135" s="1">
         <f ca="1" t="shared" si="240"/>
-        <v>0.37651569524252</v>
+        <v>0.888611554221538</v>
       </c>
       <c r="N135" s="1">
         <f ca="1" t="shared" si="241"/>
-        <v>5.26113727079469</v>
+        <v>5.26190249251962</v>
       </c>
       <c r="O135" s="1">
         <f ca="1" t="shared" si="240"/>
-        <v>0.432857647765777</v>
+        <v>0.242369004031934</v>
       </c>
       <c r="P135" s="1">
         <f ca="1" t="shared" si="241"/>
-        <v>5.6354859904888</v>
+        <v>5.63571679227283</v>
       </c>
     </row>
     <row r="136" ht="16.5" spans="1:16">
@@ -14064,27 +14039,27 @@
       </c>
       <c r="K136" s="1">
         <f ca="1" t="shared" ref="K136:O136" si="242">RAND()</f>
-        <v>0.866439721365903</v>
+        <v>0.405803792052952</v>
       </c>
       <c r="L136" s="1">
         <f ca="1" t="shared" ref="L136:P136" si="243">J136+$R$1*K136/MAX(1,($A136*($A136-1)))++$R$1/$A136</f>
-        <v>4.85037711365773</v>
+        <v>4.84910393530142</v>
       </c>
       <c r="M136" s="1">
         <f ca="1" t="shared" si="242"/>
-        <v>0.684635648696918</v>
+        <v>0.557464606493435</v>
       </c>
       <c r="N136" s="1">
         <f ca="1" t="shared" si="243"/>
-        <v>5.22263978819807</v>
+        <v>5.22101511442385</v>
       </c>
       <c r="O136" s="1">
         <f ca="1" t="shared" si="242"/>
-        <v>0.986136323063586</v>
+        <v>0.946399649266383</v>
       </c>
       <c r="P136" s="1">
         <f ca="1" t="shared" si="243"/>
-        <v>5.59573579793567</v>
+        <v>5.59400129366449</v>
       </c>
     </row>
     <row r="137" ht="16.5" spans="1:16">
@@ -14124,27 +14099,27 @@
       </c>
       <c r="K137" s="1">
         <f ca="1" t="shared" ref="K137:O137" si="244">RAND()</f>
-        <v>0.872418576166974</v>
+        <v>0.426666352894792</v>
       </c>
       <c r="L137" s="1">
         <f ca="1" t="shared" ref="L137:P137" si="245">J137+$R$1*K137/MAX(1,($A137*($A137-1)))++$R$1/$A137</f>
-        <v>4.81446737085013</v>
+        <v>4.81325344867346</v>
       </c>
       <c r="M137" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.0345593111157321</v>
+        <v>0.282382200893075</v>
       </c>
       <c r="N137" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>5.18220854544467</v>
+        <v>5.1816695222053</v>
       </c>
       <c r="O137" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.730841904874036</v>
+        <v>0.916567750936346</v>
       </c>
       <c r="P137" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>5.55184591446666</v>
+        <v>5.55181268056842</v>
       </c>
     </row>
     <row r="138" ht="16.5" spans="1:16">
@@ -14298,27 +14273,27 @@
       </c>
       <c r="K140" s="1">
         <f ca="1" t="shared" ref="K140:O140" si="249">RAND()</f>
-        <v>0.189756676189047</v>
+        <v>0.182449984100255</v>
       </c>
       <c r="L140" s="1">
         <f ca="1" t="shared" ref="L140:P140" si="250">J140+$R$1*K140/MAX(1,($A140*($A140-1)))++$R$1/$A140</f>
-        <v>4.70803293889112</v>
+        <v>4.70801389319179</v>
       </c>
       <c r="M140" s="1">
         <f ca="1" t="shared" si="249"/>
-        <v>0.130669852668834</v>
+        <v>0.934632028292852</v>
       </c>
       <c r="N140" s="1">
         <f ca="1" t="shared" si="250"/>
-        <v>5.06808577449916</v>
+        <v>5.07016234493899</v>
       </c>
       <c r="O140" s="1">
         <f ca="1" t="shared" si="249"/>
-        <v>0.231967332384337</v>
+        <v>0.181614643786489</v>
       </c>
       <c r="P140" s="1">
         <f ca="1" t="shared" si="250"/>
-        <v>5.42840265316766</v>
+        <v>5.43034797376754</v>
       </c>
     </row>
     <row r="141" ht="16.5" spans="1:16">
@@ -14358,27 +14333,27 @@
       </c>
       <c r="K141" s="1">
         <f ca="1" t="shared" ref="K141:O141" si="251">RAND()</f>
-        <v>0.12536378515157</v>
+        <v>0.698040167785316</v>
       </c>
       <c r="L141" s="1">
         <f ca="1" t="shared" ref="L141:P141" si="252">J141+$R$1*K141/MAX(1,($A141*($A141-1)))++$R$1/$A141</f>
-        <v>4.67401172606668</v>
+        <v>4.67548314534375</v>
       </c>
       <c r="M141" s="1">
         <f ca="1" t="shared" si="251"/>
-        <v>0.188437591801571</v>
+        <v>0.0728137965835227</v>
       </c>
       <c r="N141" s="1">
         <f ca="1" t="shared" si="252"/>
-        <v>5.03163874968385</v>
+        <v>5.03281308829489</v>
       </c>
       <c r="O141" s="1">
         <f ca="1" t="shared" si="251"/>
-        <v>0.86006751308708</v>
+        <v>0.584572915766364</v>
       </c>
       <c r="P141" s="1">
         <f ca="1" t="shared" si="252"/>
-        <v>5.39099144113576</v>
+        <v>5.3914579313467</v>
       </c>
     </row>
     <row r="142" ht="16.5" spans="1:16">
@@ -14418,27 +14393,27 @@
       </c>
       <c r="K142" s="1">
         <f ca="1" t="shared" ref="K142:O142" si="253">RAND()</f>
-        <v>0.521836219207846</v>
+        <v>0.621287131901224</v>
       </c>
       <c r="L142" s="1">
         <f ca="1" t="shared" ref="L142:P142" si="254">J142+$R$1*K142/MAX(1,($A142*($A142-1)))++$R$1/$A142</f>
-        <v>4.64164598839718</v>
+        <v>4.64189789040502</v>
       </c>
       <c r="M142" s="1">
         <f ca="1" t="shared" si="253"/>
-        <v>0.355410079851384</v>
+        <v>0.123181485444877</v>
       </c>
       <c r="N142" s="1">
         <f ca="1" t="shared" si="254"/>
-        <v>4.99715614564098</v>
+        <v>4.99681982932459</v>
       </c>
       <c r="O142" s="1">
         <f ca="1" t="shared" si="253"/>
-        <v>0.0580549645213801</v>
+        <v>0.63916646767991</v>
       </c>
       <c r="P142" s="1">
         <f ca="1" t="shared" si="254"/>
-        <v>5.35191312376794</v>
+        <v>5.3530487210867</v>
       </c>
     </row>
     <row r="143" ht="16.5" spans="1:16">
@@ -14478,27 +14453,27 @@
       </c>
       <c r="K143" s="1">
         <f ca="1" t="shared" ref="K143:O143" si="255">RAND()</f>
-        <v>0.664070833565638</v>
+        <v>0.475324580394063</v>
       </c>
       <c r="L143" s="1">
         <f ca="1" t="shared" ref="L143:P143" si="256">J143+$R$1*K143/MAX(1,($A143*($A143-1)))++$R$1/$A143</f>
-        <v>4.60909017788824</v>
+        <v>4.60861883073717</v>
       </c>
       <c r="M143" s="1">
         <f ca="1" t="shared" si="255"/>
-        <v>0.239402483198481</v>
+        <v>0.076115213196541</v>
       </c>
       <c r="N143" s="1">
         <f ca="1" t="shared" si="256"/>
-        <v>4.96180070251914</v>
+        <v>4.96092158573966</v>
       </c>
       <c r="O143" s="1">
         <f ca="1" t="shared" si="255"/>
-        <v>0.810343068422792</v>
+        <v>0.185459080247326</v>
       </c>
       <c r="P143" s="1">
         <f ca="1" t="shared" si="256"/>
-        <v>5.31593701025169</v>
+        <v>5.31349740004455</v>
       </c>
     </row>
     <row r="144" ht="16.5" spans="1:16">
@@ -14538,27 +14513,27 @@
       </c>
       <c r="K144" s="1">
         <f ca="1" t="shared" ref="K144:O144" si="257">RAND()</f>
-        <v>0.453935963148194</v>
+        <v>0.852742869159644</v>
       </c>
       <c r="L144" s="1">
         <f ca="1" t="shared" ref="L144:P144" si="258">J144+$R$1*K144/MAX(1,($A144*($A144-1)))++$R$1/$A144</f>
-        <v>4.57612020083509</v>
+        <v>4.57710219361066</v>
       </c>
       <c r="M144" s="1">
         <f ca="1" t="shared" si="257"/>
-        <v>0.548928797527012</v>
+        <v>0.447452775574789</v>
       </c>
       <c r="N144" s="1">
         <f ca="1" t="shared" si="258"/>
-        <v>4.9271221923586</v>
+        <v>4.92785431804574</v>
       </c>
       <c r="O144" s="1">
         <f ca="1" t="shared" si="257"/>
-        <v>0.548932923410916</v>
+        <v>0.621357863707703</v>
       </c>
       <c r="P144" s="1">
         <f ca="1" t="shared" si="258"/>
-        <v>5.27812419404138</v>
+        <v>5.27903465357147</v>
       </c>
     </row>
     <row r="145" ht="16.5" spans="1:16">
@@ -14598,27 +14573,27 @@
       </c>
       <c r="K145" s="1">
         <f ca="1" t="shared" ref="K145:O145" si="259">RAND()</f>
-        <v>0.419520031272103</v>
+        <v>0.0714927420936007</v>
       </c>
       <c r="L145" s="1">
         <f ca="1" t="shared" ref="L145:P145" si="260">J145+$R$1*K145/MAX(1,($A145*($A145-1)))++$R$1/$A145</f>
-        <v>4.544045066121</v>
+        <v>4.54320001151441</v>
       </c>
       <c r="M145" s="1">
         <f ca="1" t="shared" si="259"/>
-        <v>0.723876092525075</v>
+        <v>0.849572088144171</v>
       </c>
       <c r="N145" s="1">
         <f ca="1" t="shared" si="260"/>
-        <v>4.89302495173805</v>
+        <v>4.89248510302603</v>
       </c>
       <c r="O145" s="1">
         <f ca="1" t="shared" si="259"/>
-        <v>0.178617054419616</v>
+        <v>0.446022972838068</v>
       </c>
       <c r="P145" s="1">
         <f ca="1" t="shared" si="260"/>
-        <v>5.24068087892924</v>
+        <v>5.24079032586217</v>
       </c>
     </row>
     <row r="146" ht="16.5" spans="1:16">
@@ -14658,27 +14633,27 @@
       </c>
       <c r="K146" s="1">
         <f ca="1" t="shared" ref="K146:O146" si="261">RAND()</f>
-        <v>0.910963337872674</v>
+        <v>0.747288521200101</v>
       </c>
       <c r="L146" s="1">
         <f ca="1" t="shared" ref="L146:P146" si="262">J146+$R$1*K146/MAX(1,($A146*($A146-1)))++$R$1/$A146</f>
-        <v>4.51367567849107</v>
+        <v>4.51328373688027</v>
       </c>
       <c r="M146" s="1">
         <f ca="1" t="shared" si="261"/>
-        <v>0.492652693408461</v>
+        <v>0.265805264621673</v>
       </c>
       <c r="N146" s="1">
         <f ca="1" t="shared" si="262"/>
-        <v>4.85968298858065</v>
+        <v>4.85874782994689</v>
       </c>
       <c r="O146" s="1">
         <f ca="1" t="shared" si="261"/>
-        <v>0.352100023069459</v>
+        <v>0.0123957875185674</v>
       </c>
       <c r="P146" s="1">
         <f ca="1" t="shared" si="262"/>
-        <v>5.20535372618379</v>
+        <v>5.20360509955302</v>
       </c>
     </row>
     <row r="147" ht="16.5" spans="1:16">
@@ -14718,27 +14693,27 @@
       </c>
       <c r="K147" s="1">
         <f ca="1" t="shared" ref="K147:O147" si="263">RAND()</f>
-        <v>0.575422934494747</v>
+        <v>0.843981041019977</v>
       </c>
       <c r="L147" s="1">
         <f ca="1" t="shared" ref="L147:P147" si="264">J147+$R$1*K147/MAX(1,($A147*($A147-1)))++$R$1/$A147</f>
-        <v>4.48175584065776</v>
+        <v>4.48239012999769</v>
       </c>
       <c r="M147" s="1">
         <f ca="1" t="shared" si="263"/>
-        <v>0.658924334316825</v>
+        <v>0.143903642948609</v>
       </c>
       <c r="N147" s="1">
         <f ca="1" t="shared" si="264"/>
-        <v>4.82577786317622</v>
+        <v>4.82519575976374</v>
       </c>
       <c r="O147" s="1">
         <f ca="1" t="shared" si="263"/>
-        <v>0.495765656340835</v>
+        <v>0.508847793082839</v>
       </c>
       <c r="P147" s="1">
         <f ca="1" t="shared" si="264"/>
-        <v>5.16941453218033</v>
+        <v>5.16886332658727</v>
       </c>
     </row>
     <row r="148" ht="16.5" spans="1:16">
@@ -14778,27 +14753,27 @@
       </c>
       <c r="K148" s="1">
         <f ca="1" t="shared" ref="K148:O148" si="265">RAND()</f>
-        <v>0.332342850204909</v>
+        <v>0.490140231422315</v>
       </c>
       <c r="L148" s="1">
         <f ca="1" t="shared" ref="L148:P148" si="266">J148+$R$1*K148/MAX(1,($A148*($A148-1)))++$R$1/$A148</f>
-        <v>4.4504993543244</v>
+        <v>4.45086697472608</v>
       </c>
       <c r="M148" s="1">
         <f ca="1" t="shared" si="265"/>
-        <v>0.875531777884317</v>
+        <v>0.226379819788213</v>
       </c>
       <c r="N148" s="1">
         <f ca="1" t="shared" si="266"/>
-        <v>4.7926751342561</v>
+        <v>4.79153042598828</v>
       </c>
       <c r="O148" s="1">
         <f ca="1" t="shared" si="265"/>
-        <v>0.161655966264323</v>
+        <v>0.249072123260716</v>
       </c>
       <c r="P148" s="1">
         <f ca="1" t="shared" si="266"/>
-        <v>5.13318779842129</v>
+        <v>5.13224674348726</v>
       </c>
     </row>
     <row r="149" ht="16.5" spans="1:16">
@@ -14838,27 +14813,27 @@
       </c>
       <c r="K149" s="1">
         <f ca="1" t="shared" ref="K149:O149" si="267">RAND()</f>
-        <v>0.279280386036641</v>
+        <v>0.935379634618219</v>
       </c>
       <c r="L149" s="1">
         <f ca="1" t="shared" ref="L149:P149" si="268">J149+$R$1*K149/MAX(1,($A149*($A149-1)))++$R$1/$A149</f>
-        <v>4.42011233771382</v>
+        <v>4.42162019588761</v>
       </c>
       <c r="M149" s="1">
         <f ca="1" t="shared" si="267"/>
-        <v>0.694569277171401</v>
+        <v>0.595668882216416</v>
       </c>
       <c r="N149" s="1">
         <f ca="1" t="shared" si="268"/>
-        <v>4.75954644618314</v>
+        <v>4.76082700982909</v>
       </c>
       <c r="O149" s="1">
         <f ca="1" t="shared" si="267"/>
-        <v>0.255122775879501</v>
+        <v>0.118729550855468</v>
       </c>
       <c r="P149" s="1">
         <f ca="1" t="shared" si="268"/>
-        <v>5.09797061141544</v>
+        <v>5.0989377138897</v>
       </c>
     </row>
     <row r="150" ht="16.5" spans="1:16">
@@ -14898,27 +14873,27 @@
       </c>
       <c r="K150" s="1">
         <f ca="1" t="shared" ref="K150:O150" si="269">RAND()</f>
-        <v>0.914622552766787</v>
+        <v>0.469953366174397</v>
       </c>
       <c r="L150" s="1">
         <f ca="1" t="shared" ref="L150:P150" si="270">J150+$R$1*K150/MAX(1,($A150*($A150-1)))++$R$1/$A150</f>
-        <v>4.39169830979677</v>
+        <v>4.39069008109508</v>
       </c>
       <c r="M150" s="1">
         <f ca="1" t="shared" si="269"/>
-        <v>0.208718988011959</v>
+        <v>0.462706194937515</v>
       </c>
       <c r="N150" s="1">
         <f ca="1" t="shared" si="270"/>
-        <v>4.72774202235801</v>
+        <v>4.72730967613167</v>
       </c>
       <c r="O150" s="1">
         <f ca="1" t="shared" si="269"/>
-        <v>0.103992851211123</v>
+        <v>0.475842748244774</v>
       </c>
       <c r="P150" s="1">
         <f ca="1" t="shared" si="270"/>
-        <v>5.06354828222381</v>
+        <v>5.06395905656937</v>
       </c>
     </row>
     <row r="151" ht="16.5" spans="1:16">
@@ -14958,27 +14933,27 @@
       </c>
       <c r="K151" s="1">
         <f ca="1" t="shared" ref="K151:O151" si="271">RAND()</f>
-        <v>0.144327907124999</v>
+        <v>0.6402885542673</v>
       </c>
       <c r="L151" s="1">
         <f ca="1" t="shared" ref="L151:P151" si="272">J151+$R$1*K151/MAX(1,($A151*($A151-1)))++$R$1/$A151</f>
-        <v>4.36050185214122</v>
+        <v>4.3616113837903</v>
       </c>
       <c r="M151" s="1">
         <f ca="1" t="shared" si="271"/>
-        <v>0.396563473897157</v>
+        <v>0.615286257169193</v>
       </c>
       <c r="N151" s="1">
         <f ca="1" t="shared" si="272"/>
-        <v>4.69472235208282</v>
+        <v>4.69632119644616</v>
       </c>
       <c r="O151" s="1">
         <f ca="1" t="shared" si="271"/>
-        <v>0.422600657636848</v>
+        <v>0.110031907779639</v>
       </c>
       <c r="P151" s="1">
         <f ca="1" t="shared" si="272"/>
-        <v>5.02900110075763</v>
+        <v>5.02990068617274</v>
       </c>
     </row>
     <row r="152" ht="16.5" spans="1:16">
@@ -15018,27 +14993,27 @@
       </c>
       <c r="K152" s="1">
         <f ca="1" t="shared" ref="K152:O152" si="273">RAND()</f>
-        <v>0.619166470076546</v>
+        <v>0.482801655084355</v>
       </c>
       <c r="L152" s="1">
         <f ca="1" t="shared" ref="L152:P152" si="274">J152+$R$1*K152/MAX(1,($A152*($A152-1)))++$R$1/$A152</f>
-        <v>4.3324926412143</v>
+        <v>4.33219161513264</v>
       </c>
       <c r="M152" s="1">
         <f ca="1" t="shared" si="273"/>
-        <v>0.674532403900122</v>
+        <v>0.123313191752354</v>
       </c>
       <c r="N152" s="1">
         <f ca="1" t="shared" si="274"/>
-        <v>4.66510750303306</v>
+        <v>4.66358965749854</v>
       </c>
       <c r="O152" s="1">
         <f ca="1" t="shared" si="273"/>
-        <v>0.895743759588841</v>
+        <v>0.940895975360622</v>
       </c>
       <c r="P152" s="1">
         <f ca="1" t="shared" si="274"/>
-        <v>4.99821069014032</v>
+        <v>4.9967925183713</v>
       </c>
     </row>
     <row r="153" ht="16.5" spans="1:16">
@@ -15078,27 +15053,27 @@
       </c>
       <c r="K153" s="1">
         <f ca="1" t="shared" ref="K153:O153" si="275">RAND()</f>
-        <v>0.26312860078913</v>
+        <v>0.982426530776519</v>
       </c>
       <c r="L153" s="1">
         <f ca="1" t="shared" ref="L153:P153" si="276">J153+$R$1*K153/MAX(1,($A153*($A153-1)))++$R$1/$A153</f>
-        <v>4.30303051716798</v>
+        <v>4.30459747850029</v>
       </c>
       <c r="M153" s="1">
         <f ca="1" t="shared" si="275"/>
-        <v>0.915532939172332</v>
+        <v>0.677742220078547</v>
       </c>
       <c r="N153" s="1">
         <f ca="1" t="shared" si="276"/>
-        <v>4.63397233692045</v>
+        <v>4.63502128082706</v>
       </c>
       <c r="O153" s="1">
         <f ca="1" t="shared" si="275"/>
-        <v>0.6426555924791</v>
+        <v>0.46799759523637</v>
       </c>
       <c r="P153" s="1">
         <f ca="1" t="shared" si="276"/>
-        <v>4.96431970445373</v>
+        <v>4.9649881630056</v>
       </c>
     </row>
     <row r="154" ht="16.5" spans="1:16">
@@ -15138,27 +15113,27 @@
       </c>
       <c r="K154" s="1">
         <f ca="1" t="shared" ref="K154:O154" si="277">RAND()</f>
-        <v>0.66302756609362</v>
+        <v>0.50662804654046</v>
       </c>
       <c r="L154" s="1">
         <f ca="1" t="shared" ref="L154:P154" si="278">J154+$R$1*K154/MAX(1,($A154*($A154-1)))++$R$1/$A154</f>
-        <v>4.27559130453667</v>
+        <v>4.27525504825967</v>
       </c>
       <c r="M154" s="1">
         <f ca="1" t="shared" si="277"/>
-        <v>0.398693570825402</v>
+        <v>0.651807109711602</v>
       </c>
       <c r="N154" s="1">
         <f ca="1" t="shared" si="278"/>
-        <v>4.60324587447738</v>
+        <v>4.60345380795548</v>
       </c>
       <c r="O154" s="1">
         <f ca="1" t="shared" si="277"/>
-        <v>0.137399782995886</v>
+        <v>0.732913884547882</v>
       </c>
       <c r="P154" s="1">
         <f ca="1" t="shared" si="278"/>
-        <v>4.93033866726848</v>
+        <v>4.93182694582215</v>
       </c>
     </row>
     <row r="155" ht="16.5" spans="1:16">
@@ -15198,27 +15173,27 @@
       </c>
       <c r="K155" s="1">
         <f ca="1" t="shared" ref="K155:O155" si="279">RAND()</f>
-        <v>0.0389381187974223</v>
+        <v>0.801966208025797</v>
       </c>
       <c r="L155" s="1">
         <f ca="1" t="shared" ref="L155:P155" si="280">J155+$R$1*K155/MAX(1,($A155*($A155-1)))++$R$1/$A155</f>
-        <v>4.2463265811875</v>
+        <v>4.24794577329604</v>
       </c>
       <c r="M155" s="1">
         <f ca="1" t="shared" si="279"/>
-        <v>0.248841632356281</v>
+        <v>0.362937485627268</v>
       </c>
       <c r="N155" s="1">
         <f ca="1" t="shared" si="280"/>
-        <v>4.57152996297248</v>
+        <v>4.5733912734353</v>
       </c>
       <c r="O155" s="1">
         <f ca="1" t="shared" si="279"/>
-        <v>0.307567295938602</v>
+        <v>0.549099133638734</v>
       </c>
       <c r="P155" s="1">
         <f ca="1" t="shared" si="280"/>
-        <v>4.89685796419466</v>
+        <v>4.89923181993738</v>
       </c>
     </row>
     <row r="156" ht="16.5" spans="1:16">
@@ -15258,27 +15233,27 @@
       </c>
       <c r="K156" s="1">
         <f ca="1" t="shared" ref="K156:O156" si="281">RAND()</f>
-        <v>0.434641819822373</v>
+        <v>0.0991371294072729</v>
       </c>
       <c r="L156" s="1">
         <f ca="1" t="shared" ref="L156:P156" si="282">J156+$R$1*K156/MAX(1,($A156*($A156-1)))++$R$1/$A156</f>
-        <v>4.21959497658111</v>
+        <v>4.21889220177924</v>
       </c>
       <c r="M156" s="1">
         <f ca="1" t="shared" si="281"/>
-        <v>0.210688954969326</v>
+        <v>0.710070289156725</v>
       </c>
       <c r="N156" s="1">
         <f ca="1" t="shared" si="282"/>
-        <v>4.54261694758021</v>
+        <v>4.54296021662875</v>
       </c>
       <c r="O156" s="1">
         <f ca="1" t="shared" si="281"/>
-        <v>0.767014991847148</v>
+        <v>0.431802266913488</v>
       </c>
       <c r="P156" s="1">
         <f ca="1" t="shared" si="282"/>
-        <v>4.86680424333188</v>
+        <v>4.86644534915266</v>
       </c>
     </row>
     <row r="157" ht="16.5" spans="1:16">
@@ -15318,27 +15293,27 @@
       </c>
       <c r="K157" s="1">
         <f ca="1" t="shared" ref="K157:O157" si="283">RAND()</f>
-        <v>0.283872757371769</v>
+        <v>0.971658653700924</v>
       </c>
       <c r="L157" s="1">
         <f ca="1" t="shared" ref="L157:P157" si="284">J157+$R$1*K157/MAX(1,($A157*($A157-1)))++$R$1/$A157</f>
-        <v>4.19206756153303</v>
+        <v>4.19348978216232</v>
       </c>
       <c r="M157" s="1">
         <f ca="1" t="shared" si="283"/>
-        <v>0.823055557033796</v>
+        <v>0.482293102542092</v>
       </c>
       <c r="N157" s="1">
         <f ca="1" t="shared" si="284"/>
-        <v>4.51428231661374</v>
+        <v>4.51499990024037</v>
       </c>
       <c r="O157" s="1">
         <f ca="1" t="shared" si="283"/>
-        <v>0.684422668628677</v>
+        <v>0.95117431204223</v>
       </c>
       <c r="P157" s="1">
         <f ca="1" t="shared" si="284"/>
-        <v>4.83621040319072</v>
+        <v>4.83747958244062</v>
       </c>
     </row>
     <row r="158" ht="16.5" spans="1:16">
@@ -15378,27 +15353,27 @@
       </c>
       <c r="K158" s="1">
         <f ca="1" t="shared" ref="K158:O158" si="285">RAND()</f>
-        <v>0.0228781247198615</v>
+        <v>0.756867121157168</v>
       </c>
       <c r="L158" s="1">
         <f ca="1" t="shared" ref="L158:P158" si="286">J158+$R$1*K158/MAX(1,($A158*($A158-1)))++$R$1/$A158</f>
-        <v>4.16467188903462</v>
+        <v>4.16617031504401</v>
       </c>
       <c r="M158" s="1">
         <f ca="1" t="shared" si="285"/>
-        <v>0.442289844130787</v>
+        <v>0.0384432267683179</v>
       </c>
       <c r="N158" s="1">
         <f ca="1" t="shared" si="286"/>
-        <v>4.48404615378256</v>
+        <v>4.48472013381498</v>
       </c>
       <c r="O158" s="1">
         <f ca="1" t="shared" si="285"/>
-        <v>0.730726176551307</v>
+        <v>0.708396265724768</v>
       </c>
       <c r="P158" s="1">
         <f ca="1" t="shared" si="286"/>
-        <v>4.80400925638046</v>
+        <v>4.80463765028102</v>
       </c>
     </row>
     <row r="159" ht="16.5" spans="1:16">
@@ -15552,27 +15527,27 @@
       </c>
       <c r="K161" s="1">
         <f ca="1" t="shared" ref="K161:O161" si="289">RAND()</f>
-        <v>0.207609238286062</v>
+        <v>0.316622996670307</v>
       </c>
       <c r="L161" s="1">
         <f ca="1" t="shared" ref="L161:P161" si="290">J161+$R$1*K161/MAX(1,($A161*($A161-1)))++$R$1/$A161</f>
-        <v>4.08649294268531</v>
+        <v>4.08670719928591</v>
       </c>
       <c r="M161" s="1">
         <f ca="1" t="shared" si="289"/>
-        <v>0.94350683115999</v>
+        <v>0.536233395757451</v>
       </c>
       <c r="N161" s="1">
         <f ca="1" t="shared" si="290"/>
-        <v>4.40084731931888</v>
+        <v>4.40026111712348</v>
       </c>
       <c r="O161" s="1">
         <f ca="1" t="shared" si="289"/>
-        <v>0.776158492397464</v>
+        <v>0.247423633414281</v>
       </c>
       <c r="P161" s="1">
         <f ca="1" t="shared" si="290"/>
-        <v>4.71487278805394</v>
+        <v>4.71324740571117</v>
       </c>
     </row>
     <row r="162" ht="16.5" spans="1:16">
@@ -15612,27 +15587,27 @@
       </c>
       <c r="K162" s="1">
         <f ca="1" t="shared" ref="K162:O162" si="291">RAND()</f>
-        <v>0.593398850368057</v>
+        <v>0.0456916663892792</v>
       </c>
       <c r="L162" s="1">
         <f ca="1" t="shared" ref="L162:P162" si="292">J162+$R$1*K162/MAX(1,($A162*($A162-1)))++$R$1/$A162</f>
-        <v>4.06171078969404</v>
+        <v>4.06064769345184</v>
       </c>
       <c r="M162" s="1">
         <f ca="1" t="shared" si="291"/>
-        <v>0.0391485508184053</v>
+        <v>0.366511292131</v>
       </c>
       <c r="N162" s="1">
         <f ca="1" t="shared" si="292"/>
-        <v>4.3723457829992</v>
+        <v>4.37191809580458</v>
       </c>
       <c r="O162" s="1">
         <f ca="1" t="shared" si="291"/>
-        <v>0.371527272671447</v>
+        <v>0.951015424639877</v>
       </c>
       <c r="P162" s="1">
         <f ca="1" t="shared" si="292"/>
-        <v>4.68362592133901</v>
+        <v>4.68432301704806</v>
       </c>
     </row>
     <row r="163" ht="16.5" spans="1:16">
@@ -15672,27 +15647,27 @@
       </c>
       <c r="K163" s="1">
         <f ca="1" t="shared" ref="K163:O163" si="293">RAND()</f>
-        <v>0.840725868438</v>
+        <v>0.945112341325919</v>
       </c>
       <c r="L163" s="1">
         <f ca="1" t="shared" ref="L163:P163" si="294">J163+$R$1*K163/MAX(1,($A163*($A163-1)))++$R$1/$A163</f>
-        <v>4.03696174731316</v>
+        <v>4.03716185940749</v>
       </c>
       <c r="M163" s="1">
         <f ca="1" t="shared" si="293"/>
-        <v>0.483739358375265</v>
+        <v>0.858247790767617</v>
       </c>
       <c r="N163" s="1">
         <f ca="1" t="shared" si="294"/>
-        <v>4.34653106592058</v>
+        <v>4.34744912225307</v>
       </c>
       <c r="O163" s="1">
         <f ca="1" t="shared" si="293"/>
-        <v>0.335582490224503</v>
+        <v>0.107014508419901</v>
       </c>
       <c r="P163" s="1">
         <f ca="1" t="shared" si="294"/>
-        <v>4.65581636323334</v>
+        <v>4.65629624768137</v>
       </c>
     </row>
     <row r="164" ht="16.5" spans="1:16">
@@ -15846,27 +15821,27 @@
       </c>
       <c r="K166" s="1">
         <f ca="1" t="shared" ref="K166:O166" si="297">RAND()</f>
-        <v>0.0367493227908349</v>
+        <v>0.31465456569605</v>
       </c>
       <c r="L166" s="1">
         <f ca="1" t="shared" ref="L166:P166" si="298">J166+$R$1*K166/MAX(1,($A166*($A166-1)))++$R$1/$A166</f>
-        <v>3.96163479180117</v>
+        <v>3.96214829003269</v>
       </c>
       <c r="M166" s="1">
         <f ca="1" t="shared" si="297"/>
-        <v>0.34325249165544</v>
+        <v>0.31611753905501</v>
       </c>
       <c r="N166" s="1">
         <f ca="1" t="shared" si="298"/>
-        <v>4.26529933816416</v>
+        <v>4.26576269790235</v>
       </c>
       <c r="O166" s="1">
         <f ca="1" t="shared" si="297"/>
-        <v>0.972779432285425</v>
+        <v>0.735779718172795</v>
       </c>
       <c r="P166" s="1">
         <f ca="1" t="shared" si="298"/>
-        <v>4.57012709025634</v>
+        <v>4.57015253477997</v>
       </c>
     </row>
     <row r="167" ht="16.5" spans="1:16">
@@ -15906,27 +15881,27 @@
       </c>
       <c r="K167" s="1">
         <f ca="1" t="shared" ref="K167:O167" si="299">RAND()</f>
-        <v>0.171646833715583</v>
+        <v>0.693481094864809</v>
       </c>
       <c r="L167" s="1">
         <f ca="1" t="shared" ref="L167:P167" si="300">J167+$R$1*K167/MAX(1,($A167*($A167-1)))++$R$1/$A167</f>
-        <v>3.93788179414698</v>
+        <v>3.93883439411257</v>
       </c>
       <c r="M167" s="1">
         <f ca="1" t="shared" si="299"/>
-        <v>0.993611807044426</v>
+        <v>0.411858299051561</v>
       </c>
       <c r="N167" s="1">
         <f ca="1" t="shared" si="300"/>
-        <v>4.24090043563483</v>
+        <v>4.24079105402322</v>
       </c>
       <c r="O167" s="1">
         <f ca="1" t="shared" si="299"/>
-        <v>0.563956130835687</v>
+        <v>0.85765867233341</v>
       </c>
       <c r="P167" s="1">
         <f ca="1" t="shared" si="300"/>
-        <v>4.54313474766629</v>
+        <v>4.54356151527246</v>
       </c>
     </row>
     <row r="168" ht="16.5" spans="1:16">
@@ -15966,27 +15941,27 @@
       </c>
       <c r="K168" s="1">
         <f ca="1" t="shared" ref="K168:O168" si="301">RAND()</f>
-        <v>0.559518861718097</v>
+        <v>0.0818801023183058</v>
       </c>
       <c r="L168" s="1">
         <f ca="1" t="shared" ref="L168:P168" si="302">J168+$R$1*K168/MAX(1,($A168*($A168-1)))++$R$1/$A168</f>
-        <v>3.91486818927516</v>
+        <v>3.91400670965716</v>
       </c>
       <c r="M168" s="1">
         <f ca="1" t="shared" si="301"/>
-        <v>0.809420781931021</v>
+        <v>0.765404228730195</v>
       </c>
       <c r="N168" s="1">
         <f ca="1" t="shared" si="302"/>
-        <v>4.21572927574426</v>
+        <v>4.21478840691698</v>
       </c>
       <c r="O168" s="1">
         <f ca="1" t="shared" si="301"/>
-        <v>0.176068745961786</v>
+        <v>0.0731041105265664</v>
       </c>
       <c r="P168" s="1">
         <f ca="1" t="shared" si="302"/>
-        <v>4.51544803475509</v>
+        <v>4.51432145667985</v>
       </c>
     </row>
     <row r="169" ht="16.5" spans="1:16">
@@ -16026,27 +16001,27 @@
       </c>
       <c r="K169" s="1">
         <f ca="1" t="shared" ref="K169:O169" si="303">RAND()</f>
-        <v>0.127700316997654</v>
+        <v>0.375076344124229</v>
       </c>
       <c r="L169" s="1">
         <f ca="1" t="shared" ref="L169:P169" si="304">J169+$R$1*K169/MAX(1,($A169*($A169-1)))++$R$1/$A169</f>
-        <v>3.89066099999465</v>
+        <v>3.89110186117787</v>
       </c>
       <c r="M169" s="1">
         <f ca="1" t="shared" si="303"/>
-        <v>0.0598057969472932</v>
+        <v>0.131295622117587</v>
       </c>
       <c r="N169" s="1">
         <f ca="1" t="shared" si="304"/>
-        <v>4.18838663051387</v>
+        <v>4.188954897288</v>
       </c>
       <c r="O169" s="1">
         <f ca="1" t="shared" si="303"/>
-        <v>0.518911446331743</v>
+        <v>0.400589451159715</v>
       </c>
       <c r="P169" s="1">
         <f ca="1" t="shared" si="304"/>
-        <v>4.4869304561596</v>
+        <v>4.48728785539172</v>
       </c>
     </row>
     <row r="170" ht="16.5" spans="1:16">
@@ -16086,27 +16061,27 @@
       </c>
       <c r="K170" s="1">
         <f ca="1" t="shared" ref="K170:O170" si="305">RAND()</f>
-        <v>0.871181352024839</v>
+        <v>0.623036171725732</v>
       </c>
       <c r="L170" s="1">
         <f ca="1" t="shared" ref="L170:P170" si="306">J170+$R$1*K170/MAX(1,($A170*($A170-1)))++$R$1/$A170</f>
-        <v>3.86882076174983</v>
+        <v>3.86838376333426</v>
       </c>
       <c r="M170" s="1">
         <f ca="1" t="shared" si="305"/>
-        <v>0.800055568767865</v>
+        <v>0.310587100415163</v>
       </c>
       <c r="N170" s="1">
         <f ca="1" t="shared" si="306"/>
-        <v>4.16608769533811</v>
+        <v>4.16478871384922</v>
       </c>
       <c r="O170" s="1">
         <f ca="1" t="shared" si="305"/>
-        <v>0.880320638946008</v>
+        <v>0.982826552369839</v>
       </c>
       <c r="P170" s="1">
         <f ca="1" t="shared" si="306"/>
-        <v>4.463495980487</v>
+        <v>4.46237751800597</v>
       </c>
     </row>
     <row r="171" ht="16.5" spans="1:16">
@@ -16146,27 +16121,27 @@
       </c>
       <c r="K171" s="1">
         <f ca="1" t="shared" ref="K171:O171" si="307">RAND()</f>
-        <v>0.784867990686037</v>
+        <v>0.691682324861054</v>
       </c>
       <c r="L171" s="1">
         <f ca="1" t="shared" ref="L171:P171" si="308">J171+$R$1*K171/MAX(1,($A171*($A171-1)))++$R$1/$A171</f>
-        <v>3.84577944307464</v>
+        <v>3.84561726822984</v>
       </c>
       <c r="M171" s="1">
         <f ca="1" t="shared" si="307"/>
-        <v>0.0348605598370113</v>
+        <v>0.687579777255205</v>
       </c>
       <c r="N171" s="1">
         <f ca="1" t="shared" si="308"/>
-        <v>4.13995775939875</v>
+        <v>4.14093153863926</v>
       </c>
       <c r="O171" s="1">
         <f ca="1" t="shared" si="307"/>
-        <v>0.0676920889891606</v>
+        <v>0.0342771673188944</v>
       </c>
       <c r="P171" s="1">
         <f ca="1" t="shared" si="308"/>
-        <v>4.43419321378265</v>
+        <v>4.43510883966139</v>
       </c>
     </row>
     <row r="172" ht="16.5" spans="1:16">
@@ -16206,27 +16181,27 @@
       </c>
       <c r="K172" s="1">
         <f ca="1" t="shared" ref="K172:O172" si="309">RAND()</f>
-        <v>0.022095030104949</v>
+        <v>0.611368368238394</v>
       </c>
       <c r="L172" s="1">
         <f ca="1" t="shared" ref="L172:P172" si="310">J172+$R$1*K172/MAX(1,($A172*($A172-1)))++$R$1/$A172</f>
-        <v>3.82184742867235</v>
+        <v>3.8228609707056</v>
       </c>
       <c r="M172" s="1">
         <f ca="1" t="shared" si="309"/>
-        <v>0.461768396525737</v>
+        <v>0.244317878857667</v>
       </c>
       <c r="N172" s="1">
         <f ca="1" t="shared" si="310"/>
-        <v>4.11503932477921</v>
+        <v>4.11567885491416</v>
       </c>
       <c r="O172" s="1">
         <f ca="1" t="shared" si="309"/>
-        <v>0.370704054758529</v>
+        <v>0.452626551980554</v>
       </c>
       <c r="P172" s="1">
         <f ca="1" t="shared" si="310"/>
-        <v>4.40807459147126</v>
+        <v>4.40885502717419</v>
       </c>
     </row>
     <row r="173" ht="16.5" spans="1:16">
@@ -16266,27 +16241,27 @@
       </c>
       <c r="K173" s="1">
         <f ca="1" t="shared" ref="K173:O173" si="311">RAND()</f>
-        <v>0.932580610448176</v>
+        <v>0.796014720983948</v>
       </c>
       <c r="L173" s="1">
         <f ca="1" t="shared" ref="L173:P173" si="312">J173+$R$1*K173/MAX(1,($A173*($A173-1)))++$R$1/$A173</f>
-        <v>3.80105497859793</v>
+        <v>3.80082281844312</v>
       </c>
       <c r="M173" s="1">
         <f ca="1" t="shared" si="311"/>
-        <v>0.224895549619725</v>
+        <v>0.528579329269264</v>
       </c>
       <c r="N173" s="1">
         <f ca="1" t="shared" si="312"/>
-        <v>4.09213497239234</v>
+        <v>4.09241907053286</v>
       </c>
       <c r="O173" s="1">
         <f ca="1" t="shared" si="311"/>
-        <v>0.638193660082393</v>
+        <v>0.21355812114534</v>
       </c>
       <c r="P173" s="1">
         <f ca="1" t="shared" si="312"/>
-        <v>4.38391756735372</v>
+        <v>4.38347979085305</v>
       </c>
     </row>
     <row r="174" ht="16.5" spans="1:16">
@@ -16326,27 +16301,27 @@
       </c>
       <c r="K174" s="1">
         <f ca="1" t="shared" ref="K174:O174" si="313">RAND()</f>
-        <v>0.449660915113974</v>
+        <v>0.845966626331044</v>
       </c>
       <c r="L174" s="1">
         <f ca="1" t="shared" ref="L174:P174" si="314">J174+$R$1*K174/MAX(1,($A174*($A174-1)))++$R$1/$A174</f>
-        <v>3.77814501430823</v>
+        <v>3.77881094002274</v>
       </c>
       <c r="M174" s="1">
         <f ca="1" t="shared" si="313"/>
-        <v>0.621444371783886</v>
+        <v>0.56145470472357</v>
       </c>
       <c r="N174" s="1">
         <f ca="1" t="shared" si="314"/>
-        <v>4.06820658906926</v>
+        <v>4.06877171214387</v>
       </c>
       <c r="O174" s="1">
         <f ca="1" t="shared" si="313"/>
-        <v>0.729473560653999</v>
+        <v>0.634762036420426</v>
       </c>
       <c r="P174" s="1">
         <f ca="1" t="shared" si="314"/>
-        <v>4.35844968888216</v>
+        <v>4.3588556650213</v>
       </c>
     </row>
     <row r="175" ht="16.5" spans="1:16">
@@ -16386,27 +16361,27 @@
       </c>
       <c r="K175" s="1">
         <f ca="1" t="shared" ref="K175:O175" si="315">RAND()</f>
-        <v>0.222197775328725</v>
+        <v>0.95196600882557</v>
       </c>
       <c r="L175" s="1">
         <f ca="1" t="shared" ref="L175:P175" si="316">J175+$R$1*K175/MAX(1,($A175*($A175-1)))++$R$1/$A175</f>
-        <v>3.75593348909596</v>
+        <v>3.75714564814435</v>
       </c>
       <c r="M175" s="1">
         <f ca="1" t="shared" si="315"/>
-        <v>0.217082772695268</v>
+        <v>0.255980981235062</v>
       </c>
       <c r="N175" s="1">
         <f ca="1" t="shared" si="316"/>
-        <v>4.04365038958877</v>
+        <v>4.04492715930845</v>
       </c>
       <c r="O175" s="1">
         <f ca="1" t="shared" si="315"/>
-        <v>0.714566551966202</v>
+        <v>0.658902033239524</v>
       </c>
       <c r="P175" s="1">
         <f ca="1" t="shared" si="316"/>
-        <v>4.33219362019133</v>
+        <v>4.33337793007657</v>
       </c>
     </row>
     <row r="176" ht="16.5" spans="1:16">
@@ -16446,27 +16421,27 @@
       </c>
       <c r="K176" s="1">
         <f ca="1" t="shared" ref="K176:O176" si="317">RAND()</f>
-        <v>0.948123127852096</v>
+        <v>0.642172426443474</v>
       </c>
       <c r="L176" s="1">
         <f ca="1" t="shared" ref="L176:P176" si="318">J176+$R$1*K176/MAX(1,($A176*($A176-1)))++$R$1/$A176</f>
-        <v>3.73554700020994</v>
+        <v>3.73504461810582</v>
       </c>
       <c r="M176" s="1">
         <f ca="1" t="shared" si="317"/>
-        <v>0.835997933235475</v>
+        <v>0.713131693183489</v>
       </c>
       <c r="N176" s="1">
         <f ca="1" t="shared" si="318"/>
-        <v>4.02263402473085</v>
+        <v>4.02192989182205</v>
       </c>
       <c r="O176" s="1">
         <f ca="1" t="shared" si="317"/>
-        <v>0.984635631175947</v>
+        <v>0.990660678430287</v>
       </c>
       <c r="P176" s="1">
         <f ca="1" t="shared" si="318"/>
-        <v>4.30996511772129</v>
+        <v>4.30927087815773</v>
       </c>
     </row>
     <row r="177" ht="16.5" spans="1:16">
@@ -16506,27 +16481,27 @@
       </c>
       <c r="K177" s="1">
         <f ca="1" t="shared" ref="K177:O177" si="319">RAND()</f>
-        <v>0.606206217559284</v>
+        <v>0.769527423778976</v>
       </c>
       <c r="L177" s="1">
         <f ca="1" t="shared" ref="L177:P177" si="320">J177+$R$1*K177/MAX(1,($A177*($A177-1)))++$R$1/$A177</f>
-        <v>3.71364643866487</v>
+        <v>3.71391157049315</v>
       </c>
       <c r="M177" s="1">
         <f ca="1" t="shared" si="319"/>
-        <v>0.513959985025248</v>
+        <v>0.558909992550241</v>
       </c>
       <c r="N177" s="1">
         <f ca="1" t="shared" si="320"/>
-        <v>3.99857169838082</v>
+        <v>3.99890980100054</v>
       </c>
       <c r="O177" s="1">
         <f ca="1" t="shared" si="319"/>
-        <v>0.019392715273298</v>
+        <v>0.743271354379516</v>
       </c>
       <c r="P177" s="1">
         <f ca="1" t="shared" si="320"/>
-        <v>4.28269408915237</v>
+        <v>4.28420731943297</v>
       </c>
     </row>
     <row r="178" ht="16.5" spans="1:16">
@@ -16566,27 +16541,27 @@
       </c>
       <c r="K178" s="1">
         <f ca="1" t="shared" ref="K178:O178" si="321">RAND()</f>
-        <v>0.99449174732599</v>
+        <v>0.301173184276524</v>
       </c>
       <c r="L178" s="1">
         <f ca="1" t="shared" ref="L178:P178" si="322">J178+$R$1*K178/MAX(1,($A178*($A178-1)))++$R$1/$A178</f>
-        <v>3.69317297725238</v>
+        <v>3.69206017781246</v>
       </c>
       <c r="M178" s="1">
         <f ca="1" t="shared" si="321"/>
-        <v>0.472536325738922</v>
+        <v>0.24412245241795</v>
       </c>
       <c r="N178" s="1">
         <f ca="1" t="shared" si="322"/>
-        <v>3.97641728953689</v>
+        <v>3.97493787820476</v>
       </c>
       <c r="O178" s="1">
         <f ca="1" t="shared" si="321"/>
-        <v>0.0161986531772673</v>
+        <v>0.131358742929683</v>
       </c>
       <c r="P178" s="1">
         <f ca="1" t="shared" si="322"/>
-        <v>4.25892916462224</v>
+        <v>4.25763458907875</v>
       </c>
     </row>
     <row r="179" ht="16.5" spans="1:16">
@@ -16626,27 +16601,27 @@
       </c>
       <c r="K179" s="1">
         <f ca="1" t="shared" ref="K179:O179" si="323">RAND()</f>
-        <v>0.463437877405256</v>
+        <v>0.886268285865971</v>
       </c>
       <c r="L179" s="1">
         <f ca="1" t="shared" ref="L179:P179" si="324">J179+$R$1*K179/MAX(1,($A179*($A179-1)))++$R$1/$A179</f>
-        <v>3.6714648604669</v>
+        <v>3.67213589202988</v>
       </c>
       <c r="M179" s="1">
         <f ca="1" t="shared" si="323"/>
-        <v>0.845777617193302</v>
+        <v>0.917475049784889</v>
       </c>
       <c r="N179" s="1">
         <f ca="1" t="shared" si="324"/>
-        <v>3.95370598535929</v>
+        <v>3.95449080069773</v>
       </c>
       <c r="O179" s="1">
         <f ca="1" t="shared" si="323"/>
-        <v>0.652105549657908</v>
+        <v>0.113146254344223</v>
       </c>
       <c r="P179" s="1">
         <f ca="1" t="shared" si="324"/>
-        <v>4.23563975281574</v>
+        <v>4.23556924012886</v>
       </c>
     </row>
     <row r="180" ht="16.5" spans="1:16">
@@ -16686,27 +16661,27 @@
       </c>
       <c r="K180" s="1">
         <f ca="1" t="shared" ref="K180:O180" si="325">RAND()</f>
-        <v>0.350388284737618</v>
+        <v>0.0549206226011512</v>
       </c>
       <c r="L180" s="1">
         <f ca="1" t="shared" ref="L180:P180" si="326">J180+$R$1*K180/MAX(1,($A180*($A180-1)))++$R$1/$A180</f>
-        <v>3.65066597872817</v>
+        <v>3.65020231093873</v>
       </c>
       <c r="M180" s="1">
         <f ca="1" t="shared" si="325"/>
-        <v>0.308624900373839</v>
+        <v>0.613682293247714</v>
       </c>
       <c r="N180" s="1">
         <f ca="1" t="shared" si="326"/>
-        <v>3.93047990268205</v>
+        <v>3.9304949515345</v>
       </c>
       <c r="O180" s="1">
         <f ca="1" t="shared" si="325"/>
-        <v>0.958420894288291</v>
+        <v>0.187042289532085</v>
       </c>
       <c r="P180" s="1">
         <f ca="1" t="shared" si="326"/>
-        <v>4.21131353034869</v>
+        <v>4.21011807985277</v>
       </c>
     </row>
     <row r="181" ht="16.5" spans="1:16">
@@ -16746,27 +16721,27 @@
       </c>
       <c r="K181" s="1">
         <f ca="1" t="shared" ref="K181:O181" si="327">RAND()</f>
-        <v>0.309688933421029</v>
+        <v>0.618426849154694</v>
       </c>
       <c r="L181" s="1">
         <f ca="1" t="shared" ref="L181:P181" si="328">J181+$R$1*K181/MAX(1,($A181*($A181-1)))++$R$1/$A181</f>
-        <v>3.63021366997738</v>
+        <v>3.63069277909552</v>
       </c>
       <c r="M181" s="1">
         <f ca="1" t="shared" si="327"/>
-        <v>0.693997363316754</v>
+        <v>0.661539608149198</v>
       </c>
       <c r="N181" s="1">
         <f ca="1" t="shared" si="328"/>
-        <v>3.90906841448904</v>
+        <v>3.90949715465131</v>
       </c>
       <c r="O181" s="1">
         <f ca="1" t="shared" si="327"/>
-        <v>0.365782135871125</v>
+        <v>0.0319941128665067</v>
       </c>
       <c r="P181" s="1">
         <f ca="1" t="shared" si="328"/>
-        <v>4.18741382438332</v>
+        <v>4.18732458189039</v>
       </c>
     </row>
     <row r="182" ht="16.5" spans="1:16">
@@ -16806,27 +16781,27 @@
       </c>
       <c r="K182" s="1">
         <f ca="1" t="shared" ref="K182:O182" si="329">RAND()</f>
-        <v>0.507238418206479</v>
+        <v>0.125525043551333</v>
       </c>
       <c r="L182" s="1">
         <f ca="1" t="shared" ref="L182:P182" si="330">J182+$R$1*K182/MAX(1,($A182*($A182-1)))++$R$1/$A182</f>
-        <v>3.61035487786711</v>
+        <v>3.60976906851373</v>
       </c>
       <c r="M182" s="1">
         <f ca="1" t="shared" si="329"/>
-        <v>0.536228739152586</v>
+        <v>0.137464441808355</v>
       </c>
       <c r="N182" s="1">
         <f ca="1" t="shared" si="330"/>
-        <v>3.88742091337839</v>
+        <v>3.88622312689588</v>
       </c>
       <c r="O182" s="1">
         <f ca="1" t="shared" si="329"/>
-        <v>0.992078634882462</v>
+        <v>0.651263931456679</v>
       </c>
       <c r="P182" s="1">
         <f ca="1" t="shared" si="330"/>
-        <v>4.16518653436501</v>
+        <v>4.16346570505957</v>
       </c>
     </row>
     <row r="183" ht="16.5" spans="1:16">
@@ -16866,27 +16841,27 @@
       </c>
       <c r="K183" s="1">
         <f ca="1" t="shared" ref="K183:O183" si="331">RAND()</f>
-        <v>0.510110948004659</v>
+        <v>0.451412360804146</v>
       </c>
       <c r="L183" s="1">
         <f ca="1" t="shared" ref="L183:P183" si="332">J183+$R$1*K183/MAX(1,($A183*($A183-1)))++$R$1/$A183</f>
-        <v>3.59041665798677</v>
+        <v>3.59032756414426</v>
       </c>
       <c r="M183" s="1">
         <f ca="1" t="shared" si="331"/>
-        <v>0.679062094922708</v>
+        <v>0.152398056038809</v>
       </c>
       <c r="N183" s="1">
         <f ca="1" t="shared" si="332"/>
-        <v>3.86617262619593</v>
+        <v>3.86528415156463</v>
       </c>
       <c r="O183" s="1">
         <f ca="1" t="shared" si="331"/>
-        <v>0.649251917710715</v>
+        <v>0.717455796152389</v>
       </c>
       <c r="P183" s="1">
         <f ca="1" t="shared" si="332"/>
-        <v>4.14188334794584</v>
+        <v>4.14109839447057</v>
       </c>
     </row>
     <row r="184" ht="16.5" spans="1:16">
@@ -16926,27 +16901,27 @@
       </c>
       <c r="K184" s="1">
         <f ca="1" t="shared" ref="K184:O184" si="333">RAND()</f>
-        <v>0.255671943440078</v>
+        <v>0.641536780039009</v>
       </c>
       <c r="L184" s="1">
         <f ca="1" t="shared" ref="L184:P184" si="334">J184+$R$1*K184/MAX(1,($A184*($A184-1)))++$R$1/$A184</f>
-        <v>3.57031116306888</v>
+        <v>3.57089043532703</v>
       </c>
       <c r="M184" s="1">
         <f ca="1" t="shared" si="333"/>
-        <v>0.300316544050534</v>
+        <v>0.919256621881135</v>
       </c>
       <c r="N184" s="1">
         <f ca="1" t="shared" si="334"/>
-        <v>3.8439860512933</v>
+        <v>3.84549449558927</v>
       </c>
       <c r="O184" s="1">
         <f ca="1" t="shared" si="333"/>
-        <v>0.328271647938223</v>
+        <v>0.718736846182948</v>
       </c>
       <c r="P184" s="1">
         <f ca="1" t="shared" si="334"/>
-        <v>4.11770290658654</v>
+        <v>4.11979752934622</v>
       </c>
     </row>
     <row r="185" ht="16.5" spans="1:16">
@@ -16986,27 +16961,27 @@
       </c>
       <c r="K185" s="1">
         <f ca="1" t="shared" ref="K185:O185" si="335">RAND()</f>
-        <v>0.147409912518345</v>
+        <v>0.416670186865664</v>
       </c>
       <c r="L185" s="1">
         <f ca="1" t="shared" ref="L185:P185" si="336">J185+$R$1*K185/MAX(1,($A185*($A185-1)))++$R$1/$A185</f>
-        <v>3.55064654596181</v>
+        <v>3.55104637411924</v>
       </c>
       <c r="M185" s="1">
         <f ca="1" t="shared" si="335"/>
-        <v>0.816895860704265</v>
+        <v>0.532612400496881</v>
       </c>
       <c r="N185" s="1">
         <f ca="1" t="shared" si="336"/>
-        <v>3.82359869590939</v>
+        <v>3.82357638778118</v>
       </c>
       <c r="O185" s="1">
         <f ca="1" t="shared" si="335"/>
-        <v>0.961486597167507</v>
+        <v>0.421468817879256</v>
       </c>
       <c r="P185" s="1">
         <f ca="1" t="shared" si="336"/>
-        <v>4.09676555056188</v>
+        <v>4.09594136286119</v>
       </c>
     </row>
     <row r="186" ht="16.5" spans="1:16">
@@ -17046,27 +17021,27 @@
       </c>
       <c r="K186" s="1">
         <f ca="1" t="shared" ref="K186:O186" si="337">RAND()</f>
-        <v>0.100882476109203</v>
+        <v>0.904215399340236</v>
       </c>
       <c r="L186" s="1">
         <f ca="1" t="shared" ref="L186:P186" si="338">J186+$R$1*K186/MAX(1,($A186*($A186-1)))++$R$1/$A186</f>
-        <v>3.53128801773812</v>
+        <v>3.53246800146789</v>
       </c>
       <c r="M186" s="1">
         <f ca="1" t="shared" si="337"/>
-        <v>0.578044896247381</v>
+        <v>0.950296610243612</v>
       </c>
       <c r="N186" s="1">
         <f ca="1" t="shared" si="338"/>
-        <v>3.80240735512978</v>
+        <v>3.80413412457342</v>
       </c>
       <c r="O186" s="1">
         <f ca="1" t="shared" si="337"/>
-        <v>0.845317858745851</v>
+        <v>0.148876474944558</v>
       </c>
       <c r="P186" s="1">
         <f ca="1" t="shared" si="338"/>
-        <v>4.07391927912912</v>
+        <v>4.07462307356717</v>
       </c>
     </row>
     <row r="187" ht="16.5" spans="1:16">
@@ -17106,27 +17081,27 @@
       </c>
       <c r="K187" s="1">
         <f ca="1" t="shared" ref="K187:O187" si="339">RAND()</f>
-        <v>0.560358182501538</v>
+        <v>0.45530634076213</v>
       </c>
       <c r="L187" s="1">
         <f ca="1" t="shared" ref="L187:P187" si="340">J187+$R$1*K187/MAX(1,($A187*($A187-1)))++$R$1/$A187</f>
-        <v>3.51287468494987</v>
+        <v>3.51272203769363</v>
       </c>
       <c r="M187" s="1">
         <f ca="1" t="shared" si="339"/>
-        <v>0.669239447710063</v>
+        <v>0.800847048119902</v>
       </c>
       <c r="N187" s="1">
         <f ca="1" t="shared" si="340"/>
-        <v>3.78266433831766</v>
+        <v>3.78270292558686</v>
       </c>
       <c r="O187" s="1">
         <f ca="1" t="shared" si="339"/>
-        <v>0.594836020017226</v>
+        <v>0.83042134278014</v>
       </c>
       <c r="P187" s="1">
         <f ca="1" t="shared" si="340"/>
-        <v>4.05234587859667</v>
+        <v>4.05272678688123</v>
       </c>
     </row>
     <row r="188" ht="16.5" spans="1:16">
@@ -17166,27 +17141,27 @@
       </c>
       <c r="K188" s="1">
         <f ca="1" t="shared" ref="K188:O188" si="341">RAND()</f>
-        <v>0.173630716624076</v>
+        <v>0.810782095631261</v>
       </c>
       <c r="L188" s="1">
         <f ca="1" t="shared" ref="L188:P188" si="342">J188+$R$1*K188/MAX(1,($A188*($A188-1)))++$R$1/$A188</f>
-        <v>3.49343572928041</v>
+        <v>3.49435165041635</v>
       </c>
       <c r="M188" s="1">
         <f ca="1" t="shared" si="341"/>
-        <v>0.981477997915099</v>
+        <v>0.212375879871325</v>
       </c>
       <c r="N188" s="1">
         <f ca="1" t="shared" si="342"/>
-        <v>3.76222630773754</v>
+        <v>3.76203662523072</v>
       </c>
       <c r="O188" s="1">
         <f ca="1" t="shared" si="341"/>
-        <v>0.617366680997818</v>
+        <v>0.883748040820916</v>
       </c>
       <c r="P188" s="1">
         <f ca="1" t="shared" si="342"/>
-        <v>4.03049346701676</v>
+        <v>4.03068671441596</v>
       </c>
     </row>
     <row r="189" ht="16.5" spans="1:16">
@@ -17226,27 +17201,27 @@
       </c>
       <c r="K189" s="1">
         <f ca="1" t="shared" ref="K189:O189" si="343">RAND()</f>
-        <v>0.629852702611651</v>
+        <v>0.292044107278647</v>
       </c>
       <c r="L189" s="1">
         <f ca="1" t="shared" ref="L189:P189" si="344">J189+$R$1*K189/MAX(1,($A189*($A189-1)))++$R$1/$A189</f>
-        <v>3.47540939342162</v>
+        <v>3.474928951114</v>
       </c>
       <c r="M189" s="1">
         <f ca="1" t="shared" si="343"/>
-        <v>0.818020484960454</v>
+        <v>0.574745621852196</v>
       </c>
       <c r="N189" s="1">
         <f ca="1" t="shared" si="344"/>
-        <v>3.74253025541525</v>
+        <v>3.74170381973081</v>
       </c>
       <c r="O189" s="1">
         <f ca="1" t="shared" si="343"/>
-        <v>0.274721574250325</v>
+        <v>0.654095547022563</v>
       </c>
       <c r="P189" s="1">
         <f ca="1" t="shared" si="344"/>
-        <v>4.00887842013002</v>
+        <v>4.00859154237705</v>
       </c>
     </row>
     <row r="190" ht="16.5" spans="1:16">
@@ -17286,27 +17261,27 @@
       </c>
       <c r="K190" s="1">
         <f ca="1" t="shared" ref="K190:O190" si="345">RAND()</f>
-        <v>0.98998421614668</v>
+        <v>0.903516451284927</v>
       </c>
       <c r="L190" s="1">
         <f ca="1" t="shared" ref="L190:P190" si="346">J190+$R$1*K190/MAX(1,($A190*($A190-1)))++$R$1/$A190</f>
-        <v>3.4574327144773</v>
+        <v>3.45731103857268</v>
       </c>
       <c r="M190" s="1">
         <f ca="1" t="shared" si="345"/>
-        <v>0.448199238998235</v>
+        <v>0.0960302748155417</v>
       </c>
       <c r="N190" s="1">
         <f ca="1" t="shared" si="346"/>
-        <v>3.72261367704484</v>
+        <v>3.72199643522192</v>
       </c>
       <c r="O190" s="1">
         <f ca="1" t="shared" si="345"/>
-        <v>0.873759706341328</v>
+        <v>0.097604493745483</v>
       </c>
       <c r="P190" s="1">
         <f ca="1" t="shared" si="346"/>
-        <v>3.98839348075184</v>
+        <v>3.9866840470841</v>
       </c>
     </row>
     <row r="191" ht="16.5" spans="1:16">
@@ -17346,27 +17321,27 @@
       </c>
       <c r="K191" s="1">
         <f ca="1" t="shared" ref="K191:O191" si="347">RAND()</f>
-        <v>0.858089852834503</v>
+        <v>0.217808649275842</v>
       </c>
       <c r="L191" s="1">
         <f ca="1" t="shared" ref="L191:P191" si="348">J191+$R$1*K191/MAX(1,($A191*($A191-1)))++$R$1/$A191</f>
-        <v>3.43895584774831</v>
+        <v>3.43806433952837</v>
       </c>
       <c r="M191" s="1">
         <f ca="1" t="shared" si="347"/>
-        <v>0.276487599096904</v>
+        <v>0.67715525940037</v>
       </c>
       <c r="N191" s="1">
         <f ca="1" t="shared" si="348"/>
-        <v>3.70249871547192</v>
+        <v>3.7021650848074</v>
       </c>
       <c r="O191" s="1">
         <f ca="1" t="shared" si="347"/>
-        <v>0.859145288089643</v>
+        <v>0.425868212268018</v>
       </c>
       <c r="P191" s="1">
         <f ca="1" t="shared" si="348"/>
-        <v>3.96685285817324</v>
+        <v>3.9659159455875</v>
       </c>
     </row>
     <row r="192" ht="16.5" spans="1:16">
@@ -17406,27 +17381,27 @@
       </c>
       <c r="K192" s="1">
         <f ca="1" t="shared" ref="K192:O192" si="349">RAND()</f>
-        <v>0.277735265635867</v>
+        <v>0.357068288226025</v>
       </c>
       <c r="L192" s="1">
         <f ca="1" t="shared" ref="L192:P192" si="350">J192+$R$1*K192/MAX(1,($A192*($A192-1)))++$R$1/$A192</f>
-        <v>3.42005750243268</v>
+        <v>3.42016680667984</v>
       </c>
       <c r="M192" s="1">
         <f ca="1" t="shared" si="349"/>
-        <v>0.60040384294082</v>
+        <v>0.320243438072373</v>
       </c>
       <c r="N192" s="1">
         <f ca="1" t="shared" si="350"/>
-        <v>3.68266483757037</v>
+        <v>3.68238813960637</v>
       </c>
       <c r="O192" s="1">
         <f ca="1" t="shared" si="349"/>
-        <v>0.372306270751213</v>
+        <v>0.685216899471506</v>
       </c>
       <c r="P192" s="1">
         <f ca="1" t="shared" si="350"/>
-        <v>3.94495790214843</v>
+        <v>3.94511232932733</v>
       </c>
     </row>
     <row r="193" ht="16.5" spans="1:16">
@@ -17466,27 +17441,27 @@
       </c>
       <c r="K193" s="1">
         <f ca="1" t="shared" ref="K193:O193" si="351">RAND()</f>
-        <v>0.116570260483989</v>
+        <v>0.0575312710161024</v>
       </c>
       <c r="L193" s="1">
         <f ca="1" t="shared" ref="L193:P193" si="352">J193+$R$1*K193/MAX(1,($A193*($A193-1)))++$R$1/$A193</f>
-        <v>3.40193685953927</v>
+        <v>3.40185636353487</v>
       </c>
       <c r="M193" s="1">
         <f ca="1" t="shared" si="351"/>
-        <v>0.34494460893045</v>
+        <v>0.527203713460068</v>
       </c>
       <c r="N193" s="1">
         <f ca="1" t="shared" si="352"/>
-        <v>3.6628238368093</v>
+        <v>3.66299183980213</v>
       </c>
       <c r="O193" s="1">
         <f ca="1" t="shared" si="351"/>
-        <v>0.276607083160114</v>
+        <v>0.23864677786071</v>
       </c>
       <c r="P193" s="1">
         <f ca="1" t="shared" si="352"/>
-        <v>3.92361764009677</v>
+        <v>3.92373388656514</v>
       </c>
     </row>
     <row r="194" ht="16.5" spans="1:16">
@@ -17526,27 +17501,27 @@
       </c>
       <c r="K194" s="1">
         <f ca="1" t="shared" ref="K194:O194" si="356">RAND()</f>
-        <v>0.78019390336437</v>
+        <v>0.258591435404137</v>
       </c>
       <c r="L194" s="1">
         <f ca="1" t="shared" ref="L194:P194" si="357">J194+$R$1*K194/MAX(1,($A194*($A194-1)))++$R$1/$A194</f>
-        <v>3.38512008028843</v>
+        <v>3.38441627730382</v>
       </c>
       <c r="M194" s="1">
         <f ca="1" t="shared" si="356"/>
-        <v>0.0695477045986073</v>
+        <v>0.169312541221733</v>
       </c>
       <c r="N194" s="1">
         <f ca="1" t="shared" si="357"/>
-        <v>3.64428127915582</v>
+        <v>3.64371208977848</v>
       </c>
       <c r="O194" s="1">
         <f ca="1" t="shared" si="356"/>
-        <v>0.502662096451108</v>
+        <v>0.167265378911811</v>
       </c>
       <c r="P194" s="1">
         <f ca="1" t="shared" si="357"/>
-        <v>3.90402688323674</v>
+        <v>3.9030051399983</v>
       </c>
     </row>
     <row r="195" ht="16.5" spans="1:16">
@@ -17586,27 +17561,27 @@
       </c>
       <c r="K195" s="1">
         <f ca="1" t="shared" ref="K195:O195" si="358">RAND()</f>
-        <v>0.375421344197973</v>
+        <v>0.86272665911422</v>
       </c>
       <c r="L195" s="1">
         <f ca="1" t="shared" ref="L195:P195" si="359">J195+$R$1*K195/MAX(1,($A195*($A195-1)))++$R$1/$A195</f>
-        <v>3.36704158611212</v>
+        <v>3.36769233302056</v>
       </c>
       <c r="M195" s="1">
         <f ca="1" t="shared" si="358"/>
-        <v>0.588219209636149</v>
+        <v>0.483611730118906</v>
       </c>
       <c r="N195" s="1">
         <f ca="1" t="shared" si="359"/>
-        <v>3.62555905207232</v>
+        <v>3.62607010628336</v>
       </c>
       <c r="O195" s="1">
         <f ca="1" t="shared" si="358"/>
-        <v>0.798965685240522</v>
+        <v>0.509375366442102</v>
       </c>
       <c r="P195" s="1">
         <f ca="1" t="shared" si="359"/>
-        <v>3.88435794861262</v>
+        <v>3.88448228427391</v>
       </c>
     </row>
     <row r="196" ht="16.5" spans="1:16">
@@ -17646,27 +17621,27 @@
       </c>
       <c r="K196" s="1">
         <f ca="1" t="shared" ref="K196:O196" si="360">RAND()</f>
-        <v>0.00390705331289332</v>
+        <v>0.119222647561923</v>
       </c>
       <c r="L196" s="1">
         <f ca="1" t="shared" ref="L196:P196" si="361">J196+$R$1*K196/MAX(1,($A196*($A196-1)))++$R$1/$A196</f>
-        <v>3.34919892552645</v>
+        <v>3.34935133841867</v>
       </c>
       <c r="M196" s="1">
         <f ca="1" t="shared" si="360"/>
-        <v>0.341618423158104</v>
+        <v>0.838273935813452</v>
       </c>
       <c r="N196" s="1">
         <f ca="1" t="shared" si="361"/>
-        <v>3.6060606998103</v>
+        <v>3.60686954346204</v>
       </c>
       <c r="O196" s="1">
         <f ca="1" t="shared" si="360"/>
-        <v>0.310760762950018</v>
+        <v>0.0448779510230113</v>
       </c>
       <c r="P196" s="1">
         <f ca="1" t="shared" si="361"/>
-        <v>3.86288168945205</v>
+        <v>3.86333911516574</v>
       </c>
     </row>
     <row r="197" ht="16.5" spans="1:16">
@@ -17706,27 +17681,27 @@
       </c>
       <c r="K197" s="1">
         <f ca="1" t="shared" ref="K197:O197" si="362">RAND()</f>
-        <v>0.161834953521243</v>
+        <v>0.33933057515426</v>
       </c>
       <c r="L197" s="1">
         <f ca="1" t="shared" ref="L197:P197" si="363">J197+$R$1*K197/MAX(1,($A197*($A197-1)))++$R$1/$A197</f>
-        <v>3.33223683274924</v>
+        <v>3.33246903528932</v>
       </c>
       <c r="M197" s="1">
         <f ca="1" t="shared" si="362"/>
-        <v>0.972110896975111</v>
+        <v>0.832473439286346</v>
       </c>
       <c r="N197" s="1">
         <f ca="1" t="shared" si="363"/>
-        <v>3.58861060420002</v>
+        <v>3.58866013084045</v>
       </c>
       <c r="O197" s="1">
         <f ca="1" t="shared" si="362"/>
-        <v>0.174921379442487</v>
+        <v>0.00100113473069618</v>
       </c>
       <c r="P197" s="1">
         <f ca="1" t="shared" si="363"/>
-        <v>3.84394147989265</v>
+        <v>3.84376348135685</v>
       </c>
     </row>
     <row r="198" ht="16.5" spans="1:16">
@@ -17766,27 +17741,27 @@
       </c>
       <c r="K198" s="1">
         <f ca="1" t="shared" ref="K198:O198" si="364">RAND()</f>
-        <v>0.466951948861994</v>
+        <v>0.610278709286187</v>
       </c>
       <c r="L198" s="1">
         <f ca="1" t="shared" ref="L198:P198" si="365">J198+$R$1*K198/MAX(1,($A198*($A198-1)))++$R$1/$A198</f>
-        <v>3.31563626845134</v>
+        <v>3.31582186717767</v>
       </c>
       <c r="M198" s="1">
         <f ca="1" t="shared" si="364"/>
-        <v>0.507367575799965</v>
+        <v>0.688399894058278</v>
       </c>
       <c r="N198" s="1">
         <f ca="1" t="shared" si="365"/>
-        <v>3.570100382685</v>
+        <v>3.57052040635469</v>
       </c>
       <c r="O198" s="1">
         <f ca="1" t="shared" si="364"/>
-        <v>0.404995634493024</v>
+        <v>0.713138182467403</v>
       </c>
       <c r="P198" s="1">
         <f ca="1" t="shared" si="365"/>
-        <v>3.82443193198896</v>
+        <v>3.82525097998784</v>
       </c>
     </row>
     <row r="199" ht="16.5" spans="1:16">
@@ -17826,27 +17801,27 @@
       </c>
       <c r="K199" s="1">
         <f ca="1" t="shared" ref="K199:O199" si="366">RAND()</f>
-        <v>0.292763783742044</v>
+        <v>0.344633542569147</v>
       </c>
       <c r="L199" s="1">
         <f ca="1" t="shared" ref="L199:P199" si="367">J199+$R$1*K199/MAX(1,($A199*($A199-1)))++$R$1/$A199</f>
-        <v>3.2985858121619</v>
+        <v>3.29865230162356</v>
       </c>
       <c r="M199" s="1">
         <f ca="1" t="shared" si="366"/>
-        <v>0.244123496341496</v>
+        <v>0.175739212345279</v>
       </c>
       <c r="N199" s="1">
         <f ca="1" t="shared" si="367"/>
-        <v>3.55142399538543</v>
+        <v>3.55140282617407</v>
       </c>
       <c r="O199" s="1">
         <f ca="1" t="shared" si="366"/>
-        <v>0.755671241889692</v>
+        <v>0.949796879216076</v>
       </c>
       <c r="P199" s="1">
         <f ca="1" t="shared" si="367"/>
-        <v>3.8049179081705</v>
+        <v>3.80514557969816</v>
       </c>
     </row>
     <row r="200" ht="16.5" spans="1:16">
@@ -17886,27 +17861,27 @@
       </c>
       <c r="K200" s="1">
         <f ca="1" t="shared" ref="K200:O200" si="368">RAND()</f>
-        <v>0.188521185626939</v>
+        <v>0.277975584655842</v>
       </c>
       <c r="L200" s="1">
         <f ca="1" t="shared" ref="L200:P200" si="369">J200+$R$1*K200/MAX(1,($A200*($A200-1)))++$R$1/$A200</f>
-        <v>3.2817985396498</v>
+        <v>3.28191205469856</v>
       </c>
       <c r="M200" s="1">
         <f ca="1" t="shared" si="368"/>
-        <v>0.656127820359607</v>
+        <v>0.191414372757536</v>
       </c>
       <c r="N200" s="1">
         <f ca="1" t="shared" si="369"/>
-        <v>3.53388742831073</v>
+        <v>3.53341123541624</v>
       </c>
       <c r="O200" s="1">
         <f ca="1" t="shared" si="368"/>
-        <v>0.793988178268241</v>
+        <v>0.585528237565001</v>
       </c>
       <c r="P200" s="1">
         <f ca="1" t="shared" si="369"/>
-        <v>3.78615125778419</v>
+        <v>3.78541053524564</v>
       </c>
     </row>
     <row r="201" ht="16.5" spans="1:16">
@@ -17946,27 +17921,27 @@
       </c>
       <c r="K201" s="1">
         <f ca="1" t="shared" ref="K201:O201" si="370">RAND()</f>
-        <v>0.387357903981592</v>
+        <v>0.100801728533406</v>
       </c>
       <c r="L201" s="1">
         <f ca="1" t="shared" ref="L201:P201" si="371">J201+$R$1*K201/MAX(1,($A201*($A201-1)))++$R$1/$A201</f>
-        <v>3.26556200741706</v>
+        <v>3.26520201222177</v>
       </c>
       <c r="M201" s="1">
         <f ca="1" t="shared" si="370"/>
-        <v>0.0849284883389689</v>
+        <v>0.118361287455495</v>
       </c>
       <c r="N201" s="1">
         <f ca="1" t="shared" si="371"/>
-        <v>3.51566870149789</v>
+        <v>3.51535070730652</v>
       </c>
       <c r="O201" s="1">
         <f ca="1" t="shared" si="370"/>
-        <v>0.940113604298282</v>
+        <v>0.276283354312706</v>
       </c>
       <c r="P201" s="1">
         <f ca="1" t="shared" si="371"/>
-        <v>3.76684974873947</v>
+        <v>3.76569779694761</v>
       </c>
     </row>
     <row r="202" ht="16.5" spans="1:16">
@@ -18006,27 +17981,27 @@
       </c>
       <c r="K202" s="1">
         <f ca="1" t="shared" ref="K202:O202" si="372">RAND()</f>
-        <v>0.505116354729027</v>
+        <v>0.232997812012145</v>
       </c>
       <c r="L202" s="1">
         <f ca="1" t="shared" ref="L202:P202" si="373">J202+$R$1*K202/MAX(1,($A202*($A202-1)))++$R$1/$A202</f>
-        <v>3.24938447307802</v>
+        <v>3.24904601717912</v>
       </c>
       <c r="M202" s="1">
         <f ca="1" t="shared" si="372"/>
-        <v>0.868459525434303</v>
+        <v>0.579740712361303</v>
       </c>
       <c r="N202" s="1">
         <f ca="1" t="shared" si="373"/>
-        <v>3.49922086552259</v>
+        <v>3.49852330662235</v>
       </c>
       <c r="O202" s="1">
         <f ca="1" t="shared" si="372"/>
-        <v>0.340845414983368</v>
+        <v>0.105431639480181</v>
       </c>
       <c r="P202" s="1">
         <f ca="1" t="shared" si="373"/>
-        <v>3.74840102151138</v>
+        <v>3.74741065940778</v>
       </c>
     </row>
     <row r="203" ht="16.5" spans="1:16">
@@ -18066,27 +18041,27 @@
       </c>
       <c r="K203" s="1">
         <f ca="1" t="shared" ref="K203:O203" si="374">RAND()</f>
-        <v>0.0398087434260455</v>
+        <v>0.171318824267704</v>
       </c>
       <c r="L203" s="1">
         <f ca="1" t="shared" ref="L203:P203" si="375">J203+$R$1*K203/MAX(1,($A203*($A203-1)))++$R$1/$A203</f>
-        <v>3.23264840247208</v>
+        <v>3.23281035272187</v>
       </c>
       <c r="M203" s="1">
         <f ca="1" t="shared" si="374"/>
-        <v>0.00989804628517255</v>
+        <v>0.578805010793843</v>
       </c>
       <c r="N203" s="1">
         <f ca="1" t="shared" si="375"/>
-        <v>3.48018534405905</v>
+        <v>3.48104788413756</v>
       </c>
       <c r="O203" s="1">
         <f ca="1" t="shared" si="374"/>
-        <v>0.0780025265186011</v>
+        <v>0.726809293476737</v>
       </c>
       <c r="P203" s="1">
         <f ca="1" t="shared" si="375"/>
-        <v>3.72780615402718</v>
+        <v>3.72946767785889</v>
       </c>
     </row>
     <row r="204" ht="16.5" spans="1:16">
@@ -18126,27 +18101,27 @@
       </c>
       <c r="K204" s="1">
         <f ca="1" t="shared" ref="K204:O204" si="377">RAND()</f>
-        <v>0.314615194443491</v>
+        <v>0.653853902086833</v>
       </c>
       <c r="L204" s="1">
         <f ca="1" t="shared" ref="L204:P204" si="378">J204+$R$1*K204/MAX(1,($A204*($A204-1)))++$R$1/$A204</f>
-        <v>3.21698606934893</v>
+        <v>3.21739971455651</v>
       </c>
       <c r="M204" s="1">
         <f ca="1" t="shared" si="377"/>
-        <v>0.575742782885451</v>
+        <v>0.582729260272955</v>
       </c>
       <c r="N204" s="1">
         <f ca="1" t="shared" si="378"/>
-        <v>3.46399351067811</v>
+        <v>3.4644156747334</v>
       </c>
       <c r="O204" s="1">
         <f ca="1" t="shared" si="377"/>
-        <v>0.0401175322605962</v>
+        <v>0.224620272572832</v>
       </c>
       <c r="P204" s="1">
         <f ca="1" t="shared" si="378"/>
-        <v>3.71034784605861</v>
+        <v>3.71099498053325</v>
       </c>
     </row>
     <row r="205" ht="16.5" spans="1:16">
@@ -18186,27 +18161,27 @@
       </c>
       <c r="K205" s="1">
         <f ca="1" t="shared" ref="K205:O205" si="379">RAND()</f>
-        <v>0.0480899439671814</v>
+        <v>0.247815327109465</v>
       </c>
       <c r="L205" s="1">
         <f ca="1" t="shared" ref="L205:P205" si="380">J205+$R$1*K205/MAX(1,($A205*($A205-1)))++$R$1/$A205</f>
-        <v>3.2008211266589</v>
+        <v>3.20106227099284</v>
       </c>
       <c r="M205" s="1">
         <f ca="1" t="shared" si="379"/>
-        <v>0.0483338736272603</v>
+        <v>0.306059436782089</v>
       </c>
       <c r="N205" s="1">
         <f ca="1" t="shared" si="380"/>
-        <v>3.44597752320293</v>
+        <v>3.44652984009936</v>
       </c>
       <c r="O205" s="1">
         <f ca="1" t="shared" si="379"/>
-        <v>0.244165080383814</v>
+        <v>0.782403732467425</v>
       </c>
       <c r="P205" s="1">
         <f ca="1" t="shared" si="380"/>
-        <v>3.69137036233215</v>
+        <v>3.6925725375451</v>
       </c>
     </row>
     <row r="206" ht="16.5" spans="1:16">
@@ -18246,27 +18221,27 @@
       </c>
       <c r="K206" s="1">
         <f ca="1" t="shared" ref="K206:O206" si="381">RAND()</f>
-        <v>0.223360841430607</v>
+        <v>0.690704319188747</v>
       </c>
       <c r="L206" s="1">
         <f ca="1" t="shared" ref="L206:P206" si="382">J206+$R$1*K206/MAX(1,($A206*($A206-1)))++$R$1/$A206</f>
-        <v>3.18534595987737</v>
+        <v>3.18590471582878</v>
       </c>
       <c r="M206" s="1">
         <f ca="1" t="shared" si="381"/>
-        <v>0.483667130090045</v>
+        <v>0.736027452809205</v>
       </c>
       <c r="N206" s="1">
         <f ca="1" t="shared" si="382"/>
-        <v>3.42982667141502</v>
+        <v>3.43068714941655</v>
       </c>
       <c r="O206" s="1">
         <f ca="1" t="shared" si="381"/>
-        <v>0.389043908087543</v>
+        <v>0.907055852422636</v>
       </c>
       <c r="P206" s="1">
         <f ca="1" t="shared" si="382"/>
-        <v>3.67419425141034</v>
+        <v>3.67567406459161</v>
       </c>
     </row>
     <row r="207" ht="16.5" spans="1:16">
@@ -18306,27 +18281,27 @@
       </c>
       <c r="K207" s="1">
         <f ca="1" t="shared" ref="K207:O207" si="383">RAND()</f>
-        <v>0.321226194527486</v>
+        <v>0.781171031346008</v>
       </c>
       <c r="L207" s="1">
         <f ca="1" t="shared" ref="L207:P207" si="384">J207+$R$1*K207/MAX(1,($A207*($A207-1)))++$R$1/$A207</f>
-        <v>3.16992804427484</v>
+        <v>3.17047261547637</v>
       </c>
       <c r="M207" s="1">
         <f ca="1" t="shared" si="383"/>
-        <v>0.0231776621592708</v>
+        <v>0.818426481251116</v>
       </c>
       <c r="N207" s="1">
         <f ca="1" t="shared" si="384"/>
-        <v>3.41267393305315</v>
+        <v>3.41416007283045</v>
       </c>
       <c r="O207" s="1">
         <f ca="1" t="shared" si="383"/>
-        <v>0.0872613141984773</v>
+        <v>0.904346424110119</v>
       </c>
       <c r="P207" s="1">
         <f ca="1" t="shared" si="384"/>
-        <v>3.65549569638987</v>
+        <v>3.6579492587458</v>
       </c>
     </row>
     <row r="208" ht="16.5" spans="1:16">
@@ -18366,27 +18341,27 @@
       </c>
       <c r="K208" s="1">
         <f ca="1" t="shared" ref="K208:O208" si="385">RAND()</f>
-        <v>0.417983553680151</v>
+        <v>0.718883704097641</v>
       </c>
       <c r="L208" s="1">
         <f ca="1" t="shared" ref="L208:P208" si="386">J208+$R$1*K208/MAX(1,($A208*($A208-1)))++$R$1/$A208</f>
-        <v>3.15465736076366</v>
+        <v>3.15501018210227</v>
       </c>
       <c r="M208" s="1">
         <f ca="1" t="shared" si="385"/>
-        <v>0.0797788372468669</v>
+        <v>0.0886888838382278</v>
       </c>
       <c r="N208" s="1">
         <f ca="1" t="shared" si="386"/>
-        <v>3.39629679938901</v>
+        <v>3.39666006822843</v>
       </c>
       <c r="O208" s="1">
         <f ca="1" t="shared" si="385"/>
-        <v>0.332517689823276</v>
+        <v>0.105552525468074</v>
       </c>
       <c r="P208" s="1">
         <f ca="1" t="shared" si="386"/>
-        <v>3.63823258768438</v>
+        <v>3.63832972786619</v>
       </c>
     </row>
     <row r="209" ht="16.5" spans="1:16">
@@ -18426,27 +18401,27 @@
       </c>
       <c r="K209" s="1">
         <f ca="1" t="shared" ref="K209:O209" si="387">RAND()</f>
-        <v>0.595244876883545</v>
+        <v>0.371034769757149</v>
       </c>
       <c r="L209" s="1">
         <f ca="1" t="shared" ref="L209:P209" si="388">J209+$R$1*K209/MAX(1,($A209*($A209-1)))++$R$1/$A209</f>
-        <v>3.13962658500195</v>
+        <v>3.13936621466202</v>
       </c>
       <c r="M209" s="1">
         <f ca="1" t="shared" si="387"/>
-        <v>0.843642003091852</v>
+        <v>0.918825388835043</v>
       </c>
       <c r="N209" s="1">
         <f ca="1" t="shared" si="388"/>
-        <v>3.38099090356742</v>
+        <v>3.38081784206451</v>
       </c>
       <c r="O209" s="1">
         <f ca="1" t="shared" si="387"/>
-        <v>0.988179897076324</v>
+        <v>0.399586591244745</v>
       </c>
       <c r="P209" s="1">
         <f ca="1" t="shared" si="388"/>
-        <v>3.62252307085778</v>
+        <v>3.62166648870057</v>
       </c>
     </row>
     <row r="210" ht="16.5" spans="1:16">
@@ -18486,27 +18461,27 @@
       </c>
       <c r="K210" s="1">
         <f ca="1" t="shared" ref="K210:O210" si="389">RAND()</f>
-        <v>0.574676333278963</v>
+        <v>0.892632388664145</v>
       </c>
       <c r="L210" s="1">
         <f ca="1" t="shared" ref="L210:P210" si="390">J210+$R$1*K210/MAX(1,($A210*($A210-1)))++$R$1/$A210</f>
-        <v>3.12451080733953</v>
+        <v>3.12487650946432</v>
       </c>
       <c r="M210" s="1">
         <f ca="1" t="shared" si="389"/>
-        <v>0.940496255961959</v>
+        <v>0.163494734108787</v>
       </c>
       <c r="N210" s="1">
         <f ca="1" t="shared" si="390"/>
-        <v>3.36482698356326</v>
+        <v>3.36429900524794</v>
       </c>
       <c r="O210" s="1">
         <f ca="1" t="shared" si="389"/>
-        <v>0.645222155829818</v>
+        <v>0.529168351435076</v>
       </c>
       <c r="P210" s="1">
         <f ca="1" t="shared" si="390"/>
-        <v>3.60480354566741</v>
+        <v>3.60414208625576</v>
       </c>
     </row>
     <row r="211" ht="16.5" spans="1:16">
@@ -18546,27 +18521,27 @@
       </c>
       <c r="K211" s="1">
         <f ca="1" t="shared" ref="K211:O211" si="391">RAND()</f>
-        <v>0.806137531045831</v>
+        <v>0.912800908627571</v>
       </c>
       <c r="L211" s="1">
         <f ca="1" t="shared" ref="L211:P211" si="392">J211+$R$1*K211/MAX(1,($A211*($A211-1)))++$R$1/$A211</f>
-        <v>3.10982699650381</v>
+        <v>3.10994850866784</v>
       </c>
       <c r="M211" s="1">
         <f ca="1" t="shared" si="391"/>
-        <v>0.704501837038735</v>
+        <v>0.00758491226753999</v>
       </c>
       <c r="N211" s="1">
         <f ca="1" t="shared" si="392"/>
-        <v>3.34872481131019</v>
+        <v>3.34805238758362</v>
       </c>
       <c r="O211" s="1">
         <f ca="1" t="shared" si="391"/>
-        <v>0.623696852946489</v>
+        <v>0.814736295150393</v>
       </c>
       <c r="P211" s="1">
         <f ca="1" t="shared" si="392"/>
-        <v>3.58753057213606</v>
+        <v>3.58707578277062</v>
       </c>
     </row>
     <row r="212" ht="16.5" spans="1:16">
@@ -18606,27 +18581,27 @@
       </c>
       <c r="K212" s="1">
         <f ca="1" t="shared" ref="K212:O212" si="393">RAND()</f>
-        <v>0.565517800606676</v>
+        <v>0.898583294834618</v>
       </c>
       <c r="L212" s="1">
         <f ca="1" t="shared" ref="L212:P212" si="394">J212+$R$1*K212/MAX(1,($A212*($A212-1)))++$R$1/$A212</f>
-        <v>3.09474781968021</v>
+        <v>3.09512365526386</v>
       </c>
       <c r="M212" s="1">
         <f ca="1" t="shared" si="393"/>
-        <v>0.384142638715648</v>
+        <v>0.145453587013513</v>
       </c>
       <c r="N212" s="1">
         <f ca="1" t="shared" si="394"/>
-        <v>3.33214811604527</v>
+        <v>3.33225461169245</v>
       </c>
       <c r="O212" s="1">
         <f ca="1" t="shared" si="393"/>
-        <v>0.216245031679958</v>
+        <v>0.794221387407795</v>
       </c>
       <c r="P212" s="1">
         <f ca="1" t="shared" si="394"/>
-        <v>3.56935895449222</v>
+        <v>3.57011764643338</v>
       </c>
     </row>
     <row r="213" ht="16.5" spans="1:16">
@@ -18666,27 +18641,27 @@
       </c>
       <c r="K213" s="1">
         <f ca="1" t="shared" ref="K213:O213" si="395">RAND()</f>
-        <v>0.401099626917105</v>
+        <v>0.0571930102515199</v>
       </c>
       <c r="L213" s="1">
         <f ca="1" t="shared" ref="L213:P213" si="396">J213+$R$1*K213/MAX(1,($A213*($A213-1)))++$R$1/$A213</f>
-        <v>3.07989928868251</v>
+        <v>3.07951488085739</v>
       </c>
       <c r="M213" s="1">
         <f ca="1" t="shared" si="395"/>
-        <v>0.469700420635025</v>
+        <v>0.0670128242111621</v>
       </c>
       <c r="N213" s="1">
         <f ca="1" t="shared" si="396"/>
-        <v>3.3162733614052</v>
+        <v>3.31543884225439</v>
       </c>
       <c r="O213" s="1">
         <f ca="1" t="shared" si="395"/>
-        <v>0.394272820647324</v>
+        <v>0.811742939702002</v>
       </c>
       <c r="P213" s="1">
         <f ca="1" t="shared" si="396"/>
-        <v>3.55256312356724</v>
+        <v>3.55219523917349</v>
       </c>
     </row>
     <row r="214" ht="16.5" spans="1:16">
@@ -18726,27 +18701,27 @@
       </c>
       <c r="K214" s="1">
         <f ca="1" t="shared" ref="K214:O214" si="397">RAND()</f>
-        <v>0.627788305195731</v>
+        <v>0.542354921677436</v>
       </c>
       <c r="L214" s="1">
         <f ca="1" t="shared" ref="L214:P214" si="398">J214+$R$1*K214/MAX(1,($A214*($A214-1)))++$R$1/$A214</f>
-        <v>3.06562559605058</v>
+        <v>3.06553099800876</v>
       </c>
       <c r="M214" s="1">
         <f ca="1" t="shared" si="397"/>
-        <v>0.106268319132225</v>
+        <v>0.857062211978508</v>
       </c>
       <c r="N214" s="1">
         <f ca="1" t="shared" si="398"/>
-        <v>3.30048504808257</v>
+        <v>3.30122178352119</v>
       </c>
       <c r="O214" s="1">
         <f ca="1" t="shared" si="397"/>
-        <v>0.558274206424185</v>
+        <v>0.766072332939956</v>
       </c>
       <c r="P214" s="1">
         <f ca="1" t="shared" si="398"/>
-        <v>3.53584499383332</v>
+        <v>3.53681181843674</v>
       </c>
     </row>
     <row r="215" ht="16.5" spans="1:16">
@@ -18786,27 +18761,27 @@
       </c>
       <c r="K215" s="1">
         <f ca="1" t="shared" ref="K215:O215" si="399">RAND()</f>
-        <v>0.722563724178273</v>
+        <v>0.492261785392366</v>
       </c>
       <c r="L215" s="1">
         <f ca="1" t="shared" ref="L215:P215" si="400">J215+$R$1*K215/MAX(1,($A215*($A215-1)))++$R$1/$A215</f>
-        <v>3.05133886591657</v>
+        <v>3.05108624214096</v>
       </c>
       <c r="M215" s="1">
         <f ca="1" t="shared" si="399"/>
-        <v>0.340141962259289</v>
+        <v>0.970818915432733</v>
       </c>
       <c r="N215" s="1">
         <f ca="1" t="shared" si="400"/>
-        <v>3.28535683568781</v>
+        <v>3.28579601673996</v>
       </c>
       <c r="O215" s="1">
         <f ca="1" t="shared" si="399"/>
-        <v>0.802877289192145</v>
+        <v>0.409078279445272</v>
       </c>
       <c r="P215" s="1">
         <f ca="1" t="shared" si="400"/>
-        <v>3.51988239104869</v>
+        <v>3.51988960442748</v>
       </c>
     </row>
     <row r="216" ht="16.5" spans="1:16">
@@ -18846,27 +18821,27 @@
       </c>
       <c r="K216" s="1">
         <f ca="1" t="shared" ref="K216:O216" si="401">RAND()</f>
-        <v>0.483659314246092</v>
+        <v>0.367514439062794</v>
       </c>
       <c r="L216" s="1">
         <f ca="1" t="shared" ref="L216:P216" si="402">J216+$R$1*K216/MAX(1,($A216*($A216-1)))++$R$1/$A216</f>
-        <v>3.03682205967642</v>
+        <v>3.03669584268535</v>
       </c>
       <c r="M216" s="1">
         <f ca="1" t="shared" si="401"/>
-        <v>0.431726378561407</v>
+        <v>0.487965131932788</v>
       </c>
       <c r="N216" s="1">
         <f ca="1" t="shared" si="402"/>
-        <v>3.26984936502152</v>
+        <v>3.26978426382416</v>
       </c>
       <c r="O216" s="1">
         <f ca="1" t="shared" si="401"/>
-        <v>0.138218637651738</v>
+        <v>0.601562045812954</v>
       </c>
       <c r="P216" s="1">
         <f ca="1" t="shared" si="402"/>
-        <v>3.50255770955277</v>
+        <v>3.50299613303283</v>
       </c>
     </row>
     <row r="217" ht="16.5" spans="1:16">
@@ -18906,27 +18881,27 @@
       </c>
       <c r="K217" s="1">
         <f ca="1" t="shared" ref="K217:O217" si="403">RAND()</f>
-        <v>0.436655300340377</v>
+        <v>0.775925862483005</v>
       </c>
       <c r="L217" s="1">
         <f ca="1" t="shared" ref="L217:P217" si="404">J217+$R$1*K217/MAX(1,($A217*($A217-1)))++$R$1/$A217</f>
-        <v>3.02264928434576</v>
+        <v>3.02301456272877</v>
       </c>
       <c r="M217" s="1">
         <f ca="1" t="shared" si="403"/>
-        <v>0.283676280042888</v>
+        <v>0.234662783946257</v>
       </c>
       <c r="N217" s="1">
         <f ca="1" t="shared" si="404"/>
-        <v>3.25443618817871</v>
+        <v>3.25474869578642</v>
       </c>
       <c r="O217" s="1">
         <f ca="1" t="shared" si="403"/>
-        <v>0.941366211085666</v>
+        <v>0.329124483869139</v>
       </c>
       <c r="P217" s="1">
         <f ca="1" t="shared" si="404"/>
-        <v>3.48693119917255</v>
+        <v>3.48658453179403</v>
       </c>
     </row>
     <row r="218" ht="16.5" spans="1:16">
@@ -18966,27 +18941,27 @@
       </c>
       <c r="K218" s="1">
         <f ca="1" t="shared" ref="K218:O218" si="405">RAND()</f>
-        <v>0.99570624911497</v>
+        <v>0.683632945345016</v>
       </c>
       <c r="L218" s="1">
         <f ca="1" t="shared" ref="L218:P218" si="406">J218+$R$1*K218/MAX(1,($A218*($A218-1)))++$R$1/$A218</f>
-        <v>3.00925467896518</v>
+        <v>3.00892177946892</v>
       </c>
       <c r="M218" s="1">
         <f ca="1" t="shared" si="405"/>
-        <v>0.778933249686283</v>
+        <v>0.0281423525044195</v>
       </c>
       <c r="N218" s="1">
         <f ca="1" t="shared" si="406"/>
-        <v>3.24050034082053</v>
+        <v>3.23936654644335</v>
       </c>
       <c r="O218" s="1">
         <f ca="1" t="shared" si="405"/>
-        <v>0.50656797696351</v>
+        <v>0.327893753491507</v>
       </c>
       <c r="P218" s="1">
         <f ca="1" t="shared" si="406"/>
-        <v>3.47145546112366</v>
+        <v>3.47013106870983</v>
       </c>
     </row>
     <row r="219" ht="16.5" spans="1:16">
@@ -19026,27 +19001,27 @@
       </c>
       <c r="K219" s="1">
         <f ca="1" t="shared" ref="K219:O219" si="407">RAND()</f>
-        <v>0.128701720260158</v>
+        <v>0.991128773632407</v>
       </c>
       <c r="L219" s="1">
         <f ca="1" t="shared" ref="L219:P219" si="408">J219+$R$1*K219/MAX(1,($A219*($A219-1)))++$R$1/$A219</f>
-        <v>2.99447078776504</v>
+        <v>2.9953823286408</v>
       </c>
       <c r="M219" s="1">
         <f ca="1" t="shared" si="407"/>
-        <v>0.55080417641477</v>
+        <v>0.337926069012739</v>
       </c>
       <c r="N219" s="1">
         <f ca="1" t="shared" si="408"/>
-        <v>3.22441075751139</v>
+        <v>3.22509729721668</v>
       </c>
       <c r="O219" s="1">
         <f ca="1" t="shared" si="407"/>
-        <v>0.04426660559145</v>
+        <v>0.313477886604755</v>
       </c>
       <c r="P219" s="1">
         <f ca="1" t="shared" si="408"/>
-        <v>3.45381534319353</v>
+        <v>3.45478642532581</v>
       </c>
     </row>
     <row r="220" ht="16.5" spans="1:16">
@@ -19086,27 +19061,27 @@
       </c>
       <c r="K220" s="1">
         <f ca="1" t="shared" ref="K220:O220" si="409">RAND()</f>
-        <v>0.116723934651961</v>
+        <v>0.378171025940171</v>
       </c>
       <c r="L220" s="1">
         <f ca="1" t="shared" ref="L220:P220" si="410">J220+$R$1*K220/MAX(1,($A220*($A220-1)))++$R$1/$A220</f>
-        <v>2.98072632476085</v>
+        <v>2.98100013722293</v>
       </c>
       <c r="M220" s="1">
         <f ca="1" t="shared" si="409"/>
-        <v>0.516977907028558</v>
+        <v>0.759466221885918</v>
       </c>
       <c r="N220" s="1">
         <f ca="1" t="shared" si="410"/>
-        <v>3.20957825587709</v>
+        <v>3.21010602535275</v>
       </c>
       <c r="O220" s="1">
         <f ca="1" t="shared" si="409"/>
-        <v>0.992589234886895</v>
+        <v>0.848712674343904</v>
       </c>
       <c r="P220" s="1">
         <f ca="1" t="shared" si="410"/>
-        <v>3.43892829277844</v>
+        <v>3.43930538092473</v>
       </c>
     </row>
     <row r="221" ht="16.5" spans="1:16">
@@ -19146,27 +19121,27 @@
       </c>
       <c r="K221" s="1">
         <f ca="1" t="shared" ref="K221:O221" si="411">RAND()</f>
-        <v>0.802961615649594</v>
+        <v>0.247665756419147</v>
       </c>
       <c r="L221" s="1">
         <f ca="1" t="shared" ref="L221:P221" si="412">J221+$R$1*K221/MAX(1,($A221*($A221-1)))++$R$1/$A221</f>
-        <v>2.967832048169</v>
+        <v>2.96725577600293</v>
       </c>
       <c r="M221" s="1">
         <f ca="1" t="shared" si="411"/>
-        <v>0.131765190615289</v>
+        <v>0.322005477431868</v>
       </c>
       <c r="N221" s="1">
         <f ca="1" t="shared" si="412"/>
-        <v>3.19524151806379</v>
+        <v>3.19486267251334</v>
       </c>
       <c r="O221" s="1">
         <f ca="1" t="shared" si="411"/>
-        <v>0.609721157666565</v>
+        <v>0.765286421980486</v>
       </c>
       <c r="P221" s="1">
         <f ca="1" t="shared" si="412"/>
-        <v>3.42314699871724</v>
+        <v>3.42292959491058</v>
       </c>
     </row>
     <row r="222" ht="16.5" spans="1:16">
@@ -19206,27 +19181,27 @@
       </c>
       <c r="K222" s="1">
         <f ca="1" t="shared" ref="K222:O222" si="413">RAND()</f>
-        <v>0.116609225620897</v>
+        <v>0.197325533473771</v>
       </c>
       <c r="L222" s="1">
         <f ca="1" t="shared" ref="L222:P222" si="414">J222+$R$1*K222/MAX(1,($A222*($A222-1)))++$R$1/$A222</f>
-        <v>2.95363699015387</v>
+        <v>2.95371999746347</v>
       </c>
       <c r="M222" s="1">
         <f ca="1" t="shared" si="413"/>
-        <v>0.118307667483742</v>
+        <v>0.125753323524544</v>
       </c>
       <c r="N222" s="1">
         <f ca="1" t="shared" si="414"/>
-        <v>3.18000299968439</v>
+        <v>3.18009366398293</v>
       </c>
       <c r="O222" s="1">
         <f ca="1" t="shared" si="413"/>
-        <v>0.73367534720632</v>
+        <v>0.578301991752992</v>
       </c>
       <c r="P222" s="1">
         <f ca="1" t="shared" si="414"/>
-        <v>3.40700184311015</v>
+        <v>3.40693272403204</v>
       </c>
     </row>
     <row r="223" ht="16.5" spans="1:16">
@@ -19266,27 +19241,27 @@
       </c>
       <c r="K223" s="1">
         <f ca="1" t="shared" ref="K223:O223" si="415">RAND()</f>
-        <v>0.368916073921523</v>
+        <v>0.735767297831978</v>
       </c>
       <c r="L223" s="1">
         <f ca="1" t="shared" ref="L223:P223" si="416">J223+$R$1*K223/MAX(1,($A223*($A223-1)))++$R$1/$A223</f>
-        <v>2.94053332117924</v>
+        <v>2.94090718610924</v>
       </c>
       <c r="M223" s="1">
         <f ca="1" t="shared" si="415"/>
-        <v>0.0986429273084055</v>
+        <v>0.0235699171793335</v>
       </c>
       <c r="N223" s="1">
         <f ca="1" t="shared" si="416"/>
-        <v>3.16585907525298</v>
+        <v>3.16615643187702</v>
       </c>
       <c r="O223" s="1">
         <f ca="1" t="shared" si="415"/>
-        <v>0.701258763040147</v>
+        <v>0.0134274478925576</v>
       </c>
       <c r="P223" s="1">
         <f ca="1" t="shared" si="416"/>
-        <v>3.39179896637344</v>
+        <v>3.39139534126503</v>
       </c>
     </row>
     <row r="224" ht="16.5" spans="1:16">
@@ -19326,27 +19301,27 @@
       </c>
       <c r="K224" s="1">
         <f ca="1" t="shared" ref="K224:O224" si="417">RAND()</f>
-        <v>0.626868350737818</v>
+        <v>0.239221838006869</v>
       </c>
       <c r="L224" s="1">
         <f ca="1" t="shared" ref="L224:P224" si="418">J224+$R$1*K224/MAX(1,($A224*($A224-1)))++$R$1/$A224</f>
-        <v>2.9275510729515</v>
+        <v>2.92715955827375</v>
       </c>
       <c r="M224" s="1">
         <f ca="1" t="shared" si="417"/>
-        <v>0.871790709586377</v>
+        <v>0.474254376690265</v>
       </c>
       <c r="N224" s="1">
         <f ca="1" t="shared" si="418"/>
-        <v>3.15264680953857</v>
+        <v>3.15185379167646</v>
       </c>
       <c r="O224" s="1">
         <f ca="1" t="shared" si="417"/>
-        <v>0.415795497915863</v>
+        <v>0.498661422699038</v>
       </c>
       <c r="P224" s="1">
         <f ca="1" t="shared" si="418"/>
-        <v>3.37728200072541</v>
+        <v>3.37657267567304</v>
       </c>
     </row>
     <row r="225" ht="16.5" spans="1:16">
@@ -19386,27 +19361,27 @@
       </c>
       <c r="K225" s="1">
         <f ca="1" t="shared" ref="K225:O225" si="419">RAND()</f>
-        <v>0.083936365255721</v>
+        <v>0.0185309207064379</v>
       </c>
       <c r="L225" s="1">
         <f ca="1" t="shared" ref="L225:P225" si="420">J225+$R$1*K225/MAX(1,($A225*($A225-1)))++$R$1/$A225</f>
-        <v>2.91388126237714</v>
+        <v>2.91381579408303</v>
       </c>
       <c r="M225" s="1">
         <f ca="1" t="shared" si="419"/>
-        <v>0.0309660424847507</v>
+        <v>0.382453886763214</v>
       </c>
       <c r="N225" s="1">
         <f ca="1" t="shared" si="420"/>
-        <v>3.13712654388987</v>
+        <v>3.13741290119262</v>
       </c>
       <c r="O225" s="1">
         <f ca="1" t="shared" si="419"/>
-        <v>0.134722973803799</v>
+        <v>0.34624931808414</v>
       </c>
       <c r="P225" s="1">
         <f ca="1" t="shared" si="420"/>
-        <v>3.3604756820363</v>
+        <v>3.36097376894374</v>
       </c>
     </row>
     <row r="226" ht="16.5" spans="1:16">
@@ -19446,27 +19421,27 @@
       </c>
       <c r="K226" s="1">
         <f ca="1" t="shared" ref="K226:O226" si="421">RAND()</f>
-        <v>0.13830882413438</v>
+        <v>0.816218421526823</v>
       </c>
       <c r="L226" s="1">
         <f ca="1" t="shared" ref="L226:P226" si="422">J226+$R$1*K226/MAX(1,($A226*($A226-1)))++$R$1/$A226</f>
-        <v>2.9009308619287</v>
+        <v>2.9016033912912</v>
       </c>
       <c r="M226" s="1">
         <f ca="1" t="shared" si="421"/>
-        <v>0.717662257155728</v>
+        <v>0.218301989234996</v>
       </c>
       <c r="N226" s="1">
         <f ca="1" t="shared" si="422"/>
-        <v>3.12386505067588</v>
+        <v>3.12404218294719</v>
       </c>
       <c r="O226" s="1">
         <f ca="1" t="shared" si="421"/>
-        <v>0.0455591178898793</v>
+        <v>0.90240935496227</v>
       </c>
       <c r="P226" s="1">
         <f ca="1" t="shared" si="422"/>
-        <v>3.34613247043569</v>
+        <v>3.34715965254536</v>
       </c>
     </row>
     <row r="227" ht="16.5" spans="1:16">
@@ -19506,27 +19481,27 @@
       </c>
       <c r="K227" s="1">
         <f ca="1" t="shared" ref="K227:O227" si="423">RAND()</f>
-        <v>0.52092422575476</v>
+        <v>0.395698767693285</v>
       </c>
       <c r="L227" s="1">
         <f ca="1" t="shared" ref="L227:P227" si="424">J227+$R$1*K227/MAX(1,($A227*($A227-1)))++$R$1/$A227</f>
-        <v>2.88841782126426</v>
+        <v>2.88829468905378</v>
       </c>
       <c r="M227" s="1">
         <f ca="1" t="shared" si="423"/>
-        <v>0.27620904907146</v>
+        <v>0.93580449360204</v>
       </c>
       <c r="N227" s="1">
         <f ca="1" t="shared" si="424"/>
-        <v>3.10992835130268</v>
+        <v>3.11045378885083</v>
       </c>
       <c r="O227" s="1">
         <f ca="1" t="shared" si="423"/>
-        <v>0.682612213992722</v>
+        <v>0.641045243296221</v>
       </c>
       <c r="P227" s="1">
         <f ca="1" t="shared" si="424"/>
-        <v>3.33183849113945</v>
+        <v>3.33232305654336</v>
       </c>
     </row>
     <row r="228" ht="16.5" spans="1:16">
@@ -19566,27 +19541,27 @@
       </c>
       <c r="K228" s="1">
         <f ca="1" t="shared" ref="K228:O228" si="425">RAND()</f>
-        <v>0.744920906406962</v>
+        <v>0.584443795996144</v>
       </c>
       <c r="L228" s="1">
         <f ca="1" t="shared" ref="L228:P228" si="426">J228+$R$1*K228/MAX(1,($A228*($A228-1)))++$R$1/$A228</f>
-        <v>2.87585758928152</v>
+        <v>2.87570118494016</v>
       </c>
       <c r="M228" s="1">
         <f ca="1" t="shared" si="425"/>
-        <v>0.413272500771001</v>
+        <v>0.150993388479141</v>
       </c>
       <c r="N228" s="1">
         <f ca="1" t="shared" si="426"/>
-        <v>3.09652469046741</v>
+        <v>3.09611266342879</v>
       </c>
       <c r="O228" s="1">
         <f ca="1" t="shared" si="425"/>
-        <v>0.740183207785097</v>
+        <v>0.488621975098301</v>
       </c>
       <c r="P228" s="1">
         <f ca="1" t="shared" si="426"/>
-        <v>3.31751040565179</v>
+        <v>3.31685320178509</v>
       </c>
     </row>
     <row r="229" ht="16.5" spans="1:16">
@@ -19626,27 +19601,27 @@
       </c>
       <c r="K229" s="1">
         <f ca="1" t="shared" ref="K229:O229" si="427">RAND()</f>
-        <v>0.724405027737153</v>
+        <v>0.273199312953636</v>
       </c>
       <c r="L229" s="1">
         <f ca="1" t="shared" ref="L229:P229" si="428">J229+$R$1*K229/MAX(1,($A229*($A229-1)))++$R$1/$A229</f>
-        <v>2.86316987888142</v>
+        <v>2.86273398186969</v>
       </c>
       <c r="M229" s="1">
         <f ca="1" t="shared" si="427"/>
-        <v>0.970296993650595</v>
+        <v>0.522357765965931</v>
       </c>
       <c r="N229" s="1">
         <f ca="1" t="shared" si="428"/>
-        <v>3.08340550083216</v>
+        <v>3.08253686246901</v>
       </c>
       <c r="O229" s="1">
         <f ca="1" t="shared" si="427"/>
-        <v>0.338094217053288</v>
+        <v>0.0563994547275739</v>
       </c>
       <c r="P229" s="1">
         <f ca="1" t="shared" si="428"/>
-        <v>3.30303036965612</v>
+        <v>3.30188959399263</v>
       </c>
     </row>
     <row r="230" ht="16.5" spans="1:16">
@@ -19686,27 +19661,27 @@
       </c>
       <c r="K230" s="1">
         <f ca="1" t="shared" ref="K230:O230" si="429">RAND()</f>
-        <v>0.951796634428056</v>
+        <v>0.322958512464188</v>
       </c>
       <c r="L230" s="1">
         <f ca="1" t="shared" ref="L230:P230" si="430">J230+$R$1*K230/MAX(1,($A230*($A230-1)))++$R$1/$A230</f>
-        <v>2.85083103178812</v>
+        <v>2.85022883485833</v>
       </c>
       <c r="M230" s="1">
         <f ca="1" t="shared" si="429"/>
-        <v>0.605394880597828</v>
+        <v>0.819551123448149</v>
       </c>
       <c r="N230" s="1">
         <f ca="1" t="shared" si="430"/>
-        <v>3.06975139002052</v>
+        <v>3.06935427644594</v>
       </c>
       <c r="O230" s="1">
         <f ca="1" t="shared" si="429"/>
-        <v>0.324161797710275</v>
+        <v>0.503763201596064</v>
       </c>
       <c r="P230" s="1">
         <f ca="1" t="shared" si="430"/>
-        <v>3.2884024298176</v>
+        <v>3.28817730870059</v>
       </c>
     </row>
     <row r="231" ht="16.5" spans="1:16">
@@ -19746,27 +19721,27 @@
       </c>
       <c r="K231" s="1">
         <f ca="1" t="shared" ref="K231:O231" si="431">RAND()</f>
-        <v>0.468818363077248</v>
+        <v>0.598273813304875</v>
       </c>
       <c r="L231" s="1">
         <f ca="1" t="shared" ref="L231:P231" si="432">J231+$R$1*K231/MAX(1,($A231*($A231-1)))++$R$1/$A231</f>
-        <v>2.83792369314892</v>
+        <v>2.83804658611477</v>
       </c>
       <c r="M231" s="1">
         <f ca="1" t="shared" si="431"/>
-        <v>0.196599805776983</v>
+        <v>0.221719476720498</v>
       </c>
       <c r="N231" s="1">
         <f ca="1" t="shared" si="432"/>
-        <v>3.05550163106973</v>
+        <v>3.05564837031519</v>
       </c>
       <c r="O231" s="1">
         <f ca="1" t="shared" si="431"/>
-        <v>0.311140146141406</v>
+        <v>0.31514028760511</v>
       </c>
       <c r="P231" s="1">
         <f ca="1" t="shared" si="432"/>
-        <v>3.2731883029381</v>
+        <v>3.27333883954588</v>
       </c>
     </row>
     <row r="232" ht="16.5" spans="1:16">
@@ -19806,27 +19781,27 @@
       </c>
       <c r="K232" s="1">
         <f ca="1" t="shared" ref="K232:O232" si="433">RAND()</f>
-        <v>0.537062902450854</v>
+        <v>0.115885907731581</v>
       </c>
       <c r="L232" s="1">
         <f ca="1" t="shared" ref="L232:P232" si="434">J232+$R$1*K232/MAX(1,($A232*($A232-1)))++$R$1/$A232</f>
-        <v>2.82565129202188</v>
+        <v>2.8252549274494</v>
       </c>
       <c r="M232" s="1">
         <f ca="1" t="shared" si="433"/>
-        <v>0.209740330932603</v>
+        <v>0.466465440367584</v>
       </c>
       <c r="N232" s="1">
         <f ca="1" t="shared" si="434"/>
-        <v>3.04229889255918</v>
+        <v>3.0421441288802</v>
       </c>
       <c r="O232" s="1">
         <f ca="1" t="shared" si="433"/>
-        <v>0.00760020327925304</v>
+        <v>0.310460385995228</v>
       </c>
       <c r="P232" s="1">
         <f ca="1" t="shared" si="434"/>
-        <v>3.25875626146872</v>
+        <v>3.25888651584236</v>
       </c>
     </row>
     <row r="233" ht="16.5" spans="1:16">
@@ -19866,27 +19841,27 @@
       </c>
       <c r="K233" s="1">
         <f ca="1" t="shared" ref="K233:O233" si="435">RAND()</f>
-        <v>0.745774226480979</v>
+        <v>0.566119110063336</v>
       </c>
       <c r="L233" s="1">
         <f ca="1" t="shared" ref="L233:P233" si="436">J233+$R$1*K233/MAX(1,($A233*($A233-1)))++$R$1/$A233</f>
-        <v>2.81361562754374</v>
+        <v>2.81344801379876</v>
       </c>
       <c r="M233" s="1">
         <f ca="1" t="shared" si="435"/>
-        <v>0.223317680607569</v>
+        <v>0.611289757390858</v>
       </c>
       <c r="N233" s="1">
         <f ca="1" t="shared" si="436"/>
-        <v>3.02934121875195</v>
+        <v>3.02953557328282</v>
       </c>
       <c r="O233" s="1">
         <f ca="1" t="shared" si="435"/>
-        <v>0.0573093675636571</v>
+        <v>0.783702098322645</v>
       </c>
       <c r="P233" s="1">
         <f ca="1" t="shared" si="436"/>
-        <v>3.24491192834253</v>
+        <v>3.24578398918288</v>
       </c>
     </row>
     <row r="234" ht="16.5" spans="1:16">
@@ -19926,27 +19901,27 @@
       </c>
       <c r="K234" s="1">
         <f ca="1" t="shared" ref="K234:O234" si="437">RAND()</f>
-        <v>0.26437015384098</v>
+        <v>0.817515135298605</v>
       </c>
       <c r="L234" s="1">
         <f ca="1" t="shared" ref="L234:P234" si="438">J234+$R$1*K234/MAX(1,($A234*($A234-1)))++$R$1/$A234</f>
-        <v>2.80104370481893</v>
+        <v>2.80155534550771</v>
       </c>
       <c r="M234" s="1">
         <f ca="1" t="shared" si="437"/>
-        <v>0.0477915304899326</v>
+        <v>0.248251852976627</v>
       </c>
       <c r="N234" s="1">
         <f ca="1" t="shared" si="438"/>
-        <v>3.01568018507134</v>
+        <v>3.01637724488333</v>
       </c>
       <c r="O234" s="1">
         <f ca="1" t="shared" si="437"/>
-        <v>0.431567909092828</v>
+        <v>0.904334152816121</v>
       </c>
       <c r="P234" s="1">
         <f ca="1" t="shared" si="438"/>
-        <v>3.23067164569467</v>
+        <v>3.23180599853956</v>
       </c>
     </row>
     <row r="235" ht="16.5" spans="1:16">
@@ -19986,27 +19961,27 @@
       </c>
       <c r="K235" s="1">
         <f ca="1" t="shared" ref="K235:O235" si="439">RAND()</f>
-        <v>0.541263632351251</v>
+        <v>0.31685404099189</v>
       </c>
       <c r="L235" s="1">
         <f ca="1" t="shared" ref="L235:P235" si="440">J235+$R$1*K235/MAX(1,($A235*($A235-1)))++$R$1/$A235</f>
-        <v>2.78927888158207</v>
+        <v>2.78907308429716</v>
       </c>
       <c r="M235" s="1">
         <f ca="1" t="shared" si="439"/>
-        <v>0.519396653645257</v>
+        <v>0.822621294279857</v>
       </c>
       <c r="N235" s="1">
         <f ca="1" t="shared" si="440"/>
-        <v>3.00343041367338</v>
+        <v>3.00350269188151</v>
       </c>
       <c r="O235" s="1">
         <f ca="1" t="shared" si="439"/>
-        <v>0.896540912198896</v>
+        <v>0.79544371536828</v>
       </c>
       <c r="P235" s="1">
         <f ca="1" t="shared" si="440"/>
-        <v>3.21792781005667</v>
+        <v>3.21790737596809</v>
       </c>
     </row>
     <row r="236" ht="16.5" spans="1:16">
@@ -20046,27 +20021,27 @@
       </c>
       <c r="K236" s="1">
         <f ca="1" t="shared" ref="K236:O236" si="441">RAND()</f>
-        <v>0.287700473972448</v>
+        <v>0.0525072399554281</v>
       </c>
       <c r="L236" s="1">
         <f ca="1" t="shared" ref="L236:P236" si="442">J236+$R$1*K236/MAX(1,($A236*($A236-1)))++$R$1/$A236</f>
-        <v>2.77713011499725</v>
+        <v>2.77691626408433</v>
       </c>
       <c r="M236" s="1">
         <f ca="1" t="shared" si="441"/>
-        <v>0.368988635409665</v>
+        <v>0.727768295572741</v>
       </c>
       <c r="N236" s="1">
         <f ca="1" t="shared" si="442"/>
-        <v>2.99023157765901</v>
+        <v>2.99034394938673</v>
       </c>
       <c r="O236" s="1">
         <f ca="1" t="shared" si="441"/>
-        <v>0.240060079265689</v>
+        <v>0.964320908786596</v>
       </c>
       <c r="P236" s="1">
         <f ca="1" t="shared" si="442"/>
-        <v>3.20321581122808</v>
+        <v>3.20398672162603</v>
       </c>
     </row>
     <row r="237" ht="16.5" spans="1:16">
@@ -20106,27 +20081,27 @@
       </c>
       <c r="K237" s="1">
         <f ca="1" t="shared" ref="K237:O237" si="443">RAND()</f>
-        <v>0.653899766801256</v>
+        <v>0.923387803859467</v>
       </c>
       <c r="L237" s="1">
         <f ca="1" t="shared" ref="L237:P237" si="444">J237+$R$1*K237/MAX(1,($A237*($A237-1)))++$R$1/$A237</f>
-        <v>2.76564541991237</v>
+        <v>2.76588837703197</v>
       </c>
       <c r="M237" s="1">
         <f ca="1" t="shared" si="443"/>
-        <v>0.148883773202615</v>
+        <v>0.96171223360049</v>
       </c>
       <c r="N237" s="1">
         <f ca="1" t="shared" si="444"/>
-        <v>2.97764405295709</v>
+        <v>2.97861981611743</v>
       </c>
       <c r="O237" s="1">
         <f ca="1" t="shared" si="443"/>
-        <v>0.0395198154911678</v>
+        <v>0.0698316784699697</v>
       </c>
       <c r="P237" s="1">
         <f ca="1" t="shared" si="444"/>
-        <v>3.18954408885277</v>
+        <v>3.19054717969341</v>
       </c>
     </row>
     <row r="238" ht="16.5" spans="1:16">
@@ -20166,27 +20141,27 @@
       </c>
       <c r="K238" s="1">
         <f ca="1" t="shared" ref="K238:O238" si="445">RAND()</f>
-        <v>0.862125728512049</v>
+        <v>0.270059221079768</v>
       </c>
       <c r="L238" s="1">
         <f ca="1" t="shared" ref="L238:P238" si="446">J238+$R$1*K238/MAX(1,($A238*($A238-1)))++$R$1/$A238</f>
-        <v>2.75411403644471</v>
+        <v>2.75358476294525</v>
       </c>
       <c r="M238" s="1">
         <f ca="1" t="shared" si="445"/>
-        <v>0.0819293037241267</v>
+        <v>0.441166873553058</v>
       </c>
       <c r="N238" s="1">
         <f ca="1" t="shared" si="446"/>
-        <v>2.96515774067818</v>
+        <v>2.96494960496195</v>
       </c>
       <c r="O238" s="1">
         <f ca="1" t="shared" si="445"/>
-        <v>0.799692037346412</v>
+        <v>0.353815717188228</v>
       </c>
       <c r="P238" s="1">
         <f ca="1" t="shared" si="446"/>
-        <v>3.17684308362796</v>
+        <v>3.1762363600549</v>
       </c>
     </row>
     <row r="239" ht="16.5" spans="1:16">
@@ -20226,27 +20201,27 @@
       </c>
       <c r="K239" s="1">
         <f ca="1" t="shared" ref="K239:O239" si="447">RAND()</f>
-        <v>0.9811513736114</v>
+        <v>0.844978717749476</v>
       </c>
       <c r="L239" s="1">
         <f ca="1" t="shared" ref="L239:P239" si="448">J239+$R$1*K239/MAX(1,($A239*($A239-1)))++$R$1/$A239</f>
-        <v>2.74259932575755</v>
+        <v>2.74247861815919</v>
       </c>
       <c r="M239" s="1">
         <f ca="1" t="shared" si="447"/>
-        <v>0.288655667922833</v>
+        <v>0.278543829663951</v>
       </c>
       <c r="N239" s="1">
         <f ca="1" t="shared" si="448"/>
-        <v>2.95293923256527</v>
+        <v>2.95280956152485</v>
       </c>
       <c r="O239" s="1">
         <f ca="1" t="shared" si="447"/>
-        <v>0.324189761472293</v>
+        <v>0.400297597889542</v>
       </c>
       <c r="P239" s="1">
         <f ca="1" t="shared" si="448"/>
-        <v>3.16331063787807</v>
+        <v>3.16324843114677</v>
       </c>
     </row>
     <row r="240" ht="16.5" spans="1:16">
@@ -20286,27 +20261,27 @@
       </c>
       <c r="K240" s="1">
         <f ca="1" t="shared" ref="K240:O240" si="449">RAND()</f>
-        <v>0.681806085653218</v>
+        <v>0.927408512435156</v>
       </c>
       <c r="L240" s="1">
         <f ca="1" t="shared" ref="L240:P240" si="450">J240+$R$1*K240/MAX(1,($A240*($A240-1)))++$R$1/$A240</f>
-        <v>2.73081274048526</v>
+        <v>2.73102862813582</v>
       </c>
       <c r="M240" s="1">
         <f ca="1" t="shared" si="449"/>
-        <v>0.219897441418434</v>
+        <v>0.219164058966348</v>
       </c>
       <c r="N240" s="1">
         <f ca="1" t="shared" si="450"/>
-        <v>2.94021105404792</v>
+        <v>2.94042629704599</v>
       </c>
       <c r="O240" s="1">
         <f ca="1" t="shared" si="449"/>
-        <v>0.488722575659188</v>
+        <v>0.299002676667429</v>
       </c>
       <c r="P240" s="1">
         <f ca="1" t="shared" si="450"/>
-        <v>3.14984566831575</v>
+        <v>3.1498941451145</v>
       </c>
     </row>
     <row r="241" ht="16.5" spans="1:16">
@@ -20346,27 +20321,27 @@
       </c>
       <c r="K241" s="1">
         <f ca="1" t="shared" ref="K241:O241" si="451">RAND()</f>
-        <v>0.434844264177411</v>
+        <v>0.372048061659355</v>
       </c>
       <c r="L241" s="1">
         <f ca="1" t="shared" ref="L241:P241" si="452">J241+$R$1*K241/MAX(1,($A241*($A241-1)))++$R$1/$A241</f>
-        <v>2.71917263272679</v>
+        <v>2.71911789405653</v>
       </c>
       <c r="M241" s="1">
         <f ca="1" t="shared" si="451"/>
-        <v>0.975389982447192</v>
+        <v>0.401613608072135</v>
       </c>
       <c r="N241" s="1">
         <f ca="1" t="shared" si="452"/>
-        <v>2.92835620140047</v>
+        <v>2.92780130898686</v>
       </c>
       <c r="O241" s="1">
         <f ca="1" t="shared" si="451"/>
-        <v>0.0921145595582904</v>
+        <v>0.809889646867811</v>
       </c>
       <c r="P241" s="1">
         <f ca="1" t="shared" si="452"/>
-        <v>3.13676982985197</v>
+        <v>3.13684061307234</v>
       </c>
     </row>
     <row r="242" ht="16.5" spans="1:16">
@@ -20406,27 +20381,27 @@
       </c>
       <c r="K242" s="1">
         <f ca="1" t="shared" ref="K242:O242" si="453">RAND()</f>
-        <v>0.388661795983662</v>
+        <v>0.89192543112858</v>
       </c>
       <c r="L242" s="1">
         <f ca="1" t="shared" ref="L242:P242" si="454">J242+$R$1*K242/MAX(1,($A242*($A242-1)))++$R$1/$A242</f>
-        <v>2.70780485978214</v>
+        <v>2.70823990787615</v>
       </c>
       <c r="M242" s="1">
         <f ca="1" t="shared" si="453"/>
-        <v>0.79398505319928</v>
+        <v>0.845732434810955</v>
       </c>
       <c r="N242" s="1">
         <f ca="1" t="shared" si="454"/>
-        <v>2.91596010273961</v>
+        <v>2.91643988404732</v>
       </c>
       <c r="O242" s="1">
         <f ca="1" t="shared" si="453"/>
-        <v>0.320841598616987</v>
+        <v>0.0725350429389595</v>
       </c>
       <c r="P242" s="1">
         <f ca="1" t="shared" si="454"/>
-        <v>3.12370633510356</v>
+        <v>3.1239714668991</v>
       </c>
     </row>
     <row r="243" ht="16.5" spans="1:16">
@@ -20466,27 +20441,27 @@
       </c>
       <c r="K243" s="1">
         <f ca="1" t="shared" ref="K243:O243" si="455">RAND()</f>
-        <v>0.80173681346722</v>
+        <v>0.587595098206718</v>
       </c>
       <c r="L243" s="1">
         <f ca="1" t="shared" ref="L243:P243" si="456">J243+$R$1*K243/MAX(1,($A243*($A243-1)))++$R$1/$A243</f>
-        <v>2.69692546278717</v>
+        <v>2.69674187707744</v>
       </c>
       <c r="M243" s="1">
         <f ca="1" t="shared" si="455"/>
-        <v>0.157722835856027</v>
+        <v>0.0549743606915762</v>
       </c>
       <c r="N243" s="1">
         <f ca="1" t="shared" si="456"/>
-        <v>2.90367225030805</v>
+        <v>2.90340057736266</v>
       </c>
       <c r="O243" s="1">
         <f ca="1" t="shared" si="455"/>
-        <v>0.689752855744228</v>
+        <v>0.891182852264323</v>
       </c>
       <c r="P243" s="1">
         <f ca="1" t="shared" si="456"/>
-        <v>3.11087515217677</v>
+        <v>3.11077616706489</v>
       </c>
     </row>
     <row r="244" ht="16.5" spans="1:16">
@@ -20526,27 +20501,27 @@
       </c>
       <c r="K244" s="1">
         <f ca="1" t="shared" ref="K244:O244" si="457">RAND()</f>
-        <v>0.853657690974068</v>
+        <v>0.739403768784701</v>
       </c>
       <c r="L244" s="1">
         <f ca="1" t="shared" ref="L244:P244" si="458">J244+$R$1*K244/MAX(1,($A244*($A244-1)))++$R$1/$A244</f>
-        <v>2.68582598518091</v>
+        <v>2.68572884039791</v>
       </c>
       <c r="M244" s="1">
         <f ca="1" t="shared" si="457"/>
-        <v>0.35824230387845</v>
+        <v>0.379405582794188</v>
       </c>
       <c r="N244" s="1">
         <f ca="1" t="shared" si="458"/>
-        <v>2.89189189878146</v>
+        <v>2.89181274814779</v>
       </c>
       <c r="O244" s="1">
         <f ca="1" t="shared" si="457"/>
-        <v>0.730929134256589</v>
+        <v>0.326104793443493</v>
       </c>
       <c r="P244" s="1">
         <f ca="1" t="shared" si="458"/>
-        <v>3.09827469061755</v>
+        <v>3.09785133672162</v>
       </c>
     </row>
     <row r="245" ht="16.5" spans="1:16">
@@ -20586,27 +20561,27 @@
       </c>
       <c r="K245" s="1">
         <f ca="1" t="shared" ref="K245:O245" si="459">RAND()</f>
-        <v>0.234833462816142</v>
+        <v>0.185703353473224</v>
       </c>
       <c r="L245" s="1">
         <f ca="1" t="shared" ref="L245:P245" si="460">J245+$R$1*K245/MAX(1,($A245*($A245-1)))++$R$1/$A245</f>
-        <v>2.67425186657797</v>
+        <v>2.67421043593864</v>
       </c>
       <c r="M245" s="1">
         <f ca="1" t="shared" si="459"/>
-        <v>0.0137731226087567</v>
+        <v>0.0463240376131679</v>
       </c>
       <c r="N245" s="1">
         <f ca="1" t="shared" si="460"/>
-        <v>2.87918151401996</v>
+        <v>2.87916753304922</v>
       </c>
       <c r="O245" s="1">
         <f ca="1" t="shared" si="459"/>
-        <v>0.226267099685305</v>
+        <v>0.938453946278724</v>
       </c>
       <c r="P245" s="1">
         <f ca="1" t="shared" si="460"/>
-        <v>3.08429035425109</v>
+        <v>3.08487694911402</v>
       </c>
     </row>
     <row r="246" ht="16.5" spans="1:16">
@@ -20646,27 +20621,27 @@
       </c>
       <c r="K246" s="1">
         <f ca="1" t="shared" ref="K246:O246" si="461">RAND()</f>
-        <v>0.0946460872380752</v>
+        <v>0.664560179847556</v>
       </c>
       <c r="L246" s="1">
         <f ca="1" t="shared" ref="L246:P246" si="462">J246+$R$1*K246/MAX(1,($A246*($A246-1)))++$R$1/$A246</f>
-        <v>2.66317718809572</v>
+        <v>2.66365386431904</v>
       </c>
       <c r="M246" s="1">
         <f ca="1" t="shared" si="461"/>
-        <v>0.240109215604341</v>
+        <v>0.753243773327922</v>
       </c>
       <c r="N246" s="1">
         <f ca="1" t="shared" si="462"/>
-        <v>2.86745964812884</v>
+        <v>2.86836551016491</v>
       </c>
       <c r="O246" s="1">
         <f ca="1" t="shared" si="461"/>
-        <v>0.269891920960468</v>
+        <v>0.618923360408209</v>
       </c>
       <c r="P246" s="1">
         <f ca="1" t="shared" si="462"/>
-        <v>3.07176701842071</v>
+        <v>3.07296481039945</v>
       </c>
     </row>
     <row r="247" ht="16.5" spans="1:16">
@@ -20706,27 +20681,27 @@
       </c>
       <c r="K247" s="1">
         <f ca="1" t="shared" ref="K247:O247" si="463">RAND()</f>
-        <v>0.186015030321392</v>
+        <v>0.580462516177809</v>
       </c>
       <c r="L247" s="1">
         <f ca="1" t="shared" ref="L247:P247" si="464">J247+$R$1*K247/MAX(1,($A247*($A247-1)))++$R$1/$A247</f>
-        <v>2.65238594245091</v>
+        <v>2.65271317613752</v>
       </c>
       <c r="M247" s="1">
         <f ca="1" t="shared" si="463"/>
-        <v>0.0495261008250085</v>
+        <v>0.663395585962516</v>
       </c>
       <c r="N247" s="1">
         <f ca="1" t="shared" si="464"/>
-        <v>2.85567906183105</v>
+        <v>2.85651556172402</v>
       </c>
       <c r="O247" s="1">
         <f ca="1" t="shared" si="463"/>
-        <v>0.512916729018339</v>
+        <v>0.354498495942495</v>
       </c>
       <c r="P247" s="1">
         <f ca="1" t="shared" si="464"/>
-        <v>3.05935661013785</v>
+        <v>3.06006168624363</v>
       </c>
     </row>
     <row r="248" ht="16.5" spans="1:16">
@@ -20766,27 +20741,27 @@
       </c>
       <c r="K248" s="1">
         <f ca="1" t="shared" ref="K248:O248" si="465">RAND()</f>
-        <v>0.516724557703222</v>
+        <v>0.803452560047167</v>
       </c>
       <c r="L248" s="1">
         <f ca="1" t="shared" ref="L248:P248" si="466">J248+$R$1*K248/MAX(1,($A248*($A248-1)))++$R$1/$A248</f>
-        <v>2.64187874375243</v>
+        <v>2.64211468727169</v>
       </c>
       <c r="M248" s="1">
         <f ca="1" t="shared" si="465"/>
-        <v>0.283684185081902</v>
+        <v>0.253403615132324</v>
       </c>
       <c r="N248" s="1">
         <f ca="1" t="shared" si="466"/>
-        <v>2.84454133236462</v>
+        <v>2.84475235852603</v>
       </c>
       <c r="O248" s="1">
         <f ca="1" t="shared" si="465"/>
-        <v>0.906399664990877</v>
+        <v>0.212538856829084</v>
       </c>
       <c r="P248" s="1">
         <f ca="1" t="shared" si="466"/>
-        <v>3.04771634278643</v>
+        <v>3.0473564028768</v>
       </c>
     </row>
     <row r="249" ht="16.5" spans="1:16">
@@ -20826,27 +20801,27 @@
       </c>
       <c r="K249" s="1">
         <f ca="1" t="shared" ref="K249:O249" si="467">RAND()</f>
-        <v>0.978381891978829</v>
+        <v>0.540080328667375</v>
       </c>
       <c r="L249" s="1">
         <f ca="1" t="shared" ref="L249:P249" si="468">J249+$R$1*K249/MAX(1,($A249*($A249-1)))++$R$1/$A249</f>
-        <v>2.63156130166186</v>
+        <v>2.63120353951341</v>
       </c>
       <c r="M249" s="1">
         <f ca="1" t="shared" si="467"/>
-        <v>0.690910181168497</v>
+        <v>0.440424803342194</v>
       </c>
       <c r="N249" s="1">
         <f ca="1" t="shared" si="468"/>
-        <v>2.83373815795444</v>
+        <v>2.83317593797506</v>
       </c>
       <c r="O249" s="1">
         <f ca="1" t="shared" si="467"/>
-        <v>0.00121091503922433</v>
+        <v>0.351749689816704</v>
       </c>
       <c r="P249" s="1">
         <f ca="1" t="shared" si="468"/>
-        <v>3.0353520495855</v>
+        <v>3.0350759556793</v>
       </c>
     </row>
     <row r="250" ht="16.5" spans="1:16">
@@ -20886,27 +20861,27 @@
       </c>
       <c r="K250" s="1">
         <f ca="1" t="shared" ref="K250:O250" si="469">RAND()</f>
-        <v>0.0913015612646164</v>
+        <v>0.493309958216058</v>
       </c>
       <c r="L250" s="1">
         <f ca="1" t="shared" ref="L250:P250" si="470">J250+$R$1*K250/MAX(1,($A250*($A250-1)))++$R$1/$A250</f>
-        <v>2.62023197755641</v>
+        <v>2.62055747988585</v>
       </c>
       <c r="M250" s="1">
         <f ca="1" t="shared" si="469"/>
-        <v>0.488056817163422</v>
+        <v>0.915555153766084</v>
       </c>
       <c r="N250" s="1">
         <f ca="1" t="shared" si="470"/>
-        <v>2.82143036531483</v>
+        <v>2.82210200893249</v>
       </c>
       <c r="O250" s="1">
         <f ca="1" t="shared" si="469"/>
-        <v>0.900811663415115</v>
+        <v>0.492336178514464</v>
       </c>
       <c r="P250" s="1">
         <f ca="1" t="shared" si="470"/>
-        <v>3.02296295669925</v>
+        <v>3.02330386164861</v>
       </c>
     </row>
     <row r="251" ht="16.5" spans="1:16">
@@ -20946,27 +20921,27 @@
       </c>
       <c r="K251" s="1">
         <f ca="1" t="shared" ref="K251:O251" si="471">RAND()</f>
-        <v>0.829673283798399</v>
+        <v>0.372775775644827</v>
       </c>
       <c r="L251" s="1">
         <f ca="1" t="shared" ref="L251:P251" si="472">J251+$R$1*K251/MAX(1,($A251*($A251-1)))++$R$1/$A251</f>
-        <v>2.61030495846088</v>
+        <v>2.60993797251056</v>
       </c>
       <c r="M251" s="1">
         <f ca="1" t="shared" si="471"/>
-        <v>0.35311414044645</v>
+        <v>0.524355562430299</v>
       </c>
       <c r="N251" s="1">
         <f ca="1" t="shared" si="472"/>
-        <v>2.8105885842765</v>
+        <v>2.81035914163701</v>
       </c>
       <c r="O251" s="1">
         <f ca="1" t="shared" si="471"/>
-        <v>0.751352523423629</v>
+        <v>0.639756613011018</v>
       </c>
       <c r="P251" s="1">
         <f ca="1" t="shared" si="472"/>
-        <v>3.01119208027925</v>
+        <v>3.01087300237035</v>
       </c>
     </row>
     <row r="252" ht="16.5" spans="1:16">
@@ -21006,27 +20981,27 @@
       </c>
       <c r="K252" s="1">
         <f ca="1" t="shared" ref="K252:O252" si="473">RAND()</f>
-        <v>0.973157117039837</v>
+        <v>0.73176056331269</v>
       </c>
       <c r="L252" s="1">
         <f ca="1" t="shared" ref="L252:P252" si="474">J252+$R$1*K252/MAX(1,($A252*($A252-1)))++$R$1/$A252</f>
-        <v>2.59997861124864</v>
+        <v>2.59978626339706</v>
       </c>
       <c r="M252" s="1">
         <f ca="1" t="shared" si="473"/>
-        <v>0.203128056159342</v>
+        <v>0.38242579337481</v>
       </c>
       <c r="N252" s="1">
         <f ca="1" t="shared" si="474"/>
-        <v>2.79934365352446</v>
+        <v>2.79929417239577</v>
       </c>
       <c r="O252" s="1">
         <f ca="1" t="shared" si="473"/>
-        <v>0.359670837299626</v>
+        <v>0.189767769199439</v>
       </c>
       <c r="P252" s="1">
         <f ca="1" t="shared" si="474"/>
-        <v>2.99883343108406</v>
+        <v>2.99864856902461</v>
       </c>
     </row>
     <row r="253" ht="16.5" spans="1:16">
@@ -21066,27 +21041,27 @@
       </c>
       <c r="K253" s="1">
         <f ca="1" t="shared" ref="K253:O253" si="475">RAND()</f>
-        <v>0.551628312986642</v>
+        <v>0.346079232461598</v>
       </c>
       <c r="L253" s="1">
         <f ca="1" t="shared" ref="L253:P253" si="476">J253+$R$1*K253/MAX(1,($A253*($A253-1)))++$R$1/$A253</f>
-        <v>2.58928700144896</v>
+        <v>2.58912451719508</v>
       </c>
       <c r="M253" s="1">
         <f ca="1" t="shared" si="475"/>
-        <v>0.832753437304312</v>
+        <v>0.249441370750408</v>
       </c>
       <c r="N253" s="1">
         <f ca="1" t="shared" si="476"/>
-        <v>2.7883579821589</v>
+        <v>2.78773439622716</v>
       </c>
       <c r="O253" s="1">
         <f ca="1" t="shared" si="475"/>
-        <v>0.50548180593142</v>
+        <v>0.978013501670164</v>
       </c>
       <c r="P253" s="1">
         <f ca="1" t="shared" si="476"/>
-        <v>2.98717025829715</v>
+        <v>2.98692020339664</v>
       </c>
     </row>
     <row r="254" ht="16.5" spans="1:16">
@@ -21126,27 +21101,27 @@
       </c>
       <c r="K254" s="1">
         <f ca="1" t="shared" ref="K254:O254" si="477">RAND()</f>
-        <v>0.188183563739052</v>
+        <v>0.689359275132571</v>
       </c>
       <c r="L254" s="1">
         <f ca="1" t="shared" ref="L254:P254" si="478">J254+$R$1*K254/MAX(1,($A254*($A254-1)))++$R$1/$A254</f>
-        <v>2.57872842051237</v>
+        <v>2.57912146250951</v>
       </c>
       <c r="M254" s="1">
         <f ca="1" t="shared" si="477"/>
-        <v>0.09311388675398</v>
+        <v>0.0993271686892332</v>
       </c>
       <c r="N254" s="1">
         <f ca="1" t="shared" si="478"/>
-        <v>2.776429902637</v>
+        <v>2.77682781733784</v>
       </c>
       <c r="O254" s="1">
         <f ca="1" t="shared" si="477"/>
-        <v>0.43322355352189</v>
+        <v>0.469554388009755</v>
       </c>
       <c r="P254" s="1">
         <f ca="1" t="shared" si="478"/>
-        <v>2.97439811233767</v>
+        <v>2.97482451912905</v>
       </c>
     </row>
     <row r="255" ht="16.5" spans="1:16">
@@ -21186,27 +21161,27 @@
       </c>
       <c r="K255" s="1">
         <f ca="1" t="shared" ref="K255:O255" si="479">RAND()</f>
-        <v>0.0347197523523719</v>
+        <v>0.606798653216017</v>
       </c>
       <c r="L255" s="1">
         <f ca="1" t="shared" ref="L255:P255" si="480">J255+$R$1*K255/MAX(1,($A255*($A255-1)))++$R$1/$A255</f>
-        <v>2.56841890989415</v>
+        <v>2.56886402434815</v>
       </c>
       <c r="M255" s="1">
         <f ca="1" t="shared" si="479"/>
-        <v>0.725504143902178</v>
+        <v>0.642743311420143</v>
       </c>
       <c r="N255" s="1">
         <f ca="1" t="shared" si="480"/>
-        <v>2.76583379282955</v>
+        <v>2.76621451399321</v>
       </c>
       <c r="O255" s="1">
         <f ca="1" t="shared" si="479"/>
-        <v>0.470207320217892</v>
+        <v>0.346635608938248</v>
       </c>
       <c r="P255" s="1">
         <f ca="1" t="shared" si="480"/>
-        <v>2.9630500382936</v>
+        <v>2.96333461265878</v>
       </c>
     </row>
     <row r="256" ht="16.5" spans="1:16">
@@ -21246,27 +21221,27 @@
       </c>
       <c r="K256" s="1">
         <f ca="1" t="shared" ref="K256:O256" si="481">RAND()</f>
-        <v>0.357125801298324</v>
+        <v>0.633140729110262</v>
       </c>
       <c r="L256" s="1">
         <f ca="1" t="shared" ref="L256:P256" si="482">J256+$R$1*K256/MAX(1,($A256*($A256-1)))++$R$1/$A256</f>
-        <v>2.55855884344704</v>
+        <v>2.55877191657335</v>
       </c>
       <c r="M256" s="1">
         <f ca="1" t="shared" si="481"/>
-        <v>0.153053620818691</v>
+        <v>0.0610215254166848</v>
       </c>
       <c r="N256" s="1">
         <f ca="1" t="shared" si="482"/>
-        <v>2.75475542644906</v>
+        <v>2.75489745426473</v>
       </c>
       <c r="O256" s="1">
         <f ca="1" t="shared" si="481"/>
-        <v>0.269428996300308</v>
+        <v>0.612637756265834</v>
       </c>
       <c r="P256" s="1">
         <f ca="1" t="shared" si="482"/>
-        <v>2.95104184685689</v>
+        <v>2.95144881890597</v>
       </c>
     </row>
     <row r="257" ht="16.5" spans="1:16">
@@ -21306,27 +21281,27 @@
       </c>
       <c r="K257" s="1">
         <f ca="1" t="shared" ref="K257:O257" si="483">RAND()</f>
-        <v>0.43665539806083</v>
+        <v>0.881442291526386</v>
       </c>
       <c r="L257" s="1">
         <f ca="1" t="shared" ref="L257:P257" si="484">J257+$R$1*K257/MAX(1,($A257*($A257-1)))++$R$1/$A257</f>
-        <v>2.54858812453896</v>
+        <v>2.54892880077476</v>
       </c>
       <c r="M257" s="1">
         <f ca="1" t="shared" si="483"/>
-        <v>0.670087465800912</v>
+        <v>0.522082632698038</v>
       </c>
       <c r="N257" s="1">
         <f ca="1" t="shared" si="484"/>
-        <v>2.74441386555136</v>
+        <v>2.74464118024221</v>
       </c>
       <c r="O257" s="1">
         <f ca="1" t="shared" si="483"/>
-        <v>0.867479657193746</v>
+        <v>0.951242343256384</v>
       </c>
       <c r="P257" s="1">
         <f ca="1" t="shared" si="484"/>
-        <v>2.94039079543586</v>
+        <v>2.94068226659581</v>
       </c>
     </row>
     <row r="258" ht="16.5" spans="1:16">
@@ -21366,27 +21341,27 @@
       </c>
       <c r="K258" s="1">
         <f ca="1" t="shared" ref="K258:O258" si="488">RAND()</f>
-        <v>0.423593800605853</v>
+        <v>0.430569506719683</v>
       </c>
       <c r="L258" s="1">
         <f ca="1" t="shared" ref="L258:P258" si="489">J258+$R$1*K258/MAX(1,($A258*($A258-1)))++$R$1/$A258</f>
-        <v>2.53862444810965</v>
+        <v>2.53862974944273</v>
       </c>
       <c r="M258" s="1">
         <f ca="1" t="shared" si="488"/>
-        <v>0.666492339137145</v>
+        <v>0.358331600565867</v>
       </c>
       <c r="N258" s="1">
         <f ca="1" t="shared" si="489"/>
-        <v>2.73368349202011</v>
+        <v>2.73345460018489</v>
       </c>
       <c r="O258" s="1">
         <f ca="1" t="shared" si="488"/>
-        <v>0.334864365117755</v>
+        <v>0.140362792498112</v>
       </c>
       <c r="P258" s="1">
         <f ca="1" t="shared" si="489"/>
-        <v>2.92849050834817</v>
+        <v>2.92811380099388</v>
       </c>
     </row>
     <row r="259" ht="16.5" spans="1:16">
@@ -21426,27 +21401,27 @@
       </c>
       <c r="K259" s="1">
         <f ca="1" t="shared" ref="K259:O259" si="490">RAND()</f>
-        <v>0.359864147573335</v>
+        <v>0.385443552121613</v>
       </c>
       <c r="L259" s="1">
         <f ca="1" t="shared" ref="L259:P259" si="491">J259+$R$1*K259/MAX(1,($A259*($A259-1)))++$R$1/$A259</f>
-        <v>2.52870016600879</v>
+        <v>2.52871945491518</v>
       </c>
       <c r="M259" s="1">
         <f ca="1" t="shared" si="490"/>
-        <v>0.255514938172871</v>
+        <v>0.806739193263646</v>
       </c>
       <c r="N259" s="1">
         <f ca="1" t="shared" si="491"/>
-        <v>2.72269129421602</v>
+        <v>2.72312625007193</v>
       </c>
       <c r="O259" s="1">
         <f ca="1" t="shared" si="490"/>
-        <v>0.290287597918685</v>
+        <v>0.0351772460404203</v>
       </c>
       <c r="P259" s="1">
         <f ca="1" t="shared" si="491"/>
-        <v>2.91670864377557</v>
+        <v>2.91695122612691</v>
       </c>
     </row>
     <row r="260" ht="16.5" spans="1:16">
@@ -21486,27 +21461,27 @@
       </c>
       <c r="K260" s="1">
         <f ca="1" t="shared" ref="K260:O260" si="492">RAND()</f>
-        <v>0.890525916533161</v>
+        <v>0.44367346002978</v>
       </c>
       <c r="L260" s="1">
         <f ca="1" t="shared" ref="L260:P260" si="493">J260+$R$1*K260/MAX(1,($A260*($A260-1)))++$R$1/$A260</f>
-        <v>2.51929793025989</v>
+        <v>2.51896356997698</v>
       </c>
       <c r="M260" s="1">
         <f ca="1" t="shared" si="492"/>
-        <v>0.940329965267014</v>
+        <v>0.526225945720574</v>
       </c>
       <c r="N260" s="1">
         <f ca="1" t="shared" si="493"/>
-        <v>2.71305173137724</v>
+        <v>2.71240751504426</v>
       </c>
       <c r="O260" s="1">
         <f ca="1" t="shared" si="492"/>
-        <v>0.704512774696211</v>
+        <v>0.377590888688745</v>
       </c>
       <c r="P260" s="1">
         <f ca="1" t="shared" si="493"/>
-        <v>2.90662908073426</v>
+        <v>2.90574024295475</v>
       </c>
     </row>
     <row r="261" ht="16.5" spans="1:16">
@@ -21546,27 +21521,27 @@
       </c>
       <c r="K261" s="1">
         <f ca="1" t="shared" ref="K261:O261" si="494">RAND()</f>
-        <v>0.6968350141346</v>
+        <v>0.65374040756572</v>
       </c>
       <c r="L261" s="1">
         <f ca="1" t="shared" ref="L261:P261" si="495">J261+$R$1*K261/MAX(1,($A261*($A261-1)))++$R$1/$A261</f>
-        <v>2.5094274094254</v>
+        <v>2.50939541164803</v>
       </c>
       <c r="M261" s="1">
         <f ca="1" t="shared" si="494"/>
-        <v>0.721279577552345</v>
+        <v>0.175430823421151</v>
       </c>
       <c r="N261" s="1">
         <f ca="1" t="shared" si="495"/>
-        <v>2.70227065235498</v>
+        <v>2.70183336147237</v>
       </c>
       <c r="O261" s="1">
         <f ca="1" t="shared" si="494"/>
-        <v>0.494189499176024</v>
+        <v>0.56906260610168</v>
       </c>
       <c r="P261" s="1">
         <f ca="1" t="shared" si="495"/>
-        <v>2.89494528073275</v>
+        <v>2.89456358318762</v>
       </c>
     </row>
     <row r="262" ht="16.5" spans="1:16">
@@ -21606,27 +21581,27 @@
       </c>
       <c r="K262" s="1">
         <f ca="1" t="shared" ref="K262:O262" si="496">RAND()</f>
-        <v>0.759079598298562</v>
+        <v>0.980843678917018</v>
       </c>
       <c r="L262" s="1">
         <f ca="1" t="shared" ref="L262:P262" si="497">J262+$R$1*K262/MAX(1,($A262*($A262-1)))++$R$1/$A262</f>
-        <v>2.49982248717823</v>
+        <v>2.49998588541034</v>
       </c>
       <c r="M262" s="1">
         <f ca="1" t="shared" si="496"/>
-        <v>0.791389533383261</v>
+        <v>0.000123691621741306</v>
       </c>
       <c r="N262" s="1">
         <f ca="1" t="shared" si="497"/>
-        <v>2.69197647298238</v>
+        <v>2.69155685777376</v>
       </c>
       <c r="O262" s="1">
         <f ca="1" t="shared" si="496"/>
-        <v>0.643459176262884</v>
+        <v>0.0709163361473986</v>
       </c>
       <c r="P262" s="1">
         <f ca="1" t="shared" si="497"/>
-        <v>2.88402146206008</v>
+        <v>2.88317999094215</v>
       </c>
     </row>
     <row r="263" ht="16.5" spans="1:16">
@@ -21666,27 +21641,27 @@
       </c>
       <c r="K263" s="1">
         <f ca="1" t="shared" ref="K263:O263" si="498">RAND()</f>
-        <v>0.266293337223472</v>
+        <v>0.174647404730048</v>
       </c>
       <c r="L263" s="1">
         <f ca="1" t="shared" ref="L263:P263" si="499">J263+$R$1*K263/MAX(1,($A263*($A263-1)))++$R$1/$A263</f>
-        <v>2.48988497948087</v>
+        <v>2.48981796920588</v>
       </c>
       <c r="M263" s="1">
         <f ca="1" t="shared" si="498"/>
-        <v>0.840989266637482</v>
+        <v>0.138618581201072</v>
       </c>
       <c r="N263" s="1">
         <f ca="1" t="shared" si="499"/>
-        <v>2.68133959419428</v>
+        <v>2.68075901990723</v>
       </c>
       <c r="O263" s="1">
         <f ca="1" t="shared" si="498"/>
-        <v>0.283416480698171</v>
+        <v>0.506146209202958</v>
       </c>
       <c r="P263" s="1">
         <f ca="1" t="shared" si="499"/>
-        <v>2.87238651917505</v>
+        <v>2.87196880187413</v>
       </c>
     </row>
     <row r="264" ht="16.5" spans="1:16">
@@ -21726,27 +21701,27 @@
       </c>
       <c r="K264" s="1">
         <f ca="1" t="shared" ref="K264:O264" si="500">RAND()</f>
-        <v>0.745045311592056</v>
+        <v>0.573057453675056</v>
       </c>
       <c r="L264" s="1">
         <f ca="1" t="shared" ref="L264:P264" si="501">J264+$R$1*K264/MAX(1,($A264*($A264-1)))++$R$1/$A264</f>
-        <v>2.4807310287287</v>
+        <v>2.48060622983026</v>
       </c>
       <c r="M264" s="1">
         <f ca="1" t="shared" si="500"/>
-        <v>0.970953149848837</v>
+        <v>0.817692408613159</v>
       </c>
       <c r="N264" s="1">
         <f ca="1" t="shared" si="501"/>
-        <v>2.67154964622924</v>
+        <v>2.67131363731916</v>
       </c>
       <c r="O264" s="1">
         <f ca="1" t="shared" si="500"/>
-        <v>0.629018277112448</v>
+        <v>0.252531790475128</v>
       </c>
       <c r="P264" s="1">
         <f ca="1" t="shared" si="501"/>
-        <v>2.86212014682216</v>
+        <v>2.86161094944762</v>
       </c>
     </row>
     <row r="265" ht="16.5" spans="1:16">
@@ -21786,27 +21761,27 @@
       </c>
       <c r="K265" s="1">
         <f ca="1" t="shared" ref="K265:O265" si="502">RAND()</f>
-        <v>0.088851859534506</v>
+        <v>0.969567643682453</v>
       </c>
       <c r="L265" s="1">
         <f ca="1" t="shared" ref="L265:P265" si="503">J265+$R$1*K265/MAX(1,($A265*($A265-1)))++$R$1/$A265</f>
-        <v>2.47082674549166</v>
+        <v>2.47146097451009</v>
       </c>
       <c r="M265" s="1">
         <f ca="1" t="shared" si="502"/>
-        <v>0.0474974805261836</v>
+        <v>0.58280248007538</v>
       </c>
       <c r="N265" s="1">
         <f ca="1" t="shared" si="503"/>
-        <v>2.66025488920099</v>
+        <v>2.66127460689867</v>
       </c>
       <c r="O265" s="1">
         <f ca="1" t="shared" si="502"/>
-        <v>0.43914844518709</v>
+        <v>0.372590119852328</v>
       </c>
       <c r="P265" s="1">
         <f ca="1" t="shared" si="503"/>
-        <v>2.84996507214631</v>
+        <v>2.85093685926058</v>
       </c>
     </row>
     <row r="266" ht="16.5" spans="1:16">
@@ -21846,27 +21821,27 @@
       </c>
       <c r="K266" s="1">
         <f ca="1" t="shared" ref="K266:O266" si="504">RAND()</f>
-        <v>0.739544801294059</v>
+        <v>0.629382185278572</v>
       </c>
       <c r="L266" s="1">
         <f ca="1" t="shared" ref="L266:P266" si="505">J266+$R$1*K266/MAX(1,($A266*($A266-1)))++$R$1/$A266</f>
-        <v>2.46193506632454</v>
+        <v>2.46185633375163</v>
       </c>
       <c r="M266" s="1">
         <f ca="1" t="shared" si="504"/>
-        <v>0.5950875216982</v>
+        <v>0.318218354952314</v>
       </c>
       <c r="N266" s="1">
         <f ca="1" t="shared" si="505"/>
-        <v>2.6510396171548</v>
+        <v>2.65076300781892</v>
       </c>
       <c r="O266" s="1">
         <f ca="1" t="shared" si="504"/>
-        <v>0.529501989420498</v>
+        <v>0.731317761398354</v>
       </c>
       <c r="P266" s="1">
         <f ca="1" t="shared" si="505"/>
-        <v>2.84009729439138</v>
+        <v>2.83996492159922</v>
       </c>
     </row>
     <row r="267" ht="16.5" spans="1:16">
@@ -21906,27 +21881,27 @@
       </c>
       <c r="K267" s="1">
         <f ca="1" t="shared" ref="K267:O267" si="506">RAND()</f>
-        <v>0.661458946898128</v>
+        <v>0.845105154011236</v>
       </c>
       <c r="L267" s="1">
         <f ca="1" t="shared" ref="L267:P267" si="507">J267+$R$1*K267/MAX(1,($A267*($A267-1)))++$R$1/$A267</f>
-        <v>2.45259005458001</v>
+        <v>2.45272031859414</v>
       </c>
       <c r="M267" s="1">
         <f ca="1" t="shared" si="506"/>
-        <v>0.977542084224031</v>
+        <v>0.485138474199137</v>
       </c>
       <c r="N267" s="1">
         <f ca="1" t="shared" si="507"/>
-        <v>2.64125337000363</v>
+        <v>2.64103436205718</v>
       </c>
       <c r="O267" s="1">
         <f ca="1" t="shared" si="506"/>
-        <v>0.673279908890037</v>
+        <v>0.416177066849635</v>
       </c>
       <c r="P267" s="1">
         <f ca="1" t="shared" si="507"/>
-        <v>2.82970086603774</v>
+        <v>2.82929948978228</v>
       </c>
     </row>
     <row r="268" ht="16.5" spans="1:16">
@@ -21966,27 +21941,27 @@
       </c>
       <c r="K268" s="1">
         <f ca="1" t="shared" ref="K268:O268" si="509">RAND()</f>
-        <v>0.494356617880797</v>
+        <v>0.334822459997089</v>
       </c>
       <c r="L268" s="1">
         <f ca="1" t="shared" ref="L268:P268" si="510">J268+$R$1*K268/MAX(1,($A268*($A268-1)))++$R$1/$A268</f>
-        <v>2.44325304597018</v>
+        <v>2.44314073277294</v>
       </c>
       <c r="M268" s="1">
         <f ca="1" t="shared" si="509"/>
-        <v>0.674568716740593</v>
+        <v>0.237187416650541</v>
       </c>
       <c r="N268" s="1">
         <f ca="1" t="shared" si="510"/>
-        <v>2.63099386481275</v>
+        <v>2.63057363202715</v>
       </c>
       <c r="O268" s="1">
         <f ca="1" t="shared" si="509"/>
-        <v>0.58836938395386</v>
+        <v>0.175869022290539</v>
       </c>
       <c r="P268" s="1">
         <f ca="1" t="shared" si="510"/>
-        <v>2.81867399870362</v>
+        <v>2.81796336268969</v>
       </c>
     </row>
     <row r="269" ht="16.5" spans="1:16">
@@ -22026,27 +22001,27 @@
       </c>
       <c r="K269" s="1">
         <f ca="1" t="shared" ref="K269:O269" si="511">RAND()</f>
-        <v>0.442734451866806</v>
+        <v>0.910561030535691</v>
       </c>
       <c r="L269" s="1">
         <f ca="1" t="shared" ref="L269:P269" si="512">J269+$R$1*K269/MAX(1,($A269*($A269-1)))++$R$1/$A269</f>
-        <v>2.43406753762918</v>
+        <v>2.4343944330528</v>
       </c>
       <c r="M269" s="1">
         <f ca="1" t="shared" si="511"/>
-        <v>0.399594844419081</v>
+        <v>0.973911503961922</v>
       </c>
       <c r="N269" s="1">
         <f ca="1" t="shared" si="512"/>
-        <v>2.62091392007399</v>
+        <v>2.62164212122987</v>
       </c>
       <c r="O269" s="1">
         <f ca="1" t="shared" si="511"/>
-        <v>0.159624960067215</v>
+        <v>0.760327597494841</v>
       </c>
       <c r="P269" s="1">
         <f ca="1" t="shared" si="512"/>
-        <v>2.80759262274048</v>
+        <v>2.808740566921</v>
       </c>
     </row>
     <row r="270" ht="16.5" spans="1:16">
@@ -22086,27 +22061,27 @@
       </c>
       <c r="K270" s="1">
         <f ca="1" t="shared" ref="K270:O270" si="513">RAND()</f>
-        <v>0.453296446951215</v>
+        <v>0.555109197464071</v>
       </c>
       <c r="L270" s="1">
         <f ca="1" t="shared" ref="L270:P270" si="514">J270+$R$1*K270/MAX(1,($A270*($A270-1)))++$R$1/$A270</f>
-        <v>2.42499396357914</v>
+        <v>2.42506457665029</v>
       </c>
       <c r="M270" s="1">
         <f ca="1" t="shared" si="513"/>
-        <v>0.783906190741726</v>
+        <v>0.438602120574973</v>
       </c>
       <c r="N270" s="1">
         <f ca="1" t="shared" si="514"/>
-        <v>2.61141125411814</v>
+        <v>2.61124237870917</v>
       </c>
       <c r="O270" s="1">
         <f ca="1" t="shared" si="513"/>
-        <v>0.529919895216501</v>
+        <v>0.00746213591624678</v>
       </c>
       <c r="P270" s="1">
         <f ca="1" t="shared" si="514"/>
-        <v>2.79765239037127</v>
+        <v>2.79712116008291</v>
       </c>
     </row>
     <row r="271" ht="16.5" spans="1:16">
@@ -22146,27 +22121,27 @@
       </c>
       <c r="K271" s="1">
         <f ca="1" t="shared" ref="K271:O271" si="515">RAND()</f>
-        <v>0.211070743685993</v>
+        <v>0.129084042057562</v>
       </c>
       <c r="L271" s="1">
         <f ca="1" t="shared" ref="L271:P271" si="516">J271+$R$1*K271/MAX(1,($A271*($A271-1)))++$R$1/$A271</f>
-        <v>2.41581376204302</v>
+        <v>2.41575732069534</v>
       </c>
       <c r="M271" s="1">
         <f ca="1" t="shared" si="515"/>
-        <v>0.30795232983013</v>
+        <v>0.47273121910444</v>
       </c>
       <c r="N271" s="1">
         <f ca="1" t="shared" si="516"/>
-        <v>2.601210948006</v>
+        <v>2.60126794386697</v>
       </c>
       <c r="O271" s="1">
         <f ca="1" t="shared" si="515"/>
-        <v>0.177010997934204</v>
+        <v>0.550511835271384</v>
       </c>
       <c r="P271" s="1">
         <f ca="1" t="shared" si="516"/>
-        <v>2.7865179912374</v>
+        <v>2.7868321128297</v>
       </c>
     </row>
     <row r="272" ht="16.5" spans="1:16">
@@ -22206,27 +22181,27 @@
       </c>
       <c r="K272" s="1">
         <f ca="1" t="shared" ref="K272:O272" si="517">RAND()</f>
-        <v>0.0718628237137955</v>
+        <v>0.676493726604586</v>
       </c>
       <c r="L272" s="1">
         <f ca="1" t="shared" ref="L272:P272" si="518">J272+$R$1*K272/MAX(1,($A272*($A272-1)))++$R$1/$A272</f>
-        <v>2.40677317399461</v>
+        <v>2.4071863425766</v>
       </c>
       <c r="M272" s="1">
         <f ca="1" t="shared" si="517"/>
-        <v>0.73786562879797</v>
+        <v>0.752858569050411</v>
       </c>
       <c r="N272" s="1">
         <f ca="1" t="shared" si="518"/>
-        <v>2.59177923223487</v>
+        <v>2.59220264609516</v>
       </c>
       <c r="O272" s="1">
         <f ca="1" t="shared" si="517"/>
-        <v>0.949472145358558</v>
+        <v>0.275309354288879</v>
       </c>
       <c r="P272" s="1">
         <f ca="1" t="shared" si="518"/>
-        <v>2.77692988970744</v>
+        <v>2.77689262105367</v>
       </c>
     </row>
     <row r="273" ht="16.5" spans="1:16">
@@ -22266,27 +22241,27 @@
       </c>
       <c r="K273" s="1">
         <f ca="1" t="shared" ref="K273:O273" si="519">RAND()</f>
-        <v>0.0798039419988985</v>
+        <v>0.713181789764163</v>
       </c>
       <c r="L273" s="1">
         <f ca="1" t="shared" ref="L273:P273" si="520">J273+$R$1*K273/MAX(1,($A273*($A273-1)))++$R$1/$A273</f>
-        <v>2.3978998018925</v>
+        <v>2.39832943197157</v>
       </c>
       <c r="M273" s="1">
         <f ca="1" t="shared" si="519"/>
-        <v>0.157900014879065</v>
+        <v>0.998299766963771</v>
       </c>
       <c r="N273" s="1">
         <f ca="1" t="shared" si="520"/>
-        <v>2.58183043734865</v>
+        <v>2.58283012369541</v>
       </c>
       <c r="O273" s="1">
         <f ca="1" t="shared" si="519"/>
-        <v>0.933928566241409</v>
+        <v>0.5698447232648</v>
       </c>
       <c r="P273" s="1">
         <f ca="1" t="shared" si="520"/>
-        <v>2.76628746508243</v>
+        <v>2.76704018767635</v>
       </c>
     </row>
     <row r="274" ht="16.5" spans="1:16">
@@ -22326,27 +22301,27 @@
       </c>
       <c r="K274" s="1">
         <f ca="1" t="shared" ref="K274:O274" si="521">RAND()</f>
-        <v>0.360837389604773</v>
+        <v>0.955683641117266</v>
       </c>
       <c r="L274" s="1">
         <f ca="1" t="shared" ref="L274:P274" si="522">J274+$R$1*K274/MAX(1,($A274*($A274-1)))++$R$1/$A274</f>
-        <v>2.38927550459869</v>
+        <v>2.38967604209836</v>
       </c>
       <c r="M274" s="1">
         <f ca="1" t="shared" si="521"/>
-        <v>0.0640575771486735</v>
+        <v>0.816402992816019</v>
       </c>
       <c r="N274" s="1">
         <f ca="1" t="shared" si="522"/>
-        <v>2.57246882067897</v>
+        <v>2.5733759471517</v>
       </c>
       <c r="O274" s="1">
         <f ca="1" t="shared" si="521"/>
-        <v>0.215842100611856</v>
+        <v>0.0259301040780726</v>
       </c>
       <c r="P274" s="1">
         <f ca="1" t="shared" si="522"/>
-        <v>2.75576434030069</v>
+        <v>2.75654359024053</v>
       </c>
     </row>
     <row r="275" ht="16.5" spans="1:16">
@@ -22386,27 +22361,27 @@
       </c>
       <c r="K275" s="1">
         <f ca="1" t="shared" ref="K275:O275" si="523">RAND()</f>
-        <v>0.504449185020426</v>
+        <v>0.0488480531450013</v>
       </c>
       <c r="L275" s="1">
         <f ca="1" t="shared" ref="L275:P275" si="524">J275+$R$1*K275/MAX(1,($A275*($A275-1)))++$R$1/$A275</f>
-        <v>2.38062113926434</v>
+        <v>2.38031660119592</v>
       </c>
       <c r="M275" s="1">
         <f ca="1" t="shared" si="523"/>
-        <v>0.0135013268288766</v>
+        <v>0.904385407541228</v>
       </c>
       <c r="N275" s="1">
         <f ca="1" t="shared" si="524"/>
-        <v>2.56311191579894</v>
+        <v>2.56340287255734</v>
       </c>
       <c r="O275" s="1">
         <f ca="1" t="shared" si="523"/>
-        <v>0.380411057502996</v>
+        <v>0.149324656925863</v>
       </c>
       <c r="P275" s="1">
         <f ca="1" t="shared" si="524"/>
-        <v>2.74584794629111</v>
+        <v>2.7459844376605</v>
       </c>
     </row>
     <row r="276" ht="16.5" spans="1:16">
@@ -22446,27 +22421,27 @@
       </c>
       <c r="K276" s="1">
         <f ca="1" t="shared" ref="K276:O276" si="525">RAND()</f>
-        <v>0.987810148495242</v>
+        <v>0.783776183864135</v>
       </c>
       <c r="L276" s="1">
         <f ca="1" t="shared" ref="L276:P276" si="526">J276+$R$1*K276/MAX(1,($A276*($A276-1)))++$R$1/$A276</f>
-        <v>2.37225468490278</v>
+        <v>2.37211929408352</v>
       </c>
       <c r="M276" s="1">
         <f ca="1" t="shared" si="525"/>
-        <v>0.280736250623614</v>
+        <v>0.965108779042892</v>
       </c>
       <c r="N276" s="1">
         <f ca="1" t="shared" si="526"/>
-        <v>2.55425915487665</v>
+        <v>2.55457789314061</v>
       </c>
       <c r="O276" s="1">
         <f ca="1" t="shared" si="525"/>
-        <v>0.556224932176502</v>
+        <v>0.721191066369475</v>
       </c>
       <c r="P276" s="1">
         <f ca="1" t="shared" si="526"/>
-        <v>2.73644643087677</v>
+        <v>2.73687463571949</v>
       </c>
     </row>
     <row r="277" ht="16.5" spans="1:16">
@@ -22506,27 +22481,27 @@
       </c>
       <c r="K277" s="1">
         <f ca="1" t="shared" ref="K277:O277" si="527">RAND()</f>
-        <v>0.860502196103434</v>
+        <v>0.757581178694102</v>
       </c>
       <c r="L277" s="1">
         <f ca="1" t="shared" ref="L277:P277" si="528">J277+$R$1*K277/MAX(1,($A277*($A277-1)))++$R$1/$A277</f>
-        <v>2.36354446784987</v>
+        <v>2.36347666744314</v>
       </c>
       <c r="M277" s="1">
         <f ca="1" t="shared" si="527"/>
-        <v>0.0658788253021585</v>
+        <v>0.311011432424255</v>
       </c>
       <c r="N277" s="1">
         <f ca="1" t="shared" si="528"/>
-        <v>2.54474728657537</v>
+        <v>2.54484097009955</v>
       </c>
       <c r="O277" s="1">
         <f ca="1" t="shared" si="527"/>
-        <v>0.622384348457664</v>
+        <v>0.217378108855714</v>
       </c>
       <c r="P277" s="1">
         <f ca="1" t="shared" si="528"/>
-        <v>2.72631670972982</v>
+        <v>2.72614359072462</v>
       </c>
     </row>
     <row r="278" ht="16.5" spans="1:16">
@@ -22566,27 +22541,27 @@
       </c>
       <c r="K278" s="1">
         <f ca="1" t="shared" ref="K278:O278" si="529">RAND()</f>
-        <v>0.789330521616408</v>
+        <v>0.58684820200422</v>
       </c>
       <c r="L278" s="1">
         <f ca="1" t="shared" ref="L278:P278" si="530">J278+$R$1*K278/MAX(1,($A278*($A278-1)))++$R$1/$A278</f>
-        <v>2.35493468484907</v>
+        <v>2.35480226037383</v>
       </c>
       <c r="M278" s="1">
         <f ca="1" t="shared" si="529"/>
-        <v>0.802908089760573</v>
+        <v>0.357136064285996</v>
       </c>
       <c r="N278" s="1">
         <f ca="1" t="shared" si="530"/>
-        <v>2.53596520601906</v>
+        <v>2.53554124435351</v>
       </c>
       <c r="O278" s="1">
         <f ca="1" t="shared" si="529"/>
-        <v>0.155786062285489</v>
+        <v>0.785518937534723</v>
       </c>
       <c r="P278" s="1">
         <f ca="1" t="shared" si="530"/>
-        <v>2.71657250606502</v>
+        <v>2.71656039292878</v>
       </c>
     </row>
     <row r="279" ht="16.5" spans="1:16">
@@ -22626,27 +22601,27 @@
       </c>
       <c r="K279" s="1">
         <f ca="1" t="shared" ref="K279:O279" si="531">RAND()</f>
-        <v>0.380214216114935</v>
+        <v>0.550273615235948</v>
       </c>
       <c r="L279" s="1">
         <f ca="1" t="shared" ref="L279:P279" si="532">J279+$R$1*K279/MAX(1,($A279*($A279-1)))++$R$1/$A279</f>
-        <v>2.34616797016863</v>
+        <v>2.34627838974576</v>
       </c>
       <c r="M279" s="1">
         <f ca="1" t="shared" si="531"/>
-        <v>0.838135286733658</v>
+        <v>0.223581609976086</v>
       </c>
       <c r="N279" s="1">
         <f ca="1" t="shared" si="532"/>
-        <v>2.52656828656394</v>
+        <v>2.52627967640522</v>
       </c>
       <c r="O279" s="1">
         <f ca="1" t="shared" si="531"/>
-        <v>0.434964498049909</v>
+        <v>0.942062813869972</v>
       </c>
       <c r="P279" s="1">
         <f ca="1" t="shared" si="532"/>
-        <v>2.70670682414416</v>
+        <v>2.70674747294957</v>
       </c>
     </row>
     <row r="280" ht="16.5" spans="1:16">
@@ -22686,27 +22661,27 @@
       </c>
       <c r="K280" s="1">
         <f ca="1" t="shared" ref="K280:O280" si="533">RAND()</f>
-        <v>0.0458881533996061</v>
+        <v>0.45302766974298</v>
       </c>
       <c r="L280" s="1">
         <f ca="1" t="shared" ref="L280:P280" si="534">J280+$R$1*K280/MAX(1,($A280*($A280-1)))++$R$1/$A280</f>
-        <v>2.337514432424</v>
+        <v>2.33777689311115</v>
       </c>
       <c r="M280" s="1">
         <f ca="1" t="shared" si="533"/>
-        <v>0.0144442743298434</v>
+        <v>0.355353984051115</v>
       </c>
       <c r="N280" s="1">
         <f ca="1" t="shared" si="534"/>
-        <v>2.51673521339556</v>
+        <v>2.51721744001817</v>
       </c>
       <c r="O280" s="1">
         <f ca="1" t="shared" si="533"/>
-        <v>0.106970500776107</v>
+        <v>0.795305092381639</v>
       </c>
       <c r="P280" s="1">
         <f ca="1" t="shared" si="534"/>
-        <v>2.69601564098947</v>
+        <v>2.6969415994599</v>
       </c>
     </row>
     <row r="281" ht="16.5" spans="1:16">
@@ -22746,27 +22721,27 @@
       </c>
       <c r="K281" s="1">
         <f ca="1" t="shared" ref="K281:O281" si="535">RAND()</f>
-        <v>0.596048405188073</v>
+        <v>0.143572525379785</v>
       </c>
       <c r="L281" s="1">
         <f ca="1" t="shared" ref="L281:P281" si="536">J281+$R$1*K281/MAX(1,($A281*($A281-1)))++$R$1/$A281</f>
-        <v>2.32949055837506</v>
+        <v>2.32920095527738</v>
       </c>
       <c r="M281" s="1">
         <f ca="1" t="shared" si="535"/>
-        <v>0.0375030197583559</v>
+        <v>0.844214391854637</v>
       </c>
       <c r="N281" s="1">
         <f ca="1" t="shared" si="536"/>
-        <v>2.50808599041535</v>
+        <v>2.50831271564083</v>
       </c>
       <c r="O281" s="1">
         <f ca="1" t="shared" si="535"/>
-        <v>0.019340793628547</v>
+        <v>0.0596449179829561</v>
       </c>
       <c r="P281" s="1">
         <f ca="1" t="shared" si="536"/>
-        <v>2.68666979788695</v>
+        <v>2.68692231940298</v>
       </c>
     </row>
     <row r="282" ht="16.5" spans="1:16">
@@ -22806,27 +22781,27 @@
       </c>
       <c r="K282" s="1">
         <f ca="1" t="shared" ref="K282:O282" si="537">RAND()</f>
-        <v>0.806838108619731</v>
+        <v>0.967986098886761</v>
       </c>
       <c r="L282" s="1">
         <f ca="1" t="shared" ref="L282:P282" si="538">J282+$R$1*K282/MAX(1,($A282*($A282-1)))++$R$1/$A282</f>
-        <v>2.32130581984534</v>
+        <v>2.32140822705826</v>
       </c>
       <c r="M282" s="1">
         <f ca="1" t="shared" si="537"/>
-        <v>0.0474771447812095</v>
+        <v>0.222715664189887</v>
       </c>
       <c r="N282" s="1">
         <f ca="1" t="shared" si="538"/>
-        <v>2.49927193394344</v>
+        <v>2.49948570269641</v>
       </c>
       <c r="O282" s="1">
         <f ca="1" t="shared" si="537"/>
-        <v>0.433938943007846</v>
+        <v>0.183902649968747</v>
       </c>
       <c r="P282" s="1">
         <f ca="1" t="shared" si="538"/>
-        <v>2.67748363891485</v>
+        <v>2.67753851322639</v>
       </c>
     </row>
     <row r="283" ht="16.5" spans="1:16">
@@ -22866,27 +22841,27 @@
       </c>
       <c r="K283" s="1">
         <f ca="1" t="shared" ref="K283:O283" si="539">RAND()</f>
-        <v>0.948806776655763</v>
+        <v>0.976660818588005</v>
       </c>
       <c r="L283" s="1">
         <f ca="1" t="shared" ref="L283:P283" si="540">J283+$R$1*K283/MAX(1,($A283*($A283-1)))++$R$1/$A283</f>
-        <v>2.3131349579621</v>
+        <v>2.3131525332643</v>
       </c>
       <c r="M283" s="1">
         <f ca="1" t="shared" si="539"/>
-        <v>0.090460928120798</v>
+        <v>0.289901539374315</v>
       </c>
       <c r="N283" s="1">
         <f ca="1" t="shared" si="540"/>
-        <v>2.49049700140379</v>
+        <v>2.490640419448</v>
       </c>
       <c r="O283" s="1">
         <f ca="1" t="shared" si="539"/>
-        <v>0.776528896767138</v>
+        <v>0.525372253321137</v>
       </c>
       <c r="P283" s="1">
         <f ca="1" t="shared" si="540"/>
-        <v>2.66829193899797</v>
+        <v>2.66827688259464</v>
       </c>
     </row>
     <row r="284" ht="16.5" spans="1:16">
@@ -22926,27 +22901,27 @@
       </c>
       <c r="K284" s="1">
         <f ca="1" t="shared" ref="K284:O284" si="541">RAND()</f>
-        <v>0.725363988884087</v>
+        <v>0.0913446964659061</v>
       </c>
       <c r="L284" s="1">
         <f ca="1" t="shared" ref="L284:P284" si="542">J284+$R$1*K284/MAX(1,($A284*($A284-1)))++$R$1/$A284</f>
-        <v>2.30479247424309</v>
+        <v>2.3043952489139</v>
       </c>
       <c r="M284" s="1">
         <f ca="1" t="shared" si="541"/>
-        <v>0.135414666384994</v>
+        <v>0.732046807142632</v>
       </c>
       <c r="N284" s="1">
         <f ca="1" t="shared" si="542"/>
-        <v>2.48155575937603</v>
+        <v>2.48153233560359</v>
       </c>
       <c r="O284" s="1">
         <f ca="1" t="shared" si="541"/>
-        <v>0.00692848281359049</v>
+        <v>0.473301962512264</v>
       </c>
       <c r="P284" s="1">
         <f ca="1" t="shared" si="542"/>
-        <v>2.65823854543398</v>
+        <v>2.65850731365193</v>
       </c>
     </row>
     <row r="285" ht="16.5" spans="1:16">
@@ -22986,27 +22961,27 @@
       </c>
       <c r="K285" s="1">
         <f ca="1" t="shared" ref="K285:O285" si="543">RAND()</f>
-        <v>0.653537986938142</v>
+        <v>0.315273778235291</v>
       </c>
       <c r="L285" s="1">
         <f ca="1" t="shared" ref="L285:P285" si="544">J285+$R$1*K285/MAX(1,($A285*($A285-1)))++$R$1/$A285</f>
-        <v>2.29660425147249</v>
+        <v>2.29639381487224</v>
       </c>
       <c r="M285" s="1">
         <f ca="1" t="shared" si="543"/>
-        <v>0.22380078753361</v>
+        <v>0.641831029311649</v>
       </c>
       <c r="N285" s="1">
         <f ca="1" t="shared" si="544"/>
-        <v>2.47279981758229</v>
+        <v>2.4728494406059</v>
       </c>
       <c r="O285" s="1">
         <f ca="1" t="shared" si="543"/>
-        <v>0.950941798737799</v>
+        <v>0.261140899656978</v>
       </c>
       <c r="P285" s="1">
         <f ca="1" t="shared" si="544"/>
-        <v>2.64944774335167</v>
+        <v>2.64906823626835</v>
       </c>
     </row>
     <row r="286" ht="16.5" spans="1:16">
@@ -23046,27 +23021,27 @@
       </c>
       <c r="K286" s="1">
         <f ca="1" t="shared" ref="K286:O286" si="545">RAND()</f>
-        <v>0.824160088982337</v>
+        <v>0.485001271383222</v>
       </c>
       <c r="L286" s="1">
         <f ca="1" t="shared" ref="L286:P286" si="546">J286+$R$1*K286/MAX(1,($A286*($A286-1)))++$R$1/$A286</f>
-        <v>2.28862377074931</v>
+        <v>2.28841425826006</v>
       </c>
       <c r="M286" s="1">
         <f ca="1" t="shared" si="545"/>
-        <v>0.755343913736468</v>
+        <v>0.922872150464817</v>
       </c>
       <c r="N286" s="1">
         <f ca="1" t="shared" si="546"/>
-        <v>2.46452897455073</v>
+        <v>2.46442295121192</v>
       </c>
       <c r="O286" s="1">
         <f ca="1" t="shared" si="545"/>
-        <v>0.384927677158255</v>
+        <v>0.17419363375927</v>
       </c>
       <c r="P286" s="1">
         <f ca="1" t="shared" si="546"/>
-        <v>2.64020535685685</v>
+        <v>2.63996915434619</v>
       </c>
     </row>
     <row r="287" ht="16.5" spans="1:16">
@@ -23106,27 +23081,27 @@
       </c>
       <c r="K287" s="1">
         <f ca="1" t="shared" ref="K287:O287" si="547">RAND()</f>
-        <v>0.583513606809759</v>
+        <v>0.468056491973642</v>
       </c>
       <c r="L287" s="1">
         <f ca="1" t="shared" ref="L287:P287" si="548">J287+$R$1*K287/MAX(1,($A287*($A287-1)))++$R$1/$A287</f>
-        <v>2.28044627260877</v>
+        <v>2.28037544871303</v>
       </c>
       <c r="M287" s="1">
         <f ca="1" t="shared" si="547"/>
-        <v>0.324845093060491</v>
+        <v>0.901267608383032</v>
       </c>
       <c r="N287" s="1">
         <f ca="1" t="shared" si="548"/>
-        <v>2.45547071445214</v>
+        <v>2.4557534806161</v>
       </c>
       <c r="O287" s="1">
         <f ca="1" t="shared" si="547"/>
-        <v>0.718204804095526</v>
+        <v>0.0977679223371068</v>
       </c>
       <c r="P287" s="1">
         <f ca="1" t="shared" si="548"/>
-        <v>2.63073645166481</v>
+        <v>2.63063862840308</v>
       </c>
     </row>
     <row r="288" ht="16.5" spans="1:16">
@@ -23166,27 +23141,27 @@
       </c>
       <c r="K288" s="1">
         <f ca="1" t="shared" ref="K288:O288" si="549">RAND()</f>
-        <v>0.468991758270946</v>
+        <v>0.39448669883907</v>
       </c>
       <c r="L288" s="1">
         <f ca="1" t="shared" ref="L288:P288" si="550">J288+$R$1*K288/MAX(1,($A288*($A288-1)))++$R$1/$A288</f>
-        <v>2.27240381067607</v>
+        <v>2.27235842614632</v>
       </c>
       <c r="M288" s="1">
         <f ca="1" t="shared" si="549"/>
-        <v>0.590920614180785</v>
+        <v>0.883752126228621</v>
       </c>
       <c r="N288" s="1">
         <f ca="1" t="shared" si="550"/>
-        <v>2.44697979604082</v>
+        <v>2.44711278893367</v>
       </c>
       <c r="O288" s="1">
         <f ca="1" t="shared" si="549"/>
-        <v>0.0442133576205539</v>
+        <v>0.145035226425778</v>
       </c>
       <c r="P288" s="1">
         <f ca="1" t="shared" si="550"/>
-        <v>2.62122275634735</v>
+        <v>2.62141716457414</v>
       </c>
     </row>
     <row r="289" ht="16.5" spans="1:16">
@@ -23226,27 +23201,27 @@
       </c>
       <c r="K289" s="1">
         <f ca="1" t="shared" ref="K289:O289" si="551">RAND()</f>
-        <v>0.47913155449222</v>
+        <v>0.932482273736736</v>
       </c>
       <c r="L289" s="1">
         <f ca="1" t="shared" ref="L289:P289" si="552">J289+$R$1*K289/MAX(1,($A289*($A289-1)))++$R$1/$A289</f>
-        <v>2.2644932803151</v>
+        <v>2.26476751976489</v>
       </c>
       <c r="M289" s="1">
         <f ca="1" t="shared" si="551"/>
-        <v>0.256632046635887</v>
+        <v>0.963722480151328</v>
       </c>
       <c r="N289" s="1">
         <f ca="1" t="shared" si="552"/>
-        <v>2.43825963245326</v>
+        <v>2.43896160275956</v>
       </c>
       <c r="O289" s="1">
         <f ca="1" t="shared" si="551"/>
-        <v>0.0655749385539341</v>
+        <v>0.82871467046692</v>
       </c>
       <c r="P289" s="1">
         <f ca="1" t="shared" si="552"/>
-        <v>2.61191041094396</v>
+        <v>2.61307401726696</v>
       </c>
     </row>
     <row r="290" ht="16.5" spans="1:16">
@@ -23286,27 +23261,27 @@
       </c>
       <c r="K290" s="1">
         <f ca="1" t="shared" ref="K290:O290" si="553">RAND()</f>
-        <v>0.965684402927274</v>
+        <v>0.0278499415859739</v>
       </c>
       <c r="L290" s="1">
         <f ca="1" t="shared" ref="L290:P290" si="554">J290+$R$1*K290/MAX(1,($A290*($A290-1)))++$R$1/$A290</f>
-        <v>2.25692383001906</v>
+        <v>2.25636044426517</v>
       </c>
       <c r="M290" s="1">
         <f ca="1" t="shared" si="553"/>
-        <v>0.763218709220938</v>
+        <v>0.974002846929536</v>
       </c>
       <c r="N290" s="1">
         <f ca="1" t="shared" si="554"/>
-        <v>2.43039269938975</v>
+        <v>2.42995593809383</v>
       </c>
       <c r="O290" s="1">
         <f ca="1" t="shared" si="553"/>
-        <v>0.0400969913655558</v>
+        <v>0.531260613608055</v>
       </c>
       <c r="P290" s="1">
         <f ca="1" t="shared" si="554"/>
-        <v>2.60342716749779</v>
+        <v>2.60328546316448</v>
       </c>
     </row>
     <row r="291" ht="16.5" spans="1:16">
@@ -23346,27 +23321,27 @@
       </c>
       <c r="K291" s="1">
         <f ca="1" t="shared" ref="K291:O291" si="555">RAND()</f>
-        <v>0.961511475819828</v>
+        <v>0.0783691876588255</v>
       </c>
       <c r="L291" s="1">
         <f ca="1" t="shared" ref="L291:P291" si="556">J291+$R$1*K291/MAX(1,($A291*($A291-1)))++$R$1/$A291</f>
-        <v>2.24911198632372</v>
+        <v>2.24858511465676</v>
       </c>
       <c r="M291" s="1">
         <f ca="1" t="shared" si="555"/>
-        <v>0.0618021407788525</v>
+        <v>0.623637292443375</v>
       </c>
       <c r="N291" s="1">
         <f ca="1" t="shared" si="556"/>
-        <v>2.42156264981303</v>
+        <v>2.42137096198551</v>
       </c>
       <c r="O291" s="1">
         <f ca="1" t="shared" si="555"/>
-        <v>0.0631564629473149</v>
+        <v>0.996448611846944</v>
       </c>
       <c r="P291" s="1">
         <f ca="1" t="shared" si="556"/>
-        <v>2.59401412127404</v>
+        <v>2.59437922389449</v>
       </c>
     </row>
     <row r="292" ht="16.5" spans="1:16">
@@ -23406,27 +23381,27 @@
       </c>
       <c r="K292" s="1">
         <f ca="1" t="shared" ref="K292:O292" si="557">RAND()</f>
-        <v>0.116490722646344</v>
+        <v>0.578233372300561</v>
       </c>
       <c r="L292" s="1">
         <f ca="1" t="shared" ref="L292:P292" si="558">J292+$R$1*K292/MAX(1,($A292*($A292-1)))++$R$1/$A292</f>
-        <v>2.24085584235256</v>
+        <v>2.24112941899058</v>
       </c>
       <c r="M292" s="1">
         <f ca="1" t="shared" si="557"/>
-        <v>0.305533550608821</v>
+        <v>0.39278557083457</v>
       </c>
       <c r="N292" s="1">
         <f ca="1" t="shared" si="558"/>
-        <v>2.41285817293119</v>
+        <v>2.41318344527973</v>
       </c>
       <c r="O292" s="1">
         <f ca="1" t="shared" si="557"/>
-        <v>0.426556417898086</v>
+        <v>0.75740505970884</v>
       </c>
       <c r="P292" s="1">
         <f ca="1" t="shared" si="558"/>
-        <v>2.58493220801704</v>
+        <v>2.58545350397135</v>
       </c>
     </row>
     <row r="293" ht="16.5" spans="1:16">
@@ -23466,27 +23441,27 @@
       </c>
       <c r="K293" s="1">
         <f ca="1" t="shared" ref="K293:O293" si="559">RAND()</f>
-        <v>0.846633473648878</v>
+        <v>0.755244319593654</v>
       </c>
       <c r="L293" s="1">
         <f ca="1" t="shared" ref="L293:P293" si="560">J293+$R$1*K293/MAX(1,($A293*($A293-1)))++$R$1/$A293</f>
-        <v>2.23358673061341</v>
+        <v>2.23353295457303</v>
       </c>
       <c r="M293" s="1">
         <f ca="1" t="shared" si="559"/>
-        <v>0.773212050059876</v>
+        <v>0.436040848187687</v>
       </c>
       <c r="N293" s="1">
         <f ca="1" t="shared" si="560"/>
-        <v>2.40527458781934</v>
+        <v>2.40502241042213</v>
       </c>
       <c r="O293" s="1">
         <f ca="1" t="shared" si="559"/>
-        <v>0.991750899126342</v>
+        <v>0.861462114985591</v>
       </c>
       <c r="P293" s="1">
         <f ca="1" t="shared" si="560"/>
-        <v>2.57709103965002</v>
+        <v>2.57676219653695</v>
       </c>
     </row>
     <row r="294" ht="16.5" spans="1:16">
@@ -23526,27 +23501,27 @@
       </c>
       <c r="K294" s="1">
         <f ca="1" t="shared" ref="K294:O294" si="561">RAND()</f>
-        <v>0.284606122068487</v>
+        <v>0.428931939173207</v>
       </c>
       <c r="L294" s="1">
         <f ca="1" t="shared" ref="L294:P294" si="562">J294+$R$1*K294/MAX(1,($A294*($A294-1)))++$R$1/$A294</f>
-        <v>2.22560931210089</v>
+        <v>2.22569365791947</v>
       </c>
       <c r="M294" s="1">
         <f ca="1" t="shared" si="561"/>
-        <v>0.153071074547126</v>
+        <v>0.671344825282648</v>
       </c>
       <c r="N294" s="1">
         <f ca="1" t="shared" si="562"/>
-        <v>2.39634723292149</v>
+        <v>2.39673446442356</v>
       </c>
       <c r="O294" s="1">
         <f ca="1" t="shared" si="561"/>
-        <v>0.701947580349115</v>
+        <v>0.0473432883127376</v>
       </c>
       <c r="P294" s="1">
         <f ca="1" t="shared" si="562"/>
-        <v>2.56740592405966</v>
+        <v>2.56741059659916</v>
       </c>
     </row>
     <row r="295" ht="16.5" spans="1:16">
@@ -23586,27 +23561,27 @@
       </c>
       <c r="K295" s="1">
         <f ca="1" t="shared" ref="K295:O295" si="563">RAND()</f>
-        <v>0.163818178914301</v>
+        <v>0.362005847603114</v>
       </c>
       <c r="L295" s="1">
         <f ca="1" t="shared" ref="L295:P295" si="564">J295+$R$1*K295/MAX(1,($A295*($A295-1)))++$R$1/$A295</f>
-        <v>2.21794468330136</v>
+        <v>2.21805971874788</v>
       </c>
       <c r="M295" s="1">
         <f ca="1" t="shared" si="563"/>
-        <v>0.501673377302222</v>
+        <v>0.534322995503444</v>
       </c>
       <c r="N295" s="1">
         <f ca="1" t="shared" si="564"/>
-        <v>2.38830390027874</v>
+        <v>2.38843788677016</v>
       </c>
       <c r="O295" s="1">
         <f ca="1" t="shared" si="563"/>
-        <v>0.656331648032165</v>
+        <v>0.094132422228286</v>
       </c>
       <c r="P295" s="1">
         <f ca="1" t="shared" si="564"/>
-        <v>2.55875288663152</v>
+        <v>2.55856055191738</v>
       </c>
     </row>
     <row r="296" ht="16.5" spans="1:16">
@@ -23646,27 +23621,27 @@
       </c>
       <c r="K296" s="1">
         <f ca="1" t="shared" ref="K296:O296" si="565">RAND()</f>
-        <v>0.52559541308183</v>
+        <v>0.735129453538173</v>
       </c>
       <c r="L296" s="1">
         <f ca="1" t="shared" ref="L296:P296" si="566">J296+$R$1*K296/MAX(1,($A296*($A296-1)))++$R$1/$A296</f>
-        <v>2.2106108586493</v>
+        <v>2.21073165539809</v>
       </c>
       <c r="M296" s="1">
         <f ca="1" t="shared" si="565"/>
-        <v>0.656193506871044</v>
+        <v>0.333064243599411</v>
       </c>
       <c r="N296" s="1">
         <f ca="1" t="shared" si="566"/>
-        <v>2.38048068080246</v>
+        <v>2.3804151929535</v>
       </c>
       <c r="O296" s="1">
         <f ca="1" t="shared" si="565"/>
-        <v>0.871325203495902</v>
+        <v>0.631938521082072</v>
       </c>
       <c r="P296" s="1">
         <f ca="1" t="shared" si="566"/>
-        <v>2.5504745267632</v>
+        <v>2.550271032064</v>
       </c>
     </row>
     <row r="297" ht="16.5" spans="1:16">
@@ -23706,27 +23681,27 @@
       </c>
       <c r="K297" s="1">
         <f ca="1" t="shared" ref="K297:O297" si="567">RAND()</f>
-        <v>0.362983889671878</v>
+        <v>0.613080410635461</v>
       </c>
       <c r="L297" s="1">
         <f ca="1" t="shared" ref="L297:P297" si="568">J297+$R$1*K297/MAX(1,($A297*($A297-1)))++$R$1/$A297</f>
-        <v>2.20302507094003</v>
+        <v>2.20316827783477</v>
       </c>
       <c r="M297" s="1">
         <f ca="1" t="shared" si="567"/>
-        <v>0.349509031819287</v>
+        <v>0.252630638571063</v>
       </c>
       <c r="N297" s="1">
         <f ca="1" t="shared" si="568"/>
-        <v>2.37214412100406</v>
+        <v>2.37223185470065</v>
       </c>
       <c r="O297" s="1">
         <f ca="1" t="shared" si="567"/>
-        <v>0.761860823122236</v>
+        <v>0.949277720090463</v>
       </c>
       <c r="P297" s="1">
         <f ca="1" t="shared" si="568"/>
-        <v>2.54149928638606</v>
+        <v>2.54169433621696</v>
       </c>
     </row>
     <row r="298" ht="16.5" spans="1:16">
@@ -23766,27 +23741,27 @@
       </c>
       <c r="K298" s="1">
         <f ca="1" t="shared" ref="K298:O298" si="569">RAND()</f>
-        <v>0.224866662940929</v>
+        <v>0.828871527618896</v>
       </c>
       <c r="L298" s="1">
         <f ca="1" t="shared" ref="L298:P298" si="570">J298+$R$1*K298/MAX(1,($A298*($A298-1)))++$R$1/$A298</f>
-        <v>2.19550508841964</v>
+        <v>2.19584861652995</v>
       </c>
       <c r="M298" s="1">
         <f ca="1" t="shared" si="569"/>
-        <v>0.538582261099955</v>
+        <v>0.178071358751315</v>
       </c>
       <c r="N298" s="1">
         <f ca="1" t="shared" si="570"/>
-        <v>2.36416157573712</v>
+        <v>2.36430006306669</v>
       </c>
       <c r="O298" s="1">
         <f ca="1" t="shared" si="569"/>
-        <v>0.784194726500004</v>
+        <v>0.250641849139948</v>
       </c>
       <c r="P298" s="1">
         <f ca="1" t="shared" si="570"/>
-        <v>2.532957755284</v>
+        <v>2.53279278411111</v>
       </c>
     </row>
     <row r="299" ht="16.5" spans="1:16">
@@ -23826,27 +23801,27 @@
       </c>
       <c r="K299" s="1">
         <f ca="1" t="shared" ref="K299:O299" si="571">RAND()</f>
-        <v>0.976724773641082</v>
+        <v>0.180084204580526</v>
       </c>
       <c r="L299" s="1">
         <f ca="1" t="shared" ref="L299:P299" si="572">J299+$R$1*K299/MAX(1,($A299*($A299-1)))++$R$1/$A299</f>
-        <v>2.18853903959824</v>
+        <v>2.18808899069248</v>
       </c>
       <c r="M299" s="1">
         <f ca="1" t="shared" si="571"/>
-        <v>0.191063987781239</v>
+        <v>0.660595790802689</v>
       </c>
       <c r="N299" s="1">
         <f ca="1" t="shared" si="572"/>
-        <v>2.35643221293552</v>
+        <v>2.35624741825152</v>
       </c>
       <c r="O299" s="1">
         <f ca="1" t="shared" si="571"/>
-        <v>0.528044966022089</v>
+        <v>0.179057523088347</v>
       </c>
       <c r="P299" s="1">
         <f ca="1" t="shared" si="572"/>
-        <v>2.5245157580997</v>
+        <v>2.52413380873527</v>
       </c>
     </row>
     <row r="300" ht="16.5" spans="1:16">
@@ -23886,27 +23861,27 @@
       </c>
       <c r="K300" s="1">
         <f ca="1" t="shared" ref="K300:O300" si="573">RAND()</f>
-        <v>0.00175408569116864</v>
+        <v>0.0434819788104792</v>
       </c>
       <c r="L300" s="1">
         <f ca="1" t="shared" ref="L300:P300" si="574">J300+$R$1*K300/MAX(1,($A300*($A300-1)))++$R$1/$A300</f>
-        <v>2.18064788337281</v>
+        <v>2.18067129917332</v>
       </c>
       <c r="M300" s="1">
         <f ca="1" t="shared" si="573"/>
-        <v>0.582921368221199</v>
+        <v>0.468107898287111</v>
       </c>
       <c r="N300" s="1">
         <f ca="1" t="shared" si="574"/>
-        <v>2.34819907266611</v>
+        <v>2.34815806035617</v>
       </c>
       <c r="O300" s="1">
         <f ca="1" t="shared" si="573"/>
-        <v>0.553385256080998</v>
+        <v>0.372172097660633</v>
       </c>
       <c r="P300" s="1">
         <f ca="1" t="shared" si="574"/>
-        <v>2.51573368763327</v>
+        <v>2.51559098672014</v>
       </c>
     </row>
     <row r="301" ht="16.5" spans="1:16">
@@ -23946,27 +23921,27 @@
       </c>
       <c r="K301" s="1">
         <f ca="1" t="shared" ref="K301:O301" si="575">RAND()</f>
-        <v>0.826095472895163</v>
+        <v>0.914256095240711</v>
       </c>
       <c r="L301" s="1">
         <f ca="1" t="shared" ref="L301:P301" si="576">J301+$R$1*K301/MAX(1,($A301*($A301-1)))++$R$1/$A301</f>
-        <v>2.1738161067296</v>
+        <v>2.17386524865955</v>
       </c>
       <c r="M301" s="1">
         <f ca="1" t="shared" si="575"/>
-        <v>0.726772149029242</v>
+        <v>0.855477422391248</v>
       </c>
       <c r="N301" s="1">
         <f ca="1" t="shared" si="576"/>
-        <v>2.34088788607688</v>
+        <v>2.34100877007672</v>
       </c>
       <c r="O301" s="1">
         <f ca="1" t="shared" si="575"/>
-        <v>0.0166810850985397</v>
+        <v>0.973093306636978</v>
       </c>
       <c r="P301" s="1">
         <f ca="1" t="shared" si="576"/>
-        <v>2.50756385100726</v>
+        <v>2.50821785218744</v>
       </c>
     </row>
     <row r="302" spans="1:16">

--- a/table/resources/sample/PointsAwardRanking.xlsx
+++ b/table/resources/sample/PointsAwardRanking.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="PointsAwardRanking" sheetId="1" r:id="rId1"/>
@@ -176,7 +176,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="111">
   <si>
     <t>序列ID</t>
   </si>
@@ -469,7 +469,19 @@
     <t>1990000_15750000</t>
   </si>
   <si>
-    <t>2036/08/01 00:00:00</t>
+    <t>wdcc_ccb_1.png</t>
+  </si>
+  <si>
+    <t>2026/08/01 00:00:00</t>
+  </si>
+  <si>
+    <t>wdcc_ccb_2.png</t>
+  </si>
+  <si>
+    <t>wdcc_ccb_3.png</t>
+  </si>
+  <si>
+    <t>itemicon_1010101.png</t>
   </si>
   <si>
     <t>名次</t>
@@ -1171,7 +1183,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1239,9 +1251,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3912,12 +3921,14 @@
       <c r="G86" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H86" s="21"/>
+      <c r="H86" s="21">
+        <v>33333333</v>
+      </c>
       <c r="I86" s="21" t="s">
-        <v>23</v>
+        <v>97</v>
       </c>
       <c r="J86" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K86" s="18"/>
       <c r="L86" s="18"/>
@@ -3940,12 +3951,14 @@
       <c r="G87" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="H87" s="21"/>
+      <c r="H87" s="21">
+        <v>22222222</v>
+      </c>
       <c r="I87" s="21" t="s">
-        <v>25</v>
+        <v>99</v>
       </c>
       <c r="J87" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K87" s="18"/>
       <c r="L87" s="18"/>
@@ -3968,12 +3981,14 @@
       <c r="G88" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="H88" s="21"/>
+      <c r="H88" s="21">
+        <v>11111111</v>
+      </c>
       <c r="I88" s="21" t="s">
-        <v>27</v>
+        <v>100</v>
       </c>
       <c r="J88" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K88" s="18"/>
       <c r="L88" s="18"/>
@@ -3996,10 +4011,14 @@
       <c r="G89" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="H89" s="21"/>
-      <c r="I89" s="21"/>
+      <c r="H89" s="21">
+        <v>5000000</v>
+      </c>
+      <c r="I89" s="21" t="s">
+        <v>101</v>
+      </c>
       <c r="J89" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K89" s="18"/>
       <c r="L89" s="18"/>
@@ -4022,10 +4041,14 @@
       <c r="G90" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="H90" s="21"/>
-      <c r="I90" s="21"/>
+      <c r="H90" s="21">
+        <v>3000000</v>
+      </c>
+      <c r="I90" s="21" t="s">
+        <v>101</v>
+      </c>
       <c r="J90" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K90" s="18"/>
       <c r="L90" s="19"/>
@@ -4052,7 +4075,7 @@
       <c r="H91" s="21"/>
       <c r="I91" s="21"/>
       <c r="J91" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K91" s="18"/>
       <c r="L91" s="19"/>
@@ -4079,7 +4102,7 @@
       <c r="H92" s="21"/>
       <c r="I92" s="21"/>
       <c r="J92" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K92" s="18"/>
       <c r="L92" s="19"/>
@@ -4106,7 +4129,7 @@
       <c r="H93" s="21"/>
       <c r="I93" s="21"/>
       <c r="J93" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K93" s="18"/>
       <c r="L93" s="19"/>
@@ -4133,7 +4156,7 @@
       <c r="H94" s="21"/>
       <c r="I94" s="21"/>
       <c r="J94" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K94" s="18"/>
       <c r="N94" s="3"/>
@@ -4159,7 +4182,7 @@
       <c r="H95" s="21"/>
       <c r="I95" s="21"/>
       <c r="J95" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K95" s="18"/>
       <c r="N95" s="3"/>
@@ -4185,7 +4208,7 @@
       <c r="H96" s="21"/>
       <c r="I96" s="21"/>
       <c r="J96" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K96" s="18"/>
       <c r="L96" s="9"/>
@@ -4212,7 +4235,7 @@
       <c r="H97" s="21"/>
       <c r="I97" s="21"/>
       <c r="J97" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K97" s="18"/>
       <c r="L97" s="19"/>
@@ -4239,7 +4262,7 @@
       <c r="H98" s="21"/>
       <c r="I98" s="21"/>
       <c r="J98" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K98" s="18"/>
       <c r="L98" s="19"/>
@@ -4266,7 +4289,7 @@
       <c r="H99" s="21"/>
       <c r="I99" s="21"/>
       <c r="J99" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K99" s="18"/>
       <c r="L99" s="19"/>
@@ -4293,7 +4316,7 @@
       <c r="H100" s="21"/>
       <c r="I100" s="21"/>
       <c r="J100" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K100" s="18"/>
       <c r="L100" s="19"/>
@@ -4320,7 +4343,7 @@
       <c r="H101" s="21"/>
       <c r="I101" s="21"/>
       <c r="J101" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K101" s="18"/>
       <c r="L101" s="19"/>
@@ -4347,7 +4370,7 @@
       <c r="H102" s="21"/>
       <c r="I102" s="21"/>
       <c r="J102" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K102" s="18"/>
       <c r="L102" s="19"/>
@@ -4374,7 +4397,7 @@
       <c r="H103" s="21"/>
       <c r="I103" s="21"/>
       <c r="J103" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K103" s="18"/>
       <c r="L103" s="19"/>
@@ -4401,7 +4424,7 @@
       <c r="H104" s="21"/>
       <c r="I104" s="21"/>
       <c r="J104" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K104" s="18"/>
       <c r="L104" s="19"/>
@@ -4428,7 +4451,7 @@
       <c r="H105" s="21"/>
       <c r="I105" s="21"/>
       <c r="J105" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K105" s="18"/>
       <c r="L105" s="19"/>
@@ -4455,7 +4478,7 @@
       <c r="H106" s="21"/>
       <c r="I106" s="21"/>
       <c r="J106" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K106" s="18"/>
       <c r="L106" s="19"/>
@@ -4482,7 +4505,7 @@
       <c r="H107" s="21"/>
       <c r="I107" s="21"/>
       <c r="J107" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K107" s="18"/>
       <c r="L107" s="19"/>
@@ -4509,7 +4532,7 @@
       <c r="H108" s="21"/>
       <c r="I108" s="21"/>
       <c r="J108" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K108" s="18"/>
       <c r="L108" s="19"/>
@@ -4536,7 +4559,7 @@
       <c r="H109" s="21"/>
       <c r="I109" s="21"/>
       <c r="J109" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K109" s="18"/>
       <c r="L109" s="19"/>
@@ -4563,7 +4586,7 @@
       <c r="H110" s="21"/>
       <c r="I110" s="21"/>
       <c r="J110" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K110" s="18"/>
       <c r="L110" s="19"/>
@@ -4590,7 +4613,7 @@
       <c r="H111" s="21"/>
       <c r="I111" s="21"/>
       <c r="J111" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K111" s="18"/>
       <c r="L111" s="19"/>
@@ -4617,7 +4640,7 @@
       <c r="H112" s="21"/>
       <c r="I112" s="21"/>
       <c r="J112" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K112" s="18"/>
       <c r="L112" s="19"/>
@@ -4641,12 +4664,14 @@
       <c r="G113" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="H113" s="21"/>
+      <c r="H113" s="21">
+        <v>33333333</v>
+      </c>
       <c r="I113" s="21" t="s">
-        <v>23</v>
+        <v>97</v>
       </c>
       <c r="J113" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K113" s="18"/>
       <c r="L113" s="19"/>
@@ -4670,12 +4695,14 @@
       <c r="G114" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H114" s="21"/>
+      <c r="H114" s="21">
+        <v>22222222</v>
+      </c>
       <c r="I114" s="21" t="s">
-        <v>25</v>
+        <v>99</v>
       </c>
       <c r="J114" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K114" s="18"/>
       <c r="L114" s="18"/>
@@ -4699,12 +4726,14 @@
       <c r="G115" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="H115" s="21"/>
+      <c r="H115" s="21">
+        <v>11111111</v>
+      </c>
       <c r="I115" s="21" t="s">
-        <v>27</v>
+        <v>100</v>
       </c>
       <c r="J115" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="116" s="4" customFormat="1" spans="1:14">
@@ -4725,10 +4754,14 @@
       <c r="G116" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="H116" s="21"/>
-      <c r="I116" s="21"/>
+      <c r="H116" s="21">
+        <v>5000000</v>
+      </c>
+      <c r="I116" s="21" t="s">
+        <v>101</v>
+      </c>
       <c r="J116" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K116" s="18"/>
       <c r="L116" s="19"/>
@@ -4751,10 +4784,14 @@
       <c r="G117" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="H117" s="21"/>
-      <c r="I117" s="21"/>
+      <c r="H117" s="21">
+        <v>3000000</v>
+      </c>
+      <c r="I117" s="21" t="s">
+        <v>101</v>
+      </c>
       <c r="J117" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K117" s="18"/>
       <c r="L117" s="19"/>
@@ -4780,7 +4817,7 @@
       <c r="H118" s="21"/>
       <c r="I118" s="21"/>
       <c r="J118" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K118" s="18"/>
       <c r="L118" s="19"/>
@@ -4806,7 +4843,7 @@
       <c r="H119" s="21"/>
       <c r="I119" s="21"/>
       <c r="J119" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K119" s="18"/>
       <c r="L119" s="19"/>
@@ -4832,7 +4869,7 @@
       <c r="H120" s="21"/>
       <c r="I120" s="21"/>
       <c r="J120" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K120" s="18"/>
       <c r="L120" s="18"/>
@@ -4858,7 +4895,7 @@
       <c r="H121" s="21"/>
       <c r="I121" s="21"/>
       <c r="J121" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K121" s="18"/>
     </row>
@@ -4883,7 +4920,7 @@
       <c r="H122" s="21"/>
       <c r="I122" s="21"/>
       <c r="J122" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K122" s="18"/>
     </row>
@@ -4908,7 +4945,7 @@
       <c r="H123" s="21"/>
       <c r="I123" s="21"/>
       <c r="J123" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K123" s="18"/>
     </row>
@@ -4933,7 +4970,7 @@
       <c r="H124" s="21"/>
       <c r="I124" s="21"/>
       <c r="J124" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K124" s="18"/>
     </row>
@@ -4958,7 +4995,7 @@
       <c r="H125" s="21"/>
       <c r="I125" s="21"/>
       <c r="J125" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K125" s="18"/>
     </row>
@@ -4983,7 +5020,7 @@
       <c r="H126" s="21"/>
       <c r="I126" s="21"/>
       <c r="J126" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K126" s="18"/>
     </row>
@@ -5008,7 +5045,7 @@
       <c r="H127" s="21"/>
       <c r="I127" s="21"/>
       <c r="J127" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K127" s="18"/>
     </row>
@@ -5033,7 +5070,7 @@
       <c r="H128" s="21"/>
       <c r="I128" s="21"/>
       <c r="J128" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K128" s="18"/>
     </row>
@@ -5058,7 +5095,7 @@
       <c r="H129" s="21"/>
       <c r="I129" s="21"/>
       <c r="J129" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K129" s="18"/>
     </row>
@@ -5083,7 +5120,7 @@
       <c r="H130" s="21"/>
       <c r="I130" s="21"/>
       <c r="J130" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K130" s="18"/>
     </row>
@@ -5108,7 +5145,7 @@
       <c r="H131" s="21"/>
       <c r="I131" s="21"/>
       <c r="J131" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K131" s="18"/>
     </row>
@@ -5133,7 +5170,7 @@
       <c r="H132" s="21"/>
       <c r="I132" s="21"/>
       <c r="J132" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K132" s="18"/>
     </row>
@@ -5158,7 +5195,7 @@
       <c r="H133" s="21"/>
       <c r="I133" s="21"/>
       <c r="J133" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K133" s="18"/>
     </row>
@@ -5183,7 +5220,7 @@
       <c r="H134" s="21"/>
       <c r="I134" s="21"/>
       <c r="J134" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K134" s="18"/>
     </row>
@@ -5208,7 +5245,7 @@
       <c r="H135" s="21"/>
       <c r="I135" s="21"/>
       <c r="J135" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K135" s="18"/>
     </row>
@@ -5233,7 +5270,7 @@
       <c r="H136" s="21"/>
       <c r="I136" s="21"/>
       <c r="J136" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K136" s="18"/>
     </row>
@@ -5258,7 +5295,7 @@
       <c r="H137" s="21"/>
       <c r="I137" s="21"/>
       <c r="J137" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K137" s="18"/>
     </row>
@@ -5283,7 +5320,7 @@
       <c r="H138" s="21"/>
       <c r="I138" s="21"/>
       <c r="J138" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K138" s="18"/>
     </row>
@@ -5308,7 +5345,7 @@
       <c r="H139" s="21"/>
       <c r="I139" s="21"/>
       <c r="J139" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K139" s="18"/>
     </row>
@@ -5330,12 +5367,14 @@
       <c r="G140" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="H140" s="21"/>
+      <c r="H140" s="21">
+        <v>99999999</v>
+      </c>
       <c r="I140" s="21" t="s">
-        <v>23</v>
+        <v>97</v>
       </c>
       <c r="J140" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K140" s="18"/>
     </row>
@@ -5357,12 +5396,14 @@
       <c r="G141" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="H141" s="21"/>
+      <c r="H141" s="21">
+        <v>88888888</v>
+      </c>
       <c r="I141" s="21" t="s">
-        <v>25</v>
+        <v>99</v>
       </c>
       <c r="J141" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K141" s="18"/>
     </row>
@@ -5384,12 +5425,14 @@
       <c r="G142" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="H142" s="21"/>
+      <c r="H142" s="21">
+        <v>77777777</v>
+      </c>
       <c r="I142" s="21" t="s">
-        <v>27</v>
+        <v>100</v>
       </c>
       <c r="J142" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K142" s="18"/>
     </row>
@@ -5411,10 +5454,14 @@
       <c r="G143" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="H143" s="21"/>
-      <c r="I143" s="21"/>
+      <c r="H143" s="21">
+        <v>66666666</v>
+      </c>
+      <c r="I143" s="21" t="s">
+        <v>101</v>
+      </c>
       <c r="J143" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K143" s="18"/>
     </row>
@@ -5436,10 +5483,14 @@
       <c r="G144" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="H144" s="21"/>
-      <c r="I144" s="21"/>
+      <c r="H144" s="21">
+        <v>55555555</v>
+      </c>
+      <c r="I144" s="21" t="s">
+        <v>101</v>
+      </c>
       <c r="J144" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K144" s="18"/>
     </row>
@@ -5464,7 +5515,7 @@
       <c r="H145" s="21"/>
       <c r="I145" s="21"/>
       <c r="J145" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K145" s="18"/>
     </row>
@@ -5489,7 +5540,7 @@
       <c r="H146" s="21"/>
       <c r="I146" s="21"/>
       <c r="J146" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K146" s="18"/>
     </row>
@@ -5514,7 +5565,7 @@
       <c r="H147" s="21"/>
       <c r="I147" s="21"/>
       <c r="J147" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K147" s="18"/>
     </row>
@@ -5539,7 +5590,7 @@
       <c r="H148" s="21"/>
       <c r="I148" s="21"/>
       <c r="J148" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K148" s="18"/>
     </row>
@@ -5564,7 +5615,7 @@
       <c r="H149" s="21"/>
       <c r="I149" s="21"/>
       <c r="J149" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K149" s="18"/>
     </row>
@@ -5589,7 +5640,7 @@
       <c r="H150" s="21"/>
       <c r="I150" s="21"/>
       <c r="J150" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K150" s="18"/>
     </row>
@@ -5614,7 +5665,7 @@
       <c r="H151" s="21"/>
       <c r="I151" s="21"/>
       <c r="J151" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="152" spans="1:11">
@@ -5638,7 +5689,7 @@
       <c r="H152" s="21"/>
       <c r="I152" s="21"/>
       <c r="J152" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="153" spans="1:11">
@@ -5662,7 +5713,7 @@
       <c r="H153" s="21"/>
       <c r="I153" s="21"/>
       <c r="J153" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="154" spans="1:11">
@@ -5675,8 +5726,6 @@
       <c r="C154" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="D154" s="23"/>
-      <c r="E154" s="23"/>
       <c r="F154" s="22" t="s">
         <v>21</v>
       </c>
@@ -5686,7 +5735,7 @@
       <c r="H154" s="21"/>
       <c r="I154" s="21"/>
       <c r="J154" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="155" spans="1:11">
@@ -5699,8 +5748,6 @@
       <c r="C155" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="D155" s="23"/>
-      <c r="E155" s="23"/>
       <c r="F155" s="22" t="s">
         <v>21</v>
       </c>
@@ -5710,7 +5757,7 @@
       <c r="H155" s="21"/>
       <c r="I155" s="21"/>
       <c r="J155" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="156" spans="1:11">
@@ -5723,8 +5770,6 @@
       <c r="C156" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="D156" s="23"/>
-      <c r="E156" s="23"/>
       <c r="F156" s="22" t="s">
         <v>21</v>
       </c>
@@ -5734,7 +5779,7 @@
       <c r="H156" s="21"/>
       <c r="I156" s="21"/>
       <c r="J156" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="157" spans="1:11">
@@ -5747,8 +5792,6 @@
       <c r="C157" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="D157" s="23"/>
-      <c r="E157" s="23"/>
       <c r="F157" s="22" t="s">
         <v>21</v>
       </c>
@@ -5758,7 +5801,7 @@
       <c r="H157" s="21"/>
       <c r="I157" s="21"/>
       <c r="J157" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="158" spans="1:11">
@@ -5771,8 +5814,6 @@
       <c r="C158" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="D158" s="23"/>
-      <c r="E158" s="23"/>
       <c r="F158" s="22" t="s">
         <v>21</v>
       </c>
@@ -5782,7 +5823,7 @@
       <c r="H158" s="21"/>
       <c r="I158" s="21"/>
       <c r="J158" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="159" spans="1:11">
@@ -5795,8 +5836,6 @@
       <c r="C159" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="D159" s="23"/>
-      <c r="E159" s="23"/>
       <c r="F159" s="22" t="s">
         <v>21</v>
       </c>
@@ -5806,7 +5845,7 @@
       <c r="H159" s="21"/>
       <c r="I159" s="21"/>
       <c r="J159" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="160" spans="1:11">
@@ -5819,8 +5858,6 @@
       <c r="C160" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="D160" s="23"/>
-      <c r="E160" s="23"/>
       <c r="F160" s="22" t="s">
         <v>21</v>
       </c>
@@ -5830,7 +5867,7 @@
       <c r="H160" s="21"/>
       <c r="I160" s="21"/>
       <c r="J160" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="161" spans="1:10">
@@ -5843,8 +5880,6 @@
       <c r="C161" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="D161" s="23"/>
-      <c r="E161" s="23"/>
       <c r="F161" s="22" t="s">
         <v>21</v>
       </c>
@@ -5854,7 +5889,7 @@
       <c r="H161" s="21"/>
       <c r="I161" s="21"/>
       <c r="J161" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="162" spans="1:10">
@@ -5867,8 +5902,6 @@
       <c r="C162" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="D162" s="23"/>
-      <c r="E162" s="23"/>
       <c r="F162" s="22" t="s">
         <v>21</v>
       </c>
@@ -5878,7 +5911,7 @@
       <c r="H162" s="21"/>
       <c r="I162" s="21"/>
       <c r="J162" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="163" spans="1:10">
@@ -5891,8 +5924,6 @@
       <c r="C163" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="D163" s="23"/>
-      <c r="E163" s="23"/>
       <c r="F163" s="22" t="s">
         <v>21</v>
       </c>
@@ -5902,7 +5933,7 @@
       <c r="H163" s="21"/>
       <c r="I163" s="21"/>
       <c r="J163" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="164" spans="1:10">
@@ -5915,8 +5946,6 @@
       <c r="C164" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="D164" s="23"/>
-      <c r="E164" s="23"/>
       <c r="F164" s="22" t="s">
         <v>21</v>
       </c>
@@ -5926,7 +5955,7 @@
       <c r="H164" s="21"/>
       <c r="I164" s="21"/>
       <c r="J164" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="165" spans="1:10">
@@ -5939,8 +5968,6 @@
       <c r="C165" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="D165" s="23"/>
-      <c r="E165" s="23"/>
       <c r="F165" s="22" t="s">
         <v>21</v>
       </c>
@@ -5950,7 +5977,7 @@
       <c r="H165" s="21"/>
       <c r="I165" s="21"/>
       <c r="J165" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="166" spans="1:10">
@@ -5963,8 +5990,6 @@
       <c r="C166" s="22" t="s">
         <v>71</v>
       </c>
-      <c r="D166" s="23"/>
-      <c r="E166" s="23"/>
       <c r="F166" s="22" t="s">
         <v>21</v>
       </c>
@@ -5974,7 +5999,7 @@
       <c r="H166" s="21"/>
       <c r="I166" s="21"/>
       <c r="J166" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -6011,34 +6036,34 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="R1" s="1">
         <v>50</v>
@@ -6081,30 +6106,30 @@
       </c>
       <c r="K2" s="1">
         <f ca="1" t="shared" ref="K2:O2" si="4">RAND()</f>
-        <v>0.816183286213281</v>
+        <v>0.0259208143240577</v>
       </c>
       <c r="L2" s="1">
         <f ca="1" t="shared" ref="L2:P2" si="5">J2+$R$1*K2/MAX(1,($A2*($A2-1)))++$R$1/$A2</f>
-        <v>1140.80916431066</v>
+        <v>1101.2960407162</v>
       </c>
       <c r="M2" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>0.224176597207967</v>
+        <v>0.616528769787779</v>
       </c>
       <c r="N2" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>1202.01799417106</v>
+        <v>1182.12247920559</v>
       </c>
       <c r="O2" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>0.392322832471508</v>
+        <v>0.235092717854201</v>
       </c>
       <c r="P2" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>1271.63413579464</v>
+        <v>1243.8771150983</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="R2" s="1">
         <v>1</v>
@@ -6147,30 +6172,30 @@
       </c>
       <c r="K3" s="1">
         <f ca="1" t="shared" ref="K3:O3" si="6">RAND()</f>
-        <v>0.439008271570802</v>
+        <v>0.642058514706658</v>
       </c>
       <c r="L3" s="1">
         <f ca="1" t="shared" ref="L3:P3" si="7">J3+$R$1*K3/MAX(1,($A3*($A3-1)))++$R$1/$A3</f>
-        <v>335.97520678927</v>
+        <v>341.051462867666</v>
       </c>
       <c r="M3" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>0.534055166913635</v>
+        <v>0.545843418453009</v>
       </c>
       <c r="N3" s="1">
         <f ca="1" t="shared" si="7"/>
-        <v>374.326585962111</v>
+        <v>379.697548328992</v>
       </c>
       <c r="O3" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>0.849880224124062</v>
+        <v>0.811542046855817</v>
       </c>
       <c r="P3" s="1">
         <f ca="1" t="shared" si="7"/>
-        <v>420.573591565212</v>
+        <v>424.986099500387</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="R3" s="1">
         <v>30</v>
@@ -6213,30 +6238,30 @@
       </c>
       <c r="K4" s="1">
         <f ca="1" t="shared" ref="K4:O4" si="8">RAND()</f>
-        <v>0.248106901434934</v>
+        <v>0.733399523674593</v>
       </c>
       <c r="L4" s="1">
         <f ca="1" t="shared" ref="L4:P4" si="9">J4+$R$1*K4/MAX(1,($A4*($A4-1)))++$R$1/$A4</f>
-        <v>318.734224178624</v>
+        <v>322.778329363955</v>
       </c>
       <c r="M4" s="1">
         <f ca="1" t="shared" si="8"/>
-        <v>0.0215654732939499</v>
+        <v>0.197439253783861</v>
       </c>
       <c r="N4" s="1">
         <f ca="1" t="shared" si="9"/>
-        <v>335.580603122741</v>
+        <v>341.090323145487</v>
       </c>
       <c r="O4" s="1">
         <f ca="1" t="shared" si="8"/>
-        <v>0.694202077048308</v>
+        <v>0.832324778558032</v>
       </c>
       <c r="P4" s="1">
         <f ca="1" t="shared" si="9"/>
-        <v>358.032287098143</v>
+        <v>364.693029633471</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="R4" s="1">
         <f>24*60/R3</f>
@@ -6280,30 +6305,30 @@
       </c>
       <c r="K5" s="1">
         <f ca="1" t="shared" ref="K5:O5" si="10">RAND()</f>
-        <v>0.113481989811328</v>
+        <v>0.281974666187661</v>
       </c>
       <c r="L5" s="1">
         <f ca="1" t="shared" ref="L5:P5" si="11">J5+$R$1*K5/MAX(1,($A5*($A5-1)))++$R$1/$A5</f>
-        <v>162.972841624214</v>
+        <v>163.674894442449</v>
       </c>
       <c r="M5" s="1">
         <f ca="1" t="shared" si="10"/>
-        <v>0.660395992139216</v>
+        <v>0.543647312379003</v>
       </c>
       <c r="N5" s="1">
         <f ca="1" t="shared" si="11"/>
-        <v>178.224491591461</v>
+        <v>178.440091577361</v>
       </c>
       <c r="O5" s="1">
         <f ca="1" t="shared" si="10"/>
-        <v>0.98717294959106</v>
+        <v>0.656658814252148</v>
       </c>
       <c r="P5" s="1">
         <f ca="1" t="shared" si="11"/>
-        <v>194.837712214757</v>
+        <v>193.676169970078</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="R5" s="1">
         <v>6500</v>
@@ -6346,30 +6371,30 @@
       </c>
       <c r="K6" s="1">
         <f ca="1" t="shared" ref="K6:O6" si="12">RAND()</f>
-        <v>0.795876842518287</v>
+        <v>0.162884797559768</v>
       </c>
       <c r="L6" s="1">
         <f ca="1" t="shared" ref="L6:P6" si="13">J6+$R$1*K6/MAX(1,($A6*($A6-1)))++$R$1/$A6</f>
-        <v>161.989692106296</v>
+        <v>160.407211993899</v>
       </c>
       <c r="M6" s="1">
         <f ca="1" t="shared" si="12"/>
-        <v>0.697130138072451</v>
+        <v>0.284581693997958</v>
       </c>
       <c r="N6" s="1">
         <f ca="1" t="shared" si="13"/>
-        <v>173.732517451477</v>
+        <v>171.118666228894</v>
       </c>
       <c r="O6" s="1">
         <f ca="1" t="shared" si="12"/>
-        <v>0.819606043124285</v>
+        <v>0.98191942442169</v>
       </c>
       <c r="P6" s="1">
         <f ca="1" t="shared" si="13"/>
-        <v>185.781532559288</v>
+        <v>183.573464789949</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="R6" s="1">
         <f>R5/R4</f>
@@ -7781,27 +7806,27 @@
       </c>
       <c r="K31" s="1">
         <f ca="1" t="shared" ref="K31:O31" si="39">RAND()</f>
-        <v>0.949075059305236</v>
+        <v>0.0967208005162257</v>
       </c>
       <c r="L31" s="1">
         <f ca="1" t="shared" ref="L31:P31" si="40">J31+$R$1*K31/MAX(1,($A31*($A31-1)))++$R$1/$A31</f>
-        <v>22.4108663827187</v>
+        <v>22.3618805057768</v>
       </c>
       <c r="M31" s="1">
         <f ca="1" t="shared" si="39"/>
-        <v>0.0542003799881181</v>
+        <v>0.448708758551681</v>
       </c>
       <c r="N31" s="1">
         <f ca="1" t="shared" si="40"/>
-        <v>24.0806480137525</v>
+        <v>24.0543350321303</v>
       </c>
       <c r="O31" s="1">
         <f ca="1" t="shared" si="39"/>
-        <v>0.783768319687715</v>
+        <v>0.277728470404801</v>
       </c>
       <c r="P31" s="1">
         <f ca="1" t="shared" si="40"/>
-        <v>25.7923588367231</v>
+        <v>25.7369631051421</v>
       </c>
     </row>
     <row r="32" ht="16.5" spans="1:16">
@@ -8069,27 +8094,27 @@
       </c>
       <c r="K36" s="1">
         <f ca="1" t="shared" ref="K36:O36" si="45">RAND()</f>
-        <v>0.901376199713249</v>
+        <v>0.311153057333273</v>
       </c>
       <c r="L36" s="1">
         <f ca="1" t="shared" ref="L36:P36" si="46">J36+$R$1*K36/MAX(1,($A36*($A36-1)))++$R$1/$A36</f>
-        <v>19.1135032016686</v>
+        <v>19.088703909972</v>
       </c>
       <c r="M36" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.830665005243266</v>
+        <v>0.0888939408753595</v>
       </c>
       <c r="N36" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>20.5769765212166</v>
+        <v>20.521010378076</v>
       </c>
       <c r="O36" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.432229608780747</v>
+        <v>0.117025872305315</v>
       </c>
       <c r="P36" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>22.02370885772</v>
+        <v>21.9544988601056</v>
       </c>
     </row>
     <row r="37" ht="16.5" spans="1:16">
@@ -8129,27 +8154,27 @@
       </c>
       <c r="K37" s="1">
         <f ca="1" t="shared" ref="K37:O37" si="47">RAND()</f>
-        <v>0.0225498032988156</v>
+        <v>0.29536002553011</v>
       </c>
       <c r="L37" s="1">
         <f ca="1" t="shared" ref="L37:P37" si="48">J37+$R$1*K37/MAX(1,($A37*($A37-1)))++$R$1/$A37</f>
-        <v>18.5326408652102</v>
+        <v>18.5434666676798</v>
       </c>
       <c r="M37" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.205981672207753</v>
+        <v>0.31099270299798</v>
       </c>
       <c r="N37" s="1">
         <f ca="1" t="shared" si="48"/>
-        <v>19.9297036299804</v>
+        <v>19.9446965368464</v>
       </c>
       <c r="O37" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.0797426207330985</v>
+        <v>0.436192380041265</v>
       </c>
       <c r="P37" s="1">
         <f ca="1" t="shared" si="48"/>
-        <v>21.3217569085809</v>
+        <v>21.3508946471655</v>
       </c>
     </row>
     <row r="38" ht="16.5" spans="1:16">
@@ -8189,27 +8214,27 @@
       </c>
       <c r="K38" s="1">
         <f ca="1" t="shared" ref="K38:O38" si="49">RAND()</f>
-        <v>0.453949731680878</v>
+        <v>0.272156454142164</v>
       </c>
       <c r="L38" s="1">
         <f ca="1" t="shared" ref="L38:P38" si="50">J38+$R$1*K38/MAX(1,($A38*($A38-1)))++$R$1/$A38</f>
-        <v>18.0350581731112</v>
+        <v>18.0282341011315</v>
       </c>
       <c r="M38" s="1">
         <f ca="1" t="shared" si="49"/>
-        <v>0.77971454652506</v>
+        <v>0.0339165234993521</v>
       </c>
       <c r="N38" s="1">
         <f ca="1" t="shared" si="50"/>
-        <v>19.4156780885213</v>
+        <v>19.3808585952568</v>
       </c>
       <c r="O38" s="1">
         <f ca="1" t="shared" si="49"/>
-        <v>0.0150306605572645</v>
+        <v>0.989297118732469</v>
       </c>
       <c r="P38" s="1">
         <f ca="1" t="shared" si="50"/>
-        <v>20.7675936538575</v>
+        <v>20.7693457243384</v>
       </c>
     </row>
     <row r="39" ht="16.5" spans="1:16">
@@ -8249,27 +8274,27 @@
       </c>
       <c r="K39" s="1">
         <f ca="1" t="shared" ref="K39:O39" si="51">RAND()</f>
-        <v>0.203753320168378</v>
+        <v>0.251789636035714</v>
       </c>
       <c r="L39" s="1">
         <f ca="1" t="shared" ref="L39:P39" si="52">J39+$R$1*K39/MAX(1,($A39*($A39-1)))++$R$1/$A39</f>
-        <v>17.5392515405465</v>
+        <v>17.540959802135</v>
       </c>
       <c r="M39" s="1">
         <f ca="1" t="shared" si="51"/>
-        <v>0.403609233573458</v>
+        <v>0.356041334280435</v>
       </c>
       <c r="N39" s="1">
         <f ca="1" t="shared" si="52"/>
-        <v>18.8693941164204</v>
+        <v>18.8694107741933</v>
       </c>
       <c r="O39" s="1">
         <f ca="1" t="shared" si="51"/>
-        <v>0.892908018769496</v>
+        <v>0.447860070300623</v>
       </c>
       <c r="P39" s="1">
         <f ca="1" t="shared" si="52"/>
-        <v>20.2169370758361</v>
+        <v>20.2011269929096</v>
       </c>
     </row>
     <row r="40" ht="16.5" spans="1:16">
@@ -8309,27 +8334,27 @@
       </c>
       <c r="K40" s="1">
         <f ca="1" t="shared" ref="K40:O40" si="53">RAND()</f>
-        <v>0.341556422898264</v>
+        <v>0.0995314381813581</v>
       </c>
       <c r="L40" s="1">
         <f ca="1" t="shared" ref="L40:P40" si="54">J40+$R$1*K40/MAX(1,($A40*($A40-1)))++$R$1/$A40</f>
-        <v>17.083048462311</v>
+        <v>17.0748829769967</v>
       </c>
       <c r="M40" s="1">
         <f ca="1" t="shared" si="53"/>
-        <v>0.0976756490240525</v>
+        <v>0.342596253256693</v>
       </c>
       <c r="N40" s="1">
         <f ca="1" t="shared" si="54"/>
-        <v>18.3683951441269</v>
+        <v>18.3684928370931</v>
       </c>
       <c r="O40" s="1">
         <f ca="1" t="shared" si="53"/>
-        <v>0.153097371006048</v>
+        <v>0.854492457796838</v>
       </c>
       <c r="P40" s="1">
         <f ca="1" t="shared" si="54"/>
-        <v>19.6556116546197</v>
+        <v>19.6793731494344</v>
       </c>
     </row>
     <row r="41" ht="16.5" spans="1:16">
@@ -8369,27 +8394,27 @@
       </c>
       <c r="K41" s="1">
         <f ca="1" t="shared" ref="K41:O41" si="55">RAND()</f>
-        <v>0.747372638900624</v>
+        <v>0.349504771847821</v>
       </c>
       <c r="L41" s="1">
         <f ca="1" t="shared" ref="L41:P41" si="56">J41+$R$1*K41/MAX(1,($A41*($A41-1)))++$R$1/$A41</f>
-        <v>16.6585696358622</v>
+        <v>16.6458174606361</v>
       </c>
       <c r="M41" s="1">
         <f ca="1" t="shared" si="55"/>
-        <v>0.443272978515616</v>
+        <v>0.592535980618994</v>
       </c>
       <c r="N41" s="1">
         <f ca="1" t="shared" si="56"/>
-        <v>17.9227771031223</v>
+        <v>17.9148089984765</v>
       </c>
       <c r="O41" s="1">
         <f ca="1" t="shared" si="55"/>
-        <v>0.531959370886758</v>
+        <v>0.119392905479516</v>
       </c>
       <c r="P41" s="1">
         <f ca="1" t="shared" si="56"/>
-        <v>19.1898270829584</v>
+        <v>19.1686356941649</v>
       </c>
     </row>
     <row r="42" ht="16.5" spans="1:16">
@@ -8429,27 +8454,27 @@
       </c>
       <c r="K42" s="1">
         <f ca="1" t="shared" ref="K42:O42" si="57">RAND()</f>
-        <v>0.388149333156535</v>
+        <v>0.99678651018773</v>
       </c>
       <c r="L42" s="1">
         <f ca="1" t="shared" ref="L42:P42" si="58">J42+$R$1*K42/MAX(1,($A42*($A42-1)))++$R$1/$A42</f>
-        <v>16.2313460162548</v>
+        <v>16.2499020277496</v>
       </c>
       <c r="M42" s="1">
         <f ca="1" t="shared" si="57"/>
-        <v>0.740554041428543</v>
+        <v>0.581346274772516</v>
       </c>
       <c r="N42" s="1">
         <f ca="1" t="shared" si="58"/>
-        <v>17.4734360784934</v>
+        <v>17.4871381946634</v>
       </c>
       <c r="O42" s="1">
         <f ca="1" t="shared" si="57"/>
-        <v>0.102471034649306</v>
+        <v>0.974452457449112</v>
       </c>
       <c r="P42" s="1">
         <f ca="1" t="shared" si="58"/>
-        <v>18.6960723905254</v>
+        <v>18.736359306171</v>
       </c>
     </row>
     <row r="43" ht="16.5" spans="1:16">
@@ -8489,27 +8514,27 @@
       </c>
       <c r="K43" s="1">
         <f ca="1" t="shared" ref="K43:O43" si="59">RAND()</f>
-        <v>0.0704419139434409</v>
+        <v>0.722922380038765</v>
       </c>
       <c r="L43" s="1">
         <f ca="1" t="shared" ref="L43:P43" si="60">J43+$R$1*K43/MAX(1,($A43*($A43-1)))++$R$1/$A43</f>
-        <v>15.8266678836801</v>
+        <v>15.8456133095249</v>
       </c>
       <c r="M43" s="1">
         <f ca="1" t="shared" si="59"/>
-        <v>0.803343488300972</v>
+        <v>0.230081126590797</v>
       </c>
       <c r="N43" s="1">
         <f ca="1" t="shared" si="60"/>
-        <v>17.0404699594147</v>
+        <v>17.0427701366617</v>
       </c>
       <c r="O43" s="1">
         <f ca="1" t="shared" si="59"/>
-        <v>0.552877881174804</v>
+        <v>0.0918041872616333</v>
       </c>
       <c r="P43" s="1">
         <f ca="1" t="shared" si="60"/>
-        <v>18.2469995146173</v>
+        <v>18.2359119539457</v>
       </c>
     </row>
     <row r="44" ht="16.5" spans="1:16">
@@ -8549,27 +8574,27 @@
       </c>
       <c r="K44" s="1">
         <f ca="1" t="shared" ref="K44:O44" si="61">RAND()</f>
-        <v>0.0573570945425994</v>
+        <v>0.954954721612753</v>
       </c>
       <c r="L44" s="1">
         <f ca="1" t="shared" ref="L44:P44" si="62">J44+$R$1*K44/MAX(1,($A44*($A44-1)))++$R$1/$A44</f>
-        <v>15.4500929428168</v>
+        <v>15.4749433754599</v>
       </c>
       <c r="M44" s="1">
         <f ca="1" t="shared" si="61"/>
-        <v>0.10200067550006</v>
+        <v>0.283306525924844</v>
       </c>
       <c r="N44" s="1">
         <f ca="1" t="shared" si="62"/>
-        <v>16.6157075794586</v>
+        <v>16.6455775539185</v>
       </c>
       <c r="O44" s="1">
         <f ca="1" t="shared" si="61"/>
-        <v>0.671670320002679</v>
+        <v>0.919771391185308</v>
       </c>
       <c r="P44" s="1">
         <f ca="1" t="shared" si="62"/>
-        <v>17.7970938009426</v>
+        <v>17.8338325758229</v>
       </c>
     </row>
     <row r="45" ht="16.5" spans="1:16">
@@ -8609,27 +8634,27 @@
       </c>
       <c r="K45" s="1">
         <f ca="1" t="shared" ref="K45:O45" si="63">RAND()</f>
-        <v>0.863024300709164</v>
+        <v>0.947485353364613</v>
       </c>
       <c r="L45" s="1">
         <f ca="1" t="shared" ref="L45:P45" si="64">J45+$R$1*K45/MAX(1,($A45*($A45-1)))++$R$1/$A45</f>
-        <v>15.1126592045642</v>
+        <v>15.1148912619811</v>
       </c>
       <c r="M45" s="1">
         <f ca="1" t="shared" si="63"/>
-        <v>0.284319774663767</v>
+        <v>0.0903219565601399</v>
       </c>
       <c r="N45" s="1">
         <f ca="1" t="shared" si="64"/>
-        <v>16.2565365770447</v>
+        <v>16.2536418422285</v>
       </c>
       <c r="O45" s="1">
         <f ca="1" t="shared" si="63"/>
-        <v>0.0596387256844793</v>
+        <v>0.970490533394766</v>
       </c>
       <c r="P45" s="1">
         <f ca="1" t="shared" si="64"/>
-        <v>17.3944762896685</v>
+        <v>17.4156526914197</v>
       </c>
     </row>
     <row r="46" ht="16.5" spans="1:16">
@@ -8669,27 +8694,27 @@
       </c>
       <c r="K46" s="1">
         <f ca="1" t="shared" ref="K46:O46" si="65">RAND()</f>
-        <v>0.985853375371285</v>
+        <v>0.86894854826434</v>
       </c>
       <c r="L46" s="1">
         <f ca="1" t="shared" ref="L46:P46" si="66">J46+$R$1*K46/MAX(1,($A46*($A46-1)))++$R$1/$A46</f>
-        <v>14.7723700347316</v>
+        <v>14.7694178926329</v>
       </c>
       <c r="M46" s="1">
         <f ca="1" t="shared" si="65"/>
-        <v>0.251335398585788</v>
+        <v>0.939554941644274</v>
       </c>
       <c r="N46" s="1">
         <f ca="1" t="shared" si="66"/>
-        <v>15.8898279993423</v>
+        <v>15.9042551386341</v>
       </c>
       <c r="O46" s="1">
         <f ca="1" t="shared" si="65"/>
-        <v>0.00627655796000703</v>
+        <v>0.116322616219509</v>
       </c>
       <c r="P46" s="1">
         <f ca="1" t="shared" si="66"/>
-        <v>17.0010976093918</v>
+        <v>17.0183036895487</v>
       </c>
     </row>
     <row r="47" ht="16.5" spans="1:16">
@@ -8729,27 +8754,27 @@
       </c>
       <c r="K47" s="1">
         <f ca="1" t="shared" ref="K47:O47" si="67">RAND()</f>
-        <v>0.0638825235358458</v>
+        <v>0.197668293583851</v>
       </c>
       <c r="L47" s="1">
         <f ca="1" t="shared" ref="L47:P47" si="68">J47+$R$1*K47/MAX(1,($A47*($A47-1)))++$R$1/$A47</f>
-        <v>14.4218329111965</v>
+        <v>14.4250644515358</v>
       </c>
       <c r="M47" s="1">
         <f ca="1" t="shared" si="67"/>
-        <v>0.263710393349165</v>
+        <v>0.340857838308714</v>
       </c>
       <c r="N47" s="1">
         <f ca="1" t="shared" si="68"/>
-        <v>15.5151592492001</v>
+        <v>15.5202542543935</v>
       </c>
       <c r="O47" s="1">
         <f ca="1" t="shared" si="67"/>
-        <v>0.159870507737641</v>
+        <v>0.978509659483502</v>
       </c>
       <c r="P47" s="1">
         <f ca="1" t="shared" si="68"/>
-        <v>16.6059773774063</v>
+        <v>16.630846275154</v>
       </c>
     </row>
     <row r="48" ht="16.5" spans="1:16">
@@ -8789,27 +8814,27 @@
       </c>
       <c r="K48" s="1">
         <f ca="1" t="shared" ref="K48:O48" si="69">RAND()</f>
-        <v>0.917284534919631</v>
+        <v>0.0912851377057509</v>
       </c>
       <c r="L48" s="1">
         <f ca="1" t="shared" ref="L48:P48" si="70">J48+$R$1*K48/MAX(1,($A48*($A48-1)))++$R$1/$A48</f>
-        <v>14.1285218440084</v>
+        <v>14.1094191752476</v>
       </c>
       <c r="M48" s="1">
         <f ca="1" t="shared" si="69"/>
-        <v>0.528647329160902</v>
+        <v>0.653056223431998</v>
       </c>
       <c r="N48" s="1">
         <f ca="1" t="shared" si="70"/>
-        <v>15.2045775176707</v>
+        <v>15.1883520203778</v>
       </c>
       <c r="O48" s="1">
         <f ca="1" t="shared" si="69"/>
-        <v>0.970285229320827</v>
+        <v>0.449332412948018</v>
       </c>
       <c r="P48" s="1">
         <f ca="1" t="shared" si="70"/>
-        <v>16.2908468337975</v>
+        <v>16.2625733990307</v>
       </c>
     </row>
     <row r="49" ht="16.5" spans="1:16">
@@ -8849,27 +8874,27 @@
       </c>
       <c r="K49" s="1">
         <f ca="1" t="shared" ref="K49:O49" si="71">RAND()</f>
-        <v>0.222334643267628</v>
+        <v>0.292643916167011</v>
       </c>
       <c r="L49" s="1">
         <f ca="1" t="shared" ref="L49:P49" si="72">J49+$R$1*K49/MAX(1,($A49*($A49-1)))++$R$1/$A49</f>
-        <v>13.8125517429802</v>
+        <v>13.8141100158725</v>
       </c>
       <c r="M49" s="1">
         <f ca="1" t="shared" si="71"/>
-        <v>0.957547264286712</v>
+        <v>0.352652237806029</v>
       </c>
       <c r="N49" s="1">
         <f ca="1" t="shared" si="72"/>
-        <v>14.8754406451142</v>
+        <v>14.863592556604</v>
       </c>
       <c r="O49" s="1">
         <f ca="1" t="shared" si="71"/>
-        <v>0.370630625976557</v>
+        <v>0.0642356659017287</v>
       </c>
       <c r="P49" s="1">
         <f ca="1" t="shared" si="72"/>
-        <v>15.9253216430304</v>
+        <v>15.9066828860788</v>
       </c>
     </row>
     <row r="50" ht="16.5" spans="1:16">
@@ -8909,27 +8934,27 @@
       </c>
       <c r="K50" s="1">
         <f ca="1" t="shared" ref="K50:O50" si="73">RAND()</f>
-        <v>0.358524759852181</v>
+        <v>0.462891257286927</v>
       </c>
       <c r="L50" s="1">
         <f ca="1" t="shared" ref="L50:P50" si="74">J50+$R$1*K50/MAX(1,($A50*($A50-1)))++$R$1/$A50</f>
-        <v>13.5280298630921</v>
+        <v>13.5302485386328</v>
       </c>
       <c r="M50" s="1">
         <f ca="1" t="shared" si="73"/>
-        <v>0.187529376043008</v>
+        <v>0.584558934852071</v>
       </c>
       <c r="N50" s="1">
         <f ca="1" t="shared" si="74"/>
-        <v>14.5524246202359</v>
+        <v>14.563083550003</v>
       </c>
       <c r="O50" s="1">
         <f ca="1" t="shared" si="73"/>
-        <v>0.882426679749641</v>
+        <v>0.93634825546527</v>
       </c>
       <c r="P50" s="1">
         <f ca="1" t="shared" si="74"/>
-        <v>15.5915918540741</v>
+        <v>15.6033970758419</v>
       </c>
     </row>
     <row r="51" ht="16.5" spans="1:16">
@@ -8969,27 +8994,27 @@
       </c>
       <c r="K51" s="1">
         <f ca="1" t="shared" ref="K51:O51" si="75">RAND()</f>
-        <v>0.609682005254878</v>
+        <v>0.508518477789458</v>
       </c>
       <c r="L51" s="1">
         <f ca="1" t="shared" ref="L51:P51" si="76">J51+$R$1*K51/MAX(1,($A51*($A51-1)))++$R$1/$A51</f>
-        <v>13.2573404490869</v>
+        <v>13.2552758873018</v>
       </c>
       <c r="M51" s="1">
         <f ca="1" t="shared" si="75"/>
-        <v>0.183344110382654</v>
+        <v>0.649880051636582</v>
       </c>
       <c r="N51" s="1">
         <f ca="1" t="shared" si="76"/>
-        <v>14.2610821656253</v>
+        <v>14.2685387454985</v>
       </c>
       <c r="O51" s="1">
         <f ca="1" t="shared" si="75"/>
-        <v>0.526782935281393</v>
+        <v>0.591106114221508</v>
       </c>
       <c r="P51" s="1">
         <f ca="1" t="shared" si="76"/>
-        <v>15.2718328377739</v>
+        <v>15.2806021355846</v>
       </c>
     </row>
     <row r="52" ht="16.5" spans="1:16">
@@ -9029,27 +9054,27 @@
       </c>
       <c r="K52" s="1">
         <f ca="1" t="shared" ref="K52:O52" si="77">RAND()</f>
-        <v>0.976043246877303</v>
+        <v>0.45599822262234</v>
       </c>
       <c r="L52" s="1">
         <f ca="1" t="shared" ref="L52:P52" si="78">J52+$R$1*K52/MAX(1,($A52*($A52-1)))++$R$1/$A52</f>
-        <v>12.9995302597427</v>
+        <v>12.9893332984828</v>
       </c>
       <c r="M52" s="1">
         <f ca="1" t="shared" si="77"/>
-        <v>0.778143790862758</v>
+        <v>0.29857410657279</v>
       </c>
       <c r="N52" s="1">
         <f ca="1" t="shared" si="78"/>
-        <v>13.9951801379949</v>
+        <v>13.9755798495921</v>
       </c>
       <c r="O52" s="1">
         <f ca="1" t="shared" si="77"/>
-        <v>0.277154781091727</v>
+        <v>0.329089972449196</v>
       </c>
       <c r="P52" s="1">
         <f ca="1" t="shared" si="78"/>
-        <v>14.98100670233</v>
+        <v>14.9624247510126</v>
       </c>
     </row>
     <row r="53" ht="16.5" spans="1:16">
@@ -9089,27 +9114,27 @@
       </c>
       <c r="K53" s="1">
         <f ca="1" t="shared" ref="K53:O53" si="79">RAND()</f>
-        <v>0.955895957190924</v>
+        <v>0.138150228296106</v>
       </c>
       <c r="L53" s="1">
         <f ca="1" t="shared" ref="L53:P53" si="80">J53+$R$1*K53/MAX(1,($A53*($A53-1)))++$R$1/$A53</f>
-        <v>12.74426651503</v>
+        <v>12.7288489862047</v>
       </c>
       <c r="M53" s="1">
         <f ca="1" t="shared" si="79"/>
-        <v>0.973384399024627</v>
+        <v>0.563233938239164</v>
       </c>
       <c r="N53" s="1">
         <f ca="1" t="shared" si="80"/>
-        <v>13.724156869461</v>
+        <v>13.701006488811</v>
       </c>
       <c r="O53" s="1">
         <f ca="1" t="shared" si="79"/>
-        <v>0.335297555088612</v>
+        <v>0.869757202540743</v>
       </c>
       <c r="P53" s="1">
         <f ca="1" t="shared" si="80"/>
-        <v>14.6920169289461</v>
+        <v>14.6789430876523</v>
       </c>
     </row>
     <row r="54" ht="16.5" spans="1:16">
@@ -9263,27 +9288,27 @@
       </c>
       <c r="K56" s="1">
         <f ca="1" t="shared" ref="K56:O56" si="83">RAND()</f>
-        <v>0.238528396258783</v>
+        <v>0.250745951446983</v>
       </c>
       <c r="L56" s="1">
         <f ca="1" t="shared" ref="L56:P56" si="84">J56+$R$1*K56/MAX(1,($A56*($A56-1)))++$R$1/$A56</f>
-        <v>12.0242176497687</v>
+        <v>12.0244233325159</v>
       </c>
       <c r="M56" s="1">
         <f ca="1" t="shared" si="83"/>
-        <v>0.309452156591731</v>
+        <v>0.223556750853385</v>
       </c>
       <c r="N56" s="1">
         <f ca="1" t="shared" si="84"/>
-        <v>12.9385181911254</v>
+        <v>12.937277823271</v>
       </c>
       <c r="O56" s="1">
         <f ca="1" t="shared" si="83"/>
-        <v>0.710845230387937</v>
+        <v>0.596105019148938</v>
       </c>
       <c r="P56" s="1">
         <f ca="1" t="shared" si="84"/>
-        <v>13.859576191637</v>
+        <v>13.8564041703948</v>
       </c>
     </row>
     <row r="57" ht="16.5" spans="1:16">
@@ -9323,27 +9348,27 @@
       </c>
       <c r="K57" s="1">
         <f ca="1" t="shared" ref="K57:O57" si="85">RAND()</f>
-        <v>0.576767502105547</v>
+        <v>0.962047566684816</v>
       </c>
       <c r="L57" s="1">
         <f ca="1" t="shared" ref="L57:P57" si="86">J57+$R$1*K57/MAX(1,($A57*($A57-1)))++$R$1/$A57</f>
-        <v>11.8113111607485</v>
+        <v>11.8175657072514</v>
       </c>
       <c r="M57" s="1">
         <f ca="1" t="shared" si="85"/>
-        <v>0.188817814245969</v>
+        <v>0.637920487431689</v>
       </c>
       <c r="N57" s="1">
         <f ca="1" t="shared" si="86"/>
-        <v>12.7072335278628</v>
+        <v>12.7207787021772</v>
       </c>
       <c r="O57" s="1">
         <f ca="1" t="shared" si="85"/>
-        <v>0.674658131529615</v>
+        <v>0.490869545945595</v>
       </c>
       <c r="P57" s="1">
         <f ca="1" t="shared" si="86"/>
-        <v>13.6110429131149</v>
+        <v>13.6216045064945</v>
       </c>
     </row>
     <row r="58" ht="16.5" spans="1:16">
@@ -9383,27 +9408,27 @@
       </c>
       <c r="K58" s="1">
         <f ca="1" t="shared" ref="K58:O58" si="87">RAND()</f>
-        <v>0.299030887163281</v>
+        <v>0.954701629868488</v>
       </c>
       <c r="L58" s="1">
         <f ca="1" t="shared" ref="L58:P58" si="88">J58+$R$1*K58/MAX(1,($A58*($A58-1)))++$R$1/$A58</f>
-        <v>11.5961627645232</v>
+        <v>11.6064332962072</v>
       </c>
       <c r="M58" s="1">
         <f ca="1" t="shared" si="87"/>
-        <v>0.115320494040202</v>
+        <v>0.00104380673915427</v>
       </c>
       <c r="N58" s="1">
         <f ca="1" t="shared" si="88"/>
-        <v>12.4751621456955</v>
+        <v>12.4836426290195</v>
       </c>
       <c r="O58" s="1">
         <f ca="1" t="shared" si="87"/>
-        <v>0.0141786351823994</v>
+        <v>0.230674039046092</v>
       </c>
       <c r="P58" s="1">
         <f ca="1" t="shared" si="88"/>
-        <v>13.3525772245674</v>
+        <v>13.3644489266236</v>
       </c>
     </row>
     <row r="59" ht="16.5" spans="1:16">
@@ -9443,27 +9468,27 @@
       </c>
       <c r="K59" s="1">
         <f ca="1" t="shared" ref="K59:O59" si="89">RAND()</f>
-        <v>0.176199690308285</v>
+        <v>0.489704951255368</v>
       </c>
       <c r="L59" s="1">
         <f ca="1" t="shared" ref="L59:P59" si="90">J59+$R$1*K59/MAX(1,($A59*($A59-1)))++$R$1/$A59</f>
-        <v>11.3910496020918</v>
+        <v>11.3957910609688</v>
       </c>
       <c r="M59" s="1">
         <f ca="1" t="shared" si="89"/>
-        <v>0.874591502756476</v>
+        <v>0.433388545263016</v>
       </c>
       <c r="N59" s="1">
         <f ca="1" t="shared" si="90"/>
-        <v>12.2663459043113</v>
+        <v>12.2644146021857</v>
       </c>
       <c r="O59" s="1">
         <f ca="1" t="shared" si="89"/>
-        <v>0.587819849369956</v>
+        <v>0.709852136754094</v>
       </c>
       <c r="P59" s="1">
         <f ca="1" t="shared" si="90"/>
-        <v>13.1373050671875</v>
+        <v>13.1372193834433</v>
       </c>
     </row>
     <row r="60" ht="16.5" spans="1:16">
@@ -9503,27 +9528,27 @@
       </c>
       <c r="K60" s="1">
         <f ca="1" t="shared" ref="K60:O60" si="91">RAND()</f>
-        <v>0.363385008828885</v>
+        <v>0.357662246792222</v>
       </c>
       <c r="L60" s="1">
         <f ca="1" t="shared" ref="L60:P60" si="92">J60+$R$1*K60/MAX(1,($A60*($A60-1)))++$R$1/$A60</f>
-        <v>11.1975947546585</v>
+        <v>11.1975111374458</v>
       </c>
       <c r="M60" s="1">
         <f ca="1" t="shared" si="91"/>
-        <v>0.163219420572725</v>
+        <v>0.580649172100631</v>
       </c>
       <c r="N60" s="1">
         <f ca="1" t="shared" si="92"/>
-        <v>12.0474372359644</v>
+        <v>12.0534528261089</v>
       </c>
       <c r="O60" s="1">
         <f ca="1" t="shared" si="91"/>
-        <v>0.879152714737619</v>
+        <v>0.877194210126674</v>
       </c>
       <c r="P60" s="1">
         <f ca="1" t="shared" si="92"/>
-        <v>12.9077404609021</v>
+        <v>12.913727434673</v>
       </c>
     </row>
     <row r="61" ht="16.5" spans="1:16">
@@ -9563,27 +9588,27 @@
       </c>
       <c r="K61" s="1">
         <f ca="1" t="shared" ref="K61:O61" si="93">RAND()</f>
-        <v>0.982371338371249</v>
+        <v>0.320828526655423</v>
       </c>
       <c r="L61" s="1">
         <f ca="1" t="shared" ref="L61:P61" si="94">J61+$R$1*K61/MAX(1,($A61*($A61-1)))++$R$1/$A61</f>
-        <v>11.0167001601465</v>
+        <v>11.0073563351223</v>
       </c>
       <c r="M61" s="1">
         <f ca="1" t="shared" si="93"/>
-        <v>0.0206072356353579</v>
+        <v>0.954598846465882</v>
       </c>
       <c r="N61" s="1">
         <f ca="1" t="shared" si="94"/>
-        <v>11.85032455613</v>
+        <v>11.8541727030102</v>
       </c>
       <c r="O61" s="1">
         <f ca="1" t="shared" si="93"/>
-        <v>0.598507004948683</v>
+        <v>0.036162413558319</v>
       </c>
       <c r="P61" s="1">
         <f ca="1" t="shared" si="94"/>
-        <v>12.6921113782338</v>
+        <v>12.6880168048966</v>
       </c>
     </row>
     <row r="62" ht="16.5" spans="1:16">
@@ -9623,27 +9648,27 @@
       </c>
       <c r="K62" s="1">
         <f ca="1" t="shared" ref="K62:O62" si="95">RAND()</f>
-        <v>0.107720843854193</v>
+        <v>0.292914699823084</v>
       </c>
       <c r="L62" s="1">
         <f ca="1" t="shared" ref="L62:P62" si="96">J62+$R$1*K62/MAX(1,($A62*($A62-1)))++$R$1/$A62</f>
-        <v>10.8211437273751</v>
+        <v>10.823673698085</v>
       </c>
       <c r="M62" s="1">
         <f ca="1" t="shared" si="95"/>
-        <v>0.236239281134709</v>
+        <v>0.813383894259287</v>
       </c>
       <c r="N62" s="1">
         <f ca="1" t="shared" si="96"/>
-        <v>11.6440431711064</v>
+        <v>11.6544576310667</v>
       </c>
       <c r="O62" s="1">
         <f ca="1" t="shared" si="95"/>
-        <v>0.728344249564206</v>
+        <v>0.00589061449918038</v>
       </c>
       <c r="P62" s="1">
         <f ca="1" t="shared" si="96"/>
-        <v>12.4736653603081</v>
+        <v>12.4742102350899</v>
       </c>
     </row>
     <row r="63" ht="16.5" spans="1:16">
@@ -9683,27 +9708,27 @@
       </c>
       <c r="K63" s="1">
         <f ca="1" t="shared" ref="K63:O63" si="97">RAND()</f>
-        <v>0.630225026736764</v>
+        <v>0.34418245948752</v>
       </c>
       <c r="L63" s="1">
         <f ca="1" t="shared" ref="L63:P63" si="98">J63+$R$1*K63/MAX(1,($A63*($A63-1)))++$R$1/$A63</f>
-        <v>10.6508490881377</v>
+        <v>10.6470674571587</v>
       </c>
       <c r="M63" s="1">
         <f ca="1" t="shared" si="97"/>
-        <v>0.829719330858715</v>
+        <v>0.506912520152858</v>
       </c>
       <c r="N63" s="1">
         <f ca="1" t="shared" si="98"/>
-        <v>11.4682700205922</v>
+        <v>11.4602207162829</v>
       </c>
       <c r="O63" s="1">
         <f ca="1" t="shared" si="97"/>
-        <v>0.551673421651819</v>
+        <v>0.812096815633903</v>
       </c>
       <c r="P63" s="1">
         <f ca="1" t="shared" si="98"/>
-        <v>12.2820150420313</v>
+        <v>12.2774086699534</v>
       </c>
     </row>
     <row r="64" ht="16.5" spans="1:16">
@@ -9743,27 +9768,27 @@
       </c>
       <c r="K64" s="1">
         <f ca="1" t="shared" ref="K64:O64" si="99">RAND()</f>
-        <v>0.316160166155489</v>
+        <v>0.221902101084516</v>
       </c>
       <c r="L64" s="1">
         <f ca="1" t="shared" ref="L64:P64" si="100">J64+$R$1*K64/MAX(1,($A64*($A64-1)))++$R$1/$A64</f>
-        <v>10.4751172576313</v>
+        <v>10.4739106771772</v>
       </c>
       <c r="M64" s="1">
         <f ca="1" t="shared" si="99"/>
-        <v>0.872622382589964</v>
+        <v>0.115340715178015</v>
       </c>
       <c r="N64" s="1">
         <f ca="1" t="shared" si="100"/>
-        <v>11.2799383326772</v>
+        <v>11.2690379264755</v>
       </c>
       <c r="O64" s="1">
         <f ca="1" t="shared" si="99"/>
-        <v>0.839854450767654</v>
+        <v>0.539840104719847</v>
       </c>
       <c r="P64" s="1">
         <f ca="1" t="shared" si="100"/>
-        <v>12.0843399513507</v>
+        <v>12.069599115732</v>
       </c>
     </row>
     <row r="65" ht="16.5" spans="1:16">
@@ -9803,27 +9828,27 @@
       </c>
       <c r="K65" s="1">
         <f ca="1" t="shared" ref="K65:O65" si="101">RAND()</f>
-        <v>0.536074587596445</v>
+        <v>0.664277473241323</v>
       </c>
       <c r="L65" s="1">
         <f ca="1" t="shared" ref="L65:P65" si="102">J65+$R$1*K65/MAX(1,($A65*($A65-1)))++$R$1/$A65</f>
-        <v>10.3117072741517</v>
+        <v>10.3132970916821</v>
       </c>
       <c r="M65" s="1">
         <f ca="1" t="shared" si="101"/>
-        <v>0.811016406939302</v>
+        <v>0.137117689924259</v>
       </c>
       <c r="N65" s="1">
         <f ca="1" t="shared" si="102"/>
-        <v>11.1030145212616</v>
+        <v>11.0962474598607</v>
       </c>
       <c r="O65" s="1">
         <f ca="1" t="shared" si="101"/>
-        <v>0.306478819907076</v>
+        <v>0.54058717372212</v>
       </c>
       <c r="P65" s="1">
         <f ca="1" t="shared" si="102"/>
-        <v>11.8880651018656</v>
+        <v>11.8842011698523</v>
       </c>
     </row>
     <row r="66" ht="16.5" spans="1:16">
@@ -9863,27 +9888,27 @@
       </c>
       <c r="K66" s="1">
         <f ca="1" t="shared" ref="K66:O66" si="106">RAND()</f>
-        <v>0.879230280011452</v>
+        <v>0.422352666634542</v>
       </c>
       <c r="L66" s="1">
         <f ca="1" t="shared" ref="L66:P66" si="107">J66+$R$1*K66/MAX(1,($A66*($A66-1)))++$R$1/$A66</f>
-        <v>10.1547984408655</v>
+        <v>10.1493071233971</v>
       </c>
       <c r="M66" s="1">
         <f ca="1" t="shared" si="106"/>
-        <v>0.0757285120322477</v>
+        <v>0.12984397532311</v>
       </c>
       <c r="N66" s="1">
         <f ca="1" t="shared" si="107"/>
-        <v>10.9249394085582</v>
+        <v>10.9200985173312</v>
       </c>
       <c r="O66" s="1">
         <f ca="1" t="shared" si="106"/>
-        <v>0.291629548201985</v>
+        <v>0.784110312170466</v>
       </c>
       <c r="P66" s="1">
         <f ca="1" t="shared" si="107"/>
-        <v>11.697675340628</v>
+        <v>11.6987536893525</v>
       </c>
     </row>
     <row r="67" ht="16.5" spans="1:16">
@@ -9923,27 +9948,27 @@
       </c>
       <c r="K67" s="1">
         <f ca="1" t="shared" ref="K67:O67" si="108">RAND()</f>
-        <v>0.0621229473248055</v>
+        <v>0.116063482558666</v>
       </c>
       <c r="L67" s="1">
         <f ca="1" t="shared" ref="L67:P67" si="109">J67+$R$1*K67/MAX(1,($A67*($A67-1)))++$R$1/$A67</f>
-        <v>9.9890690320201</v>
+        <v>9.98969770958693</v>
       </c>
       <c r="M67" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.151786549342834</v>
+        <v>0.0276004189768104</v>
       </c>
       <c r="N67" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>10.7484138635975</v>
+        <v>10.7475951503675</v>
       </c>
       <c r="O67" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.163349017963036</v>
+        <v>0.465378016613301</v>
       </c>
       <c r="P67" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>11.5078934558815</v>
+        <v>11.5105948941509</v>
       </c>
     </row>
     <row r="68" ht="16.5" spans="1:16">
@@ -9983,27 +10008,27 @@
       </c>
       <c r="K68" s="1">
         <f ca="1" t="shared" ref="K68:O68" si="110">RAND()</f>
-        <v>0.0832016202171213</v>
+        <v>0.793003984059914</v>
       </c>
       <c r="L68" s="1">
         <f ca="1" t="shared" ref="L68:P68" si="111">J68+$R$1*K68/MAX(1,($A68*($A68-1)))++$R$1/$A68</f>
-        <v>9.83811851673696</v>
+        <v>9.84614432365513</v>
       </c>
       <c r="M68" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.257709859327856</v>
+        <v>0.208661737534123</v>
       </c>
       <c r="N68" s="1">
         <f ca="1" t="shared" si="111"/>
-        <v>10.5873011248252</v>
+        <v>10.5947723396833</v>
       </c>
       <c r="O68" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.396013975588541</v>
+        <v>0.721242081299206</v>
       </c>
       <c r="P68" s="1">
         <f ca="1" t="shared" si="111"/>
-        <v>11.3380475515054</v>
+        <v>11.349196153357</v>
       </c>
     </row>
     <row r="69" ht="16.5" spans="1:16">
@@ -10043,27 +10068,27 @@
       </c>
       <c r="K69" s="1">
         <f ca="1" t="shared" ref="K69:O69" si="112">RAND()</f>
-        <v>0.235391599021674</v>
+        <v>0.80717506717012</v>
       </c>
       <c r="L69" s="1">
         <f ca="1" t="shared" ref="L69:P69" si="113">J69+$R$1*K69/MAX(1,($A69*($A69-1)))++$R$1/$A69</f>
-        <v>9.69310131254413</v>
+        <v>9.69937637255454</v>
       </c>
       <c r="M69" s="1">
         <f ca="1" t="shared" si="112"/>
-        <v>0.187009232662606</v>
+        <v>0.848772732615186</v>
       </c>
       <c r="N69" s="1">
         <f ca="1" t="shared" si="113"/>
-        <v>10.4304477703214</v>
+        <v>10.4439853797167</v>
       </c>
       <c r="O69" s="1">
         <f ca="1" t="shared" si="112"/>
-        <v>0.435395476167456</v>
+        <v>0.337533111330811</v>
       </c>
       <c r="P69" s="1">
         <f ca="1" t="shared" si="113"/>
-        <v>11.1705201526323</v>
+        <v>11.1829837676813</v>
       </c>
     </row>
     <row r="70" ht="16.5" spans="1:16">
@@ -10103,27 +10128,27 @@
       </c>
       <c r="K70" s="1">
         <f ca="1" t="shared" ref="K70:O70" si="114">RAND()</f>
-        <v>0.537174930079317</v>
+        <v>0.711114505187117</v>
       </c>
       <c r="L70" s="1">
         <f ca="1" t="shared" ref="L70:P70" si="115">J70+$R$1*K70/MAX(1,($A70*($A70-1)))++$R$1/$A70</f>
-        <v>9.55389146344927</v>
+        <v>9.55574503948409</v>
       </c>
       <c r="M70" s="1">
         <f ca="1" t="shared" si="114"/>
-        <v>0.383153057817261</v>
+        <v>0.86293008520673</v>
       </c>
       <c r="N70" s="1">
         <f ca="1" t="shared" si="115"/>
-        <v>10.2826121908344</v>
+        <v>10.2895784802898</v>
       </c>
       <c r="O70" s="1">
         <f ca="1" t="shared" si="114"/>
-        <v>0.0494511995502229</v>
+        <v>0.39636066566757</v>
       </c>
       <c r="P70" s="1">
         <f ca="1" t="shared" si="115"/>
-        <v>11.007776845561</v>
+        <v>11.0184399537091</v>
       </c>
     </row>
     <row r="71" ht="16.5" spans="1:16">
@@ -10163,27 +10188,27 @@
       </c>
       <c r="K71" s="1">
         <f ca="1" t="shared" ref="K71:O71" si="116">RAND()</f>
-        <v>0.451528294435207</v>
+        <v>0.510480766377873</v>
       </c>
       <c r="L71" s="1">
         <f ca="1" t="shared" ref="L71:P71" si="117">J71+$R$1*K71/MAX(1,($A71*($A71-1)))++$R$1/$A71</f>
-        <v>9.41461209414529</v>
+        <v>9.41522236818196</v>
       </c>
       <c r="M71" s="1">
         <f ca="1" t="shared" si="116"/>
-        <v>0.0941078967374904</v>
+        <v>0.862697263335984</v>
       </c>
       <c r="N71" s="1">
         <f ca="1" t="shared" si="117"/>
-        <v>10.1298720102606</v>
+        <v>10.1384386959598</v>
       </c>
       <c r="O71" s="1">
         <f ca="1" t="shared" si="116"/>
-        <v>0.32933752950083</v>
+        <v>0.986463050341222</v>
       </c>
       <c r="P71" s="1">
         <f ca="1" t="shared" si="117"/>
-        <v>10.847567015742</v>
+        <v>10.8629362430648</v>
       </c>
     </row>
     <row r="72" ht="16.5" spans="1:16">
@@ -10223,27 +10248,27 @@
       </c>
       <c r="K72" s="1">
         <f ca="1" t="shared" ref="K72:O72" si="118">RAND()</f>
-        <v>0.254373136504336</v>
+        <v>0.829420391893495</v>
       </c>
       <c r="L72" s="1">
         <f ca="1" t="shared" ref="L72:P72" si="119">J72+$R$1*K72/MAX(1,($A72*($A72-1)))++$R$1/$A72</f>
-        <v>9.27821300942157</v>
+        <v>9.2839981930774</v>
       </c>
       <c r="M72" s="1">
         <f ca="1" t="shared" si="118"/>
-        <v>0.654524023152058</v>
+        <v>0.345993731583923</v>
       </c>
       <c r="N72" s="1">
         <f ca="1" t="shared" si="119"/>
-        <v>9.98902311025811</v>
+        <v>9.99170436743941</v>
       </c>
       <c r="O72" s="1">
         <f ca="1" t="shared" si="118"/>
-        <v>0.55723419657592</v>
+        <v>0.405272883621372</v>
       </c>
       <c r="P72" s="1">
         <f ca="1" t="shared" si="119"/>
-        <v>10.6988544402035</v>
+        <v>10.7000069115402</v>
       </c>
     </row>
     <row r="73" ht="16.5" spans="1:16">
@@ -10283,27 +10308,27 @@
       </c>
       <c r="K73" s="1">
         <f ca="1" t="shared" ref="K73:O73" si="120">RAND()</f>
-        <v>0.3082357185735</v>
+        <v>0.310725889539223</v>
       </c>
       <c r="L73" s="1">
         <f ca="1" t="shared" ref="L73:P73" si="121">J73+$R$1*K73/MAX(1,($A73*($A73-1)))++$R$1/$A73</f>
-        <v>9.14816349489997</v>
+        <v>9.14818785103227</v>
       </c>
       <c r="M73" s="1">
         <f ca="1" t="shared" si="120"/>
-        <v>0.120953986586239</v>
+        <v>0.990286944852194</v>
       </c>
       <c r="N73" s="1">
         <f ca="1" t="shared" si="121"/>
-        <v>9.84379097911932</v>
+        <v>9.85231820064937</v>
       </c>
       <c r="O73" s="1">
         <f ca="1" t="shared" si="120"/>
-        <v>0.880377745747247</v>
+        <v>0.607969753897316</v>
       </c>
       <c r="P73" s="1">
         <f ca="1" t="shared" si="121"/>
-        <v>10.5468463170081</v>
+        <v>10.5527091411218</v>
       </c>
     </row>
     <row r="74" ht="16.5" spans="1:16">
@@ -10343,27 +10368,27 @@
       </c>
       <c r="K74" s="1">
         <f ca="1" t="shared" ref="K74:O74" si="122">RAND()</f>
-        <v>0.645538643745291</v>
+        <v>0.473592346170097</v>
       </c>
       <c r="L74" s="1">
         <f ca="1" t="shared" ref="L74:P74" si="123">J74+$R$1*K74/MAX(1,($A74*($A74-1)))++$R$1/$A74</f>
-        <v>9.02440580901584</v>
+        <v>9.02277009461729</v>
       </c>
       <c r="M74" s="1">
         <f ca="1" t="shared" si="122"/>
-        <v>0.73577912987757</v>
+        <v>0.485499004476773</v>
       </c>
       <c r="N74" s="1">
         <f ca="1" t="shared" si="123"/>
-        <v>9.71633673681148</v>
+        <v>9.7123201231987</v>
       </c>
       <c r="O74" s="1">
         <f ca="1" t="shared" si="122"/>
-        <v>0.298553000673609</v>
+        <v>0.206941219710501</v>
       </c>
       <c r="P74" s="1">
         <f ca="1" t="shared" si="123"/>
-        <v>10.404108359725</v>
+        <v>10.399220248957</v>
       </c>
     </row>
     <row r="75" ht="16.5" spans="1:16">
@@ -10517,27 +10542,27 @@
       </c>
       <c r="K77" s="1">
         <f ca="1" t="shared" ref="K77:O77" si="127">RAND()</f>
-        <v>0.908666444176373</v>
+        <v>0.609462606608179</v>
       </c>
       <c r="L77" s="1">
         <f ca="1" t="shared" ref="L77:P77" si="128">J77+$R$1*K77/MAX(1,($A77*($A77-1)))++$R$1/$A77</f>
-        <v>8.66586549512435</v>
+        <v>8.66324090005797</v>
       </c>
       <c r="M77" s="1">
         <f ca="1" t="shared" si="127"/>
-        <v>0.525592987613641</v>
+        <v>0.270461364211288</v>
       </c>
       <c r="N77" s="1">
         <f ca="1" t="shared" si="128"/>
-        <v>9.32837069677009</v>
+        <v>9.32350810500719</v>
       </c>
       <c r="O77" s="1">
         <f ca="1" t="shared" si="127"/>
-        <v>0.882750612430578</v>
+        <v>0.483830270242076</v>
       </c>
       <c r="P77" s="1">
         <f ca="1" t="shared" si="128"/>
-        <v>9.99400886003702</v>
+        <v>9.98564696702686</v>
       </c>
     </row>
     <row r="78" ht="16.5" spans="1:16">
@@ -10577,27 +10602,27 @@
       </c>
       <c r="K78" s="1">
         <f ca="1" t="shared" ref="K78:O78" si="129">RAND()</f>
-        <v>0.480501511784591</v>
+        <v>0.65595379700631</v>
       </c>
       <c r="L78" s="1">
         <f ca="1" t="shared" ref="L78:P78" si="130">J78+$R$1*K78/MAX(1,($A78*($A78-1)))++$R$1/$A78</f>
-        <v>8.54819293841237</v>
+        <v>8.54969201808789</v>
       </c>
       <c r="M78" s="1">
         <f ca="1" t="shared" si="129"/>
-        <v>0.839714498195246</v>
+        <v>0.110659019333865</v>
       </c>
       <c r="N78" s="1">
         <f ca="1" t="shared" si="130"/>
-        <v>9.20471818190345</v>
+        <v>9.19998814778144</v>
       </c>
       <c r="O78" s="1">
         <f ca="1" t="shared" si="129"/>
-        <v>0.814921332720053</v>
+        <v>0.6154491607344</v>
       </c>
       <c r="P78" s="1">
         <f ca="1" t="shared" si="130"/>
-        <v>9.86103159041951</v>
+        <v>9.85459724860795</v>
       </c>
     </row>
     <row r="79" ht="16.5" spans="1:16">
@@ -10637,27 +10662,27 @@
       </c>
       <c r="K79" s="1">
         <f ca="1" t="shared" ref="K79:O79" si="131">RAND()</f>
-        <v>0.336690869957127</v>
+        <v>0.520200098862502</v>
       </c>
       <c r="L79" s="1">
         <f ca="1" t="shared" ref="L79:P79" si="132">J79+$R$1*K79/MAX(1,($A79*($A79-1)))++$R$1/$A79</f>
-        <v>8.43603638752878</v>
+        <v>8.43756410338714</v>
       </c>
       <c r="M79" s="1">
         <f ca="1" t="shared" si="131"/>
-        <v>0.100366274804318</v>
+        <v>0.644903391085741</v>
       </c>
       <c r="N79" s="1">
         <f ca="1" t="shared" si="132"/>
-        <v>9.07789757862771</v>
+        <v>9.08395857051239</v>
       </c>
       <c r="O79" s="1">
         <f ca="1" t="shared" si="131"/>
-        <v>0.971244534126548</v>
+        <v>0.972413028235047</v>
       </c>
       <c r="P79" s="1">
         <f ca="1" t="shared" si="132"/>
-        <v>9.72700883848558</v>
+        <v>9.73307955809343</v>
       </c>
     </row>
     <row r="80" ht="16.5" spans="1:16">
@@ -10697,27 +10722,27 @@
       </c>
       <c r="K80" s="1">
         <f ca="1" t="shared" ref="K80:O80" si="133">RAND()</f>
-        <v>0.863557987828934</v>
+        <v>0.144062079330552</v>
       </c>
       <c r="L80" s="1">
         <f ca="1" t="shared" ref="L80:P80" si="134">J80+$R$1*K80/MAX(1,($A80*($A80-1)))++$R$1/$A80</f>
-        <v>8.33222620892428</v>
+        <v>8.32638804024124</v>
       </c>
       <c r="M80" s="1">
         <f ca="1" t="shared" si="133"/>
-        <v>0.889971532346015</v>
+        <v>0.732216321102323</v>
       </c>
       <c r="N80" s="1">
         <f ca="1" t="shared" si="134"/>
-        <v>8.97235905160804</v>
+        <v>8.96524081791977</v>
       </c>
       <c r="O80" s="1">
         <f ca="1" t="shared" si="133"/>
-        <v>0.0949073880809694</v>
+        <v>0.35173430895447</v>
       </c>
       <c r="P80" s="1">
         <f ca="1" t="shared" si="134"/>
-        <v>9.60604054615592</v>
+        <v>9.60100626995608</v>
       </c>
     </row>
     <row r="81" ht="16.5" spans="1:16">
@@ -10757,27 +10782,27 @@
       </c>
       <c r="K81" s="1">
         <f ca="1" t="shared" ref="K81:O81" si="135">RAND()</f>
-        <v>0.957160990690132</v>
+        <v>0.694101005915298</v>
       </c>
       <c r="L81" s="1">
         <f ca="1" t="shared" ref="L81:P81" si="136">J81+$R$1*K81/MAX(1,($A81*($A81-1)))++$R$1/$A81</f>
-        <v>8.22750918505293</v>
+        <v>8.22542801428731</v>
       </c>
       <c r="M81" s="1">
         <f ca="1" t="shared" si="135"/>
-        <v>0.290078294064353</v>
+        <v>0.366974324941202</v>
       </c>
       <c r="N81" s="1">
         <f ca="1" t="shared" si="136"/>
-        <v>8.85480410826546</v>
+        <v>8.8533312921745</v>
       </c>
       <c r="O81" s="1">
         <f ca="1" t="shared" si="135"/>
-        <v>0.354544735672425</v>
+        <v>0.52071070683963</v>
       </c>
       <c r="P81" s="1">
         <f ca="1" t="shared" si="136"/>
-        <v>9.48260905079452</v>
+        <v>9.48245083890582</v>
       </c>
     </row>
     <row r="82" ht="16.5" spans="1:16">
@@ -10817,27 +10842,27 @@
       </c>
       <c r="K82" s="1">
         <f ca="1" t="shared" ref="K82:O82" si="137">RAND()</f>
-        <v>0.942481516259535</v>
+        <v>0.150160322266386</v>
       </c>
       <c r="L82" s="1">
         <f ca="1" t="shared" ref="L82:P82" si="138">J82+$R$1*K82/MAX(1,($A82*($A82-1)))++$R$1/$A82</f>
-        <v>8.12455618453904</v>
+        <v>8.11844259507922</v>
       </c>
       <c r="M82" s="1">
         <f ca="1" t="shared" si="137"/>
-        <v>0.149150466413088</v>
+        <v>0.365240467508827</v>
       </c>
       <c r="N82" s="1">
         <f ca="1" t="shared" si="138"/>
-        <v>8.74299098752062</v>
+        <v>8.73854475918036</v>
       </c>
       <c r="O82" s="1">
         <f ca="1" t="shared" si="137"/>
-        <v>0.53402533378029</v>
+        <v>0.0608171508912438</v>
       </c>
       <c r="P82" s="1">
         <f ca="1" t="shared" si="138"/>
-        <v>9.36439550398497</v>
+        <v>9.35629797793724</v>
       </c>
     </row>
     <row r="83" ht="16.5" spans="1:16">
@@ -10877,27 +10902,27 @@
       </c>
       <c r="K83" s="1">
         <f ca="1" t="shared" ref="K83:O83" si="139">RAND()</f>
-        <v>0.36043049098472</v>
+        <v>0.413594471221387</v>
       </c>
       <c r="L83" s="1">
         <f ca="1" t="shared" ref="L83:P83" si="140">J83+$R$1*K83/MAX(1,($A83*($A83-1)))++$R$1/$A83</f>
-        <v>8.01987677274153</v>
+        <v>8.02027698337264</v>
       </c>
       <c r="M83" s="1">
         <f ca="1" t="shared" si="139"/>
-        <v>0.899537795894995</v>
+        <v>0.867458832949618</v>
       </c>
       <c r="N83" s="1">
         <f ca="1" t="shared" si="140"/>
-        <v>8.6364044586486</v>
+        <v>8.63656318356046</v>
       </c>
       <c r="O83" s="1">
         <f ca="1" t="shared" si="139"/>
-        <v>0.830967139246133</v>
+        <v>0.617973992491609</v>
       </c>
       <c r="P83" s="1">
         <f ca="1" t="shared" si="140"/>
-        <v>9.25241595472844</v>
+        <v>9.25097129852953</v>
       </c>
     </row>
     <row r="84" ht="16.5" spans="1:16">
@@ -10937,27 +10962,27 @@
       </c>
       <c r="K84" s="1">
         <f ca="1" t="shared" ref="K84:O84" si="141">RAND()</f>
-        <v>0.477031962793678</v>
+        <v>0.121038354914054</v>
       </c>
       <c r="L84" s="1">
         <f ca="1" t="shared" ref="L84:P84" si="142">J84+$R$1*K84/MAX(1,($A84*($A84-1)))++$R$1/$A84</f>
-        <v>7.92298730504551</v>
+        <v>7.92037201259855</v>
       </c>
       <c r="M84" s="1">
         <f ca="1" t="shared" si="141"/>
-        <v>0.509556887167194</v>
+        <v>0.929994245963429</v>
       </c>
       <c r="N84" s="1">
         <f ca="1" t="shared" si="142"/>
-        <v>8.52914038238291</v>
+        <v>8.52961381575725</v>
       </c>
       <c r="O84" s="1">
         <f ca="1" t="shared" si="141"/>
-        <v>0.632329190614911</v>
+        <v>0.610087232100242</v>
       </c>
       <c r="P84" s="1">
         <f ca="1" t="shared" si="142"/>
-        <v>9.13619540141475</v>
+        <v>9.13650543515264</v>
       </c>
     </row>
     <row r="85" ht="16.5" spans="1:16">
@@ -10997,27 +11022,27 @@
       </c>
       <c r="K85" s="1">
         <f ca="1" t="shared" ref="K85:O85" si="143">RAND()</f>
-        <v>0.00517069878615417</v>
+        <v>0.452532052232778</v>
       </c>
       <c r="L85" s="1">
         <f ca="1" t="shared" ref="L85:P85" si="144">J85+$R$1*K85/MAX(1,($A85*($A85-1)))++$R$1/$A85</f>
-        <v>7.82419083977901</v>
+        <v>7.82739911110322</v>
       </c>
       <c r="M85" s="1">
         <f ca="1" t="shared" si="143"/>
-        <v>0.184384392808018</v>
+        <v>0.949455270817597</v>
       </c>
       <c r="N85" s="1">
         <f ca="1" t="shared" si="144"/>
-        <v>8.42075125567695</v>
+        <v>8.4294462659427</v>
       </c>
       <c r="O85" s="1">
         <f ca="1" t="shared" si="143"/>
-        <v>0.226429562055273</v>
+        <v>0.105116187030152</v>
       </c>
       <c r="P85" s="1">
         <f ca="1" t="shared" si="144"/>
-        <v>9.01761320032737</v>
+        <v>9.02543820646931</v>
       </c>
     </row>
     <row r="86" ht="16.5" spans="1:16">
@@ -11057,27 +11082,27 @@
       </c>
       <c r="K86" s="1">
         <f ca="1" t="shared" ref="K86:O86" si="145">RAND()</f>
-        <v>0.672364482630485</v>
+        <v>0.951542069967869</v>
       </c>
       <c r="L86" s="1">
         <f ca="1" t="shared" ref="L86:P86" si="146">J86+$R$1*K86/MAX(1,($A86*($A86-1)))++$R$1/$A86</f>
-        <v>7.7358008717271</v>
+        <v>7.73775589684851</v>
       </c>
       <c r="M86" s="1">
         <f ca="1" t="shared" si="145"/>
-        <v>0.814084581937174</v>
+        <v>0.509286867680148</v>
       </c>
       <c r="N86" s="1">
         <f ca="1" t="shared" si="146"/>
-        <v>8.32973703826728</v>
+        <v>8.32955762561378</v>
       </c>
       <c r="O86" s="1">
         <f ca="1" t="shared" si="145"/>
-        <v>0.64932794447973</v>
+        <v>0.333409154044211</v>
       </c>
       <c r="P86" s="1">
         <f ca="1" t="shared" si="146"/>
-        <v>8.92251944684206</v>
+        <v>8.92012771772894</v>
       </c>
     </row>
     <row r="87" ht="16.5" spans="1:16">
@@ -11231,27 +11256,27 @@
       </c>
       <c r="K89" s="1">
         <f ca="1" t="shared" ref="K89:O89" si="149">RAND()</f>
-        <v>0.992515759561432</v>
+        <v>0.999690439092608</v>
       </c>
       <c r="L89" s="1">
         <f ca="1" t="shared" ref="L89:P89" si="150">J89+$R$1*K89/MAX(1,($A89*($A89-1)))++$R$1/$A89</f>
-        <v>7.47121548954781</v>
+        <v>7.47126234612783</v>
       </c>
       <c r="M89" s="1">
         <f ca="1" t="shared" si="149"/>
-        <v>0.511438568582007</v>
+        <v>0.410626201004421</v>
       </c>
       <c r="N89" s="1">
         <f ca="1" t="shared" si="150"/>
-        <v>8.04273742377314</v>
+        <v>8.04212589237263</v>
       </c>
       <c r="O89" s="1">
         <f ca="1" t="shared" si="149"/>
-        <v>0.336631886970153</v>
+        <v>0.274384719253801</v>
       </c>
       <c r="P89" s="1">
         <f ca="1" t="shared" si="150"/>
-        <v>8.61311772606527</v>
+        <v>8.61209966927476</v>
       </c>
     </row>
     <row r="90" ht="16.5" spans="1:16">
@@ -11291,27 +11316,27 @@
       </c>
       <c r="K90" s="1">
         <f ca="1" t="shared" ref="K90:O90" si="151">RAND()</f>
-        <v>0.252040224032516</v>
+        <v>0.99035656624007</v>
       </c>
       <c r="L90" s="1">
         <f ca="1" t="shared" ref="L90:P90" si="152">J90+$R$1*K90/MAX(1,($A90*($A90-1)))++$R$1/$A90</f>
-        <v>7.38158861225762</v>
+        <v>7.38630207205209</v>
       </c>
       <c r="M90" s="1">
         <f ca="1" t="shared" si="151"/>
-        <v>0.111339157713189</v>
+        <v>0.911885629987566</v>
       </c>
       <c r="N90" s="1">
         <f ca="1" t="shared" si="152"/>
-        <v>7.944097161528</v>
+        <v>7.95392136233547</v>
       </c>
       <c r="O90" s="1">
         <f ca="1" t="shared" si="151"/>
-        <v>0.112132179207351</v>
+        <v>0.31637724951607</v>
       </c>
       <c r="P90" s="1">
         <f ca="1" t="shared" si="152"/>
-        <v>8.50661077349945</v>
+        <v>8.51773888818784</v>
       </c>
     </row>
     <row r="91" ht="16.5" spans="1:16">
@@ -11351,27 +11376,27 @@
       </c>
       <c r="K91" s="1">
         <f ca="1" t="shared" ref="K91:O91" si="153">RAND()</f>
-        <v>0.391749662452552</v>
+        <v>0.951087001070644</v>
       </c>
       <c r="L91" s="1">
         <f ca="1" t="shared" ref="L91:P91" si="154">J91+$R$1*K91/MAX(1,($A91*($A91-1)))++$R$1/$A91</f>
-        <v>7.29957396793041</v>
+        <v>7.30306546192928</v>
       </c>
       <c r="M91" s="1">
         <f ca="1" t="shared" si="153"/>
-        <v>0.0461749782474896</v>
+        <v>0.595716379622113</v>
       </c>
       <c r="N91" s="1">
         <f ca="1" t="shared" si="154"/>
-        <v>7.85541775680836</v>
+        <v>7.86233959663354</v>
       </c>
       <c r="O91" s="1">
         <f ca="1" t="shared" si="153"/>
-        <v>0.909215152794394</v>
+        <v>0.481953573499023</v>
       </c>
       <c r="P91" s="1">
         <f ca="1" t="shared" si="154"/>
-        <v>8.41664881269347</v>
+        <v>8.42090360146187</v>
       </c>
     </row>
     <row r="92" ht="16.5" spans="1:16">
@@ -11411,27 +11436,27 @@
       </c>
       <c r="K92" s="1">
         <f ca="1" t="shared" ref="K92:O92" si="155">RAND()</f>
-        <v>0.435227951559306</v>
+        <v>0.207825961888096</v>
       </c>
       <c r="L92" s="1">
         <f ca="1" t="shared" ref="L92:P92" si="156">J92+$R$1*K92/MAX(1,($A92*($A92-1)))++$R$1/$A92</f>
-        <v>7.21877428541856</v>
+        <v>7.21738599488332</v>
       </c>
       <c r="M92" s="1">
         <f ca="1" t="shared" si="155"/>
-        <v>0.982030489703067</v>
+        <v>0.874879870443335</v>
       </c>
       <c r="N92" s="1">
         <f ca="1" t="shared" si="156"/>
-        <v>7.77422013700405</v>
+        <v>7.77217769128408</v>
       </c>
       <c r="O92" s="1">
         <f ca="1" t="shared" si="155"/>
-        <v>0.0275580913552955</v>
+        <v>0.645407831435425</v>
       </c>
       <c r="P92" s="1">
         <f ca="1" t="shared" si="156"/>
-        <v>8.32383892877056</v>
+        <v>8.32556845948576</v>
       </c>
     </row>
     <row r="93" ht="16.5" spans="1:16">
@@ -11471,27 +11496,27 @@
       </c>
       <c r="K93" s="1">
         <f ca="1" t="shared" ref="K93:O93" si="157">RAND()</f>
-        <v>0.17548769559197</v>
+        <v>0.978844558017969</v>
       </c>
       <c r="L93" s="1">
         <f ca="1" t="shared" ref="L93:P93" si="158">J93+$R$1*K93/MAX(1,($A93*($A93-1)))++$R$1/$A93</f>
-        <v>7.13793291743664</v>
+        <v>7.14273079645257</v>
       </c>
       <c r="M93" s="1">
         <f ca="1" t="shared" si="157"/>
-        <v>0.0323797095398477</v>
+        <v>0.665080316996187</v>
       </c>
       <c r="N93" s="1">
         <f ca="1" t="shared" si="158"/>
-        <v>7.68160455927575</v>
+        <v>7.69018110890477</v>
       </c>
       <c r="O93" s="1">
         <f ca="1" t="shared" si="157"/>
-        <v>0.635758358648453</v>
+        <v>0.391456053543648</v>
       </c>
       <c r="P93" s="1">
         <f ca="1" t="shared" si="158"/>
-        <v>8.22887975253094</v>
+        <v>8.23599725829287</v>
       </c>
     </row>
     <row r="94" ht="16.5" spans="1:16">
@@ -11531,27 +11556,27 @@
       </c>
       <c r="K94" s="1">
         <f ca="1" t="shared" ref="K94:O94" si="159">RAND()</f>
-        <v>0.117687989812941</v>
+        <v>0.952203965750061</v>
       </c>
       <c r="L94" s="1">
         <f ca="1" t="shared" ref="L94:P94" si="160">J94+$R$1*K94/MAX(1,($A94*($A94-1)))++$R$1/$A94</f>
-        <v>7.06006129026305</v>
+        <v>7.06493807834122</v>
       </c>
       <c r="M94" s="1">
         <f ca="1" t="shared" si="159"/>
-        <v>0.369314653966818</v>
+        <v>0.616071238290789</v>
       </c>
       <c r="N94" s="1">
         <f ca="1" t="shared" si="160"/>
-        <v>7.59985391914317</v>
+        <v>7.60617271624615</v>
       </c>
       <c r="O94" s="1">
         <f ca="1" t="shared" si="159"/>
-        <v>0.530536664251997</v>
+        <v>0.973458206867605</v>
       </c>
       <c r="P94" s="1">
         <f ca="1" t="shared" si="160"/>
-        <v>8.14058870563366</v>
+        <v>8.14949587079773</v>
       </c>
     </row>
     <row r="95" ht="16.5" spans="1:16">
@@ -11591,27 +11616,27 @@
       </c>
       <c r="K95" s="1">
         <f ca="1" t="shared" ref="K95:O95" si="161">RAND()</f>
-        <v>0.844648361894326</v>
+        <v>0.214934503918403</v>
       </c>
       <c r="L95" s="1">
         <f ca="1" t="shared" ref="L95:P95" si="162">J95+$R$1*K95/MAX(1,($A95*($A95-1)))++$R$1/$A95</f>
-        <v>6.98835877580585</v>
+        <v>6.98475711795881</v>
       </c>
       <c r="M95" s="1">
         <f ca="1" t="shared" si="161"/>
-        <v>0.248311841534792</v>
+        <v>0.61848523668268</v>
       </c>
       <c r="N95" s="1">
         <f ca="1" t="shared" si="162"/>
-        <v>7.52169389272151</v>
+        <v>7.52020944715512</v>
       </c>
       <c r="O95" s="1">
         <f ca="1" t="shared" si="161"/>
-        <v>0.278681015960751</v>
+        <v>0.822783671039529</v>
       </c>
       <c r="P95" s="1">
         <f ca="1" t="shared" si="162"/>
-        <v>8.05520270658539</v>
+        <v>8.05683026430817</v>
       </c>
     </row>
     <row r="96" ht="16.5" spans="1:16">
@@ -11651,27 +11676,27 @@
       </c>
       <c r="K96" s="1">
         <f ca="1" t="shared" ref="K96:O96" si="163">RAND()</f>
-        <v>0.535535182922426</v>
+        <v>0.555194704212947</v>
       </c>
       <c r="L96" s="1">
         <f ca="1" t="shared" ref="L96:P96" si="164">J96+$R$1*K96/MAX(1,($A96*($A96-1)))++$R$1/$A96</f>
-        <v>6.91229303013955</v>
+        <v>6.91240310584666</v>
       </c>
       <c r="M96" s="1">
         <f ca="1" t="shared" si="163"/>
-        <v>0.685700945423441</v>
+        <v>0.837822215646088</v>
       </c>
       <c r="N96" s="1">
         <f ca="1" t="shared" si="164"/>
-        <v>7.44244813061784</v>
+        <v>7.44340994915934</v>
       </c>
       <c r="O96" s="1">
         <f ca="1" t="shared" si="163"/>
-        <v>0.883468314147892</v>
+        <v>0.576394803967761</v>
       </c>
       <c r="P96" s="1">
         <f ca="1" t="shared" si="164"/>
-        <v>7.97371055118978</v>
+        <v>7.97295303316812</v>
       </c>
     </row>
     <row r="97" ht="16.5" spans="1:16">
@@ -11711,27 +11736,27 @@
       </c>
       <c r="K97" s="1">
         <f ca="1" t="shared" ref="K97:O97" si="165">RAND()</f>
-        <v>0.982894403782189</v>
+        <v>0.214680857356646</v>
       </c>
       <c r="L97" s="1">
         <f ca="1" t="shared" ref="L97:P97" si="166">J97+$R$1*K97/MAX(1,($A97*($A97-1)))++$R$1/$A97</f>
-        <v>6.84201148247687</v>
+        <v>6.83779978540217</v>
       </c>
       <c r="M97" s="1">
         <f ca="1" t="shared" si="165"/>
-        <v>0.0219822370655671</v>
+        <v>0.697312309469668</v>
       </c>
       <c r="N97" s="1">
         <f ca="1" t="shared" si="166"/>
-        <v>7.36296533246079</v>
+        <v>7.3624561028883</v>
       </c>
       <c r="O97" s="1">
         <f ca="1" t="shared" si="165"/>
-        <v>0.177352024136529</v>
+        <v>0.509987229539316</v>
       </c>
       <c r="P97" s="1">
         <f ca="1" t="shared" si="166"/>
-        <v>7.88477099048785</v>
+        <v>7.88608541883972</v>
       </c>
     </row>
     <row r="98" ht="16.5" spans="1:16">
@@ -11771,27 +11796,27 @@
       </c>
       <c r="K98" s="1">
         <f ca="1" t="shared" ref="K98:O98" si="167">RAND()</f>
-        <v>0.339603445482476</v>
+        <v>0.14002666594476</v>
       </c>
       <c r="L98" s="1">
         <f ca="1" t="shared" ref="L98:P98" si="168">J98+$R$1*K98/MAX(1,($A98*($A98-1)))++$R$1/$A98</f>
-        <v>6.76728738963425</v>
+        <v>6.76621577891938</v>
       </c>
       <c r="M98" s="1">
         <f ca="1" t="shared" si="167"/>
-        <v>0.366214816348723</v>
+        <v>0.86015783624368</v>
       </c>
       <c r="N98" s="1">
         <f ca="1" t="shared" si="168"/>
-        <v>7.28471766678389</v>
+        <v>7.28629824152807</v>
       </c>
       <c r="O98" s="1">
         <f ca="1" t="shared" si="167"/>
-        <v>0.317865201925549</v>
+        <v>0.24121113456431</v>
       </c>
       <c r="P98" s="1">
         <f ca="1" t="shared" si="168"/>
-        <v>7.80188833474955</v>
+        <v>7.80305732193274</v>
       </c>
     </row>
     <row r="99" ht="16.5" spans="1:16">
@@ -11831,27 +11856,27 @@
       </c>
       <c r="K99" s="1">
         <f ca="1" t="shared" ref="K99:O99" si="169">RAND()</f>
-        <v>0.749522523163122</v>
+        <v>0.900004067501697</v>
       </c>
       <c r="L99" s="1">
         <f ca="1" t="shared" ref="L99:P99" si="170">J99+$R$1*K99/MAX(1,($A99*($A99-1)))++$R$1/$A99</f>
-        <v>6.69971345741197</v>
+        <v>6.70050496564013</v>
       </c>
       <c r="M99" s="1">
         <f ca="1" t="shared" si="169"/>
-        <v>0.340573613094492</v>
+        <v>0.605050483647492</v>
       </c>
       <c r="N99" s="1">
         <f ca="1" t="shared" si="170"/>
-        <v>7.21170890035903</v>
+        <v>7.21389151352382</v>
       </c>
       <c r="O99" s="1">
         <f ca="1" t="shared" si="169"/>
-        <v>0.678411648269607</v>
+        <v>0.0498744894551026</v>
       </c>
       <c r="P99" s="1">
         <f ca="1" t="shared" si="170"/>
-        <v>7.72548131592956</v>
+        <v>7.72435792678626</v>
       </c>
     </row>
     <row r="100" ht="16.5" spans="1:16">
@@ -11891,27 +11916,27 @@
       </c>
       <c r="K100" s="1">
         <f ca="1" t="shared" ref="K100:O100" si="171">RAND()</f>
-        <v>0.12099284205504</v>
+        <v>0.546421722243013</v>
       </c>
       <c r="L100" s="1">
         <f ca="1" t="shared" ref="L100:P100" si="172">J100+$R$1*K100/MAX(1,($A100*($A100-1)))++$R$1/$A100</f>
-        <v>6.62812303051977</v>
+        <v>6.63031551083407</v>
       </c>
       <c r="M100" s="1">
         <f ca="1" t="shared" si="171"/>
-        <v>0.0308410036039357</v>
+        <v>0.780177401782107</v>
       </c>
       <c r="N100" s="1">
         <f ca="1" t="shared" si="172"/>
-        <v>7.13333247704422</v>
+        <v>7.13938671987232</v>
       </c>
       <c r="O100" s="1">
         <f ca="1" t="shared" si="171"/>
-        <v>0.919116666297905</v>
+        <v>0.859575981240703</v>
       </c>
       <c r="P100" s="1">
         <f ca="1" t="shared" si="172"/>
-        <v>7.64311972022242</v>
+        <v>7.64886711557032</v>
       </c>
     </row>
     <row r="101" ht="16.5" spans="1:16">
@@ -11951,27 +11976,27 @@
       </c>
       <c r="K101" s="1">
         <f ca="1" t="shared" ref="K101:O101" si="173">RAND()</f>
-        <v>0.600452107815753</v>
+        <v>0.209018321639142</v>
       </c>
       <c r="L101" s="1">
         <f ca="1" t="shared" ref="L101:P101" si="174">J101+$R$1*K101/MAX(1,($A101*($A101-1)))++$R$1/$A101</f>
-        <v>6.56363864700917</v>
+        <v>6.56166170869515</v>
       </c>
       <c r="M101" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.407420601875879</v>
+        <v>0.609475433002806</v>
       </c>
       <c r="N101" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>7.06569632681662</v>
+        <v>7.06473986744769</v>
       </c>
       <c r="O101" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.957656777936848</v>
+        <v>0.282776555708112</v>
       </c>
       <c r="P101" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>7.57053297721024</v>
+        <v>7.56616803187045</v>
       </c>
     </row>
     <row r="102" ht="16.5" spans="1:16">
@@ -12125,27 +12150,27 @@
       </c>
       <c r="K104" s="1">
         <f ca="1" t="shared" ref="K104:O104" si="177">RAND()</f>
-        <v>0.68444488522771</v>
+        <v>0.379248664745552</v>
       </c>
       <c r="L104" s="1">
         <f ca="1" t="shared" ref="L104:P104" si="178">J104+$R$1*K104/MAX(1,($A104*($A104-1)))++$R$1/$A104</f>
-        <v>6.37104723436716</v>
+        <v>6.36959474902316</v>
       </c>
       <c r="M104" s="1">
         <f ca="1" t="shared" si="177"/>
-        <v>0.152213849745762</v>
+        <v>0.447308455312509</v>
       </c>
       <c r="N104" s="1">
         <f ca="1" t="shared" si="178"/>
-        <v>6.85720854147617</v>
+        <v>6.85716046601969</v>
       </c>
       <c r="O104" s="1">
         <f ca="1" t="shared" si="177"/>
-        <v>0.593618003463857</v>
+        <v>0.492044212279471</v>
       </c>
       <c r="P104" s="1">
         <f ca="1" t="shared" si="178"/>
-        <v>7.34547057271291</v>
+        <v>7.34493908876993</v>
       </c>
     </row>
     <row r="105" ht="16.5" spans="1:16">
@@ -12185,27 +12210,27 @@
       </c>
       <c r="K105" s="1">
         <f ca="1" t="shared" ref="K105:O105" si="179">RAND()</f>
-        <v>0.28875264694334</v>
+        <v>0.712280991910336</v>
       </c>
       <c r="L105" s="1">
         <f ca="1" t="shared" ref="L105:P105" si="180">J105+$R$1*K105/MAX(1,($A105*($A105-1)))++$R$1/$A105</f>
-        <v>6.30735974909888</v>
+        <v>6.30933663644469</v>
       </c>
       <c r="M105" s="1">
         <f ca="1" t="shared" si="179"/>
-        <v>0.348531426105049</v>
+        <v>0.208961669202934</v>
       </c>
       <c r="N105" s="1">
         <f ca="1" t="shared" si="180"/>
-        <v>6.78975580691303</v>
+        <v>6.79108122974754</v>
       </c>
       <c r="O105" s="1">
         <f ca="1" t="shared" si="179"/>
-        <v>0.559986884364687</v>
+        <v>0.321808007063908</v>
       </c>
       <c r="P105" s="1">
         <f ca="1" t="shared" si="180"/>
-        <v>7.27313886742631</v>
+        <v>7.27335255166252</v>
       </c>
     </row>
     <row r="106" ht="16.5" spans="1:16">
@@ -12245,27 +12270,27 @@
       </c>
       <c r="K106" s="1">
         <f ca="1" t="shared" ref="K106:O106" si="181">RAND()</f>
-        <v>0.452252573532014</v>
+        <v>0.110387146208951</v>
       </c>
       <c r="L106" s="1">
         <f ca="1" t="shared" ref="L106:P106" si="182">J106+$R$1*K106/MAX(1,($A106*($A106-1)))++$R$1/$A106</f>
-        <v>6.24749199896306</v>
+        <v>6.24592668107239</v>
       </c>
       <c r="M106" s="1">
         <f ca="1" t="shared" si="181"/>
-        <v>0.676263267020408</v>
+        <v>0.794557896587722</v>
       </c>
       <c r="N106" s="1">
         <f ca="1" t="shared" si="182"/>
-        <v>6.72677891868385</v>
+        <v>6.72575524286995</v>
       </c>
       <c r="O106" s="1">
         <f ca="1" t="shared" si="181"/>
-        <v>0.223736401958934</v>
+        <v>0.757742811932833</v>
       </c>
       <c r="P106" s="1">
         <f ca="1" t="shared" si="182"/>
-        <v>7.20399382894923</v>
+        <v>7.20541523743008</v>
       </c>
     </row>
     <row r="107" ht="16.5" spans="1:16">
@@ -12305,27 +12330,27 @@
       </c>
       <c r="K107" s="1">
         <f ca="1" t="shared" ref="K107:O107" si="183">RAND()</f>
-        <v>0.932591054036461</v>
+        <v>0.767779976481766</v>
       </c>
       <c r="L107" s="1">
         <f ca="1" t="shared" ref="L107:P107" si="184">J107+$R$1*K107/MAX(1,($A107*($A107-1)))++$R$1/$A107</f>
-        <v>6.19017336502262</v>
+        <v>6.18943297383864</v>
       </c>
       <c r="M107" s="1">
         <f ca="1" t="shared" si="183"/>
-        <v>0.144677044802197</v>
+        <v>0.529320342285459</v>
       </c>
       <c r="N107" s="1">
         <f ca="1" t="shared" si="184"/>
-        <v>6.66252142003072</v>
+        <v>6.66350898615798</v>
       </c>
       <c r="O107" s="1">
         <f ca="1" t="shared" si="183"/>
-        <v>0.30802908226998</v>
+        <v>0.0981825102895508</v>
       </c>
       <c r="P107" s="1">
         <f ca="1" t="shared" si="184"/>
-        <v>7.13560331168512</v>
+        <v>7.13564817084033</v>
       </c>
     </row>
     <row r="108" ht="16.5" spans="1:16">
@@ -12365,27 +12390,27 @@
       </c>
       <c r="K108" s="1">
         <f ca="1" t="shared" ref="K108:O108" si="185">RAND()</f>
-        <v>0.868731002370915</v>
+        <v>0.879910427825525</v>
       </c>
       <c r="L108" s="1">
         <f ca="1" t="shared" ref="L108:P108" si="186">J108+$R$1*K108/MAX(1,($A108*($A108-1)))++$R$1/$A108</f>
-        <v>6.13149678629154</v>
+        <v>6.13154606959895</v>
       </c>
       <c r="M108" s="1">
         <f ca="1" t="shared" si="185"/>
-        <v>0.426743766490888</v>
+        <v>0.984143983720996</v>
       </c>
       <c r="N108" s="1">
         <f ca="1" t="shared" si="186"/>
-        <v>6.6006677603988</v>
+        <v>6.60317428324611</v>
       </c>
       <c r="O108" s="1">
         <f ca="1" t="shared" si="185"/>
-        <v>0.619690643929398</v>
+        <v>0.240198700292095</v>
       </c>
       <c r="P108" s="1">
         <f ca="1" t="shared" si="186"/>
-        <v>7.0706893202821</v>
+        <v>7.0715228932809</v>
       </c>
     </row>
     <row r="109" ht="16.5" spans="1:16">
@@ -12425,27 +12450,27 @@
       </c>
       <c r="K109" s="1">
         <f ca="1" t="shared" ref="K109:O109" si="187">RAND()</f>
-        <v>0.779666818186753</v>
+        <v>0.199391710333226</v>
       </c>
       <c r="L109" s="1">
         <f ca="1" t="shared" ref="L109:P109" si="188">J109+$R$1*K109/MAX(1,($A109*($A109-1)))++$R$1/$A109</f>
-        <v>6.07381302707765</v>
+        <v>6.07130231788825</v>
       </c>
       <c r="M109" s="1">
         <f ca="1" t="shared" si="187"/>
-        <v>0.559277991316197</v>
+        <v>0.949882389641663</v>
       </c>
       <c r="N109" s="1">
         <f ca="1" t="shared" si="188"/>
-        <v>6.53919584981613</v>
+        <v>6.53837519080986</v>
       </c>
       <c r="O109" s="1">
         <f ca="1" t="shared" si="187"/>
-        <v>0.341484115083428</v>
+        <v>0.858938554073766</v>
       </c>
       <c r="P109" s="1">
         <f ca="1" t="shared" si="188"/>
-        <v>7.00363633144941</v>
+        <v>7.00505457188495</v>
       </c>
     </row>
     <row r="110" ht="16.5" spans="1:16">
@@ -12485,27 +12510,27 @@
       </c>
       <c r="K110" s="1">
         <f ca="1" t="shared" ref="K110:O110" si="189">RAND()</f>
-        <v>0.849864230307227</v>
+        <v>0.00885750462309942</v>
       </c>
       <c r="L110" s="1">
         <f ca="1" t="shared" ref="L110:P110" si="190">J110+$R$1*K110/MAX(1,($A110*($A110-1)))++$R$1/$A110</f>
-        <v>6.01788083685996</v>
+        <v>6.01430877295542</v>
       </c>
       <c r="M110" s="1">
         <f ca="1" t="shared" si="189"/>
-        <v>0.640077401100398</v>
+        <v>0.250269239617228</v>
       </c>
       <c r="N110" s="1">
         <f ca="1" t="shared" si="190"/>
-        <v>6.479315076586</v>
+        <v>6.47408735450323</v>
       </c>
       <c r="O110" s="1">
         <f ca="1" t="shared" si="189"/>
-        <v>0.711022188121851</v>
+        <v>0.97863553728878</v>
       </c>
       <c r="P110" s="1">
         <f ca="1" t="shared" si="190"/>
-        <v>6.94105064483321</v>
+        <v>6.93695957476015</v>
       </c>
     </row>
     <row r="111" ht="16.5" spans="1:16">
@@ -12545,27 +12570,27 @@
       </c>
       <c r="K111" s="1">
         <f ca="1" t="shared" ref="K111:O111" si="191">RAND()</f>
-        <v>0.441168093766404</v>
+        <v>0.665300597703811</v>
       </c>
       <c r="L111" s="1">
         <f ca="1" t="shared" ref="L111:P111" si="192">J111+$R$1*K111/MAX(1,($A111*($A111-1)))++$R$1/$A111</f>
-        <v>5.9609723440107</v>
+        <v>5.96190700833071</v>
       </c>
       <c r="M111" s="1">
         <f ca="1" t="shared" si="191"/>
-        <v>0.717702971146798</v>
+        <v>0.642223274274544</v>
       </c>
       <c r="N111" s="1">
         <f ca="1" t="shared" si="192"/>
-        <v>6.41851072170522</v>
+        <v>6.4191306249874</v>
       </c>
       <c r="O111" s="1">
         <f ca="1" t="shared" si="191"/>
-        <v>0.372499474168782</v>
+        <v>0.378680838020478</v>
       </c>
       <c r="P111" s="1">
         <f ca="1" t="shared" si="192"/>
-        <v>6.87460955187273</v>
+        <v>6.87525523231859</v>
       </c>
     </row>
     <row r="112" ht="16.5" spans="1:16">
@@ -12605,27 +12630,27 @@
       </c>
       <c r="K112" s="1">
         <f ca="1" t="shared" ref="K112:O112" si="193">RAND()</f>
-        <v>0.65663031653283</v>
+        <v>0.349360904766976</v>
       </c>
       <c r="L112" s="1">
         <f ca="1" t="shared" ref="L112:P112" si="194">J112+$R$1*K112/MAX(1,($A112*($A112-1)))++$R$1/$A112</f>
-        <v>5.90768480883101</v>
+        <v>5.90642653933156</v>
       </c>
       <c r="M112" s="1">
         <f ca="1" t="shared" si="193"/>
-        <v>0.39960383421644</v>
+        <v>0.581799834716415</v>
       </c>
       <c r="N112" s="1">
         <f ca="1" t="shared" si="194"/>
-        <v>6.35977163861895</v>
+        <v>6.35925946248765</v>
       </c>
       <c r="O112" s="1">
         <f ca="1" t="shared" si="193"/>
-        <v>0.389440592055012</v>
+        <v>0.68691738227944</v>
       </c>
       <c r="P112" s="1">
         <f ca="1" t="shared" si="194"/>
-        <v>6.81181684988863</v>
+        <v>6.81252284243146</v>
       </c>
     </row>
     <row r="113" ht="16.5" spans="1:16">
@@ -12665,27 +12690,27 @@
       </c>
       <c r="K113" s="1">
         <f ca="1" t="shared" ref="K113:O113" si="195">RAND()</f>
-        <v>0.786603088060525</v>
+        <v>0.586846208963064</v>
       </c>
       <c r="L113" s="1">
         <f ca="1" t="shared" ref="L113:P113" si="196">J113+$R$1*K113/MAX(1,($A113*($A113-1)))++$R$1/$A113</f>
-        <v>5.8549975992924</v>
+        <v>5.85419420129087</v>
       </c>
       <c r="M113" s="1">
         <f ca="1" t="shared" si="195"/>
-        <v>0.264135112059419</v>
+        <v>0.599237953354005</v>
       </c>
       <c r="N113" s="1">
         <f ca="1" t="shared" si="196"/>
-        <v>6.3024884901871</v>
+        <v>6.30303283527315</v>
       </c>
       <c r="O113" s="1">
         <f ca="1" t="shared" si="195"/>
-        <v>0.739998520235792</v>
+        <v>0.531734047838465</v>
       </c>
       <c r="P113" s="1">
         <f ca="1" t="shared" si="196"/>
-        <v>6.75189324614043</v>
+        <v>6.75159997671394</v>
       </c>
     </row>
     <row r="114" ht="16.5" spans="1:16">
@@ -12725,27 +12750,27 @@
       </c>
       <c r="K114" s="1">
         <f ca="1" t="shared" ref="K114:O114" si="197">RAND()</f>
-        <v>0.459958193707205</v>
+        <v>0.742690668749125</v>
       </c>
       <c r="L114" s="1">
         <f ca="1" t="shared" ref="L114:P114" si="198">J114+$R$1*K114/MAX(1,($A114*($A114-1)))++$R$1/$A114</f>
-        <v>5.80143788793342</v>
+        <v>5.80255487780005</v>
       </c>
       <c r="M114" s="1">
         <f ca="1" t="shared" si="197"/>
-        <v>0.731791116316434</v>
+        <v>0.855311968959515</v>
       </c>
       <c r="N114" s="1">
         <f ca="1" t="shared" si="198"/>
-        <v>6.24680684777981</v>
+        <v>6.24841183090119</v>
       </c>
       <c r="O114" s="1">
         <f ca="1" t="shared" si="197"/>
-        <v>0.569592947935174</v>
+        <v>0.0131012946181568</v>
       </c>
       <c r="P114" s="1">
         <f ca="1" t="shared" si="198"/>
-        <v>6.69153501208107</v>
+        <v>6.69094146623075</v>
       </c>
     </row>
     <row r="115" ht="16.5" spans="1:16">
@@ -12785,27 +12810,27 @@
       </c>
       <c r="K115" s="1">
         <f ca="1" t="shared" ref="K115:O115" si="199">RAND()</f>
-        <v>0.969106002294464</v>
+        <v>0.367598932070455</v>
       </c>
       <c r="L115" s="1">
         <f ca="1" t="shared" ref="L115:P115" si="200">J115+$R$1*K115/MAX(1,($A115*($A115-1)))++$R$1/$A115</f>
-        <v>5.75209247788502</v>
+        <v>5.74975779743856</v>
       </c>
       <c r="M115" s="1">
         <f ca="1" t="shared" si="199"/>
-        <v>0.70422188127564</v>
+        <v>0.892894212520041</v>
       </c>
       <c r="N115" s="1">
         <f ca="1" t="shared" si="200"/>
-        <v>6.19342232527391</v>
+        <v>6.19181995476087</v>
       </c>
       <c r="O115" s="1">
         <f ca="1" t="shared" si="199"/>
-        <v>0.174526808200813</v>
+        <v>0.221586245797323</v>
       </c>
       <c r="P115" s="1">
         <f ca="1" t="shared" si="200"/>
-        <v>6.63269622221616</v>
+        <v>6.63127650749258</v>
       </c>
     </row>
     <row r="116" ht="16.5" spans="1:16">
@@ -12845,27 +12870,27 @@
       </c>
       <c r="K116" s="1">
         <f ca="1" t="shared" ref="K116:O116" si="201">RAND()</f>
-        <v>0.974647187700575</v>
+        <v>0.4188249948734</v>
       </c>
       <c r="L116" s="1">
         <f ca="1" t="shared" ref="L116:P116" si="202">J116+$R$1*K116/MAX(1,($A116*($A116-1)))++$R$1/$A116</f>
-        <v>5.70165769331693</v>
+        <v>5.69953785276458</v>
       </c>
       <c r="M116" s="1">
         <f ca="1" t="shared" si="201"/>
-        <v>0.477045198149884</v>
+        <v>0.334098940590187</v>
       </c>
       <c r="N116" s="1">
         <f ca="1" t="shared" si="202"/>
-        <v>6.13825969636098</v>
+        <v>6.13559467557385</v>
       </c>
       <c r="O116" s="1">
         <f ca="1" t="shared" si="201"/>
-        <v>0.905453979474853</v>
+        <v>0.75599060737138</v>
       </c>
       <c r="P116" s="1">
         <f ca="1" t="shared" si="202"/>
-        <v>6.57649560017286</v>
+        <v>6.57326054364163</v>
       </c>
     </row>
     <row r="117" ht="16.5" spans="1:16">
@@ -12905,27 +12930,27 @@
       </c>
       <c r="K117" s="1">
         <f ca="1" t="shared" ref="K117:O117" si="203">RAND()</f>
-        <v>0.510587273704762</v>
+        <v>0.873967375646127</v>
       </c>
       <c r="L117" s="1">
         <f ca="1" t="shared" ref="L117:P117" si="204">J117+$R$1*K117/MAX(1,($A117*($A117-1)))++$R$1/$A117</f>
-        <v>5.65033953251014</v>
+        <v>5.65170152689523</v>
       </c>
       <c r="M117" s="1">
         <f ca="1" t="shared" si="203"/>
-        <v>0.32142127547192</v>
+        <v>0.608096119691846</v>
       </c>
       <c r="N117" s="1">
         <f ca="1" t="shared" si="204"/>
-        <v>6.08257874268807</v>
+        <v>6.08501523049227</v>
       </c>
       <c r="O117" s="1">
         <f ca="1" t="shared" si="203"/>
-        <v>0.0896040566111227</v>
+        <v>0.961793268348814</v>
       </c>
       <c r="P117" s="1">
         <f ca="1" t="shared" si="204"/>
-        <v>6.51394907273534</v>
+        <v>6.51965463554605</v>
       </c>
     </row>
     <row r="118" ht="16.5" spans="1:16">
@@ -12965,27 +12990,27 @@
       </c>
       <c r="K118" s="1">
         <f ca="1" t="shared" ref="K118:O118" si="205">RAND()</f>
-        <v>0.664306312023906</v>
+        <v>0.215159913859936</v>
       </c>
       <c r="L118" s="1">
         <f ca="1" t="shared" ref="L118:P118" si="206">J118+$R$1*K118/MAX(1,($A118*($A118-1)))++$R$1/$A118</f>
-        <v>5.60221156171539</v>
+        <v>5.60055688149816</v>
       </c>
       <c r="M118" s="1">
         <f ca="1" t="shared" si="205"/>
-        <v>0.63743543805456</v>
+        <v>0.453497367751454</v>
       </c>
       <c r="N118" s="1">
         <f ca="1" t="shared" si="206"/>
-        <v>6.03191033653875</v>
+        <v>6.02957801827885</v>
       </c>
       <c r="O118" s="1">
         <f ca="1" t="shared" si="205"/>
-        <v>0.0924699522445693</v>
+        <v>0.831494383991431</v>
       </c>
       <c r="P118" s="1">
         <f ca="1" t="shared" si="206"/>
-        <v>6.45960142831684</v>
+        <v>6.4599917170115</v>
       </c>
     </row>
     <row r="119" ht="16.5" spans="1:16">
@@ -13025,27 +13050,27 @@
       </c>
       <c r="K119" s="1">
         <f ca="1" t="shared" ref="K119:O119" si="207">RAND()</f>
-        <v>0.228016421651428</v>
+        <v>0.0236062097827208</v>
       </c>
       <c r="L119" s="1">
         <f ca="1" t="shared" ref="L119:P119" si="208">J119+$R$1*K119/MAX(1,($A119*($A119-1)))++$R$1/$A119</f>
-        <v>5.5527597291817</v>
+        <v>5.55201943433935</v>
       </c>
       <c r="M119" s="1">
         <f ca="1" t="shared" si="207"/>
-        <v>0.447453422882474</v>
+        <v>0.603771055526294</v>
       </c>
       <c r="N119" s="1">
         <f ca="1" t="shared" si="208"/>
-        <v>5.97810904622821</v>
+        <v>5.97793487348004</v>
       </c>
       <c r="O119" s="1">
         <f ca="1" t="shared" si="207"/>
-        <v>0.901207041903617</v>
+        <v>0.824174210487703</v>
       </c>
       <c r="P119" s="1">
         <f ca="1" t="shared" si="208"/>
-        <v>6.40510168363913</v>
+        <v>6.40464852772634</v>
       </c>
     </row>
     <row r="120" ht="16.5" spans="1:16">
@@ -13199,27 +13224,27 @@
       </c>
       <c r="K122" s="1">
         <f ca="1" t="shared" ref="K122:O122" si="211">RAND()</f>
-        <v>0.930191726553585</v>
+        <v>0.11609359452046</v>
       </c>
       <c r="L122" s="1">
         <f ca="1" t="shared" ref="L122:P122" si="212">J122+$R$1*K122/MAX(1,($A122*($A122-1)))++$R$1/$A122</f>
-        <v>5.41642628005012</v>
+        <v>5.41362291182686</v>
       </c>
       <c r="M122" s="1">
         <f ca="1" t="shared" si="211"/>
-        <v>0.157439060729432</v>
+        <v>0.471762075912724</v>
       </c>
       <c r="N122" s="1">
         <f ca="1" t="shared" si="212"/>
-        <v>5.83019156607191</v>
+        <v>5.82847057737752</v>
       </c>
       <c r="O122" s="1">
         <f ca="1" t="shared" si="211"/>
-        <v>0.273202295861578</v>
+        <v>0.0661612653303922</v>
       </c>
       <c r="P122" s="1">
         <f ca="1" t="shared" si="212"/>
-        <v>6.2443554858235</v>
+        <v>6.24192154592205</v>
       </c>
     </row>
     <row r="123" ht="16.5" spans="1:16">
@@ -13259,27 +13284,27 @@
       </c>
       <c r="K123" s="1">
         <f ca="1" t="shared" ref="K123:O123" si="213">RAND()</f>
-        <v>0.545763563420471</v>
+        <v>0.791539763147667</v>
       </c>
       <c r="L123" s="1">
         <f ca="1" t="shared" ref="L123:P123" si="214">J123+$R$1*K123/MAX(1,($A123*($A123-1)))++$R$1/$A123</f>
-        <v>5.37036229360324</v>
+        <v>5.37119475600578</v>
       </c>
       <c r="M123" s="1">
         <f ca="1" t="shared" si="213"/>
-        <v>0.520749704770044</v>
+        <v>0.77797211886292</v>
       </c>
       <c r="N123" s="1">
         <f ca="1" t="shared" si="214"/>
-        <v>5.78196217744272</v>
+        <v>5.78366587143345</v>
       </c>
       <c r="O123" s="1">
         <f ca="1" t="shared" si="213"/>
-        <v>0.159463857837399</v>
+        <v>0.0974363216102665</v>
       </c>
       <c r="P123" s="1">
         <f ca="1" t="shared" si="214"/>
-        <v>6.19233835905036</v>
+        <v>6.19383196112864</v>
       </c>
     </row>
     <row r="124" ht="16.5" spans="1:16">
@@ -13319,27 +13344,27 @@
       </c>
       <c r="K124" s="1">
         <f ca="1" t="shared" ref="K124:O124" si="215">RAND()</f>
-        <v>0.374330849180655</v>
+        <v>0.303199667199125</v>
       </c>
       <c r="L124" s="1">
         <f ca="1" t="shared" ref="L124:P124" si="216">J124+$R$1*K124/MAX(1,($A124*($A124-1)))++$R$1/$A124</f>
-        <v>5.32578412251493</v>
+        <v>5.32554711337865</v>
       </c>
       <c r="M124" s="1">
         <f ca="1" t="shared" si="215"/>
-        <v>0.523893591619577</v>
+        <v>0.0122211600887334</v>
       </c>
       <c r="N124" s="1">
         <f ca="1" t="shared" si="216"/>
-        <v>5.73403380128216</v>
+        <v>5.73209189933123</v>
       </c>
       <c r="O124" s="1">
         <f ca="1" t="shared" si="215"/>
-        <v>0.140068805257194</v>
+        <v>0.159011636489625</v>
       </c>
       <c r="P124" s="1">
         <f ca="1" t="shared" si="216"/>
-        <v>6.1410045756566</v>
+        <v>6.13912579122943</v>
       </c>
     </row>
     <row r="125" ht="16.5" spans="1:16">
@@ -13379,27 +13404,27 @@
       </c>
       <c r="K125" s="1">
         <f ca="1" t="shared" ref="K125:O125" si="217">RAND()</f>
-        <v>0.360566232252989</v>
+        <v>0.406873285080035</v>
       </c>
       <c r="L125" s="1">
         <f ca="1" t="shared" ref="L125:P125" si="218">J125+$R$1*K125/MAX(1,($A125*($A125-1)))++$R$1/$A125</f>
-        <v>5.28245661628721</v>
+        <v>5.28260842278088</v>
       </c>
       <c r="M125" s="1">
         <f ca="1" t="shared" si="217"/>
-        <v>0.438297765767388</v>
+        <v>0.549289244976262</v>
       </c>
       <c r="N125" s="1">
         <f ca="1" t="shared" si="218"/>
-        <v>5.68711927615401</v>
+        <v>5.6876349414177</v>
       </c>
       <c r="O125" s="1">
         <f ca="1" t="shared" si="217"/>
-        <v>0.972601073707403</v>
+        <v>0.918841175525932</v>
       </c>
       <c r="P125" s="1">
         <f ca="1" t="shared" si="218"/>
-        <v>6.09353352042921</v>
+        <v>6.09387294684495</v>
       </c>
     </row>
     <row r="126" ht="16.5" spans="1:16">
@@ -13439,27 +13464,27 @@
       </c>
       <c r="K126" s="1">
         <f ca="1" t="shared" ref="K126:O126" si="219">RAND()</f>
-        <v>0.548075337312242</v>
+        <v>0.482023559703589</v>
       </c>
       <c r="L126" s="1">
         <f ca="1" t="shared" ref="L126:P126" si="220">J126+$R$1*K126/MAX(1,($A126*($A126-1)))++$R$1/$A126</f>
-        <v>5.24047766237842</v>
+        <v>5.24026459212808</v>
       </c>
       <c r="M126" s="1">
         <f ca="1" t="shared" si="219"/>
-        <v>0.604445972071556</v>
+        <v>0.553296707180553</v>
       </c>
       <c r="N126" s="1">
         <f ca="1" t="shared" si="220"/>
-        <v>5.64242748809478</v>
+        <v>5.64204942021576</v>
       </c>
       <c r="O126" s="1">
         <f ca="1" t="shared" si="219"/>
-        <v>0.850713143486417</v>
+        <v>0.623179507872836</v>
       </c>
       <c r="P126" s="1">
         <f ca="1" t="shared" si="220"/>
-        <v>6.04517172404151</v>
+        <v>6.04405967669276</v>
       </c>
     </row>
     <row r="127" ht="16.5" spans="1:16">
@@ -13499,27 +13524,27 @@
       </c>
       <c r="K127" s="1">
         <f ca="1" t="shared" ref="K127:O127" si="221">RAND()</f>
-        <v>0.680679585888173</v>
+        <v>0.328850124847131</v>
       </c>
       <c r="L127" s="1">
         <f ca="1" t="shared" ref="L127:P127" si="222">J127+$R$1*K127/MAX(1,($A127*($A127-1)))++$R$1/$A127</f>
-        <v>5.19898628439964</v>
+        <v>5.19786936547571</v>
       </c>
       <c r="M127" s="1">
         <f ca="1" t="shared" si="221"/>
-        <v>0.0108745869511837</v>
+        <v>0.629931194895083</v>
       </c>
       <c r="N127" s="1">
         <f ca="1" t="shared" si="222"/>
-        <v>5.5958462037233</v>
+        <v>5.5966945438722</v>
       </c>
       <c r="O127" s="1">
         <f ca="1" t="shared" si="221"/>
-        <v>0.821331568791543</v>
+        <v>0.00778379714357924</v>
       </c>
       <c r="P127" s="1">
         <f ca="1" t="shared" si="222"/>
-        <v>5.99527900235438</v>
+        <v>5.99354465116472</v>
       </c>
     </row>
     <row r="128" ht="16.5" spans="1:16">
@@ -13559,27 +13584,27 @@
       </c>
       <c r="K128" s="1">
         <f ca="1" t="shared" ref="K128:O128" si="223">RAND()</f>
-        <v>0.758871571479732</v>
+        <v>0.598802642285196</v>
       </c>
       <c r="L128" s="1">
         <f ca="1" t="shared" ref="L128:P128" si="224">J128+$R$1*K128/MAX(1,($A128*($A128-1)))++$R$1/$A128</f>
-        <v>5.15797672657005</v>
+        <v>5.15747657368543</v>
       </c>
       <c r="M128" s="1">
         <f ca="1" t="shared" si="223"/>
-        <v>0.717651928461352</v>
+        <v>0.0697312146947697</v>
       </c>
       <c r="N128" s="1">
         <f ca="1" t="shared" si="224"/>
-        <v>5.55391989595032</v>
+        <v>5.55139524389758</v>
       </c>
       <c r="O128" s="1">
         <f ca="1" t="shared" si="223"/>
-        <v>0.125285143404439</v>
+        <v>0.886539311130365</v>
       </c>
       <c r="P128" s="1">
         <f ca="1" t="shared" si="224"/>
-        <v>5.94801215049164</v>
+        <v>5.9478661203853</v>
       </c>
     </row>
     <row r="129" ht="16.5" spans="1:16">
@@ -13619,27 +13644,27 @@
       </c>
       <c r="K129" s="1">
         <f ca="1" t="shared" ref="K129:O129" si="225">RAND()</f>
-        <v>0.633593007894304</v>
+        <v>0.70304897673046</v>
       </c>
       <c r="L129" s="1">
         <f ca="1" t="shared" ref="L129:P129" si="226">J129+$R$1*K129/MAX(1,($A129*($A129-1)))++$R$1/$A129</f>
-        <v>5.11698324621031</v>
+        <v>5.11719687800422</v>
       </c>
       <c r="M129" s="1">
         <f ca="1" t="shared" si="225"/>
-        <v>0.59623065502605</v>
+        <v>0.0480712020117291</v>
       </c>
       <c r="N129" s="1">
         <f ca="1" t="shared" si="226"/>
-        <v>5.50944212494747</v>
+        <v>5.50796973480174</v>
       </c>
       <c r="O129" s="1">
         <f ca="1" t="shared" si="225"/>
-        <v>0.567221293347914</v>
+        <v>0.237225615784711</v>
       </c>
       <c r="P129" s="1">
         <f ca="1" t="shared" si="226"/>
-        <v>5.90181177705545</v>
+        <v>5.8993243903621</v>
       </c>
     </row>
     <row r="130" ht="16.5" spans="1:16">
@@ -13679,27 +13704,27 @@
       </c>
       <c r="K130" s="1">
         <f ca="1" t="shared" ref="K130:O130" si="230">RAND()</f>
-        <v>0.600372005408779</v>
+        <v>0.0499125936022906</v>
       </c>
       <c r="L130" s="1">
         <f ca="1" t="shared" ref="L130:P130" si="231">J130+$R$1*K130/MAX(1,($A130*($A130-1)))++$R$1/$A130</f>
-        <v>5.07691488615979</v>
+        <v>5.07524803958819</v>
       </c>
       <c r="M130" s="1">
         <f ca="1" t="shared" si="230"/>
-        <v>0.328176452378097</v>
+        <v>0.747979045583004</v>
       </c>
       <c r="N130" s="1">
         <f ca="1" t="shared" si="231"/>
-        <v>5.46550553675444</v>
+        <v>5.46510989474075</v>
       </c>
       <c r="O130" s="1">
         <f ca="1" t="shared" si="230"/>
-        <v>0.776862113874067</v>
+        <v>0.951345828388679</v>
       </c>
       <c r="P130" s="1">
         <f ca="1" t="shared" si="231"/>
-        <v>5.85545485274849</v>
+        <v>5.85558756500598</v>
       </c>
     </row>
     <row r="131" ht="16.5" spans="1:16">
@@ -13739,27 +13764,27 @@
       </c>
       <c r="K131" s="1">
         <f ca="1" t="shared" ref="K131:O131" si="232">RAND()</f>
-        <v>0.977817149135306</v>
+        <v>0.915746825856607</v>
       </c>
       <c r="L131" s="1">
         <f ca="1" t="shared" ref="L131:P131" si="233">J131+$R$1*K131/MAX(1,($A131*($A131-1)))++$R$1/$A131</f>
-        <v>5.03869355142854</v>
+        <v>5.03850848785288</v>
       </c>
       <c r="M131" s="1">
         <f ca="1" t="shared" si="232"/>
-        <v>0.429033354348831</v>
+        <v>0.582351871082393</v>
       </c>
       <c r="N131" s="1">
         <f ca="1" t="shared" si="233"/>
-        <v>5.42458810525785</v>
+        <v>5.42486016307972</v>
       </c>
       <c r="O131" s="1">
         <f ca="1" t="shared" si="232"/>
-        <v>0.995295218637135</v>
+        <v>0.918616427007583</v>
       </c>
       <c r="P131" s="1">
         <f ca="1" t="shared" si="233"/>
-        <v>5.81217097710829</v>
+        <v>5.81221441599269</v>
       </c>
     </row>
     <row r="132" ht="16.5" spans="1:16">
@@ -13799,27 +13824,27 @@
       </c>
       <c r="K132" s="1">
         <f ca="1" t="shared" ref="K132:O132" si="234">RAND()</f>
-        <v>0.259404787989981</v>
+        <v>0.966296777688442</v>
       </c>
       <c r="L132" s="1">
         <f ca="1" t="shared" ref="L132:P132" si="235">J132+$R$1*K132/MAX(1,($A132*($A132-1)))++$R$1/$A132</f>
-        <v>4.99782561593656</v>
+        <v>4.99990104749762</v>
       </c>
       <c r="M132" s="1">
         <f ca="1" t="shared" si="234"/>
-        <v>0.682105406813657</v>
+        <v>0.68649208419386</v>
       </c>
       <c r="N132" s="1">
         <f ca="1" t="shared" si="235"/>
-        <v>5.38150766351969</v>
+        <v>5.38359597434493</v>
       </c>
       <c r="O132" s="1">
         <f ca="1" t="shared" si="234"/>
-        <v>0.669949291563362</v>
+        <v>0.785511336221281</v>
       </c>
       <c r="P132" s="1">
         <f ca="1" t="shared" si="235"/>
-        <v>5.76515402080555</v>
+        <v>5.76758162125104</v>
       </c>
     </row>
     <row r="133" ht="16.5" spans="1:16">
@@ -13859,27 +13884,27 @@
       </c>
       <c r="K133" s="1">
         <f ca="1" t="shared" ref="K133:O133" si="236">RAND()</f>
-        <v>0.125960562508985</v>
+        <v>0.636244921835134</v>
       </c>
       <c r="L133" s="1">
         <f ca="1" t="shared" ref="L133:P133" si="237">J133+$R$1*K133/MAX(1,($A133*($A133-1)))++$R$1/$A133</f>
-        <v>4.95930476683585</v>
+        <v>4.96078025943163</v>
       </c>
       <c r="M133" s="1">
         <f ca="1" t="shared" si="236"/>
-        <v>0.456412741020075</v>
+        <v>0.350464378608861</v>
       </c>
       <c r="N133" s="1">
         <f ca="1" t="shared" si="237"/>
-        <v>5.33941236786818</v>
+        <v>5.34058150965893</v>
       </c>
       <c r="O133" s="1">
         <f ca="1" t="shared" si="236"/>
-        <v>0.0130279520629923</v>
+        <v>0.842769997485998</v>
       </c>
       <c r="P133" s="1">
         <f ca="1" t="shared" si="237"/>
-        <v>5.71823791711657</v>
+        <v>5.72180626676478</v>
       </c>
     </row>
     <row r="134" ht="16.5" spans="1:16">
@@ -13919,27 +13944,27 @@
       </c>
       <c r="K134" s="1">
         <f ca="1" t="shared" ref="K134:O134" si="238">RAND()</f>
-        <v>0.476555922771988</v>
+        <v>0.866501008002905</v>
       </c>
       <c r="L134" s="1">
         <f ca="1" t="shared" ref="L134:P134" si="239">J134+$R$1*K134/MAX(1,($A134*($A134-1)))++$R$1/$A134</f>
-        <v>4.92275164024486</v>
+        <v>4.92386221521988</v>
       </c>
       <c r="M134" s="1">
         <f ca="1" t="shared" si="238"/>
-        <v>0.670244912802232</v>
+        <v>0.633620568641428</v>
       </c>
       <c r="N134" s="1">
         <f ca="1" t="shared" si="239"/>
-        <v>5.30060036692748</v>
+        <v>5.30160663470222</v>
       </c>
       <c r="O134" s="1">
         <f ca="1" t="shared" si="238"/>
-        <v>0.42954024231167</v>
+        <v>0.282442527742521</v>
       </c>
       <c r="P134" s="1">
         <f ca="1" t="shared" si="239"/>
-        <v>5.67776355968867</v>
+        <v>5.6783508888824</v>
       </c>
     </row>
     <row r="135" ht="16.5" spans="1:16">
@@ -13979,27 +14004,27 @@
       </c>
       <c r="K135" s="1">
         <f ca="1" t="shared" ref="K135:O135" si="240">RAND()</f>
-        <v>0.663912879473421</v>
+        <v>0.903253106817275</v>
       </c>
       <c r="L135" s="1">
         <f ca="1" t="shared" ref="L135:P135" si="241">J135+$R$1*K135/MAX(1,($A135*($A135-1)))++$R$1/$A135</f>
-        <v>4.88627514554896</v>
+        <v>4.88694661964655</v>
       </c>
       <c r="M135" s="1">
         <f ca="1" t="shared" si="240"/>
-        <v>0.888611554221538</v>
+        <v>0.37651569524252</v>
       </c>
       <c r="N135" s="1">
         <f ca="1" t="shared" si="241"/>
-        <v>5.26190249251962</v>
+        <v>5.26113727079469</v>
       </c>
       <c r="O135" s="1">
         <f ca="1" t="shared" si="240"/>
-        <v>0.242369004031934</v>
+        <v>0.432857647765777</v>
       </c>
       <c r="P135" s="1">
         <f ca="1" t="shared" si="241"/>
-        <v>5.63571679227283</v>
+        <v>5.6354859904888</v>
       </c>
     </row>
     <row r="136" ht="16.5" spans="1:16">
@@ -14039,27 +14064,27 @@
       </c>
       <c r="K136" s="1">
         <f ca="1" t="shared" ref="K136:O136" si="242">RAND()</f>
-        <v>0.405803792052952</v>
+        <v>0.866439721365903</v>
       </c>
       <c r="L136" s="1">
         <f ca="1" t="shared" ref="L136:P136" si="243">J136+$R$1*K136/MAX(1,($A136*($A136-1)))++$R$1/$A136</f>
-        <v>4.84910393530142</v>
+        <v>4.85037711365773</v>
       </c>
       <c r="M136" s="1">
         <f ca="1" t="shared" si="242"/>
-        <v>0.557464606493435</v>
+        <v>0.684635648696918</v>
       </c>
       <c r="N136" s="1">
         <f ca="1" t="shared" si="243"/>
-        <v>5.22101511442385</v>
+        <v>5.22263978819807</v>
       </c>
       <c r="O136" s="1">
         <f ca="1" t="shared" si="242"/>
-        <v>0.946399649266383</v>
+        <v>0.986136323063586</v>
       </c>
       <c r="P136" s="1">
         <f ca="1" t="shared" si="243"/>
-        <v>5.59400129366449</v>
+        <v>5.59573579793567</v>
       </c>
     </row>
     <row r="137" ht="16.5" spans="1:16">
@@ -14099,27 +14124,27 @@
       </c>
       <c r="K137" s="1">
         <f ca="1" t="shared" ref="K137:O137" si="244">RAND()</f>
-        <v>0.426666352894792</v>
+        <v>0.872418576166974</v>
       </c>
       <c r="L137" s="1">
         <f ca="1" t="shared" ref="L137:P137" si="245">J137+$R$1*K137/MAX(1,($A137*($A137-1)))++$R$1/$A137</f>
-        <v>4.81325344867346</v>
+        <v>4.81446737085013</v>
       </c>
       <c r="M137" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.282382200893075</v>
+        <v>0.0345593111157321</v>
       </c>
       <c r="N137" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>5.1816695222053</v>
+        <v>5.18220854544467</v>
       </c>
       <c r="O137" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.916567750936346</v>
+        <v>0.730841904874036</v>
       </c>
       <c r="P137" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>5.55181268056842</v>
+        <v>5.55184591446666</v>
       </c>
     </row>
     <row r="138" ht="16.5" spans="1:16">
@@ -14273,27 +14298,27 @@
       </c>
       <c r="K140" s="1">
         <f ca="1" t="shared" ref="K140:O140" si="249">RAND()</f>
-        <v>0.182449984100255</v>
+        <v>0.189756676189047</v>
       </c>
       <c r="L140" s="1">
         <f ca="1" t="shared" ref="L140:P140" si="250">J140+$R$1*K140/MAX(1,($A140*($A140-1)))++$R$1/$A140</f>
-        <v>4.70801389319179</v>
+        <v>4.70803293889112</v>
       </c>
       <c r="M140" s="1">
         <f ca="1" t="shared" si="249"/>
-        <v>0.934632028292852</v>
+        <v>0.130669852668834</v>
       </c>
       <c r="N140" s="1">
         <f ca="1" t="shared" si="250"/>
-        <v>5.07016234493899</v>
+        <v>5.06808577449916</v>
       </c>
       <c r="O140" s="1">
         <f ca="1" t="shared" si="249"/>
-        <v>0.181614643786489</v>
+        <v>0.231967332384337</v>
       </c>
       <c r="P140" s="1">
         <f ca="1" t="shared" si="250"/>
-        <v>5.43034797376754</v>
+        <v>5.42840265316766</v>
       </c>
     </row>
     <row r="141" ht="16.5" spans="1:16">
@@ -14333,27 +14358,27 @@
       </c>
       <c r="K141" s="1">
         <f ca="1" t="shared" ref="K141:O141" si="251">RAND()</f>
-        <v>0.698040167785316</v>
+        <v>0.12536378515157</v>
       </c>
       <c r="L141" s="1">
         <f ca="1" t="shared" ref="L141:P141" si="252">J141+$R$1*K141/MAX(1,($A141*($A141-1)))++$R$1/$A141</f>
-        <v>4.67548314534375</v>
+        <v>4.67401172606668</v>
       </c>
       <c r="M141" s="1">
         <f ca="1" t="shared" si="251"/>
-        <v>0.0728137965835227</v>
+        <v>0.188437591801571</v>
       </c>
       <c r="N141" s="1">
         <f ca="1" t="shared" si="252"/>
-        <v>5.03281308829489</v>
+        <v>5.03163874968385</v>
       </c>
       <c r="O141" s="1">
         <f ca="1" t="shared" si="251"/>
-        <v>0.584572915766364</v>
+        <v>0.86006751308708</v>
       </c>
       <c r="P141" s="1">
         <f ca="1" t="shared" si="252"/>
-        <v>5.3914579313467</v>
+        <v>5.39099144113576</v>
       </c>
     </row>
     <row r="142" ht="16.5" spans="1:16">
@@ -14393,27 +14418,27 @@
       </c>
       <c r="K142" s="1">
         <f ca="1" t="shared" ref="K142:O142" si="253">RAND()</f>
-        <v>0.621287131901224</v>
+        <v>0.521836219207846</v>
       </c>
       <c r="L142" s="1">
         <f ca="1" t="shared" ref="L142:P142" si="254">J142+$R$1*K142/MAX(1,($A142*($A142-1)))++$R$1/$A142</f>
-        <v>4.64189789040502</v>
+        <v>4.64164598839718</v>
       </c>
       <c r="M142" s="1">
         <f ca="1" t="shared" si="253"/>
-        <v>0.123181485444877</v>
+        <v>0.355410079851384</v>
       </c>
       <c r="N142" s="1">
         <f ca="1" t="shared" si="254"/>
-        <v>4.99681982932459</v>
+        <v>4.99715614564098</v>
       </c>
       <c r="O142" s="1">
         <f ca="1" t="shared" si="253"/>
-        <v>0.63916646767991</v>
+        <v>0.0580549645213801</v>
       </c>
       <c r="P142" s="1">
         <f ca="1" t="shared" si="254"/>
-        <v>5.3530487210867</v>
+        <v>5.35191312376794</v>
       </c>
     </row>
     <row r="143" ht="16.5" spans="1:16">
@@ -14453,27 +14478,27 @@
       </c>
       <c r="K143" s="1">
         <f ca="1" t="shared" ref="K143:O143" si="255">RAND()</f>
-        <v>0.475324580394063</v>
+        <v>0.664070833565638</v>
       </c>
       <c r="L143" s="1">
         <f ca="1" t="shared" ref="L143:P143" si="256">J143+$R$1*K143/MAX(1,($A143*($A143-1)))++$R$1/$A143</f>
-        <v>4.60861883073717</v>
+        <v>4.60909017788824</v>
       </c>
       <c r="M143" s="1">
         <f ca="1" t="shared" si="255"/>
-        <v>0.076115213196541</v>
+        <v>0.239402483198481</v>
       </c>
       <c r="N143" s="1">
         <f ca="1" t="shared" si="256"/>
-        <v>4.96092158573966</v>
+        <v>4.96180070251914</v>
       </c>
       <c r="O143" s="1">
         <f ca="1" t="shared" si="255"/>
-        <v>0.185459080247326</v>
+        <v>0.810343068422792</v>
       </c>
       <c r="P143" s="1">
         <f ca="1" t="shared" si="256"/>
-        <v>5.31349740004455</v>
+        <v>5.31593701025169</v>
       </c>
     </row>
     <row r="144" ht="16.5" spans="1:16">
@@ -14513,27 +14538,27 @@
       </c>
       <c r="K144" s="1">
         <f ca="1" t="shared" ref="K144:O144" si="257">RAND()</f>
-        <v>0.852742869159644</v>
+        <v>0.453935963148194</v>
       </c>
       <c r="L144" s="1">
         <f ca="1" t="shared" ref="L144:P144" si="258">J144+$R$1*K144/MAX(1,($A144*($A144-1)))++$R$1/$A144</f>
-        <v>4.57710219361066</v>
+        <v>4.57612020083509</v>
       </c>
       <c r="M144" s="1">
         <f ca="1" t="shared" si="257"/>
-        <v>0.447452775574789</v>
+        <v>0.548928797527012</v>
       </c>
       <c r="N144" s="1">
         <f ca="1" t="shared" si="258"/>
-        <v>4.92785431804574</v>
+        <v>4.9271221923586</v>
       </c>
       <c r="O144" s="1">
         <f ca="1" t="shared" si="257"/>
-        <v>0.621357863707703</v>
+        <v>0.548932923410916</v>
       </c>
       <c r="P144" s="1">
         <f ca="1" t="shared" si="258"/>
-        <v>5.27903465357147</v>
+        <v>5.27812419404138</v>
       </c>
     </row>
     <row r="145" ht="16.5" spans="1:16">
@@ -14573,27 +14598,27 @@
       </c>
       <c r="K145" s="1">
         <f ca="1" t="shared" ref="K145:O145" si="259">RAND()</f>
-        <v>0.0714927420936007</v>
+        <v>0.419520031272103</v>
       </c>
       <c r="L145" s="1">
         <f ca="1" t="shared" ref="L145:P145" si="260">J145+$R$1*K145/MAX(1,($A145*($A145-1)))++$R$1/$A145</f>
-        <v>4.54320001151441</v>
+        <v>4.544045066121</v>
       </c>
       <c r="M145" s="1">
         <f ca="1" t="shared" si="259"/>
-        <v>0.849572088144171</v>
+        <v>0.723876092525075</v>
       </c>
       <c r="N145" s="1">
         <f ca="1" t="shared" si="260"/>
-        <v>4.89248510302603</v>
+        <v>4.89302495173805</v>
       </c>
       <c r="O145" s="1">
         <f ca="1" t="shared" si="259"/>
-        <v>0.446022972838068</v>
+        <v>0.178617054419616</v>
       </c>
       <c r="P145" s="1">
         <f ca="1" t="shared" si="260"/>
-        <v>5.24079032586217</v>
+        <v>5.24068087892924</v>
       </c>
     </row>
     <row r="146" ht="16.5" spans="1:16">
@@ -14633,27 +14658,27 @@
       </c>
       <c r="K146" s="1">
         <f ca="1" t="shared" ref="K146:O146" si="261">RAND()</f>
-        <v>0.747288521200101</v>
+        <v>0.910963337872674</v>
       </c>
       <c r="L146" s="1">
         <f ca="1" t="shared" ref="L146:P146" si="262">J146+$R$1*K146/MAX(1,($A146*($A146-1)))++$R$1/$A146</f>
-        <v>4.51328373688027</v>
+        <v>4.51367567849107</v>
       </c>
       <c r="M146" s="1">
         <f ca="1" t="shared" si="261"/>
-        <v>0.265805264621673</v>
+        <v>0.492652693408461</v>
       </c>
       <c r="N146" s="1">
         <f ca="1" t="shared" si="262"/>
-        <v>4.85874782994689</v>
+        <v>4.85968298858065</v>
       </c>
       <c r="O146" s="1">
         <f ca="1" t="shared" si="261"/>
-        <v>0.0123957875185674</v>
+        <v>0.352100023069459</v>
       </c>
       <c r="P146" s="1">
         <f ca="1" t="shared" si="262"/>
-        <v>5.20360509955302</v>
+        <v>5.20535372618379</v>
       </c>
     </row>
     <row r="147" ht="16.5" spans="1:16">
@@ -14693,27 +14718,27 @@
       </c>
       <c r="K147" s="1">
         <f ca="1" t="shared" ref="K147:O147" si="263">RAND()</f>
-        <v>0.843981041019977</v>
+        <v>0.575422934494747</v>
       </c>
       <c r="L147" s="1">
         <f ca="1" t="shared" ref="L147:P147" si="264">J147+$R$1*K147/MAX(1,($A147*($A147-1)))++$R$1/$A147</f>
-        <v>4.48239012999769</v>
+        <v>4.48175584065776</v>
       </c>
       <c r="M147" s="1">
         <f ca="1" t="shared" si="263"/>
-        <v>0.143903642948609</v>
+        <v>0.658924334316825</v>
       </c>
       <c r="N147" s="1">
         <f ca="1" t="shared" si="264"/>
-        <v>4.82519575976374</v>
+        <v>4.82577786317622</v>
       </c>
       <c r="O147" s="1">
         <f ca="1" t="shared" si="263"/>
-        <v>0.508847793082839</v>
+        <v>0.495765656340835</v>
       </c>
       <c r="P147" s="1">
         <f ca="1" t="shared" si="264"/>
-        <v>5.16886332658727</v>
+        <v>5.16941453218033</v>
       </c>
     </row>
     <row r="148" ht="16.5" spans="1:16">
@@ -14753,27 +14778,27 @@
       </c>
       <c r="K148" s="1">
         <f ca="1" t="shared" ref="K148:O148" si="265">RAND()</f>
-        <v>0.490140231422315</v>
+        <v>0.332342850204909</v>
       </c>
       <c r="L148" s="1">
         <f ca="1" t="shared" ref="L148:P148" si="266">J148+$R$1*K148/MAX(1,($A148*($A148-1)))++$R$1/$A148</f>
-        <v>4.45086697472608</v>
+        <v>4.4504993543244</v>
       </c>
       <c r="M148" s="1">
         <f ca="1" t="shared" si="265"/>
-        <v>0.226379819788213</v>
+        <v>0.875531777884317</v>
       </c>
       <c r="N148" s="1">
         <f ca="1" t="shared" si="266"/>
-        <v>4.79153042598828</v>
+        <v>4.7926751342561</v>
       </c>
       <c r="O148" s="1">
         <f ca="1" t="shared" si="265"/>
-        <v>0.249072123260716</v>
+        <v>0.161655966264323</v>
       </c>
       <c r="P148" s="1">
         <f ca="1" t="shared" si="266"/>
-        <v>5.13224674348726</v>
+        <v>5.13318779842129</v>
       </c>
     </row>
     <row r="149" ht="16.5" spans="1:16">
@@ -14813,27 +14838,27 @@
       </c>
       <c r="K149" s="1">
         <f ca="1" t="shared" ref="K149:O149" si="267">RAND()</f>
-        <v>0.935379634618219</v>
+        <v>0.279280386036641</v>
       </c>
       <c r="L149" s="1">
         <f ca="1" t="shared" ref="L149:P149" si="268">J149+$R$1*K149/MAX(1,($A149*($A149-1)))++$R$1/$A149</f>
-        <v>4.42162019588761</v>
+        <v>4.42011233771382</v>
       </c>
       <c r="M149" s="1">
         <f ca="1" t="shared" si="267"/>
-        <v>0.595668882216416</v>
+        <v>0.694569277171401</v>
       </c>
       <c r="N149" s="1">
         <f ca="1" t="shared" si="268"/>
-        <v>4.76082700982909</v>
+        <v>4.75954644618314</v>
       </c>
       <c r="O149" s="1">
         <f ca="1" t="shared" si="267"/>
-        <v>0.118729550855468</v>
+        <v>0.255122775879501</v>
       </c>
       <c r="P149" s="1">
         <f ca="1" t="shared" si="268"/>
-        <v>5.0989377138897</v>
+        <v>5.09797061141544</v>
       </c>
     </row>
     <row r="150" ht="16.5" spans="1:16">
@@ -14873,27 +14898,27 @@
       </c>
       <c r="K150" s="1">
         <f ca="1" t="shared" ref="K150:O150" si="269">RAND()</f>
-        <v>0.469953366174397</v>
+        <v>0.914622552766787</v>
       </c>
       <c r="L150" s="1">
         <f ca="1" t="shared" ref="L150:P150" si="270">J150+$R$1*K150/MAX(1,($A150*($A150-1)))++$R$1/$A150</f>
-        <v>4.39069008109508</v>
+        <v>4.39169830979677</v>
       </c>
       <c r="M150" s="1">
         <f ca="1" t="shared" si="269"/>
-        <v>0.462706194937515</v>
+        <v>0.208718988011959</v>
       </c>
       <c r="N150" s="1">
         <f ca="1" t="shared" si="270"/>
-        <v>4.72730967613167</v>
+        <v>4.72774202235801</v>
       </c>
       <c r="O150" s="1">
         <f ca="1" t="shared" si="269"/>
-        <v>0.475842748244774</v>
+        <v>0.103992851211123</v>
       </c>
       <c r="P150" s="1">
         <f ca="1" t="shared" si="270"/>
-        <v>5.06395905656937</v>
+        <v>5.06354828222381</v>
       </c>
     </row>
     <row r="151" ht="16.5" spans="1:16">
@@ -14933,27 +14958,27 @@
       </c>
       <c r="K151" s="1">
         <f ca="1" t="shared" ref="K151:O151" si="271">RAND()</f>
-        <v>0.6402885542673</v>
+        <v>0.144327907124999</v>
       </c>
       <c r="L151" s="1">
         <f ca="1" t="shared" ref="L151:P151" si="272">J151+$R$1*K151/MAX(1,($A151*($A151-1)))++$R$1/$A151</f>
-        <v>4.3616113837903</v>
+        <v>4.36050185214122</v>
       </c>
       <c r="M151" s="1">
         <f ca="1" t="shared" si="271"/>
-        <v>0.615286257169193</v>
+        <v>0.396563473897157</v>
       </c>
       <c r="N151" s="1">
         <f ca="1" t="shared" si="272"/>
-        <v>4.69632119644616</v>
+        <v>4.69472235208282</v>
       </c>
       <c r="O151" s="1">
         <f ca="1" t="shared" si="271"/>
-        <v>0.110031907779639</v>
+        <v>0.422600657636848</v>
       </c>
       <c r="P151" s="1">
         <f ca="1" t="shared" si="272"/>
-        <v>5.02990068617274</v>
+        <v>5.02900110075763</v>
       </c>
     </row>
     <row r="152" ht="16.5" spans="1:16">
@@ -14993,27 +15018,27 @@
       </c>
       <c r="K152" s="1">
         <f ca="1" t="shared" ref="K152:O152" si="273">RAND()</f>
-        <v>0.482801655084355</v>
+        <v>0.619166470076546</v>
       </c>
       <c r="L152" s="1">
         <f ca="1" t="shared" ref="L152:P152" si="274">J152+$R$1*K152/MAX(1,($A152*($A152-1)))++$R$1/$A152</f>
-        <v>4.33219161513264</v>
+        <v>4.3324926412143</v>
       </c>
       <c r="M152" s="1">
         <f ca="1" t="shared" si="273"/>
-        <v>0.123313191752354</v>
+        <v>0.674532403900122</v>
       </c>
       <c r="N152" s="1">
         <f ca="1" t="shared" si="274"/>
-        <v>4.66358965749854</v>
+        <v>4.66510750303306</v>
       </c>
       <c r="O152" s="1">
         <f ca="1" t="shared" si="273"/>
-        <v>0.940895975360622</v>
+        <v>0.895743759588841</v>
       </c>
       <c r="P152" s="1">
         <f ca="1" t="shared" si="274"/>
-        <v>4.9967925183713</v>
+        <v>4.99821069014032</v>
       </c>
     </row>
     <row r="153" ht="16.5" spans="1:16">
@@ -15053,27 +15078,27 @@
       </c>
       <c r="K153" s="1">
         <f ca="1" t="shared" ref="K153:O153" si="275">RAND()</f>
-        <v>0.982426530776519</v>
+        <v>0.26312860078913</v>
       </c>
       <c r="L153" s="1">
         <f ca="1" t="shared" ref="L153:P153" si="276">J153+$R$1*K153/MAX(1,($A153*($A153-1)))++$R$1/$A153</f>
-        <v>4.30459747850029</v>
+        <v>4.30303051716798</v>
       </c>
       <c r="M153" s="1">
         <f ca="1" t="shared" si="275"/>
-        <v>0.677742220078547</v>
+        <v>0.915532939172332</v>
       </c>
       <c r="N153" s="1">
         <f ca="1" t="shared" si="276"/>
-        <v>4.63502128082706</v>
+        <v>4.63397233692045</v>
       </c>
       <c r="O153" s="1">
         <f ca="1" t="shared" si="275"/>
-        <v>0.46799759523637</v>
+        <v>0.6426555924791</v>
       </c>
       <c r="P153" s="1">
         <f ca="1" t="shared" si="276"/>
-        <v>4.9649881630056</v>
+        <v>4.96431970445373</v>
       </c>
     </row>
     <row r="154" ht="16.5" spans="1:16">
@@ -15113,27 +15138,27 @@
       </c>
       <c r="K154" s="1">
         <f ca="1" t="shared" ref="K154:O154" si="277">RAND()</f>
-        <v>0.50662804654046</v>
+        <v>0.66302756609362</v>
       </c>
       <c r="L154" s="1">
         <f ca="1" t="shared" ref="L154:P154" si="278">J154+$R$1*K154/MAX(1,($A154*($A154-1)))++$R$1/$A154</f>
-        <v>4.27525504825967</v>
+        <v>4.27559130453667</v>
       </c>
       <c r="M154" s="1">
         <f ca="1" t="shared" si="277"/>
-        <v>0.651807109711602</v>
+        <v>0.398693570825402</v>
       </c>
       <c r="N154" s="1">
         <f ca="1" t="shared" si="278"/>
-        <v>4.60345380795548</v>
+        <v>4.60324587447738</v>
       </c>
       <c r="O154" s="1">
         <f ca="1" t="shared" si="277"/>
-        <v>0.732913884547882</v>
+        <v>0.137399782995886</v>
       </c>
       <c r="P154" s="1">
         <f ca="1" t="shared" si="278"/>
-        <v>4.93182694582215</v>
+        <v>4.93033866726848</v>
       </c>
     </row>
     <row r="155" ht="16.5" spans="1:16">
@@ -15173,27 +15198,27 @@
       </c>
       <c r="K155" s="1">
         <f ca="1" t="shared" ref="K155:O155" si="279">RAND()</f>
-        <v>0.801966208025797</v>
+        <v>0.0389381187974223</v>
       </c>
       <c r="L155" s="1">
         <f ca="1" t="shared" ref="L155:P155" si="280">J155+$R$1*K155/MAX(1,($A155*($A155-1)))++$R$1/$A155</f>
-        <v>4.24794577329604</v>
+        <v>4.2463265811875</v>
       </c>
       <c r="M155" s="1">
         <f ca="1" t="shared" si="279"/>
-        <v>0.362937485627268</v>
+        <v>0.248841632356281</v>
       </c>
       <c r="N155" s="1">
         <f ca="1" t="shared" si="280"/>
-        <v>4.5733912734353</v>
+        <v>4.57152996297248</v>
       </c>
       <c r="O155" s="1">
         <f ca="1" t="shared" si="279"/>
-        <v>0.549099133638734</v>
+        <v>0.307567295938602</v>
       </c>
       <c r="P155" s="1">
         <f ca="1" t="shared" si="280"/>
-        <v>4.89923181993738</v>
+        <v>4.89685796419466</v>
       </c>
     </row>
     <row r="156" ht="16.5" spans="1:16">
@@ -15233,27 +15258,27 @@
       </c>
       <c r="K156" s="1">
         <f ca="1" t="shared" ref="K156:O156" si="281">RAND()</f>
-        <v>0.0991371294072729</v>
+        <v>0.434641819822373</v>
       </c>
       <c r="L156" s="1">
         <f ca="1" t="shared" ref="L156:P156" si="282">J156+$R$1*K156/MAX(1,($A156*($A156-1)))++$R$1/$A156</f>
-        <v>4.21889220177924</v>
+        <v>4.21959497658111</v>
       </c>
       <c r="M156" s="1">
         <f ca="1" t="shared" si="281"/>
-        <v>0.710070289156725</v>
+        <v>0.210688954969326</v>
       </c>
       <c r="N156" s="1">
         <f ca="1" t="shared" si="282"/>
-        <v>4.54296021662875</v>
+        <v>4.54261694758021</v>
       </c>
       <c r="O156" s="1">
         <f ca="1" t="shared" si="281"/>
-        <v>0.431802266913488</v>
+        <v>0.767014991847148</v>
       </c>
       <c r="P156" s="1">
         <f ca="1" t="shared" si="282"/>
-        <v>4.86644534915266</v>
+        <v>4.86680424333188</v>
       </c>
     </row>
     <row r="157" ht="16.5" spans="1:16">
@@ -15293,27 +15318,27 @@
       </c>
       <c r="K157" s="1">
         <f ca="1" t="shared" ref="K157:O157" si="283">RAND()</f>
-        <v>0.971658653700924</v>
+        <v>0.283872757371769</v>
       </c>
       <c r="L157" s="1">
         <f ca="1" t="shared" ref="L157:P157" si="284">J157+$R$1*K157/MAX(1,($A157*($A157-1)))++$R$1/$A157</f>
-        <v>4.19348978216232</v>
+        <v>4.19206756153303</v>
       </c>
       <c r="M157" s="1">
         <f ca="1" t="shared" si="283"/>
-        <v>0.482293102542092</v>
+        <v>0.823055557033796</v>
       </c>
       <c r="N157" s="1">
         <f ca="1" t="shared" si="284"/>
-        <v>4.51499990024037</v>
+        <v>4.51428231661374</v>
       </c>
       <c r="O157" s="1">
         <f ca="1" t="shared" si="283"/>
-        <v>0.95117431204223</v>
+        <v>0.684422668628677</v>
       </c>
       <c r="P157" s="1">
         <f ca="1" t="shared" si="284"/>
-        <v>4.83747958244062</v>
+        <v>4.83621040319072</v>
       </c>
     </row>
     <row r="158" ht="16.5" spans="1:16">
@@ -15353,27 +15378,27 @@
       </c>
       <c r="K158" s="1">
         <f ca="1" t="shared" ref="K158:O158" si="285">RAND()</f>
-        <v>0.756867121157168</v>
+        <v>0.0228781247198615</v>
       </c>
       <c r="L158" s="1">
         <f ca="1" t="shared" ref="L158:P158" si="286">J158+$R$1*K158/MAX(1,($A158*($A158-1)))++$R$1/$A158</f>
-        <v>4.16617031504401</v>
+        <v>4.16467188903462</v>
       </c>
       <c r="M158" s="1">
         <f ca="1" t="shared" si="285"/>
-        <v>0.0384432267683179</v>
+        <v>0.442289844130787</v>
       </c>
       <c r="N158" s="1">
         <f ca="1" t="shared" si="286"/>
-        <v>4.48472013381498</v>
+        <v>4.48404615378256</v>
       </c>
       <c r="O158" s="1">
         <f ca="1" t="shared" si="285"/>
-        <v>0.708396265724768</v>
+        <v>0.730726176551307</v>
       </c>
       <c r="P158" s="1">
         <f ca="1" t="shared" si="286"/>
-        <v>4.80463765028102</v>
+        <v>4.80400925638046</v>
       </c>
     </row>
     <row r="159" ht="16.5" spans="1:16">
@@ -15527,27 +15552,27 @@
       </c>
       <c r="K161" s="1">
         <f ca="1" t="shared" ref="K161:O161" si="289">RAND()</f>
-        <v>0.316622996670307</v>
+        <v>0.207609238286062</v>
       </c>
       <c r="L161" s="1">
         <f ca="1" t="shared" ref="L161:P161" si="290">J161+$R$1*K161/MAX(1,($A161*($A161-1)))++$R$1/$A161</f>
-        <v>4.08670719928591</v>
+        <v>4.08649294268531</v>
       </c>
       <c r="M161" s="1">
         <f ca="1" t="shared" si="289"/>
-        <v>0.536233395757451</v>
+        <v>0.94350683115999</v>
       </c>
       <c r="N161" s="1">
         <f ca="1" t="shared" si="290"/>
-        <v>4.40026111712348</v>
+        <v>4.40084731931888</v>
       </c>
       <c r="O161" s="1">
         <f ca="1" t="shared" si="289"/>
-        <v>0.247423633414281</v>
+        <v>0.776158492397464</v>
       </c>
       <c r="P161" s="1">
         <f ca="1" t="shared" si="290"/>
-        <v>4.71324740571117</v>
+        <v>4.71487278805394</v>
       </c>
     </row>
     <row r="162" ht="16.5" spans="1:16">
@@ -15587,27 +15612,27 @@
       </c>
       <c r="K162" s="1">
         <f ca="1" t="shared" ref="K162:O162" si="291">RAND()</f>
-        <v>0.0456916663892792</v>
+        <v>0.593398850368057</v>
       </c>
       <c r="L162" s="1">
         <f ca="1" t="shared" ref="L162:P162" si="292">J162+$R$1*K162/MAX(1,($A162*($A162-1)))++$R$1/$A162</f>
-        <v>4.06064769345184</v>
+        <v>4.06171078969404</v>
       </c>
       <c r="M162" s="1">
         <f ca="1" t="shared" si="291"/>
-        <v>0.366511292131</v>
+        <v>0.0391485508184053</v>
       </c>
       <c r="N162" s="1">
         <f ca="1" t="shared" si="292"/>
-        <v>4.37191809580458</v>
+        <v>4.3723457829992</v>
       </c>
       <c r="O162" s="1">
         <f ca="1" t="shared" si="291"/>
-        <v>0.951015424639877</v>
+        <v>0.371527272671447</v>
       </c>
       <c r="P162" s="1">
         <f ca="1" t="shared" si="292"/>
-        <v>4.68432301704806</v>
+        <v>4.68362592133901</v>
       </c>
     </row>
     <row r="163" ht="16.5" spans="1:16">
@@ -15647,27 +15672,27 @@
       </c>
       <c r="K163" s="1">
         <f ca="1" t="shared" ref="K163:O163" si="293">RAND()</f>
-        <v>0.945112341325919</v>
+        <v>0.840725868438</v>
       </c>
       <c r="L163" s="1">
         <f ca="1" t="shared" ref="L163:P163" si="294">J163+$R$1*K163/MAX(1,($A163*($A163-1)))++$R$1/$A163</f>
-        <v>4.03716185940749</v>
+        <v>4.03696174731316</v>
       </c>
       <c r="M163" s="1">
         <f ca="1" t="shared" si="293"/>
-        <v>0.858247790767617</v>
+        <v>0.483739358375265</v>
       </c>
       <c r="N163" s="1">
         <f ca="1" t="shared" si="294"/>
-        <v>4.34744912225307</v>
+        <v>4.34653106592058</v>
       </c>
       <c r="O163" s="1">
         <f ca="1" t="shared" si="293"/>
-        <v>0.107014508419901</v>
+        <v>0.335582490224503</v>
       </c>
       <c r="P163" s="1">
         <f ca="1" t="shared" si="294"/>
-        <v>4.65629624768137</v>
+        <v>4.65581636323334</v>
       </c>
     </row>
     <row r="164" ht="16.5" spans="1:16">
@@ -15821,27 +15846,27 @@
       </c>
       <c r="K166" s="1">
         <f ca="1" t="shared" ref="K166:O166" si="297">RAND()</f>
-        <v>0.31465456569605</v>
+        <v>0.0367493227908349</v>
       </c>
       <c r="L166" s="1">
         <f ca="1" t="shared" ref="L166:P166" si="298">J166+$R$1*K166/MAX(1,($A166*($A166-1)))++$R$1/$A166</f>
-        <v>3.96214829003269</v>
+        <v>3.96163479180117</v>
       </c>
       <c r="M166" s="1">
         <f ca="1" t="shared" si="297"/>
-        <v>0.31611753905501</v>
+        <v>0.34325249165544</v>
       </c>
       <c r="N166" s="1">
         <f ca="1" t="shared" si="298"/>
-        <v>4.26576269790235</v>
+        <v>4.26529933816416</v>
       </c>
       <c r="O166" s="1">
         <f ca="1" t="shared" si="297"/>
-        <v>0.735779718172795</v>
+        <v>0.972779432285425</v>
       </c>
       <c r="P166" s="1">
         <f ca="1" t="shared" si="298"/>
-        <v>4.57015253477997</v>
+        <v>4.57012709025634</v>
       </c>
     </row>
     <row r="167" ht="16.5" spans="1:16">
@@ -15881,27 +15906,27 @@
       </c>
       <c r="K167" s="1">
         <f ca="1" t="shared" ref="K167:O167" si="299">RAND()</f>
-        <v>0.693481094864809</v>
+        <v>0.171646833715583</v>
       </c>
       <c r="L167" s="1">
         <f ca="1" t="shared" ref="L167:P167" si="300">J167+$R$1*K167/MAX(1,($A167*($A167-1)))++$R$1/$A167</f>
-        <v>3.93883439411257</v>
+        <v>3.93788179414698</v>
       </c>
       <c r="M167" s="1">
         <f ca="1" t="shared" si="299"/>
-        <v>0.411858299051561</v>
+        <v>0.993611807044426</v>
       </c>
       <c r="N167" s="1">
         <f ca="1" t="shared" si="300"/>
-        <v>4.24079105402322</v>
+        <v>4.24090043563483</v>
       </c>
       <c r="O167" s="1">
         <f ca="1" t="shared" si="299"/>
-        <v>0.85765867233341</v>
+        <v>0.563956130835687</v>
       </c>
       <c r="P167" s="1">
         <f ca="1" t="shared" si="300"/>
-        <v>4.54356151527246</v>
+        <v>4.54313474766629</v>
       </c>
     </row>
     <row r="168" ht="16.5" spans="1:16">
@@ -15941,27 +15966,27 @@
       </c>
       <c r="K168" s="1">
         <f ca="1" t="shared" ref="K168:O168" si="301">RAND()</f>
-        <v>0.0818801023183058</v>
+        <v>0.559518861718097</v>
       </c>
       <c r="L168" s="1">
         <f ca="1" t="shared" ref="L168:P168" si="302">J168+$R$1*K168/MAX(1,($A168*($A168-1)))++$R$1/$A168</f>
-        <v>3.91400670965716</v>
+        <v>3.91486818927516</v>
       </c>
       <c r="M168" s="1">
         <f ca="1" t="shared" si="301"/>
-        <v>0.765404228730195</v>
+        <v>0.809420781931021</v>
       </c>
       <c r="N168" s="1">
         <f ca="1" t="shared" si="302"/>
-        <v>4.21478840691698</v>
+        <v>4.21572927574426</v>
       </c>
       <c r="O168" s="1">
         <f ca="1" t="shared" si="301"/>
-        <v>0.0731041105265664</v>
+        <v>0.176068745961786</v>
       </c>
       <c r="P168" s="1">
         <f ca="1" t="shared" si="302"/>
-        <v>4.51432145667985</v>
+        <v>4.51544803475509</v>
       </c>
     </row>
     <row r="169" ht="16.5" spans="1:16">
@@ -16001,27 +16026,27 @@
       </c>
       <c r="K169" s="1">
         <f ca="1" t="shared" ref="K169:O169" si="303">RAND()</f>
-        <v>0.375076344124229</v>
+        <v>0.127700316997654</v>
       </c>
       <c r="L169" s="1">
         <f ca="1" t="shared" ref="L169:P169" si="304">J169+$R$1*K169/MAX(1,($A169*($A169-1)))++$R$1/$A169</f>
-        <v>3.89110186117787</v>
+        <v>3.89066099999465</v>
       </c>
       <c r="M169" s="1">
         <f ca="1" t="shared" si="303"/>
-        <v>0.131295622117587</v>
+        <v>0.0598057969472932</v>
       </c>
       <c r="N169" s="1">
         <f ca="1" t="shared" si="304"/>
-        <v>4.188954897288</v>
+        <v>4.18838663051387</v>
       </c>
       <c r="O169" s="1">
         <f ca="1" t="shared" si="303"/>
-        <v>0.400589451159715</v>
+        <v>0.518911446331743</v>
       </c>
       <c r="P169" s="1">
         <f ca="1" t="shared" si="304"/>
-        <v>4.48728785539172</v>
+        <v>4.4869304561596</v>
       </c>
     </row>
     <row r="170" ht="16.5" spans="1:16">
@@ -16061,27 +16086,27 @@
       </c>
       <c r="K170" s="1">
         <f ca="1" t="shared" ref="K170:O170" si="305">RAND()</f>
-        <v>0.623036171725732</v>
+        <v>0.871181352024839</v>
       </c>
       <c r="L170" s="1">
         <f ca="1" t="shared" ref="L170:P170" si="306">J170+$R$1*K170/MAX(1,($A170*($A170-1)))++$R$1/$A170</f>
-        <v>3.86838376333426</v>
+        <v>3.86882076174983</v>
       </c>
       <c r="M170" s="1">
         <f ca="1" t="shared" si="305"/>
-        <v>0.310587100415163</v>
+        <v>0.800055568767865</v>
       </c>
       <c r="N170" s="1">
         <f ca="1" t="shared" si="306"/>
-        <v>4.16478871384922</v>
+        <v>4.16608769533811</v>
       </c>
       <c r="O170" s="1">
         <f ca="1" t="shared" si="305"/>
-        <v>0.982826552369839</v>
+        <v>0.880320638946008</v>
       </c>
       <c r="P170" s="1">
         <f ca="1" t="shared" si="306"/>
-        <v>4.46237751800597</v>
+        <v>4.463495980487</v>
       </c>
     </row>
     <row r="171" ht="16.5" spans="1:16">
@@ -16121,27 +16146,27 @@
       </c>
       <c r="K171" s="1">
         <f ca="1" t="shared" ref="K171:O171" si="307">RAND()</f>
-        <v>0.691682324861054</v>
+        <v>0.784867990686037</v>
       </c>
       <c r="L171" s="1">
         <f ca="1" t="shared" ref="L171:P171" si="308">J171+$R$1*K171/MAX(1,($A171*($A171-1)))++$R$1/$A171</f>
-        <v>3.84561726822984</v>
+        <v>3.84577944307464</v>
       </c>
       <c r="M171" s="1">
         <f ca="1" t="shared" si="307"/>
-        <v>0.687579777255205</v>
+        <v>0.0348605598370113</v>
       </c>
       <c r="N171" s="1">
         <f ca="1" t="shared" si="308"/>
-        <v>4.14093153863926</v>
+        <v>4.13995775939875</v>
       </c>
       <c r="O171" s="1">
         <f ca="1" t="shared" si="307"/>
-        <v>0.0342771673188944</v>
+        <v>0.0676920889891606</v>
       </c>
       <c r="P171" s="1">
         <f ca="1" t="shared" si="308"/>
-        <v>4.43510883966139</v>
+        <v>4.43419321378265</v>
       </c>
     </row>
     <row r="172" ht="16.5" spans="1:16">
@@ -16181,27 +16206,27 @@
       </c>
       <c r="K172" s="1">
         <f ca="1" t="shared" ref="K172:O172" si="309">RAND()</f>
-        <v>0.611368368238394</v>
+        <v>0.022095030104949</v>
       </c>
       <c r="L172" s="1">
         <f ca="1" t="shared" ref="L172:P172" si="310">J172+$R$1*K172/MAX(1,($A172*($A172-1)))++$R$1/$A172</f>
-        <v>3.8228609707056</v>
+        <v>3.82184742867235</v>
       </c>
       <c r="M172" s="1">
         <f ca="1" t="shared" si="309"/>
-        <v>0.244317878857667</v>
+        <v>0.461768396525737</v>
       </c>
       <c r="N172" s="1">
         <f ca="1" t="shared" si="310"/>
-        <v>4.11567885491416</v>
+        <v>4.11503932477921</v>
       </c>
       <c r="O172" s="1">
         <f ca="1" t="shared" si="309"/>
-        <v>0.452626551980554</v>
+        <v>0.370704054758529</v>
       </c>
       <c r="P172" s="1">
         <f ca="1" t="shared" si="310"/>
-        <v>4.40885502717419</v>
+        <v>4.40807459147126</v>
       </c>
     </row>
     <row r="173" ht="16.5" spans="1:16">
@@ -16241,27 +16266,27 @@
       </c>
       <c r="K173" s="1">
         <f ca="1" t="shared" ref="K173:O173" si="311">RAND()</f>
-        <v>0.796014720983948</v>
+        <v>0.932580610448176</v>
       </c>
       <c r="L173" s="1">
         <f ca="1" t="shared" ref="L173:P173" si="312">J173+$R$1*K173/MAX(1,($A173*($A173-1)))++$R$1/$A173</f>
-        <v>3.80082281844312</v>
+        <v>3.80105497859793</v>
       </c>
       <c r="M173" s="1">
         <f ca="1" t="shared" si="311"/>
-        <v>0.528579329269264</v>
+        <v>0.224895549619725</v>
       </c>
       <c r="N173" s="1">
         <f ca="1" t="shared" si="312"/>
-        <v>4.09241907053286</v>
+        <v>4.09213497239234</v>
       </c>
       <c r="O173" s="1">
         <f ca="1" t="shared" si="311"/>
-        <v>0.21355812114534</v>
+        <v>0.638193660082393</v>
       </c>
       <c r="P173" s="1">
         <f ca="1" t="shared" si="312"/>
-        <v>4.38347979085305</v>
+        <v>4.38391756735372</v>
       </c>
     </row>
     <row r="174" ht="16.5" spans="1:16">
@@ -16301,27 +16326,27 @@
       </c>
       <c r="K174" s="1">
         <f ca="1" t="shared" ref="K174:O174" si="313">RAND()</f>
-        <v>0.845966626331044</v>
+        <v>0.449660915113974</v>
       </c>
       <c r="L174" s="1">
         <f ca="1" t="shared" ref="L174:P174" si="314">J174+$R$1*K174/MAX(1,($A174*($A174-1)))++$R$1/$A174</f>
-        <v>3.77881094002274</v>
+        <v>3.77814501430823</v>
       </c>
       <c r="M174" s="1">
         <f ca="1" t="shared" si="313"/>
-        <v>0.56145470472357</v>
+        <v>0.621444371783886</v>
       </c>
       <c r="N174" s="1">
         <f ca="1" t="shared" si="314"/>
-        <v>4.06877171214387</v>
+        <v>4.06820658906926</v>
       </c>
       <c r="O174" s="1">
         <f ca="1" t="shared" si="313"/>
-        <v>0.634762036420426</v>
+        <v>0.729473560653999</v>
       </c>
       <c r="P174" s="1">
         <f ca="1" t="shared" si="314"/>
-        <v>4.3588556650213</v>
+        <v>4.35844968888216</v>
       </c>
     </row>
     <row r="175" ht="16.5" spans="1:16">
@@ -16361,27 +16386,27 @@
       </c>
       <c r="K175" s="1">
         <f ca="1" t="shared" ref="K175:O175" si="315">RAND()</f>
-        <v>0.95196600882557</v>
+        <v>0.222197775328725</v>
       </c>
       <c r="L175" s="1">
         <f ca="1" t="shared" ref="L175:P175" si="316">J175+$R$1*K175/MAX(1,($A175*($A175-1)))++$R$1/$A175</f>
-        <v>3.75714564814435</v>
+        <v>3.75593348909596</v>
       </c>
       <c r="M175" s="1">
         <f ca="1" t="shared" si="315"/>
-        <v>0.255980981235062</v>
+        <v>0.217082772695268</v>
       </c>
       <c r="N175" s="1">
         <f ca="1" t="shared" si="316"/>
-        <v>4.04492715930845</v>
+        <v>4.04365038958877</v>
       </c>
       <c r="O175" s="1">
         <f ca="1" t="shared" si="315"/>
-        <v>0.658902033239524</v>
+        <v>0.714566551966202</v>
       </c>
       <c r="P175" s="1">
         <f ca="1" t="shared" si="316"/>
-        <v>4.33337793007657</v>
+        <v>4.33219362019133</v>
       </c>
     </row>
     <row r="176" ht="16.5" spans="1:16">
@@ -16421,27 +16446,27 @@
       </c>
       <c r="K176" s="1">
         <f ca="1" t="shared" ref="K176:O176" si="317">RAND()</f>
-        <v>0.642172426443474</v>
+        <v>0.948123127852096</v>
       </c>
       <c r="L176" s="1">
         <f ca="1" t="shared" ref="L176:P176" si="318">J176+$R$1*K176/MAX(1,($A176*($A176-1)))++$R$1/$A176</f>
-        <v>3.73504461810582</v>
+        <v>3.73554700020994</v>
       </c>
       <c r="M176" s="1">
         <f ca="1" t="shared" si="317"/>
-        <v>0.713131693183489</v>
+        <v>0.835997933235475</v>
       </c>
       <c r="N176" s="1">
         <f ca="1" t="shared" si="318"/>
-        <v>4.02192989182205</v>
+        <v>4.02263402473085</v>
       </c>
       <c r="O176" s="1">
         <f ca="1" t="shared" si="317"/>
-        <v>0.990660678430287</v>
+        <v>0.984635631175947</v>
       </c>
       <c r="P176" s="1">
         <f ca="1" t="shared" si="318"/>
-        <v>4.30927087815773</v>
+        <v>4.30996511772129</v>
       </c>
     </row>
     <row r="177" ht="16.5" spans="1:16">
@@ -16481,27 +16506,27 @@
       </c>
       <c r="K177" s="1">
         <f ca="1" t="shared" ref="K177:O177" si="319">RAND()</f>
-        <v>0.769527423778976</v>
+        <v>0.606206217559284</v>
       </c>
       <c r="L177" s="1">
         <f ca="1" t="shared" ref="L177:P177" si="320">J177+$R$1*K177/MAX(1,($A177*($A177-1)))++$R$1/$A177</f>
-        <v>3.71391157049315</v>
+        <v>3.71364643866487</v>
       </c>
       <c r="M177" s="1">
         <f ca="1" t="shared" si="319"/>
-        <v>0.558909992550241</v>
+        <v>0.513959985025248</v>
       </c>
       <c r="N177" s="1">
         <f ca="1" t="shared" si="320"/>
-        <v>3.99890980100054</v>
+        <v>3.99857169838082</v>
       </c>
       <c r="O177" s="1">
         <f ca="1" t="shared" si="319"/>
-        <v>0.743271354379516</v>
+        <v>0.019392715273298</v>
       </c>
       <c r="P177" s="1">
         <f ca="1" t="shared" si="320"/>
-        <v>4.28420731943297</v>
+        <v>4.28269408915237</v>
       </c>
     </row>
     <row r="178" ht="16.5" spans="1:16">
@@ -16541,27 +16566,27 @@
       </c>
       <c r="K178" s="1">
         <f ca="1" t="shared" ref="K178:O178" si="321">RAND()</f>
-        <v>0.301173184276524</v>
+        <v>0.99449174732599</v>
       </c>
       <c r="L178" s="1">
         <f ca="1" t="shared" ref="L178:P178" si="322">J178+$R$1*K178/MAX(1,($A178*($A178-1)))++$R$1/$A178</f>
-        <v>3.69206017781246</v>
+        <v>3.69317297725238</v>
       </c>
       <c r="M178" s="1">
         <f ca="1" t="shared" si="321"/>
-        <v>0.24412245241795</v>
+        <v>0.472536325738922</v>
       </c>
       <c r="N178" s="1">
         <f ca="1" t="shared" si="322"/>
-        <v>3.97493787820476</v>
+        <v>3.97641728953689</v>
       </c>
       <c r="O178" s="1">
         <f ca="1" t="shared" si="321"/>
-        <v>0.131358742929683</v>
+        <v>0.0161986531772673</v>
       </c>
       <c r="P178" s="1">
         <f ca="1" t="shared" si="322"/>
-        <v>4.25763458907875</v>
+        <v>4.25892916462224</v>
       </c>
     </row>
     <row r="179" ht="16.5" spans="1:16">
@@ -16601,27 +16626,27 @@
       </c>
       <c r="K179" s="1">
         <f ca="1" t="shared" ref="K179:O179" si="323">RAND()</f>
-        <v>0.886268285865971</v>
+        <v>0.463437877405256</v>
       </c>
       <c r="L179" s="1">
         <f ca="1" t="shared" ref="L179:P179" si="324">J179+$R$1*K179/MAX(1,($A179*($A179-1)))++$R$1/$A179</f>
-        <v>3.67213589202988</v>
+        <v>3.6714648604669</v>
       </c>
       <c r="M179" s="1">
         <f ca="1" t="shared" si="323"/>
-        <v>0.917475049784889</v>
+        <v>0.845777617193302</v>
       </c>
       <c r="N179" s="1">
         <f ca="1" t="shared" si="324"/>
-        <v>3.95449080069773</v>
+        <v>3.95370598535929</v>
       </c>
       <c r="O179" s="1">
         <f ca="1" t="shared" si="323"/>
-        <v>0.113146254344223</v>
+        <v>0.652105549657908</v>
       </c>
       <c r="P179" s="1">
         <f ca="1" t="shared" si="324"/>
-        <v>4.23556924012886</v>
+        <v>4.23563975281574</v>
       </c>
     </row>
     <row r="180" ht="16.5" spans="1:16">
@@ -16661,27 +16686,27 @@
       </c>
       <c r="K180" s="1">
         <f ca="1" t="shared" ref="K180:O180" si="325">RAND()</f>
-        <v>0.0549206226011512</v>
+        <v>0.350388284737618</v>
       </c>
       <c r="L180" s="1">
         <f ca="1" t="shared" ref="L180:P180" si="326">J180+$R$1*K180/MAX(1,($A180*($A180-1)))++$R$1/$A180</f>
-        <v>3.65020231093873</v>
+        <v>3.65066597872817</v>
       </c>
       <c r="M180" s="1">
         <f ca="1" t="shared" si="325"/>
-        <v>0.613682293247714</v>
+        <v>0.308624900373839</v>
       </c>
       <c r="N180" s="1">
         <f ca="1" t="shared" si="326"/>
-        <v>3.9304949515345</v>
+        <v>3.93047990268205</v>
       </c>
       <c r="O180" s="1">
         <f ca="1" t="shared" si="325"/>
-        <v>0.187042289532085</v>
+        <v>0.958420894288291</v>
       </c>
       <c r="P180" s="1">
         <f ca="1" t="shared" si="326"/>
-        <v>4.21011807985277</v>
+        <v>4.21131353034869</v>
       </c>
     </row>
     <row r="181" ht="16.5" spans="1:16">
@@ -16721,27 +16746,27 @@
       </c>
       <c r="K181" s="1">
         <f ca="1" t="shared" ref="K181:O181" si="327">RAND()</f>
-        <v>0.618426849154694</v>
+        <v>0.309688933421029</v>
       </c>
       <c r="L181" s="1">
         <f ca="1" t="shared" ref="L181:P181" si="328">J181+$R$1*K181/MAX(1,($A181*($A181-1)))++$R$1/$A181</f>
-        <v>3.63069277909552</v>
+        <v>3.63021366997738</v>
       </c>
       <c r="M181" s="1">
         <f ca="1" t="shared" si="327"/>
-        <v>0.661539608149198</v>
+        <v>0.693997363316754</v>
       </c>
       <c r="N181" s="1">
         <f ca="1" t="shared" si="328"/>
-        <v>3.90949715465131</v>
+        <v>3.90906841448904</v>
       </c>
       <c r="O181" s="1">
         <f ca="1" t="shared" si="327"/>
-        <v>0.0319941128665067</v>
+        <v>0.365782135871125</v>
       </c>
       <c r="P181" s="1">
         <f ca="1" t="shared" si="328"/>
-        <v>4.18732458189039</v>
+        <v>4.18741382438332</v>
       </c>
     </row>
     <row r="182" ht="16.5" spans="1:16">
@@ -16781,27 +16806,27 @@
       </c>
       <c r="K182" s="1">
         <f ca="1" t="shared" ref="K182:O182" si="329">RAND()</f>
-        <v>0.125525043551333</v>
+        <v>0.507238418206479</v>
       </c>
       <c r="L182" s="1">
         <f ca="1" t="shared" ref="L182:P182" si="330">J182+$R$1*K182/MAX(1,($A182*($A182-1)))++$R$1/$A182</f>
-        <v>3.60976906851373</v>
+        <v>3.61035487786711</v>
       </c>
       <c r="M182" s="1">
         <f ca="1" t="shared" si="329"/>
-        <v>0.137464441808355</v>
+        <v>0.536228739152586</v>
       </c>
       <c r="N182" s="1">
         <f ca="1" t="shared" si="330"/>
-        <v>3.88622312689588</v>
+        <v>3.88742091337839</v>
       </c>
       <c r="O182" s="1">
         <f ca="1" t="shared" si="329"/>
-        <v>0.651263931456679</v>
+        <v>0.992078634882462</v>
       </c>
       <c r="P182" s="1">
         <f ca="1" t="shared" si="330"/>
-        <v>4.16346570505957</v>
+        <v>4.16518653436501</v>
       </c>
     </row>
     <row r="183" ht="16.5" spans="1:16">
@@ -16841,27 +16866,27 @@
       </c>
       <c r="K183" s="1">
         <f ca="1" t="shared" ref="K183:O183" si="331">RAND()</f>
-        <v>0.451412360804146</v>
+        <v>0.510110948004659</v>
       </c>
       <c r="L183" s="1">
         <f ca="1" t="shared" ref="L183:P183" si="332">J183+$R$1*K183/MAX(1,($A183*($A183-1)))++$R$1/$A183</f>
-        <v>3.59032756414426</v>
+        <v>3.59041665798677</v>
       </c>
       <c r="M183" s="1">
         <f ca="1" t="shared" si="331"/>
-        <v>0.152398056038809</v>
+        <v>0.679062094922708</v>
       </c>
       <c r="N183" s="1">
         <f ca="1" t="shared" si="332"/>
-        <v>3.86528415156463</v>
+        <v>3.86617262619593</v>
       </c>
       <c r="O183" s="1">
         <f ca="1" t="shared" si="331"/>
-        <v>0.717455796152389</v>
+        <v>0.649251917710715</v>
       </c>
       <c r="P183" s="1">
         <f ca="1" t="shared" si="332"/>
-        <v>4.14109839447057</v>
+        <v>4.14188334794584</v>
       </c>
     </row>
     <row r="184" ht="16.5" spans="1:16">
@@ -16901,27 +16926,27 @@
       </c>
       <c r="K184" s="1">
         <f ca="1" t="shared" ref="K184:O184" si="333">RAND()</f>
-        <v>0.641536780039009</v>
+        <v>0.255671943440078</v>
       </c>
       <c r="L184" s="1">
         <f ca="1" t="shared" ref="L184:P184" si="334">J184+$R$1*K184/MAX(1,($A184*($A184-1)))++$R$1/$A184</f>
-        <v>3.57089043532703</v>
+        <v>3.57031116306888</v>
       </c>
       <c r="M184" s="1">
         <f ca="1" t="shared" si="333"/>
-        <v>0.919256621881135</v>
+        <v>0.300316544050534</v>
       </c>
       <c r="N184" s="1">
         <f ca="1" t="shared" si="334"/>
-        <v>3.84549449558927</v>
+        <v>3.8439860512933</v>
       </c>
       <c r="O184" s="1">
         <f ca="1" t="shared" si="333"/>
-        <v>0.718736846182948</v>
+        <v>0.328271647938223</v>
       </c>
       <c r="P184" s="1">
         <f ca="1" t="shared" si="334"/>
-        <v>4.11979752934622</v>
+        <v>4.11770290658654</v>
       </c>
     </row>
     <row r="185" ht="16.5" spans="1:16">
@@ -16961,27 +16986,27 @@
       </c>
       <c r="K185" s="1">
         <f ca="1" t="shared" ref="K185:O185" si="335">RAND()</f>
-        <v>0.416670186865664</v>
+        <v>0.147409912518345</v>
       </c>
       <c r="L185" s="1">
         <f ca="1" t="shared" ref="L185:P185" si="336">J185+$R$1*K185/MAX(1,($A185*($A185-1)))++$R$1/$A185</f>
-        <v>3.55104637411924</v>
+        <v>3.55064654596181</v>
       </c>
       <c r="M185" s="1">
         <f ca="1" t="shared" si="335"/>
-        <v>0.532612400496881</v>
+        <v>0.816895860704265</v>
       </c>
       <c r="N185" s="1">
         <f ca="1" t="shared" si="336"/>
-        <v>3.82357638778118</v>
+        <v>3.82359869590939</v>
       </c>
       <c r="O185" s="1">
         <f ca="1" t="shared" si="335"/>
-        <v>0.421468817879256</v>
+        <v>0.961486597167507</v>
       </c>
       <c r="P185" s="1">
         <f ca="1" t="shared" si="336"/>
-        <v>4.09594136286119</v>
+        <v>4.09676555056188</v>
       </c>
     </row>
     <row r="186" ht="16.5" spans="1:16">
@@ -17021,27 +17046,27 @@
       </c>
       <c r="K186" s="1">
         <f ca="1" t="shared" ref="K186:O186" si="337">RAND()</f>
-        <v>0.904215399340236</v>
+        <v>0.100882476109203</v>
       </c>
       <c r="L186" s="1">
         <f ca="1" t="shared" ref="L186:P186" si="338">J186+$R$1*K186/MAX(1,($A186*($A186-1)))++$R$1/$A186</f>
-        <v>3.53246800146789</v>
+        <v>3.53128801773812</v>
       </c>
       <c r="M186" s="1">
         <f ca="1" t="shared" si="337"/>
-        <v>0.950296610243612</v>
+        <v>0.578044896247381</v>
       </c>
       <c r="N186" s="1">
         <f ca="1" t="shared" si="338"/>
-        <v>3.80413412457342</v>
+        <v>3.80240735512978</v>
       </c>
       <c r="O186" s="1">
         <f ca="1" t="shared" si="337"/>
-        <v>0.148876474944558</v>
+        <v>0.845317858745851</v>
       </c>
       <c r="P186" s="1">
         <f ca="1" t="shared" si="338"/>
-        <v>4.07462307356717</v>
+        <v>4.07391927912912</v>
       </c>
     </row>
     <row r="187" ht="16.5" spans="1:16">
@@ -17081,27 +17106,27 @@
       </c>
       <c r="K187" s="1">
         <f ca="1" t="shared" ref="K187:O187" si="339">RAND()</f>
-        <v>0.45530634076213</v>
+        <v>0.560358182501538</v>
       </c>
       <c r="L187" s="1">
         <f ca="1" t="shared" ref="L187:P187" si="340">J187+$R$1*K187/MAX(1,($A187*($A187-1)))++$R$1/$A187</f>
-        <v>3.51272203769363</v>
+        <v>3.51287468494987</v>
       </c>
       <c r="M187" s="1">
         <f ca="1" t="shared" si="339"/>
-        <v>0.800847048119902</v>
+        <v>0.669239447710063</v>
       </c>
       <c r="N187" s="1">
         <f ca="1" t="shared" si="340"/>
-        <v>3.78270292558686</v>
+        <v>3.78266433831766</v>
       </c>
       <c r="O187" s="1">
         <f ca="1" t="shared" si="339"/>
-        <v>0.83042134278014</v>
+        <v>0.594836020017226</v>
       </c>
       <c r="P187" s="1">
         <f ca="1" t="shared" si="340"/>
-        <v>4.05272678688123</v>
+        <v>4.05234587859667</v>
       </c>
     </row>
     <row r="188" ht="16.5" spans="1:16">
@@ -17141,27 +17166,27 @@
       </c>
       <c r="K188" s="1">
         <f ca="1" t="shared" ref="K188:O188" si="341">RAND()</f>
-        <v>0.810782095631261</v>
+        <v>0.173630716624076</v>
       </c>
       <c r="L188" s="1">
         <f ca="1" t="shared" ref="L188:P188" si="342">J188+$R$1*K188/MAX(1,($A188*($A188-1)))++$R$1/$A188</f>
-        <v>3.49435165041635</v>
+        <v>3.49343572928041</v>
       </c>
       <c r="M188" s="1">
         <f ca="1" t="shared" si="341"/>
-        <v>0.212375879871325</v>
+        <v>0.981477997915099</v>
       </c>
       <c r="N188" s="1">
         <f ca="1" t="shared" si="342"/>
-        <v>3.76203662523072</v>
+        <v>3.76222630773754</v>
       </c>
       <c r="O188" s="1">
         <f ca="1" t="shared" si="341"/>
-        <v>0.883748040820916</v>
+        <v>0.617366680997818</v>
       </c>
       <c r="P188" s="1">
         <f ca="1" t="shared" si="342"/>
-        <v>4.03068671441596</v>
+        <v>4.03049346701676</v>
       </c>
     </row>
     <row r="189" ht="16.5" spans="1:16">
@@ -17201,27 +17226,27 @@
       </c>
       <c r="K189" s="1">
         <f ca="1" t="shared" ref="K189:O189" si="343">RAND()</f>
-        <v>0.292044107278647</v>
+        <v>0.629852702611651</v>
       </c>
       <c r="L189" s="1">
         <f ca="1" t="shared" ref="L189:P189" si="344">J189+$R$1*K189/MAX(1,($A189*($A189-1)))++$R$1/$A189</f>
-        <v>3.474928951114</v>
+        <v>3.47540939342162</v>
       </c>
       <c r="M189" s="1">
         <f ca="1" t="shared" si="343"/>
-        <v>0.574745621852196</v>
+        <v>0.818020484960454</v>
       </c>
       <c r="N189" s="1">
         <f ca="1" t="shared" si="344"/>
-        <v>3.74170381973081</v>
+        <v>3.74253025541525</v>
       </c>
       <c r="O189" s="1">
         <f ca="1" t="shared" si="343"/>
-        <v>0.654095547022563</v>
+        <v>0.274721574250325</v>
       </c>
       <c r="P189" s="1">
         <f ca="1" t="shared" si="344"/>
-        <v>4.00859154237705</v>
+        <v>4.00887842013002</v>
       </c>
     </row>
     <row r="190" ht="16.5" spans="1:16">
@@ -17261,27 +17286,27 @@
       </c>
       <c r="K190" s="1">
         <f ca="1" t="shared" ref="K190:O190" si="345">RAND()</f>
-        <v>0.903516451284927</v>
+        <v>0.98998421614668</v>
       </c>
       <c r="L190" s="1">
         <f ca="1" t="shared" ref="L190:P190" si="346">J190+$R$1*K190/MAX(1,($A190*($A190-1)))++$R$1/$A190</f>
-        <v>3.45731103857268</v>
+        <v>3.4574327144773</v>
       </c>
       <c r="M190" s="1">
         <f ca="1" t="shared" si="345"/>
-        <v>0.0960302748155417</v>
+        <v>0.448199238998235</v>
       </c>
       <c r="N190" s="1">
         <f ca="1" t="shared" si="346"/>
-        <v>3.72199643522192</v>
+        <v>3.72261367704484</v>
       </c>
       <c r="O190" s="1">
         <f ca="1" t="shared" si="345"/>
-        <v>0.097604493745483</v>
+        <v>0.873759706341328</v>
       </c>
       <c r="P190" s="1">
         <f ca="1" t="shared" si="346"/>
-        <v>3.9866840470841</v>
+        <v>3.98839348075184</v>
       </c>
     </row>
     <row r="191" ht="16.5" spans="1:16">
@@ -17321,27 +17346,27 @@
       </c>
       <c r="K191" s="1">
         <f ca="1" t="shared" ref="K191:O191" si="347">RAND()</f>
-        <v>0.217808649275842</v>
+        <v>0.858089852834503</v>
       </c>
       <c r="L191" s="1">
         <f ca="1" t="shared" ref="L191:P191" si="348">J191+$R$1*K191/MAX(1,($A191*($A191-1)))++$R$1/$A191</f>
-        <v>3.43806433952837</v>
+        <v>3.43895584774831</v>
       </c>
       <c r="M191" s="1">
         <f ca="1" t="shared" si="347"/>
-        <v>0.67715525940037</v>
+        <v>0.276487599096904</v>
       </c>
       <c r="N191" s="1">
         <f ca="1" t="shared" si="348"/>
-        <v>3.7021650848074</v>
+        <v>3.70249871547192</v>
       </c>
       <c r="O191" s="1">
         <f ca="1" t="shared" si="347"/>
-        <v>0.425868212268018</v>
+        <v>0.859145288089643</v>
       </c>
       <c r="P191" s="1">
         <f ca="1" t="shared" si="348"/>
-        <v>3.9659159455875</v>
+        <v>3.96685285817324</v>
       </c>
     </row>
     <row r="192" ht="16.5" spans="1:16">
@@ -17381,27 +17406,27 @@
       </c>
       <c r="K192" s="1">
         <f ca="1" t="shared" ref="K192:O192" si="349">RAND()</f>
-        <v>0.357068288226025</v>
+        <v>0.277735265635867</v>
       </c>
       <c r="L192" s="1">
         <f ca="1" t="shared" ref="L192:P192" si="350">J192+$R$1*K192/MAX(1,($A192*($A192-1)))++$R$1/$A192</f>
-        <v>3.42016680667984</v>
+        <v>3.42005750243268</v>
       </c>
       <c r="M192" s="1">
         <f ca="1" t="shared" si="349"/>
-        <v>0.320243438072373</v>
+        <v>0.60040384294082</v>
       </c>
       <c r="N192" s="1">
         <f ca="1" t="shared" si="350"/>
-        <v>3.68238813960637</v>
+        <v>3.68266483757037</v>
       </c>
       <c r="O192" s="1">
         <f ca="1" t="shared" si="349"/>
-        <v>0.685216899471506</v>
+        <v>0.372306270751213</v>
       </c>
       <c r="P192" s="1">
         <f ca="1" t="shared" si="350"/>
-        <v>3.94511232932733</v>
+        <v>3.94495790214843</v>
       </c>
     </row>
     <row r="193" ht="16.5" spans="1:16">
@@ -17441,27 +17466,27 @@
       </c>
       <c r="K193" s="1">
         <f ca="1" t="shared" ref="K193:O193" si="351">RAND()</f>
-        <v>0.0575312710161024</v>
+        <v>0.116570260483989</v>
       </c>
       <c r="L193" s="1">
         <f ca="1" t="shared" ref="L193:P193" si="352">J193+$R$1*K193/MAX(1,($A193*($A193-1)))++$R$1/$A193</f>
-        <v>3.40185636353487</v>
+        <v>3.40193685953927</v>
       </c>
       <c r="M193" s="1">
         <f ca="1" t="shared" si="351"/>
-        <v>0.527203713460068</v>
+        <v>0.34494460893045</v>
       </c>
       <c r="N193" s="1">
         <f ca="1" t="shared" si="352"/>
-        <v>3.66299183980213</v>
+        <v>3.6628238368093</v>
       </c>
       <c r="O193" s="1">
         <f ca="1" t="shared" si="351"/>
-        <v>0.23864677786071</v>
+        <v>0.276607083160114</v>
       </c>
       <c r="P193" s="1">
         <f ca="1" t="shared" si="352"/>
-        <v>3.92373388656514</v>
+        <v>3.92361764009677</v>
       </c>
     </row>
     <row r="194" ht="16.5" spans="1:16">
@@ -17501,27 +17526,27 @@
       </c>
       <c r="K194" s="1">
         <f ca="1" t="shared" ref="K194:O194" si="356">RAND()</f>
-        <v>0.258591435404137</v>
+        <v>0.78019390336437</v>
       </c>
       <c r="L194" s="1">
         <f ca="1" t="shared" ref="L194:P194" si="357">J194+$R$1*K194/MAX(1,($A194*($A194-1)))++$R$1/$A194</f>
-        <v>3.38441627730382</v>
+        <v>3.38512008028843</v>
       </c>
       <c r="M194" s="1">
         <f ca="1" t="shared" si="356"/>
-        <v>0.169312541221733</v>
+        <v>0.0695477045986073</v>
       </c>
       <c r="N194" s="1">
         <f ca="1" t="shared" si="357"/>
-        <v>3.64371208977848</v>
+        <v>3.64428127915582</v>
       </c>
       <c r="O194" s="1">
         <f ca="1" t="shared" si="356"/>
-        <v>0.167265378911811</v>
+        <v>0.502662096451108</v>
       </c>
       <c r="P194" s="1">
         <f ca="1" t="shared" si="357"/>
-        <v>3.9030051399983</v>
+        <v>3.90402688323674</v>
       </c>
     </row>
     <row r="195" ht="16.5" spans="1:16">
@@ -17561,27 +17586,27 @@
       </c>
       <c r="K195" s="1">
         <f ca="1" t="shared" ref="K195:O195" si="358">RAND()</f>
-        <v>0.86272665911422</v>
+        <v>0.375421344197973</v>
       </c>
       <c r="L195" s="1">
         <f ca="1" t="shared" ref="L195:P195" si="359">J195+$R$1*K195/MAX(1,($A195*($A195-1)))++$R$1/$A195</f>
-        <v>3.36769233302056</v>
+        <v>3.36704158611212</v>
       </c>
       <c r="M195" s="1">
         <f ca="1" t="shared" si="358"/>
-        <v>0.483611730118906</v>
+        <v>0.588219209636149</v>
       </c>
       <c r="N195" s="1">
         <f ca="1" t="shared" si="359"/>
-        <v>3.62607010628336</v>
+        <v>3.62555905207232</v>
       </c>
       <c r="O195" s="1">
         <f ca="1" t="shared" si="358"/>
-        <v>0.509375366442102</v>
+        <v>0.798965685240522</v>
       </c>
       <c r="P195" s="1">
         <f ca="1" t="shared" si="359"/>
-        <v>3.88448228427391</v>
+        <v>3.88435794861262</v>
       </c>
     </row>
     <row r="196" ht="16.5" spans="1:16">
@@ -17621,27 +17646,27 @@
       </c>
       <c r="K196" s="1">
         <f ca="1" t="shared" ref="K196:O196" si="360">RAND()</f>
-        <v>0.119222647561923</v>
+        <v>0.00390705331289332</v>
       </c>
       <c r="L196" s="1">
         <f ca="1" t="shared" ref="L196:P196" si="361">J196+$R$1*K196/MAX(1,($A196*($A196-1)))++$R$1/$A196</f>
-        <v>3.34935133841867</v>
+        <v>3.34919892552645</v>
       </c>
       <c r="M196" s="1">
         <f ca="1" t="shared" si="360"/>
-        <v>0.838273935813452</v>
+        <v>0.341618423158104</v>
       </c>
       <c r="N196" s="1">
         <f ca="1" t="shared" si="361"/>
-        <v>3.60686954346204</v>
+        <v>3.6060606998103</v>
       </c>
       <c r="O196" s="1">
         <f ca="1" t="shared" si="360"/>
-        <v>0.0448779510230113</v>
+        <v>0.310760762950018</v>
       </c>
       <c r="P196" s="1">
         <f ca="1" t="shared" si="361"/>
-        <v>3.86333911516574</v>
+        <v>3.86288168945205</v>
       </c>
     </row>
     <row r="197" ht="16.5" spans="1:16">
@@ -17681,27 +17706,27 @@
       </c>
       <c r="K197" s="1">
         <f ca="1" t="shared" ref="K197:O197" si="362">RAND()</f>
-        <v>0.33933057515426</v>
+        <v>0.161834953521243</v>
       </c>
       <c r="L197" s="1">
         <f ca="1" t="shared" ref="L197:P197" si="363">J197+$R$1*K197/MAX(1,($A197*($A197-1)))++$R$1/$A197</f>
-        <v>3.33246903528932</v>
+        <v>3.33223683274924</v>
       </c>
       <c r="M197" s="1">
         <f ca="1" t="shared" si="362"/>
-        <v>0.832473439286346</v>
+        <v>0.972110896975111</v>
       </c>
       <c r="N197" s="1">
         <f ca="1" t="shared" si="363"/>
-        <v>3.58866013084045</v>
+        <v>3.58861060420002</v>
       </c>
       <c r="O197" s="1">
         <f ca="1" t="shared" si="362"/>
-        <v>0.00100113473069618</v>
+        <v>0.174921379442487</v>
       </c>
       <c r="P197" s="1">
         <f ca="1" t="shared" si="363"/>
-        <v>3.84376348135685</v>
+        <v>3.84394147989265</v>
       </c>
     </row>
     <row r="198" ht="16.5" spans="1:16">
@@ -17741,27 +17766,27 @@
       </c>
       <c r="K198" s="1">
         <f ca="1" t="shared" ref="K198:O198" si="364">RAND()</f>
-        <v>0.610278709286187</v>
+        <v>0.466951948861994</v>
       </c>
       <c r="L198" s="1">
         <f ca="1" t="shared" ref="L198:P198" si="365">J198+$R$1*K198/MAX(1,($A198*($A198-1)))++$R$1/$A198</f>
-        <v>3.31582186717767</v>
+        <v>3.31563626845134</v>
       </c>
       <c r="M198" s="1">
         <f ca="1" t="shared" si="364"/>
-        <v>0.688399894058278</v>
+        <v>0.507367575799965</v>
       </c>
       <c r="N198" s="1">
         <f ca="1" t="shared" si="365"/>
-        <v>3.57052040635469</v>
+        <v>3.570100382685</v>
       </c>
       <c r="O198" s="1">
         <f ca="1" t="shared" si="364"/>
-        <v>0.713138182467403</v>
+        <v>0.404995634493024</v>
       </c>
       <c r="P198" s="1">
         <f ca="1" t="shared" si="365"/>
-        <v>3.82525097998784</v>
+        <v>3.82443193198896</v>
       </c>
     </row>
     <row r="199" ht="16.5" spans="1:16">
@@ -17801,27 +17826,27 @@
       </c>
       <c r="K199" s="1">
         <f ca="1" t="shared" ref="K199:O199" si="366">RAND()</f>
-        <v>0.344633542569147</v>
+        <v>0.292763783742044</v>
       </c>
       <c r="L199" s="1">
         <f ca="1" t="shared" ref="L199:P199" si="367">J199+$R$1*K199/MAX(1,($A199*($A199-1)))++$R$1/$A199</f>
-        <v>3.29865230162356</v>
+        <v>3.2985858121619</v>
       </c>
       <c r="M199" s="1">
         <f ca="1" t="shared" si="366"/>
-        <v>0.175739212345279</v>
+        <v>0.244123496341496</v>
       </c>
       <c r="N199" s="1">
         <f ca="1" t="shared" si="367"/>
-        <v>3.55140282617407</v>
+        <v>3.55142399538543</v>
       </c>
       <c r="O199" s="1">
         <f ca="1" t="shared" si="366"/>
-        <v>0.949796879216076</v>
+        <v>0.755671241889692</v>
       </c>
       <c r="P199" s="1">
         <f ca="1" t="shared" si="367"/>
-        <v>3.80514557969816</v>
+        <v>3.8049179081705</v>
       </c>
     </row>
     <row r="200" ht="16.5" spans="1:16">
@@ -17861,27 +17886,27 @@
       </c>
       <c r="K200" s="1">
         <f ca="1" t="shared" ref="K200:O200" si="368">RAND()</f>
-        <v>0.277975584655842</v>
+        <v>0.188521185626939</v>
       </c>
       <c r="L200" s="1">
         <f ca="1" t="shared" ref="L200:P200" si="369">J200+$R$1*K200/MAX(1,($A200*($A200-1)))++$R$1/$A200</f>
-        <v>3.28191205469856</v>
+        <v>3.2817985396498</v>
       </c>
       <c r="M200" s="1">
         <f ca="1" t="shared" si="368"/>
-        <v>0.191414372757536</v>
+        <v>0.656127820359607</v>
       </c>
       <c r="N200" s="1">
         <f ca="1" t="shared" si="369"/>
-        <v>3.53341123541624</v>
+        <v>3.53388742831073</v>
       </c>
       <c r="O200" s="1">
         <f ca="1" t="shared" si="368"/>
-        <v>0.585528237565001</v>
+        <v>0.793988178268241</v>
       </c>
       <c r="P200" s="1">
         <f ca="1" t="shared" si="369"/>
-        <v>3.78541053524564</v>
+        <v>3.78615125778419</v>
       </c>
     </row>
     <row r="201" ht="16.5" spans="1:16">
@@ -17921,27 +17946,27 @@
       </c>
       <c r="K201" s="1">
         <f ca="1" t="shared" ref="K201:O201" si="370">RAND()</f>
-        <v>0.100801728533406</v>
+        <v>0.387357903981592</v>
       </c>
       <c r="L201" s="1">
         <f ca="1" t="shared" ref="L201:P201" si="371">J201+$R$1*K201/MAX(1,($A201*($A201-1)))++$R$1/$A201</f>
-        <v>3.26520201222177</v>
+        <v>3.26556200741706</v>
       </c>
       <c r="M201" s="1">
         <f ca="1" t="shared" si="370"/>
-        <v>0.118361287455495</v>
+        <v>0.0849284883389689</v>
       </c>
       <c r="N201" s="1">
         <f ca="1" t="shared" si="371"/>
-        <v>3.51535070730652</v>
+        <v>3.51566870149789</v>
       </c>
       <c r="O201" s="1">
         <f ca="1" t="shared" si="370"/>
-        <v>0.276283354312706</v>
+        <v>0.940113604298282</v>
       </c>
       <c r="P201" s="1">
         <f ca="1" t="shared" si="371"/>
-        <v>3.76569779694761</v>
+        <v>3.76684974873947</v>
       </c>
     </row>
     <row r="202" ht="16.5" spans="1:16">
@@ -17981,27 +18006,27 @@
       </c>
       <c r="K202" s="1">
         <f ca="1" t="shared" ref="K202:O202" si="372">RAND()</f>
-        <v>0.232997812012145</v>
+        <v>0.505116354729027</v>
       </c>
       <c r="L202" s="1">
         <f ca="1" t="shared" ref="L202:P202" si="373">J202+$R$1*K202/MAX(1,($A202*($A202-1)))++$R$1/$A202</f>
-        <v>3.24904601717912</v>
+        <v>3.24938447307802</v>
       </c>
       <c r="M202" s="1">
         <f ca="1" t="shared" si="372"/>
-        <v>0.579740712361303</v>
+        <v>0.868459525434303</v>
       </c>
       <c r="N202" s="1">
         <f ca="1" t="shared" si="373"/>
-        <v>3.49852330662235</v>
+        <v>3.49922086552259</v>
       </c>
       <c r="O202" s="1">
         <f ca="1" t="shared" si="372"/>
-        <v>0.105431639480181</v>
+        <v>0.340845414983368</v>
       </c>
       <c r="P202" s="1">
         <f ca="1" t="shared" si="373"/>
-        <v>3.74741065940778</v>
+        <v>3.74840102151138</v>
       </c>
     </row>
     <row r="203" ht="16.5" spans="1:16">
@@ -18041,27 +18066,27 @@
       </c>
       <c r="K203" s="1">
         <f ca="1" t="shared" ref="K203:O203" si="374">RAND()</f>
-        <v>0.171318824267704</v>
+        <v>0.0398087434260455</v>
       </c>
       <c r="L203" s="1">
         <f ca="1" t="shared" ref="L203:P203" si="375">J203+$R$1*K203/MAX(1,($A203*($A203-1)))++$R$1/$A203</f>
-        <v>3.23281035272187</v>
+        <v>3.23264840247208</v>
       </c>
       <c r="M203" s="1">
         <f ca="1" t="shared" si="374"/>
-        <v>0.578805010793843</v>
+        <v>0.00989804628517255</v>
       </c>
       <c r="N203" s="1">
         <f ca="1" t="shared" si="375"/>
-        <v>3.48104788413756</v>
+        <v>3.48018534405905</v>
       </c>
       <c r="O203" s="1">
         <f ca="1" t="shared" si="374"/>
-        <v>0.726809293476737</v>
+        <v>0.0780025265186011</v>
       </c>
       <c r="P203" s="1">
         <f ca="1" t="shared" si="375"/>
-        <v>3.72946767785889</v>
+        <v>3.72780615402718</v>
       </c>
     </row>
     <row r="204" ht="16.5" spans="1:16">
@@ -18101,27 +18126,27 @@
       </c>
       <c r="K204" s="1">
         <f ca="1" t="shared" ref="K204:O204" si="377">RAND()</f>
-        <v>0.653853902086833</v>
+        <v>0.314615194443491</v>
       </c>
       <c r="L204" s="1">
         <f ca="1" t="shared" ref="L204:P204" si="378">J204+$R$1*K204/MAX(1,($A204*($A204-1)))++$R$1/$A204</f>
-        <v>3.21739971455651</v>
+        <v>3.21698606934893</v>
       </c>
       <c r="M204" s="1">
         <f ca="1" t="shared" si="377"/>
-        <v>0.582729260272955</v>
+        <v>0.575742782885451</v>
       </c>
       <c r="N204" s="1">
         <f ca="1" t="shared" si="378"/>
-        <v>3.4644156747334</v>
+        <v>3.46399351067811</v>
       </c>
       <c r="O204" s="1">
         <f ca="1" t="shared" si="377"/>
-        <v>0.224620272572832</v>
+        <v>0.0401175322605962</v>
       </c>
       <c r="P204" s="1">
         <f ca="1" t="shared" si="378"/>
-        <v>3.71099498053325</v>
+        <v>3.71034784605861</v>
       </c>
     </row>
     <row r="205" ht="16.5" spans="1:16">
@@ -18161,27 +18186,27 @@
       </c>
       <c r="K205" s="1">
         <f ca="1" t="shared" ref="K205:O205" si="379">RAND()</f>
-        <v>0.247815327109465</v>
+        <v>0.0480899439671814</v>
       </c>
       <c r="L205" s="1">
         <f ca="1" t="shared" ref="L205:P205" si="380">J205+$R$1*K205/MAX(1,($A205*($A205-1)))++$R$1/$A205</f>
-        <v>3.20106227099284</v>
+        <v>3.2008211266589</v>
       </c>
       <c r="M205" s="1">
         <f ca="1" t="shared" si="379"/>
-        <v>0.306059436782089</v>
+        <v>0.0483338736272603</v>
       </c>
       <c r="N205" s="1">
         <f ca="1" t="shared" si="380"/>
-        <v>3.44652984009936</v>
+        <v>3.44597752320293</v>
       </c>
       <c r="O205" s="1">
         <f ca="1" t="shared" si="379"/>
-        <v>0.782403732467425</v>
+        <v>0.244165080383814</v>
       </c>
       <c r="P205" s="1">
         <f ca="1" t="shared" si="380"/>
-        <v>3.6925725375451</v>
+        <v>3.69137036233215</v>
       </c>
     </row>
     <row r="206" ht="16.5" spans="1:16">
@@ -18221,27 +18246,27 @@
       </c>
       <c r="K206" s="1">
         <f ca="1" t="shared" ref="K206:O206" si="381">RAND()</f>
-        <v>0.690704319188747</v>
+        <v>0.223360841430607</v>
       </c>
       <c r="L206" s="1">
         <f ca="1" t="shared" ref="L206:P206" si="382">J206+$R$1*K206/MAX(1,($A206*($A206-1)))++$R$1/$A206</f>
-        <v>3.18590471582878</v>
+        <v>3.18534595987737</v>
       </c>
       <c r="M206" s="1">
         <f ca="1" t="shared" si="381"/>
-        <v>0.736027452809205</v>
+        <v>0.483667130090045</v>
       </c>
       <c r="N206" s="1">
         <f ca="1" t="shared" si="382"/>
-        <v>3.43068714941655</v>
+        <v>3.42982667141502</v>
       </c>
       <c r="O206" s="1">
         <f ca="1" t="shared" si="381"/>
-        <v>0.907055852422636</v>
+        <v>0.389043908087543</v>
       </c>
       <c r="P206" s="1">
         <f ca="1" t="shared" si="382"/>
-        <v>3.67567406459161</v>
+        <v>3.67419425141034</v>
       </c>
     </row>
     <row r="207" ht="16.5" spans="1:16">
@@ -18281,27 +18306,27 @@
       </c>
       <c r="K207" s="1">
         <f ca="1" t="shared" ref="K207:O207" si="383">RAND()</f>
-        <v>0.781171031346008</v>
+        <v>0.321226194527486</v>
       </c>
       <c r="L207" s="1">
         <f ca="1" t="shared" ref="L207:P207" si="384">J207+$R$1*K207/MAX(1,($A207*($A207-1)))++$R$1/$A207</f>
-        <v>3.17047261547637</v>
+        <v>3.16992804427484</v>
       </c>
       <c r="M207" s="1">
         <f ca="1" t="shared" si="383"/>
-        <v>0.818426481251116</v>
+        <v>0.0231776621592708</v>
       </c>
       <c r="N207" s="1">
         <f ca="1" t="shared" si="384"/>
-        <v>3.41416007283045</v>
+        <v>3.41267393305315</v>
       </c>
       <c r="O207" s="1">
         <f ca="1" t="shared" si="383"/>
-        <v>0.904346424110119</v>
+        <v>0.0872613141984773</v>
       </c>
       <c r="P207" s="1">
         <f ca="1" t="shared" si="384"/>
-        <v>3.6579492587458</v>
+        <v>3.65549569638987</v>
       </c>
     </row>
     <row r="208" ht="16.5" spans="1:16">
@@ -18341,27 +18366,27 @@
       </c>
       <c r="K208" s="1">
         <f ca="1" t="shared" ref="K208:O208" si="385">RAND()</f>
-        <v>0.718883704097641</v>
+        <v>0.417983553680151</v>
       </c>
       <c r="L208" s="1">
         <f ca="1" t="shared" ref="L208:P208" si="386">J208+$R$1*K208/MAX(1,($A208*($A208-1)))++$R$1/$A208</f>
-        <v>3.15501018210227</v>
+        <v>3.15465736076366</v>
       </c>
       <c r="M208" s="1">
         <f ca="1" t="shared" si="385"/>
-        <v>0.0886888838382278</v>
+        <v>0.0797788372468669</v>
       </c>
       <c r="N208" s="1">
         <f ca="1" t="shared" si="386"/>
-        <v>3.39666006822843</v>
+        <v>3.39629679938901</v>
       </c>
       <c r="O208" s="1">
         <f ca="1" t="shared" si="385"/>
-        <v>0.105552525468074</v>
+        <v>0.332517689823276</v>
       </c>
       <c r="P208" s="1">
         <f ca="1" t="shared" si="386"/>
-        <v>3.63832972786619</v>
+        <v>3.63823258768438</v>
       </c>
     </row>
     <row r="209" ht="16.5" spans="1:16">
@@ -18401,27 +18426,27 @@
       </c>
       <c r="K209" s="1">
         <f ca="1" t="shared" ref="K209:O209" si="387">RAND()</f>
-        <v>0.371034769757149</v>
+        <v>0.595244876883545</v>
       </c>
       <c r="L209" s="1">
         <f ca="1" t="shared" ref="L209:P209" si="388">J209+$R$1*K209/MAX(1,($A209*($A209-1)))++$R$1/$A209</f>
-        <v>3.13936621466202</v>
+        <v>3.13962658500195</v>
       </c>
       <c r="M209" s="1">
         <f ca="1" t="shared" si="387"/>
-        <v>0.918825388835043</v>
+        <v>0.843642003091852</v>
       </c>
       <c r="N209" s="1">
         <f ca="1" t="shared" si="388"/>
-        <v>3.38081784206451</v>
+        <v>3.38099090356742</v>
       </c>
       <c r="O209" s="1">
         <f ca="1" t="shared" si="387"/>
-        <v>0.399586591244745</v>
+        <v>0.988179897076324</v>
       </c>
       <c r="P209" s="1">
         <f ca="1" t="shared" si="388"/>
-        <v>3.62166648870057</v>
+        <v>3.62252307085778</v>
       </c>
     </row>
     <row r="210" ht="16.5" spans="1:16">
@@ -18461,27 +18486,27 @@
       </c>
       <c r="K210" s="1">
         <f ca="1" t="shared" ref="K210:O210" si="389">RAND()</f>
-        <v>0.892632388664145</v>
+        <v>0.574676333278963</v>
       </c>
       <c r="L210" s="1">
         <f ca="1" t="shared" ref="L210:P210" si="390">J210+$R$1*K210/MAX(1,($A210*($A210-1)))++$R$1/$A210</f>
-        <v>3.12487650946432</v>
+        <v>3.12451080733953</v>
       </c>
       <c r="M210" s="1">
         <f ca="1" t="shared" si="389"/>
-        <v>0.163494734108787</v>
+        <v>0.940496255961959</v>
       </c>
       <c r="N210" s="1">
         <f ca="1" t="shared" si="390"/>
-        <v>3.36429900524794</v>
+        <v>3.36482698356326</v>
       </c>
       <c r="O210" s="1">
         <f ca="1" t="shared" si="389"/>
-        <v>0.529168351435076</v>
+        <v>0.645222155829818</v>
       </c>
       <c r="P210" s="1">
         <f ca="1" t="shared" si="390"/>
-        <v>3.60414208625576</v>
+        <v>3.60480354566741</v>
       </c>
     </row>
     <row r="211" ht="16.5" spans="1:16">
@@ -18521,27 +18546,27 @@
       </c>
       <c r="K211" s="1">
         <f ca="1" t="shared" ref="K211:O211" si="391">RAND()</f>
-        <v>0.912800908627571</v>
+        <v>0.806137531045831</v>
       </c>
       <c r="L211" s="1">
         <f ca="1" t="shared" ref="L211:P211" si="392">J211+$R$1*K211/MAX(1,($A211*($A211-1)))++$R$1/$A211</f>
-        <v>3.10994850866784</v>
+        <v>3.10982699650381</v>
       </c>
       <c r="M211" s="1">
         <f ca="1" t="shared" si="391"/>
-        <v>0.00758491226753999</v>
+        <v>0.704501837038735</v>
       </c>
       <c r="N211" s="1">
         <f ca="1" t="shared" si="392"/>
-        <v>3.34805238758362</v>
+        <v>3.34872481131019</v>
       </c>
       <c r="O211" s="1">
         <f ca="1" t="shared" si="391"/>
-        <v>0.814736295150393</v>
+        <v>0.623696852946489</v>
       </c>
       <c r="P211" s="1">
         <f ca="1" t="shared" si="392"/>
-        <v>3.58707578277062</v>
+        <v>3.58753057213606</v>
       </c>
     </row>
     <row r="212" ht="16.5" spans="1:16">
@@ -18581,27 +18606,27 @@
       </c>
       <c r="K212" s="1">
         <f ca="1" t="shared" ref="K212:O212" si="393">RAND()</f>
-        <v>0.898583294834618</v>
+        <v>0.565517800606676</v>
       </c>
       <c r="L212" s="1">
         <f ca="1" t="shared" ref="L212:P212" si="394">J212+$R$1*K212/MAX(1,($A212*($A212-1)))++$R$1/$A212</f>
-        <v>3.09512365526386</v>
+        <v>3.09474781968021</v>
       </c>
       <c r="M212" s="1">
         <f ca="1" t="shared" si="393"/>
-        <v>0.145453587013513</v>
+        <v>0.384142638715648</v>
       </c>
       <c r="N212" s="1">
         <f ca="1" t="shared" si="394"/>
-        <v>3.33225461169245</v>
+        <v>3.33214811604527</v>
       </c>
       <c r="O212" s="1">
         <f ca="1" t="shared" si="393"/>
-        <v>0.794221387407795</v>
+        <v>0.216245031679958</v>
       </c>
       <c r="P212" s="1">
         <f ca="1" t="shared" si="394"/>
-        <v>3.57011764643338</v>
+        <v>3.56935895449222</v>
       </c>
     </row>
     <row r="213" ht="16.5" spans="1:16">
@@ -18641,27 +18666,27 @@
       </c>
       <c r="K213" s="1">
         <f ca="1" t="shared" ref="K213:O213" si="395">RAND()</f>
-        <v>0.0571930102515199</v>
+        <v>0.401099626917105</v>
       </c>
       <c r="L213" s="1">
         <f ca="1" t="shared" ref="L213:P213" si="396">J213+$R$1*K213/MAX(1,($A213*($A213-1)))++$R$1/$A213</f>
-        <v>3.07951488085739</v>
+        <v>3.07989928868251</v>
       </c>
       <c r="M213" s="1">
         <f ca="1" t="shared" si="395"/>
-        <v>0.0670128242111621</v>
+        <v>0.469700420635025</v>
       </c>
       <c r="N213" s="1">
         <f ca="1" t="shared" si="396"/>
-        <v>3.31543884225439</v>
+        <v>3.3162733614052</v>
       </c>
       <c r="O213" s="1">
         <f ca="1" t="shared" si="395"/>
-        <v>0.811742939702002</v>
+        <v>0.394272820647324</v>
       </c>
       <c r="P213" s="1">
         <f ca="1" t="shared" si="396"/>
-        <v>3.55219523917349</v>
+        <v>3.55256312356724</v>
       </c>
     </row>
     <row r="214" ht="16.5" spans="1:16">
@@ -18701,27 +18726,27 @@
       </c>
       <c r="K214" s="1">
         <f ca="1" t="shared" ref="K214:O214" si="397">RAND()</f>
-        <v>0.542354921677436</v>
+        <v>0.627788305195731</v>
       </c>
       <c r="L214" s="1">
         <f ca="1" t="shared" ref="L214:P214" si="398">J214+$R$1*K214/MAX(1,($A214*($A214-1)))++$R$1/$A214</f>
-        <v>3.06553099800876</v>
+        <v>3.06562559605058</v>
       </c>
       <c r="M214" s="1">
         <f ca="1" t="shared" si="397"/>
-        <v>0.857062211978508</v>
+        <v>0.106268319132225</v>
       </c>
       <c r="N214" s="1">
         <f ca="1" t="shared" si="398"/>
-        <v>3.30122178352119</v>
+        <v>3.30048504808257</v>
       </c>
       <c r="O214" s="1">
         <f ca="1" t="shared" si="397"/>
-        <v>0.766072332939956</v>
+        <v>0.558274206424185</v>
       </c>
       <c r="P214" s="1">
         <f ca="1" t="shared" si="398"/>
-        <v>3.53681181843674</v>
+        <v>3.53584499383332</v>
       </c>
     </row>
     <row r="215" ht="16.5" spans="1:16">
@@ -18761,27 +18786,27 @@
       </c>
       <c r="K215" s="1">
         <f ca="1" t="shared" ref="K215:O215" si="399">RAND()</f>
-        <v>0.492261785392366</v>
+        <v>0.722563724178273</v>
       </c>
       <c r="L215" s="1">
         <f ca="1" t="shared" ref="L215:P215" si="400">J215+$R$1*K215/MAX(1,($A215*($A215-1)))++$R$1/$A215</f>
-        <v>3.05108624214096</v>
+        <v>3.05133886591657</v>
       </c>
       <c r="M215" s="1">
         <f ca="1" t="shared" si="399"/>
-        <v>0.970818915432733</v>
+        <v>0.340141962259289</v>
       </c>
       <c r="N215" s="1">
         <f ca="1" t="shared" si="400"/>
-        <v>3.28579601673996</v>
+        <v>3.28535683568781</v>
       </c>
       <c r="O215" s="1">
         <f ca="1" t="shared" si="399"/>
-        <v>0.409078279445272</v>
+        <v>0.802877289192145</v>
       </c>
       <c r="P215" s="1">
         <f ca="1" t="shared" si="400"/>
-        <v>3.51988960442748</v>
+        <v>3.51988239104869</v>
       </c>
     </row>
     <row r="216" ht="16.5" spans="1:16">
@@ -18821,27 +18846,27 @@
       </c>
       <c r="K216" s="1">
         <f ca="1" t="shared" ref="K216:O216" si="401">RAND()</f>
-        <v>0.367514439062794</v>
+        <v>0.483659314246092</v>
       </c>
       <c r="L216" s="1">
         <f ca="1" t="shared" ref="L216:P216" si="402">J216+$R$1*K216/MAX(1,($A216*($A216-1)))++$R$1/$A216</f>
-        <v>3.03669584268535</v>
+        <v>3.03682205967642</v>
       </c>
       <c r="M216" s="1">
         <f ca="1" t="shared" si="401"/>
-        <v>0.487965131932788</v>
+        <v>0.431726378561407</v>
       </c>
       <c r="N216" s="1">
         <f ca="1" t="shared" si="402"/>
-        <v>3.26978426382416</v>
+        <v>3.26984936502152</v>
       </c>
       <c r="O216" s="1">
         <f ca="1" t="shared" si="401"/>
-        <v>0.601562045812954</v>
+        <v>0.138218637651738</v>
       </c>
       <c r="P216" s="1">
         <f ca="1" t="shared" si="402"/>
-        <v>3.50299613303283</v>
+        <v>3.50255770955277</v>
       </c>
     </row>
     <row r="217" ht="16.5" spans="1:16">
@@ -18881,27 +18906,27 @@
       </c>
       <c r="K217" s="1">
         <f ca="1" t="shared" ref="K217:O217" si="403">RAND()</f>
-        <v>0.775925862483005</v>
+        <v>0.436655300340377</v>
       </c>
       <c r="L217" s="1">
         <f ca="1" t="shared" ref="L217:P217" si="404">J217+$R$1*K217/MAX(1,($A217*($A217-1)))++$R$1/$A217</f>
-        <v>3.02301456272877</v>
+        <v>3.02264928434576</v>
       </c>
       <c r="M217" s="1">
         <f ca="1" t="shared" si="403"/>
-        <v>0.234662783946257</v>
+        <v>0.283676280042888</v>
       </c>
       <c r="N217" s="1">
         <f ca="1" t="shared" si="404"/>
-        <v>3.25474869578642</v>
+        <v>3.25443618817871</v>
       </c>
       <c r="O217" s="1">
         <f ca="1" t="shared" si="403"/>
-        <v>0.329124483869139</v>
+        <v>0.941366211085666</v>
       </c>
       <c r="P217" s="1">
         <f ca="1" t="shared" si="404"/>
-        <v>3.48658453179403</v>
+        <v>3.48693119917255</v>
       </c>
     </row>
     <row r="218" ht="16.5" spans="1:16">
@@ -18941,27 +18966,27 @@
       </c>
       <c r="K218" s="1">
         <f ca="1" t="shared" ref="K218:O218" si="405">RAND()</f>
-        <v>0.683632945345016</v>
+        <v>0.99570624911497</v>
       </c>
       <c r="L218" s="1">
         <f ca="1" t="shared" ref="L218:P218" si="406">J218+$R$1*K218/MAX(1,($A218*($A218-1)))++$R$1/$A218</f>
-        <v>3.00892177946892</v>
+        <v>3.00925467896518</v>
       </c>
       <c r="M218" s="1">
         <f ca="1" t="shared" si="405"/>
-        <v>0.0281423525044195</v>
+        <v>0.778933249686283</v>
       </c>
       <c r="N218" s="1">
         <f ca="1" t="shared" si="406"/>
-        <v>3.23936654644335</v>
+        <v>3.24050034082053</v>
       </c>
       <c r="O218" s="1">
         <f ca="1" t="shared" si="405"/>
-        <v>0.327893753491507</v>
+        <v>0.50656797696351</v>
       </c>
       <c r="P218" s="1">
         <f ca="1" t="shared" si="406"/>
-        <v>3.47013106870983</v>
+        <v>3.47145546112366</v>
       </c>
     </row>
     <row r="219" ht="16.5" spans="1:16">
@@ -19001,27 +19026,27 @@
       </c>
       <c r="K219" s="1">
         <f ca="1" t="shared" ref="K219:O219" si="407">RAND()</f>
-        <v>0.991128773632407</v>
+        <v>0.128701720260158</v>
       </c>
       <c r="L219" s="1">
         <f ca="1" t="shared" ref="L219:P219" si="408">J219+$R$1*K219/MAX(1,($A219*($A219-1)))++$R$1/$A219</f>
-        <v>2.9953823286408</v>
+        <v>2.99447078776504</v>
       </c>
       <c r="M219" s="1">
         <f ca="1" t="shared" si="407"/>
-        <v>0.337926069012739</v>
+        <v>0.55080417641477</v>
       </c>
       <c r="N219" s="1">
         <f ca="1" t="shared" si="408"/>
-        <v>3.22509729721668</v>
+        <v>3.22441075751139</v>
       </c>
       <c r="O219" s="1">
         <f ca="1" t="shared" si="407"/>
-        <v>0.313477886604755</v>
+        <v>0.04426660559145</v>
       </c>
       <c r="P219" s="1">
         <f ca="1" t="shared" si="408"/>
-        <v>3.45478642532581</v>
+        <v>3.45381534319353</v>
       </c>
     </row>
     <row r="220" ht="16.5" spans="1:16">
@@ -19061,27 +19086,27 @@
       </c>
       <c r="K220" s="1">
         <f ca="1" t="shared" ref="K220:O220" si="409">RAND()</f>
-        <v>0.378171025940171</v>
+        <v>0.116723934651961</v>
       </c>
       <c r="L220" s="1">
         <f ca="1" t="shared" ref="L220:P220" si="410">J220+$R$1*K220/MAX(1,($A220*($A220-1)))++$R$1/$A220</f>
-        <v>2.98100013722293</v>
+        <v>2.98072632476085</v>
       </c>
       <c r="M220" s="1">
         <f ca="1" t="shared" si="409"/>
-        <v>0.759466221885918</v>
+        <v>0.516977907028558</v>
       </c>
       <c r="N220" s="1">
         <f ca="1" t="shared" si="410"/>
-        <v>3.21010602535275</v>
+        <v>3.20957825587709</v>
       </c>
       <c r="O220" s="1">
         <f ca="1" t="shared" si="409"/>
-        <v>0.848712674343904</v>
+        <v>0.992589234886895</v>
       </c>
       <c r="P220" s="1">
         <f ca="1" t="shared" si="410"/>
-        <v>3.43930538092473</v>
+        <v>3.43892829277844</v>
       </c>
     </row>
     <row r="221" ht="16.5" spans="1:16">
@@ -19121,27 +19146,27 @@
       </c>
       <c r="K221" s="1">
         <f ca="1" t="shared" ref="K221:O221" si="411">RAND()</f>
-        <v>0.247665756419147</v>
+        <v>0.802961615649594</v>
       </c>
       <c r="L221" s="1">
         <f ca="1" t="shared" ref="L221:P221" si="412">J221+$R$1*K221/MAX(1,($A221*($A221-1)))++$R$1/$A221</f>
-        <v>2.96725577600293</v>
+        <v>2.967832048169</v>
       </c>
       <c r="M221" s="1">
         <f ca="1" t="shared" si="411"/>
-        <v>0.322005477431868</v>
+        <v>0.131765190615289</v>
       </c>
       <c r="N221" s="1">
         <f ca="1" t="shared" si="412"/>
-        <v>3.19486267251334</v>
+        <v>3.19524151806379</v>
       </c>
       <c r="O221" s="1">
         <f ca="1" t="shared" si="411"/>
-        <v>0.765286421980486</v>
+        <v>0.609721157666565</v>
       </c>
       <c r="P221" s="1">
         <f ca="1" t="shared" si="412"/>
-        <v>3.42292959491058</v>
+        <v>3.42314699871724</v>
       </c>
     </row>
     <row r="222" ht="16.5" spans="1:16">
@@ -19181,27 +19206,27 @@
       </c>
       <c r="K222" s="1">
         <f ca="1" t="shared" ref="K222:O222" si="413">RAND()</f>
-        <v>0.197325533473771</v>
+        <v>0.116609225620897</v>
       </c>
       <c r="L222" s="1">
         <f ca="1" t="shared" ref="L222:P222" si="414">J222+$R$1*K222/MAX(1,($A222*($A222-1)))++$R$1/$A222</f>
-        <v>2.95371999746347</v>
+        <v>2.95363699015387</v>
       </c>
       <c r="M222" s="1">
         <f ca="1" t="shared" si="413"/>
-        <v>0.125753323524544</v>
+        <v>0.118307667483742</v>
       </c>
       <c r="N222" s="1">
         <f ca="1" t="shared" si="414"/>
-        <v>3.18009366398293</v>
+        <v>3.18000299968439</v>
       </c>
       <c r="O222" s="1">
         <f ca="1" t="shared" si="413"/>
-        <v>0.578301991752992</v>
+        <v>0.73367534720632</v>
       </c>
       <c r="P222" s="1">
         <f ca="1" t="shared" si="414"/>
-        <v>3.40693272403204</v>
+        <v>3.40700184311015</v>
       </c>
     </row>
     <row r="223" ht="16.5" spans="1:16">
@@ -19241,27 +19266,27 @@
       </c>
       <c r="K223" s="1">
         <f ca="1" t="shared" ref="K223:O223" si="415">RAND()</f>
-        <v>0.735767297831978</v>
+        <v>0.368916073921523</v>
       </c>
       <c r="L223" s="1">
         <f ca="1" t="shared" ref="L223:P223" si="416">J223+$R$1*K223/MAX(1,($A223*($A223-1)))++$R$1/$A223</f>
-        <v>2.94090718610924</v>
+        <v>2.94053332117924</v>
       </c>
       <c r="M223" s="1">
         <f ca="1" t="shared" si="415"/>
-        <v>0.0235699171793335</v>
+        <v>0.0986429273084055</v>
       </c>
       <c r="N223" s="1">
         <f ca="1" t="shared" si="416"/>
-        <v>3.16615643187702</v>
+        <v>3.16585907525298</v>
       </c>
       <c r="O223" s="1">
         <f ca="1" t="shared" si="415"/>
-        <v>0.0134274478925576</v>
+        <v>0.701258763040147</v>
       </c>
       <c r="P223" s="1">
         <f ca="1" t="shared" si="416"/>
-        <v>3.39139534126503</v>
+        <v>3.39179896637344</v>
       </c>
     </row>
     <row r="224" ht="16.5" spans="1:16">
@@ -19301,27 +19326,27 @@
       </c>
       <c r="K224" s="1">
         <f ca="1" t="shared" ref="K224:O224" si="417">RAND()</f>
-        <v>0.239221838006869</v>
+        <v>0.626868350737818</v>
       </c>
       <c r="L224" s="1">
         <f ca="1" t="shared" ref="L224:P224" si="418">J224+$R$1*K224/MAX(1,($A224*($A224-1)))++$R$1/$A224</f>
-        <v>2.92715955827375</v>
+        <v>2.9275510729515</v>
       </c>
       <c r="M224" s="1">
         <f ca="1" t="shared" si="417"/>
-        <v>0.474254376690265</v>
+        <v>0.871790709586377</v>
       </c>
       <c r="N224" s="1">
         <f ca="1" t="shared" si="418"/>
-        <v>3.15185379167646</v>
+        <v>3.15264680953857</v>
       </c>
       <c r="O224" s="1">
         <f ca="1" t="shared" si="417"/>
-        <v>0.498661422699038</v>
+        <v>0.415795497915863</v>
       </c>
       <c r="P224" s="1">
         <f ca="1" t="shared" si="418"/>
-        <v>3.37657267567304</v>
+        <v>3.37728200072541</v>
       </c>
     </row>
     <row r="225" ht="16.5" spans="1:16">
@@ -19361,27 +19386,27 @@
       </c>
       <c r="K225" s="1">
         <f ca="1" t="shared" ref="K225:O225" si="419">RAND()</f>
-        <v>0.0185309207064379</v>
+        <v>0.083936365255721</v>
       </c>
       <c r="L225" s="1">
         <f ca="1" t="shared" ref="L225:P225" si="420">J225+$R$1*K225/MAX(1,($A225*($A225-1)))++$R$1/$A225</f>
-        <v>2.91381579408303</v>
+        <v>2.91388126237714</v>
       </c>
       <c r="M225" s="1">
         <f ca="1" t="shared" si="419"/>
-        <v>0.382453886763214</v>
+        <v>0.0309660424847507</v>
       </c>
       <c r="N225" s="1">
         <f ca="1" t="shared" si="420"/>
-        <v>3.13741290119262</v>
+        <v>3.13712654388987</v>
       </c>
       <c r="O225" s="1">
         <f ca="1" t="shared" si="419"/>
-        <v>0.34624931808414</v>
+        <v>0.134722973803799</v>
       </c>
       <c r="P225" s="1">
         <f ca="1" t="shared" si="420"/>
-        <v>3.36097376894374</v>
+        <v>3.3604756820363</v>
       </c>
     </row>
     <row r="226" ht="16.5" spans="1:16">
@@ -19421,27 +19446,27 @@
       </c>
       <c r="K226" s="1">
         <f ca="1" t="shared" ref="K226:O226" si="421">RAND()</f>
-        <v>0.816218421526823</v>
+        <v>0.13830882413438</v>
       </c>
       <c r="L226" s="1">
         <f ca="1" t="shared" ref="L226:P226" si="422">J226+$R$1*K226/MAX(1,($A226*($A226-1)))++$R$1/$A226</f>
-        <v>2.9016033912912</v>
+        <v>2.9009308619287</v>
       </c>
       <c r="M226" s="1">
         <f ca="1" t="shared" si="421"/>
-        <v>0.218301989234996</v>
+        <v>0.717662257155728</v>
       </c>
       <c r="N226" s="1">
         <f ca="1" t="shared" si="422"/>
-        <v>3.12404218294719</v>
+        <v>3.12386505067588</v>
       </c>
       <c r="O226" s="1">
         <f ca="1" t="shared" si="421"/>
-        <v>0.90240935496227</v>
+        <v>0.0455591178898793</v>
       </c>
       <c r="P226" s="1">
         <f ca="1" t="shared" si="422"/>
-        <v>3.34715965254536</v>
+        <v>3.34613247043569</v>
       </c>
     </row>
     <row r="227" ht="16.5" spans="1:16">
@@ -19481,27 +19506,27 @@
       </c>
       <c r="K227" s="1">
         <f ca="1" t="shared" ref="K227:O227" si="423">RAND()</f>
-        <v>0.395698767693285</v>
+        <v>0.52092422575476</v>
       </c>
       <c r="L227" s="1">
         <f ca="1" t="shared" ref="L227:P227" si="424">J227+$R$1*K227/MAX(1,($A227*($A227-1)))++$R$1/$A227</f>
-        <v>2.88829468905378</v>
+        <v>2.88841782126426</v>
       </c>
       <c r="M227" s="1">
         <f ca="1" t="shared" si="423"/>
-        <v>0.93580449360204</v>
+        <v>0.27620904907146</v>
       </c>
       <c r="N227" s="1">
         <f ca="1" t="shared" si="424"/>
-        <v>3.11045378885083</v>
+        <v>3.10992835130268</v>
       </c>
       <c r="O227" s="1">
         <f ca="1" t="shared" si="423"/>
-        <v>0.641045243296221</v>
+        <v>0.682612213992722</v>
       </c>
       <c r="P227" s="1">
         <f ca="1" t="shared" si="424"/>
-        <v>3.33232305654336</v>
+        <v>3.33183849113945</v>
       </c>
     </row>
     <row r="228" ht="16.5" spans="1:16">
@@ -19541,27 +19566,27 @@
       </c>
       <c r="K228" s="1">
         <f ca="1" t="shared" ref="K228:O228" si="425">RAND()</f>
-        <v>0.584443795996144</v>
+        <v>0.744920906406962</v>
       </c>
       <c r="L228" s="1">
         <f ca="1" t="shared" ref="L228:P228" si="426">J228+$R$1*K228/MAX(1,($A228*($A228-1)))++$R$1/$A228</f>
-        <v>2.87570118494016</v>
+        <v>2.87585758928152</v>
       </c>
       <c r="M228" s="1">
         <f ca="1" t="shared" si="425"/>
-        <v>0.150993388479141</v>
+        <v>0.413272500771001</v>
       </c>
       <c r="N228" s="1">
         <f ca="1" t="shared" si="426"/>
-        <v>3.09611266342879</v>
+        <v>3.09652469046741</v>
       </c>
       <c r="O228" s="1">
         <f ca="1" t="shared" si="425"/>
-        <v>0.488621975098301</v>
+        <v>0.740183207785097</v>
       </c>
       <c r="P228" s="1">
         <f ca="1" t="shared" si="426"/>
-        <v>3.31685320178509</v>
+        <v>3.31751040565179</v>
       </c>
     </row>
     <row r="229" ht="16.5" spans="1:16">
@@ -19601,27 +19626,27 @@
       </c>
       <c r="K229" s="1">
         <f ca="1" t="shared" ref="K229:O229" si="427">RAND()</f>
-        <v>0.273199312953636</v>
+        <v>0.724405027737153</v>
       </c>
       <c r="L229" s="1">
         <f ca="1" t="shared" ref="L229:P229" si="428">J229+$R$1*K229/MAX(1,($A229*($A229-1)))++$R$1/$A229</f>
-        <v>2.86273398186969</v>
+        <v>2.86316987888142</v>
       </c>
       <c r="M229" s="1">
         <f ca="1" t="shared" si="427"/>
-        <v>0.522357765965931</v>
+        <v>0.970296993650595</v>
       </c>
       <c r="N229" s="1">
         <f ca="1" t="shared" si="428"/>
-        <v>3.08253686246901</v>
+        <v>3.08340550083216</v>
       </c>
       <c r="O229" s="1">
         <f ca="1" t="shared" si="427"/>
-        <v>0.0563994547275739</v>
+        <v>0.338094217053288</v>
       </c>
       <c r="P229" s="1">
         <f ca="1" t="shared" si="428"/>
-        <v>3.30188959399263</v>
+        <v>3.30303036965612</v>
       </c>
     </row>
     <row r="230" ht="16.5" spans="1:16">
@@ -19661,27 +19686,27 @@
       </c>
       <c r="K230" s="1">
         <f ca="1" t="shared" ref="K230:O230" si="429">RAND()</f>
-        <v>0.322958512464188</v>
+        <v>0.951796634428056</v>
       </c>
       <c r="L230" s="1">
         <f ca="1" t="shared" ref="L230:P230" si="430">J230+$R$1*K230/MAX(1,($A230*($A230-1)))++$R$1/$A230</f>
-        <v>2.85022883485833</v>
+        <v>2.85083103178812</v>
       </c>
       <c r="M230" s="1">
         <f ca="1" t="shared" si="429"/>
-        <v>0.819551123448149</v>
+        <v>0.605394880597828</v>
       </c>
       <c r="N230" s="1">
         <f ca="1" t="shared" si="430"/>
-        <v>3.06935427644594</v>
+        <v>3.06975139002052</v>
       </c>
       <c r="O230" s="1">
         <f ca="1" t="shared" si="429"/>
-        <v>0.503763201596064</v>
+        <v>0.324161797710275</v>
       </c>
       <c r="P230" s="1">
         <f ca="1" t="shared" si="430"/>
-        <v>3.28817730870059</v>
+        <v>3.2884024298176</v>
       </c>
     </row>
     <row r="231" ht="16.5" spans="1:16">
@@ -19721,27 +19746,27 @@
       </c>
       <c r="K231" s="1">
         <f ca="1" t="shared" ref="K231:O231" si="431">RAND()</f>
-        <v>0.598273813304875</v>
+        <v>0.468818363077248</v>
       </c>
       <c r="L231" s="1">
         <f ca="1" t="shared" ref="L231:P231" si="432">J231+$R$1*K231/MAX(1,($A231*($A231-1)))++$R$1/$A231</f>
-        <v>2.83804658611477</v>
+        <v>2.83792369314892</v>
       </c>
       <c r="M231" s="1">
         <f ca="1" t="shared" si="431"/>
-        <v>0.221719476720498</v>
+        <v>0.196599805776983</v>
       </c>
       <c r="N231" s="1">
         <f ca="1" t="shared" si="432"/>
-        <v>3.05564837031519</v>
+        <v>3.05550163106973</v>
       </c>
       <c r="O231" s="1">
         <f ca="1" t="shared" si="431"/>
-        <v>0.31514028760511</v>
+        <v>0.311140146141406</v>
       </c>
       <c r="P231" s="1">
         <f ca="1" t="shared" si="432"/>
-        <v>3.27333883954588</v>
+        <v>3.2731883029381</v>
       </c>
     </row>
     <row r="232" ht="16.5" spans="1:16">
@@ -19781,27 +19806,27 @@
       </c>
       <c r="K232" s="1">
         <f ca="1" t="shared" ref="K232:O232" si="433">RAND()</f>
-        <v>0.115885907731581</v>
+        <v>0.537062902450854</v>
       </c>
       <c r="L232" s="1">
         <f ca="1" t="shared" ref="L232:P232" si="434">J232+$R$1*K232/MAX(1,($A232*($A232-1)))++$R$1/$A232</f>
-        <v>2.8252549274494</v>
+        <v>2.82565129202188</v>
       </c>
       <c r="M232" s="1">
         <f ca="1" t="shared" si="433"/>
-        <v>0.466465440367584</v>
+        <v>0.209740330932603</v>
       </c>
       <c r="N232" s="1">
         <f ca="1" t="shared" si="434"/>
-        <v>3.0421441288802</v>
+        <v>3.04229889255918</v>
       </c>
       <c r="O232" s="1">
         <f ca="1" t="shared" si="433"/>
-        <v>0.310460385995228</v>
+        <v>0.00760020327925304</v>
       </c>
       <c r="P232" s="1">
         <f ca="1" t="shared" si="434"/>
-        <v>3.25888651584236</v>
+        <v>3.25875626146872</v>
       </c>
     </row>
     <row r="233" ht="16.5" spans="1:16">
@@ -19841,27 +19866,27 @@
       </c>
       <c r="K233" s="1">
         <f ca="1" t="shared" ref="K233:O233" si="435">RAND()</f>
-        <v>0.566119110063336</v>
+        <v>0.745774226480979</v>
       </c>
       <c r="L233" s="1">
         <f ca="1" t="shared" ref="L233:P233" si="436">J233+$R$1*K233/MAX(1,($A233*($A233-1)))++$R$1/$A233</f>
-        <v>2.81344801379876</v>
+        <v>2.81361562754374</v>
       </c>
       <c r="M233" s="1">
         <f ca="1" t="shared" si="435"/>
-        <v>0.611289757390858</v>
+        <v>0.223317680607569</v>
       </c>
       <c r="N233" s="1">
         <f ca="1" t="shared" si="436"/>
-        <v>3.02953557328282</v>
+        <v>3.02934121875195</v>
       </c>
       <c r="O233" s="1">
         <f ca="1" t="shared" si="435"/>
-        <v>0.783702098322645</v>
+        <v>0.0573093675636571</v>
       </c>
       <c r="P233" s="1">
         <f ca="1" t="shared" si="436"/>
-        <v>3.24578398918288</v>
+        <v>3.24491192834253</v>
       </c>
     </row>
     <row r="234" ht="16.5" spans="1:16">
@@ -19901,27 +19926,27 @@
       </c>
       <c r="K234" s="1">
         <f ca="1" t="shared" ref="K234:O234" si="437">RAND()</f>
-        <v>0.817515135298605</v>
+        <v>0.26437015384098</v>
       </c>
       <c r="L234" s="1">
         <f ca="1" t="shared" ref="L234:P234" si="438">J234+$R$1*K234/MAX(1,($A234*($A234-1)))++$R$1/$A234</f>
-        <v>2.80155534550771</v>
+        <v>2.80104370481893</v>
       </c>
       <c r="M234" s="1">
         <f ca="1" t="shared" si="437"/>
-        <v>0.248251852976627</v>
+        <v>0.0477915304899326</v>
       </c>
       <c r="N234" s="1">
         <f ca="1" t="shared" si="438"/>
-        <v>3.01637724488333</v>
+        <v>3.01568018507134</v>
       </c>
       <c r="O234" s="1">
         <f ca="1" t="shared" si="437"/>
-        <v>0.904334152816121</v>
+        <v>0.431567909092828</v>
       </c>
       <c r="P234" s="1">
         <f ca="1" t="shared" si="438"/>
-        <v>3.23180599853956</v>
+        <v>3.23067164569467</v>
       </c>
     </row>
     <row r="235" ht="16.5" spans="1:16">
@@ -19961,27 +19986,27 @@
       </c>
       <c r="K235" s="1">
         <f ca="1" t="shared" ref="K235:O235" si="439">RAND()</f>
-        <v>0.31685404099189</v>
+        <v>0.541263632351251</v>
       </c>
       <c r="L235" s="1">
         <f ca="1" t="shared" ref="L235:P235" si="440">J235+$R$1*K235/MAX(1,($A235*($A235-1)))++$R$1/$A235</f>
-        <v>2.78907308429716</v>
+        <v>2.78927888158207</v>
       </c>
       <c r="M235" s="1">
         <f ca="1" t="shared" si="439"/>
-        <v>0.822621294279857</v>
+        <v>0.519396653645257</v>
       </c>
       <c r="N235" s="1">
         <f ca="1" t="shared" si="440"/>
-        <v>3.00350269188151</v>
+        <v>3.00343041367338</v>
       </c>
       <c r="O235" s="1">
         <f ca="1" t="shared" si="439"/>
-        <v>0.79544371536828</v>
+        <v>0.896540912198896</v>
       </c>
       <c r="P235" s="1">
         <f ca="1" t="shared" si="440"/>
-        <v>3.21790737596809</v>
+        <v>3.21792781005667</v>
       </c>
     </row>
     <row r="236" ht="16.5" spans="1:16">
@@ -20021,27 +20046,27 @@
       </c>
       <c r="K236" s="1">
         <f ca="1" t="shared" ref="K236:O236" si="441">RAND()</f>
-        <v>0.0525072399554281</v>
+        <v>0.287700473972448</v>
       </c>
       <c r="L236" s="1">
         <f ca="1" t="shared" ref="L236:P236" si="442">J236+$R$1*K236/MAX(1,($A236*($A236-1)))++$R$1/$A236</f>
-        <v>2.77691626408433</v>
+        <v>2.77713011499725</v>
       </c>
       <c r="M236" s="1">
         <f ca="1" t="shared" si="441"/>
-        <v>0.727768295572741</v>
+        <v>0.368988635409665</v>
       </c>
       <c r="N236" s="1">
         <f ca="1" t="shared" si="442"/>
-        <v>2.99034394938673</v>
+        <v>2.99023157765901</v>
       </c>
       <c r="O236" s="1">
         <f ca="1" t="shared" si="441"/>
-        <v>0.964320908786596</v>
+        <v>0.240060079265689</v>
       </c>
       <c r="P236" s="1">
         <f ca="1" t="shared" si="442"/>
-        <v>3.20398672162603</v>
+        <v>3.20321581122808</v>
       </c>
     </row>
     <row r="237" ht="16.5" spans="1:16">
@@ -20081,27 +20106,27 @@
       </c>
       <c r="K237" s="1">
         <f ca="1" t="shared" ref="K237:O237" si="443">RAND()</f>
-        <v>0.923387803859467</v>
+        <v>0.653899766801256</v>
       </c>
       <c r="L237" s="1">
         <f ca="1" t="shared" ref="L237:P237" si="444">J237+$R$1*K237/MAX(1,($A237*($A237-1)))++$R$1/$A237</f>
-        <v>2.76588837703197</v>
+        <v>2.76564541991237</v>
       </c>
       <c r="M237" s="1">
         <f ca="1" t="shared" si="443"/>
-        <v>0.96171223360049</v>
+        <v>0.148883773202615</v>
       </c>
       <c r="N237" s="1">
         <f ca="1" t="shared" si="444"/>
-        <v>2.97861981611743</v>
+        <v>2.97764405295709</v>
       </c>
       <c r="O237" s="1">
         <f ca="1" t="shared" si="443"/>
-        <v>0.0698316784699697</v>
+        <v>0.0395198154911678</v>
       </c>
       <c r="P237" s="1">
         <f ca="1" t="shared" si="444"/>
-        <v>3.19054717969341</v>
+        <v>3.18954408885277</v>
       </c>
     </row>
     <row r="238" ht="16.5" spans="1:16">
@@ -20141,27 +20166,27 @@
       </c>
       <c r="K238" s="1">
         <f ca="1" t="shared" ref="K238:O238" si="445">RAND()</f>
-        <v>0.270059221079768</v>
+        <v>0.862125728512049</v>
       </c>
       <c r="L238" s="1">
         <f ca="1" t="shared" ref="L238:P238" si="446">J238+$R$1*K238/MAX(1,($A238*($A238-1)))++$R$1/$A238</f>
-        <v>2.75358476294525</v>
+        <v>2.75411403644471</v>
       </c>
       <c r="M238" s="1">
         <f ca="1" t="shared" si="445"/>
-        <v>0.441166873553058</v>
+        <v>0.0819293037241267</v>
       </c>
       <c r="N238" s="1">
         <f ca="1" t="shared" si="446"/>
-        <v>2.96494960496195</v>
+        <v>2.96515774067818</v>
       </c>
       <c r="O238" s="1">
         <f ca="1" t="shared" si="445"/>
-        <v>0.353815717188228</v>
+        <v>0.799692037346412</v>
       </c>
       <c r="P238" s="1">
         <f ca="1" t="shared" si="446"/>
-        <v>3.1762363600549</v>
+        <v>3.17684308362796</v>
       </c>
     </row>
     <row r="239" ht="16.5" spans="1:16">
@@ -20201,27 +20226,27 @@
       </c>
       <c r="K239" s="1">
         <f ca="1" t="shared" ref="K239:O239" si="447">RAND()</f>
-        <v>0.844978717749476</v>
+        <v>0.9811513736114</v>
       </c>
       <c r="L239" s="1">
         <f ca="1" t="shared" ref="L239:P239" si="448">J239+$R$1*K239/MAX(1,($A239*($A239-1)))++$R$1/$A239</f>
-        <v>2.74247861815919</v>
+        <v>2.74259932575755</v>
       </c>
       <c r="M239" s="1">
         <f ca="1" t="shared" si="447"/>
-        <v>0.278543829663951</v>
+        <v>0.288655667922833</v>
       </c>
       <c r="N239" s="1">
         <f ca="1" t="shared" si="448"/>
-        <v>2.95280956152485</v>
+        <v>2.95293923256527</v>
       </c>
       <c r="O239" s="1">
         <f ca="1" t="shared" si="447"/>
-        <v>0.400297597889542</v>
+        <v>0.324189761472293</v>
       </c>
       <c r="P239" s="1">
         <f ca="1" t="shared" si="448"/>
-        <v>3.16324843114677</v>
+        <v>3.16331063787807</v>
       </c>
     </row>
     <row r="240" ht="16.5" spans="1:16">
@@ -20261,27 +20286,27 @@
       </c>
       <c r="K240" s="1">
         <f ca="1" t="shared" ref="K240:O240" si="449">RAND()</f>
-        <v>0.927408512435156</v>
+        <v>0.681806085653218</v>
       </c>
       <c r="L240" s="1">
         <f ca="1" t="shared" ref="L240:P240" si="450">J240+$R$1*K240/MAX(1,($A240*($A240-1)))++$R$1/$A240</f>
-        <v>2.73102862813582</v>
+        <v>2.73081274048526</v>
       </c>
       <c r="M240" s="1">
         <f ca="1" t="shared" si="449"/>
-        <v>0.219164058966348</v>
+        <v>0.219897441418434</v>
       </c>
       <c r="N240" s="1">
         <f ca="1" t="shared" si="450"/>
-        <v>2.94042629704599</v>
+        <v>2.94021105404792</v>
       </c>
       <c r="O240" s="1">
         <f ca="1" t="shared" si="449"/>
-        <v>0.299002676667429</v>
+        <v>0.488722575659188</v>
       </c>
       <c r="P240" s="1">
         <f ca="1" t="shared" si="450"/>
-        <v>3.1498941451145</v>
+        <v>3.14984566831575</v>
       </c>
     </row>
     <row r="241" ht="16.5" spans="1:16">
@@ -20321,27 +20346,27 @@
       </c>
       <c r="K241" s="1">
         <f ca="1" t="shared" ref="K241:O241" si="451">RAND()</f>
-        <v>0.372048061659355</v>
+        <v>0.434844264177411</v>
       </c>
       <c r="L241" s="1">
         <f ca="1" t="shared" ref="L241:P241" si="452">J241+$R$1*K241/MAX(1,($A241*($A241-1)))++$R$1/$A241</f>
-        <v>2.71911789405653</v>
+        <v>2.71917263272679</v>
       </c>
       <c r="M241" s="1">
         <f ca="1" t="shared" si="451"/>
-        <v>0.401613608072135</v>
+        <v>0.975389982447192</v>
       </c>
       <c r="N241" s="1">
         <f ca="1" t="shared" si="452"/>
-        <v>2.92780130898686</v>
+        <v>2.92835620140047</v>
       </c>
       <c r="O241" s="1">
         <f ca="1" t="shared" si="451"/>
-        <v>0.809889646867811</v>
+        <v>0.0921145595582904</v>
       </c>
       <c r="P241" s="1">
         <f ca="1" t="shared" si="452"/>
-        <v>3.13684061307234</v>
+        <v>3.13676982985197</v>
       </c>
     </row>
     <row r="242" ht="16.5" spans="1:16">
@@ -20381,27 +20406,27 @@
       </c>
       <c r="K242" s="1">
         <f ca="1" t="shared" ref="K242:O242" si="453">RAND()</f>
-        <v>0.89192543112858</v>
+        <v>0.388661795983662</v>
       </c>
       <c r="L242" s="1">
         <f ca="1" t="shared" ref="L242:P242" si="454">J242+$R$1*K242/MAX(1,($A242*($A242-1)))++$R$1/$A242</f>
-        <v>2.70823990787615</v>
+        <v>2.70780485978214</v>
       </c>
       <c r="M242" s="1">
         <f ca="1" t="shared" si="453"/>
-        <v>0.845732434810955</v>
+        <v>0.79398505319928</v>
       </c>
       <c r="N242" s="1">
         <f ca="1" t="shared" si="454"/>
-        <v>2.91643988404732</v>
+        <v>2.91596010273961</v>
       </c>
       <c r="O242" s="1">
         <f ca="1" t="shared" si="453"/>
-        <v>0.0725350429389595</v>
+        <v>0.320841598616987</v>
       </c>
       <c r="P242" s="1">
         <f ca="1" t="shared" si="454"/>
-        <v>3.1239714668991</v>
+        <v>3.12370633510356</v>
       </c>
     </row>
     <row r="243" ht="16.5" spans="1:16">
@@ -20441,27 +20466,27 @@
       </c>
       <c r="K243" s="1">
         <f ca="1" t="shared" ref="K243:O243" si="455">RAND()</f>
-        <v>0.587595098206718</v>
+        <v>0.80173681346722</v>
       </c>
       <c r="L243" s="1">
         <f ca="1" t="shared" ref="L243:P243" si="456">J243+$R$1*K243/MAX(1,($A243*($A243-1)))++$R$1/$A243</f>
-        <v>2.69674187707744</v>
+        <v>2.69692546278717</v>
       </c>
       <c r="M243" s="1">
         <f ca="1" t="shared" si="455"/>
-        <v>0.0549743606915762</v>
+        <v>0.157722835856027</v>
       </c>
       <c r="N243" s="1">
         <f ca="1" t="shared" si="456"/>
-        <v>2.90340057736266</v>
+        <v>2.90367225030805</v>
       </c>
       <c r="O243" s="1">
         <f ca="1" t="shared" si="455"/>
-        <v>0.891182852264323</v>
+        <v>0.689752855744228</v>
       </c>
       <c r="P243" s="1">
         <f ca="1" t="shared" si="456"/>
-        <v>3.11077616706489</v>
+        <v>3.11087515217677</v>
       </c>
     </row>
     <row r="244" ht="16.5" spans="1:16">
@@ -20501,27 +20526,27 @@
       </c>
       <c r="K244" s="1">
         <f ca="1" t="shared" ref="K244:O244" si="457">RAND()</f>
-        <v>0.739403768784701</v>
+        <v>0.853657690974068</v>
       </c>
       <c r="L244" s="1">
         <f ca="1" t="shared" ref="L244:P244" si="458">J244+$R$1*K244/MAX(1,($A244*($A244-1)))++$R$1/$A244</f>
-        <v>2.68572884039791</v>
+        <v>2.68582598518091</v>
       </c>
       <c r="M244" s="1">
         <f ca="1" t="shared" si="457"/>
-        <v>0.379405582794188</v>
+        <v>0.35824230387845</v>
       </c>
       <c r="N244" s="1">
         <f ca="1" t="shared" si="458"/>
-        <v>2.89181274814779</v>
+        <v>2.89189189878146</v>
       </c>
       <c r="O244" s="1">
         <f ca="1" t="shared" si="457"/>
-        <v>0.326104793443493</v>
+        <v>0.730929134256589</v>
       </c>
       <c r="P244" s="1">
         <f ca="1" t="shared" si="458"/>
-        <v>3.09785133672162</v>
+        <v>3.09827469061755</v>
       </c>
     </row>
     <row r="245" ht="16.5" spans="1:16">
@@ -20561,27 +20586,27 @@
       </c>
       <c r="K245" s="1">
         <f ca="1" t="shared" ref="K245:O245" si="459">RAND()</f>
-        <v>0.185703353473224</v>
+        <v>0.234833462816142</v>
       </c>
       <c r="L245" s="1">
         <f ca="1" t="shared" ref="L245:P245" si="460">J245+$R$1*K245/MAX(1,($A245*($A245-1)))++$R$1/$A245</f>
-        <v>2.67421043593864</v>
+        <v>2.67425186657797</v>
       </c>
       <c r="M245" s="1">
         <f ca="1" t="shared" si="459"/>
-        <v>0.0463240376131679</v>
+        <v>0.0137731226087567</v>
       </c>
       <c r="N245" s="1">
         <f ca="1" t="shared" si="460"/>
-        <v>2.87916753304922</v>
+        <v>2.87918151401996</v>
       </c>
       <c r="O245" s="1">
         <f ca="1" t="shared" si="459"/>
-        <v>0.938453946278724</v>
+        <v>0.226267099685305</v>
       </c>
       <c r="P245" s="1">
         <f ca="1" t="shared" si="460"/>
-        <v>3.08487694911402</v>
+        <v>3.08429035425109</v>
       </c>
     </row>
     <row r="246" ht="16.5" spans="1:16">
@@ -20621,27 +20646,27 @@
       </c>
       <c r="K246" s="1">
         <f ca="1" t="shared" ref="K246:O246" si="461">RAND()</f>
-        <v>0.664560179847556</v>
+        <v>0.0946460872380752</v>
       </c>
       <c r="L246" s="1">
         <f ca="1" t="shared" ref="L246:P246" si="462">J246+$R$1*K246/MAX(1,($A246*($A246-1)))++$R$1/$A246</f>
-        <v>2.66365386431904</v>
+        <v>2.66317718809572</v>
       </c>
       <c r="M246" s="1">
         <f ca="1" t="shared" si="461"/>
-        <v>0.753243773327922</v>
+        <v>0.240109215604341</v>
       </c>
       <c r="N246" s="1">
         <f ca="1" t="shared" si="462"/>
-        <v>2.86836551016491</v>
+        <v>2.86745964812884</v>
       </c>
       <c r="O246" s="1">
         <f ca="1" t="shared" si="461"/>
-        <v>0.618923360408209</v>
+        <v>0.269891920960468</v>
       </c>
       <c r="P246" s="1">
         <f ca="1" t="shared" si="462"/>
-        <v>3.07296481039945</v>
+        <v>3.07176701842071</v>
       </c>
     </row>
     <row r="247" ht="16.5" spans="1:16">
@@ -20681,27 +20706,27 @@
       </c>
       <c r="K247" s="1">
         <f ca="1" t="shared" ref="K247:O247" si="463">RAND()</f>
-        <v>0.580462516177809</v>
+        <v>0.186015030321392</v>
       </c>
       <c r="L247" s="1">
         <f ca="1" t="shared" ref="L247:P247" si="464">J247+$R$1*K247/MAX(1,($A247*($A247-1)))++$R$1/$A247</f>
-        <v>2.65271317613752</v>
+        <v>2.65238594245091</v>
       </c>
       <c r="M247" s="1">
         <f ca="1" t="shared" si="463"/>
-        <v>0.663395585962516</v>
+        <v>0.0495261008250085</v>
       </c>
       <c r="N247" s="1">
         <f ca="1" t="shared" si="464"/>
-        <v>2.85651556172402</v>
+        <v>2.85567906183105</v>
       </c>
       <c r="O247" s="1">
         <f ca="1" t="shared" si="463"/>
-        <v>0.354498495942495</v>
+        <v>0.512916729018339</v>
       </c>
       <c r="P247" s="1">
         <f ca="1" t="shared" si="464"/>
-        <v>3.06006168624363</v>
+        <v>3.05935661013785</v>
       </c>
     </row>
     <row r="248" ht="16.5" spans="1:16">
@@ -20741,27 +20766,27 @@
       </c>
       <c r="K248" s="1">
         <f ca="1" t="shared" ref="K248:O248" si="465">RAND()</f>
-        <v>0.803452560047167</v>
+        <v>0.516724557703222</v>
       </c>
       <c r="L248" s="1">
         <f ca="1" t="shared" ref="L248:P248" si="466">J248+$R$1*K248/MAX(1,($A248*($A248-1)))++$R$1/$A248</f>
-        <v>2.64211468727169</v>
+        <v>2.64187874375243</v>
       </c>
       <c r="M248" s="1">
         <f ca="1" t="shared" si="465"/>
-        <v>0.253403615132324</v>
+        <v>0.283684185081902</v>
       </c>
       <c r="N248" s="1">
         <f ca="1" t="shared" si="466"/>
-        <v>2.84475235852603</v>
+        <v>2.84454133236462</v>
       </c>
       <c r="O248" s="1">
         <f ca="1" t="shared" si="465"/>
-        <v>0.212538856829084</v>
+        <v>0.906399664990877</v>
       </c>
       <c r="P248" s="1">
         <f ca="1" t="shared" si="466"/>
-        <v>3.0473564028768</v>
+        <v>3.04771634278643</v>
       </c>
     </row>
     <row r="249" ht="16.5" spans="1:16">
@@ -20801,27 +20826,27 @@
       </c>
       <c r="K249" s="1">
         <f ca="1" t="shared" ref="K249:O249" si="467">RAND()</f>
-        <v>0.540080328667375</v>
+        <v>0.978381891978829</v>
       </c>
       <c r="L249" s="1">
         <f ca="1" t="shared" ref="L249:P249" si="468">J249+$R$1*K249/MAX(1,($A249*($A249-1)))++$R$1/$A249</f>
-        <v>2.63120353951341</v>
+        <v>2.63156130166186</v>
       </c>
       <c r="M249" s="1">
         <f ca="1" t="shared" si="467"/>
-        <v>0.440424803342194</v>
+        <v>0.690910181168497</v>
       </c>
       <c r="N249" s="1">
         <f ca="1" t="shared" si="468"/>
-        <v>2.83317593797506</v>
+        <v>2.83373815795444</v>
       </c>
       <c r="O249" s="1">
         <f ca="1" t="shared" si="467"/>
-        <v>0.351749689816704</v>
+        <v>0.00121091503922433</v>
       </c>
       <c r="P249" s="1">
         <f ca="1" t="shared" si="468"/>
-        <v>3.0350759556793</v>
+        <v>3.0353520495855</v>
       </c>
     </row>
     <row r="250" ht="16.5" spans="1:16">
@@ -20861,27 +20886,27 @@
       </c>
       <c r="K250" s="1">
         <f ca="1" t="shared" ref="K250:O250" si="469">RAND()</f>
-        <v>0.493309958216058</v>
+        <v>0.0913015612646164</v>
       </c>
       <c r="L250" s="1">
         <f ca="1" t="shared" ref="L250:P250" si="470">J250+$R$1*K250/MAX(1,($A250*($A250-1)))++$R$1/$A250</f>
-        <v>2.62055747988585</v>
+        <v>2.62023197755641</v>
       </c>
       <c r="M250" s="1">
         <f ca="1" t="shared" si="469"/>
-        <v>0.915555153766084</v>
+        <v>0.488056817163422</v>
       </c>
       <c r="N250" s="1">
         <f ca="1" t="shared" si="470"/>
-        <v>2.82210200893249</v>
+        <v>2.82143036531483</v>
       </c>
       <c r="O250" s="1">
         <f ca="1" t="shared" si="469"/>
-        <v>0.492336178514464</v>
+        <v>0.900811663415115</v>
       </c>
       <c r="P250" s="1">
         <f ca="1" t="shared" si="470"/>
-        <v>3.02330386164861</v>
+        <v>3.02296295669925</v>
       </c>
     </row>
     <row r="251" ht="16.5" spans="1:16">
@@ -20921,27 +20946,27 @@
       </c>
       <c r="K251" s="1">
         <f ca="1" t="shared" ref="K251:O251" si="471">RAND()</f>
-        <v>0.372775775644827</v>
+        <v>0.829673283798399</v>
       </c>
       <c r="L251" s="1">
         <f ca="1" t="shared" ref="L251:P251" si="472">J251+$R$1*K251/MAX(1,($A251*($A251-1)))++$R$1/$A251</f>
-        <v>2.60993797251056</v>
+        <v>2.61030495846088</v>
       </c>
       <c r="M251" s="1">
         <f ca="1" t="shared" si="471"/>
-        <v>0.524355562430299</v>
+        <v>0.35311414044645</v>
       </c>
       <c r="N251" s="1">
         <f ca="1" t="shared" si="472"/>
-        <v>2.81035914163701</v>
+        <v>2.8105885842765</v>
       </c>
       <c r="O251" s="1">
         <f ca="1" t="shared" si="471"/>
-        <v>0.639756613011018</v>
+        <v>0.751352523423629</v>
       </c>
       <c r="P251" s="1">
         <f ca="1" t="shared" si="472"/>
-        <v>3.01087300237035</v>
+        <v>3.01119208027925</v>
       </c>
     </row>
     <row r="252" ht="16.5" spans="1:16">
@@ -20981,27 +21006,27 @@
       </c>
       <c r="K252" s="1">
         <f ca="1" t="shared" ref="K252:O252" si="473">RAND()</f>
-        <v>0.73176056331269</v>
+        <v>0.973157117039837</v>
       </c>
       <c r="L252" s="1">
         <f ca="1" t="shared" ref="L252:P252" si="474">J252+$R$1*K252/MAX(1,($A252*($A252-1)))++$R$1/$A252</f>
-        <v>2.59978626339706</v>
+        <v>2.59997861124864</v>
       </c>
       <c r="M252" s="1">
         <f ca="1" t="shared" si="473"/>
-        <v>0.38242579337481</v>
+        <v>0.203128056159342</v>
       </c>
       <c r="N252" s="1">
         <f ca="1" t="shared" si="474"/>
-        <v>2.79929417239577</v>
+        <v>2.79934365352446</v>
       </c>
       <c r="O252" s="1">
         <f ca="1" t="shared" si="473"/>
-        <v>0.189767769199439</v>
+        <v>0.359670837299626</v>
       </c>
       <c r="P252" s="1">
         <f ca="1" t="shared" si="474"/>
-        <v>2.99864856902461</v>
+        <v>2.99883343108406</v>
       </c>
     </row>
     <row r="253" ht="16.5" spans="1:16">
@@ -21041,27 +21066,27 @@
       </c>
       <c r="K253" s="1">
         <f ca="1" t="shared" ref="K253:O253" si="475">RAND()</f>
-        <v>0.346079232461598</v>
+        <v>0.551628312986642</v>
       </c>
       <c r="L253" s="1">
         <f ca="1" t="shared" ref="L253:P253" si="476">J253+$R$1*K253/MAX(1,($A253*($A253-1)))++$R$1/$A253</f>
-        <v>2.58912451719508</v>
+        <v>2.58928700144896</v>
       </c>
       <c r="M253" s="1">
         <f ca="1" t="shared" si="475"/>
-        <v>0.249441370750408</v>
+        <v>0.832753437304312</v>
       </c>
       <c r="N253" s="1">
         <f ca="1" t="shared" si="476"/>
-        <v>2.78773439622716</v>
+        <v>2.7883579821589</v>
       </c>
       <c r="O253" s="1">
         <f ca="1" t="shared" si="475"/>
-        <v>0.978013501670164</v>
+        <v>0.50548180593142</v>
       </c>
       <c r="P253" s="1">
         <f ca="1" t="shared" si="476"/>
-        <v>2.98692020339664</v>
+        <v>2.98717025829715</v>
       </c>
     </row>
     <row r="254" ht="16.5" spans="1:16">
@@ -21101,27 +21126,27 @@
       </c>
       <c r="K254" s="1">
         <f ca="1" t="shared" ref="K254:O254" si="477">RAND()</f>
-        <v>0.689359275132571</v>
+        <v>0.188183563739052</v>
       </c>
       <c r="L254" s="1">
         <f ca="1" t="shared" ref="L254:P254" si="478">J254+$R$1*K254/MAX(1,($A254*($A254-1)))++$R$1/$A254</f>
-        <v>2.57912146250951</v>
+        <v>2.57872842051237</v>
       </c>
       <c r="M254" s="1">
         <f ca="1" t="shared" si="477"/>
-        <v>0.0993271686892332</v>
+        <v>0.09311388675398</v>
       </c>
       <c r="N254" s="1">
         <f ca="1" t="shared" si="478"/>
-        <v>2.77682781733784</v>
+        <v>2.776429902637</v>
       </c>
       <c r="O254" s="1">
         <f ca="1" t="shared" si="477"/>
-        <v>0.469554388009755</v>
+        <v>0.43322355352189</v>
       </c>
       <c r="P254" s="1">
         <f ca="1" t="shared" si="478"/>
-        <v>2.97482451912905</v>
+        <v>2.97439811233767</v>
       </c>
     </row>
     <row r="255" ht="16.5" spans="1:16">
@@ -21161,27 +21186,27 @@
       </c>
       <c r="K255" s="1">
         <f ca="1" t="shared" ref="K255:O255" si="479">RAND()</f>
-        <v>0.606798653216017</v>
+        <v>0.0347197523523719</v>
       </c>
       <c r="L255" s="1">
         <f ca="1" t="shared" ref="L255:P255" si="480">J255+$R$1*K255/MAX(1,($A255*($A255-1)))++$R$1/$A255</f>
-        <v>2.56886402434815</v>
+        <v>2.56841890989415</v>
       </c>
       <c r="M255" s="1">
         <f ca="1" t="shared" si="479"/>
-        <v>0.642743311420143</v>
+        <v>0.725504143902178</v>
       </c>
       <c r="N255" s="1">
         <f ca="1" t="shared" si="480"/>
-        <v>2.76621451399321</v>
+        <v>2.76583379282955</v>
       </c>
       <c r="O255" s="1">
         <f ca="1" t="shared" si="479"/>
-        <v>0.346635608938248</v>
+        <v>0.470207320217892</v>
       </c>
       <c r="P255" s="1">
         <f ca="1" t="shared" si="480"/>
-        <v>2.96333461265878</v>
+        <v>2.9630500382936</v>
       </c>
     </row>
     <row r="256" ht="16.5" spans="1:16">
@@ -21221,27 +21246,27 @@
       </c>
       <c r="K256" s="1">
         <f ca="1" t="shared" ref="K256:O256" si="481">RAND()</f>
-        <v>0.633140729110262</v>
+        <v>0.357125801298324</v>
       </c>
       <c r="L256" s="1">
         <f ca="1" t="shared" ref="L256:P256" si="482">J256+$R$1*K256/MAX(1,($A256*($A256-1)))++$R$1/$A256</f>
-        <v>2.55877191657335</v>
+        <v>2.55855884344704</v>
       </c>
       <c r="M256" s="1">
         <f ca="1" t="shared" si="481"/>
-        <v>0.0610215254166848</v>
+        <v>0.153053620818691</v>
       </c>
       <c r="N256" s="1">
         <f ca="1" t="shared" si="482"/>
-        <v>2.75489745426473</v>
+        <v>2.75475542644906</v>
       </c>
       <c r="O256" s="1">
         <f ca="1" t="shared" si="481"/>
-        <v>0.612637756265834</v>
+        <v>0.269428996300308</v>
       </c>
       <c r="P256" s="1">
         <f ca="1" t="shared" si="482"/>
-        <v>2.95144881890597</v>
+        <v>2.95104184685689</v>
       </c>
     </row>
     <row r="257" ht="16.5" spans="1:16">
@@ -21281,27 +21306,27 @@
       </c>
       <c r="K257" s="1">
         <f ca="1" t="shared" ref="K257:O257" si="483">RAND()</f>
-        <v>0.881442291526386</v>
+        <v>0.43665539806083</v>
       </c>
       <c r="L257" s="1">
         <f ca="1" t="shared" ref="L257:P257" si="484">J257+$R$1*K257/MAX(1,($A257*($A257-1)))++$R$1/$A257</f>
-        <v>2.54892880077476</v>
+        <v>2.54858812453896</v>
       </c>
       <c r="M257" s="1">
         <f ca="1" t="shared" si="483"/>
-        <v>0.522082632698038</v>
+        <v>0.670087465800912</v>
       </c>
       <c r="N257" s="1">
         <f ca="1" t="shared" si="484"/>
-        <v>2.74464118024221</v>
+        <v>2.74441386555136</v>
       </c>
       <c r="O257" s="1">
         <f ca="1" t="shared" si="483"/>
-        <v>0.951242343256384</v>
+        <v>0.867479657193746</v>
       </c>
       <c r="P257" s="1">
         <f ca="1" t="shared" si="484"/>
-        <v>2.94068226659581</v>
+        <v>2.94039079543586</v>
       </c>
     </row>
     <row r="258" ht="16.5" spans="1:16">
@@ -21341,27 +21366,27 @@
       </c>
       <c r="K258" s="1">
         <f ca="1" t="shared" ref="K258:O258" si="488">RAND()</f>
-        <v>0.430569506719683</v>
+        <v>0.423593800605853</v>
       </c>
       <c r="L258" s="1">
         <f ca="1" t="shared" ref="L258:P258" si="489">J258+$R$1*K258/MAX(1,($A258*($A258-1)))++$R$1/$A258</f>
-        <v>2.53862974944273</v>
+        <v>2.53862444810965</v>
       </c>
       <c r="M258" s="1">
         <f ca="1" t="shared" si="488"/>
-        <v>0.358331600565867</v>
+        <v>0.666492339137145</v>
       </c>
       <c r="N258" s="1">
         <f ca="1" t="shared" si="489"/>
-        <v>2.73345460018489</v>
+        <v>2.73368349202011</v>
       </c>
       <c r="O258" s="1">
         <f ca="1" t="shared" si="488"/>
-        <v>0.140362792498112</v>
+        <v>0.334864365117755</v>
       </c>
       <c r="P258" s="1">
         <f ca="1" t="shared" si="489"/>
-        <v>2.92811380099388</v>
+        <v>2.92849050834817</v>
       </c>
     </row>
     <row r="259" ht="16.5" spans="1:16">
@@ -21401,27 +21426,27 @@
       </c>
       <c r="K259" s="1">
         <f ca="1" t="shared" ref="K259:O259" si="490">RAND()</f>
-        <v>0.385443552121613</v>
+        <v>0.359864147573335</v>
       </c>
       <c r="L259" s="1">
         <f ca="1" t="shared" ref="L259:P259" si="491">J259+$R$1*K259/MAX(1,($A259*($A259-1)))++$R$1/$A259</f>
-        <v>2.52871945491518</v>
+        <v>2.52870016600879</v>
       </c>
       <c r="M259" s="1">
         <f ca="1" t="shared" si="490"/>
-        <v>0.806739193263646</v>
+        <v>0.255514938172871</v>
       </c>
       <c r="N259" s="1">
         <f ca="1" t="shared" si="491"/>
-        <v>2.72312625007193</v>
+        <v>2.72269129421602</v>
       </c>
       <c r="O259" s="1">
         <f ca="1" t="shared" si="490"/>
-        <v>0.0351772460404203</v>
+        <v>0.290287597918685</v>
       </c>
       <c r="P259" s="1">
         <f ca="1" t="shared" si="491"/>
-        <v>2.91695122612691</v>
+        <v>2.91670864377557</v>
       </c>
     </row>
     <row r="260" ht="16.5" spans="1:16">
@@ -21461,27 +21486,27 @@
       </c>
       <c r="K260" s="1">
         <f ca="1" t="shared" ref="K260:O260" si="492">RAND()</f>
-        <v>0.44367346002978</v>
+        <v>0.890525916533161</v>
       </c>
       <c r="L260" s="1">
         <f ca="1" t="shared" ref="L260:P260" si="493">J260+$R$1*K260/MAX(1,($A260*($A260-1)))++$R$1/$A260</f>
-        <v>2.51896356997698</v>
+        <v>2.51929793025989</v>
       </c>
       <c r="M260" s="1">
         <f ca="1" t="shared" si="492"/>
-        <v>0.526225945720574</v>
+        <v>0.940329965267014</v>
       </c>
       <c r="N260" s="1">
         <f ca="1" t="shared" si="493"/>
-        <v>2.71240751504426</v>
+        <v>2.71305173137724</v>
       </c>
       <c r="O260" s="1">
         <f ca="1" t="shared" si="492"/>
-        <v>0.377590888688745</v>
+        <v>0.704512774696211</v>
       </c>
       <c r="P260" s="1">
         <f ca="1" t="shared" si="493"/>
-        <v>2.90574024295475</v>
+        <v>2.90662908073426</v>
       </c>
     </row>
     <row r="261" ht="16.5" spans="1:16">
@@ -21521,27 +21546,27 @@
       </c>
       <c r="K261" s="1">
         <f ca="1" t="shared" ref="K261:O261" si="494">RAND()</f>
-        <v>0.65374040756572</v>
+        <v>0.6968350141346</v>
       </c>
       <c r="L261" s="1">
         <f ca="1" t="shared" ref="L261:P261" si="495">J261+$R$1*K261/MAX(1,($A261*($A261-1)))++$R$1/$A261</f>
-        <v>2.50939541164803</v>
+        <v>2.5094274094254</v>
       </c>
       <c r="M261" s="1">
         <f ca="1" t="shared" si="494"/>
-        <v>0.175430823421151</v>
+        <v>0.721279577552345</v>
       </c>
       <c r="N261" s="1">
         <f ca="1" t="shared" si="495"/>
-        <v>2.70183336147237</v>
+        <v>2.70227065235498</v>
       </c>
       <c r="O261" s="1">
         <f ca="1" t="shared" si="494"/>
-        <v>0.56906260610168</v>
+        <v>0.494189499176024</v>
       </c>
       <c r="P261" s="1">
         <f ca="1" t="shared" si="495"/>
-        <v>2.89456358318762</v>
+        <v>2.89494528073275</v>
       </c>
     </row>
     <row r="262" ht="16.5" spans="1:16">
@@ -21581,27 +21606,27 @@
       </c>
       <c r="K262" s="1">
         <f ca="1" t="shared" ref="K262:O262" si="496">RAND()</f>
-        <v>0.980843678917018</v>
+        <v>0.759079598298562</v>
       </c>
       <c r="L262" s="1">
         <f ca="1" t="shared" ref="L262:P262" si="497">J262+$R$1*K262/MAX(1,($A262*($A262-1)))++$R$1/$A262</f>
-        <v>2.49998588541034</v>
+        <v>2.49982248717823</v>
       </c>
       <c r="M262" s="1">
         <f ca="1" t="shared" si="496"/>
-        <v>0.000123691621741306</v>
+        <v>0.791389533383261</v>
       </c>
       <c r="N262" s="1">
         <f ca="1" t="shared" si="497"/>
-        <v>2.69155685777376</v>
+        <v>2.69197647298238</v>
       </c>
       <c r="O262" s="1">
         <f ca="1" t="shared" si="496"/>
-        <v>0.0709163361473986</v>
+        <v>0.643459176262884</v>
       </c>
       <c r="P262" s="1">
         <f ca="1" t="shared" si="497"/>
-        <v>2.88317999094215</v>
+        <v>2.88402146206008</v>
       </c>
     </row>
     <row r="263" ht="16.5" spans="1:16">
@@ -21641,27 +21666,27 @@
       </c>
       <c r="K263" s="1">
         <f ca="1" t="shared" ref="K263:O263" si="498">RAND()</f>
-        <v>0.174647404730048</v>
+        <v>0.266293337223472</v>
       </c>
       <c r="L263" s="1">
         <f ca="1" t="shared" ref="L263:P263" si="499">J263+$R$1*K263/MAX(1,($A263*($A263-1)))++$R$1/$A263</f>
-        <v>2.48981796920588</v>
+        <v>2.48988497948087</v>
       </c>
       <c r="M263" s="1">
         <f ca="1" t="shared" si="498"/>
-        <v>0.138618581201072</v>
+        <v>0.840989266637482</v>
       </c>
       <c r="N263" s="1">
         <f ca="1" t="shared" si="499"/>
-        <v>2.68075901990723</v>
+        <v>2.68133959419428</v>
       </c>
       <c r="O263" s="1">
         <f ca="1" t="shared" si="498"/>
-        <v>0.506146209202958</v>
+        <v>0.283416480698171</v>
       </c>
       <c r="P263" s="1">
         <f ca="1" t="shared" si="499"/>
-        <v>2.87196880187413</v>
+        <v>2.87238651917505</v>
       </c>
     </row>
     <row r="264" ht="16.5" spans="1:16">
@@ -21701,27 +21726,27 @@
       </c>
       <c r="K264" s="1">
         <f ca="1" t="shared" ref="K264:O264" si="500">RAND()</f>
-        <v>0.573057453675056</v>
+        <v>0.745045311592056</v>
       </c>
       <c r="L264" s="1">
         <f ca="1" t="shared" ref="L264:P264" si="501">J264+$R$1*K264/MAX(1,($A264*($A264-1)))++$R$1/$A264</f>
-        <v>2.48060622983026</v>
+        <v>2.4807310287287</v>
       </c>
       <c r="M264" s="1">
         <f ca="1" t="shared" si="500"/>
-        <v>0.817692408613159</v>
+        <v>0.970953149848837</v>
       </c>
       <c r="N264" s="1">
         <f ca="1" t="shared" si="501"/>
-        <v>2.67131363731916</v>
+        <v>2.67154964622924</v>
       </c>
       <c r="O264" s="1">
         <f ca="1" t="shared" si="500"/>
-        <v>0.252531790475128</v>
+        <v>0.629018277112448</v>
       </c>
       <c r="P264" s="1">
         <f ca="1" t="shared" si="501"/>
-        <v>2.86161094944762</v>
+        <v>2.86212014682216</v>
       </c>
     </row>
     <row r="265" ht="16.5" spans="1:16">
@@ -21761,27 +21786,27 @@
       </c>
       <c r="K265" s="1">
         <f ca="1" t="shared" ref="K265:O265" si="502">RAND()</f>
-        <v>0.969567643682453</v>
+        <v>0.088851859534506</v>
       </c>
       <c r="L265" s="1">
         <f ca="1" t="shared" ref="L265:P265" si="503">J265+$R$1*K265/MAX(1,($A265*($A265-1)))++$R$1/$A265</f>
-        <v>2.47146097451009</v>
+        <v>2.47082674549166</v>
       </c>
       <c r="M265" s="1">
         <f ca="1" t="shared" si="502"/>
-        <v>0.58280248007538</v>
+        <v>0.0474974805261836</v>
       </c>
       <c r="N265" s="1">
         <f ca="1" t="shared" si="503"/>
-        <v>2.66127460689867</v>
+        <v>2.66025488920099</v>
       </c>
       <c r="O265" s="1">
         <f ca="1" t="shared" si="502"/>
-        <v>0.372590119852328</v>
+        <v>0.43914844518709</v>
       </c>
       <c r="P265" s="1">
         <f ca="1" t="shared" si="503"/>
-        <v>2.85093685926058</v>
+        <v>2.84996507214631</v>
       </c>
     </row>
     <row r="266" ht="16.5" spans="1:16">
@@ -21821,27 +21846,27 @@
       </c>
       <c r="K266" s="1">
         <f ca="1" t="shared" ref="K266:O266" si="504">RAND()</f>
-        <v>0.629382185278572</v>
+        <v>0.739544801294059</v>
       </c>
       <c r="L266" s="1">
         <f ca="1" t="shared" ref="L266:P266" si="505">J266+$R$1*K266/MAX(1,($A266*($A266-1)))++$R$1/$A266</f>
-        <v>2.46185633375163</v>
+        <v>2.46193506632454</v>
       </c>
       <c r="M266" s="1">
         <f ca="1" t="shared" si="504"/>
-        <v>0.318218354952314</v>
+        <v>0.5950875216982</v>
       </c>
       <c r="N266" s="1">
         <f ca="1" t="shared" si="505"/>
-        <v>2.65076300781892</v>
+        <v>2.6510396171548</v>
       </c>
       <c r="O266" s="1">
         <f ca="1" t="shared" si="504"/>
-        <v>0.731317761398354</v>
+        <v>0.529501989420498</v>
       </c>
       <c r="P266" s="1">
         <f ca="1" t="shared" si="505"/>
-        <v>2.83996492159922</v>
+        <v>2.84009729439138</v>
       </c>
     </row>
     <row r="267" ht="16.5" spans="1:16">
@@ -21881,27 +21906,27 @@
       </c>
       <c r="K267" s="1">
         <f ca="1" t="shared" ref="K267:O267" si="506">RAND()</f>
-        <v>0.845105154011236</v>
+        <v>0.661458946898128</v>
       </c>
       <c r="L267" s="1">
         <f ca="1" t="shared" ref="L267:P267" si="507">J267+$R$1*K267/MAX(1,($A267*($A267-1)))++$R$1/$A267</f>
-        <v>2.45272031859414</v>
+        <v>2.45259005458001</v>
       </c>
       <c r="M267" s="1">
         <f ca="1" t="shared" si="506"/>
-        <v>0.485138474199137</v>
+        <v>0.977542084224031</v>
       </c>
       <c r="N267" s="1">
         <f ca="1" t="shared" si="507"/>
-        <v>2.64103436205718</v>
+        <v>2.64125337000363</v>
       </c>
       <c r="O267" s="1">
         <f ca="1" t="shared" si="506"/>
-        <v>0.416177066849635</v>
+        <v>0.673279908890037</v>
       </c>
       <c r="P267" s="1">
         <f ca="1" t="shared" si="507"/>
-        <v>2.82929948978228</v>
+        <v>2.82970086603774</v>
       </c>
     </row>
     <row r="268" ht="16.5" spans="1:16">
@@ -21941,27 +21966,27 @@
       </c>
       <c r="K268" s="1">
         <f ca="1" t="shared" ref="K268:O268" si="509">RAND()</f>
-        <v>0.334822459997089</v>
+        <v>0.494356617880797</v>
       </c>
       <c r="L268" s="1">
         <f ca="1" t="shared" ref="L268:P268" si="510">J268+$R$1*K268/MAX(1,($A268*($A268-1)))++$R$1/$A268</f>
-        <v>2.44314073277294</v>
+        <v>2.44325304597018</v>
       </c>
       <c r="M268" s="1">
         <f ca="1" t="shared" si="509"/>
-        <v>0.237187416650541</v>
+        <v>0.674568716740593</v>
       </c>
       <c r="N268" s="1">
         <f ca="1" t="shared" si="510"/>
-        <v>2.63057363202715</v>
+        <v>2.63099386481275</v>
       </c>
       <c r="O268" s="1">
         <f ca="1" t="shared" si="509"/>
-        <v>0.175869022290539</v>
+        <v>0.58836938395386</v>
       </c>
       <c r="P268" s="1">
         <f ca="1" t="shared" si="510"/>
-        <v>2.81796336268969</v>
+        <v>2.81867399870362</v>
       </c>
     </row>
     <row r="269" ht="16.5" spans="1:16">
@@ -22001,27 +22026,27 @@
       </c>
       <c r="K269" s="1">
         <f ca="1" t="shared" ref="K269:O269" si="511">RAND()</f>
-        <v>0.910561030535691</v>
+        <v>0.442734451866806</v>
       </c>
       <c r="L269" s="1">
         <f ca="1" t="shared" ref="L269:P269" si="512">J269+$R$1*K269/MAX(1,($A269*($A269-1)))++$R$1/$A269</f>
-        <v>2.4343944330528</v>
+        <v>2.43406753762918</v>
       </c>
       <c r="M269" s="1">
         <f ca="1" t="shared" si="511"/>
-        <v>0.973911503961922</v>
+        <v>0.399594844419081</v>
       </c>
       <c r="N269" s="1">
         <f ca="1" t="shared" si="512"/>
-        <v>2.62164212122987</v>
+        <v>2.62091392007399</v>
       </c>
       <c r="O269" s="1">
         <f ca="1" t="shared" si="511"/>
-        <v>0.760327597494841</v>
+        <v>0.159624960067215</v>
       </c>
       <c r="P269" s="1">
         <f ca="1" t="shared" si="512"/>
-        <v>2.808740566921</v>
+        <v>2.80759262274048</v>
       </c>
     </row>
     <row r="270" ht="16.5" spans="1:16">
@@ -22061,27 +22086,27 @@
       </c>
       <c r="K270" s="1">
         <f ca="1" t="shared" ref="K270:O270" si="513">RAND()</f>
-        <v>0.555109197464071</v>
+        <v>0.453296446951215</v>
       </c>
       <c r="L270" s="1">
         <f ca="1" t="shared" ref="L270:P270" si="514">J270+$R$1*K270/MAX(1,($A270*($A270-1)))++$R$1/$A270</f>
-        <v>2.42506457665029</v>
+        <v>2.42499396357914</v>
       </c>
       <c r="M270" s="1">
         <f ca="1" t="shared" si="513"/>
-        <v>0.438602120574973</v>
+        <v>0.783906190741726</v>
       </c>
       <c r="N270" s="1">
         <f ca="1" t="shared" si="514"/>
-        <v>2.61124237870917</v>
+        <v>2.61141125411814</v>
       </c>
       <c r="O270" s="1">
         <f ca="1" t="shared" si="513"/>
-        <v>0.00746213591624678</v>
+        <v>0.529919895216501</v>
       </c>
       <c r="P270" s="1">
         <f ca="1" t="shared" si="514"/>
-        <v>2.79712116008291</v>
+        <v>2.79765239037127</v>
       </c>
     </row>
     <row r="271" ht="16.5" spans="1:16">
@@ -22121,27 +22146,27 @@
       </c>
       <c r="K271" s="1">
         <f ca="1" t="shared" ref="K271:O271" si="515">RAND()</f>
-        <v>0.129084042057562</v>
+        <v>0.211070743685993</v>
       </c>
       <c r="L271" s="1">
         <f ca="1" t="shared" ref="L271:P271" si="516">J271+$R$1*K271/MAX(1,($A271*($A271-1)))++$R$1/$A271</f>
-        <v>2.41575732069534</v>
+        <v>2.41581376204302</v>
       </c>
       <c r="M271" s="1">
         <f ca="1" t="shared" si="515"/>
-        <v>0.47273121910444</v>
+        <v>0.30795232983013</v>
       </c>
       <c r="N271" s="1">
         <f ca="1" t="shared" si="516"/>
-        <v>2.60126794386697</v>
+        <v>2.601210948006</v>
       </c>
       <c r="O271" s="1">
         <f ca="1" t="shared" si="515"/>
-        <v>0.550511835271384</v>
+        <v>0.177010997934204</v>
       </c>
       <c r="P271" s="1">
         <f ca="1" t="shared" si="516"/>
-        <v>2.7868321128297</v>
+        <v>2.7865179912374</v>
       </c>
     </row>
     <row r="272" ht="16.5" spans="1:16">
@@ -22181,27 +22206,27 @@
       </c>
       <c r="K272" s="1">
         <f ca="1" t="shared" ref="K272:O272" si="517">RAND()</f>
-        <v>0.676493726604586</v>
+        <v>0.0718628237137955</v>
       </c>
       <c r="L272" s="1">
         <f ca="1" t="shared" ref="L272:P272" si="518">J272+$R$1*K272/MAX(1,($A272*($A272-1)))++$R$1/$A272</f>
-        <v>2.4071863425766</v>
+        <v>2.40677317399461</v>
       </c>
       <c r="M272" s="1">
         <f ca="1" t="shared" si="517"/>
-        <v>0.752858569050411</v>
+        <v>0.73786562879797</v>
       </c>
       <c r="N272" s="1">
         <f ca="1" t="shared" si="518"/>
-        <v>2.59220264609516</v>
+        <v>2.59177923223487</v>
       </c>
       <c r="O272" s="1">
         <f ca="1" t="shared" si="517"/>
-        <v>0.275309354288879</v>
+        <v>0.949472145358558</v>
       </c>
       <c r="P272" s="1">
         <f ca="1" t="shared" si="518"/>
-        <v>2.77689262105367</v>
+        <v>2.77692988970744</v>
       </c>
     </row>
     <row r="273" ht="16.5" spans="1:16">
@@ -22241,27 +22266,27 @@
       </c>
       <c r="K273" s="1">
         <f ca="1" t="shared" ref="K273:O273" si="519">RAND()</f>
-        <v>0.713181789764163</v>
+        <v>0.0798039419988985</v>
       </c>
       <c r="L273" s="1">
         <f ca="1" t="shared" ref="L273:P273" si="520">J273+$R$1*K273/MAX(1,($A273*($A273-1)))++$R$1/$A273</f>
-        <v>2.39832943197157</v>
+        <v>2.3978998018925</v>
       </c>
       <c r="M273" s="1">
         <f ca="1" t="shared" si="519"/>
-        <v>0.998299766963771</v>
+        <v>0.157900014879065</v>
       </c>
       <c r="N273" s="1">
         <f ca="1" t="shared" si="520"/>
-        <v>2.58283012369541</v>
+        <v>2.58183043734865</v>
       </c>
       <c r="O273" s="1">
         <f ca="1" t="shared" si="519"/>
-        <v>0.5698447232648</v>
+        <v>0.933928566241409</v>
       </c>
       <c r="P273" s="1">
         <f ca="1" t="shared" si="520"/>
-        <v>2.76704018767635</v>
+        <v>2.76628746508243</v>
       </c>
     </row>
     <row r="274" ht="16.5" spans="1:16">
@@ -22301,27 +22326,27 @@
       </c>
       <c r="K274" s="1">
         <f ca="1" t="shared" ref="K274:O274" si="521">RAND()</f>
-        <v>0.955683641117266</v>
+        <v>0.360837389604773</v>
       </c>
       <c r="L274" s="1">
         <f ca="1" t="shared" ref="L274:P274" si="522">J274+$R$1*K274/MAX(1,($A274*($A274-1)))++$R$1/$A274</f>
-        <v>2.38967604209836</v>
+        <v>2.38927550459869</v>
       </c>
       <c r="M274" s="1">
         <f ca="1" t="shared" si="521"/>
-        <v>0.816402992816019</v>
+        <v>0.0640575771486735</v>
       </c>
       <c r="N274" s="1">
         <f ca="1" t="shared" si="522"/>
-        <v>2.5733759471517</v>
+        <v>2.57246882067897</v>
       </c>
       <c r="O274" s="1">
         <f ca="1" t="shared" si="521"/>
-        <v>0.0259301040780726</v>
+        <v>0.215842100611856</v>
       </c>
       <c r="P274" s="1">
         <f ca="1" t="shared" si="522"/>
-        <v>2.75654359024053</v>
+        <v>2.75576434030069</v>
       </c>
     </row>
     <row r="275" ht="16.5" spans="1:16">
@@ -22361,27 +22386,27 @@
       </c>
       <c r="K275" s="1">
         <f ca="1" t="shared" ref="K275:O275" si="523">RAND()</f>
-        <v>0.0488480531450013</v>
+        <v>0.504449185020426</v>
       </c>
       <c r="L275" s="1">
         <f ca="1" t="shared" ref="L275:P275" si="524">J275+$R$1*K275/MAX(1,($A275*($A275-1)))++$R$1/$A275</f>
-        <v>2.38031660119592</v>
+        <v>2.38062113926434</v>
       </c>
       <c r="M275" s="1">
         <f ca="1" t="shared" si="523"/>
-        <v>0.904385407541228</v>
+        <v>0.0135013268288766</v>
       </c>
       <c r="N275" s="1">
         <f ca="1" t="shared" si="524"/>
-        <v>2.56340287255734</v>
+        <v>2.56311191579894</v>
       </c>
       <c r="O275" s="1">
         <f ca="1" t="shared" si="523"/>
-        <v>0.149324656925863</v>
+        <v>0.380411057502996</v>
       </c>
       <c r="P275" s="1">
         <f ca="1" t="shared" si="524"/>
-        <v>2.7459844376605</v>
+        <v>2.74584794629111</v>
       </c>
     </row>
     <row r="276" ht="16.5" spans="1:16">
@@ -22421,27 +22446,27 @@
       </c>
       <c r="K276" s="1">
         <f ca="1" t="shared" ref="K276:O276" si="525">RAND()</f>
-        <v>0.783776183864135</v>
+        <v>0.987810148495242</v>
       </c>
       <c r="L276" s="1">
         <f ca="1" t="shared" ref="L276:P276" si="526">J276+$R$1*K276/MAX(1,($A276*($A276-1)))++$R$1/$A276</f>
-        <v>2.37211929408352</v>
+        <v>2.37225468490278</v>
       </c>
       <c r="M276" s="1">
         <f ca="1" t="shared" si="525"/>
-        <v>0.965108779042892</v>
+        <v>0.280736250623614</v>
       </c>
       <c r="N276" s="1">
         <f ca="1" t="shared" si="526"/>
-        <v>2.55457789314061</v>
+        <v>2.55425915487665</v>
       </c>
       <c r="O276" s="1">
         <f ca="1" t="shared" si="525"/>
-        <v>0.721191066369475</v>
+        <v>0.556224932176502</v>
       </c>
       <c r="P276" s="1">
         <f ca="1" t="shared" si="526"/>
-        <v>2.73687463571949</v>
+        <v>2.73644643087677</v>
       </c>
     </row>
     <row r="277" ht="16.5" spans="1:16">
@@ -22481,27 +22506,27 @@
       </c>
       <c r="K277" s="1">
         <f ca="1" t="shared" ref="K277:O277" si="527">RAND()</f>
-        <v>0.757581178694102</v>
+        <v>0.860502196103434</v>
       </c>
       <c r="L277" s="1">
         <f ca="1" t="shared" ref="L277:P277" si="528">J277+$R$1*K277/MAX(1,($A277*($A277-1)))++$R$1/$A277</f>
-        <v>2.36347666744314</v>
+        <v>2.36354446784987</v>
       </c>
       <c r="M277" s="1">
         <f ca="1" t="shared" si="527"/>
-        <v>0.311011432424255</v>
+        <v>0.0658788253021585</v>
       </c>
       <c r="N277" s="1">
         <f ca="1" t="shared" si="528"/>
-        <v>2.54484097009955</v>
+        <v>2.54474728657537</v>
       </c>
       <c r="O277" s="1">
         <f ca="1" t="shared" si="527"/>
-        <v>0.217378108855714</v>
+        <v>0.622384348457664</v>
       </c>
       <c r="P277" s="1">
         <f ca="1" t="shared" si="528"/>
-        <v>2.72614359072462</v>
+        <v>2.72631670972982</v>
       </c>
     </row>
     <row r="278" ht="16.5" spans="1:16">
@@ -22541,27 +22566,27 @@
       </c>
       <c r="K278" s="1">
         <f ca="1" t="shared" ref="K278:O278" si="529">RAND()</f>
-        <v>0.58684820200422</v>
+        <v>0.789330521616408</v>
       </c>
       <c r="L278" s="1">
         <f ca="1" t="shared" ref="L278:P278" si="530">J278+$R$1*K278/MAX(1,($A278*($A278-1)))++$R$1/$A278</f>
-        <v>2.35480226037383</v>
+        <v>2.35493468484907</v>
       </c>
       <c r="M278" s="1">
         <f ca="1" t="shared" si="529"/>
-        <v>0.357136064285996</v>
+        <v>0.802908089760573</v>
       </c>
       <c r="N278" s="1">
         <f ca="1" t="shared" si="530"/>
-        <v>2.53554124435351</v>
+        <v>2.53596520601906</v>
       </c>
       <c r="O278" s="1">
         <f ca="1" t="shared" si="529"/>
-        <v>0.785518937534723</v>
+        <v>0.155786062285489</v>
       </c>
       <c r="P278" s="1">
         <f ca="1" t="shared" si="530"/>
-        <v>2.71656039292878</v>
+        <v>2.71657250606502</v>
       </c>
     </row>
     <row r="279" ht="16.5" spans="1:16">
@@ -22601,27 +22626,27 @@
       </c>
       <c r="K279" s="1">
         <f ca="1" t="shared" ref="K279:O279" si="531">RAND()</f>
-        <v>0.550273615235948</v>
+        <v>0.380214216114935</v>
       </c>
       <c r="L279" s="1">
         <f ca="1" t="shared" ref="L279:P279" si="532">J279+$R$1*K279/MAX(1,($A279*($A279-1)))++$R$1/$A279</f>
-        <v>2.34627838974576</v>
+        <v>2.34616797016863</v>
       </c>
       <c r="M279" s="1">
         <f ca="1" t="shared" si="531"/>
-        <v>0.223581609976086</v>
+        <v>0.838135286733658</v>
       </c>
       <c r="N279" s="1">
         <f ca="1" t="shared" si="532"/>
-        <v>2.52627967640522</v>
+        <v>2.52656828656394</v>
       </c>
       <c r="O279" s="1">
         <f ca="1" t="shared" si="531"/>
-        <v>0.942062813869972</v>
+        <v>0.434964498049909</v>
       </c>
       <c r="P279" s="1">
         <f ca="1" t="shared" si="532"/>
-        <v>2.70674747294957</v>
+        <v>2.70670682414416</v>
       </c>
     </row>
     <row r="280" ht="16.5" spans="1:16">
@@ -22661,27 +22686,27 @@
       </c>
       <c r="K280" s="1">
         <f ca="1" t="shared" ref="K280:O280" si="533">RAND()</f>
-        <v>0.45302766974298</v>
+        <v>0.0458881533996061</v>
       </c>
       <c r="L280" s="1">
         <f ca="1" t="shared" ref="L280:P280" si="534">J280+$R$1*K280/MAX(1,($A280*($A280-1)))++$R$1/$A280</f>
-        <v>2.33777689311115</v>
+        <v>2.337514432424</v>
       </c>
       <c r="M280" s="1">
         <f ca="1" t="shared" si="533"/>
-        <v>0.355353984051115</v>
+        <v>0.0144442743298434</v>
       </c>
       <c r="N280" s="1">
         <f ca="1" t="shared" si="534"/>
-        <v>2.51721744001817</v>
+        <v>2.51673521339556</v>
       </c>
       <c r="O280" s="1">
         <f ca="1" t="shared" si="533"/>
-        <v>0.795305092381639</v>
+        <v>0.106970500776107</v>
       </c>
       <c r="P280" s="1">
         <f ca="1" t="shared" si="534"/>
-        <v>2.6969415994599</v>
+        <v>2.69601564098947</v>
       </c>
     </row>
     <row r="281" ht="16.5" spans="1:16">
@@ -22721,27 +22746,27 @@
       </c>
       <c r="K281" s="1">
         <f ca="1" t="shared" ref="K281:O281" si="535">RAND()</f>
-        <v>0.143572525379785</v>
+        <v>0.596048405188073</v>
       </c>
       <c r="L281" s="1">
         <f ca="1" t="shared" ref="L281:P281" si="536">J281+$R$1*K281/MAX(1,($A281*($A281-1)))++$R$1/$A281</f>
-        <v>2.32920095527738</v>
+        <v>2.32949055837506</v>
       </c>
       <c r="M281" s="1">
         <f ca="1" t="shared" si="535"/>
-        <v>0.844214391854637</v>
+        <v>0.0375030197583559</v>
       </c>
       <c r="N281" s="1">
         <f ca="1" t="shared" si="536"/>
-        <v>2.50831271564083</v>
+        <v>2.50808599041535</v>
       </c>
       <c r="O281" s="1">
         <f ca="1" t="shared" si="535"/>
-        <v>0.0596449179829561</v>
+        <v>0.019340793628547</v>
       </c>
       <c r="P281" s="1">
         <f ca="1" t="shared" si="536"/>
-        <v>2.68692231940298</v>
+        <v>2.68666979788695</v>
       </c>
     </row>
     <row r="282" ht="16.5" spans="1:16">
@@ -22781,27 +22806,27 @@
       </c>
       <c r="K282" s="1">
         <f ca="1" t="shared" ref="K282:O282" si="537">RAND()</f>
-        <v>0.967986098886761</v>
+        <v>0.806838108619731</v>
       </c>
       <c r="L282" s="1">
         <f ca="1" t="shared" ref="L282:P282" si="538">J282+$R$1*K282/MAX(1,($A282*($A282-1)))++$R$1/$A282</f>
-        <v>2.32140822705826</v>
+        <v>2.32130581984534</v>
       </c>
       <c r="M282" s="1">
         <f ca="1" t="shared" si="537"/>
-        <v>0.222715664189887</v>
+        <v>0.0474771447812095</v>
       </c>
       <c r="N282" s="1">
         <f ca="1" t="shared" si="538"/>
-        <v>2.49948570269641</v>
+        <v>2.49927193394344</v>
       </c>
       <c r="O282" s="1">
         <f ca="1" t="shared" si="537"/>
-        <v>0.183902649968747</v>
+        <v>0.433938943007846</v>
       </c>
       <c r="P282" s="1">
         <f ca="1" t="shared" si="538"/>
-        <v>2.67753851322639</v>
+        <v>2.67748363891485</v>
       </c>
     </row>
     <row r="283" ht="16.5" spans="1:16">
@@ -22841,27 +22866,27 @@
       </c>
       <c r="K283" s="1">
         <f ca="1" t="shared" ref="K283:O283" si="539">RAND()</f>
-        <v>0.976660818588005</v>
+        <v>0.948806776655763</v>
       </c>
       <c r="L283" s="1">
         <f ca="1" t="shared" ref="L283:P283" si="540">J283+$R$1*K283/MAX(1,($A283*($A283-1)))++$R$1/$A283</f>
-        <v>2.3131525332643</v>
+        <v>2.3131349579621</v>
       </c>
       <c r="M283" s="1">
         <f ca="1" t="shared" si="539"/>
-        <v>0.289901539374315</v>
+        <v>0.090460928120798</v>
       </c>
       <c r="N283" s="1">
         <f ca="1" t="shared" si="540"/>
-        <v>2.490640419448</v>
+        <v>2.49049700140379</v>
       </c>
       <c r="O283" s="1">
         <f ca="1" t="shared" si="539"/>
-        <v>0.525372253321137</v>
+        <v>0.776528896767138</v>
       </c>
       <c r="P283" s="1">
         <f ca="1" t="shared" si="540"/>
-        <v>2.66827688259464</v>
+        <v>2.66829193899797</v>
       </c>
     </row>
     <row r="284" ht="16.5" spans="1:16">
@@ -22901,27 +22926,27 @@
       </c>
       <c r="K284" s="1">
         <f ca="1" t="shared" ref="K284:O284" si="541">RAND()</f>
-        <v>0.0913446964659061</v>
+        <v>0.725363988884087</v>
       </c>
       <c r="L284" s="1">
         <f ca="1" t="shared" ref="L284:P284" si="542">J284+$R$1*K284/MAX(1,($A284*($A284-1)))++$R$1/$A284</f>
-        <v>2.3043952489139</v>
+        <v>2.30479247424309</v>
       </c>
       <c r="M284" s="1">
         <f ca="1" t="shared" si="541"/>
-        <v>0.732046807142632</v>
+        <v>0.135414666384994</v>
       </c>
       <c r="N284" s="1">
         <f ca="1" t="shared" si="542"/>
-        <v>2.48153233560359</v>
+        <v>2.48155575937603</v>
       </c>
       <c r="O284" s="1">
         <f ca="1" t="shared" si="541"/>
-        <v>0.473301962512264</v>
+        <v>0.00692848281359049</v>
       </c>
       <c r="P284" s="1">
         <f ca="1" t="shared" si="542"/>
-        <v>2.65850731365193</v>
+        <v>2.65823854543398</v>
       </c>
     </row>
     <row r="285" ht="16.5" spans="1:16">
@@ -22961,27 +22986,27 @@
       </c>
       <c r="K285" s="1">
         <f ca="1" t="shared" ref="K285:O285" si="543">RAND()</f>
-        <v>0.315273778235291</v>
+        <v>0.653537986938142</v>
       </c>
       <c r="L285" s="1">
         <f ca="1" t="shared" ref="L285:P285" si="544">J285+$R$1*K285/MAX(1,($A285*($A285-1)))++$R$1/$A285</f>
-        <v>2.29639381487224</v>
+        <v>2.29660425147249</v>
       </c>
       <c r="M285" s="1">
         <f ca="1" t="shared" si="543"/>
-        <v>0.641831029311649</v>
+        <v>0.22380078753361</v>
       </c>
       <c r="N285" s="1">
         <f ca="1" t="shared" si="544"/>
-        <v>2.4728494406059</v>
+        <v>2.47279981758229</v>
       </c>
       <c r="O285" s="1">
         <f ca="1" t="shared" si="543"/>
-        <v>0.261140899656978</v>
+        <v>0.950941798737799</v>
       </c>
       <c r="P285" s="1">
         <f ca="1" t="shared" si="544"/>
-        <v>2.64906823626835</v>
+        <v>2.64944774335167</v>
       </c>
     </row>
     <row r="286" ht="16.5" spans="1:16">
@@ -23021,27 +23046,27 @@
       </c>
       <c r="K286" s="1">
         <f ca="1" t="shared" ref="K286:O286" si="545">RAND()</f>
-        <v>0.485001271383222</v>
+        <v>0.824160088982337</v>
       </c>
       <c r="L286" s="1">
         <f ca="1" t="shared" ref="L286:P286" si="546">J286+$R$1*K286/MAX(1,($A286*($A286-1)))++$R$1/$A286</f>
-        <v>2.28841425826006</v>
+        <v>2.28862377074931</v>
       </c>
       <c r="M286" s="1">
         <f ca="1" t="shared" si="545"/>
-        <v>0.922872150464817</v>
+        <v>0.755343913736468</v>
       </c>
       <c r="N286" s="1">
         <f ca="1" t="shared" si="546"/>
-        <v>2.46442295121192</v>
+        <v>2.46452897455073</v>
       </c>
       <c r="O286" s="1">
         <f ca="1" t="shared" si="545"/>
-        <v>0.17419363375927</v>
+        <v>0.384927677158255</v>
       </c>
       <c r="P286" s="1">
         <f ca="1" t="shared" si="546"/>
-        <v>2.63996915434619</v>
+        <v>2.64020535685685</v>
       </c>
     </row>
     <row r="287" ht="16.5" spans="1:16">
@@ -23081,27 +23106,27 @@
       </c>
       <c r="K287" s="1">
         <f ca="1" t="shared" ref="K287:O287" si="547">RAND()</f>
-        <v>0.468056491973642</v>
+        <v>0.583513606809759</v>
       </c>
       <c r="L287" s="1">
         <f ca="1" t="shared" ref="L287:P287" si="548">J287+$R$1*K287/MAX(1,($A287*($A287-1)))++$R$1/$A287</f>
-        <v>2.28037544871303</v>
+        <v>2.28044627260877</v>
       </c>
       <c r="M287" s="1">
         <f ca="1" t="shared" si="547"/>
-        <v>0.901267608383032</v>
+        <v>0.324845093060491</v>
       </c>
       <c r="N287" s="1">
         <f ca="1" t="shared" si="548"/>
-        <v>2.4557534806161</v>
+        <v>2.45547071445214</v>
       </c>
       <c r="O287" s="1">
         <f ca="1" t="shared" si="547"/>
-        <v>0.0977679223371068</v>
+        <v>0.718204804095526</v>
       </c>
       <c r="P287" s="1">
         <f ca="1" t="shared" si="548"/>
-        <v>2.63063862840308</v>
+        <v>2.63073645166481</v>
       </c>
     </row>
     <row r="288" ht="16.5" spans="1:16">
@@ -23141,27 +23166,27 @@
       </c>
       <c r="K288" s="1">
         <f ca="1" t="shared" ref="K288:O288" si="549">RAND()</f>
-        <v>0.39448669883907</v>
+        <v>0.468991758270946</v>
       </c>
       <c r="L288" s="1">
         <f ca="1" t="shared" ref="L288:P288" si="550">J288+$R$1*K288/MAX(1,($A288*($A288-1)))++$R$1/$A288</f>
-        <v>2.27235842614632</v>
+        <v>2.27240381067607</v>
       </c>
       <c r="M288" s="1">
         <f ca="1" t="shared" si="549"/>
-        <v>0.883752126228621</v>
+        <v>0.590920614180785</v>
       </c>
       <c r="N288" s="1">
         <f ca="1" t="shared" si="550"/>
-        <v>2.44711278893367</v>
+        <v>2.44697979604082</v>
       </c>
       <c r="O288" s="1">
         <f ca="1" t="shared" si="549"/>
-        <v>0.145035226425778</v>
+        <v>0.0442133576205539</v>
       </c>
       <c r="P288" s="1">
         <f ca="1" t="shared" si="550"/>
-        <v>2.62141716457414</v>
+        <v>2.62122275634735</v>
       </c>
     </row>
     <row r="289" ht="16.5" spans="1:16">
@@ -23201,27 +23226,27 @@
       </c>
       <c r="K289" s="1">
         <f ca="1" t="shared" ref="K289:O289" si="551">RAND()</f>
-        <v>0.932482273736736</v>
+        <v>0.47913155449222</v>
       </c>
       <c r="L289" s="1">
         <f ca="1" t="shared" ref="L289:P289" si="552">J289+$R$1*K289/MAX(1,($A289*($A289-1)))++$R$1/$A289</f>
-        <v>2.26476751976489</v>
+        <v>2.2644932803151</v>
       </c>
       <c r="M289" s="1">
         <f ca="1" t="shared" si="551"/>
-        <v>0.963722480151328</v>
+        <v>0.256632046635887</v>
       </c>
       <c r="N289" s="1">
         <f ca="1" t="shared" si="552"/>
-        <v>2.43896160275956</v>
+        <v>2.43825963245326</v>
       </c>
       <c r="O289" s="1">
         <f ca="1" t="shared" si="551"/>
-        <v>0.82871467046692</v>
+        <v>0.0655749385539341</v>
       </c>
       <c r="P289" s="1">
         <f ca="1" t="shared" si="552"/>
-        <v>2.61307401726696</v>
+        <v>2.61191041094396</v>
       </c>
     </row>
     <row r="290" ht="16.5" spans="1:16">
@@ -23261,27 +23286,27 @@
       </c>
       <c r="K290" s="1">
         <f ca="1" t="shared" ref="K290:O290" si="553">RAND()</f>
-        <v>0.0278499415859739</v>
+        <v>0.965684402927274</v>
       </c>
       <c r="L290" s="1">
         <f ca="1" t="shared" ref="L290:P290" si="554">J290+$R$1*K290/MAX(1,($A290*($A290-1)))++$R$1/$A290</f>
-        <v>2.25636044426517</v>
+        <v>2.25692383001906</v>
       </c>
       <c r="M290" s="1">
         <f ca="1" t="shared" si="553"/>
-        <v>0.974002846929536</v>
+        <v>0.763218709220938</v>
       </c>
       <c r="N290" s="1">
         <f ca="1" t="shared" si="554"/>
-        <v>2.42995593809383</v>
+        <v>2.43039269938975</v>
       </c>
       <c r="O290" s="1">
         <f ca="1" t="shared" si="553"/>
-        <v>0.531260613608055</v>
+        <v>0.0400969913655558</v>
       </c>
       <c r="P290" s="1">
         <f ca="1" t="shared" si="554"/>
-        <v>2.60328546316448</v>
+        <v>2.60342716749779</v>
       </c>
     </row>
     <row r="291" ht="16.5" spans="1:16">
@@ -23321,27 +23346,27 @@
       </c>
       <c r="K291" s="1">
         <f ca="1" t="shared" ref="K291:O291" si="555">RAND()</f>
-        <v>0.0783691876588255</v>
+        <v>0.961511475819828</v>
       </c>
       <c r="L291" s="1">
         <f ca="1" t="shared" ref="L291:P291" si="556">J291+$R$1*K291/MAX(1,($A291*($A291-1)))++$R$1/$A291</f>
-        <v>2.24858511465676</v>
+        <v>2.24911198632372</v>
       </c>
       <c r="M291" s="1">
         <f ca="1" t="shared" si="555"/>
-        <v>0.623637292443375</v>
+        <v>0.0618021407788525</v>
       </c>
       <c r="N291" s="1">
         <f ca="1" t="shared" si="556"/>
-        <v>2.42137096198551</v>
+        <v>2.42156264981303</v>
       </c>
       <c r="O291" s="1">
         <f ca="1" t="shared" si="555"/>
-        <v>0.996448611846944</v>
+        <v>0.0631564629473149</v>
       </c>
       <c r="P291" s="1">
         <f ca="1" t="shared" si="556"/>
-        <v>2.59437922389449</v>
+        <v>2.59401412127404</v>
       </c>
     </row>
     <row r="292" ht="16.5" spans="1:16">
@@ -23381,27 +23406,27 @@
       </c>
       <c r="K292" s="1">
         <f ca="1" t="shared" ref="K292:O292" si="557">RAND()</f>
-        <v>0.578233372300561</v>
+        <v>0.116490722646344</v>
       </c>
       <c r="L292" s="1">
         <f ca="1" t="shared" ref="L292:P292" si="558">J292+$R$1*K292/MAX(1,($A292*($A292-1)))++$R$1/$A292</f>
-        <v>2.24112941899058</v>
+        <v>2.24085584235256</v>
       </c>
       <c r="M292" s="1">
         <f ca="1" t="shared" si="557"/>
-        <v>0.39278557083457</v>
+        <v>0.305533550608821</v>
       </c>
       <c r="N292" s="1">
         <f ca="1" t="shared" si="558"/>
-        <v>2.41318344527973</v>
+        <v>2.41285817293119</v>
       </c>
       <c r="O292" s="1">
         <f ca="1" t="shared" si="557"/>
-        <v>0.75740505970884</v>
+        <v>0.426556417898086</v>
       </c>
       <c r="P292" s="1">
         <f ca="1" t="shared" si="558"/>
-        <v>2.58545350397135</v>
+        <v>2.58493220801704</v>
       </c>
     </row>
     <row r="293" ht="16.5" spans="1:16">
@@ -23441,27 +23466,27 @@
       </c>
       <c r="K293" s="1">
         <f ca="1" t="shared" ref="K293:O293" si="559">RAND()</f>
-        <v>0.755244319593654</v>
+        <v>0.846633473648878</v>
       </c>
       <c r="L293" s="1">
         <f ca="1" t="shared" ref="L293:P293" si="560">J293+$R$1*K293/MAX(1,($A293*($A293-1)))++$R$1/$A293</f>
-        <v>2.23353295457303</v>
+        <v>2.23358673061341</v>
       </c>
       <c r="M293" s="1">
         <f ca="1" t="shared" si="559"/>
-        <v>0.436040848187687</v>
+        <v>0.773212050059876</v>
       </c>
       <c r="N293" s="1">
         <f ca="1" t="shared" si="560"/>
-        <v>2.40502241042213</v>
+        <v>2.40527458781934</v>
       </c>
       <c r="O293" s="1">
         <f ca="1" t="shared" si="559"/>
-        <v>0.861462114985591</v>
+        <v>0.991750899126342</v>
       </c>
       <c r="P293" s="1">
         <f ca="1" t="shared" si="560"/>
-        <v>2.57676219653695</v>
+        <v>2.57709103965002</v>
       </c>
     </row>
     <row r="294" ht="16.5" spans="1:16">
@@ -23501,27 +23526,27 @@
       </c>
       <c r="K294" s="1">
         <f ca="1" t="shared" ref="K294:O294" si="561">RAND()</f>
-        <v>0.428931939173207</v>
+        <v>0.284606122068487</v>
       </c>
       <c r="L294" s="1">
         <f ca="1" t="shared" ref="L294:P294" si="562">J294+$R$1*K294/MAX(1,($A294*($A294-1)))++$R$1/$A294</f>
-        <v>2.22569365791947</v>
+        <v>2.22560931210089</v>
       </c>
       <c r="M294" s="1">
         <f ca="1" t="shared" si="561"/>
-        <v>0.671344825282648</v>
+        <v>0.153071074547126</v>
       </c>
       <c r="N294" s="1">
         <f ca="1" t="shared" si="562"/>
-        <v>2.39673446442356</v>
+        <v>2.39634723292149</v>
       </c>
       <c r="O294" s="1">
         <f ca="1" t="shared" si="561"/>
-        <v>0.0473432883127376</v>
+        <v>0.701947580349115</v>
       </c>
       <c r="P294" s="1">
         <f ca="1" t="shared" si="562"/>
-        <v>2.56741059659916</v>
+        <v>2.56740592405966</v>
       </c>
     </row>
     <row r="295" ht="16.5" spans="1:16">
@@ -23561,27 +23586,27 @@
       </c>
       <c r="K295" s="1">
         <f ca="1" t="shared" ref="K295:O295" si="563">RAND()</f>
-        <v>0.362005847603114</v>
+        <v>0.163818178914301</v>
       </c>
       <c r="L295" s="1">
         <f ca="1" t="shared" ref="L295:P295" si="564">J295+$R$1*K295/MAX(1,($A295*($A295-1)))++$R$1/$A295</f>
-        <v>2.21805971874788</v>
+        <v>2.21794468330136</v>
       </c>
       <c r="M295" s="1">
         <f ca="1" t="shared" si="563"/>
-        <v>0.534322995503444</v>
+        <v>0.501673377302222</v>
       </c>
       <c r="N295" s="1">
         <f ca="1" t="shared" si="564"/>
-        <v>2.38843788677016</v>
+        <v>2.38830390027874</v>
       </c>
       <c r="O295" s="1">
         <f ca="1" t="shared" si="563"/>
-        <v>0.094132422228286</v>
+        <v>0.656331648032165</v>
       </c>
       <c r="P295" s="1">
         <f ca="1" t="shared" si="564"/>
-        <v>2.55856055191738</v>
+        <v>2.55875288663152</v>
       </c>
     </row>
     <row r="296" ht="16.5" spans="1:16">
@@ -23621,27 +23646,27 @@
       </c>
       <c r="K296" s="1">
         <f ca="1" t="shared" ref="K296:O296" si="565">RAND()</f>
-        <v>0.735129453538173</v>
+        <v>0.52559541308183</v>
       </c>
       <c r="L296" s="1">
         <f ca="1" t="shared" ref="L296:P296" si="566">J296+$R$1*K296/MAX(1,($A296*($A296-1)))++$R$1/$A296</f>
-        <v>2.21073165539809</v>
+        <v>2.2106108586493</v>
       </c>
       <c r="M296" s="1">
         <f ca="1" t="shared" si="565"/>
-        <v>0.333064243599411</v>
+        <v>0.656193506871044</v>
       </c>
       <c r="N296" s="1">
         <f ca="1" t="shared" si="566"/>
-        <v>2.3804151929535</v>
+        <v>2.38048068080246</v>
       </c>
       <c r="O296" s="1">
         <f ca="1" t="shared" si="565"/>
-        <v>0.631938521082072</v>
+        <v>0.871325203495902</v>
       </c>
       <c r="P296" s="1">
         <f ca="1" t="shared" si="566"/>
-        <v>2.550271032064</v>
+        <v>2.5504745267632</v>
       </c>
     </row>
     <row r="297" ht="16.5" spans="1:16">
@@ -23681,27 +23706,27 @@
       </c>
       <c r="K297" s="1">
         <f ca="1" t="shared" ref="K297:O297" si="567">RAND()</f>
-        <v>0.613080410635461</v>
+        <v>0.362983889671878</v>
       </c>
       <c r="L297" s="1">
         <f ca="1" t="shared" ref="L297:P297" si="568">J297+$R$1*K297/MAX(1,($A297*($A297-1)))++$R$1/$A297</f>
-        <v>2.20316827783477</v>
+        <v>2.20302507094003</v>
       </c>
       <c r="M297" s="1">
         <f ca="1" t="shared" si="567"/>
-        <v>0.252630638571063</v>
+        <v>0.349509031819287</v>
       </c>
       <c r="N297" s="1">
         <f ca="1" t="shared" si="568"/>
-        <v>2.37223185470065</v>
+        <v>2.37214412100406</v>
       </c>
       <c r="O297" s="1">
         <f ca="1" t="shared" si="567"/>
-        <v>0.949277720090463</v>
+        <v>0.761860823122236</v>
       </c>
       <c r="P297" s="1">
         <f ca="1" t="shared" si="568"/>
-        <v>2.54169433621696</v>
+        <v>2.54149928638606</v>
       </c>
     </row>
     <row r="298" ht="16.5" spans="1:16">
@@ -23741,27 +23766,27 @@
       </c>
       <c r="K298" s="1">
         <f ca="1" t="shared" ref="K298:O298" si="569">RAND()</f>
-        <v>0.828871527618896</v>
+        <v>0.224866662940929</v>
       </c>
       <c r="L298" s="1">
         <f ca="1" t="shared" ref="L298:P298" si="570">J298+$R$1*K298/MAX(1,($A298*($A298-1)))++$R$1/$A298</f>
-        <v>2.19584861652995</v>
+        <v>2.19550508841964</v>
       </c>
       <c r="M298" s="1">
         <f ca="1" t="shared" si="569"/>
-        <v>0.178071358751315</v>
+        <v>0.538582261099955</v>
       </c>
       <c r="N298" s="1">
         <f ca="1" t="shared" si="570"/>
-        <v>2.36430006306669</v>
+        <v>2.36416157573712</v>
       </c>
       <c r="O298" s="1">
         <f ca="1" t="shared" si="569"/>
-        <v>0.250641849139948</v>
+        <v>0.784194726500004</v>
       </c>
       <c r="P298" s="1">
         <f ca="1" t="shared" si="570"/>
-        <v>2.53279278411111</v>
+        <v>2.532957755284</v>
       </c>
     </row>
     <row r="299" ht="16.5" spans="1:16">
@@ -23801,27 +23826,27 @@
       </c>
       <c r="K299" s="1">
         <f ca="1" t="shared" ref="K299:O299" si="571">RAND()</f>
-        <v>0.180084204580526</v>
+        <v>0.976724773641082</v>
       </c>
       <c r="L299" s="1">
         <f ca="1" t="shared" ref="L299:P299" si="572">J299+$R$1*K299/MAX(1,($A299*($A299-1)))++$R$1/$A299</f>
-        <v>2.18808899069248</v>
+        <v>2.18853903959824</v>
       </c>
       <c r="M299" s="1">
         <f ca="1" t="shared" si="571"/>
-        <v>0.660595790802689</v>
+        <v>0.191063987781239</v>
       </c>
       <c r="N299" s="1">
         <f ca="1" t="shared" si="572"/>
-        <v>2.35624741825152</v>
+        <v>2.35643221293552</v>
       </c>
       <c r="O299" s="1">
         <f ca="1" t="shared" si="571"/>
-        <v>0.179057523088347</v>
+        <v>0.528044966022089</v>
       </c>
       <c r="P299" s="1">
         <f ca="1" t="shared" si="572"/>
-        <v>2.52413380873527</v>
+        <v>2.5245157580997</v>
       </c>
     </row>
     <row r="300" ht="16.5" spans="1:16">
@@ -23861,27 +23886,27 @@
       </c>
       <c r="K300" s="1">
         <f ca="1" t="shared" ref="K300:O300" si="573">RAND()</f>
-        <v>0.0434819788104792</v>
+        <v>0.00175408569116864</v>
       </c>
       <c r="L300" s="1">
         <f ca="1" t="shared" ref="L300:P300" si="574">J300+$R$1*K300/MAX(1,($A300*($A300-1)))++$R$1/$A300</f>
-        <v>2.18067129917332</v>
+        <v>2.18064788337281</v>
       </c>
       <c r="M300" s="1">
         <f ca="1" t="shared" si="573"/>
-        <v>0.468107898287111</v>
+        <v>0.582921368221199</v>
       </c>
       <c r="N300" s="1">
         <f ca="1" t="shared" si="574"/>
-        <v>2.34815806035617</v>
+        <v>2.34819907266611</v>
       </c>
       <c r="O300" s="1">
         <f ca="1" t="shared" si="573"/>
-        <v>0.372172097660633</v>
+        <v>0.553385256080998</v>
       </c>
       <c r="P300" s="1">
         <f ca="1" t="shared" si="574"/>
-        <v>2.51559098672014</v>
+        <v>2.51573368763327</v>
       </c>
     </row>
     <row r="301" ht="16.5" spans="1:16">
@@ -23921,27 +23946,27 @@
       </c>
       <c r="K301" s="1">
         <f ca="1" t="shared" ref="K301:O301" si="575">RAND()</f>
-        <v>0.914256095240711</v>
+        <v>0.826095472895163</v>
       </c>
       <c r="L301" s="1">
         <f ca="1" t="shared" ref="L301:P301" si="576">J301+$R$1*K301/MAX(1,($A301*($A301-1)))++$R$1/$A301</f>
-        <v>2.17386524865955</v>
+        <v>2.1738161067296</v>
       </c>
       <c r="M301" s="1">
         <f ca="1" t="shared" si="575"/>
-        <v>0.855477422391248</v>
+        <v>0.726772149029242</v>
       </c>
       <c r="N301" s="1">
         <f ca="1" t="shared" si="576"/>
-        <v>2.34100877007672</v>
+        <v>2.34088788607688</v>
       </c>
       <c r="O301" s="1">
         <f ca="1" t="shared" si="575"/>
-        <v>0.973093306636978</v>
+        <v>0.0166810850985397</v>
       </c>
       <c r="P301" s="1">
         <f ca="1" t="shared" si="576"/>
-        <v>2.50821785218744</v>
+        <v>2.50756385100726</v>
       </c>
     </row>
     <row r="302" spans="1:16">

--- a/table/resources/sample/PointsAwardRanking.xlsx
+++ b/table/resources/sample/PointsAwardRanking.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="PointsAwardRanking" sheetId="1" r:id="rId1"/>
@@ -176,7 +176,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="91">
   <si>
     <t>序列ID</t>
   </si>
@@ -244,133 +244,178 @@
     <t>2</t>
   </si>
   <si>
-    <t>1990000_55000000</t>
+    <t>1990000_3640000</t>
   </si>
   <si>
     <t>jfdj_box_1.png</t>
   </si>
   <si>
-    <t>1990000_50000000</t>
+    <t>1990000_3309000</t>
   </si>
   <si>
     <t>jfdj_box_2.png</t>
   </si>
   <si>
-    <t>1990000_45000000</t>
+    <t>1990000_2978000</t>
   </si>
   <si>
     <t>jfdj_box_3.png</t>
   </si>
   <si>
-    <t>1990000_40000000</t>
+    <t>1990000_2647000</t>
   </si>
   <si>
-    <t>1990000_35000000</t>
+    <t>1990000_2316000</t>
   </si>
   <si>
-    <t>1990000_30000000</t>
+    <t>1990000_1985000</t>
   </si>
   <si>
-    <t>1990000_25000000</t>
+    <t>1990000_1654000</t>
   </si>
   <si>
-    <t>1990000_20000000</t>
+    <t>1990000_1324000</t>
   </si>
   <si>
-    <t>1990000_15000000</t>
+    <t>1990000_993000</t>
   </si>
   <si>
-    <t>1990000_10000000</t>
+    <t>1990000_662000</t>
   </si>
   <si>
     <t>11_15</t>
   </si>
   <si>
-    <t>1990000_5000000</t>
+    <t>1990000_331000</t>
   </si>
   <si>
     <t>16_20</t>
   </si>
   <si>
-    <t>1990000_3000000</t>
+    <t>1990000_199000</t>
   </si>
   <si>
     <t>21_25</t>
   </si>
   <si>
-    <t>1990000_2000000</t>
+    <t>1990000_132000</t>
   </si>
   <si>
     <t>26_30</t>
   </si>
   <si>
-    <t>1990000_1000000</t>
+    <t>1990000_66000</t>
   </si>
   <si>
     <t>31_40</t>
   </si>
   <si>
-    <t>1990000_500000</t>
+    <t>1990000_33000</t>
   </si>
   <si>
     <t>41_50</t>
   </si>
   <si>
-    <t>1990000_300000</t>
+    <t>1990000_20000</t>
   </si>
   <si>
     <t>51_100</t>
   </si>
   <si>
-    <t>1990000_200000</t>
+    <t>1990000_13000</t>
   </si>
   <si>
     <t>101_150</t>
   </si>
   <si>
-    <t>1990000_100000</t>
+    <t>1990000_7000</t>
   </si>
   <si>
     <t>151_200</t>
   </si>
   <si>
-    <t>1990000_50000</t>
+    <t>1990000_3000</t>
   </si>
   <si>
     <t>201_250</t>
   </si>
   <si>
-    <t>1990000_30000</t>
+    <t>1990000_2000</t>
   </si>
   <si>
     <t>251_300</t>
   </si>
   <si>
-    <t>1990000_20000</t>
+    <t>1990000_1000</t>
   </si>
   <si>
-    <t>1990000_200000000</t>
+    <t>1990000_8170000</t>
   </si>
   <si>
-    <t>1990000_150000000</t>
+    <t>1990000_6130000</t>
   </si>
   <si>
-    <t>1990000_100000000</t>
+    <t>1990000_4090000</t>
   </si>
   <si>
-    <t>1990000_80000000</t>
+    <t>1990000_3270000</t>
   </si>
   <si>
-    <t>1990000_60000000</t>
+    <t>1990000_2450000</t>
   </si>
   <si>
-    <t>1990000_8000000</t>
+    <t>1990000_2040000</t>
   </si>
   <si>
-    <t>1990000_500000000</t>
+    <t>1990000_1230000</t>
   </si>
   <si>
-    <t>1990000_300000000</t>
+    <t>1990000_820000</t>
+  </si>
+  <si>
+    <t>1990000_410000</t>
+  </si>
+  <si>
+    <t>1990000_330000</t>
+  </si>
+  <si>
+    <t>1990000_200000</t>
+  </si>
+  <si>
+    <t>1990000_120000</t>
+  </si>
+  <si>
+    <t>1990000_80000</t>
+  </si>
+  <si>
+    <t>1990000_40000</t>
+  </si>
+  <si>
+    <t>1990000_10000</t>
+  </si>
+  <si>
+    <t>1990000_11000000</t>
+  </si>
+  <si>
+    <t>1990000_6600000</t>
+  </si>
+  <si>
+    <t>1990000_4400000</t>
+  </si>
+  <si>
+    <t>1990000_2200000</t>
+  </si>
+  <si>
+    <t>1990000_1100000</t>
+  </si>
+  <si>
+    <t>1990000_700000</t>
+  </si>
+  <si>
+    <t>1990000_400000</t>
+  </si>
+  <si>
+    <t>1990000_100000</t>
   </si>
   <si>
     <t>2036/08/01 00:00:00</t>
@@ -2228,7 +2273,7 @@
         <v>21</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
@@ -2250,7 +2295,7 @@
         <v>21</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
@@ -2272,7 +2317,7 @@
         <v>21</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
@@ -2294,7 +2339,7 @@
         <v>21</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
@@ -2316,7 +2361,7 @@
         <v>21</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
@@ -2339,7 +2384,7 @@
         <v>21</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
@@ -2362,7 +2407,7 @@
         <v>21</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
@@ -2385,7 +2430,7 @@
         <v>21</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
@@ -2406,7 +2451,7 @@
         <v>21</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="F39" s="2"/>
       <c r="G39" s="2"/>
@@ -2427,7 +2472,7 @@
         <v>21</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
@@ -2448,7 +2493,7 @@
         <v>21</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
@@ -2469,7 +2514,7 @@
         <v>21</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="F42" s="2"/>
       <c r="G42" s="2" t="s">
@@ -2492,7 +2537,7 @@
         <v>21</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="F43" s="2"/>
       <c r="G43" s="2" t="s">
@@ -2515,7 +2560,7 @@
         <v>21</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="F44" s="2"/>
       <c r="G44" s="2" t="s">
@@ -2538,7 +2583,7 @@
         <v>21</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
@@ -2559,7 +2604,7 @@
         <v>21</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>24</v>
+        <v>76</v>
       </c>
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
@@ -2580,7 +2625,7 @@
         <v>21</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
@@ -2601,7 +2646,7 @@
         <v>21</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>32</v>
+        <v>78</v>
       </c>
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
@@ -2622,7 +2667,7 @@
         <v>21</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
@@ -2644,7 +2689,7 @@
         <v>21</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
@@ -2666,7 +2711,7 @@
         <v>21</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>36</v>
+        <v>79</v>
       </c>
       <c r="F51" s="2"/>
       <c r="G51" s="2"/>
@@ -2695,7 +2740,7 @@
         <v>23</v>
       </c>
       <c r="H52" s="25" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="I52" s="20"/>
       <c r="J52" s="20"/>
@@ -2721,7 +2766,7 @@
         <v>25</v>
       </c>
       <c r="H53" s="25" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="I53" s="20"/>
       <c r="J53" s="20"/>
@@ -2747,7 +2792,7 @@
         <v>27</v>
       </c>
       <c r="H54" s="25" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="I54" s="20"/>
       <c r="J54" s="20"/>
@@ -2771,7 +2816,7 @@
       <c r="F55" s="23"/>
       <c r="G55" s="23"/>
       <c r="H55" s="25" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="I55" s="20"/>
       <c r="J55" s="20"/>
@@ -2795,7 +2840,7 @@
       <c r="F56" s="23"/>
       <c r="G56" s="23"/>
       <c r="H56" s="25" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="I56" s="20"/>
       <c r="J56" s="21"/>
@@ -2820,7 +2865,7 @@
       <c r="F57" s="23"/>
       <c r="G57" s="23"/>
       <c r="H57" s="25" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="I57" s="20"/>
       <c r="J57" s="21"/>
@@ -2845,7 +2890,7 @@
       <c r="F58" s="23"/>
       <c r="G58" s="23"/>
       <c r="H58" s="25" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="I58" s="20"/>
       <c r="J58" s="21"/>
@@ -2870,7 +2915,7 @@
       <c r="F59" s="23"/>
       <c r="G59" s="23"/>
       <c r="H59" s="25" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="I59" s="20"/>
       <c r="J59" s="21"/>
@@ -2895,7 +2940,7 @@
       <c r="F60" s="23"/>
       <c r="G60" s="23"/>
       <c r="H60" s="25" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="I60" s="20"/>
       <c r="L60" s="3"/>
@@ -2919,7 +2964,7 @@
       <c r="F61" s="23"/>
       <c r="G61" s="23"/>
       <c r="H61" s="25" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="I61" s="20"/>
       <c r="L61" s="3"/>
@@ -2943,7 +2988,7 @@
       <c r="F62" s="23"/>
       <c r="G62" s="23"/>
       <c r="H62" s="25" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="I62" s="20"/>
       <c r="J62" s="10"/>
@@ -2968,7 +3013,7 @@
       <c r="F63" s="23"/>
       <c r="G63" s="23"/>
       <c r="H63" s="25" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="I63" s="20"/>
       <c r="J63" s="21"/>
@@ -2993,7 +3038,7 @@
       <c r="F64" s="23"/>
       <c r="G64" s="23"/>
       <c r="H64" s="25" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="I64" s="20"/>
       <c r="J64" s="21"/>
@@ -3018,7 +3063,7 @@
       <c r="F65" s="23"/>
       <c r="G65" s="23"/>
       <c r="H65" s="25" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="I65" s="20"/>
       <c r="J65" s="21"/>
@@ -3043,7 +3088,7 @@
       <c r="F66" s="23"/>
       <c r="G66" s="23"/>
       <c r="H66" s="25" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="I66" s="20"/>
       <c r="J66" s="21"/>
@@ -3068,7 +3113,7 @@
       <c r="F67" s="23"/>
       <c r="G67" s="23"/>
       <c r="H67" s="25" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="I67" s="20"/>
       <c r="J67" s="21"/>
@@ -3093,7 +3138,7 @@
       <c r="F68" s="23"/>
       <c r="G68" s="23"/>
       <c r="H68" s="25" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="I68" s="20"/>
       <c r="J68" s="21"/>
@@ -3118,7 +3163,7 @@
       <c r="F69" s="23"/>
       <c r="G69" s="23"/>
       <c r="H69" s="25" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="I69" s="20"/>
       <c r="J69" s="21"/>
@@ -3143,7 +3188,7 @@
       <c r="F70" s="23"/>
       <c r="G70" s="23"/>
       <c r="H70" s="25" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="I70" s="20"/>
       <c r="J70" s="21"/>
@@ -3168,7 +3213,7 @@
       <c r="F71" s="23"/>
       <c r="G71" s="23"/>
       <c r="H71" s="25" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="I71" s="20"/>
       <c r="J71" s="21"/>
@@ -3193,7 +3238,7 @@
       <c r="F72" s="23"/>
       <c r="G72" s="23"/>
       <c r="H72" s="25" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="I72" s="20"/>
       <c r="J72" s="21"/>
@@ -3220,7 +3265,7 @@
         <v>23</v>
       </c>
       <c r="H73" s="25" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="I73" s="20"/>
       <c r="J73" s="21"/>
@@ -3247,7 +3292,7 @@
         <v>25</v>
       </c>
       <c r="H74" s="25" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="I74" s="20"/>
       <c r="J74" s="21"/>
@@ -3274,7 +3319,7 @@
         <v>27</v>
       </c>
       <c r="H75" s="25" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="I75" s="20"/>
       <c r="J75" s="21"/>
@@ -3299,7 +3344,7 @@
       <c r="F76" s="23"/>
       <c r="G76" s="23"/>
       <c r="H76" s="25" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="I76" s="20"/>
       <c r="J76" s="21"/>
@@ -3324,7 +3369,7 @@
       <c r="F77" s="23"/>
       <c r="G77" s="23"/>
       <c r="H77" s="25" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="I77" s="20"/>
       <c r="J77" s="21"/>
@@ -3344,12 +3389,12 @@
         <v>21</v>
       </c>
       <c r="E78" s="23" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="F78" s="23"/>
       <c r="G78" s="23"/>
       <c r="H78" s="25" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="I78" s="20"/>
       <c r="J78" s="21"/>
@@ -3369,12 +3414,12 @@
         <v>21</v>
       </c>
       <c r="E79" s="23" t="s">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="F79" s="23"/>
       <c r="G79" s="23"/>
       <c r="H79" s="25" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="I79" s="20"/>
       <c r="J79" s="21"/>
@@ -3394,12 +3439,12 @@
         <v>21</v>
       </c>
       <c r="E80" s="23" t="s">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="F80" s="23"/>
       <c r="G80" s="23"/>
       <c r="H80" s="25" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="I80" s="20"/>
       <c r="J80" s="21"/>
@@ -3418,12 +3463,12 @@
         <v>21</v>
       </c>
       <c r="E81" s="23" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="F81" s="23"/>
       <c r="G81" s="23"/>
       <c r="H81" s="25" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="I81" s="20"/>
       <c r="J81" s="21"/>
@@ -3442,12 +3487,12 @@
         <v>21</v>
       </c>
       <c r="E82" s="23" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F82" s="23"/>
       <c r="G82" s="23"/>
       <c r="H82" s="25" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="I82" s="20"/>
       <c r="J82" s="20"/>
@@ -3466,12 +3511,12 @@
         <v>21</v>
       </c>
       <c r="E83" s="23" t="s">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="F83" s="23"/>
       <c r="G83" s="23"/>
       <c r="H83" s="25" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="I83" s="20"/>
     </row>
@@ -3489,12 +3534,12 @@
         <v>21</v>
       </c>
       <c r="E84" s="23" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="F84" s="23"/>
       <c r="G84" s="23"/>
       <c r="H84" s="25" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="I84" s="20"/>
     </row>
@@ -3512,12 +3557,12 @@
         <v>21</v>
       </c>
       <c r="E85" s="23" t="s">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="F85" s="23"/>
       <c r="G85" s="23"/>
       <c r="H85" s="25" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="I85" s="20"/>
     </row>
@@ -3535,12 +3580,12 @@
         <v>21</v>
       </c>
       <c r="E86" s="23" t="s">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="F86" s="23"/>
       <c r="G86" s="23"/>
       <c r="H86" s="25" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="I86" s="20"/>
     </row>
@@ -3558,12 +3603,12 @@
         <v>21</v>
       </c>
       <c r="E87" s="23" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F87" s="23"/>
       <c r="G87" s="23"/>
       <c r="H87" s="25" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="I87" s="20"/>
     </row>
@@ -3581,12 +3626,12 @@
         <v>21</v>
       </c>
       <c r="E88" s="23" t="s">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="F88" s="23"/>
       <c r="G88" s="23"/>
       <c r="H88" s="25" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="I88" s="20"/>
     </row>
@@ -3604,14 +3649,14 @@
         <v>21</v>
       </c>
       <c r="E89" s="23" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="F89" s="23"/>
       <c r="G89" s="23" t="s">
         <v>23</v>
       </c>
       <c r="H89" s="25" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="I89" s="20"/>
     </row>
@@ -3629,14 +3674,14 @@
         <v>21</v>
       </c>
       <c r="E90" s="27" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="F90" s="23"/>
       <c r="G90" s="23" t="s">
         <v>25</v>
       </c>
       <c r="H90" s="25" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
     </row>
     <row r="91" spans="1:10">
@@ -3653,14 +3698,14 @@
         <v>21</v>
       </c>
       <c r="E91" s="27" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="F91" s="23"/>
       <c r="G91" s="23" t="s">
         <v>27</v>
       </c>
       <c r="H91" s="25" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
     </row>
     <row r="92" spans="1:10">
@@ -3677,12 +3722,12 @@
         <v>21</v>
       </c>
       <c r="E92" s="27" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="F92" s="23"/>
       <c r="G92" s="23"/>
       <c r="H92" s="25" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
     </row>
     <row r="93" spans="1:10">
@@ -3699,12 +3744,12 @@
         <v>21</v>
       </c>
       <c r="E93" s="27" t="s">
-        <v>24</v>
+        <v>76</v>
       </c>
       <c r="F93" s="23"/>
       <c r="G93" s="23"/>
       <c r="H93" s="25" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
     </row>
     <row r="94" spans="1:10">
@@ -3721,12 +3766,12 @@
         <v>21</v>
       </c>
       <c r="E94" s="27" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="F94" s="23"/>
       <c r="G94" s="23"/>
       <c r="H94" s="25" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
     </row>
     <row r="95" spans="1:10">
@@ -3743,12 +3788,12 @@
         <v>21</v>
       </c>
       <c r="E95" s="27" t="s">
-        <v>32</v>
+        <v>78</v>
       </c>
       <c r="F95" s="23"/>
       <c r="G95" s="23"/>
       <c r="H95" s="25" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
     </row>
     <row r="96" spans="1:10">
@@ -3765,12 +3810,12 @@
         <v>21</v>
       </c>
       <c r="E96" s="27" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="F96" s="23"/>
       <c r="G96" s="23"/>
       <c r="H96" s="25" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
     </row>
     <row r="97" spans="1:8">
@@ -3787,12 +3832,12 @@
         <v>21</v>
       </c>
       <c r="E97" s="27" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F97" s="23"/>
       <c r="G97" s="23"/>
       <c r="H97" s="25" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
     </row>
     <row r="98" spans="1:8">
@@ -3809,12 +3854,12 @@
         <v>21</v>
       </c>
       <c r="E98" s="27" t="s">
-        <v>36</v>
+        <v>79</v>
       </c>
       <c r="F98" s="23"/>
       <c r="G98" s="23"/>
       <c r="H98" s="25" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -3852,34 +3897,34 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="R1" s="1">
         <v>46</v>
@@ -3922,30 +3967,30 @@
       </c>
       <c r="K2" s="1">
         <f ca="1" t="shared" ref="K2:O2" si="3">RAND()</f>
-        <v>0.749492411782194</v>
+        <v>0.652441457006768</v>
       </c>
       <c r="L2" s="1">
         <f ca="1" t="shared" ref="L2:L65" si="4">J2+($R$1*$R$7*K2/MAX(1,($A2*($A2-1)))+$R$1*$R$7/$A2)/100</f>
-        <v>134.542995282594</v>
+        <v>133.203692106693</v>
       </c>
       <c r="M2" s="1">
         <f ca="1" t="shared" si="3"/>
-        <v>0.297760407449499</v>
+        <v>0.124668265120187</v>
       </c>
       <c r="N2" s="1">
         <f ca="1" t="shared" ref="N2:N65" si="5">L2+($R$1*$R$7*M2/MAX(1,($A2*($A2-1)))+$R$1*$R$7/$A2)/100</f>
-        <v>152.452088905397</v>
+        <v>148.724114165352</v>
       </c>
       <c r="O2" s="1">
         <f ca="1" t="shared" si="3"/>
-        <v>0.669844616935961</v>
+        <v>0.253894602342103</v>
       </c>
       <c r="P2" s="1">
         <f ca="1" t="shared" ref="P2:P65" si="6">N2+($R$1*$R$7*O2/MAX(1,($A2*($A2-1)))+$R$1*$R$7/$A2)/100</f>
-        <v>175.495944619114</v>
+        <v>166.027859677673</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="R2" s="1">
         <v>1</v>
@@ -3988,30 +4033,30 @@
       </c>
       <c r="K3" s="1">
         <f ca="1" t="shared" ref="K3:O3" si="8">RAND()</f>
-        <v>0.989715039010322</v>
+        <v>0.00499239174961907</v>
       </c>
       <c r="L3" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>41.3290337691712</v>
+        <v>34.5344475030724</v>
       </c>
       <c r="M3" s="1">
         <f ca="1" t="shared" si="8"/>
-        <v>0.482545499701252</v>
+        <v>0.729927815781742</v>
       </c>
       <c r="N3" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>51.5585977171099</v>
+        <v>46.4709494319664</v>
       </c>
       <c r="O3" s="1">
         <f ca="1" t="shared" si="8"/>
-        <v>0.561556872451645</v>
+        <v>0.398732994087178</v>
       </c>
       <c r="P3" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>62.3333401370262</v>
+        <v>56.1222070911679</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="R3" s="1">
         <v>10</v>
@@ -4054,30 +4099,30 @@
       </c>
       <c r="K4" s="1">
         <f ca="1" t="shared" ref="K4:O4" si="9">RAND()</f>
-        <v>0.739466536391512</v>
+        <v>0.899964909135736</v>
       </c>
       <c r="L4" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>33.9007730337005</v>
+        <v>34.2699192910122</v>
       </c>
       <c r="M4" s="1">
         <f ca="1" t="shared" si="9"/>
-        <v>0.0207537374132565</v>
+        <v>0.577551684244162</v>
       </c>
       <c r="N4" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>38.548506629751</v>
+        <v>40.1982881647738</v>
       </c>
       <c r="O4" s="1">
         <f ca="1" t="shared" si="9"/>
-        <v>0.652581848784105</v>
+        <v>0.472518087372499</v>
       </c>
       <c r="P4" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>44.6494448819544</v>
+        <v>45.8850797657305</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="R4" s="1">
         <f>24*60/R3</f>
@@ -4121,30 +4166,30 @@
       </c>
       <c r="K5" s="1">
         <f ca="1" t="shared" ref="K5:O5" si="10">RAND()</f>
-        <v>0.494368309219273</v>
+        <v>0.769717617419658</v>
       </c>
       <c r="L5" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>17.8185235556022</v>
+        <v>18.1351752600326</v>
       </c>
       <c r="M5" s="1">
         <f ca="1" t="shared" si="10"/>
-        <v>0.886081034048043</v>
+        <v>0.580842144493361</v>
       </c>
       <c r="N5" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>22.2875167447574</v>
+        <v>22.2531437262</v>
       </c>
       <c r="O5" s="1">
         <f ca="1" t="shared" si="10"/>
-        <v>0.821836747048154</v>
+        <v>0.639755469051341</v>
       </c>
       <c r="P5" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>26.6826290038628</v>
+        <v>26.438862515609</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="R5" s="1">
         <v>6000</v>
@@ -4187,30 +4232,30 @@
       </c>
       <c r="K6" s="1">
         <f ca="1" t="shared" ref="K6:O6" si="11">RAND()</f>
-        <v>0.572905574664843</v>
+        <v>0.242700885693266</v>
       </c>
       <c r="L6" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>16.9553048465187</v>
+        <v>16.7274636111284</v>
       </c>
       <c r="M6" s="1">
         <f ca="1" t="shared" si="11"/>
-        <v>0.585003122390469</v>
+        <v>0.145277927882112</v>
       </c>
       <c r="N6" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>20.1189570009682</v>
+        <v>19.587705381367</v>
       </c>
       <c r="O6" s="1">
         <f ca="1" t="shared" si="11"/>
-        <v>0.573605262731329</v>
+        <v>0.467320872084037</v>
       </c>
       <c r="P6" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>23.2747446322528</v>
+        <v>22.670156783105</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="R6" s="1">
         <f>R5/R4</f>
@@ -4274,7 +4319,7 @@
         <v>16.1</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="R7" s="1">
         <v>30</v>
@@ -5628,27 +5673,27 @@
       </c>
       <c r="K31" s="1">
         <f ca="1" t="shared" ref="K31:O31" si="12">RAND()</f>
-        <v>0.164169566217422</v>
+        <v>0.492685169318414</v>
       </c>
       <c r="L31" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>2.36605234484345</v>
+        <v>2.37126328199609</v>
       </c>
       <c r="M31" s="1">
         <f ca="1" t="shared" si="12"/>
-        <v>0.418782000070081</v>
+        <v>0.255077941083049</v>
       </c>
       <c r="N31" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>2.83269509381008</v>
+        <v>2.83530934588913</v>
       </c>
       <c r="O31" s="1">
         <f ca="1" t="shared" si="12"/>
-        <v>0.969923399701768</v>
+        <v>0.907128072639998</v>
       </c>
       <c r="P31" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>3.30808008566742</v>
+        <v>3.3096982739379</v>
       </c>
     </row>
     <row r="32" ht="16.5" spans="1:16">
@@ -5916,27 +5961,27 @@
       </c>
       <c r="K36" s="1">
         <f ca="1" t="shared" ref="K36:O36" si="13">RAND()</f>
-        <v>0.853246884687391</v>
+        <v>0.325753534468455</v>
       </c>
       <c r="L36" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>2.02770992185604</v>
+        <v>2.02159277208039</v>
       </c>
       <c r="M36" s="1">
         <f ca="1" t="shared" si="13"/>
-        <v>0.705359785852965</v>
+        <v>0.626916474226437</v>
       </c>
       <c r="N36" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>2.43017543870039</v>
+        <v>2.42314861018487</v>
       </c>
       <c r="O36" s="1">
         <f ca="1" t="shared" si="13"/>
-        <v>0.167076720320322</v>
+        <v>0.183597417808244</v>
       </c>
       <c r="P36" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>2.8263986813394</v>
+        <v>2.81956343738298</v>
       </c>
     </row>
     <row r="37" ht="16.5" spans="1:16">
@@ -5976,27 +6021,27 @@
       </c>
       <c r="K37" s="1">
         <f ca="1" t="shared" ref="K37:O37" si="14">RAND()</f>
-        <v>0.0310273873484188</v>
+        <v>0.0811719877054662</v>
       </c>
       <c r="L37" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.96081601424239</v>
+        <v>1.96136521700821</v>
       </c>
       <c r="M37" s="1">
         <f ca="1" t="shared" si="14"/>
-        <v>0.0636130631204708</v>
+        <v>0.331769779028674</v>
       </c>
       <c r="N37" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>2.34484606207657</v>
+        <v>2.34833221934995</v>
       </c>
       <c r="O37" s="1">
         <f ca="1" t="shared" si="14"/>
-        <v>0.971752076785295</v>
+        <v>0.128911001576272</v>
       </c>
       <c r="P37" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>2.73882239434612</v>
+        <v>2.7330774350815</v>
       </c>
     </row>
     <row r="38" ht="16.5" spans="1:16">
@@ -6036,27 +6081,27 @@
       </c>
       <c r="K38" s="1">
         <f ca="1" t="shared" ref="K38:O38" si="15">RAND()</f>
-        <v>0.506525706835785</v>
+        <v>0.773526457568217</v>
       </c>
       <c r="L38" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.91155409516091</v>
+        <v>1.91432031915498</v>
       </c>
       <c r="M38" s="1">
         <f ca="1" t="shared" si="15"/>
-        <v>0.828486571139765</v>
+        <v>0.954815579212579</v>
       </c>
       <c r="N38" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>2.29311048756461</v>
+        <v>2.29718552560628</v>
       </c>
       <c r="O38" s="1">
         <f ca="1" t="shared" si="15"/>
-        <v>0.375290673522345</v>
+        <v>0.963428049598807</v>
       </c>
       <c r="P38" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>2.66997160715515</v>
+        <v>2.68013996035438</v>
       </c>
     </row>
     <row r="39" ht="16.5" spans="1:16">
@@ -6096,27 +6141,27 @@
       </c>
       <c r="K39" s="1">
         <f ca="1" t="shared" ref="K39:O39" si="16">RAND()</f>
-        <v>0.51236342987866</v>
+        <v>0.874510871365545</v>
       </c>
       <c r="L39" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.86007867377832</v>
+        <v>1.86363317924953</v>
       </c>
       <c r="M39" s="1">
         <f ca="1" t="shared" si="16"/>
-        <v>0.480727056121112</v>
+        <v>0.671767266963824</v>
       </c>
       <c r="N39" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>2.22795494218122</v>
+        <v>2.2333845222681</v>
       </c>
       <c r="O39" s="1">
         <f ca="1" t="shared" si="16"/>
-        <v>0.0856365118939457</v>
+        <v>0.473989328307985</v>
       </c>
       <c r="P39" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>2.59195336598217</v>
+        <v>2.60119465934537</v>
       </c>
     </row>
     <row r="40" ht="16.5" spans="1:16">
@@ -6156,27 +6201,27 @@
       </c>
       <c r="K40" s="1">
         <f ca="1" t="shared" ref="K40:O40" si="17">RAND()</f>
-        <v>0.858341195905825</v>
+        <v>0.553792768725295</v>
       </c>
       <c r="L40" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.8144703836056</v>
+        <v>1.81163450756303</v>
       </c>
       <c r="M40" s="1">
         <f ca="1" t="shared" si="17"/>
-        <v>0.445788547711513</v>
+        <v>0.844457633860992</v>
       </c>
       <c r="N40" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>2.17246760490008</v>
+        <v>2.17334403208886</v>
       </c>
       <c r="O40" s="1">
         <f ca="1" t="shared" si="17"/>
-        <v>0.33446020602863</v>
+        <v>0.598209393547398</v>
       </c>
       <c r="P40" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>2.52942816552302</v>
+        <v>2.5327605568061</v>
       </c>
     </row>
     <row r="41" ht="16.5" spans="1:16">
@@ -6216,27 +6261,27 @@
       </c>
       <c r="K41" s="1">
         <f ca="1" t="shared" ref="K41:O41" si="18">RAND()</f>
-        <v>0.231620057044313</v>
+        <v>0.0291770943708951</v>
       </c>
       <c r="L41" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.76243356204309</v>
+        <v>1.76064272045021</v>
       </c>
       <c r="M41" s="1">
         <f ca="1" t="shared" si="18"/>
-        <v>0.543688671243225</v>
+        <v>0.361440114869941</v>
       </c>
       <c r="N41" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>2.11224311567332</v>
+        <v>2.10884007531252</v>
       </c>
       <c r="O41" s="1">
         <f ca="1" t="shared" si="18"/>
-        <v>0.0849730280406107</v>
+        <v>0.622497295730196</v>
       </c>
       <c r="P41" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>2.45799480015214</v>
+        <v>2.45934678215936</v>
       </c>
     </row>
     <row r="42" ht="16.5" spans="1:16">
@@ -6276,27 +6321,27 @@
       </c>
       <c r="K42" s="1">
         <f ca="1" t="shared" ref="K42:O42" si="19">RAND()</f>
-        <v>0.850677797901137</v>
+        <v>0.937547357397353</v>
       </c>
       <c r="L42" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.72374350829941</v>
+        <v>1.72447448386103</v>
       </c>
       <c r="M42" s="1">
         <f ca="1" t="shared" si="19"/>
-        <v>0.455910185996836</v>
+        <v>0.995062205997697</v>
       </c>
       <c r="N42" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>2.06416519157182</v>
+        <v>2.06943293413101</v>
       </c>
       <c r="O42" s="1">
         <f ca="1" t="shared" si="19"/>
-        <v>0.359782196854906</v>
+        <v>0.0763910997565338</v>
       </c>
       <c r="P42" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>2.40377799298438</v>
+        <v>2.40666110314115</v>
       </c>
     </row>
     <row r="43" ht="16.5" spans="1:16">
@@ -6336,27 +6381,27 @@
       </c>
       <c r="K43" s="1">
         <f ca="1" t="shared" ref="K43:O43" si="20">RAND()</f>
-        <v>0.666843207010579</v>
+        <v>0.983653956724317</v>
       </c>
       <c r="L43" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.68025693162412</v>
+        <v>1.68279583310266</v>
       </c>
       <c r="M43" s="1">
         <f ca="1" t="shared" si="20"/>
-        <v>0.951480408787449</v>
+        <v>0.608726192883077</v>
       </c>
       <c r="N43" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>2.01645346451684</v>
+        <v>2.01624555520591</v>
       </c>
       <c r="O43" s="1">
         <f ca="1" t="shared" si="20"/>
-        <v>0.644671813816454</v>
+        <v>0.694931941963451</v>
       </c>
       <c r="P43" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>2.35019125257182</v>
+        <v>2.35038612477565</v>
       </c>
     </row>
     <row r="44" ht="16.5" spans="1:16">
@@ -6396,27 +6441,27 @@
       </c>
       <c r="K44" s="1">
         <f ca="1" t="shared" ref="K44:O44" si="21">RAND()</f>
-        <v>0.208361686857122</v>
+        <v>0.629515484205592</v>
       </c>
       <c r="L44" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.63680807933478</v>
+        <v>1.64002619805207</v>
       </c>
       <c r="M44" s="1">
         <f ca="1" t="shared" si="21"/>
-        <v>0.485040102999144</v>
+        <v>0.28056350586291</v>
       </c>
       <c r="N44" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>1.96144459839425</v>
+        <v>1.96310027135268</v>
       </c>
       <c r="O44" s="1">
         <f ca="1" t="shared" si="21"/>
-        <v>0.851398121965856</v>
+        <v>0.101723072110228</v>
       </c>
       <c r="P44" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>2.28888053088767</v>
+        <v>2.28480778984389</v>
       </c>
     </row>
     <row r="45" ht="16.5" spans="1:16">
@@ -6456,27 +6501,27 @@
       </c>
       <c r="K45" s="1">
         <f ca="1" t="shared" ref="K45:O45" si="22">RAND()</f>
-        <v>0.874184799069777</v>
+        <v>0.339521229103051</v>
       </c>
       <c r="L45" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.60373348320675</v>
+        <v>1.59983371721016</v>
       </c>
       <c r="M45" s="1">
         <f ca="1" t="shared" si="22"/>
-        <v>0.961664105076351</v>
+        <v>0.2944996438343</v>
       </c>
       <c r="N45" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>1.92438409877232</v>
+        <v>1.91561812264616</v>
       </c>
       <c r="O45" s="1">
         <f ca="1" t="shared" si="22"/>
-        <v>0.0572704667577091</v>
+        <v>0.887656494826967</v>
       </c>
       <c r="P45" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>2.2384381856863</v>
+        <v>2.23572893640336</v>
       </c>
     </row>
     <row r="46" ht="16.5" spans="1:16">
@@ -6516,27 +6561,27 @@
       </c>
       <c r="K46" s="1">
         <f ca="1" t="shared" ref="K46:O46" si="23">RAND()</f>
-        <v>0.500581547309588</v>
+        <v>0.00279814772137232</v>
       </c>
       <c r="L46" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.56470102290549</v>
+        <v>1.56123162345381</v>
       </c>
       <c r="M46" s="1">
         <f ca="1" t="shared" si="23"/>
-        <v>0.558582064005993</v>
+        <v>0.152348796362948</v>
       </c>
       <c r="N46" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>1.87526083729098</v>
+        <v>1.86896011506483</v>
       </c>
       <c r="O46" s="1">
         <f ca="1" t="shared" si="23"/>
-        <v>0.970459023823768</v>
+        <v>0.747709195623462</v>
       </c>
       <c r="P46" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>2.18869130927521</v>
+        <v>2.18083808824644</v>
       </c>
     </row>
     <row r="47" ht="16.5" spans="1:16">
@@ -6576,27 +6621,27 @@
       </c>
       <c r="K47" s="1">
         <f ca="1" t="shared" ref="K47:O47" si="24">RAND()</f>
-        <v>0.858821214278588</v>
+        <v>0.144728576019429</v>
       </c>
       <c r="L47" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.53239214142853</v>
+        <v>1.52763152384013</v>
       </c>
       <c r="M47" s="1">
         <f ca="1" t="shared" si="24"/>
-        <v>0.462434651554449</v>
+        <v>0.330653590050872</v>
       </c>
       <c r="N47" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>1.83547503910556</v>
+        <v>1.82983588110714</v>
       </c>
       <c r="O47" s="1">
         <f ca="1" t="shared" si="24"/>
-        <v>0.337128511021451</v>
+        <v>0.918622998092507</v>
       </c>
       <c r="P47" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>2.13772256251237</v>
+        <v>2.13596003442776</v>
       </c>
     </row>
     <row r="48" ht="16.5" spans="1:16">
@@ -6636,27 +6681,27 @@
       </c>
       <c r="K48" s="1">
         <f ca="1" t="shared" ref="K48:O48" si="25">RAND()</f>
-        <v>0.891957307592499</v>
+        <v>0.440631091421108</v>
       </c>
       <c r="L48" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.49931036579314</v>
+        <v>1.49642956015801</v>
       </c>
       <c r="M48" s="1">
         <f ca="1" t="shared" si="25"/>
-        <v>0.647923982416104</v>
+        <v>0.945590254761364</v>
       </c>
       <c r="N48" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>1.79706307206388</v>
+        <v>1.7960822639118</v>
       </c>
       <c r="O48" s="1">
         <f ca="1" t="shared" si="25"/>
-        <v>0.947000442677701</v>
+        <v>0.641291709042339</v>
       </c>
       <c r="P48" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>2.09672477701715</v>
+        <v>2.09379263652271</v>
       </c>
     </row>
     <row r="49" ht="16.5" spans="1:16">
@@ -6696,27 +6741,27 @@
       </c>
       <c r="K49" s="1">
         <f ca="1" t="shared" ref="K49:O49" si="26">RAND()</f>
-        <v>0.419033442304805</v>
+        <v>0.639739450029199</v>
       </c>
       <c r="L49" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.46453132158856</v>
+        <v>1.46588138493369</v>
       </c>
       <c r="M49" s="1">
         <f ca="1" t="shared" si="26"/>
-        <v>0.773234911690017</v>
+        <v>0.213379767623794</v>
       </c>
       <c r="N49" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>1.75676121599518</v>
+        <v>1.75468663351224</v>
       </c>
       <c r="O49" s="1">
         <f ca="1" t="shared" si="26"/>
-        <v>0.716438676879699</v>
+        <v>0.034027994774269</v>
       </c>
       <c r="P49" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>2.04864368662503</v>
+        <v>2.04239478348027</v>
       </c>
     </row>
     <row r="50" ht="16.5" spans="1:16">
@@ -6756,27 +6801,27 @@
       </c>
       <c r="K50" s="1">
         <f ca="1" t="shared" ref="K50:O50" si="27">RAND()</f>
-        <v>0.415799725840638</v>
+        <v>0.406342357933846</v>
       </c>
       <c r="L50" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.43407229430978</v>
+        <v>1.43401680465114</v>
       </c>
       <c r="M50" s="1">
         <f ca="1" t="shared" si="27"/>
-        <v>0.74804092106023</v>
+        <v>0.344558427656227</v>
       </c>
       <c r="N50" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>1.72009396297927</v>
+        <v>1.7176711015481</v>
       </c>
       <c r="O50" s="1">
         <f ca="1" t="shared" si="27"/>
-        <v>0.551700166587368</v>
+        <v>0.659079356298016</v>
       </c>
       <c r="P50" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>2.00496363232404</v>
+        <v>2.00317080185291</v>
       </c>
     </row>
     <row r="51" ht="16.5" spans="1:16">
@@ -6816,27 +6861,27 @@
       </c>
       <c r="K51" s="1">
         <f ca="1" t="shared" ref="K51:O51" si="28">RAND()</f>
-        <v>0.0452116048757587</v>
+        <v>0.559286267431367</v>
       </c>
       <c r="L51" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.40278527352951</v>
+        <v>1.40568087775125</v>
       </c>
       <c r="M51" s="1">
         <f ca="1" t="shared" si="28"/>
-        <v>0.795784769550266</v>
+        <v>0.150133416157306</v>
       </c>
       <c r="N51" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>1.68326765304779</v>
+        <v>1.68252652719736</v>
       </c>
       <c r="O51" s="1">
         <f ca="1" t="shared" si="28"/>
-        <v>0.864390831174343</v>
+        <v>0.162938462407195</v>
       </c>
       <c r="P51" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>1.9641364667091</v>
+        <v>1.95944430302643</v>
       </c>
     </row>
     <row r="52" ht="16.5" spans="1:16">
@@ -6876,27 +6921,27 @@
       </c>
       <c r="K52" s="1">
         <f ca="1" t="shared" ref="K52:O52" si="29">RAND()</f>
-        <v>0.770538189993797</v>
+        <v>0.595153632369968</v>
       </c>
       <c r="L52" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.37875820667526</v>
+        <v>1.37780906671636</v>
       </c>
       <c r="M52" s="1">
         <f ca="1" t="shared" si="29"/>
-        <v>0.536676453083507</v>
+        <v>0.628285972547546</v>
       </c>
       <c r="N52" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>1.65225080865665</v>
+        <v>1.65179743786191</v>
       </c>
       <c r="O52" s="1">
         <f ca="1" t="shared" si="29"/>
-        <v>0.465064927151584</v>
+        <v>0.539516021970741</v>
       </c>
       <c r="P52" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>1.92535586590947</v>
+        <v>1.92530540692198</v>
       </c>
     </row>
     <row r="53" ht="16.5" spans="1:16">
@@ -6936,27 +6981,27 @@
       </c>
       <c r="K53" s="1">
         <f ca="1" t="shared" ref="K53:O53" si="30">RAND()</f>
-        <v>0.317942469049118</v>
+        <v>0.866004640213882</v>
       </c>
       <c r="L53" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.34939200832311</v>
+        <v>1.35224391554862</v>
       </c>
       <c r="M53" s="1">
         <f ca="1" t="shared" si="30"/>
-        <v>0.493125523316523</v>
+        <v>0.898710846527853</v>
       </c>
       <c r="N53" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>1.61734266149873</v>
+        <v>1.62230508058712</v>
       </c>
       <c r="O53" s="1">
         <f ca="1" t="shared" si="30"/>
-        <v>0.731773047425618</v>
+        <v>0.334504331609332</v>
       </c>
       <c r="P53" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>1.88653514568217</v>
+        <v>1.88943032937151</v>
       </c>
     </row>
     <row r="54" ht="16.5" spans="1:16">
@@ -7110,27 +7155,27 @@
       </c>
       <c r="K56" s="1">
         <f ca="1" t="shared" ref="K56:O56" si="31">RAND()</f>
-        <v>0.14845167502942</v>
+        <v>0.753272907164252</v>
       </c>
       <c r="L56" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.27382108859104</v>
+        <v>1.27663136906359</v>
       </c>
       <c r="M56" s="1">
         <f ca="1" t="shared" si="31"/>
-        <v>0.839610294868257</v>
+        <v>0.57683346919195</v>
       </c>
       <c r="N56" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>1.52863139905205</v>
+        <v>1.53022069629418</v>
       </c>
       <c r="O56" s="1">
         <f ca="1" t="shared" si="31"/>
-        <v>0.450534015247501</v>
+        <v>0.779788947415073</v>
       </c>
       <c r="P56" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>1.78163388033502</v>
+        <v>1.78475304897914</v>
       </c>
     </row>
     <row r="57" ht="16.5" spans="1:16">
@@ -7170,27 +7215,27 @@
       </c>
       <c r="K57" s="1">
         <f ca="1" t="shared" ref="K57:O57" si="32">RAND()</f>
-        <v>0.955391274333896</v>
+        <v>0.587860713617248</v>
       </c>
       <c r="L57" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.2543455842811</v>
+        <v>1.25269885644413</v>
       </c>
       <c r="M57" s="1">
         <f ca="1" t="shared" si="32"/>
-        <v>0.668380533410959</v>
+        <v>0.27416680541071</v>
       </c>
       <c r="N57" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>1.50376884771002</v>
+        <v>1.50035583758525</v>
       </c>
       <c r="O57" s="1">
         <f ca="1" t="shared" si="32"/>
-        <v>0.0127156771164136</v>
+        <v>0.333641111785494</v>
       </c>
       <c r="P57" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>1.75025439197762</v>
+        <v>1.74827929451468</v>
       </c>
     </row>
     <row r="58" ht="16.5" spans="1:16">
@@ -7230,27 +7275,27 @@
       </c>
       <c r="K58" s="1">
         <f ca="1" t="shared" ref="K58:O58" si="33">RAND()</f>
-        <v>0.216100868680226</v>
+        <v>0.301286115166365</v>
       </c>
       <c r="L58" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.22875381954505</v>
+        <v>1.22912210162572</v>
       </c>
       <c r="M58" s="1">
         <f ca="1" t="shared" si="33"/>
-        <v>0.623014111097113</v>
+        <v>0.777820961887139</v>
       </c>
       <c r="N58" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>1.4735525647622</v>
+        <v>1.47459012458125</v>
       </c>
       <c r="O58" s="1">
         <f ca="1" t="shared" si="33"/>
-        <v>0.74591768483321</v>
+        <v>0.803461986540639</v>
       </c>
       <c r="P58" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>1.71888266001617</v>
+        <v>1.72016900159073</v>
       </c>
     </row>
     <row r="59" ht="16.5" spans="1:16">
@@ -7290,27 +7335,27 @@
       </c>
       <c r="K59" s="1">
         <f ca="1" t="shared" ref="K59:O59" si="34">RAND()</f>
-        <v>0.768758610514749</v>
+        <v>0.236664281734846</v>
       </c>
       <c r="L59" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.20956106135061</v>
+        <v>1.20733997794554</v>
       </c>
       <c r="M59" s="1">
         <f ca="1" t="shared" si="34"/>
-        <v>0.911459155506041</v>
+        <v>0.578323492919942</v>
       </c>
       <c r="N59" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>1.45129673477649</v>
+        <v>1.44768506693595</v>
       </c>
       <c r="O59" s="1">
         <f ca="1" t="shared" si="34"/>
-        <v>0.31310106461413</v>
+        <v>0.0919238450542239</v>
       </c>
       <c r="P59" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>1.69053472470138</v>
+        <v>1.68599981256866</v>
       </c>
     </row>
     <row r="60" ht="16.5" spans="1:16">
@@ -7350,27 +7395,27 @@
       </c>
       <c r="K60" s="1">
         <f ca="1" t="shared" ref="K60:O60" si="35">RAND()</f>
-        <v>0.00571083545278306</v>
+        <v>0.586069593443086</v>
       </c>
       <c r="L60" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.1856454732698</v>
+        <v>1.18798590309454</v>
       </c>
       <c r="M60" s="1">
         <f ca="1" t="shared" si="35"/>
-        <v>0.399669875763031</v>
+        <v>0.492104562715373</v>
       </c>
       <c r="N60" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>1.42115553881203</v>
+        <v>1.42386873271624</v>
       </c>
       <c r="O60" s="1">
         <f ca="1" t="shared" si="35"/>
-        <v>0.569780387285557</v>
+        <v>0.212699366070055</v>
       </c>
       <c r="P60" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>1.657351614015</v>
+        <v>1.65862479678748</v>
       </c>
     </row>
     <row r="61" ht="16.5" spans="1:16">
@@ -7410,27 +7455,27 @@
       </c>
       <c r="K61" s="1">
         <f ca="1" t="shared" ref="K61:O61" si="36">RAND()</f>
-        <v>0.110295591311315</v>
+        <v>0.431586827499292</v>
       </c>
       <c r="L61" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.16602318620342</v>
+        <v>1.16727567746313</v>
       </c>
       <c r="M61" s="1">
         <f ca="1" t="shared" si="36"/>
-        <v>0.302687118340386</v>
+        <v>0.973634833996631</v>
       </c>
       <c r="N61" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>1.39720315293593</v>
+        <v>1.40107120308719</v>
       </c>
       <c r="O61" s="1">
         <f ca="1" t="shared" si="36"/>
-        <v>0.560454976601167</v>
+        <v>0.730290477864451</v>
       </c>
       <c r="P61" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>1.62938797742099</v>
+        <v>1.63391809817039</v>
       </c>
     </row>
     <row r="62" ht="16.5" spans="1:16">
@@ -7470,27 +7515,27 @@
       </c>
       <c r="K62" s="1">
         <f ca="1" t="shared" ref="K62:O62" si="37">RAND()</f>
-        <v>0.84834771661436</v>
+        <v>0.0628397811660899</v>
       </c>
       <c r="L62" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.14942819630855</v>
+        <v>1.14646644507653</v>
       </c>
       <c r="M62" s="1">
         <f ca="1" t="shared" si="37"/>
-        <v>0.650780655532786</v>
+        <v>0.172027159678613</v>
       </c>
       <c r="N62" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>1.37811146763269</v>
+        <v>1.37334458026876</v>
       </c>
       <c r="O62" s="1">
         <f ca="1" t="shared" si="37"/>
-        <v>0.197511267007876</v>
+        <v>0.516837242757877</v>
       </c>
       <c r="P62" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>1.60508569044272</v>
+        <v>1.60152281905293</v>
       </c>
     </row>
     <row r="63" ht="16.5" spans="1:16">
@@ -7530,27 +7575,27 @@
       </c>
       <c r="K63" s="1">
         <f ca="1" t="shared" ref="K63:O63" si="38">RAND()</f>
-        <v>0.0762616902753452</v>
+        <v>0.596025551897708</v>
       </c>
       <c r="L63" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.12777694641084</v>
+        <v>1.12967349355267</v>
       </c>
       <c r="M63" s="1">
         <f ca="1" t="shared" si="38"/>
-        <v>0.848912319377219</v>
+        <v>0.143852694783666</v>
       </c>
       <c r="N63" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>1.35345515635463</v>
+        <v>1.3527790374945</v>
       </c>
       <c r="O63" s="1">
         <f ca="1" t="shared" si="38"/>
-        <v>0.937523420506543</v>
+        <v>0.346920239149978</v>
       </c>
       <c r="P63" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>1.57945669606986</v>
+        <v>1.57662554709267</v>
       </c>
     </row>
     <row r="64" ht="16.5" spans="1:16">
@@ -7590,27 +7635,27 @@
       </c>
       <c r="K64" s="1">
         <f ca="1" t="shared" ref="K64:O64" si="39">RAND()</f>
-        <v>0.640305502221258</v>
+        <v>0.591967118389784</v>
       </c>
       <c r="L64" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.11163241575286</v>
+        <v>1.11146163498049</v>
       </c>
       <c r="M64" s="1">
         <f ca="1" t="shared" si="39"/>
-        <v>0.183487075756153</v>
+        <v>0.816976994240393</v>
       </c>
       <c r="N64" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>1.33132829943064</v>
+        <v>1.33339565508303</v>
       </c>
       <c r="O64" s="1">
         <f ca="1" t="shared" si="39"/>
-        <v>0.00366099762584926</v>
+        <v>0.254328907451207</v>
       </c>
       <c r="P64" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>1.55038885287848</v>
+        <v>1.55334182480213</v>
       </c>
     </row>
     <row r="65" ht="16.5" spans="1:16">
@@ -7650,27 +7695,27 @@
       </c>
       <c r="K65" s="1">
         <f ca="1" t="shared" ref="K65:O65" si="40">RAND()</f>
-        <v>0.284017835611467</v>
+        <v>0.817072648596606</v>
       </c>
       <c r="L65" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.0927875610445</v>
+        <v>1.09461200460085</v>
       </c>
       <c r="M65" s="1">
         <f ca="1" t="shared" si="40"/>
-        <v>0.35311795316335</v>
+        <v>0.279014512767259</v>
       </c>
       <c r="N65" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>1.30962114927706</v>
+        <v>1.31119196498681</v>
       </c>
       <c r="O65" s="1">
         <f ca="1" t="shared" si="40"/>
-        <v>0.725191825814004</v>
+        <v>0.0883012720346654</v>
       </c>
       <c r="P65" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>1.52772820463327</v>
+        <v>1.52711918660241</v>
       </c>
     </row>
     <row r="66" ht="16.5" spans="1:16">
@@ -7710,27 +7755,27 @@
       </c>
       <c r="K66" s="1">
         <f ca="1" t="shared" ref="K66:O66" si="44">RAND()</f>
-        <v>0.753711933858184</v>
+        <v>0.360046580249211</v>
       </c>
       <c r="L66" s="1">
         <f ca="1" t="shared" ref="L66:L129" si="45">J66+($R$1*$R$7*K66/MAX(1,($A66*($A66-1)))+$R$1*$R$7/$A66)/100</f>
-        <v>1.07730798670366</v>
+        <v>1.07600207759794</v>
       </c>
       <c r="M66" s="1">
         <f ca="1" t="shared" si="44"/>
-        <v>0.680171989197801</v>
+        <v>0.928797359008673</v>
       </c>
       <c r="N66" s="1">
         <f ca="1" t="shared" ref="N66:N129" si="46">L66+($R$1*$R$7*M66/MAX(1,($A66*($A66-1)))+$R$1*$R$7/$A66)/100</f>
-        <v>1.29187201878321</v>
+        <v>1.29139087652927</v>
       </c>
       <c r="O66" s="1">
         <f ca="1" t="shared" si="44"/>
-        <v>0.36585841363554</v>
+        <v>0.362521079174264</v>
       </c>
       <c r="P66" s="1">
         <f ca="1" t="shared" ref="P66:P129" si="47">N66+($R$1*$R$7*O66/MAX(1,($A66*($A66-1)))+$R$1*$R$7/$A66)/100</f>
-        <v>1.50539337602076</v>
+        <v>1.50490116280153</v>
       </c>
     </row>
     <row r="67" ht="16.5" spans="1:16">
@@ -7770,27 +7815,27 @@
       </c>
       <c r="K67" s="1">
         <f ca="1" t="shared" ref="K67:O67" si="49">RAND()</f>
-        <v>0.243790816414253</v>
+        <v>0.661348153544794</v>
       </c>
       <c r="L67" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>1.05910590052833</v>
+        <v>1.06044909196245</v>
       </c>
       <c r="M67" s="1">
         <f ca="1" t="shared" si="49"/>
-        <v>0.418219050844119</v>
+        <v>0.762310270561727</v>
       </c>
       <c r="N67" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>1.26954212964293</v>
+        <v>1.27199218793769</v>
       </c>
       <c r="O67" s="1">
         <f ca="1" t="shared" si="49"/>
-        <v>0.952579154429266</v>
+        <v>0.757531367699347</v>
       </c>
       <c r="P67" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.48169727937046</v>
+        <v>1.4835199112184</v>
       </c>
     </row>
     <row r="68" ht="16.5" spans="1:16">
@@ -7830,27 +7875,27 @@
       </c>
       <c r="K68" s="1">
         <f ca="1" t="shared" ref="K68:O68" si="50">RAND()</f>
-        <v>0.365298891169326</v>
+        <v>0.818918236642868</v>
       </c>
       <c r="L68" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>1.04347379572549</v>
+        <v>1.04488943276021</v>
       </c>
       <c r="M68" s="1">
         <f ca="1" t="shared" si="50"/>
-        <v>0.891368618782482</v>
+        <v>0.358878965478386</v>
       </c>
       <c r="N68" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>1.25222569236484</v>
+        <v>1.25197955707582</v>
       </c>
       <c r="O68" s="1">
         <f ca="1" t="shared" si="50"/>
-        <v>0.229338245189812</v>
+        <v>0.38364125095912</v>
       </c>
       <c r="P68" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.45891155120329</v>
+        <v>1.45914695853743</v>
       </c>
     </row>
     <row r="69" ht="16.5" spans="1:16">
@@ -7890,27 +7935,27 @@
       </c>
       <c r="K69" s="1">
         <f ca="1" t="shared" ref="K69:O69" si="51">RAND()</f>
-        <v>0.925727922837103</v>
+        <v>0.245145330108641</v>
       </c>
       <c r="L69" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>1.02962577816838</v>
+        <v>1.02756431201833</v>
       </c>
       <c r="M69" s="1">
         <f ca="1" t="shared" si="51"/>
-        <v>0.35739603776167</v>
+        <v>0.919415005550831</v>
       </c>
       <c r="N69" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>1.23364949751015</v>
+        <v>1.23329037151714</v>
       </c>
       <c r="O69" s="1">
         <f ca="1" t="shared" si="51"/>
-        <v>0.351551006631903</v>
+        <v>0.204941300190674</v>
       </c>
       <c r="P69" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.43765551241172</v>
+        <v>1.43685230960815</v>
       </c>
     </row>
     <row r="70" ht="16.5" spans="1:16">
@@ -7950,27 +7995,27 @@
       </c>
       <c r="K70" s="1">
         <f ca="1" t="shared" ref="K70:O70" si="52">RAND()</f>
-        <v>0.233602794936942</v>
+        <v>0.647343622898482</v>
       </c>
       <c r="L70" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>1.01245177292629</v>
+        <v>1.01366865771441</v>
       </c>
       <c r="M70" s="1">
         <f ca="1" t="shared" si="52"/>
-        <v>0.90680273313522</v>
+        <v>0.10104978787263</v>
       </c>
       <c r="N70" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>1.21511883978845</v>
+        <v>1.21396586297286</v>
       </c>
       <c r="O70" s="1">
         <f ca="1" t="shared" si="52"/>
-        <v>0.0295502562551027</v>
+        <v>0.357395954615545</v>
       </c>
       <c r="P70" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.41520575230684</v>
+        <v>1.41501702754525</v>
       </c>
     </row>
     <row r="71" ht="16.5" spans="1:16">
@@ -8010,27 +8055,27 @@
       </c>
       <c r="K71" s="1">
         <f ca="1" t="shared" ref="K71:O71" si="53">RAND()</f>
-        <v>0.716425661103296</v>
+        <v>0.0456641687027004</v>
       </c>
       <c r="L71" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.999189787603152</v>
+        <v>0.997273326196293</v>
       </c>
       <c r="M71" s="1">
         <f ca="1" t="shared" si="53"/>
-        <v>0.888469294254548</v>
+        <v>0.514604013541268</v>
       </c>
       <c r="N71" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>1.19887112844388</v>
+        <v>1.1958864805207</v>
       </c>
       <c r="O71" s="1">
         <f ca="1" t="shared" si="53"/>
-        <v>0.393619039563932</v>
+        <v>0.898199959278147</v>
       </c>
       <c r="P71" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.39713861141406</v>
+        <v>1.39559562326149</v>
       </c>
     </row>
     <row r="72" ht="16.5" spans="1:16">
@@ -8070,27 +8115,27 @@
       </c>
       <c r="K72" s="1">
         <f ca="1" t="shared" ref="K72:O72" si="54">RAND()</f>
-        <v>0.38530115476987</v>
+        <v>0.0154145491429656</v>
       </c>
       <c r="L72" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.984007476043426</v>
+        <v>0.982980426715931</v>
       </c>
       <c r="M72" s="1">
         <f ca="1" t="shared" si="54"/>
-        <v>0.568784280818166</v>
+        <v>0.178933080650038</v>
       </c>
       <c r="N72" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>1.17995299376481</v>
+        <v>1.17784346021955</v>
       </c>
       <c r="O72" s="1">
         <f ca="1" t="shared" si="54"/>
-        <v>0.697861646065709</v>
+        <v>0.716847816867781</v>
       </c>
       <c r="P72" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.37625691543799</v>
+        <v>1.37420010003298</v>
       </c>
     </row>
     <row r="73" ht="16.5" spans="1:16">
@@ -8130,27 +8175,27 @@
       </c>
       <c r="K73" s="1">
         <f ca="1" t="shared" ref="K73:O73" si="55">RAND()</f>
-        <v>0.187248087895666</v>
+        <v>0.37186661428282</v>
       </c>
       <c r="L73" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.969636937326479</v>
+        <v>0.970135320672359</v>
       </c>
       <c r="M73" s="1">
         <f ca="1" t="shared" si="55"/>
-        <v>0.404538502822944</v>
+        <v>0.817217523774017</v>
       </c>
       <c r="N73" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>1.16239566802659</v>
+        <v>1.16400809098302</v>
       </c>
       <c r="O73" s="1">
         <f ca="1" t="shared" si="55"/>
-        <v>0.146307905399968</v>
+        <v>0.642159565661802</v>
       </c>
       <c r="P73" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.35445729734868</v>
+        <v>1.35740828699361</v>
       </c>
     </row>
     <row r="74" ht="16.5" spans="1:16">
@@ -8190,27 +8235,27 @@
       </c>
       <c r="K74" s="1">
         <f ca="1" t="shared" ref="K74:O74" si="56">RAND()</f>
-        <v>0.995521163591055</v>
+        <v>0.458871667073488</v>
       </c>
       <c r="L74" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.958321573831347</v>
+        <v>0.956912562596198</v>
       </c>
       <c r="M74" s="1">
         <f ca="1" t="shared" si="56"/>
-        <v>0.121578296116915</v>
+        <v>0.741807702610128</v>
       </c>
       <c r="N74" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>1.14768188214307</v>
+        <v>1.14790132711218</v>
       </c>
       <c r="O74" s="1">
         <f ca="1" t="shared" si="56"/>
-        <v>0.286539270895521</v>
+        <v>0.920383494127865</v>
       </c>
       <c r="P74" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.33747530716939</v>
+        <v>1.33935895500772</v>
       </c>
     </row>
     <row r="75" ht="16.5" spans="1:16">
@@ -8364,27 +8409,27 @@
       </c>
       <c r="K77" s="1">
         <f ca="1" t="shared" ref="K77:O77" si="57">RAND()</f>
-        <v>0.942885247565756</v>
+        <v>0.304822120396118</v>
       </c>
       <c r="L77" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.919861722178317</v>
+        <v>0.91831693776517</v>
       </c>
       <c r="M77" s="1">
         <f ca="1" t="shared" si="57"/>
-        <v>0.48716892335841</v>
+        <v>0.224595068739552</v>
       </c>
       <c r="N77" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>1.10262013115066</v>
+        <v>1.1004396416158</v>
       </c>
       <c r="O77" s="1">
         <f ca="1" t="shared" si="57"/>
-        <v>0.517007247325172</v>
+        <v>0.673304807820807</v>
       </c>
       <c r="P77" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.28545078027576</v>
+        <v>1.28364869536105</v>
       </c>
     </row>
     <row r="78" ht="16.5" spans="1:16">
@@ -8424,27 +8469,27 @@
       </c>
       <c r="K78" s="1">
         <f ca="1" t="shared" ref="K78:O78" si="58">RAND()</f>
-        <v>0.665787627293688</v>
+        <v>0.639904827380355</v>
       </c>
       <c r="L78" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.907106607870241</v>
+        <v>0.907045571875914</v>
       </c>
       <c r="M78" s="1">
         <f ca="1" t="shared" si="58"/>
-        <v>0.626645093821389</v>
+        <v>0.820612236203548</v>
       </c>
       <c r="N78" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>1.08780512159115</v>
+        <v>1.08820149273367</v>
       </c>
       <c r="O78" s="1">
         <f ca="1" t="shared" si="58"/>
-        <v>0.307193625001169</v>
+        <v>0.358458922378442</v>
       </c>
       <c r="P78" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.26775031503356</v>
+        <v>1.26826757836744</v>
       </c>
     </row>
     <row r="79" ht="16.5" spans="1:16">
@@ -8484,27 +8529,27 @@
       </c>
       <c r="K79" s="1">
         <f ca="1" t="shared" ref="K79:O79" si="59">RAND()</f>
-        <v>0.0676899678872744</v>
+        <v>0.785687858364907</v>
       </c>
       <c r="L79" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.89396172520094</v>
+        <v>0.895611470603636</v>
       </c>
       <c r="M79" s="1">
         <f ca="1" t="shared" si="59"/>
-        <v>0.729442900253128</v>
+        <v>0.310512680616204</v>
       </c>
       <c r="N79" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>1.07256084475197</v>
+        <v>1.07324801322643</v>
       </c>
       <c r="O79" s="1">
         <f ca="1" t="shared" si="59"/>
-        <v>0.0610553378320355</v>
+        <v>0.177205735967582</v>
       </c>
       <c r="P79" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.24962420866507</v>
+        <v>1.25057825617621</v>
       </c>
     </row>
     <row r="80" ht="16.5" spans="1:16">
@@ -8544,27 +8589,27 @@
       </c>
       <c r="K80" s="1">
         <f ca="1" t="shared" ref="K80:O80" si="60">RAND()</f>
-        <v>0.246617451835095</v>
+        <v>0.586454031746368</v>
       </c>
       <c r="L80" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.882928159823974</v>
+        <v>0.883689234929909</v>
       </c>
       <c r="M80" s="1">
         <f ca="1" t="shared" si="60"/>
-        <v>0.751075587656822</v>
+        <v>0.992456273518966</v>
       </c>
       <c r="N80" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>1.05929376240587</v>
+        <v>1.06059541743146</v>
       </c>
       <c r="O80" s="1">
         <f ca="1" t="shared" si="60"/>
-        <v>0.163890668211619</v>
+        <v>0.261997607927235</v>
       </c>
       <c r="P80" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.23434434520713</v>
+        <v>1.23586571392438</v>
       </c>
     </row>
     <row r="81" ht="16.5" spans="1:16">
@@ -8604,27 +8649,27 @@
       </c>
       <c r="K81" s="1">
         <f ca="1" t="shared" ref="K81:O81" si="61">RAND()</f>
-        <v>0.557050220715724</v>
+        <v>0.0289345447697966</v>
       </c>
       <c r="L81" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.872450521051563</v>
+        <v>0.871297357075605</v>
       </c>
       <c r="M81" s="1">
         <f ca="1" t="shared" si="61"/>
-        <v>0.404498601162313</v>
+        <v>0.979176876440262</v>
       </c>
       <c r="N81" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>1.04583376166802</v>
+        <v>1.04593543316657</v>
       </c>
       <c r="O81" s="1">
         <f ca="1" t="shared" si="61"/>
-        <v>0.92598579405831</v>
+        <v>0.796291009853386</v>
       </c>
       <c r="P81" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.22035569267404</v>
+        <v>1.2201741698653</v>
       </c>
     </row>
     <row r="82" ht="16.5" spans="1:16">
@@ -8664,27 +8709,27 @@
       </c>
       <c r="K82" s="1">
         <f ca="1" t="shared" ref="K82:O82" si="62">RAND()</f>
-        <v>0.43282229281806</v>
+        <v>0.513739055651798</v>
       </c>
       <c r="L82" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.86129212154952</v>
+        <v>0.861464444285184</v>
       </c>
       <c r="M82" s="1">
         <f ca="1" t="shared" si="62"/>
-        <v>0.0684476270362586</v>
+        <v>0.242551862291542</v>
       </c>
       <c r="N82" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>1.0318082600145</v>
+        <v>1.03235136028821</v>
       </c>
       <c r="O82" s="1">
         <f ca="1" t="shared" si="62"/>
-        <v>0.63634037557006</v>
+        <v>0.924357655098216</v>
       </c>
       <c r="P82" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.20353379970322</v>
+        <v>1.20469027010926</v>
       </c>
     </row>
     <row r="83" ht="16.5" spans="1:16">
@@ -8724,27 +8769,27 @@
       </c>
       <c r="K83" s="1">
         <f ca="1" t="shared" ref="K83:O83" si="63">RAND()</f>
-        <v>0.110404282712243</v>
+        <v>0.715026111812996</v>
       </c>
       <c r="L83" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.850003550000215</v>
+        <v>0.851259765182628</v>
       </c>
       <c r="M83" s="1">
         <f ca="1" t="shared" si="63"/>
-        <v>0.5898179452447</v>
+        <v>0.356226457665214</v>
       </c>
       <c r="N83" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>1.01952169026585</v>
+        <v>1.02029257534761</v>
       </c>
       <c r="O83" s="1">
         <f ca="1" t="shared" si="63"/>
-        <v>0.557000774047557</v>
+        <v>0.545896977005114</v>
       </c>
       <c r="P83" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.18897164670696</v>
+        <v>1.18971946156903</v>
       </c>
     </row>
     <row r="84" ht="16.5" spans="1:16">
@@ -8784,27 +8829,27 @@
       </c>
       <c r="K84" s="1">
         <f ca="1" t="shared" ref="K84:O84" si="64">RAND()</f>
-        <v>0.496970400254789</v>
+        <v>0.279655625332477</v>
       </c>
       <c r="L84" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.840443460406041</v>
+        <v>0.840002828038435</v>
       </c>
       <c r="M84" s="1">
         <f ca="1" t="shared" si="64"/>
-        <v>0.226305355528829</v>
+        <v>0.0735944213613304</v>
       </c>
       <c r="N84" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>1.00716738251981</v>
+        <v>1.0064171099977</v>
       </c>
       <c r="O84" s="1">
         <f ca="1" t="shared" si="64"/>
-        <v>0.242367286922282</v>
+        <v>0.633941431714504</v>
       </c>
       <c r="P84" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.17392387217005</v>
+        <v>1.17396756426712</v>
       </c>
     </row>
     <row r="85" ht="16.5" spans="1:16">
@@ -8844,27 +8889,27 @@
       </c>
       <c r="K85" s="1">
         <f ca="1" t="shared" ref="K85:O85" si="65">RAND()</f>
-        <v>0.228663852157515</v>
+        <v>0.637399301207959</v>
       </c>
       <c r="L85" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.829798560120449</v>
+        <v>0.830607588978294</v>
       </c>
       <c r="M85" s="1">
         <f ca="1" t="shared" si="65"/>
-        <v>0.0874919039320829</v>
+        <v>0.0734367085112446</v>
       </c>
       <c r="N85" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.994257451152328</v>
+        <v>0.995038659915967</v>
       </c>
       <c r="O85" s="1">
         <f ca="1" t="shared" si="65"/>
-        <v>0.617699913134683</v>
+        <v>0.684115706313748</v>
       </c>
       <c r="P85" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.15976580726266</v>
+        <v>1.1606784758579</v>
       </c>
     </row>
     <row r="86" ht="16.5" spans="1:16">
@@ -8904,27 +8949,27 @@
       </c>
       <c r="K86" s="1">
         <f ca="1" t="shared" ref="K86:O86" si="66">RAND()</f>
-        <v>0.681381705975858</v>
+        <v>0.499851088359718</v>
       </c>
       <c r="L86" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.820812754557768</v>
+        <v>0.820461897061535</v>
       </c>
       <c r="M86" s="1">
         <f ca="1" t="shared" si="66"/>
-        <v>0.799575055504191</v>
+        <v>0.421597743782684</v>
       </c>
       <c r="N86" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.98471109290034</v>
+        <v>0.983629691020107</v>
       </c>
       <c r="O86" s="1">
         <f ca="1" t="shared" si="66"/>
-        <v>0.292082513391474</v>
+        <v>0.155375553505144</v>
       </c>
       <c r="P86" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.14762856330437</v>
+        <v>1.14628293788823</v>
       </c>
     </row>
     <row r="87" ht="16.5" spans="1:16">
@@ -9078,27 +9123,27 @@
       </c>
       <c r="K89" s="1">
         <f ca="1" t="shared" ref="K89:O89" si="67">RAND()</f>
-        <v>0.821200866017316</v>
+        <v>0.68662060344619</v>
       </c>
       <c r="L89" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.792781161435612</v>
+        <v>0.792538579457623</v>
       </c>
       <c r="M89" s="1">
         <f ca="1" t="shared" si="67"/>
-        <v>0.824969202167852</v>
+        <v>0.633449220631183</v>
       </c>
       <c r="N89" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.951086356705977</v>
+        <v>0.950498558460328</v>
       </c>
       <c r="O89" s="1">
         <f ca="1" t="shared" si="67"/>
-        <v>0.720241050954987</v>
+        <v>0.496295726727763</v>
       </c>
       <c r="P89" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.10920277866303</v>
+        <v>1.1082113172154</v>
       </c>
     </row>
     <row r="90" ht="16.5" spans="1:16">
@@ -9138,27 +9183,27 @@
       </c>
       <c r="K90" s="1">
         <f ca="1" t="shared" ref="K90:O90" si="68">RAND()</f>
-        <v>0.955865739498059</v>
+        <v>0.342939413943605</v>
       </c>
       <c r="L90" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.784013144433742</v>
+        <v>0.782933166995968</v>
       </c>
       <c r="M90" s="1">
         <f ca="1" t="shared" si="68"/>
-        <v>0.255021065394773</v>
+        <v>0.159111319268042</v>
       </c>
       <c r="N90" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.939518671847232</v>
+        <v>0.938269701240848</v>
       </c>
       <c r="O90" s="1">
         <f ca="1" t="shared" si="68"/>
-        <v>0.732927698219571</v>
+        <v>0.0890890061556266</v>
       </c>
       <c r="P90" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.09586627172407</v>
+        <v>1.09348285602697</v>
       </c>
     </row>
     <row r="91" ht="16.5" spans="1:16">
@@ -9198,27 +9243,27 @@
       </c>
       <c r="K91" s="1">
         <f ca="1" t="shared" ref="K91:O91" si="69">RAND()</f>
-        <v>0.584792257605967</v>
+        <v>0.602926172961376</v>
       </c>
       <c r="L91" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.774565559694752</v>
+        <v>0.774596801646301</v>
       </c>
       <c r="M91" s="1">
         <f ca="1" t="shared" si="69"/>
-        <v>0.755707147138504</v>
+        <v>0.903526362546955</v>
       </c>
       <c r="N91" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.929200860397688</v>
+        <v>0.929486772158554</v>
       </c>
       <c r="O91" s="1">
         <f ca="1" t="shared" si="69"/>
-        <v>0.70729989341874</v>
+        <v>0.292221613529058</v>
       </c>
       <c r="P91" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.08375276283579</v>
+        <v>1.08332355845902</v>
       </c>
     </row>
     <row r="92" ht="16.5" spans="1:16">
@@ -9258,27 +9303,27 @@
       </c>
       <c r="K92" s="1">
         <f ca="1" t="shared" ref="K92:O92" si="70">RAND()</f>
-        <v>0.677048035604413</v>
+        <v>0.762201582383329</v>
       </c>
       <c r="L92" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.766122498521531</v>
+        <v>0.766265980688265</v>
       </c>
       <c r="M92" s="1">
         <f ca="1" t="shared" si="70"/>
-        <v>0.678523280037445</v>
+        <v>0.622348248546139</v>
       </c>
       <c r="N92" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.918914149469579</v>
+        <v>0.918962977737097</v>
       </c>
       <c r="O92" s="1">
         <f ca="1" t="shared" si="70"/>
-        <v>0.463587484974013</v>
+        <v>0.992159233767402</v>
       </c>
       <c r="P92" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.0713436375395</v>
+        <v>1.07228309952293</v>
       </c>
     </row>
     <row r="93" ht="16.5" spans="1:16">
@@ -9318,27 +9363,27 @@
       </c>
       <c r="K93" s="1">
         <f ca="1" t="shared" ref="K93:O93" si="71">RAND()</f>
-        <v>0.997793648305385</v>
+        <v>0.210426266952822</v>
       </c>
       <c r="L93" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.758238121398306</v>
+        <v>0.756940263077395</v>
       </c>
       <c r="M93" s="1">
         <f ca="1" t="shared" si="71"/>
-        <v>0.360347980834415</v>
+        <v>0.981081366594728</v>
       </c>
       <c r="N93" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.908832101586495</v>
+        <v>0.908557430165189</v>
       </c>
       <c r="O93" s="1">
         <f ca="1" t="shared" si="71"/>
-        <v>0.73816669866877</v>
+        <v>0.131915272244682</v>
       </c>
       <c r="P93" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.060048859881</v>
+        <v>1.05877487292164</v>
       </c>
     </row>
     <row r="94" ht="16.5" spans="1:16">
@@ -9378,27 +9423,27 @@
       </c>
       <c r="K94" s="1">
         <f ca="1" t="shared" ref="K94:O94" si="72">RAND()</f>
-        <v>0.0906331509240668</v>
+        <v>0.765949036773986</v>
       </c>
       <c r="L94" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.748533279275684</v>
+        <v>0.74962249844641</v>
       </c>
       <c r="M94" s="1">
         <f ca="1" t="shared" si="72"/>
-        <v>0.303209774325662</v>
+        <v>0.534094617811786</v>
       </c>
       <c r="N94" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.897409424072983</v>
+        <v>0.898871038152558</v>
       </c>
       <c r="O94" s="1">
         <f ca="1" t="shared" si="72"/>
-        <v>0.316255275699098</v>
+        <v>0.104972111582092</v>
       </c>
       <c r="P94" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.04630661000153</v>
+        <v>1.04742744478414</v>
       </c>
     </row>
     <row r="95" ht="16.5" spans="1:16">
@@ -9438,27 +9483,27 @@
       </c>
       <c r="K95" s="1">
         <f ca="1" t="shared" ref="K95:O95" si="73">RAND()</f>
-        <v>0.667943291270698</v>
+        <v>0.635392145688059</v>
       </c>
       <c r="L95" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.741411303754236</v>
+        <v>0.741359918967112</v>
       </c>
       <c r="M95" s="1">
         <f ca="1" t="shared" si="73"/>
-        <v>0.847148236546069</v>
+        <v>0.563677505734053</v>
       </c>
       <c r="N95" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.889557110853794</v>
+        <v>0.889058243101078</v>
       </c>
       <c r="O95" s="1">
         <f ca="1" t="shared" si="73"/>
-        <v>0.623165954232671</v>
+        <v>0.419012207758694</v>
       </c>
       <c r="P95" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.03734934262781</v>
+        <v>1.03652820060131</v>
       </c>
     </row>
     <row r="96" ht="16.5" spans="1:16">
@@ -9498,27 +9543,27 @@
       </c>
       <c r="K96" s="1">
         <f ca="1" t="shared" ref="K96:O96" si="74">RAND()</f>
-        <v>0.622366792544445</v>
+        <v>0.28948885815763</v>
       </c>
       <c r="L96" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.733458976678289</v>
+        <v>0.732944562849113</v>
       </c>
       <c r="M96" s="1">
         <f ca="1" t="shared" si="74"/>
-        <v>0.570736346994501</v>
+        <v>0.16013091761248</v>
       </c>
       <c r="N96" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.879604123552703</v>
+        <v>0.878455179496711</v>
       </c>
       <c r="O96" s="1">
         <f ca="1" t="shared" si="74"/>
-        <v>0.79341006371262</v>
+        <v>0.0222756315154289</v>
       </c>
       <c r="P96" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.02609337986617</v>
+        <v>1.02375276109973</v>
       </c>
     </row>
     <row r="97" ht="16.5" spans="1:16">
@@ -9558,27 +9603,27 @@
       </c>
       <c r="K97" s="1">
         <f ca="1" t="shared" ref="K97:O97" si="75">RAND()</f>
-        <v>0.626397574383574</v>
+        <v>0.412355168955357</v>
       </c>
       <c r="L97" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.725750470013869</v>
+        <v>0.725426590058287</v>
       </c>
       <c r="M97" s="1">
         <f ca="1" t="shared" si="75"/>
-        <v>0.776553569187321</v>
+        <v>0.133941093370888</v>
       </c>
       <c r="N97" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.870675518177771</v>
+        <v>0.869379264081151</v>
       </c>
       <c r="O97" s="1">
         <f ca="1" t="shared" si="75"/>
-        <v>0.880119165301199</v>
+        <v>0.394159002778099</v>
       </c>
       <c r="P97" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.01575727744106</v>
+        <v>1.01372568888799</v>
       </c>
     </row>
     <row r="98" ht="16.5" spans="1:16">
@@ -9618,27 +9663,27 @@
       </c>
       <c r="K98" s="1">
         <f ca="1" t="shared" ref="K98:O98" si="76">RAND()</f>
-        <v>0.942079764036331</v>
+        <v>0.854039497349887</v>
       </c>
       <c r="L98" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.718664164598765</v>
+        <v>0.718533692554062</v>
       </c>
       <c r="M98" s="1">
         <f ca="1" t="shared" si="76"/>
-        <v>0.558004515773646</v>
+        <v>0.587113075612645</v>
       </c>
       <c r="N98" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.86175914551776</v>
+        <v>0.861671811158385</v>
       </c>
       <c r="O98" s="1">
         <f ca="1" t="shared" si="76"/>
-        <v>0.0310386053074714</v>
+        <v>0.613594402011032</v>
       </c>
       <c r="P98" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.004073184688</v>
+        <v>1.00484917399642</v>
       </c>
     </row>
     <row r="99" ht="16.5" spans="1:16">
@@ -9678,27 +9723,27 @@
       </c>
       <c r="K99" s="1">
         <f ca="1" t="shared" ref="K99:O99" si="77">RAND()</f>
-        <v>0.764690330732363</v>
+        <v>0.968288290561638</v>
       </c>
       <c r="L99" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.71099860367811</v>
+        <v>0.711294169830607</v>
       </c>
       <c r="M99" s="1">
         <f ca="1" t="shared" si="77"/>
-        <v>0.581776233431329</v>
+        <v>0.905522980136709</v>
       </c>
       <c r="N99" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.852659503322687</v>
+        <v>0.853425057388559</v>
       </c>
       <c r="O99" s="1">
         <f ca="1" t="shared" si="77"/>
-        <v>0.834519143847487</v>
+        <v>0.74650395296837</v>
       </c>
       <c r="P99" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.99468731356728</v>
+        <v>0.995325094686157</v>
       </c>
     </row>
     <row r="100" ht="16.5" spans="1:16">
@@ -9738,27 +9783,27 @@
       </c>
       <c r="K100" s="1">
         <f ca="1" t="shared" ref="K100:O100" si="78">RAND()</f>
-        <v>0.642988641825476</v>
+        <v>0.972624612863629</v>
       </c>
       <c r="L100" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.703573824289548</v>
+        <v>0.704042694254537</v>
       </c>
       <c r="M100" s="1">
         <f ca="1" t="shared" si="78"/>
-        <v>0.297901336264148</v>
+        <v>0.544131608646738</v>
       </c>
       <c r="N100" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.843391494712187</v>
+        <v>0.844210599449273</v>
       </c>
       <c r="O100" s="1">
         <f ca="1" t="shared" si="78"/>
-        <v>0.828806952234387</v>
+        <v>0.438314540517094</v>
       </c>
       <c r="P100" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.983964318453769</v>
+        <v>0.98422799180746</v>
       </c>
     </row>
     <row r="101" ht="16.5" spans="1:16">
@@ -9798,27 +9843,27 @@
       </c>
       <c r="K101" s="1">
         <f ca="1" t="shared" ref="K101:O101" si="79">RAND()</f>
-        <v>0.577435465657748</v>
+        <v>0.304770808724298</v>
       </c>
       <c r="L101" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.696380667618796</v>
+        <v>0.696000589612161</v>
       </c>
       <c r="M101" s="1">
         <f ca="1" t="shared" si="79"/>
-        <v>0.528240943170544</v>
+        <v>0.955955052391892</v>
       </c>
       <c r="N101" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.835117003478973</v>
+        <v>0.835333133018526</v>
       </c>
       <c r="O101" s="1">
         <f ca="1" t="shared" si="79"/>
-        <v>0.354809444076097</v>
+        <v>0.434508596987935</v>
       </c>
       <c r="P101" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.973611586340412</v>
+        <v>0.973938811668873</v>
       </c>
     </row>
     <row r="102" ht="16.5" spans="1:16">
@@ -9972,27 +10017,27 @@
       </c>
       <c r="K104" s="1">
         <f ca="1" t="shared" ref="K104:O104" si="80">RAND()</f>
-        <v>0.381375058861429</v>
+        <v>0.788009410675107</v>
       </c>
       <c r="L104" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.675658002647276</v>
+        <v>0.676192131150515</v>
       </c>
       <c r="M104" s="1">
         <f ca="1" t="shared" si="80"/>
-        <v>0.418287168415509</v>
+        <v>0.356576818680486</v>
       </c>
       <c r="N104" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.810188020058673</v>
+        <v>0.810641089850096</v>
       </c>
       <c r="O104" s="1">
         <f ca="1" t="shared" si="80"/>
-        <v>0.361785873936691</v>
+        <v>0.425165925258007</v>
       </c>
       <c r="P104" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.944643821035289</v>
+        <v>0.945180142750206</v>
       </c>
     </row>
     <row r="105" ht="16.5" spans="1:16">
@@ -10032,27 +10077,27 @@
       </c>
       <c r="K105" s="1">
         <f ca="1" t="shared" ref="K105:O105" si="81">RAND()</f>
-        <v>0.268514200184489</v>
+        <v>0.921100217931938</v>
       </c>
       <c r="L105" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.668960557875517</v>
+        <v>0.669801268017873</v>
       </c>
       <c r="M105" s="1">
         <f ca="1" t="shared" si="81"/>
-        <v>0.360472216256329</v>
+        <v>0.546811567594024</v>
       </c>
       <c r="N105" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.80211725285165</v>
+        <v>0.803198019290539</v>
       </c>
       <c r="O105" s="1">
         <f ca="1" t="shared" si="81"/>
-        <v>0.233651659211759</v>
+        <v>0.312831511325016</v>
       </c>
       <c r="P105" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.935110568095967</v>
+        <v>0.936293339945532</v>
       </c>
     </row>
     <row r="106" ht="16.5" spans="1:16">
@@ -10092,27 +10137,27 @@
       </c>
       <c r="K106" s="1">
         <f ca="1" t="shared" ref="K106:O106" si="82">RAND()</f>
-        <v>0.724167202432447</v>
+        <v>0.352832016956529</v>
       </c>
       <c r="L106" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.663112958552525</v>
+        <v>0.662643688812638</v>
       </c>
       <c r="M106" s="1">
         <f ca="1" t="shared" si="82"/>
-        <v>0.698395603564174</v>
+        <v>0.376603633656323</v>
       </c>
       <c r="N106" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.795424117831754</v>
+        <v>0.794548187910115</v>
       </c>
       <c r="O106" s="1">
         <f ca="1" t="shared" si="82"/>
-        <v>0.499069415318552</v>
+        <v>0.711506531147809</v>
       </c>
       <c r="P106" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.927483381378585</v>
+        <v>0.926875915943983</v>
       </c>
     </row>
     <row r="107" ht="16.5" spans="1:16">
@@ -10152,27 +10197,27 @@
       </c>
       <c r="K107" s="1">
         <f ca="1" t="shared" ref="K107:O107" si="83">RAND()</f>
-        <v>0.733040182360555</v>
+        <v>0.527572740070728</v>
       </c>
       <c r="L107" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.656811855751714</v>
+        <v>0.656557098276099</v>
       </c>
       <c r="M107" s="1">
         <f ca="1" t="shared" si="83"/>
-        <v>0.648577266284286</v>
+        <v>0.712043182919787</v>
       </c>
       <c r="N107" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.787804700879722</v>
+        <v>0.787628634298048</v>
       </c>
       <c r="O107" s="1">
         <f ca="1" t="shared" si="83"/>
-        <v>0.350743315486385</v>
+        <v>0.448750883165929</v>
       </c>
       <c r="P107" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.918428264020217</v>
+        <v>0.918373716255612</v>
       </c>
     </row>
     <row r="108" ht="16.5" spans="1:16">
@@ -10212,27 +10257,27 @@
       </c>
       <c r="K108" s="1">
         <f ca="1" t="shared" ref="K108:O108" si="84">RAND()</f>
-        <v>0.826823118018537</v>
+        <v>0.231896028583023</v>
       </c>
       <c r="L108" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.650732689034443</v>
+        <v>0.650008831352005</v>
       </c>
       <c r="M108" s="1">
         <f ca="1" t="shared" si="84"/>
-        <v>0.564375452367166</v>
+        <v>0.715495576514137</v>
       </c>
       <c r="N108" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.780391336648856</v>
+        <v>0.779851349334363</v>
       </c>
       <c r="O108" s="1">
         <f ca="1" t="shared" si="84"/>
-        <v>0.151815614925456</v>
+        <v>0.510559720657452</v>
       </c>
       <c r="P108" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.909548015848818</v>
+        <v>0.909444518453131</v>
       </c>
     </row>
     <row r="109" ht="16.5" spans="1:16">
@@ -10272,27 +10317,27 @@
       </c>
       <c r="K109" s="1">
         <f ca="1" t="shared" ref="K109:O109" si="85">RAND()</f>
-        <v>0.910092552219015</v>
+        <v>0.638627016160401</v>
       </c>
       <c r="L109" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.644752446973055</v>
+        <v>0.644428266945571</v>
       </c>
       <c r="M109" s="1">
         <f ca="1" t="shared" si="85"/>
-        <v>0.388490791501449</v>
+        <v>0.546134025658486</v>
       </c>
       <c r="N109" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.772994154564153</v>
+        <v>0.772858229696876</v>
       </c>
       <c r="O109" s="1">
         <f ca="1" t="shared" si="85"/>
-        <v>0.222148603863664</v>
+        <v>0.73315858912911</v>
       </c>
       <c r="P109" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.901037218836679</v>
+        <v>0.901511534346408</v>
       </c>
     </row>
     <row r="110" ht="16.5" spans="1:16">
@@ -10332,27 +10377,27 @@
       </c>
       <c r="K110" s="1">
         <f ca="1" t="shared" ref="K110:O110" si="86">RAND()</f>
-        <v>0.3008098480007</v>
+        <v>0.691967591085636</v>
       </c>
       <c r="L110" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.638069247018553</v>
+        <v>0.638527790754076</v>
       </c>
       <c r="M110" s="1">
         <f ca="1" t="shared" si="86"/>
-        <v>0.131032487905381</v>
+        <v>0.93397227237405</v>
       </c>
       <c r="N110" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.764828357478381</v>
+        <v>0.76622816599692</v>
       </c>
       <c r="O110" s="1">
         <f ca="1" t="shared" si="86"/>
-        <v>0.940830530014164</v>
+        <v>0.936623051680065</v>
       </c>
       <c r="P110" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.892536772472791</v>
+        <v>0.893931648677279</v>
       </c>
     </row>
     <row r="111" ht="16.5" spans="1:16">
@@ -10392,27 +10437,27 @@
       </c>
       <c r="K111" s="1">
         <f ca="1" t="shared" ref="K111:O111" si="87">RAND()</f>
-        <v>0.325191775512108</v>
+        <v>0.756488523585909</v>
       </c>
       <c r="L111" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.632250846247045</v>
+        <v>0.632747251178106</v>
       </c>
       <c r="M111" s="1">
         <f ca="1" t="shared" si="87"/>
-        <v>0.6054051059612</v>
+        <v>0.0391883143389395</v>
       </c>
       <c r="N111" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.758402188237225</v>
+        <v>0.758246900780931</v>
       </c>
       <c r="O111" s="1">
         <f ca="1" t="shared" si="87"/>
-        <v>0.392608744640776</v>
+        <v>0.26173704908514</v>
       </c>
       <c r="P111" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.884308610311958</v>
+        <v>0.884002694882464</v>
       </c>
     </row>
     <row r="112" ht="16.5" spans="1:16">
@@ -10452,27 +10497,27 @@
       </c>
       <c r="K112" s="1">
         <f ca="1" t="shared" ref="K112:O112" si="88">RAND()</f>
-        <v>0.620321530025159</v>
+        <v>0.220395957583143</v>
       </c>
       <c r="L112" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.626843606643272</v>
+        <v>0.626391602310782</v>
       </c>
       <c r="M112" s="1">
         <f ca="1" t="shared" si="88"/>
-        <v>0.469366106155461</v>
+        <v>0.5684409578855</v>
       </c>
       <c r="N112" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.751698418458583</v>
+        <v>0.751358390616992</v>
       </c>
       <c r="O112" s="1">
         <f ca="1" t="shared" si="88"/>
-        <v>0.0492616283882887</v>
+        <v>0.630554063694376</v>
       </c>
       <c r="P112" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.876078419316221</v>
+        <v>0.87639538046785</v>
       </c>
     </row>
     <row r="113" ht="16.5" spans="1:16">
@@ -10512,27 +10557,27 @@
       </c>
       <c r="K113" s="1">
         <f ca="1" t="shared" ref="K113:O113" si="89">RAND()</f>
-        <v>0.0391191455492432</v>
+        <v>0.686842147408414</v>
       </c>
       <c r="L113" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.620555006773534</v>
+        <v>0.621274004314208</v>
       </c>
       <c r="M113" s="1">
         <f ca="1" t="shared" si="89"/>
-        <v>0.257029662755007</v>
+        <v>0.954815264044312</v>
       </c>
       <c r="N113" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.744054605337403</v>
+        <v>0.745548171837037</v>
       </c>
       <c r="O113" s="1">
         <f ca="1" t="shared" si="89"/>
-        <v>0.000889522918118502</v>
+        <v>0.520688587299485</v>
       </c>
       <c r="P113" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.867269878456472</v>
+        <v>0.869340441987032</v>
       </c>
     </row>
     <row r="114" ht="16.5" spans="1:16">
@@ -10572,27 +10617,27 @@
       </c>
       <c r="K114" s="1">
         <f ca="1" t="shared" ref="K114:O114" si="90">RAND()</f>
-        <v>0.0175068472646798</v>
+        <v>0.373960703652771</v>
       </c>
       <c r="L114" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.615000125987062</v>
+        <v>0.615388800387991</v>
       </c>
       <c r="M114" s="1">
         <f ca="1" t="shared" si="90"/>
-        <v>0.0544248056246359</v>
+        <v>0.389564979273639</v>
       </c>
       <c r="N114" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.737183364160072</v>
+        <v>0.737937472694721</v>
       </c>
       <c r="O114" s="1">
         <f ca="1" t="shared" si="90"/>
-        <v>0.337786066948599</v>
+        <v>0.4540772839559</v>
       </c>
       <c r="P114" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.859675577159748</v>
+        <v>0.860556488696506</v>
       </c>
     </row>
     <row r="115" ht="16.5" spans="1:16">
@@ -10632,27 +10677,27 @@
       </c>
       <c r="K115" s="1">
         <f ca="1" t="shared" ref="K115:O115" si="91">RAND()</f>
-        <v>0.422883263647376</v>
+        <v>0.738608585591316</v>
       </c>
       <c r="L115" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.610001225666693</v>
+        <v>0.610339450277997</v>
       </c>
       <c r="M115" s="1">
         <f ca="1" t="shared" si="91"/>
-        <v>0.0989793562458432</v>
+        <v>0.790617431442529</v>
       </c>
       <c r="N115" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.731159890091176</v>
+        <v>0.732239040446753</v>
       </c>
       <c r="O115" s="1">
         <f ca="1" t="shared" si="91"/>
-        <v>0.611060646075599</v>
+        <v>0.339073636520947</v>
       </c>
       <c r="P115" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.852867127858281</v>
+        <v>0.85365490880446</v>
       </c>
     </row>
     <row r="116" ht="16.5" spans="1:16">
@@ -10692,27 +10737,27 @@
       </c>
       <c r="K116" s="1">
         <f ca="1" t="shared" ref="K116:O116" si="92">RAND()</f>
-        <v>0.740402840966264</v>
+        <v>0.660539505497743</v>
       </c>
       <c r="L116" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.604989897727332</v>
+        <v>0.604905831058418</v>
       </c>
       <c r="M116" s="1">
         <f ca="1" t="shared" si="92"/>
-        <v>0.27359371682711</v>
+        <v>0.102563798492554</v>
       </c>
       <c r="N116" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.725277891113466</v>
+        <v>0.725013792951568</v>
       </c>
       <c r="O116" s="1">
         <f ca="1" t="shared" si="92"/>
-        <v>0.172658670058026</v>
+        <v>0.719880666778056</v>
       </c>
       <c r="P116" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.845459637081948</v>
+        <v>0.845771562074493</v>
       </c>
     </row>
     <row r="117" ht="16.5" spans="1:16">
@@ -10752,27 +10797,27 @@
       </c>
       <c r="K117" s="1">
         <f ca="1" t="shared" ref="K117:O117" si="93">RAND()</f>
-        <v>0.23534822497159</v>
+        <v>0.582099621342851</v>
       </c>
       <c r="L117" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.599208980922384</v>
+        <v>0.599567689263458</v>
       </c>
       <c r="M117" s="1">
         <f ca="1" t="shared" si="93"/>
-        <v>0.743222362225832</v>
+        <v>0.413231590467032</v>
       </c>
       <c r="N117" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.718943348883308</v>
+        <v>0.718960687460493</v>
       </c>
       <c r="O117" s="1">
         <f ca="1" t="shared" si="93"/>
-        <v>0.887611842047885</v>
+        <v>0.494476024641805</v>
       </c>
       <c r="P117" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.838827085271633</v>
+        <v>0.838437731623915</v>
       </c>
     </row>
     <row r="118" ht="16.5" spans="1:16">
@@ -10812,27 +10857,27 @@
       </c>
       <c r="K118" s="1">
         <f ca="1" t="shared" ref="K118:O118" si="94">RAND()</f>
-        <v>0.726067064497289</v>
+        <v>0.208958974912543</v>
       </c>
       <c r="L118" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.594549051391841</v>
+        <v>0.594023256252121</v>
       </c>
       <c r="M118" s="1">
         <f ca="1" t="shared" si="94"/>
-        <v>0.435946034313533</v>
+        <v>0.90928161863363</v>
       </c>
       <c r="N118" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.712941038959887</v>
+        <v>0.712896531107496</v>
       </c>
       <c r="O118" s="1">
         <f ca="1" t="shared" si="94"/>
-        <v>0.532097594897167</v>
+        <v>0.802839428292712</v>
       </c>
       <c r="P118" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.831430793366723</v>
+        <v>0.831661575619022</v>
       </c>
     </row>
     <row r="119" ht="16.5" spans="1:16">
@@ -10872,27 +10917,27 @@
       </c>
       <c r="K119" s="1">
         <f ca="1" t="shared" ref="K119:O119" si="95">RAND()</f>
-        <v>0.337181260241293</v>
+        <v>0.705778364494019</v>
       </c>
       <c r="L119" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.58908105906065</v>
+        <v>0.58944949597494</v>
       </c>
       <c r="M119" s="1">
         <f ca="1" t="shared" si="95"/>
-        <v>0.813064288926042</v>
+        <v>0.650059306816145</v>
       </c>
       <c r="N119" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.706842922539368</v>
+        <v>0.707048425312479</v>
       </c>
       <c r="O119" s="1">
         <f ca="1" t="shared" si="95"/>
-        <v>0.180921068932887</v>
+        <v>0.64785098162816</v>
       </c>
       <c r="P119" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.823972917523525</v>
+        <v>0.824645147284554</v>
       </c>
     </row>
     <row r="120" ht="16.5" spans="1:16">
@@ -11046,27 +11091,27 @@
       </c>
       <c r="K122" s="1">
         <f ca="1" t="shared" ref="K122:O122" si="96">RAND()</f>
-        <v>0.0199148821546393</v>
+        <v>0.198109742708034</v>
       </c>
       <c r="L122" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.574068514144197</v>
+        <v>0.574237872895962</v>
       </c>
       <c r="M122" s="1">
         <f ca="1" t="shared" si="96"/>
-        <v>0.491912038613519</v>
+        <v>0.193054292898699</v>
       </c>
       <c r="N122" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.688585620627176</v>
+        <v>0.688470941025577</v>
       </c>
       <c r="O122" s="1">
         <f ca="1" t="shared" si="96"/>
-        <v>0.655130850273262</v>
+        <v>0.487099921330097</v>
       </c>
       <c r="P122" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.803257852427023</v>
+        <v>0.802983474008659</v>
       </c>
     </row>
     <row r="123" ht="16.5" spans="1:16">
@@ -11106,27 +11151,27 @@
       </c>
       <c r="K123" s="1">
         <f ca="1" t="shared" ref="K123:O123" si="97">RAND()</f>
-        <v>0.0329003659648475</v>
+        <v>0.00389769164661646</v>
       </c>
       <c r="L123" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.569343857543037</v>
+        <v>0.569316744895321</v>
       </c>
       <c r="M123" s="1">
         <f ca="1" t="shared" si="97"/>
-        <v>0.37107749385759</v>
+        <v>0.963301257015584</v>
       </c>
       <c r="N123" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.682805507008911</v>
+        <v>0.683332024487978</v>
       </c>
       <c r="O123" s="1">
         <f ca="1" t="shared" si="97"/>
-        <v>0.396798810036563</v>
+        <v>0.145772849306681</v>
       </c>
       <c r="P123" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.796291201601684</v>
+        <v>0.796583051809509</v>
       </c>
     </row>
     <row r="124" ht="16.5" spans="1:16">
@@ -11166,27 +11211,27 @@
       </c>
       <c r="K124" s="1">
         <f ca="1" t="shared" ref="K124:O124" si="98">RAND()</f>
-        <v>0.084692421529345</v>
+        <v>0.772943283942658</v>
       </c>
       <c r="L124" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.56473202421812</v>
+        <v>0.565364961836493</v>
       </c>
       <c r="M124" s="1">
         <f ca="1" t="shared" si="98"/>
-        <v>0.28260724399816</v>
+        <v>0.311077763642249</v>
       </c>
       <c r="N124" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.677187040875935</v>
+        <v>0.677846160899419</v>
       </c>
       <c r="O124" s="1">
         <f ca="1" t="shared" si="98"/>
-        <v>0.885497208698641</v>
+        <v>0.862433182377083</v>
       </c>
       <c r="P124" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.790196494526478</v>
+        <v>0.790834404129913</v>
       </c>
     </row>
     <row r="125" ht="16.5" spans="1:16">
@@ -11226,27 +11271,27 @@
       </c>
       <c r="K125" s="1">
         <f ca="1" t="shared" ref="K125:O125" si="99">RAND()</f>
-        <v>0.443818451445232</v>
+        <v>0.651077362439663</v>
       </c>
       <c r="L125" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.56047237704104</v>
+        <v>0.560659904773254</v>
       </c>
       <c r="M125" s="1">
         <f ca="1" t="shared" si="99"/>
-        <v>0.468630991368278</v>
+        <v>0.577717930377048</v>
       </c>
       <c r="N125" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.672186716647707</v>
+        <v>0.672472946173674</v>
       </c>
       <c r="O125" s="1">
         <f ca="1" t="shared" si="99"/>
-        <v>0.0878654391224434</v>
+        <v>0.43930018741617</v>
       </c>
       <c r="P125" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.783556539822365</v>
+        <v>0.784160747287386</v>
       </c>
     </row>
     <row r="126" ht="16.5" spans="1:16">
@@ -11286,27 +11331,27 @@
       </c>
       <c r="K126" s="1">
         <f ca="1" t="shared" ref="K126:O126" si="100">RAND()</f>
-        <v>0.840559896487247</v>
+        <v>0.121480377446395</v>
       </c>
       <c r="L126" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.556309659778808</v>
+        <v>0.555669447045727</v>
       </c>
       <c r="M126" s="1">
         <f ca="1" t="shared" si="100"/>
-        <v>0.128847015752882</v>
+        <v>0.592392172132676</v>
       </c>
       <c r="N126" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.666824375186382</v>
+        <v>0.666596867173174</v>
       </c>
       <c r="O126" s="1">
         <f ca="1" t="shared" si="100"/>
-        <v>0.789660260778759</v>
+        <v>0.368271754555236</v>
       </c>
       <c r="P126" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.777927427547591</v>
+        <v>0.777324747832068</v>
       </c>
     </row>
     <row r="127" ht="16.5" spans="1:16">
@@ -11346,27 +11391,27 @@
       </c>
       <c r="K127" s="1">
         <f ca="1" t="shared" ref="K127:O127" si="101">RAND()</f>
-        <v>0.462206173643516</v>
+        <v>0.573157304126605</v>
       </c>
       <c r="L127" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.551528790171192</v>
+        <v>0.551626004495044</v>
       </c>
       <c r="M127" s="1">
         <f ca="1" t="shared" si="101"/>
-        <v>0.548823325308193</v>
+        <v>0.222880089415206</v>
       </c>
       <c r="N127" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.661533473465748</v>
+        <v>0.661345099430532</v>
       </c>
       <c r="O127" s="1">
         <f ca="1" t="shared" si="101"/>
-        <v>0.571539493893601</v>
+        <v>0.948198339873494</v>
       </c>
       <c r="P127" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.771558060450874</v>
+        <v>0.771699711309278</v>
       </c>
     </row>
     <row r="128" ht="16.5" spans="1:16">
@@ -11406,27 +11451,27 @@
       </c>
       <c r="K128" s="1">
         <f ca="1" t="shared" ref="K128:O128" si="102">RAND()</f>
-        <v>0.15767687052459</v>
+        <v>0.713878016244346</v>
       </c>
       <c r="L128" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.546892634721487</v>
+        <v>0.547372298251729</v>
       </c>
       <c r="M128" s="1">
         <f ca="1" t="shared" si="102"/>
-        <v>0.587916386151558</v>
+        <v>0.663476544587091</v>
       </c>
       <c r="N128" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.656061066550564</v>
+        <v>0.656605892572146</v>
       </c>
       <c r="O128" s="1">
         <f ca="1" t="shared" si="102"/>
-        <v>0.682246352145585</v>
+        <v>0.559544851275066</v>
       </c>
       <c r="P128" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.765310847806633</v>
+        <v>0.765749857010815</v>
       </c>
     </row>
     <row r="129" ht="16.5" spans="1:16">
@@ -11466,27 +11511,27 @@
       </c>
       <c r="K129" s="1">
         <f ca="1" t="shared" ref="K129:O129" si="103">RAND()</f>
-        <v>0.86823878796882</v>
+        <v>0.121038058989964</v>
       </c>
       <c r="L129" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.543195232238803</v>
+        <v>0.542560920596338</v>
       </c>
       <c r="M129" s="1">
         <f ca="1" t="shared" si="103"/>
-        <v>0.654097729946019</v>
+        <v>0.440075555916616</v>
       </c>
       <c r="N129" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.651563007132581</v>
+        <v>0.650747008359112</v>
       </c>
       <c r="O129" s="1">
         <f ca="1" t="shared" si="103"/>
-        <v>0.571328140549385</v>
+        <v>0.211661499849323</v>
       </c>
       <c r="P129" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.759860517488116</v>
+        <v>0.758739191472911</v>
       </c>
     </row>
     <row r="130" ht="16.5" spans="1:16">
@@ -11526,27 +11571,27 @@
       </c>
       <c r="K130" s="1">
         <f ca="1" t="shared" ref="K130:O130" si="107">RAND()</f>
-        <v>0.287323456160806</v>
+        <v>0.180366615353553</v>
       </c>
       <c r="L130" s="1">
         <f ca="1" t="shared" ref="L130:L193" si="108">J130+($R$1*$R$7*K130/MAX(1,($A130*($A130-1)))+$R$1*$R$7/$A130)/100</f>
-        <v>0.538466876435018</v>
+        <v>0.538377486633471</v>
       </c>
       <c r="M130" s="1">
         <f ca="1" t="shared" si="107"/>
-        <v>0.992345536754037</v>
+        <v>0.778356486221663</v>
       </c>
       <c r="N130" s="1">
         <f ca="1" t="shared" ref="N130:N193" si="109">L130+($R$1*$R$7*M130/MAX(1,($A130*($A130-1)))+$R$1*$R$7/$A130)/100</f>
-        <v>0.646272979172858</v>
+        <v>0.646004746778206</v>
       </c>
       <c r="O130" s="1">
         <f ca="1" t="shared" si="107"/>
-        <v>0.62565044730168</v>
+        <v>0.278266377592587</v>
       </c>
       <c r="P130" s="1">
         <f ca="1" t="shared" ref="P130:P193" si="110">N130+($R$1*$R$7*O130/MAX(1,($A130*($A130-1)))+$R$1*$R$7/$A130)/100</f>
-        <v>0.753772614357739</v>
+        <v>0.753214053707153</v>
       </c>
     </row>
     <row r="131" ht="16.5" spans="1:16">
@@ -11586,27 +11631,27 @@
       </c>
       <c r="K131" s="1">
         <f ca="1" t="shared" ref="K131:O131" si="112">RAND()</f>
-        <v>0.237860578429377</v>
+        <v>0.175868371561379</v>
       </c>
       <c r="L131" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.53425655789996</v>
+        <v>0.534205544634916</v>
       </c>
       <c r="M131" s="1">
         <f ca="1" t="shared" si="112"/>
-        <v>0.0672562318492931</v>
+        <v>0.712445198754131</v>
       </c>
       <c r="N131" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.640465749074648</v>
+        <v>0.640945660540868</v>
       </c>
       <c r="O131" s="1">
         <f ca="1" t="shared" si="112"/>
-        <v>0.768854723643575</v>
+        <v>0.657762838898418</v>
       </c>
       <c r="P131" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.747252284267628</v>
+        <v>0.747640778440498</v>
       </c>
     </row>
     <row r="132" ht="16.5" spans="1:16">
@@ -11646,27 +11691,27 @@
       </c>
       <c r="K132" s="1">
         <f ca="1" t="shared" ref="K132:O132" si="113">RAND()</f>
-        <v>0.800645121113625</v>
+        <v>0.332822645029691</v>
       </c>
       <c r="L132" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.530607686592565</v>
+        <v>0.530228593805133</v>
       </c>
       <c r="M132" s="1">
         <f ca="1" t="shared" si="113"/>
-        <v>0.100112773496142</v>
+        <v>0.96427665201271</v>
       </c>
       <c r="N132" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.63603232289757</v>
+        <v>0.636353492090381</v>
       </c>
       <c r="O132" s="1">
         <f ca="1" t="shared" si="113"/>
-        <v>0.478707900996426</v>
+        <v>0.245595814105342</v>
       </c>
       <c r="P132" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.741763747972952</v>
+        <v>0.741896018351958</v>
       </c>
     </row>
     <row r="133" ht="16.5" spans="1:16">
@@ -11706,27 +11751,27 @@
       </c>
       <c r="K133" s="1">
         <f ca="1" t="shared" ref="K133:O133" si="114">RAND()</f>
-        <v>0.752880490182528</v>
+        <v>0.790696816921629</v>
       </c>
       <c r="L133" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.526520341820757</v>
+        <v>0.52655052140143</v>
       </c>
       <c r="M133" s="1">
         <f ca="1" t="shared" si="114"/>
-        <v>0.747097218058212</v>
+        <v>0.241925806526114</v>
       </c>
       <c r="N133" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.631662022459734</v>
+        <v>0.631289046507263</v>
       </c>
       <c r="O133" s="1">
         <f ca="1" t="shared" si="114"/>
-        <v>0.470395176368626</v>
+        <v>0.265244450541251</v>
       </c>
       <c r="P133" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.736582879123734</v>
+        <v>0.736046181217965</v>
       </c>
     </row>
     <row r="134" ht="16.5" spans="1:16">
@@ -11766,27 +11811,27 @@
       </c>
       <c r="K134" s="1">
         <f ca="1" t="shared" ref="K134:O134" si="115">RAND()</f>
-        <v>0.873535049670381</v>
+        <v>0.729129442859771</v>
       </c>
       <c r="L134" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.522627864188052</v>
+        <v>0.522514353287278</v>
       </c>
       <c r="M134" s="1">
         <f ca="1" t="shared" si="115"/>
-        <v>0.718677122513178</v>
+        <v>0.478653308048087</v>
       </c>
       <c r="N134" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.626952183183876</v>
+        <v>0.626650000111787</v>
       </c>
       <c r="O134" s="1">
         <f ca="1" t="shared" si="115"/>
-        <v>0.253815450708718</v>
+        <v>0.988285064366338</v>
       </c>
       <c r="P134" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.73091109485053</v>
+        <v>0.73118624606122</v>
       </c>
     </row>
     <row r="135" ht="16.5" spans="1:16">
@@ -11826,27 +11871,27 @@
       </c>
       <c r="K135" s="1">
         <f ca="1" t="shared" ref="K135:O135" si="116">RAND()</f>
-        <v>0.908732608568533</v>
+        <v>0.885854621070964</v>
       </c>
       <c r="L135" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.518726321961522</v>
+        <v>0.518708606989719</v>
       </c>
       <c r="M135" s="1">
         <f ca="1" t="shared" si="116"/>
-        <v>0.6382906642531</v>
+        <v>0.112100964960672</v>
       </c>
       <c r="N135" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.622205640285318</v>
+        <v>0.621780484069534</v>
       </c>
       <c r="O135" s="1">
         <f ca="1" t="shared" si="116"/>
-        <v>0.745900861584274</v>
+        <v>0.63480188074484</v>
       </c>
       <c r="P135" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.725768283753495</v>
+        <v>0.725257100944984</v>
       </c>
     </row>
     <row r="136" ht="16.5" spans="1:16">
@@ -11886,27 +11931,27 @@
       </c>
       <c r="K136" s="1">
         <f ca="1" t="shared" ref="K136:O136" si="117">RAND()</f>
-        <v>0.964845613005692</v>
+        <v>0.681313502526312</v>
       </c>
       <c r="L136" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.514898555525676</v>
+        <v>0.514682262373403</v>
       </c>
       <c r="M136" s="1">
         <f ca="1" t="shared" si="117"/>
-        <v>0.722880210619442</v>
+        <v>0.440162582919554</v>
       </c>
       <c r="N136" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.617672228654839</v>
+        <v>0.61724026368044</v>
       </c>
       <c r="O136" s="1">
         <f ca="1" t="shared" si="117"/>
-        <v>0.26915935514524</v>
+        <v>0.344199118366279</v>
       </c>
       <c r="P136" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.720099779738366</v>
+        <v>0.719725059027784</v>
       </c>
     </row>
     <row r="137" ht="16.5" spans="1:16">
@@ -11946,27 +11991,27 @@
       </c>
       <c r="K137" s="1">
         <f ca="1" t="shared" ref="K137:O137" si="118">RAND()</f>
-        <v>0.307630731285437</v>
+        <v>0.281523289707955</v>
       </c>
       <c r="L137" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.510590702837241</v>
+        <v>0.510571079596839</v>
       </c>
       <c r="M137" s="1">
         <f ca="1" t="shared" si="118"/>
-        <v>0.90743172060857</v>
+        <v>0.589585739431541</v>
       </c>
       <c r="N137" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.612743347594561</v>
+        <v>0.612484820512098</v>
       </c>
       <c r="O137" s="1">
         <f ca="1" t="shared" si="118"/>
-        <v>0.411475759140656</v>
+        <v>0.283479342639</v>
       </c>
       <c r="P137" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.714523214995222</v>
+        <v>0.714168481455912</v>
       </c>
     </row>
     <row r="138" ht="16.5" spans="1:16">
@@ -12120,27 +12165,27 @@
       </c>
       <c r="K140" s="1">
         <f ca="1" t="shared" ref="K140:O140" si="119">RAND()</f>
-        <v>0.729266384247821</v>
+        <v>0.701029571250151</v>
       </c>
       <c r="L140" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.499805227614567</v>
+        <v>0.499784913360612</v>
       </c>
       <c r="M140" s="1">
         <f ca="1" t="shared" si="119"/>
-        <v>0.1896524062559</v>
+        <v>0.333451971350174</v>
       </c>
       <c r="N140" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.599222243734175</v>
+        <v>0.599305382404749</v>
       </c>
       <c r="O140" s="1">
         <f ca="1" t="shared" si="119"/>
-        <v>0.956516789575229</v>
+        <v>0.885260596125443</v>
       </c>
       <c r="P140" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.699190960848978</v>
+        <v>0.699222836071026</v>
       </c>
     </row>
     <row r="141" ht="16.5" spans="1:16">
@@ -12180,27 +12225,27 @@
       </c>
       <c r="K141" s="1">
         <f ca="1" t="shared" ref="K141:O141" si="120">RAND()</f>
-        <v>0.370496455302103</v>
+        <v>0.453722848332957</v>
       </c>
       <c r="L141" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.495956467167686</v>
+        <v>0.496015486911973</v>
       </c>
       <c r="M141" s="1">
         <f ca="1" t="shared" si="120"/>
-        <v>0.0533278389600071</v>
+        <v>0.336911566555148</v>
       </c>
       <c r="N141" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.59456571301443</v>
+        <v>0.594825835299355</v>
       </c>
       <c r="O141" s="1">
         <f ca="1" t="shared" si="120"/>
-        <v>0.794028346939889</v>
+        <v>0.531967460161422</v>
       </c>
       <c r="P141" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.693700224380708</v>
+        <v>0.693774506982306</v>
       </c>
     </row>
     <row r="142" ht="16.5" spans="1:16">
@@ -12240,27 +12285,27 @@
       </c>
       <c r="K142" s="1">
         <f ca="1" t="shared" ref="K142:O142" si="121">RAND()</f>
-        <v>0.107660624389254</v>
+        <v>0.496714390316509</v>
       </c>
       <c r="L142" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.492233318977536</v>
+        <v>0.492505301853412</v>
       </c>
       <c r="M142" s="1">
         <f ca="1" t="shared" si="121"/>
-        <v>0.622476680939623</v>
+        <v>0.857448020281082</v>
       </c>
       <c r="N142" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.59054082547181</v>
+        <v>0.590977074025645</v>
       </c>
       <c r="O142" s="1">
         <f ca="1" t="shared" si="121"/>
-        <v>0.944036879874905</v>
+        <v>0.126064076148284</v>
       </c>
       <c r="P142" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.689073130889352</v>
+        <v>0.688937544352436</v>
       </c>
     </row>
     <row r="143" ht="16.5" spans="1:16">
@@ -12300,27 +12345,27 @@
       </c>
       <c r="K143" s="1">
         <f ca="1" t="shared" ref="K143:O143" si="122">RAND()</f>
-        <v>0.251829305514502</v>
+        <v>0.615384856057882</v>
       </c>
       <c r="L143" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.488846031586061</v>
+        <v>0.489096609280472</v>
       </c>
       <c r="M143" s="1">
         <f ca="1" t="shared" si="122"/>
-        <v>0.229561098321646</v>
+        <v>0.930556923999512</v>
       </c>
       <c r="N143" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.586187353290028</v>
+        <v>0.586921086632944</v>
       </c>
       <c r="O143" s="1">
         <f ca="1" t="shared" si="122"/>
-        <v>0.372900336741696</v>
+        <v>0.637692072138728</v>
       </c>
       <c r="P143" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.683627470393566</v>
+        <v>0.68454370927781</v>
       </c>
     </row>
     <row r="144" ht="16.5" spans="1:16">
@@ -12360,27 +12405,27 @@
       </c>
       <c r="K144" s="1">
         <f ca="1" t="shared" ref="K144:O144" si="123">RAND()</f>
-        <v>0.0986851214823237</v>
+        <v>0.55865720538249</v>
       </c>
       <c r="L144" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.485302957484313</v>
+        <v>0.485615555472977</v>
       </c>
       <c r="M144" s="1">
         <f ca="1" t="shared" si="123"/>
-        <v>0.470175715077762</v>
+        <v>0.121086705706089</v>
       </c>
       <c r="N144" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.582125986385528</v>
+        <v>0.582201342754507</v>
       </c>
       <c r="O144" s="1">
         <f ca="1" t="shared" si="123"/>
-        <v>0.562589270089482</v>
+        <v>0.143887763259302</v>
       </c>
       <c r="P144" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.679011819731693</v>
+        <v>0.67880262568236</v>
       </c>
     </row>
     <row r="145" ht="16.5" spans="1:16">
@@ -12420,27 +12465,27 @@
       </c>
       <c r="K145" s="1">
         <f ca="1" t="shared" ref="K145:O145" si="124">RAND()</f>
-        <v>0.858683319768813</v>
+        <v>0.0576039524196708</v>
       </c>
       <c r="L145" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.482422777283062</v>
+        <v>0.481885923394687</v>
       </c>
       <c r="M145" s="1">
         <f ca="1" t="shared" si="124"/>
-        <v>0.108233004275755</v>
+        <v>0.0939125599168287</v>
       </c>
       <c r="N145" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.578328644389657</v>
+        <v>0.577782193466892</v>
       </c>
       <c r="O145" s="1">
         <f ca="1" t="shared" si="124"/>
-        <v>0.296733470285459</v>
+        <v>0.137855985785924</v>
       </c>
       <c r="P145" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.67436083756613</v>
+        <v>0.673707912804686</v>
       </c>
     </row>
     <row r="146" ht="16.5" spans="1:16">
@@ -12480,27 +12525,27 @@
       </c>
       <c r="K146" s="1">
         <f ca="1" t="shared" ref="K146:O146" si="125">RAND()</f>
-        <v>0.130823015976573</v>
+        <v>0.0611155445680487</v>
       </c>
       <c r="L146" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.478592210614007</v>
+        <v>0.478546139584053</v>
       </c>
       <c r="M146" s="1">
         <f ca="1" t="shared" si="125"/>
-        <v>0.868503691008353</v>
+        <v>0.526310365715942</v>
       </c>
       <c r="N146" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.57433863546726</v>
+        <v>0.574066402182084</v>
       </c>
       <c r="O146" s="1">
         <f ca="1" t="shared" si="125"/>
-        <v>0.622086282113545</v>
+        <v>0.44052620792396</v>
       </c>
       <c r="P146" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.669922198239921</v>
+        <v>0.669529968353988</v>
       </c>
     </row>
     <row r="147" ht="16.5" spans="1:16">
@@ -12540,27 +12585,27 @@
       </c>
       <c r="K147" s="1">
         <f ca="1" t="shared" ref="K147:O147" si="126">RAND()</f>
-        <v>0.353176229982738</v>
+        <v>0.36046108293755</v>
       </c>
       <c r="L147" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.475440426640235</v>
+        <v>0.475445175387083</v>
       </c>
       <c r="M147" s="1">
         <f ca="1" t="shared" si="126"/>
-        <v>0.252589329572041</v>
+        <v>0.199146031643913</v>
       </c>
       <c r="N147" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.570125628942932</v>
+        <v>0.570095539829061</v>
       </c>
       <c r="O147" s="1">
         <f ca="1" t="shared" si="126"/>
-        <v>0.111404232105593</v>
+        <v>0.989149620907558</v>
       </c>
       <c r="P147" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.664718797502358</v>
+        <v>0.665260880630598</v>
       </c>
     </row>
     <row r="148" ht="16.5" spans="1:16">
@@ -12600,27 +12645,27 @@
       </c>
       <c r="K148" s="1">
         <f ca="1" t="shared" ref="K148:O148" si="127">RAND()</f>
-        <v>0.484915866063976</v>
+        <v>0.118084090716107</v>
       </c>
       <c r="L148" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.472271542211895</v>
+        <v>0.472035670508428</v>
       </c>
       <c r="M148" s="1">
         <f ca="1" t="shared" si="127"/>
-        <v>0.389043720379527</v>
+        <v>0.524482580882684</v>
       </c>
       <c r="N148" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.566399247148119</v>
+        <v>0.566250462215454</v>
       </c>
       <c r="O148" s="1">
         <f ca="1" t="shared" si="127"/>
-        <v>0.725890108416368</v>
+        <v>0.391782195350346</v>
       </c>
       <c r="P148" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.660743543275979</v>
+        <v>0.660379927982662</v>
       </c>
     </row>
     <row r="149" ht="16.5" spans="1:16">
@@ -12660,27 +12705,27 @@
       </c>
       <c r="K149" s="1">
         <f ca="1" t="shared" ref="K149:O149" si="128">RAND()</f>
-        <v>0.601173944044978</v>
+        <v>0.068668160457362</v>
       </c>
       <c r="L149" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.469134776633013</v>
+        <v>0.468797004073098</v>
       </c>
       <c r="M149" s="1">
         <f ca="1" t="shared" si="128"/>
-        <v>0.399217914730991</v>
+        <v>0.60299879509919</v>
       </c>
       <c r="N149" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.562631246904354</v>
+        <v>0.562422734141694</v>
       </c>
       <c r="O149" s="1">
         <f ca="1" t="shared" si="128"/>
-        <v>0.655459427315494</v>
+        <v>0.374253474324357</v>
       </c>
       <c r="P149" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.656290253159959</v>
+        <v>0.655903369274332</v>
       </c>
     </row>
     <row r="150" ht="16.5" spans="1:16">
@@ -12720,27 +12765,27 @@
       </c>
       <c r="K150" s="1">
         <f ca="1" t="shared" ref="K150:O150" si="129">RAND()</f>
-        <v>0.229609398573577</v>
+        <v>0.163815921776437</v>
       </c>
       <c r="L150" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.465734110724665</v>
+        <v>0.465692937589358</v>
       </c>
       <c r="M150" s="1">
         <f ca="1" t="shared" si="129"/>
-        <v>0.935398901290737</v>
+        <v>0.0380929970390818</v>
       </c>
       <c r="N150" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.558936927015152</v>
+        <v>0.558334225606732</v>
       </c>
       <c r="O150" s="1">
         <f ca="1" t="shared" si="129"/>
-        <v>0.559649902898658</v>
+        <v>0.786156416704199</v>
       </c>
       <c r="P150" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.651904601995199</v>
+        <v>0.651443646908678</v>
       </c>
     </row>
     <row r="151" ht="16.5" spans="1:16">
@@ -12780,27 +12825,27 @@
       </c>
       <c r="K151" s="1">
         <f ca="1" t="shared" ref="K151:O151" si="130">RAND()</f>
-        <v>0.135265053776152</v>
+        <v>0.420706716339472</v>
       </c>
       <c r="L151" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.462553318019781</v>
+        <v>0.462729563878545</v>
       </c>
       <c r="M151" s="1">
         <f ca="1" t="shared" si="130"/>
-        <v>0.574828996086424</v>
+        <v>0.428496393417585</v>
       </c>
       <c r="N151" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.554908245990519</v>
+        <v>0.55499413883287</v>
       </c>
       <c r="O151" s="1">
         <f ca="1" t="shared" si="130"/>
-        <v>0.164368717925993</v>
+        <v>0.663297784297078</v>
       </c>
       <c r="P151" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.647009735400245</v>
+        <v>0.647403691827201</v>
       </c>
     </row>
     <row r="152" ht="16.5" spans="1:16">
@@ -12840,27 +12885,27 @@
       </c>
       <c r="K152" s="1">
         <f ca="1" t="shared" ref="K152:O152" si="131">RAND()</f>
-        <v>0.812507801723357</v>
+        <v>0.598350498131029</v>
       </c>
       <c r="L152" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.459885766342772</v>
+        <v>0.459755286396212</v>
       </c>
       <c r="M152" s="1">
         <f ca="1" t="shared" si="131"/>
-        <v>0.472747068298023</v>
+        <v>0.89689297197566</v>
       </c>
       <c r="N152" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.551564526145973</v>
+        <v>0.551692466220197</v>
       </c>
       <c r="O152" s="1">
         <f ca="1" t="shared" si="131"/>
-        <v>0.698514507390359</v>
+        <v>0.0213717076587794</v>
       </c>
       <c r="P152" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.643380839620675</v>
+        <v>0.643096215869897</v>
       </c>
     </row>
     <row r="153" ht="16.5" spans="1:16">
@@ -12900,27 +12945,27 @@
       </c>
       <c r="K153" s="1">
         <f ca="1" t="shared" ref="K153:O153" si="132">RAND()</f>
-        <v>0.62411789422488</v>
+        <v>0.345283638052482</v>
       </c>
       <c r="L153" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.456727641466552</v>
+        <v>0.456559991033685</v>
       </c>
       <c r="M153" s="1">
         <f ca="1" t="shared" si="132"/>
-        <v>0.876658698417175</v>
+        <v>0.581514898976818</v>
       </c>
       <c r="N153" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.54804421039467</v>
+        <v>0.54769910333788</v>
       </c>
       <c r="O153" s="1">
         <f ca="1" t="shared" si="132"/>
-        <v>0.829866991842518</v>
+        <v>0.184389803892525</v>
       </c>
       <c r="P153" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.639332645584955</v>
+        <v>0.638599442275389</v>
       </c>
     </row>
     <row r="154" ht="16.5" spans="1:16">
@@ -12960,27 +13005,27 @@
       </c>
       <c r="K154" s="1">
         <f ca="1" t="shared" ref="K154:O154" si="133">RAND()</f>
-        <v>0.936497830547583</v>
+        <v>0.731294363780777</v>
       </c>
       <c r="L154" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.453909686535155</v>
+        <v>0.453787919772109</v>
       </c>
       <c r="M154" s="1">
         <f ca="1" t="shared" si="133"/>
-        <v>0.171043189853867</v>
+        <v>0.98620080928819</v>
       </c>
       <c r="N154" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.544207261183417</v>
+        <v>0.544569205082058</v>
       </c>
       <c r="O154" s="1">
         <f ca="1" t="shared" si="133"/>
-        <v>0.0288492719488569</v>
+        <v>0.826308995449729</v>
       </c>
       <c r="P154" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.634420458635812</v>
+        <v>0.635255611348708</v>
       </c>
     </row>
     <row r="155" ht="16.5" spans="1:16">
@@ -13020,27 +13065,27 @@
       </c>
       <c r="K155" s="1">
         <f ca="1" t="shared" ref="K155:O155" si="134">RAND()</f>
-        <v>0.238733493878615</v>
+        <v>0.4630519889014</v>
       </c>
       <c r="L155" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.450534526874439</v>
+        <v>0.450665907709313</v>
       </c>
       <c r="M155" s="1">
         <f ca="1" t="shared" si="134"/>
-        <v>0.0577975923692189</v>
+        <v>0.932955309940608</v>
       </c>
       <c r="N155" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.540178767888558</v>
+        <v>0.540822718815212</v>
       </c>
       <c r="O155" s="1">
         <f ca="1" t="shared" si="134"/>
-        <v>0.71063819953121</v>
+        <v>0.142379050226805</v>
       </c>
       <c r="P155" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.630205370348177</v>
+        <v>0.630516498243661</v>
       </c>
     </row>
     <row r="156" ht="16.5" spans="1:16">
@@ -13080,27 +13125,27 @@
       </c>
       <c r="K156" s="1">
         <f ca="1" t="shared" ref="K156:O156" si="135">RAND()</f>
-        <v>0.0591030077446513</v>
+        <v>0.813715934383489</v>
       </c>
       <c r="L156" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.447507985819307</v>
+        <v>0.447944251357121</v>
       </c>
       <c r="M156" s="1">
         <f ca="1" t="shared" si="135"/>
-        <v>0.700306521565512</v>
+        <v>0.646579253016443</v>
       </c>
       <c r="N156" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.536945113175721</v>
+        <v>0.537350317284713</v>
       </c>
       <c r="O156" s="1">
         <f ca="1" t="shared" si="135"/>
-        <v>0.0454014829707339</v>
+        <v>0.0141728589648957</v>
       </c>
       <c r="P156" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.626003619269772</v>
+        <v>0.626390769126092</v>
       </c>
     </row>
     <row r="157" ht="16.5" spans="1:16">
@@ -13140,27 +13185,27 @@
       </c>
       <c r="K157" s="1">
         <f ca="1" t="shared" ref="K157:O157" si="136">RAND()</f>
-        <v>0.743755793588513</v>
+        <v>0.13910771765096</v>
       </c>
       <c r="L157" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.445015046730833</v>
+        <v>0.444669962220992</v>
       </c>
       <c r="M157" s="1">
         <f ca="1" t="shared" si="136"/>
-        <v>0.207341485278386</v>
+        <v>0.125309692292423</v>
       </c>
       <c r="N157" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.53359491904253</v>
+        <v>0.533203017380365</v>
       </c>
       <c r="O157" s="1">
         <f ca="1" t="shared" si="136"/>
-        <v>0.475586693955158</v>
+        <v>0.974993948211238</v>
       </c>
       <c r="P157" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.622327884153224</v>
+        <v>0.622221004000932</v>
       </c>
     </row>
     <row r="158" ht="16.5" spans="1:16">
@@ -13200,27 +13245,27 @@
       </c>
       <c r="K158" s="1">
         <f ca="1" t="shared" ref="K158:O158" si="137">RAND()</f>
-        <v>0.336763707087911</v>
+        <v>0.603183395933707</v>
       </c>
       <c r="L158" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.441933992289638</v>
+        <v>0.442084106274044</v>
       </c>
       <c r="M158" s="1">
         <f ca="1" t="shared" si="137"/>
-        <v>0.773552865874515</v>
+        <v>0.918891785792099</v>
       </c>
       <c r="N158" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.53026793927433</v>
+        <v>0.530499944369909</v>
       </c>
       <c r="O158" s="1">
         <f ca="1" t="shared" si="137"/>
-        <v>0.376238197781462</v>
+        <v>0.241277101990598</v>
       </c>
       <c r="P158" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.618378019591551</v>
+        <v>0.618533980953589</v>
       </c>
     </row>
     <row r="159" ht="16.5" spans="1:16">
@@ -13374,27 +13419,27 @@
       </c>
       <c r="K161" s="1">
         <f ca="1" t="shared" ref="K161:O161" si="138">RAND()</f>
-        <v>0.45230748810833</v>
+        <v>0.413442074136419</v>
       </c>
       <c r="L161" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.433665166797795</v>
+        <v>0.433644084143989</v>
       </c>
       <c r="M161" s="1">
         <f ca="1" t="shared" si="138"/>
-        <v>0.312567983598693</v>
+        <v>0.710267406516834</v>
       </c>
       <c r="N161" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.520084720185124</v>
+        <v>0.520279370708845</v>
       </c>
       <c r="O161" s="1">
         <f ca="1" t="shared" si="138"/>
-        <v>0.154695038864904</v>
+        <v>0.287925527791594</v>
       </c>
       <c r="P161" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.606418634946773</v>
+        <v>0.606685556726279</v>
       </c>
     </row>
     <row r="162" ht="16.5" spans="1:16">
@@ -13434,27 +13479,27 @@
       </c>
       <c r="K162" s="1">
         <f ca="1" t="shared" ref="K162:O162" si="139">RAND()</f>
-        <v>0.319613189770435</v>
+        <v>0.227578324787413</v>
       </c>
       <c r="L162" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.430885507065948</v>
+        <v>0.430836202673993</v>
       </c>
       <c r="M162" s="1">
         <f ca="1" t="shared" si="139"/>
-        <v>0.0171630785681922</v>
+        <v>0.914105916507051</v>
       </c>
       <c r="N162" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.51660898728661</v>
+        <v>0.517040187986408</v>
       </c>
       <c r="O162" s="1">
         <f ca="1" t="shared" si="139"/>
-        <v>0.0231124950444617</v>
+        <v>0.272484812772606</v>
       </c>
       <c r="P162" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.60233565469467</v>
+        <v>0.602900447707536</v>
       </c>
     </row>
     <row r="163" ht="16.5" spans="1:16">
@@ -13494,27 +13539,27 @@
       </c>
       <c r="K163" s="1">
         <f ca="1" t="shared" ref="K163:O163" si="140">RAND()</f>
-        <v>0.864496793040779</v>
+        <v>0.447305401554559</v>
       </c>
       <c r="L163" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.428499733752932</v>
+        <v>0.42827899756696</v>
       </c>
       <c r="M163" s="1">
         <f ca="1" t="shared" si="140"/>
-        <v>0.730909711041072</v>
+        <v>0.380046712001268</v>
       </c>
       <c r="N163" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.514071643652954</v>
+        <v>0.513665265668548</v>
       </c>
       <c r="O163" s="1">
         <f ca="1" t="shared" si="140"/>
-        <v>0.876528203727603</v>
+        <v>0.781563077871354</v>
       </c>
       <c r="P163" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.599720600374503</v>
+        <v>0.599263976291761</v>
       </c>
     </row>
     <row r="164" ht="16.5" spans="1:16">
@@ -13668,27 +13713,27 @@
       </c>
       <c r="K166" s="1">
         <f ca="1" t="shared" ref="K166:O166" si="141">RAND()</f>
-        <v>0.671888684129902</v>
+        <v>0.0272188903325832</v>
       </c>
       <c r="L166" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.420564377821175</v>
+        <v>0.420235610520569</v>
       </c>
       <c r="M166" s="1">
         <f ca="1" t="shared" si="141"/>
-        <v>0.589374339306953</v>
+        <v>0.860522685642203</v>
       </c>
       <c r="N166" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.504501309302418</v>
+        <v>0.504310821646285</v>
       </c>
       <c r="O166" s="1">
         <f ca="1" t="shared" si="141"/>
-        <v>0.385752463088084</v>
+        <v>0.957889322007217</v>
       </c>
       <c r="P166" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.588334398141687</v>
+        <v>0.588435687597641</v>
       </c>
     </row>
     <row r="167" ht="16.5" spans="1:16">
@@ -13728,27 +13773,27 @@
       </c>
       <c r="K167" s="1">
         <f ca="1" t="shared" ref="K167:O167" si="142">RAND()</f>
-        <v>0.415443923590198</v>
+        <v>0.579711190603315</v>
       </c>
       <c r="L167" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.417887299238611</v>
+        <v>0.417970062593295</v>
       </c>
       <c r="M167" s="1">
         <f ca="1" t="shared" si="142"/>
-        <v>0.883688842004023</v>
+        <v>0.658662791971828</v>
       </c>
       <c r="N167" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.501465061415305</v>
+        <v>0.501434449104036</v>
       </c>
       <c r="O167" s="1">
         <f ca="1" t="shared" si="142"/>
-        <v>0.19805007646186</v>
+        <v>0.854387350701417</v>
       </c>
       <c r="P167" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.584697375802132</v>
+        <v>0.584997448207347</v>
       </c>
     </row>
     <row r="168" ht="16.5" spans="1:16">
@@ -13788,27 +13833,27 @@
       </c>
       <c r="K168" s="1">
         <f ca="1" t="shared" ref="K168:O168" si="143">RAND()</f>
-        <v>0.145016544119798</v>
+        <v>0.980522831070655</v>
       </c>
       <c r="L168" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.415237040195832</v>
+        <v>0.415652954875867</v>
       </c>
       <c r="M168" s="1">
         <f ca="1" t="shared" si="143"/>
-        <v>0.519684431567627</v>
+        <v>0.880086295050647</v>
       </c>
       <c r="N168" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.498130469427332</v>
+        <v>0.498725792004202</v>
       </c>
       <c r="O168" s="1">
         <f ca="1" t="shared" si="143"/>
-        <v>0.244584027191029</v>
+        <v>0.763323367626465</v>
       </c>
       <c r="P168" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.580886953792646</v>
+        <v>0.581740504596123</v>
       </c>
     </row>
     <row r="169" ht="16.5" spans="1:16">
@@ -13848,27 +13893,27 @@
       </c>
       <c r="K169" s="1">
         <f ca="1" t="shared" ref="K169:O169" si="144">RAND()</f>
-        <v>0.15765190057001</v>
+        <v>0.989923178314694</v>
       </c>
       <c r="L169" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.412759324074276</v>
+        <v>0.413168696174107</v>
       </c>
       <c r="M169" s="1">
         <f ca="1" t="shared" si="144"/>
-        <v>0.149330939281487</v>
+        <v>0.0857663676670932</v>
       </c>
       <c r="N169" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.494975633133375</v>
+        <v>0.495353739511497</v>
       </c>
       <c r="O169" s="1">
         <f ca="1" t="shared" si="144"/>
-        <v>0.930298582591856</v>
+        <v>0.786265984085774</v>
       </c>
       <c r="P169" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.577576079399406</v>
+        <v>0.577883339974157</v>
       </c>
     </row>
     <row r="170" ht="16.5" spans="1:16">
@@ -13908,27 +13953,27 @@
       </c>
       <c r="K170" s="1">
         <f ca="1" t="shared" ref="K170:O170" si="145">RAND()</f>
-        <v>0.736415070713142</v>
+        <v>0.0762563606738877</v>
       </c>
       <c r="L170" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.410586169624396</v>
+        <v>0.410265297892974</v>
       </c>
       <c r="M170" s="1">
         <f ca="1" t="shared" si="145"/>
-        <v>0.727392418254579</v>
+        <v>0.748040299377204</v>
       </c>
       <c r="N170" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.492596525195399</v>
+        <v>0.49228568941634</v>
       </c>
       <c r="O170" s="1">
         <f ca="1" t="shared" si="145"/>
-        <v>0.444857828044496</v>
+        <v>0.197247945799362</v>
       </c>
       <c r="P170" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.574469554148168</v>
+        <v>0.574038366989319</v>
       </c>
     </row>
     <row r="171" ht="16.5" spans="1:16">
@@ -13968,27 +14013,27 @@
       </c>
       <c r="K171" s="1">
         <f ca="1" t="shared" ref="K171:O171" si="146">RAND()</f>
-        <v>0.183282038852484</v>
+        <v>0.261197565713968</v>
       </c>
       <c r="L171" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.407891726144663</v>
+        <v>0.407929151632678</v>
       </c>
       <c r="M171" s="1">
         <f ca="1" t="shared" si="146"/>
-        <v>0.174261777098732</v>
+        <v>0.598576609879461</v>
       </c>
       <c r="N171" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.489151900614693</v>
+        <v>0.489393139005332</v>
       </c>
       <c r="O171" s="1">
         <f ca="1" t="shared" si="146"/>
-        <v>0.109718913246988</v>
+        <v>0.820856407140599</v>
       </c>
       <c r="P171" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.570381072943367</v>
+        <v>0.570963894954463</v>
       </c>
     </row>
     <row r="172" ht="16.5" spans="1:16">
@@ -14028,27 +14073,27 @@
       </c>
       <c r="K172" s="1">
         <f ca="1" t="shared" ref="K172:O172" si="147">RAND()</f>
-        <v>0.63422953181275</v>
+        <v>0.960476562542008</v>
       </c>
       <c r="L172" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.405708715773616</v>
+        <v>0.405863590525046</v>
       </c>
       <c r="M172" s="1">
         <f ca="1" t="shared" si="147"/>
-        <v>0.676614062567832</v>
+        <v>0.71961152092977</v>
       </c>
       <c r="N172" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.486731669817766</v>
+        <v>0.486906956159336</v>
       </c>
       <c r="O172" s="1">
         <f ca="1" t="shared" si="147"/>
-        <v>0.375661794985491</v>
+        <v>0.69665110007135</v>
       </c>
       <c r="P172" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.567611756944384</v>
+        <v>0.567939422109835</v>
       </c>
     </row>
     <row r="173" ht="16.5" spans="1:16">
@@ -14088,27 +14133,27 @@
       </c>
       <c r="K173" s="1">
         <f ca="1" t="shared" ref="K173:O173" si="148">RAND()</f>
-        <v>0.581130359397553</v>
+        <v>0.265194013009317</v>
       </c>
       <c r="L173" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.403312239866711</v>
+        <v>0.403164003718875</v>
       </c>
       <c r="M173" s="1">
         <f ca="1" t="shared" si="148"/>
-        <v>0.681603192867214</v>
+        <v>0.26785648841924</v>
       </c>
       <c r="N173" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.483864603665894</v>
+        <v>0.483522239117358</v>
       </c>
       <c r="O173" s="1">
         <f ca="1" t="shared" si="148"/>
-        <v>0.517926180991795</v>
+        <v>0.970277181650024</v>
       </c>
       <c r="P173" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.564340170825478</v>
+        <v>0.564210047668519</v>
       </c>
     </row>
     <row r="174" ht="16.5" spans="1:16">
@@ -14148,27 +14193,27 @@
       </c>
       <c r="K174" s="1">
         <f ca="1" t="shared" ref="K174:O174" si="149">RAND()</f>
-        <v>0.64135393763195</v>
+        <v>0.301896835068895</v>
       </c>
       <c r="L174" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.400996460691603</v>
+        <v>0.400839029988035</v>
       </c>
       <c r="M174" s="1">
         <f ca="1" t="shared" si="149"/>
-        <v>0.323206819873087</v>
+        <v>0.513816955453139</v>
       </c>
       <c r="N174" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.480915141096034</v>
+        <v>0.480846110038621</v>
       </c>
       <c r="O174" s="1">
         <f ca="1" t="shared" si="149"/>
-        <v>0.516570042796159</v>
+        <v>0.510565927933109</v>
       </c>
       <c r="P174" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.560923497951478</v>
+        <v>0.560851682353633</v>
       </c>
     </row>
     <row r="175" ht="16.5" spans="1:16">
@@ -14208,27 +14253,27 @@
       </c>
       <c r="K175" s="1">
         <f ca="1" t="shared" ref="K175:O175" si="150">RAND()</f>
-        <v>0.978719837692339</v>
+        <v>0.490273652400067</v>
       </c>
       <c r="L175" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.398834174930575</v>
+        <v>0.398610251026614</v>
       </c>
       <c r="M175" s="1">
         <f ca="1" t="shared" si="150"/>
-        <v>0.410940260994194</v>
+        <v>0.155122060367322</v>
       </c>
       <c r="N175" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.478332911745462</v>
+        <v>0.477991710213149</v>
       </c>
       <c r="O175" s="1">
         <f ca="1" t="shared" si="150"/>
-        <v>0.161293288578442</v>
+        <v>0.999261028039465</v>
       </c>
       <c r="P175" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.557717200077878</v>
+        <v>0.557760157565051</v>
       </c>
     </row>
     <row r="176" ht="16.5" spans="1:16">
@@ -14268,27 +14313,27 @@
       </c>
       <c r="K176" s="1">
         <f ca="1" t="shared" ref="K176:O176" si="151">RAND()</f>
-        <v>0.0452513908260699</v>
+        <v>0.744500846903881</v>
       </c>
       <c r="L176" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.396119030186976</v>
+        <v>0.396435931418301</v>
       </c>
       <c r="M176" s="1">
         <f ca="1" t="shared" si="151"/>
-        <v>0.00037135711009606</v>
+        <v>0.642949694641372</v>
       </c>
       <c r="N176" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.474976341343892</v>
+        <v>0.475584460343952</v>
       </c>
       <c r="O176" s="1">
         <f ca="1" t="shared" si="151"/>
-        <v>0.473558379163563</v>
+        <v>0.569975833856632</v>
       </c>
       <c r="P176" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.554048101791592</v>
+        <v>0.554699917372104</v>
       </c>
     </row>
     <row r="177" ht="16.5" spans="1:16">
@@ -14328,27 +14373,27 @@
       </c>
       <c r="K177" s="1">
         <f ca="1" t="shared" ref="K177:O177" si="152">RAND()</f>
-        <v>0.979064932142887</v>
+        <v>0.541568773531009</v>
       </c>
       <c r="L177" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.394276334287778</v>
+        <v>0.394080313281647</v>
       </c>
       <c r="M177" s="1">
         <f ca="1" t="shared" si="152"/>
-        <v>0.514870983963508</v>
+        <v>0.725889139808635</v>
       </c>
       <c r="N177" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.472916114144229</v>
+        <v>0.472814640233899</v>
       </c>
       <c r="O177" s="1">
         <f ca="1" t="shared" si="152"/>
-        <v>0.0514101377649627</v>
+        <v>0.313447329625245</v>
       </c>
       <c r="P177" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.551348239465695</v>
+        <v>0.55136417182964</v>
       </c>
     </row>
     <row r="178" ht="16.5" spans="1:16">
@@ -14388,27 +14433,27 @@
       </c>
       <c r="K178" s="1">
         <f ca="1" t="shared" ref="K178:O178" si="153">RAND()</f>
-        <v>0.598322082122583</v>
+        <v>0.390751519652646</v>
       </c>
       <c r="L178" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.391867515560263</v>
+        <v>0.391775564039908</v>
       </c>
       <c r="M178" s="1">
         <f ca="1" t="shared" si="153"/>
-        <v>0.39508966528378</v>
+        <v>0.738502328401627</v>
       </c>
       <c r="N178" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.470008637715531</v>
+        <v>0.470068814300949</v>
       </c>
       <c r="O178" s="1">
         <f ca="1" t="shared" si="153"/>
-        <v>0.969492579505085</v>
+        <v>0.484179753351901</v>
       </c>
       <c r="P178" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.54840421416639</v>
+        <v>0.548249402404321</v>
       </c>
     </row>
     <row r="179" ht="16.5" spans="1:16">
@@ -14448,27 +14493,27 @@
       </c>
       <c r="K179" s="1">
         <f ca="1" t="shared" ref="K179:O179" si="154">RAND()</f>
-        <v>0.695603312027087</v>
+        <v>0.437243698462635</v>
       </c>
       <c r="L179" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.389697179131149</v>
+        <v>0.389584014569885</v>
       </c>
       <c r="M179" s="1">
         <f ca="1" t="shared" si="154"/>
-        <v>0.789193177265243</v>
+        <v>0.0440651281504152</v>
       </c>
       <c r="N179" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.467570944948652</v>
+        <v>0.467131405503944</v>
       </c>
       <c r="O179" s="1">
         <f ca="1" t="shared" si="154"/>
-        <v>0.0687840037889975</v>
+        <v>0.258228462448059</v>
       </c>
       <c r="P179" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.545129163042104</v>
+        <v>0.544772602507111</v>
       </c>
     </row>
     <row r="180" ht="16.5" spans="1:16">
@@ -14508,27 +14553,27 @@
       </c>
       <c r="K180" s="1">
         <f ca="1" t="shared" ref="K180:O180" si="155">RAND()</f>
-        <v>0.510598494971675</v>
+        <v>0.349912782844926</v>
       </c>
       <c r="L180" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.387428480924946</v>
+        <v>0.387358885079507</v>
       </c>
       <c r="M180" s="1">
         <f ca="1" t="shared" si="155"/>
-        <v>0.998055646854131</v>
+        <v>0.358347638342468</v>
       </c>
       <c r="N180" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.464955728678589</v>
+        <v>0.464609063894683</v>
       </c>
       <c r="O180" s="1">
         <f ca="1" t="shared" si="155"/>
-        <v>0.176356308208125</v>
+        <v>0.996201658260387</v>
       </c>
       <c r="P180" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.542127083805488</v>
+        <v>0.542135508652827</v>
       </c>
     </row>
     <row r="181" ht="16.5" spans="1:16">
@@ -14568,27 +14613,27 @@
       </c>
       <c r="K181" s="1">
         <f ca="1" t="shared" ref="K181:O181" si="156">RAND()</f>
-        <v>0.948566978216332</v>
+        <v>0.0879119986143371</v>
       </c>
       <c r="L181" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.385452831294208</v>
+        <v>0.385084208118587</v>
       </c>
       <c r="M181" s="1">
         <f ca="1" t="shared" si="156"/>
-        <v>0.873582268374472</v>
+        <v>0.0136358408974027</v>
       </c>
       <c r="N181" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.462493657964089</v>
+        <v>0.461756715089548</v>
       </c>
       <c r="O181" s="1">
         <f ca="1" t="shared" si="156"/>
-        <v>0.955844902760087</v>
+        <v>0.0815538291550253</v>
       </c>
       <c r="P181" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.539569718164526</v>
+        <v>0.538458311701663</v>
       </c>
     </row>
     <row r="182" ht="16.5" spans="1:16">
@@ -14628,27 +14673,27 @@
       </c>
       <c r="K182" s="1">
         <f ca="1" t="shared" ref="K182:O182" si="157">RAND()</f>
-        <v>0.232918781694526</v>
+        <v>0.33430661467835</v>
       </c>
       <c r="L182" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.383008418636814</v>
+        <v>0.38305136375944</v>
       </c>
       <c r="M182" s="1">
         <f ca="1" t="shared" si="157"/>
-        <v>0.175675492155689</v>
+        <v>0.686879854434339</v>
       </c>
       <c r="N182" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.459325923909734</v>
+        <v>0.459585401266844</v>
       </c>
       <c r="O182" s="1">
         <f ca="1" t="shared" si="157"/>
-        <v>0.227566201465196</v>
+        <v>0.337869656300585</v>
       </c>
       <c r="P182" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.535665408672786</v>
+        <v>0.535971607566934</v>
       </c>
     </row>
     <row r="183" ht="16.5" spans="1:16">
@@ -14688,27 +14733,27 @@
       </c>
       <c r="K183" s="1">
         <f ca="1" t="shared" ref="K183:O183" si="158">RAND()</f>
-        <v>0.552242428556152</v>
+        <v>0.583071868167505</v>
       </c>
       <c r="L183" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.381027895862852</v>
+        <v>0.381040810873071</v>
       </c>
       <c r="M183" s="1">
         <f ca="1" t="shared" si="158"/>
-        <v>0.0340775440781738</v>
+        <v>0.694888119177258</v>
       </c>
       <c r="N183" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.456866347386994</v>
+        <v>0.457156087906787</v>
       </c>
       <c r="O183" s="1">
         <f ca="1" t="shared" si="158"/>
-        <v>0.000353508142419967</v>
+        <v>0.33620743136205</v>
       </c>
       <c r="P183" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.532690671302129</v>
+        <v>0.533121107108802</v>
       </c>
     </row>
     <row r="184" ht="16.5" spans="1:16">
@@ -14748,27 +14793,27 @@
       </c>
       <c r="K184" s="1">
         <f ca="1" t="shared" ref="K184:O184" si="159">RAND()</f>
-        <v>0.0619372967576652</v>
+        <v>0.758873652136714</v>
       </c>
       <c r="L184" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.378732202446864</v>
+        <v>0.379020970888113</v>
       </c>
       <c r="M184" s="1">
         <f ca="1" t="shared" si="159"/>
-        <v>0.723597186088636</v>
+        <v>0.553600827916851</v>
       </c>
       <c r="N184" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.454441853595847</v>
+        <v>0.454660185787087</v>
       </c>
       <c r="O184" s="1">
         <f ca="1" t="shared" si="159"/>
-        <v>0.487086449503956</v>
+        <v>0.138339133745078</v>
       </c>
       <c r="P184" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.530053508943326</v>
+        <v>0.530127341255942</v>
       </c>
     </row>
     <row r="185" ht="16.5" spans="1:16">
@@ -14808,27 +14853,27 @@
       </c>
       <c r="K185" s="1">
         <f ca="1" t="shared" ref="K185:O185" si="160">RAND()</f>
-        <v>0.230038040427817</v>
+        <v>0.969303848263618</v>
       </c>
       <c r="L185" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.376733622147716</v>
+        <v>0.377036599937813</v>
       </c>
       <c r="M185" s="1">
         <f ca="1" t="shared" si="160"/>
-        <v>0.475695003912859</v>
+        <v>0.819795826986787</v>
       </c>
       <c r="N185" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.451928579116533</v>
+        <v>0.452372581834119</v>
       </c>
       <c r="O185" s="1">
         <f ca="1" t="shared" si="160"/>
-        <v>0.655694372332759</v>
+        <v>0.901713104890203</v>
       </c>
       <c r="P185" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.527197306318309</v>
+        <v>0.527742136385303</v>
       </c>
     </row>
     <row r="186" ht="16.5" spans="1:16">
@@ -14868,27 +14913,27 @@
       </c>
       <c r="K186" s="1">
         <f ca="1" t="shared" ref="K186:O186" si="161">RAND()</f>
-        <v>0.842949984732338</v>
+        <v>0.672770161357535</v>
       </c>
       <c r="L186" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.374936331074891</v>
+        <v>0.374867339254604</v>
       </c>
       <c r="M186" s="1">
         <f ca="1" t="shared" si="161"/>
-        <v>0.2226715933595</v>
+        <v>0.863577072279923</v>
       </c>
       <c r="N186" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.449621197937064</v>
+        <v>0.449812032662285</v>
       </c>
       <c r="O186" s="1">
         <f ca="1" t="shared" si="161"/>
-        <v>0.321133647971888</v>
+        <v>0.926113916663856</v>
       </c>
       <c r="P186" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.524345981848404</v>
+        <v>0.524782078844717</v>
       </c>
     </row>
     <row r="187" ht="16.5" spans="1:16">
@@ -14928,27 +14973,27 @@
       </c>
       <c r="K187" s="1">
         <f ca="1" t="shared" ref="K187:O187" si="162">RAND()</f>
-        <v>0.568249408356814</v>
+        <v>0.0295084841107895</v>
       </c>
       <c r="L187" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.372799821035609</v>
+        <v>0.372583761031116</v>
       </c>
       <c r="M187" s="1">
         <f ca="1" t="shared" si="162"/>
-        <v>0.844860184310761</v>
+        <v>0.550094687522926</v>
       </c>
       <c r="N187" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.44733219739549</v>
+        <v>0.446997922806409</v>
       </c>
       <c r="O187" s="1">
         <f ca="1" t="shared" si="162"/>
-        <v>0.847255999020588</v>
+        <v>0.613343305740389</v>
       </c>
       <c r="P187" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.521865534587773</v>
+        <v>0.521437450200167</v>
       </c>
     </row>
     <row r="188" ht="16.5" spans="1:16">
@@ -14988,27 +15033,27 @@
       </c>
       <c r="K188" s="1">
         <f ca="1" t="shared" ref="K188:O188" si="163">RAND()</f>
-        <v>0.398463768073933</v>
+        <v>0.849274434918365</v>
       </c>
       <c r="L188" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.370729078258853</v>
+        <v>0.370907940521013</v>
       </c>
       <c r="M188" s="1">
         <f ca="1" t="shared" si="163"/>
-        <v>0.052434463135197</v>
+        <v>0.723993308176547</v>
       </c>
       <c r="N188" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.444546673440017</v>
+        <v>0.444991981336746</v>
       </c>
       <c r="O188" s="1">
         <f ca="1" t="shared" si="163"/>
-        <v>0.510671626051615</v>
+        <v>0.148972853160791</v>
       </c>
       <c r="P188" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.518546077397223</v>
+        <v>0.518847878794443</v>
       </c>
     </row>
     <row r="189" ht="16.5" spans="1:16">
@@ -15048,27 +15093,27 @@
       </c>
       <c r="K189" s="1">
         <f ca="1" t="shared" ref="K189:O189" si="164">RAND()</f>
-        <v>0.840578771491339</v>
+        <v>0.442434835383954</v>
       </c>
       <c r="L189" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.368921378628017</v>
+        <v>0.368765092750264</v>
       </c>
       <c r="M189" s="1">
         <f ca="1" t="shared" si="164"/>
-        <v>0.598779336289619</v>
+        <v>0.793619522807328</v>
       </c>
       <c r="N189" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.442560676467385</v>
+        <v>0.442480872401383</v>
       </c>
       <c r="O189" s="1">
         <f ca="1" t="shared" si="164"/>
-        <v>0.320886006687479</v>
+        <v>0.677725615664984</v>
       </c>
       <c r="P189" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.51609089113607</v>
+        <v>0.516151159507316</v>
       </c>
     </row>
     <row r="190" ht="16.5" spans="1:16">
@@ -15108,27 +15153,27 @@
       </c>
       <c r="K190" s="1">
         <f ca="1" t="shared" ref="K190:O190" si="165">RAND()</f>
-        <v>0.0247577161030461</v>
+        <v>0.422606364354905</v>
       </c>
       <c r="L190" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.366642509751273</v>
+        <v>0.366797027125636</v>
       </c>
       <c r="M190" s="1">
         <f ca="1" t="shared" si="165"/>
-        <v>0.808773482614377</v>
+        <v>0.629228206600969</v>
       </c>
       <c r="N190" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.439972496075152</v>
+        <v>0.440057281241675</v>
       </c>
       <c r="O190" s="1">
         <f ca="1" t="shared" si="165"/>
-        <v>0.280082036742196</v>
+        <v>0.125203661844143</v>
       </c>
       <c r="P190" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.513097147997561</v>
+        <v>0.513121781144114</v>
       </c>
     </row>
     <row r="191" ht="16.5" spans="1:16">
@@ -15168,27 +15213,27 @@
       </c>
       <c r="K191" s="1">
         <f ca="1" t="shared" ref="K191:O191" si="166">RAND()</f>
-        <v>0.519248822885472</v>
+        <v>0.206699101751428</v>
       </c>
       <c r="L191" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.364894615253573</v>
+        <v>0.364774504249629</v>
       </c>
       <c r="M191" s="1">
         <f ca="1" t="shared" si="166"/>
-        <v>0.147402375801256</v>
+        <v>0.749828918669743</v>
       </c>
       <c r="N191" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.437582840059646</v>
+        <v>0.437694238002835</v>
       </c>
       <c r="O191" s="1">
         <f ca="1" t="shared" si="166"/>
-        <v>0.0303433141087814</v>
+        <v>0.438474010315705</v>
       </c>
       <c r="P191" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.510226079762645</v>
+        <v>0.510494319911561</v>
       </c>
     </row>
     <row r="192" ht="16.5" spans="1:16">
@@ -15228,27 +15273,27 @@
       </c>
       <c r="K192" s="1">
         <f ca="1" t="shared" ref="K192:O192" si="167">RAND()</f>
-        <v>0.670019676845276</v>
+        <v>0.943843649501848</v>
       </c>
       <c r="L192" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.363032413103898</v>
+        <v>0.363136540158808</v>
       </c>
       <c r="M192" s="1">
         <f ca="1" t="shared" si="167"/>
-        <v>0.137775385436082</v>
+        <v>0.32491188146274</v>
       </c>
       <c r="N192" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.435336113856696</v>
+        <v>0.435511403315716</v>
       </c>
       <c r="O192" s="1">
         <f ca="1" t="shared" si="167"/>
-        <v>0.413094638891418</v>
+        <v>0.525080879273041</v>
       </c>
       <c r="P192" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.507744510274902</v>
+        <v>0.507962384746798</v>
       </c>
     </row>
     <row r="193" ht="16.5" spans="1:16">
@@ -15288,27 +15333,27 @@
       </c>
       <c r="K193" s="1">
         <f ca="1" t="shared" ref="K193:O193" si="168">RAND()</f>
-        <v>0.123752227658114</v>
+        <v>0.763876605580379</v>
       </c>
       <c r="L193" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.360926804666821</v>
+        <v>0.361167689167676</v>
       </c>
       <c r="M193" s="1">
         <f ca="1" t="shared" si="168"/>
-        <v>0.827628579429147</v>
+        <v>0.606457077416693</v>
       </c>
       <c r="N193" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.433113248667588</v>
+        <v>0.433270904363693</v>
       </c>
       <c r="O193" s="1">
         <f ca="1" t="shared" si="168"/>
-        <v>0.986558822608753</v>
+        <v>0.74650573340989</v>
       </c>
       <c r="P193" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.505359499533426</v>
+        <v>0.505426821115467</v>
       </c>
     </row>
     <row r="194" ht="16.5" spans="1:16">
@@ -15348,27 +15393,27 @@
       </c>
       <c r="K194" s="1">
         <f ca="1" t="shared" ref="K194:O194" si="172">RAND()</f>
-        <v>0.161175524313301</v>
+        <v>0.56777336446855</v>
       </c>
       <c r="L194" s="1">
         <f ca="1" t="shared" ref="L194:L257" si="173">J194+($R$1*$R$7*K194/MAX(1,($A194*($A194-1)))+$R$1*$R$7/$A194)/100</f>
-        <v>0.359062613942021</v>
+        <v>0.359214034769799</v>
       </c>
       <c r="M194" s="1">
         <f ca="1" t="shared" si="172"/>
-        <v>0.49047394371216</v>
+        <v>0.172966661076368</v>
       </c>
       <c r="N194" s="1">
         <f ca="1" t="shared" ref="N194:N257" si="174">L194+($R$1*$R$7*M194/MAX(1,($A194*($A194-1)))+$R$1*$R$7/$A194)/100</f>
-        <v>0.430747861686603</v>
+        <v>0.430781039841119</v>
       </c>
       <c r="O194" s="1">
         <f ca="1" t="shared" si="172"/>
-        <v>0.88271022781335</v>
+        <v>0.939109789529354</v>
       </c>
       <c r="P194" s="1">
         <f ca="1" t="shared" ref="P194:P257" si="175">N194+($R$1*$R$7*O194/MAX(1,($A194*($A194-1)))+$R$1*$R$7/$A194)/100</f>
-        <v>0.502579181881546</v>
+        <v>0.502633363758852</v>
       </c>
     </row>
     <row r="195" ht="16.5" spans="1:16">
@@ -15408,27 +15453,27 @@
       </c>
       <c r="K195" s="1">
         <f ca="1" t="shared" ref="K195:O195" si="177">RAND()</f>
-        <v>0.790636659831126</v>
+        <v>0.935357358553519</v>
       </c>
       <c r="L195" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.357435788310071</v>
+        <v>0.357489128025962</v>
       </c>
       <c r="M195" s="1">
         <f ca="1" t="shared" si="177"/>
-        <v>0.615146896834187</v>
+        <v>0.635577227628648</v>
       </c>
       <c r="N195" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.428796533654239</v>
+        <v>0.428857403378274</v>
       </c>
       <c r="O195" s="1">
         <f ca="1" t="shared" si="177"/>
-        <v>0.976803606578023</v>
+        <v>0.235453939579551</v>
       </c>
       <c r="P195" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.500290574831814</v>
+        <v>0.500078205268296</v>
       </c>
     </row>
     <row r="196" ht="16.5" spans="1:16">
@@ -15468,27 +15513,27 @@
       </c>
       <c r="K196" s="1">
         <f ca="1" t="shared" ref="K196:O196" si="178">RAND()</f>
-        <v>0.118759348373794</v>
+        <v>0.448361307136872</v>
       </c>
       <c r="L196" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.355348635448257</v>
+        <v>0.355468870897132</v>
       </c>
       <c r="M196" s="1">
         <f ca="1" t="shared" si="178"/>
-        <v>0.772565083506921</v>
+        <v>0.96691577402914</v>
       </c>
       <c r="N196" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.426399690117895</v>
+        <v>0.426590822725882</v>
       </c>
       <c r="O196" s="1">
         <f ca="1" t="shared" si="178"/>
-        <v>0.817207831701587</v>
+        <v>0.823404398352708</v>
       </c>
       <c r="P196" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.49746703000892</v>
+        <v>0.497660423061522</v>
       </c>
     </row>
     <row r="197" ht="16.5" spans="1:16">
@@ -15528,27 +15573,27 @@
       </c>
       <c r="K197" s="1">
         <f ca="1" t="shared" ref="K197:O197" si="179">RAND()</f>
-        <v>0.460742228337006</v>
+        <v>0.850771149284939</v>
       </c>
       <c r="L197" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.353651445388567</v>
+        <v>0.353792272157513</v>
       </c>
       <c r="M197" s="1">
         <f ca="1" t="shared" si="179"/>
-        <v>0.704063399120042</v>
+        <v>0.62306227474112</v>
       </c>
       <c r="N197" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.424313823067998</v>
+        <v>0.424425402963149</v>
       </c>
       <c r="O197" s="1">
         <f ca="1" t="shared" si="179"/>
-        <v>0.575689443620879</v>
+        <v>0.526442854186705</v>
       </c>
       <c r="P197" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.494929849083749</v>
+        <v>0.495023647635775</v>
       </c>
     </row>
     <row r="198" ht="16.5" spans="1:16">
@@ -15588,27 +15633,27 @@
       </c>
       <c r="K198" s="1">
         <f ca="1" t="shared" ref="K198:O198" si="180">RAND()</f>
-        <v>0.136667709680586</v>
+        <v>0.912437805407503</v>
       </c>
       <c r="L198" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.351732259773998</v>
+        <v>0.35200952143672</v>
       </c>
       <c r="M198" s="1">
         <f ca="1" t="shared" si="180"/>
-        <v>0.21605179038991</v>
+        <v>0.55472406565484</v>
       </c>
       <c r="N198" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.4218602385036</v>
+        <v>0.422258542262009</v>
       </c>
       <c r="O198" s="1">
         <f ca="1" t="shared" si="180"/>
-        <v>0.980629503265317</v>
+        <v>0.884103514021015</v>
       </c>
       <c r="P198" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.492261478717654</v>
+        <v>0.492625283909514</v>
       </c>
     </row>
     <row r="199" ht="16.5" spans="1:16">
@@ -15648,27 +15693,27 @@
       </c>
       <c r="K199" s="1">
         <f ca="1" t="shared" ref="K199:O199" si="181">RAND()</f>
-        <v>0.793826044261135</v>
+        <v>0.0628296963971184</v>
       </c>
       <c r="L199" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.350180864467282</v>
+        <v>0.349922244008877</v>
       </c>
       <c r="M199" s="1">
         <f ca="1" t="shared" si="181"/>
-        <v>0.564629227654984</v>
+        <v>0.402609865792579</v>
       </c>
       <c r="N199" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.420077595312322</v>
+        <v>0.419761653744506</v>
       </c>
       <c r="O199" s="1">
         <f ca="1" t="shared" si="181"/>
-        <v>0.957836802760784</v>
+        <v>0.172749828877912</v>
       </c>
       <c r="P199" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.490113439743387</v>
+        <v>0.489519740901316</v>
       </c>
     </row>
     <row r="200" ht="16.5" spans="1:16">
@@ -15708,27 +15753,27 @@
       </c>
       <c r="K200" s="1">
         <f ca="1" t="shared" ref="K200:O200" si="182">RAND()</f>
-        <v>0.650678993933303</v>
+        <v>0.960359006756749</v>
       </c>
       <c r="L200" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.348362503682968</v>
+        <v>0.348470964780804</v>
       </c>
       <c r="M200" s="1">
         <f ca="1" t="shared" si="182"/>
-        <v>0.4234688667757</v>
+        <v>0.391072206658393</v>
       </c>
       <c r="N200" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.417857551405456</v>
+        <v>0.417954666025713</v>
       </c>
       <c r="O200" s="1">
         <f ca="1" t="shared" si="182"/>
-        <v>0.323714373725391</v>
+        <v>0.0349095082744371</v>
       </c>
       <c r="P200" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.487317661510461</v>
+        <v>0.487313626261594</v>
       </c>
     </row>
     <row r="201" ht="16.5" spans="1:16">
@@ -15768,27 +15813,27 @@
       </c>
       <c r="K201" s="1">
         <f ca="1" t="shared" ref="K201:O201" si="183">RAND()</f>
-        <v>0.0133194141512958</v>
+        <v>0.158544456431611</v>
       </c>
       <c r="L201" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.346391552962696</v>
+        <v>0.346441907374341</v>
       </c>
       <c r="M201" s="1">
         <f ca="1" t="shared" si="183"/>
-        <v>0.538879882214023</v>
+        <v>0.169172716604031</v>
       </c>
       <c r="N201" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.415578400761051</v>
+        <v>0.415500565250952</v>
       </c>
       <c r="O201" s="1">
         <f ca="1" t="shared" si="183"/>
-        <v>0.852928820661946</v>
+        <v>0.573552626981232</v>
       </c>
       <c r="P201" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.484874139899874</v>
+        <v>0.484699435257292</v>
       </c>
     </row>
     <row r="202" ht="16.5" spans="1:16">
@@ -15828,27 +15873,27 @@
       </c>
       <c r="K202" s="1">
         <f ca="1" t="shared" ref="K202:O202" si="184">RAND()</f>
-        <v>0.815372576794795</v>
+        <v>0.175147937838008</v>
       </c>
       <c r="L202" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.34493662043681</v>
+        <v>0.344716841829407</v>
       </c>
       <c r="M202" s="1">
         <f ca="1" t="shared" si="184"/>
-        <v>0.912386420939471</v>
+        <v>0.755085179236538</v>
       </c>
       <c r="N202" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.413906544133551</v>
+        <v>0.413632766592429</v>
       </c>
       <c r="O202" s="1">
         <f ca="1" t="shared" si="184"/>
-        <v>0.0175173772850536</v>
+        <v>0.682871316390398</v>
       </c>
       <c r="P202" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.482569273979484</v>
+        <v>0.482523901521936</v>
       </c>
     </row>
     <row r="203" ht="16.5" spans="1:16">
@@ -15888,27 +15933,27 @@
       </c>
       <c r="K203" s="1">
         <f ca="1" t="shared" ref="K203:O203" si="185">RAND()</f>
-        <v>0.405164890033027</v>
+        <v>0.46322221578183</v>
       </c>
       <c r="L203" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.343081406715986</v>
+        <v>0.343101139514748</v>
       </c>
       <c r="M203" s="1">
         <f ca="1" t="shared" si="185"/>
-        <v>0.125743187591134</v>
+        <v>0.303274580470424</v>
       </c>
       <c r="N203" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.411440976589114</v>
+        <v>0.411521049598254</v>
       </c>
       <c r="O203" s="1">
         <f ca="1" t="shared" si="185"/>
-        <v>0.231908709937844</v>
+        <v>0.457653145681281</v>
       </c>
       <c r="P203" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.479836630502644</v>
+        <v>0.479993430599446</v>
       </c>
     </row>
     <row r="204" ht="16.5" spans="1:16">
@@ -15948,27 +15993,27 @@
       </c>
       <c r="K204" s="1">
         <f ca="1" t="shared" ref="K204:O204" si="186">RAND()</f>
-        <v>0.901532028448794</v>
+        <v>0.891845609413652</v>
       </c>
       <c r="L204" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.34155102038708</v>
+        <v>0.341547760557233</v>
       </c>
       <c r="M204" s="1">
         <f ca="1" t="shared" si="186"/>
-        <v>0.615239303115255</v>
+        <v>0.45356864536013</v>
       </c>
       <c r="N204" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.409738366199473</v>
+        <v>0.409680698354286</v>
       </c>
       <c r="O204" s="1">
         <f ca="1" t="shared" si="186"/>
-        <v>0.78598877859817</v>
+        <v>0.676894568237272</v>
       </c>
       <c r="P204" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.477983175377267</v>
+        <v>0.477888793390176</v>
       </c>
     </row>
     <row r="205" ht="16.5" spans="1:16">
@@ -16008,27 +16053,27 @@
       </c>
       <c r="K205" s="1">
         <f ca="1" t="shared" ref="K205:O205" si="187">RAND()</f>
-        <v>0.452535840044937</v>
+        <v>0.301706928097665</v>
       </c>
       <c r="L205" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.339719042658955</v>
+        <v>0.339668780923591</v>
       </c>
       <c r="M205" s="1">
         <f ca="1" t="shared" si="187"/>
-        <v>0.542495406217127</v>
+        <v>0.681724042630485</v>
       </c>
       <c r="N205" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.40754688088473</v>
+        <v>0.407543015246693</v>
       </c>
       <c r="O205" s="1">
         <f ca="1" t="shared" si="187"/>
-        <v>0.728716419600906</v>
+        <v>0.177822727875861</v>
       </c>
       <c r="P205" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.475436774794478</v>
+        <v>0.475249331136886</v>
       </c>
     </row>
     <row r="206" ht="16.5" spans="1:16">
@@ -16068,27 +16113,27 @@
       </c>
       <c r="K206" s="1">
         <f ca="1" t="shared" ref="K206:O206" si="188">RAND()</f>
-        <v>0.369032166613684</v>
+        <v>0.700752007735311</v>
       </c>
       <c r="L206" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.338027083785253</v>
+        <v>0.338136546573572</v>
       </c>
       <c r="M206" s="1">
         <f ca="1" t="shared" si="188"/>
-        <v>0.543174539579196</v>
+        <v>0.897739743007569</v>
       </c>
       <c r="N206" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.405523396761011</v>
+        <v>0.405749860979442</v>
       </c>
       <c r="O206" s="1">
         <f ca="1" t="shared" si="188"/>
-        <v>0.73352477227554</v>
+        <v>0.537832858920094</v>
       </c>
       <c r="P206" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.473082522582565</v>
+        <v>0.473244411277221</v>
       </c>
     </row>
     <row r="207" ht="16.5" spans="1:16">
@@ -16128,27 +16173,27 @@
       </c>
       <c r="K207" s="1">
         <f ca="1" t="shared" ref="K207:O207" si="189">RAND()</f>
-        <v>0.734826759213429</v>
+        <v>0.879439386883585</v>
       </c>
       <c r="L207" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.336498712035926</v>
+        <v>0.336545968826403</v>
       </c>
       <c r="M207" s="1">
         <f ca="1" t="shared" si="189"/>
-        <v>0.827403027646679</v>
+        <v>0.330980351577609</v>
       </c>
       <c r="N207" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.403759383638614</v>
+        <v>0.403644418479535</v>
       </c>
       <c r="O207" s="1">
         <f ca="1" t="shared" si="189"/>
-        <v>0.28903018861235</v>
+        <v>0.513934982713855</v>
       </c>
       <c r="P207" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.470844124737427</v>
+        <v>0.470802654396217</v>
       </c>
     </row>
     <row r="208" ht="16.5" spans="1:16">
@@ -16188,27 +16233,27 @@
       </c>
       <c r="K208" s="1">
         <f ca="1" t="shared" ref="K208:O208" si="190">RAND()</f>
-        <v>0.489589941055744</v>
+        <v>0.0232232698927937</v>
       </c>
       <c r="L208" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.334786275061831</v>
+        <v>0.334635347336535</v>
       </c>
       <c r="M208" s="1">
         <f ca="1" t="shared" si="190"/>
-        <v>0.202173320170258</v>
+        <v>0.106078428657424</v>
       </c>
       <c r="N208" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.401518369987452</v>
+        <v>0.401336343591764</v>
       </c>
       <c r="O208" s="1">
         <f ca="1" t="shared" si="190"/>
-        <v>0.327175309966295</v>
+        <v>0.736339725773301</v>
       </c>
       <c r="P208" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.468290918631454</v>
+        <v>0.468241307904312</v>
       </c>
     </row>
     <row r="209" ht="16.5" spans="1:16">
@@ -16248,27 +16293,27 @@
       </c>
       <c r="K209" s="1">
         <f ca="1" t="shared" ref="K209:O209" si="191">RAND()</f>
-        <v>0.0490726057065309</v>
+        <v>0.174276485333227</v>
       </c>
       <c r="L209" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.333028548912086</v>
+        <v>0.333068678360684</v>
       </c>
       <c r="M209" s="1">
         <f ca="1" t="shared" si="191"/>
-        <v>0.304665367964224</v>
+        <v>0.19335659325846</v>
       </c>
       <c r="N209" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.399472351914638</v>
+        <v>0.399476805473908</v>
       </c>
       <c r="O209" s="1">
         <f ca="1" t="shared" si="191"/>
-        <v>0.221950075622899</v>
+        <v>0.233806246481326</v>
       </c>
       <c r="P209" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.465889643605543</v>
+        <v>0.465897897219575</v>
       </c>
     </row>
     <row r="210" ht="16.5" spans="1:16">
@@ -16308,27 +16353,27 @@
       </c>
       <c r="K210" s="1">
         <f ca="1" t="shared" ref="K210:O210" si="192">RAND()</f>
-        <v>0.550742348553606</v>
+        <v>0.719580512499612</v>
       </c>
       <c r="L210" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.331588154315652</v>
+        <v>0.331641751266849</v>
       </c>
       <c r="M210" s="1">
         <f ca="1" t="shared" si="192"/>
-        <v>0.306320681218623</v>
+        <v>0.111746641237556</v>
       </c>
       <c r="N210" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.397714102636429</v>
+        <v>0.397705932892932</v>
       </c>
       <c r="O210" s="1">
         <f ca="1" t="shared" si="192"/>
-        <v>0.715305262310378</v>
+        <v>0.39808371918046</v>
       </c>
       <c r="P210" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.463969881358822</v>
+        <v>0.463861010996647</v>
       </c>
     </row>
     <row r="211" ht="16.5" spans="1:16">
@@ -16368,27 +16413,27 @@
       </c>
       <c r="K211" s="1">
         <f ca="1" t="shared" ref="K211:O211" si="193">RAND()</f>
-        <v>0.4861659972505</v>
+        <v>0.25035833463201</v>
       </c>
       <c r="L211" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.329981979739395</v>
+        <v>0.329907836523534</v>
       </c>
       <c r="M211" s="1">
         <f ca="1" t="shared" si="193"/>
-        <v>0.70600109260861</v>
+        <v>0.34273930221526</v>
       </c>
       <c r="N211" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.395918248025519</v>
+        <v>0.395729887158544</v>
       </c>
       <c r="O211" s="1">
         <f ca="1" t="shared" si="193"/>
-        <v>0.983029807052627</v>
+        <v>0.0052106986164393</v>
       </c>
       <c r="P211" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.461941620350362</v>
+        <v>0.461445811233297</v>
       </c>
     </row>
     <row r="212" ht="16.5" spans="1:16">
@@ -16428,27 +16473,27 @@
       </c>
       <c r="K212" s="1">
         <f ca="1" t="shared" ref="K212:O212" si="194">RAND()</f>
-        <v>0.529891055898046</v>
+        <v>0.27615228585865</v>
       </c>
       <c r="L212" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.328425016848824</v>
+        <v>0.328345991910288</v>
       </c>
       <c r="M212" s="1">
         <f ca="1" t="shared" si="194"/>
-        <v>0.747946084083151</v>
+        <v>0.406885333526143</v>
       </c>
       <c r="N212" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.394060802359101</v>
+        <v>0.393875556739957</v>
       </c>
       <c r="O212" s="1">
         <f ca="1" t="shared" si="194"/>
-        <v>0.528321268975306</v>
+        <v>0.208707453079767</v>
       </c>
       <c r="P212" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.459628187453027</v>
+        <v>0.459343400631912</v>
       </c>
     </row>
     <row r="213" ht="16.5" spans="1:16">
@@ -16488,27 +16533,27 @@
       </c>
       <c r="K213" s="1">
         <f ca="1" t="shared" ref="K213:O213" si="195">RAND()</f>
-        <v>0.997748504857988</v>
+        <v>0.56390408153769</v>
       </c>
       <c r="L213" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.327013523414268</v>
+        <v>0.326879680683297</v>
       </c>
       <c r="M213" s="1">
         <f ca="1" t="shared" si="195"/>
-        <v>0.980699435391032</v>
+        <v>0.966514611028662</v>
       </c>
       <c r="N213" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.39241041271518</v>
+        <v>0.392272193909448</v>
       </c>
       <c r="O213" s="1">
         <f ca="1" t="shared" si="195"/>
-        <v>0.40805155955586</v>
+        <v>0.937999774990549</v>
       </c>
       <c r="P213" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.457630637867686</v>
+        <v>0.457655910195213</v>
       </c>
     </row>
     <row r="214" ht="16.5" spans="1:16">
@@ -16548,27 +16593,27 @@
       </c>
       <c r="K214" s="1">
         <f ca="1" t="shared" ref="K214:O214" si="196">RAND()</f>
-        <v>0.942523366702454</v>
+        <v>0.16392037063422</v>
       </c>
       <c r="L214" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.325454132838615</v>
+        <v>0.32521618613506</v>
       </c>
       <c r="M214" s="1">
         <f ca="1" t="shared" si="196"/>
-        <v>0.832236386165199</v>
+        <v>0.704674272808766</v>
       </c>
       <c r="N214" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.390497202688227</v>
+        <v>0.390220272080776</v>
       </c>
       <c r="O214" s="1">
         <f ca="1" t="shared" si="196"/>
-        <v>0.999051831301258</v>
+        <v>0.313679626892458</v>
       </c>
       <c r="P214" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.45559125254366</v>
+        <v>0.455104867236483</v>
       </c>
     </row>
     <row r="215" ht="16.5" spans="1:16">
@@ -16608,27 +16653,27 @@
       </c>
       <c r="K215" s="1">
         <f ca="1" t="shared" ref="K215:O215" si="197">RAND()</f>
-        <v>0.638283735920454</v>
+        <v>0.0654882615009809</v>
       </c>
       <c r="L215" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.323834151980074</v>
+        <v>0.323660737528163</v>
       </c>
       <c r="M215" s="1">
         <f ca="1" t="shared" si="197"/>
-        <v>0.036854133112862</v>
+        <v>0.432142936233056</v>
       </c>
       <c r="N215" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.388331290917307</v>
+        <v>0.388277550579807</v>
       </c>
       <c r="O215" s="1">
         <f ca="1" t="shared" si="197"/>
-        <v>0.532310144595306</v>
+        <v>0.244102368864514</v>
       </c>
       <c r="P215" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.452978429700059</v>
+        <v>0.452837434145476</v>
       </c>
     </row>
     <row r="216" ht="16.5" spans="1:16">
@@ -16668,27 +16713,27 @@
       </c>
       <c r="K216" s="1">
         <f ca="1" t="shared" ref="K216:O216" si="198">RAND()</f>
-        <v>0.395666799584146</v>
+        <v>0.371300918011866</v>
       </c>
       <c r="L216" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.3222486459864</v>
+        <v>0.322241337810662</v>
       </c>
       <c r="M216" s="1">
         <f ca="1" t="shared" si="198"/>
-        <v>0.227479955011969</v>
+        <v>0.600557353393174</v>
       </c>
       <c r="N216" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.386502921652107</v>
+        <v>0.386607512370037</v>
       </c>
       <c r="O216" s="1">
         <f ca="1" t="shared" si="198"/>
-        <v>0.681742552569482</v>
+        <v>0.0236042785781794</v>
       </c>
       <c r="P216" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.450893446477698</v>
+        <v>0.450800638626163</v>
       </c>
     </row>
     <row r="217" ht="16.5" spans="1:16">
@@ -16728,27 +16773,27 @@
       </c>
       <c r="K217" s="1">
         <f ca="1" t="shared" ref="K217:O217" si="199">RAND()</f>
-        <v>0.831955336256854</v>
+        <v>0.603140263715487</v>
       </c>
       <c r="L217" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.320880296805348</v>
+        <v>0.320812302662345</v>
       </c>
       <c r="M217" s="1">
         <f ca="1" t="shared" si="199"/>
-        <v>0.746241564247315</v>
+        <v>0.784264974835464</v>
       </c>
       <c r="N217" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.384990937063458</v>
+        <v>0.384934241866753</v>
       </c>
       <c r="O217" s="1">
         <f ca="1" t="shared" si="199"/>
-        <v>0.376325307923883</v>
+        <v>0.857409209587314</v>
       </c>
       <c r="P217" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.448991653886226</v>
+        <v>0.449077916438078</v>
       </c>
     </row>
     <row r="218" ht="16.5" spans="1:16">
@@ -16788,27 +16833,27 @@
       </c>
       <c r="K218" s="1">
         <f ca="1" t="shared" ref="K218:O218" si="200">RAND()</f>
-        <v>0.0100525283003752</v>
+        <v>0.226462693747472</v>
       </c>
       <c r="L218" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.319152985255388</v>
+        <v>0.319216700485871</v>
       </c>
       <c r="M218" s="1">
         <f ca="1" t="shared" si="200"/>
-        <v>0.60711696492869</v>
+        <v>0.139472736181241</v>
       </c>
       <c r="N218" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.382926201975733</v>
+        <v>0.382852233933543</v>
       </c>
       <c r="O218" s="1">
         <f ca="1" t="shared" si="200"/>
-        <v>0.0541330827364073</v>
+        <v>0.995763849926964</v>
       </c>
       <c r="P218" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.446536609821393</v>
+        <v>0.44673987562003</v>
       </c>
     </row>
     <row r="219" ht="16.5" spans="1:16">
@@ -16848,27 +16893,27 @@
       </c>
       <c r="K219" s="1">
         <f ca="1" t="shared" ref="K219:O219" si="201">RAND()</f>
-        <v>0.394253275520156</v>
+        <v>0.169028406299876</v>
       </c>
       <c r="L219" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.317795643157362</v>
+        <v>0.317729941064705</v>
       </c>
       <c r="M219" s="1">
         <f ca="1" t="shared" si="201"/>
-        <v>0.950167498446092</v>
+        <v>0.532240514558225</v>
       </c>
       <c r="N219" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.38137557617809</v>
+        <v>0.381187957364982</v>
       </c>
       <c r="O219" s="1">
         <f ca="1" t="shared" si="201"/>
-        <v>0.86604565278638</v>
+        <v>0.696085829446348</v>
       </c>
       <c r="P219" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.444930969363066</v>
+        <v>0.444693770252277</v>
       </c>
     </row>
     <row r="220" ht="16.5" spans="1:16">
@@ -16908,27 +16953,27 @@
       </c>
       <c r="K220" s="1">
         <f ca="1" t="shared" ref="K220:O220" si="202">RAND()</f>
-        <v>0.553676556441572</v>
+        <v>0.831376922595128</v>
       </c>
       <c r="L220" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.31638475004145</v>
+        <v>0.316465020349625</v>
       </c>
       <c r="M220" s="1">
         <f ca="1" t="shared" si="202"/>
-        <v>0.606784403883391</v>
+        <v>0.196592719636962</v>
       </c>
       <c r="N220" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.379573841926448</v>
+        <v>0.379535544825579</v>
       </c>
       <c r="O220" s="1">
         <f ca="1" t="shared" si="202"/>
-        <v>0.432459578846994</v>
+        <v>0.954668393840736</v>
       </c>
       <c r="P220" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.442712544582141</v>
+        <v>0.442825193852327</v>
       </c>
     </row>
     <row r="221" ht="16.5" spans="1:16">
@@ -16968,27 +17013,27 @@
       </c>
       <c r="K221" s="1">
         <f ca="1" t="shared" ref="K221:O221" si="203">RAND()</f>
-        <v>0.774461181702793</v>
+        <v>0.536348133780935</v>
       </c>
       <c r="L221" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.315003892991023</v>
+        <v>0.314935691246289</v>
       </c>
       <c r="M221" s="1">
         <f ca="1" t="shared" si="203"/>
-        <v>0.322911428882823</v>
+        <v>0.968865678430854</v>
       </c>
       <c r="N221" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.377823655915859</v>
+        <v>0.37794047220026</v>
       </c>
       <c r="O221" s="1">
         <f ca="1" t="shared" si="203"/>
-        <v>0.276045847154802</v>
+        <v>0.0276769733107427</v>
       </c>
       <c r="P221" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.440629995324135</v>
+        <v>0.440675672329602</v>
       </c>
     </row>
     <row r="222" ht="16.5" spans="1:16">
@@ -17028,27 +17073,27 @@
       </c>
       <c r="K222" s="1">
         <f ca="1" t="shared" ref="K222:O222" si="204">RAND()</f>
-        <v>0.420775217644348</v>
+        <v>0.585715194146565</v>
       </c>
       <c r="L222" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.313471960057661</v>
+        <v>0.313518775600149</v>
       </c>
       <c r="M222" s="1">
         <f ca="1" t="shared" si="204"/>
-        <v>0.419250014609792</v>
+        <v>0.789270500063387</v>
       </c>
       <c r="N222" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.376034396302039</v>
+        <v>0.376186236169891</v>
       </c>
       <c r="O222" s="1">
         <f ca="1" t="shared" si="204"/>
-        <v>0.978999868039693</v>
+        <v>0.508205403512531</v>
       </c>
       <c r="P222" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.438755708481778</v>
+        <v>0.438773920961509</v>
       </c>
     </row>
     <row r="223" ht="16.5" spans="1:16">
@@ -17088,27 +17133,27 @@
       </c>
       <c r="K223" s="1">
         <f ca="1" t="shared" ref="K223:O223" si="205">RAND()</f>
-        <v>0.761977039687723</v>
+        <v>0.461430390897928</v>
       </c>
       <c r="L223" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.31215024424499</v>
+        <v>0.312065707459835</v>
       </c>
       <c r="M223" s="1">
         <f ca="1" t="shared" si="205"/>
-        <v>0.321632565643598</v>
+        <v>0.10428881651991</v>
       </c>
       <c r="N223" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.374402874170511</v>
+        <v>0.374257203641563</v>
       </c>
       <c r="O223" s="1">
         <f ca="1" t="shared" si="205"/>
-        <v>0.983026167722097</v>
+        <v>0.246479352465007</v>
       </c>
       <c r="P223" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.436841538740128</v>
+        <v>0.436488694715389</v>
       </c>
     </row>
     <row r="224" ht="16.5" spans="1:16">
@@ -17148,27 +17193,27 @@
       </c>
       <c r="K224" s="1">
         <f ca="1" t="shared" ref="K224:O224" si="206">RAND()</f>
-        <v>0.798856567382171</v>
+        <v>0.0260204782023221</v>
       </c>
       <c r="L224" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.310754741256209</v>
+        <v>0.310539310035131</v>
       </c>
       <c r="M224" s="1">
         <f ca="1" t="shared" si="206"/>
-        <v>0.0748691655748759</v>
+        <v>0.583624772643519</v>
       </c>
       <c r="N224" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.372659019414108</v>
+        <v>0.372585405899521</v>
       </c>
       <c r="O224" s="1">
         <f ca="1" t="shared" si="206"/>
-        <v>0.626764161441064</v>
+        <v>0.948443118517936</v>
       </c>
       <c r="P224" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.434717140559583</v>
+        <v>0.434733196370081</v>
       </c>
     </row>
     <row r="225" ht="16.5" spans="1:16">
@@ -17208,27 +17253,27 @@
       </c>
       <c r="K225" s="1">
         <f ca="1" t="shared" ref="K225:O225" si="207">RAND()</f>
-        <v>0.231105604408658</v>
+        <v>0.886584984947861</v>
       </c>
       <c r="L225" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.309204621583537</v>
+        <v>0.309385707735272</v>
       </c>
       <c r="M225" s="1">
         <f ca="1" t="shared" si="207"/>
-        <v>0.669133295199382</v>
+        <v>0.832583233124579</v>
       </c>
       <c r="N225" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.370996622694079</v>
+        <v>0.371222864377991</v>
       </c>
       <c r="O225" s="1">
         <f ca="1" t="shared" si="207"/>
-        <v>0.220115986905052</v>
+        <v>0.025800932752865</v>
       </c>
       <c r="P225" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.432664575941582</v>
+        <v>0.432837135135358</v>
       </c>
     </row>
     <row r="226" ht="16.5" spans="1:16">
@@ -17268,27 +17313,27 @@
       </c>
       <c r="K226" s="1">
         <f ca="1" t="shared" ref="K226:O226" si="208">RAND()</f>
-        <v>0.0300909758452035</v>
+        <v>0.648216614058283</v>
       </c>
       <c r="L226" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.307770143957671</v>
+        <v>0.307939392644325</v>
       </c>
       <c r="M226" s="1">
         <f ca="1" t="shared" si="208"/>
-        <v>0.469878095680439</v>
+        <v>0.505694209072633</v>
       </c>
       <c r="N226" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.369232134388632</v>
+        <v>0.369411189868238</v>
       </c>
       <c r="O226" s="1">
         <f ca="1" t="shared" si="208"/>
-        <v>0.677229337486455</v>
+        <v>0.722661253051593</v>
       </c>
       <c r="P226" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.430750899564372</v>
+        <v>0.430942394735145</v>
       </c>
     </row>
     <row r="227" ht="16.5" spans="1:16">
@@ -17328,27 +17373,27 @@
       </c>
       <c r="K227" s="1">
         <f ca="1" t="shared" ref="K227:O227" si="209">RAND()</f>
-        <v>0.700611082897131</v>
+        <v>0.107228967985044</v>
       </c>
       <c r="L227" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.306585416577069</v>
+        <v>0.306424380722875</v>
       </c>
       <c r="M227" s="1">
         <f ca="1" t="shared" si="209"/>
-        <v>0.628491276951554</v>
+        <v>0.468141257993287</v>
       </c>
       <c r="N227" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.367817927484088</v>
+        <v>0.36761337481059</v>
       </c>
       <c r="O227" s="1">
         <f ca="1" t="shared" si="209"/>
-        <v>0.984988696948224</v>
+        <v>0.564939361547621</v>
       </c>
       <c r="P227" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.429147186953467</v>
+        <v>0.428828638590125</v>
       </c>
     </row>
     <row r="228" ht="16.5" spans="1:16">
@@ -17388,27 +17433,27 @@
       </c>
       <c r="K228" s="1">
         <f ca="1" t="shared" ref="K228:O228" si="210">RAND()</f>
-        <v>0.0446972394726923</v>
+        <v>0.864962090827123</v>
       </c>
       <c r="L228" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.305052762502528</v>
+        <v>0.305273409942174</v>
       </c>
       <c r="M228" s="1">
         <f ca="1" t="shared" si="210"/>
-        <v>0.149123709996517</v>
+        <v>0.0261598138066412</v>
       </c>
       <c r="N228" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.365885827630553</v>
+        <v>0.366073398352577</v>
       </c>
       <c r="O228" s="1">
         <f ca="1" t="shared" si="210"/>
-        <v>0.35274247043393</v>
+        <v>0.268767304063206</v>
       </c>
       <c r="P228" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.426773665260509</v>
+        <v>0.426938647052357</v>
       </c>
     </row>
     <row r="229" ht="16.5" spans="1:16">
@@ -17448,27 +17493,27 @@
       </c>
       <c r="K229" s="1">
         <f ca="1" t="shared" ref="K229:O229" si="211">RAND()</f>
-        <v>0.150823361692953</v>
+        <v>0.0263147781720534</v>
       </c>
       <c r="L229" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.303738336857396</v>
+        <v>0.303705138417551</v>
       </c>
       <c r="M229" s="1">
         <f ca="1" t="shared" si="211"/>
-        <v>0.0202315499501364</v>
+        <v>0.431390612704121</v>
       </c>
       <c r="N229" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.364270047101412</v>
+        <v>0.364346478367611</v>
       </c>
       <c r="O229" s="1">
         <f ca="1" t="shared" si="211"/>
-        <v>0.486435804136223</v>
+        <v>0.381146934770554</v>
       </c>
       <c r="P229" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.424926064067504</v>
+        <v>0.424974421556804</v>
       </c>
     </row>
     <row r="230" ht="16.5" spans="1:16">
@@ -17508,27 +17553,27 @@
       </c>
       <c r="K230" s="1">
         <f ca="1" t="shared" ref="K230:O230" si="212">RAND()</f>
-        <v>0.906775729299257</v>
+        <v>0.0344062522916604</v>
       </c>
       <c r="L230" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.302606939114846</v>
+        <v>0.302376365706765</v>
       </c>
       <c r="M230" s="1">
         <f ca="1" t="shared" si="212"/>
-        <v>0.618268861694931</v>
+        <v>0.243048357277375</v>
       </c>
       <c r="N230" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.363032360671028</v>
+        <v>0.362702613836131</v>
       </c>
       <c r="O230" s="1">
         <f ca="1" t="shared" si="212"/>
-        <v>0.890217579298056</v>
+        <v>0.265116607967152</v>
       </c>
       <c r="P230" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.423529660192102</v>
+        <v>0.423034694759864</v>
       </c>
     </row>
     <row r="231" ht="16.5" spans="1:16">
@@ -17568,27 +17613,27 @@
       </c>
       <c r="K231" s="1">
         <f ca="1" t="shared" ref="K231:O231" si="213">RAND()</f>
-        <v>0.833896718921485</v>
+        <v>0.921332440314491</v>
       </c>
       <c r="L231" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.301266523157796</v>
+        <v>0.301289432080432</v>
       </c>
       <c r="M231" s="1">
         <f ca="1" t="shared" si="213"/>
-        <v>0.811711233800445</v>
+        <v>0.845811231217825</v>
       </c>
       <c r="N231" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.361479198590233</v>
+        <v>0.361511042010009</v>
       </c>
       <c r="O231" s="1">
         <f ca="1" t="shared" si="213"/>
-        <v>0.109856046807824</v>
+        <v>0.290410839635034</v>
       </c>
       <c r="P231" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.421507981833938</v>
+        <v>0.421587132186332</v>
       </c>
     </row>
     <row r="232" ht="16.5" spans="1:16">
@@ -17628,27 +17673,27 @@
       </c>
       <c r="K232" s="1">
         <f ca="1" t="shared" ref="K232:O232" si="214">RAND()</f>
-        <v>0.336441326683386</v>
+        <v>0.536272792034007</v>
       </c>
       <c r="L232" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.29982764709784</v>
+        <v>0.299879551374554</v>
       </c>
       <c r="M232" s="1">
         <f ca="1" t="shared" si="214"/>
-        <v>0.36480726420608</v>
+        <v>0.218087208093748</v>
       </c>
       <c r="N232" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.35966266197166</v>
+        <v>0.35967645714289</v>
       </c>
       <c r="O232" s="1">
         <f ca="1" t="shared" si="214"/>
-        <v>0.499484543074759</v>
+        <v>0.952127162937497</v>
       </c>
       <c r="P232" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.419532657956874</v>
+        <v>0.419664022639757</v>
       </c>
     </row>
     <row r="233" ht="16.5" spans="1:16">
@@ -17688,27 +17733,27 @@
       </c>
       <c r="K233" s="1">
         <f ca="1" t="shared" ref="K233:O233" si="215">RAND()</f>
-        <v>0.287223831984796</v>
+        <v>0.414380162535747</v>
       </c>
       <c r="L233" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.298517758040032</v>
+        <v>0.298550500937509</v>
       </c>
       <c r="M233" s="1">
         <f ca="1" t="shared" si="215"/>
-        <v>0.0865302187890895</v>
+        <v>0.464992788162022</v>
       </c>
       <c r="N233" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.358022798288936</v>
+        <v>0.358152995721743</v>
       </c>
       <c r="O233" s="1">
         <f ca="1" t="shared" si="215"/>
-        <v>0.408014148975218</v>
+        <v>0.607051376873059</v>
       </c>
       <c r="P233" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.417610621009788</v>
+        <v>0.417792070751614</v>
       </c>
     </row>
     <row r="234" ht="16.5" spans="1:16">
@@ -17748,27 +17793,27 @@
       </c>
       <c r="K234" s="1">
         <f ca="1" t="shared" ref="K234:O234" si="216">RAND()</f>
-        <v>0.147049287451102</v>
+        <v>0.688953187323924</v>
       </c>
       <c r="L234" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.297196042625552</v>
+        <v>0.297334385710839</v>
       </c>
       <c r="M234" s="1">
         <f ca="1" t="shared" si="216"/>
-        <v>0.611757093356053</v>
+        <v>0.536437889044449</v>
       </c>
       <c r="N234" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.35657968640031</v>
+        <v>0.356698801184955</v>
       </c>
       <c r="O234" s="1">
         <f ca="1" t="shared" si="216"/>
-        <v>0.738361806237173</v>
+        <v>0.132853375430662</v>
       </c>
       <c r="P234" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.41599565119471</v>
+        <v>0.415960185241876</v>
       </c>
     </row>
     <row r="235" ht="16.5" spans="1:16">
@@ -17808,27 +17853,27 @@
       </c>
       <c r="K235" s="1">
         <f ca="1" t="shared" ref="K235:O235" si="217">RAND()</f>
-        <v>0.638783766863796</v>
+        <v>0.336185692777904</v>
       </c>
       <c r="L235" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.296045912035191</v>
+        <v>0.295969321788642</v>
       </c>
       <c r="M235" s="1">
         <f ca="1" t="shared" si="217"/>
-        <v>0.124404005594118</v>
+        <v>0.0888378544709971</v>
       </c>
       <c r="N235" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.3550517587627</v>
+        <v>0.35496616640901</v>
       </c>
       <c r="O235" s="1">
         <f ca="1" t="shared" si="217"/>
-        <v>0.910064793815708</v>
+        <v>0.426185324856773</v>
       </c>
       <c r="P235" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.414256463178434</v>
+        <v>0.414048396655204</v>
       </c>
     </row>
     <row r="236" ht="16.5" spans="1:16">
@@ -17868,27 +17913,27 @@
       </c>
       <c r="K236" s="1">
         <f ca="1" t="shared" ref="K236:O236" si="218">RAND()</f>
-        <v>0.568020570822666</v>
+        <v>0.536058866002008</v>
       </c>
       <c r="L236" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.294763387595515</v>
+        <v>0.294755366654861</v>
       </c>
       <c r="M236" s="1">
         <f ca="1" t="shared" si="218"/>
-        <v>0.905877821667822</v>
+        <v>0.0623210435196502</v>
       </c>
       <c r="N236" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.353714126165055</v>
+        <v>0.353494410670147</v>
       </c>
       <c r="O236" s="1">
         <f ca="1" t="shared" si="218"/>
-        <v>0.546576067681081</v>
+        <v>0.102011999064976</v>
       </c>
       <c r="P236" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.412574696263873</v>
+        <v>0.412243415318031</v>
       </c>
     </row>
     <row r="237" ht="16.5" spans="1:16">
@@ -17928,27 +17973,27 @@
       </c>
       <c r="K237" s="1">
         <f ca="1" t="shared" ref="K237:O237" si="219">RAND()</f>
-        <v>0.34927649860456</v>
+        <v>0.613010743040954</v>
       </c>
       <c r="L237" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.293455103059516</v>
+        <v>0.293520727519906</v>
       </c>
       <c r="M237" s="1">
         <f ca="1" t="shared" si="219"/>
-        <v>0.346840268730516</v>
+        <v>0.1344959701893</v>
       </c>
       <c r="N237" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.352015982895587</v>
+        <v>0.352028770152229</v>
       </c>
       <c r="O237" s="1">
         <f ca="1" t="shared" si="219"/>
-        <v>0.330893034049986</v>
+        <v>0.0301518034617061</v>
       </c>
       <c r="P237" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.4105728946134</v>
+        <v>0.410510849035888</v>
       </c>
     </row>
     <row r="238" ht="16.5" spans="1:16">
@@ -17988,27 +18033,27 @@
       </c>
       <c r="K238" s="1">
         <f ca="1" t="shared" ref="K238:O238" si="220">RAND()</f>
-        <v>0.867223762776907</v>
+        <v>0.585281610338818</v>
       </c>
       <c r="L238" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.292340121717913</v>
+        <v>0.292270558646619</v>
       </c>
       <c r="M238" s="1">
         <f ca="1" t="shared" si="220"/>
-        <v>0.0930168128598778</v>
+        <v>0.3537116949395</v>
       </c>
       <c r="N238" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.350590919687188</v>
+        <v>0.350585677387057</v>
       </c>
       <c r="O238" s="1">
         <f ca="1" t="shared" si="220"/>
-        <v>0.771076097774389</v>
+        <v>0.982511915028191</v>
       </c>
       <c r="P238" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.409009013982927</v>
+        <v>0.409055938855043</v>
       </c>
     </row>
     <row r="239" ht="16.5" spans="1:16">
@@ -18048,27 +18093,27 @@
       </c>
       <c r="K239" s="1">
         <f ca="1" t="shared" ref="K239:O239" si="221">RAND()</f>
-        <v>0.406220048580975</v>
+        <v>0.514538467799113</v>
       </c>
       <c r="L239" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.290993969376846</v>
+        <v>0.291020470000631</v>
       </c>
       <c r="M239" s="1">
         <f ca="1" t="shared" si="221"/>
-        <v>0.792986797184213</v>
+        <v>0.370837292428377</v>
       </c>
       <c r="N239" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.349171170699421</v>
+        <v>0.349094390410437</v>
       </c>
       <c r="O239" s="1">
         <f ca="1" t="shared" si="221"/>
-        <v>0.12206338390002</v>
+        <v>0.68701079496842</v>
       </c>
       <c r="P239" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.407184227372431</v>
+        <v>0.407245664192846</v>
       </c>
     </row>
     <row r="240" ht="16.5" spans="1:16">
@@ -18108,27 +18153,27 @@
       </c>
       <c r="K240" s="1">
         <f ca="1" t="shared" ref="K240:O240" si="222">RAND()</f>
-        <v>0.0110990249708538</v>
+        <v>0.52618511219996</v>
       </c>
       <c r="L240" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.289676051590039</v>
+        <v>0.289801015339622</v>
       </c>
       <c r="M240" s="1">
         <f ca="1" t="shared" si="222"/>
-        <v>0.348566631379906</v>
+        <v>0.357478821428082</v>
       </c>
       <c r="N240" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.347501202244254</v>
+        <v>0.347628328158013</v>
       </c>
       <c r="O240" s="1">
         <f ca="1" t="shared" si="222"/>
-        <v>0.973689905200832</v>
+        <v>0.474022855444584</v>
       </c>
       <c r="P240" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.405478012495155</v>
+        <v>0.405483915433515</v>
       </c>
     </row>
     <row r="241" ht="16.5" spans="1:16">
@@ -18168,27 +18213,27 @@
       </c>
       <c r="K241" s="1">
         <f ca="1" t="shared" ref="K241:O241" si="223">RAND()</f>
-        <v>0.0173185034155154</v>
+        <v>0.655850910953628</v>
       </c>
       <c r="L241" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.288466509681784</v>
+        <v>0.288620131495313</v>
       </c>
       <c r="M241" s="1">
         <f ca="1" t="shared" si="223"/>
-        <v>0.893298838915957</v>
+        <v>0.36604907742889</v>
       </c>
       <c r="N241" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.34618142467441</v>
+        <v>0.346208197695949</v>
       </c>
       <c r="O241" s="1">
         <f ca="1" t="shared" si="223"/>
-        <v>0.0773380429672381</v>
+        <v>0.684277035933278</v>
       </c>
       <c r="P241" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.403700031107341</v>
+        <v>0.40387282501631</v>
       </c>
     </row>
     <row r="242" ht="16.5" spans="1:16">
@@ -18228,27 +18273,27 @@
       </c>
       <c r="K242" s="1">
         <f ca="1" t="shared" ref="K242:O242" si="224">RAND()</f>
-        <v>0.840275112902519</v>
+        <v>0.48762847925286</v>
       </c>
       <c r="L242" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.287461891365112</v>
+        <v>0.287377753682809</v>
       </c>
       <c r="M242" s="1">
         <f ca="1" t="shared" si="224"/>
-        <v>0.649739077775946</v>
+        <v>0.654126971982805</v>
       </c>
       <c r="N242" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.344878322887818</v>
+        <v>0.344795232109735</v>
       </c>
       <c r="O242" s="1">
         <f ca="1" t="shared" si="224"/>
-        <v>0.319350250293615</v>
+        <v>0.693825685833263</v>
       </c>
       <c r="P242" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.402215927200647</v>
+        <v>0.4022221822215</v>
       </c>
     </row>
     <row r="243" ht="16.5" spans="1:16">
@@ -18288,27 +18333,27 @@
       </c>
       <c r="K243" s="1">
         <f ca="1" t="shared" ref="K243:O243" si="225">RAND()</f>
-        <v>0.114140058042909</v>
+        <v>0.258150462258248</v>
       </c>
       <c r="L243" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.286097444065721</v>
+        <v>0.286131519433133</v>
       </c>
       <c r="M243" s="1">
         <f ca="1" t="shared" si="225"/>
-        <v>0.912381007661693</v>
+        <v>0.354686780519099</v>
       </c>
       <c r="N243" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.343338122675949</v>
+        <v>0.343240237885366</v>
       </c>
       <c r="O243" s="1">
         <f ca="1" t="shared" si="225"/>
-        <v>0.616999948888502</v>
+        <v>0.187215791700348</v>
       </c>
       <c r="P243" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.400508908988056</v>
+        <v>0.400309329787658</v>
       </c>
     </row>
     <row r="244" ht="16.5" spans="1:16">
@@ -18348,27 +18393,27 @@
       </c>
       <c r="K244" s="1">
         <f ca="1" t="shared" ref="K244:O244" si="226">RAND()</f>
-        <v>0.824970154923256</v>
+        <v>0.789072510631531</v>
       </c>
       <c r="L244" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.28508289270037</v>
+        <v>0.285074468602638</v>
       </c>
       <c r="M244" s="1">
         <f ca="1" t="shared" si="226"/>
-        <v>0.975285424975528</v>
+        <v>0.0960937769915082</v>
       </c>
       <c r="N244" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.342101886321168</v>
+        <v>0.341887142379505</v>
       </c>
       <c r="O244" s="1">
         <f ca="1" t="shared" si="226"/>
-        <v>0.427431848599158</v>
+        <v>0.0454960119861196</v>
       </c>
       <c r="P244" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.398992315180649</v>
+        <v>0.398687942382318</v>
       </c>
     </row>
     <row r="245" ht="16.5" spans="1:16">
@@ -18408,27 +18453,27 @@
       </c>
       <c r="K245" s="1">
         <f ca="1" t="shared" ref="K245:O245" si="227">RAND()</f>
-        <v>0.0838918489418703</v>
+        <v>0.206147827197239</v>
       </c>
       <c r="L245" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.283737396402809</v>
+        <v>0.283765851042557</v>
       </c>
       <c r="M245" s="1">
         <f ca="1" t="shared" si="227"/>
-        <v>0.741294480218761</v>
+        <v>0.935415814616671</v>
       </c>
       <c r="N245" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.340467307079241</v>
+        <v>0.340540942762211</v>
       </c>
       <c r="O245" s="1">
         <f ca="1" t="shared" si="227"/>
-        <v>0.548944991258956</v>
+        <v>0.148114403066006</v>
       </c>
       <c r="P245" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.397152449103113</v>
+        <v>0.39713279290662</v>
       </c>
     </row>
     <row r="246" ht="16.5" spans="1:16">
@@ -18468,27 +18513,27 @@
       </c>
       <c r="K246" s="1">
         <f ca="1" t="shared" ref="K246:O246" si="228">RAND()</f>
-        <v>0.349883012247402</v>
+        <v>0.326228846222527</v>
       </c>
       <c r="L246" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.282636808055687</v>
+        <v>0.282631347575742</v>
       </c>
       <c r="M246" s="1">
         <f ca="1" t="shared" si="228"/>
-        <v>0.00578607773989859</v>
+        <v>0.612704722409924</v>
       </c>
       <c r="N246" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.338964674363362</v>
+        <v>0.339099318890049</v>
       </c>
       <c r="O246" s="1">
         <f ca="1" t="shared" si="228"/>
-        <v>0.304344618303602</v>
+        <v>0.0400375133764375</v>
       </c>
       <c r="P246" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.395361461846343</v>
+        <v>0.3954350920196</v>
       </c>
     </row>
     <row r="247" ht="16.5" spans="1:16">
@@ -18528,27 +18573,27 @@
       </c>
       <c r="K247" s="1">
         <f ca="1" t="shared" ref="K247:O247" si="229">RAND()</f>
-        <v>0.362649427253528</v>
+        <v>0.885782580035614</v>
       </c>
       <c r="L247" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.281486719132174</v>
+        <v>0.281606500740078</v>
       </c>
       <c r="M247" s="1">
         <f ca="1" t="shared" si="229"/>
-        <v>0.605396899032993</v>
+        <v>0.152462336732524</v>
       </c>
       <c r="N247" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.337722897615775</v>
+        <v>0.33773897096153</v>
       </c>
       <c r="O247" s="1">
         <f ca="1" t="shared" si="229"/>
-        <v>0.300805235858932</v>
+        <v>0.997521856931633</v>
       </c>
       <c r="P247" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.393889333856938</v>
+        <v>0.394064934154257</v>
       </c>
     </row>
     <row r="248" ht="16.5" spans="1:16">
@@ -18588,27 +18633,27 @@
       </c>
       <c r="K248" s="1">
         <f ca="1" t="shared" ref="K248:O248" si="230">RAND()</f>
-        <v>0.240999468772418</v>
+        <v>0.671037188403177</v>
       </c>
       <c r="L248" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.280315423993105</v>
+        <v>0.280413092281359</v>
       </c>
       <c r="M248" s="1">
         <f ca="1" t="shared" si="230"/>
-        <v>0.2366800673309</v>
+        <v>0.158531247886185</v>
       </c>
       <c r="N248" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.336239623080185</v>
+        <v>0.336319542549962</v>
       </c>
       <c r="O248" s="1">
         <f ca="1" t="shared" si="230"/>
-        <v>0.394675125366877</v>
+        <v>0.96120452811019</v>
       </c>
       <c r="P248" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.392199705314642</v>
+        <v>0.392408292467475</v>
       </c>
     </row>
     <row r="249" ht="16.5" spans="1:16">
@@ -18648,27 +18693,27 @@
       </c>
       <c r="K249" s="1">
         <f ca="1" t="shared" ref="K249:O249" si="231">RAND()</f>
-        <v>0.628213935223277</v>
+        <v>0.961488270689439</v>
       </c>
       <c r="L249" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.279268469248826</v>
+        <v>0.279343550642149</v>
       </c>
       <c r="M249" s="1">
         <f ca="1" t="shared" si="231"/>
-        <v>0.615923795082514</v>
+        <v>0.525677256027214</v>
       </c>
       <c r="N249" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.335052388348541</v>
+        <v>0.335107138635704</v>
       </c>
       <c r="O249" s="1">
         <f ca="1" t="shared" si="231"/>
-        <v>0.534689000653609</v>
+        <v>0.799761817152766</v>
       </c>
       <c r="P249" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.390818006544457</v>
+        <v>0.390932473510275</v>
       </c>
     </row>
     <row r="250" ht="16.5" spans="1:16">
@@ -18708,27 +18753,27 @@
       </c>
       <c r="K250" s="1">
         <f ca="1" t="shared" ref="K250:O250" si="232">RAND()</f>
-        <v>0.0662795736837314</v>
+        <v>0.754723720143701</v>
       </c>
       <c r="L250" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.278017143705739</v>
+        <v>0.278170993446981</v>
       </c>
       <c r="M250" s="1">
         <f ca="1" t="shared" si="232"/>
-        <v>0.319573545282235</v>
+        <v>0.190350207498488</v>
       </c>
       <c r="N250" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.333510247004821</v>
+        <v>0.333635218619663</v>
       </c>
       <c r="O250" s="1">
         <f ca="1" t="shared" si="232"/>
-        <v>0.457910118915721</v>
+        <v>0.402815720720824</v>
       </c>
       <c r="P250" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.389034265006522</v>
+        <v>0.389146924425887</v>
       </c>
     </row>
     <row r="251" ht="16.5" spans="1:16">
@@ -18768,27 +18813,27 @@
       </c>
       <c r="K251" s="1">
         <f ca="1" t="shared" ref="K251:O251" si="233">RAND()</f>
-        <v>0.681364660828402</v>
+        <v>0.638841973827432</v>
       </c>
       <c r="L251" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.277037796503124</v>
+        <v>0.277028369786969</v>
       </c>
       <c r="M251" s="1">
         <f ca="1" t="shared" si="233"/>
-        <v>0.230879366202023</v>
+        <v>0.481040737917155</v>
       </c>
       <c r="N251" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.332288979398764</v>
+        <v>0.332335010143327</v>
       </c>
       <c r="O251" s="1">
         <f ca="1" t="shared" si="233"/>
-        <v>0.719722688219514</v>
+        <v>0.705171859947073</v>
       </c>
       <c r="P251" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.387648532380248</v>
+        <v>0.387691337399026</v>
       </c>
     </row>
     <row r="252" ht="16.5" spans="1:16">
@@ -18828,27 +18873,27 @@
       </c>
       <c r="K252" s="1">
         <f ca="1" t="shared" ref="K252:O252" si="234">RAND()</f>
-        <v>0.996196925063059</v>
+        <v>0.330460506003101</v>
       </c>
       <c r="L252" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.275999163626548</v>
+        <v>0.275852754661081</v>
       </c>
       <c r="M252" s="1">
         <f ca="1" t="shared" si="234"/>
-        <v>0.63098849170334</v>
+        <v>0.139338771053014</v>
       </c>
       <c r="N252" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.33111801049803</v>
+        <v>0.330863477769297</v>
       </c>
       <c r="O252" s="1">
         <f ca="1" t="shared" si="234"/>
-        <v>0.484241114713412</v>
+        <v>0.04614219329516</v>
       </c>
       <c r="P252" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.386204584639592</v>
+        <v>0.385853705056428</v>
       </c>
     </row>
     <row r="253" ht="16.5" spans="1:16">
@@ -18888,27 +18933,27 @@
       </c>
       <c r="K253" s="1">
         <f ca="1" t="shared" ref="K253:O253" si="235">RAND()</f>
-        <v>0.955555724314511</v>
+        <v>0.84568970867451</v>
       </c>
       <c r="L253" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.274890701780111</v>
+        <v>0.274866731771007</v>
       </c>
       <c r="M253" s="1">
         <f ca="1" t="shared" si="235"/>
-        <v>0.681631711825288</v>
+        <v>0.437084121262731</v>
       </c>
       <c r="N253" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.329801321485783</v>
+        <v>0.329723997325826</v>
       </c>
       <c r="O253" s="1">
         <f ca="1" t="shared" si="235"/>
-        <v>0.484504671089492</v>
+        <v>0.881750572557898</v>
       </c>
       <c r="P253" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.384668933015237</v>
+        <v>0.384678277947803</v>
       </c>
     </row>
     <row r="254" ht="16.5" spans="1:16">
@@ -18948,27 +18993,27 @@
       </c>
       <c r="K254" s="1">
         <f ca="1" t="shared" ref="K254:O254" si="236">RAND()</f>
-        <v>0.131219047366234</v>
+        <v>0.537085490551956</v>
       </c>
       <c r="L254" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.273621475984278</v>
+        <v>0.273709325863756</v>
       </c>
       <c r="M254" s="1">
         <f ca="1" t="shared" si="236"/>
-        <v>0.550206110661693</v>
+        <v>0.791038326228115</v>
       </c>
       <c r="N254" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.328286022761478</v>
+        <v>0.328426000826143</v>
       </c>
       <c r="O254" s="1">
         <f ca="1" t="shared" si="236"/>
-        <v>0.337377734915428</v>
+        <v>0.329907411803292</v>
       </c>
       <c r="P254" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.38290450279068</v>
+        <v>0.383042863902291</v>
       </c>
     </row>
     <row r="255" ht="16.5" spans="1:16">
@@ -19008,27 +19053,27 @@
       </c>
       <c r="K255" s="1">
         <f ca="1" t="shared" ref="K255:O255" si="237">RAND()</f>
-        <v>0.25647781924315</v>
+        <v>0.277484231678879</v>
       </c>
       <c r="L255" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.272567604399265</v>
+        <v>0.272572115439874</v>
       </c>
       <c r="M255" s="1">
         <f ca="1" t="shared" si="237"/>
-        <v>0.224133534686379</v>
+        <v>0.685821510739683</v>
       </c>
       <c r="N255" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.326946444814731</v>
+        <v>0.327050101447906</v>
       </c>
       <c r="O255" s="1">
         <f ca="1" t="shared" si="237"/>
-        <v>0.37672016838505</v>
+        <v>0.69319032401376</v>
       </c>
       <c r="P255" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.381358052581742</v>
+        <v>0.38152966987826</v>
       </c>
     </row>
     <row r="256" ht="16.5" spans="1:16">
@@ -19068,27 +19113,27 @@
       </c>
       <c r="K256" s="1">
         <f ca="1" t="shared" ref="K256:O256" si="238">RAND()</f>
-        <v>0.501577683452229</v>
+        <v>0.839402236621761</v>
       </c>
       <c r="L256" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.271547348649554</v>
+        <v>0.271619326090248</v>
       </c>
       <c r="M256" s="1">
         <f ca="1" t="shared" si="238"/>
-        <v>0.87905392511647</v>
+        <v>0.260861149071828</v>
       </c>
       <c r="N256" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.325852288346429</v>
+        <v>0.325792552643547</v>
       </c>
       <c r="O256" s="1">
         <f ca="1" t="shared" si="238"/>
-        <v>0.260046430067808</v>
+        <v>0.437951812939597</v>
       </c>
       <c r="P256" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.380025341314392</v>
+        <v>0.380003510417495</v>
       </c>
     </row>
     <row r="257" ht="16.5" spans="1:16">
@@ -19128,27 +19173,27 @@
       </c>
       <c r="K257" s="1">
         <f ca="1" t="shared" ref="K257:O257" si="239">RAND()</f>
-        <v>0.934045366600827</v>
+        <v>0.925468584102654</v>
       </c>
       <c r="L257" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.270574292678601</v>
+        <v>0.270572479572007</v>
       </c>
       <c r="M257" s="1">
         <f ca="1" t="shared" si="239"/>
-        <v>0.992099211302455</v>
+        <v>0.558932000612047</v>
       </c>
       <c r="N257" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.324690269533932</v>
+        <v>0.324596886153019</v>
       </c>
       <c r="O257" s="1">
         <f ca="1" t="shared" si="239"/>
-        <v>0.95094558161881</v>
+        <v>0.994917102161162</v>
       </c>
       <c r="P257" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.378797546632987</v>
+        <v>0.378713458702189</v>
       </c>
     </row>
     <row r="258" ht="16.5" spans="1:16">
@@ -19188,27 +19233,27 @@
       </c>
       <c r="K258" s="1">
         <f ca="1" t="shared" ref="K258:O258" si="243">RAND()</f>
-        <v>0.579824210004098</v>
+        <v>0.491247057072529</v>
       </c>
       <c r="L258" s="1">
         <f ca="1" t="shared" ref="L258:L302" si="244">J258+($R$1*$R$7*K258/MAX(1,($A258*($A258-1)))+$R$1*$R$7/$A258)/100</f>
-        <v>0.269443117310586</v>
+        <v>0.269424538080429</v>
       </c>
       <c r="M258" s="1">
         <f ca="1" t="shared" si="243"/>
-        <v>0.126248450206202</v>
+        <v>0.508946056200216</v>
       </c>
       <c r="N258" s="1">
         <f ca="1" t="shared" ref="N258:N302" si="245">L258+($R$1*$R$7*M258/MAX(1,($A258*($A258-1)))+$R$1*$R$7/$A258)/100</f>
-        <v>0.323166096223111</v>
+        <v>0.323227788560359</v>
       </c>
       <c r="O258" s="1">
         <f ca="1" t="shared" si="243"/>
-        <v>0.697183036716332</v>
+        <v>0.28683124810176</v>
       </c>
       <c r="P258" s="1">
         <f ca="1" t="shared" ref="P258:P302" si="246">N258+($R$1*$R$7*O258/MAX(1,($A258*($A258-1)))+$R$1*$R$7/$A258)/100</f>
-        <v>0.377008829775924</v>
+        <v>0.376984450027161</v>
       </c>
     </row>
     <row r="259" ht="16.5" spans="1:16">
@@ -19248,27 +19293,27 @@
       </c>
       <c r="K259" s="1">
         <f ca="1" t="shared" ref="K259:O259" si="248">RAND()</f>
-        <v>0.186708383497262</v>
+        <v>0.267545950406828</v>
       </c>
       <c r="L259" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.268313223172749</v>
+        <v>0.268330047569083</v>
       </c>
       <c r="M259" s="1">
         <f ca="1" t="shared" si="248"/>
-        <v>0.921599715163699</v>
+        <v>0.635772850738634</v>
       </c>
       <c r="N259" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.321993404092564</v>
+        <v>0.321950740497931</v>
       </c>
       <c r="O259" s="1">
         <f ca="1" t="shared" si="248"/>
-        <v>0.793267063320925</v>
+        <v>0.571677605360809</v>
       </c>
       <c r="P259" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.375646875655828</v>
+        <v>0.37555809354221</v>
       </c>
     </row>
     <row r="260" ht="16.5" spans="1:16">
@@ -19308,27 +19353,27 @@
       </c>
       <c r="K260" s="1">
         <f ca="1" t="shared" ref="K260:O260" si="249">RAND()</f>
-        <v>0.149458825911911</v>
+        <v>0.865855998907701</v>
       </c>
       <c r="L260" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.267266207712992</v>
+        <v>0.267414157205485</v>
       </c>
       <c r="M260" s="1">
         <f ca="1" t="shared" si="249"/>
-        <v>0.588911182623035</v>
+        <v>0.63945689712348</v>
       </c>
       <c r="N260" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.320669682232166</v>
+        <v>0.320828070365527</v>
       </c>
       <c r="O260" s="1">
         <f ca="1" t="shared" si="249"/>
-        <v>0.953513248616648</v>
+        <v>0.0418663284029013</v>
       </c>
       <c r="P260" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.374148453936558</v>
+        <v>0.37411856983175</v>
       </c>
     </row>
     <row r="261" ht="16.5" spans="1:16">
@@ -19368,27 +19413,27 @@
       </c>
       <c r="K261" s="1">
         <f ca="1" t="shared" ref="K261:O261" si="250">RAND()</f>
-        <v>0.979871400414442</v>
+        <v>0.61448113946991</v>
       </c>
       <c r="L261" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.266405141451228</v>
+        <v>0.266330261950173</v>
       </c>
       <c r="M261" s="1">
         <f ca="1" t="shared" si="250"/>
-        <v>0.0574743976763481</v>
+        <v>0.998456361884895</v>
       </c>
       <c r="N261" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.319493842768245</v>
+        <v>0.319611798893951</v>
       </c>
       <c r="O261" s="1">
         <f ca="1" t="shared" si="250"/>
-        <v>0.271301016210044</v>
+        <v>0.602556991556013</v>
       </c>
       <c r="P261" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.372626363618018</v>
+        <v>0.372812204098636</v>
       </c>
     </row>
     <row r="262" ht="16.5" spans="1:16">
@@ -19428,27 +19473,27 @@
       </c>
       <c r="K262" s="1">
         <f ca="1" t="shared" ref="K262:O262" si="251">RAND()</f>
-        <v>0.557251395487248</v>
+        <v>0.415215724056521</v>
       </c>
       <c r="L262" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.265294578091036</v>
+        <v>0.265265693736987</v>
       </c>
       <c r="M262" s="1">
         <f ca="1" t="shared" si="251"/>
-        <v>0.179094734905581</v>
+        <v>0.632596541819085</v>
       </c>
       <c r="N262" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.318204561989381</v>
+        <v>0.31826790169863</v>
       </c>
       <c r="O262" s="1">
         <f ca="1" t="shared" si="251"/>
-        <v>0.0563182059771679</v>
+        <v>0.646216495410187</v>
       </c>
       <c r="P262" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.371089578070172</v>
+        <v>0.371272879412109</v>
       </c>
     </row>
     <row r="263" ht="16.5" spans="1:16">
@@ -19488,27 +19533,27 @@
       </c>
       <c r="K263" s="1">
         <f ca="1" t="shared" ref="K263:O263" si="252">RAND()</f>
-        <v>0.720231325021224</v>
+        <v>0.590473697045564</v>
       </c>
       <c r="L263" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.26431135667698</v>
+        <v>0.264285170615355</v>
       </c>
       <c r="M263" s="1">
         <f ca="1" t="shared" si="252"/>
-        <v>0.673166327916454</v>
+        <v>0.72681804223248</v>
       </c>
       <c r="N263" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.317118962411315</v>
+        <v>0.317103603667661</v>
       </c>
       <c r="O263" s="1">
         <f ca="1" t="shared" si="252"/>
-        <v>0.0135726578882258</v>
+        <v>0.548126193339316</v>
       </c>
       <c r="P263" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.36979345720057</v>
+        <v>0.369885975365887</v>
       </c>
     </row>
     <row r="264" ht="16.5" spans="1:16">
@@ -19548,27 +19593,27 @@
       </c>
       <c r="K264" s="1">
         <f ca="1" t="shared" ref="K264:O264" si="253">RAND()</f>
-        <v>0.807796544305334</v>
+        <v>0.327435294388643</v>
       </c>
       <c r="L264" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.263320285494897</v>
+        <v>0.263224082185333</v>
       </c>
       <c r="M264" s="1">
         <f ca="1" t="shared" si="253"/>
-        <v>0.872136391369429</v>
+        <v>0.748216207239837</v>
       </c>
       <c r="N264" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.315966433612636</v>
+        <v>0.315845412456425</v>
       </c>
       <c r="O264" s="1">
         <f ca="1" t="shared" si="253"/>
-        <v>0.0976041751720487</v>
+        <v>0.356216436697158</v>
       </c>
       <c r="P264" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.368457463967284</v>
+        <v>0.368388235821973</v>
       </c>
     </row>
     <row r="265" ht="16.5" spans="1:16">
@@ -19608,27 +19653,27 @@
       </c>
       <c r="K265" s="1">
         <f ca="1" t="shared" ref="K265:O265" si="254">RAND()</f>
-        <v>0.273338955262583</v>
+        <v>0.839026600084055</v>
       </c>
       <c r="L265" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.262212986484367</v>
+        <v>0.262325420081247</v>
       </c>
       <c r="M265" s="1">
         <f ca="1" t="shared" si="254"/>
-        <v>0.294867573859914</v>
+        <v>0.808901140170524</v>
       </c>
       <c r="N265" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.314544320343672</v>
+        <v>0.314758920999186</v>
       </c>
       <c r="O265" s="1">
         <f ca="1" t="shared" si="254"/>
-        <v>0.513882796780893</v>
+        <v>0.389664018417168</v>
       </c>
       <c r="P265" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.366919184708743</v>
+        <v>0.367109096184319</v>
       </c>
     </row>
     <row r="266" ht="16.5" spans="1:16">
@@ -19668,27 +19713,27 @@
       </c>
       <c r="K266" s="1">
         <f ca="1" t="shared" ref="K266:O266" si="255">RAND()</f>
-        <v>0.703916881418029</v>
+        <v>0.749450763681398</v>
       </c>
       <c r="L266" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.261305232317947</v>
+        <v>0.261314214130057</v>
       </c>
       <c r="M266" s="1">
         <f ca="1" t="shared" si="255"/>
-        <v>0.553228776972704</v>
+        <v>0.826342436439061</v>
       </c>
       <c r="N266" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.313489831476355</v>
+        <v>0.313552686480298</v>
       </c>
       <c r="O266" s="1">
         <f ca="1" t="shared" si="255"/>
-        <v>0.498762177222888</v>
+        <v>0.00112691166388346</v>
       </c>
       <c r="P266" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.365663686794332</v>
+        <v>0.365628380468019</v>
       </c>
     </row>
     <row r="267" ht="16.5" spans="1:16">
@@ -19728,27 +19773,27 @@
       </c>
       <c r="K267" s="1">
         <f ca="1" t="shared" ref="K267:O267" si="256">RAND()</f>
-        <v>0.00225310003717039</v>
+        <v>0.123001549337078</v>
       </c>
       <c r="L267" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.260182027135488</v>
+        <v>0.26020566635524</v>
       </c>
       <c r="M267" s="1">
         <f ca="1" t="shared" si="256"/>
-        <v>0.825357173157125</v>
+        <v>0.570235066836323</v>
       </c>
       <c r="N267" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.312223308579516</v>
+        <v>0.312197001919467</v>
       </c>
       <c r="O267" s="1">
         <f ca="1" t="shared" si="256"/>
-        <v>0.125265019970923</v>
+        <v>0.517076915431808</v>
       </c>
       <c r="P267" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.364127531267495</v>
+        <v>0.364177930582156</v>
       </c>
     </row>
     <row r="268" ht="16.5" spans="1:16">
@@ -19788,27 +19833,27 @@
       </c>
       <c r="K268" s="1">
         <f ca="1" t="shared" ref="K268:O268" si="257">RAND()</f>
-        <v>0.0136014580818713</v>
+        <v>0.590131029042013</v>
       </c>
       <c r="L268" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.259206833095682</v>
+        <v>0.259318856244555</v>
       </c>
       <c r="M268" s="1">
         <f ca="1" t="shared" si="257"/>
-        <v>0.283042971051224</v>
+        <v>0.408845976824684</v>
       </c>
       <c r="N268" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.310947223298725</v>
+        <v>0.311083690725141</v>
       </c>
       <c r="O268" s="1">
         <f ca="1" t="shared" si="257"/>
-        <v>0.136808936603895</v>
+        <v>0.486517890943784</v>
       </c>
       <c r="P268" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.362659199352977</v>
+        <v>0.362863617323871</v>
       </c>
     </row>
     <row r="269" ht="16.5" spans="1:16">
@@ -19848,27 +19893,27 @@
       </c>
       <c r="K269" s="1">
         <f ca="1" t="shared" ref="K269:O269" si="258">RAND()</f>
-        <v>0.625238979114183</v>
+        <v>0.721374083132929</v>
       </c>
       <c r="L269" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.258354691401305</v>
+        <v>0.258373231627638</v>
       </c>
       <c r="M269" s="1">
         <f ca="1" t="shared" si="258"/>
-        <v>0.158713857800223</v>
+        <v>0.471807158093504</v>
       </c>
       <c r="N269" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.309877837625768</v>
+        <v>0.3099567597564</v>
       </c>
       <c r="O269" s="1">
         <f ca="1" t="shared" si="258"/>
-        <v>0.161010280144399</v>
+        <v>0.923326944236778</v>
       </c>
       <c r="P269" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.361401426728931</v>
+        <v>0.361627366160202</v>
       </c>
     </row>
     <row r="270" ht="16.5" spans="1:16">
@@ -19908,27 +19953,27 @@
       </c>
       <c r="K270" s="1">
         <f ca="1" t="shared" ref="K270:O270" si="259">RAND()</f>
-        <v>0.201674633980013</v>
+        <v>0.978395533624806</v>
       </c>
       <c r="L270" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.257309869471632</v>
+        <v>0.25745855099545</v>
       </c>
       <c r="M270" s="1">
         <f ca="1" t="shared" si="259"/>
-        <v>0.470368601908546</v>
+        <v>0.168892667205693</v>
       </c>
       <c r="N270" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.308701023645553</v>
+        <v>0.308791996021354</v>
       </c>
       <c r="O270" s="1">
         <f ca="1" t="shared" si="259"/>
-        <v>0.0959805609922393</v>
+        <v>0.614443812400499</v>
       </c>
       <c r="P270" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.360020511685027</v>
+        <v>0.360210729370562</v>
       </c>
     </row>
     <row r="271" ht="16.5" spans="1:16">
@@ -19968,27 +20013,27 @@
       </c>
       <c r="K271" s="1">
         <f ca="1" t="shared" ref="K271:O271" si="260">RAND()</f>
-        <v>0.724437448191209</v>
+        <v>0.789118168708264</v>
       </c>
       <c r="L271" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.256453218185117</v>
+        <v>0.256465507789181</v>
       </c>
       <c r="M271" s="1">
         <f ca="1" t="shared" si="260"/>
-        <v>0.402061780766563</v>
+        <v>0.907794733950388</v>
       </c>
       <c r="N271" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.3076407226953</v>
+        <v>0.307749103649411</v>
       </c>
       <c r="O271" s="1">
         <f ca="1" t="shared" si="260"/>
-        <v>0.378457263318318</v>
+        <v>0.731112834466138</v>
       </c>
       <c r="P271" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.358823742249669</v>
+        <v>0.35899912921895</v>
       </c>
     </row>
     <row r="272" ht="16.5" spans="1:16">
@@ -20028,27 +20073,27 @@
       </c>
       <c r="K272" s="1">
         <f ca="1" t="shared" ref="K272:O272" si="261">RAND()</f>
-        <v>0.152957602560751</v>
+        <v>0.489321822787572</v>
       </c>
       <c r="L272" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.25539580176186</v>
+        <v>0.255459240688184</v>
       </c>
       <c r="M272" s="1">
         <f ca="1" t="shared" si="261"/>
-        <v>0.243451273703929</v>
+        <v>0.326072545038649</v>
       </c>
       <c r="N272" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.306364226356327</v>
+        <v>0.30644324781025</v>
       </c>
       <c r="O272" s="1">
         <f ca="1" t="shared" si="261"/>
-        <v>0.422511030977244</v>
+        <v>0.814314885667792</v>
       </c>
       <c r="P272" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.357366421958725</v>
+        <v>0.357519338358592</v>
       </c>
     </row>
     <row r="273" ht="16.5" spans="1:16">
@@ -20088,27 +20133,27 @@
       </c>
       <c r="K273" s="1">
         <f ca="1" t="shared" ref="K273:O273" si="262">RAND()</f>
-        <v>0.873404800289203</v>
+        <v>0.560694004174665</v>
       </c>
       <c r="L273" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.254588845591545</v>
+        <v>0.254530301406251</v>
       </c>
       <c r="M273" s="1">
         <f ca="1" t="shared" si="262"/>
-        <v>0.771099476549105</v>
+        <v>0.515450636149698</v>
       </c>
       <c r="N273" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.305468501180545</v>
+        <v>0.305362095670128</v>
       </c>
       <c r="O273" s="1">
         <f ca="1" t="shared" si="262"/>
-        <v>0.213036392649651</v>
+        <v>0.0340174250466927</v>
       </c>
       <c r="P273" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.356243678929332</v>
+        <v>0.35610375836366</v>
       </c>
     </row>
     <row r="274" ht="16.5" spans="1:16">
@@ -20148,27 +20193,27 @@
       </c>
       <c r="K274" s="1">
         <f ca="1" t="shared" ref="K274:O274" si="263">RAND()</f>
-        <v>0.634839084026446</v>
+        <v>0.65388866961432</v>
       </c>
       <c r="L274" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.253608607780645</v>
+        <v>0.253612148023603</v>
       </c>
       <c r="M274" s="1">
         <f ca="1" t="shared" si="263"/>
-        <v>0.206123348936466</v>
+        <v>0.0360377339450815</v>
       </c>
       <c r="N274" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.30419636502875</v>
+        <v>0.30416829595412</v>
       </c>
       <c r="O274" s="1">
         <f ca="1" t="shared" si="263"/>
-        <v>0.346533158878773</v>
+        <v>0.450365876053852</v>
       </c>
       <c r="P274" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.354810216536945</v>
+        <v>0.35480144410497</v>
       </c>
     </row>
     <row r="275" ht="16.5" spans="1:16">
@@ -20208,27 +20253,27 @@
       </c>
       <c r="K275" s="1">
         <f ca="1" t="shared" ref="K275:O275" si="264">RAND()</f>
-        <v>0.371031745674756</v>
+        <v>0.275387531492072</v>
       </c>
       <c r="L275" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.25263121625211</v>
+        <v>0.252613571133587</v>
       </c>
       <c r="M275" s="1">
         <f ca="1" t="shared" si="264"/>
-        <v>0.812300399077382</v>
+        <v>0.845106764092639</v>
       </c>
       <c r="N275" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.303146038656688</v>
+        <v>0.30313444588753</v>
       </c>
       <c r="O275" s="1">
         <f ca="1" t="shared" si="264"/>
-        <v>0.821133971505535</v>
+        <v>0.913907022922097</v>
       </c>
       <c r="P275" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.353662490740947</v>
+        <v>0.353668013397976</v>
       </c>
     </row>
     <row r="276" ht="16.5" spans="1:16">
@@ -20268,27 +20313,27 @@
       </c>
       <c r="K276" s="1">
         <f ca="1" t="shared" ref="K276:O276" si="265">RAND()</f>
-        <v>0.955419339257545</v>
+        <v>0.817846803767968</v>
       </c>
       <c r="L276" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.25181665277879</v>
+        <v>0.251791457012502</v>
       </c>
       <c r="M276" s="1">
         <f ca="1" t="shared" si="265"/>
-        <v>0.211741367210911</v>
+        <v>0.61112440840095</v>
       </c>
       <c r="N276" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.302037250401451</v>
+        <v>0.302085199770776</v>
       </c>
       <c r="O276" s="1">
         <f ca="1" t="shared" si="265"/>
-        <v>0.799842947962585</v>
+        <v>0.276972000054781</v>
       </c>
       <c r="P276" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.352365556077388</v>
+        <v>0.352317744078682</v>
       </c>
     </row>
     <row r="277" ht="16.5" spans="1:16">
@@ -20328,27 +20373,27 @@
       </c>
       <c r="K277" s="1">
         <f ca="1" t="shared" ref="K277:O277" si="266">RAND()</f>
-        <v>0.0738700835167625</v>
+        <v>0.270088548426555</v>
       </c>
       <c r="L277" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.250740703651549</v>
+        <v>0.250776379736078</v>
       </c>
       <c r="M277" s="1">
         <f ca="1" t="shared" si="266"/>
-        <v>0.22615432455578</v>
+        <v>0.375916997735328</v>
       </c>
       <c r="N277" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.30078182261965</v>
+        <v>0.300844728281121</v>
       </c>
       <c r="O277" s="1">
         <f ca="1" t="shared" si="266"/>
-        <v>0.892580368657694</v>
+        <v>0.675034862378851</v>
       </c>
       <c r="P277" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.350944109959406</v>
+        <v>0.350967461892462</v>
       </c>
     </row>
     <row r="278" ht="16.5" spans="1:16">
@@ -20388,27 +20433,27 @@
       </c>
       <c r="K278" s="1">
         <f ca="1" t="shared" ref="K278:O278" si="267">RAND()</f>
-        <v>0.601095976030627</v>
+        <v>0.331960196254539</v>
       </c>
       <c r="L278" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.249927995663543</v>
+        <v>0.24987941519788</v>
       </c>
       <c r="M278" s="1">
         <f ca="1" t="shared" si="267"/>
-        <v>0.925748013653593</v>
+        <v>0.0255380193144072</v>
       </c>
       <c r="N278" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.299914592777921</v>
+        <v>0.299703519533496</v>
       </c>
       <c r="O278" s="1">
         <f ca="1" t="shared" si="267"/>
-        <v>0.410874798968545</v>
+        <v>0.913795320421845</v>
       </c>
       <c r="P278" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.349808252488927</v>
+        <v>0.34968795912202</v>
       </c>
     </row>
     <row r="279" ht="16.5" spans="1:16">
@@ -20448,27 +20493,27 @@
       </c>
       <c r="K279" s="1">
         <f ca="1" t="shared" ref="K279:O279" si="268">RAND()</f>
-        <v>0.281866106175279</v>
+        <v>0.00635072312231055</v>
       </c>
       <c r="L279" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.248968778436293</v>
+        <v>0.248919404201998</v>
       </c>
       <c r="M279" s="1">
         <f ca="1" t="shared" si="268"/>
-        <v>0.834526050494494</v>
+        <v>0.364110852832682</v>
       </c>
       <c r="N279" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.298758618961666</v>
+        <v>0.298624943118045</v>
       </c>
       <c r="O279" s="1">
         <f ca="1" t="shared" si="268"/>
-        <v>0.0681341090793837</v>
+        <v>0.337084291621872</v>
       </c>
       <c r="P279" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.348411116828135</v>
+        <v>0.348325638690135</v>
       </c>
     </row>
     <row r="280" ht="16.5" spans="1:16">
@@ -20508,27 +20553,27 @@
       </c>
       <c r="K280" s="1">
         <f ca="1" t="shared" ref="K280:O280" si="269">RAND()</f>
-        <v>0.255077571542631</v>
+        <v>0.490768307988678</v>
       </c>
       <c r="L280" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.248068900627721</v>
+        <v>0.248110835236975</v>
       </c>
       <c r="M280" s="1">
         <f ca="1" t="shared" si="269"/>
-        <v>0.683836192990601</v>
+        <v>0.463876365036416</v>
       </c>
       <c r="N280" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.297652935844235</v>
+        <v>0.297655734721742</v>
       </c>
       <c r="O280" s="1">
         <f ca="1" t="shared" si="269"/>
-        <v>0.157027201321951</v>
+        <v>0.25375637580592</v>
       </c>
       <c r="P280" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.347143240057358</v>
+        <v>0.347163249200303</v>
       </c>
     </row>
     <row r="281" ht="16.5" spans="1:16">
@@ -20568,27 +20613,27 @@
       </c>
       <c r="K281" s="1">
         <f ca="1" t="shared" ref="K281:O281" si="270">RAND()</f>
-        <v>0.324581831249612</v>
+        <v>0.808032882253953</v>
       </c>
       <c r="L281" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.247192514455597</v>
+        <v>0.247277916714991</v>
       </c>
       <c r="M281" s="1">
         <f ca="1" t="shared" si="270"/>
-        <v>0.313226652802177</v>
+        <v>0.310084986548145</v>
       </c>
       <c r="N281" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.296533560638503</v>
+        <v>0.296618407918452</v>
       </c>
       <c r="O281" s="1">
         <f ca="1" t="shared" si="270"/>
-        <v>0.637976256850621</v>
+        <v>0.576466602678682</v>
       </c>
       <c r="P281" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.345931974262985</v>
+        <v>0.346005955782212</v>
       </c>
     </row>
     <row r="282" ht="16.5" spans="1:16">
@@ -20628,27 +20673,27 @@
       </c>
       <c r="K282" s="1">
         <f ca="1" t="shared" ref="K282:O282" si="271">RAND()</f>
-        <v>0.00669503979911301</v>
+        <v>0.216909840590615</v>
       </c>
       <c r="L282" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.246254351697372</v>
+        <v>0.246291222112356</v>
       </c>
       <c r="M282" s="1">
         <f ca="1" t="shared" si="271"/>
-        <v>0.250545160410667</v>
+        <v>0.88744117903853</v>
       </c>
       <c r="N282" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.295408616100189</v>
+        <v>0.295557194256112</v>
       </c>
       <c r="O282" s="1">
         <f ca="1" t="shared" si="271"/>
-        <v>0.233457537913387</v>
+        <v>0.972847498424198</v>
       </c>
       <c r="P282" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.344559883436529</v>
+        <v>0.344838146155937</v>
       </c>
     </row>
     <row r="283" ht="16.5" spans="1:16">
@@ -20688,27 +20733,27 @@
       </c>
       <c r="K283" s="1">
         <f ca="1" t="shared" ref="K283:O283" si="272">RAND()</f>
-        <v>0.131018982396711</v>
+        <v>0.773854425585387</v>
       </c>
       <c r="L283" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.245400268316765</v>
+        <v>0.245512218155436</v>
       </c>
       <c r="M283" s="1">
         <f ca="1" t="shared" si="272"/>
-        <v>0.803409090107178</v>
+        <v>0.693672045393269</v>
       </c>
       <c r="N283" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.294476352280363</v>
+        <v>0.294569191404804</v>
       </c>
       <c r="O283" s="1">
         <f ca="1" t="shared" si="272"/>
-        <v>0.154225520183936</v>
+        <v>0.793296005941769</v>
       </c>
       <c r="P283" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.343439380878563</v>
+        <v>0.343643514174068</v>
       </c>
     </row>
     <row r="284" ht="16.5" spans="1:16">
@@ -20748,27 +20793,27 @@
       </c>
       <c r="K284" s="1">
         <f ca="1" t="shared" ref="K284:O284" si="273">RAND()</f>
-        <v>0.148346701731559</v>
+        <v>0.0858574301038972</v>
       </c>
       <c r="L284" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.244533583746634</v>
+        <v>0.244522778143692</v>
       </c>
       <c r="M284" s="1">
         <f ca="1" t="shared" si="273"/>
-        <v>0.293127881602556</v>
+        <v>0.391245446449857</v>
       </c>
       <c r="N284" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.293347522106734</v>
+        <v>0.293353682927304</v>
       </c>
       <c r="O284" s="1">
         <f ca="1" t="shared" si="273"/>
-        <v>0.825203332746357</v>
+        <v>0.179126894873013</v>
       </c>
       <c r="P284" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.342253466597022</v>
+        <v>0.342147908313231</v>
       </c>
     </row>
     <row r="285" ht="16.5" spans="1:16">
@@ -20808,27 +20853,27 @@
       </c>
       <c r="K285" s="1">
         <f ca="1" t="shared" ref="K285:O285" si="274">RAND()</f>
-        <v>0.215619600608802</v>
+        <v>0.355641311184621</v>
       </c>
       <c r="L285" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.24368157505709</v>
+        <v>0.243705617007096</v>
       </c>
       <c r="M285" s="1">
         <f ca="1" t="shared" si="274"/>
-        <v>0.690037756105079</v>
+        <v>0.907886851897449</v>
       </c>
       <c r="N285" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.292391604931104</v>
+        <v>0.292453051916719</v>
       </c>
       <c r="O285" s="1">
         <f ca="1" t="shared" si="274"/>
-        <v>0.522011342353181</v>
+        <v>0.624024336296423</v>
       </c>
       <c r="P285" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.341072784403115</v>
+        <v>0.341151747181748</v>
       </c>
     </row>
     <row r="286" ht="16.5" spans="1:16">
@@ -20868,27 +20913,27 @@
       </c>
       <c r="K286" s="1">
         <f ca="1" t="shared" ref="K286:O286" si="275">RAND()</f>
-        <v>0.115826958285</v>
+        <v>0.310428898888178</v>
       </c>
       <c r="L286" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.242806997924689</v>
+        <v>0.242840176906408</v>
       </c>
       <c r="M286" s="1">
         <f ca="1" t="shared" si="275"/>
-        <v>0.668265279724054</v>
+        <v>0.942342649525658</v>
       </c>
       <c r="N286" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.291341987557259</v>
+        <v>0.291421895816261</v>
       </c>
       <c r="O286" s="1">
         <f ca="1" t="shared" si="275"/>
-        <v>0.883258547993693</v>
+        <v>0.418007829216528</v>
       </c>
       <c r="P286" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.339913632824893</v>
+        <v>0.339914217388329</v>
       </c>
     </row>
     <row r="287" ht="16.5" spans="1:16">
@@ -20928,27 +20973,27 @@
       </c>
       <c r="K287" s="1">
         <f ca="1" t="shared" ref="K287:O287" si="276">RAND()</f>
-        <v>0.355339242426965</v>
+        <v>0.206797267230924</v>
       </c>
       <c r="L287" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.241996119268133</v>
+        <v>0.241970970461143</v>
       </c>
       <c r="M287" s="1">
         <f ca="1" t="shared" si="276"/>
-        <v>0.833415740296595</v>
+        <v>0.868207091367582</v>
       </c>
       <c r="N287" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.290388968454933</v>
+        <v>0.29036970997606</v>
       </c>
       <c r="O287" s="1">
         <f ca="1" t="shared" si="276"/>
-        <v>0.148861875506305</v>
+        <v>0.642365065244853</v>
       </c>
       <c r="P287" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.338665919674194</v>
+        <v>0.338730213446805</v>
       </c>
     </row>
     <row r="288" ht="16.5" spans="1:16">
@@ -20988,27 +21033,27 @@
       </c>
       <c r="K288" s="1">
         <f ca="1" t="shared" ref="K288:O288" si="277">RAND()</f>
-        <v>0.0369848152124432</v>
+        <v>0.665441774513212</v>
       </c>
       <c r="L288" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.241096834756097</v>
+        <v>0.241202493804833</v>
       </c>
       <c r="M288" s="1">
         <f ca="1" t="shared" si="277"/>
-        <v>0.344063135456747</v>
+        <v>0.257340517878823</v>
       </c>
       <c r="N288" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.289238303912176</v>
+        <v>0.289329382759131</v>
       </c>
       <c r="O288" s="1">
         <f ca="1" t="shared" si="277"/>
-        <v>0.728447712052512</v>
+        <v>0.495057549201746</v>
       </c>
       <c r="P288" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.337444397555439</v>
+        <v>0.337496237784338</v>
       </c>
     </row>
     <row r="289" ht="16.5" spans="1:16">
@@ -21048,27 +21093,27 @@
       </c>
       <c r="K289" s="1">
         <f ca="1" t="shared" ref="K289:O289" si="278">RAND()</f>
-        <v>0.113384172759864</v>
+        <v>0.51475999235802</v>
       </c>
       <c r="L289" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.240270091724546</v>
+        <v>0.240337104237981</v>
       </c>
       <c r="M289" s="1">
         <f ca="1" t="shared" si="278"/>
-        <v>0.880043749376383</v>
+        <v>0.628889408785953</v>
       </c>
       <c r="N289" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.288333687878986</v>
+        <v>0.28835876841047</v>
       </c>
       <c r="O289" s="1">
         <f ca="1" t="shared" si="278"/>
-        <v>0.846679022171208</v>
+        <v>0.534455735124833</v>
       </c>
       <c r="P289" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.336391713557775</v>
+        <v>0.336364666217582</v>
       </c>
     </row>
     <row r="290" ht="16.5" spans="1:16">
@@ -21108,27 +21153,27 @@
       </c>
       <c r="K290" s="1">
         <f ca="1" t="shared" ref="K290:O290" si="279">RAND()</f>
-        <v>0.514862710242783</v>
+        <v>0.220142377908732</v>
       </c>
       <c r="L290" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.23950289678731</v>
+        <v>0.239454031680305</v>
       </c>
       <c r="M290" s="1">
         <f ca="1" t="shared" si="279"/>
-        <v>0.102721104680058</v>
+        <v>0.105179045926255</v>
       </c>
       <c r="N290" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.287270793164239</v>
+        <v>0.287222335587862</v>
       </c>
       <c r="O290" s="1">
         <f ca="1" t="shared" si="279"/>
-        <v>0.290422500275015</v>
+        <v>0.250929335067295</v>
       </c>
       <c r="P290" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.335069810735652</v>
+        <v>0.335014805128711</v>
       </c>
     </row>
     <row r="291" ht="16.5" spans="1:16">
@@ -21168,27 +21213,27 @@
       </c>
       <c r="K291" s="1">
         <f ca="1" t="shared" ref="K291:O291" si="280">RAND()</f>
-        <v>0.354284570615667</v>
+        <v>0.285764341223699</v>
       </c>
       <c r="L291" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.238648002948031</v>
+        <v>0.238636720533455</v>
       </c>
       <c r="M291" s="1">
         <f ca="1" t="shared" si="280"/>
-        <v>0.734121064919921</v>
+        <v>0.441308101971102</v>
       </c>
       <c r="N291" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.286355088864937</v>
+        <v>0.286295592408019</v>
       </c>
       <c r="O291" s="1">
         <f ca="1" t="shared" si="280"/>
-        <v>0.214683944931897</v>
+        <v>0.204439001574513</v>
       </c>
       <c r="P291" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.333976645223845</v>
+        <v>0.333915461853452</v>
       </c>
     </row>
     <row r="292" ht="16.5" spans="1:16">
@@ -21228,27 +21273,27 @@
       </c>
       <c r="K292" s="1">
         <f ca="1" t="shared" ref="K292:O292" si="281">RAND()</f>
-        <v>0.160528698566278</v>
+        <v>0.556416627193586</v>
       </c>
       <c r="L292" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.237793758692265</v>
+        <v>0.237858496853363</v>
       </c>
       <c r="M292" s="1">
         <f ca="1" t="shared" si="281"/>
-        <v>0.80489890927692</v>
+        <v>0.452792302059309</v>
       </c>
       <c r="N292" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.285348061393391</v>
+        <v>0.285355220798954</v>
       </c>
       <c r="O292" s="1">
         <f ca="1" t="shared" si="281"/>
-        <v>0.328351074296222</v>
+        <v>0.9119920178083</v>
       </c>
       <c r="P292" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.332824435902518</v>
+        <v>0.332927036059598</v>
       </c>
     </row>
     <row r="293" ht="16.5" spans="1:16">
@@ -21288,27 +21333,27 @@
       </c>
       <c r="K293" s="1">
         <f ca="1" t="shared" ref="K293:O293" si="282">RAND()</f>
-        <v>0.547987766470502</v>
+        <v>0.934964155216734</v>
       </c>
       <c r="L293" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.237039992364277</v>
+        <v>0.237102839821848</v>
       </c>
       <c r="M293" s="1">
         <f ca="1" t="shared" si="282"/>
-        <v>0.266077869825067</v>
+        <v>0.670876307064558</v>
       </c>
       <c r="N293" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.284343479096419</v>
+        <v>0.284472068427006</v>
       </c>
       <c r="O293" s="1">
         <f ca="1" t="shared" si="282"/>
-        <v>0.812364042035201</v>
+        <v>0.917434069381672</v>
       </c>
       <c r="P293" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.331735686220885</v>
+        <v>0.331881339600539</v>
       </c>
     </row>
     <row r="294" ht="16.5" spans="1:16">
@@ -21348,27 +21393,27 @@
       </c>
       <c r="K294" s="1">
         <f ca="1" t="shared" ref="K294:O294" si="283">RAND()</f>
-        <v>0.26586720563199</v>
+        <v>0.417798181377978</v>
       </c>
       <c r="L294" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.236182955811839</v>
+        <v>0.23620746195361</v>
       </c>
       <c r="M294" s="1">
         <f ca="1" t="shared" si="283"/>
-        <v>0.815490624196551</v>
+        <v>0.272964188408738</v>
       </c>
       <c r="N294" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.28341346881635</v>
+        <v>0.283350466603196</v>
       </c>
       <c r="O294" s="1">
         <f ca="1" t="shared" si="283"/>
-        <v>0.472020083193115</v>
+        <v>0.136033525045152</v>
       </c>
       <c r="P294" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.33058858075646</v>
+        <v>0.33047138462935</v>
       </c>
     </row>
     <row r="295" ht="16.5" spans="1:16">
@@ -21408,27 +21453,27 @@
       </c>
       <c r="K295" s="1">
         <f ca="1" t="shared" ref="K295:O295" si="284">RAND()</f>
-        <v>0.0371694147615194</v>
+        <v>0.644401571223226</v>
       </c>
       <c r="L295" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.235340634509574</v>
+        <v>0.235437913464778</v>
       </c>
       <c r="M295" s="1">
         <f ca="1" t="shared" si="284"/>
-        <v>0.101039176324911</v>
+        <v>0.824269055855583</v>
       </c>
       <c r="N295" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.282295596556349</v>
+        <v>0.282508737371476</v>
       </c>
       <c r="O295" s="1">
         <f ca="1" t="shared" si="284"/>
-        <v>0.777841718815488</v>
+        <v>0.0290573398043892</v>
       </c>
       <c r="P295" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.329358982775843</v>
+        <v>0.329452167884922</v>
       </c>
     </row>
     <row r="296" ht="16.5" spans="1:16">
@@ -21468,27 +21513,27 @@
       </c>
       <c r="K296" s="1">
         <f ca="1" t="shared" ref="K296:O296" si="285">RAND()</f>
-        <v>0.494826128609588</v>
+        <v>0.684090849066208</v>
       </c>
       <c r="L296" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.234613497066468</v>
+        <v>0.234643611826555</v>
       </c>
       <c r="M296" s="1">
         <f ca="1" t="shared" si="285"/>
-        <v>0.908305128513663</v>
+        <v>0.555084323960963</v>
       </c>
       <c r="N296" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.281537682593662</v>
+        <v>0.281511594804425</v>
       </c>
       <c r="O296" s="1">
         <f ca="1" t="shared" si="285"/>
-        <v>0.986417083349488</v>
+        <v>0.900709545566821</v>
       </c>
       <c r="P296" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.328474296864966</v>
+        <v>0.328434571764287</v>
       </c>
     </row>
     <row r="297" ht="16.5" spans="1:16">
@@ -21528,27 +21573,27 @@
       </c>
       <c r="K297" s="1">
         <f ca="1" t="shared" ref="K297:O297" si="286">RAND()</f>
-        <v>0.635733787835218</v>
+        <v>0.629123141719259</v>
       </c>
       <c r="L297" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.233840736672837</v>
+        <v>0.233839691930322</v>
       </c>
       <c r="M297" s="1">
         <f ca="1" t="shared" si="286"/>
-        <v>0.636413659222153</v>
+        <v>0.543710785633423</v>
       </c>
       <c r="N297" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.280562936724341</v>
+        <v>0.280547241275739</v>
       </c>
       <c r="O297" s="1">
         <f ca="1" t="shared" si="286"/>
-        <v>0.257343626281154</v>
+        <v>0.543614504873917</v>
       </c>
       <c r="P297" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.327225228777051</v>
+        <v>0.327254775405002</v>
       </c>
     </row>
     <row r="298" ht="16.5" spans="1:16">
@@ -21588,27 +21633,27 @@
       </c>
       <c r="K298" s="1">
         <f ca="1" t="shared" ref="K298:O298" si="287">RAND()</f>
-        <v>0.445046541970323</v>
+        <v>0.629451439584845</v>
       </c>
       <c r="L298" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.23302099420192</v>
+        <v>0.23304994118967</v>
       </c>
       <c r="M298" s="1">
         <f ca="1" t="shared" si="287"/>
-        <v>0.922994569939904</v>
+        <v>0.894178291816452</v>
       </c>
       <c r="N298" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.27963052788407</v>
+        <v>0.279654951432038</v>
       </c>
       <c r="O298" s="1">
         <f ca="1" t="shared" si="287"/>
-        <v>0.38749861825986</v>
+        <v>0.602170841484808</v>
       </c>
       <c r="P298" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.326156002005145</v>
+        <v>0.326214123759052</v>
       </c>
     </row>
     <row r="299" ht="16.5" spans="1:16">
@@ -21648,27 +21693,27 @@
       </c>
       <c r="K299" s="1">
         <f ca="1" t="shared" ref="K299:O299" si="288">RAND()</f>
-        <v>0.968748277413763</v>
+        <v>0.0588430135215321</v>
       </c>
       <c r="L299" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.232318359503631</v>
+        <v>0.232176485589526</v>
       </c>
       <c r="M299" s="1">
         <f ca="1" t="shared" si="288"/>
-        <v>0.945951843953851</v>
+        <v>0.872261229115832</v>
       </c>
       <c r="N299" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.278774578691556</v>
+        <v>0.278621214816492</v>
       </c>
       <c r="O299" s="1">
         <f ca="1" t="shared" si="288"/>
-        <v>0.674483032224723</v>
+        <v>0.402379183734636</v>
       </c>
       <c r="P299" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.325188470019203</v>
+        <v>0.324992679267891</v>
       </c>
     </row>
     <row r="300" ht="16.5" spans="1:16">
@@ -21708,27 +21753,27 @@
       </c>
       <c r="K300" s="1">
         <f ca="1" t="shared" ref="K300:O300" si="289">RAND()</f>
-        <v>0.158475940804812</v>
+        <v>0.436345526499104</v>
       </c>
       <c r="L300" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.23141329002697</v>
+        <v>0.231456326101161</v>
       </c>
       <c r="M300" s="1">
         <f ca="1" t="shared" si="289"/>
-        <v>0.912667844325896</v>
+        <v>0.0999716642187729</v>
       </c>
       <c r="N300" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.277708488970335</v>
+        <v>0.277625655734236</v>
       </c>
       <c r="O300" s="1">
         <f ca="1" t="shared" si="289"/>
-        <v>0.133224520217329</v>
+        <v>0.661328914545833</v>
       </c>
       <c r="P300" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.323882968761799</v>
+        <v>0.323881927636334</v>
       </c>
     </row>
     <row r="301" ht="16.5" spans="1:16">
@@ -21768,27 +21813,27 @@
       </c>
       <c r="K301" s="1">
         <f ca="1" t="shared" ref="K301:O301" si="290">RAND()</f>
-        <v>0.64399195597121</v>
+        <v>0.802917091459511</v>
       </c>
       <c r="L301" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.230714460300919</v>
+        <v>0.230738910321763</v>
       </c>
       <c r="M301" s="1">
         <f ca="1" t="shared" si="290"/>
-        <v>0.143380315344217</v>
+        <v>0.0248263120981038</v>
       </c>
       <c r="N301" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.276736518810972</v>
+        <v>0.276742729754394</v>
       </c>
       <c r="O301" s="1">
         <f ca="1" t="shared" si="290"/>
-        <v>0.168036122984884</v>
+        <v>0.15571493934909</v>
       </c>
       <c r="P301" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.3227623705222</v>
+        <v>0.322766685898909</v>
       </c>
     </row>
     <row r="302" spans="1:16">

--- a/table/resources/sample/PointsAwardRanking.xlsx
+++ b/table/resources/sample/PointsAwardRanking.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="PointsAwardRanking" sheetId="1" r:id="rId1"/>
@@ -176,7 +176,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="94">
   <si>
     <t>序列ID</t>
   </si>
@@ -349,73 +349,82 @@
     <t>1990000_1000</t>
   </si>
   <si>
-    <t>1990000_8170000</t>
+    <t>1990000_4410000</t>
   </si>
   <si>
-    <t>1990000_6130000</t>
+    <t>1990000_4100000</t>
   </si>
   <si>
-    <t>1990000_4090000</t>
+    <t>1990000_3780000</t>
   </si>
   <si>
-    <t>1990000_3270000</t>
+    <t>1990000_3150000</t>
   </si>
   <si>
-    <t>1990000_2450000</t>
+    <t>1990000_2610000</t>
   </si>
   <si>
-    <t>1990000_2040000</t>
+    <t>1990000_2210000</t>
   </si>
   <si>
-    <t>1990000_1230000</t>
+    <t>1990000_1890000</t>
   </si>
   <si>
-    <t>1990000_820000</t>
+    <t>1990000_1580000</t>
   </si>
   <si>
-    <t>1990000_410000</t>
+    <t>1990000_950000</t>
   </si>
   <si>
-    <t>1990000_330000</t>
+    <t>1990000_630000</t>
   </si>
   <si>
-    <t>1990000_200000</t>
+    <t>1990000_500000</t>
   </si>
   <si>
-    <t>1990000_120000</t>
+    <t>1990000_250000</t>
   </si>
   <si>
-    <t>1990000_80000</t>
+    <t>1990000_190000</t>
+  </si>
+  <si>
+    <t>1990000_90000</t>
+  </si>
+  <si>
+    <t>1990000_60000</t>
   </si>
   <si>
     <t>1990000_40000</t>
   </si>
   <si>
-    <t>1990000_10000</t>
+    <t>1990000_4600000</t>
   </si>
   <si>
-    <t>1990000_11000000</t>
+    <t>1990000_4300000</t>
   </si>
   <si>
-    <t>1990000_6600000</t>
+    <t>1990000_3900000</t>
   </si>
   <si>
-    <t>1990000_4400000</t>
+    <t>1990000_3400000</t>
   </si>
   <si>
-    <t>1990000_2200000</t>
+    <t>1990000_2800000</t>
+  </si>
+  <si>
+    <t>1990000_2400000</t>
+  </si>
+  <si>
+    <t>1990000_2000000</t>
+  </si>
+  <si>
+    <t>1990000_1800000</t>
   </si>
   <si>
     <t>1990000_1100000</t>
   </si>
   <si>
     <t>1990000_700000</t>
-  </si>
-  <si>
-    <t>1990000_400000</t>
-  </si>
-  <si>
-    <t>1990000_100000</t>
   </si>
   <si>
     <t>2036/08/01 00:00:00</t>
@@ -2472,7 +2481,7 @@
         <v>21</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
@@ -2493,7 +2502,7 @@
         <v>21</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
@@ -2514,7 +2523,7 @@
         <v>21</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F42" s="2"/>
       <c r="G42" s="2" t="s">
@@ -2537,7 +2546,7 @@
         <v>21</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F43" s="2"/>
       <c r="G43" s="2" t="s">
@@ -2560,7 +2569,7 @@
         <v>21</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F44" s="2"/>
       <c r="G44" s="2" t="s">
@@ -2583,7 +2592,7 @@
         <v>21</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
@@ -2604,7 +2613,7 @@
         <v>21</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
@@ -2625,7 +2634,7 @@
         <v>21</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
@@ -2646,7 +2655,7 @@
         <v>21</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
@@ -2667,7 +2676,7 @@
         <v>21</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
@@ -2689,7 +2698,7 @@
         <v>21</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
@@ -2711,7 +2720,7 @@
         <v>21</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F51" s="2"/>
       <c r="G51" s="2"/>
@@ -2740,7 +2749,7 @@
         <v>23</v>
       </c>
       <c r="H52" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I52" s="20"/>
       <c r="J52" s="20"/>
@@ -2766,7 +2775,7 @@
         <v>25</v>
       </c>
       <c r="H53" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I53" s="20"/>
       <c r="J53" s="20"/>
@@ -2792,7 +2801,7 @@
         <v>27</v>
       </c>
       <c r="H54" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I54" s="20"/>
       <c r="J54" s="20"/>
@@ -2816,7 +2825,7 @@
       <c r="F55" s="23"/>
       <c r="G55" s="23"/>
       <c r="H55" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I55" s="20"/>
       <c r="J55" s="20"/>
@@ -2840,7 +2849,7 @@
       <c r="F56" s="23"/>
       <c r="G56" s="23"/>
       <c r="H56" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I56" s="20"/>
       <c r="J56" s="21"/>
@@ -2865,7 +2874,7 @@
       <c r="F57" s="23"/>
       <c r="G57" s="23"/>
       <c r="H57" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I57" s="20"/>
       <c r="J57" s="21"/>
@@ -2890,7 +2899,7 @@
       <c r="F58" s="23"/>
       <c r="G58" s="23"/>
       <c r="H58" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I58" s="20"/>
       <c r="J58" s="21"/>
@@ -2915,7 +2924,7 @@
       <c r="F59" s="23"/>
       <c r="G59" s="23"/>
       <c r="H59" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I59" s="20"/>
       <c r="J59" s="21"/>
@@ -2940,7 +2949,7 @@
       <c r="F60" s="23"/>
       <c r="G60" s="23"/>
       <c r="H60" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I60" s="20"/>
       <c r="L60" s="3"/>
@@ -2964,7 +2973,7 @@
       <c r="F61" s="23"/>
       <c r="G61" s="23"/>
       <c r="H61" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I61" s="20"/>
       <c r="L61" s="3"/>
@@ -2988,7 +2997,7 @@
       <c r="F62" s="23"/>
       <c r="G62" s="23"/>
       <c r="H62" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I62" s="20"/>
       <c r="J62" s="10"/>
@@ -3013,7 +3022,7 @@
       <c r="F63" s="23"/>
       <c r="G63" s="23"/>
       <c r="H63" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I63" s="20"/>
       <c r="J63" s="21"/>
@@ -3038,7 +3047,7 @@
       <c r="F64" s="23"/>
       <c r="G64" s="23"/>
       <c r="H64" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I64" s="20"/>
       <c r="J64" s="21"/>
@@ -3063,7 +3072,7 @@
       <c r="F65" s="23"/>
       <c r="G65" s="23"/>
       <c r="H65" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I65" s="20"/>
       <c r="J65" s="21"/>
@@ -3088,7 +3097,7 @@
       <c r="F66" s="23"/>
       <c r="G66" s="23"/>
       <c r="H66" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I66" s="20"/>
       <c r="J66" s="21"/>
@@ -3113,7 +3122,7 @@
       <c r="F67" s="23"/>
       <c r="G67" s="23"/>
       <c r="H67" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I67" s="20"/>
       <c r="J67" s="21"/>
@@ -3138,7 +3147,7 @@
       <c r="F68" s="23"/>
       <c r="G68" s="23"/>
       <c r="H68" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I68" s="20"/>
       <c r="J68" s="21"/>
@@ -3163,7 +3172,7 @@
       <c r="F69" s="23"/>
       <c r="G69" s="23"/>
       <c r="H69" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I69" s="20"/>
       <c r="J69" s="21"/>
@@ -3188,7 +3197,7 @@
       <c r="F70" s="23"/>
       <c r="G70" s="23"/>
       <c r="H70" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I70" s="20"/>
       <c r="J70" s="21"/>
@@ -3213,7 +3222,7 @@
       <c r="F71" s="23"/>
       <c r="G71" s="23"/>
       <c r="H71" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I71" s="20"/>
       <c r="J71" s="21"/>
@@ -3238,7 +3247,7 @@
       <c r="F72" s="23"/>
       <c r="G72" s="23"/>
       <c r="H72" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I72" s="20"/>
       <c r="J72" s="21"/>
@@ -3265,7 +3274,7 @@
         <v>23</v>
       </c>
       <c r="H73" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I73" s="20"/>
       <c r="J73" s="21"/>
@@ -3292,7 +3301,7 @@
         <v>25</v>
       </c>
       <c r="H74" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I74" s="20"/>
       <c r="J74" s="21"/>
@@ -3319,7 +3328,7 @@
         <v>27</v>
       </c>
       <c r="H75" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I75" s="20"/>
       <c r="J75" s="21"/>
@@ -3344,7 +3353,7 @@
       <c r="F76" s="23"/>
       <c r="G76" s="23"/>
       <c r="H76" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I76" s="20"/>
       <c r="J76" s="21"/>
@@ -3369,7 +3378,7 @@
       <c r="F77" s="23"/>
       <c r="G77" s="23"/>
       <c r="H77" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I77" s="20"/>
       <c r="J77" s="21"/>
@@ -3394,7 +3403,7 @@
       <c r="F78" s="23"/>
       <c r="G78" s="23"/>
       <c r="H78" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I78" s="20"/>
       <c r="J78" s="21"/>
@@ -3419,7 +3428,7 @@
       <c r="F79" s="23"/>
       <c r="G79" s="23"/>
       <c r="H79" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I79" s="20"/>
       <c r="J79" s="21"/>
@@ -3444,7 +3453,7 @@
       <c r="F80" s="23"/>
       <c r="G80" s="23"/>
       <c r="H80" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I80" s="20"/>
       <c r="J80" s="21"/>
@@ -3468,7 +3477,7 @@
       <c r="F81" s="23"/>
       <c r="G81" s="23"/>
       <c r="H81" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I81" s="20"/>
       <c r="J81" s="21"/>
@@ -3492,7 +3501,7 @@
       <c r="F82" s="23"/>
       <c r="G82" s="23"/>
       <c r="H82" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I82" s="20"/>
       <c r="J82" s="20"/>
@@ -3516,7 +3525,7 @@
       <c r="F83" s="23"/>
       <c r="G83" s="23"/>
       <c r="H83" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I83" s="20"/>
     </row>
@@ -3539,7 +3548,7 @@
       <c r="F84" s="23"/>
       <c r="G84" s="23"/>
       <c r="H84" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I84" s="20"/>
     </row>
@@ -3562,7 +3571,7 @@
       <c r="F85" s="23"/>
       <c r="G85" s="23"/>
       <c r="H85" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I85" s="20"/>
     </row>
@@ -3585,7 +3594,7 @@
       <c r="F86" s="23"/>
       <c r="G86" s="23"/>
       <c r="H86" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I86" s="20"/>
     </row>
@@ -3603,12 +3612,12 @@
         <v>21</v>
       </c>
       <c r="E87" s="23" t="s">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="F87" s="23"/>
       <c r="G87" s="23"/>
       <c r="H87" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I87" s="20"/>
     </row>
@@ -3626,12 +3635,12 @@
         <v>21</v>
       </c>
       <c r="E88" s="23" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F88" s="23"/>
       <c r="G88" s="23"/>
       <c r="H88" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I88" s="20"/>
     </row>
@@ -3649,14 +3658,14 @@
         <v>21</v>
       </c>
       <c r="E89" s="23" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F89" s="23"/>
       <c r="G89" s="23" t="s">
         <v>23</v>
       </c>
       <c r="H89" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I89" s="20"/>
     </row>
@@ -3674,14 +3683,14 @@
         <v>21</v>
       </c>
       <c r="E90" s="27" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F90" s="23"/>
       <c r="G90" s="23" t="s">
         <v>25</v>
       </c>
       <c r="H90" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="91" spans="1:10">
@@ -3698,14 +3707,14 @@
         <v>21</v>
       </c>
       <c r="E91" s="27" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F91" s="23"/>
       <c r="G91" s="23" t="s">
         <v>27</v>
       </c>
       <c r="H91" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="92" spans="1:10">
@@ -3722,12 +3731,12 @@
         <v>21</v>
       </c>
       <c r="E92" s="27" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F92" s="23"/>
       <c r="G92" s="23"/>
       <c r="H92" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="93" spans="1:10">
@@ -3744,12 +3753,12 @@
         <v>21</v>
       </c>
       <c r="E93" s="27" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F93" s="23"/>
       <c r="G93" s="23"/>
       <c r="H93" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="94" spans="1:10">
@@ -3766,12 +3775,12 @@
         <v>21</v>
       </c>
       <c r="E94" s="27" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F94" s="23"/>
       <c r="G94" s="23"/>
       <c r="H94" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="95" spans="1:10">
@@ -3788,12 +3797,12 @@
         <v>21</v>
       </c>
       <c r="E95" s="27" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F95" s="23"/>
       <c r="G95" s="23"/>
       <c r="H95" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="96" spans="1:10">
@@ -3810,12 +3819,12 @@
         <v>21</v>
       </c>
       <c r="E96" s="27" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="F96" s="23"/>
       <c r="G96" s="23"/>
       <c r="H96" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="97" spans="1:8">
@@ -3832,12 +3841,12 @@
         <v>21</v>
       </c>
       <c r="E97" s="27" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="F97" s="23"/>
       <c r="G97" s="23"/>
       <c r="H97" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="98" spans="1:8">
@@ -3854,12 +3863,12 @@
         <v>21</v>
       </c>
       <c r="E98" s="27" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F98" s="23"/>
       <c r="G98" s="23"/>
       <c r="H98" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -3897,34 +3906,34 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="R1" s="1">
         <v>46</v>
@@ -3967,30 +3976,30 @@
       </c>
       <c r="K2" s="1">
         <f ca="1" t="shared" ref="K2:O2" si="3">RAND()</f>
-        <v>0.652441457006768</v>
+        <v>0.206098305917123</v>
       </c>
       <c r="L2" s="1">
         <f ca="1" t="shared" ref="L2:L65" si="4">J2+($R$1*$R$7*K2/MAX(1,($A2*($A2-1)))+$R$1*$R$7/$A2)/100</f>
-        <v>133.203692106693</v>
+        <v>127.044156621656</v>
       </c>
       <c r="M2" s="1">
         <f ca="1" t="shared" si="3"/>
-        <v>0.124668265120187</v>
+        <v>0.318911205948596</v>
       </c>
       <c r="N2" s="1">
         <f ca="1" t="shared" ref="N2:N65" si="5">L2+($R$1*$R$7*M2/MAX(1,($A2*($A2-1)))+$R$1*$R$7/$A2)/100</f>
-        <v>148.724114165352</v>
+        <v>145.245131263747</v>
       </c>
       <c r="O2" s="1">
         <f ca="1" t="shared" si="3"/>
-        <v>0.253894602342103</v>
+        <v>0.402769665419057</v>
       </c>
       <c r="P2" s="1">
         <f ca="1" t="shared" ref="P2:P65" si="6">N2+($R$1*$R$7*O2/MAX(1,($A2*($A2-1)))+$R$1*$R$7/$A2)/100</f>
-        <v>166.027859677673</v>
+        <v>164.60335264653</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="R2" s="1">
         <v>1</v>
@@ -4033,30 +4042,30 @@
       </c>
       <c r="K3" s="1">
         <f ca="1" t="shared" ref="K3:O3" si="8">RAND()</f>
-        <v>0.00499239174961907</v>
+        <v>0.803239439208689</v>
       </c>
       <c r="L3" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>34.5344475030724</v>
+        <v>40.04235213054</v>
       </c>
       <c r="M3" s="1">
         <f ca="1" t="shared" si="8"/>
-        <v>0.729927815781742</v>
+        <v>0.151919120287883</v>
       </c>
       <c r="N3" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>46.4709494319664</v>
+        <v>47.9905940605263</v>
       </c>
       <c r="O3" s="1">
         <f ca="1" t="shared" si="8"/>
-        <v>0.398732994087178</v>
+        <v>0.778787374679508</v>
       </c>
       <c r="P3" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>56.1222070911679</v>
+        <v>60.264226945815</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="R3" s="1">
         <v>10</v>
@@ -4099,30 +4108,30 @@
       </c>
       <c r="K4" s="1">
         <f ca="1" t="shared" ref="K4:O4" si="9">RAND()</f>
-        <v>0.899964909135736</v>
+        <v>0.612430410169176</v>
       </c>
       <c r="L4" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>34.2699192910122</v>
+        <v>33.6085899433891</v>
       </c>
       <c r="M4" s="1">
         <f ca="1" t="shared" si="9"/>
-        <v>0.577551684244162</v>
+        <v>0.78655635676391</v>
       </c>
       <c r="N4" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>40.1982881647738</v>
+        <v>40.0176695639461</v>
       </c>
       <c r="O4" s="1">
         <f ca="1" t="shared" si="9"/>
-        <v>0.472518087372499</v>
+        <v>0.715264869160387</v>
       </c>
       <c r="P4" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>45.8850797657305</v>
+        <v>46.262778763015</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="R4" s="1">
         <f>24*60/R3</f>
@@ -4166,30 +4175,30 @@
       </c>
       <c r="K5" s="1">
         <f ca="1" t="shared" ref="K5:O5" si="10">RAND()</f>
-        <v>0.769717617419658</v>
+        <v>0.33564312815046</v>
       </c>
       <c r="L5" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>18.1351752600326</v>
+        <v>17.635989597373</v>
       </c>
       <c r="M5" s="1">
         <f ca="1" t="shared" si="10"/>
-        <v>0.580842144493361</v>
+        <v>0.443959807461753</v>
       </c>
       <c r="N5" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>22.2531437262</v>
+        <v>21.596543375954</v>
       </c>
       <c r="O5" s="1">
         <f ca="1" t="shared" si="10"/>
-        <v>0.639755469051341</v>
+        <v>0.0816383103551725</v>
       </c>
       <c r="P5" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>26.438862515609</v>
+        <v>25.1404274328625</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="R5" s="1">
         <v>6000</v>
@@ -4232,30 +4241,30 @@
       </c>
       <c r="K6" s="1">
         <f ca="1" t="shared" ref="K6:O6" si="11">RAND()</f>
-        <v>0.242700885693266</v>
+        <v>0.0343441259209838</v>
       </c>
       <c r="L6" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>16.7274636111284</v>
+        <v>16.5836974468855</v>
       </c>
       <c r="M6" s="1">
         <f ca="1" t="shared" si="11"/>
-        <v>0.145277927882112</v>
+        <v>0.787113299015338</v>
       </c>
       <c r="N6" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>19.587705381367</v>
+        <v>19.8868056232061</v>
       </c>
       <c r="O6" s="1">
         <f ca="1" t="shared" si="11"/>
-        <v>0.467320872084037</v>
+        <v>0.168236672544477</v>
       </c>
       <c r="P6" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>22.670156783105</v>
+        <v>22.7628889272618</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="R6" s="1">
         <f>R5/R4</f>
@@ -4319,7 +4328,7 @@
         <v>16.1</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="R7" s="1">
         <v>30</v>
@@ -5673,27 +5682,27 @@
       </c>
       <c r="K31" s="1">
         <f ca="1" t="shared" ref="K31:O31" si="12">RAND()</f>
-        <v>0.492685169318414</v>
+        <v>0.915336876680116</v>
       </c>
       <c r="L31" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>2.37126328199609</v>
+        <v>2.37796741252665</v>
       </c>
       <c r="M31" s="1">
         <f ca="1" t="shared" si="12"/>
-        <v>0.255077941083049</v>
+        <v>0.101027055672027</v>
       </c>
       <c r="N31" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>2.83530934588913</v>
+        <v>2.8395699106511</v>
       </c>
       <c r="O31" s="1">
         <f ca="1" t="shared" si="12"/>
-        <v>0.907128072639998</v>
+        <v>0.213498662510728</v>
       </c>
       <c r="P31" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>3.3096982739379</v>
+        <v>3.30295644115989</v>
       </c>
     </row>
     <row r="32" ht="16.5" spans="1:16">
@@ -5961,27 +5970,27 @@
       </c>
       <c r="K36" s="1">
         <f ca="1" t="shared" ref="K36:O36" si="13">RAND()</f>
-        <v>0.325753534468455</v>
+        <v>0.704091192170805</v>
       </c>
       <c r="L36" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>2.02159277208039</v>
+        <v>2.02598021718652</v>
       </c>
       <c r="M36" s="1">
         <f ca="1" t="shared" si="13"/>
-        <v>0.626916474226437</v>
+        <v>0.363826889172524</v>
       </c>
       <c r="N36" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>2.42314861018487</v>
+        <v>2.42448510043911</v>
       </c>
       <c r="O36" s="1">
         <f ca="1" t="shared" si="13"/>
-        <v>0.183597417808244</v>
+        <v>0.244712248993438</v>
       </c>
       <c r="P36" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>2.81956343738298</v>
+        <v>2.82160865425097</v>
       </c>
     </row>
     <row r="37" ht="16.5" spans="1:16">
@@ -6021,27 +6030,27 @@
       </c>
       <c r="K37" s="1">
         <f ca="1" t="shared" ref="K37:O37" si="14">RAND()</f>
-        <v>0.0811719877054662</v>
+        <v>0.744968393245758</v>
       </c>
       <c r="L37" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.96136521700821</v>
+        <v>1.9686353681165</v>
       </c>
       <c r="M37" s="1">
         <f ca="1" t="shared" si="14"/>
-        <v>0.331769779028674</v>
+        <v>0.492233604493358</v>
       </c>
       <c r="N37" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>2.34833221934995</v>
+        <v>2.35735983140381</v>
       </c>
       <c r="O37" s="1">
         <f ca="1" t="shared" si="14"/>
-        <v>0.128911001576272</v>
+        <v>0.923938471551586</v>
       </c>
       <c r="P37" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>2.7330774350815</v>
+        <v>2.75081249085414</v>
       </c>
     </row>
     <row r="38" ht="16.5" spans="1:16">
@@ -6081,27 +6090,27 @@
       </c>
       <c r="K38" s="1">
         <f ca="1" t="shared" ref="K38:O38" si="15">RAND()</f>
-        <v>0.773526457568217</v>
+        <v>0.951692045587845</v>
       </c>
       <c r="L38" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.91432031915498</v>
+        <v>1.91616617885068</v>
       </c>
       <c r="M38" s="1">
         <f ca="1" t="shared" si="15"/>
-        <v>0.954815579212579</v>
+        <v>0.979388109748552</v>
       </c>
       <c r="N38" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>2.29718552560628</v>
+        <v>2.2992859655733</v>
       </c>
       <c r="O38" s="1">
         <f ca="1" t="shared" si="15"/>
-        <v>0.963428049598807</v>
+        <v>0.965510208880439</v>
       </c>
       <c r="P38" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>2.68013996035438</v>
+        <v>2.68226197224188</v>
       </c>
     </row>
     <row r="39" ht="16.5" spans="1:16">
@@ -6141,27 +6150,27 @@
       </c>
       <c r="K39" s="1">
         <f ca="1" t="shared" ref="K39:O39" si="16">RAND()</f>
-        <v>0.874510871365545</v>
+        <v>0.541030503181903</v>
       </c>
       <c r="L39" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.86363317924953</v>
+        <v>1.8603600433456</v>
       </c>
       <c r="M39" s="1">
         <f ca="1" t="shared" si="16"/>
-        <v>0.671767266963824</v>
+        <v>0.398488246189035</v>
       </c>
       <c r="N39" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>2.2333845222681</v>
+        <v>2.22742913139496</v>
       </c>
       <c r="O39" s="1">
         <f ca="1" t="shared" si="16"/>
-        <v>0.473989328307985</v>
+        <v>0.60334597309493</v>
       </c>
       <c r="P39" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>2.60119465934537</v>
+        <v>2.59650891406119</v>
       </c>
     </row>
     <row r="40" ht="16.5" spans="1:16">
@@ -6201,27 +6210,27 @@
       </c>
       <c r="K40" s="1">
         <f ca="1" t="shared" ref="K40:O40" si="17">RAND()</f>
-        <v>0.553792768725295</v>
+        <v>0.351771281297278</v>
       </c>
       <c r="L40" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.81163450756303</v>
+        <v>1.80975333581775</v>
       </c>
       <c r="M40" s="1">
         <f ca="1" t="shared" si="17"/>
-        <v>0.844457633860992</v>
+        <v>0.517308408887736</v>
       </c>
       <c r="N40" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>2.17334403208886</v>
+        <v>2.16841653152804</v>
       </c>
       <c r="O40" s="1">
         <f ca="1" t="shared" si="17"/>
-        <v>0.598209393547398</v>
+        <v>0.649115210994889</v>
       </c>
       <c r="P40" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>2.5327605568061</v>
+        <v>2.52830707802718</v>
       </c>
     </row>
     <row r="41" ht="16.5" spans="1:16">
@@ -6261,27 +6270,27 @@
       </c>
       <c r="K41" s="1">
         <f ca="1" t="shared" ref="K41:O41" si="18">RAND()</f>
-        <v>0.0291770943708951</v>
+        <v>0.0985257669693878</v>
       </c>
       <c r="L41" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.76064272045021</v>
+        <v>1.76125618947704</v>
       </c>
       <c r="M41" s="1">
         <f ca="1" t="shared" si="18"/>
-        <v>0.361440114869941</v>
+        <v>0.481187373876705</v>
       </c>
       <c r="N41" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>2.10884007531252</v>
+        <v>2.11051284701518</v>
       </c>
       <c r="O41" s="1">
         <f ca="1" t="shared" si="18"/>
-        <v>0.622497295730196</v>
+        <v>0.788826962610973</v>
       </c>
       <c r="P41" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>2.45934678215936</v>
+        <v>2.46249093168443</v>
       </c>
     </row>
     <row r="42" ht="16.5" spans="1:16">
@@ -6321,27 +6330,27 @@
       </c>
       <c r="K42" s="1">
         <f ca="1" t="shared" ref="K42:O42" si="19">RAND()</f>
-        <v>0.937547357397353</v>
+        <v>0.608352098738534</v>
       </c>
       <c r="L42" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.72447448386103</v>
+        <v>1.7217044261967</v>
       </c>
       <c r="M42" s="1">
         <f ca="1" t="shared" si="19"/>
-        <v>0.995062205997697</v>
+        <v>0.918781675482521</v>
       </c>
       <c r="N42" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>2.06943293413101</v>
+        <v>2.06602100370991</v>
       </c>
       <c r="O42" s="1">
         <f ca="1" t="shared" si="19"/>
-        <v>0.0763910997565338</v>
+        <v>0.593520511057099</v>
       </c>
       <c r="P42" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>2.40666110314115</v>
+        <v>2.40760062752246</v>
       </c>
     </row>
     <row r="43" ht="16.5" spans="1:16">
@@ -6381,27 +6390,27 @@
       </c>
       <c r="K43" s="1">
         <f ca="1" t="shared" ref="K43:O43" si="20">RAND()</f>
-        <v>0.983653956724317</v>
+        <v>0.911889675970522</v>
       </c>
       <c r="L43" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.68279583310266</v>
+        <v>1.6822207186576</v>
       </c>
       <c r="M43" s="1">
         <f ca="1" t="shared" si="20"/>
-        <v>0.608726192883077</v>
+        <v>0.134025014360624</v>
       </c>
       <c r="N43" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>2.01624555520591</v>
+        <v>2.01186621528836</v>
       </c>
       <c r="O43" s="1">
         <f ca="1" t="shared" si="20"/>
-        <v>0.694931941963451</v>
+        <v>0.6481202355552</v>
       </c>
       <c r="P43" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>2.35038612477565</v>
+        <v>2.34563163877888</v>
       </c>
     </row>
     <row r="44" ht="16.5" spans="1:16">
@@ -6441,27 +6450,27 @@
       </c>
       <c r="K44" s="1">
         <f ca="1" t="shared" ref="K44:O44" si="21">RAND()</f>
-        <v>0.629515484205592</v>
+        <v>0.174742712374042</v>
       </c>
       <c r="L44" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.64002619805207</v>
+        <v>1.63655119016099</v>
       </c>
       <c r="M44" s="1">
         <f ca="1" t="shared" si="21"/>
-        <v>0.28056350586291</v>
+        <v>0.508080656048228</v>
       </c>
       <c r="N44" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>1.96310027135268</v>
+        <v>1.96136376660256</v>
       </c>
       <c r="O44" s="1">
         <f ca="1" t="shared" si="21"/>
-        <v>0.101723072110228</v>
+        <v>0.493314186255633</v>
       </c>
       <c r="P44" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>2.28480778984389</v>
+        <v>2.28606350955401</v>
       </c>
     </row>
     <row r="45" ht="16.5" spans="1:16">
@@ -6501,27 +6510,27 @@
       </c>
       <c r="K45" s="1">
         <f ca="1" t="shared" ref="K45:O45" si="22">RAND()</f>
-        <v>0.339521229103051</v>
+        <v>0.398193267946903</v>
       </c>
       <c r="L45" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.59983371721016</v>
+        <v>1.60026166337086</v>
       </c>
       <c r="M45" s="1">
         <f ca="1" t="shared" si="22"/>
-        <v>0.2944996438343</v>
+        <v>0.0433821561953887</v>
       </c>
       <c r="N45" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>1.91561812264616</v>
+        <v>1.91421445076806</v>
       </c>
       <c r="O45" s="1">
         <f ca="1" t="shared" si="22"/>
-        <v>0.887656494826967</v>
+        <v>0.308011036951478</v>
       </c>
       <c r="P45" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>2.23572893640336</v>
+        <v>2.23009740653441</v>
       </c>
     </row>
     <row r="46" ht="16.5" spans="1:16">
@@ -6561,27 +6570,27 @@
       </c>
       <c r="K46" s="1">
         <f ca="1" t="shared" ref="K46:O46" si="23">RAND()</f>
-        <v>0.00279814772137232</v>
+        <v>0.0165163615831188</v>
       </c>
       <c r="L46" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.56123162345381</v>
+        <v>1.56132723524739</v>
       </c>
       <c r="M46" s="1">
         <f ca="1" t="shared" si="23"/>
-        <v>0.152348796362948</v>
+        <v>0.0458547398593596</v>
       </c>
       <c r="N46" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>1.86896011506483</v>
+        <v>1.8683134955555</v>
       </c>
       <c r="O46" s="1">
         <f ca="1" t="shared" si="23"/>
-        <v>0.747709195623462</v>
+        <v>0.849556670814552</v>
       </c>
       <c r="P46" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>2.18083808824644</v>
+        <v>2.18090131477633</v>
       </c>
     </row>
     <row r="47" ht="16.5" spans="1:16">
@@ -6621,27 +6630,27 @@
       </c>
       <c r="K47" s="1">
         <f ca="1" t="shared" ref="K47:O47" si="24">RAND()</f>
-        <v>0.144728576019429</v>
+        <v>0.803547729891694</v>
       </c>
       <c r="L47" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.52763152384013</v>
+        <v>1.53202365153261</v>
       </c>
       <c r="M47" s="1">
         <f ca="1" t="shared" si="24"/>
-        <v>0.330653590050872</v>
+        <v>0.0986524650004146</v>
       </c>
       <c r="N47" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>1.82983588110714</v>
+        <v>1.83268133463262</v>
       </c>
       <c r="O47" s="1">
         <f ca="1" t="shared" si="24"/>
-        <v>0.918622998092507</v>
+        <v>0.74473216455245</v>
       </c>
       <c r="P47" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>2.13596003442776</v>
+        <v>2.13764621572963</v>
       </c>
     </row>
     <row r="48" ht="16.5" spans="1:16">
@@ -6681,27 +6690,27 @@
       </c>
       <c r="K48" s="1">
         <f ca="1" t="shared" ref="K48:O48" si="25">RAND()</f>
-        <v>0.440631091421108</v>
+        <v>0.409633223454231</v>
       </c>
       <c r="L48" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.49642956015801</v>
+        <v>1.4962317014263</v>
       </c>
       <c r="M48" s="1">
         <f ca="1" t="shared" si="25"/>
-        <v>0.945590254761364</v>
+        <v>0.167939778838008</v>
       </c>
       <c r="N48" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>1.7960822639118</v>
+        <v>1.79092067873804</v>
       </c>
       <c r="O48" s="1">
         <f ca="1" t="shared" si="25"/>
-        <v>0.641291709042339</v>
+        <v>0.364486362760386</v>
       </c>
       <c r="P48" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>2.09379263652271</v>
+        <v>2.0868642087131</v>
       </c>
     </row>
     <row r="49" ht="16.5" spans="1:16">
@@ -6741,27 +6750,27 @@
       </c>
       <c r="K49" s="1">
         <f ca="1" t="shared" ref="K49:O49" si="26">RAND()</f>
-        <v>0.639739450029199</v>
+        <v>0.764024981393227</v>
       </c>
       <c r="L49" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.46588138493369</v>
+        <v>1.46664164217341</v>
       </c>
       <c r="M49" s="1">
         <f ca="1" t="shared" si="26"/>
-        <v>0.213379767623794</v>
+        <v>0.0598300579193607</v>
       </c>
       <c r="N49" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>1.75468663351224</v>
+        <v>1.75450762391069</v>
       </c>
       <c r="O49" s="1">
         <f ca="1" t="shared" si="26"/>
-        <v>0.034027994774269</v>
+        <v>0.559085501219162</v>
       </c>
       <c r="P49" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>2.04239478348027</v>
+        <v>2.04542756181708</v>
       </c>
     </row>
     <row r="50" ht="16.5" spans="1:16">
@@ -6801,27 +6810,27 @@
       </c>
       <c r="K50" s="1">
         <f ca="1" t="shared" ref="K50:O50" si="27">RAND()</f>
-        <v>0.406342357933846</v>
+        <v>0.146586202562309</v>
       </c>
       <c r="L50" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.43401680465114</v>
+        <v>1.4324927251681</v>
       </c>
       <c r="M50" s="1">
         <f ca="1" t="shared" si="27"/>
-        <v>0.344558427656227</v>
+        <v>0.715504955166795</v>
       </c>
       <c r="N50" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>1.7176711015481</v>
+        <v>1.7183234940377</v>
       </c>
       <c r="O50" s="1">
         <f ca="1" t="shared" si="27"/>
-        <v>0.659079356298016</v>
+        <v>0.780340706327692</v>
       </c>
       <c r="P50" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>2.00317080185291</v>
+        <v>2.00453467675339</v>
       </c>
     </row>
     <row r="51" ht="16.5" spans="1:16">
@@ -6861,27 +6870,27 @@
       </c>
       <c r="K51" s="1">
         <f ca="1" t="shared" ref="K51:O51" si="28">RAND()</f>
-        <v>0.559286267431367</v>
+        <v>0.689219517528243</v>
       </c>
       <c r="L51" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.40568087775125</v>
+        <v>1.40641274667016</v>
       </c>
       <c r="M51" s="1">
         <f ca="1" t="shared" si="28"/>
-        <v>0.150133416157306</v>
+        <v>0.904185689737895</v>
       </c>
       <c r="N51" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>1.68252652719736</v>
+        <v>1.68750571096338</v>
       </c>
       <c r="O51" s="1">
         <f ca="1" t="shared" si="28"/>
-        <v>0.162938462407195</v>
+        <v>0.945419729124187</v>
       </c>
       <c r="P51" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>1.95944430302643</v>
+        <v>1.96883093229477</v>
       </c>
     </row>
     <row r="52" ht="16.5" spans="1:16">
@@ -6921,27 +6930,27 @@
       </c>
       <c r="K52" s="1">
         <f ca="1" t="shared" ref="K52:O52" si="29">RAND()</f>
-        <v>0.595153632369968</v>
+        <v>0.453932249856447</v>
       </c>
       <c r="L52" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.37780906671636</v>
+        <v>1.37704480982275</v>
       </c>
       <c r="M52" s="1">
         <f ca="1" t="shared" si="29"/>
-        <v>0.628285972547546</v>
+        <v>0.425270748392524</v>
       </c>
       <c r="N52" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>1.65179743786191</v>
+        <v>1.64993451034347</v>
       </c>
       <c r="O52" s="1">
         <f ca="1" t="shared" si="29"/>
-        <v>0.539516021970741</v>
+        <v>0.503380255106067</v>
       </c>
       <c r="P52" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>1.92530540692198</v>
+        <v>1.9232469211358</v>
       </c>
     </row>
     <row r="53" ht="16.5" spans="1:16">
@@ -6981,27 +6990,27 @@
       </c>
       <c r="K53" s="1">
         <f ca="1" t="shared" ref="K53:O53" si="30">RAND()</f>
-        <v>0.866004640213882</v>
+        <v>0.860716240825026</v>
       </c>
       <c r="L53" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.35224391554862</v>
+        <v>1.35221639672827</v>
       </c>
       <c r="M53" s="1">
         <f ca="1" t="shared" si="30"/>
-        <v>0.898710846527853</v>
+        <v>0.964133950229772</v>
       </c>
       <c r="N53" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>1.62230508058712</v>
+        <v>1.62261799873173</v>
       </c>
       <c r="O53" s="1">
         <f ca="1" t="shared" si="30"/>
-        <v>0.334504331609332</v>
+        <v>0.832987060243394</v>
       </c>
       <c r="P53" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>1.88943032937151</v>
+        <v>1.89233716216739</v>
       </c>
     </row>
     <row r="54" ht="16.5" spans="1:16">
@@ -7155,27 +7164,27 @@
       </c>
       <c r="K56" s="1">
         <f ca="1" t="shared" ref="K56:O56" si="31">RAND()</f>
-        <v>0.753272907164252</v>
+        <v>0.505998370777141</v>
       </c>
       <c r="L56" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.27663136906359</v>
+        <v>1.2754824166723</v>
       </c>
       <c r="M56" s="1">
         <f ca="1" t="shared" si="31"/>
-        <v>0.57683346919195</v>
+        <v>0.887917316122551</v>
       </c>
       <c r="N56" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>1.53022069629418</v>
+        <v>1.53051718399973</v>
       </c>
       <c r="O56" s="1">
         <f ca="1" t="shared" si="31"/>
-        <v>0.779788947415073</v>
+        <v>0.413647910706335</v>
       </c>
       <c r="P56" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>1.78475304897914</v>
+        <v>1.78334827530201</v>
       </c>
     </row>
     <row r="57" ht="16.5" spans="1:16">
@@ -7215,27 +7224,27 @@
       </c>
       <c r="K57" s="1">
         <f ca="1" t="shared" ref="K57:O57" si="32">RAND()</f>
-        <v>0.587860713617248</v>
+        <v>0.293269814130132</v>
       </c>
       <c r="L57" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.25269885644413</v>
+        <v>1.25137893618019</v>
       </c>
       <c r="M57" s="1">
         <f ca="1" t="shared" si="32"/>
-        <v>0.27416680541071</v>
+        <v>0.880404166919311</v>
       </c>
       <c r="N57" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>1.50035583758525</v>
+        <v>1.50175217562937</v>
       </c>
       <c r="O57" s="1">
         <f ca="1" t="shared" si="32"/>
-        <v>0.333641111785494</v>
+        <v>0.0331912940938</v>
       </c>
       <c r="P57" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>1.74827929451468</v>
+        <v>1.74832946129772</v>
       </c>
     </row>
     <row r="58" ht="16.5" spans="1:16">
@@ -7275,27 +7284,27 @@
       </c>
       <c r="K58" s="1">
         <f ca="1" t="shared" ref="K58:O58" si="33">RAND()</f>
-        <v>0.301286115166365</v>
+        <v>0.589209809388357</v>
       </c>
       <c r="L58" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.22912210162572</v>
+        <v>1.23036688451427</v>
       </c>
       <c r="M58" s="1">
         <f ca="1" t="shared" si="33"/>
-        <v>0.777820961887139</v>
+        <v>0.36898719975435</v>
       </c>
       <c r="N58" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>1.47459012458125</v>
+        <v>1.47406739308464</v>
       </c>
       <c r="O58" s="1">
         <f ca="1" t="shared" si="33"/>
-        <v>0.803461986540639</v>
+        <v>0.606893921209571</v>
       </c>
       <c r="P58" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>1.72016900159073</v>
+        <v>1.71879644575152</v>
       </c>
     </row>
     <row r="59" ht="16.5" spans="1:16">
@@ -7335,27 +7344,27 @@
       </c>
       <c r="K59" s="1">
         <f ca="1" t="shared" ref="K59:O59" si="34">RAND()</f>
-        <v>0.236664281734846</v>
+        <v>0.0402358999351617</v>
       </c>
       <c r="L59" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.20733997794554</v>
+        <v>1.20652004096162</v>
       </c>
       <c r="M59" s="1">
         <f ca="1" t="shared" si="34"/>
-        <v>0.578323492919942</v>
+        <v>0.640098458570236</v>
       </c>
       <c r="N59" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>1.44768506693595</v>
+        <v>1.44712299278505</v>
       </c>
       <c r="O59" s="1">
         <f ca="1" t="shared" si="34"/>
-        <v>0.0919238450542239</v>
+        <v>0.883164268629318</v>
       </c>
       <c r="P59" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>1.68599981256866</v>
+        <v>1.68874055688278</v>
       </c>
     </row>
     <row r="60" ht="16.5" spans="1:16">
@@ -7395,27 +7404,27 @@
       </c>
       <c r="K60" s="1">
         <f ca="1" t="shared" ref="K60:O60" si="35">RAND()</f>
-        <v>0.586069593443086</v>
+        <v>0.803113652213788</v>
       </c>
       <c r="L60" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.18798590309454</v>
+        <v>1.18886118305101</v>
       </c>
       <c r="M60" s="1">
         <f ca="1" t="shared" si="35"/>
-        <v>0.492104562715373</v>
+        <v>0.340847626141369</v>
       </c>
       <c r="N60" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>1.42386873271624</v>
+        <v>1.42413403437794</v>
       </c>
       <c r="O60" s="1">
         <f ca="1" t="shared" si="35"/>
-        <v>0.212699366070055</v>
+        <v>0.877728657823998</v>
       </c>
       <c r="P60" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>1.65862479678748</v>
+        <v>1.66157198162457</v>
       </c>
     </row>
     <row r="61" ht="16.5" spans="1:16">
@@ -7455,27 +7464,27 @@
       </c>
       <c r="K61" s="1">
         <f ca="1" t="shared" ref="K61:O61" si="36">RAND()</f>
-        <v>0.431586827499292</v>
+        <v>0.474483587633084</v>
       </c>
       <c r="L61" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.16727567746313</v>
+        <v>1.16744290212128</v>
       </c>
       <c r="M61" s="1">
         <f ca="1" t="shared" si="36"/>
-        <v>0.973634833996631</v>
+        <v>0.232863233973853</v>
       </c>
       <c r="N61" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>1.40107120308719</v>
+        <v>1.39835067405033</v>
       </c>
       <c r="O61" s="1">
         <f ca="1" t="shared" si="36"/>
-        <v>0.730290477864451</v>
+        <v>0.868063023123045</v>
       </c>
       <c r="P61" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>1.63391809817039</v>
+        <v>1.63173464854725</v>
       </c>
     </row>
     <row r="62" ht="16.5" spans="1:16">
@@ -7515,27 +7524,27 @@
       </c>
       <c r="K62" s="1">
         <f ca="1" t="shared" ref="K62:O62" si="37">RAND()</f>
-        <v>0.0628397811660899</v>
+        <v>0.293622027313524</v>
       </c>
       <c r="L62" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.14646644507653</v>
+        <v>1.14733660764397</v>
       </c>
       <c r="M62" s="1">
         <f ca="1" t="shared" si="37"/>
-        <v>0.172027159678613</v>
+        <v>0.394786237981992</v>
       </c>
       <c r="N62" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>1.37334458026876</v>
+        <v>1.37505465411505</v>
       </c>
       <c r="O62" s="1">
         <f ca="1" t="shared" si="37"/>
-        <v>0.516837242757877</v>
+        <v>0.96996261999011</v>
       </c>
       <c r="P62" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>1.60152281905293</v>
+        <v>1.60494139841993</v>
       </c>
     </row>
     <row r="63" ht="16.5" spans="1:16">
@@ -7575,27 +7584,27 @@
       </c>
       <c r="K63" s="1">
         <f ca="1" t="shared" ref="K63:O63" si="38">RAND()</f>
-        <v>0.596025551897708</v>
+        <v>0.32049113669176</v>
       </c>
       <c r="L63" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.12967349355267</v>
+        <v>1.12866810621003</v>
       </c>
       <c r="M63" s="1">
         <f ca="1" t="shared" si="38"/>
-        <v>0.143852694783666</v>
+        <v>0.124439810916418</v>
       </c>
       <c r="N63" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>1.3527790374945</v>
+        <v>1.35170281519751</v>
       </c>
       <c r="O63" s="1">
         <f ca="1" t="shared" si="38"/>
-        <v>0.346920239149978</v>
+        <v>0.851498574986947</v>
       </c>
       <c r="P63" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>1.57662554709267</v>
+        <v>1.57739046203379</v>
       </c>
     </row>
     <row r="64" ht="16.5" spans="1:16">
@@ -7635,27 +7644,27 @@
       </c>
       <c r="K64" s="1">
         <f ca="1" t="shared" ref="K64:O64" si="39">RAND()</f>
-        <v>0.591967118389784</v>
+        <v>0.357734283381208</v>
       </c>
       <c r="L64" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.11146163498049</v>
+        <v>1.11063408425772</v>
       </c>
       <c r="M64" s="1">
         <f ca="1" t="shared" si="39"/>
-        <v>0.816976994240393</v>
+        <v>0.294031274553335</v>
       </c>
       <c r="N64" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>1.33339565508303</v>
+        <v>1.33072052347657</v>
       </c>
       <c r="O64" s="1">
         <f ca="1" t="shared" si="39"/>
-        <v>0.254328907451207</v>
+        <v>0.42369145208134</v>
       </c>
       <c r="P64" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>1.55334182480213</v>
+        <v>1.55126505548853</v>
       </c>
     </row>
     <row r="65" ht="16.5" spans="1:16">
@@ -7695,27 +7704,27 @@
       </c>
       <c r="K65" s="1">
         <f ca="1" t="shared" ref="K65:O65" si="40">RAND()</f>
-        <v>0.817072648596606</v>
+        <v>0.786266390918642</v>
       </c>
       <c r="L65" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.09461200460085</v>
+        <v>1.09450656651654</v>
       </c>
       <c r="M65" s="1">
         <f ca="1" t="shared" si="40"/>
-        <v>0.279014512767259</v>
+        <v>0.152366378618641</v>
       </c>
       <c r="N65" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>1.31119196498681</v>
+        <v>1.31065305858621</v>
       </c>
       <c r="O65" s="1">
         <f ca="1" t="shared" si="40"/>
-        <v>0.0883012720346654</v>
+        <v>0.702459518509709</v>
       </c>
       <c r="P65" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>1.52711918660241</v>
+        <v>1.52868230991445</v>
       </c>
     </row>
     <row r="66" ht="16.5" spans="1:16">
@@ -7755,27 +7764,27 @@
       </c>
       <c r="K66" s="1">
         <f ca="1" t="shared" ref="K66:O66" si="44">RAND()</f>
-        <v>0.360046580249211</v>
+        <v>0.839804998418849</v>
       </c>
       <c r="L66" s="1">
         <f ca="1" t="shared" ref="L66:L129" si="45">J66+($R$1*$R$7*K66/MAX(1,($A66*($A66-1)))+$R$1*$R$7/$A66)/100</f>
-        <v>1.07600207759794</v>
+        <v>1.07759358388899</v>
       </c>
       <c r="M66" s="1">
         <f ca="1" t="shared" si="44"/>
-        <v>0.928797359008673</v>
+        <v>0.557956060331373</v>
       </c>
       <c r="N66" s="1">
         <f ca="1" t="shared" ref="N66:N129" si="46">L66+($R$1*$R$7*M66/MAX(1,($A66*($A66-1)))+$R$1*$R$7/$A66)/100</f>
-        <v>1.29139087652927</v>
+        <v>1.29175218812758</v>
       </c>
       <c r="O66" s="1">
         <f ca="1" t="shared" si="44"/>
-        <v>0.362521079174264</v>
+        <v>0.14895778483136</v>
       </c>
       <c r="P66" s="1">
         <f ca="1" t="shared" ref="P66:P129" si="47">N66+($R$1*$R$7*O66/MAX(1,($A66*($A66-1)))+$R$1*$R$7/$A66)/100</f>
-        <v>1.50490116280153</v>
+        <v>1.50455401924073</v>
       </c>
     </row>
     <row r="67" ht="16.5" spans="1:16">
@@ -7815,27 +7824,27 @@
       </c>
       <c r="K67" s="1">
         <f ca="1" t="shared" ref="K67:O67" si="49">RAND()</f>
-        <v>0.661348153544794</v>
+        <v>0.541780312502568</v>
       </c>
       <c r="L67" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>1.06044909196245</v>
+        <v>1.06006446813812</v>
       </c>
       <c r="M67" s="1">
         <f ca="1" t="shared" si="49"/>
-        <v>0.762310270561727</v>
+        <v>0.396699589123628</v>
       </c>
       <c r="N67" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>1.27199218793769</v>
+        <v>1.27043147380943</v>
       </c>
       <c r="O67" s="1">
         <f ca="1" t="shared" si="49"/>
-        <v>0.757531367699347</v>
+        <v>0.363061343493959</v>
       </c>
       <c r="P67" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.4835199112184</v>
+        <v>1.48069027253675</v>
       </c>
     </row>
     <row r="68" ht="16.5" spans="1:16">
@@ -7875,27 +7884,27 @@
       </c>
       <c r="K68" s="1">
         <f ca="1" t="shared" ref="K68:O68" si="50">RAND()</f>
-        <v>0.818918236642868</v>
+        <v>0.911434416744683</v>
       </c>
       <c r="L68" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>1.04488943276021</v>
+        <v>1.04517815353937</v>
       </c>
       <c r="M68" s="1">
         <f ca="1" t="shared" si="50"/>
-        <v>0.358878965478386</v>
+        <v>0.709381911648488</v>
       </c>
       <c r="N68" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>1.25197955707582</v>
+        <v>1.25336211337219</v>
       </c>
       <c r="O68" s="1">
         <f ca="1" t="shared" si="50"/>
-        <v>0.38364125095912</v>
+        <v>0.882139918964819</v>
       </c>
       <c r="P68" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.45914695853743</v>
+        <v>1.4620852094558</v>
       </c>
     </row>
     <row r="69" ht="16.5" spans="1:16">
@@ -7935,27 +7944,27 @@
       </c>
       <c r="K69" s="1">
         <f ca="1" t="shared" ref="K69:O69" si="51">RAND()</f>
-        <v>0.245145330108641</v>
+        <v>0.0376599138853935</v>
       </c>
       <c r="L69" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>1.02756431201833</v>
+        <v>1.02693584433969</v>
       </c>
       <c r="M69" s="1">
         <f ca="1" t="shared" si="51"/>
-        <v>0.919415005550831</v>
+        <v>0.185900322532944</v>
       </c>
       <c r="N69" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>1.23329037151714</v>
+        <v>1.23044010782761</v>
       </c>
       <c r="O69" s="1">
         <f ca="1" t="shared" si="51"/>
-        <v>0.204941300190674</v>
+        <v>0.318541829813728</v>
       </c>
       <c r="P69" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.43685230960815</v>
+        <v>1.43434613883099</v>
       </c>
     </row>
     <row r="70" ht="16.5" spans="1:16">
@@ -7995,27 +8004,27 @@
       </c>
       <c r="K70" s="1">
         <f ca="1" t="shared" ref="K70:O70" si="52">RAND()</f>
-        <v>0.647343622898482</v>
+        <v>0.833298672642534</v>
       </c>
       <c r="L70" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>1.01366865771441</v>
+        <v>1.0142155843313</v>
       </c>
       <c r="M70" s="1">
         <f ca="1" t="shared" si="52"/>
-        <v>0.10104978787263</v>
+        <v>0.0540923818131593</v>
       </c>
       <c r="N70" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>1.21396586297286</v>
+        <v>1.21437467957193</v>
       </c>
       <c r="O70" s="1">
         <f ca="1" t="shared" si="52"/>
-        <v>0.357395954615545</v>
+        <v>0.796403437311043</v>
       </c>
       <c r="P70" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.41501702754525</v>
+        <v>1.41671704262284</v>
       </c>
     </row>
     <row r="71" ht="16.5" spans="1:16">
@@ -8055,27 +8064,27 @@
       </c>
       <c r="K71" s="1">
         <f ca="1" t="shared" ref="K71:O71" si="53">RAND()</f>
-        <v>0.0456641687027004</v>
+        <v>0.454782891494287</v>
       </c>
       <c r="L71" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.997273326196293</v>
+        <v>0.998442236832841</v>
       </c>
       <c r="M71" s="1">
         <f ca="1" t="shared" si="53"/>
-        <v>0.514604013541268</v>
+        <v>0.992500363772983</v>
       </c>
       <c r="N71" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>1.1958864805207</v>
+        <v>1.19842080930076</v>
       </c>
       <c r="O71" s="1">
         <f ca="1" t="shared" si="53"/>
-        <v>0.898199959278147</v>
+        <v>0.0206433022141357</v>
       </c>
       <c r="P71" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.39559562326149</v>
+        <v>1.39562264730709</v>
       </c>
     </row>
     <row r="72" ht="16.5" spans="1:16">
@@ -8115,27 +8124,27 @@
       </c>
       <c r="K72" s="1">
         <f ca="1" t="shared" ref="K72:O72" si="54">RAND()</f>
-        <v>0.0154145491429656</v>
+        <v>0.684279089279556</v>
       </c>
       <c r="L72" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.982980426715931</v>
+        <v>0.98483763610303</v>
       </c>
       <c r="M72" s="1">
         <f ca="1" t="shared" si="54"/>
-        <v>0.178933080650038</v>
+        <v>0.49285744821491</v>
       </c>
       <c r="N72" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>1.17784346021955</v>
+        <v>1.18057233082846</v>
       </c>
       <c r="O72" s="1">
         <f ca="1" t="shared" si="54"/>
-        <v>0.716847816867781</v>
+        <v>0.903795997732738</v>
       </c>
       <c r="P72" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.37420010003298</v>
+        <v>1.37744806217025</v>
       </c>
     </row>
     <row r="73" ht="16.5" spans="1:16">
@@ -8175,27 +8184,27 @@
       </c>
       <c r="K73" s="1">
         <f ca="1" t="shared" ref="K73:O73" si="55">RAND()</f>
-        <v>0.37186661428282</v>
+        <v>0.0161383054757671</v>
       </c>
       <c r="L73" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.970135320672359</v>
+        <v>0.969175021247176</v>
       </c>
       <c r="M73" s="1">
         <f ca="1" t="shared" si="55"/>
-        <v>0.817217523774017</v>
+        <v>0.157697408383412</v>
       </c>
       <c r="N73" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>1.16400809098302</v>
+        <v>1.16126739688014</v>
       </c>
       <c r="O73" s="1">
         <f ca="1" t="shared" si="55"/>
-        <v>0.642159565661802</v>
+        <v>0.37708534389963</v>
       </c>
       <c r="P73" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.35740828699361</v>
+        <v>1.35395201693996</v>
       </c>
     </row>
     <row r="74" ht="16.5" spans="1:16">
@@ -8235,27 +8244,27 @@
       </c>
       <c r="K74" s="1">
         <f ca="1" t="shared" ref="K74:O74" si="56">RAND()</f>
-        <v>0.458871667073488</v>
+        <v>0.088839576062663</v>
       </c>
       <c r="L74" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.956912562596198</v>
+        <v>0.955941017151763</v>
       </c>
       <c r="M74" s="1">
         <f ca="1" t="shared" si="56"/>
-        <v>0.741807702610128</v>
+        <v>0.890386021534666</v>
       </c>
       <c r="N74" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>1.14790132711218</v>
+        <v>1.1473198845599</v>
       </c>
       <c r="O74" s="1">
         <f ca="1" t="shared" si="56"/>
-        <v>0.920383494127865</v>
+        <v>0.829601057279817</v>
       </c>
       <c r="P74" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.33935895500772</v>
+        <v>1.33853915674226</v>
       </c>
     </row>
     <row r="75" ht="16.5" spans="1:16">
@@ -8409,27 +8418,27 @@
       </c>
       <c r="K77" s="1">
         <f ca="1" t="shared" ref="K77:O77" si="57">RAND()</f>
-        <v>0.304822120396118</v>
+        <v>0.374969722632078</v>
       </c>
       <c r="L77" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.91831693776517</v>
+        <v>0.918486768802162</v>
       </c>
       <c r="M77" s="1">
         <f ca="1" t="shared" si="57"/>
-        <v>0.224595068739552</v>
+        <v>0.676424923134985</v>
       </c>
       <c r="N77" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>1.1004396416158</v>
+        <v>1.1017033765108</v>
       </c>
       <c r="O77" s="1">
         <f ca="1" t="shared" si="57"/>
-        <v>0.673304807820807</v>
+        <v>0.543404588667065</v>
       </c>
       <c r="P77" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.28364869536105</v>
+        <v>1.28459793498863</v>
       </c>
     </row>
     <row r="78" ht="16.5" spans="1:16">
@@ -8469,27 +8478,27 @@
       </c>
       <c r="K78" s="1">
         <f ca="1" t="shared" ref="K78:O78" si="58">RAND()</f>
-        <v>0.639904827380355</v>
+        <v>0.790652243249524</v>
       </c>
       <c r="L78" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.907045571875914</v>
+        <v>0.907401059630356</v>
       </c>
       <c r="M78" s="1">
         <f ca="1" t="shared" si="58"/>
-        <v>0.820612236203548</v>
+        <v>0.281598985982435</v>
       </c>
       <c r="N78" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>1.08820149273367</v>
+        <v>1.08728589661029</v>
       </c>
       <c r="O78" s="1">
         <f ca="1" t="shared" si="58"/>
-        <v>0.358458922378442</v>
+        <v>0.954829730244715</v>
       </c>
       <c r="P78" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.26826757836744</v>
+        <v>1.26875832488735</v>
       </c>
     </row>
     <row r="79" ht="16.5" spans="1:16">
@@ -8529,27 +8538,27 @@
       </c>
       <c r="K79" s="1">
         <f ca="1" t="shared" ref="K79:O79" si="59">RAND()</f>
-        <v>0.785687858364907</v>
+        <v>0.315758092566375</v>
       </c>
       <c r="L79" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.895611470603636</v>
+        <v>0.894531711901002</v>
       </c>
       <c r="M79" s="1">
         <f ca="1" t="shared" si="59"/>
-        <v>0.310512680616204</v>
+        <v>0.424558297279346</v>
       </c>
       <c r="N79" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>1.07324801322643</v>
+        <v>1.07243029739925</v>
       </c>
       <c r="O79" s="1">
         <f ca="1" t="shared" si="59"/>
-        <v>0.177205735967582</v>
+        <v>0.427192351463482</v>
       </c>
       <c r="P79" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.25057825617621</v>
+        <v>1.25033493516984</v>
       </c>
     </row>
     <row r="80" ht="16.5" spans="1:16">
@@ -8589,27 +8598,27 @@
       </c>
       <c r="K80" s="1">
         <f ca="1" t="shared" ref="K80:O80" si="60">RAND()</f>
-        <v>0.586454031746368</v>
+        <v>0.802179317337763</v>
       </c>
       <c r="L80" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.883689234929909</v>
+        <v>0.884172358743795</v>
       </c>
       <c r="M80" s="1">
         <f ca="1" t="shared" si="60"/>
-        <v>0.992456273518966</v>
+        <v>0.913984936065974</v>
       </c>
       <c r="N80" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>1.06059541743146</v>
+        <v>1.06090280212544</v>
       </c>
       <c r="O80" s="1">
         <f ca="1" t="shared" si="60"/>
-        <v>0.261997607927235</v>
+        <v>0.039232702724977</v>
       </c>
       <c r="P80" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.23586571392438</v>
+        <v>1.23567420934673</v>
       </c>
     </row>
     <row r="81" ht="16.5" spans="1:16">
@@ -8649,27 +8658,27 @@
       </c>
       <c r="K81" s="1">
         <f ca="1" t="shared" ref="K81:O81" si="61">RAND()</f>
-        <v>0.0289345447697966</v>
+        <v>0.294965634927237</v>
       </c>
       <c r="L81" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.871297357075605</v>
+        <v>0.871878247747151</v>
       </c>
       <c r="M81" s="1">
         <f ca="1" t="shared" si="61"/>
-        <v>0.979176876440262</v>
+        <v>0.254091744215868</v>
       </c>
       <c r="N81" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>1.04593543316657</v>
+        <v>1.04493306832788</v>
       </c>
       <c r="O81" s="1">
         <f ca="1" t="shared" si="61"/>
-        <v>0.796291009853386</v>
+        <v>0.439248140713212</v>
       </c>
       <c r="P81" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.2201741698653</v>
+        <v>1.21839218610348</v>
       </c>
     </row>
     <row r="82" ht="16.5" spans="1:16">
@@ -8709,27 +8718,27 @@
       </c>
       <c r="K82" s="1">
         <f ca="1" t="shared" ref="K82:O82" si="62">RAND()</f>
-        <v>0.513739055651798</v>
+        <v>0.187326469575055</v>
       </c>
       <c r="L82" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.861464444285184</v>
+        <v>0.860769306370391</v>
       </c>
       <c r="M82" s="1">
         <f ca="1" t="shared" si="62"/>
-        <v>0.242551862291542</v>
+        <v>0.910033927263722</v>
       </c>
       <c r="N82" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>1.03235136028821</v>
+        <v>1.03307771195623</v>
       </c>
       <c r="O82" s="1">
         <f ca="1" t="shared" si="62"/>
-        <v>0.924357655098216</v>
+        <v>0.812066726190274</v>
       </c>
       <c r="P82" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.20469027010926</v>
+        <v>1.20517748368793</v>
       </c>
     </row>
     <row r="83" ht="16.5" spans="1:16">
@@ -8769,27 +8778,27 @@
       </c>
       <c r="K83" s="1">
         <f ca="1" t="shared" ref="K83:O83" si="63">RAND()</f>
-        <v>0.715026111812996</v>
+        <v>0.88243455369104</v>
       </c>
       <c r="L83" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.851259765182628</v>
+        <v>0.851607587600261</v>
       </c>
       <c r="M83" s="1">
         <f ca="1" t="shared" si="63"/>
-        <v>0.356226457665214</v>
+        <v>0.938347197422208</v>
       </c>
       <c r="N83" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>1.02029257534761</v>
+        <v>1.02184986271686</v>
       </c>
       <c r="O83" s="1">
         <f ca="1" t="shared" si="63"/>
-        <v>0.545896977005114</v>
+        <v>0.527815755512266</v>
       </c>
       <c r="P83" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.18971946156903</v>
+        <v>1.19123918181142</v>
       </c>
     </row>
     <row r="84" ht="16.5" spans="1:16">
@@ -8829,27 +8838,27 @@
       </c>
       <c r="K84" s="1">
         <f ca="1" t="shared" ref="K84:O84" si="64">RAND()</f>
-        <v>0.279655625332477</v>
+        <v>0.645157318857686</v>
       </c>
       <c r="L84" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.840002828038435</v>
+        <v>0.840743927563949</v>
       </c>
       <c r="M84" s="1">
         <f ca="1" t="shared" si="64"/>
-        <v>0.0735944213613304</v>
+        <v>0.237065440625187</v>
       </c>
       <c r="N84" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>1.0064171099977</v>
+        <v>1.00748966707036</v>
       </c>
       <c r="O84" s="1">
         <f ca="1" t="shared" si="64"/>
-        <v>0.633941431714504</v>
+        <v>0.297794734180048</v>
       </c>
       <c r="P84" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.17396756426712</v>
+        <v>1.17435854267008</v>
       </c>
     </row>
     <row r="85" ht="16.5" spans="1:16">
@@ -8889,27 +8898,27 @@
       </c>
       <c r="K85" s="1">
         <f ca="1" t="shared" ref="K85:O85" si="65">RAND()</f>
-        <v>0.637399301207959</v>
+        <v>0.0370046279291725</v>
       </c>
       <c r="L85" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.830607588978294</v>
+        <v>0.829419200210186</v>
       </c>
       <c r="M85" s="1">
         <f ca="1" t="shared" si="65"/>
-        <v>0.0734367085112446</v>
+        <v>0.959949618231128</v>
       </c>
       <c r="N85" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.995038659915967</v>
+        <v>0.99560498688999</v>
       </c>
       <c r="O85" s="1">
         <f ca="1" t="shared" si="65"/>
-        <v>0.684115706313748</v>
+        <v>0.922315129725974</v>
       </c>
       <c r="P85" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.1606784758579</v>
+        <v>1.16171628189719</v>
       </c>
     </row>
     <row r="86" ht="16.5" spans="1:16">
@@ -8949,27 +8958,27 @@
       </c>
       <c r="K86" s="1">
         <f ca="1" t="shared" ref="K86:O86" si="66">RAND()</f>
-        <v>0.499851088359718</v>
+        <v>0.456419154704697</v>
       </c>
       <c r="L86" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.820461897061535</v>
+        <v>0.820377952988085</v>
       </c>
       <c r="M86" s="1">
         <f ca="1" t="shared" si="66"/>
-        <v>0.421597743782684</v>
+        <v>0.851307321211443</v>
       </c>
       <c r="N86" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.983629691020107</v>
+        <v>0.984376278062695</v>
       </c>
       <c r="O86" s="1">
         <f ca="1" t="shared" si="66"/>
-        <v>0.155375553505144</v>
+        <v>0.217463954316514</v>
       </c>
       <c r="P86" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.14628293788823</v>
+        <v>1.1471495277223</v>
       </c>
     </row>
     <row r="87" ht="16.5" spans="1:16">
@@ -9123,27 +9132,27 @@
       </c>
       <c r="K89" s="1">
         <f ca="1" t="shared" ref="K89:O89" si="67">RAND()</f>
-        <v>0.68662060344619</v>
+        <v>0.596909151310536</v>
       </c>
       <c r="L89" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.792538579457623</v>
+        <v>0.79237687386208</v>
       </c>
       <c r="M89" s="1">
         <f ca="1" t="shared" si="67"/>
-        <v>0.633449220631183</v>
+        <v>0.601689280259883</v>
       </c>
       <c r="N89" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.950498558460328</v>
+        <v>0.950279605323364</v>
       </c>
       <c r="O89" s="1">
         <f ca="1" t="shared" si="67"/>
-        <v>0.496295726727763</v>
+        <v>0.679959841764056</v>
       </c>
       <c r="P89" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.1082113172154</v>
+        <v>1.10832342008516</v>
       </c>
     </row>
     <row r="90" ht="16.5" spans="1:16">
@@ -9183,27 +9192,27 @@
       </c>
       <c r="K90" s="1">
         <f ca="1" t="shared" ref="K90:O90" si="68">RAND()</f>
-        <v>0.342939413943605</v>
+        <v>0.157712383731999</v>
       </c>
       <c r="L90" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.782933166995968</v>
+        <v>0.782606796590334</v>
       </c>
       <c r="M90" s="1">
         <f ca="1" t="shared" si="68"/>
-        <v>0.159111319268042</v>
+        <v>0.378740460557913</v>
       </c>
       <c r="N90" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.938269701240848</v>
+        <v>0.938330317830848</v>
       </c>
       <c r="O90" s="1">
         <f ca="1" t="shared" si="68"/>
-        <v>0.0890890061556266</v>
+        <v>0.775816770608026</v>
       </c>
       <c r="P90" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.09348285602697</v>
+        <v>1.09475348834086</v>
       </c>
     </row>
     <row r="91" ht="16.5" spans="1:16">
@@ -9243,27 +9252,27 @@
       </c>
       <c r="K91" s="1">
         <f ca="1" t="shared" ref="K91:O91" si="69">RAND()</f>
-        <v>0.602926172961376</v>
+        <v>0.959074384491831</v>
       </c>
       <c r="L91" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.774596801646301</v>
+        <v>0.775210390325342</v>
       </c>
       <c r="M91" s="1">
         <f ca="1" t="shared" si="69"/>
-        <v>0.903526362546955</v>
+        <v>0.929574152627153</v>
       </c>
       <c r="N91" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.929486772158554</v>
+        <v>0.930145237180056</v>
       </c>
       <c r="O91" s="1">
         <f ca="1" t="shared" si="69"/>
-        <v>0.292221613529058</v>
+        <v>0.641254946197238</v>
       </c>
       <c r="P91" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.08332355845902</v>
+        <v>1.08458335431583</v>
       </c>
     </row>
     <row r="92" ht="16.5" spans="1:16">
@@ -9303,27 +9312,27 @@
       </c>
       <c r="K92" s="1">
         <f ca="1" t="shared" ref="K92:O92" si="70">RAND()</f>
-        <v>0.762201582383329</v>
+        <v>0.499269511518253</v>
       </c>
       <c r="L92" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.766265980688265</v>
+        <v>0.765822944964463</v>
       </c>
       <c r="M92" s="1">
         <f ca="1" t="shared" si="70"/>
-        <v>0.622348248546139</v>
+        <v>0.789161778408258</v>
       </c>
       <c r="N92" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.918962977737097</v>
+        <v>0.91880101975592</v>
       </c>
       <c r="O92" s="1">
         <f ca="1" t="shared" si="70"/>
-        <v>0.992159233767402</v>
+        <v>0.909241265419956</v>
       </c>
       <c r="P92" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.07228309952293</v>
+        <v>1.07198142628373</v>
       </c>
     </row>
     <row r="93" ht="16.5" spans="1:16">
@@ -9363,27 +9372,27 @@
       </c>
       <c r="K93" s="1">
         <f ca="1" t="shared" ref="K93:O93" si="71">RAND()</f>
-        <v>0.210426266952822</v>
+        <v>0.65872273568949</v>
       </c>
       <c r="L93" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.756940263077395</v>
+        <v>0.757679213300587</v>
       </c>
       <c r="M93" s="1">
         <f ca="1" t="shared" si="71"/>
-        <v>0.981081366594728</v>
+        <v>0.566203245840586</v>
       </c>
       <c r="N93" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.908557430165189</v>
+        <v>0.908612515354171</v>
       </c>
       <c r="O93" s="1">
         <f ca="1" t="shared" si="71"/>
-        <v>0.131915272244682</v>
+        <v>0.912115639961176</v>
       </c>
       <c r="P93" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.05877487292164</v>
+        <v>1.06011600267279</v>
       </c>
     </row>
     <row r="94" ht="16.5" spans="1:16">
@@ -9423,27 +9432,27 @@
       </c>
       <c r="K94" s="1">
         <f ca="1" t="shared" ref="K94:O94" si="72">RAND()</f>
-        <v>0.765949036773986</v>
+        <v>0.660379270489586</v>
       </c>
       <c r="L94" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.74962249844641</v>
+        <v>0.749452224629822</v>
       </c>
       <c r="M94" s="1">
         <f ca="1" t="shared" si="72"/>
-        <v>0.534094617811786</v>
+        <v>0.933877624885091</v>
       </c>
       <c r="N94" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.898871038152558</v>
+        <v>0.899345575637701</v>
       </c>
       <c r="O94" s="1">
         <f ca="1" t="shared" si="72"/>
-        <v>0.104972111582092</v>
+        <v>0.602204095319864</v>
       </c>
       <c r="P94" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.04742744478414</v>
+        <v>1.04870396933983</v>
       </c>
     </row>
     <row r="95" ht="16.5" spans="1:16">
@@ -9483,27 +9492,27 @@
       </c>
       <c r="K95" s="1">
         <f ca="1" t="shared" ref="K95:O95" si="73">RAND()</f>
-        <v>0.635392145688059</v>
+        <v>0.179515715968981</v>
       </c>
       <c r="L95" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.741359918967112</v>
+        <v>0.740640278755476</v>
       </c>
       <c r="M95" s="1">
         <f ca="1" t="shared" si="73"/>
-        <v>0.563677505734053</v>
+        <v>0.144714424176943</v>
       </c>
       <c r="N95" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.889058243101078</v>
+        <v>0.887677233577444</v>
       </c>
       <c r="O95" s="1">
         <f ca="1" t="shared" si="73"/>
-        <v>0.419012207758694</v>
+        <v>0.743662951231508</v>
       </c>
       <c r="P95" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.03652820060131</v>
+        <v>1.03565968024033</v>
       </c>
     </row>
     <row r="96" ht="16.5" spans="1:16">
@@ -9543,27 +9552,27 @@
       </c>
       <c r="K96" s="1">
         <f ca="1" t="shared" ref="K96:O96" si="74">RAND()</f>
-        <v>0.28948885815763</v>
+        <v>0.281867208161493</v>
       </c>
       <c r="L96" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.732944562849113</v>
+        <v>0.732932784711381</v>
       </c>
       <c r="M96" s="1">
         <f ca="1" t="shared" si="74"/>
-        <v>0.16013091761248</v>
+        <v>0.507322886686909</v>
       </c>
       <c r="N96" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.878455179496711</v>
+        <v>0.878979935420931</v>
       </c>
       <c r="O96" s="1">
         <f ca="1" t="shared" si="74"/>
-        <v>0.0222756315154289</v>
+        <v>0.2988528445258</v>
       </c>
       <c r="P96" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.02375276109973</v>
+        <v>1.02470492637888</v>
       </c>
     </row>
     <row r="97" ht="16.5" spans="1:16">
@@ -9603,27 +9612,27 @@
       </c>
       <c r="K97" s="1">
         <f ca="1" t="shared" ref="K97:O97" si="75">RAND()</f>
-        <v>0.412355168955357</v>
+        <v>0.336461635322046</v>
       </c>
       <c r="L97" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.725426590058287</v>
+        <v>0.725311751158711</v>
       </c>
       <c r="M97" s="1">
         <f ca="1" t="shared" si="75"/>
-        <v>0.133941093370888</v>
+        <v>0.742980805502537</v>
       </c>
       <c r="N97" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.869379264081151</v>
+        <v>0.870185998430195</v>
       </c>
       <c r="O97" s="1">
         <f ca="1" t="shared" si="75"/>
-        <v>0.394159002778099</v>
+        <v>0.597282748382504</v>
       </c>
       <c r="P97" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.01372568888799</v>
+        <v>1.0148397815363</v>
       </c>
     </row>
     <row r="98" ht="16.5" spans="1:16">
@@ -9663,27 +9672,27 @@
       </c>
       <c r="K98" s="1">
         <f ca="1" t="shared" ref="K98:O98" si="76">RAND()</f>
-        <v>0.854039497349887</v>
+        <v>0.240827065461946</v>
       </c>
       <c r="L98" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.718533692554062</v>
+        <v>0.717624937017115</v>
       </c>
       <c r="M98" s="1">
         <f ca="1" t="shared" si="76"/>
-        <v>0.587113075612645</v>
+        <v>0.682818600604236</v>
       </c>
       <c r="N98" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.861671811158385</v>
+        <v>0.860904887262856</v>
       </c>
       <c r="O98" s="1">
         <f ca="1" t="shared" si="76"/>
-        <v>0.613594402011032</v>
+        <v>0.343749373608804</v>
       </c>
       <c r="P98" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.00484917399642</v>
+        <v>1.00368235089643</v>
       </c>
     </row>
     <row r="99" ht="16.5" spans="1:16">
@@ -9723,27 +9732,27 @@
       </c>
       <c r="K99" s="1">
         <f ca="1" t="shared" ref="K99:O99" si="77">RAND()</f>
-        <v>0.968288290561638</v>
+        <v>0.701446757879204</v>
       </c>
       <c r="L99" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.711294169830607</v>
+        <v>0.710906792053307</v>
       </c>
       <c r="M99" s="1">
         <f ca="1" t="shared" si="77"/>
-        <v>0.905522980136709</v>
+        <v>0.239464658942824</v>
       </c>
       <c r="N99" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.853425057388559</v>
+        <v>0.852070752950994</v>
       </c>
       <c r="O99" s="1">
         <f ca="1" t="shared" si="77"/>
-        <v>0.74650395296837</v>
+        <v>0.386514234831646</v>
       </c>
       <c r="P99" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.995325094686157</v>
+        <v>0.993448187880583</v>
       </c>
     </row>
     <row r="100" ht="16.5" spans="1:16">
@@ -9783,27 +9792,27 @@
       </c>
       <c r="K100" s="1">
         <f ca="1" t="shared" ref="K100:O100" si="78">RAND()</f>
-        <v>0.972624612863629</v>
+        <v>0.545151645229442</v>
       </c>
       <c r="L100" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.704042694254537</v>
+        <v>0.703434662204099</v>
       </c>
       <c r="M100" s="1">
         <f ca="1" t="shared" si="78"/>
-        <v>0.544131608646738</v>
+        <v>0.992497081366859</v>
       </c>
       <c r="N100" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.844210599449273</v>
+        <v>0.84424031667976</v>
       </c>
       <c r="O100" s="1">
         <f ca="1" t="shared" si="78"/>
-        <v>0.438314540517094</v>
+        <v>0.490687396566149</v>
       </c>
       <c r="P100" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.98422799180746</v>
+        <v>0.984332203514702</v>
       </c>
     </row>
     <row r="101" ht="16.5" spans="1:16">
@@ -9843,27 +9852,27 @@
       </c>
       <c r="K101" s="1">
         <f ca="1" t="shared" ref="K101:O101" si="79">RAND()</f>
-        <v>0.304770808724298</v>
+        <v>0.806444163408101</v>
       </c>
       <c r="L101" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.696000589612161</v>
+        <v>0.696699891864145</v>
       </c>
       <c r="M101" s="1">
         <f ca="1" t="shared" si="79"/>
-        <v>0.955955052391892</v>
+        <v>0.989985072690047</v>
       </c>
       <c r="N101" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.835333133018526</v>
+        <v>0.836079871056379</v>
       </c>
       <c r="O101" s="1">
         <f ca="1" t="shared" si="79"/>
-        <v>0.434508596987935</v>
+        <v>0.93541123461885</v>
       </c>
       <c r="P101" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.973938811668873</v>
+        <v>0.975383777625848</v>
       </c>
     </row>
     <row r="102" ht="16.5" spans="1:16">
@@ -10017,27 +10026,27 @@
       </c>
       <c r="K104" s="1">
         <f ca="1" t="shared" ref="K104:O104" si="80">RAND()</f>
-        <v>0.788009410675107</v>
+        <v>0.222622454220841</v>
       </c>
       <c r="L104" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.676192131150515</v>
+        <v>0.675449475525247</v>
       </c>
       <c r="M104" s="1">
         <f ca="1" t="shared" si="80"/>
-        <v>0.356576818680486</v>
+        <v>0.260546675817102</v>
       </c>
       <c r="N104" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.810641089850096</v>
+        <v>0.80977229525933</v>
       </c>
       <c r="O104" s="1">
         <f ca="1" t="shared" si="80"/>
-        <v>0.425165925258007</v>
+        <v>0.238409895701395</v>
       </c>
       <c r="P104" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.945180142750206</v>
+        <v>0.944066037555226</v>
       </c>
     </row>
     <row r="105" ht="16.5" spans="1:16">
@@ -10077,27 +10086,27 @@
       </c>
       <c r="K105" s="1">
         <f ca="1" t="shared" ref="K105:O105" si="81">RAND()</f>
-        <v>0.921100217931938</v>
+        <v>0.708851370306729</v>
       </c>
       <c r="L105" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.669801268017873</v>
+        <v>0.669527833169364</v>
       </c>
       <c r="M105" s="1">
         <f ca="1" t="shared" si="81"/>
-        <v>0.546811567594024</v>
+        <v>0.377098659077386</v>
       </c>
       <c r="N105" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.803198019290539</v>
+        <v>0.802705947573329</v>
       </c>
       <c r="O105" s="1">
         <f ca="1" t="shared" si="81"/>
-        <v>0.312831511325016</v>
+        <v>0.534421868752661</v>
       </c>
       <c r="P105" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.936293339945532</v>
+        <v>0.936086737508802</v>
       </c>
     </row>
     <row r="106" ht="16.5" spans="1:16">
@@ -10137,27 +10146,27 @@
       </c>
       <c r="K106" s="1">
         <f ca="1" t="shared" ref="K106:O106" si="82">RAND()</f>
-        <v>0.352832016956529</v>
+        <v>0.0520965994850608</v>
       </c>
       <c r="L106" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.662643688812638</v>
+        <v>0.662263638559789</v>
       </c>
       <c r="M106" s="1">
         <f ca="1" t="shared" si="82"/>
-        <v>0.376603633656323</v>
+        <v>0.18651087192035</v>
       </c>
       <c r="N106" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.794548187910115</v>
+        <v>0.793927910540787</v>
       </c>
       <c r="O106" s="1">
         <f ca="1" t="shared" si="82"/>
-        <v>0.711506531147809</v>
+        <v>0.160259288353946</v>
       </c>
       <c r="P106" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.926875915943983</v>
+        <v>0.925559007443652</v>
       </c>
     </row>
     <row r="107" ht="16.5" spans="1:16">
@@ -10197,27 +10206,27 @@
       </c>
       <c r="K107" s="1">
         <f ca="1" t="shared" ref="K107:O107" si="83">RAND()</f>
-        <v>0.527572740070728</v>
+        <v>0.27517178561624</v>
       </c>
       <c r="L107" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.656557098276099</v>
+        <v>0.656244148305616</v>
       </c>
       <c r="M107" s="1">
         <f ca="1" t="shared" si="83"/>
-        <v>0.712043182919787</v>
+        <v>0.386865866309492</v>
       </c>
       <c r="N107" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.787628634298048</v>
+        <v>0.786912499514517</v>
       </c>
       <c r="O107" s="1">
         <f ca="1" t="shared" si="83"/>
-        <v>0.448750883165929</v>
+        <v>0.74535130308657</v>
       </c>
       <c r="P107" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.918373716255612</v>
+        <v>0.918025334014301</v>
       </c>
     </row>
     <row r="108" ht="16.5" spans="1:16">
@@ -10257,27 +10266,27 @@
       </c>
       <c r="K108" s="1">
         <f ca="1" t="shared" ref="K108:O108" si="84">RAND()</f>
-        <v>0.231896028583023</v>
+        <v>0.644790908071166</v>
       </c>
       <c r="L108" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.650008831352005</v>
+        <v>0.650511207417685</v>
       </c>
       <c r="M108" s="1">
         <f ca="1" t="shared" si="84"/>
-        <v>0.715495576514137</v>
+        <v>0.362479768845281</v>
       </c>
       <c r="N108" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.779851349334363</v>
+        <v>0.779924205196742</v>
       </c>
       <c r="O108" s="1">
         <f ca="1" t="shared" si="84"/>
-        <v>0.510559720657452</v>
+        <v>0.210225672461489</v>
       </c>
       <c r="P108" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.909444518453131</v>
+        <v>0.909151952884977</v>
       </c>
     </row>
     <row r="109" ht="16.5" spans="1:16">
@@ -10317,27 +10326,27 @@
       </c>
       <c r="K109" s="1">
         <f ca="1" t="shared" ref="K109:O109" si="85">RAND()</f>
-        <v>0.638627016160401</v>
+        <v>0.883664061349077</v>
       </c>
       <c r="L109" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.644428266945571</v>
+        <v>0.64472088646994</v>
       </c>
       <c r="M109" s="1">
         <f ca="1" t="shared" si="85"/>
-        <v>0.546134025658486</v>
+        <v>0.051048299824495</v>
       </c>
       <c r="N109" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.772858229696876</v>
+        <v>0.772559625353427</v>
       </c>
       <c r="O109" s="1">
         <f ca="1" t="shared" si="85"/>
-        <v>0.73315858912911</v>
+        <v>0.213190914279058</v>
       </c>
       <c r="P109" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.901511534346408</v>
+        <v>0.900591992488859</v>
       </c>
     </row>
     <row r="110" ht="16.5" spans="1:16">
@@ -10377,27 +10386,27 @@
       </c>
       <c r="K110" s="1">
         <f ca="1" t="shared" ref="K110:O110" si="86">RAND()</f>
-        <v>0.691967591085636</v>
+        <v>0.937012875639719</v>
       </c>
       <c r="L110" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.638527790754076</v>
+        <v>0.638815050771647</v>
       </c>
       <c r="M110" s="1">
         <f ca="1" t="shared" si="86"/>
-        <v>0.93397227237405</v>
+        <v>0.98936869529829</v>
       </c>
       <c r="N110" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.76622816599692</v>
+        <v>0.766580365755941</v>
       </c>
       <c r="O110" s="1">
         <f ca="1" t="shared" si="86"/>
-        <v>0.936623051680065</v>
+        <v>0.798414208893518</v>
       </c>
       <c r="P110" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.893931648677279</v>
+        <v>0.894121829915195</v>
       </c>
     </row>
     <row r="111" ht="16.5" spans="1:16">
@@ -10437,27 +10446,27 @@
       </c>
       <c r="K111" s="1">
         <f ca="1" t="shared" ref="K111:O111" si="87">RAND()</f>
-        <v>0.756488523585909</v>
+        <v>0.400381158610658</v>
       </c>
       <c r="L111" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.632747251178106</v>
+        <v>0.632337386154198</v>
       </c>
       <c r="M111" s="1">
         <f ca="1" t="shared" si="87"/>
-        <v>0.0391883143389395</v>
+        <v>0.795496771989483</v>
       </c>
       <c r="N111" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.758246900780931</v>
+        <v>0.758707515883426</v>
       </c>
       <c r="O111" s="1">
         <f ca="1" t="shared" si="87"/>
-        <v>0.26173704908514</v>
+        <v>0.87983461893799</v>
       </c>
       <c r="P111" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.884002694882464</v>
+        <v>0.885174715027826</v>
       </c>
     </row>
     <row r="112" ht="16.5" spans="1:16">
@@ -10497,27 +10506,27 @@
       </c>
       <c r="K112" s="1">
         <f ca="1" t="shared" ref="K112:O112" si="88">RAND()</f>
-        <v>0.220395957583143</v>
+        <v>0.983897126997855</v>
       </c>
       <c r="L112" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.626391602310782</v>
+        <v>0.627254527465403</v>
       </c>
       <c r="M112" s="1">
         <f ca="1" t="shared" si="88"/>
-        <v>0.5684409578855</v>
+        <v>0.232257080170303</v>
       </c>
       <c r="N112" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.751358390616992</v>
+        <v>0.75184135364938</v>
       </c>
       <c r="O112" s="1">
         <f ca="1" t="shared" si="88"/>
-        <v>0.630554063694376</v>
+        <v>0.247372011190599</v>
       </c>
       <c r="P112" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.87639538046785</v>
+        <v>0.876445263047777</v>
       </c>
     </row>
     <row r="113" ht="16.5" spans="1:16">
@@ -10557,27 +10566,27 @@
       </c>
       <c r="K113" s="1">
         <f ca="1" t="shared" ref="K113:O113" si="89">RAND()</f>
-        <v>0.686842147408414</v>
+        <v>0.470786805803385</v>
       </c>
       <c r="L113" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.621274004314208</v>
+        <v>0.621034174543121</v>
       </c>
       <c r="M113" s="1">
         <f ca="1" t="shared" si="89"/>
-        <v>0.954815264044312</v>
+        <v>0.45849875327481</v>
       </c>
       <c r="N113" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.745548171837037</v>
+        <v>0.744757411576196</v>
       </c>
       <c r="O113" s="1">
         <f ca="1" t="shared" si="89"/>
-        <v>0.520688587299485</v>
+        <v>0.210562997388295</v>
       </c>
       <c r="P113" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.869340441987032</v>
+        <v>0.868205430347429</v>
       </c>
     </row>
     <row r="114" ht="16.5" spans="1:16">
@@ -10617,27 +10626,27 @@
       </c>
       <c r="K114" s="1">
         <f ca="1" t="shared" ref="K114:O114" si="90">RAND()</f>
-        <v>0.373960703652771</v>
+        <v>0.744730946242836</v>
       </c>
       <c r="L114" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.615388800387991</v>
+        <v>0.6157930852606</v>
       </c>
       <c r="M114" s="1">
         <f ca="1" t="shared" si="90"/>
-        <v>0.389564979273639</v>
+        <v>0.930423267720453</v>
       </c>
       <c r="N114" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.737937472694721</v>
+        <v>0.738931505068955</v>
       </c>
       <c r="O114" s="1">
         <f ca="1" t="shared" si="90"/>
-        <v>0.4540772839559</v>
+        <v>0.00569070931616467</v>
       </c>
       <c r="P114" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.860556488696506</v>
+        <v>0.86106160397766</v>
       </c>
     </row>
     <row r="115" ht="16.5" spans="1:16">
@@ -10677,27 +10686,27 @@
       </c>
       <c r="K115" s="1">
         <f ca="1" t="shared" ref="K115:O115" si="91">RAND()</f>
-        <v>0.738608585591316</v>
+        <v>0.467383317291562</v>
       </c>
       <c r="L115" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.610339450277997</v>
+        <v>0.610048896893233</v>
       </c>
       <c r="M115" s="1">
         <f ca="1" t="shared" si="91"/>
-        <v>0.790617431442529</v>
+        <v>0.816099911026437</v>
       </c>
       <c r="N115" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.732239040446753</v>
+        <v>0.7319757854798</v>
       </c>
       <c r="O115" s="1">
         <f ca="1" t="shared" si="91"/>
-        <v>0.339073636520947</v>
+        <v>0.66408324233248</v>
       </c>
       <c r="P115" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.85365490880446</v>
+        <v>0.853739824351419</v>
       </c>
     </row>
     <row r="116" ht="16.5" spans="1:16">
@@ -10737,27 +10746,27 @@
       </c>
       <c r="K116" s="1">
         <f ca="1" t="shared" ref="K116:O116" si="92">RAND()</f>
-        <v>0.660539505497743</v>
+        <v>0.727090788742856</v>
       </c>
       <c r="L116" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.604905831058418</v>
+        <v>0.604975885040781</v>
       </c>
       <c r="M116" s="1">
         <f ca="1" t="shared" si="92"/>
-        <v>0.102563798492554</v>
+        <v>0.0879973035159507</v>
       </c>
       <c r="N116" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.725013792951568</v>
+        <v>0.725068513781325</v>
       </c>
       <c r="O116" s="1">
         <f ca="1" t="shared" si="92"/>
-        <v>0.719880666778056</v>
+        <v>0.398555129538558</v>
       </c>
       <c r="P116" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.845771562074493</v>
+        <v>0.845488045496628</v>
       </c>
     </row>
     <row r="117" ht="16.5" spans="1:16">
@@ -10797,27 +10806,27 @@
       </c>
       <c r="K117" s="1">
         <f ca="1" t="shared" ref="K117:O117" si="93">RAND()</f>
-        <v>0.582099621342851</v>
+        <v>0.91958847170324</v>
       </c>
       <c r="L117" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.599567689263458</v>
+        <v>0.599916815660383</v>
       </c>
       <c r="M117" s="1">
         <f ca="1" t="shared" si="93"/>
-        <v>0.413231590467032</v>
+        <v>0.597866012936575</v>
       </c>
       <c r="N117" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.718960687460493</v>
+        <v>0.71950081498411</v>
       </c>
       <c r="O117" s="1">
         <f ca="1" t="shared" si="93"/>
-        <v>0.494476024641805</v>
+        <v>0.763156252487397</v>
       </c>
       <c r="P117" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.838437731623915</v>
+        <v>0.839255804210821</v>
       </c>
     </row>
     <row r="118" ht="16.5" spans="1:16">
@@ -10857,27 +10866,27 @@
       </c>
       <c r="K118" s="1">
         <f ca="1" t="shared" ref="K118:O118" si="94">RAND()</f>
-        <v>0.208958974912543</v>
+        <v>0.277611273989369</v>
       </c>
       <c r="L118" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.594023256252121</v>
+        <v>0.594093061861262</v>
       </c>
       <c r="M118" s="1">
         <f ca="1" t="shared" si="94"/>
-        <v>0.90928161863363</v>
+        <v>0.0696529035840694</v>
       </c>
       <c r="N118" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.712896531107496</v>
+        <v>0.712112602833076</v>
       </c>
       <c r="O118" s="1">
         <f ca="1" t="shared" si="94"/>
-        <v>0.802839428292712</v>
+        <v>0.765394664962716</v>
       </c>
       <c r="P118" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.831661575619022</v>
+        <v>0.830839573535735</v>
       </c>
     </row>
     <row r="119" ht="16.5" spans="1:16">
@@ -10917,27 +10926,27 @@
       </c>
       <c r="K119" s="1">
         <f ca="1" t="shared" ref="K119:O119" si="95">RAND()</f>
-        <v>0.705778364494019</v>
+        <v>0.323494596366406</v>
       </c>
       <c r="L119" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.58944949597494</v>
+        <v>0.589067378344912</v>
       </c>
       <c r="M119" s="1">
         <f ca="1" t="shared" si="95"/>
-        <v>0.650059306816145</v>
+        <v>0.318957048399907</v>
       </c>
       <c r="N119" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.707048425312479</v>
+        <v>0.706335349318976</v>
       </c>
       <c r="O119" s="1">
         <f ca="1" t="shared" si="95"/>
-        <v>0.64785098162816</v>
+        <v>0.552107249118635</v>
       </c>
       <c r="P119" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.824645147284554</v>
+        <v>0.82383636916816</v>
       </c>
     </row>
     <row r="120" ht="16.5" spans="1:16">
@@ -11091,27 +11100,27 @@
       </c>
       <c r="K122" s="1">
         <f ca="1" t="shared" ref="K122:O122" si="96">RAND()</f>
-        <v>0.198109742708034</v>
+        <v>0.175820977192783</v>
       </c>
       <c r="L122" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.574237872895962</v>
+        <v>0.574216689358489</v>
       </c>
       <c r="M122" s="1">
         <f ca="1" t="shared" si="96"/>
-        <v>0.193054292898699</v>
+        <v>0.826301809488503</v>
       </c>
       <c r="N122" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.688470941025577</v>
+        <v>0.689051604301391</v>
       </c>
       <c r="O122" s="1">
         <f ca="1" t="shared" si="96"/>
-        <v>0.487099921330097</v>
+        <v>0.585443049652331</v>
       </c>
       <c r="P122" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.802983474008659</v>
+        <v>0.803657603894036</v>
       </c>
     </row>
     <row r="123" ht="16.5" spans="1:16">
@@ -11151,27 +11160,27 @@
       </c>
       <c r="K123" s="1">
         <f ca="1" t="shared" ref="K123:O123" si="97">RAND()</f>
-        <v>0.00389769164661646</v>
+        <v>0.541691846616119</v>
       </c>
       <c r="L123" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.569316744895321</v>
+        <v>0.569819492445692</v>
       </c>
       <c r="M123" s="1">
         <f ca="1" t="shared" si="97"/>
-        <v>0.963301257015584</v>
+        <v>0.462222072770883</v>
       </c>
       <c r="N123" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.683332024487978</v>
+        <v>0.683366346842402</v>
       </c>
       <c r="O123" s="1">
         <f ca="1" t="shared" si="97"/>
-        <v>0.145772849306681</v>
+        <v>0.754606925098758</v>
       </c>
       <c r="P123" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.796583051809509</v>
+        <v>0.797186532153767</v>
       </c>
     </row>
     <row r="124" ht="16.5" spans="1:16">
@@ -11211,27 +11220,27 @@
       </c>
       <c r="K124" s="1">
         <f ca="1" t="shared" ref="K124:O124" si="98">RAND()</f>
-        <v>0.772943283942658</v>
+        <v>0.163331431936711</v>
       </c>
       <c r="L124" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.565364961836493</v>
+        <v>0.56480434318011</v>
       </c>
       <c r="M124" s="1">
         <f ca="1" t="shared" si="98"/>
-        <v>0.311077763642249</v>
+        <v>0.824742507598474</v>
       </c>
       <c r="N124" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.677846160899419</v>
+        <v>0.677757924854431</v>
       </c>
       <c r="O124" s="1">
         <f ca="1" t="shared" si="98"/>
-        <v>0.862433182377083</v>
+        <v>0.899522347346395</v>
       </c>
       <c r="P124" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.790834404129913</v>
+        <v>0.790780276473342</v>
       </c>
     </row>
     <row r="125" ht="16.5" spans="1:16">
@@ -11271,27 +11280,27 @@
       </c>
       <c r="K125" s="1">
         <f ca="1" t="shared" ref="K125:O125" si="99">RAND()</f>
-        <v>0.651077362439663</v>
+        <v>0.780175098904093</v>
       </c>
       <c r="L125" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.560659904773254</v>
+        <v>0.560776712323949</v>
       </c>
       <c r="M125" s="1">
         <f ca="1" t="shared" si="99"/>
-        <v>0.577717930377048</v>
+        <v>0.37939623010241</v>
       </c>
       <c r="N125" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.672472946173674</v>
+        <v>0.672410312374789</v>
       </c>
       <c r="O125" s="1">
         <f ca="1" t="shared" si="99"/>
-        <v>0.43930018741617</v>
+        <v>0.796415473986678</v>
       </c>
       <c r="P125" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.784160747287386</v>
+        <v>0.784421231175013</v>
       </c>
     </row>
     <row r="126" ht="16.5" spans="1:16">
@@ -11331,27 +11340,27 @@
       </c>
       <c r="K126" s="1">
         <f ca="1" t="shared" ref="K126:O126" si="100">RAND()</f>
-        <v>0.121480377446395</v>
+        <v>0.452630247220889</v>
       </c>
       <c r="L126" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.555669447045727</v>
+        <v>0.555964277252365</v>
       </c>
       <c r="M126" s="1">
         <f ca="1" t="shared" si="100"/>
-        <v>0.592392172132676</v>
+        <v>0.274342886554688</v>
       </c>
       <c r="N126" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.666596867173174</v>
+        <v>0.666608530919104</v>
       </c>
       <c r="O126" s="1">
         <f ca="1" t="shared" si="100"/>
-        <v>0.368271754555236</v>
+        <v>0.0215985061145929</v>
       </c>
       <c r="P126" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.777324747832068</v>
+        <v>0.777027760556806</v>
       </c>
     </row>
     <row r="127" ht="16.5" spans="1:16">
@@ -11391,27 +11400,27 @@
       </c>
       <c r="K127" s="1">
         <f ca="1" t="shared" ref="K127:O127" si="101">RAND()</f>
-        <v>0.573157304126605</v>
+        <v>0.683731390962754</v>
       </c>
       <c r="L127" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.551626004495044</v>
+        <v>0.551722888456844</v>
       </c>
       <c r="M127" s="1">
         <f ca="1" t="shared" si="101"/>
-        <v>0.222880089415206</v>
+        <v>0.687975700627025</v>
       </c>
       <c r="N127" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.661345099430532</v>
+        <v>0.661849495737393</v>
       </c>
       <c r="O127" s="1">
         <f ca="1" t="shared" si="101"/>
-        <v>0.948198339873494</v>
+        <v>0.613710776630821</v>
       </c>
       <c r="P127" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.771699711309278</v>
+        <v>0.771911032798822</v>
       </c>
     </row>
     <row r="128" ht="16.5" spans="1:16">
@@ -11451,27 +11460,27 @@
       </c>
       <c r="K128" s="1">
         <f ca="1" t="shared" ref="K128:O128" si="102">RAND()</f>
-        <v>0.713878016244346</v>
+        <v>0.627502295769987</v>
       </c>
       <c r="L128" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.547372298251729</v>
+        <v>0.547297808504039</v>
       </c>
       <c r="M128" s="1">
         <f ca="1" t="shared" si="102"/>
-        <v>0.663476544587091</v>
+        <v>0.160755676478342</v>
       </c>
       <c r="N128" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.656605892572146</v>
+        <v>0.656097860268531</v>
       </c>
       <c r="O128" s="1">
         <f ca="1" t="shared" si="102"/>
-        <v>0.559544851275066</v>
+        <v>0.382706043111877</v>
       </c>
       <c r="P128" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.765749857010815</v>
+        <v>0.765089320298211</v>
       </c>
     </row>
     <row r="129" ht="16.5" spans="1:16">
@@ -11511,27 +11520,27 @@
       </c>
       <c r="K129" s="1">
         <f ca="1" t="shared" ref="K129:O129" si="103">RAND()</f>
-        <v>0.121038058989964</v>
+        <v>0.650019742957763</v>
       </c>
       <c r="L129" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.542560920596338</v>
+        <v>0.54300998231132</v>
       </c>
       <c r="M129" s="1">
         <f ca="1" t="shared" si="103"/>
-        <v>0.440075555916616</v>
+        <v>0.179454314574947</v>
       </c>
       <c r="N129" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.650747008359112</v>
+        <v>0.65097482418762</v>
       </c>
       <c r="O129" s="1">
         <f ca="1" t="shared" si="103"/>
-        <v>0.211661499849323</v>
+        <v>0.242181646939646</v>
       </c>
       <c r="P129" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.758739191472911</v>
+        <v>0.75899291638298</v>
       </c>
     </row>
     <row r="130" ht="16.5" spans="1:16">
@@ -11571,27 +11580,27 @@
       </c>
       <c r="K130" s="1">
         <f ca="1" t="shared" ref="K130:O130" si="107">RAND()</f>
-        <v>0.180366615353553</v>
+        <v>0.105262784263307</v>
       </c>
       <c r="L130" s="1">
         <f ca="1" t="shared" ref="L130:L193" si="108">J130+($R$1*$R$7*K130/MAX(1,($A130*($A130-1)))+$R$1*$R$7/$A130)/100</f>
-        <v>0.538377486633471</v>
+        <v>0.538314718169988</v>
       </c>
       <c r="M130" s="1">
         <f ca="1" t="shared" si="107"/>
-        <v>0.778356486221663</v>
+        <v>0.00936152036740689</v>
       </c>
       <c r="N130" s="1">
         <f ca="1" t="shared" ref="N130:N193" si="109">L130+($R$1*$R$7*M130/MAX(1,($A130*($A130-1)))+$R$1*$R$7/$A130)/100</f>
-        <v>0.646004746778206</v>
+        <v>0.645299286301109</v>
       </c>
       <c r="O130" s="1">
         <f ca="1" t="shared" si="107"/>
-        <v>0.278266377592587</v>
+        <v>0.327670539376462</v>
       </c>
       <c r="P130" s="1">
         <f ca="1" t="shared" ref="P130:P193" si="110">N130+($R$1*$R$7*O130/MAX(1,($A130*($A130-1)))+$R$1*$R$7/$A130)/100</f>
-        <v>0.753214053707153</v>
+        <v>0.7525498830455</v>
       </c>
     </row>
     <row r="131" ht="16.5" spans="1:16">
@@ -11631,27 +11640,27 @@
       </c>
       <c r="K131" s="1">
         <f ca="1" t="shared" ref="K131:O131" si="112">RAND()</f>
-        <v>0.175868371561379</v>
+        <v>0.971689963431821</v>
       </c>
       <c r="L131" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.534205544634916</v>
+        <v>0.534860424656849</v>
       </c>
       <c r="M131" s="1">
         <f ca="1" t="shared" si="112"/>
-        <v>0.712445198754131</v>
+        <v>0.187411398465906</v>
       </c>
       <c r="N131" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.640945660540868</v>
+        <v>0.641168491281705</v>
       </c>
       <c r="O131" s="1">
         <f ca="1" t="shared" si="112"/>
-        <v>0.657762838898418</v>
+        <v>0.319102219479067</v>
       </c>
       <c r="P131" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.747640778440498</v>
+        <v>0.747584926024031</v>
       </c>
     </row>
     <row r="132" ht="16.5" spans="1:16">
@@ -11691,27 +11700,27 @@
       </c>
       <c r="K132" s="1">
         <f ca="1" t="shared" ref="K132:O132" si="113">RAND()</f>
-        <v>0.332822645029691</v>
+        <v>0.576477980746396</v>
       </c>
       <c r="L132" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.530228593805133</v>
+        <v>0.530426036179349</v>
       </c>
       <c r="M132" s="1">
         <f ca="1" t="shared" si="113"/>
-        <v>0.96427665201271</v>
+        <v>0.0361697900587761</v>
       </c>
       <c r="N132" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.636353492090381</v>
+        <v>0.635798857265832</v>
       </c>
       <c r="O132" s="1">
         <f ca="1" t="shared" si="113"/>
-        <v>0.245595814105342</v>
+        <v>0.798349014610862</v>
       </c>
       <c r="P132" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.741896018351958</v>
+        <v>0.74178929862823</v>
       </c>
     </row>
     <row r="133" ht="16.5" spans="1:16">
@@ -11751,27 +11760,27 @@
       </c>
       <c r="K133" s="1">
         <f ca="1" t="shared" ref="K133:O133" si="114">RAND()</f>
-        <v>0.790696816921629</v>
+        <v>0.484525873147827</v>
       </c>
       <c r="L133" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.52655052140143</v>
+        <v>0.526306179565663</v>
       </c>
       <c r="M133" s="1">
         <f ca="1" t="shared" si="114"/>
-        <v>0.241925806526114</v>
+        <v>0.917406794596325</v>
       </c>
       <c r="N133" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.631289046507263</v>
+        <v>0.631583776938172</v>
       </c>
       <c r="O133" s="1">
         <f ca="1" t="shared" si="114"/>
-        <v>0.265244450541251</v>
+        <v>0.343348765757016</v>
       </c>
       <c r="P133" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.736046181217965</v>
+        <v>0.736403243336937</v>
       </c>
     </row>
     <row r="134" ht="16.5" spans="1:16">
@@ -11811,27 +11820,27 @@
       </c>
       <c r="K134" s="1">
         <f ca="1" t="shared" ref="K134:O134" si="115">RAND()</f>
-        <v>0.729129442859771</v>
+        <v>0.327672124602298</v>
       </c>
       <c r="L134" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.522514353287278</v>
+        <v>0.522198785333761</v>
       </c>
       <c r="M134" s="1">
         <f ca="1" t="shared" si="115"/>
-        <v>0.478653308048087</v>
+        <v>0.0670517284854384</v>
       </c>
       <c r="N134" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.626650000111787</v>
+        <v>0.626010890246788</v>
       </c>
       <c r="O134" s="1">
         <f ca="1" t="shared" si="115"/>
-        <v>0.988285064366338</v>
+        <v>0.118514580758835</v>
       </c>
       <c r="P134" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.73118624606122</v>
+        <v>0.729863447846154</v>
       </c>
     </row>
     <row r="135" ht="16.5" spans="1:16">
@@ -11871,27 +11880,27 @@
       </c>
       <c r="K135" s="1">
         <f ca="1" t="shared" ref="K135:O135" si="116">RAND()</f>
-        <v>0.885854621070964</v>
+        <v>0.530620113197162</v>
       </c>
       <c r="L135" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.518708606989719</v>
+        <v>0.518433540431047</v>
       </c>
       <c r="M135" s="1">
         <f ca="1" t="shared" si="116"/>
-        <v>0.112100964960672</v>
+        <v>0.521328911231493</v>
       </c>
       <c r="N135" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.621780484069534</v>
+        <v>0.621822292477674</v>
       </c>
       <c r="O135" s="1">
         <f ca="1" t="shared" si="116"/>
-        <v>0.63480188074484</v>
+        <v>0.934874498685232</v>
       </c>
       <c r="P135" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.725257100944984</v>
+        <v>0.725531262743742</v>
       </c>
     </row>
     <row r="136" ht="16.5" spans="1:16">
@@ -11931,27 +11940,27 @@
       </c>
       <c r="K136" s="1">
         <f ca="1" t="shared" ref="K136:O136" si="117">RAND()</f>
-        <v>0.681313502526312</v>
+        <v>0.0235191614587897</v>
       </c>
       <c r="L136" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.514682262373403</v>
+        <v>0.514180462378559</v>
       </c>
       <c r="M136" s="1">
         <f ca="1" t="shared" si="117"/>
-        <v>0.440162582919554</v>
+        <v>0.154988688720942</v>
       </c>
       <c r="N136" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.61724026368044</v>
+        <v>0.616520918094665</v>
       </c>
       <c r="O136" s="1">
         <f ca="1" t="shared" si="117"/>
-        <v>0.344199118366279</v>
+        <v>0.4159630024952</v>
       </c>
       <c r="P136" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.719725059027784</v>
+        <v>0.719060458693583</v>
       </c>
     </row>
     <row r="137" ht="16.5" spans="1:16">
@@ -11991,27 +12000,27 @@
       </c>
       <c r="K137" s="1">
         <f ca="1" t="shared" ref="K137:O137" si="118">RAND()</f>
-        <v>0.281523289707955</v>
+        <v>0.641839816015439</v>
       </c>
       <c r="L137" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.510571079596839</v>
+        <v>0.510841905744064</v>
       </c>
       <c r="M137" s="1">
         <f ca="1" t="shared" si="118"/>
-        <v>0.589585739431541</v>
+        <v>0.527891232330132</v>
       </c>
       <c r="N137" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.612484820512098</v>
+        <v>0.612709274970979</v>
       </c>
       <c r="O137" s="1">
         <f ca="1" t="shared" si="118"/>
-        <v>0.283479342639</v>
+        <v>0.144388285505085</v>
       </c>
       <c r="P137" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.714168481455912</v>
+        <v>0.714288390348973</v>
       </c>
     </row>
     <row r="138" ht="16.5" spans="1:16">
@@ -12165,27 +12174,27 @@
       </c>
       <c r="K140" s="1">
         <f ca="1" t="shared" ref="K140:O140" si="119">RAND()</f>
-        <v>0.701029571250151</v>
+        <v>0.88166226078028</v>
       </c>
       <c r="L140" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.499784913360612</v>
+        <v>0.499914864935813</v>
       </c>
       <c r="M140" s="1">
         <f ca="1" t="shared" si="119"/>
-        <v>0.333451971350174</v>
+        <v>0.31892816904955</v>
       </c>
       <c r="N140" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.599305382404749</v>
+        <v>0.599424885201316</v>
       </c>
       <c r="O140" s="1">
         <f ca="1" t="shared" si="119"/>
-        <v>0.885260596125443</v>
+        <v>0.811127296092816</v>
       </c>
       <c r="P140" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.699222836071026</v>
+        <v>0.699289005558218</v>
       </c>
     </row>
     <row r="141" ht="16.5" spans="1:16">
@@ -12225,27 +12234,27 @@
       </c>
       <c r="K141" s="1">
         <f ca="1" t="shared" ref="K141:O141" si="120">RAND()</f>
-        <v>0.453722848332957</v>
+        <v>0.394092140489924</v>
       </c>
       <c r="L141" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.496015486911973</v>
+        <v>0.495973199976298</v>
       </c>
       <c r="M141" s="1">
         <f ca="1" t="shared" si="120"/>
-        <v>0.336911566555148</v>
+        <v>0.548075034806988</v>
       </c>
       <c r="N141" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.594825835299355</v>
+        <v>0.594933294296973</v>
       </c>
       <c r="O141" s="1">
         <f ca="1" t="shared" si="120"/>
-        <v>0.531967460161422</v>
+        <v>0.227331001775063</v>
       </c>
       <c r="P141" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.693774506982306</v>
+        <v>0.693665933959074</v>
       </c>
     </row>
     <row r="142" ht="16.5" spans="1:16">
@@ -12285,27 +12294,27 @@
       </c>
       <c r="K142" s="1">
         <f ca="1" t="shared" ref="K142:O142" si="121">RAND()</f>
-        <v>0.496714390316509</v>
+        <v>0.665271616261859</v>
       </c>
       <c r="L142" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.492505301853412</v>
+        <v>0.492623138211976</v>
       </c>
       <c r="M142" s="1">
         <f ca="1" t="shared" si="121"/>
-        <v>0.857448020281082</v>
+        <v>0.889129893247358</v>
       </c>
       <c r="N142" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.590977074025645</v>
+        <v>0.59111705880604</v>
       </c>
       <c r="O142" s="1">
         <f ca="1" t="shared" si="121"/>
-        <v>0.126064076148284</v>
+        <v>0.0762488312429224</v>
       </c>
       <c r="P142" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.688937544352436</v>
+        <v>0.689042703885632</v>
       </c>
     </row>
     <row r="143" ht="16.5" spans="1:16">
@@ -12345,27 +12354,27 @@
       </c>
       <c r="K143" s="1">
         <f ca="1" t="shared" ref="K143:O143" si="122">RAND()</f>
-        <v>0.615384856057882</v>
+        <v>0.151703604021677</v>
       </c>
       <c r="L143" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.489096609280472</v>
+        <v>0.488777020763935</v>
       </c>
       <c r="M143" s="1">
         <f ca="1" t="shared" si="122"/>
-        <v>0.930556923999512</v>
+        <v>0.866721572200574</v>
       </c>
       <c r="N143" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.586921086632944</v>
+        <v>0.58655750012146</v>
       </c>
       <c r="O143" s="1">
         <f ca="1" t="shared" si="122"/>
-        <v>0.637692072138728</v>
+        <v>0.0886653121052452</v>
       </c>
       <c r="P143" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.68454370927781</v>
+        <v>0.683801710555335</v>
       </c>
     </row>
     <row r="144" ht="16.5" spans="1:16">
@@ -12405,27 +12414,27 @@
       </c>
       <c r="K144" s="1">
         <f ca="1" t="shared" ref="K144:O144" si="123">RAND()</f>
-        <v>0.55865720538249</v>
+        <v>0.706115325755825</v>
       </c>
       <c r="L144" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.485615555472977</v>
+        <v>0.485715768319483</v>
       </c>
       <c r="M144" s="1">
         <f ca="1" t="shared" si="123"/>
-        <v>0.121086705706089</v>
+        <v>0.734861998244186</v>
       </c>
       <c r="N144" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.582201342754507</v>
+        <v>0.582718678571417</v>
       </c>
       <c r="O144" s="1">
         <f ca="1" t="shared" si="123"/>
-        <v>0.143887763259302</v>
+        <v>0.222601532851685</v>
       </c>
       <c r="P144" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.67880262568236</v>
+        <v>0.679373455541443</v>
       </c>
     </row>
     <row r="145" ht="16.5" spans="1:16">
@@ -12465,27 +12474,27 @@
       </c>
       <c r="K145" s="1">
         <f ca="1" t="shared" ref="K145:O145" si="124">RAND()</f>
-        <v>0.0576039524196708</v>
+        <v>0.485417331251071</v>
       </c>
       <c r="L145" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.481885923394687</v>
+        <v>0.482172628164883</v>
       </c>
       <c r="M145" s="1">
         <f ca="1" t="shared" si="124"/>
-        <v>0.0939125599168287</v>
+        <v>0.320021372009279</v>
       </c>
       <c r="N145" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.577782193466892</v>
+        <v>0.578220428035402</v>
       </c>
       <c r="O145" s="1">
         <f ca="1" t="shared" si="124"/>
-        <v>0.137855985785924</v>
+        <v>0.394410565402192</v>
       </c>
       <c r="P145" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.673707912804686</v>
+        <v>0.674318080803591</v>
       </c>
     </row>
     <row r="146" ht="16.5" spans="1:16">
@@ -12525,27 +12534,27 @@
       </c>
       <c r="K146" s="1">
         <f ca="1" t="shared" ref="K146:O146" si="125">RAND()</f>
-        <v>0.0611155445680487</v>
+        <v>0.844037714117559</v>
       </c>
       <c r="L146" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.478546139584053</v>
+        <v>0.479063588144388</v>
       </c>
       <c r="M146" s="1">
         <f ca="1" t="shared" si="125"/>
-        <v>0.526310365715942</v>
+        <v>0.0905936381900196</v>
       </c>
       <c r="N146" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.574066402182084</v>
+        <v>0.574295877043192</v>
       </c>
       <c r="O146" s="1">
         <f ca="1" t="shared" si="125"/>
-        <v>0.44052620792396</v>
+        <v>0.227188980551899</v>
       </c>
       <c r="P146" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.669529968353988</v>
+        <v>0.669618444472867</v>
       </c>
     </row>
     <row r="147" ht="16.5" spans="1:16">
@@ -12585,27 +12594,27 @@
       </c>
       <c r="K147" s="1">
         <f ca="1" t="shared" ref="K147:O147" si="126">RAND()</f>
-        <v>0.36046108293755</v>
+        <v>0.708905880754734</v>
       </c>
       <c r="L147" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.475445175387083</v>
+        <v>0.475672314650658</v>
       </c>
       <c r="M147" s="1">
         <f ca="1" t="shared" si="126"/>
-        <v>0.199146031643913</v>
+        <v>0.584535847456254</v>
       </c>
       <c r="N147" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.570095539829061</v>
+        <v>0.570573901551692</v>
       </c>
       <c r="O147" s="1">
         <f ca="1" t="shared" si="126"/>
-        <v>0.989149620907558</v>
+        <v>0.325571433591749</v>
       </c>
       <c r="P147" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.665260880630598</v>
+        <v>0.665306678395507</v>
       </c>
     </row>
     <row r="148" ht="16.5" spans="1:16">
@@ -12645,27 +12654,27 @@
       </c>
       <c r="K148" s="1">
         <f ca="1" t="shared" ref="K148:O148" si="127">RAND()</f>
-        <v>0.118084090716107</v>
+        <v>0.207108889701011</v>
       </c>
       <c r="L148" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.472035670508428</v>
+        <v>0.472092913180406</v>
       </c>
       <c r="M148" s="1">
         <f ca="1" t="shared" si="127"/>
-        <v>0.524482580882684</v>
+        <v>0.297580703691461</v>
       </c>
       <c r="N148" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.566250462215454</v>
+        <v>0.566161807678167</v>
       </c>
       <c r="O148" s="1">
         <f ca="1" t="shared" si="127"/>
-        <v>0.391782195350346</v>
+        <v>0.928563155623644</v>
       </c>
       <c r="P148" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.660379927982662</v>
+        <v>0.660636421952121</v>
       </c>
     </row>
     <row r="149" ht="16.5" spans="1:16">
@@ -12705,27 +12714,27 @@
       </c>
       <c r="K149" s="1">
         <f ca="1" t="shared" ref="K149:O149" si="128">RAND()</f>
-        <v>0.068668160457362</v>
+        <v>0.598944677672388</v>
       </c>
       <c r="L149" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.468797004073098</v>
+        <v>0.469133362592015</v>
       </c>
       <c r="M149" s="1">
         <f ca="1" t="shared" si="128"/>
-        <v>0.60299879509919</v>
+        <v>0.305781338956156</v>
       </c>
       <c r="N149" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.562422734141694</v>
+        <v>0.56257056531667</v>
       </c>
       <c r="O149" s="1">
         <f ca="1" t="shared" si="128"/>
-        <v>0.374253474324357</v>
+        <v>0.505340925332598</v>
       </c>
       <c r="P149" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.655903369274332</v>
+        <v>0.656134350238972</v>
       </c>
     </row>
     <row r="150" ht="16.5" spans="1:16">
@@ -12765,27 +12774,27 @@
       </c>
       <c r="K150" s="1">
         <f ca="1" t="shared" ref="K150:O150" si="129">RAND()</f>
-        <v>0.163815921776437</v>
+        <v>0.472365182516812</v>
       </c>
       <c r="L150" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.465692937589358</v>
+        <v>0.465886025735477</v>
       </c>
       <c r="M150" s="1">
         <f ca="1" t="shared" si="129"/>
-        <v>0.0380929970390818</v>
+        <v>0.338689002054153</v>
       </c>
       <c r="N150" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.558334225606732</v>
+        <v>0.558715424802607</v>
       </c>
       <c r="O150" s="1">
         <f ca="1" t="shared" si="129"/>
-        <v>0.786156416704199</v>
+        <v>0.43646927039916</v>
       </c>
       <c r="P150" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.651443646908678</v>
+        <v>0.651606014133801</v>
       </c>
     </row>
     <row r="151" ht="16.5" spans="1:16">
@@ -12825,27 +12834,27 @@
       </c>
       <c r="K151" s="1">
         <f ca="1" t="shared" ref="K151:O151" si="130">RAND()</f>
-        <v>0.420706716339472</v>
+        <v>0.198678703333134</v>
       </c>
       <c r="L151" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.462729563878545</v>
+        <v>0.46259247275642</v>
       </c>
       <c r="M151" s="1">
         <f ca="1" t="shared" si="130"/>
-        <v>0.428496393417585</v>
+        <v>0.641182937793508</v>
       </c>
       <c r="N151" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.55499413883287</v>
+        <v>0.554988370946199</v>
       </c>
       <c r="O151" s="1">
         <f ca="1" t="shared" si="130"/>
-        <v>0.663297784297078</v>
+        <v>0.137478019826632</v>
       </c>
       <c r="P151" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.647403691827201</v>
+        <v>0.647073256703407</v>
       </c>
     </row>
     <row r="152" ht="16.5" spans="1:16">
@@ -12885,27 +12894,27 @@
       </c>
       <c r="K152" s="1">
         <f ca="1" t="shared" ref="K152:O152" si="131">RAND()</f>
-        <v>0.598350498131029</v>
+        <v>0.564871645263328</v>
       </c>
       <c r="L152" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.459755286396212</v>
+        <v>0.459734888684531</v>
       </c>
       <c r="M152" s="1">
         <f ca="1" t="shared" si="131"/>
-        <v>0.89689297197566</v>
+        <v>0.888962439318891</v>
       </c>
       <c r="N152" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.551692466220197</v>
+        <v>0.551667236660805</v>
       </c>
       <c r="O152" s="1">
         <f ca="1" t="shared" si="131"/>
-        <v>0.0213717076587794</v>
+        <v>0.233269091359214</v>
       </c>
       <c r="P152" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.643096215869897</v>
+        <v>0.643200089352229</v>
       </c>
     </row>
     <row r="153" ht="16.5" spans="1:16">
@@ -12945,27 +12954,27 @@
       </c>
       <c r="K153" s="1">
         <f ca="1" t="shared" ref="K153:O153" si="132">RAND()</f>
-        <v>0.345283638052482</v>
+        <v>0.254277777483909</v>
       </c>
       <c r="L153" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.456559991033685</v>
+        <v>0.456505273323862</v>
       </c>
       <c r="M153" s="1">
         <f ca="1" t="shared" si="132"/>
-        <v>0.581514898976818</v>
+        <v>0.884763500515604</v>
       </c>
       <c r="N153" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.54769910333788</v>
+        <v>0.547826715303085</v>
       </c>
       <c r="O153" s="1">
         <f ca="1" t="shared" si="132"/>
-        <v>0.184389803892525</v>
+        <v>0.716916156178264</v>
       </c>
       <c r="P153" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.638599442275389</v>
+        <v>0.639047238262097</v>
       </c>
     </row>
     <row r="154" ht="16.5" spans="1:16">
@@ -13005,27 +13014,27 @@
       </c>
       <c r="K154" s="1">
         <f ca="1" t="shared" ref="K154:O154" si="133">RAND()</f>
-        <v>0.731294363780777</v>
+        <v>0.923880580453127</v>
       </c>
       <c r="L154" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.453787919772109</v>
+        <v>0.453902199518845</v>
       </c>
       <c r="M154" s="1">
         <f ca="1" t="shared" si="133"/>
-        <v>0.98620080928819</v>
+        <v>0.898362262328225</v>
       </c>
       <c r="N154" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.544569205082058</v>
+        <v>0.544631361852012</v>
       </c>
       <c r="O154" s="1">
         <f ca="1" t="shared" si="133"/>
-        <v>0.826308995449729</v>
+        <v>0.204167075644234</v>
       </c>
       <c r="P154" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.635255611348708</v>
+        <v>0.634948592056857</v>
       </c>
     </row>
     <row r="155" ht="16.5" spans="1:16">
@@ -13065,27 +13074,27 @@
       </c>
       <c r="K155" s="1">
         <f ca="1" t="shared" ref="K155:O155" si="134">RAND()</f>
-        <v>0.4630519889014</v>
+        <v>0.974205940239352</v>
       </c>
       <c r="L155" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.450665907709313</v>
+        <v>0.450965284864413</v>
       </c>
       <c r="M155" s="1">
         <f ca="1" t="shared" si="134"/>
-        <v>0.932955309940608</v>
+        <v>0.19376233764249</v>
       </c>
       <c r="N155" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.540822718815212</v>
+        <v>0.540689158909887</v>
       </c>
       <c r="O155" s="1">
         <f ca="1" t="shared" si="134"/>
-        <v>0.142379050226805</v>
+        <v>0.673399313627064</v>
       </c>
       <c r="P155" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.630516498243661</v>
+        <v>0.630693950970326</v>
       </c>
     </row>
     <row r="156" ht="16.5" spans="1:16">
@@ -13125,27 +13134,27 @@
       </c>
       <c r="K156" s="1">
         <f ca="1" t="shared" ref="K156:O156" si="135">RAND()</f>
-        <v>0.813715934383489</v>
+        <v>0.547923845744103</v>
       </c>
       <c r="L156" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.447944251357121</v>
+        <v>0.447790588566035</v>
       </c>
       <c r="M156" s="1">
         <f ca="1" t="shared" si="135"/>
-        <v>0.646579253016443</v>
+        <v>0.350015719534364</v>
       </c>
       <c r="N156" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.537350317284713</v>
+        <v>0.537025201759566</v>
       </c>
       <c r="O156" s="1">
         <f ca="1" t="shared" si="135"/>
-        <v>0.0141728589648957</v>
+        <v>0.809076296163786</v>
       </c>
       <c r="P156" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.626390769126092</v>
+        <v>0.626525212353912</v>
       </c>
     </row>
     <row r="157" ht="16.5" spans="1:16">
@@ -13185,27 +13194,27 @@
       </c>
       <c r="K157" s="1">
         <f ca="1" t="shared" ref="K157:O157" si="136">RAND()</f>
-        <v>0.13910771765096</v>
+        <v>0.723611059296182</v>
       </c>
       <c r="L157" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.444669962220992</v>
+        <v>0.445003549736075</v>
       </c>
       <c r="M157" s="1">
         <f ca="1" t="shared" si="136"/>
-        <v>0.125309692292423</v>
+        <v>0.792912435839272</v>
       </c>
       <c r="N157" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.533203017380365</v>
+        <v>0.533917618868192</v>
       </c>
       <c r="O157" s="1">
         <f ca="1" t="shared" si="136"/>
-        <v>0.974993948211238</v>
+        <v>0.423383418913631</v>
       </c>
       <c r="P157" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.622221004000932</v>
+        <v>0.62262079054648</v>
       </c>
     </row>
     <row r="158" ht="16.5" spans="1:16">
@@ -13245,27 +13254,27 @@
       </c>
       <c r="K158" s="1">
         <f ca="1" t="shared" ref="K158:O158" si="137">RAND()</f>
-        <v>0.603183395933707</v>
+        <v>0.851450700276301</v>
       </c>
       <c r="L158" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.442084106274044</v>
+        <v>0.442223992310298</v>
       </c>
       <c r="M158" s="1">
         <f ca="1" t="shared" si="137"/>
-        <v>0.918891785792099</v>
+        <v>0.810962841893088</v>
       </c>
       <c r="N158" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.530499944369909</v>
+        <v>0.5305790179194</v>
       </c>
       <c r="O158" s="1">
         <f ca="1" t="shared" si="137"/>
-        <v>0.241277101990598</v>
+        <v>0.869160694620932</v>
       </c>
       <c r="P158" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.618533980953589</v>
+        <v>0.618966835067275</v>
       </c>
     </row>
     <row r="159" ht="16.5" spans="1:16">
@@ -13419,27 +13428,27 @@
       </c>
       <c r="K161" s="1">
         <f ca="1" t="shared" ref="K161:O161" si="138">RAND()</f>
-        <v>0.413442074136419</v>
+        <v>0.235103973239705</v>
       </c>
       <c r="L161" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.433644084143989</v>
+        <v>0.433547344136427</v>
       </c>
       <c r="M161" s="1">
         <f ca="1" t="shared" si="138"/>
-        <v>0.710267406516834</v>
+        <v>0.537218810040951</v>
       </c>
       <c r="N161" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.520279370708845</v>
+        <v>0.520088760000365</v>
       </c>
       <c r="O161" s="1">
         <f ca="1" t="shared" si="138"/>
-        <v>0.287925527791594</v>
+        <v>0.513114983971165</v>
       </c>
       <c r="P161" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.606685556726279</v>
+        <v>0.606617100675632</v>
       </c>
     </row>
     <row r="162" ht="16.5" spans="1:16">
@@ -13479,27 +13488,27 @@
       </c>
       <c r="K162" s="1">
         <f ca="1" t="shared" ref="K162:O162" si="139">RAND()</f>
-        <v>0.227578324787413</v>
+        <v>0.53668523748409</v>
       </c>
       <c r="L162" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.430836202673993</v>
+        <v>0.431001795662938</v>
       </c>
       <c r="M162" s="1">
         <f ca="1" t="shared" si="139"/>
-        <v>0.914105916507051</v>
+        <v>0.0252192251749956</v>
       </c>
       <c r="N162" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.517040187986408</v>
+        <v>0.516729591676424</v>
       </c>
       <c r="O162" s="1">
         <f ca="1" t="shared" si="139"/>
-        <v>0.272484812772606</v>
+        <v>0.584514432830605</v>
       </c>
       <c r="P162" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.602900447707536</v>
+        <v>0.602757010122584</v>
       </c>
     </row>
     <row r="163" ht="16.5" spans="1:16">
@@ -13539,27 +13548,27 @@
       </c>
       <c r="K163" s="1">
         <f ca="1" t="shared" ref="K163:O163" si="140">RAND()</f>
-        <v>0.447305401554559</v>
+        <v>0.836266691877724</v>
       </c>
       <c r="L163" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.42827899756696</v>
+        <v>0.42848479719147</v>
       </c>
       <c r="M163" s="1">
         <f ca="1" t="shared" si="140"/>
-        <v>0.380046712001268</v>
+        <v>0.792082407622801</v>
       </c>
       <c r="N163" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.513665265668548</v>
+        <v>0.51408907359762</v>
       </c>
       <c r="O163" s="1">
         <f ca="1" t="shared" si="140"/>
-        <v>0.781563077871354</v>
+        <v>0.524982710966772</v>
       </c>
       <c r="P163" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.599263976291761</v>
+        <v>0.599552027412946</v>
       </c>
     </row>
     <row r="164" ht="16.5" spans="1:16">
@@ -13713,27 +13722,27 @@
       </c>
       <c r="K166" s="1">
         <f ca="1" t="shared" ref="K166:O166" si="141">RAND()</f>
-        <v>0.0272188903325832</v>
+        <v>0.544107256501033</v>
       </c>
       <c r="L166" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.420235610520569</v>
+        <v>0.420499212126376</v>
       </c>
       <c r="M166" s="1">
         <f ca="1" t="shared" si="141"/>
-        <v>0.860522685642203</v>
+        <v>0.826274285030836</v>
       </c>
       <c r="N166" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.504310821646285</v>
+        <v>0.504556957327167</v>
       </c>
       <c r="O166" s="1">
         <f ca="1" t="shared" si="141"/>
-        <v>0.957889322007217</v>
+        <v>0.819407172811954</v>
       </c>
       <c r="P166" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.588435687597641</v>
+        <v>0.588611200452992</v>
       </c>
     </row>
     <row r="167" ht="16.5" spans="1:16">
@@ -13773,27 +13782,27 @@
       </c>
       <c r="K167" s="1">
         <f ca="1" t="shared" ref="K167:O167" si="142">RAND()</f>
-        <v>0.579711190603315</v>
+        <v>0.150658225679812</v>
       </c>
       <c r="L167" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.417970062593295</v>
+        <v>0.417753891329478</v>
       </c>
       <c r="M167" s="1">
         <f ca="1" t="shared" si="142"/>
-        <v>0.658662791971828</v>
+        <v>0.739456793991404</v>
       </c>
       <c r="N167" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.501434449104036</v>
+        <v>0.501258984566319</v>
       </c>
       <c r="O167" s="1">
         <f ca="1" t="shared" si="142"/>
-        <v>0.854387350701417</v>
+        <v>0.907765082288061</v>
       </c>
       <c r="P167" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.584997448207347</v>
+        <v>0.584848877159805</v>
       </c>
     </row>
     <row r="168" ht="16.5" spans="1:16">
@@ -13833,27 +13842,27 @@
       </c>
       <c r="K168" s="1">
         <f ca="1" t="shared" ref="K168:O168" si="143">RAND()</f>
-        <v>0.980522831070655</v>
+        <v>0.595392664355544</v>
       </c>
       <c r="L168" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.415652954875867</v>
+        <v>0.41546123724003</v>
       </c>
       <c r="M168" s="1">
         <f ca="1" t="shared" si="143"/>
-        <v>0.880086295050647</v>
+        <v>0.0169072473414307</v>
       </c>
       <c r="N168" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.498725792004202</v>
+        <v>0.498104384199604</v>
       </c>
       <c r="O168" s="1">
         <f ca="1" t="shared" si="143"/>
-        <v>0.763323367626465</v>
+        <v>0.917489517857392</v>
       </c>
       <c r="P168" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.581740504596123</v>
+        <v>0.581195840636601</v>
       </c>
     </row>
     <row r="169" ht="16.5" spans="1:16">
@@ -13893,27 +13902,27 @@
       </c>
       <c r="K169" s="1">
         <f ca="1" t="shared" ref="K169:O169" si="144">RAND()</f>
-        <v>0.989923178314694</v>
+        <v>0.485223289181002</v>
       </c>
       <c r="L169" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.413168696174107</v>
+        <v>0.412920447725645</v>
       </c>
       <c r="M169" s="1">
         <f ca="1" t="shared" si="144"/>
-        <v>0.0857663676670932</v>
+        <v>0.111146240534318</v>
       </c>
       <c r="N169" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.495353739511497</v>
+        <v>0.495117974747294</v>
       </c>
       <c r="O169" s="1">
         <f ca="1" t="shared" si="144"/>
-        <v>0.786265984085774</v>
+        <v>0.587845986244503</v>
       </c>
       <c r="P169" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.577883339974157</v>
+        <v>0.577549977691768</v>
       </c>
     </row>
     <row r="170" ht="16.5" spans="1:16">
@@ -13953,27 +13962,27 @@
       </c>
       <c r="K170" s="1">
         <f ca="1" t="shared" ref="K170:O170" si="145">RAND()</f>
-        <v>0.0762563606738877</v>
+        <v>0.874124450258531</v>
       </c>
       <c r="L170" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.410265297892974</v>
+        <v>0.410653103600084</v>
       </c>
       <c r="M170" s="1">
         <f ca="1" t="shared" si="145"/>
-        <v>0.748040299377204</v>
+        <v>0.383963694741233</v>
       </c>
       <c r="N170" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.49228568941634</v>
+        <v>0.492496534812659</v>
       </c>
       <c r="O170" s="1">
         <f ca="1" t="shared" si="145"/>
-        <v>0.197247945799362</v>
+        <v>0.391544399927198</v>
       </c>
       <c r="P170" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.574038366989319</v>
+        <v>0.574343650645252</v>
       </c>
     </row>
     <row r="171" ht="16.5" spans="1:16">
@@ -14013,27 +14022,27 @@
       </c>
       <c r="K171" s="1">
         <f ca="1" t="shared" ref="K171:O171" si="146">RAND()</f>
-        <v>0.261197565713968</v>
+        <v>0.713962972338236</v>
       </c>
       <c r="L171" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.407929151632678</v>
+        <v>0.408146630317378</v>
       </c>
       <c r="M171" s="1">
         <f ca="1" t="shared" si="146"/>
-        <v>0.598576609879461</v>
+        <v>0.853062369870532</v>
       </c>
       <c r="N171" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.489393139005332</v>
+        <v>0.489732855890097</v>
       </c>
       <c r="O171" s="1">
         <f ca="1" t="shared" si="146"/>
-        <v>0.820856407140599</v>
+        <v>0.483317748057511</v>
       </c>
       <c r="P171" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.570963894954463</v>
+        <v>0.571141480495846</v>
       </c>
     </row>
     <row r="172" ht="16.5" spans="1:16">
@@ -14073,27 +14082,27 @@
       </c>
       <c r="K172" s="1">
         <f ca="1" t="shared" ref="K172:O172" si="147">RAND()</f>
-        <v>0.960476562542008</v>
+        <v>0.789836734487008</v>
       </c>
       <c r="L172" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.405863590525046</v>
+        <v>0.405782585033915</v>
       </c>
       <c r="M172" s="1">
         <f ca="1" t="shared" si="147"/>
-        <v>0.71961152092977</v>
+        <v>0.673454730138527</v>
       </c>
       <c r="N172" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.486906956159336</v>
+        <v>0.486804039291773</v>
       </c>
       <c r="O172" s="1">
         <f ca="1" t="shared" si="147"/>
-        <v>0.69665110007135</v>
+        <v>0.946585693888857</v>
       </c>
       <c r="P172" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.567939422109835</v>
+        <v>0.567955153243464</v>
       </c>
     </row>
     <row r="173" ht="16.5" spans="1:16">
@@ -14133,27 +14142,27 @@
       </c>
       <c r="K173" s="1">
         <f ca="1" t="shared" ref="K173:O173" si="148">RAND()</f>
-        <v>0.265194013009317</v>
+        <v>0.302234250198409</v>
       </c>
       <c r="L173" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.403164003718875</v>
+        <v>0.403181382859131</v>
       </c>
       <c r="M173" s="1">
         <f ca="1" t="shared" si="148"/>
-        <v>0.26785648841924</v>
+        <v>0.780743200310679</v>
       </c>
       <c r="N173" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.483522239117358</v>
+        <v>0.483780262777677</v>
       </c>
       <c r="O173" s="1">
         <f ca="1" t="shared" si="148"/>
-        <v>0.970277181650024</v>
+        <v>0.768584419217554</v>
       </c>
       <c r="P173" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.564210047668519</v>
+        <v>0.564373437841773</v>
       </c>
     </row>
     <row r="174" ht="16.5" spans="1:16">
@@ -14193,27 +14202,27 @@
       </c>
       <c r="K174" s="1">
         <f ca="1" t="shared" ref="K174:O174" si="149">RAND()</f>
-        <v>0.301896835068895</v>
+        <v>0.679156371615847</v>
       </c>
       <c r="L174" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.400839029988035</v>
+        <v>0.401013992402484</v>
       </c>
       <c r="M174" s="1">
         <f ca="1" t="shared" si="149"/>
-        <v>0.513816955453139</v>
+        <v>0.316441194727904</v>
       </c>
       <c r="N174" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.480846110038621</v>
+        <v>0.480929535099326</v>
       </c>
       <c r="O174" s="1">
         <f ca="1" t="shared" si="149"/>
-        <v>0.510565927933109</v>
+        <v>0.535415563718584</v>
       </c>
       <c r="P174" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.560851682353633</v>
+        <v>0.560946631979933</v>
       </c>
     </row>
     <row r="175" ht="16.5" spans="1:16">
@@ -14253,27 +14262,27 @@
       </c>
       <c r="K175" s="1">
         <f ca="1" t="shared" ref="K175:O175" si="150">RAND()</f>
-        <v>0.490273652400067</v>
+        <v>0.857259084669881</v>
       </c>
       <c r="L175" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.398610251026614</v>
+        <v>0.398778492305111</v>
       </c>
       <c r="M175" s="1">
         <f ca="1" t="shared" si="150"/>
-        <v>0.155122060367322</v>
+        <v>0.257815747366952</v>
       </c>
       <c r="N175" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.477991710213149</v>
+        <v>0.478207030518973</v>
       </c>
       <c r="O175" s="1">
         <f ca="1" t="shared" si="150"/>
-        <v>0.999261028039465</v>
+        <v>0.120127087126451</v>
       </c>
       <c r="P175" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.557760157565051</v>
+        <v>0.557572446564496</v>
       </c>
     </row>
     <row r="176" ht="16.5" spans="1:16">
@@ -14313,27 +14322,27 @@
       </c>
       <c r="K176" s="1">
         <f ca="1" t="shared" ref="K176:O176" si="151">RAND()</f>
-        <v>0.744500846903881</v>
+        <v>0.373717177357587</v>
       </c>
       <c r="L176" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.396435931418301</v>
+        <v>0.396267891528655</v>
       </c>
       <c r="M176" s="1">
         <f ca="1" t="shared" si="151"/>
-        <v>0.642949694641372</v>
+        <v>0.358270259948233</v>
       </c>
       <c r="N176" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.475584460343952</v>
+        <v>0.475287403173558</v>
       </c>
       <c r="O176" s="1">
         <f ca="1" t="shared" si="151"/>
-        <v>0.569975833856632</v>
+        <v>0.364858424773183</v>
       </c>
       <c r="P176" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.554699917372104</v>
+        <v>0.55430990058774</v>
       </c>
     </row>
     <row r="177" ht="16.5" spans="1:16">
@@ -14373,27 +14382,27 @@
       </c>
       <c r="K177" s="1">
         <f ca="1" t="shared" ref="K177:O177" si="152">RAND()</f>
-        <v>0.541568773531009</v>
+        <v>0.257090652607451</v>
       </c>
       <c r="L177" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.394080313281647</v>
+        <v>0.393952852305389</v>
       </c>
       <c r="M177" s="1">
         <f ca="1" t="shared" si="152"/>
-        <v>0.725889139808635</v>
+        <v>0.0659975548016611</v>
       </c>
       <c r="N177" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.472814640233899</v>
+        <v>0.472391513547475</v>
       </c>
       <c r="O177" s="1">
         <f ca="1" t="shared" si="152"/>
-        <v>0.313447329625245</v>
+        <v>0.477383989893682</v>
       </c>
       <c r="P177" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.55136417182964</v>
+        <v>0.551014497283207</v>
       </c>
     </row>
     <row r="178" ht="16.5" spans="1:16">
@@ -14433,27 +14442,27 @@
       </c>
       <c r="K178" s="1">
         <f ca="1" t="shared" ref="K178:O178" si="153">RAND()</f>
-        <v>0.390751519652646</v>
+        <v>0.242546506941882</v>
       </c>
       <c r="L178" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.391775564039908</v>
+        <v>0.39170991081779</v>
       </c>
       <c r="M178" s="1">
         <f ca="1" t="shared" si="153"/>
-        <v>0.738502328401627</v>
+        <v>0.531465463502196</v>
       </c>
       <c r="N178" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.470068814300949</v>
+        <v>0.469911445980744</v>
       </c>
       <c r="O178" s="1">
         <f ca="1" t="shared" si="153"/>
-        <v>0.484179753351901</v>
+        <v>0.885124268663327</v>
       </c>
       <c r="P178" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.548249402404321</v>
+        <v>0.548269648179882</v>
       </c>
     </row>
     <row r="179" ht="16.5" spans="1:16">
@@ -14493,27 +14502,27 @@
       </c>
       <c r="K179" s="1">
         <f ca="1" t="shared" ref="K179:O179" si="154">RAND()</f>
-        <v>0.437243698462635</v>
+        <v>0.658441456849937</v>
       </c>
       <c r="L179" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.389584014569885</v>
+        <v>0.389680901799801</v>
       </c>
       <c r="M179" s="1">
         <f ca="1" t="shared" si="154"/>
-        <v>0.0440651281504152</v>
+        <v>0.325143977979454</v>
       </c>
       <c r="N179" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.467131405503944</v>
+        <v>0.467351408588861</v>
       </c>
       <c r="O179" s="1">
         <f ca="1" t="shared" si="154"/>
-        <v>0.258228462448059</v>
+        <v>0.678437462831568</v>
       </c>
       <c r="P179" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.544772602507111</v>
+        <v>0.545176662095719</v>
       </c>
     </row>
     <row r="180" ht="16.5" spans="1:16">
@@ -14553,27 +14562,27 @@
       </c>
       <c r="K180" s="1">
         <f ca="1" t="shared" ref="K180:O180" si="155">RAND()</f>
-        <v>0.349912782844926</v>
+        <v>0.178624607972294</v>
       </c>
       <c r="L180" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.387358885079507</v>
+        <v>0.387284697118512</v>
       </c>
       <c r="M180" s="1">
         <f ca="1" t="shared" si="155"/>
-        <v>0.358347638342468</v>
+        <v>0.0794512955249971</v>
       </c>
       <c r="N180" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.464609063894683</v>
+        <v>0.464414080957513</v>
       </c>
       <c r="O180" s="1">
         <f ca="1" t="shared" si="155"/>
-        <v>0.996201658260387</v>
+        <v>0.180459145135147</v>
       </c>
       <c r="P180" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.542135508652827</v>
+        <v>0.5415872130962</v>
       </c>
     </row>
     <row r="181" ht="16.5" spans="1:16">
@@ -14613,27 +14622,27 @@
       </c>
       <c r="K181" s="1">
         <f ca="1" t="shared" ref="K181:O181" si="156">RAND()</f>
-        <v>0.0879119986143371</v>
+        <v>0.326169883254188</v>
       </c>
       <c r="L181" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.385084208118587</v>
+        <v>0.385186255257259</v>
       </c>
       <c r="M181" s="1">
         <f ca="1" t="shared" si="156"/>
-        <v>0.0136358408974027</v>
+        <v>0.139361346775275</v>
       </c>
       <c r="N181" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.461756715089548</v>
+        <v>0.461912611141353</v>
       </c>
       <c r="O181" s="1">
         <f ca="1" t="shared" si="156"/>
-        <v>0.0815538291550253</v>
+        <v>0.519240649856729</v>
       </c>
       <c r="P181" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.538458311701663</v>
+        <v>0.538801671382446</v>
       </c>
     </row>
     <row r="182" ht="16.5" spans="1:16">
@@ -14673,27 +14682,27 @@
       </c>
       <c r="K182" s="1">
         <f ca="1" t="shared" ref="K182:O182" si="157">RAND()</f>
-        <v>0.33430661467835</v>
+        <v>0.762929670967833</v>
       </c>
       <c r="L182" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.38305136375944</v>
+        <v>0.383232916803541</v>
       </c>
       <c r="M182" s="1">
         <f ca="1" t="shared" si="157"/>
-        <v>0.686879854434339</v>
+        <v>0.916475695421366</v>
       </c>
       <c r="N182" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.459585401266844</v>
+        <v>0.459864204851325</v>
       </c>
       <c r="O182" s="1">
         <f ca="1" t="shared" si="157"/>
-        <v>0.337869656300585</v>
+        <v>0.264677964938214</v>
       </c>
       <c r="P182" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.535971607566934</v>
+        <v>0.536219409145866</v>
       </c>
     </row>
     <row r="183" ht="16.5" spans="1:16">
@@ -14733,27 +14742,27 @@
       </c>
       <c r="K183" s="1">
         <f ca="1" t="shared" ref="K183:O183" si="158">RAND()</f>
-        <v>0.583071868167505</v>
+        <v>0.408746764523841</v>
       </c>
       <c r="L183" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.381040810873071</v>
+        <v>0.380967782932136</v>
       </c>
       <c r="M183" s="1">
         <f ca="1" t="shared" si="158"/>
-        <v>0.694888119177258</v>
+        <v>0.434460471784051</v>
       </c>
       <c r="N183" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.457156087906787</v>
+        <v>0.456973962111015</v>
       </c>
       <c r="O183" s="1">
         <f ca="1" t="shared" si="158"/>
-        <v>0.33620743136205</v>
+        <v>0.12581261348209</v>
       </c>
       <c r="P183" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.533121107108802</v>
+        <v>0.532850843115995</v>
       </c>
     </row>
     <row r="184" ht="16.5" spans="1:16">
@@ -14793,27 +14802,27 @@
       </c>
       <c r="K184" s="1">
         <f ca="1" t="shared" ref="K184:O184" si="159">RAND()</f>
-        <v>0.758873652136714</v>
+        <v>0.968021117765551</v>
       </c>
       <c r="L184" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.379020970888113</v>
+        <v>0.379107628998533</v>
       </c>
       <c r="M184" s="1">
         <f ca="1" t="shared" si="159"/>
-        <v>0.553600827916851</v>
+        <v>0.353485577987975</v>
       </c>
       <c r="N184" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.454660185787087</v>
+        <v>0.45466392819316</v>
       </c>
       <c r="O184" s="1">
         <f ca="1" t="shared" si="159"/>
-        <v>0.138339133745078</v>
+        <v>0.97746106595968</v>
       </c>
       <c r="P184" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.530127341255942</v>
+        <v>0.530478765240846</v>
       </c>
     </row>
     <row r="185" ht="16.5" spans="1:16">
@@ -14853,27 +14862,27 @@
       </c>
       <c r="K185" s="1">
         <f ca="1" t="shared" ref="K185:O185" si="160">RAND()</f>
-        <v>0.969303848263618</v>
+        <v>0.496399729504923</v>
       </c>
       <c r="L185" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.377036599937813</v>
+        <v>0.376842786774387</v>
       </c>
       <c r="M185" s="1">
         <f ca="1" t="shared" si="160"/>
-        <v>0.819795826986787</v>
+        <v>0.902361431534141</v>
       </c>
       <c r="N185" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.452372581834119</v>
+        <v>0.452212607033213</v>
       </c>
       <c r="O185" s="1">
         <f ca="1" t="shared" si="160"/>
-        <v>0.901713104890203</v>
+        <v>0.567346178998773</v>
       </c>
       <c r="P185" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.527742136385303</v>
+        <v>0.527445125959032</v>
       </c>
     </row>
     <row r="186" ht="16.5" spans="1:16">
@@ -14913,27 +14922,27 @@
       </c>
       <c r="K186" s="1">
         <f ca="1" t="shared" ref="K186:O186" si="161">RAND()</f>
-        <v>0.672770161357535</v>
+        <v>0.695326915001766</v>
       </c>
       <c r="L186" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.374867339254604</v>
+        <v>0.37487648388446</v>
       </c>
       <c r="M186" s="1">
         <f ca="1" t="shared" si="161"/>
-        <v>0.863577072279923</v>
+        <v>0.404744823676398</v>
       </c>
       <c r="N186" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.449812032662285</v>
+        <v>0.449635164218383</v>
       </c>
       <c r="O186" s="1">
         <f ca="1" t="shared" si="161"/>
-        <v>0.926113916663856</v>
+        <v>0.372313393222831</v>
       </c>
       <c r="P186" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.524782078844717</v>
+        <v>0.524380696675095</v>
       </c>
     </row>
     <row r="187" ht="16.5" spans="1:16">
@@ -14973,27 +14982,27 @@
       </c>
       <c r="K187" s="1">
         <f ca="1" t="shared" ref="K187:O187" si="162">RAND()</f>
-        <v>0.0295084841107895</v>
+        <v>0.309395102252753</v>
       </c>
       <c r="L187" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.372583761031116</v>
+        <v>0.372696008497852</v>
       </c>
       <c r="M187" s="1">
         <f ca="1" t="shared" si="162"/>
-        <v>0.550094687522926</v>
+        <v>0.0195665028766383</v>
       </c>
       <c r="N187" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.446997922806409</v>
+        <v>0.446897403956721</v>
       </c>
       <c r="O187" s="1">
         <f ca="1" t="shared" si="162"/>
-        <v>0.613343305740389</v>
+        <v>0.180791497522163</v>
       </c>
       <c r="P187" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.521437450200167</v>
+        <v>0.521163458088247</v>
       </c>
     </row>
     <row r="188" ht="16.5" spans="1:16">
@@ -15033,27 +15042,27 @@
       </c>
       <c r="K188" s="1">
         <f ca="1" t="shared" ref="K188:O188" si="163">RAND()</f>
-        <v>0.849274434918365</v>
+        <v>0.216329501570898</v>
       </c>
       <c r="L188" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.370907940521013</v>
+        <v>0.370656815224015</v>
       </c>
       <c r="M188" s="1">
         <f ca="1" t="shared" si="163"/>
-        <v>0.723993308176547</v>
+        <v>0.463629854333835</v>
       </c>
       <c r="N188" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.444991981336746</v>
+        <v>0.444637555031668</v>
       </c>
       <c r="O188" s="1">
         <f ca="1" t="shared" si="163"/>
-        <v>0.148972853160791</v>
+        <v>0.318980273867858</v>
       </c>
       <c r="P188" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.518847878794443</v>
+        <v>0.518560904113934</v>
       </c>
     </row>
     <row r="189" ht="16.5" spans="1:16">
@@ -15093,27 +15102,27 @@
       </c>
       <c r="K189" s="1">
         <f ca="1" t="shared" ref="K189:O189" si="164">RAND()</f>
-        <v>0.442434835383954</v>
+        <v>0.437151141967677</v>
       </c>
       <c r="L189" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.368765092750264</v>
+        <v>0.368763018709727</v>
       </c>
       <c r="M189" s="1">
         <f ca="1" t="shared" si="164"/>
-        <v>0.793619522807328</v>
+        <v>0.639425149261624</v>
       </c>
       <c r="N189" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.442480872401383</v>
+        <v>0.442418271499003</v>
       </c>
       <c r="O189" s="1">
         <f ca="1" t="shared" si="164"/>
-        <v>0.677725615664984</v>
+        <v>0.779601219610975</v>
       </c>
       <c r="P189" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.516151159507316</v>
+        <v>0.516128548459711</v>
       </c>
     </row>
     <row r="190" ht="16.5" spans="1:16">
@@ -15153,27 +15162,27 @@
       </c>
       <c r="K190" s="1">
         <f ca="1" t="shared" ref="K190:O190" si="165">RAND()</f>
-        <v>0.422606364354905</v>
+        <v>0.67297707056477</v>
       </c>
       <c r="L190" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.366797027125636</v>
+        <v>0.366894266677187</v>
       </c>
       <c r="M190" s="1">
         <f ca="1" t="shared" si="165"/>
-        <v>0.629228206600969</v>
+        <v>0.914527869264051</v>
       </c>
       <c r="N190" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.440057281241675</v>
+        <v>0.440265326133335</v>
       </c>
       <c r="O190" s="1">
         <f ca="1" t="shared" si="165"/>
-        <v>0.125203661844143</v>
+        <v>0.473932485434517</v>
       </c>
       <c r="P190" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.513121781144114</v>
+        <v>0.513465266139498</v>
       </c>
     </row>
     <row r="191" ht="16.5" spans="1:16">
@@ -15213,27 +15222,27 @@
       </c>
       <c r="K191" s="1">
         <f ca="1" t="shared" ref="K191:O191" si="166">RAND()</f>
-        <v>0.206699101751428</v>
+        <v>0.794815377437095</v>
       </c>
       <c r="L191" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.364774504249629</v>
+        <v>0.365000513845966</v>
       </c>
       <c r="M191" s="1">
         <f ca="1" t="shared" si="166"/>
-        <v>0.749828918669743</v>
+        <v>0.165165875774981</v>
       </c>
       <c r="N191" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.437694238002835</v>
+        <v>0.437695565059714</v>
       </c>
       <c r="O191" s="1">
         <f ca="1" t="shared" si="166"/>
-        <v>0.438474010315705</v>
+        <v>0.872431076668781</v>
       </c>
       <c r="P191" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.510494319911561</v>
+        <v>0.510662414095025</v>
       </c>
     </row>
     <row r="192" ht="16.5" spans="1:16">
@@ -15273,27 +15282,27 @@
       </c>
       <c r="K192" s="1">
         <f ca="1" t="shared" ref="K192:O192" si="167">RAND()</f>
-        <v>0.943843649501848</v>
+        <v>0.685880941159405</v>
       </c>
       <c r="L192" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.363136540158808</v>
+        <v>0.363038444667622</v>
       </c>
       <c r="M192" s="1">
         <f ca="1" t="shared" si="167"/>
-        <v>0.32491188146274</v>
+        <v>0.640986871148437</v>
       </c>
       <c r="N192" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.435511403315716</v>
+        <v>0.435533501675664</v>
       </c>
       <c r="O192" s="1">
         <f ca="1" t="shared" si="167"/>
-        <v>0.525080879273041</v>
+        <v>0.978111764324593</v>
       </c>
       <c r="P192" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.507962384746798</v>
+        <v>0.508156757182627</v>
       </c>
     </row>
     <row r="193" ht="16.5" spans="1:16">
@@ -15333,27 +15342,27 @@
       </c>
       <c r="K193" s="1">
         <f ca="1" t="shared" ref="K193:O193" si="168">RAND()</f>
-        <v>0.763876605580379</v>
+        <v>0.831555922162968</v>
       </c>
       <c r="L193" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.361167689167676</v>
+        <v>0.361193157496887</v>
       </c>
       <c r="M193" s="1">
         <f ca="1" t="shared" si="168"/>
-        <v>0.606457077416693</v>
+        <v>0.0127053084322992</v>
       </c>
       <c r="N193" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.433270904363693</v>
+        <v>0.433072938617534</v>
       </c>
       <c r="O193" s="1">
         <f ca="1" t="shared" si="168"/>
-        <v>0.74650573340989</v>
+        <v>0.951595217747512</v>
       </c>
       <c r="P193" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.505426821115467</v>
+        <v>0.505306032367668</v>
       </c>
     </row>
     <row r="194" ht="16.5" spans="1:16">
@@ -15393,27 +15402,27 @@
       </c>
       <c r="K194" s="1">
         <f ca="1" t="shared" ref="K194:O194" si="172">RAND()</f>
-        <v>0.56777336446855</v>
+        <v>0.925004774993686</v>
       </c>
       <c r="L194" s="1">
         <f ca="1" t="shared" ref="L194:L257" si="173">J194+($R$1*$R$7*K194/MAX(1,($A194*($A194-1)))+$R$1*$R$7/$A194)/100</f>
-        <v>0.359214034769799</v>
+        <v>0.35934707107877</v>
       </c>
       <c r="M194" s="1">
         <f ca="1" t="shared" si="172"/>
-        <v>0.172966661076368</v>
+        <v>0.506435559999624</v>
       </c>
       <c r="N194" s="1">
         <f ca="1" t="shared" ref="N194:N257" si="174">L194+($R$1*$R$7*M194/MAX(1,($A194*($A194-1)))+$R$1*$R$7/$A194)/100</f>
-        <v>0.430781039841119</v>
+        <v>0.431038263078122</v>
       </c>
       <c r="O194" s="1">
         <f ca="1" t="shared" si="172"/>
-        <v>0.939109789529354</v>
+        <v>0.457117996383159</v>
       </c>
       <c r="P194" s="1">
         <f ca="1" t="shared" ref="P194:P257" si="175">N194+($R$1*$R$7*O194/MAX(1,($A194*($A194-1)))+$R$1*$R$7/$A194)/100</f>
-        <v>0.502633363758852</v>
+        <v>0.502711088756827</v>
       </c>
     </row>
     <row r="195" ht="16.5" spans="1:16">
@@ -15453,27 +15462,27 @@
       </c>
       <c r="K195" s="1">
         <f ca="1" t="shared" ref="K195:O195" si="177">RAND()</f>
-        <v>0.935357358553519</v>
+        <v>0.148446841418675</v>
       </c>
       <c r="L195" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.357489128025962</v>
+        <v>0.357199096373367</v>
       </c>
       <c r="M195" s="1">
         <f ca="1" t="shared" si="177"/>
-        <v>0.635577227628648</v>
+        <v>0.47427871641634</v>
       </c>
       <c r="N195" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.428857403378274</v>
+        <v>0.428507921924527</v>
       </c>
       <c r="O195" s="1">
         <f ca="1" t="shared" si="177"/>
-        <v>0.235453939579551</v>
+        <v>0.262033823979655</v>
       </c>
       <c r="P195" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.500078205268296</v>
+        <v>0.499738520364005</v>
       </c>
     </row>
     <row r="196" ht="16.5" spans="1:16">
@@ -15513,27 +15522,27 @@
       </c>
       <c r="K196" s="1">
         <f ca="1" t="shared" ref="K196:O196" si="178">RAND()</f>
-        <v>0.448361307136872</v>
+        <v>0.357862540508253</v>
       </c>
       <c r="L196" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.355468870897132</v>
+        <v>0.355435857865689</v>
       </c>
       <c r="M196" s="1">
         <f ca="1" t="shared" si="178"/>
-        <v>0.96691577402914</v>
+        <v>0.877793963400443</v>
       </c>
       <c r="N196" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.426590822725882</v>
+        <v>0.426525298962568</v>
       </c>
       <c r="O196" s="1">
         <f ca="1" t="shared" si="178"/>
-        <v>0.823404398352708</v>
+        <v>0.866698556237939</v>
       </c>
       <c r="P196" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.497660423061522</v>
+        <v>0.49761069256754</v>
       </c>
     </row>
     <row r="197" ht="16.5" spans="1:16">
@@ -15573,27 +15582,27 @@
       </c>
       <c r="K197" s="1">
         <f ca="1" t="shared" ref="K197:O197" si="179">RAND()</f>
-        <v>0.850771149284939</v>
+        <v>0.113893993134096</v>
       </c>
       <c r="L197" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.353792272157513</v>
+        <v>0.353526209762042</v>
       </c>
       <c r="M197" s="1">
         <f ca="1" t="shared" si="179"/>
-        <v>0.62306227474112</v>
+        <v>0.985002897836012</v>
       </c>
       <c r="N197" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.424425402963149</v>
+        <v>0.424290025565028</v>
       </c>
       <c r="O197" s="1">
         <f ca="1" t="shared" si="179"/>
-        <v>0.526442854186705</v>
+        <v>0.656065881678507</v>
       </c>
       <c r="P197" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.495023647635775</v>
+        <v>0.494935072900642</v>
       </c>
     </row>
     <row r="198" ht="16.5" spans="1:16">
@@ -15633,27 +15642,27 @@
       </c>
       <c r="K198" s="1">
         <f ca="1" t="shared" ref="K198:O198" si="180">RAND()</f>
-        <v>0.912437805407503</v>
+        <v>0.486451545921989</v>
       </c>
       <c r="L198" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.35200952143672</v>
+        <v>0.351857273162067</v>
       </c>
       <c r="M198" s="1">
         <f ca="1" t="shared" si="180"/>
-        <v>0.55472406565484</v>
+        <v>0.376990497461881</v>
       </c>
       <c r="N198" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.422258542262009</v>
+        <v>0.422042771682345</v>
       </c>
       <c r="O198" s="1">
         <f ca="1" t="shared" si="180"/>
-        <v>0.884103514021015</v>
+        <v>0.335881525202511</v>
       </c>
       <c r="P198" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.492625283909514</v>
+        <v>0.492213577780133</v>
       </c>
     </row>
     <row r="199" ht="16.5" spans="1:16">
@@ -15693,27 +15702,27 @@
       </c>
       <c r="K199" s="1">
         <f ca="1" t="shared" ref="K199:O199" si="181">RAND()</f>
-        <v>0.0628296963971184</v>
+        <v>0.535471761286569</v>
       </c>
       <c r="L199" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.349922244008877</v>
+        <v>0.350089460860015</v>
       </c>
       <c r="M199" s="1">
         <f ca="1" t="shared" si="181"/>
-        <v>0.402609865792579</v>
+        <v>0.780783749155199</v>
       </c>
       <c r="N199" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.419761653744506</v>
+        <v>0.420062665385943</v>
       </c>
       <c r="O199" s="1">
         <f ca="1" t="shared" si="181"/>
-        <v>0.172749828877912</v>
+        <v>0.0848611599086009</v>
       </c>
       <c r="P199" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.489519740901316</v>
+        <v>0.489789658259007</v>
       </c>
     </row>
     <row r="200" ht="16.5" spans="1:16">
@@ -15753,27 +15762,27 @@
       </c>
       <c r="K200" s="1">
         <f ca="1" t="shared" ref="K200:O200" si="182">RAND()</f>
-        <v>0.960359006756749</v>
+        <v>0.00977834301083402</v>
       </c>
       <c r="L200" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.348470964780804</v>
+        <v>0.348138037184243</v>
       </c>
       <c r="M200" s="1">
         <f ca="1" t="shared" si="182"/>
-        <v>0.391072206658393</v>
+        <v>0.559052367313283</v>
       </c>
       <c r="N200" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.417954666025713</v>
+        <v>0.417680571133508</v>
       </c>
       <c r="O200" s="1">
         <f ca="1" t="shared" si="182"/>
-        <v>0.0349095082744371</v>
+        <v>0.466637691597386</v>
       </c>
       <c r="P200" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.487313626261594</v>
+        <v>0.487190738133763</v>
       </c>
     </row>
     <row r="201" ht="16.5" spans="1:16">
@@ -15813,27 +15822,27 @@
       </c>
       <c r="K201" s="1">
         <f ca="1" t="shared" ref="K201:O201" si="183">RAND()</f>
-        <v>0.158544456431611</v>
+        <v>0.958167504502119</v>
       </c>
       <c r="L201" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.346441907374341</v>
+        <v>0.346719163607089</v>
       </c>
       <c r="M201" s="1">
         <f ca="1" t="shared" si="183"/>
-        <v>0.169172716604031</v>
+        <v>0.992838124677408</v>
       </c>
       <c r="N201" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.415500565250952</v>
+        <v>0.416063414012128</v>
       </c>
       <c r="O201" s="1">
         <f ca="1" t="shared" si="183"/>
-        <v>0.573552626981232</v>
+        <v>0.166462987921434</v>
       </c>
       <c r="P201" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.484699435257292</v>
+        <v>0.485121132334573</v>
       </c>
     </row>
     <row r="202" ht="16.5" spans="1:16">
@@ -15873,27 +15882,27 @@
       </c>
       <c r="K202" s="1">
         <f ca="1" t="shared" ref="K202:O202" si="184">RAND()</f>
-        <v>0.175147937838008</v>
+        <v>0.755355098511376</v>
       </c>
       <c r="L202" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.344716841829407</v>
+        <v>0.344916017421877</v>
       </c>
       <c r="M202" s="1">
         <f ca="1" t="shared" si="184"/>
-        <v>0.755085179236538</v>
+        <v>0.32856934526075</v>
       </c>
       <c r="N202" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.413632766592429</v>
+        <v>0.413685526301593</v>
       </c>
       <c r="O202" s="1">
         <f ca="1" t="shared" si="184"/>
-        <v>0.682871316390398</v>
+        <v>0.757595566995997</v>
       </c>
       <c r="P202" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.482523901521936</v>
+        <v>0.482602312839517</v>
       </c>
     </row>
     <row r="203" ht="16.5" spans="1:16">
@@ -15933,27 +15942,27 @@
       </c>
       <c r="K203" s="1">
         <f ca="1" t="shared" ref="K203:O203" si="185">RAND()</f>
-        <v>0.46322221578183</v>
+        <v>0.957829793426893</v>
       </c>
       <c r="L203" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.343101139514748</v>
+        <v>0.343269249080077</v>
       </c>
       <c r="M203" s="1">
         <f ca="1" t="shared" si="185"/>
-        <v>0.303274580470424</v>
+        <v>0.24030553981626</v>
       </c>
       <c r="N203" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.411521049598254</v>
+        <v>0.411667756947903</v>
       </c>
       <c r="O203" s="1">
         <f ca="1" t="shared" si="185"/>
-        <v>0.457653145681281</v>
+        <v>0.080018970044637</v>
       </c>
       <c r="P203" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.479993430599446</v>
+        <v>0.480011785857479</v>
       </c>
     </row>
     <row r="204" ht="16.5" spans="1:16">
@@ -15993,27 +16002,27 @@
       </c>
       <c r="K204" s="1">
         <f ca="1" t="shared" ref="K204:O204" si="186">RAND()</f>
-        <v>0.891845609413652</v>
+        <v>0.925461937359143</v>
       </c>
       <c r="L204" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.341547760557233</v>
+        <v>0.341559073665696</v>
       </c>
       <c r="M204" s="1">
         <f ca="1" t="shared" si="186"/>
-        <v>0.45356864536013</v>
+        <v>0.200371358487924</v>
       </c>
       <c r="N204" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.409680698354286</v>
+        <v>0.409606801431075</v>
       </c>
       <c r="O204" s="1">
         <f ca="1" t="shared" si="186"/>
-        <v>0.676894568237272</v>
+        <v>0.146313142147704</v>
       </c>
       <c r="P204" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.477888793390176</v>
+        <v>0.477636336654253</v>
       </c>
     </row>
     <row r="205" ht="16.5" spans="1:16">
@@ -16053,27 +16062,27 @@
       </c>
       <c r="K205" s="1">
         <f ca="1" t="shared" ref="K205:O205" si="187">RAND()</f>
-        <v>0.301706928097665</v>
+        <v>0.23109764163472</v>
       </c>
       <c r="L205" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.339668780923591</v>
+        <v>0.339645251314946</v>
       </c>
       <c r="M205" s="1">
         <f ca="1" t="shared" si="187"/>
-        <v>0.681724042630485</v>
+        <v>0.714172418770044</v>
       </c>
       <c r="N205" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.407543015246693</v>
+        <v>0.407530298629228</v>
       </c>
       <c r="O205" s="1">
         <f ca="1" t="shared" si="187"/>
-        <v>0.177822727875861</v>
+        <v>0.406943654344885</v>
       </c>
       <c r="P205" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.475249331136886</v>
+        <v>0.475312966030705</v>
       </c>
     </row>
     <row r="206" ht="16.5" spans="1:16">
@@ -16113,27 +16122,27 @@
       </c>
       <c r="K206" s="1">
         <f ca="1" t="shared" ref="K206:O206" si="188">RAND()</f>
-        <v>0.700752007735311</v>
+        <v>0.880455301382541</v>
       </c>
       <c r="L206" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.338136546573572</v>
+        <v>0.338195846082236</v>
       </c>
       <c r="M206" s="1">
         <f ca="1" t="shared" si="188"/>
-        <v>0.897739743007569</v>
+        <v>0.695017309269593</v>
       </c>
       <c r="N206" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.405749860979442</v>
+        <v>0.405742264993472</v>
       </c>
       <c r="O206" s="1">
         <f ca="1" t="shared" si="188"/>
-        <v>0.537832858920094</v>
+        <v>0.69190919169059</v>
       </c>
       <c r="P206" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.473244411277221</v>
+        <v>0.473287658270501</v>
       </c>
     </row>
     <row r="207" ht="16.5" spans="1:16">
@@ -16173,27 +16182,27 @@
       </c>
       <c r="K207" s="1">
         <f ca="1" t="shared" ref="K207:O207" si="189">RAND()</f>
-        <v>0.879439386883585</v>
+        <v>0.582296104593661</v>
       </c>
       <c r="L207" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.336545968826403</v>
+        <v>0.33644886777749</v>
       </c>
       <c r="M207" s="1">
         <f ca="1" t="shared" si="189"/>
-        <v>0.330980351577609</v>
+        <v>0.824512260691799</v>
       </c>
       <c r="N207" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.403644418479535</v>
+        <v>0.403708594729835</v>
       </c>
       <c r="O207" s="1">
         <f ca="1" t="shared" si="189"/>
-        <v>0.513934982713855</v>
+        <v>0.833181796626251</v>
       </c>
       <c r="P207" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.470802654396217</v>
+        <v>0.47097115472968</v>
       </c>
     </row>
     <row r="208" ht="16.5" spans="1:16">
@@ -16233,27 +16242,27 @@
       </c>
       <c r="K208" s="1">
         <f ca="1" t="shared" ref="K208:O208" si="190">RAND()</f>
-        <v>0.0232232698927937</v>
+        <v>0.170373853518952</v>
       </c>
       <c r="L208" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.334635347336535</v>
+        <v>0.334682968884634</v>
       </c>
       <c r="M208" s="1">
         <f ca="1" t="shared" si="190"/>
-        <v>0.106078428657424</v>
+        <v>0.390785899499243</v>
       </c>
       <c r="N208" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.401336343591764</v>
+        <v>0.401476103479941</v>
       </c>
       <c r="O208" s="1">
         <f ca="1" t="shared" si="190"/>
-        <v>0.736339725773301</v>
+        <v>0.984566209846254</v>
       </c>
       <c r="P208" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.468241307904312</v>
+        <v>0.468461399987982</v>
       </c>
     </row>
     <row r="209" ht="16.5" spans="1:16">
@@ -16293,27 +16302,27 @@
       </c>
       <c r="K209" s="1">
         <f ca="1" t="shared" ref="K209:O209" si="191">RAND()</f>
-        <v>0.174276485333227</v>
+        <v>0.0730724965434149</v>
       </c>
       <c r="L209" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.333068678360684</v>
+        <v>0.33303624118479</v>
       </c>
       <c r="M209" s="1">
         <f ca="1" t="shared" si="191"/>
-        <v>0.19335659325846</v>
+        <v>0.265062276618505</v>
       </c>
       <c r="N209" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.399476805473908</v>
+        <v>0.399467350888834</v>
       </c>
       <c r="O209" s="1">
         <f ca="1" t="shared" si="191"/>
-        <v>0.233806246481326</v>
+        <v>0.917862064380957</v>
       </c>
       <c r="P209" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.465897897219575</v>
+        <v>0.466107691294085</v>
       </c>
     </row>
     <row r="210" ht="16.5" spans="1:16">
@@ -16353,27 +16362,27 @@
       </c>
       <c r="K210" s="1">
         <f ca="1" t="shared" ref="K210:O210" si="192">RAND()</f>
-        <v>0.719580512499612</v>
+        <v>0.904335694758331</v>
       </c>
       <c r="L210" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.331641751266849</v>
+        <v>0.331700401007261</v>
       </c>
       <c r="M210" s="1">
         <f ca="1" t="shared" si="192"/>
-        <v>0.111746641237556</v>
+        <v>0.0139225849200473</v>
       </c>
       <c r="N210" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.397705932892932</v>
+        <v>0.397733528806118</v>
       </c>
       <c r="O210" s="1">
         <f ca="1" t="shared" si="192"/>
-        <v>0.39808371918046</v>
+        <v>0.761762337740073</v>
       </c>
       <c r="P210" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.463861010996647</v>
+        <v>0.464004055127907</v>
       </c>
     </row>
     <row r="211" ht="16.5" spans="1:16">
@@ -16413,27 +16422,27 @@
       </c>
       <c r="K211" s="1">
         <f ca="1" t="shared" ref="K211:O211" si="193">RAND()</f>
-        <v>0.25035833463201</v>
+        <v>0.356327219011191</v>
       </c>
       <c r="L211" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.329907836523534</v>
+        <v>0.329941155516572</v>
       </c>
       <c r="M211" s="1">
         <f ca="1" t="shared" si="193"/>
-        <v>0.34273930221526</v>
+        <v>0.394312651796374</v>
       </c>
       <c r="N211" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.395729887158544</v>
+        <v>0.395779421968948</v>
       </c>
       <c r="O211" s="1">
         <f ca="1" t="shared" si="193"/>
-        <v>0.0052106986164393</v>
+        <v>0.215671446211514</v>
       </c>
       <c r="P211" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.461445811233297</v>
+        <v>0.461561519621209</v>
       </c>
     </row>
     <row r="212" ht="16.5" spans="1:16">
@@ -16473,27 +16482,27 @@
       </c>
       <c r="K212" s="1">
         <f ca="1" t="shared" ref="K212:O212" si="194">RAND()</f>
-        <v>0.27615228585865</v>
+        <v>0.808387684653668</v>
       </c>
       <c r="L212" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.328345991910288</v>
+        <v>0.328511752427177</v>
       </c>
       <c r="M212" s="1">
         <f ca="1" t="shared" si="194"/>
-        <v>0.406885333526143</v>
+        <v>0.269110541159595</v>
       </c>
       <c r="N212" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.393875556739957</v>
+        <v>0.393998408384478</v>
       </c>
       <c r="O212" s="1">
         <f ca="1" t="shared" si="194"/>
-        <v>0.208707453079767</v>
+        <v>0.971579416981172</v>
       </c>
       <c r="P212" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.459343400631912</v>
+        <v>0.459703842732353</v>
       </c>
     </row>
     <row r="213" ht="16.5" spans="1:16">
@@ -16533,27 +16542,27 @@
       </c>
       <c r="K213" s="1">
         <f ca="1" t="shared" ref="K213:O213" si="195">RAND()</f>
-        <v>0.56390408153769</v>
+        <v>0.201140767232403</v>
       </c>
       <c r="L213" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.326879680683297</v>
+        <v>0.326767766757306</v>
       </c>
       <c r="M213" s="1">
         <f ca="1" t="shared" si="195"/>
-        <v>0.966514611028662</v>
+        <v>0.163174948314856</v>
       </c>
       <c r="N213" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.392272193909448</v>
+        <v>0.391912446500817</v>
       </c>
       <c r="O213" s="1">
         <f ca="1" t="shared" si="195"/>
-        <v>0.937999774990549</v>
+        <v>0.201478623073453</v>
       </c>
       <c r="P213" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.457655910195213</v>
+        <v>0.457068943080411</v>
       </c>
     </row>
     <row r="214" ht="16.5" spans="1:16">
@@ -16593,27 +16602,27 @@
       </c>
       <c r="K214" s="1">
         <f ca="1" t="shared" ref="K214:O214" si="196">RAND()</f>
-        <v>0.16392037063422</v>
+        <v>0.440074288469927</v>
       </c>
       <c r="L214" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.32521618613506</v>
+        <v>0.325300580768467</v>
       </c>
       <c r="M214" s="1">
         <f ca="1" t="shared" si="196"/>
-        <v>0.704674272808766</v>
+        <v>0.374876248522967</v>
       </c>
       <c r="N214" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.390220272080776</v>
+        <v>0.39020387805409</v>
       </c>
       <c r="O214" s="1">
         <f ca="1" t="shared" si="196"/>
-        <v>0.313679626892458</v>
+        <v>0.3347703190535</v>
       </c>
       <c r="P214" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.455104867236483</v>
+        <v>0.455094918677771</v>
       </c>
     </row>
     <row r="215" ht="16.5" spans="1:16">
@@ -16653,27 +16662,27 @@
       </c>
       <c r="K215" s="1">
         <f ca="1" t="shared" ref="K215:O215" si="197">RAND()</f>
-        <v>0.0654882615009809</v>
+        <v>0.996668393578048</v>
       </c>
       <c r="L215" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.323660737528163</v>
+        <v>0.323942653324369</v>
       </c>
       <c r="M215" s="1">
         <f ca="1" t="shared" si="197"/>
-        <v>0.432142936233056</v>
+        <v>0.285216727984634</v>
       </c>
       <c r="N215" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.388277550579807</v>
+        <v>0.38851498430691</v>
       </c>
       <c r="O215" s="1">
         <f ca="1" t="shared" si="197"/>
-        <v>0.244102368864514</v>
+        <v>0.589207330394939</v>
       </c>
       <c r="P215" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.452837434145476</v>
+        <v>0.453179348774451</v>
       </c>
     </row>
     <row r="216" ht="16.5" spans="1:16">
@@ -16713,27 +16722,27 @@
       </c>
       <c r="K216" s="1">
         <f ca="1" t="shared" ref="K216:O216" si="198">RAND()</f>
-        <v>0.371300918011866</v>
+        <v>0.21740239142638</v>
       </c>
       <c r="L216" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.322241337810662</v>
+        <v>0.322195178287366</v>
       </c>
       <c r="M216" s="1">
         <f ca="1" t="shared" si="198"/>
-        <v>0.600557353393174</v>
+        <v>0.287532534994599</v>
       </c>
       <c r="N216" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.386607512370037</v>
+        <v>0.386467465811446</v>
       </c>
       <c r="O216" s="1">
         <f ca="1" t="shared" si="198"/>
-        <v>0.0236042785781794</v>
+        <v>0.588685216632512</v>
       </c>
       <c r="P216" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.450800638626163</v>
+        <v>0.450830079503894</v>
       </c>
     </row>
     <row r="217" ht="16.5" spans="1:16">
@@ -16773,27 +16782,27 @@
       </c>
       <c r="K217" s="1">
         <f ca="1" t="shared" ref="K217:O217" si="199">RAND()</f>
-        <v>0.603140263715487</v>
+        <v>0.327018453524358</v>
       </c>
       <c r="L217" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.320812302662345</v>
+        <v>0.320730250961642</v>
       </c>
       <c r="M217" s="1">
         <f ca="1" t="shared" si="199"/>
-        <v>0.784264974835464</v>
+        <v>0.920904028006568</v>
       </c>
       <c r="N217" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.384934241866753</v>
+        <v>0.384892793502264</v>
       </c>
       <c r="O217" s="1">
         <f ca="1" t="shared" si="199"/>
-        <v>0.857409209587314</v>
+        <v>0.94880763208411</v>
       </c>
       <c r="P217" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.449077916438078</v>
+        <v>0.44906362781154</v>
       </c>
     </row>
     <row r="218" ht="16.5" spans="1:16">
@@ -16833,27 +16842,27 @@
       </c>
       <c r="K218" s="1">
         <f ca="1" t="shared" ref="K218:O218" si="200">RAND()</f>
-        <v>0.226462693747472</v>
+        <v>0.162816971166684</v>
       </c>
       <c r="L218" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.319216700485871</v>
+        <v>0.319197961985879</v>
       </c>
       <c r="M218" s="1">
         <f ca="1" t="shared" si="200"/>
-        <v>0.139472736181241</v>
+        <v>0.484718277839726</v>
       </c>
       <c r="N218" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.382852233933543</v>
+        <v>0.38293514222641</v>
       </c>
       <c r="O218" s="1">
         <f ca="1" t="shared" si="200"/>
-        <v>0.995763849926964</v>
+        <v>0.124927417341762</v>
       </c>
       <c r="P218" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.44673987562003</v>
+        <v>0.446566393258142</v>
       </c>
     </row>
     <row r="219" ht="16.5" spans="1:16">
@@ -16893,27 +16902,27 @@
       </c>
       <c r="K219" s="1">
         <f ca="1" t="shared" ref="K219:O219" si="201">RAND()</f>
-        <v>0.169028406299876</v>
+        <v>0.585758361745913</v>
       </c>
       <c r="L219" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.317729941064705</v>
+        <v>0.317851508590709</v>
       </c>
       <c r="M219" s="1">
         <f ca="1" t="shared" si="201"/>
-        <v>0.532240514558225</v>
+        <v>0.134912220214017</v>
       </c>
       <c r="N219" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.381187957364982</v>
+        <v>0.381193617173954</v>
       </c>
       <c r="O219" s="1">
         <f ca="1" t="shared" si="201"/>
-        <v>0.696085829446348</v>
+        <v>0.457358164925519</v>
       </c>
       <c r="P219" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.444693770252277</v>
+        <v>0.444629788963494</v>
       </c>
     </row>
     <row r="220" ht="16.5" spans="1:16">
@@ -16953,27 +16962,27 @@
       </c>
       <c r="K220" s="1">
         <f ca="1" t="shared" ref="K220:O220" si="202">RAND()</f>
-        <v>0.831376922595128</v>
+        <v>0.977182690454989</v>
       </c>
       <c r="L220" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.316465020349625</v>
+        <v>0.316507166040976</v>
       </c>
       <c r="M220" s="1">
         <f ca="1" t="shared" si="202"/>
-        <v>0.196592719636962</v>
+        <v>0.642831795815324</v>
       </c>
       <c r="N220" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.379535544825579</v>
+        <v>0.37970667755667</v>
       </c>
       <c r="O220" s="1">
         <f ca="1" t="shared" si="202"/>
-        <v>0.954668393840736</v>
+        <v>0.631598253541145</v>
       </c>
       <c r="P220" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.442825193852327</v>
+        <v>0.442902941975816</v>
       </c>
     </row>
     <row r="221" ht="16.5" spans="1:16">
@@ -17013,27 +17022,27 @@
       </c>
       <c r="K221" s="1">
         <f ca="1" t="shared" ref="K221:O221" si="203">RAND()</f>
-        <v>0.536348133780935</v>
+        <v>0.132533161262515</v>
       </c>
       <c r="L221" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.314935691246289</v>
+        <v>0.314820028178195</v>
       </c>
       <c r="M221" s="1">
         <f ca="1" t="shared" si="203"/>
-        <v>0.968865678430854</v>
+        <v>0.892501861510057</v>
       </c>
       <c r="N221" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.37794047220026</v>
+        <v>0.377802936556959</v>
       </c>
       <c r="O221" s="1">
         <f ca="1" t="shared" si="203"/>
-        <v>0.0276769733107427</v>
+        <v>0.516200071778644</v>
       </c>
       <c r="P221" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.440675672329602</v>
+        <v>0.440678062355849</v>
       </c>
     </row>
     <row r="222" ht="16.5" spans="1:16">
@@ -17073,27 +17082,27 @@
       </c>
       <c r="K222" s="1">
         <f ca="1" t="shared" ref="K222:O222" si="204">RAND()</f>
-        <v>0.585715194146565</v>
+        <v>0.930665961662269</v>
       </c>
       <c r="L222" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.313518775600149</v>
+        <v>0.313616684291875</v>
       </c>
       <c r="M222" s="1">
         <f ca="1" t="shared" si="204"/>
-        <v>0.789270500063387</v>
+        <v>0.0204145726452158</v>
       </c>
       <c r="N222" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.376186236169891</v>
+        <v>0.376065917551901</v>
       </c>
       <c r="O222" s="1">
         <f ca="1" t="shared" si="204"/>
-        <v>0.508205403512531</v>
+        <v>0.150435569747203</v>
       </c>
       <c r="P222" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.438773920961509</v>
+        <v>0.438552055167338</v>
       </c>
     </row>
     <row r="223" ht="16.5" spans="1:16">
@@ -17133,27 +17142,27 @@
       </c>
       <c r="K223" s="1">
         <f ca="1" t="shared" ref="K223:O223" si="205">RAND()</f>
-        <v>0.461430390897928</v>
+        <v>0.227474523823689</v>
       </c>
       <c r="L223" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.312065707459835</v>
+        <v>0.311999901113464</v>
       </c>
       <c r="M223" s="1">
         <f ca="1" t="shared" si="205"/>
-        <v>0.10428881651991</v>
+        <v>0.0671686374968998</v>
       </c>
       <c r="N223" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.374257203641563</v>
+        <v>0.374180956251809</v>
       </c>
       <c r="O223" s="1">
         <f ca="1" t="shared" si="205"/>
-        <v>0.246479352465007</v>
+        <v>0.762087664642231</v>
       </c>
       <c r="P223" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.436488694715389</v>
+        <v>0.436557475956918</v>
       </c>
     </row>
     <row r="224" ht="16.5" spans="1:16">
@@ -17193,27 +17202,27 @@
       </c>
       <c r="K224" s="1">
         <f ca="1" t="shared" ref="K224:O224" si="206">RAND()</f>
-        <v>0.0260204782023221</v>
+        <v>0.887182799181215</v>
       </c>
       <c r="L224" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.310539310035131</v>
+        <v>0.310779362554614</v>
       </c>
       <c r="M224" s="1">
         <f ca="1" t="shared" si="206"/>
-        <v>0.583624772643519</v>
+        <v>0.787915148545618</v>
       </c>
       <c r="N224" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.372585405899521</v>
+        <v>0.372882405196918</v>
       </c>
       <c r="O224" s="1">
         <f ca="1" t="shared" si="206"/>
-        <v>0.948443118517936</v>
+        <v>0.527869001959657</v>
       </c>
       <c r="P224" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.434733196370081</v>
+        <v>0.434912958912166</v>
       </c>
     </row>
     <row r="225" ht="16.5" spans="1:16">
@@ -17253,27 +17262,27 @@
       </c>
       <c r="K225" s="1">
         <f ca="1" t="shared" ref="K225:O225" si="207">RAND()</f>
-        <v>0.886584984947861</v>
+        <v>0.903006056470841</v>
       </c>
       <c r="L225" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.309385707735272</v>
+        <v>0.30939024430612</v>
       </c>
       <c r="M225" s="1">
         <f ca="1" t="shared" si="207"/>
-        <v>0.832583233124579</v>
+        <v>0.185835061603102</v>
       </c>
       <c r="N225" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.371222864377991</v>
+        <v>0.371048726926438</v>
       </c>
       <c r="O225" s="1">
         <f ca="1" t="shared" si="207"/>
-        <v>0.025800932752865</v>
+        <v>0.39018155053599</v>
       </c>
       <c r="P225" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.432837135135358</v>
+        <v>0.432763663373375</v>
       </c>
     </row>
     <row r="226" ht="16.5" spans="1:16">
@@ -17313,27 +17322,27 @@
       </c>
       <c r="K226" s="1">
         <f ca="1" t="shared" ref="K226:O226" si="208">RAND()</f>
-        <v>0.648216614058283</v>
+        <v>0.0869948083891243</v>
       </c>
       <c r="L226" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.307939392644325</v>
+        <v>0.307785724768963</v>
       </c>
       <c r="M226" s="1">
         <f ca="1" t="shared" si="208"/>
-        <v>0.505694209072633</v>
+        <v>0.266779043122451</v>
       </c>
       <c r="N226" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.369411189868238</v>
+        <v>0.369192104745056</v>
       </c>
       <c r="O226" s="1">
         <f ca="1" t="shared" si="208"/>
-        <v>0.722661253051593</v>
+        <v>0.609050200615782</v>
       </c>
       <c r="P226" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.430942394735145</v>
+        <v>0.430692201823796</v>
       </c>
     </row>
     <row r="227" ht="16.5" spans="1:16">
@@ -17373,27 +17382,27 @@
       </c>
       <c r="K227" s="1">
         <f ca="1" t="shared" ref="K227:O227" si="209">RAND()</f>
-        <v>0.107228967985044</v>
+        <v>0.38262523039036</v>
       </c>
       <c r="L227" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.306424380722875</v>
+        <v>0.306499119531551</v>
       </c>
       <c r="M227" s="1">
         <f ca="1" t="shared" si="209"/>
-        <v>0.468141257993287</v>
+        <v>0.800649155664077</v>
       </c>
       <c r="N227" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.36761337481059</v>
+        <v>0.367778351750787</v>
       </c>
       <c r="O227" s="1">
         <f ca="1" t="shared" si="209"/>
-        <v>0.564939361547621</v>
+        <v>0.0314591728261351</v>
       </c>
       <c r="P227" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.428828638590125</v>
+        <v>0.428848836246068</v>
       </c>
     </row>
     <row r="228" ht="16.5" spans="1:16">
@@ -17433,27 +17442,27 @@
       </c>
       <c r="K228" s="1">
         <f ca="1" t="shared" ref="K228:O228" si="210">RAND()</f>
-        <v>0.864962090827123</v>
+        <v>0.874501101012262</v>
       </c>
       <c r="L228" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.305273409942174</v>
+        <v>0.30527597589166</v>
       </c>
       <c r="M228" s="1">
         <f ca="1" t="shared" si="210"/>
-        <v>0.0261598138066412</v>
+        <v>0.662794037253638</v>
       </c>
       <c r="N228" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.366073398352577</v>
+        <v>0.366247215954701</v>
       </c>
       <c r="O228" s="1">
         <f ca="1" t="shared" si="210"/>
-        <v>0.268767304063206</v>
+        <v>0.100870802225939</v>
       </c>
       <c r="P228" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.426938647052357</v>
+        <v>0.42706730127439</v>
       </c>
     </row>
     <row r="229" ht="16.5" spans="1:16">
@@ -17493,27 +17502,27 @@
       </c>
       <c r="K229" s="1">
         <f ca="1" t="shared" ref="K229:O229" si="211">RAND()</f>
-        <v>0.0263147781720534</v>
+        <v>0.566998476472988</v>
       </c>
       <c r="L229" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.303705138417551</v>
+        <v>0.303849304022245</v>
       </c>
       <c r="M229" s="1">
         <f ca="1" t="shared" si="211"/>
-        <v>0.431390612704121</v>
+        <v>0.0843983800884391</v>
       </c>
       <c r="N229" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.364346478367611</v>
+        <v>0.364398123437293</v>
       </c>
       <c r="O229" s="1">
         <f ca="1" t="shared" si="211"/>
-        <v>0.381146934770554</v>
+        <v>0.105752725881492</v>
       </c>
       <c r="P229" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.424974421556804</v>
+        <v>0.424952636684398</v>
       </c>
     </row>
     <row r="230" ht="16.5" spans="1:16">
@@ -17553,27 +17562,27 @@
       </c>
       <c r="K230" s="1">
         <f ca="1" t="shared" ref="K230:O230" si="212">RAND()</f>
-        <v>0.0344062522916604</v>
+        <v>0.295929366275465</v>
       </c>
       <c r="L230" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.302376365706765</v>
+        <v>0.302445488111059</v>
       </c>
       <c r="M230" s="1">
         <f ca="1" t="shared" si="212"/>
-        <v>0.243048357277375</v>
+        <v>0.337779145822879</v>
       </c>
       <c r="N230" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.362702613836131</v>
+        <v>0.362796774256243</v>
       </c>
       <c r="O230" s="1">
         <f ca="1" t="shared" si="212"/>
-        <v>0.265116607967152</v>
+        <v>0.928099645801801</v>
       </c>
       <c r="P230" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.423034694759864</v>
+        <v>0.423304086274784</v>
       </c>
     </row>
     <row r="231" ht="16.5" spans="1:16">
@@ -17613,27 +17622,27 @@
       </c>
       <c r="K231" s="1">
         <f ca="1" t="shared" ref="K231:O231" si="213">RAND()</f>
-        <v>0.921332440314491</v>
+        <v>0.711368177869276</v>
       </c>
       <c r="L231" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.301289432080432</v>
+        <v>0.301234419609922</v>
       </c>
       <c r="M231" s="1">
         <f ca="1" t="shared" si="213"/>
-        <v>0.845811231217825</v>
+        <v>0.333622253915833</v>
       </c>
       <c r="N231" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.361511042010009</v>
+        <v>0.36132183155418</v>
       </c>
       <c r="O231" s="1">
         <f ca="1" t="shared" si="213"/>
-        <v>0.290410839635034</v>
+        <v>0.968637298697342</v>
       </c>
       <c r="P231" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.421587132186332</v>
+        <v>0.421575622986153</v>
       </c>
     </row>
     <row r="232" ht="16.5" spans="1:16">
@@ -17673,27 +17682,27 @@
       </c>
       <c r="K232" s="1">
         <f ca="1" t="shared" ref="K232:O232" si="214">RAND()</f>
-        <v>0.536272792034007</v>
+        <v>0.579692408755851</v>
       </c>
       <c r="L232" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.299879551374554</v>
+        <v>0.299890829197079</v>
       </c>
       <c r="M232" s="1">
         <f ca="1" t="shared" si="214"/>
-        <v>0.218087208093748</v>
+        <v>0.0883571913540215</v>
       </c>
       <c r="N232" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.35967645714289</v>
+        <v>0.359654038857171</v>
       </c>
       <c r="O232" s="1">
         <f ca="1" t="shared" si="214"/>
-        <v>0.952127162937497</v>
+        <v>0.962511831634011</v>
       </c>
       <c r="P232" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.419664022639757</v>
+        <v>0.419644301670583</v>
       </c>
     </row>
     <row r="233" ht="16.5" spans="1:16">
@@ -17733,27 +17742,27 @@
       </c>
       <c r="K233" s="1">
         <f ca="1" t="shared" ref="K233:O233" si="215">RAND()</f>
-        <v>0.414380162535747</v>
+        <v>0.963933841786909</v>
       </c>
       <c r="L233" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.298550500937509</v>
+        <v>0.29869201162518</v>
       </c>
       <c r="M233" s="1">
         <f ca="1" t="shared" si="215"/>
-        <v>0.464992788162022</v>
+        <v>0.42176668639859</v>
       </c>
       <c r="N233" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.358152995721743</v>
+        <v>0.358283375639815</v>
       </c>
       <c r="O233" s="1">
         <f ca="1" t="shared" si="215"/>
-        <v>0.607051376873059</v>
+        <v>0.446546061585229</v>
       </c>
       <c r="P233" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.417792070751614</v>
+        <v>0.417881120371302</v>
       </c>
     </row>
     <row r="234" ht="16.5" spans="1:16">
@@ -17793,27 +17802,27 @@
       </c>
       <c r="K234" s="1">
         <f ca="1" t="shared" ref="K234:O234" si="216">RAND()</f>
-        <v>0.688953187323924</v>
+        <v>0.680633220180851</v>
       </c>
       <c r="L234" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.297334385710839</v>
+        <v>0.297332261699691</v>
       </c>
       <c r="M234" s="1">
         <f ca="1" t="shared" si="216"/>
-        <v>0.536437889044449</v>
+        <v>0.951434929358407</v>
       </c>
       <c r="N234" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.356698801184955</v>
+        <v>0.356802622104182</v>
       </c>
       <c r="O234" s="1">
         <f ca="1" t="shared" si="216"/>
-        <v>0.132853375430662</v>
+        <v>0.622407689260199</v>
       </c>
       <c r="P234" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.415960185241876</v>
+        <v>0.41618898487819</v>
       </c>
     </row>
     <row r="235" ht="16.5" spans="1:16">
@@ -17853,27 +17862,27 @@
       </c>
       <c r="K235" s="1">
         <f ca="1" t="shared" ref="K235:O235" si="217">RAND()</f>
-        <v>0.336185692777904</v>
+        <v>0.998793534810192</v>
       </c>
       <c r="L235" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.295969321788642</v>
+        <v>0.296137033688793</v>
       </c>
       <c r="M235" s="1">
         <f ca="1" t="shared" si="217"/>
-        <v>0.0888378544709971</v>
+        <v>0.901373822350978</v>
       </c>
       <c r="N235" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.35496616640901</v>
+        <v>0.355339538342849</v>
       </c>
       <c r="O235" s="1">
         <f ca="1" t="shared" si="217"/>
-        <v>0.426185324856773</v>
+        <v>0.622823398219355</v>
       </c>
       <c r="P235" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.414048396655204</v>
+        <v>0.414471539423063</v>
       </c>
     </row>
     <row r="236" ht="16.5" spans="1:16">
@@ -17913,27 +17922,27 @@
       </c>
       <c r="K236" s="1">
         <f ca="1" t="shared" ref="K236:O236" si="218">RAND()</f>
-        <v>0.536058866002008</v>
+        <v>0.580019134349191</v>
       </c>
       <c r="L236" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.294755366654861</v>
+        <v>0.294766398691653</v>
       </c>
       <c r="M236" s="1">
         <f ca="1" t="shared" si="218"/>
-        <v>0.0623210435196502</v>
+        <v>0.282517984685737</v>
       </c>
       <c r="N236" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.353494410670147</v>
+        <v>0.353560702168443</v>
       </c>
       <c r="O236" s="1">
         <f ca="1" t="shared" si="218"/>
-        <v>0.102011999064976</v>
+        <v>0.985315570529572</v>
       </c>
       <c r="P236" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.412243415318031</v>
+        <v>0.41253137601593</v>
       </c>
     </row>
     <row r="237" ht="16.5" spans="1:16">
@@ -17973,27 +17982,27 @@
       </c>
       <c r="K237" s="1">
         <f ca="1" t="shared" ref="K237:O237" si="219">RAND()</f>
-        <v>0.613010743040954</v>
+        <v>0.102655547704325</v>
       </c>
       <c r="L237" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.293520727519906</v>
+        <v>0.293393736865459</v>
       </c>
       <c r="M237" s="1">
         <f ca="1" t="shared" si="219"/>
-        <v>0.1344959701893</v>
+        <v>0.135458486639787</v>
       </c>
       <c r="N237" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.352028770152229</v>
+        <v>0.351902018998809</v>
       </c>
       <c r="O237" s="1">
         <f ca="1" t="shared" si="219"/>
-        <v>0.0301518034617061</v>
+        <v>0.777216740920843</v>
       </c>
       <c r="P237" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.410510849035888</v>
+        <v>0.410569988544873</v>
       </c>
     </row>
     <row r="238" ht="16.5" spans="1:16">
@@ -18033,27 +18042,27 @@
       </c>
       <c r="K238" s="1">
         <f ca="1" t="shared" ref="K238:O238" si="220">RAND()</f>
-        <v>0.585281610338818</v>
+        <v>0.729175128334473</v>
       </c>
       <c r="L238" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.292270558646619</v>
+        <v>0.292306061230977</v>
       </c>
       <c r="M238" s="1">
         <f ca="1" t="shared" si="220"/>
-        <v>0.3537116949395</v>
+        <v>0.935688872890569</v>
       </c>
       <c r="N238" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.350585677387057</v>
+        <v>0.350764770135467</v>
       </c>
       <c r="O238" s="1">
         <f ca="1" t="shared" si="220"/>
-        <v>0.982511915028191</v>
+        <v>0.496685596736841</v>
       </c>
       <c r="P238" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.409055938855043</v>
+        <v>0.409115164565041</v>
       </c>
     </row>
     <row r="239" ht="16.5" spans="1:16">
@@ -18093,27 +18102,27 @@
       </c>
       <c r="K239" s="1">
         <f ca="1" t="shared" ref="K239:O239" si="221">RAND()</f>
-        <v>0.514538467799113</v>
+        <v>0.248791929309247</v>
       </c>
       <c r="L239" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.291020470000631</v>
+        <v>0.29095545382804</v>
       </c>
       <c r="M239" s="1">
         <f ca="1" t="shared" si="221"/>
-        <v>0.370837292428377</v>
+        <v>0.71820915410789</v>
       </c>
       <c r="N239" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.349094390410437</v>
+        <v>0.349114360439512</v>
       </c>
       <c r="O239" s="1">
         <f ca="1" t="shared" si="221"/>
-        <v>0.68701079496842</v>
+        <v>0.67768551048159</v>
       </c>
       <c r="P239" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.407245664192846</v>
+        <v>0.407263352746087</v>
       </c>
     </row>
     <row r="240" ht="16.5" spans="1:16">
@@ -18153,27 +18162,27 @@
       </c>
       <c r="K240" s="1">
         <f ca="1" t="shared" ref="K240:O240" si="222">RAND()</f>
-        <v>0.52618511219996</v>
+        <v>0.966676727547659</v>
       </c>
       <c r="L240" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.289801015339622</v>
+        <v>0.289907881910625</v>
       </c>
       <c r="M240" s="1">
         <f ca="1" t="shared" si="222"/>
-        <v>0.357478821428082</v>
+        <v>0.642766749133564</v>
       </c>
       <c r="N240" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.347628328158013</v>
+        <v>0.347804407720865</v>
       </c>
       <c r="O240" s="1">
         <f ca="1" t="shared" si="222"/>
-        <v>0.474022855444584</v>
+        <v>0.190092001068619</v>
       </c>
       <c r="P240" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.405483915433515</v>
+        <v>0.405591111240691</v>
       </c>
     </row>
     <row r="241" ht="16.5" spans="1:16">
@@ -18213,27 +18222,27 @@
       </c>
       <c r="K241" s="1">
         <f ca="1" t="shared" ref="K241:O241" si="223">RAND()</f>
-        <v>0.655850910953628</v>
+        <v>0.489831293565029</v>
       </c>
       <c r="L241" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.288620131495313</v>
+        <v>0.288580189537154</v>
       </c>
       <c r="M241" s="1">
         <f ca="1" t="shared" si="223"/>
-        <v>0.36604907742889</v>
+        <v>0.837970339756848</v>
       </c>
       <c r="N241" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.346208197695949</v>
+        <v>0.346281793279983</v>
       </c>
       <c r="O241" s="1">
         <f ca="1" t="shared" si="223"/>
-        <v>0.684277035933278</v>
+        <v>0.523983221160692</v>
       </c>
       <c r="P241" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.40387282501631</v>
+        <v>0.40390785618884</v>
       </c>
     </row>
     <row r="242" ht="16.5" spans="1:16">
@@ -18273,27 +18282,27 @@
       </c>
       <c r="K242" s="1">
         <f ca="1" t="shared" ref="K242:O242" si="224">RAND()</f>
-        <v>0.48762847925286</v>
+        <v>0.259456856093024</v>
       </c>
       <c r="L242" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.287377753682809</v>
+        <v>0.287323314395126</v>
       </c>
       <c r="M242" s="1">
         <f ca="1" t="shared" si="224"/>
-        <v>0.654126971982805</v>
+        <v>0.17927129755487</v>
       </c>
       <c r="N242" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.344795232109735</v>
+        <v>0.344627497381057</v>
       </c>
       <c r="O242" s="1">
         <f ca="1" t="shared" si="224"/>
-        <v>0.693825685833263</v>
+        <v>0.500389035225198</v>
       </c>
       <c r="P242" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.4022221822215</v>
+        <v>0.402008295594856</v>
       </c>
     </row>
     <row r="243" ht="16.5" spans="1:16">
@@ -18333,27 +18342,27 @@
       </c>
       <c r="K243" s="1">
         <f ca="1" t="shared" ref="K243:O243" si="225">RAND()</f>
-        <v>0.258150462258248</v>
+        <v>0.0472467948018682</v>
       </c>
       <c r="L243" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.286131519433133</v>
+        <v>0.286081615955699</v>
       </c>
       <c r="M243" s="1">
         <f ca="1" t="shared" si="225"/>
-        <v>0.354686780519099</v>
+        <v>0.919602723607989</v>
       </c>
       <c r="N243" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.343240237885366</v>
+        <v>0.343324003349577</v>
       </c>
       <c r="O243" s="1">
         <f ca="1" t="shared" si="225"/>
-        <v>0.187215791700348</v>
+        <v>0.605030124022674</v>
       </c>
       <c r="P243" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.400309329787658</v>
+        <v>0.400491957392846</v>
       </c>
     </row>
     <row r="244" ht="16.5" spans="1:16">
@@ -18393,27 +18402,27 @@
       </c>
       <c r="K244" s="1">
         <f ca="1" t="shared" ref="K244:O244" si="226">RAND()</f>
-        <v>0.789072510631531</v>
+        <v>0.590569498771872</v>
       </c>
       <c r="L244" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.285074468602638</v>
+        <v>0.285027885914414</v>
       </c>
       <c r="M244" s="1">
         <f ca="1" t="shared" si="226"/>
-        <v>0.0960937769915082</v>
+        <v>0.769528921647774</v>
       </c>
       <c r="N244" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.341887142379505</v>
+        <v>0.341998594670642</v>
       </c>
       <c r="O244" s="1">
         <f ca="1" t="shared" si="226"/>
-        <v>0.0454960119861196</v>
+        <v>0.876129392031245</v>
       </c>
       <c r="P244" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.398687942382318</v>
+        <v>0.398994319351968</v>
       </c>
     </row>
     <row r="245" ht="16.5" spans="1:16">
@@ -18453,27 +18462,27 @@
       </c>
       <c r="K245" s="1">
         <f ca="1" t="shared" ref="K245:O245" si="227">RAND()</f>
-        <v>0.206147827197239</v>
+        <v>0.472378344013581</v>
       </c>
       <c r="L245" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.283765851042557</v>
+        <v>0.283827815238942</v>
       </c>
       <c r="M245" s="1">
         <f ca="1" t="shared" si="227"/>
-        <v>0.935415814616671</v>
+        <v>0.71453556000315</v>
       </c>
       <c r="N245" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.340540942762211</v>
+        <v>0.340551497872823</v>
       </c>
       <c r="O245" s="1">
         <f ca="1" t="shared" si="227"/>
-        <v>0.148114403066006</v>
+        <v>0.70491213898906</v>
       </c>
       <c r="P245" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.39713279290662</v>
+        <v>0.397272940690033</v>
       </c>
     </row>
     <row r="246" ht="16.5" spans="1:16">
@@ -18513,27 +18522,27 @@
       </c>
       <c r="K246" s="1">
         <f ca="1" t="shared" ref="K246:O246" si="228">RAND()</f>
-        <v>0.326228846222527</v>
+        <v>0.346635132864024</v>
       </c>
       <c r="L246" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.282631347575742</v>
+        <v>0.282636058294304</v>
       </c>
       <c r="M246" s="1">
         <f ca="1" t="shared" si="228"/>
-        <v>0.612704722409924</v>
+        <v>0.748556789515627</v>
       </c>
       <c r="N246" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.339099318890049</v>
+        <v>0.339135390574253</v>
       </c>
       <c r="O246" s="1">
         <f ca="1" t="shared" si="228"/>
-        <v>0.0400375133764375</v>
+        <v>0.1119239104866</v>
       </c>
       <c r="P246" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.3954350920196</v>
+        <v>0.395487758422441</v>
       </c>
     </row>
     <row r="247" ht="16.5" spans="1:16">
@@ -18573,27 +18582,27 @@
       </c>
       <c r="K247" s="1">
         <f ca="1" t="shared" ref="K247:O247" si="229">RAND()</f>
-        <v>0.885782580035614</v>
+        <v>0.0618124711342554</v>
       </c>
       <c r="L247" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.281606500740078</v>
+        <v>0.281417836603645</v>
       </c>
       <c r="M247" s="1">
         <f ca="1" t="shared" si="229"/>
-        <v>0.152462336732524</v>
+        <v>0.296811918284043</v>
       </c>
       <c r="N247" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.33773897096153</v>
+        <v>0.337583358496333</v>
       </c>
       <c r="O247" s="1">
         <f ca="1" t="shared" si="229"/>
-        <v>0.997521856931633</v>
+        <v>0.923635746793419</v>
       </c>
       <c r="P247" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.394064934154257</v>
+        <v>0.393892404013269</v>
       </c>
     </row>
     <row r="248" ht="16.5" spans="1:16">
@@ -18633,27 +18642,27 @@
       </c>
       <c r="K248" s="1">
         <f ca="1" t="shared" ref="K248:O248" si="230">RAND()</f>
-        <v>0.671037188403177</v>
+        <v>0.64320020378938</v>
       </c>
       <c r="L248" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.280413092281359</v>
+        <v>0.28040677006702</v>
       </c>
       <c r="M248" s="1">
         <f ca="1" t="shared" si="230"/>
-        <v>0.158531247886185</v>
+        <v>0.623099646769431</v>
       </c>
       <c r="N248" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.336319542549962</v>
+        <v>0.336418731080901</v>
       </c>
       <c r="O248" s="1">
         <f ca="1" t="shared" si="230"/>
-        <v>0.96120452811019</v>
+        <v>0.808015324797403</v>
       </c>
       <c r="P248" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.392408292467475</v>
+        <v>0.392472689335768</v>
       </c>
     </row>
     <row r="249" ht="16.5" spans="1:16">
@@ -18693,27 +18702,27 @@
       </c>
       <c r="K249" s="1">
         <f ca="1" t="shared" ref="K249:O249" si="231">RAND()</f>
-        <v>0.961488270689439</v>
+        <v>0.125175286549375</v>
       </c>
       <c r="L249" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.279343550642149</v>
+        <v>0.279155142662831</v>
       </c>
       <c r="M249" s="1">
         <f ca="1" t="shared" si="231"/>
-        <v>0.525677256027214</v>
+        <v>0.698252543419158</v>
       </c>
       <c r="N249" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.335107138635704</v>
+        <v>0.334957609116716</v>
       </c>
       <c r="O249" s="1">
         <f ca="1" t="shared" si="231"/>
-        <v>0.799761817152766</v>
+        <v>0.111737047152601</v>
       </c>
       <c r="P249" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.390932473510275</v>
+        <v>0.390627942981982</v>
       </c>
     </row>
     <row r="250" ht="16.5" spans="1:16">
@@ -18753,27 +18762,27 @@
       </c>
       <c r="K250" s="1">
         <f ca="1" t="shared" ref="K250:O250" si="232">RAND()</f>
-        <v>0.754723720143701</v>
+        <v>0.776702138678233</v>
       </c>
       <c r="L250" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.278170993446981</v>
+        <v>0.278175905064026</v>
       </c>
       <c r="M250" s="1">
         <f ca="1" t="shared" si="232"/>
-        <v>0.190350207498488</v>
+        <v>0.236917895084906</v>
       </c>
       <c r="N250" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.333635218619663</v>
+        <v>0.333650536929426</v>
       </c>
       <c r="O250" s="1">
         <f ca="1" t="shared" si="232"/>
-        <v>0.402815720720824</v>
+        <v>0.623291904127995</v>
       </c>
       <c r="P250" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.389146924425887</v>
+        <v>0.389211513550053</v>
       </c>
     </row>
     <row r="251" ht="16.5" spans="1:16">
@@ -18813,27 +18822,27 @@
       </c>
       <c r="K251" s="1">
         <f ca="1" t="shared" ref="K251:O251" si="233">RAND()</f>
-        <v>0.638841973827432</v>
+        <v>0.429583441450692</v>
       </c>
       <c r="L251" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.277028369786969</v>
+        <v>0.276981979943647</v>
       </c>
       <c r="M251" s="1">
         <f ca="1" t="shared" si="233"/>
-        <v>0.481040737917155</v>
+        <v>0.138805950875864</v>
       </c>
       <c r="N251" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.332335010143327</v>
+        <v>0.332212751383359</v>
       </c>
       <c r="O251" s="1">
         <f ca="1" t="shared" si="233"/>
-        <v>0.705171859947073</v>
+        <v>0.295315002830293</v>
       </c>
       <c r="P251" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.387691337399026</v>
+        <v>0.387478218805674</v>
       </c>
     </row>
     <row r="252" ht="16.5" spans="1:16">
@@ -18873,27 +18882,27 @@
       </c>
       <c r="K252" s="1">
         <f ca="1" t="shared" ref="K252:O252" si="234">RAND()</f>
-        <v>0.330460506003101</v>
+        <v>0.0808610840898578</v>
       </c>
       <c r="L252" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.275852754661081</v>
+        <v>0.27579786267666</v>
       </c>
       <c r="M252" s="1">
         <f ca="1" t="shared" si="234"/>
-        <v>0.139338771053014</v>
+        <v>0.701007467749195</v>
       </c>
       <c r="N252" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.330863477769297</v>
+        <v>0.330932108143671</v>
       </c>
       <c r="O252" s="1">
         <f ca="1" t="shared" si="234"/>
-        <v>0.04614219329516</v>
+        <v>0.658734879804762</v>
       </c>
       <c r="P252" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.385853705056428</v>
+        <v>0.386057057009668</v>
       </c>
     </row>
     <row r="253" ht="16.5" spans="1:16">
@@ -18933,27 +18942,27 @@
       </c>
       <c r="K253" s="1">
         <f ca="1" t="shared" ref="K253:O253" si="235">RAND()</f>
-        <v>0.84568970867451</v>
+        <v>0.538951048837686</v>
       </c>
       <c r="L253" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.274866731771007</v>
+        <v>0.274799809088629</v>
       </c>
       <c r="M253" s="1">
         <f ca="1" t="shared" si="235"/>
-        <v>0.437084121262731</v>
+        <v>0.837005989519448</v>
       </c>
       <c r="N253" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.329723997325826</v>
+        <v>0.32974432756481</v>
       </c>
       <c r="O253" s="1">
         <f ca="1" t="shared" si="235"/>
-        <v>0.881750572557898</v>
+        <v>0.397799359506685</v>
       </c>
       <c r="P253" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.384678277947803</v>
+        <v>0.3845930221699</v>
       </c>
     </row>
     <row r="254" ht="16.5" spans="1:16">
@@ -18993,27 +19002,27 @@
       </c>
       <c r="K254" s="1">
         <f ca="1" t="shared" ref="K254:O254" si="236">RAND()</f>
-        <v>0.537085490551956</v>
+        <v>0.457640725304622</v>
       </c>
       <c r="L254" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.273709325863756</v>
+        <v>0.273692130027122</v>
       </c>
       <c r="M254" s="1">
         <f ca="1" t="shared" si="236"/>
-        <v>0.791038326228115</v>
+        <v>0.017165226934728</v>
       </c>
       <c r="N254" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.328426000826143</v>
+        <v>0.328241299989662</v>
       </c>
       <c r="O254" s="1">
         <f ca="1" t="shared" si="236"/>
-        <v>0.329907411803292</v>
+        <v>0.780518567417945</v>
       </c>
       <c r="P254" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.383042863902291</v>
+        <v>0.382955697947978</v>
       </c>
     </row>
     <row r="255" ht="16.5" spans="1:16">
@@ -19053,27 +19062,27 @@
       </c>
       <c r="K255" s="1">
         <f ca="1" t="shared" ref="K255:O255" si="237">RAND()</f>
-        <v>0.277484231678879</v>
+        <v>0.109598003476726</v>
       </c>
       <c r="L255" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.272572115439874</v>
+        <v>0.272536062563381</v>
       </c>
       <c r="M255" s="1">
         <f ca="1" t="shared" si="237"/>
-        <v>0.685821510739683</v>
+        <v>0.63163723524836</v>
       </c>
       <c r="N255" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.327050101447906</v>
+        <v>0.327002412721272</v>
       </c>
       <c r="O255" s="1">
         <f ca="1" t="shared" si="237"/>
-        <v>0.69319032401376</v>
+        <v>0.0329724275320598</v>
       </c>
       <c r="P255" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.38152966987826</v>
+        <v>0.381340202075789</v>
       </c>
     </row>
     <row r="256" ht="16.5" spans="1:16">
@@ -19113,27 +19122,27 @@
       </c>
       <c r="K256" s="1">
         <f ca="1" t="shared" ref="K256:O256" si="238">RAND()</f>
-        <v>0.839402236621761</v>
+        <v>0.0134840011639965</v>
       </c>
       <c r="L256" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.271619326090248</v>
+        <v>0.27144335462739</v>
       </c>
       <c r="M256" s="1">
         <f ca="1" t="shared" si="238"/>
-        <v>0.260861149071828</v>
+        <v>0.746577131914465</v>
       </c>
       <c r="N256" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.325792552643547</v>
+        <v>0.325720068606399</v>
       </c>
       <c r="O256" s="1">
         <f ca="1" t="shared" si="238"/>
-        <v>0.437951812939597</v>
+        <v>0.605034000036586</v>
       </c>
       <c r="P256" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.380003510417495</v>
+        <v>0.379966625178894</v>
       </c>
     </row>
     <row r="257" ht="16.5" spans="1:16">
@@ -19173,27 +19182,27 @@
       </c>
       <c r="K257" s="1">
         <f ca="1" t="shared" ref="K257:O257" si="239">RAND()</f>
-        <v>0.925468584102654</v>
+        <v>0.383945369901386</v>
       </c>
       <c r="L257" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.270572479572007</v>
+        <v>0.27045800315724</v>
       </c>
       <c r="M257" s="1">
         <f ca="1" t="shared" si="239"/>
-        <v>0.558932000612047</v>
+        <v>0.237442618206245</v>
       </c>
       <c r="N257" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.324596886153019</v>
+        <v>0.324414447828368</v>
       </c>
       <c r="O257" s="1">
         <f ca="1" t="shared" si="239"/>
-        <v>0.994917102161162</v>
+        <v>0.702870230457541</v>
       </c>
       <c r="P257" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.378713458702189</v>
+        <v>0.378469282527822</v>
       </c>
     </row>
     <row r="258" ht="16.5" spans="1:16">
@@ -19233,27 +19242,27 @@
       </c>
       <c r="K258" s="1">
         <f ca="1" t="shared" ref="K258:O258" si="243">RAND()</f>
-        <v>0.491247057072529</v>
+        <v>0.227422485314746</v>
       </c>
       <c r="L258" s="1">
         <f ca="1" t="shared" ref="L258:L302" si="244">J258+($R$1*$R$7*K258/MAX(1,($A258*($A258-1)))+$R$1*$R$7/$A258)/100</f>
-        <v>0.269424538080429</v>
+        <v>0.269369200363226</v>
       </c>
       <c r="M258" s="1">
         <f ca="1" t="shared" si="243"/>
-        <v>0.508946056200216</v>
+        <v>0.124317119070062</v>
       </c>
       <c r="N258" s="1">
         <f ca="1" t="shared" ref="N258:N302" si="245">L258+($R$1*$R$7*M258/MAX(1,($A258*($A258-1)))+$R$1*$R$7/$A258)/100</f>
-        <v>0.323227788560359</v>
+        <v>0.323091774175287</v>
       </c>
       <c r="O258" s="1">
         <f ca="1" t="shared" si="243"/>
-        <v>0.28683124810176</v>
+        <v>0.296795272973808</v>
       </c>
       <c r="P258" s="1">
         <f ca="1" t="shared" ref="P258:P302" si="246">N258+($R$1*$R$7*O258/MAX(1,($A258*($A258-1)))+$R$1*$R$7/$A258)/100</f>
-        <v>0.376984450027161</v>
+        <v>0.376850525615691</v>
       </c>
     </row>
     <row r="259" ht="16.5" spans="1:16">
@@ -19293,27 +19302,27 @@
       </c>
       <c r="K259" s="1">
         <f ca="1" t="shared" ref="K259:O259" si="248">RAND()</f>
-        <v>0.267545950406828</v>
+        <v>0.906132443966744</v>
       </c>
       <c r="L259" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.268330047569083</v>
+        <v>0.268462953997025</v>
       </c>
       <c r="M259" s="1">
         <f ca="1" t="shared" si="248"/>
-        <v>0.635772850738634</v>
+        <v>0.51377712829553</v>
       </c>
       <c r="N259" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.321950740497931</v>
+        <v>0.322058256448847</v>
       </c>
       <c r="O259" s="1">
         <f ca="1" t="shared" si="248"/>
-        <v>0.571677605360809</v>
+        <v>0.334446215265882</v>
       </c>
       <c r="P259" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.37555809354221</v>
+        <v>0.375616235481976</v>
       </c>
     </row>
     <row r="260" ht="16.5" spans="1:16">
@@ -19353,27 +19362,27 @@
       </c>
       <c r="K260" s="1">
         <f ca="1" t="shared" ref="K260:O260" si="249">RAND()</f>
-        <v>0.865855998907701</v>
+        <v>0.185574106446951</v>
       </c>
       <c r="L260" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.267414157205485</v>
+        <v>0.267273666197794</v>
       </c>
       <c r="M260" s="1">
         <f ca="1" t="shared" si="249"/>
-        <v>0.63945689712348</v>
+        <v>0.28684922823077</v>
       </c>
       <c r="N260" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.320828070365527</v>
+        <v>0.320614759241246</v>
       </c>
       <c r="O260" s="1">
         <f ca="1" t="shared" si="249"/>
-        <v>0.0418663284029013</v>
+        <v>0.0512285563715453</v>
       </c>
       <c r="P260" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.37411856983175</v>
+        <v>0.373907192183659</v>
       </c>
     </row>
     <row r="261" ht="16.5" spans="1:16">
@@ -19413,27 +19422,27 @@
       </c>
       <c r="K261" s="1">
         <f ca="1" t="shared" ref="K261:O261" si="250">RAND()</f>
-        <v>0.61448113946991</v>
+        <v>0.465681528108133</v>
       </c>
       <c r="L261" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.266330261950173</v>
+        <v>0.266299768415323</v>
       </c>
       <c r="M261" s="1">
         <f ca="1" t="shared" si="250"/>
-        <v>0.998456361884895</v>
+        <v>0.26090840717871</v>
       </c>
       <c r="N261" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.319611798893951</v>
+        <v>0.319430159505598</v>
       </c>
       <c r="O261" s="1">
         <f ca="1" t="shared" si="250"/>
-        <v>0.602556991556013</v>
+        <v>0.709907870251985</v>
       </c>
       <c r="P261" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.372812204098636</v>
+        <v>0.372652564147853</v>
       </c>
     </row>
     <row r="262" ht="16.5" spans="1:16">
@@ -19473,27 +19482,27 @@
       </c>
       <c r="K262" s="1">
         <f ca="1" t="shared" ref="K262:O262" si="251">RAND()</f>
-        <v>0.415215724056521</v>
+        <v>0.604135539162096</v>
       </c>
       <c r="L262" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.265265693736987</v>
+        <v>0.265304112443861</v>
       </c>
       <c r="M262" s="1">
         <f ca="1" t="shared" si="251"/>
-        <v>0.632596541819085</v>
+        <v>0.577770062000631</v>
       </c>
       <c r="N262" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.31826790169863</v>
+        <v>0.318295170900325</v>
       </c>
       <c r="O262" s="1">
         <f ca="1" t="shared" si="251"/>
-        <v>0.646216495410187</v>
+        <v>0.75434616423056</v>
       </c>
       <c r="P262" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.371272879412109</v>
+        <v>0.371322137847958</v>
       </c>
     </row>
     <row r="263" ht="16.5" spans="1:16">
@@ -19533,27 +19542,27 @@
       </c>
       <c r="K263" s="1">
         <f ca="1" t="shared" ref="K263:O263" si="252">RAND()</f>
-        <v>0.590473697045564</v>
+        <v>0.327582409846706</v>
       </c>
       <c r="L263" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.264285170615355</v>
+        <v>0.264232117183701</v>
       </c>
       <c r="M263" s="1">
         <f ca="1" t="shared" si="252"/>
-        <v>0.72681804223248</v>
+        <v>0.490509164313698</v>
       </c>
       <c r="N263" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.317103603667661</v>
+        <v>0.317002861333734</v>
       </c>
       <c r="O263" s="1">
         <f ca="1" t="shared" si="252"/>
-        <v>0.548126193339316</v>
+        <v>0.5482306712508</v>
       </c>
       <c r="P263" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.369885975365887</v>
+        <v>0.369785254116385</v>
       </c>
     </row>
     <row r="264" ht="16.5" spans="1:16">
@@ -19593,27 +19602,27 @@
       </c>
       <c r="K264" s="1">
         <f ca="1" t="shared" ref="K264:O264" si="253">RAND()</f>
-        <v>0.327435294388643</v>
+        <v>0.895967471735387</v>
       </c>
       <c r="L264" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.263224082185333</v>
+        <v>0.263337943736539</v>
       </c>
       <c r="M264" s="1">
         <f ca="1" t="shared" si="253"/>
-        <v>0.748216207239837</v>
+        <v>0.789407499004041</v>
       </c>
       <c r="N264" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.315845412456425</v>
+        <v>0.315967523504429</v>
       </c>
       <c r="O264" s="1">
         <f ca="1" t="shared" si="253"/>
-        <v>0.356216436697158</v>
+        <v>0.673498416172891</v>
       </c>
       <c r="P264" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.368388235821973</v>
+        <v>0.368573889831646</v>
       </c>
     </row>
     <row r="265" ht="16.5" spans="1:16">
@@ -19653,27 +19662,27 @@
       </c>
       <c r="K265" s="1">
         <f ca="1" t="shared" ref="K265:O265" si="254">RAND()</f>
-        <v>0.839026600084055</v>
+        <v>0.649357973424601</v>
       </c>
       <c r="L265" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.262325420081247</v>
+        <v>0.262287722376328</v>
       </c>
       <c r="M265" s="1">
         <f ca="1" t="shared" si="254"/>
-        <v>0.808901140170524</v>
+        <v>0.124577398179579</v>
       </c>
       <c r="N265" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.314758920999186</v>
+        <v>0.314585210106696</v>
       </c>
       <c r="O265" s="1">
         <f ca="1" t="shared" si="254"/>
-        <v>0.389664018417168</v>
+        <v>0.168422679459183</v>
       </c>
       <c r="P265" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.367109096184319</v>
+        <v>0.366891412332997</v>
       </c>
     </row>
     <row r="266" ht="16.5" spans="1:16">
@@ -19713,27 +19722,27 @@
       </c>
       <c r="K266" s="1">
         <f ca="1" t="shared" ref="K266:O266" si="255">RAND()</f>
-        <v>0.749450763681398</v>
+        <v>0.751468876038834</v>
       </c>
       <c r="L266" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.261314214130057</v>
+        <v>0.26131461221397</v>
       </c>
       <c r="M266" s="1">
         <f ca="1" t="shared" si="255"/>
-        <v>0.826342436439061</v>
+        <v>0.199273120475228</v>
       </c>
       <c r="N266" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.313552686480298</v>
+        <v>0.313429391645968</v>
       </c>
       <c r="O266" s="1">
         <f ca="1" t="shared" si="255"/>
-        <v>0.00112691166388346</v>
+        <v>0.0874145561165436</v>
       </c>
       <c r="P266" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.365628380468019</v>
+        <v>0.365522106352577</v>
       </c>
     </row>
     <row r="267" ht="16.5" spans="1:16">
@@ -19773,27 +19782,27 @@
       </c>
       <c r="K267" s="1">
         <f ca="1" t="shared" ref="K267:O267" si="256">RAND()</f>
-        <v>0.123001549337078</v>
+        <v>0.158057318010812</v>
       </c>
       <c r="L267" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.26020566635524</v>
+        <v>0.26021252930896</v>
       </c>
       <c r="M267" s="1">
         <f ca="1" t="shared" si="256"/>
-        <v>0.570235066836323</v>
+        <v>0.786025407059181</v>
       </c>
       <c r="N267" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.312197001919467</v>
+        <v>0.312246110676777</v>
       </c>
       <c r="O267" s="1">
         <f ca="1" t="shared" si="256"/>
-        <v>0.517076915431808</v>
+        <v>0.968250539613685</v>
       </c>
       <c r="P267" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.364177930582156</v>
+        <v>0.364315366705244</v>
       </c>
     </row>
     <row r="268" ht="16.5" spans="1:16">
@@ -19833,27 +19842,27 @@
       </c>
       <c r="K268" s="1">
         <f ca="1" t="shared" ref="K268:O268" si="257">RAND()</f>
-        <v>0.590131029042013</v>
+        <v>0.628411114278467</v>
       </c>
       <c r="L268" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.259318856244555</v>
+        <v>0.259326294294402</v>
       </c>
       <c r="M268" s="1">
         <f ca="1" t="shared" si="257"/>
-        <v>0.408845976824684</v>
+        <v>0.608615482902154</v>
       </c>
       <c r="N268" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.311083690725141</v>
+        <v>0.311129945186577</v>
       </c>
       <c r="O268" s="1">
         <f ca="1" t="shared" si="257"/>
-        <v>0.486517890943784</v>
+        <v>0.265292758343528</v>
       </c>
       <c r="P268" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.362863617323871</v>
+        <v>0.362866886416973</v>
       </c>
     </row>
     <row r="269" ht="16.5" spans="1:16">
@@ -19893,27 +19902,27 @@
       </c>
       <c r="K269" s="1">
         <f ca="1" t="shared" ref="K269:O269" si="258">RAND()</f>
-        <v>0.721374083132929</v>
+        <v>0.55431192836069</v>
       </c>
       <c r="L269" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.258373231627638</v>
+        <v>0.258341012697906</v>
       </c>
       <c r="M269" s="1">
         <f ca="1" t="shared" si="258"/>
-        <v>0.471807158093504</v>
+        <v>0.906429946288873</v>
       </c>
       <c r="N269" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.3099567597564</v>
+        <v>0.310008360415202</v>
       </c>
       <c r="O269" s="1">
         <f ca="1" t="shared" si="258"/>
-        <v>0.923326944236778</v>
+        <v>0.363269744102618</v>
       </c>
       <c r="P269" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.361627366160202</v>
+        <v>0.361570956458421</v>
       </c>
     </row>
     <row r="270" ht="16.5" spans="1:16">
@@ -19953,27 +19962,27 @@
       </c>
       <c r="K270" s="1">
         <f ca="1" t="shared" ref="K270:O270" si="259">RAND()</f>
-        <v>0.978395533624806</v>
+        <v>0.342437041165618</v>
       </c>
       <c r="L270" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.25745855099545</v>
+        <v>0.257336814503247</v>
       </c>
       <c r="M270" s="1">
         <f ca="1" t="shared" si="259"/>
-        <v>0.168892667205693</v>
+        <v>0.809283828831611</v>
       </c>
       <c r="N270" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.308791996021354</v>
+        <v>0.308792844532069</v>
       </c>
       <c r="O270" s="1">
         <f ca="1" t="shared" si="259"/>
-        <v>0.614443812400499</v>
+        <v>0.423717328899845</v>
       </c>
       <c r="P270" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.360210729370562</v>
+        <v>0.360175068622659</v>
       </c>
     </row>
     <row r="271" ht="16.5" spans="1:16">
@@ -20013,27 +20022,27 @@
       </c>
       <c r="K271" s="1">
         <f ca="1" t="shared" ref="K271:O271" si="260">RAND()</f>
-        <v>0.789118168708264</v>
+        <v>0.271863752076672</v>
       </c>
       <c r="L271" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.256465507789181</v>
+        <v>0.256367227313489</v>
       </c>
       <c r="M271" s="1">
         <f ca="1" t="shared" si="260"/>
-        <v>0.907794733950388</v>
+        <v>0.876783425742611</v>
       </c>
       <c r="N271" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.307749103649411</v>
+        <v>0.307644930897066</v>
       </c>
       <c r="O271" s="1">
         <f ca="1" t="shared" si="260"/>
-        <v>0.731112834466138</v>
+        <v>0.903199878040815</v>
       </c>
       <c r="P271" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.35899912921895</v>
+        <v>0.358927653715694</v>
       </c>
     </row>
     <row r="272" ht="16.5" spans="1:16">
@@ -20073,27 +20082,27 @@
       </c>
       <c r="K272" s="1">
         <f ca="1" t="shared" ref="K272:O272" si="261">RAND()</f>
-        <v>0.489321822787572</v>
+        <v>0.837916204123106</v>
       </c>
       <c r="L272" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.255459240688184</v>
+        <v>0.25552498624596</v>
       </c>
       <c r="M272" s="1">
         <f ca="1" t="shared" si="261"/>
-        <v>0.326072545038649</v>
+        <v>0.943489892839389</v>
       </c>
       <c r="N272" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.30644324781025</v>
+        <v>0.306625439444281</v>
       </c>
       <c r="O272" s="1">
         <f ca="1" t="shared" si="261"/>
-        <v>0.814314885667792</v>
+        <v>0.514827184232539</v>
       </c>
       <c r="P272" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.357519338358592</v>
+        <v>0.357645046047293</v>
       </c>
     </row>
     <row r="273" ht="16.5" spans="1:16">
@@ -20133,27 +20142,27 @@
       </c>
       <c r="K273" s="1">
         <f ca="1" t="shared" ref="K273:O273" si="262">RAND()</f>
-        <v>0.560694004174665</v>
+        <v>0.381396942329671</v>
       </c>
       <c r="L273" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.254530301406251</v>
+        <v>0.254496734287554</v>
       </c>
       <c r="M273" s="1">
         <f ca="1" t="shared" si="262"/>
-        <v>0.515450636149698</v>
+        <v>0.0261491412829673</v>
       </c>
       <c r="N273" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.305362095670128</v>
+        <v>0.305236923919496</v>
       </c>
       <c r="O273" s="1">
         <f ca="1" t="shared" si="262"/>
-        <v>0.0340174250466927</v>
+        <v>0.731528035682284</v>
       </c>
       <c r="P273" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.35610375836366</v>
+        <v>0.356109171136942</v>
       </c>
     </row>
     <row r="274" ht="16.5" spans="1:16">
@@ -20193,27 +20202,27 @@
       </c>
       <c r="K274" s="1">
         <f ca="1" t="shared" ref="K274:O274" si="263">RAND()</f>
-        <v>0.65388866961432</v>
+        <v>0.040971714122245</v>
       </c>
       <c r="L274" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.253612148023603</v>
+        <v>0.253498241349586</v>
       </c>
       <c r="M274" s="1">
         <f ca="1" t="shared" si="263"/>
-        <v>0.0360377339450815</v>
+        <v>0.800536991096402</v>
       </c>
       <c r="N274" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.30416829595412</v>
+        <v>0.304196466549935</v>
       </c>
       <c r="O274" s="1">
         <f ca="1" t="shared" si="263"/>
-        <v>0.450365876053852</v>
+        <v>0.758810193493543</v>
       </c>
       <c r="P274" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.35480144410497</v>
+        <v>0.354886937093329</v>
       </c>
     </row>
     <row r="275" ht="16.5" spans="1:16">
@@ -20253,27 +20262,27 @@
       </c>
       <c r="K275" s="1">
         <f ca="1" t="shared" ref="K275:O275" si="264">RAND()</f>
-        <v>0.275387531492072</v>
+        <v>0.485344390891961</v>
       </c>
       <c r="L275" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.252613571133587</v>
+        <v>0.252652305454323</v>
       </c>
       <c r="M275" s="1">
         <f ca="1" t="shared" si="264"/>
-        <v>0.845106764092639</v>
+        <v>0.83853945106929</v>
       </c>
       <c r="N275" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.30313444588753</v>
+        <v>0.303171968624088</v>
       </c>
       <c r="O275" s="1">
         <f ca="1" t="shared" si="264"/>
-        <v>0.913907022922097</v>
+        <v>0.582973327744192</v>
       </c>
       <c r="P275" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.353668013397976</v>
+        <v>0.353644483154754</v>
       </c>
     </row>
     <row r="276" ht="16.5" spans="1:16">
@@ -20313,27 +20322,27 @@
       </c>
       <c r="K276" s="1">
         <f ca="1" t="shared" ref="K276:O276" si="265">RAND()</f>
-        <v>0.817846803767968</v>
+        <v>0.27243406630448</v>
       </c>
       <c r="L276" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.251791457012502</v>
+        <v>0.251691567221168</v>
       </c>
       <c r="M276" s="1">
         <f ca="1" t="shared" si="265"/>
-        <v>0.61112440840095</v>
+        <v>0.0285702054601304</v>
       </c>
       <c r="N276" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.302085199770776</v>
+        <v>0.30187861790246</v>
       </c>
       <c r="O276" s="1">
         <f ca="1" t="shared" si="265"/>
-        <v>0.276972000054781</v>
+        <v>0.0508056224519162</v>
       </c>
       <c r="P276" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.352317744078682</v>
+        <v>0.352069740896353</v>
       </c>
     </row>
     <row r="277" ht="16.5" spans="1:16">
@@ -20373,27 +20382,27 @@
       </c>
       <c r="K277" s="1">
         <f ca="1" t="shared" ref="K277:O277" si="266">RAND()</f>
-        <v>0.270088548426555</v>
+        <v>0.436601261034724</v>
       </c>
       <c r="L277" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.250776379736078</v>
+        <v>0.250806654774734</v>
       </c>
       <c r="M277" s="1">
         <f ca="1" t="shared" si="266"/>
-        <v>0.375916997735328</v>
+        <v>0.914709510155883</v>
       </c>
       <c r="N277" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.300844728281121</v>
+        <v>0.300972965594762</v>
       </c>
       <c r="O277" s="1">
         <f ca="1" t="shared" si="266"/>
-        <v>0.675034862378851</v>
+        <v>0.503996496531872</v>
       </c>
       <c r="P277" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.350967461892462</v>
+        <v>0.351064601321404</v>
       </c>
     </row>
     <row r="278" ht="16.5" spans="1:16">
@@ -20433,27 +20442,27 @@
       </c>
       <c r="K278" s="1">
         <f ca="1" t="shared" ref="K278:O278" si="267">RAND()</f>
-        <v>0.331960196254539</v>
+        <v>0.61290169245771</v>
       </c>
       <c r="L278" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.24987941519788</v>
+        <v>0.249930126659288</v>
       </c>
       <c r="M278" s="1">
         <f ca="1" t="shared" si="267"/>
-        <v>0.0255380193144072</v>
+        <v>0.553417432445565</v>
       </c>
       <c r="N278" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.299703519533496</v>
+        <v>0.299849516087528</v>
       </c>
       <c r="O278" s="1">
         <f ca="1" t="shared" si="267"/>
-        <v>0.913795320421845</v>
+        <v>0.000974338003730368</v>
       </c>
       <c r="P278" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.34968795912202</v>
+        <v>0.349669186545651</v>
       </c>
     </row>
     <row r="279" ht="16.5" spans="1:16">
@@ -20493,27 +20502,27 @@
       </c>
       <c r="K279" s="1">
         <f ca="1" t="shared" ref="K279:O279" si="268">RAND()</f>
-        <v>0.00635072312231055</v>
+        <v>0.731026881870514</v>
       </c>
       <c r="L279" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.248919404201998</v>
+        <v>0.249049271108353</v>
       </c>
       <c r="M279" s="1">
         <f ca="1" t="shared" si="268"/>
-        <v>0.364110852832682</v>
+        <v>0.901717120634947</v>
       </c>
       <c r="N279" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.298624943118045</v>
+        <v>0.298851152731405</v>
       </c>
       <c r="O279" s="1">
         <f ca="1" t="shared" si="268"/>
-        <v>0.337084291621872</v>
+        <v>0.584975390256075</v>
       </c>
       <c r="P279" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.348325638690135</v>
+        <v>0.348596272077761</v>
       </c>
     </row>
     <row r="280" ht="16.5" spans="1:16">
@@ -20553,27 +20562,27 @@
       </c>
       <c r="K280" s="1">
         <f ca="1" t="shared" ref="K280:O280" si="269">RAND()</f>
-        <v>0.490768307988678</v>
+        <v>0.29256396041552</v>
       </c>
       <c r="L280" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.248110835236975</v>
+        <v>0.248075570287689</v>
       </c>
       <c r="M280" s="1">
         <f ca="1" t="shared" si="269"/>
-        <v>0.463876365036416</v>
+        <v>0.910137289144374</v>
       </c>
       <c r="N280" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.297655734721742</v>
+        <v>0.297699869488202</v>
       </c>
       <c r="O280" s="1">
         <f ca="1" t="shared" si="269"/>
-        <v>0.25375637580592</v>
+        <v>0.73029161639156</v>
       </c>
       <c r="P280" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.347163249200303</v>
+        <v>0.347292170154846</v>
       </c>
     </row>
     <row r="281" ht="16.5" spans="1:16">
@@ -20613,27 +20622,27 @@
       </c>
       <c r="K281" s="1">
         <f ca="1" t="shared" ref="K281:O281" si="270">RAND()</f>
-        <v>0.808032882253953</v>
+        <v>0.119096424425344</v>
       </c>
       <c r="L281" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.247277916714991</v>
+        <v>0.247156215190182</v>
       </c>
       <c r="M281" s="1">
         <f ca="1" t="shared" si="270"/>
-        <v>0.310084986548145</v>
+        <v>0.921550441526944</v>
       </c>
       <c r="N281" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.296618407918452</v>
+        <v>0.296604722564646</v>
       </c>
       <c r="O281" s="1">
         <f ca="1" t="shared" si="270"/>
-        <v>0.576466602678682</v>
+        <v>0.33365230419035</v>
       </c>
       <c r="P281" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.346005955782212</v>
+        <v>0.345949376965539</v>
       </c>
     </row>
     <row r="282" ht="16.5" spans="1:16">
@@ -20673,27 +20682,27 @@
       </c>
       <c r="K282" s="1">
         <f ca="1" t="shared" ref="K282:O282" si="271">RAND()</f>
-        <v>0.216909840590615</v>
+        <v>0.57498312989811</v>
       </c>
       <c r="L282" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.246291222112356</v>
+        <v>0.246354026019224</v>
       </c>
       <c r="M282" s="1">
         <f ca="1" t="shared" si="271"/>
-        <v>0.88744117903853</v>
+        <v>0.62096786584455</v>
       </c>
       <c r="N282" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.295557194256112</v>
+        <v>0.295573260342415</v>
       </c>
       <c r="O282" s="1">
         <f ca="1" t="shared" si="271"/>
-        <v>0.972847498424198</v>
+        <v>0.682974503091195</v>
       </c>
       <c r="P282" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.344838146155937</v>
+        <v>0.344803370257802</v>
       </c>
     </row>
     <row r="283" ht="16.5" spans="1:16">
@@ -20733,27 +20742,27 @@
       </c>
       <c r="K283" s="1">
         <f ca="1" t="shared" ref="K283:O283" si="272">RAND()</f>
-        <v>0.773854425585387</v>
+        <v>0.520902522661498</v>
       </c>
       <c r="L283" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.245512218155436</v>
+        <v>0.245468166563347</v>
       </c>
       <c r="M283" s="1">
         <f ca="1" t="shared" si="272"/>
-        <v>0.693672045393269</v>
+        <v>0.626767313662981</v>
       </c>
       <c r="N283" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.294569191404804</v>
+        <v>0.294513488348871</v>
       </c>
       <c r="O283" s="1">
         <f ca="1" t="shared" si="272"/>
-        <v>0.793296005941769</v>
+        <v>0.731549505416095</v>
       </c>
       <c r="P283" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.343643514174068</v>
+        <v>0.343577057960627</v>
       </c>
     </row>
     <row r="284" ht="16.5" spans="1:16">
@@ -20793,27 +20802,27 @@
       </c>
       <c r="K284" s="1">
         <f ca="1" t="shared" ref="K284:O284" si="273">RAND()</f>
-        <v>0.0858574301038972</v>
+        <v>0.102232271103228</v>
       </c>
       <c r="L284" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.244522778143692</v>
+        <v>0.244525609670216</v>
       </c>
       <c r="M284" s="1">
         <f ca="1" t="shared" si="273"/>
-        <v>0.391245446449857</v>
+        <v>0.083221301067663</v>
       </c>
       <c r="N284" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.293353682927304</v>
+        <v>0.293303251125178</v>
       </c>
       <c r="O284" s="1">
         <f ca="1" t="shared" si="273"/>
-        <v>0.179126894873013</v>
+        <v>0.547183900831294</v>
       </c>
       <c r="P284" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.342147908313231</v>
+        <v>0.342161120681746</v>
       </c>
     </row>
     <row r="285" ht="16.5" spans="1:16">
@@ -20853,27 +20862,27 @@
       </c>
       <c r="K285" s="1">
         <f ca="1" t="shared" ref="K285:O285" si="274">RAND()</f>
-        <v>0.355641311184621</v>
+        <v>0.947876326106188</v>
       </c>
       <c r="L285" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.243705617007096</v>
+        <v>0.243807304699401</v>
       </c>
       <c r="M285" s="1">
         <f ca="1" t="shared" si="274"/>
-        <v>0.907886851897449</v>
+        <v>0.759149800946889</v>
       </c>
       <c r="N285" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.292453051916719</v>
+        <v>0.292529201221238</v>
       </c>
       <c r="O285" s="1">
         <f ca="1" t="shared" si="274"/>
-        <v>0.624024336296423</v>
+        <v>0.592968655326533</v>
       </c>
       <c r="P285" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.341151747181748</v>
+        <v>0.34122256417654</v>
       </c>
     </row>
     <row r="286" ht="16.5" spans="1:16">
@@ -20913,27 +20922,27 @@
       </c>
       <c r="K286" s="1">
         <f ca="1" t="shared" ref="K286:O286" si="275">RAND()</f>
-        <v>0.310428898888178</v>
+        <v>0.899159591515541</v>
       </c>
       <c r="L286" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.242840176906408</v>
+        <v>0.242940553525611</v>
       </c>
       <c r="M286" s="1">
         <f ca="1" t="shared" si="275"/>
-        <v>0.942342649525658</v>
+        <v>0.675524712987982</v>
       </c>
       <c r="N286" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.291421895816261</v>
+        <v>0.291476780867336</v>
       </c>
       <c r="O286" s="1">
         <f ca="1" t="shared" si="275"/>
-        <v>0.418007829216528</v>
+        <v>0.143609826029023</v>
       </c>
       <c r="P286" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.339914217388329</v>
+        <v>0.339922318495199</v>
       </c>
     </row>
     <row r="287" ht="16.5" spans="1:16">
@@ -20973,27 +20982,27 @@
       </c>
       <c r="K287" s="1">
         <f ca="1" t="shared" ref="K287:O287" si="276">RAND()</f>
-        <v>0.206797267230924</v>
+        <v>0.902490424968299</v>
       </c>
       <c r="L287" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.241970970461143</v>
+        <v>0.242088754359767</v>
       </c>
       <c r="M287" s="1">
         <f ca="1" t="shared" si="276"/>
-        <v>0.868207091367582</v>
+        <v>0.388922680451405</v>
       </c>
       <c r="N287" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.29036970997606</v>
+        <v>0.290406348924731</v>
       </c>
       <c r="O287" s="1">
         <f ca="1" t="shared" si="276"/>
-        <v>0.642365065244853</v>
+        <v>0.348884496010512</v>
       </c>
       <c r="P287" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.338730213446805</v>
+        <v>0.338717164849709</v>
       </c>
     </row>
     <row r="288" ht="16.5" spans="1:16">
@@ -21033,27 +21042,27 @@
       </c>
       <c r="K288" s="1">
         <f ca="1" t="shared" ref="K288:O288" si="277">RAND()</f>
-        <v>0.665441774513212</v>
+        <v>0.507376000718963</v>
       </c>
       <c r="L288" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.241202493804833</v>
+        <v>0.24117591906642</v>
       </c>
       <c r="M288" s="1">
         <f ca="1" t="shared" si="277"/>
-        <v>0.257340517878823</v>
+        <v>0.0228054895071415</v>
       </c>
       <c r="N288" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.289329382759131</v>
+        <v>0.289263376922652</v>
       </c>
       <c r="O288" s="1">
         <f ca="1" t="shared" si="277"/>
-        <v>0.495057549201746</v>
+        <v>0.610745000003788</v>
       </c>
       <c r="P288" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.337496237784338</v>
+        <v>0.337449681849433</v>
       </c>
     </row>
     <row r="289" ht="16.5" spans="1:16">
@@ -21093,27 +21102,27 @@
       </c>
       <c r="K289" s="1">
         <f ca="1" t="shared" ref="K289:O289" si="278">RAND()</f>
-        <v>0.51475999235802</v>
+        <v>0.101313968830363</v>
       </c>
       <c r="L289" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.240337104237981</v>
+        <v>0.240268076519186</v>
       </c>
       <c r="M289" s="1">
         <f ca="1" t="shared" si="278"/>
-        <v>0.628889408785953</v>
+        <v>0.245261117598455</v>
       </c>
       <c r="N289" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.28835876841047</v>
+        <v>0.288225691252815</v>
       </c>
       <c r="O289" s="1">
         <f ca="1" t="shared" si="278"/>
-        <v>0.534455735124833</v>
+        <v>0.460600656572139</v>
       </c>
       <c r="P289" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.336364666217582</v>
+        <v>0.336219258435605</v>
       </c>
     </row>
     <row r="290" ht="16.5" spans="1:16">
@@ -21153,27 +21162,27 @@
       </c>
       <c r="K290" s="1">
         <f ca="1" t="shared" ref="K290:O290" si="279">RAND()</f>
-        <v>0.220142377908732</v>
+        <v>0.674309823506708</v>
       </c>
       <c r="L290" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.239454031680305</v>
+        <v>0.239529333376158</v>
       </c>
       <c r="M290" s="1">
         <f ca="1" t="shared" si="279"/>
-        <v>0.105179045926255</v>
+        <v>0.210351069115188</v>
       </c>
       <c r="N290" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.287222335587862</v>
+        <v>0.287315074974988</v>
       </c>
       <c r="O290" s="1">
         <f ca="1" t="shared" si="279"/>
-        <v>0.250929335067295</v>
+        <v>0.557237170727347</v>
       </c>
       <c r="P290" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.335014805128711</v>
+        <v>0.335158330849604</v>
       </c>
     </row>
     <row r="291" ht="16.5" spans="1:16">
@@ -21213,27 +21222,27 @@
       </c>
       <c r="K291" s="1">
         <f ca="1" t="shared" ref="K291:O291" si="280">RAND()</f>
-        <v>0.285764341223699</v>
+        <v>0.616678834174357</v>
       </c>
       <c r="L291" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.238636720533455</v>
+        <v>0.238691208303443</v>
       </c>
       <c r="M291" s="1">
         <f ca="1" t="shared" si="280"/>
-        <v>0.441308101971102</v>
+        <v>0.304659325899786</v>
       </c>
       <c r="N291" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.286295592408019</v>
+        <v>0.286327579842608</v>
       </c>
       <c r="O291" s="1">
         <f ca="1" t="shared" si="280"/>
-        <v>0.204439001574513</v>
+        <v>0.703653850053531</v>
       </c>
       <c r="P291" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.333915461853452</v>
+        <v>0.334029649084116</v>
       </c>
     </row>
     <row r="292" ht="16.5" spans="1:16">
@@ -21273,27 +21282,27 @@
       </c>
       <c r="K292" s="1">
         <f ca="1" t="shared" ref="K292:O292" si="281">RAND()</f>
-        <v>0.556416627193586</v>
+        <v>0.872478006834678</v>
       </c>
       <c r="L292" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.237858496853363</v>
+        <v>0.237910181259561</v>
       </c>
       <c r="M292" s="1">
         <f ca="1" t="shared" si="281"/>
-        <v>0.452792302059309</v>
+        <v>0.0415353462636474</v>
       </c>
       <c r="N292" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.285355220798954</v>
+        <v>0.285339653801076</v>
       </c>
       <c r="O292" s="1">
         <f ca="1" t="shared" si="281"/>
-        <v>0.9119920178083</v>
+        <v>0.452015032143917</v>
       </c>
       <c r="P292" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.332927036059598</v>
+        <v>0.33283625064245</v>
       </c>
     </row>
     <row r="293" ht="16.5" spans="1:16">
@@ -21333,27 +21342,27 @@
       </c>
       <c r="K293" s="1">
         <f ca="1" t="shared" ref="K293:O293" si="282">RAND()</f>
-        <v>0.934964155216734</v>
+        <v>0.247287765952493</v>
       </c>
       <c r="L293" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.237102839821848</v>
+        <v>0.236991156747754</v>
       </c>
       <c r="M293" s="1">
         <f ca="1" t="shared" si="282"/>
-        <v>0.670876307064558</v>
+        <v>0.55271383568699</v>
       </c>
       <c r="N293" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.284472068427006</v>
+        <v>0.284341195006622</v>
       </c>
       <c r="O293" s="1">
         <f ca="1" t="shared" si="282"/>
-        <v>0.917434069381672</v>
+        <v>0.450676780060684</v>
       </c>
       <c r="P293" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.331881339600539</v>
+        <v>0.33167466179056</v>
       </c>
     </row>
     <row r="294" ht="16.5" spans="1:16">
@@ -21393,27 +21402,27 @@
       </c>
       <c r="K294" s="1">
         <f ca="1" t="shared" ref="K294:O294" si="283">RAND()</f>
-        <v>0.417798181377978</v>
+        <v>0.0639529007934063</v>
       </c>
       <c r="L294" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.23620746195361</v>
+        <v>0.236150387465881</v>
       </c>
       <c r="M294" s="1">
         <f ca="1" t="shared" si="283"/>
-        <v>0.272964188408738</v>
+        <v>0.476316584256378</v>
       </c>
       <c r="N294" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.283350466603196</v>
+        <v>0.283326192422433</v>
       </c>
       <c r="O294" s="1">
         <f ca="1" t="shared" si="283"/>
-        <v>0.136033525045152</v>
+        <v>0.850211434386809</v>
       </c>
       <c r="P294" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.33047138462935</v>
+        <v>0.330562305819443</v>
       </c>
     </row>
     <row r="295" ht="16.5" spans="1:16">
@@ -21453,27 +21462,27 @@
       </c>
       <c r="K295" s="1">
         <f ca="1" t="shared" ref="K295:O295" si="284">RAND()</f>
-        <v>0.644401571223226</v>
+        <v>0.768754143545002</v>
       </c>
       <c r="L295" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.235437913464778</v>
+        <v>0.235457834821352</v>
       </c>
       <c r="M295" s="1">
         <f ca="1" t="shared" si="284"/>
-        <v>0.824269055855583</v>
+        <v>0.444671329407721</v>
       </c>
       <c r="N295" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.282508737371476</v>
+        <v>0.28246784694489</v>
       </c>
       <c r="O295" s="1">
         <f ca="1" t="shared" si="284"/>
-        <v>0.0290573398043892</v>
+        <v>0.88086947858379</v>
       </c>
       <c r="P295" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.329452167884922</v>
+        <v>0.329547738273214</v>
       </c>
     </row>
     <row r="296" ht="16.5" spans="1:16">
@@ -21513,27 +21522,27 @@
       </c>
       <c r="K296" s="1">
         <f ca="1" t="shared" ref="K296:O296" si="285">RAND()</f>
-        <v>0.684090849066208</v>
+        <v>0.986052117811162</v>
       </c>
       <c r="L296" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.234643611826555</v>
+        <v>0.234691658240814</v>
       </c>
       <c r="M296" s="1">
         <f ca="1" t="shared" si="285"/>
-        <v>0.555084323960963</v>
+        <v>0.813992315729781</v>
       </c>
       <c r="N296" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.281511594804425</v>
+        <v>0.281600837232594</v>
       </c>
       <c r="O296" s="1">
         <f ca="1" t="shared" si="285"/>
-        <v>0.900709545566821</v>
+        <v>0.508183406603546</v>
       </c>
       <c r="P296" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.328434571764287</v>
+        <v>0.328461357594765</v>
       </c>
     </row>
     <row r="297" ht="16.5" spans="1:16">
@@ -21573,27 +21582,27 @@
       </c>
       <c r="K297" s="1">
         <f ca="1" t="shared" ref="K297:O297" si="286">RAND()</f>
-        <v>0.629123141719259</v>
+        <v>0.30837050549043</v>
       </c>
       <c r="L297" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.233839691930322</v>
+        <v>0.233789000377643</v>
       </c>
       <c r="M297" s="1">
         <f ca="1" t="shared" si="286"/>
-        <v>0.543710785633423</v>
+        <v>0.0811677236468173</v>
       </c>
       <c r="N297" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.280547241275739</v>
+        <v>0.28042344969723</v>
       </c>
       <c r="O297" s="1">
         <f ca="1" t="shared" si="286"/>
-        <v>0.543614504873917</v>
+        <v>0.175905790968311</v>
       </c>
       <c r="P297" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.327254775405002</v>
+        <v>0.327072871363691</v>
       </c>
     </row>
     <row r="298" ht="16.5" spans="1:16">
@@ -21633,27 +21642,27 @@
       </c>
       <c r="K298" s="1">
         <f ca="1" t="shared" ref="K298:O298" si="287">RAND()</f>
-        <v>0.629451439584845</v>
+        <v>0.122881613006602</v>
       </c>
       <c r="L298" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.23304994118967</v>
+        <v>0.232970422311624</v>
       </c>
       <c r="M298" s="1">
         <f ca="1" t="shared" si="287"/>
-        <v>0.894178291816452</v>
+        <v>0.0543169869672746</v>
       </c>
       <c r="N298" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.279654951432038</v>
+        <v>0.279443595193826</v>
       </c>
       <c r="O298" s="1">
         <f ca="1" t="shared" si="287"/>
-        <v>0.602170841484808</v>
+        <v>0.0817364160296576</v>
       </c>
       <c r="P298" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.326214123759052</v>
+        <v>0.325921072245209</v>
       </c>
     </row>
     <row r="299" ht="16.5" spans="1:16">
@@ -21693,27 +21702,27 @@
       </c>
       <c r="K299" s="1">
         <f ca="1" t="shared" ref="K299:O299" si="288">RAND()</f>
-        <v>0.0588430135215321</v>
+        <v>0.1254691945432</v>
       </c>
       <c r="L299" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.232176485589526</v>
+        <v>0.232186874052434</v>
       </c>
       <c r="M299" s="1">
         <f ca="1" t="shared" si="288"/>
-        <v>0.872261229115832</v>
+        <v>0.796723322545497</v>
       </c>
       <c r="N299" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.278621214816492</v>
+        <v>0.278619825285696</v>
       </c>
       <c r="O299" s="1">
         <f ca="1" t="shared" si="288"/>
-        <v>0.402379183734636</v>
+        <v>0.658374495460761</v>
       </c>
       <c r="P299" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.324992679267891</v>
+        <v>0.325031204943995</v>
       </c>
     </row>
     <row r="300" ht="16.5" spans="1:16">
@@ -21753,27 +21762,27 @@
       </c>
       <c r="K300" s="1">
         <f ca="1" t="shared" ref="K300:O300" si="289">RAND()</f>
-        <v>0.436345526499104</v>
+        <v>0.465894444967333</v>
       </c>
       <c r="L300" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.231456326101161</v>
+        <v>0.231460902598601</v>
       </c>
       <c r="M300" s="1">
         <f ca="1" t="shared" si="289"/>
-        <v>0.0999716642187729</v>
+        <v>0.163307907146814</v>
       </c>
       <c r="N300" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.277625655734236</v>
+        <v>0.277640041665273</v>
       </c>
       <c r="O300" s="1">
         <f ca="1" t="shared" si="289"/>
-        <v>0.661328914545833</v>
+        <v>0.131615317690285</v>
       </c>
       <c r="P300" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.323881927636334</v>
+        <v>0.323814272225576</v>
       </c>
     </row>
     <row r="301" ht="16.5" spans="1:16">
@@ -21813,27 +21822,27 @@
       </c>
       <c r="K301" s="1">
         <f ca="1" t="shared" ref="K301:O301" si="290">RAND()</f>
-        <v>0.802917091459511</v>
+        <v>0.939317605438426</v>
       </c>
       <c r="L301" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.230738910321763</v>
+        <v>0.230759895016222</v>
       </c>
       <c r="M301" s="1">
         <f ca="1" t="shared" si="290"/>
-        <v>0.0248263120981038</v>
+        <v>0.0388863923563261</v>
       </c>
       <c r="N301" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.276742729754394</v>
+        <v>0.276765877538123</v>
       </c>
       <c r="O301" s="1">
         <f ca="1" t="shared" si="290"/>
-        <v>0.15571493934909</v>
+        <v>0.0229421042311757</v>
       </c>
       <c r="P301" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.322766685898909</v>
+        <v>0.32276940709262</v>
       </c>
     </row>
     <row r="302" spans="1:16">

--- a/table/resources/sample/PointsAwardRanking.xlsx
+++ b/table/resources/sample/PointsAwardRanking.xlsx
@@ -176,7 +176,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="76">
   <si>
     <t>序列ID</t>
   </si>
@@ -244,187 +244,133 @@
     <t>2</t>
   </si>
   <si>
-    <t>1990000_3640000</t>
+    <t>1990000_55000000</t>
   </si>
   <si>
     <t>jfdj_box_1.png</t>
   </si>
   <si>
-    <t>1990000_3309000</t>
+    <t>1990000_50000000</t>
   </si>
   <si>
     <t>jfdj_box_2.png</t>
   </si>
   <si>
-    <t>1990000_2978000</t>
+    <t>1990000_45000000</t>
   </si>
   <si>
     <t>jfdj_box_3.png</t>
   </si>
   <si>
-    <t>1990000_2647000</t>
+    <t>1990000_40000000</t>
   </si>
   <si>
-    <t>1990000_2316000</t>
+    <t>1990000_35000000</t>
   </si>
   <si>
-    <t>1990000_1985000</t>
+    <t>1990000_30000000</t>
   </si>
   <si>
-    <t>1990000_1654000</t>
+    <t>1990000_25000000</t>
   </si>
   <si>
-    <t>1990000_1324000</t>
+    <t>1990000_20000000</t>
   </si>
   <si>
-    <t>1990000_993000</t>
+    <t>1990000_15000000</t>
   </si>
   <si>
-    <t>1990000_662000</t>
+    <t>1990000_10000000</t>
   </si>
   <si>
     <t>11_15</t>
   </si>
   <si>
-    <t>1990000_331000</t>
+    <t>1990000_5000000</t>
   </si>
   <si>
     <t>16_20</t>
   </si>
   <si>
-    <t>1990000_199000</t>
+    <t>1990000_3000000</t>
   </si>
   <si>
     <t>21_25</t>
   </si>
   <si>
-    <t>1990000_132000</t>
+    <t>1990000_2000000</t>
   </si>
   <si>
     <t>26_30</t>
   </si>
   <si>
-    <t>1990000_66000</t>
+    <t>1990000_1000000</t>
   </si>
   <si>
     <t>31_40</t>
   </si>
   <si>
-    <t>1990000_33000</t>
+    <t>1990000_500000</t>
   </si>
   <si>
     <t>41_50</t>
   </si>
   <si>
-    <t>1990000_20000</t>
+    <t>1990000_300000</t>
   </si>
   <si>
     <t>51_100</t>
   </si>
   <si>
-    <t>1990000_13000</t>
+    <t>1990000_200000</t>
   </si>
   <si>
     <t>101_150</t>
   </si>
   <si>
-    <t>1990000_7000</t>
+    <t>1990000_100000</t>
   </si>
   <si>
     <t>151_200</t>
   </si>
   <si>
-    <t>1990000_3000</t>
+    <t>1990000_50000</t>
   </si>
   <si>
     <t>201_250</t>
   </si>
   <si>
-    <t>1990000_2000</t>
+    <t>1990000_30000</t>
   </si>
   <si>
     <t>251_300</t>
   </si>
   <si>
-    <t>1990000_1000</t>
+    <t>1990000_20000</t>
   </si>
   <si>
-    <t>1990000_4410000</t>
+    <t>1990000_200000000</t>
   </si>
   <si>
-    <t>1990000_4100000</t>
+    <t>1990000_150000000</t>
   </si>
   <si>
-    <t>1990000_3780000</t>
+    <t>1990000_100000000</t>
   </si>
   <si>
-    <t>1990000_3150000</t>
+    <t>1990000_80000000</t>
   </si>
   <si>
-    <t>1990000_2610000</t>
+    <t>1990000_60000000</t>
   </si>
   <si>
-    <t>1990000_2210000</t>
+    <t>1990000_8000000</t>
   </si>
   <si>
-    <t>1990000_1890000</t>
+    <t>1990000_500000000</t>
   </si>
   <si>
-    <t>1990000_1580000</t>
-  </si>
-  <si>
-    <t>1990000_950000</t>
-  </si>
-  <si>
-    <t>1990000_630000</t>
-  </si>
-  <si>
-    <t>1990000_500000</t>
-  </si>
-  <si>
-    <t>1990000_250000</t>
-  </si>
-  <si>
-    <t>1990000_190000</t>
-  </si>
-  <si>
-    <t>1990000_90000</t>
-  </si>
-  <si>
-    <t>1990000_60000</t>
-  </si>
-  <si>
-    <t>1990000_40000</t>
-  </si>
-  <si>
-    <t>1990000_4600000</t>
-  </si>
-  <si>
-    <t>1990000_4300000</t>
-  </si>
-  <si>
-    <t>1990000_3900000</t>
-  </si>
-  <si>
-    <t>1990000_3400000</t>
-  </si>
-  <si>
-    <t>1990000_2800000</t>
-  </si>
-  <si>
-    <t>1990000_2400000</t>
-  </si>
-  <si>
-    <t>1990000_2000000</t>
-  </si>
-  <si>
-    <t>1990000_1800000</t>
-  </si>
-  <si>
-    <t>1990000_1100000</t>
-  </si>
-  <si>
-    <t>1990000_700000</t>
+    <t>1990000_300000000</t>
   </si>
   <si>
     <t>2036/08/01 00:00:00</t>
@@ -2282,7 +2228,7 @@
         <v>21</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
@@ -2304,7 +2250,7 @@
         <v>21</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
@@ -2326,7 +2272,7 @@
         <v>21</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
@@ -2348,7 +2294,7 @@
         <v>21</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
@@ -2370,7 +2316,7 @@
         <v>21</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
@@ -2393,7 +2339,7 @@
         <v>21</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
@@ -2416,7 +2362,7 @@
         <v>21</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
@@ -2439,7 +2385,7 @@
         <v>21</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
@@ -2460,7 +2406,7 @@
         <v>21</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="F39" s="2"/>
       <c r="G39" s="2"/>
@@ -2481,7 +2427,7 @@
         <v>21</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
@@ -2502,7 +2448,7 @@
         <v>21</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
@@ -2523,7 +2469,7 @@
         <v>21</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="F42" s="2"/>
       <c r="G42" s="2" t="s">
@@ -2546,7 +2492,7 @@
         <v>21</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="F43" s="2"/>
       <c r="G43" s="2" t="s">
@@ -2569,7 +2515,7 @@
         <v>21</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="F44" s="2"/>
       <c r="G44" s="2" t="s">
@@ -2592,7 +2538,7 @@
         <v>21</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
@@ -2613,7 +2559,7 @@
         <v>21</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
@@ -2634,7 +2580,7 @@
         <v>21</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>78</v>
+        <v>30</v>
       </c>
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
@@ -2655,7 +2601,7 @@
         <v>21</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>79</v>
+        <v>32</v>
       </c>
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
@@ -2676,7 +2622,7 @@
         <v>21</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
@@ -2698,7 +2644,7 @@
         <v>21</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
@@ -2720,7 +2666,7 @@
         <v>21</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>82</v>
+        <v>36</v>
       </c>
       <c r="F51" s="2"/>
       <c r="G51" s="2"/>
@@ -2749,7 +2695,7 @@
         <v>23</v>
       </c>
       <c r="H52" s="25" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="I52" s="20"/>
       <c r="J52" s="20"/>
@@ -2775,7 +2721,7 @@
         <v>25</v>
       </c>
       <c r="H53" s="25" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="I53" s="20"/>
       <c r="J53" s="20"/>
@@ -2801,7 +2747,7 @@
         <v>27</v>
       </c>
       <c r="H54" s="25" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="I54" s="20"/>
       <c r="J54" s="20"/>
@@ -2825,7 +2771,7 @@
       <c r="F55" s="23"/>
       <c r="G55" s="23"/>
       <c r="H55" s="25" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="I55" s="20"/>
       <c r="J55" s="20"/>
@@ -2849,7 +2795,7 @@
       <c r="F56" s="23"/>
       <c r="G56" s="23"/>
       <c r="H56" s="25" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="I56" s="20"/>
       <c r="J56" s="21"/>
@@ -2874,7 +2820,7 @@
       <c r="F57" s="23"/>
       <c r="G57" s="23"/>
       <c r="H57" s="25" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="I57" s="20"/>
       <c r="J57" s="21"/>
@@ -2899,7 +2845,7 @@
       <c r="F58" s="23"/>
       <c r="G58" s="23"/>
       <c r="H58" s="25" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="I58" s="20"/>
       <c r="J58" s="21"/>
@@ -2924,7 +2870,7 @@
       <c r="F59" s="23"/>
       <c r="G59" s="23"/>
       <c r="H59" s="25" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="I59" s="20"/>
       <c r="J59" s="21"/>
@@ -2949,7 +2895,7 @@
       <c r="F60" s="23"/>
       <c r="G60" s="23"/>
       <c r="H60" s="25" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="I60" s="20"/>
       <c r="L60" s="3"/>
@@ -2973,7 +2919,7 @@
       <c r="F61" s="23"/>
       <c r="G61" s="23"/>
       <c r="H61" s="25" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="I61" s="20"/>
       <c r="L61" s="3"/>
@@ -2997,7 +2943,7 @@
       <c r="F62" s="23"/>
       <c r="G62" s="23"/>
       <c r="H62" s="25" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="I62" s="20"/>
       <c r="J62" s="10"/>
@@ -3022,7 +2968,7 @@
       <c r="F63" s="23"/>
       <c r="G63" s="23"/>
       <c r="H63" s="25" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="I63" s="20"/>
       <c r="J63" s="21"/>
@@ -3047,7 +2993,7 @@
       <c r="F64" s="23"/>
       <c r="G64" s="23"/>
       <c r="H64" s="25" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="I64" s="20"/>
       <c r="J64" s="21"/>
@@ -3072,7 +3018,7 @@
       <c r="F65" s="23"/>
       <c r="G65" s="23"/>
       <c r="H65" s="25" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="I65" s="20"/>
       <c r="J65" s="21"/>
@@ -3097,7 +3043,7 @@
       <c r="F66" s="23"/>
       <c r="G66" s="23"/>
       <c r="H66" s="25" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="I66" s="20"/>
       <c r="J66" s="21"/>
@@ -3122,7 +3068,7 @@
       <c r="F67" s="23"/>
       <c r="G67" s="23"/>
       <c r="H67" s="25" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="I67" s="20"/>
       <c r="J67" s="21"/>
@@ -3147,7 +3093,7 @@
       <c r="F68" s="23"/>
       <c r="G68" s="23"/>
       <c r="H68" s="25" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="I68" s="20"/>
       <c r="J68" s="21"/>
@@ -3172,7 +3118,7 @@
       <c r="F69" s="23"/>
       <c r="G69" s="23"/>
       <c r="H69" s="25" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="I69" s="20"/>
       <c r="J69" s="21"/>
@@ -3197,7 +3143,7 @@
       <c r="F70" s="23"/>
       <c r="G70" s="23"/>
       <c r="H70" s="25" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="I70" s="20"/>
       <c r="J70" s="21"/>
@@ -3222,7 +3168,7 @@
       <c r="F71" s="23"/>
       <c r="G71" s="23"/>
       <c r="H71" s="25" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="I71" s="20"/>
       <c r="J71" s="21"/>
@@ -3247,7 +3193,7 @@
       <c r="F72" s="23"/>
       <c r="G72" s="23"/>
       <c r="H72" s="25" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="I72" s="20"/>
       <c r="J72" s="21"/>
@@ -3274,7 +3220,7 @@
         <v>23</v>
       </c>
       <c r="H73" s="25" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="I73" s="20"/>
       <c r="J73" s="21"/>
@@ -3301,7 +3247,7 @@
         <v>25</v>
       </c>
       <c r="H74" s="25" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="I74" s="20"/>
       <c r="J74" s="21"/>
@@ -3328,7 +3274,7 @@
         <v>27</v>
       </c>
       <c r="H75" s="25" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="I75" s="20"/>
       <c r="J75" s="21"/>
@@ -3353,7 +3299,7 @@
       <c r="F76" s="23"/>
       <c r="G76" s="23"/>
       <c r="H76" s="25" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="I76" s="20"/>
       <c r="J76" s="21"/>
@@ -3378,7 +3324,7 @@
       <c r="F77" s="23"/>
       <c r="G77" s="23"/>
       <c r="H77" s="25" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="I77" s="20"/>
       <c r="J77" s="21"/>
@@ -3398,12 +3344,12 @@
         <v>21</v>
       </c>
       <c r="E78" s="23" t="s">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="F78" s="23"/>
       <c r="G78" s="23"/>
       <c r="H78" s="25" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="I78" s="20"/>
       <c r="J78" s="21"/>
@@ -3423,12 +3369,12 @@
         <v>21</v>
       </c>
       <c r="E79" s="23" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F79" s="23"/>
       <c r="G79" s="23"/>
       <c r="H79" s="25" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="I79" s="20"/>
       <c r="J79" s="21"/>
@@ -3448,12 +3394,12 @@
         <v>21</v>
       </c>
       <c r="E80" s="23" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="F80" s="23"/>
       <c r="G80" s="23"/>
       <c r="H80" s="25" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="I80" s="20"/>
       <c r="J80" s="21"/>
@@ -3472,12 +3418,12 @@
         <v>21</v>
       </c>
       <c r="E81" s="23" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="F81" s="23"/>
       <c r="G81" s="23"/>
       <c r="H81" s="25" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="I81" s="20"/>
       <c r="J81" s="21"/>
@@ -3496,12 +3442,12 @@
         <v>21</v>
       </c>
       <c r="E82" s="23" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="F82" s="23"/>
       <c r="G82" s="23"/>
       <c r="H82" s="25" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="I82" s="20"/>
       <c r="J82" s="20"/>
@@ -3520,12 +3466,12 @@
         <v>21</v>
       </c>
       <c r="E83" s="23" t="s">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="F83" s="23"/>
       <c r="G83" s="23"/>
       <c r="H83" s="25" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="I83" s="20"/>
     </row>
@@ -3543,12 +3489,12 @@
         <v>21</v>
       </c>
       <c r="E84" s="23" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F84" s="23"/>
       <c r="G84" s="23"/>
       <c r="H84" s="25" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="I84" s="20"/>
     </row>
@@ -3566,12 +3512,12 @@
         <v>21</v>
       </c>
       <c r="E85" s="23" t="s">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="F85" s="23"/>
       <c r="G85" s="23"/>
       <c r="H85" s="25" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="I85" s="20"/>
     </row>
@@ -3589,12 +3535,12 @@
         <v>21</v>
       </c>
       <c r="E86" s="23" t="s">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="F86" s="23"/>
       <c r="G86" s="23"/>
       <c r="H86" s="25" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="I86" s="20"/>
     </row>
@@ -3612,12 +3558,12 @@
         <v>21</v>
       </c>
       <c r="E87" s="23" t="s">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="F87" s="23"/>
       <c r="G87" s="23"/>
       <c r="H87" s="25" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="I87" s="20"/>
     </row>
@@ -3635,12 +3581,12 @@
         <v>21</v>
       </c>
       <c r="E88" s="23" t="s">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="F88" s="23"/>
       <c r="G88" s="23"/>
       <c r="H88" s="25" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="I88" s="20"/>
     </row>
@@ -3658,14 +3604,14 @@
         <v>21</v>
       </c>
       <c r="E89" s="23" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="F89" s="23"/>
       <c r="G89" s="23" t="s">
         <v>23</v>
       </c>
       <c r="H89" s="25" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="I89" s="20"/>
     </row>
@@ -3683,14 +3629,14 @@
         <v>21</v>
       </c>
       <c r="E90" s="27" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="F90" s="23"/>
       <c r="G90" s="23" t="s">
         <v>25</v>
       </c>
       <c r="H90" s="25" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
     </row>
     <row r="91" spans="1:10">
@@ -3707,14 +3653,14 @@
         <v>21</v>
       </c>
       <c r="E91" s="27" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="F91" s="23"/>
       <c r="G91" s="23" t="s">
         <v>27</v>
       </c>
       <c r="H91" s="25" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
     </row>
     <row r="92" spans="1:10">
@@ -3731,12 +3677,12 @@
         <v>21</v>
       </c>
       <c r="E92" s="27" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="F92" s="23"/>
       <c r="G92" s="23"/>
       <c r="H92" s="25" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
     </row>
     <row r="93" spans="1:10">
@@ -3753,12 +3699,12 @@
         <v>21</v>
       </c>
       <c r="E93" s="27" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="F93" s="23"/>
       <c r="G93" s="23"/>
       <c r="H93" s="25" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
     </row>
     <row r="94" spans="1:10">
@@ -3775,12 +3721,12 @@
         <v>21</v>
       </c>
       <c r="E94" s="27" t="s">
-        <v>78</v>
+        <v>30</v>
       </c>
       <c r="F94" s="23"/>
       <c r="G94" s="23"/>
       <c r="H94" s="25" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
     </row>
     <row r="95" spans="1:10">
@@ -3797,12 +3743,12 @@
         <v>21</v>
       </c>
       <c r="E95" s="27" t="s">
-        <v>79</v>
+        <v>32</v>
       </c>
       <c r="F95" s="23"/>
       <c r="G95" s="23"/>
       <c r="H95" s="25" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
     </row>
     <row r="96" spans="1:10">
@@ -3819,12 +3765,12 @@
         <v>21</v>
       </c>
       <c r="E96" s="27" t="s">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="F96" s="23"/>
       <c r="G96" s="23"/>
       <c r="H96" s="25" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
     </row>
     <row r="97" spans="1:8">
@@ -3841,12 +3787,12 @@
         <v>21</v>
       </c>
       <c r="E97" s="27" t="s">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="F97" s="23"/>
       <c r="G97" s="23"/>
       <c r="H97" s="25" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
     </row>
     <row r="98" spans="1:8">
@@ -3863,12 +3809,12 @@
         <v>21</v>
       </c>
       <c r="E98" s="27" t="s">
-        <v>82</v>
+        <v>36</v>
       </c>
       <c r="F98" s="23"/>
       <c r="G98" s="23"/>
       <c r="H98" s="25" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -3906,34 +3852,34 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="R1" s="1">
         <v>46</v>
@@ -3976,30 +3922,30 @@
       </c>
       <c r="K2" s="1">
         <f ca="1" t="shared" ref="K2:O2" si="3">RAND()</f>
-        <v>0.206098305917123</v>
+        <v>0.749492411782194</v>
       </c>
       <c r="L2" s="1">
         <f ca="1" t="shared" ref="L2:L65" si="4">J2+($R$1*$R$7*K2/MAX(1,($A2*($A2-1)))+$R$1*$R$7/$A2)/100</f>
-        <v>127.044156621656</v>
+        <v>134.542995282594</v>
       </c>
       <c r="M2" s="1">
         <f ca="1" t="shared" si="3"/>
-        <v>0.318911205948596</v>
+        <v>0.297760407449499</v>
       </c>
       <c r="N2" s="1">
         <f ca="1" t="shared" ref="N2:N65" si="5">L2+($R$1*$R$7*M2/MAX(1,($A2*($A2-1)))+$R$1*$R$7/$A2)/100</f>
-        <v>145.245131263747</v>
+        <v>152.452088905397</v>
       </c>
       <c r="O2" s="1">
         <f ca="1" t="shared" si="3"/>
-        <v>0.402769665419057</v>
+        <v>0.669844616935961</v>
       </c>
       <c r="P2" s="1">
         <f ca="1" t="shared" ref="P2:P65" si="6">N2+($R$1*$R$7*O2/MAX(1,($A2*($A2-1)))+$R$1*$R$7/$A2)/100</f>
-        <v>164.60335264653</v>
+        <v>175.495944619114</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="R2" s="1">
         <v>1</v>
@@ -4042,30 +3988,30 @@
       </c>
       <c r="K3" s="1">
         <f ca="1" t="shared" ref="K3:O3" si="8">RAND()</f>
-        <v>0.803239439208689</v>
+        <v>0.989715039010322</v>
       </c>
       <c r="L3" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>40.04235213054</v>
+        <v>41.3290337691712</v>
       </c>
       <c r="M3" s="1">
         <f ca="1" t="shared" si="8"/>
-        <v>0.151919120287883</v>
+        <v>0.482545499701252</v>
       </c>
       <c r="N3" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>47.9905940605263</v>
+        <v>51.5585977171099</v>
       </c>
       <c r="O3" s="1">
         <f ca="1" t="shared" si="8"/>
-        <v>0.778787374679508</v>
+        <v>0.561556872451645</v>
       </c>
       <c r="P3" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>60.264226945815</v>
+        <v>62.3333401370262</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="R3" s="1">
         <v>10</v>
@@ -4108,30 +4054,30 @@
       </c>
       <c r="K4" s="1">
         <f ca="1" t="shared" ref="K4:O4" si="9">RAND()</f>
-        <v>0.612430410169176</v>
+        <v>0.739466536391512</v>
       </c>
       <c r="L4" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>33.6085899433891</v>
+        <v>33.9007730337005</v>
       </c>
       <c r="M4" s="1">
         <f ca="1" t="shared" si="9"/>
-        <v>0.78655635676391</v>
+        <v>0.0207537374132565</v>
       </c>
       <c r="N4" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>40.0176695639461</v>
+        <v>38.548506629751</v>
       </c>
       <c r="O4" s="1">
         <f ca="1" t="shared" si="9"/>
-        <v>0.715264869160387</v>
+        <v>0.652581848784105</v>
       </c>
       <c r="P4" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>46.262778763015</v>
+        <v>44.6494448819544</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="R4" s="1">
         <f>24*60/R3</f>
@@ -4175,30 +4121,30 @@
       </c>
       <c r="K5" s="1">
         <f ca="1" t="shared" ref="K5:O5" si="10">RAND()</f>
-        <v>0.33564312815046</v>
+        <v>0.494368309219273</v>
       </c>
       <c r="L5" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>17.635989597373</v>
+        <v>17.8185235556022</v>
       </c>
       <c r="M5" s="1">
         <f ca="1" t="shared" si="10"/>
-        <v>0.443959807461753</v>
+        <v>0.886081034048043</v>
       </c>
       <c r="N5" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>21.596543375954</v>
+        <v>22.2875167447574</v>
       </c>
       <c r="O5" s="1">
         <f ca="1" t="shared" si="10"/>
-        <v>0.0816383103551725</v>
+        <v>0.821836747048154</v>
       </c>
       <c r="P5" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>25.1404274328625</v>
+        <v>26.6826290038628</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="R5" s="1">
         <v>6000</v>
@@ -4241,30 +4187,30 @@
       </c>
       <c r="K6" s="1">
         <f ca="1" t="shared" ref="K6:O6" si="11">RAND()</f>
-        <v>0.0343441259209838</v>
+        <v>0.572905574664843</v>
       </c>
       <c r="L6" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>16.5836974468855</v>
+        <v>16.9553048465187</v>
       </c>
       <c r="M6" s="1">
         <f ca="1" t="shared" si="11"/>
-        <v>0.787113299015338</v>
+        <v>0.585003122390469</v>
       </c>
       <c r="N6" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>19.8868056232061</v>
+        <v>20.1189570009682</v>
       </c>
       <c r="O6" s="1">
         <f ca="1" t="shared" si="11"/>
-        <v>0.168236672544477</v>
+        <v>0.573605262731329</v>
       </c>
       <c r="P6" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>22.7628889272618</v>
+        <v>23.2747446322528</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="R6" s="1">
         <f>R5/R4</f>
@@ -4328,7 +4274,7 @@
         <v>16.1</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="R7" s="1">
         <v>30</v>
@@ -5682,27 +5628,27 @@
       </c>
       <c r="K31" s="1">
         <f ca="1" t="shared" ref="K31:O31" si="12">RAND()</f>
-        <v>0.915336876680116</v>
+        <v>0.164169566217422</v>
       </c>
       <c r="L31" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>2.37796741252665</v>
+        <v>2.36605234484345</v>
       </c>
       <c r="M31" s="1">
         <f ca="1" t="shared" si="12"/>
-        <v>0.101027055672027</v>
+        <v>0.418782000070081</v>
       </c>
       <c r="N31" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>2.8395699106511</v>
+        <v>2.83269509381008</v>
       </c>
       <c r="O31" s="1">
         <f ca="1" t="shared" si="12"/>
-        <v>0.213498662510728</v>
+        <v>0.969923399701768</v>
       </c>
       <c r="P31" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>3.30295644115989</v>
+        <v>3.30808008566742</v>
       </c>
     </row>
     <row r="32" ht="16.5" spans="1:16">
@@ -5970,27 +5916,27 @@
       </c>
       <c r="K36" s="1">
         <f ca="1" t="shared" ref="K36:O36" si="13">RAND()</f>
-        <v>0.704091192170805</v>
+        <v>0.853246884687391</v>
       </c>
       <c r="L36" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>2.02598021718652</v>
+        <v>2.02770992185604</v>
       </c>
       <c r="M36" s="1">
         <f ca="1" t="shared" si="13"/>
-        <v>0.363826889172524</v>
+        <v>0.705359785852965</v>
       </c>
       <c r="N36" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>2.42448510043911</v>
+        <v>2.43017543870039</v>
       </c>
       <c r="O36" s="1">
         <f ca="1" t="shared" si="13"/>
-        <v>0.244712248993438</v>
+        <v>0.167076720320322</v>
       </c>
       <c r="P36" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>2.82160865425097</v>
+        <v>2.8263986813394</v>
       </c>
     </row>
     <row r="37" ht="16.5" spans="1:16">
@@ -6030,27 +5976,27 @@
       </c>
       <c r="K37" s="1">
         <f ca="1" t="shared" ref="K37:O37" si="14">RAND()</f>
-        <v>0.744968393245758</v>
+        <v>0.0310273873484188</v>
       </c>
       <c r="L37" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.9686353681165</v>
+        <v>1.96081601424239</v>
       </c>
       <c r="M37" s="1">
         <f ca="1" t="shared" si="14"/>
-        <v>0.492233604493358</v>
+        <v>0.0636130631204708</v>
       </c>
       <c r="N37" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>2.35735983140381</v>
+        <v>2.34484606207657</v>
       </c>
       <c r="O37" s="1">
         <f ca="1" t="shared" si="14"/>
-        <v>0.923938471551586</v>
+        <v>0.971752076785295</v>
       </c>
       <c r="P37" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>2.75081249085414</v>
+        <v>2.73882239434612</v>
       </c>
     </row>
     <row r="38" ht="16.5" spans="1:16">
@@ -6090,27 +6036,27 @@
       </c>
       <c r="K38" s="1">
         <f ca="1" t="shared" ref="K38:O38" si="15">RAND()</f>
-        <v>0.951692045587845</v>
+        <v>0.506525706835785</v>
       </c>
       <c r="L38" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.91616617885068</v>
+        <v>1.91155409516091</v>
       </c>
       <c r="M38" s="1">
         <f ca="1" t="shared" si="15"/>
-        <v>0.979388109748552</v>
+        <v>0.828486571139765</v>
       </c>
       <c r="N38" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>2.2992859655733</v>
+        <v>2.29311048756461</v>
       </c>
       <c r="O38" s="1">
         <f ca="1" t="shared" si="15"/>
-        <v>0.965510208880439</v>
+        <v>0.375290673522345</v>
       </c>
       <c r="P38" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>2.68226197224188</v>
+        <v>2.66997160715515</v>
       </c>
     </row>
     <row r="39" ht="16.5" spans="1:16">
@@ -6150,27 +6096,27 @@
       </c>
       <c r="K39" s="1">
         <f ca="1" t="shared" ref="K39:O39" si="16">RAND()</f>
-        <v>0.541030503181903</v>
+        <v>0.51236342987866</v>
       </c>
       <c r="L39" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.8603600433456</v>
+        <v>1.86007867377832</v>
       </c>
       <c r="M39" s="1">
         <f ca="1" t="shared" si="16"/>
-        <v>0.398488246189035</v>
+        <v>0.480727056121112</v>
       </c>
       <c r="N39" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>2.22742913139496</v>
+        <v>2.22795494218122</v>
       </c>
       <c r="O39" s="1">
         <f ca="1" t="shared" si="16"/>
-        <v>0.60334597309493</v>
+        <v>0.0856365118939457</v>
       </c>
       <c r="P39" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>2.59650891406119</v>
+        <v>2.59195336598217</v>
       </c>
     </row>
     <row r="40" ht="16.5" spans="1:16">
@@ -6210,27 +6156,27 @@
       </c>
       <c r="K40" s="1">
         <f ca="1" t="shared" ref="K40:O40" si="17">RAND()</f>
-        <v>0.351771281297278</v>
+        <v>0.858341195905825</v>
       </c>
       <c r="L40" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.80975333581775</v>
+        <v>1.8144703836056</v>
       </c>
       <c r="M40" s="1">
         <f ca="1" t="shared" si="17"/>
-        <v>0.517308408887736</v>
+        <v>0.445788547711513</v>
       </c>
       <c r="N40" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>2.16841653152804</v>
+        <v>2.17246760490008</v>
       </c>
       <c r="O40" s="1">
         <f ca="1" t="shared" si="17"/>
-        <v>0.649115210994889</v>
+        <v>0.33446020602863</v>
       </c>
       <c r="P40" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>2.52830707802718</v>
+        <v>2.52942816552302</v>
       </c>
     </row>
     <row r="41" ht="16.5" spans="1:16">
@@ -6270,27 +6216,27 @@
       </c>
       <c r="K41" s="1">
         <f ca="1" t="shared" ref="K41:O41" si="18">RAND()</f>
-        <v>0.0985257669693878</v>
+        <v>0.231620057044313</v>
       </c>
       <c r="L41" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.76125618947704</v>
+        <v>1.76243356204309</v>
       </c>
       <c r="M41" s="1">
         <f ca="1" t="shared" si="18"/>
-        <v>0.481187373876705</v>
+        <v>0.543688671243225</v>
       </c>
       <c r="N41" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>2.11051284701518</v>
+        <v>2.11224311567332</v>
       </c>
       <c r="O41" s="1">
         <f ca="1" t="shared" si="18"/>
-        <v>0.788826962610973</v>
+        <v>0.0849730280406107</v>
       </c>
       <c r="P41" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>2.46249093168443</v>
+        <v>2.45799480015214</v>
       </c>
     </row>
     <row r="42" ht="16.5" spans="1:16">
@@ -6330,27 +6276,27 @@
       </c>
       <c r="K42" s="1">
         <f ca="1" t="shared" ref="K42:O42" si="19">RAND()</f>
-        <v>0.608352098738534</v>
+        <v>0.850677797901137</v>
       </c>
       <c r="L42" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.7217044261967</v>
+        <v>1.72374350829941</v>
       </c>
       <c r="M42" s="1">
         <f ca="1" t="shared" si="19"/>
-        <v>0.918781675482521</v>
+        <v>0.455910185996836</v>
       </c>
       <c r="N42" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>2.06602100370991</v>
+        <v>2.06416519157182</v>
       </c>
       <c r="O42" s="1">
         <f ca="1" t="shared" si="19"/>
-        <v>0.593520511057099</v>
+        <v>0.359782196854906</v>
       </c>
       <c r="P42" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>2.40760062752246</v>
+        <v>2.40377799298438</v>
       </c>
     </row>
     <row r="43" ht="16.5" spans="1:16">
@@ -6390,27 +6336,27 @@
       </c>
       <c r="K43" s="1">
         <f ca="1" t="shared" ref="K43:O43" si="20">RAND()</f>
-        <v>0.911889675970522</v>
+        <v>0.666843207010579</v>
       </c>
       <c r="L43" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.6822207186576</v>
+        <v>1.68025693162412</v>
       </c>
       <c r="M43" s="1">
         <f ca="1" t="shared" si="20"/>
-        <v>0.134025014360624</v>
+        <v>0.951480408787449</v>
       </c>
       <c r="N43" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>2.01186621528836</v>
+        <v>2.01645346451684</v>
       </c>
       <c r="O43" s="1">
         <f ca="1" t="shared" si="20"/>
-        <v>0.6481202355552</v>
+        <v>0.644671813816454</v>
       </c>
       <c r="P43" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>2.34563163877888</v>
+        <v>2.35019125257182</v>
       </c>
     </row>
     <row r="44" ht="16.5" spans="1:16">
@@ -6450,27 +6396,27 @@
       </c>
       <c r="K44" s="1">
         <f ca="1" t="shared" ref="K44:O44" si="21">RAND()</f>
-        <v>0.174742712374042</v>
+        <v>0.208361686857122</v>
       </c>
       <c r="L44" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.63655119016099</v>
+        <v>1.63680807933478</v>
       </c>
       <c r="M44" s="1">
         <f ca="1" t="shared" si="21"/>
-        <v>0.508080656048228</v>
+        <v>0.485040102999144</v>
       </c>
       <c r="N44" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>1.96136376660256</v>
+        <v>1.96144459839425</v>
       </c>
       <c r="O44" s="1">
         <f ca="1" t="shared" si="21"/>
-        <v>0.493314186255633</v>
+        <v>0.851398121965856</v>
       </c>
       <c r="P44" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>2.28606350955401</v>
+        <v>2.28888053088767</v>
       </c>
     </row>
     <row r="45" ht="16.5" spans="1:16">
@@ -6510,27 +6456,27 @@
       </c>
       <c r="K45" s="1">
         <f ca="1" t="shared" ref="K45:O45" si="22">RAND()</f>
-        <v>0.398193267946903</v>
+        <v>0.874184799069777</v>
       </c>
       <c r="L45" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.60026166337086</v>
+        <v>1.60373348320675</v>
       </c>
       <c r="M45" s="1">
         <f ca="1" t="shared" si="22"/>
-        <v>0.0433821561953887</v>
+        <v>0.961664105076351</v>
       </c>
       <c r="N45" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>1.91421445076806</v>
+        <v>1.92438409877232</v>
       </c>
       <c r="O45" s="1">
         <f ca="1" t="shared" si="22"/>
-        <v>0.308011036951478</v>
+        <v>0.0572704667577091</v>
       </c>
       <c r="P45" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>2.23009740653441</v>
+        <v>2.2384381856863</v>
       </c>
     </row>
     <row r="46" ht="16.5" spans="1:16">
@@ -6570,27 +6516,27 @@
       </c>
       <c r="K46" s="1">
         <f ca="1" t="shared" ref="K46:O46" si="23">RAND()</f>
-        <v>0.0165163615831188</v>
+        <v>0.500581547309588</v>
       </c>
       <c r="L46" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.56132723524739</v>
+        <v>1.56470102290549</v>
       </c>
       <c r="M46" s="1">
         <f ca="1" t="shared" si="23"/>
-        <v>0.0458547398593596</v>
+        <v>0.558582064005993</v>
       </c>
       <c r="N46" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>1.8683134955555</v>
+        <v>1.87526083729098</v>
       </c>
       <c r="O46" s="1">
         <f ca="1" t="shared" si="23"/>
-        <v>0.849556670814552</v>
+        <v>0.970459023823768</v>
       </c>
       <c r="P46" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>2.18090131477633</v>
+        <v>2.18869130927521</v>
       </c>
     </row>
     <row r="47" ht="16.5" spans="1:16">
@@ -6630,27 +6576,27 @@
       </c>
       <c r="K47" s="1">
         <f ca="1" t="shared" ref="K47:O47" si="24">RAND()</f>
-        <v>0.803547729891694</v>
+        <v>0.858821214278588</v>
       </c>
       <c r="L47" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.53202365153261</v>
+        <v>1.53239214142853</v>
       </c>
       <c r="M47" s="1">
         <f ca="1" t="shared" si="24"/>
-        <v>0.0986524650004146</v>
+        <v>0.462434651554449</v>
       </c>
       <c r="N47" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>1.83268133463262</v>
+        <v>1.83547503910556</v>
       </c>
       <c r="O47" s="1">
         <f ca="1" t="shared" si="24"/>
-        <v>0.74473216455245</v>
+        <v>0.337128511021451</v>
       </c>
       <c r="P47" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>2.13764621572963</v>
+        <v>2.13772256251237</v>
       </c>
     </row>
     <row r="48" ht="16.5" spans="1:16">
@@ -6690,27 +6636,27 @@
       </c>
       <c r="K48" s="1">
         <f ca="1" t="shared" ref="K48:O48" si="25">RAND()</f>
-        <v>0.409633223454231</v>
+        <v>0.891957307592499</v>
       </c>
       <c r="L48" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.4962317014263</v>
+        <v>1.49931036579314</v>
       </c>
       <c r="M48" s="1">
         <f ca="1" t="shared" si="25"/>
-        <v>0.167939778838008</v>
+        <v>0.647923982416104</v>
       </c>
       <c r="N48" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>1.79092067873804</v>
+        <v>1.79706307206388</v>
       </c>
       <c r="O48" s="1">
         <f ca="1" t="shared" si="25"/>
-        <v>0.364486362760386</v>
+        <v>0.947000442677701</v>
       </c>
       <c r="P48" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>2.0868642087131</v>
+        <v>2.09672477701715</v>
       </c>
     </row>
     <row r="49" ht="16.5" spans="1:16">
@@ -6750,27 +6696,27 @@
       </c>
       <c r="K49" s="1">
         <f ca="1" t="shared" ref="K49:O49" si="26">RAND()</f>
-        <v>0.764024981393227</v>
+        <v>0.419033442304805</v>
       </c>
       <c r="L49" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.46664164217341</v>
+        <v>1.46453132158856</v>
       </c>
       <c r="M49" s="1">
         <f ca="1" t="shared" si="26"/>
-        <v>0.0598300579193607</v>
+        <v>0.773234911690017</v>
       </c>
       <c r="N49" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>1.75450762391069</v>
+        <v>1.75676121599518</v>
       </c>
       <c r="O49" s="1">
         <f ca="1" t="shared" si="26"/>
-        <v>0.559085501219162</v>
+        <v>0.716438676879699</v>
       </c>
       <c r="P49" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>2.04542756181708</v>
+        <v>2.04864368662503</v>
       </c>
     </row>
     <row r="50" ht="16.5" spans="1:16">
@@ -6810,27 +6756,27 @@
       </c>
       <c r="K50" s="1">
         <f ca="1" t="shared" ref="K50:O50" si="27">RAND()</f>
-        <v>0.146586202562309</v>
+        <v>0.415799725840638</v>
       </c>
       <c r="L50" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.4324927251681</v>
+        <v>1.43407229430978</v>
       </c>
       <c r="M50" s="1">
         <f ca="1" t="shared" si="27"/>
-        <v>0.715504955166795</v>
+        <v>0.74804092106023</v>
       </c>
       <c r="N50" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>1.7183234940377</v>
+        <v>1.72009396297927</v>
       </c>
       <c r="O50" s="1">
         <f ca="1" t="shared" si="27"/>
-        <v>0.780340706327692</v>
+        <v>0.551700166587368</v>
       </c>
       <c r="P50" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>2.00453467675339</v>
+        <v>2.00496363232404</v>
       </c>
     </row>
     <row r="51" ht="16.5" spans="1:16">
@@ -6870,27 +6816,27 @@
       </c>
       <c r="K51" s="1">
         <f ca="1" t="shared" ref="K51:O51" si="28">RAND()</f>
-        <v>0.689219517528243</v>
+        <v>0.0452116048757587</v>
       </c>
       <c r="L51" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.40641274667016</v>
+        <v>1.40278527352951</v>
       </c>
       <c r="M51" s="1">
         <f ca="1" t="shared" si="28"/>
-        <v>0.904185689737895</v>
+        <v>0.795784769550266</v>
       </c>
       <c r="N51" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>1.68750571096338</v>
+        <v>1.68326765304779</v>
       </c>
       <c r="O51" s="1">
         <f ca="1" t="shared" si="28"/>
-        <v>0.945419729124187</v>
+        <v>0.864390831174343</v>
       </c>
       <c r="P51" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>1.96883093229477</v>
+        <v>1.9641364667091</v>
       </c>
     </row>
     <row r="52" ht="16.5" spans="1:16">
@@ -6930,27 +6876,27 @@
       </c>
       <c r="K52" s="1">
         <f ca="1" t="shared" ref="K52:O52" si="29">RAND()</f>
-        <v>0.453932249856447</v>
+        <v>0.770538189993797</v>
       </c>
       <c r="L52" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.37704480982275</v>
+        <v>1.37875820667526</v>
       </c>
       <c r="M52" s="1">
         <f ca="1" t="shared" si="29"/>
-        <v>0.425270748392524</v>
+        <v>0.536676453083507</v>
       </c>
       <c r="N52" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>1.64993451034347</v>
+        <v>1.65225080865665</v>
       </c>
       <c r="O52" s="1">
         <f ca="1" t="shared" si="29"/>
-        <v>0.503380255106067</v>
+        <v>0.465064927151584</v>
       </c>
       <c r="P52" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>1.9232469211358</v>
+        <v>1.92535586590947</v>
       </c>
     </row>
     <row r="53" ht="16.5" spans="1:16">
@@ -6990,27 +6936,27 @@
       </c>
       <c r="K53" s="1">
         <f ca="1" t="shared" ref="K53:O53" si="30">RAND()</f>
-        <v>0.860716240825026</v>
+        <v>0.317942469049118</v>
       </c>
       <c r="L53" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.35221639672827</v>
+        <v>1.34939200832311</v>
       </c>
       <c r="M53" s="1">
         <f ca="1" t="shared" si="30"/>
-        <v>0.964133950229772</v>
+        <v>0.493125523316523</v>
       </c>
       <c r="N53" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>1.62261799873173</v>
+        <v>1.61734266149873</v>
       </c>
       <c r="O53" s="1">
         <f ca="1" t="shared" si="30"/>
-        <v>0.832987060243394</v>
+        <v>0.731773047425618</v>
       </c>
       <c r="P53" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>1.89233716216739</v>
+        <v>1.88653514568217</v>
       </c>
     </row>
     <row r="54" ht="16.5" spans="1:16">
@@ -7164,27 +7110,27 @@
       </c>
       <c r="K56" s="1">
         <f ca="1" t="shared" ref="K56:O56" si="31">RAND()</f>
-        <v>0.505998370777141</v>
+        <v>0.14845167502942</v>
       </c>
       <c r="L56" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.2754824166723</v>
+        <v>1.27382108859104</v>
       </c>
       <c r="M56" s="1">
         <f ca="1" t="shared" si="31"/>
-        <v>0.887917316122551</v>
+        <v>0.839610294868257</v>
       </c>
       <c r="N56" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>1.53051718399973</v>
+        <v>1.52863139905205</v>
       </c>
       <c r="O56" s="1">
         <f ca="1" t="shared" si="31"/>
-        <v>0.413647910706335</v>
+        <v>0.450534015247501</v>
       </c>
       <c r="P56" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>1.78334827530201</v>
+        <v>1.78163388033502</v>
       </c>
     </row>
     <row r="57" ht="16.5" spans="1:16">
@@ -7224,27 +7170,27 @@
       </c>
       <c r="K57" s="1">
         <f ca="1" t="shared" ref="K57:O57" si="32">RAND()</f>
-        <v>0.293269814130132</v>
+        <v>0.955391274333896</v>
       </c>
       <c r="L57" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.25137893618019</v>
+        <v>1.2543455842811</v>
       </c>
       <c r="M57" s="1">
         <f ca="1" t="shared" si="32"/>
-        <v>0.880404166919311</v>
+        <v>0.668380533410959</v>
       </c>
       <c r="N57" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>1.50175217562937</v>
+        <v>1.50376884771002</v>
       </c>
       <c r="O57" s="1">
         <f ca="1" t="shared" si="32"/>
-        <v>0.0331912940938</v>
+        <v>0.0127156771164136</v>
       </c>
       <c r="P57" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>1.74832946129772</v>
+        <v>1.75025439197762</v>
       </c>
     </row>
     <row r="58" ht="16.5" spans="1:16">
@@ -7284,27 +7230,27 @@
       </c>
       <c r="K58" s="1">
         <f ca="1" t="shared" ref="K58:O58" si="33">RAND()</f>
-        <v>0.589209809388357</v>
+        <v>0.216100868680226</v>
       </c>
       <c r="L58" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.23036688451427</v>
+        <v>1.22875381954505</v>
       </c>
       <c r="M58" s="1">
         <f ca="1" t="shared" si="33"/>
-        <v>0.36898719975435</v>
+        <v>0.623014111097113</v>
       </c>
       <c r="N58" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>1.47406739308464</v>
+        <v>1.4735525647622</v>
       </c>
       <c r="O58" s="1">
         <f ca="1" t="shared" si="33"/>
-        <v>0.606893921209571</v>
+        <v>0.74591768483321</v>
       </c>
       <c r="P58" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>1.71879644575152</v>
+        <v>1.71888266001617</v>
       </c>
     </row>
     <row r="59" ht="16.5" spans="1:16">
@@ -7344,27 +7290,27 @@
       </c>
       <c r="K59" s="1">
         <f ca="1" t="shared" ref="K59:O59" si="34">RAND()</f>
-        <v>0.0402358999351617</v>
+        <v>0.768758610514749</v>
       </c>
       <c r="L59" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.20652004096162</v>
+        <v>1.20956106135061</v>
       </c>
       <c r="M59" s="1">
         <f ca="1" t="shared" si="34"/>
-        <v>0.640098458570236</v>
+        <v>0.911459155506041</v>
       </c>
       <c r="N59" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>1.44712299278505</v>
+        <v>1.45129673477649</v>
       </c>
       <c r="O59" s="1">
         <f ca="1" t="shared" si="34"/>
-        <v>0.883164268629318</v>
+        <v>0.31310106461413</v>
       </c>
       <c r="P59" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>1.68874055688278</v>
+        <v>1.69053472470138</v>
       </c>
     </row>
     <row r="60" ht="16.5" spans="1:16">
@@ -7404,27 +7350,27 @@
       </c>
       <c r="K60" s="1">
         <f ca="1" t="shared" ref="K60:O60" si="35">RAND()</f>
-        <v>0.803113652213788</v>
+        <v>0.00571083545278306</v>
       </c>
       <c r="L60" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.18886118305101</v>
+        <v>1.1856454732698</v>
       </c>
       <c r="M60" s="1">
         <f ca="1" t="shared" si="35"/>
-        <v>0.340847626141369</v>
+        <v>0.399669875763031</v>
       </c>
       <c r="N60" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>1.42413403437794</v>
+        <v>1.42115553881203</v>
       </c>
       <c r="O60" s="1">
         <f ca="1" t="shared" si="35"/>
-        <v>0.877728657823998</v>
+        <v>0.569780387285557</v>
       </c>
       <c r="P60" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>1.66157198162457</v>
+        <v>1.657351614015</v>
       </c>
     </row>
     <row r="61" ht="16.5" spans="1:16">
@@ -7464,27 +7410,27 @@
       </c>
       <c r="K61" s="1">
         <f ca="1" t="shared" ref="K61:O61" si="36">RAND()</f>
-        <v>0.474483587633084</v>
+        <v>0.110295591311315</v>
       </c>
       <c r="L61" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.16744290212128</v>
+        <v>1.16602318620342</v>
       </c>
       <c r="M61" s="1">
         <f ca="1" t="shared" si="36"/>
-        <v>0.232863233973853</v>
+        <v>0.302687118340386</v>
       </c>
       <c r="N61" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>1.39835067405033</v>
+        <v>1.39720315293593</v>
       </c>
       <c r="O61" s="1">
         <f ca="1" t="shared" si="36"/>
-        <v>0.868063023123045</v>
+        <v>0.560454976601167</v>
       </c>
       <c r="P61" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>1.63173464854725</v>
+        <v>1.62938797742099</v>
       </c>
     </row>
     <row r="62" ht="16.5" spans="1:16">
@@ -7524,27 +7470,27 @@
       </c>
       <c r="K62" s="1">
         <f ca="1" t="shared" ref="K62:O62" si="37">RAND()</f>
-        <v>0.293622027313524</v>
+        <v>0.84834771661436</v>
       </c>
       <c r="L62" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.14733660764397</v>
+        <v>1.14942819630855</v>
       </c>
       <c r="M62" s="1">
         <f ca="1" t="shared" si="37"/>
-        <v>0.394786237981992</v>
+        <v>0.650780655532786</v>
       </c>
       <c r="N62" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>1.37505465411505</v>
+        <v>1.37811146763269</v>
       </c>
       <c r="O62" s="1">
         <f ca="1" t="shared" si="37"/>
-        <v>0.96996261999011</v>
+        <v>0.197511267007876</v>
       </c>
       <c r="P62" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>1.60494139841993</v>
+        <v>1.60508569044272</v>
       </c>
     </row>
     <row r="63" ht="16.5" spans="1:16">
@@ -7584,27 +7530,27 @@
       </c>
       <c r="K63" s="1">
         <f ca="1" t="shared" ref="K63:O63" si="38">RAND()</f>
-        <v>0.32049113669176</v>
+        <v>0.0762616902753452</v>
       </c>
       <c r="L63" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.12866810621003</v>
+        <v>1.12777694641084</v>
       </c>
       <c r="M63" s="1">
         <f ca="1" t="shared" si="38"/>
-        <v>0.124439810916418</v>
+        <v>0.848912319377219</v>
       </c>
       <c r="N63" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>1.35170281519751</v>
+        <v>1.35345515635463</v>
       </c>
       <c r="O63" s="1">
         <f ca="1" t="shared" si="38"/>
-        <v>0.851498574986947</v>
+        <v>0.937523420506543</v>
       </c>
       <c r="P63" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>1.57739046203379</v>
+        <v>1.57945669606986</v>
       </c>
     </row>
     <row r="64" ht="16.5" spans="1:16">
@@ -7644,27 +7590,27 @@
       </c>
       <c r="K64" s="1">
         <f ca="1" t="shared" ref="K64:O64" si="39">RAND()</f>
-        <v>0.357734283381208</v>
+        <v>0.640305502221258</v>
       </c>
       <c r="L64" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.11063408425772</v>
+        <v>1.11163241575286</v>
       </c>
       <c r="M64" s="1">
         <f ca="1" t="shared" si="39"/>
-        <v>0.294031274553335</v>
+        <v>0.183487075756153</v>
       </c>
       <c r="N64" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>1.33072052347657</v>
+        <v>1.33132829943064</v>
       </c>
       <c r="O64" s="1">
         <f ca="1" t="shared" si="39"/>
-        <v>0.42369145208134</v>
+        <v>0.00366099762584926</v>
       </c>
       <c r="P64" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>1.55126505548853</v>
+        <v>1.55038885287848</v>
       </c>
     </row>
     <row r="65" ht="16.5" spans="1:16">
@@ -7704,27 +7650,27 @@
       </c>
       <c r="K65" s="1">
         <f ca="1" t="shared" ref="K65:O65" si="40">RAND()</f>
-        <v>0.786266390918642</v>
+        <v>0.284017835611467</v>
       </c>
       <c r="L65" s="1">
         <f ca="1" t="shared" si="4"/>
-        <v>1.09450656651654</v>
+        <v>1.0927875610445</v>
       </c>
       <c r="M65" s="1">
         <f ca="1" t="shared" si="40"/>
-        <v>0.152366378618641</v>
+        <v>0.35311795316335</v>
       </c>
       <c r="N65" s="1">
         <f ca="1" t="shared" si="5"/>
-        <v>1.31065305858621</v>
+        <v>1.30962114927706</v>
       </c>
       <c r="O65" s="1">
         <f ca="1" t="shared" si="40"/>
-        <v>0.702459518509709</v>
+        <v>0.725191825814004</v>
       </c>
       <c r="P65" s="1">
         <f ca="1" t="shared" si="6"/>
-        <v>1.52868230991445</v>
+        <v>1.52772820463327</v>
       </c>
     </row>
     <row r="66" ht="16.5" spans="1:16">
@@ -7764,27 +7710,27 @@
       </c>
       <c r="K66" s="1">
         <f ca="1" t="shared" ref="K66:O66" si="44">RAND()</f>
-        <v>0.839804998418849</v>
+        <v>0.753711933858184</v>
       </c>
       <c r="L66" s="1">
         <f ca="1" t="shared" ref="L66:L129" si="45">J66+($R$1*$R$7*K66/MAX(1,($A66*($A66-1)))+$R$1*$R$7/$A66)/100</f>
-        <v>1.07759358388899</v>
+        <v>1.07730798670366</v>
       </c>
       <c r="M66" s="1">
         <f ca="1" t="shared" si="44"/>
-        <v>0.557956060331373</v>
+        <v>0.680171989197801</v>
       </c>
       <c r="N66" s="1">
         <f ca="1" t="shared" ref="N66:N129" si="46">L66+($R$1*$R$7*M66/MAX(1,($A66*($A66-1)))+$R$1*$R$7/$A66)/100</f>
-        <v>1.29175218812758</v>
+        <v>1.29187201878321</v>
       </c>
       <c r="O66" s="1">
         <f ca="1" t="shared" si="44"/>
-        <v>0.14895778483136</v>
+        <v>0.36585841363554</v>
       </c>
       <c r="P66" s="1">
         <f ca="1" t="shared" ref="P66:P129" si="47">N66+($R$1*$R$7*O66/MAX(1,($A66*($A66-1)))+$R$1*$R$7/$A66)/100</f>
-        <v>1.50455401924073</v>
+        <v>1.50539337602076</v>
       </c>
     </row>
     <row r="67" ht="16.5" spans="1:16">
@@ -7824,27 +7770,27 @@
       </c>
       <c r="K67" s="1">
         <f ca="1" t="shared" ref="K67:O67" si="49">RAND()</f>
-        <v>0.541780312502568</v>
+        <v>0.243790816414253</v>
       </c>
       <c r="L67" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>1.06006446813812</v>
+        <v>1.05910590052833</v>
       </c>
       <c r="M67" s="1">
         <f ca="1" t="shared" si="49"/>
-        <v>0.396699589123628</v>
+        <v>0.418219050844119</v>
       </c>
       <c r="N67" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>1.27043147380943</v>
+        <v>1.26954212964293</v>
       </c>
       <c r="O67" s="1">
         <f ca="1" t="shared" si="49"/>
-        <v>0.363061343493959</v>
+        <v>0.952579154429266</v>
       </c>
       <c r="P67" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.48069027253675</v>
+        <v>1.48169727937046</v>
       </c>
     </row>
     <row r="68" ht="16.5" spans="1:16">
@@ -7884,27 +7830,27 @@
       </c>
       <c r="K68" s="1">
         <f ca="1" t="shared" ref="K68:O68" si="50">RAND()</f>
-        <v>0.911434416744683</v>
+        <v>0.365298891169326</v>
       </c>
       <c r="L68" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>1.04517815353937</v>
+        <v>1.04347379572549</v>
       </c>
       <c r="M68" s="1">
         <f ca="1" t="shared" si="50"/>
-        <v>0.709381911648488</v>
+        <v>0.891368618782482</v>
       </c>
       <c r="N68" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>1.25336211337219</v>
+        <v>1.25222569236484</v>
       </c>
       <c r="O68" s="1">
         <f ca="1" t="shared" si="50"/>
-        <v>0.882139918964819</v>
+        <v>0.229338245189812</v>
       </c>
       <c r="P68" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.4620852094558</v>
+        <v>1.45891155120329</v>
       </c>
     </row>
     <row r="69" ht="16.5" spans="1:16">
@@ -7944,27 +7890,27 @@
       </c>
       <c r="K69" s="1">
         <f ca="1" t="shared" ref="K69:O69" si="51">RAND()</f>
-        <v>0.0376599138853935</v>
+        <v>0.925727922837103</v>
       </c>
       <c r="L69" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>1.02693584433969</v>
+        <v>1.02962577816838</v>
       </c>
       <c r="M69" s="1">
         <f ca="1" t="shared" si="51"/>
-        <v>0.185900322532944</v>
+        <v>0.35739603776167</v>
       </c>
       <c r="N69" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>1.23044010782761</v>
+        <v>1.23364949751015</v>
       </c>
       <c r="O69" s="1">
         <f ca="1" t="shared" si="51"/>
-        <v>0.318541829813728</v>
+        <v>0.351551006631903</v>
       </c>
       <c r="P69" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.43434613883099</v>
+        <v>1.43765551241172</v>
       </c>
     </row>
     <row r="70" ht="16.5" spans="1:16">
@@ -8004,27 +7950,27 @@
       </c>
       <c r="K70" s="1">
         <f ca="1" t="shared" ref="K70:O70" si="52">RAND()</f>
-        <v>0.833298672642534</v>
+        <v>0.233602794936942</v>
       </c>
       <c r="L70" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>1.0142155843313</v>
+        <v>1.01245177292629</v>
       </c>
       <c r="M70" s="1">
         <f ca="1" t="shared" si="52"/>
-        <v>0.0540923818131593</v>
+        <v>0.90680273313522</v>
       </c>
       <c r="N70" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>1.21437467957193</v>
+        <v>1.21511883978845</v>
       </c>
       <c r="O70" s="1">
         <f ca="1" t="shared" si="52"/>
-        <v>0.796403437311043</v>
+        <v>0.0295502562551027</v>
       </c>
       <c r="P70" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.41671704262284</v>
+        <v>1.41520575230684</v>
       </c>
     </row>
     <row r="71" ht="16.5" spans="1:16">
@@ -8064,27 +8010,27 @@
       </c>
       <c r="K71" s="1">
         <f ca="1" t="shared" ref="K71:O71" si="53">RAND()</f>
-        <v>0.454782891494287</v>
+        <v>0.716425661103296</v>
       </c>
       <c r="L71" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.998442236832841</v>
+        <v>0.999189787603152</v>
       </c>
       <c r="M71" s="1">
         <f ca="1" t="shared" si="53"/>
-        <v>0.992500363772983</v>
+        <v>0.888469294254548</v>
       </c>
       <c r="N71" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>1.19842080930076</v>
+        <v>1.19887112844388</v>
       </c>
       <c r="O71" s="1">
         <f ca="1" t="shared" si="53"/>
-        <v>0.0206433022141357</v>
+        <v>0.393619039563932</v>
       </c>
       <c r="P71" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.39562264730709</v>
+        <v>1.39713861141406</v>
       </c>
     </row>
     <row r="72" ht="16.5" spans="1:16">
@@ -8124,27 +8070,27 @@
       </c>
       <c r="K72" s="1">
         <f ca="1" t="shared" ref="K72:O72" si="54">RAND()</f>
-        <v>0.684279089279556</v>
+        <v>0.38530115476987</v>
       </c>
       <c r="L72" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.98483763610303</v>
+        <v>0.984007476043426</v>
       </c>
       <c r="M72" s="1">
         <f ca="1" t="shared" si="54"/>
-        <v>0.49285744821491</v>
+        <v>0.568784280818166</v>
       </c>
       <c r="N72" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>1.18057233082846</v>
+        <v>1.17995299376481</v>
       </c>
       <c r="O72" s="1">
         <f ca="1" t="shared" si="54"/>
-        <v>0.903795997732738</v>
+        <v>0.697861646065709</v>
       </c>
       <c r="P72" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.37744806217025</v>
+        <v>1.37625691543799</v>
       </c>
     </row>
     <row r="73" ht="16.5" spans="1:16">
@@ -8184,27 +8130,27 @@
       </c>
       <c r="K73" s="1">
         <f ca="1" t="shared" ref="K73:O73" si="55">RAND()</f>
-        <v>0.0161383054757671</v>
+        <v>0.187248087895666</v>
       </c>
       <c r="L73" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.969175021247176</v>
+        <v>0.969636937326479</v>
       </c>
       <c r="M73" s="1">
         <f ca="1" t="shared" si="55"/>
-        <v>0.157697408383412</v>
+        <v>0.404538502822944</v>
       </c>
       <c r="N73" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>1.16126739688014</v>
+        <v>1.16239566802659</v>
       </c>
       <c r="O73" s="1">
         <f ca="1" t="shared" si="55"/>
-        <v>0.37708534389963</v>
+        <v>0.146307905399968</v>
       </c>
       <c r="P73" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.35395201693996</v>
+        <v>1.35445729734868</v>
       </c>
     </row>
     <row r="74" ht="16.5" spans="1:16">
@@ -8244,27 +8190,27 @@
       </c>
       <c r="K74" s="1">
         <f ca="1" t="shared" ref="K74:O74" si="56">RAND()</f>
-        <v>0.088839576062663</v>
+        <v>0.995521163591055</v>
       </c>
       <c r="L74" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.955941017151763</v>
+        <v>0.958321573831347</v>
       </c>
       <c r="M74" s="1">
         <f ca="1" t="shared" si="56"/>
-        <v>0.890386021534666</v>
+        <v>0.121578296116915</v>
       </c>
       <c r="N74" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>1.1473198845599</v>
+        <v>1.14768188214307</v>
       </c>
       <c r="O74" s="1">
         <f ca="1" t="shared" si="56"/>
-        <v>0.829601057279817</v>
+        <v>0.286539270895521</v>
       </c>
       <c r="P74" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.33853915674226</v>
+        <v>1.33747530716939</v>
       </c>
     </row>
     <row r="75" ht="16.5" spans="1:16">
@@ -8418,27 +8364,27 @@
       </c>
       <c r="K77" s="1">
         <f ca="1" t="shared" ref="K77:O77" si="57">RAND()</f>
-        <v>0.374969722632078</v>
+        <v>0.942885247565756</v>
       </c>
       <c r="L77" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.918486768802162</v>
+        <v>0.919861722178317</v>
       </c>
       <c r="M77" s="1">
         <f ca="1" t="shared" si="57"/>
-        <v>0.676424923134985</v>
+        <v>0.48716892335841</v>
       </c>
       <c r="N77" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>1.1017033765108</v>
+        <v>1.10262013115066</v>
       </c>
       <c r="O77" s="1">
         <f ca="1" t="shared" si="57"/>
-        <v>0.543404588667065</v>
+        <v>0.517007247325172</v>
       </c>
       <c r="P77" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.28459793498863</v>
+        <v>1.28545078027576</v>
       </c>
     </row>
     <row r="78" ht="16.5" spans="1:16">
@@ -8478,27 +8424,27 @@
       </c>
       <c r="K78" s="1">
         <f ca="1" t="shared" ref="K78:O78" si="58">RAND()</f>
-        <v>0.790652243249524</v>
+        <v>0.665787627293688</v>
       </c>
       <c r="L78" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.907401059630356</v>
+        <v>0.907106607870241</v>
       </c>
       <c r="M78" s="1">
         <f ca="1" t="shared" si="58"/>
-        <v>0.281598985982435</v>
+        <v>0.626645093821389</v>
       </c>
       <c r="N78" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>1.08728589661029</v>
+        <v>1.08780512159115</v>
       </c>
       <c r="O78" s="1">
         <f ca="1" t="shared" si="58"/>
-        <v>0.954829730244715</v>
+        <v>0.307193625001169</v>
       </c>
       <c r="P78" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.26875832488735</v>
+        <v>1.26775031503356</v>
       </c>
     </row>
     <row r="79" ht="16.5" spans="1:16">
@@ -8538,27 +8484,27 @@
       </c>
       <c r="K79" s="1">
         <f ca="1" t="shared" ref="K79:O79" si="59">RAND()</f>
-        <v>0.315758092566375</v>
+        <v>0.0676899678872744</v>
       </c>
       <c r="L79" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.894531711901002</v>
+        <v>0.89396172520094</v>
       </c>
       <c r="M79" s="1">
         <f ca="1" t="shared" si="59"/>
-        <v>0.424558297279346</v>
+        <v>0.729442900253128</v>
       </c>
       <c r="N79" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>1.07243029739925</v>
+        <v>1.07256084475197</v>
       </c>
       <c r="O79" s="1">
         <f ca="1" t="shared" si="59"/>
-        <v>0.427192351463482</v>
+        <v>0.0610553378320355</v>
       </c>
       <c r="P79" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.25033493516984</v>
+        <v>1.24962420866507</v>
       </c>
     </row>
     <row r="80" ht="16.5" spans="1:16">
@@ -8598,27 +8544,27 @@
       </c>
       <c r="K80" s="1">
         <f ca="1" t="shared" ref="K80:O80" si="60">RAND()</f>
-        <v>0.802179317337763</v>
+        <v>0.246617451835095</v>
       </c>
       <c r="L80" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.884172358743795</v>
+        <v>0.882928159823974</v>
       </c>
       <c r="M80" s="1">
         <f ca="1" t="shared" si="60"/>
-        <v>0.913984936065974</v>
+        <v>0.751075587656822</v>
       </c>
       <c r="N80" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>1.06090280212544</v>
+        <v>1.05929376240587</v>
       </c>
       <c r="O80" s="1">
         <f ca="1" t="shared" si="60"/>
-        <v>0.039232702724977</v>
+        <v>0.163890668211619</v>
       </c>
       <c r="P80" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.23567420934673</v>
+        <v>1.23434434520713</v>
       </c>
     </row>
     <row r="81" ht="16.5" spans="1:16">
@@ -8658,27 +8604,27 @@
       </c>
       <c r="K81" s="1">
         <f ca="1" t="shared" ref="K81:O81" si="61">RAND()</f>
-        <v>0.294965634927237</v>
+        <v>0.557050220715724</v>
       </c>
       <c r="L81" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.871878247747151</v>
+        <v>0.872450521051563</v>
       </c>
       <c r="M81" s="1">
         <f ca="1" t="shared" si="61"/>
-        <v>0.254091744215868</v>
+        <v>0.404498601162313</v>
       </c>
       <c r="N81" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>1.04493306832788</v>
+        <v>1.04583376166802</v>
       </c>
       <c r="O81" s="1">
         <f ca="1" t="shared" si="61"/>
-        <v>0.439248140713212</v>
+        <v>0.92598579405831</v>
       </c>
       <c r="P81" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.21839218610348</v>
+        <v>1.22035569267404</v>
       </c>
     </row>
     <row r="82" ht="16.5" spans="1:16">
@@ -8718,27 +8664,27 @@
       </c>
       <c r="K82" s="1">
         <f ca="1" t="shared" ref="K82:O82" si="62">RAND()</f>
-        <v>0.187326469575055</v>
+        <v>0.43282229281806</v>
       </c>
       <c r="L82" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.860769306370391</v>
+        <v>0.86129212154952</v>
       </c>
       <c r="M82" s="1">
         <f ca="1" t="shared" si="62"/>
-        <v>0.910033927263722</v>
+        <v>0.0684476270362586</v>
       </c>
       <c r="N82" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>1.03307771195623</v>
+        <v>1.0318082600145</v>
       </c>
       <c r="O82" s="1">
         <f ca="1" t="shared" si="62"/>
-        <v>0.812066726190274</v>
+        <v>0.63634037557006</v>
       </c>
       <c r="P82" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.20517748368793</v>
+        <v>1.20353379970322</v>
       </c>
     </row>
     <row r="83" ht="16.5" spans="1:16">
@@ -8778,27 +8724,27 @@
       </c>
       <c r="K83" s="1">
         <f ca="1" t="shared" ref="K83:O83" si="63">RAND()</f>
-        <v>0.88243455369104</v>
+        <v>0.110404282712243</v>
       </c>
       <c r="L83" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.851607587600261</v>
+        <v>0.850003550000215</v>
       </c>
       <c r="M83" s="1">
         <f ca="1" t="shared" si="63"/>
-        <v>0.938347197422208</v>
+        <v>0.5898179452447</v>
       </c>
       <c r="N83" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>1.02184986271686</v>
+        <v>1.01952169026585</v>
       </c>
       <c r="O83" s="1">
         <f ca="1" t="shared" si="63"/>
-        <v>0.527815755512266</v>
+        <v>0.557000774047557</v>
       </c>
       <c r="P83" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.19123918181142</v>
+        <v>1.18897164670696</v>
       </c>
     </row>
     <row r="84" ht="16.5" spans="1:16">
@@ -8838,27 +8784,27 @@
       </c>
       <c r="K84" s="1">
         <f ca="1" t="shared" ref="K84:O84" si="64">RAND()</f>
-        <v>0.645157318857686</v>
+        <v>0.496970400254789</v>
       </c>
       <c r="L84" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.840743927563949</v>
+        <v>0.840443460406041</v>
       </c>
       <c r="M84" s="1">
         <f ca="1" t="shared" si="64"/>
-        <v>0.237065440625187</v>
+        <v>0.226305355528829</v>
       </c>
       <c r="N84" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>1.00748966707036</v>
+        <v>1.00716738251981</v>
       </c>
       <c r="O84" s="1">
         <f ca="1" t="shared" si="64"/>
-        <v>0.297794734180048</v>
+        <v>0.242367286922282</v>
       </c>
       <c r="P84" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.17435854267008</v>
+        <v>1.17392387217005</v>
       </c>
     </row>
     <row r="85" ht="16.5" spans="1:16">
@@ -8898,27 +8844,27 @@
       </c>
       <c r="K85" s="1">
         <f ca="1" t="shared" ref="K85:O85" si="65">RAND()</f>
-        <v>0.0370046279291725</v>
+        <v>0.228663852157515</v>
       </c>
       <c r="L85" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.829419200210186</v>
+        <v>0.829798560120449</v>
       </c>
       <c r="M85" s="1">
         <f ca="1" t="shared" si="65"/>
-        <v>0.959949618231128</v>
+        <v>0.0874919039320829</v>
       </c>
       <c r="N85" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.99560498688999</v>
+        <v>0.994257451152328</v>
       </c>
       <c r="O85" s="1">
         <f ca="1" t="shared" si="65"/>
-        <v>0.922315129725974</v>
+        <v>0.617699913134683</v>
       </c>
       <c r="P85" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.16171628189719</v>
+        <v>1.15976580726266</v>
       </c>
     </row>
     <row r="86" ht="16.5" spans="1:16">
@@ -8958,27 +8904,27 @@
       </c>
       <c r="K86" s="1">
         <f ca="1" t="shared" ref="K86:O86" si="66">RAND()</f>
-        <v>0.456419154704697</v>
+        <v>0.681381705975858</v>
       </c>
       <c r="L86" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.820377952988085</v>
+        <v>0.820812754557768</v>
       </c>
       <c r="M86" s="1">
         <f ca="1" t="shared" si="66"/>
-        <v>0.851307321211443</v>
+        <v>0.799575055504191</v>
       </c>
       <c r="N86" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.984376278062695</v>
+        <v>0.98471109290034</v>
       </c>
       <c r="O86" s="1">
         <f ca="1" t="shared" si="66"/>
-        <v>0.217463954316514</v>
+        <v>0.292082513391474</v>
       </c>
       <c r="P86" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.1471495277223</v>
+        <v>1.14762856330437</v>
       </c>
     </row>
     <row r="87" ht="16.5" spans="1:16">
@@ -9132,27 +9078,27 @@
       </c>
       <c r="K89" s="1">
         <f ca="1" t="shared" ref="K89:O89" si="67">RAND()</f>
-        <v>0.596909151310536</v>
+        <v>0.821200866017316</v>
       </c>
       <c r="L89" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.79237687386208</v>
+        <v>0.792781161435612</v>
       </c>
       <c r="M89" s="1">
         <f ca="1" t="shared" si="67"/>
-        <v>0.601689280259883</v>
+        <v>0.824969202167852</v>
       </c>
       <c r="N89" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.950279605323364</v>
+        <v>0.951086356705977</v>
       </c>
       <c r="O89" s="1">
         <f ca="1" t="shared" si="67"/>
-        <v>0.679959841764056</v>
+        <v>0.720241050954987</v>
       </c>
       <c r="P89" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.10832342008516</v>
+        <v>1.10920277866303</v>
       </c>
     </row>
     <row r="90" ht="16.5" spans="1:16">
@@ -9192,27 +9138,27 @@
       </c>
       <c r="K90" s="1">
         <f ca="1" t="shared" ref="K90:O90" si="68">RAND()</f>
-        <v>0.157712383731999</v>
+        <v>0.955865739498059</v>
       </c>
       <c r="L90" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.782606796590334</v>
+        <v>0.784013144433742</v>
       </c>
       <c r="M90" s="1">
         <f ca="1" t="shared" si="68"/>
-        <v>0.378740460557913</v>
+        <v>0.255021065394773</v>
       </c>
       <c r="N90" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.938330317830848</v>
+        <v>0.939518671847232</v>
       </c>
       <c r="O90" s="1">
         <f ca="1" t="shared" si="68"/>
-        <v>0.775816770608026</v>
+        <v>0.732927698219571</v>
       </c>
       <c r="P90" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.09475348834086</v>
+        <v>1.09586627172407</v>
       </c>
     </row>
     <row r="91" ht="16.5" spans="1:16">
@@ -9252,27 +9198,27 @@
       </c>
       <c r="K91" s="1">
         <f ca="1" t="shared" ref="K91:O91" si="69">RAND()</f>
-        <v>0.959074384491831</v>
+        <v>0.584792257605967</v>
       </c>
       <c r="L91" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.775210390325342</v>
+        <v>0.774565559694752</v>
       </c>
       <c r="M91" s="1">
         <f ca="1" t="shared" si="69"/>
-        <v>0.929574152627153</v>
+        <v>0.755707147138504</v>
       </c>
       <c r="N91" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.930145237180056</v>
+        <v>0.929200860397688</v>
       </c>
       <c r="O91" s="1">
         <f ca="1" t="shared" si="69"/>
-        <v>0.641254946197238</v>
+        <v>0.70729989341874</v>
       </c>
       <c r="P91" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.08458335431583</v>
+        <v>1.08375276283579</v>
       </c>
     </row>
     <row r="92" ht="16.5" spans="1:16">
@@ -9312,27 +9258,27 @@
       </c>
       <c r="K92" s="1">
         <f ca="1" t="shared" ref="K92:O92" si="70">RAND()</f>
-        <v>0.499269511518253</v>
+        <v>0.677048035604413</v>
       </c>
       <c r="L92" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.765822944964463</v>
+        <v>0.766122498521531</v>
       </c>
       <c r="M92" s="1">
         <f ca="1" t="shared" si="70"/>
-        <v>0.789161778408258</v>
+        <v>0.678523280037445</v>
       </c>
       <c r="N92" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.91880101975592</v>
+        <v>0.918914149469579</v>
       </c>
       <c r="O92" s="1">
         <f ca="1" t="shared" si="70"/>
-        <v>0.909241265419956</v>
+        <v>0.463587484974013</v>
       </c>
       <c r="P92" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.07198142628373</v>
+        <v>1.0713436375395</v>
       </c>
     </row>
     <row r="93" ht="16.5" spans="1:16">
@@ -9372,27 +9318,27 @@
       </c>
       <c r="K93" s="1">
         <f ca="1" t="shared" ref="K93:O93" si="71">RAND()</f>
-        <v>0.65872273568949</v>
+        <v>0.997793648305385</v>
       </c>
       <c r="L93" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.757679213300587</v>
+        <v>0.758238121398306</v>
       </c>
       <c r="M93" s="1">
         <f ca="1" t="shared" si="71"/>
-        <v>0.566203245840586</v>
+        <v>0.360347980834415</v>
       </c>
       <c r="N93" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.908612515354171</v>
+        <v>0.908832101586495</v>
       </c>
       <c r="O93" s="1">
         <f ca="1" t="shared" si="71"/>
-        <v>0.912115639961176</v>
+        <v>0.73816669866877</v>
       </c>
       <c r="P93" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.06011600267279</v>
+        <v>1.060048859881</v>
       </c>
     </row>
     <row r="94" ht="16.5" spans="1:16">
@@ -9432,27 +9378,27 @@
       </c>
       <c r="K94" s="1">
         <f ca="1" t="shared" ref="K94:O94" si="72">RAND()</f>
-        <v>0.660379270489586</v>
+        <v>0.0906331509240668</v>
       </c>
       <c r="L94" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.749452224629822</v>
+        <v>0.748533279275684</v>
       </c>
       <c r="M94" s="1">
         <f ca="1" t="shared" si="72"/>
-        <v>0.933877624885091</v>
+        <v>0.303209774325662</v>
       </c>
       <c r="N94" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.899345575637701</v>
+        <v>0.897409424072983</v>
       </c>
       <c r="O94" s="1">
         <f ca="1" t="shared" si="72"/>
-        <v>0.602204095319864</v>
+        <v>0.316255275699098</v>
       </c>
       <c r="P94" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.04870396933983</v>
+        <v>1.04630661000153</v>
       </c>
     </row>
     <row r="95" ht="16.5" spans="1:16">
@@ -9492,27 +9438,27 @@
       </c>
       <c r="K95" s="1">
         <f ca="1" t="shared" ref="K95:O95" si="73">RAND()</f>
-        <v>0.179515715968981</v>
+        <v>0.667943291270698</v>
       </c>
       <c r="L95" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.740640278755476</v>
+        <v>0.741411303754236</v>
       </c>
       <c r="M95" s="1">
         <f ca="1" t="shared" si="73"/>
-        <v>0.144714424176943</v>
+        <v>0.847148236546069</v>
       </c>
       <c r="N95" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.887677233577444</v>
+        <v>0.889557110853794</v>
       </c>
       <c r="O95" s="1">
         <f ca="1" t="shared" si="73"/>
-        <v>0.743662951231508</v>
+        <v>0.623165954232671</v>
       </c>
       <c r="P95" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.03565968024033</v>
+        <v>1.03734934262781</v>
       </c>
     </row>
     <row r="96" ht="16.5" spans="1:16">
@@ -9552,27 +9498,27 @@
       </c>
       <c r="K96" s="1">
         <f ca="1" t="shared" ref="K96:O96" si="74">RAND()</f>
-        <v>0.281867208161493</v>
+        <v>0.622366792544445</v>
       </c>
       <c r="L96" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.732932784711381</v>
+        <v>0.733458976678289</v>
       </c>
       <c r="M96" s="1">
         <f ca="1" t="shared" si="74"/>
-        <v>0.507322886686909</v>
+        <v>0.570736346994501</v>
       </c>
       <c r="N96" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.878979935420931</v>
+        <v>0.879604123552703</v>
       </c>
       <c r="O96" s="1">
         <f ca="1" t="shared" si="74"/>
-        <v>0.2988528445258</v>
+        <v>0.79341006371262</v>
       </c>
       <c r="P96" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.02470492637888</v>
+        <v>1.02609337986617</v>
       </c>
     </row>
     <row r="97" ht="16.5" spans="1:16">
@@ -9612,27 +9558,27 @@
       </c>
       <c r="K97" s="1">
         <f ca="1" t="shared" ref="K97:O97" si="75">RAND()</f>
-        <v>0.336461635322046</v>
+        <v>0.626397574383574</v>
       </c>
       <c r="L97" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.725311751158711</v>
+        <v>0.725750470013869</v>
       </c>
       <c r="M97" s="1">
         <f ca="1" t="shared" si="75"/>
-        <v>0.742980805502537</v>
+        <v>0.776553569187321</v>
       </c>
       <c r="N97" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.870185998430195</v>
+        <v>0.870675518177771</v>
       </c>
       <c r="O97" s="1">
         <f ca="1" t="shared" si="75"/>
-        <v>0.597282748382504</v>
+        <v>0.880119165301199</v>
       </c>
       <c r="P97" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.0148397815363</v>
+        <v>1.01575727744106</v>
       </c>
     </row>
     <row r="98" ht="16.5" spans="1:16">
@@ -9672,27 +9618,27 @@
       </c>
       <c r="K98" s="1">
         <f ca="1" t="shared" ref="K98:O98" si="76">RAND()</f>
-        <v>0.240827065461946</v>
+        <v>0.942079764036331</v>
       </c>
       <c r="L98" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.717624937017115</v>
+        <v>0.718664164598765</v>
       </c>
       <c r="M98" s="1">
         <f ca="1" t="shared" si="76"/>
-        <v>0.682818600604236</v>
+        <v>0.558004515773646</v>
       </c>
       <c r="N98" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.860904887262856</v>
+        <v>0.86175914551776</v>
       </c>
       <c r="O98" s="1">
         <f ca="1" t="shared" si="76"/>
-        <v>0.343749373608804</v>
+        <v>0.0310386053074714</v>
       </c>
       <c r="P98" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>1.00368235089643</v>
+        <v>1.004073184688</v>
       </c>
     </row>
     <row r="99" ht="16.5" spans="1:16">
@@ -9732,27 +9678,27 @@
       </c>
       <c r="K99" s="1">
         <f ca="1" t="shared" ref="K99:O99" si="77">RAND()</f>
-        <v>0.701446757879204</v>
+        <v>0.764690330732363</v>
       </c>
       <c r="L99" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.710906792053307</v>
+        <v>0.71099860367811</v>
       </c>
       <c r="M99" s="1">
         <f ca="1" t="shared" si="77"/>
-        <v>0.239464658942824</v>
+        <v>0.581776233431329</v>
       </c>
       <c r="N99" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.852070752950994</v>
+        <v>0.852659503322687</v>
       </c>
       <c r="O99" s="1">
         <f ca="1" t="shared" si="77"/>
-        <v>0.386514234831646</v>
+        <v>0.834519143847487</v>
       </c>
       <c r="P99" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.993448187880583</v>
+        <v>0.99468731356728</v>
       </c>
     </row>
     <row r="100" ht="16.5" spans="1:16">
@@ -9792,27 +9738,27 @@
       </c>
       <c r="K100" s="1">
         <f ca="1" t="shared" ref="K100:O100" si="78">RAND()</f>
-        <v>0.545151645229442</v>
+        <v>0.642988641825476</v>
       </c>
       <c r="L100" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.703434662204099</v>
+        <v>0.703573824289548</v>
       </c>
       <c r="M100" s="1">
         <f ca="1" t="shared" si="78"/>
-        <v>0.992497081366859</v>
+        <v>0.297901336264148</v>
       </c>
       <c r="N100" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.84424031667976</v>
+        <v>0.843391494712187</v>
       </c>
       <c r="O100" s="1">
         <f ca="1" t="shared" si="78"/>
-        <v>0.490687396566149</v>
+        <v>0.828806952234387</v>
       </c>
       <c r="P100" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.984332203514702</v>
+        <v>0.983964318453769</v>
       </c>
     </row>
     <row r="101" ht="16.5" spans="1:16">
@@ -9852,27 +9798,27 @@
       </c>
       <c r="K101" s="1">
         <f ca="1" t="shared" ref="K101:O101" si="79">RAND()</f>
-        <v>0.806444163408101</v>
+        <v>0.577435465657748</v>
       </c>
       <c r="L101" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.696699891864145</v>
+        <v>0.696380667618796</v>
       </c>
       <c r="M101" s="1">
         <f ca="1" t="shared" si="79"/>
-        <v>0.989985072690047</v>
+        <v>0.528240943170544</v>
       </c>
       <c r="N101" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.836079871056379</v>
+        <v>0.835117003478973</v>
       </c>
       <c r="O101" s="1">
         <f ca="1" t="shared" si="79"/>
-        <v>0.93541123461885</v>
+        <v>0.354809444076097</v>
       </c>
       <c r="P101" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.975383777625848</v>
+        <v>0.973611586340412</v>
       </c>
     </row>
     <row r="102" ht="16.5" spans="1:16">
@@ -10026,27 +9972,27 @@
       </c>
       <c r="K104" s="1">
         <f ca="1" t="shared" ref="K104:O104" si="80">RAND()</f>
-        <v>0.222622454220841</v>
+        <v>0.381375058861429</v>
       </c>
       <c r="L104" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.675449475525247</v>
+        <v>0.675658002647276</v>
       </c>
       <c r="M104" s="1">
         <f ca="1" t="shared" si="80"/>
-        <v>0.260546675817102</v>
+        <v>0.418287168415509</v>
       </c>
       <c r="N104" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.80977229525933</v>
+        <v>0.810188020058673</v>
       </c>
       <c r="O104" s="1">
         <f ca="1" t="shared" si="80"/>
-        <v>0.238409895701395</v>
+        <v>0.361785873936691</v>
       </c>
       <c r="P104" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.944066037555226</v>
+        <v>0.944643821035289</v>
       </c>
     </row>
     <row r="105" ht="16.5" spans="1:16">
@@ -10086,27 +10032,27 @@
       </c>
       <c r="K105" s="1">
         <f ca="1" t="shared" ref="K105:O105" si="81">RAND()</f>
-        <v>0.708851370306729</v>
+        <v>0.268514200184489</v>
       </c>
       <c r="L105" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.669527833169364</v>
+        <v>0.668960557875517</v>
       </c>
       <c r="M105" s="1">
         <f ca="1" t="shared" si="81"/>
-        <v>0.377098659077386</v>
+        <v>0.360472216256329</v>
       </c>
       <c r="N105" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.802705947573329</v>
+        <v>0.80211725285165</v>
       </c>
       <c r="O105" s="1">
         <f ca="1" t="shared" si="81"/>
-        <v>0.534421868752661</v>
+        <v>0.233651659211759</v>
       </c>
       <c r="P105" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.936086737508802</v>
+        <v>0.935110568095967</v>
       </c>
     </row>
     <row r="106" ht="16.5" spans="1:16">
@@ -10146,27 +10092,27 @@
       </c>
       <c r="K106" s="1">
         <f ca="1" t="shared" ref="K106:O106" si="82">RAND()</f>
-        <v>0.0520965994850608</v>
+        <v>0.724167202432447</v>
       </c>
       <c r="L106" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.662263638559789</v>
+        <v>0.663112958552525</v>
       </c>
       <c r="M106" s="1">
         <f ca="1" t="shared" si="82"/>
-        <v>0.18651087192035</v>
+        <v>0.698395603564174</v>
       </c>
       <c r="N106" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.793927910540787</v>
+        <v>0.795424117831754</v>
       </c>
       <c r="O106" s="1">
         <f ca="1" t="shared" si="82"/>
-        <v>0.160259288353946</v>
+        <v>0.499069415318552</v>
       </c>
       <c r="P106" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.925559007443652</v>
+        <v>0.927483381378585</v>
       </c>
     </row>
     <row r="107" ht="16.5" spans="1:16">
@@ -10206,27 +10152,27 @@
       </c>
       <c r="K107" s="1">
         <f ca="1" t="shared" ref="K107:O107" si="83">RAND()</f>
-        <v>0.27517178561624</v>
+        <v>0.733040182360555</v>
       </c>
       <c r="L107" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.656244148305616</v>
+        <v>0.656811855751714</v>
       </c>
       <c r="M107" s="1">
         <f ca="1" t="shared" si="83"/>
-        <v>0.386865866309492</v>
+        <v>0.648577266284286</v>
       </c>
       <c r="N107" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.786912499514517</v>
+        <v>0.787804700879722</v>
       </c>
       <c r="O107" s="1">
         <f ca="1" t="shared" si="83"/>
-        <v>0.74535130308657</v>
+        <v>0.350743315486385</v>
       </c>
       <c r="P107" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.918025334014301</v>
+        <v>0.918428264020217</v>
       </c>
     </row>
     <row r="108" ht="16.5" spans="1:16">
@@ -10266,27 +10212,27 @@
       </c>
       <c r="K108" s="1">
         <f ca="1" t="shared" ref="K108:O108" si="84">RAND()</f>
-        <v>0.644790908071166</v>
+        <v>0.826823118018537</v>
       </c>
       <c r="L108" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.650511207417685</v>
+        <v>0.650732689034443</v>
       </c>
       <c r="M108" s="1">
         <f ca="1" t="shared" si="84"/>
-        <v>0.362479768845281</v>
+        <v>0.564375452367166</v>
       </c>
       <c r="N108" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.779924205196742</v>
+        <v>0.780391336648856</v>
       </c>
       <c r="O108" s="1">
         <f ca="1" t="shared" si="84"/>
-        <v>0.210225672461489</v>
+        <v>0.151815614925456</v>
       </c>
       <c r="P108" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.909151952884977</v>
+        <v>0.909548015848818</v>
       </c>
     </row>
     <row r="109" ht="16.5" spans="1:16">
@@ -10326,27 +10272,27 @@
       </c>
       <c r="K109" s="1">
         <f ca="1" t="shared" ref="K109:O109" si="85">RAND()</f>
-        <v>0.883664061349077</v>
+        <v>0.910092552219015</v>
       </c>
       <c r="L109" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.64472088646994</v>
+        <v>0.644752446973055</v>
       </c>
       <c r="M109" s="1">
         <f ca="1" t="shared" si="85"/>
-        <v>0.051048299824495</v>
+        <v>0.388490791501449</v>
       </c>
       <c r="N109" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.772559625353427</v>
+        <v>0.772994154564153</v>
       </c>
       <c r="O109" s="1">
         <f ca="1" t="shared" si="85"/>
-        <v>0.213190914279058</v>
+        <v>0.222148603863664</v>
       </c>
       <c r="P109" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.900591992488859</v>
+        <v>0.901037218836679</v>
       </c>
     </row>
     <row r="110" ht="16.5" spans="1:16">
@@ -10386,27 +10332,27 @@
       </c>
       <c r="K110" s="1">
         <f ca="1" t="shared" ref="K110:O110" si="86">RAND()</f>
-        <v>0.937012875639719</v>
+        <v>0.3008098480007</v>
       </c>
       <c r="L110" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.638815050771647</v>
+        <v>0.638069247018553</v>
       </c>
       <c r="M110" s="1">
         <f ca="1" t="shared" si="86"/>
-        <v>0.98936869529829</v>
+        <v>0.131032487905381</v>
       </c>
       <c r="N110" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.766580365755941</v>
+        <v>0.764828357478381</v>
       </c>
       <c r="O110" s="1">
         <f ca="1" t="shared" si="86"/>
-        <v>0.798414208893518</v>
+        <v>0.940830530014164</v>
       </c>
       <c r="P110" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.894121829915195</v>
+        <v>0.892536772472791</v>
       </c>
     </row>
     <row r="111" ht="16.5" spans="1:16">
@@ -10446,27 +10392,27 @@
       </c>
       <c r="K111" s="1">
         <f ca="1" t="shared" ref="K111:O111" si="87">RAND()</f>
-        <v>0.400381158610658</v>
+        <v>0.325191775512108</v>
       </c>
       <c r="L111" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.632337386154198</v>
+        <v>0.632250846247045</v>
       </c>
       <c r="M111" s="1">
         <f ca="1" t="shared" si="87"/>
-        <v>0.795496771989483</v>
+        <v>0.6054051059612</v>
       </c>
       <c r="N111" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.758707515883426</v>
+        <v>0.758402188237225</v>
       </c>
       <c r="O111" s="1">
         <f ca="1" t="shared" si="87"/>
-        <v>0.87983461893799</v>
+        <v>0.392608744640776</v>
       </c>
       <c r="P111" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.885174715027826</v>
+        <v>0.884308610311958</v>
       </c>
     </row>
     <row r="112" ht="16.5" spans="1:16">
@@ -10506,27 +10452,27 @@
       </c>
       <c r="K112" s="1">
         <f ca="1" t="shared" ref="K112:O112" si="88">RAND()</f>
-        <v>0.983897126997855</v>
+        <v>0.620321530025159</v>
       </c>
       <c r="L112" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.627254527465403</v>
+        <v>0.626843606643272</v>
       </c>
       <c r="M112" s="1">
         <f ca="1" t="shared" si="88"/>
-        <v>0.232257080170303</v>
+        <v>0.469366106155461</v>
       </c>
       <c r="N112" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.75184135364938</v>
+        <v>0.751698418458583</v>
       </c>
       <c r="O112" s="1">
         <f ca="1" t="shared" si="88"/>
-        <v>0.247372011190599</v>
+        <v>0.0492616283882887</v>
       </c>
       <c r="P112" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.876445263047777</v>
+        <v>0.876078419316221</v>
       </c>
     </row>
     <row r="113" ht="16.5" spans="1:16">
@@ -10566,27 +10512,27 @@
       </c>
       <c r="K113" s="1">
         <f ca="1" t="shared" ref="K113:O113" si="89">RAND()</f>
-        <v>0.470786805803385</v>
+        <v>0.0391191455492432</v>
       </c>
       <c r="L113" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.621034174543121</v>
+        <v>0.620555006773534</v>
       </c>
       <c r="M113" s="1">
         <f ca="1" t="shared" si="89"/>
-        <v>0.45849875327481</v>
+        <v>0.257029662755007</v>
       </c>
       <c r="N113" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.744757411576196</v>
+        <v>0.744054605337403</v>
       </c>
       <c r="O113" s="1">
         <f ca="1" t="shared" si="89"/>
-        <v>0.210562997388295</v>
+        <v>0.000889522918118502</v>
       </c>
       <c r="P113" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.868205430347429</v>
+        <v>0.867269878456472</v>
       </c>
     </row>
     <row r="114" ht="16.5" spans="1:16">
@@ -10626,27 +10572,27 @@
       </c>
       <c r="K114" s="1">
         <f ca="1" t="shared" ref="K114:O114" si="90">RAND()</f>
-        <v>0.744730946242836</v>
+        <v>0.0175068472646798</v>
       </c>
       <c r="L114" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.6157930852606</v>
+        <v>0.615000125987062</v>
       </c>
       <c r="M114" s="1">
         <f ca="1" t="shared" si="90"/>
-        <v>0.930423267720453</v>
+        <v>0.0544248056246359</v>
       </c>
       <c r="N114" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.738931505068955</v>
+        <v>0.737183364160072</v>
       </c>
       <c r="O114" s="1">
         <f ca="1" t="shared" si="90"/>
-        <v>0.00569070931616467</v>
+        <v>0.337786066948599</v>
       </c>
       <c r="P114" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.86106160397766</v>
+        <v>0.859675577159748</v>
       </c>
     </row>
     <row r="115" ht="16.5" spans="1:16">
@@ -10686,27 +10632,27 @@
       </c>
       <c r="K115" s="1">
         <f ca="1" t="shared" ref="K115:O115" si="91">RAND()</f>
-        <v>0.467383317291562</v>
+        <v>0.422883263647376</v>
       </c>
       <c r="L115" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.610048896893233</v>
+        <v>0.610001225666693</v>
       </c>
       <c r="M115" s="1">
         <f ca="1" t="shared" si="91"/>
-        <v>0.816099911026437</v>
+        <v>0.0989793562458432</v>
       </c>
       <c r="N115" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.7319757854798</v>
+        <v>0.731159890091176</v>
       </c>
       <c r="O115" s="1">
         <f ca="1" t="shared" si="91"/>
-        <v>0.66408324233248</v>
+        <v>0.611060646075599</v>
       </c>
       <c r="P115" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.853739824351419</v>
+        <v>0.852867127858281</v>
       </c>
     </row>
     <row r="116" ht="16.5" spans="1:16">
@@ -10746,27 +10692,27 @@
       </c>
       <c r="K116" s="1">
         <f ca="1" t="shared" ref="K116:O116" si="92">RAND()</f>
-        <v>0.727090788742856</v>
+        <v>0.740402840966264</v>
       </c>
       <c r="L116" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.604975885040781</v>
+        <v>0.604989897727332</v>
       </c>
       <c r="M116" s="1">
         <f ca="1" t="shared" si="92"/>
-        <v>0.0879973035159507</v>
+        <v>0.27359371682711</v>
       </c>
       <c r="N116" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.725068513781325</v>
+        <v>0.725277891113466</v>
       </c>
       <c r="O116" s="1">
         <f ca="1" t="shared" si="92"/>
-        <v>0.398555129538558</v>
+        <v>0.172658670058026</v>
       </c>
       <c r="P116" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.845488045496628</v>
+        <v>0.845459637081948</v>
       </c>
     </row>
     <row r="117" ht="16.5" spans="1:16">
@@ -10806,27 +10752,27 @@
       </c>
       <c r="K117" s="1">
         <f ca="1" t="shared" ref="K117:O117" si="93">RAND()</f>
-        <v>0.91958847170324</v>
+        <v>0.23534822497159</v>
       </c>
       <c r="L117" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.599916815660383</v>
+        <v>0.599208980922384</v>
       </c>
       <c r="M117" s="1">
         <f ca="1" t="shared" si="93"/>
-        <v>0.597866012936575</v>
+        <v>0.743222362225832</v>
       </c>
       <c r="N117" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.71950081498411</v>
+        <v>0.718943348883308</v>
       </c>
       <c r="O117" s="1">
         <f ca="1" t="shared" si="93"/>
-        <v>0.763156252487397</v>
+        <v>0.887611842047885</v>
       </c>
       <c r="P117" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.839255804210821</v>
+        <v>0.838827085271633</v>
       </c>
     </row>
     <row r="118" ht="16.5" spans="1:16">
@@ -10866,27 +10812,27 @@
       </c>
       <c r="K118" s="1">
         <f ca="1" t="shared" ref="K118:O118" si="94">RAND()</f>
-        <v>0.277611273989369</v>
+        <v>0.726067064497289</v>
       </c>
       <c r="L118" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.594093061861262</v>
+        <v>0.594549051391841</v>
       </c>
       <c r="M118" s="1">
         <f ca="1" t="shared" si="94"/>
-        <v>0.0696529035840694</v>
+        <v>0.435946034313533</v>
       </c>
       <c r="N118" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.712112602833076</v>
+        <v>0.712941038959887</v>
       </c>
       <c r="O118" s="1">
         <f ca="1" t="shared" si="94"/>
-        <v>0.765394664962716</v>
+        <v>0.532097594897167</v>
       </c>
       <c r="P118" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.830839573535735</v>
+        <v>0.831430793366723</v>
       </c>
     </row>
     <row r="119" ht="16.5" spans="1:16">
@@ -10926,27 +10872,27 @@
       </c>
       <c r="K119" s="1">
         <f ca="1" t="shared" ref="K119:O119" si="95">RAND()</f>
-        <v>0.323494596366406</v>
+        <v>0.337181260241293</v>
       </c>
       <c r="L119" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.589067378344912</v>
+        <v>0.58908105906065</v>
       </c>
       <c r="M119" s="1">
         <f ca="1" t="shared" si="95"/>
-        <v>0.318957048399907</v>
+        <v>0.813064288926042</v>
       </c>
       <c r="N119" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.706335349318976</v>
+        <v>0.706842922539368</v>
       </c>
       <c r="O119" s="1">
         <f ca="1" t="shared" si="95"/>
-        <v>0.552107249118635</v>
+        <v>0.180921068932887</v>
       </c>
       <c r="P119" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.82383636916816</v>
+        <v>0.823972917523525</v>
       </c>
     </row>
     <row r="120" ht="16.5" spans="1:16">
@@ -11100,27 +11046,27 @@
       </c>
       <c r="K122" s="1">
         <f ca="1" t="shared" ref="K122:O122" si="96">RAND()</f>
-        <v>0.175820977192783</v>
+        <v>0.0199148821546393</v>
       </c>
       <c r="L122" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.574216689358489</v>
+        <v>0.574068514144197</v>
       </c>
       <c r="M122" s="1">
         <f ca="1" t="shared" si="96"/>
-        <v>0.826301809488503</v>
+        <v>0.491912038613519</v>
       </c>
       <c r="N122" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.689051604301391</v>
+        <v>0.688585620627176</v>
       </c>
       <c r="O122" s="1">
         <f ca="1" t="shared" si="96"/>
-        <v>0.585443049652331</v>
+        <v>0.655130850273262</v>
       </c>
       <c r="P122" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.803657603894036</v>
+        <v>0.803257852427023</v>
       </c>
     </row>
     <row r="123" ht="16.5" spans="1:16">
@@ -11160,27 +11106,27 @@
       </c>
       <c r="K123" s="1">
         <f ca="1" t="shared" ref="K123:O123" si="97">RAND()</f>
-        <v>0.541691846616119</v>
+        <v>0.0329003659648475</v>
       </c>
       <c r="L123" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.569819492445692</v>
+        <v>0.569343857543037</v>
       </c>
       <c r="M123" s="1">
         <f ca="1" t="shared" si="97"/>
-        <v>0.462222072770883</v>
+        <v>0.37107749385759</v>
       </c>
       <c r="N123" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.683366346842402</v>
+        <v>0.682805507008911</v>
       </c>
       <c r="O123" s="1">
         <f ca="1" t="shared" si="97"/>
-        <v>0.754606925098758</v>
+        <v>0.396798810036563</v>
       </c>
       <c r="P123" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.797186532153767</v>
+        <v>0.796291201601684</v>
       </c>
     </row>
     <row r="124" ht="16.5" spans="1:16">
@@ -11220,27 +11166,27 @@
       </c>
       <c r="K124" s="1">
         <f ca="1" t="shared" ref="K124:O124" si="98">RAND()</f>
-        <v>0.163331431936711</v>
+        <v>0.084692421529345</v>
       </c>
       <c r="L124" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.56480434318011</v>
+        <v>0.56473202421812</v>
       </c>
       <c r="M124" s="1">
         <f ca="1" t="shared" si="98"/>
-        <v>0.824742507598474</v>
+        <v>0.28260724399816</v>
       </c>
       <c r="N124" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.677757924854431</v>
+        <v>0.677187040875935</v>
       </c>
       <c r="O124" s="1">
         <f ca="1" t="shared" si="98"/>
-        <v>0.899522347346395</v>
+        <v>0.885497208698641</v>
       </c>
       <c r="P124" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.790780276473342</v>
+        <v>0.790196494526478</v>
       </c>
     </row>
     <row r="125" ht="16.5" spans="1:16">
@@ -11280,27 +11226,27 @@
       </c>
       <c r="K125" s="1">
         <f ca="1" t="shared" ref="K125:O125" si="99">RAND()</f>
-        <v>0.780175098904093</v>
+        <v>0.443818451445232</v>
       </c>
       <c r="L125" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.560776712323949</v>
+        <v>0.56047237704104</v>
       </c>
       <c r="M125" s="1">
         <f ca="1" t="shared" si="99"/>
-        <v>0.37939623010241</v>
+        <v>0.468630991368278</v>
       </c>
       <c r="N125" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.672410312374789</v>
+        <v>0.672186716647707</v>
       </c>
       <c r="O125" s="1">
         <f ca="1" t="shared" si="99"/>
-        <v>0.796415473986678</v>
+        <v>0.0878654391224434</v>
       </c>
       <c r="P125" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.784421231175013</v>
+        <v>0.783556539822365</v>
       </c>
     </row>
     <row r="126" ht="16.5" spans="1:16">
@@ -11340,27 +11286,27 @@
       </c>
       <c r="K126" s="1">
         <f ca="1" t="shared" ref="K126:O126" si="100">RAND()</f>
-        <v>0.452630247220889</v>
+        <v>0.840559896487247</v>
       </c>
       <c r="L126" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.555964277252365</v>
+        <v>0.556309659778808</v>
       </c>
       <c r="M126" s="1">
         <f ca="1" t="shared" si="100"/>
-        <v>0.274342886554688</v>
+        <v>0.128847015752882</v>
       </c>
       <c r="N126" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.666608530919104</v>
+        <v>0.666824375186382</v>
       </c>
       <c r="O126" s="1">
         <f ca="1" t="shared" si="100"/>
-        <v>0.0215985061145929</v>
+        <v>0.789660260778759</v>
       </c>
       <c r="P126" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.777027760556806</v>
+        <v>0.777927427547591</v>
       </c>
     </row>
     <row r="127" ht="16.5" spans="1:16">
@@ -11400,27 +11346,27 @@
       </c>
       <c r="K127" s="1">
         <f ca="1" t="shared" ref="K127:O127" si="101">RAND()</f>
-        <v>0.683731390962754</v>
+        <v>0.462206173643516</v>
       </c>
       <c r="L127" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.551722888456844</v>
+        <v>0.551528790171192</v>
       </c>
       <c r="M127" s="1">
         <f ca="1" t="shared" si="101"/>
-        <v>0.687975700627025</v>
+        <v>0.548823325308193</v>
       </c>
       <c r="N127" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.661849495737393</v>
+        <v>0.661533473465748</v>
       </c>
       <c r="O127" s="1">
         <f ca="1" t="shared" si="101"/>
-        <v>0.613710776630821</v>
+        <v>0.571539493893601</v>
       </c>
       <c r="P127" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.771911032798822</v>
+        <v>0.771558060450874</v>
       </c>
     </row>
     <row r="128" ht="16.5" spans="1:16">
@@ -11460,27 +11406,27 @@
       </c>
       <c r="K128" s="1">
         <f ca="1" t="shared" ref="K128:O128" si="102">RAND()</f>
-        <v>0.627502295769987</v>
+        <v>0.15767687052459</v>
       </c>
       <c r="L128" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.547297808504039</v>
+        <v>0.546892634721487</v>
       </c>
       <c r="M128" s="1">
         <f ca="1" t="shared" si="102"/>
-        <v>0.160755676478342</v>
+        <v>0.587916386151558</v>
       </c>
       <c r="N128" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.656097860268531</v>
+        <v>0.656061066550564</v>
       </c>
       <c r="O128" s="1">
         <f ca="1" t="shared" si="102"/>
-        <v>0.382706043111877</v>
+        <v>0.682246352145585</v>
       </c>
       <c r="P128" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.765089320298211</v>
+        <v>0.765310847806633</v>
       </c>
     </row>
     <row r="129" ht="16.5" spans="1:16">
@@ -11520,27 +11466,27 @@
       </c>
       <c r="K129" s="1">
         <f ca="1" t="shared" ref="K129:O129" si="103">RAND()</f>
-        <v>0.650019742957763</v>
+        <v>0.86823878796882</v>
       </c>
       <c r="L129" s="1">
         <f ca="1" t="shared" si="45"/>
-        <v>0.54300998231132</v>
+        <v>0.543195232238803</v>
       </c>
       <c r="M129" s="1">
         <f ca="1" t="shared" si="103"/>
-        <v>0.179454314574947</v>
+        <v>0.654097729946019</v>
       </c>
       <c r="N129" s="1">
         <f ca="1" t="shared" si="46"/>
-        <v>0.65097482418762</v>
+        <v>0.651563007132581</v>
       </c>
       <c r="O129" s="1">
         <f ca="1" t="shared" si="103"/>
-        <v>0.242181646939646</v>
+        <v>0.571328140549385</v>
       </c>
       <c r="P129" s="1">
         <f ca="1" t="shared" si="47"/>
-        <v>0.75899291638298</v>
+        <v>0.759860517488116</v>
       </c>
     </row>
     <row r="130" ht="16.5" spans="1:16">
@@ -11580,27 +11526,27 @@
       </c>
       <c r="K130" s="1">
         <f ca="1" t="shared" ref="K130:O130" si="107">RAND()</f>
-        <v>0.105262784263307</v>
+        <v>0.287323456160806</v>
       </c>
       <c r="L130" s="1">
         <f ca="1" t="shared" ref="L130:L193" si="108">J130+($R$1*$R$7*K130/MAX(1,($A130*($A130-1)))+$R$1*$R$7/$A130)/100</f>
-        <v>0.538314718169988</v>
+        <v>0.538466876435018</v>
       </c>
       <c r="M130" s="1">
         <f ca="1" t="shared" si="107"/>
-        <v>0.00936152036740689</v>
+        <v>0.992345536754037</v>
       </c>
       <c r="N130" s="1">
         <f ca="1" t="shared" ref="N130:N193" si="109">L130+($R$1*$R$7*M130/MAX(1,($A130*($A130-1)))+$R$1*$R$7/$A130)/100</f>
-        <v>0.645299286301109</v>
+        <v>0.646272979172858</v>
       </c>
       <c r="O130" s="1">
         <f ca="1" t="shared" si="107"/>
-        <v>0.327670539376462</v>
+        <v>0.62565044730168</v>
       </c>
       <c r="P130" s="1">
         <f ca="1" t="shared" ref="P130:P193" si="110">N130+($R$1*$R$7*O130/MAX(1,($A130*($A130-1)))+$R$1*$R$7/$A130)/100</f>
-        <v>0.7525498830455</v>
+        <v>0.753772614357739</v>
       </c>
     </row>
     <row r="131" ht="16.5" spans="1:16">
@@ -11640,27 +11586,27 @@
       </c>
       <c r="K131" s="1">
         <f ca="1" t="shared" ref="K131:O131" si="112">RAND()</f>
-        <v>0.971689963431821</v>
+        <v>0.237860578429377</v>
       </c>
       <c r="L131" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.534860424656849</v>
+        <v>0.53425655789996</v>
       </c>
       <c r="M131" s="1">
         <f ca="1" t="shared" si="112"/>
-        <v>0.187411398465906</v>
+        <v>0.0672562318492931</v>
       </c>
       <c r="N131" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.641168491281705</v>
+        <v>0.640465749074648</v>
       </c>
       <c r="O131" s="1">
         <f ca="1" t="shared" si="112"/>
-        <v>0.319102219479067</v>
+        <v>0.768854723643575</v>
       </c>
       <c r="P131" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.747584926024031</v>
+        <v>0.747252284267628</v>
       </c>
     </row>
     <row r="132" ht="16.5" spans="1:16">
@@ -11700,27 +11646,27 @@
       </c>
       <c r="K132" s="1">
         <f ca="1" t="shared" ref="K132:O132" si="113">RAND()</f>
-        <v>0.576477980746396</v>
+        <v>0.800645121113625</v>
       </c>
       <c r="L132" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.530426036179349</v>
+        <v>0.530607686592565</v>
       </c>
       <c r="M132" s="1">
         <f ca="1" t="shared" si="113"/>
-        <v>0.0361697900587761</v>
+        <v>0.100112773496142</v>
       </c>
       <c r="N132" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.635798857265832</v>
+        <v>0.63603232289757</v>
       </c>
       <c r="O132" s="1">
         <f ca="1" t="shared" si="113"/>
-        <v>0.798349014610862</v>
+        <v>0.478707900996426</v>
       </c>
       <c r="P132" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.74178929862823</v>
+        <v>0.741763747972952</v>
       </c>
     </row>
     <row r="133" ht="16.5" spans="1:16">
@@ -11760,27 +11706,27 @@
       </c>
       <c r="K133" s="1">
         <f ca="1" t="shared" ref="K133:O133" si="114">RAND()</f>
-        <v>0.484525873147827</v>
+        <v>0.752880490182528</v>
       </c>
       <c r="L133" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.526306179565663</v>
+        <v>0.526520341820757</v>
       </c>
       <c r="M133" s="1">
         <f ca="1" t="shared" si="114"/>
-        <v>0.917406794596325</v>
+        <v>0.747097218058212</v>
       </c>
       <c r="N133" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.631583776938172</v>
+        <v>0.631662022459734</v>
       </c>
       <c r="O133" s="1">
         <f ca="1" t="shared" si="114"/>
-        <v>0.343348765757016</v>
+        <v>0.470395176368626</v>
       </c>
       <c r="P133" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.736403243336937</v>
+        <v>0.736582879123734</v>
       </c>
     </row>
     <row r="134" ht="16.5" spans="1:16">
@@ -11820,27 +11766,27 @@
       </c>
       <c r="K134" s="1">
         <f ca="1" t="shared" ref="K134:O134" si="115">RAND()</f>
-        <v>0.327672124602298</v>
+        <v>0.873535049670381</v>
       </c>
       <c r="L134" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.522198785333761</v>
+        <v>0.522627864188052</v>
       </c>
       <c r="M134" s="1">
         <f ca="1" t="shared" si="115"/>
-        <v>0.0670517284854384</v>
+        <v>0.718677122513178</v>
       </c>
       <c r="N134" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.626010890246788</v>
+        <v>0.626952183183876</v>
       </c>
       <c r="O134" s="1">
         <f ca="1" t="shared" si="115"/>
-        <v>0.118514580758835</v>
+        <v>0.253815450708718</v>
       </c>
       <c r="P134" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.729863447846154</v>
+        <v>0.73091109485053</v>
       </c>
     </row>
     <row r="135" ht="16.5" spans="1:16">
@@ -11880,27 +11826,27 @@
       </c>
       <c r="K135" s="1">
         <f ca="1" t="shared" ref="K135:O135" si="116">RAND()</f>
-        <v>0.530620113197162</v>
+        <v>0.908732608568533</v>
       </c>
       <c r="L135" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.518433540431047</v>
+        <v>0.518726321961522</v>
       </c>
       <c r="M135" s="1">
         <f ca="1" t="shared" si="116"/>
-        <v>0.521328911231493</v>
+        <v>0.6382906642531</v>
       </c>
       <c r="N135" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.621822292477674</v>
+        <v>0.622205640285318</v>
       </c>
       <c r="O135" s="1">
         <f ca="1" t="shared" si="116"/>
-        <v>0.934874498685232</v>
+        <v>0.745900861584274</v>
       </c>
       <c r="P135" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.725531262743742</v>
+        <v>0.725768283753495</v>
       </c>
     </row>
     <row r="136" ht="16.5" spans="1:16">
@@ -11940,27 +11886,27 @@
       </c>
       <c r="K136" s="1">
         <f ca="1" t="shared" ref="K136:O136" si="117">RAND()</f>
-        <v>0.0235191614587897</v>
+        <v>0.964845613005692</v>
       </c>
       <c r="L136" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.514180462378559</v>
+        <v>0.514898555525676</v>
       </c>
       <c r="M136" s="1">
         <f ca="1" t="shared" si="117"/>
-        <v>0.154988688720942</v>
+        <v>0.722880210619442</v>
       </c>
       <c r="N136" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.616520918094665</v>
+        <v>0.617672228654839</v>
       </c>
       <c r="O136" s="1">
         <f ca="1" t="shared" si="117"/>
-        <v>0.4159630024952</v>
+        <v>0.26915935514524</v>
       </c>
       <c r="P136" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.719060458693583</v>
+        <v>0.720099779738366</v>
       </c>
     </row>
     <row r="137" ht="16.5" spans="1:16">
@@ -12000,27 +11946,27 @@
       </c>
       <c r="K137" s="1">
         <f ca="1" t="shared" ref="K137:O137" si="118">RAND()</f>
-        <v>0.641839816015439</v>
+        <v>0.307630731285437</v>
       </c>
       <c r="L137" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.510841905744064</v>
+        <v>0.510590702837241</v>
       </c>
       <c r="M137" s="1">
         <f ca="1" t="shared" si="118"/>
-        <v>0.527891232330132</v>
+        <v>0.90743172060857</v>
       </c>
       <c r="N137" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.612709274970979</v>
+        <v>0.612743347594561</v>
       </c>
       <c r="O137" s="1">
         <f ca="1" t="shared" si="118"/>
-        <v>0.144388285505085</v>
+        <v>0.411475759140656</v>
       </c>
       <c r="P137" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.714288390348973</v>
+        <v>0.714523214995222</v>
       </c>
     </row>
     <row r="138" ht="16.5" spans="1:16">
@@ -12174,27 +12120,27 @@
       </c>
       <c r="K140" s="1">
         <f ca="1" t="shared" ref="K140:O140" si="119">RAND()</f>
-        <v>0.88166226078028</v>
+        <v>0.729266384247821</v>
       </c>
       <c r="L140" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.499914864935813</v>
+        <v>0.499805227614567</v>
       </c>
       <c r="M140" s="1">
         <f ca="1" t="shared" si="119"/>
-        <v>0.31892816904955</v>
+        <v>0.1896524062559</v>
       </c>
       <c r="N140" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.599424885201316</v>
+        <v>0.599222243734175</v>
       </c>
       <c r="O140" s="1">
         <f ca="1" t="shared" si="119"/>
-        <v>0.811127296092816</v>
+        <v>0.956516789575229</v>
       </c>
       <c r="P140" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.699289005558218</v>
+        <v>0.699190960848978</v>
       </c>
     </row>
     <row r="141" ht="16.5" spans="1:16">
@@ -12234,27 +12180,27 @@
       </c>
       <c r="K141" s="1">
         <f ca="1" t="shared" ref="K141:O141" si="120">RAND()</f>
-        <v>0.394092140489924</v>
+        <v>0.370496455302103</v>
       </c>
       <c r="L141" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.495973199976298</v>
+        <v>0.495956467167686</v>
       </c>
       <c r="M141" s="1">
         <f ca="1" t="shared" si="120"/>
-        <v>0.548075034806988</v>
+        <v>0.0533278389600071</v>
       </c>
       <c r="N141" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.594933294296973</v>
+        <v>0.59456571301443</v>
       </c>
       <c r="O141" s="1">
         <f ca="1" t="shared" si="120"/>
-        <v>0.227331001775063</v>
+        <v>0.794028346939889</v>
       </c>
       <c r="P141" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.693665933959074</v>
+        <v>0.693700224380708</v>
       </c>
     </row>
     <row r="142" ht="16.5" spans="1:16">
@@ -12294,27 +12240,27 @@
       </c>
       <c r="K142" s="1">
         <f ca="1" t="shared" ref="K142:O142" si="121">RAND()</f>
-        <v>0.665271616261859</v>
+        <v>0.107660624389254</v>
       </c>
       <c r="L142" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.492623138211976</v>
+        <v>0.492233318977536</v>
       </c>
       <c r="M142" s="1">
         <f ca="1" t="shared" si="121"/>
-        <v>0.889129893247358</v>
+        <v>0.622476680939623</v>
       </c>
       <c r="N142" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.59111705880604</v>
+        <v>0.59054082547181</v>
       </c>
       <c r="O142" s="1">
         <f ca="1" t="shared" si="121"/>
-        <v>0.0762488312429224</v>
+        <v>0.944036879874905</v>
       </c>
       <c r="P142" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.689042703885632</v>
+        <v>0.689073130889352</v>
       </c>
     </row>
     <row r="143" ht="16.5" spans="1:16">
@@ -12354,27 +12300,27 @@
       </c>
       <c r="K143" s="1">
         <f ca="1" t="shared" ref="K143:O143" si="122">RAND()</f>
-        <v>0.151703604021677</v>
+        <v>0.251829305514502</v>
       </c>
       <c r="L143" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.488777020763935</v>
+        <v>0.488846031586061</v>
       </c>
       <c r="M143" s="1">
         <f ca="1" t="shared" si="122"/>
-        <v>0.866721572200574</v>
+        <v>0.229561098321646</v>
       </c>
       <c r="N143" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.58655750012146</v>
+        <v>0.586187353290028</v>
       </c>
       <c r="O143" s="1">
         <f ca="1" t="shared" si="122"/>
-        <v>0.0886653121052452</v>
+        <v>0.372900336741696</v>
       </c>
       <c r="P143" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.683801710555335</v>
+        <v>0.683627470393566</v>
       </c>
     </row>
     <row r="144" ht="16.5" spans="1:16">
@@ -12414,27 +12360,27 @@
       </c>
       <c r="K144" s="1">
         <f ca="1" t="shared" ref="K144:O144" si="123">RAND()</f>
-        <v>0.706115325755825</v>
+        <v>0.0986851214823237</v>
       </c>
       <c r="L144" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.485715768319483</v>
+        <v>0.485302957484313</v>
       </c>
       <c r="M144" s="1">
         <f ca="1" t="shared" si="123"/>
-        <v>0.734861998244186</v>
+        <v>0.470175715077762</v>
       </c>
       <c r="N144" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.582718678571417</v>
+        <v>0.582125986385528</v>
       </c>
       <c r="O144" s="1">
         <f ca="1" t="shared" si="123"/>
-        <v>0.222601532851685</v>
+        <v>0.562589270089482</v>
       </c>
       <c r="P144" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.679373455541443</v>
+        <v>0.679011819731693</v>
       </c>
     </row>
     <row r="145" ht="16.5" spans="1:16">
@@ -12474,27 +12420,27 @@
       </c>
       <c r="K145" s="1">
         <f ca="1" t="shared" ref="K145:O145" si="124">RAND()</f>
-        <v>0.485417331251071</v>
+        <v>0.858683319768813</v>
       </c>
       <c r="L145" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.482172628164883</v>
+        <v>0.482422777283062</v>
       </c>
       <c r="M145" s="1">
         <f ca="1" t="shared" si="124"/>
-        <v>0.320021372009279</v>
+        <v>0.108233004275755</v>
       </c>
       <c r="N145" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.578220428035402</v>
+        <v>0.578328644389657</v>
       </c>
       <c r="O145" s="1">
         <f ca="1" t="shared" si="124"/>
-        <v>0.394410565402192</v>
+        <v>0.296733470285459</v>
       </c>
       <c r="P145" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.674318080803591</v>
+        <v>0.67436083756613</v>
       </c>
     </row>
     <row r="146" ht="16.5" spans="1:16">
@@ -12534,27 +12480,27 @@
       </c>
       <c r="K146" s="1">
         <f ca="1" t="shared" ref="K146:O146" si="125">RAND()</f>
-        <v>0.844037714117559</v>
+        <v>0.130823015976573</v>
       </c>
       <c r="L146" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.479063588144388</v>
+        <v>0.478592210614007</v>
       </c>
       <c r="M146" s="1">
         <f ca="1" t="shared" si="125"/>
-        <v>0.0905936381900196</v>
+        <v>0.868503691008353</v>
       </c>
       <c r="N146" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.574295877043192</v>
+        <v>0.57433863546726</v>
       </c>
       <c r="O146" s="1">
         <f ca="1" t="shared" si="125"/>
-        <v>0.227188980551899</v>
+        <v>0.622086282113545</v>
       </c>
       <c r="P146" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.669618444472867</v>
+        <v>0.669922198239921</v>
       </c>
     </row>
     <row r="147" ht="16.5" spans="1:16">
@@ -12594,27 +12540,27 @@
       </c>
       <c r="K147" s="1">
         <f ca="1" t="shared" ref="K147:O147" si="126">RAND()</f>
-        <v>0.708905880754734</v>
+        <v>0.353176229982738</v>
       </c>
       <c r="L147" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.475672314650658</v>
+        <v>0.475440426640235</v>
       </c>
       <c r="M147" s="1">
         <f ca="1" t="shared" si="126"/>
-        <v>0.584535847456254</v>
+        <v>0.252589329572041</v>
       </c>
       <c r="N147" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.570573901551692</v>
+        <v>0.570125628942932</v>
       </c>
       <c r="O147" s="1">
         <f ca="1" t="shared" si="126"/>
-        <v>0.325571433591749</v>
+        <v>0.111404232105593</v>
       </c>
       <c r="P147" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.665306678395507</v>
+        <v>0.664718797502358</v>
       </c>
     </row>
     <row r="148" ht="16.5" spans="1:16">
@@ -12654,27 +12600,27 @@
       </c>
       <c r="K148" s="1">
         <f ca="1" t="shared" ref="K148:O148" si="127">RAND()</f>
-        <v>0.207108889701011</v>
+        <v>0.484915866063976</v>
       </c>
       <c r="L148" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.472092913180406</v>
+        <v>0.472271542211895</v>
       </c>
       <c r="M148" s="1">
         <f ca="1" t="shared" si="127"/>
-        <v>0.297580703691461</v>
+        <v>0.389043720379527</v>
       </c>
       <c r="N148" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.566161807678167</v>
+        <v>0.566399247148119</v>
       </c>
       <c r="O148" s="1">
         <f ca="1" t="shared" si="127"/>
-        <v>0.928563155623644</v>
+        <v>0.725890108416368</v>
       </c>
       <c r="P148" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.660636421952121</v>
+        <v>0.660743543275979</v>
       </c>
     </row>
     <row r="149" ht="16.5" spans="1:16">
@@ -12714,27 +12660,27 @@
       </c>
       <c r="K149" s="1">
         <f ca="1" t="shared" ref="K149:O149" si="128">RAND()</f>
-        <v>0.598944677672388</v>
+        <v>0.601173944044978</v>
       </c>
       <c r="L149" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.469133362592015</v>
+        <v>0.469134776633013</v>
       </c>
       <c r="M149" s="1">
         <f ca="1" t="shared" si="128"/>
-        <v>0.305781338956156</v>
+        <v>0.399217914730991</v>
       </c>
       <c r="N149" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.56257056531667</v>
+        <v>0.562631246904354</v>
       </c>
       <c r="O149" s="1">
         <f ca="1" t="shared" si="128"/>
-        <v>0.505340925332598</v>
+        <v>0.655459427315494</v>
       </c>
       <c r="P149" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.656134350238972</v>
+        <v>0.656290253159959</v>
       </c>
     </row>
     <row r="150" ht="16.5" spans="1:16">
@@ -12774,27 +12720,27 @@
       </c>
       <c r="K150" s="1">
         <f ca="1" t="shared" ref="K150:O150" si="129">RAND()</f>
-        <v>0.472365182516812</v>
+        <v>0.229609398573577</v>
       </c>
       <c r="L150" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.465886025735477</v>
+        <v>0.465734110724665</v>
       </c>
       <c r="M150" s="1">
         <f ca="1" t="shared" si="129"/>
-        <v>0.338689002054153</v>
+        <v>0.935398901290737</v>
       </c>
       <c r="N150" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.558715424802607</v>
+        <v>0.558936927015152</v>
       </c>
       <c r="O150" s="1">
         <f ca="1" t="shared" si="129"/>
-        <v>0.43646927039916</v>
+        <v>0.559649902898658</v>
       </c>
       <c r="P150" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.651606014133801</v>
+        <v>0.651904601995199</v>
       </c>
     </row>
     <row r="151" ht="16.5" spans="1:16">
@@ -12834,27 +12780,27 @@
       </c>
       <c r="K151" s="1">
         <f ca="1" t="shared" ref="K151:O151" si="130">RAND()</f>
-        <v>0.198678703333134</v>
+        <v>0.135265053776152</v>
       </c>
       <c r="L151" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.46259247275642</v>
+        <v>0.462553318019781</v>
       </c>
       <c r="M151" s="1">
         <f ca="1" t="shared" si="130"/>
-        <v>0.641182937793508</v>
+        <v>0.574828996086424</v>
       </c>
       <c r="N151" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.554988370946199</v>
+        <v>0.554908245990519</v>
       </c>
       <c r="O151" s="1">
         <f ca="1" t="shared" si="130"/>
-        <v>0.137478019826632</v>
+        <v>0.164368717925993</v>
       </c>
       <c r="P151" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.647073256703407</v>
+        <v>0.647009735400245</v>
       </c>
     </row>
     <row r="152" ht="16.5" spans="1:16">
@@ -12894,27 +12840,27 @@
       </c>
       <c r="K152" s="1">
         <f ca="1" t="shared" ref="K152:O152" si="131">RAND()</f>
-        <v>0.564871645263328</v>
+        <v>0.812507801723357</v>
       </c>
       <c r="L152" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.459734888684531</v>
+        <v>0.459885766342772</v>
       </c>
       <c r="M152" s="1">
         <f ca="1" t="shared" si="131"/>
-        <v>0.888962439318891</v>
+        <v>0.472747068298023</v>
       </c>
       <c r="N152" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.551667236660805</v>
+        <v>0.551564526145973</v>
       </c>
       <c r="O152" s="1">
         <f ca="1" t="shared" si="131"/>
-        <v>0.233269091359214</v>
+        <v>0.698514507390359</v>
       </c>
       <c r="P152" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.643200089352229</v>
+        <v>0.643380839620675</v>
       </c>
     </row>
     <row r="153" ht="16.5" spans="1:16">
@@ -12954,27 +12900,27 @@
       </c>
       <c r="K153" s="1">
         <f ca="1" t="shared" ref="K153:O153" si="132">RAND()</f>
-        <v>0.254277777483909</v>
+        <v>0.62411789422488</v>
       </c>
       <c r="L153" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.456505273323862</v>
+        <v>0.456727641466552</v>
       </c>
       <c r="M153" s="1">
         <f ca="1" t="shared" si="132"/>
-        <v>0.884763500515604</v>
+        <v>0.876658698417175</v>
       </c>
       <c r="N153" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.547826715303085</v>
+        <v>0.54804421039467</v>
       </c>
       <c r="O153" s="1">
         <f ca="1" t="shared" si="132"/>
-        <v>0.716916156178264</v>
+        <v>0.829866991842518</v>
       </c>
       <c r="P153" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.639047238262097</v>
+        <v>0.639332645584955</v>
       </c>
     </row>
     <row r="154" ht="16.5" spans="1:16">
@@ -13014,27 +12960,27 @@
       </c>
       <c r="K154" s="1">
         <f ca="1" t="shared" ref="K154:O154" si="133">RAND()</f>
-        <v>0.923880580453127</v>
+        <v>0.936497830547583</v>
       </c>
       <c r="L154" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.453902199518845</v>
+        <v>0.453909686535155</v>
       </c>
       <c r="M154" s="1">
         <f ca="1" t="shared" si="133"/>
-        <v>0.898362262328225</v>
+        <v>0.171043189853867</v>
       </c>
       <c r="N154" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.544631361852012</v>
+        <v>0.544207261183417</v>
       </c>
       <c r="O154" s="1">
         <f ca="1" t="shared" si="133"/>
-        <v>0.204167075644234</v>
+        <v>0.0288492719488569</v>
       </c>
       <c r="P154" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.634948592056857</v>
+        <v>0.634420458635812</v>
       </c>
     </row>
     <row r="155" ht="16.5" spans="1:16">
@@ -13074,27 +13020,27 @@
       </c>
       <c r="K155" s="1">
         <f ca="1" t="shared" ref="K155:O155" si="134">RAND()</f>
-        <v>0.974205940239352</v>
+        <v>0.238733493878615</v>
       </c>
       <c r="L155" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.450965284864413</v>
+        <v>0.450534526874439</v>
       </c>
       <c r="M155" s="1">
         <f ca="1" t="shared" si="134"/>
-        <v>0.19376233764249</v>
+        <v>0.0577975923692189</v>
       </c>
       <c r="N155" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.540689158909887</v>
+        <v>0.540178767888558</v>
       </c>
       <c r="O155" s="1">
         <f ca="1" t="shared" si="134"/>
-        <v>0.673399313627064</v>
+        <v>0.71063819953121</v>
       </c>
       <c r="P155" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.630693950970326</v>
+        <v>0.630205370348177</v>
       </c>
     </row>
     <row r="156" ht="16.5" spans="1:16">
@@ -13134,27 +13080,27 @@
       </c>
       <c r="K156" s="1">
         <f ca="1" t="shared" ref="K156:O156" si="135">RAND()</f>
-        <v>0.547923845744103</v>
+        <v>0.0591030077446513</v>
       </c>
       <c r="L156" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.447790588566035</v>
+        <v>0.447507985819307</v>
       </c>
       <c r="M156" s="1">
         <f ca="1" t="shared" si="135"/>
-        <v>0.350015719534364</v>
+        <v>0.700306521565512</v>
       </c>
       <c r="N156" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.537025201759566</v>
+        <v>0.536945113175721</v>
       </c>
       <c r="O156" s="1">
         <f ca="1" t="shared" si="135"/>
-        <v>0.809076296163786</v>
+        <v>0.0454014829707339</v>
       </c>
       <c r="P156" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.626525212353912</v>
+        <v>0.626003619269772</v>
       </c>
     </row>
     <row r="157" ht="16.5" spans="1:16">
@@ -13194,27 +13140,27 @@
       </c>
       <c r="K157" s="1">
         <f ca="1" t="shared" ref="K157:O157" si="136">RAND()</f>
-        <v>0.723611059296182</v>
+        <v>0.743755793588513</v>
       </c>
       <c r="L157" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.445003549736075</v>
+        <v>0.445015046730833</v>
       </c>
       <c r="M157" s="1">
         <f ca="1" t="shared" si="136"/>
-        <v>0.792912435839272</v>
+        <v>0.207341485278386</v>
       </c>
       <c r="N157" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.533917618868192</v>
+        <v>0.53359491904253</v>
       </c>
       <c r="O157" s="1">
         <f ca="1" t="shared" si="136"/>
-        <v>0.423383418913631</v>
+        <v>0.475586693955158</v>
       </c>
       <c r="P157" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.62262079054648</v>
+        <v>0.622327884153224</v>
       </c>
     </row>
     <row r="158" ht="16.5" spans="1:16">
@@ -13254,27 +13200,27 @@
       </c>
       <c r="K158" s="1">
         <f ca="1" t="shared" ref="K158:O158" si="137">RAND()</f>
-        <v>0.851450700276301</v>
+        <v>0.336763707087911</v>
       </c>
       <c r="L158" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.442223992310298</v>
+        <v>0.441933992289638</v>
       </c>
       <c r="M158" s="1">
         <f ca="1" t="shared" si="137"/>
-        <v>0.810962841893088</v>
+        <v>0.773552865874515</v>
       </c>
       <c r="N158" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.5305790179194</v>
+        <v>0.53026793927433</v>
       </c>
       <c r="O158" s="1">
         <f ca="1" t="shared" si="137"/>
-        <v>0.869160694620932</v>
+        <v>0.376238197781462</v>
       </c>
       <c r="P158" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.618966835067275</v>
+        <v>0.618378019591551</v>
       </c>
     </row>
     <row r="159" ht="16.5" spans="1:16">
@@ -13428,27 +13374,27 @@
       </c>
       <c r="K161" s="1">
         <f ca="1" t="shared" ref="K161:O161" si="138">RAND()</f>
-        <v>0.235103973239705</v>
+        <v>0.45230748810833</v>
       </c>
       <c r="L161" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.433547344136427</v>
+        <v>0.433665166797795</v>
       </c>
       <c r="M161" s="1">
         <f ca="1" t="shared" si="138"/>
-        <v>0.537218810040951</v>
+        <v>0.312567983598693</v>
       </c>
       <c r="N161" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.520088760000365</v>
+        <v>0.520084720185124</v>
       </c>
       <c r="O161" s="1">
         <f ca="1" t="shared" si="138"/>
-        <v>0.513114983971165</v>
+        <v>0.154695038864904</v>
       </c>
       <c r="P161" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.606617100675632</v>
+        <v>0.606418634946773</v>
       </c>
     </row>
     <row r="162" ht="16.5" spans="1:16">
@@ -13488,27 +13434,27 @@
       </c>
       <c r="K162" s="1">
         <f ca="1" t="shared" ref="K162:O162" si="139">RAND()</f>
-        <v>0.53668523748409</v>
+        <v>0.319613189770435</v>
       </c>
       <c r="L162" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.431001795662938</v>
+        <v>0.430885507065948</v>
       </c>
       <c r="M162" s="1">
         <f ca="1" t="shared" si="139"/>
-        <v>0.0252192251749956</v>
+        <v>0.0171630785681922</v>
       </c>
       <c r="N162" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.516729591676424</v>
+        <v>0.51660898728661</v>
       </c>
       <c r="O162" s="1">
         <f ca="1" t="shared" si="139"/>
-        <v>0.584514432830605</v>
+        <v>0.0231124950444617</v>
       </c>
       <c r="P162" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.602757010122584</v>
+        <v>0.60233565469467</v>
       </c>
     </row>
     <row r="163" ht="16.5" spans="1:16">
@@ -13548,27 +13494,27 @@
       </c>
       <c r="K163" s="1">
         <f ca="1" t="shared" ref="K163:O163" si="140">RAND()</f>
-        <v>0.836266691877724</v>
+        <v>0.864496793040779</v>
       </c>
       <c r="L163" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.42848479719147</v>
+        <v>0.428499733752932</v>
       </c>
       <c r="M163" s="1">
         <f ca="1" t="shared" si="140"/>
-        <v>0.792082407622801</v>
+        <v>0.730909711041072</v>
       </c>
       <c r="N163" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.51408907359762</v>
+        <v>0.514071643652954</v>
       </c>
       <c r="O163" s="1">
         <f ca="1" t="shared" si="140"/>
-        <v>0.524982710966772</v>
+        <v>0.876528203727603</v>
       </c>
       <c r="P163" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.599552027412946</v>
+        <v>0.599720600374503</v>
       </c>
     </row>
     <row r="164" ht="16.5" spans="1:16">
@@ -13722,27 +13668,27 @@
       </c>
       <c r="K166" s="1">
         <f ca="1" t="shared" ref="K166:O166" si="141">RAND()</f>
-        <v>0.544107256501033</v>
+        <v>0.671888684129902</v>
       </c>
       <c r="L166" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.420499212126376</v>
+        <v>0.420564377821175</v>
       </c>
       <c r="M166" s="1">
         <f ca="1" t="shared" si="141"/>
-        <v>0.826274285030836</v>
+        <v>0.589374339306953</v>
       </c>
       <c r="N166" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.504556957327167</v>
+        <v>0.504501309302418</v>
       </c>
       <c r="O166" s="1">
         <f ca="1" t="shared" si="141"/>
-        <v>0.819407172811954</v>
+        <v>0.385752463088084</v>
       </c>
       <c r="P166" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.588611200452992</v>
+        <v>0.588334398141687</v>
       </c>
     </row>
     <row r="167" ht="16.5" spans="1:16">
@@ -13782,27 +13728,27 @@
       </c>
       <c r="K167" s="1">
         <f ca="1" t="shared" ref="K167:O167" si="142">RAND()</f>
-        <v>0.150658225679812</v>
+        <v>0.415443923590198</v>
       </c>
       <c r="L167" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.417753891329478</v>
+        <v>0.417887299238611</v>
       </c>
       <c r="M167" s="1">
         <f ca="1" t="shared" si="142"/>
-        <v>0.739456793991404</v>
+        <v>0.883688842004023</v>
       </c>
       <c r="N167" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.501258984566319</v>
+        <v>0.501465061415305</v>
       </c>
       <c r="O167" s="1">
         <f ca="1" t="shared" si="142"/>
-        <v>0.907765082288061</v>
+        <v>0.19805007646186</v>
       </c>
       <c r="P167" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.584848877159805</v>
+        <v>0.584697375802132</v>
       </c>
     </row>
     <row r="168" ht="16.5" spans="1:16">
@@ -13842,27 +13788,27 @@
       </c>
       <c r="K168" s="1">
         <f ca="1" t="shared" ref="K168:O168" si="143">RAND()</f>
-        <v>0.595392664355544</v>
+        <v>0.145016544119798</v>
       </c>
       <c r="L168" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.41546123724003</v>
+        <v>0.415237040195832</v>
       </c>
       <c r="M168" s="1">
         <f ca="1" t="shared" si="143"/>
-        <v>0.0169072473414307</v>
+        <v>0.519684431567627</v>
       </c>
       <c r="N168" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.498104384199604</v>
+        <v>0.498130469427332</v>
       </c>
       <c r="O168" s="1">
         <f ca="1" t="shared" si="143"/>
-        <v>0.917489517857392</v>
+        <v>0.244584027191029</v>
       </c>
       <c r="P168" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.581195840636601</v>
+        <v>0.580886953792646</v>
       </c>
     </row>
     <row r="169" ht="16.5" spans="1:16">
@@ -13902,27 +13848,27 @@
       </c>
       <c r="K169" s="1">
         <f ca="1" t="shared" ref="K169:O169" si="144">RAND()</f>
-        <v>0.485223289181002</v>
+        <v>0.15765190057001</v>
       </c>
       <c r="L169" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.412920447725645</v>
+        <v>0.412759324074276</v>
       </c>
       <c r="M169" s="1">
         <f ca="1" t="shared" si="144"/>
-        <v>0.111146240534318</v>
+        <v>0.149330939281487</v>
       </c>
       <c r="N169" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.495117974747294</v>
+        <v>0.494975633133375</v>
       </c>
       <c r="O169" s="1">
         <f ca="1" t="shared" si="144"/>
-        <v>0.587845986244503</v>
+        <v>0.930298582591856</v>
       </c>
       <c r="P169" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.577549977691768</v>
+        <v>0.577576079399406</v>
       </c>
     </row>
     <row r="170" ht="16.5" spans="1:16">
@@ -13962,27 +13908,27 @@
       </c>
       <c r="K170" s="1">
         <f ca="1" t="shared" ref="K170:O170" si="145">RAND()</f>
-        <v>0.874124450258531</v>
+        <v>0.736415070713142</v>
       </c>
       <c r="L170" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.410653103600084</v>
+        <v>0.410586169624396</v>
       </c>
       <c r="M170" s="1">
         <f ca="1" t="shared" si="145"/>
-        <v>0.383963694741233</v>
+        <v>0.727392418254579</v>
       </c>
       <c r="N170" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.492496534812659</v>
+        <v>0.492596525195399</v>
       </c>
       <c r="O170" s="1">
         <f ca="1" t="shared" si="145"/>
-        <v>0.391544399927198</v>
+        <v>0.444857828044496</v>
       </c>
       <c r="P170" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.574343650645252</v>
+        <v>0.574469554148168</v>
       </c>
     </row>
     <row r="171" ht="16.5" spans="1:16">
@@ -14022,27 +13968,27 @@
       </c>
       <c r="K171" s="1">
         <f ca="1" t="shared" ref="K171:O171" si="146">RAND()</f>
-        <v>0.713962972338236</v>
+        <v>0.183282038852484</v>
       </c>
       <c r="L171" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.408146630317378</v>
+        <v>0.407891726144663</v>
       </c>
       <c r="M171" s="1">
         <f ca="1" t="shared" si="146"/>
-        <v>0.853062369870532</v>
+        <v>0.174261777098732</v>
       </c>
       <c r="N171" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.489732855890097</v>
+        <v>0.489151900614693</v>
       </c>
       <c r="O171" s="1">
         <f ca="1" t="shared" si="146"/>
-        <v>0.483317748057511</v>
+        <v>0.109718913246988</v>
       </c>
       <c r="P171" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.571141480495846</v>
+        <v>0.570381072943367</v>
       </c>
     </row>
     <row r="172" ht="16.5" spans="1:16">
@@ -14082,27 +14028,27 @@
       </c>
       <c r="K172" s="1">
         <f ca="1" t="shared" ref="K172:O172" si="147">RAND()</f>
-        <v>0.789836734487008</v>
+        <v>0.63422953181275</v>
       </c>
       <c r="L172" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.405782585033915</v>
+        <v>0.405708715773616</v>
       </c>
       <c r="M172" s="1">
         <f ca="1" t="shared" si="147"/>
-        <v>0.673454730138527</v>
+        <v>0.676614062567832</v>
       </c>
       <c r="N172" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.486804039291773</v>
+        <v>0.486731669817766</v>
       </c>
       <c r="O172" s="1">
         <f ca="1" t="shared" si="147"/>
-        <v>0.946585693888857</v>
+        <v>0.375661794985491</v>
       </c>
       <c r="P172" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.567955153243464</v>
+        <v>0.567611756944384</v>
       </c>
     </row>
     <row r="173" ht="16.5" spans="1:16">
@@ -14142,27 +14088,27 @@
       </c>
       <c r="K173" s="1">
         <f ca="1" t="shared" ref="K173:O173" si="148">RAND()</f>
-        <v>0.302234250198409</v>
+        <v>0.581130359397553</v>
       </c>
       <c r="L173" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.403181382859131</v>
+        <v>0.403312239866711</v>
       </c>
       <c r="M173" s="1">
         <f ca="1" t="shared" si="148"/>
-        <v>0.780743200310679</v>
+        <v>0.681603192867214</v>
       </c>
       <c r="N173" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.483780262777677</v>
+        <v>0.483864603665894</v>
       </c>
       <c r="O173" s="1">
         <f ca="1" t="shared" si="148"/>
-        <v>0.768584419217554</v>
+        <v>0.517926180991795</v>
       </c>
       <c r="P173" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.564373437841773</v>
+        <v>0.564340170825478</v>
       </c>
     </row>
     <row r="174" ht="16.5" spans="1:16">
@@ -14202,27 +14148,27 @@
       </c>
       <c r="K174" s="1">
         <f ca="1" t="shared" ref="K174:O174" si="149">RAND()</f>
-        <v>0.679156371615847</v>
+        <v>0.64135393763195</v>
       </c>
       <c r="L174" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.401013992402484</v>
+        <v>0.400996460691603</v>
       </c>
       <c r="M174" s="1">
         <f ca="1" t="shared" si="149"/>
-        <v>0.316441194727904</v>
+        <v>0.323206819873087</v>
       </c>
       <c r="N174" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.480929535099326</v>
+        <v>0.480915141096034</v>
       </c>
       <c r="O174" s="1">
         <f ca="1" t="shared" si="149"/>
-        <v>0.535415563718584</v>
+        <v>0.516570042796159</v>
       </c>
       <c r="P174" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.560946631979933</v>
+        <v>0.560923497951478</v>
       </c>
     </row>
     <row r="175" ht="16.5" spans="1:16">
@@ -14262,27 +14208,27 @@
       </c>
       <c r="K175" s="1">
         <f ca="1" t="shared" ref="K175:O175" si="150">RAND()</f>
-        <v>0.857259084669881</v>
+        <v>0.978719837692339</v>
       </c>
       <c r="L175" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.398778492305111</v>
+        <v>0.398834174930575</v>
       </c>
       <c r="M175" s="1">
         <f ca="1" t="shared" si="150"/>
-        <v>0.257815747366952</v>
+        <v>0.410940260994194</v>
       </c>
       <c r="N175" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.478207030518973</v>
+        <v>0.478332911745462</v>
       </c>
       <c r="O175" s="1">
         <f ca="1" t="shared" si="150"/>
-        <v>0.120127087126451</v>
+        <v>0.161293288578442</v>
       </c>
       <c r="P175" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.557572446564496</v>
+        <v>0.557717200077878</v>
       </c>
     </row>
     <row r="176" ht="16.5" spans="1:16">
@@ -14322,27 +14268,27 @@
       </c>
       <c r="K176" s="1">
         <f ca="1" t="shared" ref="K176:O176" si="151">RAND()</f>
-        <v>0.373717177357587</v>
+        <v>0.0452513908260699</v>
       </c>
       <c r="L176" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.396267891528655</v>
+        <v>0.396119030186976</v>
       </c>
       <c r="M176" s="1">
         <f ca="1" t="shared" si="151"/>
-        <v>0.358270259948233</v>
+        <v>0.00037135711009606</v>
       </c>
       <c r="N176" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.475287403173558</v>
+        <v>0.474976341343892</v>
       </c>
       <c r="O176" s="1">
         <f ca="1" t="shared" si="151"/>
-        <v>0.364858424773183</v>
+        <v>0.473558379163563</v>
       </c>
       <c r="P176" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.55430990058774</v>
+        <v>0.554048101791592</v>
       </c>
     </row>
     <row r="177" ht="16.5" spans="1:16">
@@ -14382,27 +14328,27 @@
       </c>
       <c r="K177" s="1">
         <f ca="1" t="shared" ref="K177:O177" si="152">RAND()</f>
-        <v>0.257090652607451</v>
+        <v>0.979064932142887</v>
       </c>
       <c r="L177" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.393952852305389</v>
+        <v>0.394276334287778</v>
       </c>
       <c r="M177" s="1">
         <f ca="1" t="shared" si="152"/>
-        <v>0.0659975548016611</v>
+        <v>0.514870983963508</v>
       </c>
       <c r="N177" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.472391513547475</v>
+        <v>0.472916114144229</v>
       </c>
       <c r="O177" s="1">
         <f ca="1" t="shared" si="152"/>
-        <v>0.477383989893682</v>
+        <v>0.0514101377649627</v>
       </c>
       <c r="P177" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.551014497283207</v>
+        <v>0.551348239465695</v>
       </c>
     </row>
     <row r="178" ht="16.5" spans="1:16">
@@ -14442,27 +14388,27 @@
       </c>
       <c r="K178" s="1">
         <f ca="1" t="shared" ref="K178:O178" si="153">RAND()</f>
-        <v>0.242546506941882</v>
+        <v>0.598322082122583</v>
       </c>
       <c r="L178" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.39170991081779</v>
+        <v>0.391867515560263</v>
       </c>
       <c r="M178" s="1">
         <f ca="1" t="shared" si="153"/>
-        <v>0.531465463502196</v>
+        <v>0.39508966528378</v>
       </c>
       <c r="N178" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.469911445980744</v>
+        <v>0.470008637715531</v>
       </c>
       <c r="O178" s="1">
         <f ca="1" t="shared" si="153"/>
-        <v>0.885124268663327</v>
+        <v>0.969492579505085</v>
       </c>
       <c r="P178" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.548269648179882</v>
+        <v>0.54840421416639</v>
       </c>
     </row>
     <row r="179" ht="16.5" spans="1:16">
@@ -14502,27 +14448,27 @@
       </c>
       <c r="K179" s="1">
         <f ca="1" t="shared" ref="K179:O179" si="154">RAND()</f>
-        <v>0.658441456849937</v>
+        <v>0.695603312027087</v>
       </c>
       <c r="L179" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.389680901799801</v>
+        <v>0.389697179131149</v>
       </c>
       <c r="M179" s="1">
         <f ca="1" t="shared" si="154"/>
-        <v>0.325143977979454</v>
+        <v>0.789193177265243</v>
       </c>
       <c r="N179" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.467351408588861</v>
+        <v>0.467570944948652</v>
       </c>
       <c r="O179" s="1">
         <f ca="1" t="shared" si="154"/>
-        <v>0.678437462831568</v>
+        <v>0.0687840037889975</v>
       </c>
       <c r="P179" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.545176662095719</v>
+        <v>0.545129163042104</v>
       </c>
     </row>
     <row r="180" ht="16.5" spans="1:16">
@@ -14562,27 +14508,27 @@
       </c>
       <c r="K180" s="1">
         <f ca="1" t="shared" ref="K180:O180" si="155">RAND()</f>
-        <v>0.178624607972294</v>
+        <v>0.510598494971675</v>
       </c>
       <c r="L180" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.387284697118512</v>
+        <v>0.387428480924946</v>
       </c>
       <c r="M180" s="1">
         <f ca="1" t="shared" si="155"/>
-        <v>0.0794512955249971</v>
+        <v>0.998055646854131</v>
       </c>
       <c r="N180" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.464414080957513</v>
+        <v>0.464955728678589</v>
       </c>
       <c r="O180" s="1">
         <f ca="1" t="shared" si="155"/>
-        <v>0.180459145135147</v>
+        <v>0.176356308208125</v>
       </c>
       <c r="P180" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.5415872130962</v>
+        <v>0.542127083805488</v>
       </c>
     </row>
     <row r="181" ht="16.5" spans="1:16">
@@ -14622,27 +14568,27 @@
       </c>
       <c r="K181" s="1">
         <f ca="1" t="shared" ref="K181:O181" si="156">RAND()</f>
-        <v>0.326169883254188</v>
+        <v>0.948566978216332</v>
       </c>
       <c r="L181" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.385186255257259</v>
+        <v>0.385452831294208</v>
       </c>
       <c r="M181" s="1">
         <f ca="1" t="shared" si="156"/>
-        <v>0.139361346775275</v>
+        <v>0.873582268374472</v>
       </c>
       <c r="N181" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.461912611141353</v>
+        <v>0.462493657964089</v>
       </c>
       <c r="O181" s="1">
         <f ca="1" t="shared" si="156"/>
-        <v>0.519240649856729</v>
+        <v>0.955844902760087</v>
       </c>
       <c r="P181" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.538801671382446</v>
+        <v>0.539569718164526</v>
       </c>
     </row>
     <row r="182" ht="16.5" spans="1:16">
@@ -14682,27 +14628,27 @@
       </c>
       <c r="K182" s="1">
         <f ca="1" t="shared" ref="K182:O182" si="157">RAND()</f>
-        <v>0.762929670967833</v>
+        <v>0.232918781694526</v>
       </c>
       <c r="L182" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.383232916803541</v>
+        <v>0.383008418636814</v>
       </c>
       <c r="M182" s="1">
         <f ca="1" t="shared" si="157"/>
-        <v>0.916475695421366</v>
+        <v>0.175675492155689</v>
       </c>
       <c r="N182" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.459864204851325</v>
+        <v>0.459325923909734</v>
       </c>
       <c r="O182" s="1">
         <f ca="1" t="shared" si="157"/>
-        <v>0.264677964938214</v>
+        <v>0.227566201465196</v>
       </c>
       <c r="P182" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.536219409145866</v>
+        <v>0.535665408672786</v>
       </c>
     </row>
     <row r="183" ht="16.5" spans="1:16">
@@ -14742,27 +14688,27 @@
       </c>
       <c r="K183" s="1">
         <f ca="1" t="shared" ref="K183:O183" si="158">RAND()</f>
-        <v>0.408746764523841</v>
+        <v>0.552242428556152</v>
       </c>
       <c r="L183" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.380967782932136</v>
+        <v>0.381027895862852</v>
       </c>
       <c r="M183" s="1">
         <f ca="1" t="shared" si="158"/>
-        <v>0.434460471784051</v>
+        <v>0.0340775440781738</v>
       </c>
       <c r="N183" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.456973962111015</v>
+        <v>0.456866347386994</v>
       </c>
       <c r="O183" s="1">
         <f ca="1" t="shared" si="158"/>
-        <v>0.12581261348209</v>
+        <v>0.000353508142419967</v>
       </c>
       <c r="P183" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.532850843115995</v>
+        <v>0.532690671302129</v>
       </c>
     </row>
     <row r="184" ht="16.5" spans="1:16">
@@ -14802,27 +14748,27 @@
       </c>
       <c r="K184" s="1">
         <f ca="1" t="shared" ref="K184:O184" si="159">RAND()</f>
-        <v>0.968021117765551</v>
+        <v>0.0619372967576652</v>
       </c>
       <c r="L184" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.379107628998533</v>
+        <v>0.378732202446864</v>
       </c>
       <c r="M184" s="1">
         <f ca="1" t="shared" si="159"/>
-        <v>0.353485577987975</v>
+        <v>0.723597186088636</v>
       </c>
       <c r="N184" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.45466392819316</v>
+        <v>0.454441853595847</v>
       </c>
       <c r="O184" s="1">
         <f ca="1" t="shared" si="159"/>
-        <v>0.97746106595968</v>
+        <v>0.487086449503956</v>
       </c>
       <c r="P184" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.530478765240846</v>
+        <v>0.530053508943326</v>
       </c>
     </row>
     <row r="185" ht="16.5" spans="1:16">
@@ -14862,27 +14808,27 @@
       </c>
       <c r="K185" s="1">
         <f ca="1" t="shared" ref="K185:O185" si="160">RAND()</f>
-        <v>0.496399729504923</v>
+        <v>0.230038040427817</v>
       </c>
       <c r="L185" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.376842786774387</v>
+        <v>0.376733622147716</v>
       </c>
       <c r="M185" s="1">
         <f ca="1" t="shared" si="160"/>
-        <v>0.902361431534141</v>
+        <v>0.475695003912859</v>
       </c>
       <c r="N185" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.452212607033213</v>
+        <v>0.451928579116533</v>
       </c>
       <c r="O185" s="1">
         <f ca="1" t="shared" si="160"/>
-        <v>0.567346178998773</v>
+        <v>0.655694372332759</v>
       </c>
       <c r="P185" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.527445125959032</v>
+        <v>0.527197306318309</v>
       </c>
     </row>
     <row r="186" ht="16.5" spans="1:16">
@@ -14922,27 +14868,27 @@
       </c>
       <c r="K186" s="1">
         <f ca="1" t="shared" ref="K186:O186" si="161">RAND()</f>
-        <v>0.695326915001766</v>
+        <v>0.842949984732338</v>
       </c>
       <c r="L186" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.37487648388446</v>
+        <v>0.374936331074891</v>
       </c>
       <c r="M186" s="1">
         <f ca="1" t="shared" si="161"/>
-        <v>0.404744823676398</v>
+        <v>0.2226715933595</v>
       </c>
       <c r="N186" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.449635164218383</v>
+        <v>0.449621197937064</v>
       </c>
       <c r="O186" s="1">
         <f ca="1" t="shared" si="161"/>
-        <v>0.372313393222831</v>
+        <v>0.321133647971888</v>
       </c>
       <c r="P186" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.524380696675095</v>
+        <v>0.524345981848404</v>
       </c>
     </row>
     <row r="187" ht="16.5" spans="1:16">
@@ -14982,27 +14928,27 @@
       </c>
       <c r="K187" s="1">
         <f ca="1" t="shared" ref="K187:O187" si="162">RAND()</f>
-        <v>0.309395102252753</v>
+        <v>0.568249408356814</v>
       </c>
       <c r="L187" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.372696008497852</v>
+        <v>0.372799821035609</v>
       </c>
       <c r="M187" s="1">
         <f ca="1" t="shared" si="162"/>
-        <v>0.0195665028766383</v>
+        <v>0.844860184310761</v>
       </c>
       <c r="N187" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.446897403956721</v>
+        <v>0.44733219739549</v>
       </c>
       <c r="O187" s="1">
         <f ca="1" t="shared" si="162"/>
-        <v>0.180791497522163</v>
+        <v>0.847255999020588</v>
       </c>
       <c r="P187" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.521163458088247</v>
+        <v>0.521865534587773</v>
       </c>
     </row>
     <row r="188" ht="16.5" spans="1:16">
@@ -15042,27 +14988,27 @@
       </c>
       <c r="K188" s="1">
         <f ca="1" t="shared" ref="K188:O188" si="163">RAND()</f>
-        <v>0.216329501570898</v>
+        <v>0.398463768073933</v>
       </c>
       <c r="L188" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.370656815224015</v>
+        <v>0.370729078258853</v>
       </c>
       <c r="M188" s="1">
         <f ca="1" t="shared" si="163"/>
-        <v>0.463629854333835</v>
+        <v>0.052434463135197</v>
       </c>
       <c r="N188" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.444637555031668</v>
+        <v>0.444546673440017</v>
       </c>
       <c r="O188" s="1">
         <f ca="1" t="shared" si="163"/>
-        <v>0.318980273867858</v>
+        <v>0.510671626051615</v>
       </c>
       <c r="P188" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.518560904113934</v>
+        <v>0.518546077397223</v>
       </c>
     </row>
     <row r="189" ht="16.5" spans="1:16">
@@ -15102,27 +15048,27 @@
       </c>
       <c r="K189" s="1">
         <f ca="1" t="shared" ref="K189:O189" si="164">RAND()</f>
-        <v>0.437151141967677</v>
+        <v>0.840578771491339</v>
       </c>
       <c r="L189" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.368763018709727</v>
+        <v>0.368921378628017</v>
       </c>
       <c r="M189" s="1">
         <f ca="1" t="shared" si="164"/>
-        <v>0.639425149261624</v>
+        <v>0.598779336289619</v>
       </c>
       <c r="N189" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.442418271499003</v>
+        <v>0.442560676467385</v>
       </c>
       <c r="O189" s="1">
         <f ca="1" t="shared" si="164"/>
-        <v>0.779601219610975</v>
+        <v>0.320886006687479</v>
       </c>
       <c r="P189" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.516128548459711</v>
+        <v>0.51609089113607</v>
       </c>
     </row>
     <row r="190" ht="16.5" spans="1:16">
@@ -15162,27 +15108,27 @@
       </c>
       <c r="K190" s="1">
         <f ca="1" t="shared" ref="K190:O190" si="165">RAND()</f>
-        <v>0.67297707056477</v>
+        <v>0.0247577161030461</v>
       </c>
       <c r="L190" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.366894266677187</v>
+        <v>0.366642509751273</v>
       </c>
       <c r="M190" s="1">
         <f ca="1" t="shared" si="165"/>
-        <v>0.914527869264051</v>
+        <v>0.808773482614377</v>
       </c>
       <c r="N190" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.440265326133335</v>
+        <v>0.439972496075152</v>
       </c>
       <c r="O190" s="1">
         <f ca="1" t="shared" si="165"/>
-        <v>0.473932485434517</v>
+        <v>0.280082036742196</v>
       </c>
       <c r="P190" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.513465266139498</v>
+        <v>0.513097147997561</v>
       </c>
     </row>
     <row r="191" ht="16.5" spans="1:16">
@@ -15222,27 +15168,27 @@
       </c>
       <c r="K191" s="1">
         <f ca="1" t="shared" ref="K191:O191" si="166">RAND()</f>
-        <v>0.794815377437095</v>
+        <v>0.519248822885472</v>
       </c>
       <c r="L191" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.365000513845966</v>
+        <v>0.364894615253573</v>
       </c>
       <c r="M191" s="1">
         <f ca="1" t="shared" si="166"/>
-        <v>0.165165875774981</v>
+        <v>0.147402375801256</v>
       </c>
       <c r="N191" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.437695565059714</v>
+        <v>0.437582840059646</v>
       </c>
       <c r="O191" s="1">
         <f ca="1" t="shared" si="166"/>
-        <v>0.872431076668781</v>
+        <v>0.0303433141087814</v>
       </c>
       <c r="P191" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.510662414095025</v>
+        <v>0.510226079762645</v>
       </c>
     </row>
     <row r="192" ht="16.5" spans="1:16">
@@ -15282,27 +15228,27 @@
       </c>
       <c r="K192" s="1">
         <f ca="1" t="shared" ref="K192:O192" si="167">RAND()</f>
-        <v>0.685880941159405</v>
+        <v>0.670019676845276</v>
       </c>
       <c r="L192" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.363038444667622</v>
+        <v>0.363032413103898</v>
       </c>
       <c r="M192" s="1">
         <f ca="1" t="shared" si="167"/>
-        <v>0.640986871148437</v>
+        <v>0.137775385436082</v>
       </c>
       <c r="N192" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.435533501675664</v>
+        <v>0.435336113856696</v>
       </c>
       <c r="O192" s="1">
         <f ca="1" t="shared" si="167"/>
-        <v>0.978111764324593</v>
+        <v>0.413094638891418</v>
       </c>
       <c r="P192" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.508156757182627</v>
+        <v>0.507744510274902</v>
       </c>
     </row>
     <row r="193" ht="16.5" spans="1:16">
@@ -15342,27 +15288,27 @@
       </c>
       <c r="K193" s="1">
         <f ca="1" t="shared" ref="K193:O193" si="168">RAND()</f>
-        <v>0.831555922162968</v>
+        <v>0.123752227658114</v>
       </c>
       <c r="L193" s="1">
         <f ca="1" t="shared" si="108"/>
-        <v>0.361193157496887</v>
+        <v>0.360926804666821</v>
       </c>
       <c r="M193" s="1">
         <f ca="1" t="shared" si="168"/>
-        <v>0.0127053084322992</v>
+        <v>0.827628579429147</v>
       </c>
       <c r="N193" s="1">
         <f ca="1" t="shared" si="109"/>
-        <v>0.433072938617534</v>
+        <v>0.433113248667588</v>
       </c>
       <c r="O193" s="1">
         <f ca="1" t="shared" si="168"/>
-        <v>0.951595217747512</v>
+        <v>0.986558822608753</v>
       </c>
       <c r="P193" s="1">
         <f ca="1" t="shared" si="110"/>
-        <v>0.505306032367668</v>
+        <v>0.505359499533426</v>
       </c>
     </row>
     <row r="194" ht="16.5" spans="1:16">
@@ -15402,27 +15348,27 @@
       </c>
       <c r="K194" s="1">
         <f ca="1" t="shared" ref="K194:O194" si="172">RAND()</f>
-        <v>0.925004774993686</v>
+        <v>0.161175524313301</v>
       </c>
       <c r="L194" s="1">
         <f ca="1" t="shared" ref="L194:L257" si="173">J194+($R$1*$R$7*K194/MAX(1,($A194*($A194-1)))+$R$1*$R$7/$A194)/100</f>
-        <v>0.35934707107877</v>
+        <v>0.359062613942021</v>
       </c>
       <c r="M194" s="1">
         <f ca="1" t="shared" si="172"/>
-        <v>0.506435559999624</v>
+        <v>0.49047394371216</v>
       </c>
       <c r="N194" s="1">
         <f ca="1" t="shared" ref="N194:N257" si="174">L194+($R$1*$R$7*M194/MAX(1,($A194*($A194-1)))+$R$1*$R$7/$A194)/100</f>
-        <v>0.431038263078122</v>
+        <v>0.430747861686603</v>
       </c>
       <c r="O194" s="1">
         <f ca="1" t="shared" si="172"/>
-        <v>0.457117996383159</v>
+        <v>0.88271022781335</v>
       </c>
       <c r="P194" s="1">
         <f ca="1" t="shared" ref="P194:P257" si="175">N194+($R$1*$R$7*O194/MAX(1,($A194*($A194-1)))+$R$1*$R$7/$A194)/100</f>
-        <v>0.502711088756827</v>
+        <v>0.502579181881546</v>
       </c>
     </row>
     <row r="195" ht="16.5" spans="1:16">
@@ -15462,27 +15408,27 @@
       </c>
       <c r="K195" s="1">
         <f ca="1" t="shared" ref="K195:O195" si="177">RAND()</f>
-        <v>0.148446841418675</v>
+        <v>0.790636659831126</v>
       </c>
       <c r="L195" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.357199096373367</v>
+        <v>0.357435788310071</v>
       </c>
       <c r="M195" s="1">
         <f ca="1" t="shared" si="177"/>
-        <v>0.47427871641634</v>
+        <v>0.615146896834187</v>
       </c>
       <c r="N195" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.428507921924527</v>
+        <v>0.428796533654239</v>
       </c>
       <c r="O195" s="1">
         <f ca="1" t="shared" si="177"/>
-        <v>0.262033823979655</v>
+        <v>0.976803606578023</v>
       </c>
       <c r="P195" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.499738520364005</v>
+        <v>0.500290574831814</v>
       </c>
     </row>
     <row r="196" ht="16.5" spans="1:16">
@@ -15522,27 +15468,27 @@
       </c>
       <c r="K196" s="1">
         <f ca="1" t="shared" ref="K196:O196" si="178">RAND()</f>
-        <v>0.357862540508253</v>
+        <v>0.118759348373794</v>
       </c>
       <c r="L196" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.355435857865689</v>
+        <v>0.355348635448257</v>
       </c>
       <c r="M196" s="1">
         <f ca="1" t="shared" si="178"/>
-        <v>0.877793963400443</v>
+        <v>0.772565083506921</v>
       </c>
       <c r="N196" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.426525298962568</v>
+        <v>0.426399690117895</v>
       </c>
       <c r="O196" s="1">
         <f ca="1" t="shared" si="178"/>
-        <v>0.866698556237939</v>
+        <v>0.817207831701587</v>
       </c>
       <c r="P196" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.49761069256754</v>
+        <v>0.49746703000892</v>
       </c>
     </row>
     <row r="197" ht="16.5" spans="1:16">
@@ -15582,27 +15528,27 @@
       </c>
       <c r="K197" s="1">
         <f ca="1" t="shared" ref="K197:O197" si="179">RAND()</f>
-        <v>0.113893993134096</v>
+        <v>0.460742228337006</v>
       </c>
       <c r="L197" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.353526209762042</v>
+        <v>0.353651445388567</v>
       </c>
       <c r="M197" s="1">
         <f ca="1" t="shared" si="179"/>
-        <v>0.985002897836012</v>
+        <v>0.704063399120042</v>
       </c>
       <c r="N197" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.424290025565028</v>
+        <v>0.424313823067998</v>
       </c>
       <c r="O197" s="1">
         <f ca="1" t="shared" si="179"/>
-        <v>0.656065881678507</v>
+        <v>0.575689443620879</v>
       </c>
       <c r="P197" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.494935072900642</v>
+        <v>0.494929849083749</v>
       </c>
     </row>
     <row r="198" ht="16.5" spans="1:16">
@@ -15642,27 +15588,27 @@
       </c>
       <c r="K198" s="1">
         <f ca="1" t="shared" ref="K198:O198" si="180">RAND()</f>
-        <v>0.486451545921989</v>
+        <v>0.136667709680586</v>
       </c>
       <c r="L198" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.351857273162067</v>
+        <v>0.351732259773998</v>
       </c>
       <c r="M198" s="1">
         <f ca="1" t="shared" si="180"/>
-        <v>0.376990497461881</v>
+        <v>0.21605179038991</v>
       </c>
       <c r="N198" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.422042771682345</v>
+        <v>0.4218602385036</v>
       </c>
       <c r="O198" s="1">
         <f ca="1" t="shared" si="180"/>
-        <v>0.335881525202511</v>
+        <v>0.980629503265317</v>
       </c>
       <c r="P198" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.492213577780133</v>
+        <v>0.492261478717654</v>
       </c>
     </row>
     <row r="199" ht="16.5" spans="1:16">
@@ -15702,27 +15648,27 @@
       </c>
       <c r="K199" s="1">
         <f ca="1" t="shared" ref="K199:O199" si="181">RAND()</f>
-        <v>0.535471761286569</v>
+        <v>0.793826044261135</v>
       </c>
       <c r="L199" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.350089460860015</v>
+        <v>0.350180864467282</v>
       </c>
       <c r="M199" s="1">
         <f ca="1" t="shared" si="181"/>
-        <v>0.780783749155199</v>
+        <v>0.564629227654984</v>
       </c>
       <c r="N199" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.420062665385943</v>
+        <v>0.420077595312322</v>
       </c>
       <c r="O199" s="1">
         <f ca="1" t="shared" si="181"/>
-        <v>0.0848611599086009</v>
+        <v>0.957836802760784</v>
       </c>
       <c r="P199" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.489789658259007</v>
+        <v>0.490113439743387</v>
       </c>
     </row>
     <row r="200" ht="16.5" spans="1:16">
@@ -15762,27 +15708,27 @@
       </c>
       <c r="K200" s="1">
         <f ca="1" t="shared" ref="K200:O200" si="182">RAND()</f>
-        <v>0.00977834301083402</v>
+        <v>0.650678993933303</v>
       </c>
       <c r="L200" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.348138037184243</v>
+        <v>0.348362503682968</v>
       </c>
       <c r="M200" s="1">
         <f ca="1" t="shared" si="182"/>
-        <v>0.559052367313283</v>
+        <v>0.4234688667757</v>
       </c>
       <c r="N200" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.417680571133508</v>
+        <v>0.417857551405456</v>
       </c>
       <c r="O200" s="1">
         <f ca="1" t="shared" si="182"/>
-        <v>0.466637691597386</v>
+        <v>0.323714373725391</v>
       </c>
       <c r="P200" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.487190738133763</v>
+        <v>0.487317661510461</v>
       </c>
     </row>
     <row r="201" ht="16.5" spans="1:16">
@@ -15822,27 +15768,27 @@
       </c>
       <c r="K201" s="1">
         <f ca="1" t="shared" ref="K201:O201" si="183">RAND()</f>
-        <v>0.958167504502119</v>
+        <v>0.0133194141512958</v>
       </c>
       <c r="L201" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.346719163607089</v>
+        <v>0.346391552962696</v>
       </c>
       <c r="M201" s="1">
         <f ca="1" t="shared" si="183"/>
-        <v>0.992838124677408</v>
+        <v>0.538879882214023</v>
       </c>
       <c r="N201" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.416063414012128</v>
+        <v>0.415578400761051</v>
       </c>
       <c r="O201" s="1">
         <f ca="1" t="shared" si="183"/>
-        <v>0.166462987921434</v>
+        <v>0.852928820661946</v>
       </c>
       <c r="P201" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.485121132334573</v>
+        <v>0.484874139899874</v>
       </c>
     </row>
     <row r="202" ht="16.5" spans="1:16">
@@ -15882,27 +15828,27 @@
       </c>
       <c r="K202" s="1">
         <f ca="1" t="shared" ref="K202:O202" si="184">RAND()</f>
-        <v>0.755355098511376</v>
+        <v>0.815372576794795</v>
       </c>
       <c r="L202" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.344916017421877</v>
+        <v>0.34493662043681</v>
       </c>
       <c r="M202" s="1">
         <f ca="1" t="shared" si="184"/>
-        <v>0.32856934526075</v>
+        <v>0.912386420939471</v>
       </c>
       <c r="N202" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.413685526301593</v>
+        <v>0.413906544133551</v>
       </c>
       <c r="O202" s="1">
         <f ca="1" t="shared" si="184"/>
-        <v>0.757595566995997</v>
+        <v>0.0175173772850536</v>
       </c>
       <c r="P202" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.482602312839517</v>
+        <v>0.482569273979484</v>
       </c>
     </row>
     <row r="203" ht="16.5" spans="1:16">
@@ -15942,27 +15888,27 @@
       </c>
       <c r="K203" s="1">
         <f ca="1" t="shared" ref="K203:O203" si="185">RAND()</f>
-        <v>0.957829793426893</v>
+        <v>0.405164890033027</v>
       </c>
       <c r="L203" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.343269249080077</v>
+        <v>0.343081406715986</v>
       </c>
       <c r="M203" s="1">
         <f ca="1" t="shared" si="185"/>
-        <v>0.24030553981626</v>
+        <v>0.125743187591134</v>
       </c>
       <c r="N203" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.411667756947903</v>
+        <v>0.411440976589114</v>
       </c>
       <c r="O203" s="1">
         <f ca="1" t="shared" si="185"/>
-        <v>0.080018970044637</v>
+        <v>0.231908709937844</v>
       </c>
       <c r="P203" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.480011785857479</v>
+        <v>0.479836630502644</v>
       </c>
     </row>
     <row r="204" ht="16.5" spans="1:16">
@@ -16002,27 +15948,27 @@
       </c>
       <c r="K204" s="1">
         <f ca="1" t="shared" ref="K204:O204" si="186">RAND()</f>
-        <v>0.925461937359143</v>
+        <v>0.901532028448794</v>
       </c>
       <c r="L204" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.341559073665696</v>
+        <v>0.34155102038708</v>
       </c>
       <c r="M204" s="1">
         <f ca="1" t="shared" si="186"/>
-        <v>0.200371358487924</v>
+        <v>0.615239303115255</v>
       </c>
       <c r="N204" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.409606801431075</v>
+        <v>0.409738366199473</v>
       </c>
       <c r="O204" s="1">
         <f ca="1" t="shared" si="186"/>
-        <v>0.146313142147704</v>
+        <v>0.78598877859817</v>
       </c>
       <c r="P204" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.477636336654253</v>
+        <v>0.477983175377267</v>
       </c>
     </row>
     <row r="205" ht="16.5" spans="1:16">
@@ -16062,27 +16008,27 @@
       </c>
       <c r="K205" s="1">
         <f ca="1" t="shared" ref="K205:O205" si="187">RAND()</f>
-        <v>0.23109764163472</v>
+        <v>0.452535840044937</v>
       </c>
       <c r="L205" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.339645251314946</v>
+        <v>0.339719042658955</v>
       </c>
       <c r="M205" s="1">
         <f ca="1" t="shared" si="187"/>
-        <v>0.714172418770044</v>
+        <v>0.542495406217127</v>
       </c>
       <c r="N205" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.407530298629228</v>
+        <v>0.40754688088473</v>
       </c>
       <c r="O205" s="1">
         <f ca="1" t="shared" si="187"/>
-        <v>0.406943654344885</v>
+        <v>0.728716419600906</v>
       </c>
       <c r="P205" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.475312966030705</v>
+        <v>0.475436774794478</v>
       </c>
     </row>
     <row r="206" ht="16.5" spans="1:16">
@@ -16122,27 +16068,27 @@
       </c>
       <c r="K206" s="1">
         <f ca="1" t="shared" ref="K206:O206" si="188">RAND()</f>
-        <v>0.880455301382541</v>
+        <v>0.369032166613684</v>
       </c>
       <c r="L206" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.338195846082236</v>
+        <v>0.338027083785253</v>
       </c>
       <c r="M206" s="1">
         <f ca="1" t="shared" si="188"/>
-        <v>0.695017309269593</v>
+        <v>0.543174539579196</v>
       </c>
       <c r="N206" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.405742264993472</v>
+        <v>0.405523396761011</v>
       </c>
       <c r="O206" s="1">
         <f ca="1" t="shared" si="188"/>
-        <v>0.69190919169059</v>
+        <v>0.73352477227554</v>
       </c>
       <c r="P206" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.473287658270501</v>
+        <v>0.473082522582565</v>
       </c>
     </row>
     <row r="207" ht="16.5" spans="1:16">
@@ -16182,27 +16128,27 @@
       </c>
       <c r="K207" s="1">
         <f ca="1" t="shared" ref="K207:O207" si="189">RAND()</f>
-        <v>0.582296104593661</v>
+        <v>0.734826759213429</v>
       </c>
       <c r="L207" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.33644886777749</v>
+        <v>0.336498712035926</v>
       </c>
       <c r="M207" s="1">
         <f ca="1" t="shared" si="189"/>
-        <v>0.824512260691799</v>
+        <v>0.827403027646679</v>
       </c>
       <c r="N207" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.403708594729835</v>
+        <v>0.403759383638614</v>
       </c>
       <c r="O207" s="1">
         <f ca="1" t="shared" si="189"/>
-        <v>0.833181796626251</v>
+        <v>0.28903018861235</v>
       </c>
       <c r="P207" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.47097115472968</v>
+        <v>0.470844124737427</v>
       </c>
     </row>
     <row r="208" ht="16.5" spans="1:16">
@@ -16242,27 +16188,27 @@
       </c>
       <c r="K208" s="1">
         <f ca="1" t="shared" ref="K208:O208" si="190">RAND()</f>
-        <v>0.170373853518952</v>
+        <v>0.489589941055744</v>
       </c>
       <c r="L208" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.334682968884634</v>
+        <v>0.334786275061831</v>
       </c>
       <c r="M208" s="1">
         <f ca="1" t="shared" si="190"/>
-        <v>0.390785899499243</v>
+        <v>0.202173320170258</v>
       </c>
       <c r="N208" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.401476103479941</v>
+        <v>0.401518369987452</v>
       </c>
       <c r="O208" s="1">
         <f ca="1" t="shared" si="190"/>
-        <v>0.984566209846254</v>
+        <v>0.327175309966295</v>
       </c>
       <c r="P208" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.468461399987982</v>
+        <v>0.468290918631454</v>
       </c>
     </row>
     <row r="209" ht="16.5" spans="1:16">
@@ -16302,27 +16248,27 @@
       </c>
       <c r="K209" s="1">
         <f ca="1" t="shared" ref="K209:O209" si="191">RAND()</f>
-        <v>0.0730724965434149</v>
+        <v>0.0490726057065309</v>
       </c>
       <c r="L209" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.33303624118479</v>
+        <v>0.333028548912086</v>
       </c>
       <c r="M209" s="1">
         <f ca="1" t="shared" si="191"/>
-        <v>0.265062276618505</v>
+        <v>0.304665367964224</v>
       </c>
       <c r="N209" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.399467350888834</v>
+        <v>0.399472351914638</v>
       </c>
       <c r="O209" s="1">
         <f ca="1" t="shared" si="191"/>
-        <v>0.917862064380957</v>
+        <v>0.221950075622899</v>
       </c>
       <c r="P209" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.466107691294085</v>
+        <v>0.465889643605543</v>
       </c>
     </row>
     <row r="210" ht="16.5" spans="1:16">
@@ -16362,27 +16308,27 @@
       </c>
       <c r="K210" s="1">
         <f ca="1" t="shared" ref="K210:O210" si="192">RAND()</f>
-        <v>0.904335694758331</v>
+        <v>0.550742348553606</v>
       </c>
       <c r="L210" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.331700401007261</v>
+        <v>0.331588154315652</v>
       </c>
       <c r="M210" s="1">
         <f ca="1" t="shared" si="192"/>
-        <v>0.0139225849200473</v>
+        <v>0.306320681218623</v>
       </c>
       <c r="N210" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.397733528806118</v>
+        <v>0.397714102636429</v>
       </c>
       <c r="O210" s="1">
         <f ca="1" t="shared" si="192"/>
-        <v>0.761762337740073</v>
+        <v>0.715305262310378</v>
       </c>
       <c r="P210" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.464004055127907</v>
+        <v>0.463969881358822</v>
       </c>
     </row>
     <row r="211" ht="16.5" spans="1:16">
@@ -16422,27 +16368,27 @@
       </c>
       <c r="K211" s="1">
         <f ca="1" t="shared" ref="K211:O211" si="193">RAND()</f>
-        <v>0.356327219011191</v>
+        <v>0.4861659972505</v>
       </c>
       <c r="L211" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.329941155516572</v>
+        <v>0.329981979739395</v>
       </c>
       <c r="M211" s="1">
         <f ca="1" t="shared" si="193"/>
-        <v>0.394312651796374</v>
+        <v>0.70600109260861</v>
       </c>
       <c r="N211" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.395779421968948</v>
+        <v>0.395918248025519</v>
       </c>
       <c r="O211" s="1">
         <f ca="1" t="shared" si="193"/>
-        <v>0.215671446211514</v>
+        <v>0.983029807052627</v>
       </c>
       <c r="P211" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.461561519621209</v>
+        <v>0.461941620350362</v>
       </c>
     </row>
     <row r="212" ht="16.5" spans="1:16">
@@ -16482,27 +16428,27 @@
       </c>
       <c r="K212" s="1">
         <f ca="1" t="shared" ref="K212:O212" si="194">RAND()</f>
-        <v>0.808387684653668</v>
+        <v>0.529891055898046</v>
       </c>
       <c r="L212" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.328511752427177</v>
+        <v>0.328425016848824</v>
       </c>
       <c r="M212" s="1">
         <f ca="1" t="shared" si="194"/>
-        <v>0.269110541159595</v>
+        <v>0.747946084083151</v>
       </c>
       <c r="N212" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.393998408384478</v>
+        <v>0.394060802359101</v>
       </c>
       <c r="O212" s="1">
         <f ca="1" t="shared" si="194"/>
-        <v>0.971579416981172</v>
+        <v>0.528321268975306</v>
       </c>
       <c r="P212" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.459703842732353</v>
+        <v>0.459628187453027</v>
       </c>
     </row>
     <row r="213" ht="16.5" spans="1:16">
@@ -16542,27 +16488,27 @@
       </c>
       <c r="K213" s="1">
         <f ca="1" t="shared" ref="K213:O213" si="195">RAND()</f>
-        <v>0.201140767232403</v>
+        <v>0.997748504857988</v>
       </c>
       <c r="L213" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.326767766757306</v>
+        <v>0.327013523414268</v>
       </c>
       <c r="M213" s="1">
         <f ca="1" t="shared" si="195"/>
-        <v>0.163174948314856</v>
+        <v>0.980699435391032</v>
       </c>
       <c r="N213" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.391912446500817</v>
+        <v>0.39241041271518</v>
       </c>
       <c r="O213" s="1">
         <f ca="1" t="shared" si="195"/>
-        <v>0.201478623073453</v>
+        <v>0.40805155955586</v>
       </c>
       <c r="P213" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.457068943080411</v>
+        <v>0.457630637867686</v>
       </c>
     </row>
     <row r="214" ht="16.5" spans="1:16">
@@ -16602,27 +16548,27 @@
       </c>
       <c r="K214" s="1">
         <f ca="1" t="shared" ref="K214:O214" si="196">RAND()</f>
-        <v>0.440074288469927</v>
+        <v>0.942523366702454</v>
       </c>
       <c r="L214" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.325300580768467</v>
+        <v>0.325454132838615</v>
       </c>
       <c r="M214" s="1">
         <f ca="1" t="shared" si="196"/>
-        <v>0.374876248522967</v>
+        <v>0.832236386165199</v>
       </c>
       <c r="N214" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.39020387805409</v>
+        <v>0.390497202688227</v>
       </c>
       <c r="O214" s="1">
         <f ca="1" t="shared" si="196"/>
-        <v>0.3347703190535</v>
+        <v>0.999051831301258</v>
       </c>
       <c r="P214" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.455094918677771</v>
+        <v>0.45559125254366</v>
       </c>
     </row>
     <row r="215" ht="16.5" spans="1:16">
@@ -16662,27 +16608,27 @@
       </c>
       <c r="K215" s="1">
         <f ca="1" t="shared" ref="K215:O215" si="197">RAND()</f>
-        <v>0.996668393578048</v>
+        <v>0.638283735920454</v>
       </c>
       <c r="L215" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.323942653324369</v>
+        <v>0.323834151980074</v>
       </c>
       <c r="M215" s="1">
         <f ca="1" t="shared" si="197"/>
-        <v>0.285216727984634</v>
+        <v>0.036854133112862</v>
       </c>
       <c r="N215" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.38851498430691</v>
+        <v>0.388331290917307</v>
       </c>
       <c r="O215" s="1">
         <f ca="1" t="shared" si="197"/>
-        <v>0.589207330394939</v>
+        <v>0.532310144595306</v>
       </c>
       <c r="P215" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.453179348774451</v>
+        <v>0.452978429700059</v>
       </c>
     </row>
     <row r="216" ht="16.5" spans="1:16">
@@ -16722,27 +16668,27 @@
       </c>
       <c r="K216" s="1">
         <f ca="1" t="shared" ref="K216:O216" si="198">RAND()</f>
-        <v>0.21740239142638</v>
+        <v>0.395666799584146</v>
       </c>
       <c r="L216" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.322195178287366</v>
+        <v>0.3222486459864</v>
       </c>
       <c r="M216" s="1">
         <f ca="1" t="shared" si="198"/>
-        <v>0.287532534994599</v>
+        <v>0.227479955011969</v>
       </c>
       <c r="N216" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.386467465811446</v>
+        <v>0.386502921652107</v>
       </c>
       <c r="O216" s="1">
         <f ca="1" t="shared" si="198"/>
-        <v>0.588685216632512</v>
+        <v>0.681742552569482</v>
       </c>
       <c r="P216" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.450830079503894</v>
+        <v>0.450893446477698</v>
       </c>
     </row>
     <row r="217" ht="16.5" spans="1:16">
@@ -16782,27 +16728,27 @@
       </c>
       <c r="K217" s="1">
         <f ca="1" t="shared" ref="K217:O217" si="199">RAND()</f>
-        <v>0.327018453524358</v>
+        <v>0.831955336256854</v>
       </c>
       <c r="L217" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.320730250961642</v>
+        <v>0.320880296805348</v>
       </c>
       <c r="M217" s="1">
         <f ca="1" t="shared" si="199"/>
-        <v>0.920904028006568</v>
+        <v>0.746241564247315</v>
       </c>
       <c r="N217" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.384892793502264</v>
+        <v>0.384990937063458</v>
       </c>
       <c r="O217" s="1">
         <f ca="1" t="shared" si="199"/>
-        <v>0.94880763208411</v>
+        <v>0.376325307923883</v>
       </c>
       <c r="P217" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.44906362781154</v>
+        <v>0.448991653886226</v>
       </c>
     </row>
     <row r="218" ht="16.5" spans="1:16">
@@ -16842,27 +16788,27 @@
       </c>
       <c r="K218" s="1">
         <f ca="1" t="shared" ref="K218:O218" si="200">RAND()</f>
-        <v>0.162816971166684</v>
+        <v>0.0100525283003752</v>
       </c>
       <c r="L218" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.319197961985879</v>
+        <v>0.319152985255388</v>
       </c>
       <c r="M218" s="1">
         <f ca="1" t="shared" si="200"/>
-        <v>0.484718277839726</v>
+        <v>0.60711696492869</v>
       </c>
       <c r="N218" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.38293514222641</v>
+        <v>0.382926201975733</v>
       </c>
       <c r="O218" s="1">
         <f ca="1" t="shared" si="200"/>
-        <v>0.124927417341762</v>
+        <v>0.0541330827364073</v>
       </c>
       <c r="P218" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.446566393258142</v>
+        <v>0.446536609821393</v>
       </c>
     </row>
     <row r="219" ht="16.5" spans="1:16">
@@ -16902,27 +16848,27 @@
       </c>
       <c r="K219" s="1">
         <f ca="1" t="shared" ref="K219:O219" si="201">RAND()</f>
-        <v>0.585758361745913</v>
+        <v>0.394253275520156</v>
       </c>
       <c r="L219" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.317851508590709</v>
+        <v>0.317795643157362</v>
       </c>
       <c r="M219" s="1">
         <f ca="1" t="shared" si="201"/>
-        <v>0.134912220214017</v>
+        <v>0.950167498446092</v>
       </c>
       <c r="N219" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.381193617173954</v>
+        <v>0.38137557617809</v>
       </c>
       <c r="O219" s="1">
         <f ca="1" t="shared" si="201"/>
-        <v>0.457358164925519</v>
+        <v>0.86604565278638</v>
       </c>
       <c r="P219" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.444629788963494</v>
+        <v>0.444930969363066</v>
       </c>
     </row>
     <row r="220" ht="16.5" spans="1:16">
@@ -16962,27 +16908,27 @@
       </c>
       <c r="K220" s="1">
         <f ca="1" t="shared" ref="K220:O220" si="202">RAND()</f>
-        <v>0.977182690454989</v>
+        <v>0.553676556441572</v>
       </c>
       <c r="L220" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.316507166040976</v>
+        <v>0.31638475004145</v>
       </c>
       <c r="M220" s="1">
         <f ca="1" t="shared" si="202"/>
-        <v>0.642831795815324</v>
+        <v>0.606784403883391</v>
       </c>
       <c r="N220" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.37970667755667</v>
+        <v>0.379573841926448</v>
       </c>
       <c r="O220" s="1">
         <f ca="1" t="shared" si="202"/>
-        <v>0.631598253541145</v>
+        <v>0.432459578846994</v>
       </c>
       <c r="P220" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.442902941975816</v>
+        <v>0.442712544582141</v>
       </c>
     </row>
     <row r="221" ht="16.5" spans="1:16">
@@ -17022,27 +16968,27 @@
       </c>
       <c r="K221" s="1">
         <f ca="1" t="shared" ref="K221:O221" si="203">RAND()</f>
-        <v>0.132533161262515</v>
+        <v>0.774461181702793</v>
       </c>
       <c r="L221" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.314820028178195</v>
+        <v>0.315003892991023</v>
       </c>
       <c r="M221" s="1">
         <f ca="1" t="shared" si="203"/>
-        <v>0.892501861510057</v>
+        <v>0.322911428882823</v>
       </c>
       <c r="N221" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.377802936556959</v>
+        <v>0.377823655915859</v>
       </c>
       <c r="O221" s="1">
         <f ca="1" t="shared" si="203"/>
-        <v>0.516200071778644</v>
+        <v>0.276045847154802</v>
       </c>
       <c r="P221" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.440678062355849</v>
+        <v>0.440629995324135</v>
       </c>
     </row>
     <row r="222" ht="16.5" spans="1:16">
@@ -17082,27 +17028,27 @@
       </c>
       <c r="K222" s="1">
         <f ca="1" t="shared" ref="K222:O222" si="204">RAND()</f>
-        <v>0.930665961662269</v>
+        <v>0.420775217644348</v>
       </c>
       <c r="L222" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.313616684291875</v>
+        <v>0.313471960057661</v>
       </c>
       <c r="M222" s="1">
         <f ca="1" t="shared" si="204"/>
-        <v>0.0204145726452158</v>
+        <v>0.419250014609792</v>
       </c>
       <c r="N222" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.376065917551901</v>
+        <v>0.376034396302039</v>
       </c>
       <c r="O222" s="1">
         <f ca="1" t="shared" si="204"/>
-        <v>0.150435569747203</v>
+        <v>0.978999868039693</v>
       </c>
       <c r="P222" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.438552055167338</v>
+        <v>0.438755708481778</v>
       </c>
     </row>
     <row r="223" ht="16.5" spans="1:16">
@@ -17142,27 +17088,27 @@
       </c>
       <c r="K223" s="1">
         <f ca="1" t="shared" ref="K223:O223" si="205">RAND()</f>
-        <v>0.227474523823689</v>
+        <v>0.761977039687723</v>
       </c>
       <c r="L223" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.311999901113464</v>
+        <v>0.31215024424499</v>
       </c>
       <c r="M223" s="1">
         <f ca="1" t="shared" si="205"/>
-        <v>0.0671686374968998</v>
+        <v>0.321632565643598</v>
       </c>
       <c r="N223" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.374180956251809</v>
+        <v>0.374402874170511</v>
       </c>
       <c r="O223" s="1">
         <f ca="1" t="shared" si="205"/>
-        <v>0.762087664642231</v>
+        <v>0.983026167722097</v>
       </c>
       <c r="P223" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.436557475956918</v>
+        <v>0.436841538740128</v>
       </c>
     </row>
     <row r="224" ht="16.5" spans="1:16">
@@ -17202,27 +17148,27 @@
       </c>
       <c r="K224" s="1">
         <f ca="1" t="shared" ref="K224:O224" si="206">RAND()</f>
-        <v>0.887182799181215</v>
+        <v>0.798856567382171</v>
       </c>
       <c r="L224" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.310779362554614</v>
+        <v>0.310754741256209</v>
       </c>
       <c r="M224" s="1">
         <f ca="1" t="shared" si="206"/>
-        <v>0.787915148545618</v>
+        <v>0.0748691655748759</v>
       </c>
       <c r="N224" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.372882405196918</v>
+        <v>0.372659019414108</v>
       </c>
       <c r="O224" s="1">
         <f ca="1" t="shared" si="206"/>
-        <v>0.527869001959657</v>
+        <v>0.626764161441064</v>
       </c>
       <c r="P224" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.434912958912166</v>
+        <v>0.434717140559583</v>
       </c>
     </row>
     <row r="225" ht="16.5" spans="1:16">
@@ -17262,27 +17208,27 @@
       </c>
       <c r="K225" s="1">
         <f ca="1" t="shared" ref="K225:O225" si="207">RAND()</f>
-        <v>0.903006056470841</v>
+        <v>0.231105604408658</v>
       </c>
       <c r="L225" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.30939024430612</v>
+        <v>0.309204621583537</v>
       </c>
       <c r="M225" s="1">
         <f ca="1" t="shared" si="207"/>
-        <v>0.185835061603102</v>
+        <v>0.669133295199382</v>
       </c>
       <c r="N225" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.371048726926438</v>
+        <v>0.370996622694079</v>
       </c>
       <c r="O225" s="1">
         <f ca="1" t="shared" si="207"/>
-        <v>0.39018155053599</v>
+        <v>0.220115986905052</v>
       </c>
       <c r="P225" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.432763663373375</v>
+        <v>0.432664575941582</v>
       </c>
     </row>
     <row r="226" ht="16.5" spans="1:16">
@@ -17322,27 +17268,27 @@
       </c>
       <c r="K226" s="1">
         <f ca="1" t="shared" ref="K226:O226" si="208">RAND()</f>
-        <v>0.0869948083891243</v>
+        <v>0.0300909758452035</v>
       </c>
       <c r="L226" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.307785724768963</v>
+        <v>0.307770143957671</v>
       </c>
       <c r="M226" s="1">
         <f ca="1" t="shared" si="208"/>
-        <v>0.266779043122451</v>
+        <v>0.469878095680439</v>
       </c>
       <c r="N226" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.369192104745056</v>
+        <v>0.369232134388632</v>
       </c>
       <c r="O226" s="1">
         <f ca="1" t="shared" si="208"/>
-        <v>0.609050200615782</v>
+        <v>0.677229337486455</v>
       </c>
       <c r="P226" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.430692201823796</v>
+        <v>0.430750899564372</v>
       </c>
     </row>
     <row r="227" ht="16.5" spans="1:16">
@@ -17382,27 +17328,27 @@
       </c>
       <c r="K227" s="1">
         <f ca="1" t="shared" ref="K227:O227" si="209">RAND()</f>
-        <v>0.38262523039036</v>
+        <v>0.700611082897131</v>
       </c>
       <c r="L227" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.306499119531551</v>
+        <v>0.306585416577069</v>
       </c>
       <c r="M227" s="1">
         <f ca="1" t="shared" si="209"/>
-        <v>0.800649155664077</v>
+        <v>0.628491276951554</v>
       </c>
       <c r="N227" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.367778351750787</v>
+        <v>0.367817927484088</v>
       </c>
       <c r="O227" s="1">
         <f ca="1" t="shared" si="209"/>
-        <v>0.0314591728261351</v>
+        <v>0.984988696948224</v>
       </c>
       <c r="P227" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.428848836246068</v>
+        <v>0.429147186953467</v>
       </c>
     </row>
     <row r="228" ht="16.5" spans="1:16">
@@ -17442,27 +17388,27 @@
       </c>
       <c r="K228" s="1">
         <f ca="1" t="shared" ref="K228:O228" si="210">RAND()</f>
-        <v>0.874501101012262</v>
+        <v>0.0446972394726923</v>
       </c>
       <c r="L228" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.30527597589166</v>
+        <v>0.305052762502528</v>
       </c>
       <c r="M228" s="1">
         <f ca="1" t="shared" si="210"/>
-        <v>0.662794037253638</v>
+        <v>0.149123709996517</v>
       </c>
       <c r="N228" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.366247215954701</v>
+        <v>0.365885827630553</v>
       </c>
       <c r="O228" s="1">
         <f ca="1" t="shared" si="210"/>
-        <v>0.100870802225939</v>
+        <v>0.35274247043393</v>
       </c>
       <c r="P228" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.42706730127439</v>
+        <v>0.426773665260509</v>
       </c>
     </row>
     <row r="229" ht="16.5" spans="1:16">
@@ -17502,27 +17448,27 @@
       </c>
       <c r="K229" s="1">
         <f ca="1" t="shared" ref="K229:O229" si="211">RAND()</f>
-        <v>0.566998476472988</v>
+        <v>0.150823361692953</v>
       </c>
       <c r="L229" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.303849304022245</v>
+        <v>0.303738336857396</v>
       </c>
       <c r="M229" s="1">
         <f ca="1" t="shared" si="211"/>
-        <v>0.0843983800884391</v>
+        <v>0.0202315499501364</v>
       </c>
       <c r="N229" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.364398123437293</v>
+        <v>0.364270047101412</v>
       </c>
       <c r="O229" s="1">
         <f ca="1" t="shared" si="211"/>
-        <v>0.105752725881492</v>
+        <v>0.486435804136223</v>
       </c>
       <c r="P229" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.424952636684398</v>
+        <v>0.424926064067504</v>
       </c>
     </row>
     <row r="230" ht="16.5" spans="1:16">
@@ -17562,27 +17508,27 @@
       </c>
       <c r="K230" s="1">
         <f ca="1" t="shared" ref="K230:O230" si="212">RAND()</f>
-        <v>0.295929366275465</v>
+        <v>0.906775729299257</v>
       </c>
       <c r="L230" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.302445488111059</v>
+        <v>0.302606939114846</v>
       </c>
       <c r="M230" s="1">
         <f ca="1" t="shared" si="212"/>
-        <v>0.337779145822879</v>
+        <v>0.618268861694931</v>
       </c>
       <c r="N230" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.362796774256243</v>
+        <v>0.363032360671028</v>
       </c>
       <c r="O230" s="1">
         <f ca="1" t="shared" si="212"/>
-        <v>0.928099645801801</v>
+        <v>0.890217579298056</v>
       </c>
       <c r="P230" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.423304086274784</v>
+        <v>0.423529660192102</v>
       </c>
     </row>
     <row r="231" ht="16.5" spans="1:16">
@@ -17622,27 +17568,27 @@
       </c>
       <c r="K231" s="1">
         <f ca="1" t="shared" ref="K231:O231" si="213">RAND()</f>
-        <v>0.711368177869276</v>
+        <v>0.833896718921485</v>
       </c>
       <c r="L231" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.301234419609922</v>
+        <v>0.301266523157796</v>
       </c>
       <c r="M231" s="1">
         <f ca="1" t="shared" si="213"/>
-        <v>0.333622253915833</v>
+        <v>0.811711233800445</v>
       </c>
       <c r="N231" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.36132183155418</v>
+        <v>0.361479198590233</v>
       </c>
       <c r="O231" s="1">
         <f ca="1" t="shared" si="213"/>
-        <v>0.968637298697342</v>
+        <v>0.109856046807824</v>
       </c>
       <c r="P231" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.421575622986153</v>
+        <v>0.421507981833938</v>
       </c>
     </row>
     <row r="232" ht="16.5" spans="1:16">
@@ -17682,27 +17628,27 @@
       </c>
       <c r="K232" s="1">
         <f ca="1" t="shared" ref="K232:O232" si="214">RAND()</f>
-        <v>0.579692408755851</v>
+        <v>0.336441326683386</v>
       </c>
       <c r="L232" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.299890829197079</v>
+        <v>0.29982764709784</v>
       </c>
       <c r="M232" s="1">
         <f ca="1" t="shared" si="214"/>
-        <v>0.0883571913540215</v>
+        <v>0.36480726420608</v>
       </c>
       <c r="N232" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.359654038857171</v>
+        <v>0.35966266197166</v>
       </c>
       <c r="O232" s="1">
         <f ca="1" t="shared" si="214"/>
-        <v>0.962511831634011</v>
+        <v>0.499484543074759</v>
       </c>
       <c r="P232" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.419644301670583</v>
+        <v>0.419532657956874</v>
       </c>
     </row>
     <row r="233" ht="16.5" spans="1:16">
@@ -17742,27 +17688,27 @@
       </c>
       <c r="K233" s="1">
         <f ca="1" t="shared" ref="K233:O233" si="215">RAND()</f>
-        <v>0.963933841786909</v>
+        <v>0.287223831984796</v>
       </c>
       <c r="L233" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.29869201162518</v>
+        <v>0.298517758040032</v>
       </c>
       <c r="M233" s="1">
         <f ca="1" t="shared" si="215"/>
-        <v>0.42176668639859</v>
+        <v>0.0865302187890895</v>
       </c>
       <c r="N233" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.358283375639815</v>
+        <v>0.358022798288936</v>
       </c>
       <c r="O233" s="1">
         <f ca="1" t="shared" si="215"/>
-        <v>0.446546061585229</v>
+        <v>0.408014148975218</v>
       </c>
       <c r="P233" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.417881120371302</v>
+        <v>0.417610621009788</v>
       </c>
     </row>
     <row r="234" ht="16.5" spans="1:16">
@@ -17802,27 +17748,27 @@
       </c>
       <c r="K234" s="1">
         <f ca="1" t="shared" ref="K234:O234" si="216">RAND()</f>
-        <v>0.680633220180851</v>
+        <v>0.147049287451102</v>
       </c>
       <c r="L234" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.297332261699691</v>
+        <v>0.297196042625552</v>
       </c>
       <c r="M234" s="1">
         <f ca="1" t="shared" si="216"/>
-        <v>0.951434929358407</v>
+        <v>0.611757093356053</v>
       </c>
       <c r="N234" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.356802622104182</v>
+        <v>0.35657968640031</v>
       </c>
       <c r="O234" s="1">
         <f ca="1" t="shared" si="216"/>
-        <v>0.622407689260199</v>
+        <v>0.738361806237173</v>
       </c>
       <c r="P234" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.41618898487819</v>
+        <v>0.41599565119471</v>
       </c>
     </row>
     <row r="235" ht="16.5" spans="1:16">
@@ -17862,27 +17808,27 @@
       </c>
       <c r="K235" s="1">
         <f ca="1" t="shared" ref="K235:O235" si="217">RAND()</f>
-        <v>0.998793534810192</v>
+        <v>0.638783766863796</v>
       </c>
       <c r="L235" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.296137033688793</v>
+        <v>0.296045912035191</v>
       </c>
       <c r="M235" s="1">
         <f ca="1" t="shared" si="217"/>
-        <v>0.901373822350978</v>
+        <v>0.124404005594118</v>
       </c>
       <c r="N235" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.355339538342849</v>
+        <v>0.3550517587627</v>
       </c>
       <c r="O235" s="1">
         <f ca="1" t="shared" si="217"/>
-        <v>0.622823398219355</v>
+        <v>0.910064793815708</v>
       </c>
       <c r="P235" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.414471539423063</v>
+        <v>0.414256463178434</v>
       </c>
     </row>
     <row r="236" ht="16.5" spans="1:16">
@@ -17922,27 +17868,27 @@
       </c>
       <c r="K236" s="1">
         <f ca="1" t="shared" ref="K236:O236" si="218">RAND()</f>
-        <v>0.580019134349191</v>
+        <v>0.568020570822666</v>
       </c>
       <c r="L236" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.294766398691653</v>
+        <v>0.294763387595515</v>
       </c>
       <c r="M236" s="1">
         <f ca="1" t="shared" si="218"/>
-        <v>0.282517984685737</v>
+        <v>0.905877821667822</v>
       </c>
       <c r="N236" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.353560702168443</v>
+        <v>0.353714126165055</v>
       </c>
       <c r="O236" s="1">
         <f ca="1" t="shared" si="218"/>
-        <v>0.985315570529572</v>
+        <v>0.546576067681081</v>
       </c>
       <c r="P236" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.41253137601593</v>
+        <v>0.412574696263873</v>
       </c>
     </row>
     <row r="237" ht="16.5" spans="1:16">
@@ -17982,27 +17928,27 @@
       </c>
       <c r="K237" s="1">
         <f ca="1" t="shared" ref="K237:O237" si="219">RAND()</f>
-        <v>0.102655547704325</v>
+        <v>0.34927649860456</v>
       </c>
       <c r="L237" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.293393736865459</v>
+        <v>0.293455103059516</v>
       </c>
       <c r="M237" s="1">
         <f ca="1" t="shared" si="219"/>
-        <v>0.135458486639787</v>
+        <v>0.346840268730516</v>
       </c>
       <c r="N237" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.351902018998809</v>
+        <v>0.352015982895587</v>
       </c>
       <c r="O237" s="1">
         <f ca="1" t="shared" si="219"/>
-        <v>0.777216740920843</v>
+        <v>0.330893034049986</v>
       </c>
       <c r="P237" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.410569988544873</v>
+        <v>0.4105728946134</v>
       </c>
     </row>
     <row r="238" ht="16.5" spans="1:16">
@@ -18042,27 +17988,27 @@
       </c>
       <c r="K238" s="1">
         <f ca="1" t="shared" ref="K238:O238" si="220">RAND()</f>
-        <v>0.729175128334473</v>
+        <v>0.867223762776907</v>
       </c>
       <c r="L238" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.292306061230977</v>
+        <v>0.292340121717913</v>
       </c>
       <c r="M238" s="1">
         <f ca="1" t="shared" si="220"/>
-        <v>0.935688872890569</v>
+        <v>0.0930168128598778</v>
       </c>
       <c r="N238" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.350764770135467</v>
+        <v>0.350590919687188</v>
       </c>
       <c r="O238" s="1">
         <f ca="1" t="shared" si="220"/>
-        <v>0.496685596736841</v>
+        <v>0.771076097774389</v>
       </c>
       <c r="P238" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.409115164565041</v>
+        <v>0.409009013982927</v>
       </c>
     </row>
     <row r="239" ht="16.5" spans="1:16">
@@ -18102,27 +18048,27 @@
       </c>
       <c r="K239" s="1">
         <f ca="1" t="shared" ref="K239:O239" si="221">RAND()</f>
-        <v>0.248791929309247</v>
+        <v>0.406220048580975</v>
       </c>
       <c r="L239" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.29095545382804</v>
+        <v>0.290993969376846</v>
       </c>
       <c r="M239" s="1">
         <f ca="1" t="shared" si="221"/>
-        <v>0.71820915410789</v>
+        <v>0.792986797184213</v>
       </c>
       <c r="N239" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.349114360439512</v>
+        <v>0.349171170699421</v>
       </c>
       <c r="O239" s="1">
         <f ca="1" t="shared" si="221"/>
-        <v>0.67768551048159</v>
+        <v>0.12206338390002</v>
       </c>
       <c r="P239" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.407263352746087</v>
+        <v>0.407184227372431</v>
       </c>
     </row>
     <row r="240" ht="16.5" spans="1:16">
@@ -18162,27 +18108,27 @@
       </c>
       <c r="K240" s="1">
         <f ca="1" t="shared" ref="K240:O240" si="222">RAND()</f>
-        <v>0.966676727547659</v>
+        <v>0.0110990249708538</v>
       </c>
       <c r="L240" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.289907881910625</v>
+        <v>0.289676051590039</v>
       </c>
       <c r="M240" s="1">
         <f ca="1" t="shared" si="222"/>
-        <v>0.642766749133564</v>
+        <v>0.348566631379906</v>
       </c>
       <c r="N240" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.347804407720865</v>
+        <v>0.347501202244254</v>
       </c>
       <c r="O240" s="1">
         <f ca="1" t="shared" si="222"/>
-        <v>0.190092001068619</v>
+        <v>0.973689905200832</v>
       </c>
       <c r="P240" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.405591111240691</v>
+        <v>0.405478012495155</v>
       </c>
     </row>
     <row r="241" ht="16.5" spans="1:16">
@@ -18222,27 +18168,27 @@
       </c>
       <c r="K241" s="1">
         <f ca="1" t="shared" ref="K241:O241" si="223">RAND()</f>
-        <v>0.489831293565029</v>
+        <v>0.0173185034155154</v>
       </c>
       <c r="L241" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.288580189537154</v>
+        <v>0.288466509681784</v>
       </c>
       <c r="M241" s="1">
         <f ca="1" t="shared" si="223"/>
-        <v>0.837970339756848</v>
+        <v>0.893298838915957</v>
       </c>
       <c r="N241" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.346281793279983</v>
+        <v>0.34618142467441</v>
       </c>
       <c r="O241" s="1">
         <f ca="1" t="shared" si="223"/>
-        <v>0.523983221160692</v>
+        <v>0.0773380429672381</v>
       </c>
       <c r="P241" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.40390785618884</v>
+        <v>0.403700031107341</v>
       </c>
     </row>
     <row r="242" ht="16.5" spans="1:16">
@@ -18282,27 +18228,27 @@
       </c>
       <c r="K242" s="1">
         <f ca="1" t="shared" ref="K242:O242" si="224">RAND()</f>
-        <v>0.259456856093024</v>
+        <v>0.840275112902519</v>
       </c>
       <c r="L242" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.287323314395126</v>
+        <v>0.287461891365112</v>
       </c>
       <c r="M242" s="1">
         <f ca="1" t="shared" si="224"/>
-        <v>0.17927129755487</v>
+        <v>0.649739077775946</v>
       </c>
       <c r="N242" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.344627497381057</v>
+        <v>0.344878322887818</v>
       </c>
       <c r="O242" s="1">
         <f ca="1" t="shared" si="224"/>
-        <v>0.500389035225198</v>
+        <v>0.319350250293615</v>
       </c>
       <c r="P242" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.402008295594856</v>
+        <v>0.402215927200647</v>
       </c>
     </row>
     <row r="243" ht="16.5" spans="1:16">
@@ -18342,27 +18288,27 @@
       </c>
       <c r="K243" s="1">
         <f ca="1" t="shared" ref="K243:O243" si="225">RAND()</f>
-        <v>0.0472467948018682</v>
+        <v>0.114140058042909</v>
       </c>
       <c r="L243" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.286081615955699</v>
+        <v>0.286097444065721</v>
       </c>
       <c r="M243" s="1">
         <f ca="1" t="shared" si="225"/>
-        <v>0.919602723607989</v>
+        <v>0.912381007661693</v>
       </c>
       <c r="N243" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.343324003349577</v>
+        <v>0.343338122675949</v>
       </c>
       <c r="O243" s="1">
         <f ca="1" t="shared" si="225"/>
-        <v>0.605030124022674</v>
+        <v>0.616999948888502</v>
       </c>
       <c r="P243" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.400491957392846</v>
+        <v>0.400508908988056</v>
       </c>
     </row>
     <row r="244" ht="16.5" spans="1:16">
@@ -18402,27 +18348,27 @@
       </c>
       <c r="K244" s="1">
         <f ca="1" t="shared" ref="K244:O244" si="226">RAND()</f>
-        <v>0.590569498771872</v>
+        <v>0.824970154923256</v>
       </c>
       <c r="L244" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.285027885914414</v>
+        <v>0.28508289270037</v>
       </c>
       <c r="M244" s="1">
         <f ca="1" t="shared" si="226"/>
-        <v>0.769528921647774</v>
+        <v>0.975285424975528</v>
       </c>
       <c r="N244" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.341998594670642</v>
+        <v>0.342101886321168</v>
       </c>
       <c r="O244" s="1">
         <f ca="1" t="shared" si="226"/>
-        <v>0.876129392031245</v>
+        <v>0.427431848599158</v>
       </c>
       <c r="P244" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.398994319351968</v>
+        <v>0.398992315180649</v>
       </c>
     </row>
     <row r="245" ht="16.5" spans="1:16">
@@ -18462,27 +18408,27 @@
       </c>
       <c r="K245" s="1">
         <f ca="1" t="shared" ref="K245:O245" si="227">RAND()</f>
-        <v>0.472378344013581</v>
+        <v>0.0838918489418703</v>
       </c>
       <c r="L245" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.283827815238942</v>
+        <v>0.283737396402809</v>
       </c>
       <c r="M245" s="1">
         <f ca="1" t="shared" si="227"/>
-        <v>0.71453556000315</v>
+        <v>0.741294480218761</v>
       </c>
       <c r="N245" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.340551497872823</v>
+        <v>0.340467307079241</v>
       </c>
       <c r="O245" s="1">
         <f ca="1" t="shared" si="227"/>
-        <v>0.70491213898906</v>
+        <v>0.548944991258956</v>
       </c>
       <c r="P245" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.397272940690033</v>
+        <v>0.397152449103113</v>
       </c>
     </row>
     <row r="246" ht="16.5" spans="1:16">
@@ -18522,27 +18468,27 @@
       </c>
       <c r="K246" s="1">
         <f ca="1" t="shared" ref="K246:O246" si="228">RAND()</f>
-        <v>0.346635132864024</v>
+        <v>0.349883012247402</v>
       </c>
       <c r="L246" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.282636058294304</v>
+        <v>0.282636808055687</v>
       </c>
       <c r="M246" s="1">
         <f ca="1" t="shared" si="228"/>
-        <v>0.748556789515627</v>
+        <v>0.00578607773989859</v>
       </c>
       <c r="N246" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.339135390574253</v>
+        <v>0.338964674363362</v>
       </c>
       <c r="O246" s="1">
         <f ca="1" t="shared" si="228"/>
-        <v>0.1119239104866</v>
+        <v>0.304344618303602</v>
       </c>
       <c r="P246" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.395487758422441</v>
+        <v>0.395361461846343</v>
       </c>
     </row>
     <row r="247" ht="16.5" spans="1:16">
@@ -18582,27 +18528,27 @@
       </c>
       <c r="K247" s="1">
         <f ca="1" t="shared" ref="K247:O247" si="229">RAND()</f>
-        <v>0.0618124711342554</v>
+        <v>0.362649427253528</v>
       </c>
       <c r="L247" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.281417836603645</v>
+        <v>0.281486719132174</v>
       </c>
       <c r="M247" s="1">
         <f ca="1" t="shared" si="229"/>
-        <v>0.296811918284043</v>
+        <v>0.605396899032993</v>
       </c>
       <c r="N247" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.337583358496333</v>
+        <v>0.337722897615775</v>
       </c>
       <c r="O247" s="1">
         <f ca="1" t="shared" si="229"/>
-        <v>0.923635746793419</v>
+        <v>0.300805235858932</v>
       </c>
       <c r="P247" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.393892404013269</v>
+        <v>0.393889333856938</v>
       </c>
     </row>
     <row r="248" ht="16.5" spans="1:16">
@@ -18642,27 +18588,27 @@
       </c>
       <c r="K248" s="1">
         <f ca="1" t="shared" ref="K248:O248" si="230">RAND()</f>
-        <v>0.64320020378938</v>
+        <v>0.240999468772418</v>
       </c>
       <c r="L248" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.28040677006702</v>
+        <v>0.280315423993105</v>
       </c>
       <c r="M248" s="1">
         <f ca="1" t="shared" si="230"/>
-        <v>0.623099646769431</v>
+        <v>0.2366800673309</v>
       </c>
       <c r="N248" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.336418731080901</v>
+        <v>0.336239623080185</v>
       </c>
       <c r="O248" s="1">
         <f ca="1" t="shared" si="230"/>
-        <v>0.808015324797403</v>
+        <v>0.394675125366877</v>
       </c>
       <c r="P248" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.392472689335768</v>
+        <v>0.392199705314642</v>
       </c>
     </row>
     <row r="249" ht="16.5" spans="1:16">
@@ -18702,27 +18648,27 @@
       </c>
       <c r="K249" s="1">
         <f ca="1" t="shared" ref="K249:O249" si="231">RAND()</f>
-        <v>0.125175286549375</v>
+        <v>0.628213935223277</v>
       </c>
       <c r="L249" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.279155142662831</v>
+        <v>0.279268469248826</v>
       </c>
       <c r="M249" s="1">
         <f ca="1" t="shared" si="231"/>
-        <v>0.698252543419158</v>
+        <v>0.615923795082514</v>
       </c>
       <c r="N249" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.334957609116716</v>
+        <v>0.335052388348541</v>
       </c>
       <c r="O249" s="1">
         <f ca="1" t="shared" si="231"/>
-        <v>0.111737047152601</v>
+        <v>0.534689000653609</v>
       </c>
       <c r="P249" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.390627942981982</v>
+        <v>0.390818006544457</v>
       </c>
     </row>
     <row r="250" ht="16.5" spans="1:16">
@@ -18762,27 +18708,27 @@
       </c>
       <c r="K250" s="1">
         <f ca="1" t="shared" ref="K250:O250" si="232">RAND()</f>
-        <v>0.776702138678233</v>
+        <v>0.0662795736837314</v>
       </c>
       <c r="L250" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.278175905064026</v>
+        <v>0.278017143705739</v>
       </c>
       <c r="M250" s="1">
         <f ca="1" t="shared" si="232"/>
-        <v>0.236917895084906</v>
+        <v>0.319573545282235</v>
       </c>
       <c r="N250" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.333650536929426</v>
+        <v>0.333510247004821</v>
       </c>
       <c r="O250" s="1">
         <f ca="1" t="shared" si="232"/>
-        <v>0.623291904127995</v>
+        <v>0.457910118915721</v>
       </c>
       <c r="P250" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.389211513550053</v>
+        <v>0.389034265006522</v>
       </c>
     </row>
     <row r="251" ht="16.5" spans="1:16">
@@ -18822,27 +18768,27 @@
       </c>
       <c r="K251" s="1">
         <f ca="1" t="shared" ref="K251:O251" si="233">RAND()</f>
-        <v>0.429583441450692</v>
+        <v>0.681364660828402</v>
       </c>
       <c r="L251" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.276981979943647</v>
+        <v>0.277037796503124</v>
       </c>
       <c r="M251" s="1">
         <f ca="1" t="shared" si="233"/>
-        <v>0.138805950875864</v>
+        <v>0.230879366202023</v>
       </c>
       <c r="N251" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.332212751383359</v>
+        <v>0.332288979398764</v>
       </c>
       <c r="O251" s="1">
         <f ca="1" t="shared" si="233"/>
-        <v>0.295315002830293</v>
+        <v>0.719722688219514</v>
       </c>
       <c r="P251" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.387478218805674</v>
+        <v>0.387648532380248</v>
       </c>
     </row>
     <row r="252" ht="16.5" spans="1:16">
@@ -18882,27 +18828,27 @@
       </c>
       <c r="K252" s="1">
         <f ca="1" t="shared" ref="K252:O252" si="234">RAND()</f>
-        <v>0.0808610840898578</v>
+        <v>0.996196925063059</v>
       </c>
       <c r="L252" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.27579786267666</v>
+        <v>0.275999163626548</v>
       </c>
       <c r="M252" s="1">
         <f ca="1" t="shared" si="234"/>
-        <v>0.701007467749195</v>
+        <v>0.63098849170334</v>
       </c>
       <c r="N252" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.330932108143671</v>
+        <v>0.33111801049803</v>
       </c>
       <c r="O252" s="1">
         <f ca="1" t="shared" si="234"/>
-        <v>0.658734879804762</v>
+        <v>0.484241114713412</v>
       </c>
       <c r="P252" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.386057057009668</v>
+        <v>0.386204584639592</v>
       </c>
     </row>
     <row r="253" ht="16.5" spans="1:16">
@@ -18942,27 +18888,27 @@
       </c>
       <c r="K253" s="1">
         <f ca="1" t="shared" ref="K253:O253" si="235">RAND()</f>
-        <v>0.538951048837686</v>
+        <v>0.955555724314511</v>
       </c>
       <c r="L253" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.274799809088629</v>
+        <v>0.274890701780111</v>
       </c>
       <c r="M253" s="1">
         <f ca="1" t="shared" si="235"/>
-        <v>0.837005989519448</v>
+        <v>0.681631711825288</v>
       </c>
       <c r="N253" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.32974432756481</v>
+        <v>0.329801321485783</v>
       </c>
       <c r="O253" s="1">
         <f ca="1" t="shared" si="235"/>
-        <v>0.397799359506685</v>
+        <v>0.484504671089492</v>
       </c>
       <c r="P253" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.3845930221699</v>
+        <v>0.384668933015237</v>
       </c>
     </row>
     <row r="254" ht="16.5" spans="1:16">
@@ -19002,27 +18948,27 @@
       </c>
       <c r="K254" s="1">
         <f ca="1" t="shared" ref="K254:O254" si="236">RAND()</f>
-        <v>0.457640725304622</v>
+        <v>0.131219047366234</v>
       </c>
       <c r="L254" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.273692130027122</v>
+        <v>0.273621475984278</v>
       </c>
       <c r="M254" s="1">
         <f ca="1" t="shared" si="236"/>
-        <v>0.017165226934728</v>
+        <v>0.550206110661693</v>
       </c>
       <c r="N254" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.328241299989662</v>
+        <v>0.328286022761478</v>
       </c>
       <c r="O254" s="1">
         <f ca="1" t="shared" si="236"/>
-        <v>0.780518567417945</v>
+        <v>0.337377734915428</v>
       </c>
       <c r="P254" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.382955697947978</v>
+        <v>0.38290450279068</v>
       </c>
     </row>
     <row r="255" ht="16.5" spans="1:16">
@@ -19062,27 +19008,27 @@
       </c>
       <c r="K255" s="1">
         <f ca="1" t="shared" ref="K255:O255" si="237">RAND()</f>
-        <v>0.109598003476726</v>
+        <v>0.25647781924315</v>
       </c>
       <c r="L255" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.272536062563381</v>
+        <v>0.272567604399265</v>
       </c>
       <c r="M255" s="1">
         <f ca="1" t="shared" si="237"/>
-        <v>0.63163723524836</v>
+        <v>0.224133534686379</v>
       </c>
       <c r="N255" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.327002412721272</v>
+        <v>0.326946444814731</v>
       </c>
       <c r="O255" s="1">
         <f ca="1" t="shared" si="237"/>
-        <v>0.0329724275320598</v>
+        <v>0.37672016838505</v>
       </c>
       <c r="P255" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.381340202075789</v>
+        <v>0.381358052581742</v>
       </c>
     </row>
     <row r="256" ht="16.5" spans="1:16">
@@ -19122,27 +19068,27 @@
       </c>
       <c r="K256" s="1">
         <f ca="1" t="shared" ref="K256:O256" si="238">RAND()</f>
-        <v>0.0134840011639965</v>
+        <v>0.501577683452229</v>
       </c>
       <c r="L256" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.27144335462739</v>
+        <v>0.271547348649554</v>
       </c>
       <c r="M256" s="1">
         <f ca="1" t="shared" si="238"/>
-        <v>0.746577131914465</v>
+        <v>0.87905392511647</v>
       </c>
       <c r="N256" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.325720068606399</v>
+        <v>0.325852288346429</v>
       </c>
       <c r="O256" s="1">
         <f ca="1" t="shared" si="238"/>
-        <v>0.605034000036586</v>
+        <v>0.260046430067808</v>
       </c>
       <c r="P256" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.379966625178894</v>
+        <v>0.380025341314392</v>
       </c>
     </row>
     <row r="257" ht="16.5" spans="1:16">
@@ -19182,27 +19128,27 @@
       </c>
       <c r="K257" s="1">
         <f ca="1" t="shared" ref="K257:O257" si="239">RAND()</f>
-        <v>0.383945369901386</v>
+        <v>0.934045366600827</v>
       </c>
       <c r="L257" s="1">
         <f ca="1" t="shared" si="173"/>
-        <v>0.27045800315724</v>
+        <v>0.270574292678601</v>
       </c>
       <c r="M257" s="1">
         <f ca="1" t="shared" si="239"/>
-        <v>0.237442618206245</v>
+        <v>0.992099211302455</v>
       </c>
       <c r="N257" s="1">
         <f ca="1" t="shared" si="174"/>
-        <v>0.324414447828368</v>
+        <v>0.324690269533932</v>
       </c>
       <c r="O257" s="1">
         <f ca="1" t="shared" si="239"/>
-        <v>0.702870230457541</v>
+        <v>0.95094558161881</v>
       </c>
       <c r="P257" s="1">
         <f ca="1" t="shared" si="175"/>
-        <v>0.378469282527822</v>
+        <v>0.378797546632987</v>
       </c>
     </row>
     <row r="258" ht="16.5" spans="1:16">
@@ -19242,27 +19188,27 @@
       </c>
       <c r="K258" s="1">
         <f ca="1" t="shared" ref="K258:O258" si="243">RAND()</f>
-        <v>0.227422485314746</v>
+        <v>0.579824210004098</v>
       </c>
       <c r="L258" s="1">
         <f ca="1" t="shared" ref="L258:L302" si="244">J258+($R$1*$R$7*K258/MAX(1,($A258*($A258-1)))+$R$1*$R$7/$A258)/100</f>
-        <v>0.269369200363226</v>
+        <v>0.269443117310586</v>
       </c>
       <c r="M258" s="1">
         <f ca="1" t="shared" si="243"/>
-        <v>0.124317119070062</v>
+        <v>0.126248450206202</v>
       </c>
       <c r="N258" s="1">
         <f ca="1" t="shared" ref="N258:N302" si="245">L258+($R$1*$R$7*M258/MAX(1,($A258*($A258-1)))+$R$1*$R$7/$A258)/100</f>
-        <v>0.323091774175287</v>
+        <v>0.323166096223111</v>
       </c>
       <c r="O258" s="1">
         <f ca="1" t="shared" si="243"/>
-        <v>0.296795272973808</v>
+        <v>0.697183036716332</v>
       </c>
       <c r="P258" s="1">
         <f ca="1" t="shared" ref="P258:P302" si="246">N258+($R$1*$R$7*O258/MAX(1,($A258*($A258-1)))+$R$1*$R$7/$A258)/100</f>
-        <v>0.376850525615691</v>
+        <v>0.377008829775924</v>
       </c>
     </row>
     <row r="259" ht="16.5" spans="1:16">
@@ -19302,27 +19248,27 @@
       </c>
       <c r="K259" s="1">
         <f ca="1" t="shared" ref="K259:O259" si="248">RAND()</f>
-        <v>0.906132443966744</v>
+        <v>0.186708383497262</v>
       </c>
       <c r="L259" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.268462953997025</v>
+        <v>0.268313223172749</v>
       </c>
       <c r="M259" s="1">
         <f ca="1" t="shared" si="248"/>
-        <v>0.51377712829553</v>
+        <v>0.921599715163699</v>
       </c>
       <c r="N259" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.322058256448847</v>
+        <v>0.321993404092564</v>
       </c>
       <c r="O259" s="1">
         <f ca="1" t="shared" si="248"/>
-        <v>0.334446215265882</v>
+        <v>0.793267063320925</v>
       </c>
       <c r="P259" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.375616235481976</v>
+        <v>0.375646875655828</v>
       </c>
     </row>
     <row r="260" ht="16.5" spans="1:16">
@@ -19362,27 +19308,27 @@
       </c>
       <c r="K260" s="1">
         <f ca="1" t="shared" ref="K260:O260" si="249">RAND()</f>
-        <v>0.185574106446951</v>
+        <v>0.149458825911911</v>
       </c>
       <c r="L260" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.267273666197794</v>
+        <v>0.267266207712992</v>
       </c>
       <c r="M260" s="1">
         <f ca="1" t="shared" si="249"/>
-        <v>0.28684922823077</v>
+        <v>0.588911182623035</v>
       </c>
       <c r="N260" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.320614759241246</v>
+        <v>0.320669682232166</v>
       </c>
       <c r="O260" s="1">
         <f ca="1" t="shared" si="249"/>
-        <v>0.0512285563715453</v>
+        <v>0.953513248616648</v>
       </c>
       <c r="P260" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.373907192183659</v>
+        <v>0.374148453936558</v>
       </c>
     </row>
     <row r="261" ht="16.5" spans="1:16">
@@ -19422,27 +19368,27 @@
       </c>
       <c r="K261" s="1">
         <f ca="1" t="shared" ref="K261:O261" si="250">RAND()</f>
-        <v>0.465681528108133</v>
+        <v>0.979871400414442</v>
       </c>
       <c r="L261" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.266299768415323</v>
+        <v>0.266405141451228</v>
       </c>
       <c r="M261" s="1">
         <f ca="1" t="shared" si="250"/>
-        <v>0.26090840717871</v>
+        <v>0.0574743976763481</v>
       </c>
       <c r="N261" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.319430159505598</v>
+        <v>0.319493842768245</v>
       </c>
       <c r="O261" s="1">
         <f ca="1" t="shared" si="250"/>
-        <v>0.709907870251985</v>
+        <v>0.271301016210044</v>
       </c>
       <c r="P261" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.372652564147853</v>
+        <v>0.372626363618018</v>
       </c>
     </row>
     <row r="262" ht="16.5" spans="1:16">
@@ -19482,27 +19428,27 @@
       </c>
       <c r="K262" s="1">
         <f ca="1" t="shared" ref="K262:O262" si="251">RAND()</f>
-        <v>0.604135539162096</v>
+        <v>0.557251395487248</v>
       </c>
       <c r="L262" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.265304112443861</v>
+        <v>0.265294578091036</v>
       </c>
       <c r="M262" s="1">
         <f ca="1" t="shared" si="251"/>
-        <v>0.577770062000631</v>
+        <v>0.179094734905581</v>
       </c>
       <c r="N262" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.318295170900325</v>
+        <v>0.318204561989381</v>
       </c>
       <c r="O262" s="1">
         <f ca="1" t="shared" si="251"/>
-        <v>0.75434616423056</v>
+        <v>0.0563182059771679</v>
       </c>
       <c r="P262" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.371322137847958</v>
+        <v>0.371089578070172</v>
       </c>
     </row>
     <row r="263" ht="16.5" spans="1:16">
@@ -19542,27 +19488,27 @@
       </c>
       <c r="K263" s="1">
         <f ca="1" t="shared" ref="K263:O263" si="252">RAND()</f>
-        <v>0.327582409846706</v>
+        <v>0.720231325021224</v>
       </c>
       <c r="L263" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.264232117183701</v>
+        <v>0.26431135667698</v>
       </c>
       <c r="M263" s="1">
         <f ca="1" t="shared" si="252"/>
-        <v>0.490509164313698</v>
+        <v>0.673166327916454</v>
       </c>
       <c r="N263" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.317002861333734</v>
+        <v>0.317118962411315</v>
       </c>
       <c r="O263" s="1">
         <f ca="1" t="shared" si="252"/>
-        <v>0.5482306712508</v>
+        <v>0.0135726578882258</v>
       </c>
       <c r="P263" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.369785254116385</v>
+        <v>0.36979345720057</v>
       </c>
     </row>
     <row r="264" ht="16.5" spans="1:16">
@@ -19602,27 +19548,27 @@
       </c>
       <c r="K264" s="1">
         <f ca="1" t="shared" ref="K264:O264" si="253">RAND()</f>
-        <v>0.895967471735387</v>
+        <v>0.807796544305334</v>
       </c>
       <c r="L264" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.263337943736539</v>
+        <v>0.263320285494897</v>
       </c>
       <c r="M264" s="1">
         <f ca="1" t="shared" si="253"/>
-        <v>0.789407499004041</v>
+        <v>0.872136391369429</v>
       </c>
       <c r="N264" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.315967523504429</v>
+        <v>0.315966433612636</v>
       </c>
       <c r="O264" s="1">
         <f ca="1" t="shared" si="253"/>
-        <v>0.673498416172891</v>
+        <v>0.0976041751720487</v>
       </c>
       <c r="P264" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.368573889831646</v>
+        <v>0.368457463967284</v>
       </c>
     </row>
     <row r="265" ht="16.5" spans="1:16">
@@ -19662,27 +19608,27 @@
       </c>
       <c r="K265" s="1">
         <f ca="1" t="shared" ref="K265:O265" si="254">RAND()</f>
-        <v>0.649357973424601</v>
+        <v>0.273338955262583</v>
       </c>
       <c r="L265" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.262287722376328</v>
+        <v>0.262212986484367</v>
       </c>
       <c r="M265" s="1">
         <f ca="1" t="shared" si="254"/>
-        <v>0.124577398179579</v>
+        <v>0.294867573859914</v>
       </c>
       <c r="N265" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.314585210106696</v>
+        <v>0.314544320343672</v>
       </c>
       <c r="O265" s="1">
         <f ca="1" t="shared" si="254"/>
-        <v>0.168422679459183</v>
+        <v>0.513882796780893</v>
       </c>
       <c r="P265" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.366891412332997</v>
+        <v>0.366919184708743</v>
       </c>
     </row>
     <row r="266" ht="16.5" spans="1:16">
@@ -19722,27 +19668,27 @@
       </c>
       <c r="K266" s="1">
         <f ca="1" t="shared" ref="K266:O266" si="255">RAND()</f>
-        <v>0.751468876038834</v>
+        <v>0.703916881418029</v>
       </c>
       <c r="L266" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.26131461221397</v>
+        <v>0.261305232317947</v>
       </c>
       <c r="M266" s="1">
         <f ca="1" t="shared" si="255"/>
-        <v>0.199273120475228</v>
+        <v>0.553228776972704</v>
       </c>
       <c r="N266" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.313429391645968</v>
+        <v>0.313489831476355</v>
       </c>
       <c r="O266" s="1">
         <f ca="1" t="shared" si="255"/>
-        <v>0.0874145561165436</v>
+        <v>0.498762177222888</v>
       </c>
       <c r="P266" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.365522106352577</v>
+        <v>0.365663686794332</v>
       </c>
     </row>
     <row r="267" ht="16.5" spans="1:16">
@@ -19782,27 +19728,27 @@
       </c>
       <c r="K267" s="1">
         <f ca="1" t="shared" ref="K267:O267" si="256">RAND()</f>
-        <v>0.158057318010812</v>
+        <v>0.00225310003717039</v>
       </c>
       <c r="L267" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.26021252930896</v>
+        <v>0.260182027135488</v>
       </c>
       <c r="M267" s="1">
         <f ca="1" t="shared" si="256"/>
-        <v>0.786025407059181</v>
+        <v>0.825357173157125</v>
       </c>
       <c r="N267" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.312246110676777</v>
+        <v>0.312223308579516</v>
       </c>
       <c r="O267" s="1">
         <f ca="1" t="shared" si="256"/>
-        <v>0.968250539613685</v>
+        <v>0.125265019970923</v>
       </c>
       <c r="P267" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.364315366705244</v>
+        <v>0.364127531267495</v>
       </c>
     </row>
     <row r="268" ht="16.5" spans="1:16">
@@ -19842,27 +19788,27 @@
       </c>
       <c r="K268" s="1">
         <f ca="1" t="shared" ref="K268:O268" si="257">RAND()</f>
-        <v>0.628411114278467</v>
+        <v>0.0136014580818713</v>
       </c>
       <c r="L268" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.259326294294402</v>
+        <v>0.259206833095682</v>
       </c>
       <c r="M268" s="1">
         <f ca="1" t="shared" si="257"/>
-        <v>0.608615482902154</v>
+        <v>0.283042971051224</v>
       </c>
       <c r="N268" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.311129945186577</v>
+        <v>0.310947223298725</v>
       </c>
       <c r="O268" s="1">
         <f ca="1" t="shared" si="257"/>
-        <v>0.265292758343528</v>
+        <v>0.136808936603895</v>
       </c>
       <c r="P268" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.362866886416973</v>
+        <v>0.362659199352977</v>
       </c>
     </row>
     <row r="269" ht="16.5" spans="1:16">
@@ -19902,27 +19848,27 @@
       </c>
       <c r="K269" s="1">
         <f ca="1" t="shared" ref="K269:O269" si="258">RAND()</f>
-        <v>0.55431192836069</v>
+        <v>0.625238979114183</v>
       </c>
       <c r="L269" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.258341012697906</v>
+        <v>0.258354691401305</v>
       </c>
       <c r="M269" s="1">
         <f ca="1" t="shared" si="258"/>
-        <v>0.906429946288873</v>
+        <v>0.158713857800223</v>
       </c>
       <c r="N269" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.310008360415202</v>
+        <v>0.309877837625768</v>
       </c>
       <c r="O269" s="1">
         <f ca="1" t="shared" si="258"/>
-        <v>0.363269744102618</v>
+        <v>0.161010280144399</v>
       </c>
       <c r="P269" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.361570956458421</v>
+        <v>0.361401426728931</v>
       </c>
     </row>
     <row r="270" ht="16.5" spans="1:16">
@@ -19962,27 +19908,27 @@
       </c>
       <c r="K270" s="1">
         <f ca="1" t="shared" ref="K270:O270" si="259">RAND()</f>
-        <v>0.342437041165618</v>
+        <v>0.201674633980013</v>
       </c>
       <c r="L270" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.257336814503247</v>
+        <v>0.257309869471632</v>
       </c>
       <c r="M270" s="1">
         <f ca="1" t="shared" si="259"/>
-        <v>0.809283828831611</v>
+        <v>0.470368601908546</v>
       </c>
       <c r="N270" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.308792844532069</v>
+        <v>0.308701023645553</v>
       </c>
       <c r="O270" s="1">
         <f ca="1" t="shared" si="259"/>
-        <v>0.423717328899845</v>
+        <v>0.0959805609922393</v>
       </c>
       <c r="P270" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.360175068622659</v>
+        <v>0.360020511685027</v>
       </c>
     </row>
     <row r="271" ht="16.5" spans="1:16">
@@ -20022,27 +19968,27 @@
       </c>
       <c r="K271" s="1">
         <f ca="1" t="shared" ref="K271:O271" si="260">RAND()</f>
-        <v>0.271863752076672</v>
+        <v>0.724437448191209</v>
       </c>
       <c r="L271" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.256367227313489</v>
+        <v>0.256453218185117</v>
       </c>
       <c r="M271" s="1">
         <f ca="1" t="shared" si="260"/>
-        <v>0.876783425742611</v>
+        <v>0.402061780766563</v>
       </c>
       <c r="N271" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.307644930897066</v>
+        <v>0.3076407226953</v>
       </c>
       <c r="O271" s="1">
         <f ca="1" t="shared" si="260"/>
-        <v>0.903199878040815</v>
+        <v>0.378457263318318</v>
       </c>
       <c r="P271" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.358927653715694</v>
+        <v>0.358823742249669</v>
       </c>
     </row>
     <row r="272" ht="16.5" spans="1:16">
@@ -20082,27 +20028,27 @@
       </c>
       <c r="K272" s="1">
         <f ca="1" t="shared" ref="K272:O272" si="261">RAND()</f>
-        <v>0.837916204123106</v>
+        <v>0.152957602560751</v>
       </c>
       <c r="L272" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.25552498624596</v>
+        <v>0.25539580176186</v>
       </c>
       <c r="M272" s="1">
         <f ca="1" t="shared" si="261"/>
-        <v>0.943489892839389</v>
+        <v>0.243451273703929</v>
       </c>
       <c r="N272" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.306625439444281</v>
+        <v>0.306364226356327</v>
       </c>
       <c r="O272" s="1">
         <f ca="1" t="shared" si="261"/>
-        <v>0.514827184232539</v>
+        <v>0.422511030977244</v>
       </c>
       <c r="P272" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.357645046047293</v>
+        <v>0.357366421958725</v>
       </c>
     </row>
     <row r="273" ht="16.5" spans="1:16">
@@ -20142,27 +20088,27 @@
       </c>
       <c r="K273" s="1">
         <f ca="1" t="shared" ref="K273:O273" si="262">RAND()</f>
-        <v>0.381396942329671</v>
+        <v>0.873404800289203</v>
       </c>
       <c r="L273" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.254496734287554</v>
+        <v>0.254588845591545</v>
       </c>
       <c r="M273" s="1">
         <f ca="1" t="shared" si="262"/>
-        <v>0.0261491412829673</v>
+        <v>0.771099476549105</v>
       </c>
       <c r="N273" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.305236923919496</v>
+        <v>0.305468501180545</v>
       </c>
       <c r="O273" s="1">
         <f ca="1" t="shared" si="262"/>
-        <v>0.731528035682284</v>
+        <v>0.213036392649651</v>
       </c>
       <c r="P273" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.356109171136942</v>
+        <v>0.356243678929332</v>
       </c>
     </row>
     <row r="274" ht="16.5" spans="1:16">
@@ -20202,27 +20148,27 @@
       </c>
       <c r="K274" s="1">
         <f ca="1" t="shared" ref="K274:O274" si="263">RAND()</f>
-        <v>0.040971714122245</v>
+        <v>0.634839084026446</v>
       </c>
       <c r="L274" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.253498241349586</v>
+        <v>0.253608607780645</v>
       </c>
       <c r="M274" s="1">
         <f ca="1" t="shared" si="263"/>
-        <v>0.800536991096402</v>
+        <v>0.206123348936466</v>
       </c>
       <c r="N274" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.304196466549935</v>
+        <v>0.30419636502875</v>
       </c>
       <c r="O274" s="1">
         <f ca="1" t="shared" si="263"/>
-        <v>0.758810193493543</v>
+        <v>0.346533158878773</v>
       </c>
       <c r="P274" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.354886937093329</v>
+        <v>0.354810216536945</v>
       </c>
     </row>
     <row r="275" ht="16.5" spans="1:16">
@@ -20262,27 +20208,27 @@
       </c>
       <c r="K275" s="1">
         <f ca="1" t="shared" ref="K275:O275" si="264">RAND()</f>
-        <v>0.485344390891961</v>
+        <v>0.371031745674756</v>
       </c>
       <c r="L275" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.252652305454323</v>
+        <v>0.25263121625211</v>
       </c>
       <c r="M275" s="1">
         <f ca="1" t="shared" si="264"/>
-        <v>0.83853945106929</v>
+        <v>0.812300399077382</v>
       </c>
       <c r="N275" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.303171968624088</v>
+        <v>0.303146038656688</v>
       </c>
       <c r="O275" s="1">
         <f ca="1" t="shared" si="264"/>
-        <v>0.582973327744192</v>
+        <v>0.821133971505535</v>
       </c>
       <c r="P275" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.353644483154754</v>
+        <v>0.353662490740947</v>
       </c>
     </row>
     <row r="276" ht="16.5" spans="1:16">
@@ -20322,27 +20268,27 @@
       </c>
       <c r="K276" s="1">
         <f ca="1" t="shared" ref="K276:O276" si="265">RAND()</f>
-        <v>0.27243406630448</v>
+        <v>0.955419339257545</v>
       </c>
       <c r="L276" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.251691567221168</v>
+        <v>0.25181665277879</v>
       </c>
       <c r="M276" s="1">
         <f ca="1" t="shared" si="265"/>
-        <v>0.0285702054601304</v>
+        <v>0.211741367210911</v>
       </c>
       <c r="N276" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.30187861790246</v>
+        <v>0.302037250401451</v>
       </c>
       <c r="O276" s="1">
         <f ca="1" t="shared" si="265"/>
-        <v>0.0508056224519162</v>
+        <v>0.799842947962585</v>
       </c>
       <c r="P276" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.352069740896353</v>
+        <v>0.352365556077388</v>
       </c>
     </row>
     <row r="277" ht="16.5" spans="1:16">
@@ -20382,27 +20328,27 @@
       </c>
       <c r="K277" s="1">
         <f ca="1" t="shared" ref="K277:O277" si="266">RAND()</f>
-        <v>0.436601261034724</v>
+        <v>0.0738700835167625</v>
       </c>
       <c r="L277" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.250806654774734</v>
+        <v>0.250740703651549</v>
       </c>
       <c r="M277" s="1">
         <f ca="1" t="shared" si="266"/>
-        <v>0.914709510155883</v>
+        <v>0.22615432455578</v>
       </c>
       <c r="N277" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.300972965594762</v>
+        <v>0.30078182261965</v>
       </c>
       <c r="O277" s="1">
         <f ca="1" t="shared" si="266"/>
-        <v>0.503996496531872</v>
+        <v>0.892580368657694</v>
       </c>
       <c r="P277" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.351064601321404</v>
+        <v>0.350944109959406</v>
       </c>
     </row>
     <row r="278" ht="16.5" spans="1:16">
@@ -20442,27 +20388,27 @@
       </c>
       <c r="K278" s="1">
         <f ca="1" t="shared" ref="K278:O278" si="267">RAND()</f>
-        <v>0.61290169245771</v>
+        <v>0.601095976030627</v>
       </c>
       <c r="L278" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.249930126659288</v>
+        <v>0.249927995663543</v>
       </c>
       <c r="M278" s="1">
         <f ca="1" t="shared" si="267"/>
-        <v>0.553417432445565</v>
+        <v>0.925748013653593</v>
       </c>
       <c r="N278" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.299849516087528</v>
+        <v>0.299914592777921</v>
       </c>
       <c r="O278" s="1">
         <f ca="1" t="shared" si="267"/>
-        <v>0.000974338003730368</v>
+        <v>0.410874798968545</v>
       </c>
       <c r="P278" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.349669186545651</v>
+        <v>0.349808252488927</v>
       </c>
     </row>
     <row r="279" ht="16.5" spans="1:16">
@@ -20502,27 +20448,27 @@
       </c>
       <c r="K279" s="1">
         <f ca="1" t="shared" ref="K279:O279" si="268">RAND()</f>
-        <v>0.731026881870514</v>
+        <v>0.281866106175279</v>
       </c>
       <c r="L279" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.249049271108353</v>
+        <v>0.248968778436293</v>
       </c>
       <c r="M279" s="1">
         <f ca="1" t="shared" si="268"/>
-        <v>0.901717120634947</v>
+        <v>0.834526050494494</v>
       </c>
       <c r="N279" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.298851152731405</v>
+        <v>0.298758618961666</v>
       </c>
       <c r="O279" s="1">
         <f ca="1" t="shared" si="268"/>
-        <v>0.584975390256075</v>
+        <v>0.0681341090793837</v>
       </c>
       <c r="P279" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.348596272077761</v>
+        <v>0.348411116828135</v>
       </c>
     </row>
     <row r="280" ht="16.5" spans="1:16">
@@ -20562,27 +20508,27 @@
       </c>
       <c r="K280" s="1">
         <f ca="1" t="shared" ref="K280:O280" si="269">RAND()</f>
-        <v>0.29256396041552</v>
+        <v>0.255077571542631</v>
       </c>
       <c r="L280" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.248075570287689</v>
+        <v>0.248068900627721</v>
       </c>
       <c r="M280" s="1">
         <f ca="1" t="shared" si="269"/>
-        <v>0.910137289144374</v>
+        <v>0.683836192990601</v>
       </c>
       <c r="N280" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.297699869488202</v>
+        <v>0.297652935844235</v>
       </c>
       <c r="O280" s="1">
         <f ca="1" t="shared" si="269"/>
-        <v>0.73029161639156</v>
+        <v>0.157027201321951</v>
       </c>
       <c r="P280" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.347292170154846</v>
+        <v>0.347143240057358</v>
       </c>
     </row>
     <row r="281" ht="16.5" spans="1:16">
@@ -20622,27 +20568,27 @@
       </c>
       <c r="K281" s="1">
         <f ca="1" t="shared" ref="K281:O281" si="270">RAND()</f>
-        <v>0.119096424425344</v>
+        <v>0.324581831249612</v>
       </c>
       <c r="L281" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.247156215190182</v>
+        <v>0.247192514455597</v>
       </c>
       <c r="M281" s="1">
         <f ca="1" t="shared" si="270"/>
-        <v>0.921550441526944</v>
+        <v>0.313226652802177</v>
       </c>
       <c r="N281" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.296604722564646</v>
+        <v>0.296533560638503</v>
       </c>
       <c r="O281" s="1">
         <f ca="1" t="shared" si="270"/>
-        <v>0.33365230419035</v>
+        <v>0.637976256850621</v>
       </c>
       <c r="P281" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.345949376965539</v>
+        <v>0.345931974262985</v>
       </c>
     </row>
     <row r="282" ht="16.5" spans="1:16">
@@ -20682,27 +20628,27 @@
       </c>
       <c r="K282" s="1">
         <f ca="1" t="shared" ref="K282:O282" si="271">RAND()</f>
-        <v>0.57498312989811</v>
+        <v>0.00669503979911301</v>
       </c>
       <c r="L282" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.246354026019224</v>
+        <v>0.246254351697372</v>
       </c>
       <c r="M282" s="1">
         <f ca="1" t="shared" si="271"/>
-        <v>0.62096786584455</v>
+        <v>0.250545160410667</v>
       </c>
       <c r="N282" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.295573260342415</v>
+        <v>0.295408616100189</v>
       </c>
       <c r="O282" s="1">
         <f ca="1" t="shared" si="271"/>
-        <v>0.682974503091195</v>
+        <v>0.233457537913387</v>
       </c>
       <c r="P282" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.344803370257802</v>
+        <v>0.344559883436529</v>
       </c>
     </row>
     <row r="283" ht="16.5" spans="1:16">
@@ -20742,27 +20688,27 @@
       </c>
       <c r="K283" s="1">
         <f ca="1" t="shared" ref="K283:O283" si="272">RAND()</f>
-        <v>0.520902522661498</v>
+        <v>0.131018982396711</v>
       </c>
       <c r="L283" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.245468166563347</v>
+        <v>0.245400268316765</v>
       </c>
       <c r="M283" s="1">
         <f ca="1" t="shared" si="272"/>
-        <v>0.626767313662981</v>
+        <v>0.803409090107178</v>
       </c>
       <c r="N283" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.294513488348871</v>
+        <v>0.294476352280363</v>
       </c>
       <c r="O283" s="1">
         <f ca="1" t="shared" si="272"/>
-        <v>0.731549505416095</v>
+        <v>0.154225520183936</v>
       </c>
       <c r="P283" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.343577057960627</v>
+        <v>0.343439380878563</v>
       </c>
     </row>
     <row r="284" ht="16.5" spans="1:16">
@@ -20802,27 +20748,27 @@
       </c>
       <c r="K284" s="1">
         <f ca="1" t="shared" ref="K284:O284" si="273">RAND()</f>
-        <v>0.102232271103228</v>
+        <v>0.148346701731559</v>
       </c>
       <c r="L284" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.244525609670216</v>
+        <v>0.244533583746634</v>
       </c>
       <c r="M284" s="1">
         <f ca="1" t="shared" si="273"/>
-        <v>0.083221301067663</v>
+        <v>0.293127881602556</v>
       </c>
       <c r="N284" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.293303251125178</v>
+        <v>0.293347522106734</v>
       </c>
       <c r="O284" s="1">
         <f ca="1" t="shared" si="273"/>
-        <v>0.547183900831294</v>
+        <v>0.825203332746357</v>
       </c>
       <c r="P284" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.342161120681746</v>
+        <v>0.342253466597022</v>
       </c>
     </row>
     <row r="285" ht="16.5" spans="1:16">
@@ -20862,27 +20808,27 @@
       </c>
       <c r="K285" s="1">
         <f ca="1" t="shared" ref="K285:O285" si="274">RAND()</f>
-        <v>0.947876326106188</v>
+        <v>0.215619600608802</v>
       </c>
       <c r="L285" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.243807304699401</v>
+        <v>0.24368157505709</v>
       </c>
       <c r="M285" s="1">
         <f ca="1" t="shared" si="274"/>
-        <v>0.759149800946889</v>
+        <v>0.690037756105079</v>
       </c>
       <c r="N285" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.292529201221238</v>
+        <v>0.292391604931104</v>
       </c>
       <c r="O285" s="1">
         <f ca="1" t="shared" si="274"/>
-        <v>0.592968655326533</v>
+        <v>0.522011342353181</v>
       </c>
       <c r="P285" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.34122256417654</v>
+        <v>0.341072784403115</v>
       </c>
     </row>
     <row r="286" ht="16.5" spans="1:16">
@@ -20922,27 +20868,27 @@
       </c>
       <c r="K286" s="1">
         <f ca="1" t="shared" ref="K286:O286" si="275">RAND()</f>
-        <v>0.899159591515541</v>
+        <v>0.115826958285</v>
       </c>
       <c r="L286" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.242940553525611</v>
+        <v>0.242806997924689</v>
       </c>
       <c r="M286" s="1">
         <f ca="1" t="shared" si="275"/>
-        <v>0.675524712987982</v>
+        <v>0.668265279724054</v>
       </c>
       <c r="N286" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.291476780867336</v>
+        <v>0.291341987557259</v>
       </c>
       <c r="O286" s="1">
         <f ca="1" t="shared" si="275"/>
-        <v>0.143609826029023</v>
+        <v>0.883258547993693</v>
       </c>
       <c r="P286" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.339922318495199</v>
+        <v>0.339913632824893</v>
       </c>
     </row>
     <row r="287" ht="16.5" spans="1:16">
@@ -20982,27 +20928,27 @@
       </c>
       <c r="K287" s="1">
         <f ca="1" t="shared" ref="K287:O287" si="276">RAND()</f>
-        <v>0.902490424968299</v>
+        <v>0.355339242426965</v>
       </c>
       <c r="L287" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.242088754359767</v>
+        <v>0.241996119268133</v>
       </c>
       <c r="M287" s="1">
         <f ca="1" t="shared" si="276"/>
-        <v>0.388922680451405</v>
+        <v>0.833415740296595</v>
       </c>
       <c r="N287" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.290406348924731</v>
+        <v>0.290388968454933</v>
       </c>
       <c r="O287" s="1">
         <f ca="1" t="shared" si="276"/>
-        <v>0.348884496010512</v>
+        <v>0.148861875506305</v>
       </c>
       <c r="P287" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.338717164849709</v>
+        <v>0.338665919674194</v>
       </c>
     </row>
     <row r="288" ht="16.5" spans="1:16">
@@ -21042,27 +20988,27 @@
       </c>
       <c r="K288" s="1">
         <f ca="1" t="shared" ref="K288:O288" si="277">RAND()</f>
-        <v>0.507376000718963</v>
+        <v>0.0369848152124432</v>
       </c>
       <c r="L288" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.24117591906642</v>
+        <v>0.241096834756097</v>
       </c>
       <c r="M288" s="1">
         <f ca="1" t="shared" si="277"/>
-        <v>0.0228054895071415</v>
+        <v>0.344063135456747</v>
       </c>
       <c r="N288" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.289263376922652</v>
+        <v>0.289238303912176</v>
       </c>
       <c r="O288" s="1">
         <f ca="1" t="shared" si="277"/>
-        <v>0.610745000003788</v>
+        <v>0.728447712052512</v>
       </c>
       <c r="P288" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.337449681849433</v>
+        <v>0.337444397555439</v>
       </c>
     </row>
     <row r="289" ht="16.5" spans="1:16">
@@ -21102,27 +21048,27 @@
       </c>
       <c r="K289" s="1">
         <f ca="1" t="shared" ref="K289:O289" si="278">RAND()</f>
-        <v>0.101313968830363</v>
+        <v>0.113384172759864</v>
       </c>
       <c r="L289" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.240268076519186</v>
+        <v>0.240270091724546</v>
       </c>
       <c r="M289" s="1">
         <f ca="1" t="shared" si="278"/>
-        <v>0.245261117598455</v>
+        <v>0.880043749376383</v>
       </c>
       <c r="N289" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.288225691252815</v>
+        <v>0.288333687878986</v>
       </c>
       <c r="O289" s="1">
         <f ca="1" t="shared" si="278"/>
-        <v>0.460600656572139</v>
+        <v>0.846679022171208</v>
       </c>
       <c r="P289" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.336219258435605</v>
+        <v>0.336391713557775</v>
       </c>
     </row>
     <row r="290" ht="16.5" spans="1:16">
@@ -21162,27 +21108,27 @@
       </c>
       <c r="K290" s="1">
         <f ca="1" t="shared" ref="K290:O290" si="279">RAND()</f>
-        <v>0.674309823506708</v>
+        <v>0.514862710242783</v>
       </c>
       <c r="L290" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.239529333376158</v>
+        <v>0.23950289678731</v>
       </c>
       <c r="M290" s="1">
         <f ca="1" t="shared" si="279"/>
-        <v>0.210351069115188</v>
+        <v>0.102721104680058</v>
       </c>
       <c r="N290" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.287315074974988</v>
+        <v>0.287270793164239</v>
       </c>
       <c r="O290" s="1">
         <f ca="1" t="shared" si="279"/>
-        <v>0.557237170727347</v>
+        <v>0.290422500275015</v>
       </c>
       <c r="P290" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.335158330849604</v>
+        <v>0.335069810735652</v>
       </c>
     </row>
     <row r="291" ht="16.5" spans="1:16">
@@ -21222,27 +21168,27 @@
       </c>
       <c r="K291" s="1">
         <f ca="1" t="shared" ref="K291:O291" si="280">RAND()</f>
-        <v>0.616678834174357</v>
+        <v>0.354284570615667</v>
       </c>
       <c r="L291" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.238691208303443</v>
+        <v>0.238648002948031</v>
       </c>
       <c r="M291" s="1">
         <f ca="1" t="shared" si="280"/>
-        <v>0.304659325899786</v>
+        <v>0.734121064919921</v>
       </c>
       <c r="N291" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.286327579842608</v>
+        <v>0.286355088864937</v>
       </c>
       <c r="O291" s="1">
         <f ca="1" t="shared" si="280"/>
-        <v>0.703653850053531</v>
+        <v>0.214683944931897</v>
       </c>
       <c r="P291" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.334029649084116</v>
+        <v>0.333976645223845</v>
       </c>
     </row>
     <row r="292" ht="16.5" spans="1:16">
@@ -21282,27 +21228,27 @@
       </c>
       <c r="K292" s="1">
         <f ca="1" t="shared" ref="K292:O292" si="281">RAND()</f>
-        <v>0.872478006834678</v>
+        <v>0.160528698566278</v>
       </c>
       <c r="L292" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.237910181259561</v>
+        <v>0.237793758692265</v>
       </c>
       <c r="M292" s="1">
         <f ca="1" t="shared" si="281"/>
-        <v>0.0415353462636474</v>
+        <v>0.80489890927692</v>
       </c>
       <c r="N292" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.285339653801076</v>
+        <v>0.285348061393391</v>
       </c>
       <c r="O292" s="1">
         <f ca="1" t="shared" si="281"/>
-        <v>0.452015032143917</v>
+        <v>0.328351074296222</v>
       </c>
       <c r="P292" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.33283625064245</v>
+        <v>0.332824435902518</v>
       </c>
     </row>
     <row r="293" ht="16.5" spans="1:16">
@@ -21342,27 +21288,27 @@
       </c>
       <c r="K293" s="1">
         <f ca="1" t="shared" ref="K293:O293" si="282">RAND()</f>
-        <v>0.247287765952493</v>
+        <v>0.547987766470502</v>
       </c>
       <c r="L293" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.236991156747754</v>
+        <v>0.237039992364277</v>
       </c>
       <c r="M293" s="1">
         <f ca="1" t="shared" si="282"/>
-        <v>0.55271383568699</v>
+        <v>0.266077869825067</v>
       </c>
       <c r="N293" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.284341195006622</v>
+        <v>0.284343479096419</v>
       </c>
       <c r="O293" s="1">
         <f ca="1" t="shared" si="282"/>
-        <v>0.450676780060684</v>
+        <v>0.812364042035201</v>
       </c>
       <c r="P293" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.33167466179056</v>
+        <v>0.331735686220885</v>
       </c>
     </row>
     <row r="294" ht="16.5" spans="1:16">
@@ -21402,27 +21348,27 @@
       </c>
       <c r="K294" s="1">
         <f ca="1" t="shared" ref="K294:O294" si="283">RAND()</f>
-        <v>0.0639529007934063</v>
+        <v>0.26586720563199</v>
       </c>
       <c r="L294" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.236150387465881</v>
+        <v>0.236182955811839</v>
       </c>
       <c r="M294" s="1">
         <f ca="1" t="shared" si="283"/>
-        <v>0.476316584256378</v>
+        <v>0.815490624196551</v>
       </c>
       <c r="N294" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.283326192422433</v>
+        <v>0.28341346881635</v>
       </c>
       <c r="O294" s="1">
         <f ca="1" t="shared" si="283"/>
-        <v>0.850211434386809</v>
+        <v>0.472020083193115</v>
       </c>
       <c r="P294" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.330562305819443</v>
+        <v>0.33058858075646</v>
       </c>
     </row>
     <row r="295" ht="16.5" spans="1:16">
@@ -21462,27 +21408,27 @@
       </c>
       <c r="K295" s="1">
         <f ca="1" t="shared" ref="K295:O295" si="284">RAND()</f>
-        <v>0.768754143545002</v>
+        <v>0.0371694147615194</v>
       </c>
       <c r="L295" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.235457834821352</v>
+        <v>0.235340634509574</v>
       </c>
       <c r="M295" s="1">
         <f ca="1" t="shared" si="284"/>
-        <v>0.444671329407721</v>
+        <v>0.101039176324911</v>
       </c>
       <c r="N295" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.28246784694489</v>
+        <v>0.282295596556349</v>
       </c>
       <c r="O295" s="1">
         <f ca="1" t="shared" si="284"/>
-        <v>0.88086947858379</v>
+        <v>0.777841718815488</v>
       </c>
       <c r="P295" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.329547738273214</v>
+        <v>0.329358982775843</v>
       </c>
     </row>
     <row r="296" ht="16.5" spans="1:16">
@@ -21522,27 +21468,27 @@
       </c>
       <c r="K296" s="1">
         <f ca="1" t="shared" ref="K296:O296" si="285">RAND()</f>
-        <v>0.986052117811162</v>
+        <v>0.494826128609588</v>
       </c>
       <c r="L296" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.234691658240814</v>
+        <v>0.234613497066468</v>
       </c>
       <c r="M296" s="1">
         <f ca="1" t="shared" si="285"/>
-        <v>0.813992315729781</v>
+        <v>0.908305128513663</v>
       </c>
       <c r="N296" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.281600837232594</v>
+        <v>0.281537682593662</v>
       </c>
       <c r="O296" s="1">
         <f ca="1" t="shared" si="285"/>
-        <v>0.508183406603546</v>
+        <v>0.986417083349488</v>
       </c>
       <c r="P296" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.328461357594765</v>
+        <v>0.328474296864966</v>
       </c>
     </row>
     <row r="297" ht="16.5" spans="1:16">
@@ -21582,27 +21528,27 @@
       </c>
       <c r="K297" s="1">
         <f ca="1" t="shared" ref="K297:O297" si="286">RAND()</f>
-        <v>0.30837050549043</v>
+        <v>0.635733787835218</v>
       </c>
       <c r="L297" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.233789000377643</v>
+        <v>0.233840736672837</v>
       </c>
       <c r="M297" s="1">
         <f ca="1" t="shared" si="286"/>
-        <v>0.0811677236468173</v>
+        <v>0.636413659222153</v>
       </c>
       <c r="N297" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.28042344969723</v>
+        <v>0.280562936724341</v>
       </c>
       <c r="O297" s="1">
         <f ca="1" t="shared" si="286"/>
-        <v>0.175905790968311</v>
+        <v>0.257343626281154</v>
       </c>
       <c r="P297" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.327072871363691</v>
+        <v>0.327225228777051</v>
       </c>
     </row>
     <row r="298" ht="16.5" spans="1:16">
@@ -21642,27 +21588,27 @@
       </c>
       <c r="K298" s="1">
         <f ca="1" t="shared" ref="K298:O298" si="287">RAND()</f>
-        <v>0.122881613006602</v>
+        <v>0.445046541970323</v>
       </c>
       <c r="L298" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.232970422311624</v>
+        <v>0.23302099420192</v>
       </c>
       <c r="M298" s="1">
         <f ca="1" t="shared" si="287"/>
-        <v>0.0543169869672746</v>
+        <v>0.922994569939904</v>
       </c>
       <c r="N298" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.279443595193826</v>
+        <v>0.27963052788407</v>
       </c>
       <c r="O298" s="1">
         <f ca="1" t="shared" si="287"/>
-        <v>0.0817364160296576</v>
+        <v>0.38749861825986</v>
       </c>
       <c r="P298" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.325921072245209</v>
+        <v>0.326156002005145</v>
       </c>
     </row>
     <row r="299" ht="16.5" spans="1:16">
@@ -21702,27 +21648,27 @@
       </c>
       <c r="K299" s="1">
         <f ca="1" t="shared" ref="K299:O299" si="288">RAND()</f>
-        <v>0.1254691945432</v>
+        <v>0.968748277413763</v>
       </c>
       <c r="L299" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.232186874052434</v>
+        <v>0.232318359503631</v>
       </c>
       <c r="M299" s="1">
         <f ca="1" t="shared" si="288"/>
-        <v>0.796723322545497</v>
+        <v>0.945951843953851</v>
       </c>
       <c r="N299" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.278619825285696</v>
+        <v>0.278774578691556</v>
       </c>
       <c r="O299" s="1">
         <f ca="1" t="shared" si="288"/>
-        <v>0.658374495460761</v>
+        <v>0.674483032224723</v>
       </c>
       <c r="P299" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.325031204943995</v>
+        <v>0.325188470019203</v>
       </c>
     </row>
     <row r="300" ht="16.5" spans="1:16">
@@ -21762,27 +21708,27 @@
       </c>
       <c r="K300" s="1">
         <f ca="1" t="shared" ref="K300:O300" si="289">RAND()</f>
-        <v>0.465894444967333</v>
+        <v>0.158475940804812</v>
       </c>
       <c r="L300" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.231460902598601</v>
+        <v>0.23141329002697</v>
       </c>
       <c r="M300" s="1">
         <f ca="1" t="shared" si="289"/>
-        <v>0.163307907146814</v>
+        <v>0.912667844325896</v>
       </c>
       <c r="N300" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.277640041665273</v>
+        <v>0.277708488970335</v>
       </c>
       <c r="O300" s="1">
         <f ca="1" t="shared" si="289"/>
-        <v>0.131615317690285</v>
+        <v>0.133224520217329</v>
       </c>
       <c r="P300" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.323814272225576</v>
+        <v>0.323882968761799</v>
       </c>
     </row>
     <row r="301" ht="16.5" spans="1:16">
@@ -21822,27 +21768,27 @@
       </c>
       <c r="K301" s="1">
         <f ca="1" t="shared" ref="K301:O301" si="290">RAND()</f>
-        <v>0.939317605438426</v>
+        <v>0.64399195597121</v>
       </c>
       <c r="L301" s="1">
         <f ca="1" t="shared" si="244"/>
-        <v>0.230759895016222</v>
+        <v>0.230714460300919</v>
       </c>
       <c r="M301" s="1">
         <f ca="1" t="shared" si="290"/>
-        <v>0.0388863923563261</v>
+        <v>0.143380315344217</v>
       </c>
       <c r="N301" s="1">
         <f ca="1" t="shared" si="245"/>
-        <v>0.276765877538123</v>
+        <v>0.276736518810972</v>
       </c>
       <c r="O301" s="1">
         <f ca="1" t="shared" si="290"/>
-        <v>0.0229421042311757</v>
+        <v>0.168036122984884</v>
       </c>
       <c r="P301" s="1">
         <f ca="1" t="shared" si="246"/>
-        <v>0.32276940709262</v>
+        <v>0.3227623705222</v>
       </c>
     </row>
     <row r="302" spans="1:16">

--- a/table/resources/sample/PointsAwardRanking.xlsx
+++ b/table/resources/sample/PointsAwardRanking.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="PointsAwardRanking" sheetId="1" r:id="rId1"/>
@@ -176,7 +176,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="92">
   <si>
     <t>序列ID</t>
   </si>
@@ -244,187 +244,181 @@
     <t>2</t>
   </si>
   <si>
-    <t>1990000_3640000</t>
+    <t>1990000_54596000</t>
   </si>
   <si>
     <t>jfdj_box_1.png</t>
   </si>
   <si>
-    <t>1990000_3309000</t>
+    <t>1990000_49632000</t>
   </si>
   <si>
     <t>jfdj_box_2.png</t>
   </si>
   <si>
-    <t>1990000_2978000</t>
+    <t>1990000_44669000</t>
   </si>
   <si>
     <t>jfdj_box_3.png</t>
   </si>
   <si>
-    <t>1990000_2647000</t>
+    <t>1990000_39706000</t>
   </si>
   <si>
-    <t>1990000_2316000</t>
+    <t>1990000_34743000</t>
+  </si>
+  <si>
+    <t>1990000_29779000</t>
+  </si>
+  <si>
+    <t>1990000_24816000</t>
+  </si>
+  <si>
+    <t>1990000_19853000</t>
+  </si>
+  <si>
+    <t>1990000_14890000</t>
+  </si>
+  <si>
+    <t>1990000_9926000</t>
+  </si>
+  <si>
+    <t>11_15</t>
+  </si>
+  <si>
+    <t>1990000_4963000</t>
+  </si>
+  <si>
+    <t>16_20</t>
+  </si>
+  <si>
+    <t>1990000_2978000</t>
+  </si>
+  <si>
+    <t>21_25</t>
   </si>
   <si>
     <t>1990000_1985000</t>
   </si>
   <si>
-    <t>1990000_1654000</t>
-  </si>
-  <si>
-    <t>1990000_1324000</t>
+    <t>26_30</t>
   </si>
   <si>
     <t>1990000_993000</t>
   </si>
   <si>
-    <t>1990000_662000</t>
+    <t>31_40</t>
   </si>
   <si>
-    <t>11_15</t>
+    <t>1990000_496000</t>
   </si>
   <si>
-    <t>1990000_331000</t>
+    <t>41_50</t>
   </si>
   <si>
-    <t>16_20</t>
+    <t>1990000_298000</t>
+  </si>
+  <si>
+    <t>51_100</t>
   </si>
   <si>
     <t>1990000_199000</t>
   </si>
   <si>
-    <t>21_25</t>
+    <t>101_150</t>
   </si>
   <si>
-    <t>1990000_132000</t>
+    <t>1990000_99000</t>
   </si>
   <si>
-    <t>26_30</t>
+    <t>151_200</t>
   </si>
   <si>
-    <t>1990000_66000</t>
+    <t>1990000_50000</t>
   </si>
   <si>
-    <t>31_40</t>
+    <t>201_250</t>
   </si>
   <si>
-    <t>1990000_33000</t>
+    <t>1990000_30000</t>
   </si>
   <si>
-    <t>41_50</t>
+    <t>251_300</t>
   </si>
   <si>
     <t>1990000_20000</t>
   </si>
   <si>
-    <t>51_100</t>
+    <t>1990000_121500000</t>
   </si>
   <si>
-    <t>1990000_13000</t>
+    <t>1990000_104630000</t>
   </si>
   <si>
-    <t>101_150</t>
+    <t>1990000_81000000</t>
   </si>
   <si>
-    <t>1990000_7000</t>
+    <t>1990000_60750000</t>
   </si>
   <si>
-    <t>151_200</t>
+    <t>1990000_54000000</t>
   </si>
   <si>
-    <t>1990000_3000</t>
+    <t>1990000_45900000</t>
   </si>
   <si>
-    <t>201_250</t>
+    <t>1990000_37130000</t>
   </si>
   <si>
-    <t>1990000_2000</t>
+    <t>1990000_30380000</t>
   </si>
   <si>
-    <t>251_300</t>
+    <t>1990000_21600000</t>
   </si>
   <si>
-    <t>1990000_1000</t>
+    <t>1990000_16200000</t>
   </si>
   <si>
-    <t>1990000_4410000</t>
+    <t>1990000_8100000</t>
   </si>
   <si>
-    <t>1990000_4100000</t>
+    <t>1990000_4730000</t>
   </si>
   <si>
-    <t>1990000_3780000</t>
+    <t>1990000_3110000</t>
   </si>
   <si>
-    <t>1990000_3150000</t>
+    <t>1990000_1760000</t>
   </si>
   <si>
-    <t>1990000_2610000</t>
+    <t>1990000_810000</t>
   </si>
   <si>
-    <t>1990000_2210000</t>
+    <t>1990000_540000</t>
   </si>
   <si>
-    <t>1990000_1890000</t>
+    <t>1990000_148500000</t>
   </si>
   <si>
-    <t>1990000_1580000</t>
+    <t>1990000_94500000</t>
   </si>
   <si>
-    <t>1990000_950000</t>
+    <t>1990000_74300000</t>
   </si>
   <si>
-    <t>1990000_630000</t>
+    <t>1990000_60800000</t>
   </si>
   <si>
-    <t>1990000_500000</t>
+    <t>1990000_40500000</t>
   </si>
   <si>
-    <t>1990000_250000</t>
+    <t>1990000_33800000</t>
   </si>
   <si>
-    <t>1990000_190000</t>
+    <t>1990000_27000000</t>
   </si>
   <si>
-    <t>1990000_90000</t>
-  </si>
-  <si>
-    <t>1990000_60000</t>
-  </si>
-  <si>
-    <t>1990000_40000</t>
-  </si>
-  <si>
-    <t>1990000_4600000</t>
-  </si>
-  <si>
-    <t>1990000_4300000</t>
-  </si>
-  <si>
-    <t>1990000_3900000</t>
-  </si>
-  <si>
-    <t>1990000_3400000</t>
-  </si>
-  <si>
-    <t>1990000_2800000</t>
-  </si>
-  <si>
-    <t>1990000_2400000</t>
-  </si>
-  <si>
-    <t>1990000_2000000</t>
-  </si>
-  <si>
-    <t>1990000_1800000</t>
-  </si>
-  <si>
-    <t>1990000_1100000</t>
-  </si>
-  <si>
-    <t>1990000_700000</t>
+    <t>1990000_20300000</t>
   </si>
   <si>
     <t>2036/08/01 00:00:00</t>
@@ -653,12 +647,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2546,7 +2540,7 @@
         <v>21</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="F43" s="2"/>
       <c r="G43" s="2" t="s">
@@ -2569,7 +2563,7 @@
         <v>21</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F44" s="2"/>
       <c r="G44" s="2" t="s">
@@ -2592,7 +2586,7 @@
         <v>21</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
@@ -2613,7 +2607,7 @@
         <v>21</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
@@ -2634,7 +2628,7 @@
         <v>21</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
@@ -2655,7 +2649,7 @@
         <v>21</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
@@ -2676,7 +2670,7 @@
         <v>21</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
@@ -2698,7 +2692,7 @@
         <v>21</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
@@ -2720,7 +2714,7 @@
         <v>21</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F51" s="2"/>
       <c r="G51" s="2"/>
@@ -2749,7 +2743,7 @@
         <v>23</v>
       </c>
       <c r="H52" s="25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I52" s="20"/>
       <c r="J52" s="20"/>
@@ -2775,7 +2769,7 @@
         <v>25</v>
       </c>
       <c r="H53" s="25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I53" s="20"/>
       <c r="J53" s="20"/>
@@ -2801,7 +2795,7 @@
         <v>27</v>
       </c>
       <c r="H54" s="25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I54" s="20"/>
       <c r="J54" s="20"/>
@@ -2825,7 +2819,7 @@
       <c r="F55" s="23"/>
       <c r="G55" s="23"/>
       <c r="H55" s="25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I55" s="20"/>
       <c r="J55" s="20"/>
@@ -2849,7 +2843,7 @@
       <c r="F56" s="23"/>
       <c r="G56" s="23"/>
       <c r="H56" s="25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I56" s="20"/>
       <c r="J56" s="21"/>
@@ -2874,7 +2868,7 @@
       <c r="F57" s="23"/>
       <c r="G57" s="23"/>
       <c r="H57" s="25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I57" s="20"/>
       <c r="J57" s="21"/>
@@ -2899,7 +2893,7 @@
       <c r="F58" s="23"/>
       <c r="G58" s="23"/>
       <c r="H58" s="25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I58" s="20"/>
       <c r="J58" s="21"/>
@@ -2924,7 +2918,7 @@
       <c r="F59" s="23"/>
       <c r="G59" s="23"/>
       <c r="H59" s="25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I59" s="20"/>
       <c r="J59" s="21"/>
@@ -2949,7 +2943,7 @@
       <c r="F60" s="23"/>
       <c r="G60" s="23"/>
       <c r="H60" s="25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I60" s="20"/>
       <c r="L60" s="3"/>
@@ -2973,7 +2967,7 @@
       <c r="F61" s="23"/>
       <c r="G61" s="23"/>
       <c r="H61" s="25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I61" s="20"/>
       <c r="L61" s="3"/>
@@ -2997,7 +2991,7 @@
       <c r="F62" s="23"/>
       <c r="G62" s="23"/>
       <c r="H62" s="25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I62" s="20"/>
       <c r="J62" s="10"/>
@@ -3022,7 +3016,7 @@
       <c r="F63" s="23"/>
       <c r="G63" s="23"/>
       <c r="H63" s="25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I63" s="20"/>
       <c r="J63" s="21"/>
@@ -3047,7 +3041,7 @@
       <c r="F64" s="23"/>
       <c r="G64" s="23"/>
       <c r="H64" s="25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I64" s="20"/>
       <c r="J64" s="21"/>
@@ -3072,7 +3066,7 @@
       <c r="F65" s="23"/>
       <c r="G65" s="23"/>
       <c r="H65" s="25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I65" s="20"/>
       <c r="J65" s="21"/>
@@ -3097,7 +3091,7 @@
       <c r="F66" s="23"/>
       <c r="G66" s="23"/>
       <c r="H66" s="25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I66" s="20"/>
       <c r="J66" s="21"/>
@@ -3122,7 +3116,7 @@
       <c r="F67" s="23"/>
       <c r="G67" s="23"/>
       <c r="H67" s="25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I67" s="20"/>
       <c r="J67" s="21"/>
@@ -3147,7 +3141,7 @@
       <c r="F68" s="23"/>
       <c r="G68" s="23"/>
       <c r="H68" s="25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I68" s="20"/>
       <c r="J68" s="21"/>
@@ -3172,7 +3166,7 @@
       <c r="F69" s="23"/>
       <c r="G69" s="23"/>
       <c r="H69" s="25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I69" s="20"/>
       <c r="J69" s="21"/>
@@ -3197,7 +3191,7 @@
       <c r="F70" s="23"/>
       <c r="G70" s="23"/>
       <c r="H70" s="25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I70" s="20"/>
       <c r="J70" s="21"/>
@@ -3222,7 +3216,7 @@
       <c r="F71" s="23"/>
       <c r="G71" s="23"/>
       <c r="H71" s="25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I71" s="20"/>
       <c r="J71" s="21"/>
@@ -3247,7 +3241,7 @@
       <c r="F72" s="23"/>
       <c r="G72" s="23"/>
       <c r="H72" s="25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I72" s="20"/>
       <c r="J72" s="21"/>
@@ -3274,7 +3268,7 @@
         <v>23</v>
       </c>
       <c r="H73" s="25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I73" s="20"/>
       <c r="J73" s="21"/>
@@ -3301,7 +3295,7 @@
         <v>25</v>
       </c>
       <c r="H74" s="25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I74" s="20"/>
       <c r="J74" s="21"/>
@@ -3328,7 +3322,7 @@
         <v>27</v>
       </c>
       <c r="H75" s="25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I75" s="20"/>
       <c r="J75" s="21"/>
@@ -3353,7 +3347,7 @@
       <c r="F76" s="23"/>
       <c r="G76" s="23"/>
       <c r="H76" s="25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I76" s="20"/>
       <c r="J76" s="21"/>
@@ -3378,7 +3372,7 @@
       <c r="F77" s="23"/>
       <c r="G77" s="23"/>
       <c r="H77" s="25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I77" s="20"/>
       <c r="J77" s="21"/>
@@ -3403,7 +3397,7 @@
       <c r="F78" s="23"/>
       <c r="G78" s="23"/>
       <c r="H78" s="25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I78" s="20"/>
       <c r="J78" s="21"/>
@@ -3428,7 +3422,7 @@
       <c r="F79" s="23"/>
       <c r="G79" s="23"/>
       <c r="H79" s="25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I79" s="20"/>
       <c r="J79" s="21"/>
@@ -3453,7 +3447,7 @@
       <c r="F80" s="23"/>
       <c r="G80" s="23"/>
       <c r="H80" s="25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I80" s="20"/>
       <c r="J80" s="21"/>
@@ -3477,7 +3471,7 @@
       <c r="F81" s="23"/>
       <c r="G81" s="23"/>
       <c r="H81" s="25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I81" s="20"/>
       <c r="J81" s="21"/>
@@ -3501,7 +3495,7 @@
       <c r="F82" s="23"/>
       <c r="G82" s="23"/>
       <c r="H82" s="25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I82" s="20"/>
       <c r="J82" s="20"/>
@@ -3525,7 +3519,7 @@
       <c r="F83" s="23"/>
       <c r="G83" s="23"/>
       <c r="H83" s="25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I83" s="20"/>
     </row>
@@ -3548,7 +3542,7 @@
       <c r="F84" s="23"/>
       <c r="G84" s="23"/>
       <c r="H84" s="25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I84" s="20"/>
     </row>
@@ -3571,7 +3565,7 @@
       <c r="F85" s="23"/>
       <c r="G85" s="23"/>
       <c r="H85" s="25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I85" s="20"/>
     </row>
@@ -3594,7 +3588,7 @@
       <c r="F86" s="23"/>
       <c r="G86" s="23"/>
       <c r="H86" s="25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I86" s="20"/>
     </row>
@@ -3617,7 +3611,7 @@
       <c r="F87" s="23"/>
       <c r="G87" s="23"/>
       <c r="H87" s="25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I87" s="20"/>
     </row>
@@ -3640,7 +3634,7 @@
       <c r="F88" s="23"/>
       <c r="G88" s="23"/>
       <c r="H88" s="25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I88" s="20"/>
     </row>
@@ -3665,7 +3659,7 @@
         <v>23</v>
       </c>
       <c r="H89" s="25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I89" s="20"/>
     </row>
@@ -3683,14 +3677,14 @@
         <v>21</v>
       </c>
       <c r="E90" s="27" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="F90" s="23"/>
       <c r="G90" s="23" t="s">
         <v>25</v>
       </c>
       <c r="H90" s="25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="91" spans="1:10">
@@ -3707,14 +3701,14 @@
         <v>21</v>
       </c>
       <c r="E91" s="27" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F91" s="23"/>
       <c r="G91" s="23" t="s">
         <v>27</v>
       </c>
       <c r="H91" s="25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="92" spans="1:10">
@@ -3731,12 +3725,12 @@
         <v>21</v>
       </c>
       <c r="E92" s="27" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F92" s="23"/>
       <c r="G92" s="23"/>
       <c r="H92" s="25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="93" spans="1:10">
@@ -3753,12 +3747,12 @@
         <v>21</v>
       </c>
       <c r="E93" s="27" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F93" s="23"/>
       <c r="G93" s="23"/>
       <c r="H93" s="25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="94" spans="1:10">
@@ -3775,12 +3769,12 @@
         <v>21</v>
       </c>
       <c r="E94" s="27" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="F94" s="23"/>
       <c r="G94" s="23"/>
       <c r="H94" s="25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="95" spans="1:10">
@@ -3797,12 +3791,12 @@
         <v>21</v>
       </c>
       <c r="E95" s="27" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F95" s="23"/>
       <c r="G95" s="23"/>
       <c r="H95" s="25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="96" spans="1:10">
@@ -3819,12 +3813,12 @@
         <v>21</v>
       </c>
       <c r="E96" s="27" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F96" s="23"/>
       <c r="G96" s="23"/>
       <c r="H96" s="25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="97" spans="1:8">
@@ -3841,12 +3835,12 @@
         <v>21</v>
       </c>
       <c r="E97" s="27" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F97" s="23"/>
       <c r="G97" s="23"/>
       <c r="H97" s="25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="98" spans="1:8">
@@ -3863,12 +3857,12 @@
         <v>21</v>
       </c>
       <c r="E98" s="27" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F98" s="23"/>
       <c r="G98" s="23"/>
       <c r="H98" s="25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -3906,34 +3900,34 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>85</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r